--- a/trimika_data.xlsx
+++ b/trimika_data.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" count="465" uniqueCount="132">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" count="325" uniqueCount="111">
   <si>
     <t>REFERENCE NO</t>
   </si>
@@ -66,130 +66,112 @@
     <t>EXPORT DATE</t>
   </si>
   <si>
-    <t>2565503</t>
-  </si>
-  <si>
-    <t>EF4-0231089-2</t>
+    <t>2565344</t>
+  </si>
+  <si>
+    <t>EF4-0230923-3</t>
   </si>
   <si>
     <t>Vessel, Container</t>
   </si>
   <si>
+    <t>V1626429891</t>
+  </si>
+  <si>
+    <t>9903.03.01</t>
+  </si>
+  <si>
     <t/>
   </si>
   <si>
-    <t>9903.03.01</t>
+    <t>001</t>
+  </si>
+  <si>
+    <t>3505.10.0092</t>
+  </si>
+  <si>
+    <t>ROYAL INGREDIENTS GROUP BV</t>
+  </si>
+  <si>
+    <t>ROYINGRE</t>
+  </si>
+  <si>
+    <t>074601-00962</t>
+  </si>
+  <si>
+    <t>SANGUAN WONGSE STARCH CO., LTD.</t>
+  </si>
+  <si>
+    <t>2565387</t>
+  </si>
+  <si>
+    <t>EF4-0230978-7</t>
+  </si>
+  <si>
+    <t>9903.88.15</t>
+  </si>
+  <si>
+    <t>ARTICLE OF CHINA,US NTE 20(R)</t>
+  </si>
+  <si>
+    <t>9903.03.06,9903.82.09,8302.42.3015</t>
+  </si>
+  <si>
+    <t>GRASS AMERICA INC</t>
+  </si>
+  <si>
+    <t>GRAAME</t>
+  </si>
+  <si>
+    <t>51-066023000</t>
+  </si>
+  <si>
+    <t>HANSTAR HARDWARE INTERNATIONAL LIMI</t>
+  </si>
+  <si>
+    <t>2565619</t>
+  </si>
+  <si>
+    <t>EF4-0231334-2</t>
   </si>
   <si>
     <t>SECTION 122 - 10% DUTY</t>
   </si>
   <si>
-    <t>001</t>
-  </si>
-  <si>
-    <t>8416.90.0000</t>
-  </si>
-  <si>
-    <t>LHOIST NORTH AMERICA, INC.</t>
-  </si>
-  <si>
-    <t>LHONOR01</t>
-  </si>
-  <si>
-    <t>52-212063700</t>
-  </si>
-  <si>
-    <t>PARGET MAKINA IMALAT INSAAT MUHENDI</t>
-  </si>
-  <si>
-    <t>PARGET MAKINA IMALAT INSAAT MUHENDISLIK SANAYI VE TICARET LTD.</t>
-  </si>
-  <si>
-    <t>2565458</t>
-  </si>
-  <si>
-    <t>EF4-0231111-4</t>
-  </si>
-  <si>
-    <t>V0710316899</t>
+    <t>7019.90.1100</t>
+  </si>
+  <si>
+    <t>TRENCHLESS PRODUCTS</t>
+  </si>
+  <si>
+    <t>TREPRO01</t>
+  </si>
+  <si>
+    <t>83-157973900</t>
+  </si>
+  <si>
+    <t>LATERAL REPAIRS UAB</t>
+  </si>
+  <si>
+    <t>2565655</t>
+  </si>
+  <si>
+    <t>EF4-0231436-5</t>
   </si>
   <si>
     <t>1109.00.9020</t>
   </si>
   <si>
-    <t>ROYAL INGREDIENTS GROUP BV</t>
-  </si>
-  <si>
-    <t>ROYINGRE</t>
-  </si>
-  <si>
-    <t>074601-00962</t>
-  </si>
-  <si>
-    <t>ROQUETTE FRERES</t>
-  </si>
-  <si>
-    <t>2565514</t>
-  </si>
-  <si>
-    <t>EF4-0231256-7</t>
-  </si>
-  <si>
-    <t>9903.88.15</t>
-  </si>
-  <si>
-    <t>ARTICLE OF CHINA,US NTE 20(R)</t>
-  </si>
-  <si>
-    <t>9903.03.06,9903.82.09,8302.42.3015</t>
-  </si>
-  <si>
-    <t>GRASS AMERICA INC</t>
-  </si>
-  <si>
-    <t>GRAAME</t>
-  </si>
-  <si>
-    <t>51-066023000</t>
-  </si>
-  <si>
-    <t>SACA PRECISION LTD</t>
-  </si>
-  <si>
-    <t>2565429</t>
-  </si>
-  <si>
-    <t>EF4-0231257-5</t>
-  </si>
-  <si>
-    <t>2930.90.9231</t>
-  </si>
-  <si>
-    <t>CASTLE CHEMICALS LTD</t>
-  </si>
-  <si>
-    <t>CASCHE01</t>
-  </si>
-  <si>
-    <t>151704-07138</t>
-  </si>
-  <si>
-    <t>HUBEI JINGHAN NEW MATERIALS CO. LTD</t>
-  </si>
-  <si>
-    <t>2565430</t>
-  </si>
-  <si>
-    <t>EF4-0231258-3</t>
-  </si>
-  <si>
-    <t>2565491</t>
-  </si>
-  <si>
-    <t>EF4-0231532-1</t>
-  </si>
-  <si>
-    <t>V0413857173</t>
+    <t>JACKERING MUHLEN UND NAHRMITTELWERK</t>
+  </si>
+  <si>
+    <t>JACKERING MUHLEN UND NAHRMITTELWERKE GMBH</t>
+  </si>
+  <si>
+    <t>2565611</t>
+  </si>
+  <si>
+    <t>EF4-0231497-7</t>
   </si>
   <si>
     <t>9903.03.06</t>
@@ -198,7 +180,61 @@
     <t>S122 EXCL,IRN/STL/ALUM,DERIV</t>
   </si>
   <si>
-    <t>9903.82.02,7223.00.1031</t>
+    <t>9903.82.02,7216.33.0090</t>
+  </si>
+  <si>
+    <t>MAHA USA LLC</t>
+  </si>
+  <si>
+    <t>MAHUSA</t>
+  </si>
+  <si>
+    <t>52-213556300</t>
+  </si>
+  <si>
+    <t>THYSSENKRUPP SCHULTE GMBH</t>
+  </si>
+  <si>
+    <t>9903.91.01</t>
+  </si>
+  <si>
+    <t>ARTS, PRDS OF CN SUB(B)US NT31</t>
+  </si>
+  <si>
+    <t>002</t>
+  </si>
+  <si>
+    <t>9903.03.06,9903.82.02,7228.30.6000</t>
+  </si>
+  <si>
+    <t>003</t>
+  </si>
+  <si>
+    <t>004</t>
+  </si>
+  <si>
+    <t>9903.82.02,7215.50.0016</t>
+  </si>
+  <si>
+    <t>2565713</t>
+  </si>
+  <si>
+    <t>EF4-0231526-3</t>
+  </si>
+  <si>
+    <t>LANTMANNEN BIOREFINERIES AB</t>
+  </si>
+  <si>
+    <t>2565610</t>
+  </si>
+  <si>
+    <t>EF4-0231533-9</t>
+  </si>
+  <si>
+    <t>V0710314381</t>
+  </si>
+  <si>
+    <t>9903.82.02,7223.00.1061</t>
   </si>
   <si>
     <t>VENUS WIRE INDUSTRIES PRIVATE LTD</t>
@@ -216,94 +252,28 @@
     <t>VENUS WIRE INDUSTRIES PRIVATE LIMITED</t>
   </si>
   <si>
-    <t>2565572</t>
-  </si>
-  <si>
-    <t>EF4-0231542-0</t>
-  </si>
-  <si>
-    <t>9903.76.04,9403.60.8093</t>
-  </si>
-  <si>
-    <t>VISUAL CREATIONS, INC.</t>
-  </si>
-  <si>
-    <t>VISCRE</t>
-  </si>
-  <si>
-    <t>20-461602300</t>
-  </si>
-  <si>
-    <t>VIET MOI INDUSTRIAL COMPANY LIMITED</t>
-  </si>
-  <si>
-    <t>002</t>
-  </si>
-  <si>
-    <t>9403.99.9045</t>
-  </si>
-  <si>
-    <t>003</t>
-  </si>
-  <si>
-    <t>9403.99.3080</t>
-  </si>
-  <si>
-    <t>2565652</t>
-  </si>
-  <si>
-    <t>EF4-0231567-7</t>
-  </si>
-  <si>
-    <t>9903.82.01,8483.40.9000</t>
-  </si>
-  <si>
-    <t>IMS GEAR VIRGINIA LLC</t>
-  </si>
-  <si>
-    <t>IMSGEA</t>
-  </si>
-  <si>
-    <t>20-800570900</t>
-  </si>
-  <si>
-    <t>ADOLF FOHL GMBH CO KG</t>
-  </si>
-  <si>
-    <t>2565632</t>
-  </si>
-  <si>
-    <t>EF4-0231578-4</t>
-  </si>
-  <si>
-    <t>9903.82.09,8302.42.3015</t>
-  </si>
-  <si>
-    <t>GRASS GMBH</t>
-  </si>
-  <si>
-    <t>9903.82.09,8302.42.3065</t>
-  </si>
-  <si>
-    <t>9903.82.09,8302.10.6060</t>
-  </si>
-  <si>
-    <t>2565633</t>
-  </si>
-  <si>
-    <t>EF4-0231579-2</t>
-  </si>
-  <si>
-    <t>2565644</t>
-  </si>
-  <si>
-    <t>EF4-0231580-0</t>
-  </si>
-  <si>
-    <t>9903.82.09,8302.49.6035</t>
-  </si>
-  <si>
-    <t>004</t>
+    <t>2565822</t>
+  </si>
+  <si>
+    <t>EF4-0231589-1</t>
+  </si>
+  <si>
+    <t>3923.90.0080</t>
+  </si>
+  <si>
+    <t>DOBLA USA MFG LLC</t>
+  </si>
+  <si>
+    <t>DOBUSA</t>
+  </si>
+  <si>
+    <t>41-218954800</t>
+  </si>
+  <si>
+    <t>DOBLA LOGISTICS BVBA</t>
+  </si>
+  <si>
+    <t>1806.90.9090</t>
   </si>
   <si>
     <t>005</t>
@@ -312,103 +282,70 @@
     <t>006</t>
   </si>
   <si>
-    <t>3926.30.5000</t>
-  </si>
-  <si>
-    <t>007</t>
-  </si>
-  <si>
-    <t>9903.82.02,7318.22.0000</t>
-  </si>
-  <si>
-    <t>2565868</t>
-  </si>
-  <si>
-    <t>EF4-0231736-8</t>
-  </si>
-  <si>
-    <t>9903.82.01,8424.90.9080</t>
-  </si>
-  <si>
-    <t>EISENMANN OF SOUTH CAROLINA INC</t>
-  </si>
-  <si>
-    <t>EISINC03</t>
-  </si>
-  <si>
-    <t>86-240963300</t>
-  </si>
-  <si>
-    <t>EISENMANN GMBH</t>
-  </si>
-  <si>
-    <t>2615677</t>
-  </si>
-  <si>
-    <t>EF4-0231742-6</t>
-  </si>
-  <si>
-    <t>Vessel, Non-container</t>
-  </si>
-  <si>
-    <t>9903.82.02,7318.15.8085</t>
-  </si>
-  <si>
-    <t>AUMUND CORPORATION</t>
-  </si>
-  <si>
-    <t>AUMCOR</t>
-  </si>
-  <si>
-    <t>58-138896800</t>
-  </si>
-  <si>
-    <t>AUMUND FOERDERTECHNIK GMBH</t>
-  </si>
-  <si>
-    <t>9903.82.09,8483.10.5000</t>
-  </si>
-  <si>
-    <t>2565815</t>
-  </si>
-  <si>
-    <t>EF4-0231753-3</t>
-  </si>
-  <si>
-    <t>9903.74.11,9903.94.53,8708.29.5160</t>
-  </si>
-  <si>
-    <t>BORGERS USA CORP</t>
-  </si>
-  <si>
-    <t>BORUSA</t>
-  </si>
-  <si>
-    <t>65-117296500</t>
-  </si>
-  <si>
-    <t>AUTONEUM PILSEN S.R.O</t>
-  </si>
-  <si>
-    <t>2565530</t>
-  </si>
-  <si>
-    <t>EF4-0231948-9</t>
-  </si>
-  <si>
-    <t>9903.03.01,3926.90.9910</t>
-  </si>
-  <si>
-    <t>DTPM, INC</t>
-  </si>
-  <si>
-    <t>DTPM01</t>
-  </si>
-  <si>
-    <t>63-110506700</t>
-  </si>
-  <si>
-    <t>TAIZHOU HONOD MEDICAL COLTD</t>
+    <t>DOBLA BELGIUM PRODUCTIONS NV/SA</t>
+  </si>
+  <si>
+    <t>2565720</t>
+  </si>
+  <si>
+    <t>EF4-0231593-3</t>
+  </si>
+  <si>
+    <t>1108.13.0010</t>
+  </si>
+  <si>
+    <t>AKV LANGHOLT AMBA</t>
+  </si>
+  <si>
+    <t>2565743</t>
+  </si>
+  <si>
+    <t>EF4-0231635-2</t>
+  </si>
+  <si>
+    <t>V8N61685510</t>
+  </si>
+  <si>
+    <t>1108.12.0010</t>
+  </si>
+  <si>
+    <t>TAT NISASTA INS SAN TIC AS</t>
+  </si>
+  <si>
+    <t>2565748</t>
+  </si>
+  <si>
+    <t>EF4-0231636-0</t>
+  </si>
+  <si>
+    <t>2565745</t>
+  </si>
+  <si>
+    <t>EF4-0231754-1</t>
+  </si>
+  <si>
+    <t>V1626447273</t>
+  </si>
+  <si>
+    <t>1108.11.0010</t>
+  </si>
+  <si>
+    <t>KROENER-STARKE BIO GMBH</t>
+  </si>
+  <si>
+    <t>2565747</t>
+  </si>
+  <si>
+    <t>EF4-0231756-6</t>
+  </si>
+  <si>
+    <t>2565817</t>
+  </si>
+  <si>
+    <t>EF4-0231758-2</t>
+  </si>
+  <si>
+    <t>1109.00.9010</t>
   </si>
 </sst>
 </file>
@@ -1353,7 +1290,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:Q33"/>
+  <dimension ref="A1:Q23"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="23.7109375" customWidth="true"/>
@@ -1466,45 +1403,45 @@
         <v>27</v>
       </c>
       <c r="M2" s="45">
-        <v>46164</v>
+        <v>46159</v>
       </c>
       <c r="N2" s="46">
-        <v>46163</v>
+        <v>46166</v>
       </c>
       <c r="O2" s="47" t="s">
         <v>28</v>
       </c>
       <c r="P2" s="48" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="Q2" s="49">
-        <v>46124</v>
+        <v>46115</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="33" t="s">
+        <v>29</v>
+      </c>
+      <c r="B3" s="34" t="s">
         <v>30</v>
-      </c>
-      <c r="B3" s="34" t="s">
-        <v>31</v>
       </c>
       <c r="C3" s="35" t="s">
         <v>19</v>
       </c>
       <c r="D3" s="36" t="s">
+        <v>20</v>
+      </c>
+      <c r="E3" s="37" t="s">
+        <v>31</v>
+      </c>
+      <c r="F3" s="38" t="s">
         <v>32</v>
-      </c>
-      <c r="E3" s="37" t="s">
-        <v>21</v>
-      </c>
-      <c r="F3" s="38" t="s">
-        <v>22</v>
       </c>
       <c r="G3" s="39" t="s">
         <v>23</v>
       </c>
       <c r="H3" s="40" t="s">
-        <v>21</v>
+        <v>31</v>
       </c>
       <c r="I3" s="41" t="s">
         <v>33</v>
@@ -1519,10 +1456,10 @@
         <v>36</v>
       </c>
       <c r="M3" s="45">
-        <v>46159</v>
+        <v>46164</v>
       </c>
       <c r="N3" s="46">
-        <v>46163</v>
+        <v>46166</v>
       </c>
       <c r="O3" s="47" t="s">
         <v>37</v>
@@ -1531,7 +1468,7 @@
         <v>37</v>
       </c>
       <c r="Q3" s="49">
-        <v>46123</v>
+        <v>46119</v>
       </c>
     </row>
     <row r="4">
@@ -1545,66 +1482,66 @@
         <v>19</v>
       </c>
       <c r="D4" s="36" t="s">
-        <v>32</v>
+        <v>22</v>
       </c>
       <c r="E4" s="37" t="s">
+        <v>21</v>
+      </c>
+      <c r="F4" s="38" t="s">
         <v>40</v>
-      </c>
-      <c r="F4" s="38" t="s">
-        <v>41</v>
       </c>
       <c r="G4" s="39" t="s">
         <v>23</v>
       </c>
       <c r="H4" s="40" t="s">
-        <v>40</v>
+        <v>21</v>
       </c>
       <c r="I4" s="41" t="s">
+        <v>41</v>
+      </c>
+      <c r="J4" s="42" t="s">
         <v>42</v>
       </c>
-      <c r="J4" s="42" t="s">
+      <c r="K4" s="43" t="s">
         <v>43</v>
       </c>
-      <c r="K4" s="43" t="s">
+      <c r="L4" s="44" t="s">
         <v>44</v>
       </c>
-      <c r="L4" s="44" t="s">
+      <c r="M4" s="45">
+        <v>46166</v>
+      </c>
+      <c r="N4" s="46">
+        <v>46166</v>
+      </c>
+      <c r="O4" s="47" t="s">
         <v>45</v>
       </c>
-      <c r="M4" s="45">
-        <v>46162</v>
-      </c>
-      <c r="N4" s="46">
-        <v>46163</v>
-      </c>
-      <c r="O4" s="47" t="s">
-        <v>46</v>
-      </c>
       <c r="P4" s="48" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="Q4" s="49">
-        <v>46128</v>
+        <v>46134</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="33" t="s">
+        <v>46</v>
+      </c>
+      <c r="B5" s="34" t="s">
         <v>47</v>
-      </c>
-      <c r="B5" s="34" t="s">
-        <v>48</v>
       </c>
       <c r="C5" s="35" t="s">
         <v>19</v>
       </c>
       <c r="D5" s="36" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="E5" s="37" t="s">
         <v>21</v>
       </c>
       <c r="F5" s="38" t="s">
-        <v>22</v>
+        <v>40</v>
       </c>
       <c r="G5" s="39" t="s">
         <v>23</v>
@@ -1613,243 +1550,243 @@
         <v>21</v>
       </c>
       <c r="I5" s="41" t="s">
+        <v>48</v>
+      </c>
+      <c r="J5" s="42" t="s">
+        <v>25</v>
+      </c>
+      <c r="K5" s="43" t="s">
+        <v>26</v>
+      </c>
+      <c r="L5" s="44" t="s">
+        <v>27</v>
+      </c>
+      <c r="M5" s="45">
+        <v>46166</v>
+      </c>
+      <c r="N5" s="46">
+        <v>46166</v>
+      </c>
+      <c r="O5" s="47" t="s">
         <v>49</v>
       </c>
-      <c r="J5" s="42" t="s">
+      <c r="P5" s="48" t="s">
         <v>50</v>
       </c>
-      <c r="K5" s="43" t="s">
-        <v>51</v>
-      </c>
-      <c r="L5" s="44" t="s">
-        <v>52</v>
-      </c>
-      <c r="M5" s="45">
-        <v>46166</v>
-      </c>
-      <c r="N5" s="46">
-        <v>46163</v>
-      </c>
-      <c r="O5" s="47" t="s">
-        <v>53</v>
-      </c>
-      <c r="P5" s="48" t="s">
-        <v>53</v>
-      </c>
       <c r="Q5" s="49">
-        <v>46113</v>
+        <v>46140</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="33" t="s">
-        <v>54</v>
+        <v>51</v>
       </c>
       <c r="B6" s="34" t="s">
-        <v>55</v>
+        <v>52</v>
       </c>
       <c r="C6" s="35" t="s">
         <v>19</v>
       </c>
       <c r="D6" s="36" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="E6" s="37" t="s">
-        <v>21</v>
+        <v>53</v>
       </c>
       <c r="F6" s="38" t="s">
-        <v>22</v>
+        <v>54</v>
       </c>
       <c r="G6" s="39" t="s">
         <v>23</v>
       </c>
       <c r="H6" s="40" t="s">
-        <v>21</v>
+        <v>53</v>
       </c>
       <c r="I6" s="41" t="s">
-        <v>49</v>
+        <v>55</v>
       </c>
       <c r="J6" s="42" t="s">
-        <v>50</v>
+        <v>56</v>
       </c>
       <c r="K6" s="43" t="s">
-        <v>51</v>
+        <v>57</v>
       </c>
       <c r="L6" s="44" t="s">
-        <v>52</v>
+        <v>58</v>
       </c>
       <c r="M6" s="45">
         <v>46166</v>
       </c>
       <c r="N6" s="46">
-        <v>46163</v>
+        <v>46166</v>
       </c>
       <c r="O6" s="47" t="s">
-        <v>53</v>
+        <v>59</v>
       </c>
       <c r="P6" s="48" t="s">
-        <v>53</v>
+        <v>59</v>
       </c>
       <c r="Q6" s="49">
-        <v>46113</v>
+        <v>46141</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="33" t="s">
-        <v>56</v>
+        <v>51</v>
       </c>
       <c r="B7" s="34" t="s">
-        <v>57</v>
+        <v>52</v>
       </c>
       <c r="C7" s="35" t="s">
         <v>19</v>
       </c>
       <c r="D7" s="36" t="s">
+        <v>22</v>
+      </c>
+      <c r="E7" s="37" t="s">
+        <v>60</v>
+      </c>
+      <c r="F7" s="38" t="s">
+        <v>61</v>
+      </c>
+      <c r="G7" s="39" t="s">
+        <v>62</v>
+      </c>
+      <c r="H7" s="40" t="s">
+        <v>60</v>
+      </c>
+      <c r="I7" s="41" t="s">
+        <v>63</v>
+      </c>
+      <c r="J7" s="42" t="s">
+        <v>56</v>
+      </c>
+      <c r="K7" s="43" t="s">
+        <v>57</v>
+      </c>
+      <c r="L7" s="44" t="s">
         <v>58</v>
       </c>
-      <c r="E7" s="37" t="s">
+      <c r="M7" s="45">
+        <v>46166</v>
+      </c>
+      <c r="N7" s="46">
+        <v>46166</v>
+      </c>
+      <c r="O7" s="47" t="s">
         <v>59</v>
       </c>
-      <c r="F7" s="38" t="s">
-        <v>60</v>
-      </c>
-      <c r="G7" s="39" t="s">
-        <v>23</v>
-      </c>
-      <c r="H7" s="40" t="s">
+      <c r="P7" s="48" t="s">
         <v>59</v>
       </c>
-      <c r="I7" s="41" t="s">
-        <v>61</v>
-      </c>
-      <c r="J7" s="42" t="s">
-        <v>62</v>
-      </c>
-      <c r="K7" s="43" t="s">
-        <v>63</v>
-      </c>
-      <c r="L7" s="44" t="s">
-        <v>64</v>
-      </c>
-      <c r="M7" s="45">
-        <v>46163</v>
-      </c>
-      <c r="N7" s="46">
-        <v>46163</v>
-      </c>
-      <c r="O7" s="47" t="s">
-        <v>65</v>
-      </c>
-      <c r="P7" s="48" t="s">
-        <v>66</v>
-      </c>
       <c r="Q7" s="49">
-        <v>46124</v>
+        <v>46141</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="33" t="s">
-        <v>67</v>
+        <v>51</v>
       </c>
       <c r="B8" s="34" t="s">
-        <v>68</v>
+        <v>52</v>
       </c>
       <c r="C8" s="35" t="s">
         <v>19</v>
       </c>
       <c r="D8" s="36" t="s">
+        <v>22</v>
+      </c>
+      <c r="E8" s="37" t="s">
+        <v>60</v>
+      </c>
+      <c r="F8" s="38" t="s">
+        <v>61</v>
+      </c>
+      <c r="G8" s="39" t="s">
+        <v>64</v>
+      </c>
+      <c r="H8" s="40" t="s">
+        <v>60</v>
+      </c>
+      <c r="I8" s="41" t="s">
+        <v>63</v>
+      </c>
+      <c r="J8" s="42" t="s">
+        <v>56</v>
+      </c>
+      <c r="K8" s="43" t="s">
+        <v>57</v>
+      </c>
+      <c r="L8" s="44" t="s">
         <v>58</v>
       </c>
-      <c r="E8" s="37" t="s">
-        <v>21</v>
-      </c>
-      <c r="F8" s="38" t="s">
-        <v>22</v>
-      </c>
-      <c r="G8" s="39" t="s">
-        <v>23</v>
-      </c>
-      <c r="H8" s="40" t="s">
-        <v>21</v>
-      </c>
-      <c r="I8" s="41" t="s">
-        <v>69</v>
-      </c>
-      <c r="J8" s="42" t="s">
-        <v>70</v>
-      </c>
-      <c r="K8" s="43" t="s">
-        <v>71</v>
-      </c>
-      <c r="L8" s="44" t="s">
-        <v>72</v>
-      </c>
       <c r="M8" s="45">
-        <v>46163</v>
+        <v>46166</v>
       </c>
       <c r="N8" s="46">
-        <v>46163</v>
+        <v>46166</v>
       </c>
       <c r="O8" s="47" t="s">
-        <v>73</v>
+        <v>59</v>
       </c>
       <c r="P8" s="48" t="s">
-        <v>73</v>
+        <v>59</v>
       </c>
       <c r="Q8" s="49">
-        <v>46140</v>
+        <v>46141</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="33" t="s">
-        <v>67</v>
+        <v>51</v>
       </c>
       <c r="B9" s="34" t="s">
-        <v>68</v>
+        <v>52</v>
       </c>
       <c r="C9" s="35" t="s">
         <v>19</v>
       </c>
       <c r="D9" s="36" t="s">
+        <v>22</v>
+      </c>
+      <c r="E9" s="37" t="s">
+        <v>53</v>
+      </c>
+      <c r="F9" s="38" t="s">
+        <v>54</v>
+      </c>
+      <c r="G9" s="39" t="s">
+        <v>65</v>
+      </c>
+      <c r="H9" s="40" t="s">
+        <v>53</v>
+      </c>
+      <c r="I9" s="41" t="s">
+        <v>66</v>
+      </c>
+      <c r="J9" s="42" t="s">
+        <v>56</v>
+      </c>
+      <c r="K9" s="43" t="s">
+        <v>57</v>
+      </c>
+      <c r="L9" s="44" t="s">
         <v>58</v>
       </c>
-      <c r="E9" s="37" t="s">
-        <v>21</v>
-      </c>
-      <c r="F9" s="38" t="s">
-        <v>22</v>
-      </c>
-      <c r="G9" s="39" t="s">
-        <v>74</v>
-      </c>
-      <c r="H9" s="40" t="s">
-        <v>21</v>
-      </c>
-      <c r="I9" s="41" t="s">
-        <v>75</v>
-      </c>
-      <c r="J9" s="42" t="s">
-        <v>70</v>
-      </c>
-      <c r="K9" s="43" t="s">
-        <v>71</v>
-      </c>
-      <c r="L9" s="44" t="s">
-        <v>72</v>
-      </c>
       <c r="M9" s="45">
-        <v>46163</v>
+        <v>46166</v>
       </c>
       <c r="N9" s="46">
-        <v>46163</v>
+        <v>46166</v>
       </c>
       <c r="O9" s="47" t="s">
-        <v>73</v>
+        <v>59</v>
       </c>
       <c r="P9" s="48" t="s">
-        <v>73</v>
+        <v>59</v>
       </c>
       <c r="Q9" s="49">
-        <v>46140</v>
+        <v>46141</v>
       </c>
     </row>
     <row r="10">
@@ -1863,467 +1800,467 @@
         <v>19</v>
       </c>
       <c r="D10" s="36" t="s">
-        <v>58</v>
+        <v>22</v>
       </c>
       <c r="E10" s="37" t="s">
         <v>21</v>
       </c>
       <c r="F10" s="38" t="s">
-        <v>22</v>
+        <v>40</v>
       </c>
       <c r="G10" s="39" t="s">
-        <v>76</v>
+        <v>23</v>
       </c>
       <c r="H10" s="40" t="s">
         <v>21</v>
       </c>
       <c r="I10" s="41" t="s">
-        <v>77</v>
+        <v>48</v>
       </c>
       <c r="J10" s="42" t="s">
-        <v>70</v>
+        <v>25</v>
       </c>
       <c r="K10" s="43" t="s">
-        <v>71</v>
+        <v>26</v>
       </c>
       <c r="L10" s="44" t="s">
-        <v>72</v>
+        <v>27</v>
       </c>
       <c r="M10" s="45">
-        <v>46163</v>
+        <v>46166</v>
       </c>
       <c r="N10" s="46">
-        <v>46163</v>
+        <v>46166</v>
       </c>
       <c r="O10" s="47" t="s">
-        <v>73</v>
+        <v>69</v>
       </c>
       <c r="P10" s="48" t="s">
-        <v>73</v>
+        <v>69</v>
       </c>
       <c r="Q10" s="49">
-        <v>46140</v>
+        <v>46142</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="33" t="s">
-        <v>78</v>
+        <v>70</v>
       </c>
       <c r="B11" s="34" t="s">
-        <v>79</v>
+        <v>71</v>
       </c>
       <c r="C11" s="35" t="s">
         <v>19</v>
       </c>
       <c r="D11" s="36" t="s">
-        <v>20</v>
+        <v>72</v>
       </c>
       <c r="E11" s="37" t="s">
-        <v>21</v>
+        <v>53</v>
       </c>
       <c r="F11" s="38" t="s">
-        <v>22</v>
+        <v>54</v>
       </c>
       <c r="G11" s="39" t="s">
         <v>23</v>
       </c>
       <c r="H11" s="40" t="s">
-        <v>21</v>
+        <v>53</v>
       </c>
       <c r="I11" s="41" t="s">
-        <v>80</v>
+        <v>73</v>
       </c>
       <c r="J11" s="42" t="s">
-        <v>81</v>
+        <v>74</v>
       </c>
       <c r="K11" s="43" t="s">
-        <v>82</v>
+        <v>75</v>
       </c>
       <c r="L11" s="44" t="s">
-        <v>83</v>
+        <v>76</v>
       </c>
       <c r="M11" s="45">
-        <v>46163</v>
+        <v>46159</v>
       </c>
       <c r="N11" s="46">
-        <v>46163</v>
+        <v>46166</v>
       </c>
       <c r="O11" s="47" t="s">
-        <v>84</v>
+        <v>77</v>
       </c>
       <c r="P11" s="48" t="s">
-        <v>84</v>
+        <v>78</v>
       </c>
       <c r="Q11" s="49">
-        <v>46146</v>
+        <v>46132</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="33" t="s">
-        <v>85</v>
+        <v>79</v>
       </c>
       <c r="B12" s="34" t="s">
-        <v>86</v>
+        <v>80</v>
       </c>
       <c r="C12" s="35" t="s">
         <v>19</v>
       </c>
       <c r="D12" s="36" t="s">
-        <v>20</v>
+        <v>72</v>
       </c>
       <c r="E12" s="37" t="s">
-        <v>59</v>
+        <v>21</v>
       </c>
       <c r="F12" s="38" t="s">
-        <v>60</v>
+        <v>40</v>
       </c>
       <c r="G12" s="39" t="s">
         <v>23</v>
       </c>
       <c r="H12" s="40" t="s">
-        <v>59</v>
+        <v>21</v>
       </c>
       <c r="I12" s="41" t="s">
-        <v>87</v>
+        <v>81</v>
       </c>
       <c r="J12" s="42" t="s">
-        <v>43</v>
+        <v>82</v>
       </c>
       <c r="K12" s="43" t="s">
-        <v>44</v>
+        <v>83</v>
       </c>
       <c r="L12" s="44" t="s">
-        <v>45</v>
+        <v>84</v>
       </c>
       <c r="M12" s="45">
-        <v>46163</v>
+        <v>46166</v>
       </c>
       <c r="N12" s="46">
-        <v>46163</v>
+        <v>46166</v>
       </c>
       <c r="O12" s="47" t="s">
-        <v>88</v>
+        <v>85</v>
       </c>
       <c r="P12" s="48" t="s">
-        <v>88</v>
+        <v>85</v>
       </c>
       <c r="Q12" s="49">
-        <v>46146</v>
+        <v>46141</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="33" t="s">
-        <v>85</v>
+        <v>79</v>
       </c>
       <c r="B13" s="34" t="s">
-        <v>86</v>
+        <v>80</v>
       </c>
       <c r="C13" s="35" t="s">
         <v>19</v>
       </c>
       <c r="D13" s="36" t="s">
-        <v>20</v>
+        <v>72</v>
       </c>
       <c r="E13" s="37" t="s">
-        <v>59</v>
+        <v>21</v>
       </c>
       <c r="F13" s="38" t="s">
-        <v>60</v>
+        <v>40</v>
       </c>
       <c r="G13" s="39" t="s">
-        <v>74</v>
+        <v>62</v>
       </c>
       <c r="H13" s="40" t="s">
-        <v>59</v>
+        <v>21</v>
       </c>
       <c r="I13" s="41" t="s">
-        <v>89</v>
+        <v>86</v>
       </c>
       <c r="J13" s="42" t="s">
-        <v>43</v>
+        <v>82</v>
       </c>
       <c r="K13" s="43" t="s">
-        <v>44</v>
+        <v>83</v>
       </c>
       <c r="L13" s="44" t="s">
-        <v>45</v>
+        <v>84</v>
       </c>
       <c r="M13" s="45">
-        <v>46163</v>
+        <v>46166</v>
       </c>
       <c r="N13" s="46">
-        <v>46163</v>
+        <v>46166</v>
       </c>
       <c r="O13" s="47" t="s">
-        <v>88</v>
+        <v>85</v>
       </c>
       <c r="P13" s="48" t="s">
-        <v>88</v>
+        <v>85</v>
       </c>
       <c r="Q13" s="49">
-        <v>46146</v>
+        <v>46141</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="33" t="s">
-        <v>85</v>
+        <v>79</v>
       </c>
       <c r="B14" s="34" t="s">
-        <v>86</v>
+        <v>80</v>
       </c>
       <c r="C14" s="35" t="s">
         <v>19</v>
       </c>
       <c r="D14" s="36" t="s">
-        <v>20</v>
+        <v>72</v>
       </c>
       <c r="E14" s="37" t="s">
-        <v>59</v>
+        <v>21</v>
       </c>
       <c r="F14" s="38" t="s">
-        <v>60</v>
+        <v>40</v>
       </c>
       <c r="G14" s="39" t="s">
-        <v>76</v>
+        <v>64</v>
       </c>
       <c r="H14" s="40" t="s">
-        <v>59</v>
+        <v>21</v>
       </c>
       <c r="I14" s="41" t="s">
-        <v>90</v>
+        <v>86</v>
       </c>
       <c r="J14" s="42" t="s">
-        <v>43</v>
+        <v>82</v>
       </c>
       <c r="K14" s="43" t="s">
-        <v>44</v>
+        <v>83</v>
       </c>
       <c r="L14" s="44" t="s">
-        <v>45</v>
+        <v>84</v>
       </c>
       <c r="M14" s="45">
-        <v>46163</v>
+        <v>46166</v>
       </c>
       <c r="N14" s="46">
-        <v>46163</v>
+        <v>46166</v>
       </c>
       <c r="O14" s="47" t="s">
-        <v>88</v>
+        <v>85</v>
       </c>
       <c r="P14" s="48" t="s">
-        <v>88</v>
+        <v>85</v>
       </c>
       <c r="Q14" s="49">
-        <v>46146</v>
+        <v>46141</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="33" t="s">
-        <v>91</v>
+        <v>79</v>
       </c>
       <c r="B15" s="34" t="s">
-        <v>92</v>
+        <v>80</v>
       </c>
       <c r="C15" s="35" t="s">
         <v>19</v>
       </c>
       <c r="D15" s="36" t="s">
-        <v>20</v>
+        <v>72</v>
       </c>
       <c r="E15" s="37" t="s">
-        <v>59</v>
+        <v>21</v>
       </c>
       <c r="F15" s="38" t="s">
-        <v>60</v>
+        <v>40</v>
       </c>
       <c r="G15" s="39" t="s">
-        <v>23</v>
+        <v>65</v>
       </c>
       <c r="H15" s="40" t="s">
-        <v>59</v>
+        <v>21</v>
       </c>
       <c r="I15" s="41" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="J15" s="42" t="s">
-        <v>43</v>
+        <v>82</v>
       </c>
       <c r="K15" s="43" t="s">
-        <v>44</v>
+        <v>83</v>
       </c>
       <c r="L15" s="44" t="s">
-        <v>45</v>
+        <v>84</v>
       </c>
       <c r="M15" s="45">
-        <v>46163</v>
+        <v>46166</v>
       </c>
       <c r="N15" s="46">
-        <v>46163</v>
+        <v>46166</v>
       </c>
       <c r="O15" s="47" t="s">
-        <v>88</v>
+        <v>85</v>
       </c>
       <c r="P15" s="48" t="s">
-        <v>88</v>
+        <v>85</v>
       </c>
       <c r="Q15" s="49">
-        <v>46146</v>
+        <v>46141</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="33" t="s">
-        <v>93</v>
+        <v>79</v>
       </c>
       <c r="B16" s="34" t="s">
-        <v>94</v>
+        <v>80</v>
       </c>
       <c r="C16" s="35" t="s">
         <v>19</v>
       </c>
       <c r="D16" s="36" t="s">
-        <v>20</v>
+        <v>72</v>
       </c>
       <c r="E16" s="37" t="s">
-        <v>59</v>
+        <v>21</v>
       </c>
       <c r="F16" s="38" t="s">
-        <v>60</v>
+        <v>40</v>
       </c>
       <c r="G16" s="39" t="s">
-        <v>23</v>
+        <v>87</v>
       </c>
       <c r="H16" s="40" t="s">
-        <v>59</v>
+        <v>21</v>
       </c>
       <c r="I16" s="41" t="s">
-        <v>90</v>
+        <v>86</v>
       </c>
       <c r="J16" s="42" t="s">
-        <v>43</v>
+        <v>82</v>
       </c>
       <c r="K16" s="43" t="s">
-        <v>44</v>
+        <v>83</v>
       </c>
       <c r="L16" s="44" t="s">
-        <v>45</v>
+        <v>84</v>
       </c>
       <c r="M16" s="45">
-        <v>46163</v>
+        <v>46166</v>
       </c>
       <c r="N16" s="46">
-        <v>46163</v>
+        <v>46166</v>
       </c>
       <c r="O16" s="47" t="s">
-        <v>88</v>
+        <v>85</v>
       </c>
       <c r="P16" s="48" t="s">
-        <v>88</v>
+        <v>85</v>
       </c>
       <c r="Q16" s="49">
-        <v>46146</v>
+        <v>46141</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="33" t="s">
-        <v>93</v>
+        <v>79</v>
       </c>
       <c r="B17" s="34" t="s">
-        <v>94</v>
+        <v>80</v>
       </c>
       <c r="C17" s="35" t="s">
         <v>19</v>
       </c>
       <c r="D17" s="36" t="s">
-        <v>20</v>
+        <v>72</v>
       </c>
       <c r="E17" s="37" t="s">
-        <v>59</v>
+        <v>21</v>
       </c>
       <c r="F17" s="38" t="s">
-        <v>60</v>
+        <v>40</v>
       </c>
       <c r="G17" s="39" t="s">
-        <v>74</v>
+        <v>88</v>
       </c>
       <c r="H17" s="40" t="s">
-        <v>59</v>
+        <v>21</v>
       </c>
       <c r="I17" s="41" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="J17" s="42" t="s">
-        <v>43</v>
+        <v>82</v>
       </c>
       <c r="K17" s="43" t="s">
-        <v>44</v>
+        <v>83</v>
       </c>
       <c r="L17" s="44" t="s">
-        <v>45</v>
+        <v>84</v>
       </c>
       <c r="M17" s="45">
-        <v>46163</v>
+        <v>46166</v>
       </c>
       <c r="N17" s="46">
-        <v>46163</v>
+        <v>46166</v>
       </c>
       <c r="O17" s="47" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="P17" s="48" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="Q17" s="49">
-        <v>46146</v>
+        <v>46141</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="33" t="s">
-        <v>93</v>
+        <v>90</v>
       </c>
       <c r="B18" s="34" t="s">
-        <v>94</v>
+        <v>91</v>
       </c>
       <c r="C18" s="35" t="s">
         <v>19</v>
       </c>
       <c r="D18" s="36" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="E18" s="37" t="s">
-        <v>59</v>
+        <v>21</v>
       </c>
       <c r="F18" s="38" t="s">
-        <v>60</v>
+        <v>40</v>
       </c>
       <c r="G18" s="39" t="s">
-        <v>76</v>
+        <v>23</v>
       </c>
       <c r="H18" s="40" t="s">
-        <v>59</v>
+        <v>21</v>
       </c>
       <c r="I18" s="41" t="s">
-        <v>95</v>
+        <v>92</v>
       </c>
       <c r="J18" s="42" t="s">
-        <v>43</v>
+        <v>25</v>
       </c>
       <c r="K18" s="43" t="s">
-        <v>44</v>
+        <v>26</v>
       </c>
       <c r="L18" s="44" t="s">
-        <v>45</v>
+        <v>27</v>
       </c>
       <c r="M18" s="45">
-        <v>46163</v>
+        <v>46166</v>
       </c>
       <c r="N18" s="46">
-        <v>46163</v>
+        <v>46166</v>
       </c>
       <c r="O18" s="47" t="s">
-        <v>88</v>
+        <v>93</v>
       </c>
       <c r="P18" s="48" t="s">
-        <v>88</v>
+        <v>93</v>
       </c>
       <c r="Q18" s="49">
         <v>46146</v>
@@ -2331,105 +2268,105 @@
     </row>
     <row r="19">
       <c r="A19" s="33" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="B19" s="34" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="C19" s="35" t="s">
         <v>19</v>
       </c>
       <c r="D19" s="36" t="s">
-        <v>20</v>
+        <v>96</v>
       </c>
       <c r="E19" s="37" t="s">
-        <v>59</v>
+        <v>21</v>
       </c>
       <c r="F19" s="38" t="s">
-        <v>60</v>
+        <v>22</v>
       </c>
       <c r="G19" s="39" t="s">
-        <v>96</v>
+        <v>23</v>
       </c>
       <c r="H19" s="40" t="s">
-        <v>59</v>
+        <v>21</v>
       </c>
       <c r="I19" s="41" t="s">
-        <v>89</v>
+        <v>97</v>
       </c>
       <c r="J19" s="42" t="s">
-        <v>43</v>
+        <v>25</v>
       </c>
       <c r="K19" s="43" t="s">
-        <v>44</v>
+        <v>26</v>
       </c>
       <c r="L19" s="44" t="s">
-        <v>45</v>
+        <v>27</v>
       </c>
       <c r="M19" s="45">
-        <v>46163</v>
+        <v>46166</v>
       </c>
       <c r="N19" s="46">
-        <v>46163</v>
+        <v>46166</v>
       </c>
       <c r="O19" s="47" t="s">
-        <v>88</v>
+        <v>98</v>
       </c>
       <c r="P19" s="48" t="s">
-        <v>88</v>
+        <v>98</v>
       </c>
       <c r="Q19" s="49">
-        <v>46146</v>
+        <v>46144</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="33" t="s">
-        <v>93</v>
+        <v>99</v>
       </c>
       <c r="B20" s="34" t="s">
-        <v>94</v>
+        <v>100</v>
       </c>
       <c r="C20" s="35" t="s">
         <v>19</v>
       </c>
       <c r="D20" s="36" t="s">
-        <v>20</v>
+        <v>96</v>
       </c>
       <c r="E20" s="37" t="s">
-        <v>59</v>
+        <v>21</v>
       </c>
       <c r="F20" s="38" t="s">
-        <v>60</v>
+        <v>40</v>
       </c>
       <c r="G20" s="39" t="s">
-        <v>97</v>
+        <v>23</v>
       </c>
       <c r="H20" s="40" t="s">
-        <v>59</v>
+        <v>21</v>
       </c>
       <c r="I20" s="41" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="J20" s="42" t="s">
-        <v>43</v>
+        <v>25</v>
       </c>
       <c r="K20" s="43" t="s">
-        <v>44</v>
+        <v>26</v>
       </c>
       <c r="L20" s="44" t="s">
-        <v>45</v>
+        <v>27</v>
       </c>
       <c r="M20" s="45">
-        <v>46163</v>
+        <v>46166</v>
       </c>
       <c r="N20" s="46">
-        <v>46163</v>
+        <v>46166</v>
       </c>
       <c r="O20" s="47" t="s">
-        <v>88</v>
+        <v>93</v>
       </c>
       <c r="P20" s="48" t="s">
-        <v>88</v>
+        <v>93</v>
       </c>
       <c r="Q20" s="49">
         <v>46146</v>
@@ -2437,16 +2374,16 @@
     </row>
     <row r="21">
       <c r="A21" s="33" t="s">
-        <v>93</v>
+        <v>101</v>
       </c>
       <c r="B21" s="34" t="s">
-        <v>94</v>
+        <v>102</v>
       </c>
       <c r="C21" s="35" t="s">
         <v>19</v>
       </c>
       <c r="D21" s="36" t="s">
-        <v>20</v>
+        <v>103</v>
       </c>
       <c r="E21" s="37" t="s">
         <v>21</v>
@@ -2455,110 +2392,110 @@
         <v>22</v>
       </c>
       <c r="G21" s="39" t="s">
-        <v>98</v>
+        <v>23</v>
       </c>
       <c r="H21" s="40" t="s">
         <v>21</v>
       </c>
       <c r="I21" s="41" t="s">
-        <v>99</v>
+        <v>104</v>
       </c>
       <c r="J21" s="42" t="s">
-        <v>43</v>
+        <v>25</v>
       </c>
       <c r="K21" s="43" t="s">
-        <v>44</v>
+        <v>26</v>
       </c>
       <c r="L21" s="44" t="s">
-        <v>45</v>
+        <v>27</v>
       </c>
       <c r="M21" s="45">
-        <v>46163</v>
+        <v>46166</v>
       </c>
       <c r="N21" s="46">
-        <v>46163</v>
+        <v>46166</v>
       </c>
       <c r="O21" s="47" t="s">
-        <v>88</v>
+        <v>105</v>
       </c>
       <c r="P21" s="48" t="s">
-        <v>88</v>
+        <v>105</v>
       </c>
       <c r="Q21" s="49">
-        <v>46146</v>
+        <v>46152</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="33" t="s">
-        <v>93</v>
+        <v>106</v>
       </c>
       <c r="B22" s="34" t="s">
-        <v>94</v>
+        <v>107</v>
       </c>
       <c r="C22" s="35" t="s">
         <v>19</v>
       </c>
       <c r="D22" s="36" t="s">
-        <v>20</v>
+        <v>103</v>
       </c>
       <c r="E22" s="37" t="s">
-        <v>59</v>
+        <v>21</v>
       </c>
       <c r="F22" s="38" t="s">
-        <v>60</v>
+        <v>22</v>
       </c>
       <c r="G22" s="39" t="s">
-        <v>100</v>
+        <v>23</v>
       </c>
       <c r="H22" s="40" t="s">
-        <v>59</v>
+        <v>21</v>
       </c>
       <c r="I22" s="41" t="s">
-        <v>101</v>
+        <v>104</v>
       </c>
       <c r="J22" s="42" t="s">
-        <v>43</v>
+        <v>25</v>
       </c>
       <c r="K22" s="43" t="s">
-        <v>44</v>
+        <v>26</v>
       </c>
       <c r="L22" s="44" t="s">
-        <v>45</v>
+        <v>27</v>
       </c>
       <c r="M22" s="45">
-        <v>46163</v>
+        <v>46166</v>
       </c>
       <c r="N22" s="46">
-        <v>46163</v>
+        <v>46166</v>
       </c>
       <c r="O22" s="47" t="s">
-        <v>88</v>
+        <v>105</v>
       </c>
       <c r="P22" s="48" t="s">
-        <v>88</v>
+        <v>105</v>
       </c>
       <c r="Q22" s="49">
-        <v>46146</v>
+        <v>46152</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="33" t="s">
-        <v>102</v>
+        <v>108</v>
       </c>
       <c r="B23" s="34" t="s">
-        <v>103</v>
+        <v>109</v>
       </c>
       <c r="C23" s="35" t="s">
         <v>19</v>
       </c>
       <c r="D23" s="36" t="s">
-        <v>20</v>
+        <v>103</v>
       </c>
       <c r="E23" s="37" t="s">
         <v>21</v>
       </c>
       <c r="F23" s="38" t="s">
-        <v>22</v>
+        <v>40</v>
       </c>
       <c r="G23" s="39" t="s">
         <v>23</v>
@@ -2567,566 +2504,36 @@
         <v>21</v>
       </c>
       <c r="I23" s="41" t="s">
-        <v>104</v>
+        <v>110</v>
       </c>
       <c r="J23" s="42" t="s">
+        <v>25</v>
+      </c>
+      <c r="K23" s="43" t="s">
+        <v>26</v>
+      </c>
+      <c r="L23" s="44" t="s">
+        <v>27</v>
+      </c>
+      <c r="M23" s="45">
+        <v>46166</v>
+      </c>
+      <c r="N23" s="46">
+        <v>46166</v>
+      </c>
+      <c r="O23" s="47" t="s">
         <v>105</v>
       </c>
-      <c r="K23" s="43" t="s">
-        <v>106</v>
-      </c>
-      <c r="L23" s="44" t="s">
-        <v>107</v>
-      </c>
-      <c r="M23" s="45">
-        <v>46163</v>
-      </c>
-      <c r="N23" s="46">
-        <v>46163</v>
-      </c>
-      <c r="O23" s="47" t="s">
-        <v>108</v>
-      </c>
       <c r="P23" s="48" t="s">
-        <v>108</v>
+        <v>105</v>
       </c>
       <c r="Q23" s="49">
-        <v>46151</v>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" s="33" t="s">
-        <v>109</v>
-      </c>
-      <c r="B24" s="34" t="s">
-        <v>110</v>
-      </c>
-      <c r="C24" s="35" t="s">
-        <v>111</v>
-      </c>
-      <c r="D24" s="36" t="s">
-        <v>20</v>
-      </c>
-      <c r="E24" s="37" t="s">
-        <v>59</v>
-      </c>
-      <c r="F24" s="38" t="s">
-        <v>60</v>
-      </c>
-      <c r="G24" s="39" t="s">
-        <v>23</v>
-      </c>
-      <c r="H24" s="40" t="s">
-        <v>59</v>
-      </c>
-      <c r="I24" s="41" t="s">
-        <v>112</v>
-      </c>
-      <c r="J24" s="42" t="s">
-        <v>113</v>
-      </c>
-      <c r="K24" s="43" t="s">
-        <v>114</v>
-      </c>
-      <c r="L24" s="44" t="s">
-        <v>115</v>
-      </c>
-      <c r="M24" s="45">
-        <v>46163</v>
-      </c>
-      <c r="N24" s="46">
-        <v>46163</v>
-      </c>
-      <c r="O24" s="47" t="s">
-        <v>116</v>
-      </c>
-      <c r="P24" s="48" t="s">
-        <v>116</v>
-      </c>
-      <c r="Q24" s="49">
-        <v>46150</v>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" s="33" t="s">
-        <v>109</v>
-      </c>
-      <c r="B25" s="34" t="s">
-        <v>110</v>
-      </c>
-      <c r="C25" s="35" t="s">
-        <v>111</v>
-      </c>
-      <c r="D25" s="36" t="s">
-        <v>20</v>
-      </c>
-      <c r="E25" s="37" t="s">
-        <v>59</v>
-      </c>
-      <c r="F25" s="38" t="s">
-        <v>60</v>
-      </c>
-      <c r="G25" s="39" t="s">
-        <v>74</v>
-      </c>
-      <c r="H25" s="40" t="s">
-        <v>59</v>
-      </c>
-      <c r="I25" s="41" t="s">
-        <v>117</v>
-      </c>
-      <c r="J25" s="42" t="s">
-        <v>113</v>
-      </c>
-      <c r="K25" s="43" t="s">
-        <v>114</v>
-      </c>
-      <c r="L25" s="44" t="s">
-        <v>115</v>
-      </c>
-      <c r="M25" s="45">
-        <v>46163</v>
-      </c>
-      <c r="N25" s="46">
-        <v>46163</v>
-      </c>
-      <c r="O25" s="47" t="s">
-        <v>116</v>
-      </c>
-      <c r="P25" s="48" t="s">
-        <v>116</v>
-      </c>
-      <c r="Q25" s="49">
-        <v>46150</v>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" s="33" t="s">
-        <v>118</v>
-      </c>
-      <c r="B26" s="34" t="s">
-        <v>119</v>
-      </c>
-      <c r="C26" s="35" t="s">
-        <v>19</v>
-      </c>
-      <c r="D26" s="36" t="s">
-        <v>20</v>
-      </c>
-      <c r="E26" s="37" t="s">
-        <v>59</v>
-      </c>
-      <c r="F26" s="38" t="s">
-        <v>60</v>
-      </c>
-      <c r="G26" s="39" t="s">
-        <v>23</v>
-      </c>
-      <c r="H26" s="40" t="s">
-        <v>59</v>
-      </c>
-      <c r="I26" s="41" t="s">
-        <v>120</v>
-      </c>
-      <c r="J26" s="42" t="s">
-        <v>121</v>
-      </c>
-      <c r="K26" s="43" t="s">
-        <v>122</v>
-      </c>
-      <c r="L26" s="44" t="s">
-        <v>123</v>
-      </c>
-      <c r="M26" s="45">
-        <v>46163</v>
-      </c>
-      <c r="N26" s="46">
-        <v>46163</v>
-      </c>
-      <c r="O26" s="47" t="s">
-        <v>124</v>
-      </c>
-      <c r="P26" s="48" t="s">
-        <v>124</v>
-      </c>
-      <c r="Q26" s="49">
-        <v>46151</v>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" s="33" t="s">
-        <v>118</v>
-      </c>
-      <c r="B27" s="34" t="s">
-        <v>119</v>
-      </c>
-      <c r="C27" s="35" t="s">
-        <v>19</v>
-      </c>
-      <c r="D27" s="36" t="s">
-        <v>20</v>
-      </c>
-      <c r="E27" s="37" t="s">
-        <v>59</v>
-      </c>
-      <c r="F27" s="38" t="s">
-        <v>60</v>
-      </c>
-      <c r="G27" s="39" t="s">
-        <v>74</v>
-      </c>
-      <c r="H27" s="40" t="s">
-        <v>59</v>
-      </c>
-      <c r="I27" s="41" t="s">
-        <v>120</v>
-      </c>
-      <c r="J27" s="42" t="s">
-        <v>121</v>
-      </c>
-      <c r="K27" s="43" t="s">
-        <v>122</v>
-      </c>
-      <c r="L27" s="44" t="s">
-        <v>123</v>
-      </c>
-      <c r="M27" s="45">
-        <v>46163</v>
-      </c>
-      <c r="N27" s="46">
-        <v>46163</v>
-      </c>
-      <c r="O27" s="47" t="s">
-        <v>124</v>
-      </c>
-      <c r="P27" s="48" t="s">
-        <v>124</v>
-      </c>
-      <c r="Q27" s="49">
-        <v>46151</v>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" s="33" t="s">
-        <v>118</v>
-      </c>
-      <c r="B28" s="34" t="s">
-        <v>119</v>
-      </c>
-      <c r="C28" s="35" t="s">
-        <v>19</v>
-      </c>
-      <c r="D28" s="36" t="s">
-        <v>20</v>
-      </c>
-      <c r="E28" s="37" t="s">
-        <v>59</v>
-      </c>
-      <c r="F28" s="38" t="s">
-        <v>60</v>
-      </c>
-      <c r="G28" s="39" t="s">
-        <v>76</v>
-      </c>
-      <c r="H28" s="40" t="s">
-        <v>59</v>
-      </c>
-      <c r="I28" s="41" t="s">
-        <v>120</v>
-      </c>
-      <c r="J28" s="42" t="s">
-        <v>121</v>
-      </c>
-      <c r="K28" s="43" t="s">
-        <v>122</v>
-      </c>
-      <c r="L28" s="44" t="s">
-        <v>123</v>
-      </c>
-      <c r="M28" s="45">
-        <v>46163</v>
-      </c>
-      <c r="N28" s="46">
-        <v>46163</v>
-      </c>
-      <c r="O28" s="47" t="s">
-        <v>124</v>
-      </c>
-      <c r="P28" s="48" t="s">
-        <v>124</v>
-      </c>
-      <c r="Q28" s="49">
-        <v>46151</v>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" s="33" t="s">
-        <v>118</v>
-      </c>
-      <c r="B29" s="34" t="s">
-        <v>119</v>
-      </c>
-      <c r="C29" s="35" t="s">
-        <v>19</v>
-      </c>
-      <c r="D29" s="36" t="s">
-        <v>20</v>
-      </c>
-      <c r="E29" s="37" t="s">
-        <v>59</v>
-      </c>
-      <c r="F29" s="38" t="s">
-        <v>60</v>
-      </c>
-      <c r="G29" s="39" t="s">
-        <v>96</v>
-      </c>
-      <c r="H29" s="40" t="s">
-        <v>59</v>
-      </c>
-      <c r="I29" s="41" t="s">
-        <v>120</v>
-      </c>
-      <c r="J29" s="42" t="s">
-        <v>121</v>
-      </c>
-      <c r="K29" s="43" t="s">
-        <v>122</v>
-      </c>
-      <c r="L29" s="44" t="s">
-        <v>123</v>
-      </c>
-      <c r="M29" s="45">
-        <v>46163</v>
-      </c>
-      <c r="N29" s="46">
-        <v>46163</v>
-      </c>
-      <c r="O29" s="47" t="s">
-        <v>124</v>
-      </c>
-      <c r="P29" s="48" t="s">
-        <v>124</v>
-      </c>
-      <c r="Q29" s="49">
-        <v>46151</v>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" s="33" t="s">
-        <v>118</v>
-      </c>
-      <c r="B30" s="34" t="s">
-        <v>119</v>
-      </c>
-      <c r="C30" s="35" t="s">
-        <v>19</v>
-      </c>
-      <c r="D30" s="36" t="s">
-        <v>20</v>
-      </c>
-      <c r="E30" s="37" t="s">
-        <v>59</v>
-      </c>
-      <c r="F30" s="38" t="s">
-        <v>60</v>
-      </c>
-      <c r="G30" s="39" t="s">
-        <v>97</v>
-      </c>
-      <c r="H30" s="40" t="s">
-        <v>59</v>
-      </c>
-      <c r="I30" s="41" t="s">
-        <v>120</v>
-      </c>
-      <c r="J30" s="42" t="s">
-        <v>121</v>
-      </c>
-      <c r="K30" s="43" t="s">
-        <v>122</v>
-      </c>
-      <c r="L30" s="44" t="s">
-        <v>123</v>
-      </c>
-      <c r="M30" s="45">
-        <v>46163</v>
-      </c>
-      <c r="N30" s="46">
-        <v>46163</v>
-      </c>
-      <c r="O30" s="47" t="s">
-        <v>124</v>
-      </c>
-      <c r="P30" s="48" t="s">
-        <v>124</v>
-      </c>
-      <c r="Q30" s="49">
-        <v>46151</v>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" s="33" t="s">
-        <v>118</v>
-      </c>
-      <c r="B31" s="34" t="s">
-        <v>119</v>
-      </c>
-      <c r="C31" s="35" t="s">
-        <v>19</v>
-      </c>
-      <c r="D31" s="36" t="s">
-        <v>20</v>
-      </c>
-      <c r="E31" s="37" t="s">
-        <v>59</v>
-      </c>
-      <c r="F31" s="38" t="s">
-        <v>60</v>
-      </c>
-      <c r="G31" s="39" t="s">
-        <v>98</v>
-      </c>
-      <c r="H31" s="40" t="s">
-        <v>59</v>
-      </c>
-      <c r="I31" s="41" t="s">
-        <v>120</v>
-      </c>
-      <c r="J31" s="42" t="s">
-        <v>121</v>
-      </c>
-      <c r="K31" s="43" t="s">
-        <v>122</v>
-      </c>
-      <c r="L31" s="44" t="s">
-        <v>123</v>
-      </c>
-      <c r="M31" s="45">
-        <v>46163</v>
-      </c>
-      <c r="N31" s="46">
-        <v>46163</v>
-      </c>
-      <c r="O31" s="47" t="s">
-        <v>124</v>
-      </c>
-      <c r="P31" s="48" t="s">
-        <v>124</v>
-      </c>
-      <c r="Q31" s="49">
-        <v>46151</v>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" s="33" t="s">
-        <v>118</v>
-      </c>
-      <c r="B32" s="34" t="s">
-        <v>119</v>
-      </c>
-      <c r="C32" s="35" t="s">
-        <v>19</v>
-      </c>
-      <c r="D32" s="36" t="s">
-        <v>20</v>
-      </c>
-      <c r="E32" s="37" t="s">
-        <v>59</v>
-      </c>
-      <c r="F32" s="38" t="s">
-        <v>60</v>
-      </c>
-      <c r="G32" s="39" t="s">
-        <v>100</v>
-      </c>
-      <c r="H32" s="40" t="s">
-        <v>59</v>
-      </c>
-      <c r="I32" s="41" t="s">
-        <v>120</v>
-      </c>
-      <c r="J32" s="42" t="s">
-        <v>121</v>
-      </c>
-      <c r="K32" s="43" t="s">
-        <v>122</v>
-      </c>
-      <c r="L32" s="44" t="s">
-        <v>123</v>
-      </c>
-      <c r="M32" s="45">
-        <v>46163</v>
-      </c>
-      <c r="N32" s="46">
-        <v>46163</v>
-      </c>
-      <c r="O32" s="47" t="s">
-        <v>124</v>
-      </c>
-      <c r="P32" s="48" t="s">
-        <v>124</v>
-      </c>
-      <c r="Q32" s="49">
-        <v>46151</v>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" s="33" t="s">
-        <v>125</v>
-      </c>
-      <c r="B33" s="34" t="s">
-        <v>126</v>
-      </c>
-      <c r="C33" s="35" t="s">
-        <v>19</v>
-      </c>
-      <c r="D33" s="36" t="s">
-        <v>20</v>
-      </c>
-      <c r="E33" s="37" t="s">
-        <v>40</v>
-      </c>
-      <c r="F33" s="38" t="s">
-        <v>41</v>
-      </c>
-      <c r="G33" s="39" t="s">
-        <v>23</v>
-      </c>
-      <c r="H33" s="40" t="s">
-        <v>40</v>
-      </c>
-      <c r="I33" s="41" t="s">
-        <v>127</v>
-      </c>
-      <c r="J33" s="42" t="s">
-        <v>128</v>
-      </c>
-      <c r="K33" s="43" t="s">
-        <v>129</v>
-      </c>
-      <c r="L33" s="44" t="s">
-        <v>130</v>
-      </c>
-      <c r="M33" s="45">
-        <v>46164</v>
-      </c>
-      <c r="N33" s="46">
-        <v>46163</v>
-      </c>
-      <c r="O33" s="47" t="s">
-        <v>131</v>
-      </c>
-      <c r="P33" s="48" t="s">
-        <v>131</v>
-      </c>
-      <c r="Q33" s="49">
-        <v>46129</v>
+        <v>46152</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError sqref="A1 B1 C1 D1 E1 F1 G1 H1 I1 J1 K1 L1 M1 N1 O1 P1 Q1 A2 B2 C2 D2 E2 F2 G2 H2 I2 J2 K2 L2 O2 P2 A3 B3 C3 D3 E3 F3 G3 H3 I3 J3 K3 L3 O3 P3 A4 B4 C4 D4 E4 F4 G4 H4 I4 J4 K4 L4 O4 P4 A5 B5 C5 D5 E5 F5 G5 H5 I5 J5 K5 L5 O5 P5 A6 B6 C6 D6 E6 F6 G6 H6 I6 J6 K6 L6 O6 P6 A7 B7 C7 D7 E7 F7 G7 H7 I7 J7 K7 L7 O7 P7 A8 B8 C8 D8 E8 F8 G8 H8 I8 J8 K8 L8 O8 P8 A9 B9 C9 D9 E9 F9 G9 H9 I9 J9 K9 L9 O9 P9 A10 B10 C10 D10 E10 F10 G10 H10 I10 J10 K10 L10 O10 P10 A11 B11 C11 D11 E11 F11 G11 H11 I11 J11 K11 L11 O11 P11 A12 B12 C12 D12 E12 F12 G12 H12 I12 J12 K12 L12 O12 P12 A13 B13 C13 D13 E13 F13 G13 H13 I13 J13 K13 L13 O13 P13 A14 B14 C14 D14 E14 F14 G14 H14 I14 J14 K14 L14 O14 P14 A15 B15 C15 D15 E15 F15 G15 H15 I15 J15 K15 L15 O15 P15 A16 B16 C16 D16 E16 F16 G16 H16 I16 J16 K16 L16 O16 P16 A17 B17 C17 D17 E17 F17 G17 H17 I17 J17 K17 L17 O17 P17 A18 B18 C18 D18 E18 F18 G18 H18 I18 J18 K18 L18 O18 P18 A19 B19 C19 D19 E19 F19 G19 H19 I19 J19 K19 L19 O19 P19 A20 B20 C20 D20 E20 F20 G20 H20 I20 J20 K20 L20 O20 P20 A21 B21 C21 D21 E21 F21 G21 H21 I21 J21 K21 L21 O21 P21 A22 B22 C22 D22 E22 F22 G22 H22 I22 J22 K22 L22 O22 P22 A23 B23 C23 D23 E23 F23 G23 H23 I23 J23 K23 L23 O23 P23 A24 B24 C24 D24 E24 F24 G24 H24 I24 J24 K24 L24 O24 P24 A25 B25 C25 D25 E25 F25 G25 H25 I25 J25 K25 L25 O25 P25 A26 B26 C26 D26 E26 F26 G26 H26 I26 J26 K26 L26 O26 P26 A27 B27 C27 D27 E27 F27 G27 H27 I27 J27 K27 L27 O27 P27 A28 B28 C28 D28 E28 F28 G28 H28 I28 J28 K28 L28 O28 P28 A29 B29 C29 D29 E29 F29 G29 H29 I29 J29 K29 L29 O29 P29 A30 B30 C30 D30 E30 F30 G30 H30 I30 J30 K30 L30 O30 P30 A31 B31 C31 D31 E31 F31 G31 H31 I31 J31 K31 L31 O31 P31 A32 B32 C32 D32 E32 F32 G32 H32 I32 J32 K32 L32 O32 P32 A33 B33 C33 D33 E33 F33 G33 H33 I33 J33 K33 L33 O33 P33" numberStoredAsText="true"/>
+    <ignoredError sqref="A1 B1 C1 D1 E1 F1 G1 H1 I1 J1 K1 L1 M1 N1 O1 P1 Q1 A2 B2 C2 D2 E2 F2 G2 H2 I2 J2 K2 L2 O2 P2 A3 B3 C3 D3 E3 F3 G3 H3 I3 J3 K3 L3 O3 P3 A4 B4 C4 D4 E4 F4 G4 H4 I4 J4 K4 L4 O4 P4 A5 B5 C5 D5 E5 F5 G5 H5 I5 J5 K5 L5 O5 P5 A6 B6 C6 D6 E6 F6 G6 H6 I6 J6 K6 L6 O6 P6 A7 B7 C7 D7 E7 F7 G7 H7 I7 J7 K7 L7 O7 P7 A8 B8 C8 D8 E8 F8 G8 H8 I8 J8 K8 L8 O8 P8 A9 B9 C9 D9 E9 F9 G9 H9 I9 J9 K9 L9 O9 P9 A10 B10 C10 D10 E10 F10 G10 H10 I10 J10 K10 L10 O10 P10 A11 B11 C11 D11 E11 F11 G11 H11 I11 J11 K11 L11 O11 P11 A12 B12 C12 D12 E12 F12 G12 H12 I12 J12 K12 L12 O12 P12 A13 B13 C13 D13 E13 F13 G13 H13 I13 J13 K13 L13 O13 P13 A14 B14 C14 D14 E14 F14 G14 H14 I14 J14 K14 L14 O14 P14 A15 B15 C15 D15 E15 F15 G15 H15 I15 J15 K15 L15 O15 P15 A16 B16 C16 D16 E16 F16 G16 H16 I16 J16 K16 L16 O16 P16 A17 B17 C17 D17 E17 F17 G17 H17 I17 J17 K17 L17 O17 P17 A18 B18 C18 D18 E18 F18 G18 H18 I18 J18 K18 L18 O18 P18 A19 B19 C19 D19 E19 F19 G19 H19 I19 J19 K19 L19 O19 P19 A20 B20 C20 D20 E20 F20 G20 H20 I20 J20 K20 L20 O20 P20 A21 B21 C21 D21 E21 F21 G21 H21 I21 J21 K21 L21 O21 P21 A22 B22 C22 D22 E22 F22 G22 H22 I22 J22 K22 L22 O22 P22 A23 B23 C23 D23 E23 F23 G23 H23 I23 J23 K23 L23 O23 P23" numberStoredAsText="true"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/trimika_data.xlsx
+++ b/trimika_data.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" count="325" uniqueCount="111">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" count="1431" uniqueCount="204">
   <si>
     <t>REFERENCE NO</t>
   </si>
@@ -66,28 +66,88 @@
     <t>EXPORT DATE</t>
   </si>
   <si>
-    <t>2565344</t>
-  </si>
-  <si>
-    <t>EF4-0230923-3</t>
+    <t>2565409</t>
+  </si>
+  <si>
+    <t>EF4-0231080-1</t>
   </si>
   <si>
     <t>Vessel, Container</t>
   </si>
   <si>
-    <t>V1626429891</t>
+    <t>V0710289492</t>
+  </si>
+  <si>
+    <t>9903.03.06</t>
+  </si>
+  <si>
+    <t>S122 EXCL,IRN/STL/ALUM,DERIV</t>
+  </si>
+  <si>
+    <t>001</t>
+  </si>
+  <si>
+    <t>9903.82.02,7223.00.1046</t>
+  </si>
+  <si>
+    <t>VENUS WIRE INDUSTRIES PRIVATE LTD</t>
+  </si>
+  <si>
+    <t>VENWIR</t>
+  </si>
+  <si>
+    <t>993901-03595</t>
+  </si>
+  <si>
+    <t>VENUS WIRE INDUSTRIES PRIVATE LIMIT</t>
+  </si>
+  <si>
+    <t>VENUS WIRE INDUSTRIES PRIVATE LIMITED</t>
+  </si>
+  <si>
+    <t>002</t>
+  </si>
+  <si>
+    <t>9903.82.02,7223.00.1061</t>
+  </si>
+  <si>
+    <t>2565484</t>
+  </si>
+  <si>
+    <t>EF4-0231173-4</t>
+  </si>
+  <si>
+    <t>9903.82.05,8431.20.0000</t>
+  </si>
+  <si>
+    <t>MALLAGHAN (GA) INC.</t>
+  </si>
+  <si>
+    <t>MALGA01</t>
+  </si>
+  <si>
+    <t>36-488102800</t>
+  </si>
+  <si>
+    <t>MALLAGHAN ENGINEERING  LTD</t>
+  </si>
+  <si>
+    <t>2565541</t>
+  </si>
+  <si>
+    <t>EF4-0231354-0</t>
+  </si>
+  <si>
+    <t/>
   </si>
   <si>
     <t>9903.03.01</t>
   </si>
   <si>
-    <t/>
-  </si>
-  <si>
-    <t>001</t>
-  </si>
-  <si>
-    <t>3505.10.0092</t>
+    <t>SECTION 122 - 10% DUTY</t>
+  </si>
+  <si>
+    <t>1109.00.9020</t>
   </si>
   <si>
     <t>ROYAL INGREDIENTS GROUP BV</t>
@@ -99,13 +159,118 @@
     <t>074601-00962</t>
   </si>
   <si>
-    <t>SANGUAN WONGSE STARCH CO., LTD.</t>
-  </si>
-  <si>
-    <t>2565387</t>
-  </si>
-  <si>
-    <t>EF4-0230978-7</t>
+    <t>TEREOS SYRAL S.A.S</t>
+  </si>
+  <si>
+    <t>2565537</t>
+  </si>
+  <si>
+    <t>EF4-0231383-9</t>
+  </si>
+  <si>
+    <t>9903.82.10,8428.39.0000</t>
+  </si>
+  <si>
+    <t>AUMUND CORPORATION</t>
+  </si>
+  <si>
+    <t>AUMCOR</t>
+  </si>
+  <si>
+    <t>58-138896800</t>
+  </si>
+  <si>
+    <t>SCHADE LAGERTECHNIK GMBH</t>
+  </si>
+  <si>
+    <t>9903.82.10,8431.39.0010</t>
+  </si>
+  <si>
+    <t>2565538</t>
+  </si>
+  <si>
+    <t>EF4-0231384-7</t>
+  </si>
+  <si>
+    <t>2565699</t>
+  </si>
+  <si>
+    <t>EF4-0231438-1</t>
+  </si>
+  <si>
+    <t>2565611</t>
+  </si>
+  <si>
+    <t>EF4-0231497-7</t>
+  </si>
+  <si>
+    <t>9903.82.02,7216.33.0090</t>
+  </si>
+  <si>
+    <t>MAHA USA LLC</t>
+  </si>
+  <si>
+    <t>MAHUSA</t>
+  </si>
+  <si>
+    <t>52-213556300</t>
+  </si>
+  <si>
+    <t>THYSSENKRUPP SCHULTE GMBH</t>
+  </si>
+  <si>
+    <t>9903.91.01</t>
+  </si>
+  <si>
+    <t>ARTS, PRDS OF CN SUB(B)US NT31</t>
+  </si>
+  <si>
+    <t>9903.03.06,9903.82.02,7228.30.6000</t>
+  </si>
+  <si>
+    <t>003</t>
+  </si>
+  <si>
+    <t>004</t>
+  </si>
+  <si>
+    <t>9903.82.02,7215.50.0016</t>
+  </si>
+  <si>
+    <t>2565598</t>
+  </si>
+  <si>
+    <t>EF4-0231674-1</t>
+  </si>
+  <si>
+    <t>ROQUETTE FRERES</t>
+  </si>
+  <si>
+    <t>2565704</t>
+  </si>
+  <si>
+    <t>EF4-0231684-0</t>
+  </si>
+  <si>
+    <t>4811.59.4040</t>
+  </si>
+  <si>
+    <t>BAUSCHLINNEMANN NORTH AMERICA</t>
+  </si>
+  <si>
+    <t>BAULIN</t>
+  </si>
+  <si>
+    <t>56-193913400</t>
+  </si>
+  <si>
+    <t>SURTECO GMBH</t>
+  </si>
+  <si>
+    <t>2565810</t>
+  </si>
+  <si>
+    <t>EF4-0231696-4</t>
   </si>
   <si>
     <t>9903.88.15</t>
@@ -114,52 +279,34 @@
     <t>ARTICLE OF CHINA,US NTE 20(R)</t>
   </si>
   <si>
-    <t>9903.03.06,9903.82.09,8302.42.3015</t>
-  </si>
-  <si>
-    <t>GRASS AMERICA INC</t>
-  </si>
-  <si>
-    <t>GRAAME</t>
-  </si>
-  <si>
-    <t>51-066023000</t>
-  </si>
-  <si>
-    <t>HANSTAR HARDWARE INTERNATIONAL LIMI</t>
-  </si>
-  <si>
-    <t>2565619</t>
-  </si>
-  <si>
-    <t>EF4-0231334-2</t>
-  </si>
-  <si>
-    <t>SECTION 122 - 10% DUTY</t>
-  </si>
-  <si>
-    <t>7019.90.1100</t>
-  </si>
-  <si>
-    <t>TRENCHLESS PRODUCTS</t>
-  </si>
-  <si>
-    <t>TREPRO01</t>
-  </si>
-  <si>
-    <t>83-157973900</t>
-  </si>
-  <si>
-    <t>LATERAL REPAIRS UAB</t>
-  </si>
-  <si>
-    <t>2565655</t>
-  </si>
-  <si>
-    <t>EF4-0231436-5</t>
-  </si>
-  <si>
-    <t>1109.00.9020</t>
+    <t>9903.03.06,9903.82.09,8302.42.3065</t>
+  </si>
+  <si>
+    <t>VISUAL CREATIONS, INC.</t>
+  </si>
+  <si>
+    <t>VISCRE</t>
+  </si>
+  <si>
+    <t>20-461602300</t>
+  </si>
+  <si>
+    <t>FUJIAN ANTAI NEW ENERGY TECH CO LTD</t>
+  </si>
+  <si>
+    <t>9903.88.03</t>
+  </si>
+  <si>
+    <t>ARTICLE OF CHINA,US NTE 20(F)</t>
+  </si>
+  <si>
+    <t>9903.03.01,9403.20.0075</t>
+  </si>
+  <si>
+    <t>2565889</t>
+  </si>
+  <si>
+    <t>EF4-0231848-1</t>
   </si>
   <si>
     <t>JACKERING MUHLEN UND NAHRMITTELWERK</t>
@@ -168,112 +315,28 @@
     <t>JACKERING MUHLEN UND NAHRMITTELWERKE GMBH</t>
   </si>
   <si>
-    <t>2565611</t>
-  </si>
-  <si>
-    <t>EF4-0231497-7</t>
-  </si>
-  <si>
-    <t>9903.03.06</t>
-  </si>
-  <si>
-    <t>S122 EXCL,IRN/STL/ALUM,DERIV</t>
-  </si>
-  <si>
-    <t>9903.82.02,7216.33.0090</t>
-  </si>
-  <si>
-    <t>MAHA USA LLC</t>
-  </si>
-  <si>
-    <t>MAHUSA</t>
-  </si>
-  <si>
-    <t>52-213556300</t>
-  </si>
-  <si>
-    <t>THYSSENKRUPP SCHULTE GMBH</t>
-  </si>
-  <si>
-    <t>9903.91.01</t>
-  </si>
-  <si>
-    <t>ARTS, PRDS OF CN SUB(B)US NT31</t>
-  </si>
-  <si>
-    <t>002</t>
-  </si>
-  <si>
-    <t>9903.03.06,9903.82.02,7228.30.6000</t>
-  </si>
-  <si>
-    <t>003</t>
-  </si>
-  <si>
-    <t>004</t>
-  </si>
-  <si>
-    <t>9903.82.02,7215.50.0016</t>
-  </si>
-  <si>
-    <t>2565713</t>
-  </si>
-  <si>
-    <t>EF4-0231526-3</t>
-  </si>
-  <si>
-    <t>LANTMANNEN BIOREFINERIES AB</t>
-  </si>
-  <si>
-    <t>2565610</t>
-  </si>
-  <si>
-    <t>EF4-0231533-9</t>
-  </si>
-  <si>
-    <t>V0710314381</t>
-  </si>
-  <si>
-    <t>9903.82.02,7223.00.1061</t>
-  </si>
-  <si>
-    <t>VENUS WIRE INDUSTRIES PRIVATE LTD</t>
-  </si>
-  <si>
-    <t>VENWIR</t>
-  </si>
-  <si>
-    <t>993901-03595</t>
-  </si>
-  <si>
-    <t>VENUS WIRE INDUSTRIES PRIVATE LIMIT</t>
-  </si>
-  <si>
-    <t>VENUS WIRE INDUSTRIES PRIVATE LIMITED</t>
-  </si>
-  <si>
-    <t>2565822</t>
-  </si>
-  <si>
-    <t>EF4-0231589-1</t>
-  </si>
-  <si>
-    <t>3923.90.0080</t>
-  </si>
-  <si>
-    <t>DOBLA USA MFG LLC</t>
-  </si>
-  <si>
-    <t>DOBUSA</t>
-  </si>
-  <si>
-    <t>41-218954800</t>
-  </si>
-  <si>
-    <t>DOBLA LOGISTICS BVBA</t>
-  </si>
-  <si>
-    <t>1806.90.9090</t>
+    <t>2565928</t>
+  </si>
+  <si>
+    <t>EF4-0231894-5</t>
+  </si>
+  <si>
+    <t>3209.90.0000</t>
+  </si>
+  <si>
+    <t>MANKIEWICZ COATINGS, LLC</t>
+  </si>
+  <si>
+    <t>MANCOAT</t>
+  </si>
+  <si>
+    <t>56-202308900</t>
+  </si>
+  <si>
+    <t>FINALIN GMBH</t>
+  </si>
+  <si>
+    <t>3208.10.0000</t>
   </si>
   <si>
     <t>005</t>
@@ -282,70 +345,286 @@
     <t>006</t>
   </si>
   <si>
-    <t>DOBLA BELGIUM PRODUCTIONS NV/SA</t>
-  </si>
-  <si>
-    <t>2565720</t>
-  </si>
-  <si>
-    <t>EF4-0231593-3</t>
-  </si>
-  <si>
-    <t>1108.13.0010</t>
-  </si>
-  <si>
-    <t>AKV LANGHOLT AMBA</t>
-  </si>
-  <si>
-    <t>2565743</t>
-  </si>
-  <si>
-    <t>EF4-0231635-2</t>
-  </si>
-  <si>
-    <t>V8N61685510</t>
-  </si>
-  <si>
-    <t>1108.12.0010</t>
-  </si>
-  <si>
-    <t>TAT NISASTA INS SAN TIC AS</t>
-  </si>
-  <si>
-    <t>2565748</t>
-  </si>
-  <si>
-    <t>EF4-0231636-0</t>
-  </si>
-  <si>
-    <t>2565745</t>
-  </si>
-  <si>
-    <t>EF4-0231754-1</t>
-  </si>
-  <si>
-    <t>V1626447273</t>
-  </si>
-  <si>
-    <t>1108.11.0010</t>
-  </si>
-  <si>
-    <t>KROENER-STARKE BIO GMBH</t>
-  </si>
-  <si>
-    <t>2565747</t>
-  </si>
-  <si>
-    <t>EF4-0231756-6</t>
-  </si>
-  <si>
-    <t>2565817</t>
-  </si>
-  <si>
-    <t>EF4-0231758-2</t>
-  </si>
-  <si>
-    <t>1109.00.9010</t>
+    <t>007</t>
+  </si>
+  <si>
+    <t>008</t>
+  </si>
+  <si>
+    <t>009</t>
+  </si>
+  <si>
+    <t>3208.20.0000</t>
+  </si>
+  <si>
+    <t>010</t>
+  </si>
+  <si>
+    <t>011</t>
+  </si>
+  <si>
+    <t>012</t>
+  </si>
+  <si>
+    <t>013</t>
+  </si>
+  <si>
+    <t>NORIX LACKFABRIK GMBH</t>
+  </si>
+  <si>
+    <t>9903.03.03</t>
+  </si>
+  <si>
+    <t>S122 -EXCLUSION-EXEMPTED PRDTS</t>
+  </si>
+  <si>
+    <t>014</t>
+  </si>
+  <si>
+    <t>3911.90.2500</t>
+  </si>
+  <si>
+    <t>015</t>
+  </si>
+  <si>
+    <t>3208.90.0000</t>
+  </si>
+  <si>
+    <t>016</t>
+  </si>
+  <si>
+    <t>017</t>
+  </si>
+  <si>
+    <t>2565929</t>
+  </si>
+  <si>
+    <t>EF4-0231895-2</t>
+  </si>
+  <si>
+    <t>3209.10.0000</t>
+  </si>
+  <si>
+    <t>3814.00.1000</t>
+  </si>
+  <si>
+    <t>018</t>
+  </si>
+  <si>
+    <t>019</t>
+  </si>
+  <si>
+    <t>020</t>
+  </si>
+  <si>
+    <t>021</t>
+  </si>
+  <si>
+    <t>022</t>
+  </si>
+  <si>
+    <t>023</t>
+  </si>
+  <si>
+    <t>024</t>
+  </si>
+  <si>
+    <t>025</t>
+  </si>
+  <si>
+    <t>026</t>
+  </si>
+  <si>
+    <t>027</t>
+  </si>
+  <si>
+    <t>028</t>
+  </si>
+  <si>
+    <t>029</t>
+  </si>
+  <si>
+    <t>030</t>
+  </si>
+  <si>
+    <t>031</t>
+  </si>
+  <si>
+    <t>032</t>
+  </si>
+  <si>
+    <t>033</t>
+  </si>
+  <si>
+    <t>034</t>
+  </si>
+  <si>
+    <t>035</t>
+  </si>
+  <si>
+    <t>036</t>
+  </si>
+  <si>
+    <t>037</t>
+  </si>
+  <si>
+    <t>038</t>
+  </si>
+  <si>
+    <t>039</t>
+  </si>
+  <si>
+    <t>040</t>
+  </si>
+  <si>
+    <t>041</t>
+  </si>
+  <si>
+    <t>042</t>
+  </si>
+  <si>
+    <t>043</t>
+  </si>
+  <si>
+    <t>044</t>
+  </si>
+  <si>
+    <t>045</t>
+  </si>
+  <si>
+    <t>046</t>
+  </si>
+  <si>
+    <t>047</t>
+  </si>
+  <si>
+    <t>2818.30.0000</t>
+  </si>
+  <si>
+    <t>048</t>
+  </si>
+  <si>
+    <t>9903.82.02,7310.29.0055</t>
+  </si>
+  <si>
+    <t>049</t>
+  </si>
+  <si>
+    <t>3815.90.1000</t>
+  </si>
+  <si>
+    <t>050</t>
+  </si>
+  <si>
+    <t>051</t>
+  </si>
+  <si>
+    <t>052</t>
+  </si>
+  <si>
+    <t>RUDT INDUSTRIELACKE GMBH</t>
+  </si>
+  <si>
+    <t>053</t>
+  </si>
+  <si>
+    <t>054</t>
+  </si>
+  <si>
+    <t>055</t>
+  </si>
+  <si>
+    <t>056</t>
+  </si>
+  <si>
+    <t>057</t>
+  </si>
+  <si>
+    <t>058</t>
+  </si>
+  <si>
+    <t>059</t>
+  </si>
+  <si>
+    <t>060</t>
+  </si>
+  <si>
+    <t>2615719</t>
+  </si>
+  <si>
+    <t>EF4-0231934-9</t>
+  </si>
+  <si>
+    <t>Vessel, Non-container</t>
+  </si>
+  <si>
+    <t>8412.80.1000</t>
+  </si>
+  <si>
+    <t>BORGERS USA CORP</t>
+  </si>
+  <si>
+    <t>BORUSA</t>
+  </si>
+  <si>
+    <t>65-117296500</t>
+  </si>
+  <si>
+    <t>FKT GMBH</t>
+  </si>
+  <si>
+    <t>9903.82.10,8479.90.9596</t>
+  </si>
+  <si>
+    <t>4539240</t>
+  </si>
+  <si>
+    <t>EF4-0231998-4</t>
+  </si>
+  <si>
+    <t>Air, Non-container</t>
+  </si>
+  <si>
+    <t>00645299446</t>
+  </si>
+  <si>
+    <t>9403.20.0090</t>
+  </si>
+  <si>
+    <t>LIVE! CLOTHING LLC</t>
+  </si>
+  <si>
+    <t>LIVCLO01</t>
+  </si>
+  <si>
+    <t>37-177553300</t>
+  </si>
+  <si>
+    <t>QUANTRA INDUSTRIA DE MOVIES LTDA</t>
+  </si>
+  <si>
+    <t>9903.76.04,9403.60.8093</t>
+  </si>
+  <si>
+    <t>4539337</t>
+  </si>
+  <si>
+    <t>EF4-0232027-1</t>
+  </si>
+  <si>
+    <t>8208.90.6000</t>
+  </si>
+  <si>
+    <t>CB MANUFACTURING &amp; SALES CO INC</t>
+  </si>
+  <si>
+    <t>CBMAN01</t>
+  </si>
+  <si>
+    <t>34-101525000</t>
+  </si>
+  <si>
+    <t>EXTRA SHARP TOOL &amp; KNIVES</t>
   </si>
 </sst>
 </file>
@@ -1290,7 +1569,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:Q23"/>
+  <dimension ref="A1:Q102"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="23.7109375" customWidth="true"/>
@@ -1403,27 +1682,27 @@
         <v>27</v>
       </c>
       <c r="M2" s="45">
-        <v>46159</v>
+        <v>46167</v>
       </c>
       <c r="N2" s="46">
-        <v>46166</v>
+        <v>46168</v>
       </c>
       <c r="O2" s="47" t="s">
         <v>28</v>
       </c>
       <c r="P2" s="48" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="Q2" s="49">
-        <v>46115</v>
+        <v>46109</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="33" t="s">
-        <v>29</v>
+        <v>17</v>
       </c>
       <c r="B3" s="34" t="s">
-        <v>30</v>
+        <v>18</v>
       </c>
       <c r="C3" s="35" t="s">
         <v>19</v>
@@ -1432,63 +1711,63 @@
         <v>20</v>
       </c>
       <c r="E3" s="37" t="s">
+        <v>21</v>
+      </c>
+      <c r="F3" s="38" t="s">
+        <v>22</v>
+      </c>
+      <c r="G3" s="39" t="s">
+        <v>30</v>
+      </c>
+      <c r="H3" s="40" t="s">
+        <v>21</v>
+      </c>
+      <c r="I3" s="41" t="s">
         <v>31</v>
       </c>
-      <c r="F3" s="38" t="s">
-        <v>32</v>
-      </c>
-      <c r="G3" s="39" t="s">
-        <v>23</v>
-      </c>
-      <c r="H3" s="40" t="s">
-        <v>31</v>
-      </c>
-      <c r="I3" s="41" t="s">
-        <v>33</v>
-      </c>
       <c r="J3" s="42" t="s">
-        <v>34</v>
+        <v>25</v>
       </c>
       <c r="K3" s="43" t="s">
-        <v>35</v>
+        <v>26</v>
       </c>
       <c r="L3" s="44" t="s">
-        <v>36</v>
+        <v>27</v>
       </c>
       <c r="M3" s="45">
-        <v>46164</v>
+        <v>46167</v>
       </c>
       <c r="N3" s="46">
-        <v>46166</v>
+        <v>46168</v>
       </c>
       <c r="O3" s="47" t="s">
-        <v>37</v>
+        <v>28</v>
       </c>
       <c r="P3" s="48" t="s">
-        <v>37</v>
+        <v>29</v>
       </c>
       <c r="Q3" s="49">
-        <v>46119</v>
+        <v>46109</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="33" t="s">
-        <v>38</v>
+        <v>32</v>
       </c>
       <c r="B4" s="34" t="s">
-        <v>39</v>
+        <v>33</v>
       </c>
       <c r="C4" s="35" t="s">
         <v>19</v>
       </c>
       <c r="D4" s="36" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="E4" s="37" t="s">
         <v>21</v>
       </c>
       <c r="F4" s="38" t="s">
-        <v>40</v>
+        <v>22</v>
       </c>
       <c r="G4" s="39" t="s">
         <v>23</v>
@@ -1497,422 +1776,422 @@
         <v>21</v>
       </c>
       <c r="I4" s="41" t="s">
-        <v>41</v>
+        <v>34</v>
       </c>
       <c r="J4" s="42" t="s">
-        <v>42</v>
+        <v>35</v>
       </c>
       <c r="K4" s="43" t="s">
-        <v>43</v>
+        <v>36</v>
       </c>
       <c r="L4" s="44" t="s">
-        <v>44</v>
+        <v>37</v>
       </c>
       <c r="M4" s="45">
-        <v>46166</v>
+        <v>46168</v>
       </c>
       <c r="N4" s="46">
-        <v>46166</v>
+        <v>46168</v>
       </c>
       <c r="O4" s="47" t="s">
-        <v>45</v>
+        <v>38</v>
       </c>
       <c r="P4" s="48" t="s">
-        <v>45</v>
+        <v>38</v>
       </c>
       <c r="Q4" s="49">
-        <v>46134</v>
+        <v>46127</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="33" t="s">
-        <v>46</v>
+        <v>32</v>
       </c>
       <c r="B5" s="34" t="s">
-        <v>47</v>
+        <v>33</v>
       </c>
       <c r="C5" s="35" t="s">
         <v>19</v>
       </c>
       <c r="D5" s="36" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="E5" s="37" t="s">
         <v>21</v>
       </c>
       <c r="F5" s="38" t="s">
-        <v>40</v>
+        <v>22</v>
       </c>
       <c r="G5" s="39" t="s">
-        <v>23</v>
+        <v>30</v>
       </c>
       <c r="H5" s="40" t="s">
         <v>21</v>
       </c>
       <c r="I5" s="41" t="s">
-        <v>48</v>
+        <v>34</v>
       </c>
       <c r="J5" s="42" t="s">
-        <v>25</v>
+        <v>35</v>
       </c>
       <c r="K5" s="43" t="s">
-        <v>26</v>
+        <v>36</v>
       </c>
       <c r="L5" s="44" t="s">
-        <v>27</v>
+        <v>37</v>
       </c>
       <c r="M5" s="45">
-        <v>46166</v>
+        <v>46168</v>
       </c>
       <c r="N5" s="46">
-        <v>46166</v>
+        <v>46168</v>
       </c>
       <c r="O5" s="47" t="s">
-        <v>49</v>
+        <v>38</v>
       </c>
       <c r="P5" s="48" t="s">
-        <v>50</v>
+        <v>38</v>
       </c>
       <c r="Q5" s="49">
-        <v>46140</v>
+        <v>46127</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="33" t="s">
-        <v>51</v>
+        <v>39</v>
       </c>
       <c r="B6" s="34" t="s">
-        <v>52</v>
+        <v>40</v>
       </c>
       <c r="C6" s="35" t="s">
         <v>19</v>
       </c>
       <c r="D6" s="36" t="s">
-        <v>22</v>
+        <v>41</v>
       </c>
       <c r="E6" s="37" t="s">
-        <v>53</v>
+        <v>42</v>
       </c>
       <c r="F6" s="38" t="s">
-        <v>54</v>
+        <v>43</v>
       </c>
       <c r="G6" s="39" t="s">
         <v>23</v>
       </c>
       <c r="H6" s="40" t="s">
-        <v>53</v>
+        <v>42</v>
       </c>
       <c r="I6" s="41" t="s">
-        <v>55</v>
+        <v>44</v>
       </c>
       <c r="J6" s="42" t="s">
-        <v>56</v>
+        <v>45</v>
       </c>
       <c r="K6" s="43" t="s">
-        <v>57</v>
+        <v>46</v>
       </c>
       <c r="L6" s="44" t="s">
-        <v>58</v>
+        <v>47</v>
       </c>
       <c r="M6" s="45">
-        <v>46166</v>
+        <v>46168</v>
       </c>
       <c r="N6" s="46">
-        <v>46166</v>
+        <v>46168</v>
       </c>
       <c r="O6" s="47" t="s">
-        <v>59</v>
+        <v>48</v>
       </c>
       <c r="P6" s="48" t="s">
-        <v>59</v>
+        <v>48</v>
       </c>
       <c r="Q6" s="49">
-        <v>46141</v>
+        <v>46132</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="33" t="s">
+        <v>49</v>
+      </c>
+      <c r="B7" s="34" t="s">
+        <v>50</v>
+      </c>
+      <c r="C7" s="35" t="s">
+        <v>19</v>
+      </c>
+      <c r="D7" s="36" t="s">
+        <v>41</v>
+      </c>
+      <c r="E7" s="37" t="s">
+        <v>21</v>
+      </c>
+      <c r="F7" s="38" t="s">
+        <v>22</v>
+      </c>
+      <c r="G7" s="39" t="s">
+        <v>23</v>
+      </c>
+      <c r="H7" s="40" t="s">
+        <v>21</v>
+      </c>
+      <c r="I7" s="41" t="s">
         <v>51</v>
       </c>
-      <c r="B7" s="34" t="s">
+      <c r="J7" s="42" t="s">
         <v>52</v>
       </c>
-      <c r="C7" s="35" t="s">
-        <v>19</v>
-      </c>
-      <c r="D7" s="36" t="s">
-        <v>22</v>
-      </c>
-      <c r="E7" s="37" t="s">
-        <v>60</v>
-      </c>
-      <c r="F7" s="38" t="s">
-        <v>61</v>
-      </c>
-      <c r="G7" s="39" t="s">
-        <v>62</v>
-      </c>
-      <c r="H7" s="40" t="s">
-        <v>60</v>
-      </c>
-      <c r="I7" s="41" t="s">
-        <v>63</v>
-      </c>
-      <c r="J7" s="42" t="s">
-        <v>56</v>
-      </c>
       <c r="K7" s="43" t="s">
-        <v>57</v>
+        <v>53</v>
       </c>
       <c r="L7" s="44" t="s">
-        <v>58</v>
+        <v>54</v>
       </c>
       <c r="M7" s="45">
-        <v>46166</v>
+        <v>46165</v>
       </c>
       <c r="N7" s="46">
-        <v>46166</v>
+        <v>46168</v>
       </c>
       <c r="O7" s="47" t="s">
-        <v>59</v>
+        <v>55</v>
       </c>
       <c r="P7" s="48" t="s">
-        <v>59</v>
+        <v>55</v>
       </c>
       <c r="Q7" s="49">
-        <v>46141</v>
+        <v>46132</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="33" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="B8" s="34" t="s">
+        <v>50</v>
+      </c>
+      <c r="C8" s="35" t="s">
+        <v>19</v>
+      </c>
+      <c r="D8" s="36" t="s">
+        <v>41</v>
+      </c>
+      <c r="E8" s="37" t="s">
+        <v>21</v>
+      </c>
+      <c r="F8" s="38" t="s">
+        <v>22</v>
+      </c>
+      <c r="G8" s="39" t="s">
+        <v>30</v>
+      </c>
+      <c r="H8" s="40" t="s">
+        <v>21</v>
+      </c>
+      <c r="I8" s="41" t="s">
+        <v>56</v>
+      </c>
+      <c r="J8" s="42" t="s">
         <v>52</v>
       </c>
-      <c r="C8" s="35" t="s">
-        <v>19</v>
-      </c>
-      <c r="D8" s="36" t="s">
-        <v>22</v>
-      </c>
-      <c r="E8" s="37" t="s">
-        <v>60</v>
-      </c>
-      <c r="F8" s="38" t="s">
-        <v>61</v>
-      </c>
-      <c r="G8" s="39" t="s">
-        <v>64</v>
-      </c>
-      <c r="H8" s="40" t="s">
-        <v>60</v>
-      </c>
-      <c r="I8" s="41" t="s">
-        <v>63</v>
-      </c>
-      <c r="J8" s="42" t="s">
-        <v>56</v>
-      </c>
       <c r="K8" s="43" t="s">
-        <v>57</v>
+        <v>53</v>
       </c>
       <c r="L8" s="44" t="s">
-        <v>58</v>
+        <v>54</v>
       </c>
       <c r="M8" s="45">
-        <v>46166</v>
+        <v>46165</v>
       </c>
       <c r="N8" s="46">
-        <v>46166</v>
+        <v>46168</v>
       </c>
       <c r="O8" s="47" t="s">
-        <v>59</v>
+        <v>55</v>
       </c>
       <c r="P8" s="48" t="s">
-        <v>59</v>
+        <v>55</v>
       </c>
       <c r="Q8" s="49">
-        <v>46141</v>
+        <v>46132</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="33" t="s">
+        <v>57</v>
+      </c>
+      <c r="B9" s="34" t="s">
+        <v>58</v>
+      </c>
+      <c r="C9" s="35" t="s">
+        <v>19</v>
+      </c>
+      <c r="D9" s="36" t="s">
+        <v>41</v>
+      </c>
+      <c r="E9" s="37" t="s">
+        <v>21</v>
+      </c>
+      <c r="F9" s="38" t="s">
+        <v>22</v>
+      </c>
+      <c r="G9" s="39" t="s">
+        <v>23</v>
+      </c>
+      <c r="H9" s="40" t="s">
+        <v>21</v>
+      </c>
+      <c r="I9" s="41" t="s">
         <v>51</v>
       </c>
-      <c r="B9" s="34" t="s">
+      <c r="J9" s="42" t="s">
         <v>52</v>
       </c>
-      <c r="C9" s="35" t="s">
-        <v>19</v>
-      </c>
-      <c r="D9" s="36" t="s">
-        <v>22</v>
-      </c>
-      <c r="E9" s="37" t="s">
+      <c r="K9" s="43" t="s">
         <v>53</v>
       </c>
-      <c r="F9" s="38" t="s">
+      <c r="L9" s="44" t="s">
         <v>54</v>
       </c>
-      <c r="G9" s="39" t="s">
-        <v>65</v>
-      </c>
-      <c r="H9" s="40" t="s">
-        <v>53</v>
-      </c>
-      <c r="I9" s="41" t="s">
-        <v>66</v>
-      </c>
-      <c r="J9" s="42" t="s">
-        <v>56</v>
-      </c>
-      <c r="K9" s="43" t="s">
-        <v>57</v>
-      </c>
-      <c r="L9" s="44" t="s">
-        <v>58</v>
-      </c>
       <c r="M9" s="45">
-        <v>46166</v>
+        <v>46165</v>
       </c>
       <c r="N9" s="46">
-        <v>46166</v>
+        <v>46168</v>
       </c>
       <c r="O9" s="47" t="s">
-        <v>59</v>
+        <v>55</v>
       </c>
       <c r="P9" s="48" t="s">
-        <v>59</v>
+        <v>55</v>
       </c>
       <c r="Q9" s="49">
-        <v>46141</v>
+        <v>46132</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="33" t="s">
-        <v>67</v>
+        <v>57</v>
       </c>
       <c r="B10" s="34" t="s">
-        <v>68</v>
+        <v>58</v>
       </c>
       <c r="C10" s="35" t="s">
         <v>19</v>
       </c>
       <c r="D10" s="36" t="s">
-        <v>22</v>
+        <v>41</v>
       </c>
       <c r="E10" s="37" t="s">
         <v>21</v>
       </c>
       <c r="F10" s="38" t="s">
-        <v>40</v>
+        <v>22</v>
       </c>
       <c r="G10" s="39" t="s">
-        <v>23</v>
+        <v>30</v>
       </c>
       <c r="H10" s="40" t="s">
         <v>21</v>
       </c>
       <c r="I10" s="41" t="s">
-        <v>48</v>
+        <v>56</v>
       </c>
       <c r="J10" s="42" t="s">
-        <v>25</v>
+        <v>52</v>
       </c>
       <c r="K10" s="43" t="s">
-        <v>26</v>
+        <v>53</v>
       </c>
       <c r="L10" s="44" t="s">
-        <v>27</v>
+        <v>54</v>
       </c>
       <c r="M10" s="45">
-        <v>46166</v>
+        <v>46165</v>
       </c>
       <c r="N10" s="46">
-        <v>46166</v>
+        <v>46168</v>
       </c>
       <c r="O10" s="47" t="s">
-        <v>69</v>
+        <v>55</v>
       </c>
       <c r="P10" s="48" t="s">
-        <v>69</v>
+        <v>55</v>
       </c>
       <c r="Q10" s="49">
-        <v>46142</v>
+        <v>46132</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="33" t="s">
-        <v>70</v>
+        <v>59</v>
       </c>
       <c r="B11" s="34" t="s">
-        <v>71</v>
+        <v>60</v>
       </c>
       <c r="C11" s="35" t="s">
         <v>19</v>
       </c>
       <c r="D11" s="36" t="s">
-        <v>72</v>
+        <v>41</v>
       </c>
       <c r="E11" s="37" t="s">
-        <v>53</v>
+        <v>42</v>
       </c>
       <c r="F11" s="38" t="s">
-        <v>54</v>
+        <v>43</v>
       </c>
       <c r="G11" s="39" t="s">
         <v>23</v>
       </c>
       <c r="H11" s="40" t="s">
-        <v>53</v>
+        <v>42</v>
       </c>
       <c r="I11" s="41" t="s">
-        <v>73</v>
+        <v>44</v>
       </c>
       <c r="J11" s="42" t="s">
-        <v>74</v>
+        <v>45</v>
       </c>
       <c r="K11" s="43" t="s">
-        <v>75</v>
+        <v>46</v>
       </c>
       <c r="L11" s="44" t="s">
-        <v>76</v>
+        <v>47</v>
       </c>
       <c r="M11" s="45">
-        <v>46159</v>
+        <v>46166</v>
       </c>
       <c r="N11" s="46">
-        <v>46166</v>
+        <v>46168</v>
       </c>
       <c r="O11" s="47" t="s">
-        <v>77</v>
+        <v>48</v>
       </c>
       <c r="P11" s="48" t="s">
-        <v>78</v>
+        <v>48</v>
       </c>
       <c r="Q11" s="49">
-        <v>46132</v>
+        <v>46140</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="33" t="s">
-        <v>79</v>
+        <v>61</v>
       </c>
       <c r="B12" s="34" t="s">
-        <v>80</v>
+        <v>62</v>
       </c>
       <c r="C12" s="35" t="s">
         <v>19</v>
       </c>
       <c r="D12" s="36" t="s">
-        <v>72</v>
+        <v>41</v>
       </c>
       <c r="E12" s="37" t="s">
         <v>21</v>
       </c>
       <c r="F12" s="38" t="s">
-        <v>40</v>
+        <v>22</v>
       </c>
       <c r="G12" s="39" t="s">
         <v>23</v>
@@ -1921,28 +2200,28 @@
         <v>21</v>
       </c>
       <c r="I12" s="41" t="s">
-        <v>81</v>
+        <v>63</v>
       </c>
       <c r="J12" s="42" t="s">
-        <v>82</v>
+        <v>64</v>
       </c>
       <c r="K12" s="43" t="s">
-        <v>83</v>
+        <v>65</v>
       </c>
       <c r="L12" s="44" t="s">
-        <v>84</v>
+        <v>66</v>
       </c>
       <c r="M12" s="45">
         <v>46166</v>
       </c>
       <c r="N12" s="46">
-        <v>46166</v>
+        <v>46168</v>
       </c>
       <c r="O12" s="47" t="s">
-        <v>85</v>
+        <v>67</v>
       </c>
       <c r="P12" s="48" t="s">
-        <v>85</v>
+        <v>67</v>
       </c>
       <c r="Q12" s="49">
         <v>46141</v>
@@ -1950,52 +2229,52 @@
     </row>
     <row r="13">
       <c r="A13" s="33" t="s">
-        <v>79</v>
+        <v>61</v>
       </c>
       <c r="B13" s="34" t="s">
-        <v>80</v>
+        <v>62</v>
       </c>
       <c r="C13" s="35" t="s">
         <v>19</v>
       </c>
       <c r="D13" s="36" t="s">
-        <v>72</v>
+        <v>41</v>
       </c>
       <c r="E13" s="37" t="s">
-        <v>21</v>
+        <v>68</v>
       </c>
       <c r="F13" s="38" t="s">
-        <v>40</v>
+        <v>69</v>
       </c>
       <c r="G13" s="39" t="s">
-        <v>62</v>
+        <v>30</v>
       </c>
       <c r="H13" s="40" t="s">
-        <v>21</v>
+        <v>68</v>
       </c>
       <c r="I13" s="41" t="s">
-        <v>86</v>
+        <v>70</v>
       </c>
       <c r="J13" s="42" t="s">
-        <v>82</v>
+        <v>64</v>
       </c>
       <c r="K13" s="43" t="s">
-        <v>83</v>
+        <v>65</v>
       </c>
       <c r="L13" s="44" t="s">
-        <v>84</v>
+        <v>66</v>
       </c>
       <c r="M13" s="45">
         <v>46166</v>
       </c>
       <c r="N13" s="46">
-        <v>46166</v>
+        <v>46168</v>
       </c>
       <c r="O13" s="47" t="s">
-        <v>85</v>
+        <v>67</v>
       </c>
       <c r="P13" s="48" t="s">
-        <v>85</v>
+        <v>67</v>
       </c>
       <c r="Q13" s="49">
         <v>46141</v>
@@ -2003,52 +2282,52 @@
     </row>
     <row r="14">
       <c r="A14" s="33" t="s">
-        <v>79</v>
+        <v>61</v>
       </c>
       <c r="B14" s="34" t="s">
-        <v>80</v>
+        <v>62</v>
       </c>
       <c r="C14" s="35" t="s">
         <v>19</v>
       </c>
       <c r="D14" s="36" t="s">
-        <v>72</v>
+        <v>41</v>
       </c>
       <c r="E14" s="37" t="s">
-        <v>21</v>
+        <v>68</v>
       </c>
       <c r="F14" s="38" t="s">
-        <v>40</v>
+        <v>69</v>
       </c>
       <c r="G14" s="39" t="s">
+        <v>71</v>
+      </c>
+      <c r="H14" s="40" t="s">
+        <v>68</v>
+      </c>
+      <c r="I14" s="41" t="s">
+        <v>70</v>
+      </c>
+      <c r="J14" s="42" t="s">
         <v>64</v>
       </c>
-      <c r="H14" s="40" t="s">
-        <v>21</v>
-      </c>
-      <c r="I14" s="41" t="s">
-        <v>86</v>
-      </c>
-      <c r="J14" s="42" t="s">
-        <v>82</v>
-      </c>
       <c r="K14" s="43" t="s">
-        <v>83</v>
+        <v>65</v>
       </c>
       <c r="L14" s="44" t="s">
-        <v>84</v>
+        <v>66</v>
       </c>
       <c r="M14" s="45">
         <v>46166</v>
       </c>
       <c r="N14" s="46">
-        <v>46166</v>
+        <v>46168</v>
       </c>
       <c r="O14" s="47" t="s">
-        <v>85</v>
+        <v>67</v>
       </c>
       <c r="P14" s="48" t="s">
-        <v>85</v>
+        <v>67</v>
       </c>
       <c r="Q14" s="49">
         <v>46141</v>
@@ -2056,52 +2335,52 @@
     </row>
     <row r="15">
       <c r="A15" s="33" t="s">
-        <v>79</v>
+        <v>61</v>
       </c>
       <c r="B15" s="34" t="s">
-        <v>80</v>
+        <v>62</v>
       </c>
       <c r="C15" s="35" t="s">
         <v>19</v>
       </c>
       <c r="D15" s="36" t="s">
-        <v>72</v>
+        <v>41</v>
       </c>
       <c r="E15" s="37" t="s">
         <v>21</v>
       </c>
       <c r="F15" s="38" t="s">
-        <v>40</v>
+        <v>22</v>
       </c>
       <c r="G15" s="39" t="s">
-        <v>65</v>
+        <v>72</v>
       </c>
       <c r="H15" s="40" t="s">
         <v>21</v>
       </c>
       <c r="I15" s="41" t="s">
-        <v>86</v>
+        <v>73</v>
       </c>
       <c r="J15" s="42" t="s">
-        <v>82</v>
+        <v>64</v>
       </c>
       <c r="K15" s="43" t="s">
-        <v>83</v>
+        <v>65</v>
       </c>
       <c r="L15" s="44" t="s">
-        <v>84</v>
+        <v>66</v>
       </c>
       <c r="M15" s="45">
         <v>46166</v>
       </c>
       <c r="N15" s="46">
-        <v>46166</v>
+        <v>46168</v>
       </c>
       <c r="O15" s="47" t="s">
-        <v>85</v>
+        <v>67</v>
       </c>
       <c r="P15" s="48" t="s">
-        <v>85</v>
+        <v>67</v>
       </c>
       <c r="Q15" s="49">
         <v>46141</v>
@@ -2109,431 +2388,4618 @@
     </row>
     <row r="16">
       <c r="A16" s="33" t="s">
-        <v>79</v>
+        <v>74</v>
       </c>
       <c r="B16" s="34" t="s">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="C16" s="35" t="s">
         <v>19</v>
       </c>
       <c r="D16" s="36" t="s">
-        <v>72</v>
+        <v>41</v>
       </c>
       <c r="E16" s="37" t="s">
-        <v>21</v>
+        <v>42</v>
       </c>
       <c r="F16" s="38" t="s">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="G16" s="39" t="s">
-        <v>87</v>
+        <v>23</v>
       </c>
       <c r="H16" s="40" t="s">
-        <v>21</v>
+        <v>42</v>
       </c>
       <c r="I16" s="41" t="s">
-        <v>86</v>
+        <v>44</v>
       </c>
       <c r="J16" s="42" t="s">
-        <v>82</v>
+        <v>45</v>
       </c>
       <c r="K16" s="43" t="s">
-        <v>83</v>
+        <v>46</v>
       </c>
       <c r="L16" s="44" t="s">
-        <v>84</v>
+        <v>47</v>
       </c>
       <c r="M16" s="45">
         <v>46166</v>
       </c>
       <c r="N16" s="46">
-        <v>46166</v>
+        <v>46168</v>
       </c>
       <c r="O16" s="47" t="s">
-        <v>85</v>
+        <v>76</v>
       </c>
       <c r="P16" s="48" t="s">
-        <v>85</v>
+        <v>76</v>
       </c>
       <c r="Q16" s="49">
-        <v>46141</v>
+        <v>46137</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="33" t="s">
+        <v>77</v>
+      </c>
+      <c r="B17" s="34" t="s">
+        <v>78</v>
+      </c>
+      <c r="C17" s="35" t="s">
+        <v>19</v>
+      </c>
+      <c r="D17" s="36" t="s">
+        <v>41</v>
+      </c>
+      <c r="E17" s="37" t="s">
+        <v>42</v>
+      </c>
+      <c r="F17" s="38" t="s">
+        <v>43</v>
+      </c>
+      <c r="G17" s="39" t="s">
+        <v>23</v>
+      </c>
+      <c r="H17" s="40" t="s">
+        <v>42</v>
+      </c>
+      <c r="I17" s="41" t="s">
         <v>79</v>
       </c>
-      <c r="B17" s="34" t="s">
+      <c r="J17" s="42" t="s">
         <v>80</v>
       </c>
-      <c r="C17" s="35" t="s">
-        <v>19</v>
-      </c>
-      <c r="D17" s="36" t="s">
-        <v>72</v>
-      </c>
-      <c r="E17" s="37" t="s">
-        <v>21</v>
-      </c>
-      <c r="F17" s="38" t="s">
-        <v>40</v>
-      </c>
-      <c r="G17" s="39" t="s">
-        <v>88</v>
-      </c>
-      <c r="H17" s="40" t="s">
-        <v>21</v>
-      </c>
-      <c r="I17" s="41" t="s">
-        <v>86</v>
-      </c>
-      <c r="J17" s="42" t="s">
+      <c r="K17" s="43" t="s">
+        <v>81</v>
+      </c>
+      <c r="L17" s="44" t="s">
         <v>82</v>
       </c>
-      <c r="K17" s="43" t="s">
+      <c r="M17" s="45">
+        <v>46165</v>
+      </c>
+      <c r="N17" s="46">
+        <v>46168</v>
+      </c>
+      <c r="O17" s="47" t="s">
         <v>83</v>
       </c>
-      <c r="L17" s="44" t="s">
-        <v>84</v>
-      </c>
-      <c r="M17" s="45">
-        <v>46166</v>
-      </c>
-      <c r="N17" s="46">
-        <v>46166</v>
-      </c>
-      <c r="O17" s="47" t="s">
-        <v>89</v>
-      </c>
       <c r="P17" s="48" t="s">
-        <v>89</v>
+        <v>83</v>
       </c>
       <c r="Q17" s="49">
-        <v>46141</v>
+        <v>46148</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="33" t="s">
-        <v>90</v>
+        <v>84</v>
       </c>
       <c r="B18" s="34" t="s">
-        <v>91</v>
+        <v>85</v>
       </c>
       <c r="C18" s="35" t="s">
         <v>19</v>
       </c>
       <c r="D18" s="36" t="s">
-        <v>22</v>
+        <v>41</v>
       </c>
       <c r="E18" s="37" t="s">
-        <v>21</v>
+        <v>86</v>
       </c>
       <c r="F18" s="38" t="s">
-        <v>40</v>
+        <v>87</v>
       </c>
       <c r="G18" s="39" t="s">
         <v>23</v>
       </c>
       <c r="H18" s="40" t="s">
-        <v>21</v>
+        <v>86</v>
       </c>
       <c r="I18" s="41" t="s">
+        <v>88</v>
+      </c>
+      <c r="J18" s="42" t="s">
+        <v>89</v>
+      </c>
+      <c r="K18" s="43" t="s">
+        <v>90</v>
+      </c>
+      <c r="L18" s="44" t="s">
+        <v>91</v>
+      </c>
+      <c r="M18" s="45">
+        <v>46168</v>
+      </c>
+      <c r="N18" s="46">
+        <v>46168</v>
+      </c>
+      <c r="O18" s="47" t="s">
         <v>92</v>
       </c>
-      <c r="J18" s="42" t="s">
-        <v>25</v>
-      </c>
-      <c r="K18" s="43" t="s">
-        <v>26</v>
-      </c>
-      <c r="L18" s="44" t="s">
-        <v>27</v>
-      </c>
-      <c r="M18" s="45">
-        <v>46166</v>
-      </c>
-      <c r="N18" s="46">
-        <v>46166</v>
-      </c>
-      <c r="O18" s="47" t="s">
-        <v>93</v>
-      </c>
       <c r="P18" s="48" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="Q18" s="49">
-        <v>46146</v>
+        <v>46150</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="33" t="s">
+        <v>84</v>
+      </c>
+      <c r="B19" s="34" t="s">
+        <v>85</v>
+      </c>
+      <c r="C19" s="35" t="s">
+        <v>19</v>
+      </c>
+      <c r="D19" s="36" t="s">
+        <v>41</v>
+      </c>
+      <c r="E19" s="37" t="s">
+        <v>93</v>
+      </c>
+      <c r="F19" s="38" t="s">
         <v>94</v>
       </c>
-      <c r="B19" s="34" t="s">
+      <c r="G19" s="39" t="s">
+        <v>30</v>
+      </c>
+      <c r="H19" s="40" t="s">
+        <v>93</v>
+      </c>
+      <c r="I19" s="41" t="s">
         <v>95</v>
       </c>
-      <c r="C19" s="35" t="s">
-        <v>19</v>
-      </c>
-      <c r="D19" s="36" t="s">
-        <v>96</v>
-      </c>
-      <c r="E19" s="37" t="s">
-        <v>21</v>
-      </c>
-      <c r="F19" s="38" t="s">
-        <v>22</v>
-      </c>
-      <c r="G19" s="39" t="s">
-        <v>23</v>
-      </c>
-      <c r="H19" s="40" t="s">
-        <v>21</v>
-      </c>
-      <c r="I19" s="41" t="s">
-        <v>97</v>
-      </c>
       <c r="J19" s="42" t="s">
-        <v>25</v>
+        <v>89</v>
       </c>
       <c r="K19" s="43" t="s">
-        <v>26</v>
+        <v>90</v>
       </c>
       <c r="L19" s="44" t="s">
-        <v>27</v>
+        <v>91</v>
       </c>
       <c r="M19" s="45">
-        <v>46166</v>
+        <v>46168</v>
       </c>
       <c r="N19" s="46">
-        <v>46166</v>
+        <v>46168</v>
       </c>
       <c r="O19" s="47" t="s">
-        <v>98</v>
+        <v>92</v>
       </c>
       <c r="P19" s="48" t="s">
-        <v>98</v>
+        <v>92</v>
       </c>
       <c r="Q19" s="49">
-        <v>46144</v>
+        <v>46150</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="33" t="s">
-        <v>99</v>
+        <v>96</v>
       </c>
       <c r="B20" s="34" t="s">
-        <v>100</v>
+        <v>97</v>
       </c>
       <c r="C20" s="35" t="s">
         <v>19</v>
       </c>
       <c r="D20" s="36" t="s">
-        <v>96</v>
+        <v>41</v>
       </c>
       <c r="E20" s="37" t="s">
-        <v>21</v>
+        <v>42</v>
       </c>
       <c r="F20" s="38" t="s">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="G20" s="39" t="s">
         <v>23</v>
       </c>
       <c r="H20" s="40" t="s">
-        <v>21</v>
+        <v>42</v>
       </c>
       <c r="I20" s="41" t="s">
-        <v>92</v>
+        <v>44</v>
       </c>
       <c r="J20" s="42" t="s">
-        <v>25</v>
+        <v>45</v>
       </c>
       <c r="K20" s="43" t="s">
-        <v>26</v>
+        <v>46</v>
       </c>
       <c r="L20" s="44" t="s">
-        <v>27</v>
+        <v>47</v>
       </c>
       <c r="M20" s="45">
-        <v>46166</v>
+        <v>46168</v>
       </c>
       <c r="N20" s="46">
-        <v>46166</v>
+        <v>46168</v>
       </c>
       <c r="O20" s="47" t="s">
-        <v>93</v>
+        <v>98</v>
       </c>
       <c r="P20" s="48" t="s">
-        <v>93</v>
+        <v>99</v>
       </c>
       <c r="Q20" s="49">
-        <v>46146</v>
+        <v>46155</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="33" t="s">
+        <v>100</v>
+      </c>
+      <c r="B21" s="34" t="s">
         <v>101</v>
       </c>
-      <c r="B21" s="34" t="s">
-        <v>102</v>
-      </c>
       <c r="C21" s="35" t="s">
         <v>19</v>
       </c>
       <c r="D21" s="36" t="s">
-        <v>103</v>
+        <v>41</v>
       </c>
       <c r="E21" s="37" t="s">
-        <v>21</v>
+        <v>42</v>
       </c>
       <c r="F21" s="38" t="s">
-        <v>22</v>
+        <v>43</v>
       </c>
       <c r="G21" s="39" t="s">
         <v>23</v>
       </c>
       <c r="H21" s="40" t="s">
-        <v>21</v>
+        <v>42</v>
       </c>
       <c r="I21" s="41" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="J21" s="42" t="s">
-        <v>25</v>
+        <v>103</v>
       </c>
       <c r="K21" s="43" t="s">
-        <v>26</v>
+        <v>104</v>
       </c>
       <c r="L21" s="44" t="s">
-        <v>27</v>
+        <v>105</v>
       </c>
       <c r="M21" s="45">
-        <v>46166</v>
+        <v>46168</v>
       </c>
       <c r="N21" s="46">
-        <v>46166</v>
+        <v>46168</v>
       </c>
       <c r="O21" s="47" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="P21" s="48" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="Q21" s="49">
-        <v>46152</v>
+        <v>46158</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="33" t="s">
-        <v>106</v>
+        <v>100</v>
       </c>
       <c r="B22" s="34" t="s">
+        <v>101</v>
+      </c>
+      <c r="C22" s="35" t="s">
+        <v>19</v>
+      </c>
+      <c r="D22" s="36" t="s">
+        <v>41</v>
+      </c>
+      <c r="E22" s="37" t="s">
+        <v>42</v>
+      </c>
+      <c r="F22" s="38" t="s">
+        <v>43</v>
+      </c>
+      <c r="G22" s="39" t="s">
+        <v>30</v>
+      </c>
+      <c r="H22" s="40" t="s">
+        <v>42</v>
+      </c>
+      <c r="I22" s="41" t="s">
         <v>107</v>
       </c>
-      <c r="C22" s="35" t="s">
-        <v>19</v>
-      </c>
-      <c r="D22" s="36" t="s">
-        <v>103</v>
-      </c>
-      <c r="E22" s="37" t="s">
-        <v>21</v>
-      </c>
-      <c r="F22" s="38" t="s">
-        <v>22</v>
-      </c>
-      <c r="G22" s="39" t="s">
-        <v>23</v>
-      </c>
-      <c r="H22" s="40" t="s">
-        <v>21</v>
-      </c>
-      <c r="I22" s="41" t="s">
-        <v>104</v>
-      </c>
       <c r="J22" s="42" t="s">
-        <v>25</v>
+        <v>103</v>
       </c>
       <c r="K22" s="43" t="s">
-        <v>26</v>
+        <v>104</v>
       </c>
       <c r="L22" s="44" t="s">
-        <v>27</v>
+        <v>105</v>
       </c>
       <c r="M22" s="45">
-        <v>46166</v>
+        <v>46168</v>
       </c>
       <c r="N22" s="46">
-        <v>46166</v>
+        <v>46168</v>
       </c>
       <c r="O22" s="47" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="P22" s="48" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="Q22" s="49">
-        <v>46152</v>
+        <v>46158</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="33" t="s">
+        <v>100</v>
+      </c>
+      <c r="B23" s="34" t="s">
+        <v>101</v>
+      </c>
+      <c r="C23" s="35" t="s">
+        <v>19</v>
+      </c>
+      <c r="D23" s="36" t="s">
+        <v>41</v>
+      </c>
+      <c r="E23" s="37" t="s">
+        <v>42</v>
+      </c>
+      <c r="F23" s="38" t="s">
+        <v>43</v>
+      </c>
+      <c r="G23" s="39" t="s">
+        <v>71</v>
+      </c>
+      <c r="H23" s="40" t="s">
+        <v>42</v>
+      </c>
+      <c r="I23" s="41" t="s">
+        <v>107</v>
+      </c>
+      <c r="J23" s="42" t="s">
+        <v>103</v>
+      </c>
+      <c r="K23" s="43" t="s">
+        <v>104</v>
+      </c>
+      <c r="L23" s="44" t="s">
+        <v>105</v>
+      </c>
+      <c r="M23" s="45">
+        <v>46168</v>
+      </c>
+      <c r="N23" s="46">
+        <v>46168</v>
+      </c>
+      <c r="O23" s="47" t="s">
+        <v>106</v>
+      </c>
+      <c r="P23" s="48" t="s">
+        <v>106</v>
+      </c>
+      <c r="Q23" s="49">
+        <v>46158</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="33" t="s">
+        <v>100</v>
+      </c>
+      <c r="B24" s="34" t="s">
+        <v>101</v>
+      </c>
+      <c r="C24" s="35" t="s">
+        <v>19</v>
+      </c>
+      <c r="D24" s="36" t="s">
+        <v>41</v>
+      </c>
+      <c r="E24" s="37" t="s">
+        <v>42</v>
+      </c>
+      <c r="F24" s="38" t="s">
+        <v>43</v>
+      </c>
+      <c r="G24" s="39" t="s">
+        <v>72</v>
+      </c>
+      <c r="H24" s="40" t="s">
+        <v>42</v>
+      </c>
+      <c r="I24" s="41" t="s">
+        <v>102</v>
+      </c>
+      <c r="J24" s="42" t="s">
+        <v>103</v>
+      </c>
+      <c r="K24" s="43" t="s">
+        <v>104</v>
+      </c>
+      <c r="L24" s="44" t="s">
+        <v>105</v>
+      </c>
+      <c r="M24" s="45">
+        <v>46168</v>
+      </c>
+      <c r="N24" s="46">
+        <v>46168</v>
+      </c>
+      <c r="O24" s="47" t="s">
+        <v>106</v>
+      </c>
+      <c r="P24" s="48" t="s">
+        <v>106</v>
+      </c>
+      <c r="Q24" s="49">
+        <v>46158</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="33" t="s">
+        <v>100</v>
+      </c>
+      <c r="B25" s="34" t="s">
+        <v>101</v>
+      </c>
+      <c r="C25" s="35" t="s">
+        <v>19</v>
+      </c>
+      <c r="D25" s="36" t="s">
+        <v>41</v>
+      </c>
+      <c r="E25" s="37" t="s">
+        <v>42</v>
+      </c>
+      <c r="F25" s="38" t="s">
+        <v>43</v>
+      </c>
+      <c r="G25" s="39" t="s">
         <v>108</v>
       </c>
-      <c r="B23" s="34" t="s">
+      <c r="H25" s="40" t="s">
+        <v>42</v>
+      </c>
+      <c r="I25" s="41" t="s">
+        <v>102</v>
+      </c>
+      <c r="J25" s="42" t="s">
+        <v>103</v>
+      </c>
+      <c r="K25" s="43" t="s">
+        <v>104</v>
+      </c>
+      <c r="L25" s="44" t="s">
+        <v>105</v>
+      </c>
+      <c r="M25" s="45">
+        <v>46168</v>
+      </c>
+      <c r="N25" s="46">
+        <v>46168</v>
+      </c>
+      <c r="O25" s="47" t="s">
+        <v>106</v>
+      </c>
+      <c r="P25" s="48" t="s">
+        <v>106</v>
+      </c>
+      <c r="Q25" s="49">
+        <v>46158</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="33" t="s">
+        <v>100</v>
+      </c>
+      <c r="B26" s="34" t="s">
+        <v>101</v>
+      </c>
+      <c r="C26" s="35" t="s">
+        <v>19</v>
+      </c>
+      <c r="D26" s="36" t="s">
+        <v>41</v>
+      </c>
+      <c r="E26" s="37" t="s">
+        <v>42</v>
+      </c>
+      <c r="F26" s="38" t="s">
+        <v>43</v>
+      </c>
+      <c r="G26" s="39" t="s">
         <v>109</v>
       </c>
-      <c r="C23" s="35" t="s">
-        <v>19</v>
-      </c>
-      <c r="D23" s="36" t="s">
-        <v>103</v>
-      </c>
-      <c r="E23" s="37" t="s">
+      <c r="H26" s="40" t="s">
+        <v>42</v>
+      </c>
+      <c r="I26" s="41" t="s">
+        <v>102</v>
+      </c>
+      <c r="J26" s="42" t="s">
+        <v>103</v>
+      </c>
+      <c r="K26" s="43" t="s">
+        <v>104</v>
+      </c>
+      <c r="L26" s="44" t="s">
+        <v>105</v>
+      </c>
+      <c r="M26" s="45">
+        <v>46168</v>
+      </c>
+      <c r="N26" s="46">
+        <v>46168</v>
+      </c>
+      <c r="O26" s="47" t="s">
+        <v>106</v>
+      </c>
+      <c r="P26" s="48" t="s">
+        <v>106</v>
+      </c>
+      <c r="Q26" s="49">
+        <v>46158</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="33" t="s">
+        <v>100</v>
+      </c>
+      <c r="B27" s="34" t="s">
+        <v>101</v>
+      </c>
+      <c r="C27" s="35" t="s">
+        <v>19</v>
+      </c>
+      <c r="D27" s="36" t="s">
+        <v>41</v>
+      </c>
+      <c r="E27" s="37" t="s">
+        <v>42</v>
+      </c>
+      <c r="F27" s="38" t="s">
+        <v>43</v>
+      </c>
+      <c r="G27" s="39" t="s">
+        <v>110</v>
+      </c>
+      <c r="H27" s="40" t="s">
+        <v>42</v>
+      </c>
+      <c r="I27" s="41" t="s">
+        <v>107</v>
+      </c>
+      <c r="J27" s="42" t="s">
+        <v>103</v>
+      </c>
+      <c r="K27" s="43" t="s">
+        <v>104</v>
+      </c>
+      <c r="L27" s="44" t="s">
+        <v>105</v>
+      </c>
+      <c r="M27" s="45">
+        <v>46168</v>
+      </c>
+      <c r="N27" s="46">
+        <v>46168</v>
+      </c>
+      <c r="O27" s="47" t="s">
+        <v>106</v>
+      </c>
+      <c r="P27" s="48" t="s">
+        <v>106</v>
+      </c>
+      <c r="Q27" s="49">
+        <v>46158</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="33" t="s">
+        <v>100</v>
+      </c>
+      <c r="B28" s="34" t="s">
+        <v>101</v>
+      </c>
+      <c r="C28" s="35" t="s">
+        <v>19</v>
+      </c>
+      <c r="D28" s="36" t="s">
+        <v>41</v>
+      </c>
+      <c r="E28" s="37" t="s">
+        <v>42</v>
+      </c>
+      <c r="F28" s="38" t="s">
+        <v>43</v>
+      </c>
+      <c r="G28" s="39" t="s">
+        <v>111</v>
+      </c>
+      <c r="H28" s="40" t="s">
+        <v>42</v>
+      </c>
+      <c r="I28" s="41" t="s">
+        <v>107</v>
+      </c>
+      <c r="J28" s="42" t="s">
+        <v>103</v>
+      </c>
+      <c r="K28" s="43" t="s">
+        <v>104</v>
+      </c>
+      <c r="L28" s="44" t="s">
+        <v>105</v>
+      </c>
+      <c r="M28" s="45">
+        <v>46168</v>
+      </c>
+      <c r="N28" s="46">
+        <v>46168</v>
+      </c>
+      <c r="O28" s="47" t="s">
+        <v>106</v>
+      </c>
+      <c r="P28" s="48" t="s">
+        <v>106</v>
+      </c>
+      <c r="Q28" s="49">
+        <v>46158</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="33" t="s">
+        <v>100</v>
+      </c>
+      <c r="B29" s="34" t="s">
+        <v>101</v>
+      </c>
+      <c r="C29" s="35" t="s">
+        <v>19</v>
+      </c>
+      <c r="D29" s="36" t="s">
+        <v>41</v>
+      </c>
+      <c r="E29" s="37" t="s">
+        <v>42</v>
+      </c>
+      <c r="F29" s="38" t="s">
+        <v>43</v>
+      </c>
+      <c r="G29" s="39" t="s">
+        <v>112</v>
+      </c>
+      <c r="H29" s="40" t="s">
+        <v>42</v>
+      </c>
+      <c r="I29" s="41" t="s">
+        <v>113</v>
+      </c>
+      <c r="J29" s="42" t="s">
+        <v>103</v>
+      </c>
+      <c r="K29" s="43" t="s">
+        <v>104</v>
+      </c>
+      <c r="L29" s="44" t="s">
+        <v>105</v>
+      </c>
+      <c r="M29" s="45">
+        <v>46168</v>
+      </c>
+      <c r="N29" s="46">
+        <v>46168</v>
+      </c>
+      <c r="O29" s="47" t="s">
+        <v>106</v>
+      </c>
+      <c r="P29" s="48" t="s">
+        <v>106</v>
+      </c>
+      <c r="Q29" s="49">
+        <v>46158</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="33" t="s">
+        <v>100</v>
+      </c>
+      <c r="B30" s="34" t="s">
+        <v>101</v>
+      </c>
+      <c r="C30" s="35" t="s">
+        <v>19</v>
+      </c>
+      <c r="D30" s="36" t="s">
+        <v>41</v>
+      </c>
+      <c r="E30" s="37" t="s">
+        <v>42</v>
+      </c>
+      <c r="F30" s="38" t="s">
+        <v>43</v>
+      </c>
+      <c r="G30" s="39" t="s">
+        <v>114</v>
+      </c>
+      <c r="H30" s="40" t="s">
+        <v>42</v>
+      </c>
+      <c r="I30" s="41" t="s">
+        <v>113</v>
+      </c>
+      <c r="J30" s="42" t="s">
+        <v>103</v>
+      </c>
+      <c r="K30" s="43" t="s">
+        <v>104</v>
+      </c>
+      <c r="L30" s="44" t="s">
+        <v>105</v>
+      </c>
+      <c r="M30" s="45">
+        <v>46168</v>
+      </c>
+      <c r="N30" s="46">
+        <v>46168</v>
+      </c>
+      <c r="O30" s="47" t="s">
+        <v>106</v>
+      </c>
+      <c r="P30" s="48" t="s">
+        <v>106</v>
+      </c>
+      <c r="Q30" s="49">
+        <v>46158</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="33" t="s">
+        <v>100</v>
+      </c>
+      <c r="B31" s="34" t="s">
+        <v>101</v>
+      </c>
+      <c r="C31" s="35" t="s">
+        <v>19</v>
+      </c>
+      <c r="D31" s="36" t="s">
+        <v>41</v>
+      </c>
+      <c r="E31" s="37" t="s">
+        <v>42</v>
+      </c>
+      <c r="F31" s="38" t="s">
+        <v>43</v>
+      </c>
+      <c r="G31" s="39" t="s">
+        <v>115</v>
+      </c>
+      <c r="H31" s="40" t="s">
+        <v>42</v>
+      </c>
+      <c r="I31" s="41" t="s">
+        <v>107</v>
+      </c>
+      <c r="J31" s="42" t="s">
+        <v>103</v>
+      </c>
+      <c r="K31" s="43" t="s">
+        <v>104</v>
+      </c>
+      <c r="L31" s="44" t="s">
+        <v>105</v>
+      </c>
+      <c r="M31" s="45">
+        <v>46168</v>
+      </c>
+      <c r="N31" s="46">
+        <v>46168</v>
+      </c>
+      <c r="O31" s="47" t="s">
+        <v>106</v>
+      </c>
+      <c r="P31" s="48" t="s">
+        <v>106</v>
+      </c>
+      <c r="Q31" s="49">
+        <v>46158</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="33" t="s">
+        <v>100</v>
+      </c>
+      <c r="B32" s="34" t="s">
+        <v>101</v>
+      </c>
+      <c r="C32" s="35" t="s">
+        <v>19</v>
+      </c>
+      <c r="D32" s="36" t="s">
+        <v>41</v>
+      </c>
+      <c r="E32" s="37" t="s">
+        <v>42</v>
+      </c>
+      <c r="F32" s="38" t="s">
+        <v>43</v>
+      </c>
+      <c r="G32" s="39" t="s">
+        <v>116</v>
+      </c>
+      <c r="H32" s="40" t="s">
+        <v>42</v>
+      </c>
+      <c r="I32" s="41" t="s">
+        <v>107</v>
+      </c>
+      <c r="J32" s="42" t="s">
+        <v>103</v>
+      </c>
+      <c r="K32" s="43" t="s">
+        <v>104</v>
+      </c>
+      <c r="L32" s="44" t="s">
+        <v>105</v>
+      </c>
+      <c r="M32" s="45">
+        <v>46168</v>
+      </c>
+      <c r="N32" s="46">
+        <v>46168</v>
+      </c>
+      <c r="O32" s="47" t="s">
+        <v>106</v>
+      </c>
+      <c r="P32" s="48" t="s">
+        <v>106</v>
+      </c>
+      <c r="Q32" s="49">
+        <v>46158</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="33" t="s">
+        <v>100</v>
+      </c>
+      <c r="B33" s="34" t="s">
+        <v>101</v>
+      </c>
+      <c r="C33" s="35" t="s">
+        <v>19</v>
+      </c>
+      <c r="D33" s="36" t="s">
+        <v>41</v>
+      </c>
+      <c r="E33" s="37" t="s">
+        <v>42</v>
+      </c>
+      <c r="F33" s="38" t="s">
+        <v>43</v>
+      </c>
+      <c r="G33" s="39" t="s">
+        <v>117</v>
+      </c>
+      <c r="H33" s="40" t="s">
+        <v>42</v>
+      </c>
+      <c r="I33" s="41" t="s">
+        <v>102</v>
+      </c>
+      <c r="J33" s="42" t="s">
+        <v>103</v>
+      </c>
+      <c r="K33" s="43" t="s">
+        <v>104</v>
+      </c>
+      <c r="L33" s="44" t="s">
+        <v>105</v>
+      </c>
+      <c r="M33" s="45">
+        <v>46168</v>
+      </c>
+      <c r="N33" s="46">
+        <v>46168</v>
+      </c>
+      <c r="O33" s="47" t="s">
+        <v>118</v>
+      </c>
+      <c r="P33" s="48" t="s">
+        <v>118</v>
+      </c>
+      <c r="Q33" s="49">
+        <v>46158</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="33" t="s">
+        <v>100</v>
+      </c>
+      <c r="B34" s="34" t="s">
+        <v>101</v>
+      </c>
+      <c r="C34" s="35" t="s">
+        <v>19</v>
+      </c>
+      <c r="D34" s="36" t="s">
+        <v>41</v>
+      </c>
+      <c r="E34" s="37" t="s">
+        <v>119</v>
+      </c>
+      <c r="F34" s="38" t="s">
+        <v>120</v>
+      </c>
+      <c r="G34" s="39" t="s">
+        <v>121</v>
+      </c>
+      <c r="H34" s="40" t="s">
+        <v>119</v>
+      </c>
+      <c r="I34" s="41" t="s">
+        <v>122</v>
+      </c>
+      <c r="J34" s="42" t="s">
+        <v>103</v>
+      </c>
+      <c r="K34" s="43" t="s">
+        <v>104</v>
+      </c>
+      <c r="L34" s="44" t="s">
+        <v>105</v>
+      </c>
+      <c r="M34" s="45">
+        <v>46168</v>
+      </c>
+      <c r="N34" s="46">
+        <v>46168</v>
+      </c>
+      <c r="O34" s="47" t="s">
+        <v>118</v>
+      </c>
+      <c r="P34" s="48" t="s">
+        <v>118</v>
+      </c>
+      <c r="Q34" s="49">
+        <v>46158</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="33" t="s">
+        <v>100</v>
+      </c>
+      <c r="B35" s="34" t="s">
+        <v>101</v>
+      </c>
+      <c r="C35" s="35" t="s">
+        <v>19</v>
+      </c>
+      <c r="D35" s="36" t="s">
+        <v>41</v>
+      </c>
+      <c r="E35" s="37" t="s">
+        <v>42</v>
+      </c>
+      <c r="F35" s="38" t="s">
+        <v>43</v>
+      </c>
+      <c r="G35" s="39" t="s">
+        <v>123</v>
+      </c>
+      <c r="H35" s="40" t="s">
+        <v>42</v>
+      </c>
+      <c r="I35" s="41" t="s">
+        <v>124</v>
+      </c>
+      <c r="J35" s="42" t="s">
+        <v>103</v>
+      </c>
+      <c r="K35" s="43" t="s">
+        <v>104</v>
+      </c>
+      <c r="L35" s="44" t="s">
+        <v>105</v>
+      </c>
+      <c r="M35" s="45">
+        <v>46168</v>
+      </c>
+      <c r="N35" s="46">
+        <v>46168</v>
+      </c>
+      <c r="O35" s="47" t="s">
+        <v>118</v>
+      </c>
+      <c r="P35" s="48" t="s">
+        <v>118</v>
+      </c>
+      <c r="Q35" s="49">
+        <v>46158</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="33" t="s">
+        <v>100</v>
+      </c>
+      <c r="B36" s="34" t="s">
+        <v>101</v>
+      </c>
+      <c r="C36" s="35" t="s">
+        <v>19</v>
+      </c>
+      <c r="D36" s="36" t="s">
+        <v>41</v>
+      </c>
+      <c r="E36" s="37" t="s">
+        <v>42</v>
+      </c>
+      <c r="F36" s="38" t="s">
+        <v>43</v>
+      </c>
+      <c r="G36" s="39" t="s">
+        <v>125</v>
+      </c>
+      <c r="H36" s="40" t="s">
+        <v>42</v>
+      </c>
+      <c r="I36" s="41" t="s">
+        <v>102</v>
+      </c>
+      <c r="J36" s="42" t="s">
+        <v>103</v>
+      </c>
+      <c r="K36" s="43" t="s">
+        <v>104</v>
+      </c>
+      <c r="L36" s="44" t="s">
+        <v>105</v>
+      </c>
+      <c r="M36" s="45">
+        <v>46168</v>
+      </c>
+      <c r="N36" s="46">
+        <v>46168</v>
+      </c>
+      <c r="O36" s="47" t="s">
+        <v>118</v>
+      </c>
+      <c r="P36" s="48" t="s">
+        <v>118</v>
+      </c>
+      <c r="Q36" s="49">
+        <v>46158</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="33" t="s">
+        <v>100</v>
+      </c>
+      <c r="B37" s="34" t="s">
+        <v>101</v>
+      </c>
+      <c r="C37" s="35" t="s">
+        <v>19</v>
+      </c>
+      <c r="D37" s="36" t="s">
+        <v>41</v>
+      </c>
+      <c r="E37" s="37" t="s">
+        <v>42</v>
+      </c>
+      <c r="F37" s="38" t="s">
+        <v>43</v>
+      </c>
+      <c r="G37" s="39" t="s">
+        <v>126</v>
+      </c>
+      <c r="H37" s="40" t="s">
+        <v>42</v>
+      </c>
+      <c r="I37" s="41" t="s">
+        <v>102</v>
+      </c>
+      <c r="J37" s="42" t="s">
+        <v>103</v>
+      </c>
+      <c r="K37" s="43" t="s">
+        <v>104</v>
+      </c>
+      <c r="L37" s="44" t="s">
+        <v>105</v>
+      </c>
+      <c r="M37" s="45">
+        <v>46168</v>
+      </c>
+      <c r="N37" s="46">
+        <v>46168</v>
+      </c>
+      <c r="O37" s="47" t="s">
+        <v>118</v>
+      </c>
+      <c r="P37" s="48" t="s">
+        <v>118</v>
+      </c>
+      <c r="Q37" s="49">
+        <v>46158</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="33" t="s">
+        <v>127</v>
+      </c>
+      <c r="B38" s="34" t="s">
+        <v>128</v>
+      </c>
+      <c r="C38" s="35" t="s">
+        <v>19</v>
+      </c>
+      <c r="D38" s="36" t="s">
+        <v>41</v>
+      </c>
+      <c r="E38" s="37" t="s">
+        <v>42</v>
+      </c>
+      <c r="F38" s="38" t="s">
+        <v>43</v>
+      </c>
+      <c r="G38" s="39" t="s">
+        <v>23</v>
+      </c>
+      <c r="H38" s="40" t="s">
+        <v>42</v>
+      </c>
+      <c r="I38" s="41" t="s">
+        <v>102</v>
+      </c>
+      <c r="J38" s="42" t="s">
+        <v>103</v>
+      </c>
+      <c r="K38" s="43" t="s">
+        <v>104</v>
+      </c>
+      <c r="L38" s="44" t="s">
+        <v>105</v>
+      </c>
+      <c r="M38" s="45">
+        <v>46168</v>
+      </c>
+      <c r="N38" s="46">
+        <v>46168</v>
+      </c>
+      <c r="O38" s="47" t="s">
+        <v>106</v>
+      </c>
+      <c r="P38" s="48" t="s">
+        <v>106</v>
+      </c>
+      <c r="Q38" s="49">
+        <v>46158</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="33" t="s">
+        <v>127</v>
+      </c>
+      <c r="B39" s="34" t="s">
+        <v>128</v>
+      </c>
+      <c r="C39" s="35" t="s">
+        <v>19</v>
+      </c>
+      <c r="D39" s="36" t="s">
+        <v>41</v>
+      </c>
+      <c r="E39" s="37" t="s">
+        <v>42</v>
+      </c>
+      <c r="F39" s="38" t="s">
+        <v>43</v>
+      </c>
+      <c r="G39" s="39" t="s">
+        <v>30</v>
+      </c>
+      <c r="H39" s="40" t="s">
+        <v>42</v>
+      </c>
+      <c r="I39" s="41" t="s">
+        <v>129</v>
+      </c>
+      <c r="J39" s="42" t="s">
+        <v>103</v>
+      </c>
+      <c r="K39" s="43" t="s">
+        <v>104</v>
+      </c>
+      <c r="L39" s="44" t="s">
+        <v>105</v>
+      </c>
+      <c r="M39" s="45">
+        <v>46168</v>
+      </c>
+      <c r="N39" s="46">
+        <v>46168</v>
+      </c>
+      <c r="O39" s="47" t="s">
+        <v>106</v>
+      </c>
+      <c r="P39" s="48" t="s">
+        <v>106</v>
+      </c>
+      <c r="Q39" s="49">
+        <v>46158</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="33" t="s">
+        <v>127</v>
+      </c>
+      <c r="B40" s="34" t="s">
+        <v>128</v>
+      </c>
+      <c r="C40" s="35" t="s">
+        <v>19</v>
+      </c>
+      <c r="D40" s="36" t="s">
+        <v>41</v>
+      </c>
+      <c r="E40" s="37" t="s">
+        <v>42</v>
+      </c>
+      <c r="F40" s="38" t="s">
+        <v>43</v>
+      </c>
+      <c r="G40" s="39" t="s">
+        <v>71</v>
+      </c>
+      <c r="H40" s="40" t="s">
+        <v>42</v>
+      </c>
+      <c r="I40" s="41" t="s">
+        <v>102</v>
+      </c>
+      <c r="J40" s="42" t="s">
+        <v>103</v>
+      </c>
+      <c r="K40" s="43" t="s">
+        <v>104</v>
+      </c>
+      <c r="L40" s="44" t="s">
+        <v>105</v>
+      </c>
+      <c r="M40" s="45">
+        <v>46168</v>
+      </c>
+      <c r="N40" s="46">
+        <v>46168</v>
+      </c>
+      <c r="O40" s="47" t="s">
+        <v>106</v>
+      </c>
+      <c r="P40" s="48" t="s">
+        <v>106</v>
+      </c>
+      <c r="Q40" s="49">
+        <v>46158</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="33" t="s">
+        <v>127</v>
+      </c>
+      <c r="B41" s="34" t="s">
+        <v>128</v>
+      </c>
+      <c r="C41" s="35" t="s">
+        <v>19</v>
+      </c>
+      <c r="D41" s="36" t="s">
+        <v>41</v>
+      </c>
+      <c r="E41" s="37" t="s">
+        <v>42</v>
+      </c>
+      <c r="F41" s="38" t="s">
+        <v>43</v>
+      </c>
+      <c r="G41" s="39" t="s">
+        <v>72</v>
+      </c>
+      <c r="H41" s="40" t="s">
+        <v>42</v>
+      </c>
+      <c r="I41" s="41" t="s">
+        <v>107</v>
+      </c>
+      <c r="J41" s="42" t="s">
+        <v>103</v>
+      </c>
+      <c r="K41" s="43" t="s">
+        <v>104</v>
+      </c>
+      <c r="L41" s="44" t="s">
+        <v>105</v>
+      </c>
+      <c r="M41" s="45">
+        <v>46168</v>
+      </c>
+      <c r="N41" s="46">
+        <v>46168</v>
+      </c>
+      <c r="O41" s="47" t="s">
+        <v>106</v>
+      </c>
+      <c r="P41" s="48" t="s">
+        <v>106</v>
+      </c>
+      <c r="Q41" s="49">
+        <v>46158</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="33" t="s">
+        <v>127</v>
+      </c>
+      <c r="B42" s="34" t="s">
+        <v>128</v>
+      </c>
+      <c r="C42" s="35" t="s">
+        <v>19</v>
+      </c>
+      <c r="D42" s="36" t="s">
+        <v>41</v>
+      </c>
+      <c r="E42" s="37" t="s">
+        <v>42</v>
+      </c>
+      <c r="F42" s="38" t="s">
+        <v>43</v>
+      </c>
+      <c r="G42" s="39" t="s">
+        <v>108</v>
+      </c>
+      <c r="H42" s="40" t="s">
+        <v>42</v>
+      </c>
+      <c r="I42" s="41" t="s">
+        <v>124</v>
+      </c>
+      <c r="J42" s="42" t="s">
+        <v>103</v>
+      </c>
+      <c r="K42" s="43" t="s">
+        <v>104</v>
+      </c>
+      <c r="L42" s="44" t="s">
+        <v>105</v>
+      </c>
+      <c r="M42" s="45">
+        <v>46168</v>
+      </c>
+      <c r="N42" s="46">
+        <v>46168</v>
+      </c>
+      <c r="O42" s="47" t="s">
+        <v>106</v>
+      </c>
+      <c r="P42" s="48" t="s">
+        <v>106</v>
+      </c>
+      <c r="Q42" s="49">
+        <v>46158</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="33" t="s">
+        <v>127</v>
+      </c>
+      <c r="B43" s="34" t="s">
+        <v>128</v>
+      </c>
+      <c r="C43" s="35" t="s">
+        <v>19</v>
+      </c>
+      <c r="D43" s="36" t="s">
+        <v>41</v>
+      </c>
+      <c r="E43" s="37" t="s">
+        <v>42</v>
+      </c>
+      <c r="F43" s="38" t="s">
+        <v>43</v>
+      </c>
+      <c r="G43" s="39" t="s">
+        <v>109</v>
+      </c>
+      <c r="H43" s="40" t="s">
+        <v>42</v>
+      </c>
+      <c r="I43" s="41" t="s">
+        <v>102</v>
+      </c>
+      <c r="J43" s="42" t="s">
+        <v>103</v>
+      </c>
+      <c r="K43" s="43" t="s">
+        <v>104</v>
+      </c>
+      <c r="L43" s="44" t="s">
+        <v>105</v>
+      </c>
+      <c r="M43" s="45">
+        <v>46168</v>
+      </c>
+      <c r="N43" s="46">
+        <v>46168</v>
+      </c>
+      <c r="O43" s="47" t="s">
+        <v>106</v>
+      </c>
+      <c r="P43" s="48" t="s">
+        <v>106</v>
+      </c>
+      <c r="Q43" s="49">
+        <v>46158</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="33" t="s">
+        <v>127</v>
+      </c>
+      <c r="B44" s="34" t="s">
+        <v>128</v>
+      </c>
+      <c r="C44" s="35" t="s">
+        <v>19</v>
+      </c>
+      <c r="D44" s="36" t="s">
+        <v>41</v>
+      </c>
+      <c r="E44" s="37" t="s">
+        <v>42</v>
+      </c>
+      <c r="F44" s="38" t="s">
+        <v>43</v>
+      </c>
+      <c r="G44" s="39" t="s">
+        <v>110</v>
+      </c>
+      <c r="H44" s="40" t="s">
+        <v>42</v>
+      </c>
+      <c r="I44" s="41" t="s">
+        <v>124</v>
+      </c>
+      <c r="J44" s="42" t="s">
+        <v>103</v>
+      </c>
+      <c r="K44" s="43" t="s">
+        <v>104</v>
+      </c>
+      <c r="L44" s="44" t="s">
+        <v>105</v>
+      </c>
+      <c r="M44" s="45">
+        <v>46168</v>
+      </c>
+      <c r="N44" s="46">
+        <v>46168</v>
+      </c>
+      <c r="O44" s="47" t="s">
+        <v>106</v>
+      </c>
+      <c r="P44" s="48" t="s">
+        <v>106</v>
+      </c>
+      <c r="Q44" s="49">
+        <v>46158</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="33" t="s">
+        <v>127</v>
+      </c>
+      <c r="B45" s="34" t="s">
+        <v>128</v>
+      </c>
+      <c r="C45" s="35" t="s">
+        <v>19</v>
+      </c>
+      <c r="D45" s="36" t="s">
+        <v>41</v>
+      </c>
+      <c r="E45" s="37" t="s">
+        <v>42</v>
+      </c>
+      <c r="F45" s="38" t="s">
+        <v>43</v>
+      </c>
+      <c r="G45" s="39" t="s">
+        <v>111</v>
+      </c>
+      <c r="H45" s="40" t="s">
+        <v>42</v>
+      </c>
+      <c r="I45" s="41" t="s">
+        <v>107</v>
+      </c>
+      <c r="J45" s="42" t="s">
+        <v>103</v>
+      </c>
+      <c r="K45" s="43" t="s">
+        <v>104</v>
+      </c>
+      <c r="L45" s="44" t="s">
+        <v>105</v>
+      </c>
+      <c r="M45" s="45">
+        <v>46168</v>
+      </c>
+      <c r="N45" s="46">
+        <v>46168</v>
+      </c>
+      <c r="O45" s="47" t="s">
+        <v>106</v>
+      </c>
+      <c r="P45" s="48" t="s">
+        <v>106</v>
+      </c>
+      <c r="Q45" s="49">
+        <v>46158</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="33" t="s">
+        <v>127</v>
+      </c>
+      <c r="B46" s="34" t="s">
+        <v>128</v>
+      </c>
+      <c r="C46" s="35" t="s">
+        <v>19</v>
+      </c>
+      <c r="D46" s="36" t="s">
+        <v>41</v>
+      </c>
+      <c r="E46" s="37" t="s">
+        <v>42</v>
+      </c>
+      <c r="F46" s="38" t="s">
+        <v>43</v>
+      </c>
+      <c r="G46" s="39" t="s">
+        <v>112</v>
+      </c>
+      <c r="H46" s="40" t="s">
+        <v>42</v>
+      </c>
+      <c r="I46" s="41" t="s">
+        <v>102</v>
+      </c>
+      <c r="J46" s="42" t="s">
+        <v>103</v>
+      </c>
+      <c r="K46" s="43" t="s">
+        <v>104</v>
+      </c>
+      <c r="L46" s="44" t="s">
+        <v>105</v>
+      </c>
+      <c r="M46" s="45">
+        <v>46168</v>
+      </c>
+      <c r="N46" s="46">
+        <v>46168</v>
+      </c>
+      <c r="O46" s="47" t="s">
+        <v>106</v>
+      </c>
+      <c r="P46" s="48" t="s">
+        <v>106</v>
+      </c>
+      <c r="Q46" s="49">
+        <v>46158</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="33" t="s">
+        <v>127</v>
+      </c>
+      <c r="B47" s="34" t="s">
+        <v>128</v>
+      </c>
+      <c r="C47" s="35" t="s">
+        <v>19</v>
+      </c>
+      <c r="D47" s="36" t="s">
+        <v>41</v>
+      </c>
+      <c r="E47" s="37" t="s">
+        <v>42</v>
+      </c>
+      <c r="F47" s="38" t="s">
+        <v>43</v>
+      </c>
+      <c r="G47" s="39" t="s">
+        <v>114</v>
+      </c>
+      <c r="H47" s="40" t="s">
+        <v>42</v>
+      </c>
+      <c r="I47" s="41" t="s">
+        <v>107</v>
+      </c>
+      <c r="J47" s="42" t="s">
+        <v>103</v>
+      </c>
+      <c r="K47" s="43" t="s">
+        <v>104</v>
+      </c>
+      <c r="L47" s="44" t="s">
+        <v>105</v>
+      </c>
+      <c r="M47" s="45">
+        <v>46168</v>
+      </c>
+      <c r="N47" s="46">
+        <v>46168</v>
+      </c>
+      <c r="O47" s="47" t="s">
+        <v>106</v>
+      </c>
+      <c r="P47" s="48" t="s">
+        <v>106</v>
+      </c>
+      <c r="Q47" s="49">
+        <v>46158</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="33" t="s">
+        <v>127</v>
+      </c>
+      <c r="B48" s="34" t="s">
+        <v>128</v>
+      </c>
+      <c r="C48" s="35" t="s">
+        <v>19</v>
+      </c>
+      <c r="D48" s="36" t="s">
+        <v>41</v>
+      </c>
+      <c r="E48" s="37" t="s">
+        <v>42</v>
+      </c>
+      <c r="F48" s="38" t="s">
+        <v>43</v>
+      </c>
+      <c r="G48" s="39" t="s">
+        <v>115</v>
+      </c>
+      <c r="H48" s="40" t="s">
+        <v>42</v>
+      </c>
+      <c r="I48" s="41" t="s">
+        <v>102</v>
+      </c>
+      <c r="J48" s="42" t="s">
+        <v>103</v>
+      </c>
+      <c r="K48" s="43" t="s">
+        <v>104</v>
+      </c>
+      <c r="L48" s="44" t="s">
+        <v>105</v>
+      </c>
+      <c r="M48" s="45">
+        <v>46168</v>
+      </c>
+      <c r="N48" s="46">
+        <v>46168</v>
+      </c>
+      <c r="O48" s="47" t="s">
+        <v>106</v>
+      </c>
+      <c r="P48" s="48" t="s">
+        <v>106</v>
+      </c>
+      <c r="Q48" s="49">
+        <v>46158</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="33" t="s">
+        <v>127</v>
+      </c>
+      <c r="B49" s="34" t="s">
+        <v>128</v>
+      </c>
+      <c r="C49" s="35" t="s">
+        <v>19</v>
+      </c>
+      <c r="D49" s="36" t="s">
+        <v>41</v>
+      </c>
+      <c r="E49" s="37" t="s">
+        <v>42</v>
+      </c>
+      <c r="F49" s="38" t="s">
+        <v>43</v>
+      </c>
+      <c r="G49" s="39" t="s">
+        <v>116</v>
+      </c>
+      <c r="H49" s="40" t="s">
+        <v>42</v>
+      </c>
+      <c r="I49" s="41" t="s">
+        <v>113</v>
+      </c>
+      <c r="J49" s="42" t="s">
+        <v>103</v>
+      </c>
+      <c r="K49" s="43" t="s">
+        <v>104</v>
+      </c>
+      <c r="L49" s="44" t="s">
+        <v>105</v>
+      </c>
+      <c r="M49" s="45">
+        <v>46168</v>
+      </c>
+      <c r="N49" s="46">
+        <v>46168</v>
+      </c>
+      <c r="O49" s="47" t="s">
+        <v>106</v>
+      </c>
+      <c r="P49" s="48" t="s">
+        <v>106</v>
+      </c>
+      <c r="Q49" s="49">
+        <v>46158</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="33" t="s">
+        <v>127</v>
+      </c>
+      <c r="B50" s="34" t="s">
+        <v>128</v>
+      </c>
+      <c r="C50" s="35" t="s">
+        <v>19</v>
+      </c>
+      <c r="D50" s="36" t="s">
+        <v>41</v>
+      </c>
+      <c r="E50" s="37" t="s">
+        <v>42</v>
+      </c>
+      <c r="F50" s="38" t="s">
+        <v>43</v>
+      </c>
+      <c r="G50" s="39" t="s">
+        <v>117</v>
+      </c>
+      <c r="H50" s="40" t="s">
+        <v>42</v>
+      </c>
+      <c r="I50" s="41" t="s">
+        <v>129</v>
+      </c>
+      <c r="J50" s="42" t="s">
+        <v>103</v>
+      </c>
+      <c r="K50" s="43" t="s">
+        <v>104</v>
+      </c>
+      <c r="L50" s="44" t="s">
+        <v>105</v>
+      </c>
+      <c r="M50" s="45">
+        <v>46168</v>
+      </c>
+      <c r="N50" s="46">
+        <v>46168</v>
+      </c>
+      <c r="O50" s="47" t="s">
+        <v>106</v>
+      </c>
+      <c r="P50" s="48" t="s">
+        <v>106</v>
+      </c>
+      <c r="Q50" s="49">
+        <v>46158</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="33" t="s">
+        <v>127</v>
+      </c>
+      <c r="B51" s="34" t="s">
+        <v>128</v>
+      </c>
+      <c r="C51" s="35" t="s">
+        <v>19</v>
+      </c>
+      <c r="D51" s="36" t="s">
+        <v>41</v>
+      </c>
+      <c r="E51" s="37" t="s">
+        <v>42</v>
+      </c>
+      <c r="F51" s="38" t="s">
+        <v>43</v>
+      </c>
+      <c r="G51" s="39" t="s">
+        <v>121</v>
+      </c>
+      <c r="H51" s="40" t="s">
+        <v>42</v>
+      </c>
+      <c r="I51" s="41" t="s">
+        <v>124</v>
+      </c>
+      <c r="J51" s="42" t="s">
+        <v>103</v>
+      </c>
+      <c r="K51" s="43" t="s">
+        <v>104</v>
+      </c>
+      <c r="L51" s="44" t="s">
+        <v>105</v>
+      </c>
+      <c r="M51" s="45">
+        <v>46168</v>
+      </c>
+      <c r="N51" s="46">
+        <v>46168</v>
+      </c>
+      <c r="O51" s="47" t="s">
+        <v>106</v>
+      </c>
+      <c r="P51" s="48" t="s">
+        <v>106</v>
+      </c>
+      <c r="Q51" s="49">
+        <v>46158</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="33" t="s">
+        <v>127</v>
+      </c>
+      <c r="B52" s="34" t="s">
+        <v>128</v>
+      </c>
+      <c r="C52" s="35" t="s">
+        <v>19</v>
+      </c>
+      <c r="D52" s="36" t="s">
+        <v>41</v>
+      </c>
+      <c r="E52" s="37" t="s">
+        <v>42</v>
+      </c>
+      <c r="F52" s="38" t="s">
+        <v>43</v>
+      </c>
+      <c r="G52" s="39" t="s">
+        <v>123</v>
+      </c>
+      <c r="H52" s="40" t="s">
+        <v>42</v>
+      </c>
+      <c r="I52" s="41" t="s">
+        <v>130</v>
+      </c>
+      <c r="J52" s="42" t="s">
+        <v>103</v>
+      </c>
+      <c r="K52" s="43" t="s">
+        <v>104</v>
+      </c>
+      <c r="L52" s="44" t="s">
+        <v>105</v>
+      </c>
+      <c r="M52" s="45">
+        <v>46168</v>
+      </c>
+      <c r="N52" s="46">
+        <v>46168</v>
+      </c>
+      <c r="O52" s="47" t="s">
+        <v>106</v>
+      </c>
+      <c r="P52" s="48" t="s">
+        <v>106</v>
+      </c>
+      <c r="Q52" s="49">
+        <v>46158</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="33" t="s">
+        <v>127</v>
+      </c>
+      <c r="B53" s="34" t="s">
+        <v>128</v>
+      </c>
+      <c r="C53" s="35" t="s">
+        <v>19</v>
+      </c>
+      <c r="D53" s="36" t="s">
+        <v>41</v>
+      </c>
+      <c r="E53" s="37" t="s">
+        <v>119</v>
+      </c>
+      <c r="F53" s="38" t="s">
+        <v>120</v>
+      </c>
+      <c r="G53" s="39" t="s">
+        <v>125</v>
+      </c>
+      <c r="H53" s="40" t="s">
+        <v>119</v>
+      </c>
+      <c r="I53" s="41" t="s">
+        <v>122</v>
+      </c>
+      <c r="J53" s="42" t="s">
+        <v>103</v>
+      </c>
+      <c r="K53" s="43" t="s">
+        <v>104</v>
+      </c>
+      <c r="L53" s="44" t="s">
+        <v>105</v>
+      </c>
+      <c r="M53" s="45">
+        <v>46168</v>
+      </c>
+      <c r="N53" s="46">
+        <v>46168</v>
+      </c>
+      <c r="O53" s="47" t="s">
+        <v>106</v>
+      </c>
+      <c r="P53" s="48" t="s">
+        <v>106</v>
+      </c>
+      <c r="Q53" s="49">
+        <v>46158</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="33" t="s">
+        <v>127</v>
+      </c>
+      <c r="B54" s="34" t="s">
+        <v>128</v>
+      </c>
+      <c r="C54" s="35" t="s">
+        <v>19</v>
+      </c>
+      <c r="D54" s="36" t="s">
+        <v>41</v>
+      </c>
+      <c r="E54" s="37" t="s">
+        <v>42</v>
+      </c>
+      <c r="F54" s="38" t="s">
+        <v>43</v>
+      </c>
+      <c r="G54" s="39" t="s">
+        <v>126</v>
+      </c>
+      <c r="H54" s="40" t="s">
+        <v>42</v>
+      </c>
+      <c r="I54" s="41" t="s">
+        <v>102</v>
+      </c>
+      <c r="J54" s="42" t="s">
+        <v>103</v>
+      </c>
+      <c r="K54" s="43" t="s">
+        <v>104</v>
+      </c>
+      <c r="L54" s="44" t="s">
+        <v>105</v>
+      </c>
+      <c r="M54" s="45">
+        <v>46168</v>
+      </c>
+      <c r="N54" s="46">
+        <v>46168</v>
+      </c>
+      <c r="O54" s="47" t="s">
+        <v>106</v>
+      </c>
+      <c r="P54" s="48" t="s">
+        <v>106</v>
+      </c>
+      <c r="Q54" s="49">
+        <v>46158</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="33" t="s">
+        <v>127</v>
+      </c>
+      <c r="B55" s="34" t="s">
+        <v>128</v>
+      </c>
+      <c r="C55" s="35" t="s">
+        <v>19</v>
+      </c>
+      <c r="D55" s="36" t="s">
+        <v>41</v>
+      </c>
+      <c r="E55" s="37" t="s">
+        <v>42</v>
+      </c>
+      <c r="F55" s="38" t="s">
+        <v>43</v>
+      </c>
+      <c r="G55" s="39" t="s">
+        <v>131</v>
+      </c>
+      <c r="H55" s="40" t="s">
+        <v>42</v>
+      </c>
+      <c r="I55" s="41" t="s">
+        <v>130</v>
+      </c>
+      <c r="J55" s="42" t="s">
+        <v>103</v>
+      </c>
+      <c r="K55" s="43" t="s">
+        <v>104</v>
+      </c>
+      <c r="L55" s="44" t="s">
+        <v>105</v>
+      </c>
+      <c r="M55" s="45">
+        <v>46168</v>
+      </c>
+      <c r="N55" s="46">
+        <v>46168</v>
+      </c>
+      <c r="O55" s="47" t="s">
+        <v>106</v>
+      </c>
+      <c r="P55" s="48" t="s">
+        <v>106</v>
+      </c>
+      <c r="Q55" s="49">
+        <v>46158</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="33" t="s">
+        <v>127</v>
+      </c>
+      <c r="B56" s="34" t="s">
+        <v>128</v>
+      </c>
+      <c r="C56" s="35" t="s">
+        <v>19</v>
+      </c>
+      <c r="D56" s="36" t="s">
+        <v>41</v>
+      </c>
+      <c r="E56" s="37" t="s">
+        <v>119</v>
+      </c>
+      <c r="F56" s="38" t="s">
+        <v>120</v>
+      </c>
+      <c r="G56" s="39" t="s">
+        <v>132</v>
+      </c>
+      <c r="H56" s="40" t="s">
+        <v>119</v>
+      </c>
+      <c r="I56" s="41" t="s">
+        <v>122</v>
+      </c>
+      <c r="J56" s="42" t="s">
+        <v>103</v>
+      </c>
+      <c r="K56" s="43" t="s">
+        <v>104</v>
+      </c>
+      <c r="L56" s="44" t="s">
+        <v>105</v>
+      </c>
+      <c r="M56" s="45">
+        <v>46168</v>
+      </c>
+      <c r="N56" s="46">
+        <v>46168</v>
+      </c>
+      <c r="O56" s="47" t="s">
+        <v>106</v>
+      </c>
+      <c r="P56" s="48" t="s">
+        <v>106</v>
+      </c>
+      <c r="Q56" s="49">
+        <v>46158</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="33" t="s">
+        <v>127</v>
+      </c>
+      <c r="B57" s="34" t="s">
+        <v>128</v>
+      </c>
+      <c r="C57" s="35" t="s">
+        <v>19</v>
+      </c>
+      <c r="D57" s="36" t="s">
+        <v>41</v>
+      </c>
+      <c r="E57" s="37" t="s">
+        <v>119</v>
+      </c>
+      <c r="F57" s="38" t="s">
+        <v>120</v>
+      </c>
+      <c r="G57" s="39" t="s">
+        <v>133</v>
+      </c>
+      <c r="H57" s="40" t="s">
+        <v>119</v>
+      </c>
+      <c r="I57" s="41" t="s">
+        <v>122</v>
+      </c>
+      <c r="J57" s="42" t="s">
+        <v>103</v>
+      </c>
+      <c r="K57" s="43" t="s">
+        <v>104</v>
+      </c>
+      <c r="L57" s="44" t="s">
+        <v>105</v>
+      </c>
+      <c r="M57" s="45">
+        <v>46168</v>
+      </c>
+      <c r="N57" s="46">
+        <v>46168</v>
+      </c>
+      <c r="O57" s="47" t="s">
+        <v>106</v>
+      </c>
+      <c r="P57" s="48" t="s">
+        <v>106</v>
+      </c>
+      <c r="Q57" s="49">
+        <v>46158</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="33" t="s">
+        <v>127</v>
+      </c>
+      <c r="B58" s="34" t="s">
+        <v>128</v>
+      </c>
+      <c r="C58" s="35" t="s">
+        <v>19</v>
+      </c>
+      <c r="D58" s="36" t="s">
+        <v>41</v>
+      </c>
+      <c r="E58" s="37" t="s">
+        <v>42</v>
+      </c>
+      <c r="F58" s="38" t="s">
+        <v>43</v>
+      </c>
+      <c r="G58" s="39" t="s">
+        <v>134</v>
+      </c>
+      <c r="H58" s="40" t="s">
+        <v>42</v>
+      </c>
+      <c r="I58" s="41" t="s">
+        <v>113</v>
+      </c>
+      <c r="J58" s="42" t="s">
+        <v>103</v>
+      </c>
+      <c r="K58" s="43" t="s">
+        <v>104</v>
+      </c>
+      <c r="L58" s="44" t="s">
+        <v>105</v>
+      </c>
+      <c r="M58" s="45">
+        <v>46168</v>
+      </c>
+      <c r="N58" s="46">
+        <v>46168</v>
+      </c>
+      <c r="O58" s="47" t="s">
+        <v>106</v>
+      </c>
+      <c r="P58" s="48" t="s">
+        <v>106</v>
+      </c>
+      <c r="Q58" s="49">
+        <v>46158</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="33" t="s">
+        <v>127</v>
+      </c>
+      <c r="B59" s="34" t="s">
+        <v>128</v>
+      </c>
+      <c r="C59" s="35" t="s">
+        <v>19</v>
+      </c>
+      <c r="D59" s="36" t="s">
+        <v>41</v>
+      </c>
+      <c r="E59" s="37" t="s">
+        <v>42</v>
+      </c>
+      <c r="F59" s="38" t="s">
+        <v>43</v>
+      </c>
+      <c r="G59" s="39" t="s">
+        <v>135</v>
+      </c>
+      <c r="H59" s="40" t="s">
+        <v>42</v>
+      </c>
+      <c r="I59" s="41" t="s">
+        <v>113</v>
+      </c>
+      <c r="J59" s="42" t="s">
+        <v>103</v>
+      </c>
+      <c r="K59" s="43" t="s">
+        <v>104</v>
+      </c>
+      <c r="L59" s="44" t="s">
+        <v>105</v>
+      </c>
+      <c r="M59" s="45">
+        <v>46168</v>
+      </c>
+      <c r="N59" s="46">
+        <v>46168</v>
+      </c>
+      <c r="O59" s="47" t="s">
+        <v>106</v>
+      </c>
+      <c r="P59" s="48" t="s">
+        <v>106</v>
+      </c>
+      <c r="Q59" s="49">
+        <v>46158</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="33" t="s">
+        <v>127</v>
+      </c>
+      <c r="B60" s="34" t="s">
+        <v>128</v>
+      </c>
+      <c r="C60" s="35" t="s">
+        <v>19</v>
+      </c>
+      <c r="D60" s="36" t="s">
+        <v>41</v>
+      </c>
+      <c r="E60" s="37" t="s">
+        <v>42</v>
+      </c>
+      <c r="F60" s="38" t="s">
+        <v>43</v>
+      </c>
+      <c r="G60" s="39" t="s">
+        <v>136</v>
+      </c>
+      <c r="H60" s="40" t="s">
+        <v>42</v>
+      </c>
+      <c r="I60" s="41" t="s">
+        <v>113</v>
+      </c>
+      <c r="J60" s="42" t="s">
+        <v>103</v>
+      </c>
+      <c r="K60" s="43" t="s">
+        <v>104</v>
+      </c>
+      <c r="L60" s="44" t="s">
+        <v>105</v>
+      </c>
+      <c r="M60" s="45">
+        <v>46168</v>
+      </c>
+      <c r="N60" s="46">
+        <v>46168</v>
+      </c>
+      <c r="O60" s="47" t="s">
+        <v>106</v>
+      </c>
+      <c r="P60" s="48" t="s">
+        <v>106</v>
+      </c>
+      <c r="Q60" s="49">
+        <v>46158</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="33" t="s">
+        <v>127</v>
+      </c>
+      <c r="B61" s="34" t="s">
+        <v>128</v>
+      </c>
+      <c r="C61" s="35" t="s">
+        <v>19</v>
+      </c>
+      <c r="D61" s="36" t="s">
+        <v>41</v>
+      </c>
+      <c r="E61" s="37" t="s">
+        <v>42</v>
+      </c>
+      <c r="F61" s="38" t="s">
+        <v>43</v>
+      </c>
+      <c r="G61" s="39" t="s">
+        <v>137</v>
+      </c>
+      <c r="H61" s="40" t="s">
+        <v>42</v>
+      </c>
+      <c r="I61" s="41" t="s">
+        <v>102</v>
+      </c>
+      <c r="J61" s="42" t="s">
+        <v>103</v>
+      </c>
+      <c r="K61" s="43" t="s">
+        <v>104</v>
+      </c>
+      <c r="L61" s="44" t="s">
+        <v>105</v>
+      </c>
+      <c r="M61" s="45">
+        <v>46168</v>
+      </c>
+      <c r="N61" s="46">
+        <v>46168</v>
+      </c>
+      <c r="O61" s="47" t="s">
+        <v>106</v>
+      </c>
+      <c r="P61" s="48" t="s">
+        <v>106</v>
+      </c>
+      <c r="Q61" s="49">
+        <v>46158</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="33" t="s">
+        <v>127</v>
+      </c>
+      <c r="B62" s="34" t="s">
+        <v>128</v>
+      </c>
+      <c r="C62" s="35" t="s">
+        <v>19</v>
+      </c>
+      <c r="D62" s="36" t="s">
+        <v>41</v>
+      </c>
+      <c r="E62" s="37" t="s">
+        <v>42</v>
+      </c>
+      <c r="F62" s="38" t="s">
+        <v>43</v>
+      </c>
+      <c r="G62" s="39" t="s">
+        <v>138</v>
+      </c>
+      <c r="H62" s="40" t="s">
+        <v>42</v>
+      </c>
+      <c r="I62" s="41" t="s">
+        <v>113</v>
+      </c>
+      <c r="J62" s="42" t="s">
+        <v>103</v>
+      </c>
+      <c r="K62" s="43" t="s">
+        <v>104</v>
+      </c>
+      <c r="L62" s="44" t="s">
+        <v>105</v>
+      </c>
+      <c r="M62" s="45">
+        <v>46168</v>
+      </c>
+      <c r="N62" s="46">
+        <v>46168</v>
+      </c>
+      <c r="O62" s="47" t="s">
+        <v>106</v>
+      </c>
+      <c r="P62" s="48" t="s">
+        <v>106</v>
+      </c>
+      <c r="Q62" s="49">
+        <v>46158</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="33" t="s">
+        <v>127</v>
+      </c>
+      <c r="B63" s="34" t="s">
+        <v>128</v>
+      </c>
+      <c r="C63" s="35" t="s">
+        <v>19</v>
+      </c>
+      <c r="D63" s="36" t="s">
+        <v>41</v>
+      </c>
+      <c r="E63" s="37" t="s">
+        <v>42</v>
+      </c>
+      <c r="F63" s="38" t="s">
+        <v>43</v>
+      </c>
+      <c r="G63" s="39" t="s">
+        <v>139</v>
+      </c>
+      <c r="H63" s="40" t="s">
+        <v>42</v>
+      </c>
+      <c r="I63" s="41" t="s">
+        <v>130</v>
+      </c>
+      <c r="J63" s="42" t="s">
+        <v>103</v>
+      </c>
+      <c r="K63" s="43" t="s">
+        <v>104</v>
+      </c>
+      <c r="L63" s="44" t="s">
+        <v>105</v>
+      </c>
+      <c r="M63" s="45">
+        <v>46168</v>
+      </c>
+      <c r="N63" s="46">
+        <v>46168</v>
+      </c>
+      <c r="O63" s="47" t="s">
+        <v>106</v>
+      </c>
+      <c r="P63" s="48" t="s">
+        <v>106</v>
+      </c>
+      <c r="Q63" s="49">
+        <v>46158</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="33" t="s">
+        <v>127</v>
+      </c>
+      <c r="B64" s="34" t="s">
+        <v>128</v>
+      </c>
+      <c r="C64" s="35" t="s">
+        <v>19</v>
+      </c>
+      <c r="D64" s="36" t="s">
+        <v>41</v>
+      </c>
+      <c r="E64" s="37" t="s">
+        <v>42</v>
+      </c>
+      <c r="F64" s="38" t="s">
+        <v>43</v>
+      </c>
+      <c r="G64" s="39" t="s">
+        <v>140</v>
+      </c>
+      <c r="H64" s="40" t="s">
+        <v>42</v>
+      </c>
+      <c r="I64" s="41" t="s">
+        <v>102</v>
+      </c>
+      <c r="J64" s="42" t="s">
+        <v>103</v>
+      </c>
+      <c r="K64" s="43" t="s">
+        <v>104</v>
+      </c>
+      <c r="L64" s="44" t="s">
+        <v>105</v>
+      </c>
+      <c r="M64" s="45">
+        <v>46168</v>
+      </c>
+      <c r="N64" s="46">
+        <v>46168</v>
+      </c>
+      <c r="O64" s="47" t="s">
+        <v>106</v>
+      </c>
+      <c r="P64" s="48" t="s">
+        <v>106</v>
+      </c>
+      <c r="Q64" s="49">
+        <v>46158</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="33" t="s">
+        <v>127</v>
+      </c>
+      <c r="B65" s="34" t="s">
+        <v>128</v>
+      </c>
+      <c r="C65" s="35" t="s">
+        <v>19</v>
+      </c>
+      <c r="D65" s="36" t="s">
+        <v>41</v>
+      </c>
+      <c r="E65" s="37" t="s">
+        <v>42</v>
+      </c>
+      <c r="F65" s="38" t="s">
+        <v>43</v>
+      </c>
+      <c r="G65" s="39" t="s">
+        <v>141</v>
+      </c>
+      <c r="H65" s="40" t="s">
+        <v>42</v>
+      </c>
+      <c r="I65" s="41" t="s">
+        <v>130</v>
+      </c>
+      <c r="J65" s="42" t="s">
+        <v>103</v>
+      </c>
+      <c r="K65" s="43" t="s">
+        <v>104</v>
+      </c>
+      <c r="L65" s="44" t="s">
+        <v>105</v>
+      </c>
+      <c r="M65" s="45">
+        <v>46168</v>
+      </c>
+      <c r="N65" s="46">
+        <v>46168</v>
+      </c>
+      <c r="O65" s="47" t="s">
+        <v>106</v>
+      </c>
+      <c r="P65" s="48" t="s">
+        <v>106</v>
+      </c>
+      <c r="Q65" s="49">
+        <v>46158</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" s="33" t="s">
+        <v>127</v>
+      </c>
+      <c r="B66" s="34" t="s">
+        <v>128</v>
+      </c>
+      <c r="C66" s="35" t="s">
+        <v>19</v>
+      </c>
+      <c r="D66" s="36" t="s">
+        <v>41</v>
+      </c>
+      <c r="E66" s="37" t="s">
+        <v>42</v>
+      </c>
+      <c r="F66" s="38" t="s">
+        <v>43</v>
+      </c>
+      <c r="G66" s="39" t="s">
+        <v>142</v>
+      </c>
+      <c r="H66" s="40" t="s">
+        <v>42</v>
+      </c>
+      <c r="I66" s="41" t="s">
+        <v>124</v>
+      </c>
+      <c r="J66" s="42" t="s">
+        <v>103</v>
+      </c>
+      <c r="K66" s="43" t="s">
+        <v>104</v>
+      </c>
+      <c r="L66" s="44" t="s">
+        <v>105</v>
+      </c>
+      <c r="M66" s="45">
+        <v>46168</v>
+      </c>
+      <c r="N66" s="46">
+        <v>46168</v>
+      </c>
+      <c r="O66" s="47" t="s">
+        <v>106</v>
+      </c>
+      <c r="P66" s="48" t="s">
+        <v>106</v>
+      </c>
+      <c r="Q66" s="49">
+        <v>46158</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" s="33" t="s">
+        <v>127</v>
+      </c>
+      <c r="B67" s="34" t="s">
+        <v>128</v>
+      </c>
+      <c r="C67" s="35" t="s">
+        <v>19</v>
+      </c>
+      <c r="D67" s="36" t="s">
+        <v>41</v>
+      </c>
+      <c r="E67" s="37" t="s">
+        <v>42</v>
+      </c>
+      <c r="F67" s="38" t="s">
+        <v>43</v>
+      </c>
+      <c r="G67" s="39" t="s">
+        <v>143</v>
+      </c>
+      <c r="H67" s="40" t="s">
+        <v>42</v>
+      </c>
+      <c r="I67" s="41" t="s">
+        <v>107</v>
+      </c>
+      <c r="J67" s="42" t="s">
+        <v>103</v>
+      </c>
+      <c r="K67" s="43" t="s">
+        <v>104</v>
+      </c>
+      <c r="L67" s="44" t="s">
+        <v>105</v>
+      </c>
+      <c r="M67" s="45">
+        <v>46168</v>
+      </c>
+      <c r="N67" s="46">
+        <v>46168</v>
+      </c>
+      <c r="O67" s="47" t="s">
+        <v>106</v>
+      </c>
+      <c r="P67" s="48" t="s">
+        <v>106</v>
+      </c>
+      <c r="Q67" s="49">
+        <v>46158</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" s="33" t="s">
+        <v>127</v>
+      </c>
+      <c r="B68" s="34" t="s">
+        <v>128</v>
+      </c>
+      <c r="C68" s="35" t="s">
+        <v>19</v>
+      </c>
+      <c r="D68" s="36" t="s">
+        <v>41</v>
+      </c>
+      <c r="E68" s="37" t="s">
+        <v>42</v>
+      </c>
+      <c r="F68" s="38" t="s">
+        <v>43</v>
+      </c>
+      <c r="G68" s="39" t="s">
+        <v>144</v>
+      </c>
+      <c r="H68" s="40" t="s">
+        <v>42</v>
+      </c>
+      <c r="I68" s="41" t="s">
+        <v>102</v>
+      </c>
+      <c r="J68" s="42" t="s">
+        <v>103</v>
+      </c>
+      <c r="K68" s="43" t="s">
+        <v>104</v>
+      </c>
+      <c r="L68" s="44" t="s">
+        <v>105</v>
+      </c>
+      <c r="M68" s="45">
+        <v>46168</v>
+      </c>
+      <c r="N68" s="46">
+        <v>46168</v>
+      </c>
+      <c r="O68" s="47" t="s">
+        <v>106</v>
+      </c>
+      <c r="P68" s="48" t="s">
+        <v>106</v>
+      </c>
+      <c r="Q68" s="49">
+        <v>46158</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" s="33" t="s">
+        <v>127</v>
+      </c>
+      <c r="B69" s="34" t="s">
+        <v>128</v>
+      </c>
+      <c r="C69" s="35" t="s">
+        <v>19</v>
+      </c>
+      <c r="D69" s="36" t="s">
+        <v>41</v>
+      </c>
+      <c r="E69" s="37" t="s">
+        <v>42</v>
+      </c>
+      <c r="F69" s="38" t="s">
+        <v>43</v>
+      </c>
+      <c r="G69" s="39" t="s">
+        <v>145</v>
+      </c>
+      <c r="H69" s="40" t="s">
+        <v>42</v>
+      </c>
+      <c r="I69" s="41" t="s">
+        <v>113</v>
+      </c>
+      <c r="J69" s="42" t="s">
+        <v>103</v>
+      </c>
+      <c r="K69" s="43" t="s">
+        <v>104</v>
+      </c>
+      <c r="L69" s="44" t="s">
+        <v>105</v>
+      </c>
+      <c r="M69" s="45">
+        <v>46168</v>
+      </c>
+      <c r="N69" s="46">
+        <v>46168</v>
+      </c>
+      <c r="O69" s="47" t="s">
+        <v>106</v>
+      </c>
+      <c r="P69" s="48" t="s">
+        <v>106</v>
+      </c>
+      <c r="Q69" s="49">
+        <v>46158</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" s="33" t="s">
+        <v>127</v>
+      </c>
+      <c r="B70" s="34" t="s">
+        <v>128</v>
+      </c>
+      <c r="C70" s="35" t="s">
+        <v>19</v>
+      </c>
+      <c r="D70" s="36" t="s">
+        <v>41</v>
+      </c>
+      <c r="E70" s="37" t="s">
+        <v>42</v>
+      </c>
+      <c r="F70" s="38" t="s">
+        <v>43</v>
+      </c>
+      <c r="G70" s="39" t="s">
+        <v>146</v>
+      </c>
+      <c r="H70" s="40" t="s">
+        <v>42</v>
+      </c>
+      <c r="I70" s="41" t="s">
+        <v>107</v>
+      </c>
+      <c r="J70" s="42" t="s">
+        <v>103</v>
+      </c>
+      <c r="K70" s="43" t="s">
+        <v>104</v>
+      </c>
+      <c r="L70" s="44" t="s">
+        <v>105</v>
+      </c>
+      <c r="M70" s="45">
+        <v>46168</v>
+      </c>
+      <c r="N70" s="46">
+        <v>46168</v>
+      </c>
+      <c r="O70" s="47" t="s">
+        <v>106</v>
+      </c>
+      <c r="P70" s="48" t="s">
+        <v>106</v>
+      </c>
+      <c r="Q70" s="49">
+        <v>46158</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" s="33" t="s">
+        <v>127</v>
+      </c>
+      <c r="B71" s="34" t="s">
+        <v>128</v>
+      </c>
+      <c r="C71" s="35" t="s">
+        <v>19</v>
+      </c>
+      <c r="D71" s="36" t="s">
+        <v>41</v>
+      </c>
+      <c r="E71" s="37" t="s">
+        <v>42</v>
+      </c>
+      <c r="F71" s="38" t="s">
+        <v>43</v>
+      </c>
+      <c r="G71" s="39" t="s">
+        <v>147</v>
+      </c>
+      <c r="H71" s="40" t="s">
+        <v>42</v>
+      </c>
+      <c r="I71" s="41" t="s">
+        <v>124</v>
+      </c>
+      <c r="J71" s="42" t="s">
+        <v>103</v>
+      </c>
+      <c r="K71" s="43" t="s">
+        <v>104</v>
+      </c>
+      <c r="L71" s="44" t="s">
+        <v>105</v>
+      </c>
+      <c r="M71" s="45">
+        <v>46168</v>
+      </c>
+      <c r="N71" s="46">
+        <v>46168</v>
+      </c>
+      <c r="O71" s="47" t="s">
+        <v>106</v>
+      </c>
+      <c r="P71" s="48" t="s">
+        <v>106</v>
+      </c>
+      <c r="Q71" s="49">
+        <v>46158</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" s="33" t="s">
+        <v>127</v>
+      </c>
+      <c r="B72" s="34" t="s">
+        <v>128</v>
+      </c>
+      <c r="C72" s="35" t="s">
+        <v>19</v>
+      </c>
+      <c r="D72" s="36" t="s">
+        <v>41</v>
+      </c>
+      <c r="E72" s="37" t="s">
+        <v>42</v>
+      </c>
+      <c r="F72" s="38" t="s">
+        <v>43</v>
+      </c>
+      <c r="G72" s="39" t="s">
+        <v>148</v>
+      </c>
+      <c r="H72" s="40" t="s">
+        <v>42</v>
+      </c>
+      <c r="I72" s="41" t="s">
+        <v>102</v>
+      </c>
+      <c r="J72" s="42" t="s">
+        <v>103</v>
+      </c>
+      <c r="K72" s="43" t="s">
+        <v>104</v>
+      </c>
+      <c r="L72" s="44" t="s">
+        <v>105</v>
+      </c>
+      <c r="M72" s="45">
+        <v>46168</v>
+      </c>
+      <c r="N72" s="46">
+        <v>46168</v>
+      </c>
+      <c r="O72" s="47" t="s">
+        <v>106</v>
+      </c>
+      <c r="P72" s="48" t="s">
+        <v>106</v>
+      </c>
+      <c r="Q72" s="49">
+        <v>46158</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" s="33" t="s">
+        <v>127</v>
+      </c>
+      <c r="B73" s="34" t="s">
+        <v>128</v>
+      </c>
+      <c r="C73" s="35" t="s">
+        <v>19</v>
+      </c>
+      <c r="D73" s="36" t="s">
+        <v>41</v>
+      </c>
+      <c r="E73" s="37" t="s">
+        <v>42</v>
+      </c>
+      <c r="F73" s="38" t="s">
+        <v>43</v>
+      </c>
+      <c r="G73" s="39" t="s">
+        <v>149</v>
+      </c>
+      <c r="H73" s="40" t="s">
+        <v>42</v>
+      </c>
+      <c r="I73" s="41" t="s">
+        <v>102</v>
+      </c>
+      <c r="J73" s="42" t="s">
+        <v>103</v>
+      </c>
+      <c r="K73" s="43" t="s">
+        <v>104</v>
+      </c>
+      <c r="L73" s="44" t="s">
+        <v>105</v>
+      </c>
+      <c r="M73" s="45">
+        <v>46168</v>
+      </c>
+      <c r="N73" s="46">
+        <v>46168</v>
+      </c>
+      <c r="O73" s="47" t="s">
+        <v>106</v>
+      </c>
+      <c r="P73" s="48" t="s">
+        <v>106</v>
+      </c>
+      <c r="Q73" s="49">
+        <v>46158</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" s="33" t="s">
+        <v>127</v>
+      </c>
+      <c r="B74" s="34" t="s">
+        <v>128</v>
+      </c>
+      <c r="C74" s="35" t="s">
+        <v>19</v>
+      </c>
+      <c r="D74" s="36" t="s">
+        <v>41</v>
+      </c>
+      <c r="E74" s="37" t="s">
+        <v>42</v>
+      </c>
+      <c r="F74" s="38" t="s">
+        <v>43</v>
+      </c>
+      <c r="G74" s="39" t="s">
+        <v>150</v>
+      </c>
+      <c r="H74" s="40" t="s">
+        <v>42</v>
+      </c>
+      <c r="I74" s="41" t="s">
+        <v>102</v>
+      </c>
+      <c r="J74" s="42" t="s">
+        <v>103</v>
+      </c>
+      <c r="K74" s="43" t="s">
+        <v>104</v>
+      </c>
+      <c r="L74" s="44" t="s">
+        <v>105</v>
+      </c>
+      <c r="M74" s="45">
+        <v>46168</v>
+      </c>
+      <c r="N74" s="46">
+        <v>46168</v>
+      </c>
+      <c r="O74" s="47" t="s">
+        <v>106</v>
+      </c>
+      <c r="P74" s="48" t="s">
+        <v>106</v>
+      </c>
+      <c r="Q74" s="49">
+        <v>46158</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" s="33" t="s">
+        <v>127</v>
+      </c>
+      <c r="B75" s="34" t="s">
+        <v>128</v>
+      </c>
+      <c r="C75" s="35" t="s">
+        <v>19</v>
+      </c>
+      <c r="D75" s="36" t="s">
+        <v>41</v>
+      </c>
+      <c r="E75" s="37" t="s">
+        <v>42</v>
+      </c>
+      <c r="F75" s="38" t="s">
+        <v>43</v>
+      </c>
+      <c r="G75" s="39" t="s">
+        <v>151</v>
+      </c>
+      <c r="H75" s="40" t="s">
+        <v>42</v>
+      </c>
+      <c r="I75" s="41" t="s">
+        <v>107</v>
+      </c>
+      <c r="J75" s="42" t="s">
+        <v>103</v>
+      </c>
+      <c r="K75" s="43" t="s">
+        <v>104</v>
+      </c>
+      <c r="L75" s="44" t="s">
+        <v>105</v>
+      </c>
+      <c r="M75" s="45">
+        <v>46168</v>
+      </c>
+      <c r="N75" s="46">
+        <v>46168</v>
+      </c>
+      <c r="O75" s="47" t="s">
+        <v>106</v>
+      </c>
+      <c r="P75" s="48" t="s">
+        <v>106</v>
+      </c>
+      <c r="Q75" s="49">
+        <v>46158</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" s="33" t="s">
+        <v>127</v>
+      </c>
+      <c r="B76" s="34" t="s">
+        <v>128</v>
+      </c>
+      <c r="C76" s="35" t="s">
+        <v>19</v>
+      </c>
+      <c r="D76" s="36" t="s">
+        <v>41</v>
+      </c>
+      <c r="E76" s="37" t="s">
+        <v>42</v>
+      </c>
+      <c r="F76" s="38" t="s">
+        <v>43</v>
+      </c>
+      <c r="G76" s="39" t="s">
+        <v>152</v>
+      </c>
+      <c r="H76" s="40" t="s">
+        <v>42</v>
+      </c>
+      <c r="I76" s="41" t="s">
+        <v>107</v>
+      </c>
+      <c r="J76" s="42" t="s">
+        <v>103</v>
+      </c>
+      <c r="K76" s="43" t="s">
+        <v>104</v>
+      </c>
+      <c r="L76" s="44" t="s">
+        <v>105</v>
+      </c>
+      <c r="M76" s="45">
+        <v>46168</v>
+      </c>
+      <c r="N76" s="46">
+        <v>46168</v>
+      </c>
+      <c r="O76" s="47" t="s">
+        <v>106</v>
+      </c>
+      <c r="P76" s="48" t="s">
+        <v>106</v>
+      </c>
+      <c r="Q76" s="49">
+        <v>46158</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" s="33" t="s">
+        <v>127</v>
+      </c>
+      <c r="B77" s="34" t="s">
+        <v>128</v>
+      </c>
+      <c r="C77" s="35" t="s">
+        <v>19</v>
+      </c>
+      <c r="D77" s="36" t="s">
+        <v>41</v>
+      </c>
+      <c r="E77" s="37" t="s">
+        <v>42</v>
+      </c>
+      <c r="F77" s="38" t="s">
+        <v>43</v>
+      </c>
+      <c r="G77" s="39" t="s">
+        <v>153</v>
+      </c>
+      <c r="H77" s="40" t="s">
+        <v>42</v>
+      </c>
+      <c r="I77" s="41" t="s">
+        <v>107</v>
+      </c>
+      <c r="J77" s="42" t="s">
+        <v>103</v>
+      </c>
+      <c r="K77" s="43" t="s">
+        <v>104</v>
+      </c>
+      <c r="L77" s="44" t="s">
+        <v>105</v>
+      </c>
+      <c r="M77" s="45">
+        <v>46168</v>
+      </c>
+      <c r="N77" s="46">
+        <v>46168</v>
+      </c>
+      <c r="O77" s="47" t="s">
+        <v>106</v>
+      </c>
+      <c r="P77" s="48" t="s">
+        <v>106</v>
+      </c>
+      <c r="Q77" s="49">
+        <v>46158</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" s="33" t="s">
+        <v>127</v>
+      </c>
+      <c r="B78" s="34" t="s">
+        <v>128</v>
+      </c>
+      <c r="C78" s="35" t="s">
+        <v>19</v>
+      </c>
+      <c r="D78" s="36" t="s">
+        <v>41</v>
+      </c>
+      <c r="E78" s="37" t="s">
+        <v>42</v>
+      </c>
+      <c r="F78" s="38" t="s">
+        <v>43</v>
+      </c>
+      <c r="G78" s="39" t="s">
+        <v>154</v>
+      </c>
+      <c r="H78" s="40" t="s">
+        <v>42</v>
+      </c>
+      <c r="I78" s="41" t="s">
+        <v>113</v>
+      </c>
+      <c r="J78" s="42" t="s">
+        <v>103</v>
+      </c>
+      <c r="K78" s="43" t="s">
+        <v>104</v>
+      </c>
+      <c r="L78" s="44" t="s">
+        <v>105</v>
+      </c>
+      <c r="M78" s="45">
+        <v>46168</v>
+      </c>
+      <c r="N78" s="46">
+        <v>46168</v>
+      </c>
+      <c r="O78" s="47" t="s">
+        <v>106</v>
+      </c>
+      <c r="P78" s="48" t="s">
+        <v>106</v>
+      </c>
+      <c r="Q78" s="49">
+        <v>46158</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" s="33" t="s">
+        <v>127</v>
+      </c>
+      <c r="B79" s="34" t="s">
+        <v>128</v>
+      </c>
+      <c r="C79" s="35" t="s">
+        <v>19</v>
+      </c>
+      <c r="D79" s="36" t="s">
+        <v>41</v>
+      </c>
+      <c r="E79" s="37" t="s">
+        <v>42</v>
+      </c>
+      <c r="F79" s="38" t="s">
+        <v>43</v>
+      </c>
+      <c r="G79" s="39" t="s">
+        <v>155</v>
+      </c>
+      <c r="H79" s="40" t="s">
+        <v>42</v>
+      </c>
+      <c r="I79" s="41" t="s">
+        <v>107</v>
+      </c>
+      <c r="J79" s="42" t="s">
+        <v>103</v>
+      </c>
+      <c r="K79" s="43" t="s">
+        <v>104</v>
+      </c>
+      <c r="L79" s="44" t="s">
+        <v>105</v>
+      </c>
+      <c r="M79" s="45">
+        <v>46168</v>
+      </c>
+      <c r="N79" s="46">
+        <v>46168</v>
+      </c>
+      <c r="O79" s="47" t="s">
+        <v>106</v>
+      </c>
+      <c r="P79" s="48" t="s">
+        <v>106</v>
+      </c>
+      <c r="Q79" s="49">
+        <v>46158</v>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" s="33" t="s">
+        <v>127</v>
+      </c>
+      <c r="B80" s="34" t="s">
+        <v>128</v>
+      </c>
+      <c r="C80" s="35" t="s">
+        <v>19</v>
+      </c>
+      <c r="D80" s="36" t="s">
+        <v>41</v>
+      </c>
+      <c r="E80" s="37" t="s">
+        <v>42</v>
+      </c>
+      <c r="F80" s="38" t="s">
+        <v>43</v>
+      </c>
+      <c r="G80" s="39" t="s">
+        <v>156</v>
+      </c>
+      <c r="H80" s="40" t="s">
+        <v>42</v>
+      </c>
+      <c r="I80" s="41" t="s">
+        <v>124</v>
+      </c>
+      <c r="J80" s="42" t="s">
+        <v>103</v>
+      </c>
+      <c r="K80" s="43" t="s">
+        <v>104</v>
+      </c>
+      <c r="L80" s="44" t="s">
+        <v>105</v>
+      </c>
+      <c r="M80" s="45">
+        <v>46168</v>
+      </c>
+      <c r="N80" s="46">
+        <v>46168</v>
+      </c>
+      <c r="O80" s="47" t="s">
+        <v>106</v>
+      </c>
+      <c r="P80" s="48" t="s">
+        <v>106</v>
+      </c>
+      <c r="Q80" s="49">
+        <v>46158</v>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" s="33" t="s">
+        <v>127</v>
+      </c>
+      <c r="B81" s="34" t="s">
+        <v>128</v>
+      </c>
+      <c r="C81" s="35" t="s">
+        <v>19</v>
+      </c>
+      <c r="D81" s="36" t="s">
+        <v>41</v>
+      </c>
+      <c r="E81" s="37" t="s">
+        <v>119</v>
+      </c>
+      <c r="F81" s="38" t="s">
+        <v>120</v>
+      </c>
+      <c r="G81" s="39" t="s">
+        <v>157</v>
+      </c>
+      <c r="H81" s="40" t="s">
+        <v>119</v>
+      </c>
+      <c r="I81" s="41" t="s">
+        <v>122</v>
+      </c>
+      <c r="J81" s="42" t="s">
+        <v>103</v>
+      </c>
+      <c r="K81" s="43" t="s">
+        <v>104</v>
+      </c>
+      <c r="L81" s="44" t="s">
+        <v>105</v>
+      </c>
+      <c r="M81" s="45">
+        <v>46168</v>
+      </c>
+      <c r="N81" s="46">
+        <v>46168</v>
+      </c>
+      <c r="O81" s="47" t="s">
+        <v>106</v>
+      </c>
+      <c r="P81" s="48" t="s">
+        <v>106</v>
+      </c>
+      <c r="Q81" s="49">
+        <v>46158</v>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" s="33" t="s">
+        <v>127</v>
+      </c>
+      <c r="B82" s="34" t="s">
+        <v>128</v>
+      </c>
+      <c r="C82" s="35" t="s">
+        <v>19</v>
+      </c>
+      <c r="D82" s="36" t="s">
+        <v>41</v>
+      </c>
+      <c r="E82" s="37" t="s">
+        <v>42</v>
+      </c>
+      <c r="F82" s="38" t="s">
+        <v>43</v>
+      </c>
+      <c r="G82" s="39" t="s">
+        <v>158</v>
+      </c>
+      <c r="H82" s="40" t="s">
+        <v>42</v>
+      </c>
+      <c r="I82" s="41" t="s">
+        <v>107</v>
+      </c>
+      <c r="J82" s="42" t="s">
+        <v>103</v>
+      </c>
+      <c r="K82" s="43" t="s">
+        <v>104</v>
+      </c>
+      <c r="L82" s="44" t="s">
+        <v>105</v>
+      </c>
+      <c r="M82" s="45">
+        <v>46168</v>
+      </c>
+      <c r="N82" s="46">
+        <v>46168</v>
+      </c>
+      <c r="O82" s="47" t="s">
+        <v>106</v>
+      </c>
+      <c r="P82" s="48" t="s">
+        <v>106</v>
+      </c>
+      <c r="Q82" s="49">
+        <v>46158</v>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" s="33" t="s">
+        <v>127</v>
+      </c>
+      <c r="B83" s="34" t="s">
+        <v>128</v>
+      </c>
+      <c r="C83" s="35" t="s">
+        <v>19</v>
+      </c>
+      <c r="D83" s="36" t="s">
+        <v>41</v>
+      </c>
+      <c r="E83" s="37" t="s">
+        <v>119</v>
+      </c>
+      <c r="F83" s="38" t="s">
+        <v>120</v>
+      </c>
+      <c r="G83" s="39" t="s">
+        <v>159</v>
+      </c>
+      <c r="H83" s="40" t="s">
+        <v>119</v>
+      </c>
+      <c r="I83" s="41" t="s">
+        <v>122</v>
+      </c>
+      <c r="J83" s="42" t="s">
+        <v>103</v>
+      </c>
+      <c r="K83" s="43" t="s">
+        <v>104</v>
+      </c>
+      <c r="L83" s="44" t="s">
+        <v>105</v>
+      </c>
+      <c r="M83" s="45">
+        <v>46168</v>
+      </c>
+      <c r="N83" s="46">
+        <v>46168</v>
+      </c>
+      <c r="O83" s="47" t="s">
+        <v>106</v>
+      </c>
+      <c r="P83" s="48" t="s">
+        <v>106</v>
+      </c>
+      <c r="Q83" s="49">
+        <v>46158</v>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" s="33" t="s">
+        <v>127</v>
+      </c>
+      <c r="B84" s="34" t="s">
+        <v>128</v>
+      </c>
+      <c r="C84" s="35" t="s">
+        <v>19</v>
+      </c>
+      <c r="D84" s="36" t="s">
+        <v>41</v>
+      </c>
+      <c r="E84" s="37" t="s">
+        <v>42</v>
+      </c>
+      <c r="F84" s="38" t="s">
+        <v>43</v>
+      </c>
+      <c r="G84" s="39" t="s">
+        <v>160</v>
+      </c>
+      <c r="H84" s="40" t="s">
+        <v>42</v>
+      </c>
+      <c r="I84" s="41" t="s">
+        <v>161</v>
+      </c>
+      <c r="J84" s="42" t="s">
+        <v>103</v>
+      </c>
+      <c r="K84" s="43" t="s">
+        <v>104</v>
+      </c>
+      <c r="L84" s="44" t="s">
+        <v>105</v>
+      </c>
+      <c r="M84" s="45">
+        <v>46168</v>
+      </c>
+      <c r="N84" s="46">
+        <v>46168</v>
+      </c>
+      <c r="O84" s="47" t="s">
+        <v>106</v>
+      </c>
+      <c r="P84" s="48" t="s">
+        <v>106</v>
+      </c>
+      <c r="Q84" s="49">
+        <v>46158</v>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" s="33" t="s">
+        <v>127</v>
+      </c>
+      <c r="B85" s="34" t="s">
+        <v>128</v>
+      </c>
+      <c r="C85" s="35" t="s">
+        <v>19</v>
+      </c>
+      <c r="D85" s="36" t="s">
+        <v>41</v>
+      </c>
+      <c r="E85" s="37" t="s">
         <v>21</v>
       </c>
-      <c r="F23" s="38" t="s">
-        <v>40</v>
-      </c>
-      <c r="G23" s="39" t="s">
+      <c r="F85" s="38" t="s">
+        <v>22</v>
+      </c>
+      <c r="G85" s="39" t="s">
+        <v>162</v>
+      </c>
+      <c r="H85" s="40" t="s">
+        <v>21</v>
+      </c>
+      <c r="I85" s="41" t="s">
+        <v>163</v>
+      </c>
+      <c r="J85" s="42" t="s">
+        <v>103</v>
+      </c>
+      <c r="K85" s="43" t="s">
+        <v>104</v>
+      </c>
+      <c r="L85" s="44" t="s">
+        <v>105</v>
+      </c>
+      <c r="M85" s="45">
+        <v>46168</v>
+      </c>
+      <c r="N85" s="46">
+        <v>46168</v>
+      </c>
+      <c r="O85" s="47" t="s">
+        <v>106</v>
+      </c>
+      <c r="P85" s="48" t="s">
+        <v>106</v>
+      </c>
+      <c r="Q85" s="49">
+        <v>46158</v>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" s="33" t="s">
+        <v>127</v>
+      </c>
+      <c r="B86" s="34" t="s">
+        <v>128</v>
+      </c>
+      <c r="C86" s="35" t="s">
+        <v>19</v>
+      </c>
+      <c r="D86" s="36" t="s">
+        <v>41</v>
+      </c>
+      <c r="E86" s="37" t="s">
+        <v>42</v>
+      </c>
+      <c r="F86" s="38" t="s">
+        <v>43</v>
+      </c>
+      <c r="G86" s="39" t="s">
+        <v>164</v>
+      </c>
+      <c r="H86" s="40" t="s">
+        <v>42</v>
+      </c>
+      <c r="I86" s="41" t="s">
+        <v>165</v>
+      </c>
+      <c r="J86" s="42" t="s">
+        <v>103</v>
+      </c>
+      <c r="K86" s="43" t="s">
+        <v>104</v>
+      </c>
+      <c r="L86" s="44" t="s">
+        <v>105</v>
+      </c>
+      <c r="M86" s="45">
+        <v>46168</v>
+      </c>
+      <c r="N86" s="46">
+        <v>46168</v>
+      </c>
+      <c r="O86" s="47" t="s">
+        <v>106</v>
+      </c>
+      <c r="P86" s="48" t="s">
+        <v>106</v>
+      </c>
+      <c r="Q86" s="49">
+        <v>46158</v>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" s="33" t="s">
+        <v>127</v>
+      </c>
+      <c r="B87" s="34" t="s">
+        <v>128</v>
+      </c>
+      <c r="C87" s="35" t="s">
+        <v>19</v>
+      </c>
+      <c r="D87" s="36" t="s">
+        <v>41</v>
+      </c>
+      <c r="E87" s="37" t="s">
+        <v>42</v>
+      </c>
+      <c r="F87" s="38" t="s">
+        <v>43</v>
+      </c>
+      <c r="G87" s="39" t="s">
+        <v>166</v>
+      </c>
+      <c r="H87" s="40" t="s">
+        <v>42</v>
+      </c>
+      <c r="I87" s="41" t="s">
+        <v>102</v>
+      </c>
+      <c r="J87" s="42" t="s">
+        <v>103</v>
+      </c>
+      <c r="K87" s="43" t="s">
+        <v>104</v>
+      </c>
+      <c r="L87" s="44" t="s">
+        <v>105</v>
+      </c>
+      <c r="M87" s="45">
+        <v>46168</v>
+      </c>
+      <c r="N87" s="46">
+        <v>46168</v>
+      </c>
+      <c r="O87" s="47" t="s">
+        <v>106</v>
+      </c>
+      <c r="P87" s="48" t="s">
+        <v>106</v>
+      </c>
+      <c r="Q87" s="49">
+        <v>46158</v>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" s="33" t="s">
+        <v>127</v>
+      </c>
+      <c r="B88" s="34" t="s">
+        <v>128</v>
+      </c>
+      <c r="C88" s="35" t="s">
+        <v>19</v>
+      </c>
+      <c r="D88" s="36" t="s">
+        <v>41</v>
+      </c>
+      <c r="E88" s="37" t="s">
+        <v>42</v>
+      </c>
+      <c r="F88" s="38" t="s">
+        <v>43</v>
+      </c>
+      <c r="G88" s="39" t="s">
+        <v>167</v>
+      </c>
+      <c r="H88" s="40" t="s">
+        <v>42</v>
+      </c>
+      <c r="I88" s="41" t="s">
+        <v>113</v>
+      </c>
+      <c r="J88" s="42" t="s">
+        <v>103</v>
+      </c>
+      <c r="K88" s="43" t="s">
+        <v>104</v>
+      </c>
+      <c r="L88" s="44" t="s">
+        <v>105</v>
+      </c>
+      <c r="M88" s="45">
+        <v>46168</v>
+      </c>
+      <c r="N88" s="46">
+        <v>46168</v>
+      </c>
+      <c r="O88" s="47" t="s">
+        <v>106</v>
+      </c>
+      <c r="P88" s="48" t="s">
+        <v>106</v>
+      </c>
+      <c r="Q88" s="49">
+        <v>46158</v>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" s="33" t="s">
+        <v>127</v>
+      </c>
+      <c r="B89" s="34" t="s">
+        <v>128</v>
+      </c>
+      <c r="C89" s="35" t="s">
+        <v>19</v>
+      </c>
+      <c r="D89" s="36" t="s">
+        <v>41</v>
+      </c>
+      <c r="E89" s="37" t="s">
+        <v>42</v>
+      </c>
+      <c r="F89" s="38" t="s">
+        <v>43</v>
+      </c>
+      <c r="G89" s="39" t="s">
+        <v>168</v>
+      </c>
+      <c r="H89" s="40" t="s">
+        <v>42</v>
+      </c>
+      <c r="I89" s="41" t="s">
+        <v>124</v>
+      </c>
+      <c r="J89" s="42" t="s">
+        <v>103</v>
+      </c>
+      <c r="K89" s="43" t="s">
+        <v>104</v>
+      </c>
+      <c r="L89" s="44" t="s">
+        <v>105</v>
+      </c>
+      <c r="M89" s="45">
+        <v>46168</v>
+      </c>
+      <c r="N89" s="46">
+        <v>46168</v>
+      </c>
+      <c r="O89" s="47" t="s">
+        <v>169</v>
+      </c>
+      <c r="P89" s="48" t="s">
+        <v>169</v>
+      </c>
+      <c r="Q89" s="49">
+        <v>46158</v>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" s="33" t="s">
+        <v>127</v>
+      </c>
+      <c r="B90" s="34" t="s">
+        <v>128</v>
+      </c>
+      <c r="C90" s="35" t="s">
+        <v>19</v>
+      </c>
+      <c r="D90" s="36" t="s">
+        <v>41</v>
+      </c>
+      <c r="E90" s="37" t="s">
+        <v>42</v>
+      </c>
+      <c r="F90" s="38" t="s">
+        <v>43</v>
+      </c>
+      <c r="G90" s="39" t="s">
+        <v>170</v>
+      </c>
+      <c r="H90" s="40" t="s">
+        <v>42</v>
+      </c>
+      <c r="I90" s="41" t="s">
+        <v>113</v>
+      </c>
+      <c r="J90" s="42" t="s">
+        <v>103</v>
+      </c>
+      <c r="K90" s="43" t="s">
+        <v>104</v>
+      </c>
+      <c r="L90" s="44" t="s">
+        <v>105</v>
+      </c>
+      <c r="M90" s="45">
+        <v>46168</v>
+      </c>
+      <c r="N90" s="46">
+        <v>46168</v>
+      </c>
+      <c r="O90" s="47" t="s">
+        <v>169</v>
+      </c>
+      <c r="P90" s="48" t="s">
+        <v>169</v>
+      </c>
+      <c r="Q90" s="49">
+        <v>46158</v>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" s="33" t="s">
+        <v>127</v>
+      </c>
+      <c r="B91" s="34" t="s">
+        <v>128</v>
+      </c>
+      <c r="C91" s="35" t="s">
+        <v>19</v>
+      </c>
+      <c r="D91" s="36" t="s">
+        <v>41</v>
+      </c>
+      <c r="E91" s="37" t="s">
+        <v>42</v>
+      </c>
+      <c r="F91" s="38" t="s">
+        <v>43</v>
+      </c>
+      <c r="G91" s="39" t="s">
+        <v>171</v>
+      </c>
+      <c r="H91" s="40" t="s">
+        <v>42</v>
+      </c>
+      <c r="I91" s="41" t="s">
+        <v>113</v>
+      </c>
+      <c r="J91" s="42" t="s">
+        <v>103</v>
+      </c>
+      <c r="K91" s="43" t="s">
+        <v>104</v>
+      </c>
+      <c r="L91" s="44" t="s">
+        <v>105</v>
+      </c>
+      <c r="M91" s="45">
+        <v>46168</v>
+      </c>
+      <c r="N91" s="46">
+        <v>46168</v>
+      </c>
+      <c r="O91" s="47" t="s">
+        <v>169</v>
+      </c>
+      <c r="P91" s="48" t="s">
+        <v>169</v>
+      </c>
+      <c r="Q91" s="49">
+        <v>46158</v>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" s="33" t="s">
+        <v>127</v>
+      </c>
+      <c r="B92" s="34" t="s">
+        <v>128</v>
+      </c>
+      <c r="C92" s="35" t="s">
+        <v>19</v>
+      </c>
+      <c r="D92" s="36" t="s">
+        <v>41</v>
+      </c>
+      <c r="E92" s="37" t="s">
+        <v>42</v>
+      </c>
+      <c r="F92" s="38" t="s">
+        <v>43</v>
+      </c>
+      <c r="G92" s="39" t="s">
+        <v>172</v>
+      </c>
+      <c r="H92" s="40" t="s">
+        <v>42</v>
+      </c>
+      <c r="I92" s="41" t="s">
+        <v>113</v>
+      </c>
+      <c r="J92" s="42" t="s">
+        <v>103</v>
+      </c>
+      <c r="K92" s="43" t="s">
+        <v>104</v>
+      </c>
+      <c r="L92" s="44" t="s">
+        <v>105</v>
+      </c>
+      <c r="M92" s="45">
+        <v>46168</v>
+      </c>
+      <c r="N92" s="46">
+        <v>46168</v>
+      </c>
+      <c r="O92" s="47" t="s">
+        <v>169</v>
+      </c>
+      <c r="P92" s="48" t="s">
+        <v>169</v>
+      </c>
+      <c r="Q92" s="49">
+        <v>46158</v>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" s="33" t="s">
+        <v>127</v>
+      </c>
+      <c r="B93" s="34" t="s">
+        <v>128</v>
+      </c>
+      <c r="C93" s="35" t="s">
+        <v>19</v>
+      </c>
+      <c r="D93" s="36" t="s">
+        <v>41</v>
+      </c>
+      <c r="E93" s="37" t="s">
+        <v>42</v>
+      </c>
+      <c r="F93" s="38" t="s">
+        <v>43</v>
+      </c>
+      <c r="G93" s="39" t="s">
+        <v>173</v>
+      </c>
+      <c r="H93" s="40" t="s">
+        <v>42</v>
+      </c>
+      <c r="I93" s="41" t="s">
+        <v>113</v>
+      </c>
+      <c r="J93" s="42" t="s">
+        <v>103</v>
+      </c>
+      <c r="K93" s="43" t="s">
+        <v>104</v>
+      </c>
+      <c r="L93" s="44" t="s">
+        <v>105</v>
+      </c>
+      <c r="M93" s="45">
+        <v>46168</v>
+      </c>
+      <c r="N93" s="46">
+        <v>46168</v>
+      </c>
+      <c r="O93" s="47" t="s">
+        <v>169</v>
+      </c>
+      <c r="P93" s="48" t="s">
+        <v>169</v>
+      </c>
+      <c r="Q93" s="49">
+        <v>46158</v>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" s="33" t="s">
+        <v>127</v>
+      </c>
+      <c r="B94" s="34" t="s">
+        <v>128</v>
+      </c>
+      <c r="C94" s="35" t="s">
+        <v>19</v>
+      </c>
+      <c r="D94" s="36" t="s">
+        <v>41</v>
+      </c>
+      <c r="E94" s="37" t="s">
+        <v>42</v>
+      </c>
+      <c r="F94" s="38" t="s">
+        <v>43</v>
+      </c>
+      <c r="G94" s="39" t="s">
+        <v>174</v>
+      </c>
+      <c r="H94" s="40" t="s">
+        <v>42</v>
+      </c>
+      <c r="I94" s="41" t="s">
+        <v>102</v>
+      </c>
+      <c r="J94" s="42" t="s">
+        <v>103</v>
+      </c>
+      <c r="K94" s="43" t="s">
+        <v>104</v>
+      </c>
+      <c r="L94" s="44" t="s">
+        <v>105</v>
+      </c>
+      <c r="M94" s="45">
+        <v>46168</v>
+      </c>
+      <c r="N94" s="46">
+        <v>46168</v>
+      </c>
+      <c r="O94" s="47" t="s">
+        <v>118</v>
+      </c>
+      <c r="P94" s="48" t="s">
+        <v>118</v>
+      </c>
+      <c r="Q94" s="49">
+        <v>46158</v>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" s="33" t="s">
+        <v>127</v>
+      </c>
+      <c r="B95" s="34" t="s">
+        <v>128</v>
+      </c>
+      <c r="C95" s="35" t="s">
+        <v>19</v>
+      </c>
+      <c r="D95" s="36" t="s">
+        <v>41</v>
+      </c>
+      <c r="E95" s="37" t="s">
+        <v>42</v>
+      </c>
+      <c r="F95" s="38" t="s">
+        <v>43</v>
+      </c>
+      <c r="G95" s="39" t="s">
+        <v>175</v>
+      </c>
+      <c r="H95" s="40" t="s">
+        <v>42</v>
+      </c>
+      <c r="I95" s="41" t="s">
+        <v>102</v>
+      </c>
+      <c r="J95" s="42" t="s">
+        <v>103</v>
+      </c>
+      <c r="K95" s="43" t="s">
+        <v>104</v>
+      </c>
+      <c r="L95" s="44" t="s">
+        <v>105</v>
+      </c>
+      <c r="M95" s="45">
+        <v>46168</v>
+      </c>
+      <c r="N95" s="46">
+        <v>46168</v>
+      </c>
+      <c r="O95" s="47" t="s">
+        <v>118</v>
+      </c>
+      <c r="P95" s="48" t="s">
+        <v>118</v>
+      </c>
+      <c r="Q95" s="49">
+        <v>46158</v>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" s="33" t="s">
+        <v>127</v>
+      </c>
+      <c r="B96" s="34" t="s">
+        <v>128</v>
+      </c>
+      <c r="C96" s="35" t="s">
+        <v>19</v>
+      </c>
+      <c r="D96" s="36" t="s">
+        <v>41</v>
+      </c>
+      <c r="E96" s="37" t="s">
+        <v>42</v>
+      </c>
+      <c r="F96" s="38" t="s">
+        <v>43</v>
+      </c>
+      <c r="G96" s="39" t="s">
+        <v>176</v>
+      </c>
+      <c r="H96" s="40" t="s">
+        <v>42</v>
+      </c>
+      <c r="I96" s="41" t="s">
+        <v>129</v>
+      </c>
+      <c r="J96" s="42" t="s">
+        <v>103</v>
+      </c>
+      <c r="K96" s="43" t="s">
+        <v>104</v>
+      </c>
+      <c r="L96" s="44" t="s">
+        <v>105</v>
+      </c>
+      <c r="M96" s="45">
+        <v>46168</v>
+      </c>
+      <c r="N96" s="46">
+        <v>46168</v>
+      </c>
+      <c r="O96" s="47" t="s">
+        <v>118</v>
+      </c>
+      <c r="P96" s="48" t="s">
+        <v>118</v>
+      </c>
+      <c r="Q96" s="49">
+        <v>46158</v>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" s="33" t="s">
+        <v>127</v>
+      </c>
+      <c r="B97" s="34" t="s">
+        <v>128</v>
+      </c>
+      <c r="C97" s="35" t="s">
+        <v>19</v>
+      </c>
+      <c r="D97" s="36" t="s">
+        <v>41</v>
+      </c>
+      <c r="E97" s="37" t="s">
+        <v>119</v>
+      </c>
+      <c r="F97" s="38" t="s">
+        <v>120</v>
+      </c>
+      <c r="G97" s="39" t="s">
+        <v>177</v>
+      </c>
+      <c r="H97" s="40" t="s">
+        <v>119</v>
+      </c>
+      <c r="I97" s="41" t="s">
+        <v>122</v>
+      </c>
+      <c r="J97" s="42" t="s">
+        <v>103</v>
+      </c>
+      <c r="K97" s="43" t="s">
+        <v>104</v>
+      </c>
+      <c r="L97" s="44" t="s">
+        <v>105</v>
+      </c>
+      <c r="M97" s="45">
+        <v>46168</v>
+      </c>
+      <c r="N97" s="46">
+        <v>46168</v>
+      </c>
+      <c r="O97" s="47" t="s">
+        <v>118</v>
+      </c>
+      <c r="P97" s="48" t="s">
+        <v>118</v>
+      </c>
+      <c r="Q97" s="49">
+        <v>46158</v>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" s="33" t="s">
+        <v>178</v>
+      </c>
+      <c r="B98" s="34" t="s">
+        <v>179</v>
+      </c>
+      <c r="C98" s="35" t="s">
+        <v>180</v>
+      </c>
+      <c r="D98" s="36" t="s">
+        <v>41</v>
+      </c>
+      <c r="E98" s="37" t="s">
+        <v>42</v>
+      </c>
+      <c r="F98" s="38" t="s">
+        <v>43</v>
+      </c>
+      <c r="G98" s="39" t="s">
         <v>23</v>
       </c>
-      <c r="H23" s="40" t="s">
+      <c r="H98" s="40" t="s">
+        <v>42</v>
+      </c>
+      <c r="I98" s="41" t="s">
+        <v>181</v>
+      </c>
+      <c r="J98" s="42" t="s">
+        <v>182</v>
+      </c>
+      <c r="K98" s="43" t="s">
+        <v>183</v>
+      </c>
+      <c r="L98" s="44" t="s">
+        <v>184</v>
+      </c>
+      <c r="M98" s="45">
+        <v>46168</v>
+      </c>
+      <c r="N98" s="46">
+        <v>46168</v>
+      </c>
+      <c r="O98" s="47" t="s">
+        <v>185</v>
+      </c>
+      <c r="P98" s="48" t="s">
+        <v>185</v>
+      </c>
+      <c r="Q98" s="49">
+        <v>46157</v>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" s="33" t="s">
+        <v>178</v>
+      </c>
+      <c r="B99" s="34" t="s">
+        <v>179</v>
+      </c>
+      <c r="C99" s="35" t="s">
+        <v>180</v>
+      </c>
+      <c r="D99" s="36" t="s">
+        <v>41</v>
+      </c>
+      <c r="E99" s="37" t="s">
         <v>21</v>
       </c>
-      <c r="I23" s="41" t="s">
-        <v>110</v>
-      </c>
-      <c r="J23" s="42" t="s">
-        <v>25</v>
-      </c>
-      <c r="K23" s="43" t="s">
-        <v>26</v>
-      </c>
-      <c r="L23" s="44" t="s">
-        <v>27</v>
-      </c>
-      <c r="M23" s="45">
-        <v>46166</v>
-      </c>
-      <c r="N23" s="46">
-        <v>46166</v>
-      </c>
-      <c r="O23" s="47" t="s">
-        <v>105</v>
-      </c>
-      <c r="P23" s="48" t="s">
-        <v>105</v>
-      </c>
-      <c r="Q23" s="49">
-        <v>46152</v>
+      <c r="F99" s="38" t="s">
+        <v>22</v>
+      </c>
+      <c r="G99" s="39" t="s">
+        <v>30</v>
+      </c>
+      <c r="H99" s="40" t="s">
+        <v>21</v>
+      </c>
+      <c r="I99" s="41" t="s">
+        <v>186</v>
+      </c>
+      <c r="J99" s="42" t="s">
+        <v>182</v>
+      </c>
+      <c r="K99" s="43" t="s">
+        <v>183</v>
+      </c>
+      <c r="L99" s="44" t="s">
+        <v>184</v>
+      </c>
+      <c r="M99" s="45">
+        <v>46168</v>
+      </c>
+      <c r="N99" s="46">
+        <v>46168</v>
+      </c>
+      <c r="O99" s="47" t="s">
+        <v>185</v>
+      </c>
+      <c r="P99" s="48" t="s">
+        <v>185</v>
+      </c>
+      <c r="Q99" s="49">
+        <v>46157</v>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" s="33" t="s">
+        <v>187</v>
+      </c>
+      <c r="B100" s="34" t="s">
+        <v>188</v>
+      </c>
+      <c r="C100" s="35" t="s">
+        <v>189</v>
+      </c>
+      <c r="D100" s="36" t="s">
+        <v>190</v>
+      </c>
+      <c r="E100" s="37" t="s">
+        <v>42</v>
+      </c>
+      <c r="F100" s="38" t="s">
+        <v>43</v>
+      </c>
+      <c r="G100" s="39" t="s">
+        <v>23</v>
+      </c>
+      <c r="H100" s="40" t="s">
+        <v>42</v>
+      </c>
+      <c r="I100" s="41" t="s">
+        <v>191</v>
+      </c>
+      <c r="J100" s="42" t="s">
+        <v>192</v>
+      </c>
+      <c r="K100" s="43" t="s">
+        <v>193</v>
+      </c>
+      <c r="L100" s="44" t="s">
+        <v>194</v>
+      </c>
+      <c r="M100" s="45">
+        <v>46168</v>
+      </c>
+      <c r="N100" s="46">
+        <v>46168</v>
+      </c>
+      <c r="O100" s="47" t="s">
+        <v>195</v>
+      </c>
+      <c r="P100" s="48" t="s">
+        <v>195</v>
+      </c>
+      <c r="Q100" s="49">
+        <v>46164</v>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" s="33" t="s">
+        <v>187</v>
+      </c>
+      <c r="B101" s="34" t="s">
+        <v>188</v>
+      </c>
+      <c r="C101" s="35" t="s">
+        <v>189</v>
+      </c>
+      <c r="D101" s="36" t="s">
+        <v>190</v>
+      </c>
+      <c r="E101" s="37" t="s">
+        <v>42</v>
+      </c>
+      <c r="F101" s="38" t="s">
+        <v>43</v>
+      </c>
+      <c r="G101" s="39" t="s">
+        <v>30</v>
+      </c>
+      <c r="H101" s="40" t="s">
+        <v>42</v>
+      </c>
+      <c r="I101" s="41" t="s">
+        <v>196</v>
+      </c>
+      <c r="J101" s="42" t="s">
+        <v>192</v>
+      </c>
+      <c r="K101" s="43" t="s">
+        <v>193</v>
+      </c>
+      <c r="L101" s="44" t="s">
+        <v>194</v>
+      </c>
+      <c r="M101" s="45">
+        <v>46168</v>
+      </c>
+      <c r="N101" s="46">
+        <v>46168</v>
+      </c>
+      <c r="O101" s="47" t="s">
+        <v>195</v>
+      </c>
+      <c r="P101" s="48" t="s">
+        <v>195</v>
+      </c>
+      <c r="Q101" s="49">
+        <v>46164</v>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" s="33" t="s">
+        <v>197</v>
+      </c>
+      <c r="B102" s="34" t="s">
+        <v>198</v>
+      </c>
+      <c r="C102" s="35" t="s">
+        <v>189</v>
+      </c>
+      <c r="D102" s="36" t="s">
+        <v>190</v>
+      </c>
+      <c r="E102" s="37" t="s">
+        <v>42</v>
+      </c>
+      <c r="F102" s="38" t="s">
+        <v>41</v>
+      </c>
+      <c r="G102" s="39" t="s">
+        <v>23</v>
+      </c>
+      <c r="H102" s="40" t="s">
+        <v>42</v>
+      </c>
+      <c r="I102" s="41" t="s">
+        <v>199</v>
+      </c>
+      <c r="J102" s="42" t="s">
+        <v>200</v>
+      </c>
+      <c r="K102" s="43" t="s">
+        <v>201</v>
+      </c>
+      <c r="L102" s="44" t="s">
+        <v>202</v>
+      </c>
+      <c r="M102" s="45">
+        <v>46167</v>
+      </c>
+      <c r="N102" s="46">
+        <v>46168</v>
+      </c>
+      <c r="O102" s="47" t="s">
+        <v>203</v>
+      </c>
+      <c r="P102" s="48" t="s">
+        <v>203</v>
+      </c>
+      <c r="Q102" s="49">
+        <v>46167</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError sqref="A1 B1 C1 D1 E1 F1 G1 H1 I1 J1 K1 L1 M1 N1 O1 P1 Q1 A2 B2 C2 D2 E2 F2 G2 H2 I2 J2 K2 L2 O2 P2 A3 B3 C3 D3 E3 F3 G3 H3 I3 J3 K3 L3 O3 P3 A4 B4 C4 D4 E4 F4 G4 H4 I4 J4 K4 L4 O4 P4 A5 B5 C5 D5 E5 F5 G5 H5 I5 J5 K5 L5 O5 P5 A6 B6 C6 D6 E6 F6 G6 H6 I6 J6 K6 L6 O6 P6 A7 B7 C7 D7 E7 F7 G7 H7 I7 J7 K7 L7 O7 P7 A8 B8 C8 D8 E8 F8 G8 H8 I8 J8 K8 L8 O8 P8 A9 B9 C9 D9 E9 F9 G9 H9 I9 J9 K9 L9 O9 P9 A10 B10 C10 D10 E10 F10 G10 H10 I10 J10 K10 L10 O10 P10 A11 B11 C11 D11 E11 F11 G11 H11 I11 J11 K11 L11 O11 P11 A12 B12 C12 D12 E12 F12 G12 H12 I12 J12 K12 L12 O12 P12 A13 B13 C13 D13 E13 F13 G13 H13 I13 J13 K13 L13 O13 P13 A14 B14 C14 D14 E14 F14 G14 H14 I14 J14 K14 L14 O14 P14 A15 B15 C15 D15 E15 F15 G15 H15 I15 J15 K15 L15 O15 P15 A16 B16 C16 D16 E16 F16 G16 H16 I16 J16 K16 L16 O16 P16 A17 B17 C17 D17 E17 F17 G17 H17 I17 J17 K17 L17 O17 P17 A18 B18 C18 D18 E18 F18 G18 H18 I18 J18 K18 L18 O18 P18 A19 B19 C19 D19 E19 F19 G19 H19 I19 J19 K19 L19 O19 P19 A20 B20 C20 D20 E20 F20 G20 H20 I20 J20 K20 L20 O20 P20 A21 B21 C21 D21 E21 F21 G21 H21 I21 J21 K21 L21 O21 P21 A22 B22 C22 D22 E22 F22 G22 H22 I22 J22 K22 L22 O22 P22 A23 B23 C23 D23 E23 F23 G23 H23 I23 J23 K23 L23 O23 P23" numberStoredAsText="true"/>
+    <ignoredError sqref="A1 B1 C1 D1 E1 F1 G1 H1 I1 J1 K1 L1 M1 N1 O1 P1 Q1 A2 B2 C2 D2 E2 F2 G2 H2 I2 J2 K2 L2 O2 P2 A3 B3 C3 D3 E3 F3 G3 H3 I3 J3 K3 L3 O3 P3 A4 B4 C4 D4 E4 F4 G4 H4 I4 J4 K4 L4 O4 P4 A5 B5 C5 D5 E5 F5 G5 H5 I5 J5 K5 L5 O5 P5 A6 B6 C6 D6 E6 F6 G6 H6 I6 J6 K6 L6 O6 P6 A7 B7 C7 D7 E7 F7 G7 H7 I7 J7 K7 L7 O7 P7 A8 B8 C8 D8 E8 F8 G8 H8 I8 J8 K8 L8 O8 P8 A9 B9 C9 D9 E9 F9 G9 H9 I9 J9 K9 L9 O9 P9 A10 B10 C10 D10 E10 F10 G10 H10 I10 J10 K10 L10 O10 P10 A11 B11 C11 D11 E11 F11 G11 H11 I11 J11 K11 L11 O11 P11 A12 B12 C12 D12 E12 F12 G12 H12 I12 J12 K12 L12 O12 P12 A13 B13 C13 D13 E13 F13 G13 H13 I13 J13 K13 L13 O13 P13 A14 B14 C14 D14 E14 F14 G14 H14 I14 J14 K14 L14 O14 P14 A15 B15 C15 D15 E15 F15 G15 H15 I15 J15 K15 L15 O15 P15 A16 B16 C16 D16 E16 F16 G16 H16 I16 J16 K16 L16 O16 P16 A17 B17 C17 D17 E17 F17 G17 H17 I17 J17 K17 L17 O17 P17 A18 B18 C18 D18 E18 F18 G18 H18 I18 J18 K18 L18 O18 P18 A19 B19 C19 D19 E19 F19 G19 H19 I19 J19 K19 L19 O19 P19 A20 B20 C20 D20 E20 F20 G20 H20 I20 J20 K20 L20 O20 P20 A21 B21 C21 D21 E21 F21 G21 H21 I21 J21 K21 L21 O21 P21 A22 B22 C22 D22 E22 F22 G22 H22 I22 J22 K22 L22 O22 P22 A23 B23 C23 D23 E23 F23 G23 H23 I23 J23 K23 L23 O23 P23 A24 B24 C24 D24 E24 F24 G24 H24 I24 J24 K24 L24 O24 P24 A25 B25 C25 D25 E25 F25 G25 H25 I25 J25 K25 L25 O25 P25 A26 B26 C26 D26 E26 F26 G26 H26 I26 J26 K26 L26 O26 P26 A27 B27 C27 D27 E27 F27 G27 H27 I27 J27 K27 L27 O27 P27 A28 B28 C28 D28 E28 F28 G28 H28 I28 J28 K28 L28 O28 P28 A29 B29 C29 D29 E29 F29 G29 H29 I29 J29 K29 L29 O29 P29 A30 B30 C30 D30 E30 F30 G30 H30 I30 J30 K30 L30 O30 P30 A31 B31 C31 D31 E31 F31 G31 H31 I31 J31 K31 L31 O31 P31 A32 B32 C32 D32 E32 F32 G32 H32 I32 J32 K32 L32 O32 P32 A33 B33 C33 D33 E33 F33 G33 H33 I33 J33 K33 L33 O33 P33 A34 B34 C34 D34 E34 F34 G34 H34 I34 J34 K34 L34 O34 P34 A35 B35 C35 D35 E35 F35 G35 H35 I35 J35 K35 L35 O35 P35 A36 B36 C36 D36 E36 F36 G36 H36 I36 J36 K36 L36 O36 P36 A37 B37 C37 D37 E37 F37 G37 H37 I37 J37 K37 L37 O37 P37 A38 B38 C38 D38 E38 F38 G38 H38 I38 J38 K38 L38 O38 P38 A39 B39 C39 D39 E39 F39 G39 H39 I39 J39 K39 L39 O39 P39 A40 B40 C40 D40 E40 F40 G40 H40 I40 J40 K40 L40 O40 P40 A41 B41 C41 D41 E41 F41 G41 H41 I41 J41 K41 L41 O41 P41 A42 B42 C42 D42 E42 F42 G42 H42 I42 J42 K42 L42 O42 P42 A43 B43 C43 D43 E43 F43 G43 H43 I43 J43 K43 L43 O43 P43 A44 B44 C44 D44 E44 F44 G44 H44 I44 J44 K44 L44 O44 P44 A45 B45 C45 D45 E45 F45 G45 H45 I45 J45 K45 L45 O45 P45 A46 B46 C46 D46 E46 F46 G46 H46 I46 J46 K46 L46 O46 P46 A47 B47 C47 D47 E47 F47 G47 H47 I47 J47 K47 L47 O47 P47 A48 B48 C48 D48 E48 F48 G48 H48 I48 J48 K48 L48 O48 P48 A49 B49 C49 D49 E49 F49 G49 H49 I49 J49 K49 L49 O49 P49 A50 B50 C50 D50 E50 F50 G50 H50 I50 J50 K50 L50 O50 P50 A51 B51 C51 D51 E51 F51 G51 H51 I51 J51 K51 L51 O51 P51 A52 B52 C52 D52 E52 F52 G52 H52 I52 J52 K52 L52 O52 P52 A53 B53 C53 D53 E53 F53 G53 H53 I53 J53 K53 L53 O53 P53 A54 B54 C54 D54 E54 F54 G54 H54 I54 J54 K54 L54 O54 P54 A55 B55 C55 D55 E55 F55 G55 H55 I55 J55 K55 L55 O55 P55 A56 B56 C56 D56 E56 F56 G56 H56 I56 J56 K56 L56 O56 P56 A57 B57 C57 D57 E57 F57 G57 H57 I57 J57 K57 L57 O57 P57 A58 B58 C58 D58 E58 F58 G58 H58 I58 J58 K58 L58 O58 P58 A59 B59 C59 D59 E59 F59 G59 H59 I59 J59 K59 L59 O59 P59 A60 B60 C60 D60 E60 F60 G60 H60 I60 J60 K60 L60 O60 P60 A61 B61 C61 D61 E61 F61 G61 H61 I61 J61 K61 L61 O61 P61 A62 B62 C62 D62 E62 F62 G62 H62 I62 J62 K62 L62 O62 P62 A63 B63 C63 D63 E63 F63 G63 H63 I63 J63 K63 L63 O63 P63 A64 B64 C64 D64 E64 F64 G64 H64 I64 J64 K64 L64 O64 P64 A65 B65 C65 D65 E65 F65 G65 H65 I65 J65 K65 L65 O65 P65 A66 B66 C66 D66 E66 F66 G66 H66 I66 J66 K66 L66 O66 P66 A67 B67 C67 D67 E67 F67 G67 H67 I67 J67 K67 L67 O67 P67 A68 B68 C68 D68 E68 F68 G68 H68 I68 J68 K68 L68 O68 P68 A69 B69 C69 D69 E69 F69 G69 H69 I69 J69 K69 L69 O69 P69 A70 B70 C70 D70 E70 F70 G70 H70 I70 J70 K70 L70 O70 P70 A71 B71 C71 D71 E71 F71 G71 H71 I71 J71 K71 L71 O71 P71 A72 B72 C72 D72 E72 F72 G72 H72 I72 J72 K72 L72 O72 P72 A73 B73 C73 D73 E73 F73 G73 H73 I73 J73 K73 L73 O73 P73 A74 B74 C74 D74 E74 F74 G74 H74 I74 J74 K74 L74 O74 P74 A75 B75 C75 D75 E75 F75 G75 H75 I75 J75 K75 L75 O75 P75 A76 B76 C76 D76 E76 F76 G76 H76 I76 J76 K76 L76 O76 P76 A77 B77 C77 D77 E77 F77 G77 H77 I77 J77 K77 L77 O77 P77 A78 B78 C78 D78 E78 F78 G78 H78 I78 J78 K78 L78 O78 P78 A79 B79 C79 D79 E79 F79 G79 H79 I79 J79 K79 L79 O79 P79 A80 B80 C80 D80 E80 F80 G80 H80 I80 J80 K80 L80 O80 P80 A81 B81 C81 D81 E81 F81 G81 H81 I81 J81 K81 L81 O81 P81 A82 B82 C82 D82 E82 F82 G82 H82 I82 J82 K82 L82 O82 P82 A83 B83 C83 D83 E83 F83 G83 H83 I83 J83 K83 L83 O83 P83 A84 B84 C84 D84 E84 F84 G84 H84 I84 J84 K84 L84 O84 P84 A85 B85 C85 D85 E85 F85 G85 H85 I85 J85 K85 L85 O85 P85 A86 B86 C86 D86 E86 F86 G86 H86 I86 J86 K86 L86 O86 P86 A87 B87 C87 D87 E87 F87 G87 H87 I87 J87 K87 L87 O87 P87 A88 B88 C88 D88 E88 F88 G88 H88 I88 J88 K88 L88 O88 P88 A89 B89 C89 D89 E89 F89 G89 H89 I89 J89 K89 L89 O89 P89 A90 B90 C90 D90 E90 F90 G90 H90 I90 J90 K90 L90 O90 P90 A91 B91 C91 D91 E91 F91 G91 H91 I91 J91 K91 L91 O91 P91 A92 B92 C92 D92 E92 F92 G92 H92 I92 J92 K92 L92 O92 P92 A93 B93 C93 D93 E93 F93 G93 H93 I93 J93 K93 L93 O93 P93 A94 B94 C94 D94 E94 F94 G94 H94 I94 J94 K94 L94 O94 P94 A95 B95 C95 D95 E95 F95 G95 H95 I95 J95 K95 L95 O95 P95 A96 B96 C96 D96 E96 F96 G96 H96 I96 J96 K96 L96 O96 P96 A97 B97 C97 D97 E97 F97 G97 H97 I97 J97 K97 L97 O97 P97 A98 B98 C98 D98 E98 F98 G98 H98 I98 J98 K98 L98 O98 P98 A99 B99 C99 D99 E99 F99 G99 H99 I99 J99 K99 L99 O99 P99 A100 B100 C100 D100 E100 F100 G100 H100 I100 J100 K100 L100 O100 P100 A101 B101 C101 D101 E101 F101 G101 H101 I101 J101 K101 L101 O101 P101 A102 B102 C102 D102 E102 F102 G102 H102 I102 J102 K102 L102 O102 P102" numberStoredAsText="true"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/trimika_data.xlsx
+++ b/trimika_data.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" count="157" uniqueCount="74">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" count="591" uniqueCount="177">
   <si>
     <t>REFERENCE NO</t>
   </si>
@@ -66,61 +66,472 @@
     <t>EXPORT DATE</t>
   </si>
   <si>
-    <t>2615593</t>
-  </si>
-  <si>
-    <t>EF4-0231288-0</t>
+    <t>2564901</t>
+  </si>
+  <si>
+    <t>EF4-0230143-8</t>
+  </si>
+  <si>
+    <t>Vessel, Container</t>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t>9903.03.06</t>
+  </si>
+  <si>
+    <t>S122 EXCL,IRN/STL/ALUM,DERIV</t>
+  </si>
+  <si>
+    <t>001</t>
+  </si>
+  <si>
+    <t>9903.82.10,8428.32.0000</t>
+  </si>
+  <si>
+    <t>AUMUND CORPORATION</t>
+  </si>
+  <si>
+    <t>AUMCOR</t>
+  </si>
+  <si>
+    <t>58-138896800</t>
+  </si>
+  <si>
+    <t>AUMUND ENGINEERING PVT. LTD</t>
+  </si>
+  <si>
+    <t>2565168</t>
+  </si>
+  <si>
+    <t>EF4-0230690-8</t>
+  </si>
+  <si>
+    <t>9903.03.01</t>
+  </si>
+  <si>
+    <t>SECTION 122 - 10% DUTY</t>
+  </si>
+  <si>
+    <t>4911.91.1500</t>
+  </si>
+  <si>
+    <t>MBARE LTD</t>
+  </si>
+  <si>
+    <t>MBALTD01</t>
+  </si>
+  <si>
+    <t>58-227380900</t>
+  </si>
+  <si>
+    <t>AMATULI ARTEFACTS CC</t>
+  </si>
+  <si>
+    <t>002</t>
+  </si>
+  <si>
+    <t>6810.99.0080</t>
+  </si>
+  <si>
+    <t>MUJIBHA EXPORTS  (PVT) LTD</t>
+  </si>
+  <si>
+    <t>003</t>
+  </si>
+  <si>
+    <t>4420.19.0000</t>
+  </si>
+  <si>
+    <t>004</t>
+  </si>
+  <si>
+    <t>8306.29.0000</t>
+  </si>
+  <si>
+    <t>005</t>
+  </si>
+  <si>
+    <t>9602.00.5080</t>
+  </si>
+  <si>
+    <t>006</t>
+  </si>
+  <si>
+    <t>4602.19.1600</t>
+  </si>
+  <si>
+    <t>007</t>
+  </si>
+  <si>
+    <t>7013.99.9090</t>
+  </si>
+  <si>
+    <t>NGWENYA GLASS (PTY) LTD</t>
+  </si>
+  <si>
+    <t>008</t>
+  </si>
+  <si>
+    <t>7013.49.6090</t>
+  </si>
+  <si>
+    <t>009</t>
+  </si>
+  <si>
+    <t>7013.37.2090</t>
+  </si>
+  <si>
+    <t>010</t>
+  </si>
+  <si>
+    <t>7013.28.6090</t>
+  </si>
+  <si>
+    <t>011</t>
+  </si>
+  <si>
+    <t>TINTSABA MASTER WEAVERS</t>
+  </si>
+  <si>
+    <t>2615605</t>
+  </si>
+  <si>
+    <t>EF4-0231227-8</t>
   </si>
   <si>
     <t>Vessel, Non-container</t>
   </si>
   <si>
-    <t/>
-  </si>
-  <si>
-    <t>9903.88.15</t>
-  </si>
-  <si>
-    <t>ARTICLE OF CHINA,US NTE 20(R)</t>
-  </si>
-  <si>
-    <t>001</t>
-  </si>
-  <si>
-    <t>9903.03.01,3926.30.5000</t>
-  </si>
-  <si>
-    <t>GRASS AMERICA INC</t>
-  </si>
-  <si>
-    <t>GRAAME</t>
-  </si>
-  <si>
-    <t>51-066023000</t>
-  </si>
-  <si>
-    <t>GUANGDONG JUSEN PRECISION TECHNOLOG</t>
-  </si>
-  <si>
-    <t>GUANGDONG JUSEN PRECISION TECHNOLOGY CO</t>
-  </si>
-  <si>
-    <t>2565521</t>
-  </si>
-  <si>
-    <t>EF4-0231293-0</t>
-  </si>
-  <si>
-    <t>Vessel, Container</t>
-  </si>
-  <si>
-    <t>V0710321014</t>
-  </si>
-  <si>
-    <t>9903.03.01</t>
-  </si>
-  <si>
-    <t>SECTION 122 - 10% DUTY</t>
+    <t>8532.90.0000</t>
+  </si>
+  <si>
+    <t>INTELLEGRE LLC</t>
+  </si>
+  <si>
+    <t>INTLLC04</t>
+  </si>
+  <si>
+    <t>27-303564600</t>
+  </si>
+  <si>
+    <t>KDDL LIMITED</t>
+  </si>
+  <si>
+    <t>2565475</t>
+  </si>
+  <si>
+    <t>EF4-0231259-1</t>
+  </si>
+  <si>
+    <t>V0710305991</t>
+  </si>
+  <si>
+    <t>5903.90.3090</t>
+  </si>
+  <si>
+    <t>VEER CORPORATIONS INC</t>
+  </si>
+  <si>
+    <t>VEECOR01</t>
+  </si>
+  <si>
+    <t>99-106989200</t>
+  </si>
+  <si>
+    <t>VEER PLASTIC PVT LTD</t>
+  </si>
+  <si>
+    <t>2565542</t>
+  </si>
+  <si>
+    <t>EF4-0231330-0</t>
+  </si>
+  <si>
+    <t>8422.30.9120</t>
+  </si>
+  <si>
+    <t>HERMA US INC</t>
+  </si>
+  <si>
+    <t>HERUS01</t>
+  </si>
+  <si>
+    <t>61-178066000</t>
+  </si>
+  <si>
+    <t>HERMA UK LTD</t>
+  </si>
+  <si>
+    <t>8422.90.9195</t>
+  </si>
+  <si>
+    <t>2565504</t>
+  </si>
+  <si>
+    <t>EF4-0231414-2</t>
+  </si>
+  <si>
+    <t>V1626441706</t>
+  </si>
+  <si>
+    <t>1108.12.0010</t>
+  </si>
+  <si>
+    <t>ROYAL INGREDIENTS GROUP BV</t>
+  </si>
+  <si>
+    <t>ROYINGRE</t>
+  </si>
+  <si>
+    <t>074601-00962</t>
+  </si>
+  <si>
+    <t>TAT NISASTA INS SAN TIC AS</t>
+  </si>
+  <si>
+    <t>2565685</t>
+  </si>
+  <si>
+    <t>EF4-0231464-7</t>
+  </si>
+  <si>
+    <t>9903.03.03</t>
+  </si>
+  <si>
+    <t>S122 -EXCLUSION-EXEMPTED PRDTS</t>
+  </si>
+  <si>
+    <t>2930.90.9231</t>
+  </si>
+  <si>
+    <t>CASTLE CHEMICALS LTD</t>
+  </si>
+  <si>
+    <t>CASCHE01</t>
+  </si>
+  <si>
+    <t>151704-07138</t>
+  </si>
+  <si>
+    <t>HUBEI JINGHAN NEW MATERIALS CO. LTD</t>
+  </si>
+  <si>
+    <t>2565642</t>
+  </si>
+  <si>
+    <t>EF4-0231514-9</t>
+  </si>
+  <si>
+    <t>1702.30.4085</t>
+  </si>
+  <si>
+    <t>AK NISASTA SANAYI VE TICARET AS</t>
+  </si>
+  <si>
+    <t>2565649</t>
+  </si>
+  <si>
+    <t>EF4-0231517-2</t>
+  </si>
+  <si>
+    <t>2615635-1</t>
+  </si>
+  <si>
+    <t>EF4-0231639-4</t>
+  </si>
+  <si>
+    <t>8416.90.0000</t>
+  </si>
+  <si>
+    <t>THERMAL PROCESS DEVELOPMENT LLC</t>
+  </si>
+  <si>
+    <t>THEPRO01</t>
+  </si>
+  <si>
+    <t>82-175198100</t>
+  </si>
+  <si>
+    <t>RICHARD KABLITZ &amp; MITTHOF GMBH</t>
+  </si>
+  <si>
+    <t>2615635-2</t>
+  </si>
+  <si>
+    <t>EF4-0231640-2</t>
+  </si>
+  <si>
+    <t>8208.90.6000</t>
+  </si>
+  <si>
+    <t>CB MANUFACTURING &amp; SALES CO INC</t>
+  </si>
+  <si>
+    <t>CBMAN01</t>
+  </si>
+  <si>
+    <t>34-101525000</t>
+  </si>
+  <si>
+    <t>LUTZ GMBH &amp; CO. KG</t>
+  </si>
+  <si>
+    <t>8208.30.0030</t>
+  </si>
+  <si>
+    <t>2615635-3</t>
+  </si>
+  <si>
+    <t>EF4-0231641-0</t>
+  </si>
+  <si>
+    <t>3403.19.5000</t>
+  </si>
+  <si>
+    <t>VISTA SUPPLY &amp; SERVICES LLC</t>
+  </si>
+  <si>
+    <t>VISSUP</t>
+  </si>
+  <si>
+    <t>26-240695700</t>
+  </si>
+  <si>
+    <t>PFINDER KG</t>
+  </si>
+  <si>
+    <t>2615635-5</t>
+  </si>
+  <si>
+    <t>EF4-0231643-6</t>
+  </si>
+  <si>
+    <t>9903.82.09,8483.20.8080</t>
+  </si>
+  <si>
+    <t>AUMUND FOERDERTECHNIK GMBH</t>
+  </si>
+  <si>
+    <t>2615620-2</t>
+  </si>
+  <si>
+    <t>EF4-0231664-2</t>
+  </si>
+  <si>
+    <t>9903.82.10,8483.60.8000</t>
+  </si>
+  <si>
+    <t>SCHADE LAGERTECHNIK GMBH</t>
+  </si>
+  <si>
+    <t>2615620-1</t>
+  </si>
+  <si>
+    <t>EF4-0231665-9</t>
+  </si>
+  <si>
+    <t>8483.40.3040</t>
+  </si>
+  <si>
+    <t>MAHA USA LLC</t>
+  </si>
+  <si>
+    <t>MAHUSA</t>
+  </si>
+  <si>
+    <t>52-213556300</t>
+  </si>
+  <si>
+    <t>GRADEL BAUDIN</t>
+  </si>
+  <si>
+    <t>2615620-4</t>
+  </si>
+  <si>
+    <t>EF4-0231666-7</t>
+  </si>
+  <si>
+    <t>9903.82.10,8431.39.0010</t>
+  </si>
+  <si>
+    <t>2615620-5</t>
+  </si>
+  <si>
+    <t>EF4-0231667-5</t>
+  </si>
+  <si>
+    <t>7019.66.4096</t>
+  </si>
+  <si>
+    <t>KAST TECHNICAL TEXTILES LP</t>
+  </si>
+  <si>
+    <t>KASTEC01</t>
+  </si>
+  <si>
+    <t>84-488647400</t>
+  </si>
+  <si>
+    <t>TOLNATEXT FONALFELDOLGOZO ES MUSZAK</t>
+  </si>
+  <si>
+    <t>TOLNATEXT FONALFELDOLGOZO ES MUSZAKISZOVET-GYARTO BT.</t>
+  </si>
+  <si>
+    <t>2615620-6</t>
+  </si>
+  <si>
+    <t>EF4-0231668-3</t>
+  </si>
+  <si>
+    <t>9903.82.02,7318.15.8085</t>
+  </si>
+  <si>
+    <t>9903.88.03</t>
+  </si>
+  <si>
+    <t>ARTICLE OF CHINA,US NTE 20(F)</t>
+  </si>
+  <si>
+    <t>9903.03.06,9903.82.02,7320.90.5060</t>
+  </si>
+  <si>
+    <t>2565414</t>
+  </si>
+  <si>
+    <t>EF4-0231925-7</t>
+  </si>
+  <si>
+    <t>9903.82.02,7222.20.0062</t>
+  </si>
+  <si>
+    <t>MESHA STEELS  LLC</t>
+  </si>
+  <si>
+    <t>MESSTE</t>
+  </si>
+  <si>
+    <t>20-274801900</t>
+  </si>
+  <si>
+    <t>BHANSALI BRIGHT BARS PVT. LTD.</t>
+  </si>
+  <si>
+    <t>9903.82.02,7222.20.0064</t>
+  </si>
+  <si>
+    <t>2565466</t>
+  </si>
+  <si>
+    <t>EF4-0231928-1</t>
+  </si>
+  <si>
+    <t>2565842</t>
+  </si>
+  <si>
+    <t>EF4-0231957-0</t>
   </si>
   <si>
     <t>8474.10.0010</t>
@@ -133,108 +544,6 @@
   </si>
   <si>
     <t>135501-01432</t>
-  </si>
-  <si>
-    <t>2565576</t>
-  </si>
-  <si>
-    <t>EF4-0231386-2</t>
-  </si>
-  <si>
-    <t>9903.03.03</t>
-  </si>
-  <si>
-    <t>S122 -EXCLUSION-EXEMPTED PRDTS</t>
-  </si>
-  <si>
-    <t>2930.90.9231</t>
-  </si>
-  <si>
-    <t>CASTLE CHEMICALS LTD</t>
-  </si>
-  <si>
-    <t>CASCHE01</t>
-  </si>
-  <si>
-    <t>151704-07138</t>
-  </si>
-  <si>
-    <t>HUBEI JIANGHAN NEW MATERIALS CO</t>
-  </si>
-  <si>
-    <t>2565812</t>
-  </si>
-  <si>
-    <t>EF4-0231761-6</t>
-  </si>
-  <si>
-    <t>9903.03.06</t>
-  </si>
-  <si>
-    <t>S122 EXCL,IRN/STL/ALUM,DERIV</t>
-  </si>
-  <si>
-    <t>9903.82.09,8302.42.3065</t>
-  </si>
-  <si>
-    <t>GRASS GMBH</t>
-  </si>
-  <si>
-    <t>002</t>
-  </si>
-  <si>
-    <t>9903.82.09,8302.42.3015</t>
-  </si>
-  <si>
-    <t>003</t>
-  </si>
-  <si>
-    <t>3926.30.5000</t>
-  </si>
-  <si>
-    <t>105504713</t>
-  </si>
-  <si>
-    <t>EF4-0231831-7</t>
-  </si>
-  <si>
-    <t>9805.00.50</t>
-  </si>
-  <si>
-    <t>EFFECTS US GOV EMP&amp;FAMLY/EVACU</t>
-  </si>
-  <si>
-    <t>IFF, INC.</t>
-  </si>
-  <si>
-    <t>10</t>
-  </si>
-  <si>
-    <t>58-149385700</t>
-  </si>
-  <si>
-    <t>VOLVO CAR INTERNATIONAL CORPORATION</t>
-  </si>
-  <si>
-    <t>105504721</t>
-  </si>
-  <si>
-    <t>EF4-0231843-2</t>
-  </si>
-  <si>
-    <t>VOLVO CARS GHENT</t>
-  </si>
-  <si>
-    <t>105504722</t>
-  </si>
-  <si>
-    <t>EF4-0231844-0</t>
-  </si>
-  <si>
-    <t>105504724</t>
-  </si>
-  <si>
-    <t>EF4-0231846-5</t>
   </si>
 </sst>
 </file>
@@ -1179,7 +1488,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:Q11"/>
+  <dimension ref="A1:Q42"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="23.7109375" customWidth="true"/>
@@ -1295,60 +1604,60 @@
         <v>46169</v>
       </c>
       <c r="N2" s="46">
-        <v>46169</v>
+        <v>46170</v>
       </c>
       <c r="O2" s="47" t="s">
         <v>28</v>
       </c>
       <c r="P2" s="48" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="Q2" s="49">
-        <v>46133</v>
+        <v>46076</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="33" t="s">
+        <v>29</v>
+      </c>
+      <c r="B3" s="34" t="s">
         <v>30</v>
       </c>
-      <c r="B3" s="34" t="s">
-        <v>31</v>
-      </c>
       <c r="C3" s="35" t="s">
+        <v>19</v>
+      </c>
+      <c r="D3" s="36" t="s">
+        <v>20</v>
+      </c>
+      <c r="E3" s="37" t="s">
+        <v>31</v>
+      </c>
+      <c r="F3" s="38" t="s">
         <v>32</v>
-      </c>
-      <c r="D3" s="36" t="s">
-        <v>33</v>
-      </c>
-      <c r="E3" s="37" t="s">
-        <v>34</v>
-      </c>
-      <c r="F3" s="38" t="s">
-        <v>35</v>
       </c>
       <c r="G3" s="39" t="s">
         <v>23</v>
       </c>
       <c r="H3" s="40" t="s">
+        <v>31</v>
+      </c>
+      <c r="I3" s="41" t="s">
+        <v>33</v>
+      </c>
+      <c r="J3" s="42" t="s">
         <v>34</v>
       </c>
-      <c r="I3" s="41" t="s">
+      <c r="K3" s="43" t="s">
+        <v>35</v>
+      </c>
+      <c r="L3" s="44" t="s">
         <v>36</v>
       </c>
-      <c r="J3" s="42" t="s">
-        <v>37</v>
-      </c>
-      <c r="K3" s="43" t="s">
-        <v>38</v>
-      </c>
-      <c r="L3" s="44" t="s">
-        <v>39</v>
-      </c>
       <c r="M3" s="45">
-        <v>46159</v>
+        <v>46170</v>
       </c>
       <c r="N3" s="46">
-        <v>46169</v>
+        <v>46170</v>
       </c>
       <c r="O3" s="47" t="s">
         <v>37</v>
@@ -1357,227 +1666,227 @@
         <v>37</v>
       </c>
       <c r="Q3" s="49">
-        <v>46133</v>
+        <v>46104</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="33" t="s">
+        <v>29</v>
+      </c>
+      <c r="B4" s="34" t="s">
+        <v>30</v>
+      </c>
+      <c r="C4" s="35" t="s">
+        <v>19</v>
+      </c>
+      <c r="D4" s="36" t="s">
+        <v>20</v>
+      </c>
+      <c r="E4" s="37" t="s">
+        <v>31</v>
+      </c>
+      <c r="F4" s="38" t="s">
+        <v>32</v>
+      </c>
+      <c r="G4" s="39" t="s">
+        <v>38</v>
+      </c>
+      <c r="H4" s="40" t="s">
+        <v>31</v>
+      </c>
+      <c r="I4" s="41" t="s">
+        <v>39</v>
+      </c>
+      <c r="J4" s="42" t="s">
+        <v>34</v>
+      </c>
+      <c r="K4" s="43" t="s">
+        <v>35</v>
+      </c>
+      <c r="L4" s="44" t="s">
+        <v>36</v>
+      </c>
+      <c r="M4" s="45">
+        <v>46170</v>
+      </c>
+      <c r="N4" s="46">
+        <v>46170</v>
+      </c>
+      <c r="O4" s="47" t="s">
         <v>40</v>
       </c>
-      <c r="B4" s="34" t="s">
-        <v>41</v>
-      </c>
-      <c r="C4" s="35" t="s">
-        <v>32</v>
-      </c>
-      <c r="D4" s="36" t="s">
-        <v>33</v>
-      </c>
-      <c r="E4" s="37" t="s">
-        <v>42</v>
-      </c>
-      <c r="F4" s="38" t="s">
-        <v>43</v>
-      </c>
-      <c r="G4" s="39" t="s">
-        <v>23</v>
-      </c>
-      <c r="H4" s="40" t="s">
-        <v>42</v>
-      </c>
-      <c r="I4" s="41" t="s">
-        <v>44</v>
-      </c>
-      <c r="J4" s="42" t="s">
-        <v>45</v>
-      </c>
-      <c r="K4" s="43" t="s">
-        <v>46</v>
-      </c>
-      <c r="L4" s="44" t="s">
-        <v>47</v>
-      </c>
-      <c r="M4" s="45">
-        <v>46169</v>
-      </c>
-      <c r="N4" s="46">
-        <v>46169</v>
-      </c>
-      <c r="O4" s="47" t="s">
-        <v>48</v>
-      </c>
       <c r="P4" s="48" t="s">
-        <v>48</v>
+        <v>40</v>
       </c>
       <c r="Q4" s="49">
-        <v>46120</v>
+        <v>46104</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="33" t="s">
-        <v>49</v>
+        <v>29</v>
       </c>
       <c r="B5" s="34" t="s">
-        <v>50</v>
+        <v>30</v>
       </c>
       <c r="C5" s="35" t="s">
-        <v>32</v>
+        <v>19</v>
       </c>
       <c r="D5" s="36" t="s">
         <v>20</v>
       </c>
       <c r="E5" s="37" t="s">
-        <v>51</v>
+        <v>31</v>
       </c>
       <c r="F5" s="38" t="s">
-        <v>52</v>
+        <v>32</v>
       </c>
       <c r="G5" s="39" t="s">
-        <v>23</v>
+        <v>41</v>
       </c>
       <c r="H5" s="40" t="s">
-        <v>51</v>
+        <v>31</v>
       </c>
       <c r="I5" s="41" t="s">
-        <v>53</v>
+        <v>42</v>
       </c>
       <c r="J5" s="42" t="s">
-        <v>25</v>
+        <v>34</v>
       </c>
       <c r="K5" s="43" t="s">
-        <v>26</v>
+        <v>35</v>
       </c>
       <c r="L5" s="44" t="s">
-        <v>27</v>
+        <v>36</v>
       </c>
       <c r="M5" s="45">
-        <v>46169</v>
+        <v>46170</v>
       </c>
       <c r="N5" s="46">
-        <v>46169</v>
+        <v>46170</v>
       </c>
       <c r="O5" s="47" t="s">
-        <v>54</v>
+        <v>40</v>
       </c>
       <c r="P5" s="48" t="s">
-        <v>54</v>
+        <v>40</v>
       </c>
       <c r="Q5" s="49">
-        <v>46152</v>
+        <v>46104</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="33" t="s">
-        <v>49</v>
+        <v>29</v>
       </c>
       <c r="B6" s="34" t="s">
-        <v>50</v>
+        <v>30</v>
       </c>
       <c r="C6" s="35" t="s">
-        <v>32</v>
+        <v>19</v>
       </c>
       <c r="D6" s="36" t="s">
         <v>20</v>
       </c>
       <c r="E6" s="37" t="s">
-        <v>51</v>
+        <v>31</v>
       </c>
       <c r="F6" s="38" t="s">
-        <v>52</v>
+        <v>32</v>
       </c>
       <c r="G6" s="39" t="s">
-        <v>55</v>
+        <v>43</v>
       </c>
       <c r="H6" s="40" t="s">
-        <v>51</v>
+        <v>31</v>
       </c>
       <c r="I6" s="41" t="s">
-        <v>56</v>
+        <v>44</v>
       </c>
       <c r="J6" s="42" t="s">
-        <v>25</v>
+        <v>34</v>
       </c>
       <c r="K6" s="43" t="s">
-        <v>26</v>
+        <v>35</v>
       </c>
       <c r="L6" s="44" t="s">
-        <v>27</v>
+        <v>36</v>
       </c>
       <c r="M6" s="45">
-        <v>46169</v>
+        <v>46170</v>
       </c>
       <c r="N6" s="46">
-        <v>46169</v>
+        <v>46170</v>
       </c>
       <c r="O6" s="47" t="s">
-        <v>54</v>
+        <v>40</v>
       </c>
       <c r="P6" s="48" t="s">
-        <v>54</v>
+        <v>40</v>
       </c>
       <c r="Q6" s="49">
-        <v>46152</v>
+        <v>46104</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="33" t="s">
-        <v>49</v>
+        <v>29</v>
       </c>
       <c r="B7" s="34" t="s">
-        <v>50</v>
+        <v>30</v>
       </c>
       <c r="C7" s="35" t="s">
-        <v>32</v>
+        <v>19</v>
       </c>
       <c r="D7" s="36" t="s">
         <v>20</v>
       </c>
       <c r="E7" s="37" t="s">
+        <v>31</v>
+      </c>
+      <c r="F7" s="38" t="s">
+        <v>32</v>
+      </c>
+      <c r="G7" s="39" t="s">
+        <v>45</v>
+      </c>
+      <c r="H7" s="40" t="s">
+        <v>31</v>
+      </c>
+      <c r="I7" s="41" t="s">
+        <v>46</v>
+      </c>
+      <c r="J7" s="42" t="s">
         <v>34</v>
       </c>
-      <c r="F7" s="38" t="s">
+      <c r="K7" s="43" t="s">
         <v>35</v>
       </c>
-      <c r="G7" s="39" t="s">
-        <v>57</v>
-      </c>
-      <c r="H7" s="40" t="s">
-        <v>34</v>
-      </c>
-      <c r="I7" s="41" t="s">
-        <v>58</v>
-      </c>
-      <c r="J7" s="42" t="s">
-        <v>25</v>
-      </c>
-      <c r="K7" s="43" t="s">
-        <v>26</v>
-      </c>
       <c r="L7" s="44" t="s">
-        <v>27</v>
+        <v>36</v>
       </c>
       <c r="M7" s="45">
-        <v>46169</v>
+        <v>46170</v>
       </c>
       <c r="N7" s="46">
-        <v>46169</v>
+        <v>46170</v>
       </c>
       <c r="O7" s="47" t="s">
-        <v>54</v>
+        <v>40</v>
       </c>
       <c r="P7" s="48" t="s">
-        <v>54</v>
+        <v>40</v>
       </c>
       <c r="Q7" s="49">
-        <v>46152</v>
+        <v>46104</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="33" t="s">
-        <v>59</v>
+        <v>29</v>
       </c>
       <c r="B8" s="34" t="s">
-        <v>60</v>
+        <v>30</v>
       </c>
       <c r="C8" s="35" t="s">
         <v>19</v>
@@ -1586,51 +1895,51 @@
         <v>20</v>
       </c>
       <c r="E8" s="37" t="s">
-        <v>61</v>
+        <v>31</v>
       </c>
       <c r="F8" s="38" t="s">
-        <v>62</v>
+        <v>32</v>
       </c>
       <c r="G8" s="39" t="s">
-        <v>23</v>
+        <v>47</v>
       </c>
       <c r="H8" s="40" t="s">
-        <v>61</v>
+        <v>31</v>
       </c>
       <c r="I8" s="41" t="s">
-        <v>20</v>
+        <v>48</v>
       </c>
       <c r="J8" s="42" t="s">
-        <v>63</v>
+        <v>34</v>
       </c>
       <c r="K8" s="43" t="s">
-        <v>64</v>
+        <v>35</v>
       </c>
       <c r="L8" s="44" t="s">
-        <v>65</v>
+        <v>36</v>
       </c>
       <c r="M8" s="45">
         <v>46170</v>
       </c>
       <c r="N8" s="46">
-        <v>46169</v>
+        <v>46170</v>
       </c>
       <c r="O8" s="47" t="s">
-        <v>66</v>
+        <v>40</v>
       </c>
       <c r="P8" s="48" t="s">
-        <v>66</v>
+        <v>40</v>
       </c>
       <c r="Q8" s="49">
-        <v>46156</v>
+        <v>46104</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="33" t="s">
-        <v>67</v>
+        <v>29</v>
       </c>
       <c r="B9" s="34" t="s">
-        <v>68</v>
+        <v>30</v>
       </c>
       <c r="C9" s="35" t="s">
         <v>19</v>
@@ -1639,51 +1948,51 @@
         <v>20</v>
       </c>
       <c r="E9" s="37" t="s">
-        <v>61</v>
+        <v>31</v>
       </c>
       <c r="F9" s="38" t="s">
-        <v>62</v>
+        <v>32</v>
       </c>
       <c r="G9" s="39" t="s">
-        <v>23</v>
+        <v>49</v>
       </c>
       <c r="H9" s="40" t="s">
-        <v>61</v>
+        <v>31</v>
       </c>
       <c r="I9" s="41" t="s">
-        <v>20</v>
+        <v>50</v>
       </c>
       <c r="J9" s="42" t="s">
-        <v>63</v>
+        <v>34</v>
       </c>
       <c r="K9" s="43" t="s">
-        <v>64</v>
+        <v>35</v>
       </c>
       <c r="L9" s="44" t="s">
-        <v>65</v>
+        <v>36</v>
       </c>
       <c r="M9" s="45">
         <v>46170</v>
       </c>
       <c r="N9" s="46">
-        <v>46169</v>
+        <v>46170</v>
       </c>
       <c r="O9" s="47" t="s">
-        <v>69</v>
+        <v>51</v>
       </c>
       <c r="P9" s="48" t="s">
-        <v>69</v>
+        <v>51</v>
       </c>
       <c r="Q9" s="49">
-        <v>46153</v>
+        <v>46104</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="33" t="s">
-        <v>70</v>
+        <v>29</v>
       </c>
       <c r="B10" s="34" t="s">
-        <v>71</v>
+        <v>30</v>
       </c>
       <c r="C10" s="35" t="s">
         <v>19</v>
@@ -1692,51 +2001,51 @@
         <v>20</v>
       </c>
       <c r="E10" s="37" t="s">
-        <v>61</v>
+        <v>31</v>
       </c>
       <c r="F10" s="38" t="s">
-        <v>62</v>
+        <v>32</v>
       </c>
       <c r="G10" s="39" t="s">
-        <v>23</v>
+        <v>52</v>
       </c>
       <c r="H10" s="40" t="s">
-        <v>61</v>
+        <v>31</v>
       </c>
       <c r="I10" s="41" t="s">
-        <v>20</v>
+        <v>53</v>
       </c>
       <c r="J10" s="42" t="s">
-        <v>63</v>
+        <v>34</v>
       </c>
       <c r="K10" s="43" t="s">
-        <v>64</v>
+        <v>35</v>
       </c>
       <c r="L10" s="44" t="s">
-        <v>65</v>
+        <v>36</v>
       </c>
       <c r="M10" s="45">
         <v>46170</v>
       </c>
       <c r="N10" s="46">
-        <v>46169</v>
+        <v>46170</v>
       </c>
       <c r="O10" s="47" t="s">
-        <v>69</v>
+        <v>51</v>
       </c>
       <c r="P10" s="48" t="s">
-        <v>69</v>
+        <v>51</v>
       </c>
       <c r="Q10" s="49">
-        <v>46156</v>
+        <v>46104</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="33" t="s">
-        <v>72</v>
+        <v>29</v>
       </c>
       <c r="B11" s="34" t="s">
-        <v>73</v>
+        <v>30</v>
       </c>
       <c r="C11" s="35" t="s">
         <v>19</v>
@@ -1745,48 +2054,1691 @@
         <v>20</v>
       </c>
       <c r="E11" s="37" t="s">
+        <v>31</v>
+      </c>
+      <c r="F11" s="38" t="s">
+        <v>32</v>
+      </c>
+      <c r="G11" s="39" t="s">
+        <v>54</v>
+      </c>
+      <c r="H11" s="40" t="s">
+        <v>31</v>
+      </c>
+      <c r="I11" s="41" t="s">
+        <v>55</v>
+      </c>
+      <c r="J11" s="42" t="s">
+        <v>34</v>
+      </c>
+      <c r="K11" s="43" t="s">
+        <v>35</v>
+      </c>
+      <c r="L11" s="44" t="s">
+        <v>36</v>
+      </c>
+      <c r="M11" s="45">
+        <v>46170</v>
+      </c>
+      <c r="N11" s="46">
+        <v>46170</v>
+      </c>
+      <c r="O11" s="47" t="s">
+        <v>51</v>
+      </c>
+      <c r="P11" s="48" t="s">
+        <v>51</v>
+      </c>
+      <c r="Q11" s="49">
+        <v>46104</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="33" t="s">
+        <v>29</v>
+      </c>
+      <c r="B12" s="34" t="s">
+        <v>30</v>
+      </c>
+      <c r="C12" s="35" t="s">
+        <v>19</v>
+      </c>
+      <c r="D12" s="36" t="s">
+        <v>20</v>
+      </c>
+      <c r="E12" s="37" t="s">
+        <v>31</v>
+      </c>
+      <c r="F12" s="38" t="s">
+        <v>32</v>
+      </c>
+      <c r="G12" s="39" t="s">
+        <v>56</v>
+      </c>
+      <c r="H12" s="40" t="s">
+        <v>31</v>
+      </c>
+      <c r="I12" s="41" t="s">
+        <v>57</v>
+      </c>
+      <c r="J12" s="42" t="s">
+        <v>34</v>
+      </c>
+      <c r="K12" s="43" t="s">
+        <v>35</v>
+      </c>
+      <c r="L12" s="44" t="s">
+        <v>36</v>
+      </c>
+      <c r="M12" s="45">
+        <v>46170</v>
+      </c>
+      <c r="N12" s="46">
+        <v>46170</v>
+      </c>
+      <c r="O12" s="47" t="s">
+        <v>51</v>
+      </c>
+      <c r="P12" s="48" t="s">
+        <v>51</v>
+      </c>
+      <c r="Q12" s="49">
+        <v>46104</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="33" t="s">
+        <v>29</v>
+      </c>
+      <c r="B13" s="34" t="s">
+        <v>30</v>
+      </c>
+      <c r="C13" s="35" t="s">
+        <v>19</v>
+      </c>
+      <c r="D13" s="36" t="s">
+        <v>20</v>
+      </c>
+      <c r="E13" s="37" t="s">
+        <v>31</v>
+      </c>
+      <c r="F13" s="38" t="s">
+        <v>32</v>
+      </c>
+      <c r="G13" s="39" t="s">
+        <v>58</v>
+      </c>
+      <c r="H13" s="40" t="s">
+        <v>31</v>
+      </c>
+      <c r="I13" s="41" t="s">
+        <v>48</v>
+      </c>
+      <c r="J13" s="42" t="s">
+        <v>34</v>
+      </c>
+      <c r="K13" s="43" t="s">
+        <v>35</v>
+      </c>
+      <c r="L13" s="44" t="s">
+        <v>36</v>
+      </c>
+      <c r="M13" s="45">
+        <v>46170</v>
+      </c>
+      <c r="N13" s="46">
+        <v>46170</v>
+      </c>
+      <c r="O13" s="47" t="s">
+        <v>59</v>
+      </c>
+      <c r="P13" s="48" t="s">
+        <v>59</v>
+      </c>
+      <c r="Q13" s="49">
+        <v>46104</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="33" t="s">
+        <v>60</v>
+      </c>
+      <c r="B14" s="34" t="s">
         <v>61</v>
       </c>
-      <c r="F11" s="38" t="s">
+      <c r="C14" s="35" t="s">
         <v>62</v>
       </c>
-      <c r="G11" s="39" t="s">
+      <c r="D14" s="36" t="s">
+        <v>20</v>
+      </c>
+      <c r="E14" s="37" t="s">
+        <v>31</v>
+      </c>
+      <c r="F14" s="38" t="s">
+        <v>32</v>
+      </c>
+      <c r="G14" s="39" t="s">
         <v>23</v>
       </c>
-      <c r="H11" s="40" t="s">
-        <v>61</v>
-      </c>
-      <c r="I11" s="41" t="s">
+      <c r="H14" s="40" t="s">
+        <v>31</v>
+      </c>
+      <c r="I14" s="41" t="s">
+        <v>63</v>
+      </c>
+      <c r="J14" s="42" t="s">
+        <v>64</v>
+      </c>
+      <c r="K14" s="43" t="s">
+        <v>65</v>
+      </c>
+      <c r="L14" s="44" t="s">
+        <v>66</v>
+      </c>
+      <c r="M14" s="45">
+        <v>46168</v>
+      </c>
+      <c r="N14" s="46">
+        <v>46170</v>
+      </c>
+      <c r="O14" s="47" t="s">
+        <v>67</v>
+      </c>
+      <c r="P14" s="48" t="s">
+        <v>67</v>
+      </c>
+      <c r="Q14" s="49">
+        <v>46132</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="33" t="s">
+        <v>68</v>
+      </c>
+      <c r="B15" s="34" t="s">
+        <v>69</v>
+      </c>
+      <c r="C15" s="35" t="s">
+        <v>19</v>
+      </c>
+      <c r="D15" s="36" t="s">
+        <v>70</v>
+      </c>
+      <c r="E15" s="37" t="s">
+        <v>31</v>
+      </c>
+      <c r="F15" s="38" t="s">
+        <v>32</v>
+      </c>
+      <c r="G15" s="39" t="s">
+        <v>23</v>
+      </c>
+      <c r="H15" s="40" t="s">
+        <v>31</v>
+      </c>
+      <c r="I15" s="41" t="s">
+        <v>71</v>
+      </c>
+      <c r="J15" s="42" t="s">
+        <v>72</v>
+      </c>
+      <c r="K15" s="43" t="s">
+        <v>73</v>
+      </c>
+      <c r="L15" s="44" t="s">
+        <v>74</v>
+      </c>
+      <c r="M15" s="45">
+        <v>46170</v>
+      </c>
+      <c r="N15" s="46">
+        <v>46170</v>
+      </c>
+      <c r="O15" s="47" t="s">
+        <v>75</v>
+      </c>
+      <c r="P15" s="48" t="s">
+        <v>75</v>
+      </c>
+      <c r="Q15" s="49">
+        <v>46131</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="33" t="s">
+        <v>76</v>
+      </c>
+      <c r="B16" s="34" t="s">
+        <v>77</v>
+      </c>
+      <c r="C16" s="35" t="s">
+        <v>19</v>
+      </c>
+      <c r="D16" s="36" t="s">
+        <v>70</v>
+      </c>
+      <c r="E16" s="37" t="s">
+        <v>31</v>
+      </c>
+      <c r="F16" s="38" t="s">
+        <v>32</v>
+      </c>
+      <c r="G16" s="39" t="s">
+        <v>23</v>
+      </c>
+      <c r="H16" s="40" t="s">
+        <v>31</v>
+      </c>
+      <c r="I16" s="41" t="s">
+        <v>78</v>
+      </c>
+      <c r="J16" s="42" t="s">
+        <v>79</v>
+      </c>
+      <c r="K16" s="43" t="s">
+        <v>80</v>
+      </c>
+      <c r="L16" s="44" t="s">
+        <v>81</v>
+      </c>
+      <c r="M16" s="45">
+        <v>46169</v>
+      </c>
+      <c r="N16" s="46">
+        <v>46170</v>
+      </c>
+      <c r="O16" s="47" t="s">
+        <v>82</v>
+      </c>
+      <c r="P16" s="48" t="s">
+        <v>82</v>
+      </c>
+      <c r="Q16" s="49">
+        <v>46134</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="33" t="s">
+        <v>76</v>
+      </c>
+      <c r="B17" s="34" t="s">
+        <v>77</v>
+      </c>
+      <c r="C17" s="35" t="s">
+        <v>19</v>
+      </c>
+      <c r="D17" s="36" t="s">
+        <v>70</v>
+      </c>
+      <c r="E17" s="37" t="s">
+        <v>31</v>
+      </c>
+      <c r="F17" s="38" t="s">
+        <v>32</v>
+      </c>
+      <c r="G17" s="39" t="s">
+        <v>38</v>
+      </c>
+      <c r="H17" s="40" t="s">
+        <v>31</v>
+      </c>
+      <c r="I17" s="41" t="s">
+        <v>83</v>
+      </c>
+      <c r="J17" s="42" t="s">
+        <v>79</v>
+      </c>
+      <c r="K17" s="43" t="s">
+        <v>80</v>
+      </c>
+      <c r="L17" s="44" t="s">
+        <v>81</v>
+      </c>
+      <c r="M17" s="45">
+        <v>46169</v>
+      </c>
+      <c r="N17" s="46">
+        <v>46170</v>
+      </c>
+      <c r="O17" s="47" t="s">
+        <v>82</v>
+      </c>
+      <c r="P17" s="48" t="s">
+        <v>82</v>
+      </c>
+      <c r="Q17" s="49">
+        <v>46134</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="33" t="s">
+        <v>84</v>
+      </c>
+      <c r="B18" s="34" t="s">
+        <v>85</v>
+      </c>
+      <c r="C18" s="35" t="s">
+        <v>19</v>
+      </c>
+      <c r="D18" s="36" t="s">
+        <v>86</v>
+      </c>
+      <c r="E18" s="37" t="s">
+        <v>31</v>
+      </c>
+      <c r="F18" s="38" t="s">
         <v>20</v>
       </c>
-      <c r="J11" s="42" t="s">
-        <v>63</v>
-      </c>
-      <c r="K11" s="43" t="s">
-        <v>64</v>
-      </c>
-      <c r="L11" s="44" t="s">
-        <v>65</v>
-      </c>
-      <c r="M11" s="45">
-        <v>46170</v>
-      </c>
-      <c r="N11" s="46">
-        <v>46169</v>
-      </c>
-      <c r="O11" s="47" t="s">
-        <v>66</v>
-      </c>
-      <c r="P11" s="48" t="s">
-        <v>66</v>
-      </c>
-      <c r="Q11" s="49">
-        <v>46153</v>
+      <c r="G18" s="39" t="s">
+        <v>23</v>
+      </c>
+      <c r="H18" s="40" t="s">
+        <v>31</v>
+      </c>
+      <c r="I18" s="41" t="s">
+        <v>87</v>
+      </c>
+      <c r="J18" s="42" t="s">
+        <v>88</v>
+      </c>
+      <c r="K18" s="43" t="s">
+        <v>89</v>
+      </c>
+      <c r="L18" s="44" t="s">
+        <v>90</v>
+      </c>
+      <c r="M18" s="45">
+        <v>46160</v>
+      </c>
+      <c r="N18" s="46">
+        <v>46170</v>
+      </c>
+      <c r="O18" s="47" t="s">
+        <v>91</v>
+      </c>
+      <c r="P18" s="48" t="s">
+        <v>91</v>
+      </c>
+      <c r="Q18" s="49">
+        <v>46137</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="33" t="s">
+        <v>92</v>
+      </c>
+      <c r="B19" s="34" t="s">
+        <v>93</v>
+      </c>
+      <c r="C19" s="35" t="s">
+        <v>19</v>
+      </c>
+      <c r="D19" s="36" t="s">
+        <v>86</v>
+      </c>
+      <c r="E19" s="37" t="s">
+        <v>94</v>
+      </c>
+      <c r="F19" s="38" t="s">
+        <v>95</v>
+      </c>
+      <c r="G19" s="39" t="s">
+        <v>23</v>
+      </c>
+      <c r="H19" s="40" t="s">
+        <v>94</v>
+      </c>
+      <c r="I19" s="41" t="s">
+        <v>96</v>
+      </c>
+      <c r="J19" s="42" t="s">
+        <v>97</v>
+      </c>
+      <c r="K19" s="43" t="s">
+        <v>98</v>
+      </c>
+      <c r="L19" s="44" t="s">
+        <v>99</v>
+      </c>
+      <c r="M19" s="45">
+        <v>46170</v>
+      </c>
+      <c r="N19" s="46">
+        <v>46170</v>
+      </c>
+      <c r="O19" s="47" t="s">
+        <v>100</v>
+      </c>
+      <c r="P19" s="48" t="s">
+        <v>100</v>
+      </c>
+      <c r="Q19" s="49">
+        <v>46131</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="33" t="s">
+        <v>101</v>
+      </c>
+      <c r="B20" s="34" t="s">
+        <v>102</v>
+      </c>
+      <c r="C20" s="35" t="s">
+        <v>19</v>
+      </c>
+      <c r="D20" s="36" t="s">
+        <v>86</v>
+      </c>
+      <c r="E20" s="37" t="s">
+        <v>31</v>
+      </c>
+      <c r="F20" s="38" t="s">
+        <v>32</v>
+      </c>
+      <c r="G20" s="39" t="s">
+        <v>23</v>
+      </c>
+      <c r="H20" s="40" t="s">
+        <v>31</v>
+      </c>
+      <c r="I20" s="41" t="s">
+        <v>103</v>
+      </c>
+      <c r="J20" s="42" t="s">
+        <v>88</v>
+      </c>
+      <c r="K20" s="43" t="s">
+        <v>89</v>
+      </c>
+      <c r="L20" s="44" t="s">
+        <v>90</v>
+      </c>
+      <c r="M20" s="45">
+        <v>46160</v>
+      </c>
+      <c r="N20" s="46">
+        <v>46170</v>
+      </c>
+      <c r="O20" s="47" t="s">
+        <v>104</v>
+      </c>
+      <c r="P20" s="48" t="s">
+        <v>104</v>
+      </c>
+      <c r="Q20" s="49">
+        <v>46141</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="33" t="s">
+        <v>105</v>
+      </c>
+      <c r="B21" s="34" t="s">
+        <v>106</v>
+      </c>
+      <c r="C21" s="35" t="s">
+        <v>19</v>
+      </c>
+      <c r="D21" s="36" t="s">
+        <v>86</v>
+      </c>
+      <c r="E21" s="37" t="s">
+        <v>31</v>
+      </c>
+      <c r="F21" s="38" t="s">
+        <v>32</v>
+      </c>
+      <c r="G21" s="39" t="s">
+        <v>23</v>
+      </c>
+      <c r="H21" s="40" t="s">
+        <v>31</v>
+      </c>
+      <c r="I21" s="41" t="s">
+        <v>103</v>
+      </c>
+      <c r="J21" s="42" t="s">
+        <v>88</v>
+      </c>
+      <c r="K21" s="43" t="s">
+        <v>89</v>
+      </c>
+      <c r="L21" s="44" t="s">
+        <v>90</v>
+      </c>
+      <c r="M21" s="45">
+        <v>46160</v>
+      </c>
+      <c r="N21" s="46">
+        <v>46170</v>
+      </c>
+      <c r="O21" s="47" t="s">
+        <v>104</v>
+      </c>
+      <c r="P21" s="48" t="s">
+        <v>104</v>
+      </c>
+      <c r="Q21" s="49">
+        <v>46141</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="33" t="s">
+        <v>107</v>
+      </c>
+      <c r="B22" s="34" t="s">
+        <v>108</v>
+      </c>
+      <c r="C22" s="35" t="s">
+        <v>62</v>
+      </c>
+      <c r="D22" s="36" t="s">
+        <v>86</v>
+      </c>
+      <c r="E22" s="37" t="s">
+        <v>31</v>
+      </c>
+      <c r="F22" s="38" t="s">
+        <v>32</v>
+      </c>
+      <c r="G22" s="39" t="s">
+        <v>23</v>
+      </c>
+      <c r="H22" s="40" t="s">
+        <v>31</v>
+      </c>
+      <c r="I22" s="41" t="s">
+        <v>109</v>
+      </c>
+      <c r="J22" s="42" t="s">
+        <v>110</v>
+      </c>
+      <c r="K22" s="43" t="s">
+        <v>111</v>
+      </c>
+      <c r="L22" s="44" t="s">
+        <v>112</v>
+      </c>
+      <c r="M22" s="45">
+        <v>46172</v>
+      </c>
+      <c r="N22" s="46">
+        <v>46170</v>
+      </c>
+      <c r="O22" s="47" t="s">
+        <v>113</v>
+      </c>
+      <c r="P22" s="48" t="s">
+        <v>113</v>
+      </c>
+      <c r="Q22" s="49">
+        <v>46152</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="33" t="s">
+        <v>114</v>
+      </c>
+      <c r="B23" s="34" t="s">
+        <v>115</v>
+      </c>
+      <c r="C23" s="35" t="s">
+        <v>62</v>
+      </c>
+      <c r="D23" s="36" t="s">
+        <v>20</v>
+      </c>
+      <c r="E23" s="37" t="s">
+        <v>31</v>
+      </c>
+      <c r="F23" s="38" t="s">
+        <v>32</v>
+      </c>
+      <c r="G23" s="39" t="s">
+        <v>23</v>
+      </c>
+      <c r="H23" s="40" t="s">
+        <v>31</v>
+      </c>
+      <c r="I23" s="41" t="s">
+        <v>116</v>
+      </c>
+      <c r="J23" s="42" t="s">
+        <v>117</v>
+      </c>
+      <c r="K23" s="43" t="s">
+        <v>118</v>
+      </c>
+      <c r="L23" s="44" t="s">
+        <v>119</v>
+      </c>
+      <c r="M23" s="45">
+        <v>46172</v>
+      </c>
+      <c r="N23" s="46">
+        <v>46170</v>
+      </c>
+      <c r="O23" s="47" t="s">
+        <v>120</v>
+      </c>
+      <c r="P23" s="48" t="s">
+        <v>120</v>
+      </c>
+      <c r="Q23" s="49">
+        <v>46152</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="33" t="s">
+        <v>114</v>
+      </c>
+      <c r="B24" s="34" t="s">
+        <v>115</v>
+      </c>
+      <c r="C24" s="35" t="s">
+        <v>62</v>
+      </c>
+      <c r="D24" s="36" t="s">
+        <v>20</v>
+      </c>
+      <c r="E24" s="37" t="s">
+        <v>31</v>
+      </c>
+      <c r="F24" s="38" t="s">
+        <v>32</v>
+      </c>
+      <c r="G24" s="39" t="s">
+        <v>38</v>
+      </c>
+      <c r="H24" s="40" t="s">
+        <v>31</v>
+      </c>
+      <c r="I24" s="41" t="s">
+        <v>121</v>
+      </c>
+      <c r="J24" s="42" t="s">
+        <v>117</v>
+      </c>
+      <c r="K24" s="43" t="s">
+        <v>118</v>
+      </c>
+      <c r="L24" s="44" t="s">
+        <v>119</v>
+      </c>
+      <c r="M24" s="45">
+        <v>46172</v>
+      </c>
+      <c r="N24" s="46">
+        <v>46170</v>
+      </c>
+      <c r="O24" s="47" t="s">
+        <v>120</v>
+      </c>
+      <c r="P24" s="48" t="s">
+        <v>120</v>
+      </c>
+      <c r="Q24" s="49">
+        <v>46152</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="33" t="s">
+        <v>114</v>
+      </c>
+      <c r="B25" s="34" t="s">
+        <v>115</v>
+      </c>
+      <c r="C25" s="35" t="s">
+        <v>62</v>
+      </c>
+      <c r="D25" s="36" t="s">
+        <v>20</v>
+      </c>
+      <c r="E25" s="37" t="s">
+        <v>31</v>
+      </c>
+      <c r="F25" s="38" t="s">
+        <v>32</v>
+      </c>
+      <c r="G25" s="39" t="s">
+        <v>41</v>
+      </c>
+      <c r="H25" s="40" t="s">
+        <v>31</v>
+      </c>
+      <c r="I25" s="41" t="s">
+        <v>116</v>
+      </c>
+      <c r="J25" s="42" t="s">
+        <v>117</v>
+      </c>
+      <c r="K25" s="43" t="s">
+        <v>118</v>
+      </c>
+      <c r="L25" s="44" t="s">
+        <v>119</v>
+      </c>
+      <c r="M25" s="45">
+        <v>46172</v>
+      </c>
+      <c r="N25" s="46">
+        <v>46170</v>
+      </c>
+      <c r="O25" s="47" t="s">
+        <v>120</v>
+      </c>
+      <c r="P25" s="48" t="s">
+        <v>120</v>
+      </c>
+      <c r="Q25" s="49">
+        <v>46152</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="33" t="s">
+        <v>114</v>
+      </c>
+      <c r="B26" s="34" t="s">
+        <v>115</v>
+      </c>
+      <c r="C26" s="35" t="s">
+        <v>62</v>
+      </c>
+      <c r="D26" s="36" t="s">
+        <v>20</v>
+      </c>
+      <c r="E26" s="37" t="s">
+        <v>31</v>
+      </c>
+      <c r="F26" s="38" t="s">
+        <v>32</v>
+      </c>
+      <c r="G26" s="39" t="s">
+        <v>43</v>
+      </c>
+      <c r="H26" s="40" t="s">
+        <v>31</v>
+      </c>
+      <c r="I26" s="41" t="s">
+        <v>116</v>
+      </c>
+      <c r="J26" s="42" t="s">
+        <v>117</v>
+      </c>
+      <c r="K26" s="43" t="s">
+        <v>118</v>
+      </c>
+      <c r="L26" s="44" t="s">
+        <v>119</v>
+      </c>
+      <c r="M26" s="45">
+        <v>46172</v>
+      </c>
+      <c r="N26" s="46">
+        <v>46170</v>
+      </c>
+      <c r="O26" s="47" t="s">
+        <v>120</v>
+      </c>
+      <c r="P26" s="48" t="s">
+        <v>120</v>
+      </c>
+      <c r="Q26" s="49">
+        <v>46152</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="33" t="s">
+        <v>122</v>
+      </c>
+      <c r="B27" s="34" t="s">
+        <v>123</v>
+      </c>
+      <c r="C27" s="35" t="s">
+        <v>62</v>
+      </c>
+      <c r="D27" s="36" t="s">
+        <v>20</v>
+      </c>
+      <c r="E27" s="37" t="s">
+        <v>31</v>
+      </c>
+      <c r="F27" s="38" t="s">
+        <v>32</v>
+      </c>
+      <c r="G27" s="39" t="s">
+        <v>23</v>
+      </c>
+      <c r="H27" s="40" t="s">
+        <v>31</v>
+      </c>
+      <c r="I27" s="41" t="s">
+        <v>124</v>
+      </c>
+      <c r="J27" s="42" t="s">
+        <v>125</v>
+      </c>
+      <c r="K27" s="43" t="s">
+        <v>126</v>
+      </c>
+      <c r="L27" s="44" t="s">
+        <v>127</v>
+      </c>
+      <c r="M27" s="45">
+        <v>46172</v>
+      </c>
+      <c r="N27" s="46">
+        <v>46170</v>
+      </c>
+      <c r="O27" s="47" t="s">
+        <v>128</v>
+      </c>
+      <c r="P27" s="48" t="s">
+        <v>128</v>
+      </c>
+      <c r="Q27" s="49">
+        <v>46152</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="33" t="s">
+        <v>129</v>
+      </c>
+      <c r="B28" s="34" t="s">
+        <v>130</v>
+      </c>
+      <c r="C28" s="35" t="s">
+        <v>62</v>
+      </c>
+      <c r="D28" s="36" t="s">
+        <v>20</v>
+      </c>
+      <c r="E28" s="37" t="s">
+        <v>21</v>
+      </c>
+      <c r="F28" s="38" t="s">
+        <v>22</v>
+      </c>
+      <c r="G28" s="39" t="s">
+        <v>23</v>
+      </c>
+      <c r="H28" s="40" t="s">
+        <v>21</v>
+      </c>
+      <c r="I28" s="41" t="s">
+        <v>131</v>
+      </c>
+      <c r="J28" s="42" t="s">
+        <v>25</v>
+      </c>
+      <c r="K28" s="43" t="s">
+        <v>26</v>
+      </c>
+      <c r="L28" s="44" t="s">
+        <v>27</v>
+      </c>
+      <c r="M28" s="45">
+        <v>46172</v>
+      </c>
+      <c r="N28" s="46">
+        <v>46170</v>
+      </c>
+      <c r="O28" s="47" t="s">
+        <v>132</v>
+      </c>
+      <c r="P28" s="48" t="s">
+        <v>132</v>
+      </c>
+      <c r="Q28" s="49">
+        <v>46152</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="33" t="s">
+        <v>133</v>
+      </c>
+      <c r="B29" s="34" t="s">
+        <v>134</v>
+      </c>
+      <c r="C29" s="35" t="s">
+        <v>62</v>
+      </c>
+      <c r="D29" s="36" t="s">
+        <v>20</v>
+      </c>
+      <c r="E29" s="37" t="s">
+        <v>21</v>
+      </c>
+      <c r="F29" s="38" t="s">
+        <v>22</v>
+      </c>
+      <c r="G29" s="39" t="s">
+        <v>23</v>
+      </c>
+      <c r="H29" s="40" t="s">
+        <v>21</v>
+      </c>
+      <c r="I29" s="41" t="s">
+        <v>135</v>
+      </c>
+      <c r="J29" s="42" t="s">
+        <v>25</v>
+      </c>
+      <c r="K29" s="43" t="s">
+        <v>26</v>
+      </c>
+      <c r="L29" s="44" t="s">
+        <v>27</v>
+      </c>
+      <c r="M29" s="45">
+        <v>46172</v>
+      </c>
+      <c r="N29" s="46">
+        <v>46170</v>
+      </c>
+      <c r="O29" s="47" t="s">
+        <v>136</v>
+      </c>
+      <c r="P29" s="48" t="s">
+        <v>136</v>
+      </c>
+      <c r="Q29" s="49">
+        <v>46152</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="33" t="s">
+        <v>137</v>
+      </c>
+      <c r="B30" s="34" t="s">
+        <v>138</v>
+      </c>
+      <c r="C30" s="35" t="s">
+        <v>62</v>
+      </c>
+      <c r="D30" s="36" t="s">
+        <v>20</v>
+      </c>
+      <c r="E30" s="37" t="s">
+        <v>31</v>
+      </c>
+      <c r="F30" s="38" t="s">
+        <v>32</v>
+      </c>
+      <c r="G30" s="39" t="s">
+        <v>23</v>
+      </c>
+      <c r="H30" s="40" t="s">
+        <v>31</v>
+      </c>
+      <c r="I30" s="41" t="s">
+        <v>139</v>
+      </c>
+      <c r="J30" s="42" t="s">
+        <v>140</v>
+      </c>
+      <c r="K30" s="43" t="s">
+        <v>141</v>
+      </c>
+      <c r="L30" s="44" t="s">
+        <v>142</v>
+      </c>
+      <c r="M30" s="45">
+        <v>46172</v>
+      </c>
+      <c r="N30" s="46">
+        <v>46170</v>
+      </c>
+      <c r="O30" s="47" t="s">
+        <v>143</v>
+      </c>
+      <c r="P30" s="48" t="s">
+        <v>143</v>
+      </c>
+      <c r="Q30" s="49">
+        <v>46152</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="33" t="s">
+        <v>144</v>
+      </c>
+      <c r="B31" s="34" t="s">
+        <v>145</v>
+      </c>
+      <c r="C31" s="35" t="s">
+        <v>62</v>
+      </c>
+      <c r="D31" s="36" t="s">
+        <v>20</v>
+      </c>
+      <c r="E31" s="37" t="s">
+        <v>21</v>
+      </c>
+      <c r="F31" s="38" t="s">
+        <v>22</v>
+      </c>
+      <c r="G31" s="39" t="s">
+        <v>23</v>
+      </c>
+      <c r="H31" s="40" t="s">
+        <v>21</v>
+      </c>
+      <c r="I31" s="41" t="s">
+        <v>146</v>
+      </c>
+      <c r="J31" s="42" t="s">
+        <v>25</v>
+      </c>
+      <c r="K31" s="43" t="s">
+        <v>26</v>
+      </c>
+      <c r="L31" s="44" t="s">
+        <v>27</v>
+      </c>
+      <c r="M31" s="45">
+        <v>46172</v>
+      </c>
+      <c r="N31" s="46">
+        <v>46170</v>
+      </c>
+      <c r="O31" s="47" t="s">
+        <v>132</v>
+      </c>
+      <c r="P31" s="48" t="s">
+        <v>132</v>
+      </c>
+      <c r="Q31" s="49">
+        <v>46152</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="33" t="s">
+        <v>144</v>
+      </c>
+      <c r="B32" s="34" t="s">
+        <v>145</v>
+      </c>
+      <c r="C32" s="35" t="s">
+        <v>62</v>
+      </c>
+      <c r="D32" s="36" t="s">
+        <v>20</v>
+      </c>
+      <c r="E32" s="37" t="s">
+        <v>21</v>
+      </c>
+      <c r="F32" s="38" t="s">
+        <v>22</v>
+      </c>
+      <c r="G32" s="39" t="s">
+        <v>38</v>
+      </c>
+      <c r="H32" s="40" t="s">
+        <v>21</v>
+      </c>
+      <c r="I32" s="41" t="s">
+        <v>146</v>
+      </c>
+      <c r="J32" s="42" t="s">
+        <v>25</v>
+      </c>
+      <c r="K32" s="43" t="s">
+        <v>26</v>
+      </c>
+      <c r="L32" s="44" t="s">
+        <v>27</v>
+      </c>
+      <c r="M32" s="45">
+        <v>46172</v>
+      </c>
+      <c r="N32" s="46">
+        <v>46170</v>
+      </c>
+      <c r="O32" s="47" t="s">
+        <v>132</v>
+      </c>
+      <c r="P32" s="48" t="s">
+        <v>132</v>
+      </c>
+      <c r="Q32" s="49">
+        <v>46152</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="33" t="s">
+        <v>147</v>
+      </c>
+      <c r="B33" s="34" t="s">
+        <v>148</v>
+      </c>
+      <c r="C33" s="35" t="s">
+        <v>62</v>
+      </c>
+      <c r="D33" s="36" t="s">
+        <v>20</v>
+      </c>
+      <c r="E33" s="37" t="s">
+        <v>31</v>
+      </c>
+      <c r="F33" s="38" t="s">
+        <v>32</v>
+      </c>
+      <c r="G33" s="39" t="s">
+        <v>23</v>
+      </c>
+      <c r="H33" s="40" t="s">
+        <v>31</v>
+      </c>
+      <c r="I33" s="41" t="s">
+        <v>149</v>
+      </c>
+      <c r="J33" s="42" t="s">
+        <v>150</v>
+      </c>
+      <c r="K33" s="43" t="s">
+        <v>151</v>
+      </c>
+      <c r="L33" s="44" t="s">
+        <v>152</v>
+      </c>
+      <c r="M33" s="45">
+        <v>46172</v>
+      </c>
+      <c r="N33" s="46">
+        <v>46170</v>
+      </c>
+      <c r="O33" s="47" t="s">
+        <v>153</v>
+      </c>
+      <c r="P33" s="48" t="s">
+        <v>154</v>
+      </c>
+      <c r="Q33" s="49">
+        <v>46152</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="33" t="s">
+        <v>147</v>
+      </c>
+      <c r="B34" s="34" t="s">
+        <v>148</v>
+      </c>
+      <c r="C34" s="35" t="s">
+        <v>62</v>
+      </c>
+      <c r="D34" s="36" t="s">
+        <v>20</v>
+      </c>
+      <c r="E34" s="37" t="s">
+        <v>31</v>
+      </c>
+      <c r="F34" s="38" t="s">
+        <v>32</v>
+      </c>
+      <c r="G34" s="39" t="s">
+        <v>38</v>
+      </c>
+      <c r="H34" s="40" t="s">
+        <v>31</v>
+      </c>
+      <c r="I34" s="41" t="s">
+        <v>149</v>
+      </c>
+      <c r="J34" s="42" t="s">
+        <v>150</v>
+      </c>
+      <c r="K34" s="43" t="s">
+        <v>151</v>
+      </c>
+      <c r="L34" s="44" t="s">
+        <v>152</v>
+      </c>
+      <c r="M34" s="45">
+        <v>46172</v>
+      </c>
+      <c r="N34" s="46">
+        <v>46170</v>
+      </c>
+      <c r="O34" s="47" t="s">
+        <v>153</v>
+      </c>
+      <c r="P34" s="48" t="s">
+        <v>154</v>
+      </c>
+      <c r="Q34" s="49">
+        <v>46152</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="33" t="s">
+        <v>155</v>
+      </c>
+      <c r="B35" s="34" t="s">
+        <v>156</v>
+      </c>
+      <c r="C35" s="35" t="s">
+        <v>62</v>
+      </c>
+      <c r="D35" s="36" t="s">
+        <v>20</v>
+      </c>
+      <c r="E35" s="37" t="s">
+        <v>21</v>
+      </c>
+      <c r="F35" s="38" t="s">
+        <v>22</v>
+      </c>
+      <c r="G35" s="39" t="s">
+        <v>23</v>
+      </c>
+      <c r="H35" s="40" t="s">
+        <v>21</v>
+      </c>
+      <c r="I35" s="41" t="s">
+        <v>157</v>
+      </c>
+      <c r="J35" s="42" t="s">
+        <v>25</v>
+      </c>
+      <c r="K35" s="43" t="s">
+        <v>26</v>
+      </c>
+      <c r="L35" s="44" t="s">
+        <v>27</v>
+      </c>
+      <c r="M35" s="45">
+        <v>46172</v>
+      </c>
+      <c r="N35" s="46">
+        <v>46170</v>
+      </c>
+      <c r="O35" s="47" t="s">
+        <v>132</v>
+      </c>
+      <c r="P35" s="48" t="s">
+        <v>132</v>
+      </c>
+      <c r="Q35" s="49">
+        <v>46152</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="33" t="s">
+        <v>155</v>
+      </c>
+      <c r="B36" s="34" t="s">
+        <v>156</v>
+      </c>
+      <c r="C36" s="35" t="s">
+        <v>62</v>
+      </c>
+      <c r="D36" s="36" t="s">
+        <v>20</v>
+      </c>
+      <c r="E36" s="37" t="s">
+        <v>21</v>
+      </c>
+      <c r="F36" s="38" t="s">
+        <v>22</v>
+      </c>
+      <c r="G36" s="39" t="s">
+        <v>38</v>
+      </c>
+      <c r="H36" s="40" t="s">
+        <v>21</v>
+      </c>
+      <c r="I36" s="41" t="s">
+        <v>146</v>
+      </c>
+      <c r="J36" s="42" t="s">
+        <v>25</v>
+      </c>
+      <c r="K36" s="43" t="s">
+        <v>26</v>
+      </c>
+      <c r="L36" s="44" t="s">
+        <v>27</v>
+      </c>
+      <c r="M36" s="45">
+        <v>46172</v>
+      </c>
+      <c r="N36" s="46">
+        <v>46170</v>
+      </c>
+      <c r="O36" s="47" t="s">
+        <v>132</v>
+      </c>
+      <c r="P36" s="48" t="s">
+        <v>132</v>
+      </c>
+      <c r="Q36" s="49">
+        <v>46152</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="33" t="s">
+        <v>155</v>
+      </c>
+      <c r="B37" s="34" t="s">
+        <v>156</v>
+      </c>
+      <c r="C37" s="35" t="s">
+        <v>62</v>
+      </c>
+      <c r="D37" s="36" t="s">
+        <v>20</v>
+      </c>
+      <c r="E37" s="37" t="s">
+        <v>158</v>
+      </c>
+      <c r="F37" s="38" t="s">
+        <v>159</v>
+      </c>
+      <c r="G37" s="39" t="s">
+        <v>41</v>
+      </c>
+      <c r="H37" s="40" t="s">
+        <v>158</v>
+      </c>
+      <c r="I37" s="41" t="s">
+        <v>160</v>
+      </c>
+      <c r="J37" s="42" t="s">
+        <v>25</v>
+      </c>
+      <c r="K37" s="43" t="s">
+        <v>26</v>
+      </c>
+      <c r="L37" s="44" t="s">
+        <v>27</v>
+      </c>
+      <c r="M37" s="45">
+        <v>46172</v>
+      </c>
+      <c r="N37" s="46">
+        <v>46170</v>
+      </c>
+      <c r="O37" s="47" t="s">
+        <v>132</v>
+      </c>
+      <c r="P37" s="48" t="s">
+        <v>132</v>
+      </c>
+      <c r="Q37" s="49">
+        <v>46152</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="33" t="s">
+        <v>161</v>
+      </c>
+      <c r="B38" s="34" t="s">
+        <v>162</v>
+      </c>
+      <c r="C38" s="35" t="s">
+        <v>19</v>
+      </c>
+      <c r="D38" s="36" t="s">
+        <v>20</v>
+      </c>
+      <c r="E38" s="37" t="s">
+        <v>21</v>
+      </c>
+      <c r="F38" s="38" t="s">
+        <v>22</v>
+      </c>
+      <c r="G38" s="39" t="s">
+        <v>23</v>
+      </c>
+      <c r="H38" s="40" t="s">
+        <v>21</v>
+      </c>
+      <c r="I38" s="41" t="s">
+        <v>163</v>
+      </c>
+      <c r="J38" s="42" t="s">
+        <v>164</v>
+      </c>
+      <c r="K38" s="43" t="s">
+        <v>165</v>
+      </c>
+      <c r="L38" s="44" t="s">
+        <v>166</v>
+      </c>
+      <c r="M38" s="45">
+        <v>46170</v>
+      </c>
+      <c r="N38" s="46">
+        <v>46170</v>
+      </c>
+      <c r="O38" s="47" t="s">
+        <v>167</v>
+      </c>
+      <c r="P38" s="48" t="s">
+        <v>167</v>
+      </c>
+      <c r="Q38" s="49">
+        <v>46119</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="33" t="s">
+        <v>161</v>
+      </c>
+      <c r="B39" s="34" t="s">
+        <v>162</v>
+      </c>
+      <c r="C39" s="35" t="s">
+        <v>19</v>
+      </c>
+      <c r="D39" s="36" t="s">
+        <v>20</v>
+      </c>
+      <c r="E39" s="37" t="s">
+        <v>21</v>
+      </c>
+      <c r="F39" s="38" t="s">
+        <v>22</v>
+      </c>
+      <c r="G39" s="39" t="s">
+        <v>38</v>
+      </c>
+      <c r="H39" s="40" t="s">
+        <v>21</v>
+      </c>
+      <c r="I39" s="41" t="s">
+        <v>168</v>
+      </c>
+      <c r="J39" s="42" t="s">
+        <v>164</v>
+      </c>
+      <c r="K39" s="43" t="s">
+        <v>165</v>
+      </c>
+      <c r="L39" s="44" t="s">
+        <v>166</v>
+      </c>
+      <c r="M39" s="45">
+        <v>46170</v>
+      </c>
+      <c r="N39" s="46">
+        <v>46170</v>
+      </c>
+      <c r="O39" s="47" t="s">
+        <v>167</v>
+      </c>
+      <c r="P39" s="48" t="s">
+        <v>167</v>
+      </c>
+      <c r="Q39" s="49">
+        <v>46119</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="33" t="s">
+        <v>169</v>
+      </c>
+      <c r="B40" s="34" t="s">
+        <v>170</v>
+      </c>
+      <c r="C40" s="35" t="s">
+        <v>19</v>
+      </c>
+      <c r="D40" s="36" t="s">
+        <v>20</v>
+      </c>
+      <c r="E40" s="37" t="s">
+        <v>21</v>
+      </c>
+      <c r="F40" s="38" t="s">
+        <v>22</v>
+      </c>
+      <c r="G40" s="39" t="s">
+        <v>23</v>
+      </c>
+      <c r="H40" s="40" t="s">
+        <v>21</v>
+      </c>
+      <c r="I40" s="41" t="s">
+        <v>163</v>
+      </c>
+      <c r="J40" s="42" t="s">
+        <v>164</v>
+      </c>
+      <c r="K40" s="43" t="s">
+        <v>165</v>
+      </c>
+      <c r="L40" s="44" t="s">
+        <v>166</v>
+      </c>
+      <c r="M40" s="45">
+        <v>46170</v>
+      </c>
+      <c r="N40" s="46">
+        <v>46170</v>
+      </c>
+      <c r="O40" s="47" t="s">
+        <v>167</v>
+      </c>
+      <c r="P40" s="48" t="s">
+        <v>167</v>
+      </c>
+      <c r="Q40" s="49">
+        <v>46119</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="33" t="s">
+        <v>169</v>
+      </c>
+      <c r="B41" s="34" t="s">
+        <v>170</v>
+      </c>
+      <c r="C41" s="35" t="s">
+        <v>19</v>
+      </c>
+      <c r="D41" s="36" t="s">
+        <v>20</v>
+      </c>
+      <c r="E41" s="37" t="s">
+        <v>21</v>
+      </c>
+      <c r="F41" s="38" t="s">
+        <v>22</v>
+      </c>
+      <c r="G41" s="39" t="s">
+        <v>38</v>
+      </c>
+      <c r="H41" s="40" t="s">
+        <v>21</v>
+      </c>
+      <c r="I41" s="41" t="s">
+        <v>168</v>
+      </c>
+      <c r="J41" s="42" t="s">
+        <v>164</v>
+      </c>
+      <c r="K41" s="43" t="s">
+        <v>165</v>
+      </c>
+      <c r="L41" s="44" t="s">
+        <v>166</v>
+      </c>
+      <c r="M41" s="45">
+        <v>46170</v>
+      </c>
+      <c r="N41" s="46">
+        <v>46170</v>
+      </c>
+      <c r="O41" s="47" t="s">
+        <v>167</v>
+      </c>
+      <c r="P41" s="48" t="s">
+        <v>167</v>
+      </c>
+      <c r="Q41" s="49">
+        <v>46119</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="33" t="s">
+        <v>171</v>
+      </c>
+      <c r="B42" s="34" t="s">
+        <v>172</v>
+      </c>
+      <c r="C42" s="35" t="s">
+        <v>62</v>
+      </c>
+      <c r="D42" s="36" t="s">
+        <v>20</v>
+      </c>
+      <c r="E42" s="37" t="s">
+        <v>31</v>
+      </c>
+      <c r="F42" s="38" t="s">
+        <v>32</v>
+      </c>
+      <c r="G42" s="39" t="s">
+        <v>23</v>
+      </c>
+      <c r="H42" s="40" t="s">
+        <v>31</v>
+      </c>
+      <c r="I42" s="41" t="s">
+        <v>173</v>
+      </c>
+      <c r="J42" s="42" t="s">
+        <v>174</v>
+      </c>
+      <c r="K42" s="43" t="s">
+        <v>175</v>
+      </c>
+      <c r="L42" s="44" t="s">
+        <v>176</v>
+      </c>
+      <c r="M42" s="45">
+        <v>46172</v>
+      </c>
+      <c r="N42" s="46">
+        <v>46170</v>
+      </c>
+      <c r="O42" s="47" t="s">
+        <v>174</v>
+      </c>
+      <c r="P42" s="48" t="s">
+        <v>174</v>
+      </c>
+      <c r="Q42" s="49">
+        <v>46152</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError sqref="A1 B1 C1 D1 E1 F1 G1 H1 I1 J1 K1 L1 M1 N1 O1 P1 Q1 A2 B2 C2 D2 E2 F2 G2 H2 I2 J2 K2 L2 O2 P2 A3 B3 C3 D3 E3 F3 G3 H3 I3 J3 K3 L3 O3 P3 A4 B4 C4 D4 E4 F4 G4 H4 I4 J4 K4 L4 O4 P4 A5 B5 C5 D5 E5 F5 G5 H5 I5 J5 K5 L5 O5 P5 A6 B6 C6 D6 E6 F6 G6 H6 I6 J6 K6 L6 O6 P6 A7 B7 C7 D7 E7 F7 G7 H7 I7 J7 K7 L7 O7 P7 A8 B8 C8 D8 E8 F8 G8 H8 I8 J8 K8 L8 O8 P8 A9 B9 C9 D9 E9 F9 G9 H9 I9 J9 K9 L9 O9 P9 A10 B10 C10 D10 E10 F10 G10 H10 I10 J10 K10 L10 O10 P10 A11 B11 C11 D11 E11 F11 G11 H11 I11 J11 K11 L11 O11 P11" numberStoredAsText="true"/>
+    <ignoredError sqref="A1 B1 C1 D1 E1 F1 G1 H1 I1 J1 K1 L1 M1 N1 O1 P1 Q1 A2 B2 C2 D2 E2 F2 G2 H2 I2 J2 K2 L2 O2 P2 A3 B3 C3 D3 E3 F3 G3 H3 I3 J3 K3 L3 O3 P3 A4 B4 C4 D4 E4 F4 G4 H4 I4 J4 K4 L4 O4 P4 A5 B5 C5 D5 E5 F5 G5 H5 I5 J5 K5 L5 O5 P5 A6 B6 C6 D6 E6 F6 G6 H6 I6 J6 K6 L6 O6 P6 A7 B7 C7 D7 E7 F7 G7 H7 I7 J7 K7 L7 O7 P7 A8 B8 C8 D8 E8 F8 G8 H8 I8 J8 K8 L8 O8 P8 A9 B9 C9 D9 E9 F9 G9 H9 I9 J9 K9 L9 O9 P9 A10 B10 C10 D10 E10 F10 G10 H10 I10 J10 K10 L10 O10 P10 A11 B11 C11 D11 E11 F11 G11 H11 I11 J11 K11 L11 O11 P11 A12 B12 C12 D12 E12 F12 G12 H12 I12 J12 K12 L12 O12 P12 A13 B13 C13 D13 E13 F13 G13 H13 I13 J13 K13 L13 O13 P13 A14 B14 C14 D14 E14 F14 G14 H14 I14 J14 K14 L14 O14 P14 A15 B15 C15 D15 E15 F15 G15 H15 I15 J15 K15 L15 O15 P15 A16 B16 C16 D16 E16 F16 G16 H16 I16 J16 K16 L16 O16 P16 A17 B17 C17 D17 E17 F17 G17 H17 I17 J17 K17 L17 O17 P17 A18 B18 C18 D18 E18 F18 G18 H18 I18 J18 K18 L18 O18 P18 A19 B19 C19 D19 E19 F19 G19 H19 I19 J19 K19 L19 O19 P19 A20 B20 C20 D20 E20 F20 G20 H20 I20 J20 K20 L20 O20 P20 A21 B21 C21 D21 E21 F21 G21 H21 I21 J21 K21 L21 O21 P21 A22 B22 C22 D22 E22 F22 G22 H22 I22 J22 K22 L22 O22 P22 A23 B23 C23 D23 E23 F23 G23 H23 I23 J23 K23 L23 O23 P23 A24 B24 C24 D24 E24 F24 G24 H24 I24 J24 K24 L24 O24 P24 A25 B25 C25 D25 E25 F25 G25 H25 I25 J25 K25 L25 O25 P25 A26 B26 C26 D26 E26 F26 G26 H26 I26 J26 K26 L26 O26 P26 A27 B27 C27 D27 E27 F27 G27 H27 I27 J27 K27 L27 O27 P27 A28 B28 C28 D28 E28 F28 G28 H28 I28 J28 K28 L28 O28 P28 A29 B29 C29 D29 E29 F29 G29 H29 I29 J29 K29 L29 O29 P29 A30 B30 C30 D30 E30 F30 G30 H30 I30 J30 K30 L30 O30 P30 A31 B31 C31 D31 E31 F31 G31 H31 I31 J31 K31 L31 O31 P31 A32 B32 C32 D32 E32 F32 G32 H32 I32 J32 K32 L32 O32 P32 A33 B33 C33 D33 E33 F33 G33 H33 I33 J33 K33 L33 O33 P33 A34 B34 C34 D34 E34 F34 G34 H34 I34 J34 K34 L34 O34 P34 A35 B35 C35 D35 E35 F35 G35 H35 I35 J35 K35 L35 O35 P35 A36 B36 C36 D36 E36 F36 G36 H36 I36 J36 K36 L36 O36 P36 A37 B37 C37 D37 E37 F37 G37 H37 I37 J37 K37 L37 O37 P37 A38 B38 C38 D38 E38 F38 G38 H38 I38 J38 K38 L38 O38 P38 A39 B39 C39 D39 E39 F39 G39 H39 I39 J39 K39 L39 O39 P39 A40 B40 C40 D40 E40 F40 G40 H40 I40 J40 K40 L40 O40 P40 A41 B41 C41 D41 E41 F41 G41 H41 I41 J41 K41 L41 O41 P41 A42 B42 C42 D42 E42 F42 G42 H42 I42 J42 K42 L42 O42 P42" numberStoredAsText="true"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/trimika_data.xlsx
+++ b/trimika_data.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" count="297" uniqueCount="103">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" count="633" uniqueCount="118">
   <si>
     <t>REFERENCE NO</t>
   </si>
@@ -66,10 +66,10 @@
     <t>EXPORT DATE</t>
   </si>
   <si>
-    <t>2565341</t>
-  </si>
-  <si>
-    <t>EF4-0230920-9</t>
+    <t>2565426</t>
+  </si>
+  <si>
+    <t>EF4-0231160-1</t>
   </si>
   <si>
     <t>Vessel, Container</t>
@@ -102,10 +102,10 @@
     <t>SANGUAN WONGSE STARCH CO., LTD.</t>
   </si>
   <si>
-    <t>2565342</t>
-  </si>
-  <si>
-    <t>EF4-0230921-7</t>
+    <t>2565427</t>
+  </si>
+  <si>
+    <t>EF4-0231249-2</t>
   </si>
   <si>
     <t>9903.03.03</t>
@@ -117,16 +117,40 @@
     <t>1108.14.0000</t>
   </si>
   <si>
-    <t>2565343</t>
-  </si>
-  <si>
-    <t>EF4-0230922-5</t>
-  </si>
-  <si>
-    <t>2565273</t>
-  </si>
-  <si>
-    <t>EF4-0230988-6</t>
+    <t>2565740</t>
+  </si>
+  <si>
+    <t>EF4-0231610-5</t>
+  </si>
+  <si>
+    <t>4418.75.7000</t>
+  </si>
+  <si>
+    <t>AUTHENTIC SURFACES LLC</t>
+  </si>
+  <si>
+    <t>AUTSUR01</t>
+  </si>
+  <si>
+    <t>86-279678900</t>
+  </si>
+  <si>
+    <t>CHENE DE L'EST</t>
+  </si>
+  <si>
+    <t>002</t>
+  </si>
+  <si>
+    <t>4409.29.0655</t>
+  </si>
+  <si>
+    <t>2565608</t>
+  </si>
+  <si>
+    <t>EF4-0231652-7</t>
+  </si>
+  <si>
+    <t>V0710308649</t>
   </si>
   <si>
     <t>9903.03.06</t>
@@ -135,193 +159,214 @@
     <t>S122 EXCL,IRN/STL/ALUM,DERIV</t>
   </si>
   <si>
-    <t>9903.82.05,8427.20.8020</t>
-  </si>
-  <si>
-    <t>MALLAGHAN (GA) INC.</t>
-  </si>
-  <si>
-    <t>MALGA01</t>
-  </si>
-  <si>
-    <t>36-488102800</t>
-  </si>
-  <si>
-    <t>MALLAGHAN ENGINEERING  LTD</t>
-  </si>
-  <si>
-    <t>2565367</t>
-  </si>
-  <si>
-    <t>EF4-0231033-0</t>
-  </si>
-  <si>
-    <t>5903.90.3090</t>
-  </si>
-  <si>
-    <t>VEER CORPORATIONS INC</t>
-  </si>
-  <si>
-    <t>VEECOR01</t>
-  </si>
-  <si>
-    <t>99-106989200</t>
-  </si>
-  <si>
-    <t>VEER PLASTIC PVT LTD</t>
-  </si>
-  <si>
-    <t>2565551</t>
-  </si>
-  <si>
-    <t>EF4-0231295-5</t>
-  </si>
-  <si>
-    <t>9903.82.01,8431.20.0000</t>
-  </si>
-  <si>
-    <t>2565605</t>
-  </si>
-  <si>
-    <t>EF4-0231308-6</t>
-  </si>
-  <si>
-    <t>2565623</t>
-  </si>
-  <si>
-    <t>EF4-0231418-3</t>
-  </si>
-  <si>
-    <t>1109.00.9010</t>
-  </si>
-  <si>
-    <t>SEDAMYL SPA</t>
-  </si>
-  <si>
-    <t>2565719</t>
-  </si>
-  <si>
-    <t>EF4-0231573-5</t>
-  </si>
-  <si>
-    <t>2565854</t>
-  </si>
-  <si>
-    <t>EF4-0231797-0</t>
-  </si>
-  <si>
-    <t>1108.13.0010</t>
-  </si>
-  <si>
-    <t>AKV LANGHOLT AMBA</t>
-  </si>
-  <si>
-    <t>2565887</t>
-  </si>
-  <si>
-    <t>EF4-0231799-6</t>
-  </si>
-  <si>
-    <t>2565856</t>
-  </si>
-  <si>
-    <t>EF4-0231824-2</t>
-  </si>
-  <si>
-    <t>V0710334991</t>
-  </si>
-  <si>
-    <t>1109.00.9020</t>
-  </si>
-  <si>
-    <t>JACKERING MUHLEN UND NAHRMITTELWERK</t>
-  </si>
-  <si>
-    <t>JACKERING MUHLEN UND NAHRMITTELWERKE GMBH</t>
-  </si>
-  <si>
-    <t>2565862</t>
-  </si>
-  <si>
-    <t>EF4-0231896-0</t>
-  </si>
-  <si>
-    <t>3920.61.0000</t>
-  </si>
-  <si>
-    <t>TUBUS BAUER GMBH</t>
-  </si>
-  <si>
-    <t>TUBBAU01</t>
-  </si>
-  <si>
-    <t>091601-00584</t>
-  </si>
-  <si>
-    <t>2565895</t>
-  </si>
-  <si>
-    <t>EF4-0231918-2</t>
-  </si>
-  <si>
-    <t>9031.49.9000</t>
-  </si>
-  <si>
-    <t>MAHA USA LLC</t>
-  </si>
-  <si>
-    <t>MAHUSA</t>
-  </si>
-  <si>
-    <t>52-213556300</t>
-  </si>
-  <si>
-    <t>MAHA GMBH &amp; CO</t>
-  </si>
-  <si>
-    <t>002</t>
-  </si>
-  <si>
-    <t>9903.82.02,7326.90.8688</t>
+    <t>9903.82.02,7223.00.1061</t>
+  </si>
+  <si>
+    <t>VENUS WIRE INDUSTRIES PRIVATE LTD</t>
+  </si>
+  <si>
+    <t>VENWIR</t>
+  </si>
+  <si>
+    <t>993901-03595</t>
+  </si>
+  <si>
+    <t>PRECISION METALS</t>
+  </si>
+  <si>
+    <t>2565819</t>
+  </si>
+  <si>
+    <t>EF4-0231757-4</t>
+  </si>
+  <si>
+    <t>3920.20.0055</t>
+  </si>
+  <si>
+    <t>GULF ATLANTIC PACKAGING CORP</t>
+  </si>
+  <si>
+    <t>GULATL</t>
+  </si>
+  <si>
+    <t>58-184378700</t>
+  </si>
+  <si>
+    <t>SEKISUI JUSHI BV</t>
+  </si>
+  <si>
+    <t>4539336</t>
+  </si>
+  <si>
+    <t>EF4-0232133-7</t>
+  </si>
+  <si>
+    <t>Air, Non-container</t>
+  </si>
+  <si>
+    <t>9903.82.10,8431.39.0010</t>
+  </si>
+  <si>
+    <t>EISENMANN OF SOUTH CAROLINA INC</t>
+  </si>
+  <si>
+    <t>EISINC03</t>
+  </si>
+  <si>
+    <t>86-240963300</t>
+  </si>
+  <si>
+    <t>EISENMANN GMBH</t>
   </si>
   <si>
     <t>003</t>
   </si>
   <si>
-    <t>2565755</t>
-  </si>
-  <si>
-    <t>EF4-0231921-6</t>
-  </si>
-  <si>
-    <t>PRZEDSIEBIORSTWO PRZEMYSLU ZIEMNIAC</t>
-  </si>
-  <si>
-    <t>PRZEDSIEBIORSTWO PRZEMYSLU ZIEMNIACZANEGO PEPEES S.A.</t>
-  </si>
-  <si>
-    <t>2565902</t>
-  </si>
-  <si>
-    <t>EF4-0231963-8</t>
-  </si>
-  <si>
-    <t>V0413883542</t>
-  </si>
-  <si>
-    <t>5704.90.0190</t>
-  </si>
-  <si>
-    <t>BORGERS OHIO INC.</t>
-  </si>
-  <si>
-    <t>BORUSA02</t>
-  </si>
-  <si>
-    <t>30-084196200</t>
-  </si>
-  <si>
-    <t>AUTONEUM GERMANY GMBH</t>
+    <t>004</t>
+  </si>
+  <si>
+    <t>005</t>
+  </si>
+  <si>
+    <t>9903.82.09,8544.42.9090</t>
+  </si>
+  <si>
+    <t>006</t>
+  </si>
+  <si>
+    <t>007</t>
+  </si>
+  <si>
+    <t>9903.82.09,8431.20.0000</t>
+  </si>
+  <si>
+    <t>008</t>
+  </si>
+  <si>
+    <t>8481.80.9050</t>
+  </si>
+  <si>
+    <t>009</t>
+  </si>
+  <si>
+    <t>010</t>
+  </si>
+  <si>
+    <t>011</t>
+  </si>
+  <si>
+    <t>012</t>
+  </si>
+  <si>
+    <t>013</t>
+  </si>
+  <si>
+    <t>8531.80.9005</t>
+  </si>
+  <si>
+    <t>014</t>
+  </si>
+  <si>
+    <t>8421.99.0180</t>
+  </si>
+  <si>
+    <t>015</t>
+  </si>
+  <si>
+    <t>9903.82.02,7320.20.5060</t>
+  </si>
+  <si>
+    <t>016</t>
+  </si>
+  <si>
+    <t>9903.82.09,8483.30.8040</t>
+  </si>
+  <si>
+    <t>017</t>
+  </si>
+  <si>
+    <t>9903.82.02,7415.21.0000</t>
+  </si>
+  <si>
+    <t>018</t>
+  </si>
+  <si>
+    <t>019</t>
+  </si>
+  <si>
+    <t>8484.20.0000</t>
+  </si>
+  <si>
+    <t>020</t>
+  </si>
+  <si>
+    <t>8416.90.0000</t>
+  </si>
+  <si>
+    <t>021</t>
+  </si>
+  <si>
+    <t>022</t>
+  </si>
+  <si>
+    <t>9903.74.11,9903.94.06,8501.52.4000</t>
+  </si>
+  <si>
+    <t>2565859</t>
+  </si>
+  <si>
+    <t>EF4-0232157-6</t>
+  </si>
+  <si>
+    <t>9403.99.9045</t>
+  </si>
+  <si>
+    <t>VISUAL CREATIONS, INC.</t>
+  </si>
+  <si>
+    <t>VISCRE</t>
+  </si>
+  <si>
+    <t>20-461602300</t>
+  </si>
+  <si>
+    <t>VIET MOI INDUSTRIAL COMPANY LIMITED</t>
+  </si>
+  <si>
+    <t>9903.76.04,9403.60.8093</t>
+  </si>
+  <si>
+    <t>3926.90.9989</t>
+  </si>
+  <si>
+    <t>9403.20.0075</t>
+  </si>
+  <si>
+    <t>4539378</t>
+  </si>
+  <si>
+    <t>EF4-0232172-5</t>
+  </si>
+  <si>
+    <t>9903.82.09,8302.42.3065</t>
+  </si>
+  <si>
+    <t>VIELER INTERNATIONAL LP</t>
+  </si>
+  <si>
+    <t>VIEINT</t>
+  </si>
+  <si>
+    <t>58-255440400</t>
+  </si>
+  <si>
+    <t>VIELER INTERNATIONAL GMBH + CO. KG</t>
+  </si>
+  <si>
+    <t>9903.82.02,7318.15.6010</t>
+  </si>
+  <si>
+    <t>9903.82.09,8302.10.6060</t>
   </si>
 </sst>
 </file>
@@ -1266,7 +1311,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:Q21"/>
+  <dimension ref="A1:Q45"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="23.7109375" customWidth="true"/>
@@ -1379,10 +1424,10 @@
         <v>27</v>
       </c>
       <c r="M2" s="45">
-        <v>46173</v>
+        <v>46176</v>
       </c>
       <c r="N2" s="46">
-        <v>46173</v>
+        <v>46174</v>
       </c>
       <c r="O2" s="47" t="s">
         <v>28</v>
@@ -1391,7 +1436,7 @@
         <v>28</v>
       </c>
       <c r="Q2" s="49">
-        <v>46114</v>
+        <v>46124</v>
       </c>
     </row>
     <row r="3">
@@ -1432,10 +1477,10 @@
         <v>27</v>
       </c>
       <c r="M3" s="45">
-        <v>46173</v>
+        <v>46176</v>
       </c>
       <c r="N3" s="46">
-        <v>46173</v>
+        <v>46174</v>
       </c>
       <c r="O3" s="47" t="s">
         <v>28</v>
@@ -1444,7 +1489,7 @@
         <v>28</v>
       </c>
       <c r="Q3" s="49">
-        <v>46114</v>
+        <v>46124</v>
       </c>
     </row>
     <row r="4">
@@ -1461,51 +1506,51 @@
         <v>20</v>
       </c>
       <c r="E4" s="37" t="s">
-        <v>31</v>
+        <v>21</v>
       </c>
       <c r="F4" s="38" t="s">
-        <v>32</v>
+        <v>22</v>
       </c>
       <c r="G4" s="39" t="s">
         <v>23</v>
       </c>
       <c r="H4" s="40" t="s">
-        <v>31</v>
+        <v>21</v>
       </c>
       <c r="I4" s="41" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="J4" s="42" t="s">
-        <v>25</v>
+        <v>37</v>
       </c>
       <c r="K4" s="43" t="s">
-        <v>26</v>
+        <v>38</v>
       </c>
       <c r="L4" s="44" t="s">
-        <v>27</v>
+        <v>39</v>
       </c>
       <c r="M4" s="45">
-        <v>46173</v>
+        <v>46170</v>
       </c>
       <c r="N4" s="46">
-        <v>46173</v>
+        <v>46174</v>
       </c>
       <c r="O4" s="47" t="s">
-        <v>28</v>
+        <v>40</v>
       </c>
       <c r="P4" s="48" t="s">
-        <v>28</v>
+        <v>40</v>
       </c>
       <c r="Q4" s="49">
-        <v>46114</v>
+        <v>46147</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="33" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="B5" s="34" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="C5" s="35" t="s">
         <v>19</v>
@@ -1514,110 +1559,110 @@
         <v>20</v>
       </c>
       <c r="E5" s="37" t="s">
+        <v>21</v>
+      </c>
+      <c r="F5" s="38" t="s">
+        <v>22</v>
+      </c>
+      <c r="G5" s="39" t="s">
+        <v>41</v>
+      </c>
+      <c r="H5" s="40" t="s">
+        <v>21</v>
+      </c>
+      <c r="I5" s="41" t="s">
+        <v>42</v>
+      </c>
+      <c r="J5" s="42" t="s">
+        <v>37</v>
+      </c>
+      <c r="K5" s="43" t="s">
         <v>38</v>
       </c>
-      <c r="F5" s="38" t="s">
+      <c r="L5" s="44" t="s">
         <v>39</v>
       </c>
-      <c r="G5" s="39" t="s">
-        <v>23</v>
-      </c>
-      <c r="H5" s="40" t="s">
-        <v>38</v>
-      </c>
-      <c r="I5" s="41" t="s">
+      <c r="M5" s="45">
+        <v>46170</v>
+      </c>
+      <c r="N5" s="46">
+        <v>46174</v>
+      </c>
+      <c r="O5" s="47" t="s">
         <v>40</v>
       </c>
-      <c r="J5" s="42" t="s">
-        <v>41</v>
-      </c>
-      <c r="K5" s="43" t="s">
-        <v>42</v>
-      </c>
-      <c r="L5" s="44" t="s">
-        <v>43</v>
-      </c>
-      <c r="M5" s="45">
-        <v>46172</v>
-      </c>
-      <c r="N5" s="46">
-        <v>46173</v>
-      </c>
-      <c r="O5" s="47" t="s">
-        <v>44</v>
-      </c>
       <c r="P5" s="48" t="s">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="Q5" s="49">
-        <v>46111</v>
+        <v>46147</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="33" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="B6" s="34" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="C6" s="35" t="s">
         <v>19</v>
       </c>
       <c r="D6" s="36" t="s">
-        <v>20</v>
+        <v>45</v>
       </c>
       <c r="E6" s="37" t="s">
-        <v>21</v>
+        <v>46</v>
       </c>
       <c r="F6" s="38" t="s">
-        <v>22</v>
+        <v>47</v>
       </c>
       <c r="G6" s="39" t="s">
         <v>23</v>
       </c>
       <c r="H6" s="40" t="s">
-        <v>21</v>
+        <v>46</v>
       </c>
       <c r="I6" s="41" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="J6" s="42" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="K6" s="43" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="L6" s="44" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="M6" s="45">
-        <v>46173</v>
+        <v>46174</v>
       </c>
       <c r="N6" s="46">
-        <v>46173</v>
+        <v>46174</v>
       </c>
       <c r="O6" s="47" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="P6" s="48" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="Q6" s="49">
-        <v>46122</v>
+        <v>46132</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="33" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="B7" s="34" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="C7" s="35" t="s">
         <v>19</v>
       </c>
       <c r="D7" s="36" t="s">
-        <v>20</v>
+        <v>45</v>
       </c>
       <c r="E7" s="37" t="s">
         <v>21</v>
@@ -1632,413 +1677,413 @@
         <v>21</v>
       </c>
       <c r="I7" s="41" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="J7" s="42" t="s">
-        <v>41</v>
+        <v>56</v>
       </c>
       <c r="K7" s="43" t="s">
-        <v>42</v>
+        <v>57</v>
       </c>
       <c r="L7" s="44" t="s">
-        <v>43</v>
+        <v>58</v>
       </c>
       <c r="M7" s="45">
-        <v>46172</v>
+        <v>46175</v>
       </c>
       <c r="N7" s="46">
-        <v>46173</v>
+        <v>46174</v>
       </c>
       <c r="O7" s="47" t="s">
-        <v>44</v>
+        <v>59</v>
       </c>
       <c r="P7" s="48" t="s">
-        <v>44</v>
+        <v>59</v>
       </c>
       <c r="Q7" s="49">
-        <v>46133</v>
+        <v>46152</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="33" t="s">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="B8" s="34" t="s">
-        <v>56</v>
+        <v>61</v>
       </c>
       <c r="C8" s="35" t="s">
-        <v>19</v>
+        <v>62</v>
       </c>
       <c r="D8" s="36" t="s">
         <v>20</v>
       </c>
       <c r="E8" s="37" t="s">
-        <v>21</v>
+        <v>46</v>
       </c>
       <c r="F8" s="38" t="s">
-        <v>22</v>
+        <v>47</v>
       </c>
       <c r="G8" s="39" t="s">
         <v>23</v>
       </c>
       <c r="H8" s="40" t="s">
-        <v>21</v>
+        <v>46</v>
       </c>
       <c r="I8" s="41" t="s">
-        <v>47</v>
+        <v>63</v>
       </c>
       <c r="J8" s="42" t="s">
-        <v>48</v>
+        <v>64</v>
       </c>
       <c r="K8" s="43" t="s">
-        <v>49</v>
+        <v>65</v>
       </c>
       <c r="L8" s="44" t="s">
-        <v>50</v>
+        <v>66</v>
       </c>
       <c r="M8" s="45">
-        <v>46172</v>
+        <v>46173</v>
       </c>
       <c r="N8" s="46">
-        <v>46173</v>
+        <v>46174</v>
       </c>
       <c r="O8" s="47" t="s">
-        <v>51</v>
+        <v>67</v>
       </c>
       <c r="P8" s="48" t="s">
-        <v>51</v>
+        <v>67</v>
       </c>
       <c r="Q8" s="49">
-        <v>46134</v>
+        <v>46173</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="33" t="s">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="B9" s="34" t="s">
-        <v>58</v>
+        <v>61</v>
       </c>
       <c r="C9" s="35" t="s">
-        <v>19</v>
+        <v>62</v>
       </c>
       <c r="D9" s="36" t="s">
         <v>20</v>
       </c>
       <c r="E9" s="37" t="s">
-        <v>21</v>
+        <v>46</v>
       </c>
       <c r="F9" s="38" t="s">
-        <v>22</v>
+        <v>47</v>
       </c>
       <c r="G9" s="39" t="s">
-        <v>23</v>
+        <v>41</v>
       </c>
       <c r="H9" s="40" t="s">
-        <v>21</v>
+        <v>46</v>
       </c>
       <c r="I9" s="41" t="s">
-        <v>59</v>
+        <v>63</v>
       </c>
       <c r="J9" s="42" t="s">
-        <v>25</v>
+        <v>64</v>
       </c>
       <c r="K9" s="43" t="s">
-        <v>26</v>
+        <v>65</v>
       </c>
       <c r="L9" s="44" t="s">
-        <v>27</v>
+        <v>66</v>
       </c>
       <c r="M9" s="45">
         <v>46173</v>
       </c>
       <c r="N9" s="46">
-        <v>46173</v>
+        <v>46174</v>
       </c>
       <c r="O9" s="47" t="s">
-        <v>60</v>
+        <v>67</v>
       </c>
       <c r="P9" s="48" t="s">
-        <v>60</v>
+        <v>67</v>
       </c>
       <c r="Q9" s="49">
-        <v>46133</v>
+        <v>46173</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="33" t="s">
+        <v>60</v>
+      </c>
+      <c r="B10" s="34" t="s">
         <v>61</v>
       </c>
-      <c r="B10" s="34" t="s">
+      <c r="C10" s="35" t="s">
         <v>62</v>
       </c>
-      <c r="C10" s="35" t="s">
-        <v>19</v>
-      </c>
       <c r="D10" s="36" t="s">
         <v>20</v>
       </c>
       <c r="E10" s="37" t="s">
-        <v>21</v>
+        <v>46</v>
       </c>
       <c r="F10" s="38" t="s">
-        <v>22</v>
+        <v>47</v>
       </c>
       <c r="G10" s="39" t="s">
-        <v>23</v>
+        <v>68</v>
       </c>
       <c r="H10" s="40" t="s">
-        <v>21</v>
+        <v>46</v>
       </c>
       <c r="I10" s="41" t="s">
-        <v>59</v>
+        <v>63</v>
       </c>
       <c r="J10" s="42" t="s">
-        <v>25</v>
+        <v>64</v>
       </c>
       <c r="K10" s="43" t="s">
-        <v>26</v>
+        <v>65</v>
       </c>
       <c r="L10" s="44" t="s">
-        <v>27</v>
+        <v>66</v>
       </c>
       <c r="M10" s="45">
         <v>46173</v>
       </c>
       <c r="N10" s="46">
-        <v>46173</v>
+        <v>46174</v>
       </c>
       <c r="O10" s="47" t="s">
-        <v>60</v>
+        <v>67</v>
       </c>
       <c r="P10" s="48" t="s">
-        <v>60</v>
+        <v>67</v>
       </c>
       <c r="Q10" s="49">
-        <v>46141</v>
+        <v>46173</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="33" t="s">
+        <v>60</v>
+      </c>
+      <c r="B11" s="34" t="s">
+        <v>61</v>
+      </c>
+      <c r="C11" s="35" t="s">
+        <v>62</v>
+      </c>
+      <c r="D11" s="36" t="s">
+        <v>20</v>
+      </c>
+      <c r="E11" s="37" t="s">
+        <v>46</v>
+      </c>
+      <c r="F11" s="38" t="s">
+        <v>47</v>
+      </c>
+      <c r="G11" s="39" t="s">
+        <v>69</v>
+      </c>
+      <c r="H11" s="40" t="s">
+        <v>46</v>
+      </c>
+      <c r="I11" s="41" t="s">
         <v>63</v>
       </c>
-      <c r="B11" s="34" t="s">
+      <c r="J11" s="42" t="s">
         <v>64</v>
       </c>
-      <c r="C11" s="35" t="s">
-        <v>19</v>
-      </c>
-      <c r="D11" s="36" t="s">
-        <v>20</v>
-      </c>
-      <c r="E11" s="37" t="s">
-        <v>21</v>
-      </c>
-      <c r="F11" s="38" t="s">
-        <v>22</v>
-      </c>
-      <c r="G11" s="39" t="s">
-        <v>23</v>
-      </c>
-      <c r="H11" s="40" t="s">
-        <v>21</v>
-      </c>
-      <c r="I11" s="41" t="s">
+      <c r="K11" s="43" t="s">
         <v>65</v>
       </c>
-      <c r="J11" s="42" t="s">
-        <v>25</v>
-      </c>
-      <c r="K11" s="43" t="s">
-        <v>26</v>
-      </c>
       <c r="L11" s="44" t="s">
-        <v>27</v>
+        <v>66</v>
       </c>
       <c r="M11" s="45">
         <v>46173</v>
       </c>
       <c r="N11" s="46">
-        <v>46173</v>
+        <v>46174</v>
       </c>
       <c r="O11" s="47" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="P11" s="48" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="Q11" s="49">
-        <v>46153</v>
+        <v>46173</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="33" t="s">
-        <v>67</v>
+        <v>60</v>
       </c>
       <c r="B12" s="34" t="s">
-        <v>68</v>
+        <v>61</v>
       </c>
       <c r="C12" s="35" t="s">
-        <v>19</v>
+        <v>62</v>
       </c>
       <c r="D12" s="36" t="s">
         <v>20</v>
       </c>
       <c r="E12" s="37" t="s">
-        <v>21</v>
+        <v>46</v>
       </c>
       <c r="F12" s="38" t="s">
-        <v>22</v>
+        <v>47</v>
       </c>
       <c r="G12" s="39" t="s">
-        <v>23</v>
+        <v>70</v>
       </c>
       <c r="H12" s="40" t="s">
-        <v>21</v>
+        <v>46</v>
       </c>
       <c r="I12" s="41" t="s">
+        <v>71</v>
+      </c>
+      <c r="J12" s="42" t="s">
+        <v>64</v>
+      </c>
+      <c r="K12" s="43" t="s">
         <v>65</v>
       </c>
-      <c r="J12" s="42" t="s">
-        <v>25</v>
-      </c>
-      <c r="K12" s="43" t="s">
-        <v>26</v>
-      </c>
       <c r="L12" s="44" t="s">
-        <v>27</v>
+        <v>66</v>
       </c>
       <c r="M12" s="45">
         <v>46173</v>
       </c>
       <c r="N12" s="46">
-        <v>46173</v>
+        <v>46174</v>
       </c>
       <c r="O12" s="47" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="P12" s="48" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="Q12" s="49">
-        <v>46153</v>
+        <v>46173</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="33" t="s">
-        <v>69</v>
+        <v>60</v>
       </c>
       <c r="B13" s="34" t="s">
-        <v>70</v>
+        <v>61</v>
       </c>
       <c r="C13" s="35" t="s">
-        <v>19</v>
+        <v>62</v>
       </c>
       <c r="D13" s="36" t="s">
-        <v>71</v>
+        <v>20</v>
       </c>
       <c r="E13" s="37" t="s">
-        <v>21</v>
+        <v>46</v>
       </c>
       <c r="F13" s="38" t="s">
-        <v>22</v>
+        <v>47</v>
       </c>
       <c r="G13" s="39" t="s">
-        <v>23</v>
+        <v>72</v>
       </c>
       <c r="H13" s="40" t="s">
-        <v>21</v>
+        <v>46</v>
       </c>
       <c r="I13" s="41" t="s">
-        <v>72</v>
+        <v>63</v>
       </c>
       <c r="J13" s="42" t="s">
-        <v>25</v>
+        <v>64</v>
       </c>
       <c r="K13" s="43" t="s">
-        <v>26</v>
+        <v>65</v>
       </c>
       <c r="L13" s="44" t="s">
-        <v>27</v>
+        <v>66</v>
       </c>
       <c r="M13" s="45">
         <v>46173</v>
       </c>
       <c r="N13" s="46">
-        <v>46173</v>
+        <v>46174</v>
       </c>
       <c r="O13" s="47" t="s">
-        <v>73</v>
+        <v>67</v>
       </c>
       <c r="P13" s="48" t="s">
-        <v>74</v>
+        <v>67</v>
       </c>
       <c r="Q13" s="49">
-        <v>46154</v>
+        <v>46173</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="33" t="s">
-        <v>75</v>
+        <v>60</v>
       </c>
       <c r="B14" s="34" t="s">
-        <v>76</v>
+        <v>61</v>
       </c>
       <c r="C14" s="35" t="s">
-        <v>19</v>
+        <v>62</v>
       </c>
       <c r="D14" s="36" t="s">
-        <v>71</v>
+        <v>20</v>
       </c>
       <c r="E14" s="37" t="s">
-        <v>21</v>
+        <v>46</v>
       </c>
       <c r="F14" s="38" t="s">
-        <v>22</v>
+        <v>47</v>
       </c>
       <c r="G14" s="39" t="s">
-        <v>23</v>
+        <v>73</v>
       </c>
       <c r="H14" s="40" t="s">
-        <v>21</v>
+        <v>46</v>
       </c>
       <c r="I14" s="41" t="s">
-        <v>77</v>
+        <v>74</v>
       </c>
       <c r="J14" s="42" t="s">
-        <v>78</v>
+        <v>64</v>
       </c>
       <c r="K14" s="43" t="s">
-        <v>79</v>
+        <v>65</v>
       </c>
       <c r="L14" s="44" t="s">
-        <v>80</v>
+        <v>66</v>
       </c>
       <c r="M14" s="45">
         <v>46173</v>
       </c>
       <c r="N14" s="46">
-        <v>46173</v>
+        <v>46174</v>
       </c>
       <c r="O14" s="47" t="s">
-        <v>78</v>
+        <v>67</v>
       </c>
       <c r="P14" s="48" t="s">
-        <v>78</v>
+        <v>67</v>
       </c>
       <c r="Q14" s="49">
-        <v>46157</v>
+        <v>46173</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="33" t="s">
-        <v>81</v>
+        <v>60</v>
       </c>
       <c r="B15" s="34" t="s">
-        <v>82</v>
+        <v>61</v>
       </c>
       <c r="C15" s="35" t="s">
-        <v>19</v>
+        <v>62</v>
       </c>
       <c r="D15" s="36" t="s">
         <v>20</v>
@@ -2050,263 +2095,263 @@
         <v>22</v>
       </c>
       <c r="G15" s="39" t="s">
-        <v>23</v>
+        <v>75</v>
       </c>
       <c r="H15" s="40" t="s">
         <v>21</v>
       </c>
       <c r="I15" s="41" t="s">
-        <v>83</v>
+        <v>76</v>
       </c>
       <c r="J15" s="42" t="s">
-        <v>84</v>
+        <v>64</v>
       </c>
       <c r="K15" s="43" t="s">
-        <v>85</v>
+        <v>65</v>
       </c>
       <c r="L15" s="44" t="s">
-        <v>86</v>
+        <v>66</v>
       </c>
       <c r="M15" s="45">
         <v>46173</v>
       </c>
       <c r="N15" s="46">
-        <v>46173</v>
+        <v>46174</v>
       </c>
       <c r="O15" s="47" t="s">
-        <v>87</v>
+        <v>67</v>
       </c>
       <c r="P15" s="48" t="s">
-        <v>87</v>
+        <v>67</v>
       </c>
       <c r="Q15" s="49">
-        <v>46158</v>
+        <v>46173</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="33" t="s">
-        <v>81</v>
+        <v>60</v>
       </c>
       <c r="B16" s="34" t="s">
-        <v>82</v>
+        <v>61</v>
       </c>
       <c r="C16" s="35" t="s">
-        <v>19</v>
+        <v>62</v>
       </c>
       <c r="D16" s="36" t="s">
         <v>20</v>
       </c>
       <c r="E16" s="37" t="s">
-        <v>38</v>
+        <v>46</v>
       </c>
       <c r="F16" s="38" t="s">
-        <v>39</v>
+        <v>47</v>
       </c>
       <c r="G16" s="39" t="s">
-        <v>88</v>
+        <v>77</v>
       </c>
       <c r="H16" s="40" t="s">
-        <v>38</v>
+        <v>46</v>
       </c>
       <c r="I16" s="41" t="s">
-        <v>89</v>
+        <v>63</v>
       </c>
       <c r="J16" s="42" t="s">
-        <v>84</v>
+        <v>64</v>
       </c>
       <c r="K16" s="43" t="s">
-        <v>85</v>
+        <v>65</v>
       </c>
       <c r="L16" s="44" t="s">
-        <v>86</v>
+        <v>66</v>
       </c>
       <c r="M16" s="45">
         <v>46173</v>
       </c>
       <c r="N16" s="46">
-        <v>46173</v>
+        <v>46174</v>
       </c>
       <c r="O16" s="47" t="s">
-        <v>87</v>
+        <v>67</v>
       </c>
       <c r="P16" s="48" t="s">
-        <v>87</v>
+        <v>67</v>
       </c>
       <c r="Q16" s="49">
-        <v>46158</v>
+        <v>46173</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="33" t="s">
-        <v>81</v>
+        <v>60</v>
       </c>
       <c r="B17" s="34" t="s">
-        <v>82</v>
+        <v>61</v>
       </c>
       <c r="C17" s="35" t="s">
-        <v>19</v>
+        <v>62</v>
       </c>
       <c r="D17" s="36" t="s">
         <v>20</v>
       </c>
       <c r="E17" s="37" t="s">
-        <v>38</v>
+        <v>46</v>
       </c>
       <c r="F17" s="38" t="s">
-        <v>39</v>
+        <v>47</v>
       </c>
       <c r="G17" s="39" t="s">
-        <v>90</v>
+        <v>78</v>
       </c>
       <c r="H17" s="40" t="s">
-        <v>38</v>
+        <v>46</v>
       </c>
       <c r="I17" s="41" t="s">
-        <v>89</v>
+        <v>63</v>
       </c>
       <c r="J17" s="42" t="s">
-        <v>84</v>
+        <v>64</v>
       </c>
       <c r="K17" s="43" t="s">
-        <v>85</v>
+        <v>65</v>
       </c>
       <c r="L17" s="44" t="s">
-        <v>86</v>
+        <v>66</v>
       </c>
       <c r="M17" s="45">
         <v>46173</v>
       </c>
       <c r="N17" s="46">
-        <v>46173</v>
+        <v>46174</v>
       </c>
       <c r="O17" s="47" t="s">
-        <v>87</v>
+        <v>67</v>
       </c>
       <c r="P17" s="48" t="s">
-        <v>87</v>
+        <v>67</v>
       </c>
       <c r="Q17" s="49">
-        <v>46158</v>
+        <v>46173</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="33" t="s">
-        <v>91</v>
+        <v>60</v>
       </c>
       <c r="B18" s="34" t="s">
-        <v>92</v>
+        <v>61</v>
       </c>
       <c r="C18" s="35" t="s">
-        <v>19</v>
+        <v>62</v>
       </c>
       <c r="D18" s="36" t="s">
         <v>20</v>
       </c>
       <c r="E18" s="37" t="s">
-        <v>21</v>
+        <v>46</v>
       </c>
       <c r="F18" s="38" t="s">
-        <v>20</v>
+        <v>47</v>
       </c>
       <c r="G18" s="39" t="s">
-        <v>23</v>
+        <v>79</v>
       </c>
       <c r="H18" s="40" t="s">
-        <v>21</v>
+        <v>46</v>
       </c>
       <c r="I18" s="41" t="s">
+        <v>63</v>
+      </c>
+      <c r="J18" s="42" t="s">
+        <v>64</v>
+      </c>
+      <c r="K18" s="43" t="s">
         <v>65</v>
       </c>
-      <c r="J18" s="42" t="s">
-        <v>25</v>
-      </c>
-      <c r="K18" s="43" t="s">
-        <v>26</v>
-      </c>
       <c r="L18" s="44" t="s">
-        <v>27</v>
+        <v>66</v>
       </c>
       <c r="M18" s="45">
         <v>46173</v>
       </c>
       <c r="N18" s="46">
-        <v>46173</v>
+        <v>46174</v>
       </c>
       <c r="O18" s="47" t="s">
-        <v>93</v>
+        <v>67</v>
       </c>
       <c r="P18" s="48" t="s">
-        <v>94</v>
+        <v>67</v>
       </c>
       <c r="Q18" s="49">
-        <v>46151</v>
+        <v>46173</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="33" t="s">
-        <v>95</v>
+        <v>60</v>
       </c>
       <c r="B19" s="34" t="s">
-        <v>96</v>
+        <v>61</v>
       </c>
       <c r="C19" s="35" t="s">
-        <v>19</v>
+        <v>62</v>
       </c>
       <c r="D19" s="36" t="s">
-        <v>97</v>
+        <v>20</v>
       </c>
       <c r="E19" s="37" t="s">
-        <v>21</v>
+        <v>46</v>
       </c>
       <c r="F19" s="38" t="s">
-        <v>22</v>
+        <v>47</v>
       </c>
       <c r="G19" s="39" t="s">
-        <v>23</v>
+        <v>80</v>
       </c>
       <c r="H19" s="40" t="s">
-        <v>21</v>
+        <v>46</v>
       </c>
       <c r="I19" s="41" t="s">
-        <v>98</v>
+        <v>63</v>
       </c>
       <c r="J19" s="42" t="s">
-        <v>99</v>
+        <v>64</v>
       </c>
       <c r="K19" s="43" t="s">
-        <v>100</v>
+        <v>65</v>
       </c>
       <c r="L19" s="44" t="s">
-        <v>101</v>
+        <v>66</v>
       </c>
       <c r="M19" s="45">
         <v>46173</v>
       </c>
       <c r="N19" s="46">
-        <v>46173</v>
+        <v>46174</v>
       </c>
       <c r="O19" s="47" t="s">
-        <v>102</v>
+        <v>67</v>
       </c>
       <c r="P19" s="48" t="s">
-        <v>102</v>
+        <v>67</v>
       </c>
       <c r="Q19" s="49">
-        <v>46160</v>
+        <v>46173</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="33" t="s">
-        <v>95</v>
+        <v>60</v>
       </c>
       <c r="B20" s="34" t="s">
-        <v>96</v>
+        <v>61</v>
       </c>
       <c r="C20" s="35" t="s">
-        <v>19</v>
+        <v>62</v>
       </c>
       <c r="D20" s="36" t="s">
-        <v>97</v>
+        <v>20</v>
       </c>
       <c r="E20" s="37" t="s">
         <v>21</v>
@@ -2315,51 +2360,51 @@
         <v>22</v>
       </c>
       <c r="G20" s="39" t="s">
-        <v>88</v>
+        <v>81</v>
       </c>
       <c r="H20" s="40" t="s">
         <v>21</v>
       </c>
       <c r="I20" s="41" t="s">
-        <v>98</v>
+        <v>82</v>
       </c>
       <c r="J20" s="42" t="s">
-        <v>99</v>
+        <v>64</v>
       </c>
       <c r="K20" s="43" t="s">
-        <v>100</v>
+        <v>65</v>
       </c>
       <c r="L20" s="44" t="s">
-        <v>101</v>
+        <v>66</v>
       </c>
       <c r="M20" s="45">
         <v>46173</v>
       </c>
       <c r="N20" s="46">
-        <v>46173</v>
+        <v>46174</v>
       </c>
       <c r="O20" s="47" t="s">
-        <v>102</v>
+        <v>67</v>
       </c>
       <c r="P20" s="48" t="s">
-        <v>102</v>
+        <v>67</v>
       </c>
       <c r="Q20" s="49">
-        <v>46160</v>
+        <v>46173</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="33" t="s">
-        <v>95</v>
+        <v>60</v>
       </c>
       <c r="B21" s="34" t="s">
-        <v>96</v>
+        <v>61</v>
       </c>
       <c r="C21" s="35" t="s">
-        <v>19</v>
+        <v>62</v>
       </c>
       <c r="D21" s="36" t="s">
-        <v>97</v>
+        <v>20</v>
       </c>
       <c r="E21" s="37" t="s">
         <v>21</v>
@@ -2368,42 +2413,1314 @@
         <v>22</v>
       </c>
       <c r="G21" s="39" t="s">
-        <v>90</v>
+        <v>83</v>
       </c>
       <c r="H21" s="40" t="s">
         <v>21</v>
       </c>
       <c r="I21" s="41" t="s">
+        <v>84</v>
+      </c>
+      <c r="J21" s="42" t="s">
+        <v>64</v>
+      </c>
+      <c r="K21" s="43" t="s">
+        <v>65</v>
+      </c>
+      <c r="L21" s="44" t="s">
+        <v>66</v>
+      </c>
+      <c r="M21" s="45">
+        <v>46173</v>
+      </c>
+      <c r="N21" s="46">
+        <v>46174</v>
+      </c>
+      <c r="O21" s="47" t="s">
+        <v>67</v>
+      </c>
+      <c r="P21" s="48" t="s">
+        <v>67</v>
+      </c>
+      <c r="Q21" s="49">
+        <v>46173</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="33" t="s">
+        <v>60</v>
+      </c>
+      <c r="B22" s="34" t="s">
+        <v>61</v>
+      </c>
+      <c r="C22" s="35" t="s">
+        <v>62</v>
+      </c>
+      <c r="D22" s="36" t="s">
+        <v>20</v>
+      </c>
+      <c r="E22" s="37" t="s">
+        <v>46</v>
+      </c>
+      <c r="F22" s="38" t="s">
+        <v>47</v>
+      </c>
+      <c r="G22" s="39" t="s">
+        <v>85</v>
+      </c>
+      <c r="H22" s="40" t="s">
+        <v>46</v>
+      </c>
+      <c r="I22" s="41" t="s">
+        <v>86</v>
+      </c>
+      <c r="J22" s="42" t="s">
+        <v>64</v>
+      </c>
+      <c r="K22" s="43" t="s">
+        <v>65</v>
+      </c>
+      <c r="L22" s="44" t="s">
+        <v>66</v>
+      </c>
+      <c r="M22" s="45">
+        <v>46173</v>
+      </c>
+      <c r="N22" s="46">
+        <v>46174</v>
+      </c>
+      <c r="O22" s="47" t="s">
+        <v>67</v>
+      </c>
+      <c r="P22" s="48" t="s">
+        <v>67</v>
+      </c>
+      <c r="Q22" s="49">
+        <v>46173</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="33" t="s">
+        <v>60</v>
+      </c>
+      <c r="B23" s="34" t="s">
+        <v>61</v>
+      </c>
+      <c r="C23" s="35" t="s">
+        <v>62</v>
+      </c>
+      <c r="D23" s="36" t="s">
+        <v>20</v>
+      </c>
+      <c r="E23" s="37" t="s">
+        <v>46</v>
+      </c>
+      <c r="F23" s="38" t="s">
+        <v>47</v>
+      </c>
+      <c r="G23" s="39" t="s">
+        <v>87</v>
+      </c>
+      <c r="H23" s="40" t="s">
+        <v>46</v>
+      </c>
+      <c r="I23" s="41" t="s">
+        <v>88</v>
+      </c>
+      <c r="J23" s="42" t="s">
+        <v>64</v>
+      </c>
+      <c r="K23" s="43" t="s">
+        <v>65</v>
+      </c>
+      <c r="L23" s="44" t="s">
+        <v>66</v>
+      </c>
+      <c r="M23" s="45">
+        <v>46173</v>
+      </c>
+      <c r="N23" s="46">
+        <v>46174</v>
+      </c>
+      <c r="O23" s="47" t="s">
+        <v>67</v>
+      </c>
+      <c r="P23" s="48" t="s">
+        <v>67</v>
+      </c>
+      <c r="Q23" s="49">
+        <v>46173</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="33" t="s">
+        <v>60</v>
+      </c>
+      <c r="B24" s="34" t="s">
+        <v>61</v>
+      </c>
+      <c r="C24" s="35" t="s">
+        <v>62</v>
+      </c>
+      <c r="D24" s="36" t="s">
+        <v>20</v>
+      </c>
+      <c r="E24" s="37" t="s">
+        <v>46</v>
+      </c>
+      <c r="F24" s="38" t="s">
+        <v>47</v>
+      </c>
+      <c r="G24" s="39" t="s">
+        <v>89</v>
+      </c>
+      <c r="H24" s="40" t="s">
+        <v>46</v>
+      </c>
+      <c r="I24" s="41" t="s">
+        <v>90</v>
+      </c>
+      <c r="J24" s="42" t="s">
+        <v>64</v>
+      </c>
+      <c r="K24" s="43" t="s">
+        <v>65</v>
+      </c>
+      <c r="L24" s="44" t="s">
+        <v>66</v>
+      </c>
+      <c r="M24" s="45">
+        <v>46173</v>
+      </c>
+      <c r="N24" s="46">
+        <v>46174</v>
+      </c>
+      <c r="O24" s="47" t="s">
+        <v>67</v>
+      </c>
+      <c r="P24" s="48" t="s">
+        <v>67</v>
+      </c>
+      <c r="Q24" s="49">
+        <v>46173</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="33" t="s">
+        <v>60</v>
+      </c>
+      <c r="B25" s="34" t="s">
+        <v>61</v>
+      </c>
+      <c r="C25" s="35" t="s">
+        <v>62</v>
+      </c>
+      <c r="D25" s="36" t="s">
+        <v>20</v>
+      </c>
+      <c r="E25" s="37" t="s">
+        <v>46</v>
+      </c>
+      <c r="F25" s="38" t="s">
+        <v>47</v>
+      </c>
+      <c r="G25" s="39" t="s">
+        <v>91</v>
+      </c>
+      <c r="H25" s="40" t="s">
+        <v>46</v>
+      </c>
+      <c r="I25" s="41" t="s">
+        <v>63</v>
+      </c>
+      <c r="J25" s="42" t="s">
+        <v>64</v>
+      </c>
+      <c r="K25" s="43" t="s">
+        <v>65</v>
+      </c>
+      <c r="L25" s="44" t="s">
+        <v>66</v>
+      </c>
+      <c r="M25" s="45">
+        <v>46173</v>
+      </c>
+      <c r="N25" s="46">
+        <v>46174</v>
+      </c>
+      <c r="O25" s="47" t="s">
+        <v>67</v>
+      </c>
+      <c r="P25" s="48" t="s">
+        <v>67</v>
+      </c>
+      <c r="Q25" s="49">
+        <v>46173</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="33" t="s">
+        <v>60</v>
+      </c>
+      <c r="B26" s="34" t="s">
+        <v>61</v>
+      </c>
+      <c r="C26" s="35" t="s">
+        <v>62</v>
+      </c>
+      <c r="D26" s="36" t="s">
+        <v>20</v>
+      </c>
+      <c r="E26" s="37" t="s">
+        <v>21</v>
+      </c>
+      <c r="F26" s="38" t="s">
+        <v>22</v>
+      </c>
+      <c r="G26" s="39" t="s">
+        <v>92</v>
+      </c>
+      <c r="H26" s="40" t="s">
+        <v>21</v>
+      </c>
+      <c r="I26" s="41" t="s">
+        <v>93</v>
+      </c>
+      <c r="J26" s="42" t="s">
+        <v>64</v>
+      </c>
+      <c r="K26" s="43" t="s">
+        <v>65</v>
+      </c>
+      <c r="L26" s="44" t="s">
+        <v>66</v>
+      </c>
+      <c r="M26" s="45">
+        <v>46173</v>
+      </c>
+      <c r="N26" s="46">
+        <v>46174</v>
+      </c>
+      <c r="O26" s="47" t="s">
+        <v>67</v>
+      </c>
+      <c r="P26" s="48" t="s">
+        <v>67</v>
+      </c>
+      <c r="Q26" s="49">
+        <v>46173</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="33" t="s">
+        <v>60</v>
+      </c>
+      <c r="B27" s="34" t="s">
+        <v>61</v>
+      </c>
+      <c r="C27" s="35" t="s">
+        <v>62</v>
+      </c>
+      <c r="D27" s="36" t="s">
+        <v>20</v>
+      </c>
+      <c r="E27" s="37" t="s">
+        <v>21</v>
+      </c>
+      <c r="F27" s="38" t="s">
+        <v>22</v>
+      </c>
+      <c r="G27" s="39" t="s">
+        <v>94</v>
+      </c>
+      <c r="H27" s="40" t="s">
+        <v>21</v>
+      </c>
+      <c r="I27" s="41" t="s">
+        <v>95</v>
+      </c>
+      <c r="J27" s="42" t="s">
+        <v>64</v>
+      </c>
+      <c r="K27" s="43" t="s">
+        <v>65</v>
+      </c>
+      <c r="L27" s="44" t="s">
+        <v>66</v>
+      </c>
+      <c r="M27" s="45">
+        <v>46173</v>
+      </c>
+      <c r="N27" s="46">
+        <v>46174</v>
+      </c>
+      <c r="O27" s="47" t="s">
+        <v>67</v>
+      </c>
+      <c r="P27" s="48" t="s">
+        <v>67</v>
+      </c>
+      <c r="Q27" s="49">
+        <v>46173</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="33" t="s">
+        <v>60</v>
+      </c>
+      <c r="B28" s="34" t="s">
+        <v>61</v>
+      </c>
+      <c r="C28" s="35" t="s">
+        <v>62</v>
+      </c>
+      <c r="D28" s="36" t="s">
+        <v>20</v>
+      </c>
+      <c r="E28" s="37" t="s">
+        <v>46</v>
+      </c>
+      <c r="F28" s="38" t="s">
+        <v>47</v>
+      </c>
+      <c r="G28" s="39" t="s">
+        <v>96</v>
+      </c>
+      <c r="H28" s="40" t="s">
+        <v>46</v>
+      </c>
+      <c r="I28" s="41" t="s">
+        <v>88</v>
+      </c>
+      <c r="J28" s="42" t="s">
+        <v>64</v>
+      </c>
+      <c r="K28" s="43" t="s">
+        <v>65</v>
+      </c>
+      <c r="L28" s="44" t="s">
+        <v>66</v>
+      </c>
+      <c r="M28" s="45">
+        <v>46173</v>
+      </c>
+      <c r="N28" s="46">
+        <v>46174</v>
+      </c>
+      <c r="O28" s="47" t="s">
+        <v>67</v>
+      </c>
+      <c r="P28" s="48" t="s">
+        <v>67</v>
+      </c>
+      <c r="Q28" s="49">
+        <v>46173</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="33" t="s">
+        <v>60</v>
+      </c>
+      <c r="B29" s="34" t="s">
+        <v>61</v>
+      </c>
+      <c r="C29" s="35" t="s">
+        <v>62</v>
+      </c>
+      <c r="D29" s="36" t="s">
+        <v>20</v>
+      </c>
+      <c r="E29" s="37" t="s">
+        <v>21</v>
+      </c>
+      <c r="F29" s="38" t="s">
+        <v>22</v>
+      </c>
+      <c r="G29" s="39" t="s">
+        <v>97</v>
+      </c>
+      <c r="H29" s="40" t="s">
+        <v>21</v>
+      </c>
+      <c r="I29" s="41" t="s">
         <v>98</v>
       </c>
-      <c r="J21" s="42" t="s">
+      <c r="J29" s="42" t="s">
+        <v>64</v>
+      </c>
+      <c r="K29" s="43" t="s">
+        <v>65</v>
+      </c>
+      <c r="L29" s="44" t="s">
+        <v>66</v>
+      </c>
+      <c r="M29" s="45">
+        <v>46173</v>
+      </c>
+      <c r="N29" s="46">
+        <v>46174</v>
+      </c>
+      <c r="O29" s="47" t="s">
+        <v>67</v>
+      </c>
+      <c r="P29" s="48" t="s">
+        <v>67</v>
+      </c>
+      <c r="Q29" s="49">
+        <v>46173</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="33" t="s">
         <v>99</v>
       </c>
-      <c r="K21" s="43" t="s">
+      <c r="B30" s="34" t="s">
         <v>100</v>
       </c>
-      <c r="L21" s="44" t="s">
+      <c r="C30" s="35" t="s">
+        <v>19</v>
+      </c>
+      <c r="D30" s="36" t="s">
+        <v>20</v>
+      </c>
+      <c r="E30" s="37" t="s">
+        <v>21</v>
+      </c>
+      <c r="F30" s="38" t="s">
+        <v>22</v>
+      </c>
+      <c r="G30" s="39" t="s">
+        <v>23</v>
+      </c>
+      <c r="H30" s="40" t="s">
+        <v>21</v>
+      </c>
+      <c r="I30" s="41" t="s">
         <v>101</v>
       </c>
-      <c r="M21" s="45">
-        <v>46173</v>
-      </c>
-      <c r="N21" s="46">
-        <v>46173</v>
-      </c>
-      <c r="O21" s="47" t="s">
+      <c r="J30" s="42" t="s">
         <v>102</v>
       </c>
-      <c r="P21" s="48" t="s">
+      <c r="K30" s="43" t="s">
+        <v>103</v>
+      </c>
+      <c r="L30" s="44" t="s">
+        <v>104</v>
+      </c>
+      <c r="M30" s="45">
+        <v>46174</v>
+      </c>
+      <c r="N30" s="46">
+        <v>46174</v>
+      </c>
+      <c r="O30" s="47" t="s">
+        <v>105</v>
+      </c>
+      <c r="P30" s="48" t="s">
+        <v>105</v>
+      </c>
+      <c r="Q30" s="49">
+        <v>46151</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="33" t="s">
+        <v>99</v>
+      </c>
+      <c r="B31" s="34" t="s">
+        <v>100</v>
+      </c>
+      <c r="C31" s="35" t="s">
+        <v>19</v>
+      </c>
+      <c r="D31" s="36" t="s">
+        <v>20</v>
+      </c>
+      <c r="E31" s="37" t="s">
+        <v>21</v>
+      </c>
+      <c r="F31" s="38" t="s">
+        <v>22</v>
+      </c>
+      <c r="G31" s="39" t="s">
+        <v>41</v>
+      </c>
+      <c r="H31" s="40" t="s">
+        <v>21</v>
+      </c>
+      <c r="I31" s="41" t="s">
+        <v>106</v>
+      </c>
+      <c r="J31" s="42" t="s">
         <v>102</v>
       </c>
-      <c r="Q21" s="49">
-        <v>46160</v>
+      <c r="K31" s="43" t="s">
+        <v>103</v>
+      </c>
+      <c r="L31" s="44" t="s">
+        <v>104</v>
+      </c>
+      <c r="M31" s="45">
+        <v>46174</v>
+      </c>
+      <c r="N31" s="46">
+        <v>46174</v>
+      </c>
+      <c r="O31" s="47" t="s">
+        <v>105</v>
+      </c>
+      <c r="P31" s="48" t="s">
+        <v>105</v>
+      </c>
+      <c r="Q31" s="49">
+        <v>46151</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="33" t="s">
+        <v>99</v>
+      </c>
+      <c r="B32" s="34" t="s">
+        <v>100</v>
+      </c>
+      <c r="C32" s="35" t="s">
+        <v>19</v>
+      </c>
+      <c r="D32" s="36" t="s">
+        <v>20</v>
+      </c>
+      <c r="E32" s="37" t="s">
+        <v>21</v>
+      </c>
+      <c r="F32" s="38" t="s">
+        <v>22</v>
+      </c>
+      <c r="G32" s="39" t="s">
+        <v>68</v>
+      </c>
+      <c r="H32" s="40" t="s">
+        <v>21</v>
+      </c>
+      <c r="I32" s="41" t="s">
+        <v>107</v>
+      </c>
+      <c r="J32" s="42" t="s">
+        <v>102</v>
+      </c>
+      <c r="K32" s="43" t="s">
+        <v>103</v>
+      </c>
+      <c r="L32" s="44" t="s">
+        <v>104</v>
+      </c>
+      <c r="M32" s="45">
+        <v>46174</v>
+      </c>
+      <c r="N32" s="46">
+        <v>46174</v>
+      </c>
+      <c r="O32" s="47" t="s">
+        <v>105</v>
+      </c>
+      <c r="P32" s="48" t="s">
+        <v>105</v>
+      </c>
+      <c r="Q32" s="49">
+        <v>46151</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="33" t="s">
+        <v>99</v>
+      </c>
+      <c r="B33" s="34" t="s">
+        <v>100</v>
+      </c>
+      <c r="C33" s="35" t="s">
+        <v>19</v>
+      </c>
+      <c r="D33" s="36" t="s">
+        <v>20</v>
+      </c>
+      <c r="E33" s="37" t="s">
+        <v>21</v>
+      </c>
+      <c r="F33" s="38" t="s">
+        <v>22</v>
+      </c>
+      <c r="G33" s="39" t="s">
+        <v>69</v>
+      </c>
+      <c r="H33" s="40" t="s">
+        <v>21</v>
+      </c>
+      <c r="I33" s="41" t="s">
+        <v>108</v>
+      </c>
+      <c r="J33" s="42" t="s">
+        <v>102</v>
+      </c>
+      <c r="K33" s="43" t="s">
+        <v>103</v>
+      </c>
+      <c r="L33" s="44" t="s">
+        <v>104</v>
+      </c>
+      <c r="M33" s="45">
+        <v>46174</v>
+      </c>
+      <c r="N33" s="46">
+        <v>46174</v>
+      </c>
+      <c r="O33" s="47" t="s">
+        <v>105</v>
+      </c>
+      <c r="P33" s="48" t="s">
+        <v>105</v>
+      </c>
+      <c r="Q33" s="49">
+        <v>46151</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="33" t="s">
+        <v>109</v>
+      </c>
+      <c r="B34" s="34" t="s">
+        <v>110</v>
+      </c>
+      <c r="C34" s="35" t="s">
+        <v>62</v>
+      </c>
+      <c r="D34" s="36" t="s">
+        <v>20</v>
+      </c>
+      <c r="E34" s="37" t="s">
+        <v>46</v>
+      </c>
+      <c r="F34" s="38" t="s">
+        <v>47</v>
+      </c>
+      <c r="G34" s="39" t="s">
+        <v>23</v>
+      </c>
+      <c r="H34" s="40" t="s">
+        <v>46</v>
+      </c>
+      <c r="I34" s="41" t="s">
+        <v>111</v>
+      </c>
+      <c r="J34" s="42" t="s">
+        <v>112</v>
+      </c>
+      <c r="K34" s="43" t="s">
+        <v>113</v>
+      </c>
+      <c r="L34" s="44" t="s">
+        <v>114</v>
+      </c>
+      <c r="M34" s="45">
+        <v>46173</v>
+      </c>
+      <c r="N34" s="46">
+        <v>46174</v>
+      </c>
+      <c r="O34" s="47" t="s">
+        <v>115</v>
+      </c>
+      <c r="P34" s="48" t="s">
+        <v>115</v>
+      </c>
+      <c r="Q34" s="49">
+        <v>46173</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="33" t="s">
+        <v>109</v>
+      </c>
+      <c r="B35" s="34" t="s">
+        <v>110</v>
+      </c>
+      <c r="C35" s="35" t="s">
+        <v>62</v>
+      </c>
+      <c r="D35" s="36" t="s">
+        <v>20</v>
+      </c>
+      <c r="E35" s="37" t="s">
+        <v>46</v>
+      </c>
+      <c r="F35" s="38" t="s">
+        <v>47</v>
+      </c>
+      <c r="G35" s="39" t="s">
+        <v>41</v>
+      </c>
+      <c r="H35" s="40" t="s">
+        <v>46</v>
+      </c>
+      <c r="I35" s="41" t="s">
+        <v>116</v>
+      </c>
+      <c r="J35" s="42" t="s">
+        <v>112</v>
+      </c>
+      <c r="K35" s="43" t="s">
+        <v>113</v>
+      </c>
+      <c r="L35" s="44" t="s">
+        <v>114</v>
+      </c>
+      <c r="M35" s="45">
+        <v>46173</v>
+      </c>
+      <c r="N35" s="46">
+        <v>46174</v>
+      </c>
+      <c r="O35" s="47" t="s">
+        <v>115</v>
+      </c>
+      <c r="P35" s="48" t="s">
+        <v>115</v>
+      </c>
+      <c r="Q35" s="49">
+        <v>46173</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="33" t="s">
+        <v>109</v>
+      </c>
+      <c r="B36" s="34" t="s">
+        <v>110</v>
+      </c>
+      <c r="C36" s="35" t="s">
+        <v>62</v>
+      </c>
+      <c r="D36" s="36" t="s">
+        <v>20</v>
+      </c>
+      <c r="E36" s="37" t="s">
+        <v>46</v>
+      </c>
+      <c r="F36" s="38" t="s">
+        <v>47</v>
+      </c>
+      <c r="G36" s="39" t="s">
+        <v>68</v>
+      </c>
+      <c r="H36" s="40" t="s">
+        <v>46</v>
+      </c>
+      <c r="I36" s="41" t="s">
+        <v>111</v>
+      </c>
+      <c r="J36" s="42" t="s">
+        <v>112</v>
+      </c>
+      <c r="K36" s="43" t="s">
+        <v>113</v>
+      </c>
+      <c r="L36" s="44" t="s">
+        <v>114</v>
+      </c>
+      <c r="M36" s="45">
+        <v>46173</v>
+      </c>
+      <c r="N36" s="46">
+        <v>46174</v>
+      </c>
+      <c r="O36" s="47" t="s">
+        <v>115</v>
+      </c>
+      <c r="P36" s="48" t="s">
+        <v>115</v>
+      </c>
+      <c r="Q36" s="49">
+        <v>46173</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="33" t="s">
+        <v>109</v>
+      </c>
+      <c r="B37" s="34" t="s">
+        <v>110</v>
+      </c>
+      <c r="C37" s="35" t="s">
+        <v>62</v>
+      </c>
+      <c r="D37" s="36" t="s">
+        <v>20</v>
+      </c>
+      <c r="E37" s="37" t="s">
+        <v>46</v>
+      </c>
+      <c r="F37" s="38" t="s">
+        <v>47</v>
+      </c>
+      <c r="G37" s="39" t="s">
+        <v>69</v>
+      </c>
+      <c r="H37" s="40" t="s">
+        <v>46</v>
+      </c>
+      <c r="I37" s="41" t="s">
+        <v>111</v>
+      </c>
+      <c r="J37" s="42" t="s">
+        <v>112</v>
+      </c>
+      <c r="K37" s="43" t="s">
+        <v>113</v>
+      </c>
+      <c r="L37" s="44" t="s">
+        <v>114</v>
+      </c>
+      <c r="M37" s="45">
+        <v>46173</v>
+      </c>
+      <c r="N37" s="46">
+        <v>46174</v>
+      </c>
+      <c r="O37" s="47" t="s">
+        <v>115</v>
+      </c>
+      <c r="P37" s="48" t="s">
+        <v>115</v>
+      </c>
+      <c r="Q37" s="49">
+        <v>46173</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="33" t="s">
+        <v>109</v>
+      </c>
+      <c r="B38" s="34" t="s">
+        <v>110</v>
+      </c>
+      <c r="C38" s="35" t="s">
+        <v>62</v>
+      </c>
+      <c r="D38" s="36" t="s">
+        <v>20</v>
+      </c>
+      <c r="E38" s="37" t="s">
+        <v>46</v>
+      </c>
+      <c r="F38" s="38" t="s">
+        <v>47</v>
+      </c>
+      <c r="G38" s="39" t="s">
+        <v>70</v>
+      </c>
+      <c r="H38" s="40" t="s">
+        <v>46</v>
+      </c>
+      <c r="I38" s="41" t="s">
+        <v>111</v>
+      </c>
+      <c r="J38" s="42" t="s">
+        <v>112</v>
+      </c>
+      <c r="K38" s="43" t="s">
+        <v>113</v>
+      </c>
+      <c r="L38" s="44" t="s">
+        <v>114</v>
+      </c>
+      <c r="M38" s="45">
+        <v>46173</v>
+      </c>
+      <c r="N38" s="46">
+        <v>46174</v>
+      </c>
+      <c r="O38" s="47" t="s">
+        <v>115</v>
+      </c>
+      <c r="P38" s="48" t="s">
+        <v>115</v>
+      </c>
+      <c r="Q38" s="49">
+        <v>46173</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="33" t="s">
+        <v>109</v>
+      </c>
+      <c r="B39" s="34" t="s">
+        <v>110</v>
+      </c>
+      <c r="C39" s="35" t="s">
+        <v>62</v>
+      </c>
+      <c r="D39" s="36" t="s">
+        <v>20</v>
+      </c>
+      <c r="E39" s="37" t="s">
+        <v>46</v>
+      </c>
+      <c r="F39" s="38" t="s">
+        <v>47</v>
+      </c>
+      <c r="G39" s="39" t="s">
+        <v>72</v>
+      </c>
+      <c r="H39" s="40" t="s">
+        <v>46</v>
+      </c>
+      <c r="I39" s="41" t="s">
+        <v>111</v>
+      </c>
+      <c r="J39" s="42" t="s">
+        <v>112</v>
+      </c>
+      <c r="K39" s="43" t="s">
+        <v>113</v>
+      </c>
+      <c r="L39" s="44" t="s">
+        <v>114</v>
+      </c>
+      <c r="M39" s="45">
+        <v>46173</v>
+      </c>
+      <c r="N39" s="46">
+        <v>46174</v>
+      </c>
+      <c r="O39" s="47" t="s">
+        <v>115</v>
+      </c>
+      <c r="P39" s="48" t="s">
+        <v>115</v>
+      </c>
+      <c r="Q39" s="49">
+        <v>46173</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="33" t="s">
+        <v>109</v>
+      </c>
+      <c r="B40" s="34" t="s">
+        <v>110</v>
+      </c>
+      <c r="C40" s="35" t="s">
+        <v>62</v>
+      </c>
+      <c r="D40" s="36" t="s">
+        <v>20</v>
+      </c>
+      <c r="E40" s="37" t="s">
+        <v>46</v>
+      </c>
+      <c r="F40" s="38" t="s">
+        <v>47</v>
+      </c>
+      <c r="G40" s="39" t="s">
+        <v>73</v>
+      </c>
+      <c r="H40" s="40" t="s">
+        <v>46</v>
+      </c>
+      <c r="I40" s="41" t="s">
+        <v>111</v>
+      </c>
+      <c r="J40" s="42" t="s">
+        <v>112</v>
+      </c>
+      <c r="K40" s="43" t="s">
+        <v>113</v>
+      </c>
+      <c r="L40" s="44" t="s">
+        <v>114</v>
+      </c>
+      <c r="M40" s="45">
+        <v>46173</v>
+      </c>
+      <c r="N40" s="46">
+        <v>46174</v>
+      </c>
+      <c r="O40" s="47" t="s">
+        <v>115</v>
+      </c>
+      <c r="P40" s="48" t="s">
+        <v>115</v>
+      </c>
+      <c r="Q40" s="49">
+        <v>46173</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="33" t="s">
+        <v>109</v>
+      </c>
+      <c r="B41" s="34" t="s">
+        <v>110</v>
+      </c>
+      <c r="C41" s="35" t="s">
+        <v>62</v>
+      </c>
+      <c r="D41" s="36" t="s">
+        <v>20</v>
+      </c>
+      <c r="E41" s="37" t="s">
+        <v>46</v>
+      </c>
+      <c r="F41" s="38" t="s">
+        <v>47</v>
+      </c>
+      <c r="G41" s="39" t="s">
+        <v>75</v>
+      </c>
+      <c r="H41" s="40" t="s">
+        <v>46</v>
+      </c>
+      <c r="I41" s="41" t="s">
+        <v>111</v>
+      </c>
+      <c r="J41" s="42" t="s">
+        <v>112</v>
+      </c>
+      <c r="K41" s="43" t="s">
+        <v>113</v>
+      </c>
+      <c r="L41" s="44" t="s">
+        <v>114</v>
+      </c>
+      <c r="M41" s="45">
+        <v>46173</v>
+      </c>
+      <c r="N41" s="46">
+        <v>46174</v>
+      </c>
+      <c r="O41" s="47" t="s">
+        <v>115</v>
+      </c>
+      <c r="P41" s="48" t="s">
+        <v>115</v>
+      </c>
+      <c r="Q41" s="49">
+        <v>46173</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="33" t="s">
+        <v>109</v>
+      </c>
+      <c r="B42" s="34" t="s">
+        <v>110</v>
+      </c>
+      <c r="C42" s="35" t="s">
+        <v>62</v>
+      </c>
+      <c r="D42" s="36" t="s">
+        <v>20</v>
+      </c>
+      <c r="E42" s="37" t="s">
+        <v>46</v>
+      </c>
+      <c r="F42" s="38" t="s">
+        <v>47</v>
+      </c>
+      <c r="G42" s="39" t="s">
+        <v>77</v>
+      </c>
+      <c r="H42" s="40" t="s">
+        <v>46</v>
+      </c>
+      <c r="I42" s="41" t="s">
+        <v>111</v>
+      </c>
+      <c r="J42" s="42" t="s">
+        <v>112</v>
+      </c>
+      <c r="K42" s="43" t="s">
+        <v>113</v>
+      </c>
+      <c r="L42" s="44" t="s">
+        <v>114</v>
+      </c>
+      <c r="M42" s="45">
+        <v>46173</v>
+      </c>
+      <c r="N42" s="46">
+        <v>46174</v>
+      </c>
+      <c r="O42" s="47" t="s">
+        <v>115</v>
+      </c>
+      <c r="P42" s="48" t="s">
+        <v>115</v>
+      </c>
+      <c r="Q42" s="49">
+        <v>46173</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="33" t="s">
+        <v>109</v>
+      </c>
+      <c r="B43" s="34" t="s">
+        <v>110</v>
+      </c>
+      <c r="C43" s="35" t="s">
+        <v>62</v>
+      </c>
+      <c r="D43" s="36" t="s">
+        <v>20</v>
+      </c>
+      <c r="E43" s="37" t="s">
+        <v>46</v>
+      </c>
+      <c r="F43" s="38" t="s">
+        <v>47</v>
+      </c>
+      <c r="G43" s="39" t="s">
+        <v>78</v>
+      </c>
+      <c r="H43" s="40" t="s">
+        <v>46</v>
+      </c>
+      <c r="I43" s="41" t="s">
+        <v>111</v>
+      </c>
+      <c r="J43" s="42" t="s">
+        <v>112</v>
+      </c>
+      <c r="K43" s="43" t="s">
+        <v>113</v>
+      </c>
+      <c r="L43" s="44" t="s">
+        <v>114</v>
+      </c>
+      <c r="M43" s="45">
+        <v>46173</v>
+      </c>
+      <c r="N43" s="46">
+        <v>46174</v>
+      </c>
+      <c r="O43" s="47" t="s">
+        <v>115</v>
+      </c>
+      <c r="P43" s="48" t="s">
+        <v>115</v>
+      </c>
+      <c r="Q43" s="49">
+        <v>46173</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="33" t="s">
+        <v>109</v>
+      </c>
+      <c r="B44" s="34" t="s">
+        <v>110</v>
+      </c>
+      <c r="C44" s="35" t="s">
+        <v>62</v>
+      </c>
+      <c r="D44" s="36" t="s">
+        <v>20</v>
+      </c>
+      <c r="E44" s="37" t="s">
+        <v>46</v>
+      </c>
+      <c r="F44" s="38" t="s">
+        <v>47</v>
+      </c>
+      <c r="G44" s="39" t="s">
+        <v>79</v>
+      </c>
+      <c r="H44" s="40" t="s">
+        <v>46</v>
+      </c>
+      <c r="I44" s="41" t="s">
+        <v>111</v>
+      </c>
+      <c r="J44" s="42" t="s">
+        <v>112</v>
+      </c>
+      <c r="K44" s="43" t="s">
+        <v>113</v>
+      </c>
+      <c r="L44" s="44" t="s">
+        <v>114</v>
+      </c>
+      <c r="M44" s="45">
+        <v>46173</v>
+      </c>
+      <c r="N44" s="46">
+        <v>46174</v>
+      </c>
+      <c r="O44" s="47" t="s">
+        <v>115</v>
+      </c>
+      <c r="P44" s="48" t="s">
+        <v>115</v>
+      </c>
+      <c r="Q44" s="49">
+        <v>46173</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="33" t="s">
+        <v>109</v>
+      </c>
+      <c r="B45" s="34" t="s">
+        <v>110</v>
+      </c>
+      <c r="C45" s="35" t="s">
+        <v>62</v>
+      </c>
+      <c r="D45" s="36" t="s">
+        <v>20</v>
+      </c>
+      <c r="E45" s="37" t="s">
+        <v>46</v>
+      </c>
+      <c r="F45" s="38" t="s">
+        <v>47</v>
+      </c>
+      <c r="G45" s="39" t="s">
+        <v>80</v>
+      </c>
+      <c r="H45" s="40" t="s">
+        <v>46</v>
+      </c>
+      <c r="I45" s="41" t="s">
+        <v>117</v>
+      </c>
+      <c r="J45" s="42" t="s">
+        <v>112</v>
+      </c>
+      <c r="K45" s="43" t="s">
+        <v>113</v>
+      </c>
+      <c r="L45" s="44" t="s">
+        <v>114</v>
+      </c>
+      <c r="M45" s="45">
+        <v>46173</v>
+      </c>
+      <c r="N45" s="46">
+        <v>46174</v>
+      </c>
+      <c r="O45" s="47" t="s">
+        <v>115</v>
+      </c>
+      <c r="P45" s="48" t="s">
+        <v>115</v>
+      </c>
+      <c r="Q45" s="49">
+        <v>46173</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError sqref="A1 B1 C1 D1 E1 F1 G1 H1 I1 J1 K1 L1 M1 N1 O1 P1 Q1 A2 B2 C2 D2 E2 F2 G2 H2 I2 J2 K2 L2 O2 P2 A3 B3 C3 D3 E3 F3 G3 H3 I3 J3 K3 L3 O3 P3 A4 B4 C4 D4 E4 F4 G4 H4 I4 J4 K4 L4 O4 P4 A5 B5 C5 D5 E5 F5 G5 H5 I5 J5 K5 L5 O5 P5 A6 B6 C6 D6 E6 F6 G6 H6 I6 J6 K6 L6 O6 P6 A7 B7 C7 D7 E7 F7 G7 H7 I7 J7 K7 L7 O7 P7 A8 B8 C8 D8 E8 F8 G8 H8 I8 J8 K8 L8 O8 P8 A9 B9 C9 D9 E9 F9 G9 H9 I9 J9 K9 L9 O9 P9 A10 B10 C10 D10 E10 F10 G10 H10 I10 J10 K10 L10 O10 P10 A11 B11 C11 D11 E11 F11 G11 H11 I11 J11 K11 L11 O11 P11 A12 B12 C12 D12 E12 F12 G12 H12 I12 J12 K12 L12 O12 P12 A13 B13 C13 D13 E13 F13 G13 H13 I13 J13 K13 L13 O13 P13 A14 B14 C14 D14 E14 F14 G14 H14 I14 J14 K14 L14 O14 P14 A15 B15 C15 D15 E15 F15 G15 H15 I15 J15 K15 L15 O15 P15 A16 B16 C16 D16 E16 F16 G16 H16 I16 J16 K16 L16 O16 P16 A17 B17 C17 D17 E17 F17 G17 H17 I17 J17 K17 L17 O17 P17 A18 B18 C18 D18 E18 F18 G18 H18 I18 J18 K18 L18 O18 P18 A19 B19 C19 D19 E19 F19 G19 H19 I19 J19 K19 L19 O19 P19 A20 B20 C20 D20 E20 F20 G20 H20 I20 J20 K20 L20 O20 P20 A21 B21 C21 D21 E21 F21 G21 H21 I21 J21 K21 L21 O21 P21" numberStoredAsText="true"/>
+    <ignoredError sqref="A1 B1 C1 D1 E1 F1 G1 H1 I1 J1 K1 L1 M1 N1 O1 P1 Q1 A2 B2 C2 D2 E2 F2 G2 H2 I2 J2 K2 L2 O2 P2 A3 B3 C3 D3 E3 F3 G3 H3 I3 J3 K3 L3 O3 P3 A4 B4 C4 D4 E4 F4 G4 H4 I4 J4 K4 L4 O4 P4 A5 B5 C5 D5 E5 F5 G5 H5 I5 J5 K5 L5 O5 P5 A6 B6 C6 D6 E6 F6 G6 H6 I6 J6 K6 L6 O6 P6 A7 B7 C7 D7 E7 F7 G7 H7 I7 J7 K7 L7 O7 P7 A8 B8 C8 D8 E8 F8 G8 H8 I8 J8 K8 L8 O8 P8 A9 B9 C9 D9 E9 F9 G9 H9 I9 J9 K9 L9 O9 P9 A10 B10 C10 D10 E10 F10 G10 H10 I10 J10 K10 L10 O10 P10 A11 B11 C11 D11 E11 F11 G11 H11 I11 J11 K11 L11 O11 P11 A12 B12 C12 D12 E12 F12 G12 H12 I12 J12 K12 L12 O12 P12 A13 B13 C13 D13 E13 F13 G13 H13 I13 J13 K13 L13 O13 P13 A14 B14 C14 D14 E14 F14 G14 H14 I14 J14 K14 L14 O14 P14 A15 B15 C15 D15 E15 F15 G15 H15 I15 J15 K15 L15 O15 P15 A16 B16 C16 D16 E16 F16 G16 H16 I16 J16 K16 L16 O16 P16 A17 B17 C17 D17 E17 F17 G17 H17 I17 J17 K17 L17 O17 P17 A18 B18 C18 D18 E18 F18 G18 H18 I18 J18 K18 L18 O18 P18 A19 B19 C19 D19 E19 F19 G19 H19 I19 J19 K19 L19 O19 P19 A20 B20 C20 D20 E20 F20 G20 H20 I20 J20 K20 L20 O20 P20 A21 B21 C21 D21 E21 F21 G21 H21 I21 J21 K21 L21 O21 P21 A22 B22 C22 D22 E22 F22 G22 H22 I22 J22 K22 L22 O22 P22 A23 B23 C23 D23 E23 F23 G23 H23 I23 J23 K23 L23 O23 P23 A24 B24 C24 D24 E24 F24 G24 H24 I24 J24 K24 L24 O24 P24 A25 B25 C25 D25 E25 F25 G25 H25 I25 J25 K25 L25 O25 P25 A26 B26 C26 D26 E26 F26 G26 H26 I26 J26 K26 L26 O26 P26 A27 B27 C27 D27 E27 F27 G27 H27 I27 J27 K27 L27 O27 P27 A28 B28 C28 D28 E28 F28 G28 H28 I28 J28 K28 L28 O28 P28 A29 B29 C29 D29 E29 F29 G29 H29 I29 J29 K29 L29 O29 P29 A30 B30 C30 D30 E30 F30 G30 H30 I30 J30 K30 L30 O30 P30 A31 B31 C31 D31 E31 F31 G31 H31 I31 J31 K31 L31 O31 P31 A32 B32 C32 D32 E32 F32 G32 H32 I32 J32 K32 L32 O32 P32 A33 B33 C33 D33 E33 F33 G33 H33 I33 J33 K33 L33 O33 P33 A34 B34 C34 D34 E34 F34 G34 H34 I34 J34 K34 L34 O34 P34 A35 B35 C35 D35 E35 F35 G35 H35 I35 J35 K35 L35 O35 P35 A36 B36 C36 D36 E36 F36 G36 H36 I36 J36 K36 L36 O36 P36 A37 B37 C37 D37 E37 F37 G37 H37 I37 J37 K37 L37 O37 P37 A38 B38 C38 D38 E38 F38 G38 H38 I38 J38 K38 L38 O38 P38 A39 B39 C39 D39 E39 F39 G39 H39 I39 J39 K39 L39 O39 P39 A40 B40 C40 D40 E40 F40 G40 H40 I40 J40 K40 L40 O40 P40 A41 B41 C41 D41 E41 F41 G41 H41 I41 J41 K41 L41 O41 P41 A42 B42 C42 D42 E42 F42 G42 H42 I42 J42 K42 L42 O42 P42 A43 B43 C43 D43 E43 F43 G43 H43 I43 J43 K43 L43 O43 P43 A44 B44 C44 D44 E44 F44 G44 H44 I44 J44 K44 L44 O44 P44 A45 B45 C45 D45 E45 F45 G45 H45 I45 J45 K45 L45 O45 P45" numberStoredAsText="true"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/trimika_data.xlsx
+++ b/trimika_data.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" count="633" uniqueCount="118">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" count="2075" uniqueCount="235">
   <si>
     <t>REFERENCE NO</t>
   </si>
@@ -66,28 +66,199 @@
     <t>EXPORT DATE</t>
   </si>
   <si>
-    <t>2565426</t>
-  </si>
-  <si>
-    <t>EF4-0231160-1</t>
+    <t>2565392</t>
+  </si>
+  <si>
+    <t>EF4-0230990-2</t>
   </si>
   <si>
     <t>Vessel, Container</t>
   </si>
   <si>
+    <t>218388892</t>
+  </si>
+  <si>
+    <t>9903.03.01</t>
+  </si>
+  <si>
+    <t>SECTION 122 - 10% DUTY</t>
+  </si>
+  <si>
+    <t>001</t>
+  </si>
+  <si>
+    <t>8474.10.0010</t>
+  </si>
+  <si>
+    <t>EDGE INNOVATE (NI) LTD</t>
+  </si>
+  <si>
+    <t>EDGINN01</t>
+  </si>
+  <si>
+    <t>135501-01432</t>
+  </si>
+  <si>
+    <t>105504657</t>
+  </si>
+  <si>
+    <t>EF4-0231314-4</t>
+  </si>
+  <si>
+    <t>Vessel, Non-container</t>
+  </si>
+  <si>
     <t/>
   </si>
   <si>
-    <t>9903.03.01</t>
-  </si>
-  <si>
-    <t>SECTION 122 - 10% DUTY</t>
-  </si>
-  <si>
-    <t>001</t>
-  </si>
-  <si>
-    <t>3505.10.0092</t>
+    <t>9805.00.50</t>
+  </si>
+  <si>
+    <t>EFFECTS US GOV EMP&amp;FAMLY/EVACU</t>
+  </si>
+  <si>
+    <t>CHRISTIAN, MICHAEL ANDRE</t>
+  </si>
+  <si>
+    <t>CHRMIC03</t>
+  </si>
+  <si>
+    <t>BMW MANUFACTURING CORP.</t>
+  </si>
+  <si>
+    <t>105504684</t>
+  </si>
+  <si>
+    <t>EF4-0231590-9</t>
+  </si>
+  <si>
+    <t>9903.03.06</t>
+  </si>
+  <si>
+    <t>S122 EXCL,IRN/STL/ALUM,DERIV</t>
+  </si>
+  <si>
+    <t>9903.94.51,8703.23.0190</t>
+  </si>
+  <si>
+    <t>BAVARIAN MOTOR CARS USA INC</t>
+  </si>
+  <si>
+    <t>BAVMOT01</t>
+  </si>
+  <si>
+    <t>42-176907500</t>
+  </si>
+  <si>
+    <t>BMW AG</t>
+  </si>
+  <si>
+    <t>105504685</t>
+  </si>
+  <si>
+    <t>EF4-0231591-7</t>
+  </si>
+  <si>
+    <t>105504686</t>
+  </si>
+  <si>
+    <t>EF4-0231592-5</t>
+  </si>
+  <si>
+    <t>2565762</t>
+  </si>
+  <si>
+    <t>EF4-0231596-6</t>
+  </si>
+  <si>
+    <t>9903.88.15</t>
+  </si>
+  <si>
+    <t>ARTICLE OF CHINA,US NTE 20(R)</t>
+  </si>
+  <si>
+    <t>9903.03.01,3926.90.9989</t>
+  </si>
+  <si>
+    <t>VISUAL CREATIONS, INC.</t>
+  </si>
+  <si>
+    <t>VISCRE</t>
+  </si>
+  <si>
+    <t>20-461602300</t>
+  </si>
+  <si>
+    <t>FUJIAN ANTAI NEW ENERGY TECH CO LTD</t>
+  </si>
+  <si>
+    <t>9903.88.03</t>
+  </si>
+  <si>
+    <t>ARTICLE OF CHINA,US NTE 20(F)</t>
+  </si>
+  <si>
+    <t>002</t>
+  </si>
+  <si>
+    <t>9903.03.01,9903.76.04,9403.60.8093</t>
+  </si>
+  <si>
+    <t>003</t>
+  </si>
+  <si>
+    <t>9903.03.01,9403.99.9045</t>
+  </si>
+  <si>
+    <t>004</t>
+  </si>
+  <si>
+    <t>9903.03.06,9903.82.09,8302.42.3065</t>
+  </si>
+  <si>
+    <t>005</t>
+  </si>
+  <si>
+    <t>9903.03.01,9403.20.0075</t>
+  </si>
+  <si>
+    <t>006</t>
+  </si>
+  <si>
+    <t>9903.03.06,9903.82.02,7616.99.5190</t>
+  </si>
+  <si>
+    <t>2565803</t>
+  </si>
+  <si>
+    <t>EF4-0231637-8</t>
+  </si>
+  <si>
+    <t>9903.82.02,7223.00.1061</t>
+  </si>
+  <si>
+    <t>VENUS WIRE INDUSTRIES PRIVATE LTD</t>
+  </si>
+  <si>
+    <t>VENWIR</t>
+  </si>
+  <si>
+    <t>993901-03595</t>
+  </si>
+  <si>
+    <t>PRECISION METALS</t>
+  </si>
+  <si>
+    <t>2565818</t>
+  </si>
+  <si>
+    <t>EF4-0231708-7</t>
+  </si>
+  <si>
+    <t>V1626451911</t>
+  </si>
+  <si>
+    <t>1109.00.1000</t>
   </si>
   <si>
     <t>ROYAL INGREDIENTS GROUP BV</t>
@@ -99,156 +270,147 @@
     <t>074601-00962</t>
   </si>
   <si>
+    <t>SEDAMYL UK</t>
+  </si>
+  <si>
+    <t>2565714</t>
+  </si>
+  <si>
+    <t>EF4-0231746-7</t>
+  </si>
+  <si>
+    <t>9903.03.03</t>
+  </si>
+  <si>
+    <t>S122 -EXCLUSION-EXEMPTED PRDTS</t>
+  </si>
+  <si>
+    <t>1108.14.0000</t>
+  </si>
+  <si>
     <t>SANGUAN WONGSE STARCH CO., LTD.</t>
   </si>
   <si>
-    <t>2565427</t>
-  </si>
-  <si>
-    <t>EF4-0231249-2</t>
-  </si>
-  <si>
-    <t>9903.03.03</t>
-  </si>
-  <si>
-    <t>S122 -EXCLUSION-EXEMPTED PRDTS</t>
-  </si>
-  <si>
-    <t>1108.14.0000</t>
-  </si>
-  <si>
-    <t>2565740</t>
-  </si>
-  <si>
-    <t>EF4-0231610-5</t>
-  </si>
-  <si>
-    <t>4418.75.7000</t>
-  </si>
-  <si>
-    <t>AUTHENTIC SURFACES LLC</t>
-  </si>
-  <si>
-    <t>AUTSUR01</t>
-  </si>
-  <si>
-    <t>86-279678900</t>
-  </si>
-  <si>
-    <t>CHENE DE L'EST</t>
-  </si>
-  <si>
-    <t>002</t>
-  </si>
-  <si>
-    <t>4409.29.0655</t>
-  </si>
-  <si>
-    <t>2565608</t>
-  </si>
-  <si>
-    <t>EF4-0231652-7</t>
-  </si>
-  <si>
-    <t>V0710308649</t>
-  </si>
-  <si>
-    <t>9903.03.06</t>
-  </si>
-  <si>
-    <t>S122 EXCL,IRN/STL/ALUM,DERIV</t>
-  </si>
-  <si>
-    <t>9903.82.02,7223.00.1061</t>
-  </si>
-  <si>
-    <t>VENUS WIRE INDUSTRIES PRIVATE LTD</t>
-  </si>
-  <si>
-    <t>VENWIR</t>
-  </si>
-  <si>
-    <t>993901-03595</t>
-  </si>
-  <si>
-    <t>PRECISION METALS</t>
-  </si>
-  <si>
-    <t>2565819</t>
-  </si>
-  <si>
-    <t>EF4-0231757-4</t>
-  </si>
-  <si>
-    <t>3920.20.0055</t>
-  </si>
-  <si>
-    <t>GULF ATLANTIC PACKAGING CORP</t>
-  </si>
-  <si>
-    <t>GULATL</t>
-  </si>
-  <si>
-    <t>58-184378700</t>
-  </si>
-  <si>
-    <t>SEKISUI JUSHI BV</t>
-  </si>
-  <si>
-    <t>4539336</t>
-  </si>
-  <si>
-    <t>EF4-0232133-7</t>
-  </si>
-  <si>
-    <t>Air, Non-container</t>
-  </si>
-  <si>
-    <t>9903.82.10,8431.39.0010</t>
-  </si>
-  <si>
-    <t>EISENMANN OF SOUTH CAROLINA INC</t>
-  </si>
-  <si>
-    <t>EISINC03</t>
-  </si>
-  <si>
-    <t>86-240963300</t>
-  </si>
-  <si>
-    <t>EISENMANN GMBH</t>
-  </si>
-  <si>
-    <t>003</t>
-  </si>
-  <si>
-    <t>004</t>
-  </si>
-  <si>
-    <t>005</t>
-  </si>
-  <si>
-    <t>9903.82.09,8544.42.9090</t>
-  </si>
-  <si>
-    <t>006</t>
+    <t>2565716</t>
+  </si>
+  <si>
+    <t>EF4-0231748-3</t>
+  </si>
+  <si>
+    <t>V1P06243667</t>
+  </si>
+  <si>
+    <t>2565746</t>
+  </si>
+  <si>
+    <t>EF4-0231755-8</t>
+  </si>
+  <si>
+    <t>1108.13.0010</t>
+  </si>
+  <si>
+    <t>PRZEDSIEBIORSTWO PRZEMYSLU ZIEMNIAC</t>
+  </si>
+  <si>
+    <t>PRZEDSIEBIORSTWO PRZEMYSLU ZIEMNIACZANEGO PEPEES S.A.</t>
+  </si>
+  <si>
+    <t>2565741</t>
+  </si>
+  <si>
+    <t>EF4-0231763-2</t>
+  </si>
+  <si>
+    <t>V1626447307</t>
+  </si>
+  <si>
+    <t>9903.82.02,7216.33.0090</t>
+  </si>
+  <si>
+    <t>MAHA USA LLC</t>
+  </si>
+  <si>
+    <t>MAHUSA</t>
+  </si>
+  <si>
+    <t>52-213556300</t>
+  </si>
+  <si>
+    <t>THYSSENKRUPP SCHULTE GMBH</t>
+  </si>
+  <si>
+    <t>9903.82.02,7228.50.5040</t>
+  </si>
+  <si>
+    <t>2565715</t>
+  </si>
+  <si>
+    <t>EF4-0232019-8</t>
+  </si>
+  <si>
+    <t>2566017</t>
+  </si>
+  <si>
+    <t>EF4-0232020-6</t>
+  </si>
+  <si>
+    <t>1109.00.9020</t>
+  </si>
+  <si>
+    <t>JACKERING MUHLEN UND NAHRMITTELWERK</t>
+  </si>
+  <si>
+    <t>JACKERING MUHLEN UND NAHRMITTELWERKE GMBH</t>
+  </si>
+  <si>
+    <t>2566025</t>
+  </si>
+  <si>
+    <t>EF4-0232024-8</t>
+  </si>
+  <si>
+    <t>2566087</t>
+  </si>
+  <si>
+    <t>EF4-0232093-3</t>
+  </si>
+  <si>
+    <t>3911.90.2500</t>
+  </si>
+  <si>
+    <t>MANKIEWICZ COATINGS, LLC</t>
+  </si>
+  <si>
+    <t>MANCOAT</t>
+  </si>
+  <si>
+    <t>56-202308900</t>
+  </si>
+  <si>
+    <t>FINALIN GMBH</t>
+  </si>
+  <si>
+    <t>3214.10.0090</t>
+  </si>
+  <si>
+    <t>3208.90.0000</t>
   </si>
   <si>
     <t>007</t>
   </si>
   <si>
-    <t>9903.82.09,8431.20.0000</t>
+    <t>3208.20.0000</t>
   </si>
   <si>
     <t>008</t>
   </si>
   <si>
-    <t>8481.80.9050</t>
-  </si>
-  <si>
     <t>009</t>
   </si>
   <si>
+    <t>3815.90.1000</t>
+  </si>
+  <si>
     <t>010</t>
   </si>
   <si>
@@ -261,112 +423,301 @@
     <t>013</t>
   </si>
   <si>
-    <t>8531.80.9005</t>
-  </si>
-  <si>
     <t>014</t>
   </si>
   <si>
-    <t>8421.99.0180</t>
+    <t>3208.10.0000</t>
   </si>
   <si>
     <t>015</t>
   </si>
   <si>
-    <t>9903.82.02,7320.20.5060</t>
-  </si>
-  <si>
     <t>016</t>
   </si>
   <si>
-    <t>9903.82.09,8483.30.8040</t>
-  </si>
-  <si>
     <t>017</t>
   </si>
   <si>
-    <t>9903.82.02,7415.21.0000</t>
-  </si>
-  <si>
     <t>018</t>
   </si>
   <si>
     <t>019</t>
   </si>
   <si>
-    <t>8484.20.0000</t>
-  </si>
-  <si>
     <t>020</t>
   </si>
   <si>
-    <t>8416.90.0000</t>
-  </si>
-  <si>
     <t>021</t>
   </si>
   <si>
+    <t>3209.10.0000</t>
+  </si>
+  <si>
     <t>022</t>
   </si>
   <si>
-    <t>9903.74.11,9903.94.06,8501.52.4000</t>
-  </si>
-  <si>
-    <t>2565859</t>
-  </si>
-  <si>
-    <t>EF4-0232157-6</t>
-  </si>
-  <si>
-    <t>9403.99.9045</t>
-  </si>
-  <si>
-    <t>VISUAL CREATIONS, INC.</t>
-  </si>
-  <si>
-    <t>VISCRE</t>
-  </si>
-  <si>
-    <t>20-461602300</t>
-  </si>
-  <si>
-    <t>VIET MOI INDUSTRIAL COMPANY LIMITED</t>
-  </si>
-  <si>
-    <t>9903.76.04,9403.60.8093</t>
-  </si>
-  <si>
-    <t>3926.90.9989</t>
-  </si>
-  <si>
-    <t>9403.20.0075</t>
-  </si>
-  <si>
-    <t>4539378</t>
-  </si>
-  <si>
-    <t>EF4-0232172-5</t>
-  </si>
-  <si>
-    <t>9903.82.09,8302.42.3065</t>
-  </si>
-  <si>
-    <t>VIELER INTERNATIONAL LP</t>
-  </si>
-  <si>
-    <t>VIEINT</t>
-  </si>
-  <si>
-    <t>58-255440400</t>
-  </si>
-  <si>
-    <t>VIELER INTERNATIONAL GMBH + CO. KG</t>
-  </si>
-  <si>
-    <t>9903.82.02,7318.15.6010</t>
-  </si>
-  <si>
-    <t>9903.82.09,8302.10.6060</t>
+    <t>023</t>
+  </si>
+  <si>
+    <t>2511.10.1000</t>
+  </si>
+  <si>
+    <t>024</t>
+  </si>
+  <si>
+    <t>025</t>
+  </si>
+  <si>
+    <t>2814.20.0000</t>
+  </si>
+  <si>
+    <t>2566088</t>
+  </si>
+  <si>
+    <t>EF4-0232097-4</t>
+  </si>
+  <si>
+    <t>RUDT INDUSTRIELACKE GMBH</t>
+  </si>
+  <si>
+    <t>026</t>
+  </si>
+  <si>
+    <t>027</t>
+  </si>
+  <si>
+    <t>028</t>
+  </si>
+  <si>
+    <t>029</t>
+  </si>
+  <si>
+    <t>3209.90.0000</t>
+  </si>
+  <si>
+    <t>030</t>
+  </si>
+  <si>
+    <t>3814.00.1000</t>
+  </si>
+  <si>
+    <t>031</t>
+  </si>
+  <si>
+    <t>032</t>
+  </si>
+  <si>
+    <t>033</t>
+  </si>
+  <si>
+    <t>034</t>
+  </si>
+  <si>
+    <t>035</t>
+  </si>
+  <si>
+    <t>036</t>
+  </si>
+  <si>
+    <t>037</t>
+  </si>
+  <si>
+    <t>038</t>
+  </si>
+  <si>
+    <t>039</t>
+  </si>
+  <si>
+    <t>040</t>
+  </si>
+  <si>
+    <t>041</t>
+  </si>
+  <si>
+    <t>042</t>
+  </si>
+  <si>
+    <t>043</t>
+  </si>
+  <si>
+    <t>044</t>
+  </si>
+  <si>
+    <t>045</t>
+  </si>
+  <si>
+    <t>046</t>
+  </si>
+  <si>
+    <t>047</t>
+  </si>
+  <si>
+    <t>048</t>
+  </si>
+  <si>
+    <t>049</t>
+  </si>
+  <si>
+    <t>050</t>
+  </si>
+  <si>
+    <t>051</t>
+  </si>
+  <si>
+    <t>052</t>
+  </si>
+  <si>
+    <t>053</t>
+  </si>
+  <si>
+    <t>054</t>
+  </si>
+  <si>
+    <t>055</t>
+  </si>
+  <si>
+    <t>056</t>
+  </si>
+  <si>
+    <t>057</t>
+  </si>
+  <si>
+    <t>058</t>
+  </si>
+  <si>
+    <t>059</t>
+  </si>
+  <si>
+    <t>060</t>
+  </si>
+  <si>
+    <t>061</t>
+  </si>
+  <si>
+    <t>3402.50.5100</t>
+  </si>
+  <si>
+    <t>062</t>
+  </si>
+  <si>
+    <t>063</t>
+  </si>
+  <si>
+    <t>064</t>
+  </si>
+  <si>
+    <t>065</t>
+  </si>
+  <si>
+    <t>066</t>
+  </si>
+  <si>
+    <t>067</t>
+  </si>
+  <si>
+    <t>068</t>
+  </si>
+  <si>
+    <t>069</t>
+  </si>
+  <si>
+    <t>070</t>
+  </si>
+  <si>
+    <t>071</t>
+  </si>
+  <si>
+    <t>072</t>
+  </si>
+  <si>
+    <t>073</t>
+  </si>
+  <si>
+    <t>074</t>
+  </si>
+  <si>
+    <t>075</t>
+  </si>
+  <si>
+    <t>076</t>
+  </si>
+  <si>
+    <t>077</t>
+  </si>
+  <si>
+    <t>078</t>
+  </si>
+  <si>
+    <t>079</t>
+  </si>
+  <si>
+    <t>080</t>
+  </si>
+  <si>
+    <t>081</t>
+  </si>
+  <si>
+    <t>082</t>
+  </si>
+  <si>
+    <t>083</t>
+  </si>
+  <si>
+    <t>NORIX LACKFABRIK GMBH</t>
+  </si>
+  <si>
+    <t>084</t>
+  </si>
+  <si>
+    <t>085</t>
+  </si>
+  <si>
+    <t>086</t>
+  </si>
+  <si>
+    <t>087</t>
+  </si>
+  <si>
+    <t>088</t>
+  </si>
+  <si>
+    <t>089</t>
+  </si>
+  <si>
+    <t>090</t>
+  </si>
+  <si>
+    <t>091</t>
+  </si>
+  <si>
+    <t>092</t>
+  </si>
+  <si>
+    <t>093</t>
+  </si>
+  <si>
+    <t>094</t>
+  </si>
+  <si>
+    <t>095</t>
+  </si>
+  <si>
+    <t>096</t>
+  </si>
+  <si>
+    <t>097</t>
+  </si>
+  <si>
+    <t>098</t>
+  </si>
+  <si>
+    <t>099</t>
+  </si>
+  <si>
+    <t>100</t>
+  </si>
+  <si>
+    <t>3824.99.9397</t>
   </si>
 </sst>
 </file>
@@ -1311,7 +1662,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:Q45"/>
+  <dimension ref="A1:Q148"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="23.7109375" customWidth="true"/>
@@ -1424,1305 +1775,1305 @@
         <v>27</v>
       </c>
       <c r="M2" s="45">
-        <v>46176</v>
+        <v>46175</v>
       </c>
       <c r="N2" s="46">
-        <v>46174</v>
+        <v>46175</v>
       </c>
       <c r="O2" s="47" t="s">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="P2" s="48" t="s">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="Q2" s="49">
-        <v>46124</v>
+        <v>46119</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="33" t="s">
+        <v>28</v>
+      </c>
+      <c r="B3" s="34" t="s">
         <v>29</v>
       </c>
-      <c r="B3" s="34" t="s">
+      <c r="C3" s="35" t="s">
         <v>30</v>
       </c>
-      <c r="C3" s="35" t="s">
-        <v>19</v>
-      </c>
       <c r="D3" s="36" t="s">
-        <v>20</v>
+        <v>31</v>
       </c>
       <c r="E3" s="37" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="F3" s="38" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="G3" s="39" t="s">
         <v>23</v>
       </c>
       <c r="H3" s="40" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="I3" s="41" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="J3" s="42" t="s">
-        <v>25</v>
+        <v>34</v>
       </c>
       <c r="K3" s="43" t="s">
-        <v>26</v>
+        <v>35</v>
       </c>
       <c r="L3" s="44" t="s">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="M3" s="45">
-        <v>46176</v>
+        <v>46174</v>
       </c>
       <c r="N3" s="46">
-        <v>46174</v>
+        <v>46175</v>
       </c>
       <c r="O3" s="47" t="s">
-        <v>28</v>
+        <v>36</v>
       </c>
       <c r="P3" s="48" t="s">
-        <v>28</v>
+        <v>36</v>
       </c>
       <c r="Q3" s="49">
-        <v>46124</v>
+        <v>46141</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="33" t="s">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="B4" s="34" t="s">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="C4" s="35" t="s">
-        <v>19</v>
+        <v>30</v>
       </c>
       <c r="D4" s="36" t="s">
-        <v>20</v>
+        <v>31</v>
       </c>
       <c r="E4" s="37" t="s">
-        <v>21</v>
+        <v>39</v>
       </c>
       <c r="F4" s="38" t="s">
-        <v>22</v>
+        <v>40</v>
       </c>
       <c r="G4" s="39" t="s">
         <v>23</v>
       </c>
       <c r="H4" s="40" t="s">
-        <v>21</v>
+        <v>39</v>
       </c>
       <c r="I4" s="41" t="s">
-        <v>36</v>
+        <v>41</v>
       </c>
       <c r="J4" s="42" t="s">
-        <v>37</v>
+        <v>42</v>
       </c>
       <c r="K4" s="43" t="s">
-        <v>38</v>
+        <v>43</v>
       </c>
       <c r="L4" s="44" t="s">
-        <v>39</v>
+        <v>44</v>
       </c>
       <c r="M4" s="45">
-        <v>46170</v>
+        <v>46176</v>
       </c>
       <c r="N4" s="46">
-        <v>46174</v>
+        <v>46175</v>
       </c>
       <c r="O4" s="47" t="s">
-        <v>40</v>
+        <v>45</v>
       </c>
       <c r="P4" s="48" t="s">
-        <v>40</v>
+        <v>45</v>
       </c>
       <c r="Q4" s="49">
-        <v>46147</v>
+        <v>46155</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="33" t="s">
-        <v>34</v>
+        <v>46</v>
       </c>
       <c r="B5" s="34" t="s">
-        <v>35</v>
+        <v>47</v>
       </c>
       <c r="C5" s="35" t="s">
-        <v>19</v>
+        <v>30</v>
       </c>
       <c r="D5" s="36" t="s">
-        <v>20</v>
+        <v>31</v>
       </c>
       <c r="E5" s="37" t="s">
-        <v>21</v>
+        <v>39</v>
       </c>
       <c r="F5" s="38" t="s">
-        <v>22</v>
+        <v>40</v>
       </c>
       <c r="G5" s="39" t="s">
+        <v>23</v>
+      </c>
+      <c r="H5" s="40" t="s">
+        <v>39</v>
+      </c>
+      <c r="I5" s="41" t="s">
         <v>41</v>
       </c>
-      <c r="H5" s="40" t="s">
-        <v>21</v>
-      </c>
-      <c r="I5" s="41" t="s">
+      <c r="J5" s="42" t="s">
         <v>42</v>
       </c>
-      <c r="J5" s="42" t="s">
-        <v>37</v>
-      </c>
       <c r="K5" s="43" t="s">
-        <v>38</v>
+        <v>43</v>
       </c>
       <c r="L5" s="44" t="s">
-        <v>39</v>
+        <v>44</v>
       </c>
       <c r="M5" s="45">
-        <v>46170</v>
+        <v>46176</v>
       </c>
       <c r="N5" s="46">
-        <v>46174</v>
+        <v>46175</v>
       </c>
       <c r="O5" s="47" t="s">
-        <v>40</v>
+        <v>45</v>
       </c>
       <c r="P5" s="48" t="s">
-        <v>40</v>
+        <v>45</v>
       </c>
       <c r="Q5" s="49">
-        <v>46147</v>
+        <v>46155</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="33" t="s">
-        <v>43</v>
+        <v>48</v>
       </c>
       <c r="B6" s="34" t="s">
-        <v>44</v>
+        <v>49</v>
       </c>
       <c r="C6" s="35" t="s">
-        <v>19</v>
+        <v>30</v>
       </c>
       <c r="D6" s="36" t="s">
-        <v>45</v>
+        <v>31</v>
       </c>
       <c r="E6" s="37" t="s">
-        <v>46</v>
+        <v>39</v>
       </c>
       <c r="F6" s="38" t="s">
-        <v>47</v>
+        <v>40</v>
       </c>
       <c r="G6" s="39" t="s">
         <v>23</v>
       </c>
       <c r="H6" s="40" t="s">
-        <v>46</v>
+        <v>39</v>
       </c>
       <c r="I6" s="41" t="s">
-        <v>48</v>
+        <v>41</v>
       </c>
       <c r="J6" s="42" t="s">
-        <v>49</v>
+        <v>42</v>
       </c>
       <c r="K6" s="43" t="s">
-        <v>50</v>
+        <v>43</v>
       </c>
       <c r="L6" s="44" t="s">
-        <v>51</v>
+        <v>44</v>
       </c>
       <c r="M6" s="45">
-        <v>46174</v>
+        <v>46176</v>
       </c>
       <c r="N6" s="46">
-        <v>46174</v>
+        <v>46175</v>
       </c>
       <c r="O6" s="47" t="s">
-        <v>52</v>
+        <v>45</v>
       </c>
       <c r="P6" s="48" t="s">
-        <v>52</v>
+        <v>45</v>
       </c>
       <c r="Q6" s="49">
-        <v>46132</v>
+        <v>46155</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="33" t="s">
+        <v>50</v>
+      </c>
+      <c r="B7" s="34" t="s">
+        <v>51</v>
+      </c>
+      <c r="C7" s="35" t="s">
+        <v>19</v>
+      </c>
+      <c r="D7" s="36" t="s">
+        <v>31</v>
+      </c>
+      <c r="E7" s="37" t="s">
+        <v>52</v>
+      </c>
+      <c r="F7" s="38" t="s">
         <v>53</v>
-      </c>
-      <c r="B7" s="34" t="s">
-        <v>54</v>
-      </c>
-      <c r="C7" s="35" t="s">
-        <v>19</v>
-      </c>
-      <c r="D7" s="36" t="s">
-        <v>45</v>
-      </c>
-      <c r="E7" s="37" t="s">
-        <v>21</v>
-      </c>
-      <c r="F7" s="38" t="s">
-        <v>22</v>
       </c>
       <c r="G7" s="39" t="s">
         <v>23</v>
       </c>
       <c r="H7" s="40" t="s">
-        <v>21</v>
+        <v>52</v>
       </c>
       <c r="I7" s="41" t="s">
+        <v>54</v>
+      </c>
+      <c r="J7" s="42" t="s">
         <v>55</v>
       </c>
-      <c r="J7" s="42" t="s">
+      <c r="K7" s="43" t="s">
         <v>56</v>
       </c>
-      <c r="K7" s="43" t="s">
+      <c r="L7" s="44" t="s">
         <v>57</v>
       </c>
-      <c r="L7" s="44" t="s">
+      <c r="M7" s="45">
+        <v>46175</v>
+      </c>
+      <c r="N7" s="46">
+        <v>46175</v>
+      </c>
+      <c r="O7" s="47" t="s">
         <v>58</v>
       </c>
-      <c r="M7" s="45">
-        <v>46175</v>
-      </c>
-      <c r="N7" s="46">
-        <v>46174</v>
-      </c>
-      <c r="O7" s="47" t="s">
-        <v>59</v>
-      </c>
       <c r="P7" s="48" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="Q7" s="49">
-        <v>46152</v>
+        <v>46147</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="33" t="s">
+        <v>50</v>
+      </c>
+      <c r="B8" s="34" t="s">
+        <v>51</v>
+      </c>
+      <c r="C8" s="35" t="s">
+        <v>19</v>
+      </c>
+      <c r="D8" s="36" t="s">
+        <v>31</v>
+      </c>
+      <c r="E8" s="37" t="s">
+        <v>59</v>
+      </c>
+      <c r="F8" s="38" t="s">
         <v>60</v>
       </c>
-      <c r="B8" s="34" t="s">
+      <c r="G8" s="39" t="s">
         <v>61</v>
       </c>
-      <c r="C8" s="35" t="s">
+      <c r="H8" s="40" t="s">
+        <v>59</v>
+      </c>
+      <c r="I8" s="41" t="s">
         <v>62</v>
       </c>
-      <c r="D8" s="36" t="s">
-        <v>20</v>
-      </c>
-      <c r="E8" s="37" t="s">
-        <v>46</v>
-      </c>
-      <c r="F8" s="38" t="s">
-        <v>47</v>
-      </c>
-      <c r="G8" s="39" t="s">
-        <v>23</v>
-      </c>
-      <c r="H8" s="40" t="s">
-        <v>46</v>
-      </c>
-      <c r="I8" s="41" t="s">
-        <v>63</v>
-      </c>
       <c r="J8" s="42" t="s">
-        <v>64</v>
+        <v>55</v>
       </c>
       <c r="K8" s="43" t="s">
-        <v>65</v>
+        <v>56</v>
       </c>
       <c r="L8" s="44" t="s">
-        <v>66</v>
+        <v>57</v>
       </c>
       <c r="M8" s="45">
-        <v>46173</v>
+        <v>46175</v>
       </c>
       <c r="N8" s="46">
-        <v>46174</v>
+        <v>46175</v>
       </c>
       <c r="O8" s="47" t="s">
-        <v>67</v>
+        <v>58</v>
       </c>
       <c r="P8" s="48" t="s">
-        <v>67</v>
+        <v>58</v>
       </c>
       <c r="Q8" s="49">
-        <v>46173</v>
+        <v>46147</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="33" t="s">
+        <v>50</v>
+      </c>
+      <c r="B9" s="34" t="s">
+        <v>51</v>
+      </c>
+      <c r="C9" s="35" t="s">
+        <v>19</v>
+      </c>
+      <c r="D9" s="36" t="s">
+        <v>31</v>
+      </c>
+      <c r="E9" s="37" t="s">
+        <v>59</v>
+      </c>
+      <c r="F9" s="38" t="s">
         <v>60</v>
       </c>
-      <c r="B9" s="34" t="s">
-        <v>61</v>
-      </c>
-      <c r="C9" s="35" t="s">
-        <v>62</v>
-      </c>
-      <c r="D9" s="36" t="s">
-        <v>20</v>
-      </c>
-      <c r="E9" s="37" t="s">
-        <v>46</v>
-      </c>
-      <c r="F9" s="38" t="s">
-        <v>47</v>
-      </c>
       <c r="G9" s="39" t="s">
-        <v>41</v>
+        <v>63</v>
       </c>
       <c r="H9" s="40" t="s">
-        <v>46</v>
+        <v>59</v>
       </c>
       <c r="I9" s="41" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="J9" s="42" t="s">
-        <v>64</v>
+        <v>55</v>
       </c>
       <c r="K9" s="43" t="s">
-        <v>65</v>
+        <v>56</v>
       </c>
       <c r="L9" s="44" t="s">
-        <v>66</v>
+        <v>57</v>
       </c>
       <c r="M9" s="45">
-        <v>46173</v>
+        <v>46175</v>
       </c>
       <c r="N9" s="46">
-        <v>46174</v>
+        <v>46175</v>
       </c>
       <c r="O9" s="47" t="s">
-        <v>67</v>
+        <v>58</v>
       </c>
       <c r="P9" s="48" t="s">
-        <v>67</v>
+        <v>58</v>
       </c>
       <c r="Q9" s="49">
-        <v>46173</v>
+        <v>46147</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="33" t="s">
-        <v>60</v>
+        <v>50</v>
       </c>
       <c r="B10" s="34" t="s">
-        <v>61</v>
+        <v>51</v>
       </c>
       <c r="C10" s="35" t="s">
-        <v>62</v>
+        <v>19</v>
       </c>
       <c r="D10" s="36" t="s">
-        <v>20</v>
+        <v>31</v>
       </c>
       <c r="E10" s="37" t="s">
-        <v>46</v>
+        <v>52</v>
       </c>
       <c r="F10" s="38" t="s">
-        <v>47</v>
+        <v>53</v>
       </c>
       <c r="G10" s="39" t="s">
-        <v>68</v>
+        <v>65</v>
       </c>
       <c r="H10" s="40" t="s">
-        <v>46</v>
+        <v>52</v>
       </c>
       <c r="I10" s="41" t="s">
-        <v>63</v>
+        <v>66</v>
       </c>
       <c r="J10" s="42" t="s">
-        <v>64</v>
+        <v>55</v>
       </c>
       <c r="K10" s="43" t="s">
-        <v>65</v>
+        <v>56</v>
       </c>
       <c r="L10" s="44" t="s">
-        <v>66</v>
+        <v>57</v>
       </c>
       <c r="M10" s="45">
-        <v>46173</v>
+        <v>46175</v>
       </c>
       <c r="N10" s="46">
-        <v>46174</v>
+        <v>46175</v>
       </c>
       <c r="O10" s="47" t="s">
-        <v>67</v>
+        <v>58</v>
       </c>
       <c r="P10" s="48" t="s">
-        <v>67</v>
+        <v>58</v>
       </c>
       <c r="Q10" s="49">
-        <v>46173</v>
+        <v>46147</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="33" t="s">
+        <v>50</v>
+      </c>
+      <c r="B11" s="34" t="s">
+        <v>51</v>
+      </c>
+      <c r="C11" s="35" t="s">
+        <v>19</v>
+      </c>
+      <c r="D11" s="36" t="s">
+        <v>31</v>
+      </c>
+      <c r="E11" s="37" t="s">
+        <v>59</v>
+      </c>
+      <c r="F11" s="38" t="s">
         <v>60</v>
       </c>
-      <c r="B11" s="34" t="s">
-        <v>61</v>
-      </c>
-      <c r="C11" s="35" t="s">
-        <v>62</v>
-      </c>
-      <c r="D11" s="36" t="s">
-        <v>20</v>
-      </c>
-      <c r="E11" s="37" t="s">
-        <v>46</v>
-      </c>
-      <c r="F11" s="38" t="s">
-        <v>47</v>
-      </c>
       <c r="G11" s="39" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="H11" s="40" t="s">
-        <v>46</v>
+        <v>59</v>
       </c>
       <c r="I11" s="41" t="s">
-        <v>63</v>
+        <v>68</v>
       </c>
       <c r="J11" s="42" t="s">
-        <v>64</v>
+        <v>55</v>
       </c>
       <c r="K11" s="43" t="s">
-        <v>65</v>
+        <v>56</v>
       </c>
       <c r="L11" s="44" t="s">
-        <v>66</v>
+        <v>57</v>
       </c>
       <c r="M11" s="45">
-        <v>46173</v>
+        <v>46175</v>
       </c>
       <c r="N11" s="46">
-        <v>46174</v>
+        <v>46175</v>
       </c>
       <c r="O11" s="47" t="s">
-        <v>67</v>
+        <v>58</v>
       </c>
       <c r="P11" s="48" t="s">
-        <v>67</v>
+        <v>58</v>
       </c>
       <c r="Q11" s="49">
-        <v>46173</v>
+        <v>46147</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="33" t="s">
+        <v>50</v>
+      </c>
+      <c r="B12" s="34" t="s">
+        <v>51</v>
+      </c>
+      <c r="C12" s="35" t="s">
+        <v>19</v>
+      </c>
+      <c r="D12" s="36" t="s">
+        <v>31</v>
+      </c>
+      <c r="E12" s="37" t="s">
+        <v>59</v>
+      </c>
+      <c r="F12" s="38" t="s">
         <v>60</v>
       </c>
-      <c r="B12" s="34" t="s">
-        <v>61</v>
-      </c>
-      <c r="C12" s="35" t="s">
-        <v>62</v>
-      </c>
-      <c r="D12" s="36" t="s">
-        <v>20</v>
-      </c>
-      <c r="E12" s="37" t="s">
-        <v>46</v>
-      </c>
-      <c r="F12" s="38" t="s">
-        <v>47</v>
-      </c>
       <c r="G12" s="39" t="s">
+        <v>69</v>
+      </c>
+      <c r="H12" s="40" t="s">
+        <v>59</v>
+      </c>
+      <c r="I12" s="41" t="s">
         <v>70</v>
       </c>
-      <c r="H12" s="40" t="s">
-        <v>46</v>
-      </c>
-      <c r="I12" s="41" t="s">
-        <v>71</v>
-      </c>
       <c r="J12" s="42" t="s">
-        <v>64</v>
+        <v>55</v>
       </c>
       <c r="K12" s="43" t="s">
-        <v>65</v>
+        <v>56</v>
       </c>
       <c r="L12" s="44" t="s">
-        <v>66</v>
+        <v>57</v>
       </c>
       <c r="M12" s="45">
-        <v>46173</v>
+        <v>46175</v>
       </c>
       <c r="N12" s="46">
-        <v>46174</v>
+        <v>46175</v>
       </c>
       <c r="O12" s="47" t="s">
-        <v>67</v>
+        <v>58</v>
       </c>
       <c r="P12" s="48" t="s">
-        <v>67</v>
+        <v>58</v>
       </c>
       <c r="Q12" s="49">
-        <v>46173</v>
+        <v>46147</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="33" t="s">
-        <v>60</v>
+        <v>71</v>
       </c>
       <c r="B13" s="34" t="s">
-        <v>61</v>
+        <v>72</v>
       </c>
       <c r="C13" s="35" t="s">
-        <v>62</v>
+        <v>19</v>
       </c>
       <c r="D13" s="36" t="s">
-        <v>20</v>
+        <v>31</v>
       </c>
       <c r="E13" s="37" t="s">
-        <v>46</v>
+        <v>39</v>
       </c>
       <c r="F13" s="38" t="s">
-        <v>47</v>
+        <v>40</v>
       </c>
       <c r="G13" s="39" t="s">
-        <v>72</v>
+        <v>23</v>
       </c>
       <c r="H13" s="40" t="s">
-        <v>46</v>
+        <v>39</v>
       </c>
       <c r="I13" s="41" t="s">
-        <v>63</v>
+        <v>73</v>
       </c>
       <c r="J13" s="42" t="s">
-        <v>64</v>
+        <v>74</v>
       </c>
       <c r="K13" s="43" t="s">
-        <v>65</v>
+        <v>75</v>
       </c>
       <c r="L13" s="44" t="s">
-        <v>66</v>
+        <v>76</v>
       </c>
       <c r="M13" s="45">
-        <v>46173</v>
+        <v>46175</v>
       </c>
       <c r="N13" s="46">
-        <v>46174</v>
+        <v>46175</v>
       </c>
       <c r="O13" s="47" t="s">
-        <v>67</v>
+        <v>77</v>
       </c>
       <c r="P13" s="48" t="s">
-        <v>67</v>
+        <v>77</v>
       </c>
       <c r="Q13" s="49">
-        <v>46173</v>
+        <v>46138</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="33" t="s">
-        <v>60</v>
+        <v>78</v>
       </c>
       <c r="B14" s="34" t="s">
-        <v>61</v>
+        <v>79</v>
       </c>
       <c r="C14" s="35" t="s">
-        <v>62</v>
+        <v>19</v>
       </c>
       <c r="D14" s="36" t="s">
-        <v>20</v>
+        <v>80</v>
       </c>
       <c r="E14" s="37" t="s">
-        <v>46</v>
+        <v>21</v>
       </c>
       <c r="F14" s="38" t="s">
-        <v>47</v>
+        <v>22</v>
       </c>
       <c r="G14" s="39" t="s">
-        <v>73</v>
+        <v>23</v>
       </c>
       <c r="H14" s="40" t="s">
-        <v>46</v>
+        <v>21</v>
       </c>
       <c r="I14" s="41" t="s">
-        <v>74</v>
+        <v>81</v>
       </c>
       <c r="J14" s="42" t="s">
-        <v>64</v>
+        <v>82</v>
       </c>
       <c r="K14" s="43" t="s">
-        <v>65</v>
+        <v>83</v>
       </c>
       <c r="L14" s="44" t="s">
-        <v>66</v>
+        <v>84</v>
       </c>
       <c r="M14" s="45">
-        <v>46173</v>
+        <v>46178</v>
       </c>
       <c r="N14" s="46">
-        <v>46174</v>
+        <v>46175</v>
       </c>
       <c r="O14" s="47" t="s">
-        <v>67</v>
+        <v>85</v>
       </c>
       <c r="P14" s="48" t="s">
-        <v>67</v>
+        <v>85</v>
       </c>
       <c r="Q14" s="49">
-        <v>46173</v>
+        <v>46152</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="33" t="s">
-        <v>60</v>
+        <v>86</v>
       </c>
       <c r="B15" s="34" t="s">
-        <v>61</v>
+        <v>87</v>
       </c>
       <c r="C15" s="35" t="s">
-        <v>62</v>
+        <v>19</v>
       </c>
       <c r="D15" s="36" t="s">
-        <v>20</v>
+        <v>80</v>
       </c>
       <c r="E15" s="37" t="s">
-        <v>21</v>
+        <v>88</v>
       </c>
       <c r="F15" s="38" t="s">
-        <v>22</v>
+        <v>89</v>
       </c>
       <c r="G15" s="39" t="s">
-        <v>75</v>
+        <v>23</v>
       </c>
       <c r="H15" s="40" t="s">
-        <v>21</v>
+        <v>88</v>
       </c>
       <c r="I15" s="41" t="s">
-        <v>76</v>
+        <v>90</v>
       </c>
       <c r="J15" s="42" t="s">
-        <v>64</v>
+        <v>82</v>
       </c>
       <c r="K15" s="43" t="s">
-        <v>65</v>
+        <v>83</v>
       </c>
       <c r="L15" s="44" t="s">
-        <v>66</v>
+        <v>84</v>
       </c>
       <c r="M15" s="45">
-        <v>46173</v>
+        <v>46177</v>
       </c>
       <c r="N15" s="46">
-        <v>46174</v>
+        <v>46175</v>
       </c>
       <c r="O15" s="47" t="s">
-        <v>67</v>
+        <v>91</v>
       </c>
       <c r="P15" s="48" t="s">
-        <v>67</v>
+        <v>91</v>
       </c>
       <c r="Q15" s="49">
-        <v>46173</v>
+        <v>46145</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="33" t="s">
-        <v>60</v>
+        <v>92</v>
       </c>
       <c r="B16" s="34" t="s">
-        <v>61</v>
+        <v>93</v>
       </c>
       <c r="C16" s="35" t="s">
-        <v>62</v>
+        <v>19</v>
       </c>
       <c r="D16" s="36" t="s">
-        <v>20</v>
+        <v>94</v>
       </c>
       <c r="E16" s="37" t="s">
-        <v>46</v>
+        <v>88</v>
       </c>
       <c r="F16" s="38" t="s">
-        <v>47</v>
+        <v>89</v>
       </c>
       <c r="G16" s="39" t="s">
-        <v>77</v>
+        <v>23</v>
       </c>
       <c r="H16" s="40" t="s">
-        <v>46</v>
+        <v>88</v>
       </c>
       <c r="I16" s="41" t="s">
-        <v>63</v>
+        <v>90</v>
       </c>
       <c r="J16" s="42" t="s">
-        <v>64</v>
+        <v>82</v>
       </c>
       <c r="K16" s="43" t="s">
-        <v>65</v>
+        <v>83</v>
       </c>
       <c r="L16" s="44" t="s">
-        <v>66</v>
+        <v>84</v>
       </c>
       <c r="M16" s="45">
-        <v>46173</v>
+        <v>46177</v>
       </c>
       <c r="N16" s="46">
-        <v>46174</v>
+        <v>46175</v>
       </c>
       <c r="O16" s="47" t="s">
-        <v>67</v>
+        <v>91</v>
       </c>
       <c r="P16" s="48" t="s">
-        <v>67</v>
+        <v>91</v>
       </c>
       <c r="Q16" s="49">
-        <v>46173</v>
+        <v>46145</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="33" t="s">
-        <v>60</v>
+        <v>95</v>
       </c>
       <c r="B17" s="34" t="s">
-        <v>61</v>
+        <v>96</v>
       </c>
       <c r="C17" s="35" t="s">
-        <v>62</v>
+        <v>19</v>
       </c>
       <c r="D17" s="36" t="s">
-        <v>20</v>
+        <v>94</v>
       </c>
       <c r="E17" s="37" t="s">
-        <v>46</v>
+        <v>21</v>
       </c>
       <c r="F17" s="38" t="s">
-        <v>47</v>
+        <v>31</v>
       </c>
       <c r="G17" s="39" t="s">
-        <v>78</v>
+        <v>23</v>
       </c>
       <c r="H17" s="40" t="s">
-        <v>46</v>
+        <v>21</v>
       </c>
       <c r="I17" s="41" t="s">
-        <v>63</v>
+        <v>97</v>
       </c>
       <c r="J17" s="42" t="s">
-        <v>64</v>
+        <v>82</v>
       </c>
       <c r="K17" s="43" t="s">
-        <v>65</v>
+        <v>83</v>
       </c>
       <c r="L17" s="44" t="s">
-        <v>66</v>
+        <v>84</v>
       </c>
       <c r="M17" s="45">
-        <v>46173</v>
+        <v>46169</v>
       </c>
       <c r="N17" s="46">
-        <v>46174</v>
+        <v>46175</v>
       </c>
       <c r="O17" s="47" t="s">
-        <v>67</v>
+        <v>98</v>
       </c>
       <c r="P17" s="48" t="s">
-        <v>67</v>
+        <v>99</v>
       </c>
       <c r="Q17" s="49">
-        <v>46173</v>
+        <v>46145</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="33" t="s">
-        <v>60</v>
+        <v>100</v>
       </c>
       <c r="B18" s="34" t="s">
-        <v>61</v>
+        <v>101</v>
       </c>
       <c r="C18" s="35" t="s">
-        <v>62</v>
+        <v>19</v>
       </c>
       <c r="D18" s="36" t="s">
-        <v>20</v>
+        <v>102</v>
       </c>
       <c r="E18" s="37" t="s">
-        <v>46</v>
+        <v>39</v>
       </c>
       <c r="F18" s="38" t="s">
-        <v>47</v>
+        <v>40</v>
       </c>
       <c r="G18" s="39" t="s">
-        <v>79</v>
+        <v>23</v>
       </c>
       <c r="H18" s="40" t="s">
-        <v>46</v>
+        <v>39</v>
       </c>
       <c r="I18" s="41" t="s">
-        <v>63</v>
+        <v>103</v>
       </c>
       <c r="J18" s="42" t="s">
-        <v>64</v>
+        <v>104</v>
       </c>
       <c r="K18" s="43" t="s">
-        <v>65</v>
+        <v>105</v>
       </c>
       <c r="L18" s="44" t="s">
-        <v>66</v>
+        <v>106</v>
       </c>
       <c r="M18" s="45">
-        <v>46173</v>
+        <v>46176</v>
       </c>
       <c r="N18" s="46">
-        <v>46174</v>
+        <v>46175</v>
       </c>
       <c r="O18" s="47" t="s">
-        <v>67</v>
+        <v>107</v>
       </c>
       <c r="P18" s="48" t="s">
-        <v>67</v>
+        <v>107</v>
       </c>
       <c r="Q18" s="49">
-        <v>46173</v>
+        <v>46152</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="33" t="s">
-        <v>60</v>
+        <v>100</v>
       </c>
       <c r="B19" s="34" t="s">
+        <v>101</v>
+      </c>
+      <c r="C19" s="35" t="s">
+        <v>19</v>
+      </c>
+      <c r="D19" s="36" t="s">
+        <v>102</v>
+      </c>
+      <c r="E19" s="37" t="s">
+        <v>39</v>
+      </c>
+      <c r="F19" s="38" t="s">
+        <v>40</v>
+      </c>
+      <c r="G19" s="39" t="s">
         <v>61</v>
       </c>
-      <c r="C19" s="35" t="s">
-        <v>62</v>
-      </c>
-      <c r="D19" s="36" t="s">
-        <v>20</v>
-      </c>
-      <c r="E19" s="37" t="s">
-        <v>46</v>
-      </c>
-      <c r="F19" s="38" t="s">
-        <v>47</v>
-      </c>
-      <c r="G19" s="39" t="s">
-        <v>80</v>
-      </c>
       <c r="H19" s="40" t="s">
-        <v>46</v>
+        <v>39</v>
       </c>
       <c r="I19" s="41" t="s">
-        <v>63</v>
+        <v>108</v>
       </c>
       <c r="J19" s="42" t="s">
-        <v>64</v>
+        <v>104</v>
       </c>
       <c r="K19" s="43" t="s">
-        <v>65</v>
+        <v>105</v>
       </c>
       <c r="L19" s="44" t="s">
-        <v>66</v>
+        <v>106</v>
       </c>
       <c r="M19" s="45">
-        <v>46173</v>
+        <v>46176</v>
       </c>
       <c r="N19" s="46">
-        <v>46174</v>
+        <v>46175</v>
       </c>
       <c r="O19" s="47" t="s">
-        <v>67</v>
+        <v>107</v>
       </c>
       <c r="P19" s="48" t="s">
-        <v>67</v>
+        <v>107</v>
       </c>
       <c r="Q19" s="49">
-        <v>46173</v>
+        <v>46152</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="33" t="s">
-        <v>60</v>
+        <v>100</v>
       </c>
       <c r="B20" s="34" t="s">
-        <v>61</v>
+        <v>101</v>
       </c>
       <c r="C20" s="35" t="s">
-        <v>62</v>
+        <v>19</v>
       </c>
       <c r="D20" s="36" t="s">
-        <v>20</v>
+        <v>102</v>
       </c>
       <c r="E20" s="37" t="s">
-        <v>21</v>
+        <v>39</v>
       </c>
       <c r="F20" s="38" t="s">
-        <v>22</v>
+        <v>40</v>
       </c>
       <c r="G20" s="39" t="s">
-        <v>81</v>
+        <v>63</v>
       </c>
       <c r="H20" s="40" t="s">
-        <v>21</v>
+        <v>39</v>
       </c>
       <c r="I20" s="41" t="s">
-        <v>82</v>
+        <v>108</v>
       </c>
       <c r="J20" s="42" t="s">
-        <v>64</v>
+        <v>104</v>
       </c>
       <c r="K20" s="43" t="s">
-        <v>65</v>
+        <v>105</v>
       </c>
       <c r="L20" s="44" t="s">
-        <v>66</v>
+        <v>106</v>
       </c>
       <c r="M20" s="45">
-        <v>46173</v>
+        <v>46176</v>
       </c>
       <c r="N20" s="46">
-        <v>46174</v>
+        <v>46175</v>
       </c>
       <c r="O20" s="47" t="s">
-        <v>67</v>
+        <v>107</v>
       </c>
       <c r="P20" s="48" t="s">
-        <v>67</v>
+        <v>107</v>
       </c>
       <c r="Q20" s="49">
-        <v>46173</v>
+        <v>46152</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="33" t="s">
-        <v>60</v>
+        <v>109</v>
       </c>
       <c r="B21" s="34" t="s">
-        <v>61</v>
+        <v>110</v>
       </c>
       <c r="C21" s="35" t="s">
-        <v>62</v>
+        <v>19</v>
       </c>
       <c r="D21" s="36" t="s">
-        <v>20</v>
+        <v>94</v>
       </c>
       <c r="E21" s="37" t="s">
-        <v>21</v>
+        <v>88</v>
       </c>
       <c r="F21" s="38" t="s">
-        <v>22</v>
+        <v>89</v>
       </c>
       <c r="G21" s="39" t="s">
+        <v>23</v>
+      </c>
+      <c r="H21" s="40" t="s">
+        <v>88</v>
+      </c>
+      <c r="I21" s="41" t="s">
+        <v>90</v>
+      </c>
+      <c r="J21" s="42" t="s">
+        <v>82</v>
+      </c>
+      <c r="K21" s="43" t="s">
         <v>83</v>
       </c>
-      <c r="H21" s="40" t="s">
-        <v>21</v>
-      </c>
-      <c r="I21" s="41" t="s">
+      <c r="L21" s="44" t="s">
         <v>84</v>
       </c>
-      <c r="J21" s="42" t="s">
-        <v>64</v>
-      </c>
-      <c r="K21" s="43" t="s">
-        <v>65</v>
-      </c>
-      <c r="L21" s="44" t="s">
-        <v>66</v>
-      </c>
       <c r="M21" s="45">
-        <v>46173</v>
+        <v>46177</v>
       </c>
       <c r="N21" s="46">
-        <v>46174</v>
+        <v>46175</v>
       </c>
       <c r="O21" s="47" t="s">
-        <v>67</v>
+        <v>91</v>
       </c>
       <c r="P21" s="48" t="s">
-        <v>67</v>
+        <v>91</v>
       </c>
       <c r="Q21" s="49">
-        <v>46173</v>
+        <v>46145</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="33" t="s">
-        <v>60</v>
+        <v>111</v>
       </c>
       <c r="B22" s="34" t="s">
-        <v>61</v>
+        <v>112</v>
       </c>
       <c r="C22" s="35" t="s">
-        <v>62</v>
+        <v>19</v>
       </c>
       <c r="D22" s="36" t="s">
-        <v>20</v>
+        <v>94</v>
       </c>
       <c r="E22" s="37" t="s">
-        <v>46</v>
+        <v>21</v>
       </c>
       <c r="F22" s="38" t="s">
-        <v>47</v>
+        <v>22</v>
       </c>
       <c r="G22" s="39" t="s">
-        <v>85</v>
+        <v>23</v>
       </c>
       <c r="H22" s="40" t="s">
-        <v>46</v>
+        <v>21</v>
       </c>
       <c r="I22" s="41" t="s">
-        <v>86</v>
+        <v>113</v>
       </c>
       <c r="J22" s="42" t="s">
-        <v>64</v>
+        <v>82</v>
       </c>
       <c r="K22" s="43" t="s">
-        <v>65</v>
+        <v>83</v>
       </c>
       <c r="L22" s="44" t="s">
-        <v>66</v>
+        <v>84</v>
       </c>
       <c r="M22" s="45">
-        <v>46173</v>
+        <v>46175</v>
       </c>
       <c r="N22" s="46">
-        <v>46174</v>
+        <v>46175</v>
       </c>
       <c r="O22" s="47" t="s">
-        <v>67</v>
+        <v>114</v>
       </c>
       <c r="P22" s="48" t="s">
-        <v>67</v>
+        <v>115</v>
       </c>
       <c r="Q22" s="49">
-        <v>46173</v>
+        <v>46162</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="33" t="s">
-        <v>60</v>
+        <v>116</v>
       </c>
       <c r="B23" s="34" t="s">
-        <v>61</v>
+        <v>117</v>
       </c>
       <c r="C23" s="35" t="s">
-        <v>62</v>
+        <v>19</v>
       </c>
       <c r="D23" s="36" t="s">
-        <v>20</v>
+        <v>31</v>
       </c>
       <c r="E23" s="37" t="s">
-        <v>46</v>
+        <v>21</v>
       </c>
       <c r="F23" s="38" t="s">
-        <v>47</v>
+        <v>22</v>
       </c>
       <c r="G23" s="39" t="s">
-        <v>87</v>
+        <v>23</v>
       </c>
       <c r="H23" s="40" t="s">
-        <v>46</v>
+        <v>21</v>
       </c>
       <c r="I23" s="41" t="s">
-        <v>88</v>
+        <v>113</v>
       </c>
       <c r="J23" s="42" t="s">
-        <v>64</v>
+        <v>82</v>
       </c>
       <c r="K23" s="43" t="s">
-        <v>65</v>
+        <v>83</v>
       </c>
       <c r="L23" s="44" t="s">
-        <v>66</v>
+        <v>84</v>
       </c>
       <c r="M23" s="45">
-        <v>46173</v>
+        <v>46175</v>
       </c>
       <c r="N23" s="46">
-        <v>46174</v>
+        <v>46175</v>
       </c>
       <c r="O23" s="47" t="s">
-        <v>67</v>
+        <v>114</v>
       </c>
       <c r="P23" s="48" t="s">
-        <v>67</v>
+        <v>115</v>
       </c>
       <c r="Q23" s="49">
-        <v>46173</v>
+        <v>46162</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="33" t="s">
-        <v>60</v>
+        <v>118</v>
       </c>
       <c r="B24" s="34" t="s">
-        <v>61</v>
+        <v>119</v>
       </c>
       <c r="C24" s="35" t="s">
-        <v>62</v>
+        <v>19</v>
       </c>
       <c r="D24" s="36" t="s">
-        <v>20</v>
+        <v>31</v>
       </c>
       <c r="E24" s="37" t="s">
-        <v>46</v>
+        <v>88</v>
       </c>
       <c r="F24" s="38" t="s">
-        <v>47</v>
+        <v>89</v>
       </c>
       <c r="G24" s="39" t="s">
-        <v>89</v>
+        <v>23</v>
       </c>
       <c r="H24" s="40" t="s">
-        <v>46</v>
+        <v>88</v>
       </c>
       <c r="I24" s="41" t="s">
-        <v>90</v>
+        <v>120</v>
       </c>
       <c r="J24" s="42" t="s">
-        <v>64</v>
+        <v>121</v>
       </c>
       <c r="K24" s="43" t="s">
-        <v>65</v>
+        <v>122</v>
       </c>
       <c r="L24" s="44" t="s">
-        <v>66</v>
+        <v>123</v>
       </c>
       <c r="M24" s="45">
-        <v>46173</v>
+        <v>46175</v>
       </c>
       <c r="N24" s="46">
-        <v>46174</v>
+        <v>46175</v>
       </c>
       <c r="O24" s="47" t="s">
-        <v>67</v>
+        <v>124</v>
       </c>
       <c r="P24" s="48" t="s">
-        <v>67</v>
+        <v>124</v>
       </c>
       <c r="Q24" s="49">
-        <v>46173</v>
+        <v>46165</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="33" t="s">
-        <v>60</v>
+        <v>118</v>
       </c>
       <c r="B25" s="34" t="s">
+        <v>119</v>
+      </c>
+      <c r="C25" s="35" t="s">
+        <v>19</v>
+      </c>
+      <c r="D25" s="36" t="s">
+        <v>31</v>
+      </c>
+      <c r="E25" s="37" t="s">
+        <v>88</v>
+      </c>
+      <c r="F25" s="38" t="s">
+        <v>89</v>
+      </c>
+      <c r="G25" s="39" t="s">
         <v>61</v>
       </c>
-      <c r="C25" s="35" t="s">
-        <v>62</v>
-      </c>
-      <c r="D25" s="36" t="s">
-        <v>20</v>
-      </c>
-      <c r="E25" s="37" t="s">
-        <v>46</v>
-      </c>
-      <c r="F25" s="38" t="s">
-        <v>47</v>
-      </c>
-      <c r="G25" s="39" t="s">
-        <v>91</v>
-      </c>
       <c r="H25" s="40" t="s">
-        <v>46</v>
+        <v>88</v>
       </c>
       <c r="I25" s="41" t="s">
-        <v>63</v>
+        <v>120</v>
       </c>
       <c r="J25" s="42" t="s">
-        <v>64</v>
+        <v>121</v>
       </c>
       <c r="K25" s="43" t="s">
-        <v>65</v>
+        <v>122</v>
       </c>
       <c r="L25" s="44" t="s">
-        <v>66</v>
+        <v>123</v>
       </c>
       <c r="M25" s="45">
-        <v>46173</v>
+        <v>46175</v>
       </c>
       <c r="N25" s="46">
-        <v>46174</v>
+        <v>46175</v>
       </c>
       <c r="O25" s="47" t="s">
-        <v>67</v>
+        <v>124</v>
       </c>
       <c r="P25" s="48" t="s">
-        <v>67</v>
+        <v>124</v>
       </c>
       <c r="Q25" s="49">
-        <v>46173</v>
+        <v>46165</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="33" t="s">
-        <v>60</v>
+        <v>118</v>
       </c>
       <c r="B26" s="34" t="s">
-        <v>61</v>
+        <v>119</v>
       </c>
       <c r="C26" s="35" t="s">
-        <v>62</v>
+        <v>19</v>
       </c>
       <c r="D26" s="36" t="s">
-        <v>20</v>
+        <v>31</v>
       </c>
       <c r="E26" s="37" t="s">
-        <v>21</v>
+        <v>88</v>
       </c>
       <c r="F26" s="38" t="s">
-        <v>22</v>
+        <v>89</v>
       </c>
       <c r="G26" s="39" t="s">
-        <v>92</v>
+        <v>63</v>
       </c>
       <c r="H26" s="40" t="s">
-        <v>21</v>
+        <v>88</v>
       </c>
       <c r="I26" s="41" t="s">
-        <v>93</v>
+        <v>120</v>
       </c>
       <c r="J26" s="42" t="s">
-        <v>64</v>
+        <v>121</v>
       </c>
       <c r="K26" s="43" t="s">
-        <v>65</v>
+        <v>122</v>
       </c>
       <c r="L26" s="44" t="s">
-        <v>66</v>
+        <v>123</v>
       </c>
       <c r="M26" s="45">
-        <v>46173</v>
+        <v>46175</v>
       </c>
       <c r="N26" s="46">
-        <v>46174</v>
+        <v>46175</v>
       </c>
       <c r="O26" s="47" t="s">
-        <v>67</v>
+        <v>124</v>
       </c>
       <c r="P26" s="48" t="s">
-        <v>67</v>
+        <v>124</v>
       </c>
       <c r="Q26" s="49">
-        <v>46173</v>
+        <v>46165</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="33" t="s">
-        <v>60</v>
+        <v>118</v>
       </c>
       <c r="B27" s="34" t="s">
-        <v>61</v>
+        <v>119</v>
       </c>
       <c r="C27" s="35" t="s">
-        <v>62</v>
+        <v>19</v>
       </c>
       <c r="D27" s="36" t="s">
-        <v>20</v>
+        <v>31</v>
       </c>
       <c r="E27" s="37" t="s">
         <v>21</v>
@@ -2731,104 +3082,104 @@
         <v>22</v>
       </c>
       <c r="G27" s="39" t="s">
-        <v>94</v>
+        <v>65</v>
       </c>
       <c r="H27" s="40" t="s">
         <v>21</v>
       </c>
       <c r="I27" s="41" t="s">
-        <v>95</v>
+        <v>125</v>
       </c>
       <c r="J27" s="42" t="s">
-        <v>64</v>
+        <v>121</v>
       </c>
       <c r="K27" s="43" t="s">
-        <v>65</v>
+        <v>122</v>
       </c>
       <c r="L27" s="44" t="s">
-        <v>66</v>
+        <v>123</v>
       </c>
       <c r="M27" s="45">
-        <v>46173</v>
+        <v>46175</v>
       </c>
       <c r="N27" s="46">
-        <v>46174</v>
+        <v>46175</v>
       </c>
       <c r="O27" s="47" t="s">
-        <v>67</v>
+        <v>124</v>
       </c>
       <c r="P27" s="48" t="s">
-        <v>67</v>
+        <v>124</v>
       </c>
       <c r="Q27" s="49">
-        <v>46173</v>
+        <v>46165</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="33" t="s">
-        <v>60</v>
+        <v>118</v>
       </c>
       <c r="B28" s="34" t="s">
-        <v>61</v>
+        <v>119</v>
       </c>
       <c r="C28" s="35" t="s">
-        <v>62</v>
+        <v>19</v>
       </c>
       <c r="D28" s="36" t="s">
-        <v>20</v>
+        <v>31</v>
       </c>
       <c r="E28" s="37" t="s">
-        <v>46</v>
+        <v>21</v>
       </c>
       <c r="F28" s="38" t="s">
-        <v>47</v>
+        <v>22</v>
       </c>
       <c r="G28" s="39" t="s">
-        <v>96</v>
+        <v>67</v>
       </c>
       <c r="H28" s="40" t="s">
-        <v>46</v>
+        <v>21</v>
       </c>
       <c r="I28" s="41" t="s">
-        <v>88</v>
+        <v>126</v>
       </c>
       <c r="J28" s="42" t="s">
-        <v>64</v>
+        <v>121</v>
       </c>
       <c r="K28" s="43" t="s">
-        <v>65</v>
+        <v>122</v>
       </c>
       <c r="L28" s="44" t="s">
-        <v>66</v>
+        <v>123</v>
       </c>
       <c r="M28" s="45">
-        <v>46173</v>
+        <v>46175</v>
       </c>
       <c r="N28" s="46">
-        <v>46174</v>
+        <v>46175</v>
       </c>
       <c r="O28" s="47" t="s">
-        <v>67</v>
+        <v>124</v>
       </c>
       <c r="P28" s="48" t="s">
-        <v>67</v>
+        <v>124</v>
       </c>
       <c r="Q28" s="49">
-        <v>46173</v>
+        <v>46165</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="33" t="s">
-        <v>60</v>
+        <v>118</v>
       </c>
       <c r="B29" s="34" t="s">
-        <v>61</v>
+        <v>119</v>
       </c>
       <c r="C29" s="35" t="s">
-        <v>62</v>
+        <v>19</v>
       </c>
       <c r="D29" s="36" t="s">
-        <v>20</v>
+        <v>31</v>
       </c>
       <c r="E29" s="37" t="s">
         <v>21</v>
@@ -2837,51 +3188,51 @@
         <v>22</v>
       </c>
       <c r="G29" s="39" t="s">
-        <v>97</v>
+        <v>69</v>
       </c>
       <c r="H29" s="40" t="s">
         <v>21</v>
       </c>
       <c r="I29" s="41" t="s">
-        <v>98</v>
+        <v>126</v>
       </c>
       <c r="J29" s="42" t="s">
-        <v>64</v>
+        <v>121</v>
       </c>
       <c r="K29" s="43" t="s">
-        <v>65</v>
+        <v>122</v>
       </c>
       <c r="L29" s="44" t="s">
-        <v>66</v>
+        <v>123</v>
       </c>
       <c r="M29" s="45">
-        <v>46173</v>
+        <v>46175</v>
       </c>
       <c r="N29" s="46">
-        <v>46174</v>
+        <v>46175</v>
       </c>
       <c r="O29" s="47" t="s">
-        <v>67</v>
+        <v>124</v>
       </c>
       <c r="P29" s="48" t="s">
-        <v>67</v>
+        <v>124</v>
       </c>
       <c r="Q29" s="49">
-        <v>46173</v>
+        <v>46165</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="33" t="s">
-        <v>99</v>
+        <v>118</v>
       </c>
       <c r="B30" s="34" t="s">
-        <v>100</v>
+        <v>119</v>
       </c>
       <c r="C30" s="35" t="s">
         <v>19</v>
       </c>
       <c r="D30" s="36" t="s">
-        <v>20</v>
+        <v>31</v>
       </c>
       <c r="E30" s="37" t="s">
         <v>21</v>
@@ -2890,104 +3241,104 @@
         <v>22</v>
       </c>
       <c r="G30" s="39" t="s">
-        <v>23</v>
+        <v>127</v>
       </c>
       <c r="H30" s="40" t="s">
         <v>21</v>
       </c>
       <c r="I30" s="41" t="s">
-        <v>101</v>
+        <v>128</v>
       </c>
       <c r="J30" s="42" t="s">
-        <v>102</v>
+        <v>121</v>
       </c>
       <c r="K30" s="43" t="s">
-        <v>103</v>
+        <v>122</v>
       </c>
       <c r="L30" s="44" t="s">
-        <v>104</v>
+        <v>123</v>
       </c>
       <c r="M30" s="45">
-        <v>46174</v>
+        <v>46175</v>
       </c>
       <c r="N30" s="46">
-        <v>46174</v>
+        <v>46175</v>
       </c>
       <c r="O30" s="47" t="s">
-        <v>105</v>
+        <v>124</v>
       </c>
       <c r="P30" s="48" t="s">
-        <v>105</v>
+        <v>124</v>
       </c>
       <c r="Q30" s="49">
-        <v>46151</v>
+        <v>46165</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="33" t="s">
-        <v>99</v>
+        <v>118</v>
       </c>
       <c r="B31" s="34" t="s">
-        <v>100</v>
+        <v>119</v>
       </c>
       <c r="C31" s="35" t="s">
         <v>19</v>
       </c>
       <c r="D31" s="36" t="s">
-        <v>20</v>
+        <v>31</v>
       </c>
       <c r="E31" s="37" t="s">
-        <v>21</v>
+        <v>88</v>
       </c>
       <c r="F31" s="38" t="s">
-        <v>22</v>
+        <v>89</v>
       </c>
       <c r="G31" s="39" t="s">
-        <v>41</v>
+        <v>129</v>
       </c>
       <c r="H31" s="40" t="s">
-        <v>21</v>
+        <v>88</v>
       </c>
       <c r="I31" s="41" t="s">
-        <v>106</v>
+        <v>120</v>
       </c>
       <c r="J31" s="42" t="s">
-        <v>102</v>
+        <v>121</v>
       </c>
       <c r="K31" s="43" t="s">
-        <v>103</v>
+        <v>122</v>
       </c>
       <c r="L31" s="44" t="s">
-        <v>104</v>
+        <v>123</v>
       </c>
       <c r="M31" s="45">
-        <v>46174</v>
+        <v>46175</v>
       </c>
       <c r="N31" s="46">
-        <v>46174</v>
+        <v>46175</v>
       </c>
       <c r="O31" s="47" t="s">
-        <v>105</v>
+        <v>124</v>
       </c>
       <c r="P31" s="48" t="s">
-        <v>105</v>
+        <v>124</v>
       </c>
       <c r="Q31" s="49">
-        <v>46151</v>
+        <v>46165</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="33" t="s">
-        <v>99</v>
+        <v>118</v>
       </c>
       <c r="B32" s="34" t="s">
-        <v>100</v>
+        <v>119</v>
       </c>
       <c r="C32" s="35" t="s">
         <v>19</v>
       </c>
       <c r="D32" s="36" t="s">
-        <v>20</v>
+        <v>31</v>
       </c>
       <c r="E32" s="37" t="s">
         <v>21</v>
@@ -2996,731 +3347,6190 @@
         <v>22</v>
       </c>
       <c r="G32" s="39" t="s">
-        <v>68</v>
+        <v>130</v>
       </c>
       <c r="H32" s="40" t="s">
         <v>21</v>
       </c>
       <c r="I32" s="41" t="s">
-        <v>107</v>
+        <v>131</v>
       </c>
       <c r="J32" s="42" t="s">
-        <v>102</v>
+        <v>121</v>
       </c>
       <c r="K32" s="43" t="s">
-        <v>103</v>
+        <v>122</v>
       </c>
       <c r="L32" s="44" t="s">
-        <v>104</v>
+        <v>123</v>
       </c>
       <c r="M32" s="45">
-        <v>46174</v>
+        <v>46175</v>
       </c>
       <c r="N32" s="46">
-        <v>46174</v>
+        <v>46175</v>
       </c>
       <c r="O32" s="47" t="s">
-        <v>105</v>
+        <v>124</v>
       </c>
       <c r="P32" s="48" t="s">
-        <v>105</v>
+        <v>124</v>
       </c>
       <c r="Q32" s="49">
-        <v>46151</v>
+        <v>46165</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="33" t="s">
-        <v>99</v>
+        <v>118</v>
       </c>
       <c r="B33" s="34" t="s">
-        <v>100</v>
+        <v>119</v>
       </c>
       <c r="C33" s="35" t="s">
         <v>19</v>
       </c>
       <c r="D33" s="36" t="s">
-        <v>20</v>
+        <v>31</v>
       </c>
       <c r="E33" s="37" t="s">
-        <v>21</v>
+        <v>88</v>
       </c>
       <c r="F33" s="38" t="s">
-        <v>22</v>
+        <v>89</v>
       </c>
       <c r="G33" s="39" t="s">
-        <v>69</v>
+        <v>132</v>
       </c>
       <c r="H33" s="40" t="s">
-        <v>21</v>
+        <v>88</v>
       </c>
       <c r="I33" s="41" t="s">
-        <v>108</v>
+        <v>120</v>
       </c>
       <c r="J33" s="42" t="s">
-        <v>102</v>
+        <v>121</v>
       </c>
       <c r="K33" s="43" t="s">
-        <v>103</v>
+        <v>122</v>
       </c>
       <c r="L33" s="44" t="s">
-        <v>104</v>
+        <v>123</v>
       </c>
       <c r="M33" s="45">
-        <v>46174</v>
+        <v>46175</v>
       </c>
       <c r="N33" s="46">
-        <v>46174</v>
+        <v>46175</v>
       </c>
       <c r="O33" s="47" t="s">
-        <v>105</v>
+        <v>124</v>
       </c>
       <c r="P33" s="48" t="s">
-        <v>105</v>
+        <v>124</v>
       </c>
       <c r="Q33" s="49">
-        <v>46151</v>
+        <v>46165</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="33" t="s">
-        <v>109</v>
+        <v>118</v>
       </c>
       <c r="B34" s="34" t="s">
-        <v>110</v>
+        <v>119</v>
       </c>
       <c r="C34" s="35" t="s">
-        <v>62</v>
+        <v>19</v>
       </c>
       <c r="D34" s="36" t="s">
-        <v>20</v>
+        <v>31</v>
       </c>
       <c r="E34" s="37" t="s">
-        <v>46</v>
+        <v>21</v>
       </c>
       <c r="F34" s="38" t="s">
-        <v>47</v>
+        <v>22</v>
       </c>
       <c r="G34" s="39" t="s">
-        <v>23</v>
+        <v>133</v>
       </c>
       <c r="H34" s="40" t="s">
-        <v>46</v>
+        <v>21</v>
       </c>
       <c r="I34" s="41" t="s">
-        <v>111</v>
+        <v>125</v>
       </c>
       <c r="J34" s="42" t="s">
-        <v>112</v>
+        <v>121</v>
       </c>
       <c r="K34" s="43" t="s">
-        <v>113</v>
+        <v>122</v>
       </c>
       <c r="L34" s="44" t="s">
-        <v>114</v>
+        <v>123</v>
       </c>
       <c r="M34" s="45">
-        <v>46173</v>
+        <v>46175</v>
       </c>
       <c r="N34" s="46">
-        <v>46174</v>
+        <v>46175</v>
       </c>
       <c r="O34" s="47" t="s">
-        <v>115</v>
+        <v>124</v>
       </c>
       <c r="P34" s="48" t="s">
-        <v>115</v>
+        <v>124</v>
       </c>
       <c r="Q34" s="49">
-        <v>46173</v>
+        <v>46165</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="33" t="s">
-        <v>109</v>
+        <v>118</v>
       </c>
       <c r="B35" s="34" t="s">
-        <v>110</v>
+        <v>119</v>
       </c>
       <c r="C35" s="35" t="s">
-        <v>62</v>
+        <v>19</v>
       </c>
       <c r="D35" s="36" t="s">
-        <v>20</v>
+        <v>31</v>
       </c>
       <c r="E35" s="37" t="s">
-        <v>46</v>
+        <v>21</v>
       </c>
       <c r="F35" s="38" t="s">
-        <v>47</v>
+        <v>22</v>
       </c>
       <c r="G35" s="39" t="s">
-        <v>41</v>
+        <v>134</v>
       </c>
       <c r="H35" s="40" t="s">
-        <v>46</v>
+        <v>21</v>
       </c>
       <c r="I35" s="41" t="s">
-        <v>116</v>
+        <v>128</v>
       </c>
       <c r="J35" s="42" t="s">
-        <v>112</v>
+        <v>121</v>
       </c>
       <c r="K35" s="43" t="s">
-        <v>113</v>
+        <v>122</v>
       </c>
       <c r="L35" s="44" t="s">
-        <v>114</v>
+        <v>123</v>
       </c>
       <c r="M35" s="45">
-        <v>46173</v>
+        <v>46175</v>
       </c>
       <c r="N35" s="46">
-        <v>46174</v>
+        <v>46175</v>
       </c>
       <c r="O35" s="47" t="s">
-        <v>115</v>
+        <v>124</v>
       </c>
       <c r="P35" s="48" t="s">
-        <v>115</v>
+        <v>124</v>
       </c>
       <c r="Q35" s="49">
-        <v>46173</v>
+        <v>46165</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="33" t="s">
-        <v>109</v>
+        <v>118</v>
       </c>
       <c r="B36" s="34" t="s">
-        <v>110</v>
+        <v>119</v>
       </c>
       <c r="C36" s="35" t="s">
-        <v>62</v>
+        <v>19</v>
       </c>
       <c r="D36" s="36" t="s">
-        <v>20</v>
+        <v>31</v>
       </c>
       <c r="E36" s="37" t="s">
-        <v>46</v>
+        <v>21</v>
       </c>
       <c r="F36" s="38" t="s">
-        <v>47</v>
+        <v>22</v>
       </c>
       <c r="G36" s="39" t="s">
-        <v>68</v>
+        <v>135</v>
       </c>
       <c r="H36" s="40" t="s">
-        <v>46</v>
+        <v>21</v>
       </c>
       <c r="I36" s="41" t="s">
-        <v>111</v>
+        <v>128</v>
       </c>
       <c r="J36" s="42" t="s">
-        <v>112</v>
+        <v>121</v>
       </c>
       <c r="K36" s="43" t="s">
-        <v>113</v>
+        <v>122</v>
       </c>
       <c r="L36" s="44" t="s">
-        <v>114</v>
+        <v>123</v>
       </c>
       <c r="M36" s="45">
-        <v>46173</v>
+        <v>46175</v>
       </c>
       <c r="N36" s="46">
-        <v>46174</v>
+        <v>46175</v>
       </c>
       <c r="O36" s="47" t="s">
-        <v>115</v>
+        <v>124</v>
       </c>
       <c r="P36" s="48" t="s">
-        <v>115</v>
+        <v>124</v>
       </c>
       <c r="Q36" s="49">
-        <v>46173</v>
+        <v>46165</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="33" t="s">
-        <v>109</v>
+        <v>118</v>
       </c>
       <c r="B37" s="34" t="s">
-        <v>110</v>
+        <v>119</v>
       </c>
       <c r="C37" s="35" t="s">
-        <v>62</v>
+        <v>19</v>
       </c>
       <c r="D37" s="36" t="s">
-        <v>20</v>
+        <v>31</v>
       </c>
       <c r="E37" s="37" t="s">
-        <v>46</v>
+        <v>21</v>
       </c>
       <c r="F37" s="38" t="s">
-        <v>47</v>
+        <v>22</v>
       </c>
       <c r="G37" s="39" t="s">
-        <v>69</v>
+        <v>136</v>
       </c>
       <c r="H37" s="40" t="s">
-        <v>46</v>
+        <v>21</v>
       </c>
       <c r="I37" s="41" t="s">
-        <v>111</v>
+        <v>137</v>
       </c>
       <c r="J37" s="42" t="s">
-        <v>112</v>
+        <v>121</v>
       </c>
       <c r="K37" s="43" t="s">
-        <v>113</v>
+        <v>122</v>
       </c>
       <c r="L37" s="44" t="s">
-        <v>114</v>
+        <v>123</v>
       </c>
       <c r="M37" s="45">
-        <v>46173</v>
+        <v>46175</v>
       </c>
       <c r="N37" s="46">
-        <v>46174</v>
+        <v>46175</v>
       </c>
       <c r="O37" s="47" t="s">
-        <v>115</v>
+        <v>124</v>
       </c>
       <c r="P37" s="48" t="s">
-        <v>115</v>
+        <v>124</v>
       </c>
       <c r="Q37" s="49">
-        <v>46173</v>
+        <v>46165</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="33" t="s">
-        <v>109</v>
+        <v>118</v>
       </c>
       <c r="B38" s="34" t="s">
-        <v>110</v>
+        <v>119</v>
       </c>
       <c r="C38" s="35" t="s">
-        <v>62</v>
+        <v>19</v>
       </c>
       <c r="D38" s="36" t="s">
-        <v>20</v>
+        <v>31</v>
       </c>
       <c r="E38" s="37" t="s">
-        <v>46</v>
+        <v>21</v>
       </c>
       <c r="F38" s="38" t="s">
-        <v>47</v>
+        <v>22</v>
       </c>
       <c r="G38" s="39" t="s">
-        <v>70</v>
+        <v>138</v>
       </c>
       <c r="H38" s="40" t="s">
-        <v>46</v>
+        <v>21</v>
       </c>
       <c r="I38" s="41" t="s">
-        <v>111</v>
+        <v>128</v>
       </c>
       <c r="J38" s="42" t="s">
-        <v>112</v>
+        <v>121</v>
       </c>
       <c r="K38" s="43" t="s">
-        <v>113</v>
+        <v>122</v>
       </c>
       <c r="L38" s="44" t="s">
-        <v>114</v>
+        <v>123</v>
       </c>
       <c r="M38" s="45">
-        <v>46173</v>
+        <v>46175</v>
       </c>
       <c r="N38" s="46">
-        <v>46174</v>
+        <v>46175</v>
       </c>
       <c r="O38" s="47" t="s">
-        <v>115</v>
+        <v>124</v>
       </c>
       <c r="P38" s="48" t="s">
-        <v>115</v>
+        <v>124</v>
       </c>
       <c r="Q38" s="49">
-        <v>46173</v>
+        <v>46165</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="33" t="s">
-        <v>109</v>
+        <v>118</v>
       </c>
       <c r="B39" s="34" t="s">
-        <v>110</v>
+        <v>119</v>
       </c>
       <c r="C39" s="35" t="s">
-        <v>62</v>
+        <v>19</v>
       </c>
       <c r="D39" s="36" t="s">
-        <v>20</v>
+        <v>31</v>
       </c>
       <c r="E39" s="37" t="s">
-        <v>46</v>
+        <v>21</v>
       </c>
       <c r="F39" s="38" t="s">
-        <v>47</v>
+        <v>22</v>
       </c>
       <c r="G39" s="39" t="s">
-        <v>72</v>
+        <v>139</v>
       </c>
       <c r="H39" s="40" t="s">
-        <v>46</v>
+        <v>21</v>
       </c>
       <c r="I39" s="41" t="s">
-        <v>111</v>
+        <v>125</v>
       </c>
       <c r="J39" s="42" t="s">
-        <v>112</v>
+        <v>121</v>
       </c>
       <c r="K39" s="43" t="s">
-        <v>113</v>
+        <v>122</v>
       </c>
       <c r="L39" s="44" t="s">
-        <v>114</v>
+        <v>123</v>
       </c>
       <c r="M39" s="45">
-        <v>46173</v>
+        <v>46175</v>
       </c>
       <c r="N39" s="46">
-        <v>46174</v>
+        <v>46175</v>
       </c>
       <c r="O39" s="47" t="s">
-        <v>115</v>
+        <v>124</v>
       </c>
       <c r="P39" s="48" t="s">
-        <v>115</v>
+        <v>124</v>
       </c>
       <c r="Q39" s="49">
-        <v>46173</v>
+        <v>46165</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="33" t="s">
-        <v>109</v>
+        <v>118</v>
       </c>
       <c r="B40" s="34" t="s">
-        <v>110</v>
+        <v>119</v>
       </c>
       <c r="C40" s="35" t="s">
-        <v>62</v>
+        <v>19</v>
       </c>
       <c r="D40" s="36" t="s">
-        <v>20</v>
+        <v>31</v>
       </c>
       <c r="E40" s="37" t="s">
-        <v>46</v>
+        <v>21</v>
       </c>
       <c r="F40" s="38" t="s">
-        <v>47</v>
+        <v>22</v>
       </c>
       <c r="G40" s="39" t="s">
-        <v>73</v>
+        <v>140</v>
       </c>
       <c r="H40" s="40" t="s">
-        <v>46</v>
+        <v>21</v>
       </c>
       <c r="I40" s="41" t="s">
-        <v>111</v>
+        <v>128</v>
       </c>
       <c r="J40" s="42" t="s">
-        <v>112</v>
+        <v>121</v>
       </c>
       <c r="K40" s="43" t="s">
-        <v>113</v>
+        <v>122</v>
       </c>
       <c r="L40" s="44" t="s">
-        <v>114</v>
+        <v>123</v>
       </c>
       <c r="M40" s="45">
-        <v>46173</v>
+        <v>46175</v>
       </c>
       <c r="N40" s="46">
-        <v>46174</v>
+        <v>46175</v>
       </c>
       <c r="O40" s="47" t="s">
-        <v>115</v>
+        <v>124</v>
       </c>
       <c r="P40" s="48" t="s">
-        <v>115</v>
+        <v>124</v>
       </c>
       <c r="Q40" s="49">
-        <v>46173</v>
+        <v>46165</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="33" t="s">
-        <v>109</v>
+        <v>118</v>
       </c>
       <c r="B41" s="34" t="s">
-        <v>110</v>
+        <v>119</v>
       </c>
       <c r="C41" s="35" t="s">
-        <v>62</v>
+        <v>19</v>
       </c>
       <c r="D41" s="36" t="s">
-        <v>20</v>
+        <v>31</v>
       </c>
       <c r="E41" s="37" t="s">
-        <v>46</v>
+        <v>21</v>
       </c>
       <c r="F41" s="38" t="s">
-        <v>47</v>
+        <v>22</v>
       </c>
       <c r="G41" s="39" t="s">
-        <v>75</v>
+        <v>141</v>
       </c>
       <c r="H41" s="40" t="s">
-        <v>46</v>
+        <v>21</v>
       </c>
       <c r="I41" s="41" t="s">
-        <v>111</v>
+        <v>128</v>
       </c>
       <c r="J41" s="42" t="s">
-        <v>112</v>
+        <v>121</v>
       </c>
       <c r="K41" s="43" t="s">
-        <v>113</v>
+        <v>122</v>
       </c>
       <c r="L41" s="44" t="s">
-        <v>114</v>
+        <v>123</v>
       </c>
       <c r="M41" s="45">
-        <v>46173</v>
+        <v>46175</v>
       </c>
       <c r="N41" s="46">
-        <v>46174</v>
+        <v>46175</v>
       </c>
       <c r="O41" s="47" t="s">
-        <v>115</v>
+        <v>124</v>
       </c>
       <c r="P41" s="48" t="s">
-        <v>115</v>
+        <v>124</v>
       </c>
       <c r="Q41" s="49">
-        <v>46173</v>
+        <v>46165</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="33" t="s">
-        <v>109</v>
+        <v>118</v>
       </c>
       <c r="B42" s="34" t="s">
-        <v>110</v>
+        <v>119</v>
       </c>
       <c r="C42" s="35" t="s">
-        <v>62</v>
+        <v>19</v>
       </c>
       <c r="D42" s="36" t="s">
-        <v>20</v>
+        <v>31</v>
       </c>
       <c r="E42" s="37" t="s">
-        <v>46</v>
+        <v>88</v>
       </c>
       <c r="F42" s="38" t="s">
-        <v>47</v>
+        <v>89</v>
       </c>
       <c r="G42" s="39" t="s">
-        <v>77</v>
+        <v>142</v>
       </c>
       <c r="H42" s="40" t="s">
-        <v>46</v>
+        <v>88</v>
       </c>
       <c r="I42" s="41" t="s">
-        <v>111</v>
+        <v>120</v>
       </c>
       <c r="J42" s="42" t="s">
-        <v>112</v>
+        <v>121</v>
       </c>
       <c r="K42" s="43" t="s">
-        <v>113</v>
+        <v>122</v>
       </c>
       <c r="L42" s="44" t="s">
-        <v>114</v>
+        <v>123</v>
       </c>
       <c r="M42" s="45">
-        <v>46173</v>
+        <v>46175</v>
       </c>
       <c r="N42" s="46">
-        <v>46174</v>
+        <v>46175</v>
       </c>
       <c r="O42" s="47" t="s">
-        <v>115</v>
+        <v>124</v>
       </c>
       <c r="P42" s="48" t="s">
-        <v>115</v>
+        <v>124</v>
       </c>
       <c r="Q42" s="49">
-        <v>46173</v>
+        <v>46165</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="33" t="s">
-        <v>109</v>
+        <v>118</v>
       </c>
       <c r="B43" s="34" t="s">
-        <v>110</v>
+        <v>119</v>
       </c>
       <c r="C43" s="35" t="s">
-        <v>62</v>
+        <v>19</v>
       </c>
       <c r="D43" s="36" t="s">
-        <v>20</v>
+        <v>31</v>
       </c>
       <c r="E43" s="37" t="s">
-        <v>46</v>
+        <v>21</v>
       </c>
       <c r="F43" s="38" t="s">
-        <v>47</v>
+        <v>22</v>
       </c>
       <c r="G43" s="39" t="s">
-        <v>78</v>
+        <v>143</v>
       </c>
       <c r="H43" s="40" t="s">
-        <v>46</v>
+        <v>21</v>
       </c>
       <c r="I43" s="41" t="s">
-        <v>111</v>
+        <v>128</v>
       </c>
       <c r="J43" s="42" t="s">
-        <v>112</v>
+        <v>121</v>
       </c>
       <c r="K43" s="43" t="s">
-        <v>113</v>
+        <v>122</v>
       </c>
       <c r="L43" s="44" t="s">
-        <v>114</v>
+        <v>123</v>
       </c>
       <c r="M43" s="45">
-        <v>46173</v>
+        <v>46175</v>
       </c>
       <c r="N43" s="46">
-        <v>46174</v>
+        <v>46175</v>
       </c>
       <c r="O43" s="47" t="s">
-        <v>115</v>
+        <v>124</v>
       </c>
       <c r="P43" s="48" t="s">
-        <v>115</v>
+        <v>124</v>
       </c>
       <c r="Q43" s="49">
-        <v>46173</v>
+        <v>46165</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="33" t="s">
-        <v>109</v>
+        <v>118</v>
       </c>
       <c r="B44" s="34" t="s">
-        <v>110</v>
+        <v>119</v>
       </c>
       <c r="C44" s="35" t="s">
-        <v>62</v>
+        <v>19</v>
       </c>
       <c r="D44" s="36" t="s">
-        <v>20</v>
+        <v>31</v>
       </c>
       <c r="E44" s="37" t="s">
-        <v>46</v>
+        <v>21</v>
       </c>
       <c r="F44" s="38" t="s">
-        <v>47</v>
+        <v>22</v>
       </c>
       <c r="G44" s="39" t="s">
-        <v>79</v>
+        <v>144</v>
       </c>
       <c r="H44" s="40" t="s">
-        <v>46</v>
+        <v>21</v>
       </c>
       <c r="I44" s="41" t="s">
-        <v>111</v>
+        <v>145</v>
       </c>
       <c r="J44" s="42" t="s">
-        <v>112</v>
+        <v>121</v>
       </c>
       <c r="K44" s="43" t="s">
-        <v>113</v>
+        <v>122</v>
       </c>
       <c r="L44" s="44" t="s">
-        <v>114</v>
+        <v>123</v>
       </c>
       <c r="M44" s="45">
-        <v>46173</v>
+        <v>46175</v>
       </c>
       <c r="N44" s="46">
-        <v>46174</v>
+        <v>46175</v>
       </c>
       <c r="O44" s="47" t="s">
-        <v>115</v>
+        <v>124</v>
       </c>
       <c r="P44" s="48" t="s">
-        <v>115</v>
+        <v>124</v>
       </c>
       <c r="Q44" s="49">
-        <v>46173</v>
+        <v>46165</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="33" t="s">
-        <v>109</v>
+        <v>118</v>
       </c>
       <c r="B45" s="34" t="s">
-        <v>110</v>
+        <v>119</v>
       </c>
       <c r="C45" s="35" t="s">
-        <v>62</v>
+        <v>19</v>
       </c>
       <c r="D45" s="36" t="s">
-        <v>20</v>
+        <v>31</v>
       </c>
       <c r="E45" s="37" t="s">
-        <v>46</v>
+        <v>21</v>
       </c>
       <c r="F45" s="38" t="s">
-        <v>47</v>
+        <v>22</v>
       </c>
       <c r="G45" s="39" t="s">
-        <v>80</v>
+        <v>146</v>
       </c>
       <c r="H45" s="40" t="s">
-        <v>46</v>
+        <v>21</v>
       </c>
       <c r="I45" s="41" t="s">
-        <v>117</v>
+        <v>126</v>
       </c>
       <c r="J45" s="42" t="s">
-        <v>112</v>
+        <v>121</v>
       </c>
       <c r="K45" s="43" t="s">
-        <v>113</v>
+        <v>122</v>
       </c>
       <c r="L45" s="44" t="s">
-        <v>114</v>
+        <v>123</v>
       </c>
       <c r="M45" s="45">
-        <v>46173</v>
+        <v>46175</v>
       </c>
       <c r="N45" s="46">
-        <v>46174</v>
+        <v>46175</v>
       </c>
       <c r="O45" s="47" t="s">
-        <v>115</v>
+        <v>124</v>
       </c>
       <c r="P45" s="48" t="s">
-        <v>115</v>
+        <v>124</v>
       </c>
       <c r="Q45" s="49">
-        <v>46173</v>
+        <v>46165</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="33" t="s">
+        <v>118</v>
+      </c>
+      <c r="B46" s="34" t="s">
+        <v>119</v>
+      </c>
+      <c r="C46" s="35" t="s">
+        <v>19</v>
+      </c>
+      <c r="D46" s="36" t="s">
+        <v>31</v>
+      </c>
+      <c r="E46" s="37" t="s">
+        <v>88</v>
+      </c>
+      <c r="F46" s="38" t="s">
+        <v>89</v>
+      </c>
+      <c r="G46" s="39" t="s">
+        <v>147</v>
+      </c>
+      <c r="H46" s="40" t="s">
+        <v>88</v>
+      </c>
+      <c r="I46" s="41" t="s">
+        <v>148</v>
+      </c>
+      <c r="J46" s="42" t="s">
+        <v>121</v>
+      </c>
+      <c r="K46" s="43" t="s">
+        <v>122</v>
+      </c>
+      <c r="L46" s="44" t="s">
+        <v>123</v>
+      </c>
+      <c r="M46" s="45">
+        <v>46175</v>
+      </c>
+      <c r="N46" s="46">
+        <v>46175</v>
+      </c>
+      <c r="O46" s="47" t="s">
+        <v>124</v>
+      </c>
+      <c r="P46" s="48" t="s">
+        <v>124</v>
+      </c>
+      <c r="Q46" s="49">
+        <v>46165</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="33" t="s">
+        <v>118</v>
+      </c>
+      <c r="B47" s="34" t="s">
+        <v>119</v>
+      </c>
+      <c r="C47" s="35" t="s">
+        <v>19</v>
+      </c>
+      <c r="D47" s="36" t="s">
+        <v>31</v>
+      </c>
+      <c r="E47" s="37" t="s">
+        <v>21</v>
+      </c>
+      <c r="F47" s="38" t="s">
+        <v>22</v>
+      </c>
+      <c r="G47" s="39" t="s">
+        <v>149</v>
+      </c>
+      <c r="H47" s="40" t="s">
+        <v>21</v>
+      </c>
+      <c r="I47" s="41" t="s">
+        <v>126</v>
+      </c>
+      <c r="J47" s="42" t="s">
+        <v>121</v>
+      </c>
+      <c r="K47" s="43" t="s">
+        <v>122</v>
+      </c>
+      <c r="L47" s="44" t="s">
+        <v>123</v>
+      </c>
+      <c r="M47" s="45">
+        <v>46175</v>
+      </c>
+      <c r="N47" s="46">
+        <v>46175</v>
+      </c>
+      <c r="O47" s="47" t="s">
+        <v>124</v>
+      </c>
+      <c r="P47" s="48" t="s">
+        <v>124</v>
+      </c>
+      <c r="Q47" s="49">
+        <v>46165</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="33" t="s">
+        <v>118</v>
+      </c>
+      <c r="B48" s="34" t="s">
+        <v>119</v>
+      </c>
+      <c r="C48" s="35" t="s">
+        <v>19</v>
+      </c>
+      <c r="D48" s="36" t="s">
+        <v>31</v>
+      </c>
+      <c r="E48" s="37" t="s">
+        <v>21</v>
+      </c>
+      <c r="F48" s="38" t="s">
+        <v>22</v>
+      </c>
+      <c r="G48" s="39" t="s">
+        <v>150</v>
+      </c>
+      <c r="H48" s="40" t="s">
+        <v>21</v>
+      </c>
+      <c r="I48" s="41" t="s">
+        <v>151</v>
+      </c>
+      <c r="J48" s="42" t="s">
+        <v>121</v>
+      </c>
+      <c r="K48" s="43" t="s">
+        <v>122</v>
+      </c>
+      <c r="L48" s="44" t="s">
+        <v>123</v>
+      </c>
+      <c r="M48" s="45">
+        <v>46175</v>
+      </c>
+      <c r="N48" s="46">
+        <v>46175</v>
+      </c>
+      <c r="O48" s="47" t="s">
+        <v>124</v>
+      </c>
+      <c r="P48" s="48" t="s">
+        <v>124</v>
+      </c>
+      <c r="Q48" s="49">
+        <v>46165</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="33" t="s">
+        <v>152</v>
+      </c>
+      <c r="B49" s="34" t="s">
+        <v>153</v>
+      </c>
+      <c r="C49" s="35" t="s">
+        <v>19</v>
+      </c>
+      <c r="D49" s="36" t="s">
+        <v>31</v>
+      </c>
+      <c r="E49" s="37" t="s">
+        <v>21</v>
+      </c>
+      <c r="F49" s="38" t="s">
+        <v>22</v>
+      </c>
+      <c r="G49" s="39" t="s">
+        <v>23</v>
+      </c>
+      <c r="H49" s="40" t="s">
+        <v>21</v>
+      </c>
+      <c r="I49" s="41" t="s">
+        <v>128</v>
+      </c>
+      <c r="J49" s="42" t="s">
+        <v>121</v>
+      </c>
+      <c r="K49" s="43" t="s">
+        <v>122</v>
+      </c>
+      <c r="L49" s="44" t="s">
+        <v>123</v>
+      </c>
+      <c r="M49" s="45">
+        <v>46175</v>
+      </c>
+      <c r="N49" s="46">
+        <v>46175</v>
+      </c>
+      <c r="O49" s="47" t="s">
+        <v>154</v>
+      </c>
+      <c r="P49" s="48" t="s">
+        <v>154</v>
+      </c>
+      <c r="Q49" s="49">
+        <v>46165</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="33" t="s">
+        <v>152</v>
+      </c>
+      <c r="B50" s="34" t="s">
+        <v>153</v>
+      </c>
+      <c r="C50" s="35" t="s">
+        <v>19</v>
+      </c>
+      <c r="D50" s="36" t="s">
+        <v>31</v>
+      </c>
+      <c r="E50" s="37" t="s">
+        <v>21</v>
+      </c>
+      <c r="F50" s="38" t="s">
+        <v>22</v>
+      </c>
+      <c r="G50" s="39" t="s">
+        <v>61</v>
+      </c>
+      <c r="H50" s="40" t="s">
+        <v>21</v>
+      </c>
+      <c r="I50" s="41" t="s">
+        <v>128</v>
+      </c>
+      <c r="J50" s="42" t="s">
+        <v>121</v>
+      </c>
+      <c r="K50" s="43" t="s">
+        <v>122</v>
+      </c>
+      <c r="L50" s="44" t="s">
+        <v>123</v>
+      </c>
+      <c r="M50" s="45">
+        <v>46175</v>
+      </c>
+      <c r="N50" s="46">
+        <v>46175</v>
+      </c>
+      <c r="O50" s="47" t="s">
+        <v>154</v>
+      </c>
+      <c r="P50" s="48" t="s">
+        <v>154</v>
+      </c>
+      <c r="Q50" s="49">
+        <v>46165</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="33" t="s">
+        <v>152</v>
+      </c>
+      <c r="B51" s="34" t="s">
+        <v>153</v>
+      </c>
+      <c r="C51" s="35" t="s">
+        <v>19</v>
+      </c>
+      <c r="D51" s="36" t="s">
+        <v>31</v>
+      </c>
+      <c r="E51" s="37" t="s">
+        <v>21</v>
+      </c>
+      <c r="F51" s="38" t="s">
+        <v>22</v>
+      </c>
+      <c r="G51" s="39" t="s">
+        <v>63</v>
+      </c>
+      <c r="H51" s="40" t="s">
+        <v>21</v>
+      </c>
+      <c r="I51" s="41" t="s">
+        <v>128</v>
+      </c>
+      <c r="J51" s="42" t="s">
+        <v>121</v>
+      </c>
+      <c r="K51" s="43" t="s">
+        <v>122</v>
+      </c>
+      <c r="L51" s="44" t="s">
+        <v>123</v>
+      </c>
+      <c r="M51" s="45">
+        <v>46175</v>
+      </c>
+      <c r="N51" s="46">
+        <v>46175</v>
+      </c>
+      <c r="O51" s="47" t="s">
+        <v>154</v>
+      </c>
+      <c r="P51" s="48" t="s">
+        <v>154</v>
+      </c>
+      <c r="Q51" s="49">
+        <v>46165</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="33" t="s">
+        <v>152</v>
+      </c>
+      <c r="B52" s="34" t="s">
+        <v>153</v>
+      </c>
+      <c r="C52" s="35" t="s">
+        <v>19</v>
+      </c>
+      <c r="D52" s="36" t="s">
+        <v>31</v>
+      </c>
+      <c r="E52" s="37" t="s">
+        <v>21</v>
+      </c>
+      <c r="F52" s="38" t="s">
+        <v>22</v>
+      </c>
+      <c r="G52" s="39" t="s">
+        <v>65</v>
+      </c>
+      <c r="H52" s="40" t="s">
+        <v>21</v>
+      </c>
+      <c r="I52" s="41" t="s">
+        <v>126</v>
+      </c>
+      <c r="J52" s="42" t="s">
+        <v>121</v>
+      </c>
+      <c r="K52" s="43" t="s">
+        <v>122</v>
+      </c>
+      <c r="L52" s="44" t="s">
+        <v>123</v>
+      </c>
+      <c r="M52" s="45">
+        <v>46175</v>
+      </c>
+      <c r="N52" s="46">
+        <v>46175</v>
+      </c>
+      <c r="O52" s="47" t="s">
+        <v>124</v>
+      </c>
+      <c r="P52" s="48" t="s">
+        <v>124</v>
+      </c>
+      <c r="Q52" s="49">
+        <v>46165</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="33" t="s">
+        <v>152</v>
+      </c>
+      <c r="B53" s="34" t="s">
+        <v>153</v>
+      </c>
+      <c r="C53" s="35" t="s">
+        <v>19</v>
+      </c>
+      <c r="D53" s="36" t="s">
+        <v>31</v>
+      </c>
+      <c r="E53" s="37" t="s">
+        <v>21</v>
+      </c>
+      <c r="F53" s="38" t="s">
+        <v>22</v>
+      </c>
+      <c r="G53" s="39" t="s">
+        <v>67</v>
+      </c>
+      <c r="H53" s="40" t="s">
+        <v>21</v>
+      </c>
+      <c r="I53" s="41" t="s">
+        <v>126</v>
+      </c>
+      <c r="J53" s="42" t="s">
+        <v>121</v>
+      </c>
+      <c r="K53" s="43" t="s">
+        <v>122</v>
+      </c>
+      <c r="L53" s="44" t="s">
+        <v>123</v>
+      </c>
+      <c r="M53" s="45">
+        <v>46175</v>
+      </c>
+      <c r="N53" s="46">
+        <v>46175</v>
+      </c>
+      <c r="O53" s="47" t="s">
+        <v>124</v>
+      </c>
+      <c r="P53" s="48" t="s">
+        <v>124</v>
+      </c>
+      <c r="Q53" s="49">
+        <v>46165</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="33" t="s">
+        <v>152</v>
+      </c>
+      <c r="B54" s="34" t="s">
+        <v>153</v>
+      </c>
+      <c r="C54" s="35" t="s">
+        <v>19</v>
+      </c>
+      <c r="D54" s="36" t="s">
+        <v>31</v>
+      </c>
+      <c r="E54" s="37" t="s">
+        <v>21</v>
+      </c>
+      <c r="F54" s="38" t="s">
+        <v>22</v>
+      </c>
+      <c r="G54" s="39" t="s">
+        <v>69</v>
+      </c>
+      <c r="H54" s="40" t="s">
+        <v>21</v>
+      </c>
+      <c r="I54" s="41" t="s">
+        <v>125</v>
+      </c>
+      <c r="J54" s="42" t="s">
+        <v>121</v>
+      </c>
+      <c r="K54" s="43" t="s">
+        <v>122</v>
+      </c>
+      <c r="L54" s="44" t="s">
+        <v>123</v>
+      </c>
+      <c r="M54" s="45">
+        <v>46175</v>
+      </c>
+      <c r="N54" s="46">
+        <v>46175</v>
+      </c>
+      <c r="O54" s="47" t="s">
+        <v>124</v>
+      </c>
+      <c r="P54" s="48" t="s">
+        <v>124</v>
+      </c>
+      <c r="Q54" s="49">
+        <v>46165</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="33" t="s">
+        <v>152</v>
+      </c>
+      <c r="B55" s="34" t="s">
+        <v>153</v>
+      </c>
+      <c r="C55" s="35" t="s">
+        <v>19</v>
+      </c>
+      <c r="D55" s="36" t="s">
+        <v>31</v>
+      </c>
+      <c r="E55" s="37" t="s">
+        <v>21</v>
+      </c>
+      <c r="F55" s="38" t="s">
+        <v>22</v>
+      </c>
+      <c r="G55" s="39" t="s">
+        <v>127</v>
+      </c>
+      <c r="H55" s="40" t="s">
+        <v>21</v>
+      </c>
+      <c r="I55" s="41" t="s">
+        <v>126</v>
+      </c>
+      <c r="J55" s="42" t="s">
+        <v>121</v>
+      </c>
+      <c r="K55" s="43" t="s">
+        <v>122</v>
+      </c>
+      <c r="L55" s="44" t="s">
+        <v>123</v>
+      </c>
+      <c r="M55" s="45">
+        <v>46175</v>
+      </c>
+      <c r="N55" s="46">
+        <v>46175</v>
+      </c>
+      <c r="O55" s="47" t="s">
+        <v>124</v>
+      </c>
+      <c r="P55" s="48" t="s">
+        <v>124</v>
+      </c>
+      <c r="Q55" s="49">
+        <v>46165</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="33" t="s">
+        <v>152</v>
+      </c>
+      <c r="B56" s="34" t="s">
+        <v>153</v>
+      </c>
+      <c r="C56" s="35" t="s">
+        <v>19</v>
+      </c>
+      <c r="D56" s="36" t="s">
+        <v>31</v>
+      </c>
+      <c r="E56" s="37" t="s">
+        <v>88</v>
+      </c>
+      <c r="F56" s="38" t="s">
+        <v>89</v>
+      </c>
+      <c r="G56" s="39" t="s">
+        <v>129</v>
+      </c>
+      <c r="H56" s="40" t="s">
+        <v>88</v>
+      </c>
+      <c r="I56" s="41" t="s">
+        <v>120</v>
+      </c>
+      <c r="J56" s="42" t="s">
+        <v>121</v>
+      </c>
+      <c r="K56" s="43" t="s">
+        <v>122</v>
+      </c>
+      <c r="L56" s="44" t="s">
+        <v>123</v>
+      </c>
+      <c r="M56" s="45">
+        <v>46175</v>
+      </c>
+      <c r="N56" s="46">
+        <v>46175</v>
+      </c>
+      <c r="O56" s="47" t="s">
+        <v>124</v>
+      </c>
+      <c r="P56" s="48" t="s">
+        <v>124</v>
+      </c>
+      <c r="Q56" s="49">
+        <v>46165</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="33" t="s">
+        <v>152</v>
+      </c>
+      <c r="B57" s="34" t="s">
+        <v>153</v>
+      </c>
+      <c r="C57" s="35" t="s">
+        <v>19</v>
+      </c>
+      <c r="D57" s="36" t="s">
+        <v>31</v>
+      </c>
+      <c r="E57" s="37" t="s">
+        <v>88</v>
+      </c>
+      <c r="F57" s="38" t="s">
+        <v>89</v>
+      </c>
+      <c r="G57" s="39" t="s">
+        <v>130</v>
+      </c>
+      <c r="H57" s="40" t="s">
+        <v>88</v>
+      </c>
+      <c r="I57" s="41" t="s">
+        <v>120</v>
+      </c>
+      <c r="J57" s="42" t="s">
+        <v>121</v>
+      </c>
+      <c r="K57" s="43" t="s">
+        <v>122</v>
+      </c>
+      <c r="L57" s="44" t="s">
+        <v>123</v>
+      </c>
+      <c r="M57" s="45">
+        <v>46175</v>
+      </c>
+      <c r="N57" s="46">
+        <v>46175</v>
+      </c>
+      <c r="O57" s="47" t="s">
+        <v>124</v>
+      </c>
+      <c r="P57" s="48" t="s">
+        <v>124</v>
+      </c>
+      <c r="Q57" s="49">
+        <v>46165</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="33" t="s">
+        <v>152</v>
+      </c>
+      <c r="B58" s="34" t="s">
+        <v>153</v>
+      </c>
+      <c r="C58" s="35" t="s">
+        <v>19</v>
+      </c>
+      <c r="D58" s="36" t="s">
+        <v>31</v>
+      </c>
+      <c r="E58" s="37" t="s">
+        <v>88</v>
+      </c>
+      <c r="F58" s="38" t="s">
+        <v>89</v>
+      </c>
+      <c r="G58" s="39" t="s">
+        <v>132</v>
+      </c>
+      <c r="H58" s="40" t="s">
+        <v>88</v>
+      </c>
+      <c r="I58" s="41" t="s">
+        <v>120</v>
+      </c>
+      <c r="J58" s="42" t="s">
+        <v>121</v>
+      </c>
+      <c r="K58" s="43" t="s">
+        <v>122</v>
+      </c>
+      <c r="L58" s="44" t="s">
+        <v>123</v>
+      </c>
+      <c r="M58" s="45">
+        <v>46175</v>
+      </c>
+      <c r="N58" s="46">
+        <v>46175</v>
+      </c>
+      <c r="O58" s="47" t="s">
+        <v>124</v>
+      </c>
+      <c r="P58" s="48" t="s">
+        <v>124</v>
+      </c>
+      <c r="Q58" s="49">
+        <v>46165</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="33" t="s">
+        <v>152</v>
+      </c>
+      <c r="B59" s="34" t="s">
+        <v>153</v>
+      </c>
+      <c r="C59" s="35" t="s">
+        <v>19</v>
+      </c>
+      <c r="D59" s="36" t="s">
+        <v>31</v>
+      </c>
+      <c r="E59" s="37" t="s">
+        <v>21</v>
+      </c>
+      <c r="F59" s="38" t="s">
+        <v>22</v>
+      </c>
+      <c r="G59" s="39" t="s">
+        <v>133</v>
+      </c>
+      <c r="H59" s="40" t="s">
+        <v>21</v>
+      </c>
+      <c r="I59" s="41" t="s">
+        <v>125</v>
+      </c>
+      <c r="J59" s="42" t="s">
+        <v>121</v>
+      </c>
+      <c r="K59" s="43" t="s">
+        <v>122</v>
+      </c>
+      <c r="L59" s="44" t="s">
+        <v>123</v>
+      </c>
+      <c r="M59" s="45">
+        <v>46175</v>
+      </c>
+      <c r="N59" s="46">
+        <v>46175</v>
+      </c>
+      <c r="O59" s="47" t="s">
+        <v>124</v>
+      </c>
+      <c r="P59" s="48" t="s">
+        <v>124</v>
+      </c>
+      <c r="Q59" s="49">
+        <v>46165</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="33" t="s">
+        <v>152</v>
+      </c>
+      <c r="B60" s="34" t="s">
+        <v>153</v>
+      </c>
+      <c r="C60" s="35" t="s">
+        <v>19</v>
+      </c>
+      <c r="D60" s="36" t="s">
+        <v>31</v>
+      </c>
+      <c r="E60" s="37" t="s">
+        <v>21</v>
+      </c>
+      <c r="F60" s="38" t="s">
+        <v>22</v>
+      </c>
+      <c r="G60" s="39" t="s">
+        <v>134</v>
+      </c>
+      <c r="H60" s="40" t="s">
+        <v>21</v>
+      </c>
+      <c r="I60" s="41" t="s">
+        <v>128</v>
+      </c>
+      <c r="J60" s="42" t="s">
+        <v>121</v>
+      </c>
+      <c r="K60" s="43" t="s">
+        <v>122</v>
+      </c>
+      <c r="L60" s="44" t="s">
+        <v>123</v>
+      </c>
+      <c r="M60" s="45">
+        <v>46175</v>
+      </c>
+      <c r="N60" s="46">
+        <v>46175</v>
+      </c>
+      <c r="O60" s="47" t="s">
+        <v>124</v>
+      </c>
+      <c r="P60" s="48" t="s">
+        <v>124</v>
+      </c>
+      <c r="Q60" s="49">
+        <v>46165</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="33" t="s">
+        <v>152</v>
+      </c>
+      <c r="B61" s="34" t="s">
+        <v>153</v>
+      </c>
+      <c r="C61" s="35" t="s">
+        <v>19</v>
+      </c>
+      <c r="D61" s="36" t="s">
+        <v>31</v>
+      </c>
+      <c r="E61" s="37" t="s">
+        <v>21</v>
+      </c>
+      <c r="F61" s="38" t="s">
+        <v>22</v>
+      </c>
+      <c r="G61" s="39" t="s">
+        <v>135</v>
+      </c>
+      <c r="H61" s="40" t="s">
+        <v>21</v>
+      </c>
+      <c r="I61" s="41" t="s">
+        <v>128</v>
+      </c>
+      <c r="J61" s="42" t="s">
+        <v>121</v>
+      </c>
+      <c r="K61" s="43" t="s">
+        <v>122</v>
+      </c>
+      <c r="L61" s="44" t="s">
+        <v>123</v>
+      </c>
+      <c r="M61" s="45">
+        <v>46175</v>
+      </c>
+      <c r="N61" s="46">
+        <v>46175</v>
+      </c>
+      <c r="O61" s="47" t="s">
+        <v>124</v>
+      </c>
+      <c r="P61" s="48" t="s">
+        <v>124</v>
+      </c>
+      <c r="Q61" s="49">
+        <v>46165</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="33" t="s">
+        <v>152</v>
+      </c>
+      <c r="B62" s="34" t="s">
+        <v>153</v>
+      </c>
+      <c r="C62" s="35" t="s">
+        <v>19</v>
+      </c>
+      <c r="D62" s="36" t="s">
+        <v>31</v>
+      </c>
+      <c r="E62" s="37" t="s">
+        <v>21</v>
+      </c>
+      <c r="F62" s="38" t="s">
+        <v>22</v>
+      </c>
+      <c r="G62" s="39" t="s">
+        <v>136</v>
+      </c>
+      <c r="H62" s="40" t="s">
+        <v>21</v>
+      </c>
+      <c r="I62" s="41" t="s">
+        <v>137</v>
+      </c>
+      <c r="J62" s="42" t="s">
+        <v>121</v>
+      </c>
+      <c r="K62" s="43" t="s">
+        <v>122</v>
+      </c>
+      <c r="L62" s="44" t="s">
+        <v>123</v>
+      </c>
+      <c r="M62" s="45">
+        <v>46175</v>
+      </c>
+      <c r="N62" s="46">
+        <v>46175</v>
+      </c>
+      <c r="O62" s="47" t="s">
+        <v>124</v>
+      </c>
+      <c r="P62" s="48" t="s">
+        <v>124</v>
+      </c>
+      <c r="Q62" s="49">
+        <v>46165</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="33" t="s">
+        <v>152</v>
+      </c>
+      <c r="B63" s="34" t="s">
+        <v>153</v>
+      </c>
+      <c r="C63" s="35" t="s">
+        <v>19</v>
+      </c>
+      <c r="D63" s="36" t="s">
+        <v>31</v>
+      </c>
+      <c r="E63" s="37" t="s">
+        <v>21</v>
+      </c>
+      <c r="F63" s="38" t="s">
+        <v>22</v>
+      </c>
+      <c r="G63" s="39" t="s">
+        <v>138</v>
+      </c>
+      <c r="H63" s="40" t="s">
+        <v>21</v>
+      </c>
+      <c r="I63" s="41" t="s">
+        <v>137</v>
+      </c>
+      <c r="J63" s="42" t="s">
+        <v>121</v>
+      </c>
+      <c r="K63" s="43" t="s">
+        <v>122</v>
+      </c>
+      <c r="L63" s="44" t="s">
+        <v>123</v>
+      </c>
+      <c r="M63" s="45">
+        <v>46175</v>
+      </c>
+      <c r="N63" s="46">
+        <v>46175</v>
+      </c>
+      <c r="O63" s="47" t="s">
+        <v>124</v>
+      </c>
+      <c r="P63" s="48" t="s">
+        <v>124</v>
+      </c>
+      <c r="Q63" s="49">
+        <v>46165</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="33" t="s">
+        <v>152</v>
+      </c>
+      <c r="B64" s="34" t="s">
+        <v>153</v>
+      </c>
+      <c r="C64" s="35" t="s">
+        <v>19</v>
+      </c>
+      <c r="D64" s="36" t="s">
+        <v>31</v>
+      </c>
+      <c r="E64" s="37" t="s">
+        <v>21</v>
+      </c>
+      <c r="F64" s="38" t="s">
+        <v>22</v>
+      </c>
+      <c r="G64" s="39" t="s">
+        <v>139</v>
+      </c>
+      <c r="H64" s="40" t="s">
+        <v>21</v>
+      </c>
+      <c r="I64" s="41" t="s">
+        <v>125</v>
+      </c>
+      <c r="J64" s="42" t="s">
+        <v>121</v>
+      </c>
+      <c r="K64" s="43" t="s">
+        <v>122</v>
+      </c>
+      <c r="L64" s="44" t="s">
+        <v>123</v>
+      </c>
+      <c r="M64" s="45">
+        <v>46175</v>
+      </c>
+      <c r="N64" s="46">
+        <v>46175</v>
+      </c>
+      <c r="O64" s="47" t="s">
+        <v>124</v>
+      </c>
+      <c r="P64" s="48" t="s">
+        <v>124</v>
+      </c>
+      <c r="Q64" s="49">
+        <v>46165</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="33" t="s">
+        <v>152</v>
+      </c>
+      <c r="B65" s="34" t="s">
+        <v>153</v>
+      </c>
+      <c r="C65" s="35" t="s">
+        <v>19</v>
+      </c>
+      <c r="D65" s="36" t="s">
+        <v>31</v>
+      </c>
+      <c r="E65" s="37" t="s">
+        <v>21</v>
+      </c>
+      <c r="F65" s="38" t="s">
+        <v>22</v>
+      </c>
+      <c r="G65" s="39" t="s">
+        <v>140</v>
+      </c>
+      <c r="H65" s="40" t="s">
+        <v>21</v>
+      </c>
+      <c r="I65" s="41" t="s">
+        <v>137</v>
+      </c>
+      <c r="J65" s="42" t="s">
+        <v>121</v>
+      </c>
+      <c r="K65" s="43" t="s">
+        <v>122</v>
+      </c>
+      <c r="L65" s="44" t="s">
+        <v>123</v>
+      </c>
+      <c r="M65" s="45">
+        <v>46175</v>
+      </c>
+      <c r="N65" s="46">
+        <v>46175</v>
+      </c>
+      <c r="O65" s="47" t="s">
+        <v>124</v>
+      </c>
+      <c r="P65" s="48" t="s">
+        <v>124</v>
+      </c>
+      <c r="Q65" s="49">
+        <v>46165</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" s="33" t="s">
+        <v>152</v>
+      </c>
+      <c r="B66" s="34" t="s">
+        <v>153</v>
+      </c>
+      <c r="C66" s="35" t="s">
+        <v>19</v>
+      </c>
+      <c r="D66" s="36" t="s">
+        <v>31</v>
+      </c>
+      <c r="E66" s="37" t="s">
+        <v>21</v>
+      </c>
+      <c r="F66" s="38" t="s">
+        <v>22</v>
+      </c>
+      <c r="G66" s="39" t="s">
+        <v>141</v>
+      </c>
+      <c r="H66" s="40" t="s">
+        <v>21</v>
+      </c>
+      <c r="I66" s="41" t="s">
+        <v>128</v>
+      </c>
+      <c r="J66" s="42" t="s">
+        <v>121</v>
+      </c>
+      <c r="K66" s="43" t="s">
+        <v>122</v>
+      </c>
+      <c r="L66" s="44" t="s">
+        <v>123</v>
+      </c>
+      <c r="M66" s="45">
+        <v>46175</v>
+      </c>
+      <c r="N66" s="46">
+        <v>46175</v>
+      </c>
+      <c r="O66" s="47" t="s">
+        <v>124</v>
+      </c>
+      <c r="P66" s="48" t="s">
+        <v>124</v>
+      </c>
+      <c r="Q66" s="49">
+        <v>46165</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" s="33" t="s">
+        <v>152</v>
+      </c>
+      <c r="B67" s="34" t="s">
+        <v>153</v>
+      </c>
+      <c r="C67" s="35" t="s">
+        <v>19</v>
+      </c>
+      <c r="D67" s="36" t="s">
+        <v>31</v>
+      </c>
+      <c r="E67" s="37" t="s">
+        <v>21</v>
+      </c>
+      <c r="F67" s="38" t="s">
+        <v>22</v>
+      </c>
+      <c r="G67" s="39" t="s">
+        <v>142</v>
+      </c>
+      <c r="H67" s="40" t="s">
+        <v>21</v>
+      </c>
+      <c r="I67" s="41" t="s">
+        <v>128</v>
+      </c>
+      <c r="J67" s="42" t="s">
+        <v>121</v>
+      </c>
+      <c r="K67" s="43" t="s">
+        <v>122</v>
+      </c>
+      <c r="L67" s="44" t="s">
+        <v>123</v>
+      </c>
+      <c r="M67" s="45">
+        <v>46175</v>
+      </c>
+      <c r="N67" s="46">
+        <v>46175</v>
+      </c>
+      <c r="O67" s="47" t="s">
+        <v>124</v>
+      </c>
+      <c r="P67" s="48" t="s">
+        <v>124</v>
+      </c>
+      <c r="Q67" s="49">
+        <v>46165</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" s="33" t="s">
+        <v>152</v>
+      </c>
+      <c r="B68" s="34" t="s">
+        <v>153</v>
+      </c>
+      <c r="C68" s="35" t="s">
+        <v>19</v>
+      </c>
+      <c r="D68" s="36" t="s">
+        <v>31</v>
+      </c>
+      <c r="E68" s="37" t="s">
+        <v>21</v>
+      </c>
+      <c r="F68" s="38" t="s">
+        <v>22</v>
+      </c>
+      <c r="G68" s="39" t="s">
+        <v>143</v>
+      </c>
+      <c r="H68" s="40" t="s">
+        <v>21</v>
+      </c>
+      <c r="I68" s="41" t="s">
+        <v>128</v>
+      </c>
+      <c r="J68" s="42" t="s">
+        <v>121</v>
+      </c>
+      <c r="K68" s="43" t="s">
+        <v>122</v>
+      </c>
+      <c r="L68" s="44" t="s">
+        <v>123</v>
+      </c>
+      <c r="M68" s="45">
+        <v>46175</v>
+      </c>
+      <c r="N68" s="46">
+        <v>46175</v>
+      </c>
+      <c r="O68" s="47" t="s">
+        <v>124</v>
+      </c>
+      <c r="P68" s="48" t="s">
+        <v>124</v>
+      </c>
+      <c r="Q68" s="49">
+        <v>46165</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" s="33" t="s">
+        <v>152</v>
+      </c>
+      <c r="B69" s="34" t="s">
+        <v>153</v>
+      </c>
+      <c r="C69" s="35" t="s">
+        <v>19</v>
+      </c>
+      <c r="D69" s="36" t="s">
+        <v>31</v>
+      </c>
+      <c r="E69" s="37" t="s">
+        <v>21</v>
+      </c>
+      <c r="F69" s="38" t="s">
+        <v>22</v>
+      </c>
+      <c r="G69" s="39" t="s">
+        <v>144</v>
+      </c>
+      <c r="H69" s="40" t="s">
+        <v>21</v>
+      </c>
+      <c r="I69" s="41" t="s">
+        <v>128</v>
+      </c>
+      <c r="J69" s="42" t="s">
+        <v>121</v>
+      </c>
+      <c r="K69" s="43" t="s">
+        <v>122</v>
+      </c>
+      <c r="L69" s="44" t="s">
+        <v>123</v>
+      </c>
+      <c r="M69" s="45">
+        <v>46175</v>
+      </c>
+      <c r="N69" s="46">
+        <v>46175</v>
+      </c>
+      <c r="O69" s="47" t="s">
+        <v>124</v>
+      </c>
+      <c r="P69" s="48" t="s">
+        <v>124</v>
+      </c>
+      <c r="Q69" s="49">
+        <v>46165</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" s="33" t="s">
+        <v>152</v>
+      </c>
+      <c r="B70" s="34" t="s">
+        <v>153</v>
+      </c>
+      <c r="C70" s="35" t="s">
+        <v>19</v>
+      </c>
+      <c r="D70" s="36" t="s">
+        <v>31</v>
+      </c>
+      <c r="E70" s="37" t="s">
+        <v>21</v>
+      </c>
+      <c r="F70" s="38" t="s">
+        <v>22</v>
+      </c>
+      <c r="G70" s="39" t="s">
+        <v>146</v>
+      </c>
+      <c r="H70" s="40" t="s">
+        <v>21</v>
+      </c>
+      <c r="I70" s="41" t="s">
+        <v>128</v>
+      </c>
+      <c r="J70" s="42" t="s">
+        <v>121</v>
+      </c>
+      <c r="K70" s="43" t="s">
+        <v>122</v>
+      </c>
+      <c r="L70" s="44" t="s">
+        <v>123</v>
+      </c>
+      <c r="M70" s="45">
+        <v>46175</v>
+      </c>
+      <c r="N70" s="46">
+        <v>46175</v>
+      </c>
+      <c r="O70" s="47" t="s">
+        <v>124</v>
+      </c>
+      <c r="P70" s="48" t="s">
+        <v>124</v>
+      </c>
+      <c r="Q70" s="49">
+        <v>46165</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" s="33" t="s">
+        <v>152</v>
+      </c>
+      <c r="B71" s="34" t="s">
+        <v>153</v>
+      </c>
+      <c r="C71" s="35" t="s">
+        <v>19</v>
+      </c>
+      <c r="D71" s="36" t="s">
+        <v>31</v>
+      </c>
+      <c r="E71" s="37" t="s">
+        <v>21</v>
+      </c>
+      <c r="F71" s="38" t="s">
+        <v>22</v>
+      </c>
+      <c r="G71" s="39" t="s">
+        <v>147</v>
+      </c>
+      <c r="H71" s="40" t="s">
+        <v>21</v>
+      </c>
+      <c r="I71" s="41" t="s">
+        <v>128</v>
+      </c>
+      <c r="J71" s="42" t="s">
+        <v>121</v>
+      </c>
+      <c r="K71" s="43" t="s">
+        <v>122</v>
+      </c>
+      <c r="L71" s="44" t="s">
+        <v>123</v>
+      </c>
+      <c r="M71" s="45">
+        <v>46175</v>
+      </c>
+      <c r="N71" s="46">
+        <v>46175</v>
+      </c>
+      <c r="O71" s="47" t="s">
+        <v>124</v>
+      </c>
+      <c r="P71" s="48" t="s">
+        <v>124</v>
+      </c>
+      <c r="Q71" s="49">
+        <v>46165</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" s="33" t="s">
+        <v>152</v>
+      </c>
+      <c r="B72" s="34" t="s">
+        <v>153</v>
+      </c>
+      <c r="C72" s="35" t="s">
+        <v>19</v>
+      </c>
+      <c r="D72" s="36" t="s">
+        <v>31</v>
+      </c>
+      <c r="E72" s="37" t="s">
+        <v>21</v>
+      </c>
+      <c r="F72" s="38" t="s">
+        <v>22</v>
+      </c>
+      <c r="G72" s="39" t="s">
+        <v>149</v>
+      </c>
+      <c r="H72" s="40" t="s">
+        <v>21</v>
+      </c>
+      <c r="I72" s="41" t="s">
+        <v>125</v>
+      </c>
+      <c r="J72" s="42" t="s">
+        <v>121</v>
+      </c>
+      <c r="K72" s="43" t="s">
+        <v>122</v>
+      </c>
+      <c r="L72" s="44" t="s">
+        <v>123</v>
+      </c>
+      <c r="M72" s="45">
+        <v>46175</v>
+      </c>
+      <c r="N72" s="46">
+        <v>46175</v>
+      </c>
+      <c r="O72" s="47" t="s">
+        <v>124</v>
+      </c>
+      <c r="P72" s="48" t="s">
+        <v>124</v>
+      </c>
+      <c r="Q72" s="49">
+        <v>46165</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" s="33" t="s">
+        <v>152</v>
+      </c>
+      <c r="B73" s="34" t="s">
+        <v>153</v>
+      </c>
+      <c r="C73" s="35" t="s">
+        <v>19</v>
+      </c>
+      <c r="D73" s="36" t="s">
+        <v>31</v>
+      </c>
+      <c r="E73" s="37" t="s">
+        <v>21</v>
+      </c>
+      <c r="F73" s="38" t="s">
+        <v>22</v>
+      </c>
+      <c r="G73" s="39" t="s">
+        <v>150</v>
+      </c>
+      <c r="H73" s="40" t="s">
+        <v>21</v>
+      </c>
+      <c r="I73" s="41" t="s">
+        <v>137</v>
+      </c>
+      <c r="J73" s="42" t="s">
+        <v>121</v>
+      </c>
+      <c r="K73" s="43" t="s">
+        <v>122</v>
+      </c>
+      <c r="L73" s="44" t="s">
+        <v>123</v>
+      </c>
+      <c r="M73" s="45">
+        <v>46175</v>
+      </c>
+      <c r="N73" s="46">
+        <v>46175</v>
+      </c>
+      <c r="O73" s="47" t="s">
+        <v>124</v>
+      </c>
+      <c r="P73" s="48" t="s">
+        <v>124</v>
+      </c>
+      <c r="Q73" s="49">
+        <v>46165</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" s="33" t="s">
+        <v>152</v>
+      </c>
+      <c r="B74" s="34" t="s">
+        <v>153</v>
+      </c>
+      <c r="C74" s="35" t="s">
+        <v>19</v>
+      </c>
+      <c r="D74" s="36" t="s">
+        <v>31</v>
+      </c>
+      <c r="E74" s="37" t="s">
+        <v>21</v>
+      </c>
+      <c r="F74" s="38" t="s">
+        <v>22</v>
+      </c>
+      <c r="G74" s="39" t="s">
+        <v>155</v>
+      </c>
+      <c r="H74" s="40" t="s">
+        <v>21</v>
+      </c>
+      <c r="I74" s="41" t="s">
+        <v>137</v>
+      </c>
+      <c r="J74" s="42" t="s">
+        <v>121</v>
+      </c>
+      <c r="K74" s="43" t="s">
+        <v>122</v>
+      </c>
+      <c r="L74" s="44" t="s">
+        <v>123</v>
+      </c>
+      <c r="M74" s="45">
+        <v>46175</v>
+      </c>
+      <c r="N74" s="46">
+        <v>46175</v>
+      </c>
+      <c r="O74" s="47" t="s">
+        <v>124</v>
+      </c>
+      <c r="P74" s="48" t="s">
+        <v>124</v>
+      </c>
+      <c r="Q74" s="49">
+        <v>46165</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" s="33" t="s">
+        <v>152</v>
+      </c>
+      <c r="B75" s="34" t="s">
+        <v>153</v>
+      </c>
+      <c r="C75" s="35" t="s">
+        <v>19</v>
+      </c>
+      <c r="D75" s="36" t="s">
+        <v>31</v>
+      </c>
+      <c r="E75" s="37" t="s">
+        <v>88</v>
+      </c>
+      <c r="F75" s="38" t="s">
+        <v>89</v>
+      </c>
+      <c r="G75" s="39" t="s">
+        <v>156</v>
+      </c>
+      <c r="H75" s="40" t="s">
+        <v>88</v>
+      </c>
+      <c r="I75" s="41" t="s">
+        <v>120</v>
+      </c>
+      <c r="J75" s="42" t="s">
+        <v>121</v>
+      </c>
+      <c r="K75" s="43" t="s">
+        <v>122</v>
+      </c>
+      <c r="L75" s="44" t="s">
+        <v>123</v>
+      </c>
+      <c r="M75" s="45">
+        <v>46175</v>
+      </c>
+      <c r="N75" s="46">
+        <v>46175</v>
+      </c>
+      <c r="O75" s="47" t="s">
+        <v>124</v>
+      </c>
+      <c r="P75" s="48" t="s">
+        <v>124</v>
+      </c>
+      <c r="Q75" s="49">
+        <v>46165</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" s="33" t="s">
+        <v>152</v>
+      </c>
+      <c r="B76" s="34" t="s">
+        <v>153</v>
+      </c>
+      <c r="C76" s="35" t="s">
+        <v>19</v>
+      </c>
+      <c r="D76" s="36" t="s">
+        <v>31</v>
+      </c>
+      <c r="E76" s="37" t="s">
+        <v>21</v>
+      </c>
+      <c r="F76" s="38" t="s">
+        <v>22</v>
+      </c>
+      <c r="G76" s="39" t="s">
+        <v>157</v>
+      </c>
+      <c r="H76" s="40" t="s">
+        <v>21</v>
+      </c>
+      <c r="I76" s="41" t="s">
+        <v>137</v>
+      </c>
+      <c r="J76" s="42" t="s">
+        <v>121</v>
+      </c>
+      <c r="K76" s="43" t="s">
+        <v>122</v>
+      </c>
+      <c r="L76" s="44" t="s">
+        <v>123</v>
+      </c>
+      <c r="M76" s="45">
+        <v>46175</v>
+      </c>
+      <c r="N76" s="46">
+        <v>46175</v>
+      </c>
+      <c r="O76" s="47" t="s">
+        <v>124</v>
+      </c>
+      <c r="P76" s="48" t="s">
+        <v>124</v>
+      </c>
+      <c r="Q76" s="49">
+        <v>46165</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" s="33" t="s">
+        <v>152</v>
+      </c>
+      <c r="B77" s="34" t="s">
+        <v>153</v>
+      </c>
+      <c r="C77" s="35" t="s">
+        <v>19</v>
+      </c>
+      <c r="D77" s="36" t="s">
+        <v>31</v>
+      </c>
+      <c r="E77" s="37" t="s">
+        <v>21</v>
+      </c>
+      <c r="F77" s="38" t="s">
+        <v>22</v>
+      </c>
+      <c r="G77" s="39" t="s">
+        <v>158</v>
+      </c>
+      <c r="H77" s="40" t="s">
+        <v>21</v>
+      </c>
+      <c r="I77" s="41" t="s">
+        <v>159</v>
+      </c>
+      <c r="J77" s="42" t="s">
+        <v>121</v>
+      </c>
+      <c r="K77" s="43" t="s">
+        <v>122</v>
+      </c>
+      <c r="L77" s="44" t="s">
+        <v>123</v>
+      </c>
+      <c r="M77" s="45">
+        <v>46175</v>
+      </c>
+      <c r="N77" s="46">
+        <v>46175</v>
+      </c>
+      <c r="O77" s="47" t="s">
+        <v>124</v>
+      </c>
+      <c r="P77" s="48" t="s">
+        <v>124</v>
+      </c>
+      <c r="Q77" s="49">
+        <v>46165</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" s="33" t="s">
+        <v>152</v>
+      </c>
+      <c r="B78" s="34" t="s">
+        <v>153</v>
+      </c>
+      <c r="C78" s="35" t="s">
+        <v>19</v>
+      </c>
+      <c r="D78" s="36" t="s">
+        <v>31</v>
+      </c>
+      <c r="E78" s="37" t="s">
+        <v>21</v>
+      </c>
+      <c r="F78" s="38" t="s">
+        <v>22</v>
+      </c>
+      <c r="G78" s="39" t="s">
+        <v>160</v>
+      </c>
+      <c r="H78" s="40" t="s">
+        <v>21</v>
+      </c>
+      <c r="I78" s="41" t="s">
+        <v>161</v>
+      </c>
+      <c r="J78" s="42" t="s">
+        <v>121</v>
+      </c>
+      <c r="K78" s="43" t="s">
+        <v>122</v>
+      </c>
+      <c r="L78" s="44" t="s">
+        <v>123</v>
+      </c>
+      <c r="M78" s="45">
+        <v>46175</v>
+      </c>
+      <c r="N78" s="46">
+        <v>46175</v>
+      </c>
+      <c r="O78" s="47" t="s">
+        <v>124</v>
+      </c>
+      <c r="P78" s="48" t="s">
+        <v>124</v>
+      </c>
+      <c r="Q78" s="49">
+        <v>46165</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" s="33" t="s">
+        <v>152</v>
+      </c>
+      <c r="B79" s="34" t="s">
+        <v>153</v>
+      </c>
+      <c r="C79" s="35" t="s">
+        <v>19</v>
+      </c>
+      <c r="D79" s="36" t="s">
+        <v>31</v>
+      </c>
+      <c r="E79" s="37" t="s">
+        <v>21</v>
+      </c>
+      <c r="F79" s="38" t="s">
+        <v>22</v>
+      </c>
+      <c r="G79" s="39" t="s">
+        <v>162</v>
+      </c>
+      <c r="H79" s="40" t="s">
+        <v>21</v>
+      </c>
+      <c r="I79" s="41" t="s">
+        <v>161</v>
+      </c>
+      <c r="J79" s="42" t="s">
+        <v>121</v>
+      </c>
+      <c r="K79" s="43" t="s">
+        <v>122</v>
+      </c>
+      <c r="L79" s="44" t="s">
+        <v>123</v>
+      </c>
+      <c r="M79" s="45">
+        <v>46175</v>
+      </c>
+      <c r="N79" s="46">
+        <v>46175</v>
+      </c>
+      <c r="O79" s="47" t="s">
+        <v>124</v>
+      </c>
+      <c r="P79" s="48" t="s">
+        <v>124</v>
+      </c>
+      <c r="Q79" s="49">
+        <v>46165</v>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" s="33" t="s">
+        <v>152</v>
+      </c>
+      <c r="B80" s="34" t="s">
+        <v>153</v>
+      </c>
+      <c r="C80" s="35" t="s">
+        <v>19</v>
+      </c>
+      <c r="D80" s="36" t="s">
+        <v>31</v>
+      </c>
+      <c r="E80" s="37" t="s">
+        <v>21</v>
+      </c>
+      <c r="F80" s="38" t="s">
+        <v>22</v>
+      </c>
+      <c r="G80" s="39" t="s">
+        <v>163</v>
+      </c>
+      <c r="H80" s="40" t="s">
+        <v>21</v>
+      </c>
+      <c r="I80" s="41" t="s">
+        <v>125</v>
+      </c>
+      <c r="J80" s="42" t="s">
+        <v>121</v>
+      </c>
+      <c r="K80" s="43" t="s">
+        <v>122</v>
+      </c>
+      <c r="L80" s="44" t="s">
+        <v>123</v>
+      </c>
+      <c r="M80" s="45">
+        <v>46175</v>
+      </c>
+      <c r="N80" s="46">
+        <v>46175</v>
+      </c>
+      <c r="O80" s="47" t="s">
+        <v>124</v>
+      </c>
+      <c r="P80" s="48" t="s">
+        <v>124</v>
+      </c>
+      <c r="Q80" s="49">
+        <v>46165</v>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" s="33" t="s">
+        <v>152</v>
+      </c>
+      <c r="B81" s="34" t="s">
+        <v>153</v>
+      </c>
+      <c r="C81" s="35" t="s">
+        <v>19</v>
+      </c>
+      <c r="D81" s="36" t="s">
+        <v>31</v>
+      </c>
+      <c r="E81" s="37" t="s">
+        <v>21</v>
+      </c>
+      <c r="F81" s="38" t="s">
+        <v>22</v>
+      </c>
+      <c r="G81" s="39" t="s">
+        <v>164</v>
+      </c>
+      <c r="H81" s="40" t="s">
+        <v>21</v>
+      </c>
+      <c r="I81" s="41" t="s">
+        <v>126</v>
+      </c>
+      <c r="J81" s="42" t="s">
+        <v>121</v>
+      </c>
+      <c r="K81" s="43" t="s">
+        <v>122</v>
+      </c>
+      <c r="L81" s="44" t="s">
+        <v>123</v>
+      </c>
+      <c r="M81" s="45">
+        <v>46175</v>
+      </c>
+      <c r="N81" s="46">
+        <v>46175</v>
+      </c>
+      <c r="O81" s="47" t="s">
+        <v>124</v>
+      </c>
+      <c r="P81" s="48" t="s">
+        <v>124</v>
+      </c>
+      <c r="Q81" s="49">
+        <v>46165</v>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" s="33" t="s">
+        <v>152</v>
+      </c>
+      <c r="B82" s="34" t="s">
+        <v>153</v>
+      </c>
+      <c r="C82" s="35" t="s">
+        <v>19</v>
+      </c>
+      <c r="D82" s="36" t="s">
+        <v>31</v>
+      </c>
+      <c r="E82" s="37" t="s">
+        <v>21</v>
+      </c>
+      <c r="F82" s="38" t="s">
+        <v>22</v>
+      </c>
+      <c r="G82" s="39" t="s">
+        <v>165</v>
+      </c>
+      <c r="H82" s="40" t="s">
+        <v>21</v>
+      </c>
+      <c r="I82" s="41" t="s">
+        <v>137</v>
+      </c>
+      <c r="J82" s="42" t="s">
+        <v>121</v>
+      </c>
+      <c r="K82" s="43" t="s">
+        <v>122</v>
+      </c>
+      <c r="L82" s="44" t="s">
+        <v>123</v>
+      </c>
+      <c r="M82" s="45">
+        <v>46175</v>
+      </c>
+      <c r="N82" s="46">
+        <v>46175</v>
+      </c>
+      <c r="O82" s="47" t="s">
+        <v>124</v>
+      </c>
+      <c r="P82" s="48" t="s">
+        <v>124</v>
+      </c>
+      <c r="Q82" s="49">
+        <v>46165</v>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" s="33" t="s">
+        <v>152</v>
+      </c>
+      <c r="B83" s="34" t="s">
+        <v>153</v>
+      </c>
+      <c r="C83" s="35" t="s">
+        <v>19</v>
+      </c>
+      <c r="D83" s="36" t="s">
+        <v>31</v>
+      </c>
+      <c r="E83" s="37" t="s">
+        <v>21</v>
+      </c>
+      <c r="F83" s="38" t="s">
+        <v>22</v>
+      </c>
+      <c r="G83" s="39" t="s">
+        <v>166</v>
+      </c>
+      <c r="H83" s="40" t="s">
+        <v>21</v>
+      </c>
+      <c r="I83" s="41" t="s">
+        <v>137</v>
+      </c>
+      <c r="J83" s="42" t="s">
+        <v>121</v>
+      </c>
+      <c r="K83" s="43" t="s">
+        <v>122</v>
+      </c>
+      <c r="L83" s="44" t="s">
+        <v>123</v>
+      </c>
+      <c r="M83" s="45">
+        <v>46175</v>
+      </c>
+      <c r="N83" s="46">
+        <v>46175</v>
+      </c>
+      <c r="O83" s="47" t="s">
+        <v>124</v>
+      </c>
+      <c r="P83" s="48" t="s">
+        <v>124</v>
+      </c>
+      <c r="Q83" s="49">
+        <v>46165</v>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" s="33" t="s">
+        <v>152</v>
+      </c>
+      <c r="B84" s="34" t="s">
+        <v>153</v>
+      </c>
+      <c r="C84" s="35" t="s">
+        <v>19</v>
+      </c>
+      <c r="D84" s="36" t="s">
+        <v>31</v>
+      </c>
+      <c r="E84" s="37" t="s">
+        <v>21</v>
+      </c>
+      <c r="F84" s="38" t="s">
+        <v>22</v>
+      </c>
+      <c r="G84" s="39" t="s">
+        <v>167</v>
+      </c>
+      <c r="H84" s="40" t="s">
+        <v>21</v>
+      </c>
+      <c r="I84" s="41" t="s">
+        <v>137</v>
+      </c>
+      <c r="J84" s="42" t="s">
+        <v>121</v>
+      </c>
+      <c r="K84" s="43" t="s">
+        <v>122</v>
+      </c>
+      <c r="L84" s="44" t="s">
+        <v>123</v>
+      </c>
+      <c r="M84" s="45">
+        <v>46175</v>
+      </c>
+      <c r="N84" s="46">
+        <v>46175</v>
+      </c>
+      <c r="O84" s="47" t="s">
+        <v>124</v>
+      </c>
+      <c r="P84" s="48" t="s">
+        <v>124</v>
+      </c>
+      <c r="Q84" s="49">
+        <v>46165</v>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" s="33" t="s">
+        <v>152</v>
+      </c>
+      <c r="B85" s="34" t="s">
+        <v>153</v>
+      </c>
+      <c r="C85" s="35" t="s">
+        <v>19</v>
+      </c>
+      <c r="D85" s="36" t="s">
+        <v>31</v>
+      </c>
+      <c r="E85" s="37" t="s">
+        <v>21</v>
+      </c>
+      <c r="F85" s="38" t="s">
+        <v>22</v>
+      </c>
+      <c r="G85" s="39" t="s">
+        <v>168</v>
+      </c>
+      <c r="H85" s="40" t="s">
+        <v>21</v>
+      </c>
+      <c r="I85" s="41" t="s">
+        <v>126</v>
+      </c>
+      <c r="J85" s="42" t="s">
+        <v>121</v>
+      </c>
+      <c r="K85" s="43" t="s">
+        <v>122</v>
+      </c>
+      <c r="L85" s="44" t="s">
+        <v>123</v>
+      </c>
+      <c r="M85" s="45">
+        <v>46175</v>
+      </c>
+      <c r="N85" s="46">
+        <v>46175</v>
+      </c>
+      <c r="O85" s="47" t="s">
+        <v>124</v>
+      </c>
+      <c r="P85" s="48" t="s">
+        <v>124</v>
+      </c>
+      <c r="Q85" s="49">
+        <v>46165</v>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" s="33" t="s">
+        <v>152</v>
+      </c>
+      <c r="B86" s="34" t="s">
+        <v>153</v>
+      </c>
+      <c r="C86" s="35" t="s">
+        <v>19</v>
+      </c>
+      <c r="D86" s="36" t="s">
+        <v>31</v>
+      </c>
+      <c r="E86" s="37" t="s">
+        <v>88</v>
+      </c>
+      <c r="F86" s="38" t="s">
+        <v>89</v>
+      </c>
+      <c r="G86" s="39" t="s">
+        <v>169</v>
+      </c>
+      <c r="H86" s="40" t="s">
+        <v>88</v>
+      </c>
+      <c r="I86" s="41" t="s">
+        <v>120</v>
+      </c>
+      <c r="J86" s="42" t="s">
+        <v>121</v>
+      </c>
+      <c r="K86" s="43" t="s">
+        <v>122</v>
+      </c>
+      <c r="L86" s="44" t="s">
+        <v>123</v>
+      </c>
+      <c r="M86" s="45">
+        <v>46175</v>
+      </c>
+      <c r="N86" s="46">
+        <v>46175</v>
+      </c>
+      <c r="O86" s="47" t="s">
+        <v>124</v>
+      </c>
+      <c r="P86" s="48" t="s">
+        <v>124</v>
+      </c>
+      <c r="Q86" s="49">
+        <v>46165</v>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" s="33" t="s">
+        <v>152</v>
+      </c>
+      <c r="B87" s="34" t="s">
+        <v>153</v>
+      </c>
+      <c r="C87" s="35" t="s">
+        <v>19</v>
+      </c>
+      <c r="D87" s="36" t="s">
+        <v>31</v>
+      </c>
+      <c r="E87" s="37" t="s">
+        <v>21</v>
+      </c>
+      <c r="F87" s="38" t="s">
+        <v>22</v>
+      </c>
+      <c r="G87" s="39" t="s">
+        <v>170</v>
+      </c>
+      <c r="H87" s="40" t="s">
+        <v>21</v>
+      </c>
+      <c r="I87" s="41" t="s">
+        <v>137</v>
+      </c>
+      <c r="J87" s="42" t="s">
+        <v>121</v>
+      </c>
+      <c r="K87" s="43" t="s">
+        <v>122</v>
+      </c>
+      <c r="L87" s="44" t="s">
+        <v>123</v>
+      </c>
+      <c r="M87" s="45">
+        <v>46175</v>
+      </c>
+      <c r="N87" s="46">
+        <v>46175</v>
+      </c>
+      <c r="O87" s="47" t="s">
+        <v>124</v>
+      </c>
+      <c r="P87" s="48" t="s">
+        <v>124</v>
+      </c>
+      <c r="Q87" s="49">
+        <v>46165</v>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" s="33" t="s">
+        <v>152</v>
+      </c>
+      <c r="B88" s="34" t="s">
+        <v>153</v>
+      </c>
+      <c r="C88" s="35" t="s">
+        <v>19</v>
+      </c>
+      <c r="D88" s="36" t="s">
+        <v>31</v>
+      </c>
+      <c r="E88" s="37" t="s">
+        <v>21</v>
+      </c>
+      <c r="F88" s="38" t="s">
+        <v>22</v>
+      </c>
+      <c r="G88" s="39" t="s">
+        <v>171</v>
+      </c>
+      <c r="H88" s="40" t="s">
+        <v>21</v>
+      </c>
+      <c r="I88" s="41" t="s">
+        <v>161</v>
+      </c>
+      <c r="J88" s="42" t="s">
+        <v>121</v>
+      </c>
+      <c r="K88" s="43" t="s">
+        <v>122</v>
+      </c>
+      <c r="L88" s="44" t="s">
+        <v>123</v>
+      </c>
+      <c r="M88" s="45">
+        <v>46175</v>
+      </c>
+      <c r="N88" s="46">
+        <v>46175</v>
+      </c>
+      <c r="O88" s="47" t="s">
+        <v>124</v>
+      </c>
+      <c r="P88" s="48" t="s">
+        <v>124</v>
+      </c>
+      <c r="Q88" s="49">
+        <v>46165</v>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" s="33" t="s">
+        <v>152</v>
+      </c>
+      <c r="B89" s="34" t="s">
+        <v>153</v>
+      </c>
+      <c r="C89" s="35" t="s">
+        <v>19</v>
+      </c>
+      <c r="D89" s="36" t="s">
+        <v>31</v>
+      </c>
+      <c r="E89" s="37" t="s">
+        <v>88</v>
+      </c>
+      <c r="F89" s="38" t="s">
+        <v>89</v>
+      </c>
+      <c r="G89" s="39" t="s">
+        <v>172</v>
+      </c>
+      <c r="H89" s="40" t="s">
+        <v>88</v>
+      </c>
+      <c r="I89" s="41" t="s">
+        <v>120</v>
+      </c>
+      <c r="J89" s="42" t="s">
+        <v>121</v>
+      </c>
+      <c r="K89" s="43" t="s">
+        <v>122</v>
+      </c>
+      <c r="L89" s="44" t="s">
+        <v>123</v>
+      </c>
+      <c r="M89" s="45">
+        <v>46175</v>
+      </c>
+      <c r="N89" s="46">
+        <v>46175</v>
+      </c>
+      <c r="O89" s="47" t="s">
+        <v>124</v>
+      </c>
+      <c r="P89" s="48" t="s">
+        <v>124</v>
+      </c>
+      <c r="Q89" s="49">
+        <v>46165</v>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" s="33" t="s">
+        <v>152</v>
+      </c>
+      <c r="B90" s="34" t="s">
+        <v>153</v>
+      </c>
+      <c r="C90" s="35" t="s">
+        <v>19</v>
+      </c>
+      <c r="D90" s="36" t="s">
+        <v>31</v>
+      </c>
+      <c r="E90" s="37" t="s">
+        <v>21</v>
+      </c>
+      <c r="F90" s="38" t="s">
+        <v>22</v>
+      </c>
+      <c r="G90" s="39" t="s">
+        <v>173</v>
+      </c>
+      <c r="H90" s="40" t="s">
+        <v>21</v>
+      </c>
+      <c r="I90" s="41" t="s">
+        <v>161</v>
+      </c>
+      <c r="J90" s="42" t="s">
+        <v>121</v>
+      </c>
+      <c r="K90" s="43" t="s">
+        <v>122</v>
+      </c>
+      <c r="L90" s="44" t="s">
+        <v>123</v>
+      </c>
+      <c r="M90" s="45">
+        <v>46175</v>
+      </c>
+      <c r="N90" s="46">
+        <v>46175</v>
+      </c>
+      <c r="O90" s="47" t="s">
+        <v>124</v>
+      </c>
+      <c r="P90" s="48" t="s">
+        <v>124</v>
+      </c>
+      <c r="Q90" s="49">
+        <v>46165</v>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" s="33" t="s">
+        <v>152</v>
+      </c>
+      <c r="B91" s="34" t="s">
+        <v>153</v>
+      </c>
+      <c r="C91" s="35" t="s">
+        <v>19</v>
+      </c>
+      <c r="D91" s="36" t="s">
+        <v>31</v>
+      </c>
+      <c r="E91" s="37" t="s">
+        <v>21</v>
+      </c>
+      <c r="F91" s="38" t="s">
+        <v>22</v>
+      </c>
+      <c r="G91" s="39" t="s">
+        <v>174</v>
+      </c>
+      <c r="H91" s="40" t="s">
+        <v>21</v>
+      </c>
+      <c r="I91" s="41" t="s">
+        <v>161</v>
+      </c>
+      <c r="J91" s="42" t="s">
+        <v>121</v>
+      </c>
+      <c r="K91" s="43" t="s">
+        <v>122</v>
+      </c>
+      <c r="L91" s="44" t="s">
+        <v>123</v>
+      </c>
+      <c r="M91" s="45">
+        <v>46175</v>
+      </c>
+      <c r="N91" s="46">
+        <v>46175</v>
+      </c>
+      <c r="O91" s="47" t="s">
+        <v>124</v>
+      </c>
+      <c r="P91" s="48" t="s">
+        <v>124</v>
+      </c>
+      <c r="Q91" s="49">
+        <v>46165</v>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" s="33" t="s">
+        <v>152</v>
+      </c>
+      <c r="B92" s="34" t="s">
+        <v>153</v>
+      </c>
+      <c r="C92" s="35" t="s">
+        <v>19</v>
+      </c>
+      <c r="D92" s="36" t="s">
+        <v>31</v>
+      </c>
+      <c r="E92" s="37" t="s">
+        <v>21</v>
+      </c>
+      <c r="F92" s="38" t="s">
+        <v>22</v>
+      </c>
+      <c r="G92" s="39" t="s">
+        <v>175</v>
+      </c>
+      <c r="H92" s="40" t="s">
+        <v>21</v>
+      </c>
+      <c r="I92" s="41" t="s">
+        <v>161</v>
+      </c>
+      <c r="J92" s="42" t="s">
+        <v>121</v>
+      </c>
+      <c r="K92" s="43" t="s">
+        <v>122</v>
+      </c>
+      <c r="L92" s="44" t="s">
+        <v>123</v>
+      </c>
+      <c r="M92" s="45">
+        <v>46175</v>
+      </c>
+      <c r="N92" s="46">
+        <v>46175</v>
+      </c>
+      <c r="O92" s="47" t="s">
+        <v>124</v>
+      </c>
+      <c r="P92" s="48" t="s">
+        <v>124</v>
+      </c>
+      <c r="Q92" s="49">
+        <v>46165</v>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" s="33" t="s">
+        <v>152</v>
+      </c>
+      <c r="B93" s="34" t="s">
+        <v>153</v>
+      </c>
+      <c r="C93" s="35" t="s">
+        <v>19</v>
+      </c>
+      <c r="D93" s="36" t="s">
+        <v>31</v>
+      </c>
+      <c r="E93" s="37" t="s">
+        <v>21</v>
+      </c>
+      <c r="F93" s="38" t="s">
+        <v>22</v>
+      </c>
+      <c r="G93" s="39" t="s">
+        <v>176</v>
+      </c>
+      <c r="H93" s="40" t="s">
+        <v>21</v>
+      </c>
+      <c r="I93" s="41" t="s">
+        <v>137</v>
+      </c>
+      <c r="J93" s="42" t="s">
+        <v>121</v>
+      </c>
+      <c r="K93" s="43" t="s">
+        <v>122</v>
+      </c>
+      <c r="L93" s="44" t="s">
+        <v>123</v>
+      </c>
+      <c r="M93" s="45">
+        <v>46175</v>
+      </c>
+      <c r="N93" s="46">
+        <v>46175</v>
+      </c>
+      <c r="O93" s="47" t="s">
+        <v>124</v>
+      </c>
+      <c r="P93" s="48" t="s">
+        <v>124</v>
+      </c>
+      <c r="Q93" s="49">
+        <v>46165</v>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" s="33" t="s">
+        <v>152</v>
+      </c>
+      <c r="B94" s="34" t="s">
+        <v>153</v>
+      </c>
+      <c r="C94" s="35" t="s">
+        <v>19</v>
+      </c>
+      <c r="D94" s="36" t="s">
+        <v>31</v>
+      </c>
+      <c r="E94" s="37" t="s">
+        <v>21</v>
+      </c>
+      <c r="F94" s="38" t="s">
+        <v>22</v>
+      </c>
+      <c r="G94" s="39" t="s">
+        <v>177</v>
+      </c>
+      <c r="H94" s="40" t="s">
+        <v>21</v>
+      </c>
+      <c r="I94" s="41" t="s">
+        <v>137</v>
+      </c>
+      <c r="J94" s="42" t="s">
+        <v>121</v>
+      </c>
+      <c r="K94" s="43" t="s">
+        <v>122</v>
+      </c>
+      <c r="L94" s="44" t="s">
+        <v>123</v>
+      </c>
+      <c r="M94" s="45">
+        <v>46175</v>
+      </c>
+      <c r="N94" s="46">
+        <v>46175</v>
+      </c>
+      <c r="O94" s="47" t="s">
+        <v>124</v>
+      </c>
+      <c r="P94" s="48" t="s">
+        <v>124</v>
+      </c>
+      <c r="Q94" s="49">
+        <v>46165</v>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" s="33" t="s">
+        <v>152</v>
+      </c>
+      <c r="B95" s="34" t="s">
+        <v>153</v>
+      </c>
+      <c r="C95" s="35" t="s">
+        <v>19</v>
+      </c>
+      <c r="D95" s="36" t="s">
+        <v>31</v>
+      </c>
+      <c r="E95" s="37" t="s">
+        <v>21</v>
+      </c>
+      <c r="F95" s="38" t="s">
+        <v>22</v>
+      </c>
+      <c r="G95" s="39" t="s">
+        <v>178</v>
+      </c>
+      <c r="H95" s="40" t="s">
+        <v>21</v>
+      </c>
+      <c r="I95" s="41" t="s">
+        <v>137</v>
+      </c>
+      <c r="J95" s="42" t="s">
+        <v>121</v>
+      </c>
+      <c r="K95" s="43" t="s">
+        <v>122</v>
+      </c>
+      <c r="L95" s="44" t="s">
+        <v>123</v>
+      </c>
+      <c r="M95" s="45">
+        <v>46175</v>
+      </c>
+      <c r="N95" s="46">
+        <v>46175</v>
+      </c>
+      <c r="O95" s="47" t="s">
+        <v>124</v>
+      </c>
+      <c r="P95" s="48" t="s">
+        <v>124</v>
+      </c>
+      <c r="Q95" s="49">
+        <v>46165</v>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" s="33" t="s">
+        <v>152</v>
+      </c>
+      <c r="B96" s="34" t="s">
+        <v>153</v>
+      </c>
+      <c r="C96" s="35" t="s">
+        <v>19</v>
+      </c>
+      <c r="D96" s="36" t="s">
+        <v>31</v>
+      </c>
+      <c r="E96" s="37" t="s">
+        <v>21</v>
+      </c>
+      <c r="F96" s="38" t="s">
+        <v>22</v>
+      </c>
+      <c r="G96" s="39" t="s">
+        <v>179</v>
+      </c>
+      <c r="H96" s="40" t="s">
+        <v>21</v>
+      </c>
+      <c r="I96" s="41" t="s">
+        <v>137</v>
+      </c>
+      <c r="J96" s="42" t="s">
+        <v>121</v>
+      </c>
+      <c r="K96" s="43" t="s">
+        <v>122</v>
+      </c>
+      <c r="L96" s="44" t="s">
+        <v>123</v>
+      </c>
+      <c r="M96" s="45">
+        <v>46175</v>
+      </c>
+      <c r="N96" s="46">
+        <v>46175</v>
+      </c>
+      <c r="O96" s="47" t="s">
+        <v>124</v>
+      </c>
+      <c r="P96" s="48" t="s">
+        <v>124</v>
+      </c>
+      <c r="Q96" s="49">
+        <v>46165</v>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" s="33" t="s">
+        <v>152</v>
+      </c>
+      <c r="B97" s="34" t="s">
+        <v>153</v>
+      </c>
+      <c r="C97" s="35" t="s">
+        <v>19</v>
+      </c>
+      <c r="D97" s="36" t="s">
+        <v>31</v>
+      </c>
+      <c r="E97" s="37" t="s">
+        <v>21</v>
+      </c>
+      <c r="F97" s="38" t="s">
+        <v>22</v>
+      </c>
+      <c r="G97" s="39" t="s">
+        <v>180</v>
+      </c>
+      <c r="H97" s="40" t="s">
+        <v>21</v>
+      </c>
+      <c r="I97" s="41" t="s">
+        <v>137</v>
+      </c>
+      <c r="J97" s="42" t="s">
+        <v>121</v>
+      </c>
+      <c r="K97" s="43" t="s">
+        <v>122</v>
+      </c>
+      <c r="L97" s="44" t="s">
+        <v>123</v>
+      </c>
+      <c r="M97" s="45">
+        <v>46175</v>
+      </c>
+      <c r="N97" s="46">
+        <v>46175</v>
+      </c>
+      <c r="O97" s="47" t="s">
+        <v>124</v>
+      </c>
+      <c r="P97" s="48" t="s">
+        <v>124</v>
+      </c>
+      <c r="Q97" s="49">
+        <v>46165</v>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" s="33" t="s">
+        <v>152</v>
+      </c>
+      <c r="B98" s="34" t="s">
+        <v>153</v>
+      </c>
+      <c r="C98" s="35" t="s">
+        <v>19</v>
+      </c>
+      <c r="D98" s="36" t="s">
+        <v>31</v>
+      </c>
+      <c r="E98" s="37" t="s">
+        <v>21</v>
+      </c>
+      <c r="F98" s="38" t="s">
+        <v>22</v>
+      </c>
+      <c r="G98" s="39" t="s">
+        <v>181</v>
+      </c>
+      <c r="H98" s="40" t="s">
+        <v>21</v>
+      </c>
+      <c r="I98" s="41" t="s">
+        <v>137</v>
+      </c>
+      <c r="J98" s="42" t="s">
+        <v>121</v>
+      </c>
+      <c r="K98" s="43" t="s">
+        <v>122</v>
+      </c>
+      <c r="L98" s="44" t="s">
+        <v>123</v>
+      </c>
+      <c r="M98" s="45">
+        <v>46175</v>
+      </c>
+      <c r="N98" s="46">
+        <v>46175</v>
+      </c>
+      <c r="O98" s="47" t="s">
+        <v>124</v>
+      </c>
+      <c r="P98" s="48" t="s">
+        <v>124</v>
+      </c>
+      <c r="Q98" s="49">
+        <v>46165</v>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" s="33" t="s">
+        <v>152</v>
+      </c>
+      <c r="B99" s="34" t="s">
+        <v>153</v>
+      </c>
+      <c r="C99" s="35" t="s">
+        <v>19</v>
+      </c>
+      <c r="D99" s="36" t="s">
+        <v>31</v>
+      </c>
+      <c r="E99" s="37" t="s">
+        <v>21</v>
+      </c>
+      <c r="F99" s="38" t="s">
+        <v>22</v>
+      </c>
+      <c r="G99" s="39" t="s">
+        <v>182</v>
+      </c>
+      <c r="H99" s="40" t="s">
+        <v>21</v>
+      </c>
+      <c r="I99" s="41" t="s">
+        <v>137</v>
+      </c>
+      <c r="J99" s="42" t="s">
+        <v>121</v>
+      </c>
+      <c r="K99" s="43" t="s">
+        <v>122</v>
+      </c>
+      <c r="L99" s="44" t="s">
+        <v>123</v>
+      </c>
+      <c r="M99" s="45">
+        <v>46175</v>
+      </c>
+      <c r="N99" s="46">
+        <v>46175</v>
+      </c>
+      <c r="O99" s="47" t="s">
+        <v>124</v>
+      </c>
+      <c r="P99" s="48" t="s">
+        <v>124</v>
+      </c>
+      <c r="Q99" s="49">
+        <v>46165</v>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" s="33" t="s">
+        <v>152</v>
+      </c>
+      <c r="B100" s="34" t="s">
+        <v>153</v>
+      </c>
+      <c r="C100" s="35" t="s">
+        <v>19</v>
+      </c>
+      <c r="D100" s="36" t="s">
+        <v>31</v>
+      </c>
+      <c r="E100" s="37" t="s">
+        <v>21</v>
+      </c>
+      <c r="F100" s="38" t="s">
+        <v>22</v>
+      </c>
+      <c r="G100" s="39" t="s">
+        <v>183</v>
+      </c>
+      <c r="H100" s="40" t="s">
+        <v>21</v>
+      </c>
+      <c r="I100" s="41" t="s">
+        <v>159</v>
+      </c>
+      <c r="J100" s="42" t="s">
+        <v>121</v>
+      </c>
+      <c r="K100" s="43" t="s">
+        <v>122</v>
+      </c>
+      <c r="L100" s="44" t="s">
+        <v>123</v>
+      </c>
+      <c r="M100" s="45">
+        <v>46175</v>
+      </c>
+      <c r="N100" s="46">
+        <v>46175</v>
+      </c>
+      <c r="O100" s="47" t="s">
+        <v>124</v>
+      </c>
+      <c r="P100" s="48" t="s">
+        <v>124</v>
+      </c>
+      <c r="Q100" s="49">
+        <v>46165</v>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" s="33" t="s">
+        <v>152</v>
+      </c>
+      <c r="B101" s="34" t="s">
+        <v>153</v>
+      </c>
+      <c r="C101" s="35" t="s">
+        <v>19</v>
+      </c>
+      <c r="D101" s="36" t="s">
+        <v>31</v>
+      </c>
+      <c r="E101" s="37" t="s">
+        <v>21</v>
+      </c>
+      <c r="F101" s="38" t="s">
+        <v>22</v>
+      </c>
+      <c r="G101" s="39" t="s">
+        <v>184</v>
+      </c>
+      <c r="H101" s="40" t="s">
+        <v>21</v>
+      </c>
+      <c r="I101" s="41" t="s">
+        <v>159</v>
+      </c>
+      <c r="J101" s="42" t="s">
+        <v>121</v>
+      </c>
+      <c r="K101" s="43" t="s">
+        <v>122</v>
+      </c>
+      <c r="L101" s="44" t="s">
+        <v>123</v>
+      </c>
+      <c r="M101" s="45">
+        <v>46175</v>
+      </c>
+      <c r="N101" s="46">
+        <v>46175</v>
+      </c>
+      <c r="O101" s="47" t="s">
+        <v>124</v>
+      </c>
+      <c r="P101" s="48" t="s">
+        <v>124</v>
+      </c>
+      <c r="Q101" s="49">
+        <v>46165</v>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" s="33" t="s">
+        <v>152</v>
+      </c>
+      <c r="B102" s="34" t="s">
+        <v>153</v>
+      </c>
+      <c r="C102" s="35" t="s">
+        <v>19</v>
+      </c>
+      <c r="D102" s="36" t="s">
+        <v>31</v>
+      </c>
+      <c r="E102" s="37" t="s">
+        <v>21</v>
+      </c>
+      <c r="F102" s="38" t="s">
+        <v>22</v>
+      </c>
+      <c r="G102" s="39" t="s">
+        <v>185</v>
+      </c>
+      <c r="H102" s="40" t="s">
+        <v>21</v>
+      </c>
+      <c r="I102" s="41" t="s">
+        <v>159</v>
+      </c>
+      <c r="J102" s="42" t="s">
+        <v>121</v>
+      </c>
+      <c r="K102" s="43" t="s">
+        <v>122</v>
+      </c>
+      <c r="L102" s="44" t="s">
+        <v>123</v>
+      </c>
+      <c r="M102" s="45">
+        <v>46175</v>
+      </c>
+      <c r="N102" s="46">
+        <v>46175</v>
+      </c>
+      <c r="O102" s="47" t="s">
+        <v>124</v>
+      </c>
+      <c r="P102" s="48" t="s">
+        <v>124</v>
+      </c>
+      <c r="Q102" s="49">
+        <v>46165</v>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" s="33" t="s">
+        <v>152</v>
+      </c>
+      <c r="B103" s="34" t="s">
+        <v>153</v>
+      </c>
+      <c r="C103" s="35" t="s">
+        <v>19</v>
+      </c>
+      <c r="D103" s="36" t="s">
+        <v>31</v>
+      </c>
+      <c r="E103" s="37" t="s">
+        <v>21</v>
+      </c>
+      <c r="F103" s="38" t="s">
+        <v>22</v>
+      </c>
+      <c r="G103" s="39" t="s">
+        <v>186</v>
+      </c>
+      <c r="H103" s="40" t="s">
+        <v>21</v>
+      </c>
+      <c r="I103" s="41" t="s">
+        <v>159</v>
+      </c>
+      <c r="J103" s="42" t="s">
+        <v>121</v>
+      </c>
+      <c r="K103" s="43" t="s">
+        <v>122</v>
+      </c>
+      <c r="L103" s="44" t="s">
+        <v>123</v>
+      </c>
+      <c r="M103" s="45">
+        <v>46175</v>
+      </c>
+      <c r="N103" s="46">
+        <v>46175</v>
+      </c>
+      <c r="O103" s="47" t="s">
+        <v>124</v>
+      </c>
+      <c r="P103" s="48" t="s">
+        <v>124</v>
+      </c>
+      <c r="Q103" s="49">
+        <v>46165</v>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" s="33" t="s">
+        <v>152</v>
+      </c>
+      <c r="B104" s="34" t="s">
+        <v>153</v>
+      </c>
+      <c r="C104" s="35" t="s">
+        <v>19</v>
+      </c>
+      <c r="D104" s="36" t="s">
+        <v>31</v>
+      </c>
+      <c r="E104" s="37" t="s">
+        <v>21</v>
+      </c>
+      <c r="F104" s="38" t="s">
+        <v>22</v>
+      </c>
+      <c r="G104" s="39" t="s">
+        <v>187</v>
+      </c>
+      <c r="H104" s="40" t="s">
+        <v>21</v>
+      </c>
+      <c r="I104" s="41" t="s">
+        <v>159</v>
+      </c>
+      <c r="J104" s="42" t="s">
+        <v>121</v>
+      </c>
+      <c r="K104" s="43" t="s">
+        <v>122</v>
+      </c>
+      <c r="L104" s="44" t="s">
+        <v>123</v>
+      </c>
+      <c r="M104" s="45">
+        <v>46175</v>
+      </c>
+      <c r="N104" s="46">
+        <v>46175</v>
+      </c>
+      <c r="O104" s="47" t="s">
+        <v>124</v>
+      </c>
+      <c r="P104" s="48" t="s">
+        <v>124</v>
+      </c>
+      <c r="Q104" s="49">
+        <v>46165</v>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" s="33" t="s">
+        <v>152</v>
+      </c>
+      <c r="B105" s="34" t="s">
+        <v>153</v>
+      </c>
+      <c r="C105" s="35" t="s">
+        <v>19</v>
+      </c>
+      <c r="D105" s="36" t="s">
+        <v>31</v>
+      </c>
+      <c r="E105" s="37" t="s">
+        <v>21</v>
+      </c>
+      <c r="F105" s="38" t="s">
+        <v>22</v>
+      </c>
+      <c r="G105" s="39" t="s">
+        <v>188</v>
+      </c>
+      <c r="H105" s="40" t="s">
+        <v>21</v>
+      </c>
+      <c r="I105" s="41" t="s">
+        <v>159</v>
+      </c>
+      <c r="J105" s="42" t="s">
+        <v>121</v>
+      </c>
+      <c r="K105" s="43" t="s">
+        <v>122</v>
+      </c>
+      <c r="L105" s="44" t="s">
+        <v>123</v>
+      </c>
+      <c r="M105" s="45">
+        <v>46175</v>
+      </c>
+      <c r="N105" s="46">
+        <v>46175</v>
+      </c>
+      <c r="O105" s="47" t="s">
+        <v>124</v>
+      </c>
+      <c r="P105" s="48" t="s">
+        <v>124</v>
+      </c>
+      <c r="Q105" s="49">
+        <v>46165</v>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" s="33" t="s">
+        <v>152</v>
+      </c>
+      <c r="B106" s="34" t="s">
+        <v>153</v>
+      </c>
+      <c r="C106" s="35" t="s">
+        <v>19</v>
+      </c>
+      <c r="D106" s="36" t="s">
+        <v>31</v>
+      </c>
+      <c r="E106" s="37" t="s">
+        <v>21</v>
+      </c>
+      <c r="F106" s="38" t="s">
+        <v>22</v>
+      </c>
+      <c r="G106" s="39" t="s">
+        <v>189</v>
+      </c>
+      <c r="H106" s="40" t="s">
+        <v>21</v>
+      </c>
+      <c r="I106" s="41" t="s">
+        <v>125</v>
+      </c>
+      <c r="J106" s="42" t="s">
+        <v>121</v>
+      </c>
+      <c r="K106" s="43" t="s">
+        <v>122</v>
+      </c>
+      <c r="L106" s="44" t="s">
+        <v>123</v>
+      </c>
+      <c r="M106" s="45">
+        <v>46175</v>
+      </c>
+      <c r="N106" s="46">
+        <v>46175</v>
+      </c>
+      <c r="O106" s="47" t="s">
+        <v>124</v>
+      </c>
+      <c r="P106" s="48" t="s">
+        <v>124</v>
+      </c>
+      <c r="Q106" s="49">
+        <v>46165</v>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" s="33" t="s">
+        <v>152</v>
+      </c>
+      <c r="B107" s="34" t="s">
+        <v>153</v>
+      </c>
+      <c r="C107" s="35" t="s">
+        <v>19</v>
+      </c>
+      <c r="D107" s="36" t="s">
+        <v>31</v>
+      </c>
+      <c r="E107" s="37" t="s">
+        <v>21</v>
+      </c>
+      <c r="F107" s="38" t="s">
+        <v>22</v>
+      </c>
+      <c r="G107" s="39" t="s">
+        <v>190</v>
+      </c>
+      <c r="H107" s="40" t="s">
+        <v>21</v>
+      </c>
+      <c r="I107" s="41" t="s">
+        <v>128</v>
+      </c>
+      <c r="J107" s="42" t="s">
+        <v>121</v>
+      </c>
+      <c r="K107" s="43" t="s">
+        <v>122</v>
+      </c>
+      <c r="L107" s="44" t="s">
+        <v>123</v>
+      </c>
+      <c r="M107" s="45">
+        <v>46175</v>
+      </c>
+      <c r="N107" s="46">
+        <v>46175</v>
+      </c>
+      <c r="O107" s="47" t="s">
+        <v>124</v>
+      </c>
+      <c r="P107" s="48" t="s">
+        <v>124</v>
+      </c>
+      <c r="Q107" s="49">
+        <v>46165</v>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" s="33" t="s">
+        <v>152</v>
+      </c>
+      <c r="B108" s="34" t="s">
+        <v>153</v>
+      </c>
+      <c r="C108" s="35" t="s">
+        <v>19</v>
+      </c>
+      <c r="D108" s="36" t="s">
+        <v>31</v>
+      </c>
+      <c r="E108" s="37" t="s">
+        <v>21</v>
+      </c>
+      <c r="F108" s="38" t="s">
+        <v>22</v>
+      </c>
+      <c r="G108" s="39" t="s">
+        <v>191</v>
+      </c>
+      <c r="H108" s="40" t="s">
+        <v>21</v>
+      </c>
+      <c r="I108" s="41" t="s">
+        <v>128</v>
+      </c>
+      <c r="J108" s="42" t="s">
+        <v>121</v>
+      </c>
+      <c r="K108" s="43" t="s">
+        <v>122</v>
+      </c>
+      <c r="L108" s="44" t="s">
+        <v>123</v>
+      </c>
+      <c r="M108" s="45">
+        <v>46175</v>
+      </c>
+      <c r="N108" s="46">
+        <v>46175</v>
+      </c>
+      <c r="O108" s="47" t="s">
+        <v>124</v>
+      </c>
+      <c r="P108" s="48" t="s">
+        <v>124</v>
+      </c>
+      <c r="Q108" s="49">
+        <v>46165</v>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" s="33" t="s">
+        <v>152</v>
+      </c>
+      <c r="B109" s="34" t="s">
+        <v>153</v>
+      </c>
+      <c r="C109" s="35" t="s">
+        <v>19</v>
+      </c>
+      <c r="D109" s="36" t="s">
+        <v>31</v>
+      </c>
+      <c r="E109" s="37" t="s">
+        <v>21</v>
+      </c>
+      <c r="F109" s="38" t="s">
+        <v>22</v>
+      </c>
+      <c r="G109" s="39" t="s">
+        <v>192</v>
+      </c>
+      <c r="H109" s="40" t="s">
+        <v>21</v>
+      </c>
+      <c r="I109" s="41" t="s">
+        <v>193</v>
+      </c>
+      <c r="J109" s="42" t="s">
+        <v>121</v>
+      </c>
+      <c r="K109" s="43" t="s">
+        <v>122</v>
+      </c>
+      <c r="L109" s="44" t="s">
+        <v>123</v>
+      </c>
+      <c r="M109" s="45">
+        <v>46175</v>
+      </c>
+      <c r="N109" s="46">
+        <v>46175</v>
+      </c>
+      <c r="O109" s="47" t="s">
+        <v>124</v>
+      </c>
+      <c r="P109" s="48" t="s">
+        <v>124</v>
+      </c>
+      <c r="Q109" s="49">
+        <v>46165</v>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" s="33" t="s">
+        <v>152</v>
+      </c>
+      <c r="B110" s="34" t="s">
+        <v>153</v>
+      </c>
+      <c r="C110" s="35" t="s">
+        <v>19</v>
+      </c>
+      <c r="D110" s="36" t="s">
+        <v>31</v>
+      </c>
+      <c r="E110" s="37" t="s">
+        <v>21</v>
+      </c>
+      <c r="F110" s="38" t="s">
+        <v>22</v>
+      </c>
+      <c r="G110" s="39" t="s">
+        <v>194</v>
+      </c>
+      <c r="H110" s="40" t="s">
+        <v>21</v>
+      </c>
+      <c r="I110" s="41" t="s">
+        <v>159</v>
+      </c>
+      <c r="J110" s="42" t="s">
+        <v>121</v>
+      </c>
+      <c r="K110" s="43" t="s">
+        <v>122</v>
+      </c>
+      <c r="L110" s="44" t="s">
+        <v>123</v>
+      </c>
+      <c r="M110" s="45">
+        <v>46175</v>
+      </c>
+      <c r="N110" s="46">
+        <v>46175</v>
+      </c>
+      <c r="O110" s="47" t="s">
+        <v>124</v>
+      </c>
+      <c r="P110" s="48" t="s">
+        <v>124</v>
+      </c>
+      <c r="Q110" s="49">
+        <v>46165</v>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" s="33" t="s">
+        <v>152</v>
+      </c>
+      <c r="B111" s="34" t="s">
+        <v>153</v>
+      </c>
+      <c r="C111" s="35" t="s">
+        <v>19</v>
+      </c>
+      <c r="D111" s="36" t="s">
+        <v>31</v>
+      </c>
+      <c r="E111" s="37" t="s">
+        <v>21</v>
+      </c>
+      <c r="F111" s="38" t="s">
+        <v>22</v>
+      </c>
+      <c r="G111" s="39" t="s">
+        <v>195</v>
+      </c>
+      <c r="H111" s="40" t="s">
+        <v>21</v>
+      </c>
+      <c r="I111" s="41" t="s">
+        <v>159</v>
+      </c>
+      <c r="J111" s="42" t="s">
+        <v>121</v>
+      </c>
+      <c r="K111" s="43" t="s">
+        <v>122</v>
+      </c>
+      <c r="L111" s="44" t="s">
+        <v>123</v>
+      </c>
+      <c r="M111" s="45">
+        <v>46175</v>
+      </c>
+      <c r="N111" s="46">
+        <v>46175</v>
+      </c>
+      <c r="O111" s="47" t="s">
+        <v>124</v>
+      </c>
+      <c r="P111" s="48" t="s">
+        <v>124</v>
+      </c>
+      <c r="Q111" s="49">
+        <v>46165</v>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" s="33" t="s">
+        <v>152</v>
+      </c>
+      <c r="B112" s="34" t="s">
+        <v>153</v>
+      </c>
+      <c r="C112" s="35" t="s">
+        <v>19</v>
+      </c>
+      <c r="D112" s="36" t="s">
+        <v>31</v>
+      </c>
+      <c r="E112" s="37" t="s">
+        <v>21</v>
+      </c>
+      <c r="F112" s="38" t="s">
+        <v>22</v>
+      </c>
+      <c r="G112" s="39" t="s">
+        <v>196</v>
+      </c>
+      <c r="H112" s="40" t="s">
+        <v>21</v>
+      </c>
+      <c r="I112" s="41" t="s">
+        <v>159</v>
+      </c>
+      <c r="J112" s="42" t="s">
+        <v>121</v>
+      </c>
+      <c r="K112" s="43" t="s">
+        <v>122</v>
+      </c>
+      <c r="L112" s="44" t="s">
+        <v>123</v>
+      </c>
+      <c r="M112" s="45">
+        <v>46175</v>
+      </c>
+      <c r="N112" s="46">
+        <v>46175</v>
+      </c>
+      <c r="O112" s="47" t="s">
+        <v>124</v>
+      </c>
+      <c r="P112" s="48" t="s">
+        <v>124</v>
+      </c>
+      <c r="Q112" s="49">
+        <v>46165</v>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" s="33" t="s">
+        <v>152</v>
+      </c>
+      <c r="B113" s="34" t="s">
+        <v>153</v>
+      </c>
+      <c r="C113" s="35" t="s">
+        <v>19</v>
+      </c>
+      <c r="D113" s="36" t="s">
+        <v>31</v>
+      </c>
+      <c r="E113" s="37" t="s">
+        <v>21</v>
+      </c>
+      <c r="F113" s="38" t="s">
+        <v>22</v>
+      </c>
+      <c r="G113" s="39" t="s">
+        <v>197</v>
+      </c>
+      <c r="H113" s="40" t="s">
+        <v>21</v>
+      </c>
+      <c r="I113" s="41" t="s">
+        <v>159</v>
+      </c>
+      <c r="J113" s="42" t="s">
+        <v>121</v>
+      </c>
+      <c r="K113" s="43" t="s">
+        <v>122</v>
+      </c>
+      <c r="L113" s="44" t="s">
+        <v>123</v>
+      </c>
+      <c r="M113" s="45">
+        <v>46175</v>
+      </c>
+      <c r="N113" s="46">
+        <v>46175</v>
+      </c>
+      <c r="O113" s="47" t="s">
+        <v>124</v>
+      </c>
+      <c r="P113" s="48" t="s">
+        <v>124</v>
+      </c>
+      <c r="Q113" s="49">
+        <v>46165</v>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" s="33" t="s">
+        <v>152</v>
+      </c>
+      <c r="B114" s="34" t="s">
+        <v>153</v>
+      </c>
+      <c r="C114" s="35" t="s">
+        <v>19</v>
+      </c>
+      <c r="D114" s="36" t="s">
+        <v>31</v>
+      </c>
+      <c r="E114" s="37" t="s">
+        <v>21</v>
+      </c>
+      <c r="F114" s="38" t="s">
+        <v>22</v>
+      </c>
+      <c r="G114" s="39" t="s">
+        <v>198</v>
+      </c>
+      <c r="H114" s="40" t="s">
+        <v>21</v>
+      </c>
+      <c r="I114" s="41" t="s">
+        <v>159</v>
+      </c>
+      <c r="J114" s="42" t="s">
+        <v>121</v>
+      </c>
+      <c r="K114" s="43" t="s">
+        <v>122</v>
+      </c>
+      <c r="L114" s="44" t="s">
+        <v>123</v>
+      </c>
+      <c r="M114" s="45">
+        <v>46175</v>
+      </c>
+      <c r="N114" s="46">
+        <v>46175</v>
+      </c>
+      <c r="O114" s="47" t="s">
+        <v>124</v>
+      </c>
+      <c r="P114" s="48" t="s">
+        <v>124</v>
+      </c>
+      <c r="Q114" s="49">
+        <v>46165</v>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" s="33" t="s">
+        <v>152</v>
+      </c>
+      <c r="B115" s="34" t="s">
+        <v>153</v>
+      </c>
+      <c r="C115" s="35" t="s">
+        <v>19</v>
+      </c>
+      <c r="D115" s="36" t="s">
+        <v>31</v>
+      </c>
+      <c r="E115" s="37" t="s">
+        <v>88</v>
+      </c>
+      <c r="F115" s="38" t="s">
+        <v>89</v>
+      </c>
+      <c r="G115" s="39" t="s">
+        <v>199</v>
+      </c>
+      <c r="H115" s="40" t="s">
+        <v>88</v>
+      </c>
+      <c r="I115" s="41" t="s">
+        <v>120</v>
+      </c>
+      <c r="J115" s="42" t="s">
+        <v>121</v>
+      </c>
+      <c r="K115" s="43" t="s">
+        <v>122</v>
+      </c>
+      <c r="L115" s="44" t="s">
+        <v>123</v>
+      </c>
+      <c r="M115" s="45">
+        <v>46175</v>
+      </c>
+      <c r="N115" s="46">
+        <v>46175</v>
+      </c>
+      <c r="O115" s="47" t="s">
+        <v>124</v>
+      </c>
+      <c r="P115" s="48" t="s">
+        <v>124</v>
+      </c>
+      <c r="Q115" s="49">
+        <v>46165</v>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" s="33" t="s">
+        <v>152</v>
+      </c>
+      <c r="B116" s="34" t="s">
+        <v>153</v>
+      </c>
+      <c r="C116" s="35" t="s">
+        <v>19</v>
+      </c>
+      <c r="D116" s="36" t="s">
+        <v>31</v>
+      </c>
+      <c r="E116" s="37" t="s">
+        <v>88</v>
+      </c>
+      <c r="F116" s="38" t="s">
+        <v>89</v>
+      </c>
+      <c r="G116" s="39" t="s">
+        <v>200</v>
+      </c>
+      <c r="H116" s="40" t="s">
+        <v>88</v>
+      </c>
+      <c r="I116" s="41" t="s">
+        <v>120</v>
+      </c>
+      <c r="J116" s="42" t="s">
+        <v>121</v>
+      </c>
+      <c r="K116" s="43" t="s">
+        <v>122</v>
+      </c>
+      <c r="L116" s="44" t="s">
+        <v>123</v>
+      </c>
+      <c r="M116" s="45">
+        <v>46175</v>
+      </c>
+      <c r="N116" s="46">
+        <v>46175</v>
+      </c>
+      <c r="O116" s="47" t="s">
+        <v>124</v>
+      </c>
+      <c r="P116" s="48" t="s">
+        <v>124</v>
+      </c>
+      <c r="Q116" s="49">
+        <v>46165</v>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" s="33" t="s">
+        <v>152</v>
+      </c>
+      <c r="B117" s="34" t="s">
+        <v>153</v>
+      </c>
+      <c r="C117" s="35" t="s">
+        <v>19</v>
+      </c>
+      <c r="D117" s="36" t="s">
+        <v>31</v>
+      </c>
+      <c r="E117" s="37" t="s">
+        <v>88</v>
+      </c>
+      <c r="F117" s="38" t="s">
+        <v>89</v>
+      </c>
+      <c r="G117" s="39" t="s">
+        <v>201</v>
+      </c>
+      <c r="H117" s="40" t="s">
+        <v>88</v>
+      </c>
+      <c r="I117" s="41" t="s">
+        <v>120</v>
+      </c>
+      <c r="J117" s="42" t="s">
+        <v>121</v>
+      </c>
+      <c r="K117" s="43" t="s">
+        <v>122</v>
+      </c>
+      <c r="L117" s="44" t="s">
+        <v>123</v>
+      </c>
+      <c r="M117" s="45">
+        <v>46175</v>
+      </c>
+      <c r="N117" s="46">
+        <v>46175</v>
+      </c>
+      <c r="O117" s="47" t="s">
+        <v>124</v>
+      </c>
+      <c r="P117" s="48" t="s">
+        <v>124</v>
+      </c>
+      <c r="Q117" s="49">
+        <v>46165</v>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" s="33" t="s">
+        <v>152</v>
+      </c>
+      <c r="B118" s="34" t="s">
+        <v>153</v>
+      </c>
+      <c r="C118" s="35" t="s">
+        <v>19</v>
+      </c>
+      <c r="D118" s="36" t="s">
+        <v>31</v>
+      </c>
+      <c r="E118" s="37" t="s">
+        <v>21</v>
+      </c>
+      <c r="F118" s="38" t="s">
+        <v>22</v>
+      </c>
+      <c r="G118" s="39" t="s">
+        <v>202</v>
+      </c>
+      <c r="H118" s="40" t="s">
+        <v>21</v>
+      </c>
+      <c r="I118" s="41" t="s">
+        <v>128</v>
+      </c>
+      <c r="J118" s="42" t="s">
+        <v>121</v>
+      </c>
+      <c r="K118" s="43" t="s">
+        <v>122</v>
+      </c>
+      <c r="L118" s="44" t="s">
+        <v>123</v>
+      </c>
+      <c r="M118" s="45">
+        <v>46175</v>
+      </c>
+      <c r="N118" s="46">
+        <v>46175</v>
+      </c>
+      <c r="O118" s="47" t="s">
+        <v>124</v>
+      </c>
+      <c r="P118" s="48" t="s">
+        <v>124</v>
+      </c>
+      <c r="Q118" s="49">
+        <v>46165</v>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" s="33" t="s">
+        <v>152</v>
+      </c>
+      <c r="B119" s="34" t="s">
+        <v>153</v>
+      </c>
+      <c r="C119" s="35" t="s">
+        <v>19</v>
+      </c>
+      <c r="D119" s="36" t="s">
+        <v>31</v>
+      </c>
+      <c r="E119" s="37" t="s">
+        <v>21</v>
+      </c>
+      <c r="F119" s="38" t="s">
+        <v>22</v>
+      </c>
+      <c r="G119" s="39" t="s">
+        <v>203</v>
+      </c>
+      <c r="H119" s="40" t="s">
+        <v>21</v>
+      </c>
+      <c r="I119" s="41" t="s">
+        <v>137</v>
+      </c>
+      <c r="J119" s="42" t="s">
+        <v>121</v>
+      </c>
+      <c r="K119" s="43" t="s">
+        <v>122</v>
+      </c>
+      <c r="L119" s="44" t="s">
+        <v>123</v>
+      </c>
+      <c r="M119" s="45">
+        <v>46175</v>
+      </c>
+      <c r="N119" s="46">
+        <v>46175</v>
+      </c>
+      <c r="O119" s="47" t="s">
+        <v>124</v>
+      </c>
+      <c r="P119" s="48" t="s">
+        <v>124</v>
+      </c>
+      <c r="Q119" s="49">
+        <v>46165</v>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" s="33" t="s">
+        <v>152</v>
+      </c>
+      <c r="B120" s="34" t="s">
+        <v>153</v>
+      </c>
+      <c r="C120" s="35" t="s">
+        <v>19</v>
+      </c>
+      <c r="D120" s="36" t="s">
+        <v>31</v>
+      </c>
+      <c r="E120" s="37" t="s">
+        <v>21</v>
+      </c>
+      <c r="F120" s="38" t="s">
+        <v>22</v>
+      </c>
+      <c r="G120" s="39" t="s">
+        <v>204</v>
+      </c>
+      <c r="H120" s="40" t="s">
+        <v>21</v>
+      </c>
+      <c r="I120" s="41" t="s">
+        <v>137</v>
+      </c>
+      <c r="J120" s="42" t="s">
+        <v>121</v>
+      </c>
+      <c r="K120" s="43" t="s">
+        <v>122</v>
+      </c>
+      <c r="L120" s="44" t="s">
+        <v>123</v>
+      </c>
+      <c r="M120" s="45">
+        <v>46175</v>
+      </c>
+      <c r="N120" s="46">
+        <v>46175</v>
+      </c>
+      <c r="O120" s="47" t="s">
+        <v>124</v>
+      </c>
+      <c r="P120" s="48" t="s">
+        <v>124</v>
+      </c>
+      <c r="Q120" s="49">
+        <v>46165</v>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" s="33" t="s">
+        <v>152</v>
+      </c>
+      <c r="B121" s="34" t="s">
+        <v>153</v>
+      </c>
+      <c r="C121" s="35" t="s">
+        <v>19</v>
+      </c>
+      <c r="D121" s="36" t="s">
+        <v>31</v>
+      </c>
+      <c r="E121" s="37" t="s">
+        <v>21</v>
+      </c>
+      <c r="F121" s="38" t="s">
+        <v>22</v>
+      </c>
+      <c r="G121" s="39" t="s">
+        <v>205</v>
+      </c>
+      <c r="H121" s="40" t="s">
+        <v>21</v>
+      </c>
+      <c r="I121" s="41" t="s">
+        <v>159</v>
+      </c>
+      <c r="J121" s="42" t="s">
+        <v>121</v>
+      </c>
+      <c r="K121" s="43" t="s">
+        <v>122</v>
+      </c>
+      <c r="L121" s="44" t="s">
+        <v>123</v>
+      </c>
+      <c r="M121" s="45">
+        <v>46175</v>
+      </c>
+      <c r="N121" s="46">
+        <v>46175</v>
+      </c>
+      <c r="O121" s="47" t="s">
+        <v>124</v>
+      </c>
+      <c r="P121" s="48" t="s">
+        <v>124</v>
+      </c>
+      <c r="Q121" s="49">
+        <v>46165</v>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" s="33" t="s">
+        <v>152</v>
+      </c>
+      <c r="B122" s="34" t="s">
+        <v>153</v>
+      </c>
+      <c r="C122" s="35" t="s">
+        <v>19</v>
+      </c>
+      <c r="D122" s="36" t="s">
+        <v>31</v>
+      </c>
+      <c r="E122" s="37" t="s">
+        <v>21</v>
+      </c>
+      <c r="F122" s="38" t="s">
+        <v>22</v>
+      </c>
+      <c r="G122" s="39" t="s">
+        <v>206</v>
+      </c>
+      <c r="H122" s="40" t="s">
+        <v>21</v>
+      </c>
+      <c r="I122" s="41" t="s">
+        <v>159</v>
+      </c>
+      <c r="J122" s="42" t="s">
+        <v>121</v>
+      </c>
+      <c r="K122" s="43" t="s">
+        <v>122</v>
+      </c>
+      <c r="L122" s="44" t="s">
+        <v>123</v>
+      </c>
+      <c r="M122" s="45">
+        <v>46175</v>
+      </c>
+      <c r="N122" s="46">
+        <v>46175</v>
+      </c>
+      <c r="O122" s="47" t="s">
+        <v>124</v>
+      </c>
+      <c r="P122" s="48" t="s">
+        <v>124</v>
+      </c>
+      <c r="Q122" s="49">
+        <v>46165</v>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" s="33" t="s">
+        <v>152</v>
+      </c>
+      <c r="B123" s="34" t="s">
+        <v>153</v>
+      </c>
+      <c r="C123" s="35" t="s">
+        <v>19</v>
+      </c>
+      <c r="D123" s="36" t="s">
+        <v>31</v>
+      </c>
+      <c r="E123" s="37" t="s">
+        <v>21</v>
+      </c>
+      <c r="F123" s="38" t="s">
+        <v>22</v>
+      </c>
+      <c r="G123" s="39" t="s">
+        <v>207</v>
+      </c>
+      <c r="H123" s="40" t="s">
+        <v>21</v>
+      </c>
+      <c r="I123" s="41" t="s">
+        <v>128</v>
+      </c>
+      <c r="J123" s="42" t="s">
+        <v>121</v>
+      </c>
+      <c r="K123" s="43" t="s">
+        <v>122</v>
+      </c>
+      <c r="L123" s="44" t="s">
+        <v>123</v>
+      </c>
+      <c r="M123" s="45">
+        <v>46175</v>
+      </c>
+      <c r="N123" s="46">
+        <v>46175</v>
+      </c>
+      <c r="O123" s="47" t="s">
+        <v>124</v>
+      </c>
+      <c r="P123" s="48" t="s">
+        <v>124</v>
+      </c>
+      <c r="Q123" s="49">
+        <v>46165</v>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" s="33" t="s">
+        <v>152</v>
+      </c>
+      <c r="B124" s="34" t="s">
+        <v>153</v>
+      </c>
+      <c r="C124" s="35" t="s">
+        <v>19</v>
+      </c>
+      <c r="D124" s="36" t="s">
+        <v>31</v>
+      </c>
+      <c r="E124" s="37" t="s">
+        <v>21</v>
+      </c>
+      <c r="F124" s="38" t="s">
+        <v>22</v>
+      </c>
+      <c r="G124" s="39" t="s">
+        <v>208</v>
+      </c>
+      <c r="H124" s="40" t="s">
+        <v>21</v>
+      </c>
+      <c r="I124" s="41" t="s">
+        <v>125</v>
+      </c>
+      <c r="J124" s="42" t="s">
+        <v>121</v>
+      </c>
+      <c r="K124" s="43" t="s">
+        <v>122</v>
+      </c>
+      <c r="L124" s="44" t="s">
+        <v>123</v>
+      </c>
+      <c r="M124" s="45">
+        <v>46175</v>
+      </c>
+      <c r="N124" s="46">
+        <v>46175</v>
+      </c>
+      <c r="O124" s="47" t="s">
+        <v>124</v>
+      </c>
+      <c r="P124" s="48" t="s">
+        <v>124</v>
+      </c>
+      <c r="Q124" s="49">
+        <v>46165</v>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" s="33" t="s">
+        <v>152</v>
+      </c>
+      <c r="B125" s="34" t="s">
+        <v>153</v>
+      </c>
+      <c r="C125" s="35" t="s">
+        <v>19</v>
+      </c>
+      <c r="D125" s="36" t="s">
+        <v>31</v>
+      </c>
+      <c r="E125" s="37" t="s">
+        <v>21</v>
+      </c>
+      <c r="F125" s="38" t="s">
+        <v>22</v>
+      </c>
+      <c r="G125" s="39" t="s">
+        <v>209</v>
+      </c>
+      <c r="H125" s="40" t="s">
+        <v>21</v>
+      </c>
+      <c r="I125" s="41" t="s">
+        <v>137</v>
+      </c>
+      <c r="J125" s="42" t="s">
+        <v>121</v>
+      </c>
+      <c r="K125" s="43" t="s">
+        <v>122</v>
+      </c>
+      <c r="L125" s="44" t="s">
+        <v>123</v>
+      </c>
+      <c r="M125" s="45">
+        <v>46175</v>
+      </c>
+      <c r="N125" s="46">
+        <v>46175</v>
+      </c>
+      <c r="O125" s="47" t="s">
+        <v>124</v>
+      </c>
+      <c r="P125" s="48" t="s">
+        <v>124</v>
+      </c>
+      <c r="Q125" s="49">
+        <v>46165</v>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" s="33" t="s">
+        <v>152</v>
+      </c>
+      <c r="B126" s="34" t="s">
+        <v>153</v>
+      </c>
+      <c r="C126" s="35" t="s">
+        <v>19</v>
+      </c>
+      <c r="D126" s="36" t="s">
+        <v>31</v>
+      </c>
+      <c r="E126" s="37" t="s">
+        <v>21</v>
+      </c>
+      <c r="F126" s="38" t="s">
+        <v>22</v>
+      </c>
+      <c r="G126" s="39" t="s">
+        <v>210</v>
+      </c>
+      <c r="H126" s="40" t="s">
+        <v>21</v>
+      </c>
+      <c r="I126" s="41" t="s">
+        <v>159</v>
+      </c>
+      <c r="J126" s="42" t="s">
+        <v>121</v>
+      </c>
+      <c r="K126" s="43" t="s">
+        <v>122</v>
+      </c>
+      <c r="L126" s="44" t="s">
+        <v>123</v>
+      </c>
+      <c r="M126" s="45">
+        <v>46175</v>
+      </c>
+      <c r="N126" s="46">
+        <v>46175</v>
+      </c>
+      <c r="O126" s="47" t="s">
+        <v>124</v>
+      </c>
+      <c r="P126" s="48" t="s">
+        <v>124</v>
+      </c>
+      <c r="Q126" s="49">
+        <v>46165</v>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" s="33" t="s">
+        <v>152</v>
+      </c>
+      <c r="B127" s="34" t="s">
+        <v>153</v>
+      </c>
+      <c r="C127" s="35" t="s">
+        <v>19</v>
+      </c>
+      <c r="D127" s="36" t="s">
+        <v>31</v>
+      </c>
+      <c r="E127" s="37" t="s">
+        <v>21</v>
+      </c>
+      <c r="F127" s="38" t="s">
+        <v>22</v>
+      </c>
+      <c r="G127" s="39" t="s">
+        <v>211</v>
+      </c>
+      <c r="H127" s="40" t="s">
+        <v>21</v>
+      </c>
+      <c r="I127" s="41" t="s">
+        <v>159</v>
+      </c>
+      <c r="J127" s="42" t="s">
+        <v>121</v>
+      </c>
+      <c r="K127" s="43" t="s">
+        <v>122</v>
+      </c>
+      <c r="L127" s="44" t="s">
+        <v>123</v>
+      </c>
+      <c r="M127" s="45">
+        <v>46175</v>
+      </c>
+      <c r="N127" s="46">
+        <v>46175</v>
+      </c>
+      <c r="O127" s="47" t="s">
+        <v>124</v>
+      </c>
+      <c r="P127" s="48" t="s">
+        <v>124</v>
+      </c>
+      <c r="Q127" s="49">
+        <v>46165</v>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" s="33" t="s">
+        <v>152</v>
+      </c>
+      <c r="B128" s="34" t="s">
+        <v>153</v>
+      </c>
+      <c r="C128" s="35" t="s">
+        <v>19</v>
+      </c>
+      <c r="D128" s="36" t="s">
+        <v>31</v>
+      </c>
+      <c r="E128" s="37" t="s">
+        <v>21</v>
+      </c>
+      <c r="F128" s="38" t="s">
+        <v>22</v>
+      </c>
+      <c r="G128" s="39" t="s">
+        <v>212</v>
+      </c>
+      <c r="H128" s="40" t="s">
+        <v>21</v>
+      </c>
+      <c r="I128" s="41" t="s">
+        <v>159</v>
+      </c>
+      <c r="J128" s="42" t="s">
+        <v>121</v>
+      </c>
+      <c r="K128" s="43" t="s">
+        <v>122</v>
+      </c>
+      <c r="L128" s="44" t="s">
+        <v>123</v>
+      </c>
+      <c r="M128" s="45">
+        <v>46175</v>
+      </c>
+      <c r="N128" s="46">
+        <v>46175</v>
+      </c>
+      <c r="O128" s="47" t="s">
+        <v>124</v>
+      </c>
+      <c r="P128" s="48" t="s">
+        <v>124</v>
+      </c>
+      <c r="Q128" s="49">
+        <v>46165</v>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" s="33" t="s">
+        <v>152</v>
+      </c>
+      <c r="B129" s="34" t="s">
+        <v>153</v>
+      </c>
+      <c r="C129" s="35" t="s">
+        <v>19</v>
+      </c>
+      <c r="D129" s="36" t="s">
+        <v>31</v>
+      </c>
+      <c r="E129" s="37" t="s">
+        <v>21</v>
+      </c>
+      <c r="F129" s="38" t="s">
+        <v>22</v>
+      </c>
+      <c r="G129" s="39" t="s">
+        <v>213</v>
+      </c>
+      <c r="H129" s="40" t="s">
+        <v>21</v>
+      </c>
+      <c r="I129" s="41" t="s">
+        <v>128</v>
+      </c>
+      <c r="J129" s="42" t="s">
+        <v>121</v>
+      </c>
+      <c r="K129" s="43" t="s">
+        <v>122</v>
+      </c>
+      <c r="L129" s="44" t="s">
+        <v>123</v>
+      </c>
+      <c r="M129" s="45">
+        <v>46175</v>
+      </c>
+      <c r="N129" s="46">
+        <v>46175</v>
+      </c>
+      <c r="O129" s="47" t="s">
+        <v>124</v>
+      </c>
+      <c r="P129" s="48" t="s">
+        <v>124</v>
+      </c>
+      <c r="Q129" s="49">
+        <v>46165</v>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" s="33" t="s">
+        <v>152</v>
+      </c>
+      <c r="B130" s="34" t="s">
+        <v>153</v>
+      </c>
+      <c r="C130" s="35" t="s">
+        <v>19</v>
+      </c>
+      <c r="D130" s="36" t="s">
+        <v>31</v>
+      </c>
+      <c r="E130" s="37" t="s">
+        <v>21</v>
+      </c>
+      <c r="F130" s="38" t="s">
+        <v>22</v>
+      </c>
+      <c r="G130" s="39" t="s">
+        <v>214</v>
+      </c>
+      <c r="H130" s="40" t="s">
+        <v>21</v>
+      </c>
+      <c r="I130" s="41" t="s">
+        <v>159</v>
+      </c>
+      <c r="J130" s="42" t="s">
+        <v>121</v>
+      </c>
+      <c r="K130" s="43" t="s">
+        <v>122</v>
+      </c>
+      <c r="L130" s="44" t="s">
+        <v>123</v>
+      </c>
+      <c r="M130" s="45">
+        <v>46175</v>
+      </c>
+      <c r="N130" s="46">
+        <v>46175</v>
+      </c>
+      <c r="O130" s="47" t="s">
+        <v>124</v>
+      </c>
+      <c r="P130" s="48" t="s">
+        <v>124</v>
+      </c>
+      <c r="Q130" s="49">
+        <v>46165</v>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" s="33" t="s">
+        <v>152</v>
+      </c>
+      <c r="B131" s="34" t="s">
+        <v>153</v>
+      </c>
+      <c r="C131" s="35" t="s">
+        <v>19</v>
+      </c>
+      <c r="D131" s="36" t="s">
+        <v>31</v>
+      </c>
+      <c r="E131" s="37" t="s">
+        <v>21</v>
+      </c>
+      <c r="F131" s="38" t="s">
+        <v>22</v>
+      </c>
+      <c r="G131" s="39" t="s">
+        <v>215</v>
+      </c>
+      <c r="H131" s="40" t="s">
+        <v>21</v>
+      </c>
+      <c r="I131" s="41" t="s">
+        <v>159</v>
+      </c>
+      <c r="J131" s="42" t="s">
+        <v>121</v>
+      </c>
+      <c r="K131" s="43" t="s">
+        <v>122</v>
+      </c>
+      <c r="L131" s="44" t="s">
+        <v>123</v>
+      </c>
+      <c r="M131" s="45">
+        <v>46175</v>
+      </c>
+      <c r="N131" s="46">
+        <v>46175</v>
+      </c>
+      <c r="O131" s="47" t="s">
+        <v>216</v>
+      </c>
+      <c r="P131" s="48" t="s">
+        <v>216</v>
+      </c>
+      <c r="Q131" s="49">
+        <v>46165</v>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" s="33" t="s">
+        <v>152</v>
+      </c>
+      <c r="B132" s="34" t="s">
+        <v>153</v>
+      </c>
+      <c r="C132" s="35" t="s">
+        <v>19</v>
+      </c>
+      <c r="D132" s="36" t="s">
+        <v>31</v>
+      </c>
+      <c r="E132" s="37" t="s">
+        <v>21</v>
+      </c>
+      <c r="F132" s="38" t="s">
+        <v>22</v>
+      </c>
+      <c r="G132" s="39" t="s">
+        <v>217</v>
+      </c>
+      <c r="H132" s="40" t="s">
+        <v>21</v>
+      </c>
+      <c r="I132" s="41" t="s">
+        <v>159</v>
+      </c>
+      <c r="J132" s="42" t="s">
+        <v>121</v>
+      </c>
+      <c r="K132" s="43" t="s">
+        <v>122</v>
+      </c>
+      <c r="L132" s="44" t="s">
+        <v>123</v>
+      </c>
+      <c r="M132" s="45">
+        <v>46175</v>
+      </c>
+      <c r="N132" s="46">
+        <v>46175</v>
+      </c>
+      <c r="O132" s="47" t="s">
+        <v>216</v>
+      </c>
+      <c r="P132" s="48" t="s">
+        <v>216</v>
+      </c>
+      <c r="Q132" s="49">
+        <v>46165</v>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" s="33" t="s">
+        <v>152</v>
+      </c>
+      <c r="B133" s="34" t="s">
+        <v>153</v>
+      </c>
+      <c r="C133" s="35" t="s">
+        <v>19</v>
+      </c>
+      <c r="D133" s="36" t="s">
+        <v>31</v>
+      </c>
+      <c r="E133" s="37" t="s">
+        <v>21</v>
+      </c>
+      <c r="F133" s="38" t="s">
+        <v>22</v>
+      </c>
+      <c r="G133" s="39" t="s">
+        <v>218</v>
+      </c>
+      <c r="H133" s="40" t="s">
+        <v>21</v>
+      </c>
+      <c r="I133" s="41" t="s">
+        <v>159</v>
+      </c>
+      <c r="J133" s="42" t="s">
+        <v>121</v>
+      </c>
+      <c r="K133" s="43" t="s">
+        <v>122</v>
+      </c>
+      <c r="L133" s="44" t="s">
+        <v>123</v>
+      </c>
+      <c r="M133" s="45">
+        <v>46175</v>
+      </c>
+      <c r="N133" s="46">
+        <v>46175</v>
+      </c>
+      <c r="O133" s="47" t="s">
+        <v>216</v>
+      </c>
+      <c r="P133" s="48" t="s">
+        <v>216</v>
+      </c>
+      <c r="Q133" s="49">
+        <v>46165</v>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" s="33" t="s">
+        <v>152</v>
+      </c>
+      <c r="B134" s="34" t="s">
+        <v>153</v>
+      </c>
+      <c r="C134" s="35" t="s">
+        <v>19</v>
+      </c>
+      <c r="D134" s="36" t="s">
+        <v>31</v>
+      </c>
+      <c r="E134" s="37" t="s">
+        <v>21</v>
+      </c>
+      <c r="F134" s="38" t="s">
+        <v>22</v>
+      </c>
+      <c r="G134" s="39" t="s">
+        <v>219</v>
+      </c>
+      <c r="H134" s="40" t="s">
+        <v>21</v>
+      </c>
+      <c r="I134" s="41" t="s">
+        <v>159</v>
+      </c>
+      <c r="J134" s="42" t="s">
+        <v>121</v>
+      </c>
+      <c r="K134" s="43" t="s">
+        <v>122</v>
+      </c>
+      <c r="L134" s="44" t="s">
+        <v>123</v>
+      </c>
+      <c r="M134" s="45">
+        <v>46175</v>
+      </c>
+      <c r="N134" s="46">
+        <v>46175</v>
+      </c>
+      <c r="O134" s="47" t="s">
+        <v>216</v>
+      </c>
+      <c r="P134" s="48" t="s">
+        <v>216</v>
+      </c>
+      <c r="Q134" s="49">
+        <v>46165</v>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" s="33" t="s">
+        <v>152</v>
+      </c>
+      <c r="B135" s="34" t="s">
+        <v>153</v>
+      </c>
+      <c r="C135" s="35" t="s">
+        <v>19</v>
+      </c>
+      <c r="D135" s="36" t="s">
+        <v>31</v>
+      </c>
+      <c r="E135" s="37" t="s">
+        <v>21</v>
+      </c>
+      <c r="F135" s="38" t="s">
+        <v>22</v>
+      </c>
+      <c r="G135" s="39" t="s">
+        <v>220</v>
+      </c>
+      <c r="H135" s="40" t="s">
+        <v>21</v>
+      </c>
+      <c r="I135" s="41" t="s">
+        <v>159</v>
+      </c>
+      <c r="J135" s="42" t="s">
+        <v>121</v>
+      </c>
+      <c r="K135" s="43" t="s">
+        <v>122</v>
+      </c>
+      <c r="L135" s="44" t="s">
+        <v>123</v>
+      </c>
+      <c r="M135" s="45">
+        <v>46175</v>
+      </c>
+      <c r="N135" s="46">
+        <v>46175</v>
+      </c>
+      <c r="O135" s="47" t="s">
+        <v>216</v>
+      </c>
+      <c r="P135" s="48" t="s">
+        <v>216</v>
+      </c>
+      <c r="Q135" s="49">
+        <v>46165</v>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" s="33" t="s">
+        <v>152</v>
+      </c>
+      <c r="B136" s="34" t="s">
+        <v>153</v>
+      </c>
+      <c r="C136" s="35" t="s">
+        <v>19</v>
+      </c>
+      <c r="D136" s="36" t="s">
+        <v>31</v>
+      </c>
+      <c r="E136" s="37" t="s">
+        <v>21</v>
+      </c>
+      <c r="F136" s="38" t="s">
+        <v>22</v>
+      </c>
+      <c r="G136" s="39" t="s">
+        <v>221</v>
+      </c>
+      <c r="H136" s="40" t="s">
+        <v>21</v>
+      </c>
+      <c r="I136" s="41" t="s">
+        <v>145</v>
+      </c>
+      <c r="J136" s="42" t="s">
+        <v>121</v>
+      </c>
+      <c r="K136" s="43" t="s">
+        <v>122</v>
+      </c>
+      <c r="L136" s="44" t="s">
+        <v>123</v>
+      </c>
+      <c r="M136" s="45">
+        <v>46175</v>
+      </c>
+      <c r="N136" s="46">
+        <v>46175</v>
+      </c>
+      <c r="O136" s="47" t="s">
+        <v>216</v>
+      </c>
+      <c r="P136" s="48" t="s">
+        <v>216</v>
+      </c>
+      <c r="Q136" s="49">
+        <v>46165</v>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" s="33" t="s">
+        <v>152</v>
+      </c>
+      <c r="B137" s="34" t="s">
+        <v>153</v>
+      </c>
+      <c r="C137" s="35" t="s">
+        <v>19</v>
+      </c>
+      <c r="D137" s="36" t="s">
+        <v>31</v>
+      </c>
+      <c r="E137" s="37" t="s">
+        <v>21</v>
+      </c>
+      <c r="F137" s="38" t="s">
+        <v>22</v>
+      </c>
+      <c r="G137" s="39" t="s">
+        <v>222</v>
+      </c>
+      <c r="H137" s="40" t="s">
+        <v>21</v>
+      </c>
+      <c r="I137" s="41" t="s">
+        <v>159</v>
+      </c>
+      <c r="J137" s="42" t="s">
+        <v>121</v>
+      </c>
+      <c r="K137" s="43" t="s">
+        <v>122</v>
+      </c>
+      <c r="L137" s="44" t="s">
+        <v>123</v>
+      </c>
+      <c r="M137" s="45">
+        <v>46175</v>
+      </c>
+      <c r="N137" s="46">
+        <v>46175</v>
+      </c>
+      <c r="O137" s="47" t="s">
+        <v>216</v>
+      </c>
+      <c r="P137" s="48" t="s">
+        <v>216</v>
+      </c>
+      <c r="Q137" s="49">
+        <v>46165</v>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" s="33" t="s">
+        <v>152</v>
+      </c>
+      <c r="B138" s="34" t="s">
+        <v>153</v>
+      </c>
+      <c r="C138" s="35" t="s">
+        <v>19</v>
+      </c>
+      <c r="D138" s="36" t="s">
+        <v>31</v>
+      </c>
+      <c r="E138" s="37" t="s">
+        <v>21</v>
+      </c>
+      <c r="F138" s="38" t="s">
+        <v>22</v>
+      </c>
+      <c r="G138" s="39" t="s">
+        <v>223</v>
+      </c>
+      <c r="H138" s="40" t="s">
+        <v>21</v>
+      </c>
+      <c r="I138" s="41" t="s">
+        <v>126</v>
+      </c>
+      <c r="J138" s="42" t="s">
+        <v>121</v>
+      </c>
+      <c r="K138" s="43" t="s">
+        <v>122</v>
+      </c>
+      <c r="L138" s="44" t="s">
+        <v>123</v>
+      </c>
+      <c r="M138" s="45">
+        <v>46175</v>
+      </c>
+      <c r="N138" s="46">
+        <v>46175</v>
+      </c>
+      <c r="O138" s="47" t="s">
+        <v>216</v>
+      </c>
+      <c r="P138" s="48" t="s">
+        <v>216</v>
+      </c>
+      <c r="Q138" s="49">
+        <v>46165</v>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" s="33" t="s">
+        <v>152</v>
+      </c>
+      <c r="B139" s="34" t="s">
+        <v>153</v>
+      </c>
+      <c r="C139" s="35" t="s">
+        <v>19</v>
+      </c>
+      <c r="D139" s="36" t="s">
+        <v>31</v>
+      </c>
+      <c r="E139" s="37" t="s">
+        <v>21</v>
+      </c>
+      <c r="F139" s="38" t="s">
+        <v>22</v>
+      </c>
+      <c r="G139" s="39" t="s">
+        <v>224</v>
+      </c>
+      <c r="H139" s="40" t="s">
+        <v>21</v>
+      </c>
+      <c r="I139" s="41" t="s">
+        <v>126</v>
+      </c>
+      <c r="J139" s="42" t="s">
+        <v>121</v>
+      </c>
+      <c r="K139" s="43" t="s">
+        <v>122</v>
+      </c>
+      <c r="L139" s="44" t="s">
+        <v>123</v>
+      </c>
+      <c r="M139" s="45">
+        <v>46175</v>
+      </c>
+      <c r="N139" s="46">
+        <v>46175</v>
+      </c>
+      <c r="O139" s="47" t="s">
+        <v>216</v>
+      </c>
+      <c r="P139" s="48" t="s">
+        <v>216</v>
+      </c>
+      <c r="Q139" s="49">
+        <v>46165</v>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" s="33" t="s">
+        <v>152</v>
+      </c>
+      <c r="B140" s="34" t="s">
+        <v>153</v>
+      </c>
+      <c r="C140" s="35" t="s">
+        <v>19</v>
+      </c>
+      <c r="D140" s="36" t="s">
+        <v>31</v>
+      </c>
+      <c r="E140" s="37" t="s">
+        <v>21</v>
+      </c>
+      <c r="F140" s="38" t="s">
+        <v>22</v>
+      </c>
+      <c r="G140" s="39" t="s">
+        <v>225</v>
+      </c>
+      <c r="H140" s="40" t="s">
+        <v>21</v>
+      </c>
+      <c r="I140" s="41" t="s">
+        <v>126</v>
+      </c>
+      <c r="J140" s="42" t="s">
+        <v>121</v>
+      </c>
+      <c r="K140" s="43" t="s">
+        <v>122</v>
+      </c>
+      <c r="L140" s="44" t="s">
+        <v>123</v>
+      </c>
+      <c r="M140" s="45">
+        <v>46175</v>
+      </c>
+      <c r="N140" s="46">
+        <v>46175</v>
+      </c>
+      <c r="O140" s="47" t="s">
+        <v>216</v>
+      </c>
+      <c r="P140" s="48" t="s">
+        <v>216</v>
+      </c>
+      <c r="Q140" s="49">
+        <v>46165</v>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" s="33" t="s">
+        <v>152</v>
+      </c>
+      <c r="B141" s="34" t="s">
+        <v>153</v>
+      </c>
+      <c r="C141" s="35" t="s">
+        <v>19</v>
+      </c>
+      <c r="D141" s="36" t="s">
+        <v>31</v>
+      </c>
+      <c r="E141" s="37" t="s">
+        <v>21</v>
+      </c>
+      <c r="F141" s="38" t="s">
+        <v>22</v>
+      </c>
+      <c r="G141" s="39" t="s">
+        <v>226</v>
+      </c>
+      <c r="H141" s="40" t="s">
+        <v>21</v>
+      </c>
+      <c r="I141" s="41" t="s">
+        <v>126</v>
+      </c>
+      <c r="J141" s="42" t="s">
+        <v>121</v>
+      </c>
+      <c r="K141" s="43" t="s">
+        <v>122</v>
+      </c>
+      <c r="L141" s="44" t="s">
+        <v>123</v>
+      </c>
+      <c r="M141" s="45">
+        <v>46175</v>
+      </c>
+      <c r="N141" s="46">
+        <v>46175</v>
+      </c>
+      <c r="O141" s="47" t="s">
+        <v>216</v>
+      </c>
+      <c r="P141" s="48" t="s">
+        <v>216</v>
+      </c>
+      <c r="Q141" s="49">
+        <v>46165</v>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" s="33" t="s">
+        <v>152</v>
+      </c>
+      <c r="B142" s="34" t="s">
+        <v>153</v>
+      </c>
+      <c r="C142" s="35" t="s">
+        <v>19</v>
+      </c>
+      <c r="D142" s="36" t="s">
+        <v>31</v>
+      </c>
+      <c r="E142" s="37" t="s">
+        <v>21</v>
+      </c>
+      <c r="F142" s="38" t="s">
+        <v>22</v>
+      </c>
+      <c r="G142" s="39" t="s">
+        <v>227</v>
+      </c>
+      <c r="H142" s="40" t="s">
+        <v>21</v>
+      </c>
+      <c r="I142" s="41" t="s">
+        <v>159</v>
+      </c>
+      <c r="J142" s="42" t="s">
+        <v>121</v>
+      </c>
+      <c r="K142" s="43" t="s">
+        <v>122</v>
+      </c>
+      <c r="L142" s="44" t="s">
+        <v>123</v>
+      </c>
+      <c r="M142" s="45">
+        <v>46175</v>
+      </c>
+      <c r="N142" s="46">
+        <v>46175</v>
+      </c>
+      <c r="O142" s="47" t="s">
+        <v>216</v>
+      </c>
+      <c r="P142" s="48" t="s">
+        <v>216</v>
+      </c>
+      <c r="Q142" s="49">
+        <v>46165</v>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" s="33" t="s">
+        <v>152</v>
+      </c>
+      <c r="B143" s="34" t="s">
+        <v>153</v>
+      </c>
+      <c r="C143" s="35" t="s">
+        <v>19</v>
+      </c>
+      <c r="D143" s="36" t="s">
+        <v>31</v>
+      </c>
+      <c r="E143" s="37" t="s">
+        <v>88</v>
+      </c>
+      <c r="F143" s="38" t="s">
+        <v>89</v>
+      </c>
+      <c r="G143" s="39" t="s">
+        <v>228</v>
+      </c>
+      <c r="H143" s="40" t="s">
+        <v>88</v>
+      </c>
+      <c r="I143" s="41" t="s">
+        <v>120</v>
+      </c>
+      <c r="J143" s="42" t="s">
+        <v>121</v>
+      </c>
+      <c r="K143" s="43" t="s">
+        <v>122</v>
+      </c>
+      <c r="L143" s="44" t="s">
+        <v>123</v>
+      </c>
+      <c r="M143" s="45">
+        <v>46175</v>
+      </c>
+      <c r="N143" s="46">
+        <v>46175</v>
+      </c>
+      <c r="O143" s="47" t="s">
+        <v>124</v>
+      </c>
+      <c r="P143" s="48" t="s">
+        <v>124</v>
+      </c>
+      <c r="Q143" s="49">
+        <v>46165</v>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" s="33" t="s">
+        <v>152</v>
+      </c>
+      <c r="B144" s="34" t="s">
+        <v>153</v>
+      </c>
+      <c r="C144" s="35" t="s">
+        <v>19</v>
+      </c>
+      <c r="D144" s="36" t="s">
+        <v>31</v>
+      </c>
+      <c r="E144" s="37" t="s">
+        <v>21</v>
+      </c>
+      <c r="F144" s="38" t="s">
+        <v>22</v>
+      </c>
+      <c r="G144" s="39" t="s">
+        <v>229</v>
+      </c>
+      <c r="H144" s="40" t="s">
+        <v>21</v>
+      </c>
+      <c r="I144" s="41" t="s">
+        <v>159</v>
+      </c>
+      <c r="J144" s="42" t="s">
+        <v>121</v>
+      </c>
+      <c r="K144" s="43" t="s">
+        <v>122</v>
+      </c>
+      <c r="L144" s="44" t="s">
+        <v>123</v>
+      </c>
+      <c r="M144" s="45">
+        <v>46175</v>
+      </c>
+      <c r="N144" s="46">
+        <v>46175</v>
+      </c>
+      <c r="O144" s="47" t="s">
+        <v>124</v>
+      </c>
+      <c r="P144" s="48" t="s">
+        <v>124</v>
+      </c>
+      <c r="Q144" s="49">
+        <v>46165</v>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" s="33" t="s">
+        <v>152</v>
+      </c>
+      <c r="B145" s="34" t="s">
+        <v>153</v>
+      </c>
+      <c r="C145" s="35" t="s">
+        <v>19</v>
+      </c>
+      <c r="D145" s="36" t="s">
+        <v>31</v>
+      </c>
+      <c r="E145" s="37" t="s">
+        <v>21</v>
+      </c>
+      <c r="F145" s="38" t="s">
+        <v>22</v>
+      </c>
+      <c r="G145" s="39" t="s">
+        <v>230</v>
+      </c>
+      <c r="H145" s="40" t="s">
+        <v>21</v>
+      </c>
+      <c r="I145" s="41" t="s">
+        <v>126</v>
+      </c>
+      <c r="J145" s="42" t="s">
+        <v>121</v>
+      </c>
+      <c r="K145" s="43" t="s">
+        <v>122</v>
+      </c>
+      <c r="L145" s="44" t="s">
+        <v>123</v>
+      </c>
+      <c r="M145" s="45">
+        <v>46175</v>
+      </c>
+      <c r="N145" s="46">
+        <v>46175</v>
+      </c>
+      <c r="O145" s="47" t="s">
+        <v>124</v>
+      </c>
+      <c r="P145" s="48" t="s">
+        <v>124</v>
+      </c>
+      <c r="Q145" s="49">
+        <v>46165</v>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" s="33" t="s">
+        <v>152</v>
+      </c>
+      <c r="B146" s="34" t="s">
+        <v>153</v>
+      </c>
+      <c r="C146" s="35" t="s">
+        <v>19</v>
+      </c>
+      <c r="D146" s="36" t="s">
+        <v>31</v>
+      </c>
+      <c r="E146" s="37" t="s">
+        <v>21</v>
+      </c>
+      <c r="F146" s="38" t="s">
+        <v>22</v>
+      </c>
+      <c r="G146" s="39" t="s">
+        <v>231</v>
+      </c>
+      <c r="H146" s="40" t="s">
+        <v>21</v>
+      </c>
+      <c r="I146" s="41" t="s">
+        <v>159</v>
+      </c>
+      <c r="J146" s="42" t="s">
+        <v>121</v>
+      </c>
+      <c r="K146" s="43" t="s">
+        <v>122</v>
+      </c>
+      <c r="L146" s="44" t="s">
+        <v>123</v>
+      </c>
+      <c r="M146" s="45">
+        <v>46175</v>
+      </c>
+      <c r="N146" s="46">
+        <v>46175</v>
+      </c>
+      <c r="O146" s="47" t="s">
+        <v>124</v>
+      </c>
+      <c r="P146" s="48" t="s">
+        <v>124</v>
+      </c>
+      <c r="Q146" s="49">
+        <v>46165</v>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" s="33" t="s">
+        <v>152</v>
+      </c>
+      <c r="B147" s="34" t="s">
+        <v>153</v>
+      </c>
+      <c r="C147" s="35" t="s">
+        <v>19</v>
+      </c>
+      <c r="D147" s="36" t="s">
+        <v>31</v>
+      </c>
+      <c r="E147" s="37" t="s">
+        <v>88</v>
+      </c>
+      <c r="F147" s="38" t="s">
+        <v>89</v>
+      </c>
+      <c r="G147" s="39" t="s">
+        <v>232</v>
+      </c>
+      <c r="H147" s="40" t="s">
+        <v>88</v>
+      </c>
+      <c r="I147" s="41" t="s">
+        <v>148</v>
+      </c>
+      <c r="J147" s="42" t="s">
+        <v>121</v>
+      </c>
+      <c r="K147" s="43" t="s">
+        <v>122</v>
+      </c>
+      <c r="L147" s="44" t="s">
+        <v>123</v>
+      </c>
+      <c r="M147" s="45">
+        <v>46175</v>
+      </c>
+      <c r="N147" s="46">
+        <v>46175</v>
+      </c>
+      <c r="O147" s="47" t="s">
+        <v>124</v>
+      </c>
+      <c r="P147" s="48" t="s">
+        <v>124</v>
+      </c>
+      <c r="Q147" s="49">
+        <v>46165</v>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" s="33" t="s">
+        <v>152</v>
+      </c>
+      <c r="B148" s="34" t="s">
+        <v>153</v>
+      </c>
+      <c r="C148" s="35" t="s">
+        <v>19</v>
+      </c>
+      <c r="D148" s="36" t="s">
+        <v>31</v>
+      </c>
+      <c r="E148" s="37" t="s">
+        <v>21</v>
+      </c>
+      <c r="F148" s="38" t="s">
+        <v>22</v>
+      </c>
+      <c r="G148" s="39" t="s">
+        <v>233</v>
+      </c>
+      <c r="H148" s="40" t="s">
+        <v>21</v>
+      </c>
+      <c r="I148" s="41" t="s">
+        <v>234</v>
+      </c>
+      <c r="J148" s="42" t="s">
+        <v>121</v>
+      </c>
+      <c r="K148" s="43" t="s">
+        <v>122</v>
+      </c>
+      <c r="L148" s="44" t="s">
+        <v>123</v>
+      </c>
+      <c r="M148" s="45">
+        <v>46175</v>
+      </c>
+      <c r="N148" s="46">
+        <v>46175</v>
+      </c>
+      <c r="O148" s="47" t="s">
+        <v>124</v>
+      </c>
+      <c r="P148" s="48" t="s">
+        <v>124</v>
+      </c>
+      <c r="Q148" s="49">
+        <v>46165</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError sqref="A1 B1 C1 D1 E1 F1 G1 H1 I1 J1 K1 L1 M1 N1 O1 P1 Q1 A2 B2 C2 D2 E2 F2 G2 H2 I2 J2 K2 L2 O2 P2 A3 B3 C3 D3 E3 F3 G3 H3 I3 J3 K3 L3 O3 P3 A4 B4 C4 D4 E4 F4 G4 H4 I4 J4 K4 L4 O4 P4 A5 B5 C5 D5 E5 F5 G5 H5 I5 J5 K5 L5 O5 P5 A6 B6 C6 D6 E6 F6 G6 H6 I6 J6 K6 L6 O6 P6 A7 B7 C7 D7 E7 F7 G7 H7 I7 J7 K7 L7 O7 P7 A8 B8 C8 D8 E8 F8 G8 H8 I8 J8 K8 L8 O8 P8 A9 B9 C9 D9 E9 F9 G9 H9 I9 J9 K9 L9 O9 P9 A10 B10 C10 D10 E10 F10 G10 H10 I10 J10 K10 L10 O10 P10 A11 B11 C11 D11 E11 F11 G11 H11 I11 J11 K11 L11 O11 P11 A12 B12 C12 D12 E12 F12 G12 H12 I12 J12 K12 L12 O12 P12 A13 B13 C13 D13 E13 F13 G13 H13 I13 J13 K13 L13 O13 P13 A14 B14 C14 D14 E14 F14 G14 H14 I14 J14 K14 L14 O14 P14 A15 B15 C15 D15 E15 F15 G15 H15 I15 J15 K15 L15 O15 P15 A16 B16 C16 D16 E16 F16 G16 H16 I16 J16 K16 L16 O16 P16 A17 B17 C17 D17 E17 F17 G17 H17 I17 J17 K17 L17 O17 P17 A18 B18 C18 D18 E18 F18 G18 H18 I18 J18 K18 L18 O18 P18 A19 B19 C19 D19 E19 F19 G19 H19 I19 J19 K19 L19 O19 P19 A20 B20 C20 D20 E20 F20 G20 H20 I20 J20 K20 L20 O20 P20 A21 B21 C21 D21 E21 F21 G21 H21 I21 J21 K21 L21 O21 P21 A22 B22 C22 D22 E22 F22 G22 H22 I22 J22 K22 L22 O22 P22 A23 B23 C23 D23 E23 F23 G23 H23 I23 J23 K23 L23 O23 P23 A24 B24 C24 D24 E24 F24 G24 H24 I24 J24 K24 L24 O24 P24 A25 B25 C25 D25 E25 F25 G25 H25 I25 J25 K25 L25 O25 P25 A26 B26 C26 D26 E26 F26 G26 H26 I26 J26 K26 L26 O26 P26 A27 B27 C27 D27 E27 F27 G27 H27 I27 J27 K27 L27 O27 P27 A28 B28 C28 D28 E28 F28 G28 H28 I28 J28 K28 L28 O28 P28 A29 B29 C29 D29 E29 F29 G29 H29 I29 J29 K29 L29 O29 P29 A30 B30 C30 D30 E30 F30 G30 H30 I30 J30 K30 L30 O30 P30 A31 B31 C31 D31 E31 F31 G31 H31 I31 J31 K31 L31 O31 P31 A32 B32 C32 D32 E32 F32 G32 H32 I32 J32 K32 L32 O32 P32 A33 B33 C33 D33 E33 F33 G33 H33 I33 J33 K33 L33 O33 P33 A34 B34 C34 D34 E34 F34 G34 H34 I34 J34 K34 L34 O34 P34 A35 B35 C35 D35 E35 F35 G35 H35 I35 J35 K35 L35 O35 P35 A36 B36 C36 D36 E36 F36 G36 H36 I36 J36 K36 L36 O36 P36 A37 B37 C37 D37 E37 F37 G37 H37 I37 J37 K37 L37 O37 P37 A38 B38 C38 D38 E38 F38 G38 H38 I38 J38 K38 L38 O38 P38 A39 B39 C39 D39 E39 F39 G39 H39 I39 J39 K39 L39 O39 P39 A40 B40 C40 D40 E40 F40 G40 H40 I40 J40 K40 L40 O40 P40 A41 B41 C41 D41 E41 F41 G41 H41 I41 J41 K41 L41 O41 P41 A42 B42 C42 D42 E42 F42 G42 H42 I42 J42 K42 L42 O42 P42 A43 B43 C43 D43 E43 F43 G43 H43 I43 J43 K43 L43 O43 P43 A44 B44 C44 D44 E44 F44 G44 H44 I44 J44 K44 L44 O44 P44 A45 B45 C45 D45 E45 F45 G45 H45 I45 J45 K45 L45 O45 P45" numberStoredAsText="true"/>
+    <ignoredError sqref="A1 B1 C1 D1 E1 F1 G1 H1 I1 J1 K1 L1 M1 N1 O1 P1 Q1 A2 B2 C2 D2 E2 F2 G2 H2 I2 J2 K2 L2 O2 P2 A3 B3 C3 D3 E3 F3 G3 H3 I3 J3 K3 L3 O3 P3 A4 B4 C4 D4 E4 F4 G4 H4 I4 J4 K4 L4 O4 P4 A5 B5 C5 D5 E5 F5 G5 H5 I5 J5 K5 L5 O5 P5 A6 B6 C6 D6 E6 F6 G6 H6 I6 J6 K6 L6 O6 P6 A7 B7 C7 D7 E7 F7 G7 H7 I7 J7 K7 L7 O7 P7 A8 B8 C8 D8 E8 F8 G8 H8 I8 J8 K8 L8 O8 P8 A9 B9 C9 D9 E9 F9 G9 H9 I9 J9 K9 L9 O9 P9 A10 B10 C10 D10 E10 F10 G10 H10 I10 J10 K10 L10 O10 P10 A11 B11 C11 D11 E11 F11 G11 H11 I11 J11 K11 L11 O11 P11 A12 B12 C12 D12 E12 F12 G12 H12 I12 J12 K12 L12 O12 P12 A13 B13 C13 D13 E13 F13 G13 H13 I13 J13 K13 L13 O13 P13 A14 B14 C14 D14 E14 F14 G14 H14 I14 J14 K14 L14 O14 P14 A15 B15 C15 D15 E15 F15 G15 H15 I15 J15 K15 L15 O15 P15 A16 B16 C16 D16 E16 F16 G16 H16 I16 J16 K16 L16 O16 P16 A17 B17 C17 D17 E17 F17 G17 H17 I17 J17 K17 L17 O17 P17 A18 B18 C18 D18 E18 F18 G18 H18 I18 J18 K18 L18 O18 P18 A19 B19 C19 D19 E19 F19 G19 H19 I19 J19 K19 L19 O19 P19 A20 B20 C20 D20 E20 F20 G20 H20 I20 J20 K20 L20 O20 P20 A21 B21 C21 D21 E21 F21 G21 H21 I21 J21 K21 L21 O21 P21 A22 B22 C22 D22 E22 F22 G22 H22 I22 J22 K22 L22 O22 P22 A23 B23 C23 D23 E23 F23 G23 H23 I23 J23 K23 L23 O23 P23 A24 B24 C24 D24 E24 F24 G24 H24 I24 J24 K24 L24 O24 P24 A25 B25 C25 D25 E25 F25 G25 H25 I25 J25 K25 L25 O25 P25 A26 B26 C26 D26 E26 F26 G26 H26 I26 J26 K26 L26 O26 P26 A27 B27 C27 D27 E27 F27 G27 H27 I27 J27 K27 L27 O27 P27 A28 B28 C28 D28 E28 F28 G28 H28 I28 J28 K28 L28 O28 P28 A29 B29 C29 D29 E29 F29 G29 H29 I29 J29 K29 L29 O29 P29 A30 B30 C30 D30 E30 F30 G30 H30 I30 J30 K30 L30 O30 P30 A31 B31 C31 D31 E31 F31 G31 H31 I31 J31 K31 L31 O31 P31 A32 B32 C32 D32 E32 F32 G32 H32 I32 J32 K32 L32 O32 P32 A33 B33 C33 D33 E33 F33 G33 H33 I33 J33 K33 L33 O33 P33 A34 B34 C34 D34 E34 F34 G34 H34 I34 J34 K34 L34 O34 P34 A35 B35 C35 D35 E35 F35 G35 H35 I35 J35 K35 L35 O35 P35 A36 B36 C36 D36 E36 F36 G36 H36 I36 J36 K36 L36 O36 P36 A37 B37 C37 D37 E37 F37 G37 H37 I37 J37 K37 L37 O37 P37 A38 B38 C38 D38 E38 F38 G38 H38 I38 J38 K38 L38 O38 P38 A39 B39 C39 D39 E39 F39 G39 H39 I39 J39 K39 L39 O39 P39 A40 B40 C40 D40 E40 F40 G40 H40 I40 J40 K40 L40 O40 P40 A41 B41 C41 D41 E41 F41 G41 H41 I41 J41 K41 L41 O41 P41 A42 B42 C42 D42 E42 F42 G42 H42 I42 J42 K42 L42 O42 P42 A43 B43 C43 D43 E43 F43 G43 H43 I43 J43 K43 L43 O43 P43 A44 B44 C44 D44 E44 F44 G44 H44 I44 J44 K44 L44 O44 P44 A45 B45 C45 D45 E45 F45 G45 H45 I45 J45 K45 L45 O45 P45 A46 B46 C46 D46 E46 F46 G46 H46 I46 J46 K46 L46 O46 P46 A47 B47 C47 D47 E47 F47 G47 H47 I47 J47 K47 L47 O47 P47 A48 B48 C48 D48 E48 F48 G48 H48 I48 J48 K48 L48 O48 P48 A49 B49 C49 D49 E49 F49 G49 H49 I49 J49 K49 L49 O49 P49 A50 B50 C50 D50 E50 F50 G50 H50 I50 J50 K50 L50 O50 P50 A51 B51 C51 D51 E51 F51 G51 H51 I51 J51 K51 L51 O51 P51 A52 B52 C52 D52 E52 F52 G52 H52 I52 J52 K52 L52 O52 P52 A53 B53 C53 D53 E53 F53 G53 H53 I53 J53 K53 L53 O53 P53 A54 B54 C54 D54 E54 F54 G54 H54 I54 J54 K54 L54 O54 P54 A55 B55 C55 D55 E55 F55 G55 H55 I55 J55 K55 L55 O55 P55 A56 B56 C56 D56 E56 F56 G56 H56 I56 J56 K56 L56 O56 P56 A57 B57 C57 D57 E57 F57 G57 H57 I57 J57 K57 L57 O57 P57 A58 B58 C58 D58 E58 F58 G58 H58 I58 J58 K58 L58 O58 P58 A59 B59 C59 D59 E59 F59 G59 H59 I59 J59 K59 L59 O59 P59 A60 B60 C60 D60 E60 F60 G60 H60 I60 J60 K60 L60 O60 P60 A61 B61 C61 D61 E61 F61 G61 H61 I61 J61 K61 L61 O61 P61 A62 B62 C62 D62 E62 F62 G62 H62 I62 J62 K62 L62 O62 P62 A63 B63 C63 D63 E63 F63 G63 H63 I63 J63 K63 L63 O63 P63 A64 B64 C64 D64 E64 F64 G64 H64 I64 J64 K64 L64 O64 P64 A65 B65 C65 D65 E65 F65 G65 H65 I65 J65 K65 L65 O65 P65 A66 B66 C66 D66 E66 F66 G66 H66 I66 J66 K66 L66 O66 P66 A67 B67 C67 D67 E67 F67 G67 H67 I67 J67 K67 L67 O67 P67 A68 B68 C68 D68 E68 F68 G68 H68 I68 J68 K68 L68 O68 P68 A69 B69 C69 D69 E69 F69 G69 H69 I69 J69 K69 L69 O69 P69 A70 B70 C70 D70 E70 F70 G70 H70 I70 J70 K70 L70 O70 P70 A71 B71 C71 D71 E71 F71 G71 H71 I71 J71 K71 L71 O71 P71 A72 B72 C72 D72 E72 F72 G72 H72 I72 J72 K72 L72 O72 P72 A73 B73 C73 D73 E73 F73 G73 H73 I73 J73 K73 L73 O73 P73 A74 B74 C74 D74 E74 F74 G74 H74 I74 J74 K74 L74 O74 P74 A75 B75 C75 D75 E75 F75 G75 H75 I75 J75 K75 L75 O75 P75 A76 B76 C76 D76 E76 F76 G76 H76 I76 J76 K76 L76 O76 P76 A77 B77 C77 D77 E77 F77 G77 H77 I77 J77 K77 L77 O77 P77 A78 B78 C78 D78 E78 F78 G78 H78 I78 J78 K78 L78 O78 P78 A79 B79 C79 D79 E79 F79 G79 H79 I79 J79 K79 L79 O79 P79 A80 B80 C80 D80 E80 F80 G80 H80 I80 J80 K80 L80 O80 P80 A81 B81 C81 D81 E81 F81 G81 H81 I81 J81 K81 L81 O81 P81 A82 B82 C82 D82 E82 F82 G82 H82 I82 J82 K82 L82 O82 P82 A83 B83 C83 D83 E83 F83 G83 H83 I83 J83 K83 L83 O83 P83 A84 B84 C84 D84 E84 F84 G84 H84 I84 J84 K84 L84 O84 P84 A85 B85 C85 D85 E85 F85 G85 H85 I85 J85 K85 L85 O85 P85 A86 B86 C86 D86 E86 F86 G86 H86 I86 J86 K86 L86 O86 P86 A87 B87 C87 D87 E87 F87 G87 H87 I87 J87 K87 L87 O87 P87 A88 B88 C88 D88 E88 F88 G88 H88 I88 J88 K88 L88 O88 P88 A89 B89 C89 D89 E89 F89 G89 H89 I89 J89 K89 L89 O89 P89 A90 B90 C90 D90 E90 F90 G90 H90 I90 J90 K90 L90 O90 P90 A91 B91 C91 D91 E91 F91 G91 H91 I91 J91 K91 L91 O91 P91 A92 B92 C92 D92 E92 F92 G92 H92 I92 J92 K92 L92 O92 P92 A93 B93 C93 D93 E93 F93 G93 H93 I93 J93 K93 L93 O93 P93 A94 B94 C94 D94 E94 F94 G94 H94 I94 J94 K94 L94 O94 P94 A95 B95 C95 D95 E95 F95 G95 H95 I95 J95 K95 L95 O95 P95 A96 B96 C96 D96 E96 F96 G96 H96 I96 J96 K96 L96 O96 P96 A97 B97 C97 D97 E97 F97 G97 H97 I97 J97 K97 L97 O97 P97 A98 B98 C98 D98 E98 F98 G98 H98 I98 J98 K98 L98 O98 P98 A99 B99 C99 D99 E99 F99 G99 H99 I99 J99 K99 L99 O99 P99 A100 B100 C100 D100 E100 F100 G100 H100 I100 J100 K100 L100 O100 P100 A101 B101 C101 D101 E101 F101 G101 H101 I101 J101 K101 L101 O101 P101 A102 B102 C102 D102 E102 F102 G102 H102 I102 J102 K102 L102 O102 P102 A103 B103 C103 D103 E103 F103 G103 H103 I103 J103 K103 L103 O103 P103 A104 B104 C104 D104 E104 F104 G104 H104 I104 J104 K104 L104 O104 P104 A105 B105 C105 D105 E105 F105 G105 H105 I105 J105 K105 L105 O105 P105 A106 B106 C106 D106 E106 F106 G106 H106 I106 J106 K106 L106 O106 P106 A107 B107 C107 D107 E107 F107 G107 H107 I107 J107 K107 L107 O107 P107 A108 B108 C108 D108 E108 F108 G108 H108 I108 J108 K108 L108 O108 P108 A109 B109 C109 D109 E109 F109 G109 H109 I109 J109 K109 L109 O109 P109 A110 B110 C110 D110 E110 F110 G110 H110 I110 J110 K110 L110 O110 P110 A111 B111 C111 D111 E111 F111 G111 H111 I111 J111 K111 L111 O111 P111 A112 B112 C112 D112 E112 F112 G112 H112 I112 J112 K112 L112 O112 P112 A113 B113 C113 D113 E113 F113 G113 H113 I113 J113 K113 L113 O113 P113 A114 B114 C114 D114 E114 F114 G114 H114 I114 J114 K114 L114 O114 P114 A115 B115 C115 D115 E115 F115 G115 H115 I115 J115 K115 L115 O115 P115 A116 B116 C116 D116 E116 F116 G116 H116 I116 J116 K116 L116 O116 P116 A117 B117 C117 D117 E117 F117 G117 H117 I117 J117 K117 L117 O117 P117 A118 B118 C118 D118 E118 F118 G118 H118 I118 J118 K118 L118 O118 P118 A119 B119 C119 D119 E119 F119 G119 H119 I119 J119 K119 L119 O119 P119 A120 B120 C120 D120 E120 F120 G120 H120 I120 J120 K120 L120 O120 P120 A121 B121 C121 D121 E121 F121 G121 H121 I121 J121 K121 L121 O121 P121 A122 B122 C122 D122 E122 F122 G122 H122 I122 J122 K122 L122 O122 P122 A123 B123 C123 D123 E123 F123 G123 H123 I123 J123 K123 L123 O123 P123 A124 B124 C124 D124 E124 F124 G124 H124 I124 J124 K124 L124 O124 P124 A125 B125 C125 D125 E125 F125 G125 H125 I125 J125 K125 L125 O125 P125 A126 B126 C126 D126 E126 F126 G126 H126 I126 J126 K126 L126 O126 P126 A127 B127 C127 D127 E127 F127 G127 H127 I127 J127 K127 L127 O127 P127 A128 B128 C128 D128 E128 F128 G128 H128 I128 J128 K128 L128 O128 P128 A129 B129 C129 D129 E129 F129 G129 H129 I129 J129 K129 L129 O129 P129 A130 B130 C130 D130 E130 F130 G130 H130 I130 J130 K130 L130 O130 P130 A131 B131 C131 D131 E131 F131 G131 H131 I131 J131 K131 L131 O131 P131 A132 B132 C132 D132 E132 F132 G132 H132 I132 J132 K132 L132 O132 P132 A133 B133 C133 D133 E133 F133 G133 H133 I133 J133 K133 L133 O133 P133 A134 B134 C134 D134 E134 F134 G134 H134 I134 J134 K134 L134 O134 P134 A135 B135 C135 D135 E135 F135 G135 H135 I135 J135 K135 L135 O135 P135 A136 B136 C136 D136 E136 F136 G136 H136 I136 J136 K136 L136 O136 P136 A137 B137 C137 D137 E137 F137 G137 H137 I137 J137 K137 L137 O137 P137 A138 B138 C138 D138 E138 F138 G138 H138 I138 J138 K138 L138 O138 P138 A139 B139 C139 D139 E139 F139 G139 H139 I139 J139 K139 L139 O139 P139 A140 B140 C140 D140 E140 F140 G140 H140 I140 J140 K140 L140 O140 P140 A141 B141 C141 D141 E141 F141 G141 H141 I141 J141 K141 L141 O141 P141 A142 B142 C142 D142 E142 F142 G142 H142 I142 J142 K142 L142 O142 P142 A143 B143 C143 D143 E143 F143 G143 H143 I143 J143 K143 L143 O143 P143 A144 B144 C144 D144 E144 F144 G144 H144 I144 J144 K144 L144 O144 P144 A145 B145 C145 D145 E145 F145 G145 H145 I145 J145 K145 L145 O145 P145 A146 B146 C146 D146 E146 F146 G146 H146 I146 J146 K146 L146 O146 P146 A147 B147 C147 D147 E147 F147 G147 H147 I147 J147 K147 L147 O147 P147 A148 B148 C148 D148 E148 F148 G148 H148 I148 J148 K148 L148 O148 P148" numberStoredAsText="true"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/trimika_data.xlsx
+++ b/trimika_data.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" count="269" uniqueCount="112">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" count="311" uniqueCount="107">
   <si>
     <t>REFERENCE NO</t>
   </si>
@@ -66,10 +66,10 @@
     <t>EXPORT DATE</t>
   </si>
   <si>
-    <t>2565067</t>
-  </si>
-  <si>
-    <t>EF4-0230640-3</t>
+    <t>2565445</t>
+  </si>
+  <si>
+    <t>EF4-0231218-7</t>
   </si>
   <si>
     <t>Vessel, Container</t>
@@ -87,7 +87,58 @@
     <t>001</t>
   </si>
   <si>
-    <t>1108.12.0010</t>
+    <t>5903.90.3090</t>
+  </si>
+  <si>
+    <t>VEER CORPORATIONS INC</t>
+  </si>
+  <si>
+    <t>VEECOR01</t>
+  </si>
+  <si>
+    <t>99-106989200</t>
+  </si>
+  <si>
+    <t>VEER PLASTIC PVT LTD</t>
+  </si>
+  <si>
+    <t>2565766</t>
+  </si>
+  <si>
+    <t>EF4-0231553-7</t>
+  </si>
+  <si>
+    <t>2565768</t>
+  </si>
+  <si>
+    <t>EF4-0231555-2</t>
+  </si>
+  <si>
+    <t>2565770</t>
+  </si>
+  <si>
+    <t>EF4-0231557-8</t>
+  </si>
+  <si>
+    <t>VA923700499</t>
+  </si>
+  <si>
+    <t>2565771</t>
+  </si>
+  <si>
+    <t>EF4-0231558-6</t>
+  </si>
+  <si>
+    <t>2565780</t>
+  </si>
+  <si>
+    <t>EF4-0231704-6</t>
+  </si>
+  <si>
+    <t>VA923700630</t>
+  </si>
+  <si>
+    <t>3505.10.0020</t>
   </si>
   <si>
     <t>ROYAL INGREDIENTS GROUP BV</t>
@@ -99,256 +150,190 @@
     <t>074601-00962</t>
   </si>
   <si>
-    <t>TAT NISASTA INS SAN TIC AS</t>
-  </si>
-  <si>
-    <t>2565597</t>
-  </si>
-  <si>
-    <t>EF4-0231525-5</t>
+    <t>T-FIBRE INNOVATION CO., LTD.</t>
+  </si>
+  <si>
+    <t>9903.03.03</t>
+  </si>
+  <si>
+    <t>S122 -EXCLUSION-EXEMPTED PRDTS</t>
+  </si>
+  <si>
+    <t>002</t>
+  </si>
+  <si>
+    <t>1108.14.0000</t>
+  </si>
+  <si>
+    <t>2565879</t>
+  </si>
+  <si>
+    <t>EF4-0231815-0</t>
+  </si>
+  <si>
+    <t>VVS13924784</t>
+  </si>
+  <si>
+    <t>1806.90.9090</t>
+  </si>
+  <si>
+    <t>DOBLA USA MFG LLC</t>
+  </si>
+  <si>
+    <t>DOBUSA</t>
+  </si>
+  <si>
+    <t>41-218954800</t>
+  </si>
+  <si>
+    <t>DOBLA BELGIUM PRODUCTIONS NV/SA</t>
+  </si>
+  <si>
+    <t>DOBLA LOGISTICS BVBA</t>
+  </si>
+  <si>
+    <t>2565844</t>
+  </si>
+  <si>
+    <t>EF4-0231823-4</t>
   </si>
   <si>
     <t>1108.13.0010</t>
   </si>
   <si>
-    <t>EMSLAND-STARKE GMBH</t>
-  </si>
-  <si>
-    <t>2615636</t>
-  </si>
-  <si>
-    <t>EF4-0231644-4</t>
-  </si>
-  <si>
-    <t>Vessel, Non-container</t>
-  </si>
-  <si>
-    <t>000941846</t>
-  </si>
-  <si>
-    <t>9903.88.03</t>
-  </si>
-  <si>
-    <t>ARTICLE OF CHINA,US NTE 20(F)</t>
-  </si>
-  <si>
-    <t>9903.03.01,8208.20.0060</t>
-  </si>
-  <si>
-    <t>CB MANUFACTURING &amp; SALES CO INC</t>
-  </si>
-  <si>
-    <t>CBMAN01</t>
-  </si>
-  <si>
-    <t>34-101525000</t>
-  </si>
-  <si>
-    <t>ZHUZHOU ROCKKING ENGINEERING MACHIN</t>
-  </si>
-  <si>
-    <t>2615654-1</t>
-  </si>
-  <si>
-    <t>EF4-0231669-1</t>
-  </si>
-  <si>
-    <t>9903.03.06,9903.82.09,8211.93.0060</t>
-  </si>
-  <si>
-    <t>NANJING MILSEN OLTD</t>
-  </si>
-  <si>
-    <t>2615654-2</t>
-  </si>
-  <si>
-    <t>EF4-0231670-9</t>
-  </si>
-  <si>
-    <t>843491176</t>
-  </si>
-  <si>
-    <t>9903.03.01,8208.90.6000</t>
-  </si>
-  <si>
-    <t>2565792</t>
-  </si>
-  <si>
-    <t>EF4-0231701-2</t>
-  </si>
-  <si>
-    <t>9903.03.06</t>
-  </si>
-  <si>
-    <t>S122 EXCL,IRN/STL/ALUM,DERIV</t>
-  </si>
-  <si>
-    <t>9903.82.05,8427.20.8020</t>
-  </si>
-  <si>
-    <t>MALLAGHAN (GA) INC.</t>
-  </si>
-  <si>
-    <t>MALGA01</t>
-  </si>
-  <si>
-    <t>36-488102800</t>
-  </si>
-  <si>
-    <t>MALLAGHAN ENGINEERING  LTD</t>
-  </si>
-  <si>
-    <t>2565841</t>
-  </si>
-  <si>
-    <t>EF4-0231702-0</t>
-  </si>
-  <si>
-    <t>2566048</t>
-  </si>
-  <si>
-    <t>EF4-0231956-2</t>
-  </si>
-  <si>
-    <t>9903.82.01,8424.90.9080</t>
-  </si>
-  <si>
-    <t>EISENMANN OF SOUTH CAROLINA INC</t>
-  </si>
-  <si>
-    <t>EISINC03</t>
-  </si>
-  <si>
-    <t>86-240963300</t>
-  </si>
-  <si>
-    <t>EISENMANN GMBH</t>
-  </si>
-  <si>
-    <t>2566006</t>
-  </si>
-  <si>
-    <t>EF4-0232094-1</t>
-  </si>
-  <si>
-    <t>9903.74.11,9903.94.53,8708.29.5160</t>
-  </si>
-  <si>
-    <t>BORGERS USA CORP</t>
-  </si>
-  <si>
-    <t>BORUSA</t>
-  </si>
-  <si>
-    <t>65-117296500</t>
-  </si>
-  <si>
-    <t>AUTONEUM CZ S.R.O.</t>
-  </si>
-  <si>
-    <t>002</t>
-  </si>
-  <si>
-    <t>003</t>
-  </si>
-  <si>
-    <t>2566142</t>
-  </si>
-  <si>
-    <t>EF4-0232117-0</t>
-  </si>
-  <si>
-    <t>3907.99.5050</t>
-  </si>
-  <si>
-    <t>MANKIEWICZ COATINGS, LLC</t>
-  </si>
-  <si>
-    <t>MANCOAT</t>
-  </si>
-  <si>
-    <t>56-202308900</t>
-  </si>
-  <si>
-    <t>SYNTHOPOL CHEMIE</t>
-  </si>
-  <si>
-    <t>9903.03.03</t>
-  </si>
-  <si>
-    <t>S122 -EXCLUSION-EXEMPTED PRDTS</t>
-  </si>
-  <si>
-    <t>3906.90.5000</t>
-  </si>
-  <si>
-    <t>105504757</t>
-  </si>
-  <si>
-    <t>EF4-0232265-7</t>
-  </si>
-  <si>
-    <t>Truck, Non-container</t>
-  </si>
-  <si>
-    <t>9817.85.01</t>
-  </si>
-  <si>
-    <t>PROTOTYPES, TESTING/EVALUATION</t>
-  </si>
-  <si>
-    <t>9903.03.06,9903.94.51,8703.24.0150</t>
-  </si>
-  <si>
-    <t>PORSCHE MOTORSPORT NORTH AMERICA</t>
-  </si>
-  <si>
-    <t>PORMOT01</t>
-  </si>
-  <si>
-    <t>23-234420600</t>
-  </si>
-  <si>
-    <t>DR. ING. H.C.F. PORSCHE AG</t>
-  </si>
-  <si>
-    <t>4539411</t>
-  </si>
-  <si>
-    <t>EF4-0232270-7</t>
-  </si>
-  <si>
-    <t>Air, Non-container</t>
-  </si>
-  <si>
-    <t>783000273</t>
-  </si>
-  <si>
-    <t>9903.82.10,8479.90.9596</t>
-  </si>
-  <si>
-    <t>PLUMETTAZ AMERICA CORP</t>
-  </si>
-  <si>
-    <t>PLUAME01</t>
-  </si>
-  <si>
-    <t>83-230829500</t>
-  </si>
-  <si>
-    <t>PLUMETTAZ S.A.</t>
-  </si>
-  <si>
-    <t>105504760</t>
-  </si>
-  <si>
-    <t>EF4-0232271-5</t>
-  </si>
-  <si>
-    <t>9903.03.06,9903.94.51,8703.80.0060</t>
-  </si>
-  <si>
-    <t>VOLKSWAGEN SLOVAKIA A.S</t>
+    <t>PRZEDSIEBIORSTWO PRZEMYSLU ZIEMNIAC</t>
+  </si>
+  <si>
+    <t>PRZEDSIEBIORSTWO PRZEMYSLU ZIEMNIACZANEGO PEPEES S.A.</t>
+  </si>
+  <si>
+    <t>2565742</t>
+  </si>
+  <si>
+    <t>EF4-0231828-3</t>
+  </si>
+  <si>
+    <t>V0459386715</t>
+  </si>
+  <si>
+    <t>6310.10.2020</t>
+  </si>
+  <si>
+    <t>FOOTING FIRST, LLC</t>
+  </si>
+  <si>
+    <t>FOOFIR</t>
+  </si>
+  <si>
+    <t>27-059921300</t>
+  </si>
+  <si>
+    <t>ALTEX TEXTILRECYCLING</t>
+  </si>
+  <si>
+    <t>2565910</t>
+  </si>
+  <si>
+    <t>EF4-0231923-2</t>
+  </si>
+  <si>
+    <t>1109.00.1000</t>
+  </si>
+  <si>
+    <t>SEDAMYL UK</t>
+  </si>
+  <si>
+    <t>2565947</t>
+  </si>
+  <si>
+    <t>EF4-0231924-0</t>
+  </si>
+  <si>
+    <t>1109.00.9020</t>
+  </si>
+  <si>
+    <t>2565934</t>
+  </si>
+  <si>
+    <t>EF4-0231991-9</t>
+  </si>
+  <si>
+    <t>V0710339289</t>
+  </si>
+  <si>
+    <t>AKV LANGHOLT AMBA</t>
+  </si>
+  <si>
+    <t>2565944</t>
+  </si>
+  <si>
+    <t>EF4-0231993-5</t>
+  </si>
+  <si>
+    <t>2565948</t>
+  </si>
+  <si>
+    <t>EF4-0231994-3</t>
+  </si>
+  <si>
+    <t>2566033</t>
+  </si>
+  <si>
+    <t>EF4-0232066-9</t>
+  </si>
+  <si>
+    <t>V0710333241</t>
+  </si>
+  <si>
+    <t>JACKERING MUHLEN UND NAHRMITTELWERK</t>
+  </si>
+  <si>
+    <t>JACKERING MUHLEN UND NAHRMITTELWERKE GMBH</t>
+  </si>
+  <si>
+    <t>2565912</t>
+  </si>
+  <si>
+    <t>EF4-0232086-7</t>
+  </si>
+  <si>
+    <t>3920.62.0090</t>
+  </si>
+  <si>
+    <t>TEUFELBERGER G.E.S.M.B.H</t>
+  </si>
+  <si>
+    <t>TEUSEI01</t>
+  </si>
+  <si>
+    <t>181704-13780</t>
+  </si>
+  <si>
+    <t>TEUFELBERGER GMBH</t>
+  </si>
+  <si>
+    <t>2565916</t>
+  </si>
+  <si>
+    <t>EF4-0232089-1</t>
+  </si>
+  <si>
+    <t>2565917</t>
+  </si>
+  <si>
+    <t>EF4-0232091-7</t>
+  </si>
+  <si>
+    <t>2566101</t>
+  </si>
+  <si>
+    <t>EF4-0232243-4</t>
+  </si>
+  <si>
+    <t>1109.00.9010</t>
+  </si>
+  <si>
+    <t>KROENER-STARKE BIO GMBH</t>
   </si>
 </sst>
 </file>
@@ -1293,7 +1278,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:Q19"/>
+  <dimension ref="A1:Q22"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="23.7109375" customWidth="true"/>
@@ -1409,7 +1394,7 @@
         <v>46179</v>
       </c>
       <c r="N2" s="46">
-        <v>46177</v>
+        <v>46180</v>
       </c>
       <c r="O2" s="47" t="s">
         <v>28</v>
@@ -1418,7 +1403,7 @@
         <v>28</v>
       </c>
       <c r="Q2" s="49">
-        <v>46099</v>
+        <v>46115</v>
       </c>
     </row>
     <row r="3">
@@ -1447,7 +1432,7 @@
         <v>21</v>
       </c>
       <c r="I3" s="41" t="s">
-        <v>31</v>
+        <v>24</v>
       </c>
       <c r="J3" s="42" t="s">
         <v>25</v>
@@ -1459,298 +1444,298 @@
         <v>27</v>
       </c>
       <c r="M3" s="45">
-        <v>46178</v>
+        <v>46179</v>
       </c>
       <c r="N3" s="46">
-        <v>46177</v>
+        <v>46180</v>
       </c>
       <c r="O3" s="47" t="s">
-        <v>32</v>
+        <v>28</v>
       </c>
       <c r="P3" s="48" t="s">
-        <v>32</v>
+        <v>28</v>
       </c>
       <c r="Q3" s="49">
-        <v>46142</v>
+        <v>46145</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="33" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="B4" s="34" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="C4" s="35" t="s">
-        <v>35</v>
+        <v>19</v>
       </c>
       <c r="D4" s="36" t="s">
-        <v>36</v>
+        <v>20</v>
       </c>
       <c r="E4" s="37" t="s">
-        <v>37</v>
+        <v>21</v>
       </c>
       <c r="F4" s="38" t="s">
-        <v>38</v>
+        <v>22</v>
       </c>
       <c r="G4" s="39" t="s">
         <v>23</v>
       </c>
       <c r="H4" s="40" t="s">
-        <v>37</v>
+        <v>21</v>
       </c>
       <c r="I4" s="41" t="s">
-        <v>39</v>
+        <v>24</v>
       </c>
       <c r="J4" s="42" t="s">
-        <v>40</v>
+        <v>25</v>
       </c>
       <c r="K4" s="43" t="s">
-        <v>41</v>
+        <v>26</v>
       </c>
       <c r="L4" s="44" t="s">
-        <v>42</v>
+        <v>27</v>
       </c>
       <c r="M4" s="45">
-        <v>46175</v>
+        <v>46179</v>
       </c>
       <c r="N4" s="46">
-        <v>46177</v>
+        <v>46180</v>
       </c>
       <c r="O4" s="47" t="s">
-        <v>43</v>
+        <v>28</v>
       </c>
       <c r="P4" s="48" t="s">
-        <v>43</v>
+        <v>28</v>
       </c>
       <c r="Q4" s="49">
-        <v>46146</v>
+        <v>46145</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="33" t="s">
-        <v>44</v>
+        <v>33</v>
       </c>
       <c r="B5" s="34" t="s">
-        <v>45</v>
+        <v>34</v>
       </c>
       <c r="C5" s="35" t="s">
+        <v>19</v>
+      </c>
+      <c r="D5" s="36" t="s">
         <v>35</v>
       </c>
-      <c r="D5" s="36" t="s">
-        <v>36</v>
-      </c>
       <c r="E5" s="37" t="s">
-        <v>37</v>
+        <v>21</v>
       </c>
       <c r="F5" s="38" t="s">
-        <v>38</v>
+        <v>22</v>
       </c>
       <c r="G5" s="39" t="s">
         <v>23</v>
       </c>
       <c r="H5" s="40" t="s">
-        <v>37</v>
+        <v>21</v>
       </c>
       <c r="I5" s="41" t="s">
-        <v>46</v>
+        <v>24</v>
       </c>
       <c r="J5" s="42" t="s">
-        <v>40</v>
+        <v>25</v>
       </c>
       <c r="K5" s="43" t="s">
-        <v>41</v>
+        <v>26</v>
       </c>
       <c r="L5" s="44" t="s">
-        <v>42</v>
+        <v>27</v>
       </c>
       <c r="M5" s="45">
-        <v>46175</v>
+        <v>46171</v>
       </c>
       <c r="N5" s="46">
-        <v>46177</v>
+        <v>46180</v>
       </c>
       <c r="O5" s="47" t="s">
-        <v>47</v>
+        <v>28</v>
       </c>
       <c r="P5" s="48" t="s">
-        <v>47</v>
+        <v>28</v>
       </c>
       <c r="Q5" s="49">
-        <v>46144</v>
+        <v>46145</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="33" t="s">
-        <v>48</v>
+        <v>36</v>
       </c>
       <c r="B6" s="34" t="s">
-        <v>49</v>
+        <v>37</v>
       </c>
       <c r="C6" s="35" t="s">
+        <v>19</v>
+      </c>
+      <c r="D6" s="36" t="s">
         <v>35</v>
       </c>
-      <c r="D6" s="36" t="s">
-        <v>50</v>
-      </c>
       <c r="E6" s="37" t="s">
-        <v>37</v>
+        <v>21</v>
       </c>
       <c r="F6" s="38" t="s">
-        <v>38</v>
+        <v>22</v>
       </c>
       <c r="G6" s="39" t="s">
         <v>23</v>
       </c>
       <c r="H6" s="40" t="s">
-        <v>37</v>
+        <v>21</v>
       </c>
       <c r="I6" s="41" t="s">
-        <v>51</v>
+        <v>24</v>
       </c>
       <c r="J6" s="42" t="s">
-        <v>40</v>
+        <v>25</v>
       </c>
       <c r="K6" s="43" t="s">
-        <v>41</v>
+        <v>26</v>
       </c>
       <c r="L6" s="44" t="s">
-        <v>42</v>
+        <v>27</v>
       </c>
       <c r="M6" s="45">
-        <v>46175</v>
+        <v>46171</v>
       </c>
       <c r="N6" s="46">
-        <v>46177</v>
+        <v>46180</v>
       </c>
       <c r="O6" s="47" t="s">
-        <v>47</v>
+        <v>28</v>
       </c>
       <c r="P6" s="48" t="s">
-        <v>47</v>
+        <v>28</v>
       </c>
       <c r="Q6" s="49">
-        <v>46144</v>
+        <v>46145</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="33" t="s">
-        <v>52</v>
+        <v>38</v>
       </c>
       <c r="B7" s="34" t="s">
-        <v>53</v>
+        <v>39</v>
       </c>
       <c r="C7" s="35" t="s">
-        <v>35</v>
+        <v>19</v>
       </c>
       <c r="D7" s="36" t="s">
-        <v>50</v>
+        <v>40</v>
       </c>
       <c r="E7" s="37" t="s">
-        <v>54</v>
+        <v>21</v>
       </c>
       <c r="F7" s="38" t="s">
-        <v>55</v>
+        <v>22</v>
       </c>
       <c r="G7" s="39" t="s">
         <v>23</v>
       </c>
       <c r="H7" s="40" t="s">
-        <v>54</v>
+        <v>21</v>
       </c>
       <c r="I7" s="41" t="s">
-        <v>56</v>
+        <v>41</v>
       </c>
       <c r="J7" s="42" t="s">
-        <v>57</v>
+        <v>42</v>
       </c>
       <c r="K7" s="43" t="s">
-        <v>58</v>
+        <v>43</v>
       </c>
       <c r="L7" s="44" t="s">
-        <v>59</v>
+        <v>44</v>
       </c>
       <c r="M7" s="45">
-        <v>46179</v>
+        <v>46175</v>
       </c>
       <c r="N7" s="46">
-        <v>46177</v>
+        <v>46180</v>
       </c>
       <c r="O7" s="47" t="s">
-        <v>60</v>
+        <v>45</v>
       </c>
       <c r="P7" s="48" t="s">
-        <v>60</v>
+        <v>45</v>
       </c>
       <c r="Q7" s="49">
-        <v>46150</v>
+        <v>46148</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="33" t="s">
-        <v>61</v>
+        <v>38</v>
       </c>
       <c r="B8" s="34" t="s">
-        <v>62</v>
+        <v>39</v>
       </c>
       <c r="C8" s="35" t="s">
-        <v>35</v>
+        <v>19</v>
       </c>
       <c r="D8" s="36" t="s">
-        <v>20</v>
+        <v>40</v>
       </c>
       <c r="E8" s="37" t="s">
-        <v>54</v>
+        <v>46</v>
       </c>
       <c r="F8" s="38" t="s">
-        <v>55</v>
+        <v>47</v>
       </c>
       <c r="G8" s="39" t="s">
-        <v>23</v>
+        <v>48</v>
       </c>
       <c r="H8" s="40" t="s">
-        <v>54</v>
+        <v>46</v>
       </c>
       <c r="I8" s="41" t="s">
-        <v>56</v>
+        <v>49</v>
       </c>
       <c r="J8" s="42" t="s">
-        <v>57</v>
+        <v>42</v>
       </c>
       <c r="K8" s="43" t="s">
-        <v>58</v>
+        <v>43</v>
       </c>
       <c r="L8" s="44" t="s">
-        <v>59</v>
+        <v>44</v>
       </c>
       <c r="M8" s="45">
-        <v>46179</v>
+        <v>46175</v>
       </c>
       <c r="N8" s="46">
-        <v>46177</v>
+        <v>46180</v>
       </c>
       <c r="O8" s="47" t="s">
-        <v>60</v>
+        <v>45</v>
       </c>
       <c r="P8" s="48" t="s">
-        <v>60</v>
+        <v>45</v>
       </c>
       <c r="Q8" s="49">
-        <v>46150</v>
+        <v>46148</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="33" t="s">
-        <v>63</v>
+        <v>50</v>
       </c>
       <c r="B9" s="34" t="s">
-        <v>64</v>
+        <v>51</v>
       </c>
       <c r="C9" s="35" t="s">
         <v>19</v>
       </c>
       <c r="D9" s="36" t="s">
-        <v>20</v>
+        <v>52</v>
       </c>
       <c r="E9" s="37" t="s">
         <v>21</v>
@@ -1765,92 +1750,92 @@
         <v>21</v>
       </c>
       <c r="I9" s="41" t="s">
-        <v>65</v>
+        <v>53</v>
       </c>
       <c r="J9" s="42" t="s">
-        <v>66</v>
+        <v>54</v>
       </c>
       <c r="K9" s="43" t="s">
-        <v>67</v>
+        <v>55</v>
       </c>
       <c r="L9" s="44" t="s">
-        <v>68</v>
+        <v>56</v>
       </c>
       <c r="M9" s="45">
-        <v>46177</v>
+        <v>46180</v>
       </c>
       <c r="N9" s="46">
-        <v>46177</v>
+        <v>46180</v>
       </c>
       <c r="O9" s="47" t="s">
-        <v>69</v>
+        <v>57</v>
       </c>
       <c r="P9" s="48" t="s">
-        <v>69</v>
+        <v>57</v>
       </c>
       <c r="Q9" s="49">
-        <v>46164</v>
+        <v>46154</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="33" t="s">
-        <v>70</v>
+        <v>50</v>
       </c>
       <c r="B10" s="34" t="s">
-        <v>71</v>
+        <v>51</v>
       </c>
       <c r="C10" s="35" t="s">
         <v>19</v>
       </c>
       <c r="D10" s="36" t="s">
-        <v>20</v>
+        <v>52</v>
       </c>
       <c r="E10" s="37" t="s">
+        <v>21</v>
+      </c>
+      <c r="F10" s="38" t="s">
+        <v>22</v>
+      </c>
+      <c r="G10" s="39" t="s">
+        <v>48</v>
+      </c>
+      <c r="H10" s="40" t="s">
+        <v>21</v>
+      </c>
+      <c r="I10" s="41" t="s">
+        <v>53</v>
+      </c>
+      <c r="J10" s="42" t="s">
         <v>54</v>
       </c>
-      <c r="F10" s="38" t="s">
+      <c r="K10" s="43" t="s">
         <v>55</v>
       </c>
-      <c r="G10" s="39" t="s">
-        <v>23</v>
-      </c>
-      <c r="H10" s="40" t="s">
-        <v>54</v>
-      </c>
-      <c r="I10" s="41" t="s">
-        <v>72</v>
-      </c>
-      <c r="J10" s="42" t="s">
-        <v>73</v>
-      </c>
-      <c r="K10" s="43" t="s">
-        <v>74</v>
-      </c>
       <c r="L10" s="44" t="s">
-        <v>75</v>
+        <v>56</v>
       </c>
       <c r="M10" s="45">
-        <v>46177</v>
+        <v>46180</v>
       </c>
       <c r="N10" s="46">
-        <v>46177</v>
+        <v>46180</v>
       </c>
       <c r="O10" s="47" t="s">
-        <v>76</v>
+        <v>58</v>
       </c>
       <c r="P10" s="48" t="s">
-        <v>76</v>
+        <v>58</v>
       </c>
       <c r="Q10" s="49">
-        <v>46164</v>
+        <v>46154</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="33" t="s">
-        <v>70</v>
+        <v>59</v>
       </c>
       <c r="B11" s="34" t="s">
-        <v>71</v>
+        <v>60</v>
       </c>
       <c r="C11" s="35" t="s">
         <v>19</v>
@@ -1859,110 +1844,110 @@
         <v>20</v>
       </c>
       <c r="E11" s="37" t="s">
-        <v>54</v>
+        <v>21</v>
       </c>
       <c r="F11" s="38" t="s">
-        <v>55</v>
+        <v>20</v>
       </c>
       <c r="G11" s="39" t="s">
-        <v>77</v>
+        <v>23</v>
       </c>
       <c r="H11" s="40" t="s">
-        <v>54</v>
+        <v>21</v>
       </c>
       <c r="I11" s="41" t="s">
-        <v>72</v>
+        <v>61</v>
       </c>
       <c r="J11" s="42" t="s">
-        <v>73</v>
+        <v>42</v>
       </c>
       <c r="K11" s="43" t="s">
-        <v>74</v>
+        <v>43</v>
       </c>
       <c r="L11" s="44" t="s">
-        <v>75</v>
+        <v>44</v>
       </c>
       <c r="M11" s="45">
-        <v>46177</v>
+        <v>46180</v>
       </c>
       <c r="N11" s="46">
-        <v>46177</v>
+        <v>46180</v>
       </c>
       <c r="O11" s="47" t="s">
-        <v>76</v>
+        <v>62</v>
       </c>
       <c r="P11" s="48" t="s">
-        <v>76</v>
+        <v>63</v>
       </c>
       <c r="Q11" s="49">
-        <v>46164</v>
+        <v>46153</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="33" t="s">
-        <v>70</v>
+        <v>64</v>
       </c>
       <c r="B12" s="34" t="s">
-        <v>71</v>
+        <v>65</v>
       </c>
       <c r="C12" s="35" t="s">
         <v>19</v>
       </c>
       <c r="D12" s="36" t="s">
-        <v>20</v>
+        <v>66</v>
       </c>
       <c r="E12" s="37" t="s">
-        <v>54</v>
+        <v>21</v>
       </c>
       <c r="F12" s="38" t="s">
-        <v>55</v>
+        <v>22</v>
       </c>
       <c r="G12" s="39" t="s">
-        <v>78</v>
+        <v>23</v>
       </c>
       <c r="H12" s="40" t="s">
-        <v>54</v>
+        <v>21</v>
       </c>
       <c r="I12" s="41" t="s">
-        <v>72</v>
+        <v>67</v>
       </c>
       <c r="J12" s="42" t="s">
-        <v>73</v>
+        <v>68</v>
       </c>
       <c r="K12" s="43" t="s">
-        <v>74</v>
+        <v>69</v>
       </c>
       <c r="L12" s="44" t="s">
-        <v>75</v>
+        <v>70</v>
       </c>
       <c r="M12" s="45">
-        <v>46177</v>
+        <v>46171</v>
       </c>
       <c r="N12" s="46">
-        <v>46177</v>
+        <v>46180</v>
       </c>
       <c r="O12" s="47" t="s">
-        <v>76</v>
+        <v>71</v>
       </c>
       <c r="P12" s="48" t="s">
-        <v>76</v>
+        <v>71</v>
       </c>
       <c r="Q12" s="49">
-        <v>46164</v>
+        <v>46154</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="33" t="s">
-        <v>79</v>
+        <v>72</v>
       </c>
       <c r="B13" s="34" t="s">
-        <v>80</v>
+        <v>73</v>
       </c>
       <c r="C13" s="35" t="s">
         <v>19</v>
       </c>
       <c r="D13" s="36" t="s">
-        <v>20</v>
+        <v>66</v>
       </c>
       <c r="E13" s="37" t="s">
         <v>21</v>
@@ -1977,39 +1962,39 @@
         <v>21</v>
       </c>
       <c r="I13" s="41" t="s">
-        <v>81</v>
+        <v>74</v>
       </c>
       <c r="J13" s="42" t="s">
-        <v>82</v>
+        <v>42</v>
       </c>
       <c r="K13" s="43" t="s">
-        <v>83</v>
+        <v>43</v>
       </c>
       <c r="L13" s="44" t="s">
-        <v>84</v>
+        <v>44</v>
       </c>
       <c r="M13" s="45">
-        <v>46177</v>
+        <v>46180</v>
       </c>
       <c r="N13" s="46">
-        <v>46177</v>
+        <v>46180</v>
       </c>
       <c r="O13" s="47" t="s">
-        <v>85</v>
+        <v>75</v>
       </c>
       <c r="P13" s="48" t="s">
-        <v>85</v>
+        <v>75</v>
       </c>
       <c r="Q13" s="49">
-        <v>46164</v>
+        <v>46157</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="33" t="s">
-        <v>79</v>
+        <v>76</v>
       </c>
       <c r="B14" s="34" t="s">
-        <v>80</v>
+        <v>77</v>
       </c>
       <c r="C14" s="35" t="s">
         <v>19</v>
@@ -2018,284 +2003,284 @@
         <v>20</v>
       </c>
       <c r="E14" s="37" t="s">
-        <v>86</v>
+        <v>21</v>
       </c>
       <c r="F14" s="38" t="s">
-        <v>87</v>
+        <v>22</v>
       </c>
       <c r="G14" s="39" t="s">
-        <v>77</v>
+        <v>23</v>
       </c>
       <c r="H14" s="40" t="s">
-        <v>86</v>
+        <v>21</v>
       </c>
       <c r="I14" s="41" t="s">
-        <v>88</v>
+        <v>78</v>
       </c>
       <c r="J14" s="42" t="s">
-        <v>82</v>
+        <v>42</v>
       </c>
       <c r="K14" s="43" t="s">
-        <v>83</v>
+        <v>43</v>
       </c>
       <c r="L14" s="44" t="s">
-        <v>84</v>
+        <v>44</v>
       </c>
       <c r="M14" s="45">
-        <v>46177</v>
+        <v>46180</v>
       </c>
       <c r="N14" s="46">
-        <v>46177</v>
+        <v>46180</v>
       </c>
       <c r="O14" s="47" t="s">
-        <v>85</v>
+        <v>75</v>
       </c>
       <c r="P14" s="48" t="s">
-        <v>85</v>
+        <v>75</v>
       </c>
       <c r="Q14" s="49">
-        <v>46164</v>
+        <v>46158</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="33" t="s">
-        <v>89</v>
+        <v>79</v>
       </c>
       <c r="B15" s="34" t="s">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="C15" s="35" t="s">
-        <v>91</v>
+        <v>19</v>
       </c>
       <c r="D15" s="36" t="s">
-        <v>20</v>
+        <v>81</v>
       </c>
       <c r="E15" s="37" t="s">
-        <v>92</v>
+        <v>21</v>
       </c>
       <c r="F15" s="38" t="s">
-        <v>93</v>
+        <v>22</v>
       </c>
       <c r="G15" s="39" t="s">
         <v>23</v>
       </c>
       <c r="H15" s="40" t="s">
-        <v>92</v>
+        <v>21</v>
       </c>
       <c r="I15" s="41" t="s">
-        <v>94</v>
+        <v>61</v>
       </c>
       <c r="J15" s="42" t="s">
-        <v>95</v>
+        <v>42</v>
       </c>
       <c r="K15" s="43" t="s">
-        <v>96</v>
+        <v>43</v>
       </c>
       <c r="L15" s="44" t="s">
-        <v>97</v>
+        <v>44</v>
       </c>
       <c r="M15" s="45">
-        <v>46176</v>
+        <v>46180</v>
       </c>
       <c r="N15" s="46">
-        <v>46177</v>
+        <v>46180</v>
       </c>
       <c r="O15" s="47" t="s">
-        <v>98</v>
+        <v>82</v>
       </c>
       <c r="P15" s="48" t="s">
-        <v>98</v>
+        <v>82</v>
       </c>
       <c r="Q15" s="49">
-        <v>46176</v>
+        <v>46160</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="33" t="s">
-        <v>99</v>
+        <v>83</v>
       </c>
       <c r="B16" s="34" t="s">
-        <v>100</v>
+        <v>84</v>
       </c>
       <c r="C16" s="35" t="s">
-        <v>101</v>
+        <v>19</v>
       </c>
       <c r="D16" s="36" t="s">
-        <v>102</v>
+        <v>81</v>
       </c>
       <c r="E16" s="37" t="s">
-        <v>54</v>
+        <v>21</v>
       </c>
       <c r="F16" s="38" t="s">
-        <v>55</v>
+        <v>22</v>
       </c>
       <c r="G16" s="39" t="s">
         <v>23</v>
       </c>
       <c r="H16" s="40" t="s">
-        <v>54</v>
+        <v>21</v>
       </c>
       <c r="I16" s="41" t="s">
-        <v>103</v>
+        <v>61</v>
       </c>
       <c r="J16" s="42" t="s">
-        <v>104</v>
+        <v>42</v>
       </c>
       <c r="K16" s="43" t="s">
-        <v>105</v>
+        <v>43</v>
       </c>
       <c r="L16" s="44" t="s">
-        <v>106</v>
+        <v>44</v>
       </c>
       <c r="M16" s="45">
-        <v>46171</v>
+        <v>46180</v>
       </c>
       <c r="N16" s="46">
-        <v>46177</v>
+        <v>46180</v>
       </c>
       <c r="O16" s="47" t="s">
-        <v>107</v>
+        <v>82</v>
       </c>
       <c r="P16" s="48" t="s">
-        <v>107</v>
+        <v>82</v>
       </c>
       <c r="Q16" s="49">
-        <v>46171</v>
+        <v>46160</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="33" t="s">
-        <v>108</v>
+        <v>85</v>
       </c>
       <c r="B17" s="34" t="s">
-        <v>109</v>
+        <v>86</v>
       </c>
       <c r="C17" s="35" t="s">
-        <v>91</v>
+        <v>19</v>
       </c>
       <c r="D17" s="36" t="s">
-        <v>102</v>
+        <v>81</v>
       </c>
       <c r="E17" s="37" t="s">
-        <v>92</v>
+        <v>21</v>
       </c>
       <c r="F17" s="38" t="s">
-        <v>93</v>
+        <v>22</v>
       </c>
       <c r="G17" s="39" t="s">
         <v>23</v>
       </c>
       <c r="H17" s="40" t="s">
-        <v>92</v>
+        <v>21</v>
       </c>
       <c r="I17" s="41" t="s">
-        <v>110</v>
+        <v>61</v>
       </c>
       <c r="J17" s="42" t="s">
-        <v>95</v>
+        <v>42</v>
       </c>
       <c r="K17" s="43" t="s">
-        <v>96</v>
+        <v>43</v>
       </c>
       <c r="L17" s="44" t="s">
-        <v>97</v>
+        <v>44</v>
       </c>
       <c r="M17" s="45">
-        <v>46176</v>
+        <v>46180</v>
       </c>
       <c r="N17" s="46">
-        <v>46177</v>
+        <v>46180</v>
       </c>
       <c r="O17" s="47" t="s">
-        <v>111</v>
+        <v>82</v>
       </c>
       <c r="P17" s="48" t="s">
-        <v>111</v>
+        <v>82</v>
       </c>
       <c r="Q17" s="49">
-        <v>46176</v>
+        <v>46160</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="33" t="s">
-        <v>108</v>
+        <v>87</v>
       </c>
       <c r="B18" s="34" t="s">
-        <v>109</v>
+        <v>88</v>
       </c>
       <c r="C18" s="35" t="s">
+        <v>19</v>
+      </c>
+      <c r="D18" s="36" t="s">
+        <v>89</v>
+      </c>
+      <c r="E18" s="37" t="s">
+        <v>21</v>
+      </c>
+      <c r="F18" s="38" t="s">
+        <v>22</v>
+      </c>
+      <c r="G18" s="39" t="s">
+        <v>23</v>
+      </c>
+      <c r="H18" s="40" t="s">
+        <v>21</v>
+      </c>
+      <c r="I18" s="41" t="s">
+        <v>78</v>
+      </c>
+      <c r="J18" s="42" t="s">
+        <v>42</v>
+      </c>
+      <c r="K18" s="43" t="s">
+        <v>43</v>
+      </c>
+      <c r="L18" s="44" t="s">
+        <v>44</v>
+      </c>
+      <c r="M18" s="45">
+        <v>46180</v>
+      </c>
+      <c r="N18" s="46">
+        <v>46180</v>
+      </c>
+      <c r="O18" s="47" t="s">
+        <v>90</v>
+      </c>
+      <c r="P18" s="48" t="s">
         <v>91</v>
       </c>
-      <c r="D18" s="36" t="s">
-        <v>102</v>
-      </c>
-      <c r="E18" s="37" t="s">
-        <v>92</v>
-      </c>
-      <c r="F18" s="38" t="s">
-        <v>93</v>
-      </c>
-      <c r="G18" s="39" t="s">
-        <v>77</v>
-      </c>
-      <c r="H18" s="40" t="s">
-        <v>92</v>
-      </c>
-      <c r="I18" s="41" t="s">
-        <v>110</v>
-      </c>
-      <c r="J18" s="42" t="s">
-        <v>95</v>
-      </c>
-      <c r="K18" s="43" t="s">
-        <v>96</v>
-      </c>
-      <c r="L18" s="44" t="s">
-        <v>97</v>
-      </c>
-      <c r="M18" s="45">
-        <v>46176</v>
-      </c>
-      <c r="N18" s="46">
-        <v>46177</v>
-      </c>
-      <c r="O18" s="47" t="s">
-        <v>111</v>
-      </c>
-      <c r="P18" s="48" t="s">
-        <v>111</v>
-      </c>
       <c r="Q18" s="49">
-        <v>46176</v>
+        <v>46165</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="33" t="s">
-        <v>108</v>
+        <v>92</v>
       </c>
       <c r="B19" s="34" t="s">
-        <v>109</v>
+        <v>93</v>
       </c>
       <c r="C19" s="35" t="s">
-        <v>91</v>
+        <v>19</v>
       </c>
       <c r="D19" s="36" t="s">
-        <v>102</v>
+        <v>89</v>
       </c>
       <c r="E19" s="37" t="s">
-        <v>92</v>
+        <v>21</v>
       </c>
       <c r="F19" s="38" t="s">
-        <v>93</v>
+        <v>22</v>
       </c>
       <c r="G19" s="39" t="s">
-        <v>78</v>
+        <v>23</v>
       </c>
       <c r="H19" s="40" t="s">
-        <v>92</v>
+        <v>21</v>
       </c>
       <c r="I19" s="41" t="s">
-        <v>110</v>
+        <v>94</v>
       </c>
       <c r="J19" s="42" t="s">
         <v>95</v>
@@ -2307,24 +2292,183 @@
         <v>97</v>
       </c>
       <c r="M19" s="45">
-        <v>46176</v>
+        <v>46180</v>
       </c>
       <c r="N19" s="46">
-        <v>46177</v>
+        <v>46180</v>
       </c>
       <c r="O19" s="47" t="s">
-        <v>111</v>
+        <v>98</v>
       </c>
       <c r="P19" s="48" t="s">
-        <v>111</v>
+        <v>98</v>
       </c>
       <c r="Q19" s="49">
-        <v>46176</v>
+        <v>46162</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="33" t="s">
+        <v>99</v>
+      </c>
+      <c r="B20" s="34" t="s">
+        <v>100</v>
+      </c>
+      <c r="C20" s="35" t="s">
+        <v>19</v>
+      </c>
+      <c r="D20" s="36" t="s">
+        <v>20</v>
+      </c>
+      <c r="E20" s="37" t="s">
+        <v>21</v>
+      </c>
+      <c r="F20" s="38" t="s">
+        <v>22</v>
+      </c>
+      <c r="G20" s="39" t="s">
+        <v>23</v>
+      </c>
+      <c r="H20" s="40" t="s">
+        <v>21</v>
+      </c>
+      <c r="I20" s="41" t="s">
+        <v>94</v>
+      </c>
+      <c r="J20" s="42" t="s">
+        <v>95</v>
+      </c>
+      <c r="K20" s="43" t="s">
+        <v>96</v>
+      </c>
+      <c r="L20" s="44" t="s">
+        <v>97</v>
+      </c>
+      <c r="M20" s="45">
+        <v>46180</v>
+      </c>
+      <c r="N20" s="46">
+        <v>46180</v>
+      </c>
+      <c r="O20" s="47" t="s">
+        <v>98</v>
+      </c>
+      <c r="P20" s="48" t="s">
+        <v>98</v>
+      </c>
+      <c r="Q20" s="49">
+        <v>46163</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="33" t="s">
+        <v>101</v>
+      </c>
+      <c r="B21" s="34" t="s">
+        <v>102</v>
+      </c>
+      <c r="C21" s="35" t="s">
+        <v>19</v>
+      </c>
+      <c r="D21" s="36" t="s">
+        <v>20</v>
+      </c>
+      <c r="E21" s="37" t="s">
+        <v>21</v>
+      </c>
+      <c r="F21" s="38" t="s">
+        <v>22</v>
+      </c>
+      <c r="G21" s="39" t="s">
+        <v>23</v>
+      </c>
+      <c r="H21" s="40" t="s">
+        <v>21</v>
+      </c>
+      <c r="I21" s="41" t="s">
+        <v>94</v>
+      </c>
+      <c r="J21" s="42" t="s">
+        <v>95</v>
+      </c>
+      <c r="K21" s="43" t="s">
+        <v>96</v>
+      </c>
+      <c r="L21" s="44" t="s">
+        <v>97</v>
+      </c>
+      <c r="M21" s="45">
+        <v>46180</v>
+      </c>
+      <c r="N21" s="46">
+        <v>46180</v>
+      </c>
+      <c r="O21" s="47" t="s">
+        <v>98</v>
+      </c>
+      <c r="P21" s="48" t="s">
+        <v>98</v>
+      </c>
+      <c r="Q21" s="49">
+        <v>46164</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="33" t="s">
+        <v>103</v>
+      </c>
+      <c r="B22" s="34" t="s">
+        <v>104</v>
+      </c>
+      <c r="C22" s="35" t="s">
+        <v>19</v>
+      </c>
+      <c r="D22" s="36" t="s">
+        <v>20</v>
+      </c>
+      <c r="E22" s="37" t="s">
+        <v>21</v>
+      </c>
+      <c r="F22" s="38" t="s">
+        <v>22</v>
+      </c>
+      <c r="G22" s="39" t="s">
+        <v>23</v>
+      </c>
+      <c r="H22" s="40" t="s">
+        <v>21</v>
+      </c>
+      <c r="I22" s="41" t="s">
+        <v>105</v>
+      </c>
+      <c r="J22" s="42" t="s">
+        <v>42</v>
+      </c>
+      <c r="K22" s="43" t="s">
+        <v>43</v>
+      </c>
+      <c r="L22" s="44" t="s">
+        <v>44</v>
+      </c>
+      <c r="M22" s="45">
+        <v>46180</v>
+      </c>
+      <c r="N22" s="46">
+        <v>46180</v>
+      </c>
+      <c r="O22" s="47" t="s">
+        <v>106</v>
+      </c>
+      <c r="P22" s="48" t="s">
+        <v>106</v>
+      </c>
+      <c r="Q22" s="49">
+        <v>46169</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError sqref="A1 B1 C1 D1 E1 F1 G1 H1 I1 J1 K1 L1 M1 N1 O1 P1 Q1 A2 B2 C2 D2 E2 F2 G2 H2 I2 J2 K2 L2 O2 P2 A3 B3 C3 D3 E3 F3 G3 H3 I3 J3 K3 L3 O3 P3 A4 B4 C4 D4 E4 F4 G4 H4 I4 J4 K4 L4 O4 P4 A5 B5 C5 D5 E5 F5 G5 H5 I5 J5 K5 L5 O5 P5 A6 B6 C6 D6 E6 F6 G6 H6 I6 J6 K6 L6 O6 P6 A7 B7 C7 D7 E7 F7 G7 H7 I7 J7 K7 L7 O7 P7 A8 B8 C8 D8 E8 F8 G8 H8 I8 J8 K8 L8 O8 P8 A9 B9 C9 D9 E9 F9 G9 H9 I9 J9 K9 L9 O9 P9 A10 B10 C10 D10 E10 F10 G10 H10 I10 J10 K10 L10 O10 P10 A11 B11 C11 D11 E11 F11 G11 H11 I11 J11 K11 L11 O11 P11 A12 B12 C12 D12 E12 F12 G12 H12 I12 J12 K12 L12 O12 P12 A13 B13 C13 D13 E13 F13 G13 H13 I13 J13 K13 L13 O13 P13 A14 B14 C14 D14 E14 F14 G14 H14 I14 J14 K14 L14 O14 P14 A15 B15 C15 D15 E15 F15 G15 H15 I15 J15 K15 L15 O15 P15 A16 B16 C16 D16 E16 F16 G16 H16 I16 J16 K16 L16 O16 P16 A17 B17 C17 D17 E17 F17 G17 H17 I17 J17 K17 L17 O17 P17 A18 B18 C18 D18 E18 F18 G18 H18 I18 J18 K18 L18 O18 P18 A19 B19 C19 D19 E19 F19 G19 H19 I19 J19 K19 L19 O19 P19" numberStoredAsText="true"/>
+    <ignoredError sqref="A1 B1 C1 D1 E1 F1 G1 H1 I1 J1 K1 L1 M1 N1 O1 P1 Q1 A2 B2 C2 D2 E2 F2 G2 H2 I2 J2 K2 L2 O2 P2 A3 B3 C3 D3 E3 F3 G3 H3 I3 J3 K3 L3 O3 P3 A4 B4 C4 D4 E4 F4 G4 H4 I4 J4 K4 L4 O4 P4 A5 B5 C5 D5 E5 F5 G5 H5 I5 J5 K5 L5 O5 P5 A6 B6 C6 D6 E6 F6 G6 H6 I6 J6 K6 L6 O6 P6 A7 B7 C7 D7 E7 F7 G7 H7 I7 J7 K7 L7 O7 P7 A8 B8 C8 D8 E8 F8 G8 H8 I8 J8 K8 L8 O8 P8 A9 B9 C9 D9 E9 F9 G9 H9 I9 J9 K9 L9 O9 P9 A10 B10 C10 D10 E10 F10 G10 H10 I10 J10 K10 L10 O10 P10 A11 B11 C11 D11 E11 F11 G11 H11 I11 J11 K11 L11 O11 P11 A12 B12 C12 D12 E12 F12 G12 H12 I12 J12 K12 L12 O12 P12 A13 B13 C13 D13 E13 F13 G13 H13 I13 J13 K13 L13 O13 P13 A14 B14 C14 D14 E14 F14 G14 H14 I14 J14 K14 L14 O14 P14 A15 B15 C15 D15 E15 F15 G15 H15 I15 J15 K15 L15 O15 P15 A16 B16 C16 D16 E16 F16 G16 H16 I16 J16 K16 L16 O16 P16 A17 B17 C17 D17 E17 F17 G17 H17 I17 J17 K17 L17 O17 P17 A18 B18 C18 D18 E18 F18 G18 H18 I18 J18 K18 L18 O18 P18 A19 B19 C19 D19 E19 F19 G19 H19 I19 J19 K19 L19 O19 P19 A20 B20 C20 D20 E20 F20 G20 H20 I20 J20 K20 L20 O20 P20 A21 B21 C21 D21 E21 F21 G21 H21 I21 J21 K21 L21 O21 P21 A22 B22 C22 D22 E22 F22 G22 H22 I22 J22 K22 L22 O22 P22" numberStoredAsText="true"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/trimika_data.xlsx
+++ b/trimika_data.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" count="311" uniqueCount="107">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" count="311" uniqueCount="89">
   <si>
     <t>REFERENCE NO</t>
   </si>
@@ -66,274 +66,220 @@
     <t>EXPORT DATE</t>
   </si>
   <si>
-    <t>2565445</t>
-  </si>
-  <si>
-    <t>EF4-0231218-7</t>
+    <t>2565618</t>
+  </si>
+  <si>
+    <t>EF4-0231371-4</t>
   </si>
   <si>
     <t>Vessel, Container</t>
   </si>
   <si>
+    <t>VA923640612</t>
+  </si>
+  <si>
+    <t>9903.03.01</t>
+  </si>
+  <si>
+    <t>SECTION 122 - 10% DUTY</t>
+  </si>
+  <si>
+    <t>001</t>
+  </si>
+  <si>
+    <t>5603.14.9090</t>
+  </si>
+  <si>
+    <t>VEER CORPORATIONS INC</t>
+  </si>
+  <si>
+    <t>VEECOR01</t>
+  </si>
+  <si>
+    <t>99-106989200</t>
+  </si>
+  <si>
+    <t>VEER PLASTIC PVT LTD</t>
+  </si>
+  <si>
+    <t>2565931</t>
+  </si>
+  <si>
+    <t>EF4-0231973-7</t>
+  </si>
+  <si>
+    <t>5206.11.0000</t>
+  </si>
+  <si>
+    <t>HICKORY THROWING COMPANY</t>
+  </si>
+  <si>
+    <t>HICTHR</t>
+  </si>
+  <si>
+    <t>56-124106800</t>
+  </si>
+  <si>
+    <t>HILATURAS FERRE</t>
+  </si>
+  <si>
+    <t>2565852</t>
+  </si>
+  <si>
+    <t>EF4-0231984-4</t>
+  </si>
+  <si>
     <t/>
   </si>
   <si>
-    <t>9903.03.01</t>
-  </si>
-  <si>
-    <t>SECTION 122 - 10% DUTY</t>
-  </si>
-  <si>
-    <t>001</t>
-  </si>
-  <si>
-    <t>5903.90.3090</t>
-  </si>
-  <si>
-    <t>VEER CORPORATIONS INC</t>
-  </si>
-  <si>
-    <t>VEECOR01</t>
-  </si>
-  <si>
-    <t>99-106989200</t>
-  </si>
-  <si>
-    <t>VEER PLASTIC PVT LTD</t>
-  </si>
-  <si>
-    <t>2565766</t>
-  </si>
-  <si>
-    <t>EF4-0231553-7</t>
-  </si>
-  <si>
-    <t>2565768</t>
-  </si>
-  <si>
-    <t>EF4-0231555-2</t>
-  </si>
-  <si>
-    <t>2565770</t>
-  </si>
-  <si>
-    <t>EF4-0231557-8</t>
-  </si>
-  <si>
-    <t>VA923700499</t>
-  </si>
-  <si>
-    <t>2565771</t>
-  </si>
-  <si>
-    <t>EF4-0231558-6</t>
-  </si>
-  <si>
-    <t>2565780</t>
-  </si>
-  <si>
-    <t>EF4-0231704-6</t>
-  </si>
-  <si>
-    <t>VA923700630</t>
-  </si>
-  <si>
-    <t>3505.10.0020</t>
-  </si>
-  <si>
-    <t>ROYAL INGREDIENTS GROUP BV</t>
-  </si>
-  <si>
-    <t>ROYINGRE</t>
-  </si>
-  <si>
-    <t>074601-00962</t>
-  </si>
-  <si>
-    <t>T-FIBRE INNOVATION CO., LTD.</t>
-  </si>
-  <si>
-    <t>9903.03.03</t>
-  </si>
-  <si>
-    <t>S122 -EXCLUSION-EXEMPTED PRDTS</t>
+    <t>9903.03.06</t>
+  </si>
+  <si>
+    <t>S122 EXCL,IRN/STL/ALUM,DERIV</t>
+  </si>
+  <si>
+    <t>9903.82.10,8431.39.0010</t>
+  </si>
+  <si>
+    <t>AUMUND CORPORATION</t>
+  </si>
+  <si>
+    <t>AUMCOR</t>
+  </si>
+  <si>
+    <t>58-138896800</t>
+  </si>
+  <si>
+    <t>AUMUND FOERDERTECHNIK GMBH</t>
+  </si>
+  <si>
+    <t>2615704</t>
+  </si>
+  <si>
+    <t>EF4-0232167-5</t>
+  </si>
+  <si>
+    <t>Vessel, Non-container</t>
+  </si>
+  <si>
+    <t>2916.14.2050</t>
+  </si>
+  <si>
+    <t>TRENCHLESS PRODUCTS</t>
+  </si>
+  <si>
+    <t>TREPRO01</t>
+  </si>
+  <si>
+    <t>83-157973900</t>
+  </si>
+  <si>
+    <t>POLINVENT KFT.</t>
+  </si>
+  <si>
+    <t>2615767</t>
+  </si>
+  <si>
+    <t>EF4-0232268-1</t>
+  </si>
+  <si>
+    <t>Truck, Non-container</t>
+  </si>
+  <si>
+    <t>9903.03.07</t>
+  </si>
+  <si>
+    <t>S 122-EXCLUSION, CANADA USMCA</t>
+  </si>
+  <si>
+    <t>1905.90.1041</t>
+  </si>
+  <si>
+    <t>IN 2 FOOD GOURMET LLC</t>
+  </si>
+  <si>
+    <t>IN2F</t>
+  </si>
+  <si>
+    <t>26-458152400</t>
+  </si>
+  <si>
+    <t>AGM BAKERY</t>
   </si>
   <si>
     <t>002</t>
   </si>
   <si>
-    <t>1108.14.0000</t>
-  </si>
-  <si>
-    <t>2565879</t>
-  </si>
-  <si>
-    <t>EF4-0231815-0</t>
-  </si>
-  <si>
-    <t>VVS13924784</t>
-  </si>
-  <si>
-    <t>1806.90.9090</t>
-  </si>
-  <si>
-    <t>DOBLA USA MFG LLC</t>
-  </si>
-  <si>
-    <t>DOBUSA</t>
-  </si>
-  <si>
-    <t>41-218954800</t>
-  </si>
-  <si>
-    <t>DOBLA BELGIUM PRODUCTIONS NV/SA</t>
-  </si>
-  <si>
-    <t>DOBLA LOGISTICS BVBA</t>
-  </si>
-  <si>
-    <t>2565844</t>
-  </si>
-  <si>
-    <t>EF4-0231823-4</t>
-  </si>
-  <si>
-    <t>1108.13.0010</t>
-  </si>
-  <si>
-    <t>PRZEDSIEBIORSTWO PRZEMYSLU ZIEMNIAC</t>
-  </si>
-  <si>
-    <t>PRZEDSIEBIORSTWO PRZEMYSLU ZIEMNIACZANEGO PEPEES S.A.</t>
-  </si>
-  <si>
-    <t>2565742</t>
-  </si>
-  <si>
-    <t>EF4-0231828-3</t>
-  </si>
-  <si>
-    <t>V0459386715</t>
-  </si>
-  <si>
-    <t>6310.10.2020</t>
-  </si>
-  <si>
-    <t>FOOTING FIRST, LLC</t>
-  </si>
-  <si>
-    <t>FOOFIR</t>
-  </si>
-  <si>
-    <t>27-059921300</t>
-  </si>
-  <si>
-    <t>ALTEX TEXTILRECYCLING</t>
-  </si>
-  <si>
-    <t>2565910</t>
-  </si>
-  <si>
-    <t>EF4-0231923-2</t>
-  </si>
-  <si>
-    <t>1109.00.1000</t>
-  </si>
-  <si>
-    <t>SEDAMYL UK</t>
-  </si>
-  <si>
-    <t>2565947</t>
-  </si>
-  <si>
-    <t>EF4-0231924-0</t>
-  </si>
-  <si>
-    <t>1109.00.9020</t>
-  </si>
-  <si>
-    <t>2565934</t>
-  </si>
-  <si>
-    <t>EF4-0231991-9</t>
-  </si>
-  <si>
-    <t>V0710339289</t>
-  </si>
-  <si>
-    <t>AKV LANGHOLT AMBA</t>
-  </si>
-  <si>
-    <t>2565944</t>
-  </si>
-  <si>
-    <t>EF4-0231993-5</t>
-  </si>
-  <si>
-    <t>2565948</t>
-  </si>
-  <si>
-    <t>EF4-0231994-3</t>
-  </si>
-  <si>
-    <t>2566033</t>
-  </si>
-  <si>
-    <t>EF4-0232066-9</t>
-  </si>
-  <si>
-    <t>V0710333241</t>
-  </si>
-  <si>
-    <t>JACKERING MUHLEN UND NAHRMITTELWERK</t>
-  </si>
-  <si>
-    <t>JACKERING MUHLEN UND NAHRMITTELWERKE GMBH</t>
-  </si>
-  <si>
-    <t>2565912</t>
-  </si>
-  <si>
-    <t>EF4-0232086-7</t>
-  </si>
-  <si>
-    <t>3920.62.0090</t>
-  </si>
-  <si>
-    <t>TEUFELBERGER G.E.S.M.B.H</t>
-  </si>
-  <si>
-    <t>TEUSEI01</t>
-  </si>
-  <si>
-    <t>181704-13780</t>
-  </si>
-  <si>
-    <t>TEUFELBERGER GMBH</t>
-  </si>
-  <si>
-    <t>2565916</t>
-  </si>
-  <si>
-    <t>EF4-0232089-1</t>
-  </si>
-  <si>
-    <t>2565917</t>
-  </si>
-  <si>
-    <t>EF4-0232091-7</t>
-  </si>
-  <si>
-    <t>2566101</t>
-  </si>
-  <si>
-    <t>EF4-0232243-4</t>
-  </si>
-  <si>
-    <t>1109.00.9010</t>
-  </si>
-  <si>
-    <t>KROENER-STARKE BIO GMBH</t>
+    <t>003</t>
+  </si>
+  <si>
+    <t>004</t>
+  </si>
+  <si>
+    <t>005</t>
+  </si>
+  <si>
+    <t>006</t>
+  </si>
+  <si>
+    <t>007</t>
+  </si>
+  <si>
+    <t>008</t>
+  </si>
+  <si>
+    <t>009</t>
+  </si>
+  <si>
+    <t>010</t>
+  </si>
+  <si>
+    <t>011</t>
+  </si>
+  <si>
+    <t>012</t>
+  </si>
+  <si>
+    <t>013</t>
+  </si>
+  <si>
+    <t>014</t>
+  </si>
+  <si>
+    <t>015</t>
+  </si>
+  <si>
+    <t>4539443</t>
+  </si>
+  <si>
+    <t>EF4-0232337-4</t>
+  </si>
+  <si>
+    <t>Air, Non-container</t>
+  </si>
+  <si>
+    <t>784771645</t>
+  </si>
+  <si>
+    <t>9903.94.06,8531.90.3000</t>
+  </si>
+  <si>
+    <t>CANTRELL GAINCO GROUP INC</t>
+  </si>
+  <si>
+    <t>CANGAI01</t>
+  </si>
+  <si>
+    <t>31-151121700</t>
+  </si>
+  <si>
+    <t>FORTRESS TECHNOLOGY</t>
+  </si>
+  <si>
+    <t>4539444</t>
+  </si>
+  <si>
+    <t>EF4-0232338-2</t>
   </si>
 </sst>
 </file>
@@ -1391,10 +1337,10 @@
         <v>27</v>
       </c>
       <c r="M2" s="45">
-        <v>46179</v>
+        <v>46161</v>
       </c>
       <c r="N2" s="46">
-        <v>46180</v>
+        <v>46181</v>
       </c>
       <c r="O2" s="47" t="s">
         <v>28</v>
@@ -1403,7 +1349,7 @@
         <v>28</v>
       </c>
       <c r="Q2" s="49">
-        <v>46115</v>
+        <v>46131</v>
       </c>
     </row>
     <row r="3">
@@ -1432,98 +1378,98 @@
         <v>21</v>
       </c>
       <c r="I3" s="41" t="s">
-        <v>24</v>
+        <v>31</v>
       </c>
       <c r="J3" s="42" t="s">
-        <v>25</v>
+        <v>32</v>
       </c>
       <c r="K3" s="43" t="s">
-        <v>26</v>
+        <v>33</v>
       </c>
       <c r="L3" s="44" t="s">
-        <v>27</v>
+        <v>34</v>
       </c>
       <c r="M3" s="45">
-        <v>46179</v>
+        <v>46181</v>
       </c>
       <c r="N3" s="46">
-        <v>46180</v>
+        <v>46181</v>
       </c>
       <c r="O3" s="47" t="s">
-        <v>28</v>
+        <v>35</v>
       </c>
       <c r="P3" s="48" t="s">
-        <v>28</v>
+        <v>35</v>
       </c>
       <c r="Q3" s="49">
-        <v>46145</v>
+        <v>46159</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="33" t="s">
-        <v>31</v>
+        <v>36</v>
       </c>
       <c r="B4" s="34" t="s">
-        <v>32</v>
+        <v>37</v>
       </c>
       <c r="C4" s="35" t="s">
         <v>19</v>
       </c>
       <c r="D4" s="36" t="s">
-        <v>20</v>
+        <v>38</v>
       </c>
       <c r="E4" s="37" t="s">
-        <v>21</v>
+        <v>39</v>
       </c>
       <c r="F4" s="38" t="s">
-        <v>22</v>
+        <v>40</v>
       </c>
       <c r="G4" s="39" t="s">
         <v>23</v>
       </c>
       <c r="H4" s="40" t="s">
-        <v>21</v>
+        <v>39</v>
       </c>
       <c r="I4" s="41" t="s">
-        <v>24</v>
+        <v>41</v>
       </c>
       <c r="J4" s="42" t="s">
-        <v>25</v>
+        <v>42</v>
       </c>
       <c r="K4" s="43" t="s">
-        <v>26</v>
+        <v>43</v>
       </c>
       <c r="L4" s="44" t="s">
-        <v>27</v>
+        <v>44</v>
       </c>
       <c r="M4" s="45">
-        <v>46179</v>
+        <v>46181</v>
       </c>
       <c r="N4" s="46">
-        <v>46180</v>
+        <v>46181</v>
       </c>
       <c r="O4" s="47" t="s">
-        <v>28</v>
+        <v>45</v>
       </c>
       <c r="P4" s="48" t="s">
-        <v>28</v>
+        <v>45</v>
       </c>
       <c r="Q4" s="49">
-        <v>46145</v>
+        <v>46155</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="33" t="s">
-        <v>33</v>
+        <v>46</v>
       </c>
       <c r="B5" s="34" t="s">
-        <v>34</v>
+        <v>47</v>
       </c>
       <c r="C5" s="35" t="s">
-        <v>19</v>
+        <v>48</v>
       </c>
       <c r="D5" s="36" t="s">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="E5" s="37" t="s">
         <v>21</v>
@@ -1538,932 +1484,932 @@
         <v>21</v>
       </c>
       <c r="I5" s="41" t="s">
-        <v>24</v>
+        <v>49</v>
       </c>
       <c r="J5" s="42" t="s">
-        <v>25</v>
+        <v>50</v>
       </c>
       <c r="K5" s="43" t="s">
-        <v>26</v>
+        <v>51</v>
       </c>
       <c r="L5" s="44" t="s">
-        <v>27</v>
+        <v>52</v>
       </c>
       <c r="M5" s="45">
-        <v>46171</v>
+        <v>46175</v>
       </c>
       <c r="N5" s="46">
-        <v>46180</v>
+        <v>46181</v>
       </c>
       <c r="O5" s="47" t="s">
-        <v>28</v>
+        <v>53</v>
       </c>
       <c r="P5" s="48" t="s">
-        <v>28</v>
+        <v>53</v>
       </c>
       <c r="Q5" s="49">
-        <v>46145</v>
+        <v>46164</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="33" t="s">
-        <v>36</v>
+        <v>54</v>
       </c>
       <c r="B6" s="34" t="s">
-        <v>37</v>
+        <v>55</v>
       </c>
       <c r="C6" s="35" t="s">
-        <v>19</v>
+        <v>56</v>
       </c>
       <c r="D6" s="36" t="s">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="E6" s="37" t="s">
-        <v>21</v>
+        <v>57</v>
       </c>
       <c r="F6" s="38" t="s">
-        <v>22</v>
+        <v>58</v>
       </c>
       <c r="G6" s="39" t="s">
         <v>23</v>
       </c>
       <c r="H6" s="40" t="s">
-        <v>21</v>
+        <v>57</v>
       </c>
       <c r="I6" s="41" t="s">
-        <v>24</v>
+        <v>59</v>
       </c>
       <c r="J6" s="42" t="s">
-        <v>25</v>
+        <v>60</v>
       </c>
       <c r="K6" s="43" t="s">
-        <v>26</v>
+        <v>61</v>
       </c>
       <c r="L6" s="44" t="s">
-        <v>27</v>
+        <v>62</v>
       </c>
       <c r="M6" s="45">
-        <v>46171</v>
+        <v>46177</v>
       </c>
       <c r="N6" s="46">
-        <v>46180</v>
+        <v>46181</v>
       </c>
       <c r="O6" s="47" t="s">
-        <v>28</v>
+        <v>63</v>
       </c>
       <c r="P6" s="48" t="s">
-        <v>28</v>
+        <v>63</v>
       </c>
       <c r="Q6" s="49">
-        <v>46145</v>
+        <v>46177</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="33" t="s">
+        <v>54</v>
+      </c>
+      <c r="B7" s="34" t="s">
+        <v>55</v>
+      </c>
+      <c r="C7" s="35" t="s">
+        <v>56</v>
+      </c>
+      <c r="D7" s="36" t="s">
         <v>38</v>
       </c>
-      <c r="B7" s="34" t="s">
-        <v>39</v>
-      </c>
-      <c r="C7" s="35" t="s">
-        <v>19</v>
-      </c>
-      <c r="D7" s="36" t="s">
-        <v>40</v>
-      </c>
       <c r="E7" s="37" t="s">
-        <v>21</v>
+        <v>57</v>
       </c>
       <c r="F7" s="38" t="s">
-        <v>22</v>
+        <v>58</v>
       </c>
       <c r="G7" s="39" t="s">
-        <v>23</v>
+        <v>64</v>
       </c>
       <c r="H7" s="40" t="s">
-        <v>21</v>
+        <v>57</v>
       </c>
       <c r="I7" s="41" t="s">
-        <v>41</v>
+        <v>59</v>
       </c>
       <c r="J7" s="42" t="s">
-        <v>42</v>
+        <v>60</v>
       </c>
       <c r="K7" s="43" t="s">
-        <v>43</v>
+        <v>61</v>
       </c>
       <c r="L7" s="44" t="s">
-        <v>44</v>
+        <v>62</v>
       </c>
       <c r="M7" s="45">
-        <v>46175</v>
+        <v>46177</v>
       </c>
       <c r="N7" s="46">
-        <v>46180</v>
+        <v>46181</v>
       </c>
       <c r="O7" s="47" t="s">
-        <v>45</v>
+        <v>63</v>
       </c>
       <c r="P7" s="48" t="s">
-        <v>45</v>
+        <v>63</v>
       </c>
       <c r="Q7" s="49">
-        <v>46148</v>
+        <v>46177</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="33" t="s">
+        <v>54</v>
+      </c>
+      <c r="B8" s="34" t="s">
+        <v>55</v>
+      </c>
+      <c r="C8" s="35" t="s">
+        <v>56</v>
+      </c>
+      <c r="D8" s="36" t="s">
         <v>38</v>
       </c>
-      <c r="B8" s="34" t="s">
-        <v>39</v>
-      </c>
-      <c r="C8" s="35" t="s">
-        <v>19</v>
-      </c>
-      <c r="D8" s="36" t="s">
-        <v>40</v>
-      </c>
       <c r="E8" s="37" t="s">
-        <v>46</v>
+        <v>57</v>
       </c>
       <c r="F8" s="38" t="s">
-        <v>47</v>
+        <v>58</v>
       </c>
       <c r="G8" s="39" t="s">
-        <v>48</v>
+        <v>65</v>
       </c>
       <c r="H8" s="40" t="s">
-        <v>46</v>
+        <v>57</v>
       </c>
       <c r="I8" s="41" t="s">
-        <v>49</v>
+        <v>59</v>
       </c>
       <c r="J8" s="42" t="s">
-        <v>42</v>
+        <v>60</v>
       </c>
       <c r="K8" s="43" t="s">
-        <v>43</v>
+        <v>61</v>
       </c>
       <c r="L8" s="44" t="s">
-        <v>44</v>
+        <v>62</v>
       </c>
       <c r="M8" s="45">
-        <v>46175</v>
+        <v>46177</v>
       </c>
       <c r="N8" s="46">
-        <v>46180</v>
+        <v>46181</v>
       </c>
       <c r="O8" s="47" t="s">
-        <v>45</v>
+        <v>63</v>
       </c>
       <c r="P8" s="48" t="s">
-        <v>45</v>
+        <v>63</v>
       </c>
       <c r="Q8" s="49">
-        <v>46148</v>
+        <v>46177</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="33" t="s">
-        <v>50</v>
+        <v>54</v>
       </c>
       <c r="B9" s="34" t="s">
-        <v>51</v>
+        <v>55</v>
       </c>
       <c r="C9" s="35" t="s">
-        <v>19</v>
+        <v>56</v>
       </c>
       <c r="D9" s="36" t="s">
-        <v>52</v>
+        <v>38</v>
       </c>
       <c r="E9" s="37" t="s">
-        <v>21</v>
+        <v>57</v>
       </c>
       <c r="F9" s="38" t="s">
-        <v>22</v>
+        <v>58</v>
       </c>
       <c r="G9" s="39" t="s">
-        <v>23</v>
+        <v>66</v>
       </c>
       <c r="H9" s="40" t="s">
-        <v>21</v>
+        <v>57</v>
       </c>
       <c r="I9" s="41" t="s">
-        <v>53</v>
+        <v>59</v>
       </c>
       <c r="J9" s="42" t="s">
-        <v>54</v>
+        <v>60</v>
       </c>
       <c r="K9" s="43" t="s">
-        <v>55</v>
+        <v>61</v>
       </c>
       <c r="L9" s="44" t="s">
-        <v>56</v>
+        <v>62</v>
       </c>
       <c r="M9" s="45">
-        <v>46180</v>
+        <v>46177</v>
       </c>
       <c r="N9" s="46">
-        <v>46180</v>
+        <v>46181</v>
       </c>
       <c r="O9" s="47" t="s">
-        <v>57</v>
+        <v>63</v>
       </c>
       <c r="P9" s="48" t="s">
-        <v>57</v>
+        <v>63</v>
       </c>
       <c r="Q9" s="49">
-        <v>46154</v>
+        <v>46177</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="33" t="s">
-        <v>50</v>
+        <v>54</v>
       </c>
       <c r="B10" s="34" t="s">
-        <v>51</v>
+        <v>55</v>
       </c>
       <c r="C10" s="35" t="s">
-        <v>19</v>
+        <v>56</v>
       </c>
       <c r="D10" s="36" t="s">
-        <v>52</v>
+        <v>38</v>
       </c>
       <c r="E10" s="37" t="s">
-        <v>21</v>
+        <v>57</v>
       </c>
       <c r="F10" s="38" t="s">
-        <v>22</v>
+        <v>58</v>
       </c>
       <c r="G10" s="39" t="s">
-        <v>48</v>
+        <v>67</v>
       </c>
       <c r="H10" s="40" t="s">
-        <v>21</v>
+        <v>57</v>
       </c>
       <c r="I10" s="41" t="s">
-        <v>53</v>
+        <v>59</v>
       </c>
       <c r="J10" s="42" t="s">
-        <v>54</v>
+        <v>60</v>
       </c>
       <c r="K10" s="43" t="s">
-        <v>55</v>
+        <v>61</v>
       </c>
       <c r="L10" s="44" t="s">
-        <v>56</v>
+        <v>62</v>
       </c>
       <c r="M10" s="45">
-        <v>46180</v>
+        <v>46177</v>
       </c>
       <c r="N10" s="46">
-        <v>46180</v>
+        <v>46181</v>
       </c>
       <c r="O10" s="47" t="s">
-        <v>58</v>
+        <v>63</v>
       </c>
       <c r="P10" s="48" t="s">
-        <v>58</v>
+        <v>63</v>
       </c>
       <c r="Q10" s="49">
-        <v>46154</v>
+        <v>46177</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="33" t="s">
+        <v>54</v>
+      </c>
+      <c r="B11" s="34" t="s">
+        <v>55</v>
+      </c>
+      <c r="C11" s="35" t="s">
+        <v>56</v>
+      </c>
+      <c r="D11" s="36" t="s">
+        <v>38</v>
+      </c>
+      <c r="E11" s="37" t="s">
+        <v>57</v>
+      </c>
+      <c r="F11" s="38" t="s">
+        <v>58</v>
+      </c>
+      <c r="G11" s="39" t="s">
+        <v>68</v>
+      </c>
+      <c r="H11" s="40" t="s">
+        <v>57</v>
+      </c>
+      <c r="I11" s="41" t="s">
         <v>59</v>
       </c>
-      <c r="B11" s="34" t="s">
+      <c r="J11" s="42" t="s">
         <v>60</v>
       </c>
-      <c r="C11" s="35" t="s">
-        <v>19</v>
-      </c>
-      <c r="D11" s="36" t="s">
-        <v>20</v>
-      </c>
-      <c r="E11" s="37" t="s">
-        <v>21</v>
-      </c>
-      <c r="F11" s="38" t="s">
-        <v>20</v>
-      </c>
-      <c r="G11" s="39" t="s">
-        <v>23</v>
-      </c>
-      <c r="H11" s="40" t="s">
-        <v>21</v>
-      </c>
-      <c r="I11" s="41" t="s">
+      <c r="K11" s="43" t="s">
         <v>61</v>
       </c>
-      <c r="J11" s="42" t="s">
-        <v>42</v>
-      </c>
-      <c r="K11" s="43" t="s">
-        <v>43</v>
-      </c>
       <c r="L11" s="44" t="s">
-        <v>44</v>
+        <v>62</v>
       </c>
       <c r="M11" s="45">
-        <v>46180</v>
+        <v>46177</v>
       </c>
       <c r="N11" s="46">
-        <v>46180</v>
+        <v>46181</v>
       </c>
       <c r="O11" s="47" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="P11" s="48" t="s">
         <v>63</v>
       </c>
       <c r="Q11" s="49">
-        <v>46153</v>
+        <v>46177</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="33" t="s">
-        <v>64</v>
+        <v>54</v>
       </c>
       <c r="B12" s="34" t="s">
-        <v>65</v>
+        <v>55</v>
       </c>
       <c r="C12" s="35" t="s">
-        <v>19</v>
+        <v>56</v>
       </c>
       <c r="D12" s="36" t="s">
-        <v>66</v>
+        <v>38</v>
       </c>
       <c r="E12" s="37" t="s">
-        <v>21</v>
+        <v>57</v>
       </c>
       <c r="F12" s="38" t="s">
-        <v>22</v>
+        <v>58</v>
       </c>
       <c r="G12" s="39" t="s">
-        <v>23</v>
+        <v>69</v>
       </c>
       <c r="H12" s="40" t="s">
-        <v>21</v>
+        <v>57</v>
       </c>
       <c r="I12" s="41" t="s">
-        <v>67</v>
+        <v>59</v>
       </c>
       <c r="J12" s="42" t="s">
-        <v>68</v>
+        <v>60</v>
       </c>
       <c r="K12" s="43" t="s">
-        <v>69</v>
+        <v>61</v>
       </c>
       <c r="L12" s="44" t="s">
-        <v>70</v>
+        <v>62</v>
       </c>
       <c r="M12" s="45">
-        <v>46171</v>
+        <v>46177</v>
       </c>
       <c r="N12" s="46">
-        <v>46180</v>
+        <v>46181</v>
       </c>
       <c r="O12" s="47" t="s">
-        <v>71</v>
+        <v>63</v>
       </c>
       <c r="P12" s="48" t="s">
-        <v>71</v>
+        <v>63</v>
       </c>
       <c r="Q12" s="49">
-        <v>46154</v>
+        <v>46177</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="33" t="s">
-        <v>72</v>
+        <v>54</v>
       </c>
       <c r="B13" s="34" t="s">
-        <v>73</v>
+        <v>55</v>
       </c>
       <c r="C13" s="35" t="s">
-        <v>19</v>
+        <v>56</v>
       </c>
       <c r="D13" s="36" t="s">
-        <v>66</v>
+        <v>38</v>
       </c>
       <c r="E13" s="37" t="s">
-        <v>21</v>
+        <v>57</v>
       </c>
       <c r="F13" s="38" t="s">
-        <v>22</v>
+        <v>58</v>
       </c>
       <c r="G13" s="39" t="s">
-        <v>23</v>
+        <v>70</v>
       </c>
       <c r="H13" s="40" t="s">
-        <v>21</v>
+        <v>57</v>
       </c>
       <c r="I13" s="41" t="s">
-        <v>74</v>
+        <v>59</v>
       </c>
       <c r="J13" s="42" t="s">
-        <v>42</v>
+        <v>60</v>
       </c>
       <c r="K13" s="43" t="s">
-        <v>43</v>
+        <v>61</v>
       </c>
       <c r="L13" s="44" t="s">
-        <v>44</v>
+        <v>62</v>
       </c>
       <c r="M13" s="45">
-        <v>46180</v>
+        <v>46177</v>
       </c>
       <c r="N13" s="46">
-        <v>46180</v>
+        <v>46181</v>
       </c>
       <c r="O13" s="47" t="s">
-        <v>75</v>
+        <v>63</v>
       </c>
       <c r="P13" s="48" t="s">
-        <v>75</v>
+        <v>63</v>
       </c>
       <c r="Q13" s="49">
-        <v>46157</v>
+        <v>46177</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="33" t="s">
-        <v>76</v>
+        <v>54</v>
       </c>
       <c r="B14" s="34" t="s">
-        <v>77</v>
+        <v>55</v>
       </c>
       <c r="C14" s="35" t="s">
-        <v>19</v>
+        <v>56</v>
       </c>
       <c r="D14" s="36" t="s">
-        <v>20</v>
+        <v>38</v>
       </c>
       <c r="E14" s="37" t="s">
-        <v>21</v>
+        <v>57</v>
       </c>
       <c r="F14" s="38" t="s">
-        <v>22</v>
+        <v>58</v>
       </c>
       <c r="G14" s="39" t="s">
-        <v>23</v>
+        <v>71</v>
       </c>
       <c r="H14" s="40" t="s">
-        <v>21</v>
+        <v>57</v>
       </c>
       <c r="I14" s="41" t="s">
-        <v>78</v>
+        <v>59</v>
       </c>
       <c r="J14" s="42" t="s">
-        <v>42</v>
+        <v>60</v>
       </c>
       <c r="K14" s="43" t="s">
-        <v>43</v>
+        <v>61</v>
       </c>
       <c r="L14" s="44" t="s">
-        <v>44</v>
+        <v>62</v>
       </c>
       <c r="M14" s="45">
-        <v>46180</v>
+        <v>46177</v>
       </c>
       <c r="N14" s="46">
-        <v>46180</v>
+        <v>46181</v>
       </c>
       <c r="O14" s="47" t="s">
-        <v>75</v>
+        <v>63</v>
       </c>
       <c r="P14" s="48" t="s">
-        <v>75</v>
+        <v>63</v>
       </c>
       <c r="Q14" s="49">
-        <v>46158</v>
+        <v>46177</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="33" t="s">
-        <v>79</v>
+        <v>54</v>
       </c>
       <c r="B15" s="34" t="s">
-        <v>80</v>
+        <v>55</v>
       </c>
       <c r="C15" s="35" t="s">
-        <v>19</v>
+        <v>56</v>
       </c>
       <c r="D15" s="36" t="s">
-        <v>81</v>
+        <v>38</v>
       </c>
       <c r="E15" s="37" t="s">
-        <v>21</v>
+        <v>57</v>
       </c>
       <c r="F15" s="38" t="s">
-        <v>22</v>
+        <v>58</v>
       </c>
       <c r="G15" s="39" t="s">
-        <v>23</v>
+        <v>72</v>
       </c>
       <c r="H15" s="40" t="s">
-        <v>21</v>
+        <v>57</v>
       </c>
       <c r="I15" s="41" t="s">
+        <v>59</v>
+      </c>
+      <c r="J15" s="42" t="s">
+        <v>60</v>
+      </c>
+      <c r="K15" s="43" t="s">
         <v>61</v>
       </c>
-      <c r="J15" s="42" t="s">
-        <v>42</v>
-      </c>
-      <c r="K15" s="43" t="s">
-        <v>43</v>
-      </c>
       <c r="L15" s="44" t="s">
-        <v>44</v>
+        <v>62</v>
       </c>
       <c r="M15" s="45">
-        <v>46180</v>
+        <v>46177</v>
       </c>
       <c r="N15" s="46">
-        <v>46180</v>
+        <v>46181</v>
       </c>
       <c r="O15" s="47" t="s">
-        <v>82</v>
+        <v>63</v>
       </c>
       <c r="P15" s="48" t="s">
-        <v>82</v>
+        <v>63</v>
       </c>
       <c r="Q15" s="49">
-        <v>46160</v>
+        <v>46177</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="33" t="s">
-        <v>83</v>
+        <v>54</v>
       </c>
       <c r="B16" s="34" t="s">
-        <v>84</v>
+        <v>55</v>
       </c>
       <c r="C16" s="35" t="s">
-        <v>19</v>
+        <v>56</v>
       </c>
       <c r="D16" s="36" t="s">
-        <v>81</v>
+        <v>38</v>
       </c>
       <c r="E16" s="37" t="s">
-        <v>21</v>
+        <v>57</v>
       </c>
       <c r="F16" s="38" t="s">
-        <v>22</v>
+        <v>58</v>
       </c>
       <c r="G16" s="39" t="s">
-        <v>23</v>
+        <v>73</v>
       </c>
       <c r="H16" s="40" t="s">
-        <v>21</v>
+        <v>57</v>
       </c>
       <c r="I16" s="41" t="s">
+        <v>59</v>
+      </c>
+      <c r="J16" s="42" t="s">
+        <v>60</v>
+      </c>
+      <c r="K16" s="43" t="s">
         <v>61</v>
       </c>
-      <c r="J16" s="42" t="s">
-        <v>42</v>
-      </c>
-      <c r="K16" s="43" t="s">
-        <v>43</v>
-      </c>
       <c r="L16" s="44" t="s">
-        <v>44</v>
+        <v>62</v>
       </c>
       <c r="M16" s="45">
-        <v>46180</v>
+        <v>46177</v>
       </c>
       <c r="N16" s="46">
-        <v>46180</v>
+        <v>46181</v>
       </c>
       <c r="O16" s="47" t="s">
-        <v>82</v>
+        <v>63</v>
       </c>
       <c r="P16" s="48" t="s">
-        <v>82</v>
+        <v>63</v>
       </c>
       <c r="Q16" s="49">
-        <v>46160</v>
+        <v>46177</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="33" t="s">
-        <v>85</v>
+        <v>54</v>
       </c>
       <c r="B17" s="34" t="s">
-        <v>86</v>
+        <v>55</v>
       </c>
       <c r="C17" s="35" t="s">
-        <v>19</v>
+        <v>56</v>
       </c>
       <c r="D17" s="36" t="s">
-        <v>81</v>
+        <v>38</v>
       </c>
       <c r="E17" s="37" t="s">
-        <v>21</v>
+        <v>57</v>
       </c>
       <c r="F17" s="38" t="s">
-        <v>22</v>
+        <v>58</v>
       </c>
       <c r="G17" s="39" t="s">
-        <v>23</v>
+        <v>74</v>
       </c>
       <c r="H17" s="40" t="s">
-        <v>21</v>
+        <v>57</v>
       </c>
       <c r="I17" s="41" t="s">
+        <v>59</v>
+      </c>
+      <c r="J17" s="42" t="s">
+        <v>60</v>
+      </c>
+      <c r="K17" s="43" t="s">
         <v>61</v>
       </c>
-      <c r="J17" s="42" t="s">
-        <v>42</v>
-      </c>
-      <c r="K17" s="43" t="s">
-        <v>43</v>
-      </c>
       <c r="L17" s="44" t="s">
-        <v>44</v>
+        <v>62</v>
       </c>
       <c r="M17" s="45">
-        <v>46180</v>
+        <v>46177</v>
       </c>
       <c r="N17" s="46">
-        <v>46180</v>
+        <v>46181</v>
       </c>
       <c r="O17" s="47" t="s">
-        <v>82</v>
+        <v>63</v>
       </c>
       <c r="P17" s="48" t="s">
-        <v>82</v>
+        <v>63</v>
       </c>
       <c r="Q17" s="49">
-        <v>46160</v>
+        <v>46177</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="33" t="s">
-        <v>87</v>
+        <v>54</v>
       </c>
       <c r="B18" s="34" t="s">
-        <v>88</v>
+        <v>55</v>
       </c>
       <c r="C18" s="35" t="s">
-        <v>19</v>
+        <v>56</v>
       </c>
       <c r="D18" s="36" t="s">
-        <v>89</v>
+        <v>38</v>
       </c>
       <c r="E18" s="37" t="s">
-        <v>21</v>
+        <v>57</v>
       </c>
       <c r="F18" s="38" t="s">
-        <v>22</v>
+        <v>58</v>
       </c>
       <c r="G18" s="39" t="s">
-        <v>23</v>
+        <v>75</v>
       </c>
       <c r="H18" s="40" t="s">
-        <v>21</v>
+        <v>57</v>
       </c>
       <c r="I18" s="41" t="s">
-        <v>78</v>
+        <v>59</v>
       </c>
       <c r="J18" s="42" t="s">
-        <v>42</v>
+        <v>60</v>
       </c>
       <c r="K18" s="43" t="s">
-        <v>43</v>
+        <v>61</v>
       </c>
       <c r="L18" s="44" t="s">
-        <v>44</v>
+        <v>62</v>
       </c>
       <c r="M18" s="45">
-        <v>46180</v>
+        <v>46177</v>
       </c>
       <c r="N18" s="46">
-        <v>46180</v>
+        <v>46181</v>
       </c>
       <c r="O18" s="47" t="s">
-        <v>90</v>
+        <v>63</v>
       </c>
       <c r="P18" s="48" t="s">
-        <v>91</v>
+        <v>63</v>
       </c>
       <c r="Q18" s="49">
-        <v>46165</v>
+        <v>46177</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="33" t="s">
-        <v>92</v>
+        <v>54</v>
       </c>
       <c r="B19" s="34" t="s">
-        <v>93</v>
+        <v>55</v>
       </c>
       <c r="C19" s="35" t="s">
-        <v>19</v>
+        <v>56</v>
       </c>
       <c r="D19" s="36" t="s">
-        <v>89</v>
+        <v>38</v>
       </c>
       <c r="E19" s="37" t="s">
-        <v>21</v>
+        <v>57</v>
       </c>
       <c r="F19" s="38" t="s">
-        <v>22</v>
+        <v>58</v>
       </c>
       <c r="G19" s="39" t="s">
-        <v>23</v>
+        <v>76</v>
       </c>
       <c r="H19" s="40" t="s">
-        <v>21</v>
+        <v>57</v>
       </c>
       <c r="I19" s="41" t="s">
-        <v>94</v>
+        <v>59</v>
       </c>
       <c r="J19" s="42" t="s">
-        <v>95</v>
+        <v>60</v>
       </c>
       <c r="K19" s="43" t="s">
-        <v>96</v>
+        <v>61</v>
       </c>
       <c r="L19" s="44" t="s">
-        <v>97</v>
+        <v>62</v>
       </c>
       <c r="M19" s="45">
-        <v>46180</v>
+        <v>46177</v>
       </c>
       <c r="N19" s="46">
-        <v>46180</v>
+        <v>46181</v>
       </c>
       <c r="O19" s="47" t="s">
-        <v>98</v>
+        <v>63</v>
       </c>
       <c r="P19" s="48" t="s">
-        <v>98</v>
+        <v>63</v>
       </c>
       <c r="Q19" s="49">
-        <v>46162</v>
+        <v>46177</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="33" t="s">
-        <v>99</v>
+        <v>54</v>
       </c>
       <c r="B20" s="34" t="s">
-        <v>100</v>
+        <v>55</v>
       </c>
       <c r="C20" s="35" t="s">
-        <v>19</v>
+        <v>56</v>
       </c>
       <c r="D20" s="36" t="s">
-        <v>20</v>
+        <v>38</v>
       </c>
       <c r="E20" s="37" t="s">
-        <v>21</v>
+        <v>57</v>
       </c>
       <c r="F20" s="38" t="s">
-        <v>22</v>
+        <v>58</v>
       </c>
       <c r="G20" s="39" t="s">
-        <v>23</v>
+        <v>77</v>
       </c>
       <c r="H20" s="40" t="s">
-        <v>21</v>
+        <v>57</v>
       </c>
       <c r="I20" s="41" t="s">
-        <v>94</v>
+        <v>59</v>
       </c>
       <c r="J20" s="42" t="s">
-        <v>95</v>
+        <v>60</v>
       </c>
       <c r="K20" s="43" t="s">
-        <v>96</v>
+        <v>61</v>
       </c>
       <c r="L20" s="44" t="s">
-        <v>97</v>
+        <v>62</v>
       </c>
       <c r="M20" s="45">
-        <v>46180</v>
+        <v>46177</v>
       </c>
       <c r="N20" s="46">
-        <v>46180</v>
+        <v>46181</v>
       </c>
       <c r="O20" s="47" t="s">
-        <v>98</v>
+        <v>63</v>
       </c>
       <c r="P20" s="48" t="s">
-        <v>98</v>
+        <v>63</v>
       </c>
       <c r="Q20" s="49">
-        <v>46163</v>
+        <v>46177</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="33" t="s">
-        <v>101</v>
+        <v>78</v>
       </c>
       <c r="B21" s="34" t="s">
-        <v>102</v>
+        <v>79</v>
       </c>
       <c r="C21" s="35" t="s">
-        <v>19</v>
+        <v>80</v>
       </c>
       <c r="D21" s="36" t="s">
-        <v>20</v>
+        <v>81</v>
       </c>
       <c r="E21" s="37" t="s">
-        <v>21</v>
+        <v>57</v>
       </c>
       <c r="F21" s="38" t="s">
-        <v>22</v>
+        <v>58</v>
       </c>
       <c r="G21" s="39" t="s">
         <v>23</v>
       </c>
       <c r="H21" s="40" t="s">
-        <v>21</v>
+        <v>57</v>
       </c>
       <c r="I21" s="41" t="s">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="J21" s="42" t="s">
-        <v>95</v>
+        <v>83</v>
       </c>
       <c r="K21" s="43" t="s">
-        <v>96</v>
+        <v>84</v>
       </c>
       <c r="L21" s="44" t="s">
-        <v>97</v>
+        <v>85</v>
       </c>
       <c r="M21" s="45">
-        <v>46180</v>
+        <v>46177</v>
       </c>
       <c r="N21" s="46">
-        <v>46180</v>
+        <v>46181</v>
       </c>
       <c r="O21" s="47" t="s">
-        <v>98</v>
+        <v>86</v>
       </c>
       <c r="P21" s="48" t="s">
-        <v>98</v>
+        <v>86</v>
       </c>
       <c r="Q21" s="49">
-        <v>46164</v>
+        <v>46177</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="33" t="s">
-        <v>103</v>
+        <v>87</v>
       </c>
       <c r="B22" s="34" t="s">
-        <v>104</v>
+        <v>88</v>
       </c>
       <c r="C22" s="35" t="s">
-        <v>19</v>
+        <v>80</v>
       </c>
       <c r="D22" s="36" t="s">
-        <v>20</v>
+        <v>81</v>
       </c>
       <c r="E22" s="37" t="s">
-        <v>21</v>
+        <v>57</v>
       </c>
       <c r="F22" s="38" t="s">
-        <v>22</v>
+        <v>58</v>
       </c>
       <c r="G22" s="39" t="s">
         <v>23</v>
       </c>
       <c r="H22" s="40" t="s">
-        <v>21</v>
+        <v>57</v>
       </c>
       <c r="I22" s="41" t="s">
-        <v>105</v>
+        <v>82</v>
       </c>
       <c r="J22" s="42" t="s">
-        <v>42</v>
+        <v>83</v>
       </c>
       <c r="K22" s="43" t="s">
-        <v>43</v>
+        <v>84</v>
       </c>
       <c r="L22" s="44" t="s">
-        <v>44</v>
+        <v>85</v>
       </c>
       <c r="M22" s="45">
-        <v>46180</v>
+        <v>46177</v>
       </c>
       <c r="N22" s="46">
-        <v>46180</v>
+        <v>46181</v>
       </c>
       <c r="O22" s="47" t="s">
-        <v>106</v>
+        <v>86</v>
       </c>
       <c r="P22" s="48" t="s">
-        <v>106</v>
+        <v>86</v>
       </c>
       <c r="Q22" s="49">
-        <v>46169</v>
+        <v>46177</v>
       </c>
     </row>
   </sheetData>

--- a/trimika_data.xlsx
+++ b/trimika_data.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" count="311" uniqueCount="89">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" count="227" uniqueCount="91">
   <si>
     <t>REFERENCE NO</t>
   </si>
@@ -66,16 +66,118 @@
     <t>EXPORT DATE</t>
   </si>
   <si>
-    <t>2565618</t>
-  </si>
-  <si>
-    <t>EF4-0231371-4</t>
+    <t>2565735</t>
+  </si>
+  <si>
+    <t>EF4-0231600-6</t>
   </si>
   <si>
     <t>Vessel, Container</t>
   </si>
   <si>
-    <t>VA923640612</t>
+    <t>165918675</t>
+  </si>
+  <si>
+    <t>9903.03.03</t>
+  </si>
+  <si>
+    <t>S122 -EXCLUSION-EXEMPTED PRDTS</t>
+  </si>
+  <si>
+    <t>001</t>
+  </si>
+  <si>
+    <t>2930.90.9231</t>
+  </si>
+  <si>
+    <t>CASTLE CHEMICALS LTD</t>
+  </si>
+  <si>
+    <t>CASCHE01</t>
+  </si>
+  <si>
+    <t>151704-07138</t>
+  </si>
+  <si>
+    <t>HUBEI JIANGHAN NEW MATERIALS CO LTD</t>
+  </si>
+  <si>
+    <t>2565736</t>
+  </si>
+  <si>
+    <t>EF4-0231601-4</t>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t>2565737</t>
+  </si>
+  <si>
+    <t>EF4-0231605-5</t>
+  </si>
+  <si>
+    <t>105504701</t>
+  </si>
+  <si>
+    <t>EF4-0231792-1</t>
+  </si>
+  <si>
+    <t>9903.03.06</t>
+  </si>
+  <si>
+    <t>S122 EXCL,IRN/STL/ALUM,DERIV</t>
+  </si>
+  <si>
+    <t>9903.94.51,8703.24.0150</t>
+  </si>
+  <si>
+    <t>PORSCHE MOTORSPORT NORTH AMERICA</t>
+  </si>
+  <si>
+    <t>PORMOT01</t>
+  </si>
+  <si>
+    <t>23-234420600</t>
+  </si>
+  <si>
+    <t>PORSCHE AG</t>
+  </si>
+  <si>
+    <t>002</t>
+  </si>
+  <si>
+    <t>105504723</t>
+  </si>
+  <si>
+    <t>EF4-0231845-7</t>
+  </si>
+  <si>
+    <t>Vessel, Non-container</t>
+  </si>
+  <si>
+    <t>9805.00.50</t>
+  </si>
+  <si>
+    <t>EFFECTS US GOV EMP&amp;FAMLY/EVACU</t>
+  </si>
+  <si>
+    <t>IFF, INC.</t>
+  </si>
+  <si>
+    <t>10</t>
+  </si>
+  <si>
+    <t>58-149385700</t>
+  </si>
+  <si>
+    <t>VOLVO CAR INTERNATIONAL CORPORATION</t>
+  </si>
+  <si>
+    <t>2565861</t>
+  </si>
+  <si>
+    <t>EF4-0231913-3</t>
   </si>
   <si>
     <t>9903.03.01</t>
@@ -84,115 +186,7 @@
     <t>SECTION 122 - 10% DUTY</t>
   </si>
   <si>
-    <t>001</t>
-  </si>
-  <si>
-    <t>5603.14.9090</t>
-  </si>
-  <si>
-    <t>VEER CORPORATIONS INC</t>
-  </si>
-  <si>
-    <t>VEECOR01</t>
-  </si>
-  <si>
-    <t>99-106989200</t>
-  </si>
-  <si>
-    <t>VEER PLASTIC PVT LTD</t>
-  </si>
-  <si>
-    <t>2565931</t>
-  </si>
-  <si>
-    <t>EF4-0231973-7</t>
-  </si>
-  <si>
-    <t>5206.11.0000</t>
-  </si>
-  <si>
-    <t>HICKORY THROWING COMPANY</t>
-  </si>
-  <si>
-    <t>HICTHR</t>
-  </si>
-  <si>
-    <t>56-124106800</t>
-  </si>
-  <si>
-    <t>HILATURAS FERRE</t>
-  </si>
-  <si>
-    <t>2565852</t>
-  </si>
-  <si>
-    <t>EF4-0231984-4</t>
-  </si>
-  <si>
-    <t/>
-  </si>
-  <si>
-    <t>9903.03.06</t>
-  </si>
-  <si>
-    <t>S122 EXCL,IRN/STL/ALUM,DERIV</t>
-  </si>
-  <si>
-    <t>9903.82.10,8431.39.0010</t>
-  </si>
-  <si>
-    <t>AUMUND CORPORATION</t>
-  </si>
-  <si>
-    <t>AUMCOR</t>
-  </si>
-  <si>
-    <t>58-138896800</t>
-  </si>
-  <si>
-    <t>AUMUND FOERDERTECHNIK GMBH</t>
-  </si>
-  <si>
-    <t>2615704</t>
-  </si>
-  <si>
-    <t>EF4-0232167-5</t>
-  </si>
-  <si>
-    <t>Vessel, Non-container</t>
-  </si>
-  <si>
-    <t>2916.14.2050</t>
-  </si>
-  <si>
-    <t>TRENCHLESS PRODUCTS</t>
-  </si>
-  <si>
-    <t>TREPRO01</t>
-  </si>
-  <si>
-    <t>83-157973900</t>
-  </si>
-  <si>
-    <t>POLINVENT KFT.</t>
-  </si>
-  <si>
-    <t>2615767</t>
-  </si>
-  <si>
-    <t>EF4-0232268-1</t>
-  </si>
-  <si>
-    <t>Truck, Non-container</t>
-  </si>
-  <si>
-    <t>9903.03.07</t>
-  </si>
-  <si>
-    <t>S 122-EXCLUSION, CANADA USMCA</t>
-  </si>
-  <si>
-    <t>1905.90.1041</t>
+    <t>1905.90.1050</t>
   </si>
   <si>
     <t>IN 2 FOOD GOURMET LLC</t>
@@ -204,82 +198,94 @@
     <t>26-458152400</t>
   </si>
   <si>
-    <t>AGM BAKERY</t>
-  </si>
-  <si>
-    <t>002</t>
+    <t>PIDY PRODUCTION-FRANCE</t>
+  </si>
+  <si>
+    <t>2565756</t>
+  </si>
+  <si>
+    <t>EF4-0231946-3</t>
+  </si>
+  <si>
+    <t>DOBLA USA MFG LLC</t>
+  </si>
+  <si>
+    <t>DOBUSA</t>
+  </si>
+  <si>
+    <t>41-218954800</t>
+  </si>
+  <si>
+    <t>SMILDE BAKERY BV</t>
+  </si>
+  <si>
+    <t>105504728</t>
+  </si>
+  <si>
+    <t>EF4-0231985-1</t>
+  </si>
+  <si>
+    <t>2565801</t>
+  </si>
+  <si>
+    <t>EF4-0232025-5</t>
+  </si>
+  <si>
+    <t>9903.82.02,7223.00.1061</t>
+  </si>
+  <si>
+    <t>VENUS WIRE INDUSTRIES PRIVATE LTD</t>
+  </si>
+  <si>
+    <t>VENWIR</t>
+  </si>
+  <si>
+    <t>993901-03595</t>
+  </si>
+  <si>
+    <t>PRECISION METALS</t>
+  </si>
+  <si>
+    <t>105504748</t>
+  </si>
+  <si>
+    <t>EF4-0232108-9</t>
+  </si>
+  <si>
+    <t>105504749</t>
+  </si>
+  <si>
+    <t>EF4-0232119-6</t>
+  </si>
+  <si>
+    <t>2565807</t>
+  </si>
+  <si>
+    <t>EF4-0232382-0</t>
+  </si>
+  <si>
+    <t>9903.82.02,7222.20.0043</t>
+  </si>
+  <si>
+    <t>MESHA STEELS  LLC</t>
+  </si>
+  <si>
+    <t>MESSTE</t>
+  </si>
+  <si>
+    <t>20-274801900</t>
+  </si>
+  <si>
+    <t>BHANSALI BRIGHT BARS PVT. LTD.</t>
+  </si>
+  <si>
+    <t>9903.82.02,7222.20.0064</t>
   </si>
   <si>
     <t>003</t>
   </si>
   <si>
-    <t>004</t>
-  </si>
-  <si>
-    <t>005</t>
-  </si>
-  <si>
-    <t>006</t>
-  </si>
-  <si>
-    <t>007</t>
-  </si>
-  <si>
-    <t>008</t>
-  </si>
-  <si>
-    <t>009</t>
-  </si>
-  <si>
-    <t>010</t>
-  </si>
-  <si>
-    <t>011</t>
-  </si>
-  <si>
-    <t>012</t>
-  </si>
-  <si>
-    <t>013</t>
-  </si>
-  <si>
-    <t>014</t>
-  </si>
-  <si>
-    <t>015</t>
-  </si>
-  <si>
-    <t>4539443</t>
-  </si>
-  <si>
-    <t>EF4-0232337-4</t>
-  </si>
-  <si>
-    <t>Air, Non-container</t>
-  </si>
-  <si>
-    <t>784771645</t>
-  </si>
-  <si>
-    <t>9903.94.06,8531.90.3000</t>
-  </si>
-  <si>
-    <t>CANTRELL GAINCO GROUP INC</t>
-  </si>
-  <si>
-    <t>CANGAI01</t>
-  </si>
-  <si>
-    <t>31-151121700</t>
-  </si>
-  <si>
-    <t>FORTRESS TECHNOLOGY</t>
-  </si>
-  <si>
-    <t>4539444</t>
-  </si>
-  <si>
-    <t>EF4-0232338-2</t>
+    <t>9903.82.02,7222.20.0073</t>
   </si>
 </sst>
 </file>
@@ -1224,7 +1230,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:Q22"/>
+  <dimension ref="A1:Q16"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="23.7109375" customWidth="true"/>
@@ -1337,10 +1343,10 @@
         <v>27</v>
       </c>
       <c r="M2" s="45">
-        <v>46161</v>
+        <v>46181</v>
       </c>
       <c r="N2" s="46">
-        <v>46181</v>
+        <v>46182</v>
       </c>
       <c r="O2" s="47" t="s">
         <v>28</v>
@@ -1349,7 +1355,7 @@
         <v>28</v>
       </c>
       <c r="Q2" s="49">
-        <v>46131</v>
+        <v>46147</v>
       </c>
     </row>
     <row r="3">
@@ -1363,7 +1369,7 @@
         <v>19</v>
       </c>
       <c r="D3" s="36" t="s">
-        <v>20</v>
+        <v>31</v>
       </c>
       <c r="E3" s="37" t="s">
         <v>21</v>
@@ -1378,134 +1384,134 @@
         <v>21</v>
       </c>
       <c r="I3" s="41" t="s">
-        <v>31</v>
+        <v>24</v>
       </c>
       <c r="J3" s="42" t="s">
-        <v>32</v>
+        <v>25</v>
       </c>
       <c r="K3" s="43" t="s">
-        <v>33</v>
+        <v>26</v>
       </c>
       <c r="L3" s="44" t="s">
-        <v>34</v>
+        <v>27</v>
       </c>
       <c r="M3" s="45">
         <v>46181</v>
       </c>
       <c r="N3" s="46">
-        <v>46181</v>
+        <v>46182</v>
       </c>
       <c r="O3" s="47" t="s">
-        <v>35</v>
+        <v>28</v>
       </c>
       <c r="P3" s="48" t="s">
-        <v>35</v>
+        <v>28</v>
       </c>
       <c r="Q3" s="49">
-        <v>46159</v>
+        <v>46147</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="33" t="s">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="B4" s="34" t="s">
-        <v>37</v>
+        <v>33</v>
       </c>
       <c r="C4" s="35" t="s">
         <v>19</v>
       </c>
       <c r="D4" s="36" t="s">
-        <v>38</v>
+        <v>31</v>
       </c>
       <c r="E4" s="37" t="s">
-        <v>39</v>
+        <v>21</v>
       </c>
       <c r="F4" s="38" t="s">
-        <v>40</v>
+        <v>22</v>
       </c>
       <c r="G4" s="39" t="s">
         <v>23</v>
       </c>
       <c r="H4" s="40" t="s">
-        <v>39</v>
+        <v>21</v>
       </c>
       <c r="I4" s="41" t="s">
-        <v>41</v>
+        <v>24</v>
       </c>
       <c r="J4" s="42" t="s">
-        <v>42</v>
+        <v>25</v>
       </c>
       <c r="K4" s="43" t="s">
-        <v>43</v>
+        <v>26</v>
       </c>
       <c r="L4" s="44" t="s">
-        <v>44</v>
+        <v>27</v>
       </c>
       <c r="M4" s="45">
         <v>46181</v>
       </c>
       <c r="N4" s="46">
-        <v>46181</v>
+        <v>46182</v>
       </c>
       <c r="O4" s="47" t="s">
-        <v>45</v>
+        <v>28</v>
       </c>
       <c r="P4" s="48" t="s">
-        <v>45</v>
+        <v>28</v>
       </c>
       <c r="Q4" s="49">
-        <v>46155</v>
+        <v>46147</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="33" t="s">
-        <v>46</v>
+        <v>34</v>
       </c>
       <c r="B5" s="34" t="s">
-        <v>47</v>
+        <v>35</v>
       </c>
       <c r="C5" s="35" t="s">
-        <v>48</v>
+        <v>19</v>
       </c>
       <c r="D5" s="36" t="s">
-        <v>38</v>
+        <v>31</v>
       </c>
       <c r="E5" s="37" t="s">
-        <v>21</v>
+        <v>36</v>
       </c>
       <c r="F5" s="38" t="s">
-        <v>22</v>
+        <v>37</v>
       </c>
       <c r="G5" s="39" t="s">
         <v>23</v>
       </c>
       <c r="H5" s="40" t="s">
-        <v>21</v>
+        <v>36</v>
       </c>
       <c r="I5" s="41" t="s">
-        <v>49</v>
+        <v>38</v>
       </c>
       <c r="J5" s="42" t="s">
-        <v>50</v>
+        <v>39</v>
       </c>
       <c r="K5" s="43" t="s">
-        <v>51</v>
+        <v>40</v>
       </c>
       <c r="L5" s="44" t="s">
-        <v>52</v>
+        <v>41</v>
       </c>
       <c r="M5" s="45">
-        <v>46175</v>
+        <v>46184</v>
       </c>
       <c r="N5" s="46">
-        <v>46181</v>
+        <v>46182</v>
       </c>
       <c r="O5" s="47" t="s">
-        <v>53</v>
+        <v>42</v>
       </c>
       <c r="P5" s="48" t="s">
-        <v>53</v>
+        <v>42</v>
       </c>
       <c r="Q5" s="49">
         <v>46164</v>
@@ -1513,908 +1519,590 @@
     </row>
     <row r="6">
       <c r="A6" s="33" t="s">
-        <v>54</v>
+        <v>34</v>
       </c>
       <c r="B6" s="34" t="s">
-        <v>55</v>
+        <v>35</v>
       </c>
       <c r="C6" s="35" t="s">
-        <v>56</v>
+        <v>19</v>
       </c>
       <c r="D6" s="36" t="s">
+        <v>31</v>
+      </c>
+      <c r="E6" s="37" t="s">
+        <v>36</v>
+      </c>
+      <c r="F6" s="38" t="s">
+        <v>37</v>
+      </c>
+      <c r="G6" s="39" t="s">
+        <v>43</v>
+      </c>
+      <c r="H6" s="40" t="s">
+        <v>36</v>
+      </c>
+      <c r="I6" s="41" t="s">
         <v>38</v>
       </c>
-      <c r="E6" s="37" t="s">
-        <v>57</v>
-      </c>
-      <c r="F6" s="38" t="s">
-        <v>58</v>
-      </c>
-      <c r="G6" s="39" t="s">
-        <v>23</v>
-      </c>
-      <c r="H6" s="40" t="s">
-        <v>57</v>
-      </c>
-      <c r="I6" s="41" t="s">
-        <v>59</v>
-      </c>
       <c r="J6" s="42" t="s">
-        <v>60</v>
+        <v>39</v>
       </c>
       <c r="K6" s="43" t="s">
-        <v>61</v>
+        <v>40</v>
       </c>
       <c r="L6" s="44" t="s">
-        <v>62</v>
+        <v>41</v>
       </c>
       <c r="M6" s="45">
-        <v>46177</v>
+        <v>46184</v>
       </c>
       <c r="N6" s="46">
-        <v>46181</v>
+        <v>46182</v>
       </c>
       <c r="O6" s="47" t="s">
-        <v>63</v>
+        <v>42</v>
       </c>
       <c r="P6" s="48" t="s">
-        <v>63</v>
+        <v>42</v>
       </c>
       <c r="Q6" s="49">
-        <v>46177</v>
+        <v>46164</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="33" t="s">
-        <v>54</v>
+        <v>44</v>
       </c>
       <c r="B7" s="34" t="s">
-        <v>55</v>
+        <v>45</v>
       </c>
       <c r="C7" s="35" t="s">
-        <v>56</v>
+        <v>46</v>
       </c>
       <c r="D7" s="36" t="s">
-        <v>38</v>
+        <v>31</v>
       </c>
       <c r="E7" s="37" t="s">
-        <v>57</v>
+        <v>47</v>
       </c>
       <c r="F7" s="38" t="s">
-        <v>58</v>
+        <v>48</v>
       </c>
       <c r="G7" s="39" t="s">
-        <v>64</v>
+        <v>23</v>
       </c>
       <c r="H7" s="40" t="s">
-        <v>57</v>
+        <v>47</v>
       </c>
       <c r="I7" s="41" t="s">
-        <v>59</v>
+        <v>31</v>
       </c>
       <c r="J7" s="42" t="s">
-        <v>60</v>
+        <v>49</v>
       </c>
       <c r="K7" s="43" t="s">
-        <v>61</v>
+        <v>50</v>
       </c>
       <c r="L7" s="44" t="s">
-        <v>62</v>
+        <v>51</v>
       </c>
       <c r="M7" s="45">
-        <v>46177</v>
+        <v>46181</v>
       </c>
       <c r="N7" s="46">
-        <v>46181</v>
+        <v>46182</v>
       </c>
       <c r="O7" s="47" t="s">
-        <v>63</v>
+        <v>52</v>
       </c>
       <c r="P7" s="48" t="s">
-        <v>63</v>
+        <v>52</v>
       </c>
       <c r="Q7" s="49">
-        <v>46177</v>
+        <v>46162</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="33" t="s">
+        <v>53</v>
+      </c>
+      <c r="B8" s="34" t="s">
         <v>54</v>
       </c>
-      <c r="B8" s="34" t="s">
+      <c r="C8" s="35" t="s">
+        <v>19</v>
+      </c>
+      <c r="D8" s="36" t="s">
+        <v>31</v>
+      </c>
+      <c r="E8" s="37" t="s">
         <v>55</v>
       </c>
-      <c r="C8" s="35" t="s">
+      <c r="F8" s="38" t="s">
         <v>56</v>
       </c>
-      <c r="D8" s="36" t="s">
-        <v>38</v>
-      </c>
-      <c r="E8" s="37" t="s">
+      <c r="G8" s="39" t="s">
+        <v>23</v>
+      </c>
+      <c r="H8" s="40" t="s">
+        <v>55</v>
+      </c>
+      <c r="I8" s="41" t="s">
         <v>57</v>
       </c>
-      <c r="F8" s="38" t="s">
+      <c r="J8" s="42" t="s">
         <v>58</v>
       </c>
-      <c r="G8" s="39" t="s">
-        <v>65</v>
-      </c>
-      <c r="H8" s="40" t="s">
-        <v>57</v>
-      </c>
-      <c r="I8" s="41" t="s">
+      <c r="K8" s="43" t="s">
         <v>59</v>
       </c>
-      <c r="J8" s="42" t="s">
+      <c r="L8" s="44" t="s">
         <v>60</v>
       </c>
-      <c r="K8" s="43" t="s">
+      <c r="M8" s="45">
+        <v>46181</v>
+      </c>
+      <c r="N8" s="46">
+        <v>46182</v>
+      </c>
+      <c r="O8" s="47" t="s">
         <v>61</v>
       </c>
-      <c r="L8" s="44" t="s">
-        <v>62</v>
-      </c>
-      <c r="M8" s="45">
-        <v>46177</v>
-      </c>
-      <c r="N8" s="46">
-        <v>46181</v>
-      </c>
-      <c r="O8" s="47" t="s">
-        <v>63</v>
-      </c>
       <c r="P8" s="48" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="Q8" s="49">
-        <v>46177</v>
+        <v>46155</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="33" t="s">
-        <v>54</v>
+        <v>62</v>
       </c>
       <c r="B9" s="34" t="s">
+        <v>63</v>
+      </c>
+      <c r="C9" s="35" t="s">
+        <v>19</v>
+      </c>
+      <c r="D9" s="36" t="s">
+        <v>31</v>
+      </c>
+      <c r="E9" s="37" t="s">
         <v>55</v>
       </c>
-      <c r="C9" s="35" t="s">
+      <c r="F9" s="38" t="s">
         <v>56</v>
       </c>
-      <c r="D9" s="36" t="s">
-        <v>38</v>
-      </c>
-      <c r="E9" s="37" t="s">
+      <c r="G9" s="39" t="s">
+        <v>23</v>
+      </c>
+      <c r="H9" s="40" t="s">
+        <v>55</v>
+      </c>
+      <c r="I9" s="41" t="s">
         <v>57</v>
       </c>
-      <c r="F9" s="38" t="s">
-        <v>58</v>
-      </c>
-      <c r="G9" s="39" t="s">
+      <c r="J9" s="42" t="s">
+        <v>64</v>
+      </c>
+      <c r="K9" s="43" t="s">
+        <v>65</v>
+      </c>
+      <c r="L9" s="44" t="s">
         <v>66</v>
       </c>
-      <c r="H9" s="40" t="s">
-        <v>57</v>
-      </c>
-      <c r="I9" s="41" t="s">
-        <v>59</v>
-      </c>
-      <c r="J9" s="42" t="s">
-        <v>60</v>
-      </c>
-      <c r="K9" s="43" t="s">
-        <v>61</v>
-      </c>
-      <c r="L9" s="44" t="s">
-        <v>62</v>
-      </c>
       <c r="M9" s="45">
-        <v>46177</v>
+        <v>46181</v>
       </c>
       <c r="N9" s="46">
-        <v>46181</v>
+        <v>46182</v>
       </c>
       <c r="O9" s="47" t="s">
-        <v>63</v>
+        <v>67</v>
       </c>
       <c r="P9" s="48" t="s">
-        <v>63</v>
+        <v>67</v>
       </c>
       <c r="Q9" s="49">
-        <v>46177</v>
+        <v>46161</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="33" t="s">
-        <v>54</v>
+        <v>68</v>
       </c>
       <c r="B10" s="34" t="s">
-        <v>55</v>
+        <v>69</v>
       </c>
       <c r="C10" s="35" t="s">
-        <v>56</v>
+        <v>46</v>
       </c>
       <c r="D10" s="36" t="s">
-        <v>38</v>
+        <v>31</v>
       </c>
       <c r="E10" s="37" t="s">
-        <v>57</v>
+        <v>47</v>
       </c>
       <c r="F10" s="38" t="s">
-        <v>58</v>
+        <v>48</v>
       </c>
       <c r="G10" s="39" t="s">
-        <v>67</v>
+        <v>23</v>
       </c>
       <c r="H10" s="40" t="s">
-        <v>57</v>
+        <v>47</v>
       </c>
       <c r="I10" s="41" t="s">
-        <v>59</v>
+        <v>31</v>
       </c>
       <c r="J10" s="42" t="s">
-        <v>60</v>
+        <v>49</v>
       </c>
       <c r="K10" s="43" t="s">
-        <v>61</v>
+        <v>50</v>
       </c>
       <c r="L10" s="44" t="s">
-        <v>62</v>
+        <v>51</v>
       </c>
       <c r="M10" s="45">
-        <v>46177</v>
+        <v>46181</v>
       </c>
       <c r="N10" s="46">
-        <v>46181</v>
+        <v>46182</v>
       </c>
       <c r="O10" s="47" t="s">
-        <v>63</v>
+        <v>52</v>
       </c>
       <c r="P10" s="48" t="s">
-        <v>63</v>
+        <v>52</v>
       </c>
       <c r="Q10" s="49">
-        <v>46177</v>
+        <v>46164</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="33" t="s">
-        <v>54</v>
+        <v>70</v>
       </c>
       <c r="B11" s="34" t="s">
-        <v>55</v>
+        <v>71</v>
       </c>
       <c r="C11" s="35" t="s">
-        <v>56</v>
+        <v>19</v>
       </c>
       <c r="D11" s="36" t="s">
-        <v>38</v>
+        <v>31</v>
       </c>
       <c r="E11" s="37" t="s">
-        <v>57</v>
+        <v>36</v>
       </c>
       <c r="F11" s="38" t="s">
-        <v>58</v>
+        <v>37</v>
       </c>
       <c r="G11" s="39" t="s">
-        <v>68</v>
+        <v>23</v>
       </c>
       <c r="H11" s="40" t="s">
-        <v>57</v>
+        <v>36</v>
       </c>
       <c r="I11" s="41" t="s">
-        <v>59</v>
+        <v>72</v>
       </c>
       <c r="J11" s="42" t="s">
-        <v>60</v>
+        <v>73</v>
       </c>
       <c r="K11" s="43" t="s">
-        <v>61</v>
+        <v>74</v>
       </c>
       <c r="L11" s="44" t="s">
-        <v>62</v>
+        <v>75</v>
       </c>
       <c r="M11" s="45">
-        <v>46177</v>
+        <v>46182</v>
       </c>
       <c r="N11" s="46">
-        <v>46181</v>
+        <v>46182</v>
       </c>
       <c r="O11" s="47" t="s">
-        <v>63</v>
+        <v>76</v>
       </c>
       <c r="P11" s="48" t="s">
-        <v>63</v>
+        <v>76</v>
       </c>
       <c r="Q11" s="49">
-        <v>46177</v>
+        <v>46147</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="33" t="s">
-        <v>54</v>
+        <v>77</v>
       </c>
       <c r="B12" s="34" t="s">
-        <v>55</v>
+        <v>78</v>
       </c>
       <c r="C12" s="35" t="s">
-        <v>56</v>
+        <v>46</v>
       </c>
       <c r="D12" s="36" t="s">
-        <v>38</v>
+        <v>31</v>
       </c>
       <c r="E12" s="37" t="s">
-        <v>57</v>
+        <v>47</v>
       </c>
       <c r="F12" s="38" t="s">
-        <v>58</v>
+        <v>48</v>
       </c>
       <c r="G12" s="39" t="s">
-        <v>69</v>
+        <v>23</v>
       </c>
       <c r="H12" s="40" t="s">
-        <v>57</v>
+        <v>47</v>
       </c>
       <c r="I12" s="41" t="s">
-        <v>59</v>
+        <v>31</v>
       </c>
       <c r="J12" s="42" t="s">
-        <v>60</v>
+        <v>49</v>
       </c>
       <c r="K12" s="43" t="s">
-        <v>61</v>
+        <v>50</v>
       </c>
       <c r="L12" s="44" t="s">
-        <v>62</v>
+        <v>51</v>
       </c>
       <c r="M12" s="45">
-        <v>46177</v>
+        <v>46181</v>
       </c>
       <c r="N12" s="46">
-        <v>46181</v>
+        <v>46182</v>
       </c>
       <c r="O12" s="47" t="s">
-        <v>63</v>
+        <v>52</v>
       </c>
       <c r="P12" s="48" t="s">
-        <v>63</v>
+        <v>52</v>
       </c>
       <c r="Q12" s="49">
-        <v>46177</v>
+        <v>46168</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="33" t="s">
-        <v>54</v>
+        <v>79</v>
       </c>
       <c r="B13" s="34" t="s">
-        <v>55</v>
+        <v>80</v>
       </c>
       <c r="C13" s="35" t="s">
-        <v>56</v>
+        <v>46</v>
       </c>
       <c r="D13" s="36" t="s">
-        <v>38</v>
+        <v>31</v>
       </c>
       <c r="E13" s="37" t="s">
-        <v>57</v>
+        <v>47</v>
       </c>
       <c r="F13" s="38" t="s">
-        <v>58</v>
+        <v>48</v>
       </c>
       <c r="G13" s="39" t="s">
-        <v>70</v>
+        <v>23</v>
       </c>
       <c r="H13" s="40" t="s">
-        <v>57</v>
+        <v>47</v>
       </c>
       <c r="I13" s="41" t="s">
-        <v>59</v>
+        <v>31</v>
       </c>
       <c r="J13" s="42" t="s">
-        <v>60</v>
+        <v>49</v>
       </c>
       <c r="K13" s="43" t="s">
-        <v>61</v>
+        <v>50</v>
       </c>
       <c r="L13" s="44" t="s">
-        <v>62</v>
+        <v>51</v>
       </c>
       <c r="M13" s="45">
-        <v>46177</v>
+        <v>46181</v>
       </c>
       <c r="N13" s="46">
-        <v>46181</v>
+        <v>46182</v>
       </c>
       <c r="O13" s="47" t="s">
-        <v>63</v>
+        <v>52</v>
       </c>
       <c r="P13" s="48" t="s">
-        <v>63</v>
+        <v>52</v>
       </c>
       <c r="Q13" s="49">
-        <v>46177</v>
+        <v>46168</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="33" t="s">
-        <v>54</v>
+        <v>81</v>
       </c>
       <c r="B14" s="34" t="s">
-        <v>55</v>
+        <v>82</v>
       </c>
       <c r="C14" s="35" t="s">
-        <v>56</v>
+        <v>19</v>
       </c>
       <c r="D14" s="36" t="s">
-        <v>38</v>
+        <v>31</v>
       </c>
       <c r="E14" s="37" t="s">
-        <v>57</v>
+        <v>36</v>
       </c>
       <c r="F14" s="38" t="s">
-        <v>58</v>
+        <v>37</v>
       </c>
       <c r="G14" s="39" t="s">
-        <v>71</v>
+        <v>23</v>
       </c>
       <c r="H14" s="40" t="s">
-        <v>57</v>
+        <v>36</v>
       </c>
       <c r="I14" s="41" t="s">
-        <v>59</v>
+        <v>83</v>
       </c>
       <c r="J14" s="42" t="s">
-        <v>60</v>
+        <v>84</v>
       </c>
       <c r="K14" s="43" t="s">
-        <v>61</v>
+        <v>85</v>
       </c>
       <c r="L14" s="44" t="s">
-        <v>62</v>
+        <v>86</v>
       </c>
       <c r="M14" s="45">
-        <v>46177</v>
+        <v>46182</v>
       </c>
       <c r="N14" s="46">
-        <v>46181</v>
+        <v>46182</v>
       </c>
       <c r="O14" s="47" t="s">
-        <v>63</v>
+        <v>87</v>
       </c>
       <c r="P14" s="48" t="s">
-        <v>63</v>
+        <v>87</v>
       </c>
       <c r="Q14" s="49">
-        <v>46177</v>
+        <v>46147</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="33" t="s">
-        <v>54</v>
+        <v>81</v>
       </c>
       <c r="B15" s="34" t="s">
-        <v>55</v>
+        <v>82</v>
       </c>
       <c r="C15" s="35" t="s">
-        <v>56</v>
+        <v>19</v>
       </c>
       <c r="D15" s="36" t="s">
-        <v>38</v>
+        <v>31</v>
       </c>
       <c r="E15" s="37" t="s">
-        <v>57</v>
+        <v>36</v>
       </c>
       <c r="F15" s="38" t="s">
-        <v>58</v>
+        <v>37</v>
       </c>
       <c r="G15" s="39" t="s">
-        <v>72</v>
+        <v>43</v>
       </c>
       <c r="H15" s="40" t="s">
-        <v>57</v>
+        <v>36</v>
       </c>
       <c r="I15" s="41" t="s">
-        <v>59</v>
+        <v>88</v>
       </c>
       <c r="J15" s="42" t="s">
-        <v>60</v>
+        <v>84</v>
       </c>
       <c r="K15" s="43" t="s">
-        <v>61</v>
+        <v>85</v>
       </c>
       <c r="L15" s="44" t="s">
-        <v>62</v>
+        <v>86</v>
       </c>
       <c r="M15" s="45">
-        <v>46177</v>
+        <v>46182</v>
       </c>
       <c r="N15" s="46">
-        <v>46181</v>
+        <v>46182</v>
       </c>
       <c r="O15" s="47" t="s">
-        <v>63</v>
+        <v>87</v>
       </c>
       <c r="P15" s="48" t="s">
-        <v>63</v>
+        <v>87</v>
       </c>
       <c r="Q15" s="49">
-        <v>46177</v>
+        <v>46147</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="33" t="s">
-        <v>54</v>
+        <v>81</v>
       </c>
       <c r="B16" s="34" t="s">
-        <v>55</v>
+        <v>82</v>
       </c>
       <c r="C16" s="35" t="s">
-        <v>56</v>
+        <v>19</v>
       </c>
       <c r="D16" s="36" t="s">
-        <v>38</v>
+        <v>31</v>
       </c>
       <c r="E16" s="37" t="s">
-        <v>57</v>
+        <v>36</v>
       </c>
       <c r="F16" s="38" t="s">
-        <v>58</v>
+        <v>37</v>
       </c>
       <c r="G16" s="39" t="s">
-        <v>73</v>
+        <v>89</v>
       </c>
       <c r="H16" s="40" t="s">
-        <v>57</v>
+        <v>36</v>
       </c>
       <c r="I16" s="41" t="s">
-        <v>59</v>
+        <v>90</v>
       </c>
       <c r="J16" s="42" t="s">
-        <v>60</v>
+        <v>84</v>
       </c>
       <c r="K16" s="43" t="s">
-        <v>61</v>
+        <v>85</v>
       </c>
       <c r="L16" s="44" t="s">
-        <v>62</v>
+        <v>86</v>
       </c>
       <c r="M16" s="45">
-        <v>46177</v>
+        <v>46182</v>
       </c>
       <c r="N16" s="46">
-        <v>46181</v>
+        <v>46182</v>
       </c>
       <c r="O16" s="47" t="s">
-        <v>63</v>
+        <v>87</v>
       </c>
       <c r="P16" s="48" t="s">
-        <v>63</v>
+        <v>87</v>
       </c>
       <c r="Q16" s="49">
-        <v>46177</v>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="33" t="s">
-        <v>54</v>
-      </c>
-      <c r="B17" s="34" t="s">
-        <v>55</v>
-      </c>
-      <c r="C17" s="35" t="s">
-        <v>56</v>
-      </c>
-      <c r="D17" s="36" t="s">
-        <v>38</v>
-      </c>
-      <c r="E17" s="37" t="s">
-        <v>57</v>
-      </c>
-      <c r="F17" s="38" t="s">
-        <v>58</v>
-      </c>
-      <c r="G17" s="39" t="s">
-        <v>74</v>
-      </c>
-      <c r="H17" s="40" t="s">
-        <v>57</v>
-      </c>
-      <c r="I17" s="41" t="s">
-        <v>59</v>
-      </c>
-      <c r="J17" s="42" t="s">
-        <v>60</v>
-      </c>
-      <c r="K17" s="43" t="s">
-        <v>61</v>
-      </c>
-      <c r="L17" s="44" t="s">
-        <v>62</v>
-      </c>
-      <c r="M17" s="45">
-        <v>46177</v>
-      </c>
-      <c r="N17" s="46">
-        <v>46181</v>
-      </c>
-      <c r="O17" s="47" t="s">
-        <v>63</v>
-      </c>
-      <c r="P17" s="48" t="s">
-        <v>63</v>
-      </c>
-      <c r="Q17" s="49">
-        <v>46177</v>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="33" t="s">
-        <v>54</v>
-      </c>
-      <c r="B18" s="34" t="s">
-        <v>55</v>
-      </c>
-      <c r="C18" s="35" t="s">
-        <v>56</v>
-      </c>
-      <c r="D18" s="36" t="s">
-        <v>38</v>
-      </c>
-      <c r="E18" s="37" t="s">
-        <v>57</v>
-      </c>
-      <c r="F18" s="38" t="s">
-        <v>58</v>
-      </c>
-      <c r="G18" s="39" t="s">
-        <v>75</v>
-      </c>
-      <c r="H18" s="40" t="s">
-        <v>57</v>
-      </c>
-      <c r="I18" s="41" t="s">
-        <v>59</v>
-      </c>
-      <c r="J18" s="42" t="s">
-        <v>60</v>
-      </c>
-      <c r="K18" s="43" t="s">
-        <v>61</v>
-      </c>
-      <c r="L18" s="44" t="s">
-        <v>62</v>
-      </c>
-      <c r="M18" s="45">
-        <v>46177</v>
-      </c>
-      <c r="N18" s="46">
-        <v>46181</v>
-      </c>
-      <c r="O18" s="47" t="s">
-        <v>63</v>
-      </c>
-      <c r="P18" s="48" t="s">
-        <v>63</v>
-      </c>
-      <c r="Q18" s="49">
-        <v>46177</v>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="33" t="s">
-        <v>54</v>
-      </c>
-      <c r="B19" s="34" t="s">
-        <v>55</v>
-      </c>
-      <c r="C19" s="35" t="s">
-        <v>56</v>
-      </c>
-      <c r="D19" s="36" t="s">
-        <v>38</v>
-      </c>
-      <c r="E19" s="37" t="s">
-        <v>57</v>
-      </c>
-      <c r="F19" s="38" t="s">
-        <v>58</v>
-      </c>
-      <c r="G19" s="39" t="s">
-        <v>76</v>
-      </c>
-      <c r="H19" s="40" t="s">
-        <v>57</v>
-      </c>
-      <c r="I19" s="41" t="s">
-        <v>59</v>
-      </c>
-      <c r="J19" s="42" t="s">
-        <v>60</v>
-      </c>
-      <c r="K19" s="43" t="s">
-        <v>61</v>
-      </c>
-      <c r="L19" s="44" t="s">
-        <v>62</v>
-      </c>
-      <c r="M19" s="45">
-        <v>46177</v>
-      </c>
-      <c r="N19" s="46">
-        <v>46181</v>
-      </c>
-      <c r="O19" s="47" t="s">
-        <v>63</v>
-      </c>
-      <c r="P19" s="48" t="s">
-        <v>63</v>
-      </c>
-      <c r="Q19" s="49">
-        <v>46177</v>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" s="33" t="s">
-        <v>54</v>
-      </c>
-      <c r="B20" s="34" t="s">
-        <v>55</v>
-      </c>
-      <c r="C20" s="35" t="s">
-        <v>56</v>
-      </c>
-      <c r="D20" s="36" t="s">
-        <v>38</v>
-      </c>
-      <c r="E20" s="37" t="s">
-        <v>57</v>
-      </c>
-      <c r="F20" s="38" t="s">
-        <v>58</v>
-      </c>
-      <c r="G20" s="39" t="s">
-        <v>77</v>
-      </c>
-      <c r="H20" s="40" t="s">
-        <v>57</v>
-      </c>
-      <c r="I20" s="41" t="s">
-        <v>59</v>
-      </c>
-      <c r="J20" s="42" t="s">
-        <v>60</v>
-      </c>
-      <c r="K20" s="43" t="s">
-        <v>61</v>
-      </c>
-      <c r="L20" s="44" t="s">
-        <v>62</v>
-      </c>
-      <c r="M20" s="45">
-        <v>46177</v>
-      </c>
-      <c r="N20" s="46">
-        <v>46181</v>
-      </c>
-      <c r="O20" s="47" t="s">
-        <v>63</v>
-      </c>
-      <c r="P20" s="48" t="s">
-        <v>63</v>
-      </c>
-      <c r="Q20" s="49">
-        <v>46177</v>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" s="33" t="s">
-        <v>78</v>
-      </c>
-      <c r="B21" s="34" t="s">
-        <v>79</v>
-      </c>
-      <c r="C21" s="35" t="s">
-        <v>80</v>
-      </c>
-      <c r="D21" s="36" t="s">
-        <v>81</v>
-      </c>
-      <c r="E21" s="37" t="s">
-        <v>57</v>
-      </c>
-      <c r="F21" s="38" t="s">
-        <v>58</v>
-      </c>
-      <c r="G21" s="39" t="s">
-        <v>23</v>
-      </c>
-      <c r="H21" s="40" t="s">
-        <v>57</v>
-      </c>
-      <c r="I21" s="41" t="s">
-        <v>82</v>
-      </c>
-      <c r="J21" s="42" t="s">
-        <v>83</v>
-      </c>
-      <c r="K21" s="43" t="s">
-        <v>84</v>
-      </c>
-      <c r="L21" s="44" t="s">
-        <v>85</v>
-      </c>
-      <c r="M21" s="45">
-        <v>46177</v>
-      </c>
-      <c r="N21" s="46">
-        <v>46181</v>
-      </c>
-      <c r="O21" s="47" t="s">
-        <v>86</v>
-      </c>
-      <c r="P21" s="48" t="s">
-        <v>86</v>
-      </c>
-      <c r="Q21" s="49">
-        <v>46177</v>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" s="33" t="s">
-        <v>87</v>
-      </c>
-      <c r="B22" s="34" t="s">
-        <v>88</v>
-      </c>
-      <c r="C22" s="35" t="s">
-        <v>80</v>
-      </c>
-      <c r="D22" s="36" t="s">
-        <v>81</v>
-      </c>
-      <c r="E22" s="37" t="s">
-        <v>57</v>
-      </c>
-      <c r="F22" s="38" t="s">
-        <v>58</v>
-      </c>
-      <c r="G22" s="39" t="s">
-        <v>23</v>
-      </c>
-      <c r="H22" s="40" t="s">
-        <v>57</v>
-      </c>
-      <c r="I22" s="41" t="s">
-        <v>82</v>
-      </c>
-      <c r="J22" s="42" t="s">
-        <v>83</v>
-      </c>
-      <c r="K22" s="43" t="s">
-        <v>84</v>
-      </c>
-      <c r="L22" s="44" t="s">
-        <v>85</v>
-      </c>
-      <c r="M22" s="45">
-        <v>46177</v>
-      </c>
-      <c r="N22" s="46">
-        <v>46181</v>
-      </c>
-      <c r="O22" s="47" t="s">
-        <v>86</v>
-      </c>
-      <c r="P22" s="48" t="s">
-        <v>86</v>
-      </c>
-      <c r="Q22" s="49">
-        <v>46177</v>
+        <v>46147</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError sqref="A1 B1 C1 D1 E1 F1 G1 H1 I1 J1 K1 L1 M1 N1 O1 P1 Q1 A2 B2 C2 D2 E2 F2 G2 H2 I2 J2 K2 L2 O2 P2 A3 B3 C3 D3 E3 F3 G3 H3 I3 J3 K3 L3 O3 P3 A4 B4 C4 D4 E4 F4 G4 H4 I4 J4 K4 L4 O4 P4 A5 B5 C5 D5 E5 F5 G5 H5 I5 J5 K5 L5 O5 P5 A6 B6 C6 D6 E6 F6 G6 H6 I6 J6 K6 L6 O6 P6 A7 B7 C7 D7 E7 F7 G7 H7 I7 J7 K7 L7 O7 P7 A8 B8 C8 D8 E8 F8 G8 H8 I8 J8 K8 L8 O8 P8 A9 B9 C9 D9 E9 F9 G9 H9 I9 J9 K9 L9 O9 P9 A10 B10 C10 D10 E10 F10 G10 H10 I10 J10 K10 L10 O10 P10 A11 B11 C11 D11 E11 F11 G11 H11 I11 J11 K11 L11 O11 P11 A12 B12 C12 D12 E12 F12 G12 H12 I12 J12 K12 L12 O12 P12 A13 B13 C13 D13 E13 F13 G13 H13 I13 J13 K13 L13 O13 P13 A14 B14 C14 D14 E14 F14 G14 H14 I14 J14 K14 L14 O14 P14 A15 B15 C15 D15 E15 F15 G15 H15 I15 J15 K15 L15 O15 P15 A16 B16 C16 D16 E16 F16 G16 H16 I16 J16 K16 L16 O16 P16 A17 B17 C17 D17 E17 F17 G17 H17 I17 J17 K17 L17 O17 P17 A18 B18 C18 D18 E18 F18 G18 H18 I18 J18 K18 L18 O18 P18 A19 B19 C19 D19 E19 F19 G19 H19 I19 J19 K19 L19 O19 P19 A20 B20 C20 D20 E20 F20 G20 H20 I20 J20 K20 L20 O20 P20 A21 B21 C21 D21 E21 F21 G21 H21 I21 J21 K21 L21 O21 P21 A22 B22 C22 D22 E22 F22 G22 H22 I22 J22 K22 L22 O22 P22" numberStoredAsText="true"/>
+    <ignoredError sqref="A1 B1 C1 D1 E1 F1 G1 H1 I1 J1 K1 L1 M1 N1 O1 P1 Q1 A2 B2 C2 D2 E2 F2 G2 H2 I2 J2 K2 L2 O2 P2 A3 B3 C3 D3 E3 F3 G3 H3 I3 J3 K3 L3 O3 P3 A4 B4 C4 D4 E4 F4 G4 H4 I4 J4 K4 L4 O4 P4 A5 B5 C5 D5 E5 F5 G5 H5 I5 J5 K5 L5 O5 P5 A6 B6 C6 D6 E6 F6 G6 H6 I6 J6 K6 L6 O6 P6 A7 B7 C7 D7 E7 F7 G7 H7 I7 J7 K7 L7 O7 P7 A8 B8 C8 D8 E8 F8 G8 H8 I8 J8 K8 L8 O8 P8 A9 B9 C9 D9 E9 F9 G9 H9 I9 J9 K9 L9 O9 P9 A10 B10 C10 D10 E10 F10 G10 H10 I10 J10 K10 L10 O10 P10 A11 B11 C11 D11 E11 F11 G11 H11 I11 J11 K11 L11 O11 P11 A12 B12 C12 D12 E12 F12 G12 H12 I12 J12 K12 L12 O12 P12 A13 B13 C13 D13 E13 F13 G13 H13 I13 J13 K13 L13 O13 P13 A14 B14 C14 D14 E14 F14 G14 H14 I14 J14 K14 L14 O14 P14 A15 B15 C15 D15 E15 F15 G15 H15 I15 J15 K15 L15 O15 P15 A16 B16 C16 D16 E16 F16 G16 H16 I16 J16 K16 L16 O16 P16" numberStoredAsText="true"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/trimika_data.xlsx
+++ b/trimika_data.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q16"/>
+  <dimension ref="A1:Q32"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1745,6 +1745,1358 @@
       <c r="Q16" t="inlineStr">
         <is>
           <t>2026-05-05 00:00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>2565606</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>EF4-0231310-2</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Vessel, Container</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr"/>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>9903.03.01</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>SECTION 122 - 10% DUTY</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>001</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>9903.03.01</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>5903.90.3090</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>VEER CORPORATIONS INC</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>VEECOR01</t>
+        </is>
+      </c>
+      <c r="L17" t="inlineStr">
+        <is>
+          <t>99-106989200</t>
+        </is>
+      </c>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>2026-06-10 00:00:00</t>
+        </is>
+      </c>
+      <c r="N17" t="inlineStr">
+        <is>
+          <t>2026-06-10 00:00:00</t>
+        </is>
+      </c>
+      <c r="O17" t="inlineStr">
+        <is>
+          <t>VEER PLASTIC PVT LTD</t>
+        </is>
+      </c>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>VEER PLASTIC PVT LTD</t>
+        </is>
+      </c>
+      <c r="Q17" t="inlineStr">
+        <is>
+          <t>2026-04-22 00:00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>2565607</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>EF4-0231311-0</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>Vessel, Container</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr"/>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>9903.03.01</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>SECTION 122 - 10% DUTY</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>001</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>9903.03.01</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>5903.90.3090</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>VEER CORPORATIONS INC</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>VEECOR01</t>
+        </is>
+      </c>
+      <c r="L18" t="inlineStr">
+        <is>
+          <t>99-106989200</t>
+        </is>
+      </c>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>2026-06-10 00:00:00</t>
+        </is>
+      </c>
+      <c r="N18" t="inlineStr">
+        <is>
+          <t>2026-06-10 00:00:00</t>
+        </is>
+      </c>
+      <c r="O18" t="inlineStr">
+        <is>
+          <t>VEER PLASTIC PVT LTD</t>
+        </is>
+      </c>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>VEER PLASTIC PVT LTD</t>
+        </is>
+      </c>
+      <c r="Q18" t="inlineStr">
+        <is>
+          <t>2026-04-22 00:00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>2565774</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>EF4-0231546-1</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>Vessel, Container</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>VA923704988</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>9903.03.01</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>SECTION 122 - 10% DUTY</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>001</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>9903.03.01</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>5903.90.3090</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>VEER CORPORATIONS INC</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>VEECOR01</t>
+        </is>
+      </c>
+      <c r="L19" t="inlineStr">
+        <is>
+          <t>99-106989200</t>
+        </is>
+      </c>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>2026-06-09 00:00:00</t>
+        </is>
+      </c>
+      <c r="N19" t="inlineStr">
+        <is>
+          <t>2026-06-10 00:00:00</t>
+        </is>
+      </c>
+      <c r="O19" t="inlineStr">
+        <is>
+          <t>VEER PLASTIC PVT LTD</t>
+        </is>
+      </c>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>VEER PLASTIC PVT LTD</t>
+        </is>
+      </c>
+      <c r="Q19" t="inlineStr">
+        <is>
+          <t>2026-05-06 00:00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>2565609</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>EF4-0231681-6</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>Vessel, Container</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>VA923704988</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>9903.03.06</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>S122 EXCL,IRN/STL/ALUM,DERIV</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>001</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>9903.03.06</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>9903.82.02,7223.00.1076</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>PRECISION METALS</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>PREMET</t>
+        </is>
+      </c>
+      <c r="L20" t="inlineStr">
+        <is>
+          <t>172704-21182</t>
+        </is>
+      </c>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>2026-06-10 00:00:00</t>
+        </is>
+      </c>
+      <c r="N20" t="inlineStr">
+        <is>
+          <t>2026-06-10 00:00:00</t>
+        </is>
+      </c>
+      <c r="O20" t="inlineStr">
+        <is>
+          <t>PRECISION METALS</t>
+        </is>
+      </c>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>PRECISION METALS</t>
+        </is>
+      </c>
+      <c r="Q20" t="inlineStr">
+        <is>
+          <t>2026-04-25 00:00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>2565750</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>EF4-0231718-6</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>Vessel, Container</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>V0710315396</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>9803.00.50</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>SUBSTANTIAL CONTAINERS US&amp;INTL</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>001</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>9803.00.50</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr"/>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>MEBROM LLC</t>
+        </is>
+      </c>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>MEBLLC01</t>
+        </is>
+      </c>
+      <c r="L21" t="inlineStr">
+        <is>
+          <t>84-463527000</t>
+        </is>
+      </c>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>2026-06-10 00:00:00</t>
+        </is>
+      </c>
+      <c r="N21" t="inlineStr">
+        <is>
+          <t>2026-06-10 00:00:00</t>
+        </is>
+      </c>
+      <c r="O21" t="inlineStr">
+        <is>
+          <t>SAHAMITR PRESSURE CONTAINER PUBLIC</t>
+        </is>
+      </c>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>SAHAMITR PRESSURE CONTAINER PUBLIC CO LTD</t>
+        </is>
+      </c>
+      <c r="Q21" t="inlineStr">
+        <is>
+          <t>2026-05-06 00:00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>2565714</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>EF4-0231746-7</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>Vessel, Container</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>V1P06243667</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>9903.03.03</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>S122 -EXCLUSION-EXEMPTED PRDTS</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>001</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>9903.03.03</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>1108.14.0000</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>ROYAL INGREDIENTS GROUP BV</t>
+        </is>
+      </c>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>ROYINGRE</t>
+        </is>
+      </c>
+      <c r="L22" t="inlineStr">
+        <is>
+          <t>074601-00962</t>
+        </is>
+      </c>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>2026-06-04 00:00:00</t>
+        </is>
+      </c>
+      <c r="N22" t="inlineStr">
+        <is>
+          <t>2026-06-10 00:00:00</t>
+        </is>
+      </c>
+      <c r="O22" t="inlineStr">
+        <is>
+          <t>SANGUAN WONGSE STARCH CO., LTD.</t>
+        </is>
+      </c>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t>SANGUAN WONGSE STARCH CO., LTD.</t>
+        </is>
+      </c>
+      <c r="Q22" t="inlineStr">
+        <is>
+          <t>2026-05-03 00:00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>2565716</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>EF4-0231748-3</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>Vessel, Container</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>V1P06243667</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>9903.03.03</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>S122 -EXCLUSION-EXEMPTED PRDTS</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>001</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>9903.03.03</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>1108.14.0000</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>ROYAL INGREDIENTS GROUP BV</t>
+        </is>
+      </c>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>ROYINGRE</t>
+        </is>
+      </c>
+      <c r="L23" t="inlineStr">
+        <is>
+          <t>074601-00962</t>
+        </is>
+      </c>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>2026-06-04 00:00:00</t>
+        </is>
+      </c>
+      <c r="N23" t="inlineStr">
+        <is>
+          <t>2026-06-10 00:00:00</t>
+        </is>
+      </c>
+      <c r="O23" t="inlineStr">
+        <is>
+          <t>SANGUAN WONGSE STARCH CO., LTD.</t>
+        </is>
+      </c>
+      <c r="P23" t="inlineStr">
+        <is>
+          <t>SANGUAN WONGSE STARCH CO., LTD.</t>
+        </is>
+      </c>
+      <c r="Q23" t="inlineStr">
+        <is>
+          <t>2026-05-03 00:00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>2565715</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>EF4-0232019-8</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>Vessel, Container</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>V1P06243667</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>9903.03.03</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>S122 -EXCLUSION-EXEMPTED PRDTS</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>001</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>9903.03.03</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>1108.14.0000</t>
+        </is>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>ROYAL INGREDIENTS GROUP BV</t>
+        </is>
+      </c>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t>ROYINGRE</t>
+        </is>
+      </c>
+      <c r="L24" t="inlineStr">
+        <is>
+          <t>074601-00962</t>
+        </is>
+      </c>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>2026-06-04 00:00:00</t>
+        </is>
+      </c>
+      <c r="N24" t="inlineStr">
+        <is>
+          <t>2026-06-10 00:00:00</t>
+        </is>
+      </c>
+      <c r="O24" t="inlineStr">
+        <is>
+          <t>SANGUAN WONGSE STARCH CO., LTD.</t>
+        </is>
+      </c>
+      <c r="P24" t="inlineStr">
+        <is>
+          <t>SANGUAN WONGSE STARCH CO., LTD.</t>
+        </is>
+      </c>
+      <c r="Q24" t="inlineStr">
+        <is>
+          <t>2026-05-03 00:00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>2565725</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>EF4-0232228-5</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>Vessel, Container</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>V1P06243667</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>9903.03.06</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>S122 EXCL,IRN/STL/ALUM,DERIV</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>001</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>9903.03.06</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>9903.82.09,8302.42.3015</t>
+        </is>
+      </c>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>GRASS AMERICA INC</t>
+        </is>
+      </c>
+      <c r="K25" t="inlineStr">
+        <is>
+          <t>GRAAME</t>
+        </is>
+      </c>
+      <c r="L25" t="inlineStr">
+        <is>
+          <t>51-066023000</t>
+        </is>
+      </c>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>2026-06-10 00:00:00</t>
+        </is>
+      </c>
+      <c r="N25" t="inlineStr">
+        <is>
+          <t>2026-06-10 00:00:00</t>
+        </is>
+      </c>
+      <c r="O25" t="inlineStr">
+        <is>
+          <t>GRASS GMBH</t>
+        </is>
+      </c>
+      <c r="P25" t="inlineStr">
+        <is>
+          <t>GRASS GMBH</t>
+        </is>
+      </c>
+      <c r="Q25" t="inlineStr">
+        <is>
+          <t>2026-05-06 00:00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>2566081</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>EF4-0232237-6</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>Vessel, Container</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr"/>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>9903.03.01</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>SECTION 122 - 10% DUTY</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>001</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>9903.03.01</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>9903.82.01,8483.40.9000</t>
+        </is>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>IMS GEAR VIRGINIA LLC</t>
+        </is>
+      </c>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>IMSGEA</t>
+        </is>
+      </c>
+      <c r="L26" t="inlineStr">
+        <is>
+          <t>20-800570900</t>
+        </is>
+      </c>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>2026-06-11 00:00:00</t>
+        </is>
+      </c>
+      <c r="N26" t="inlineStr">
+        <is>
+          <t>2026-06-10 00:00:00</t>
+        </is>
+      </c>
+      <c r="O26" t="inlineStr">
+        <is>
+          <t>ADOLF FOHL GMBH &amp; CO.</t>
+        </is>
+      </c>
+      <c r="P26" t="inlineStr">
+        <is>
+          <t>ADOLF FOHL GMBH &amp; CO.</t>
+        </is>
+      </c>
+      <c r="Q26" t="inlineStr">
+        <is>
+          <t>2026-05-28 00:00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>2566081</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>EF4-0232237-6</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>Vessel, Container</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr"/>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>9903.03.01</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>SECTION 122 - 10% DUTY</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>002</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>9903.03.01</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>9903.82.01,8483.40.9000</t>
+        </is>
+      </c>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>IMS GEAR VIRGINIA LLC</t>
+        </is>
+      </c>
+      <c r="K27" t="inlineStr">
+        <is>
+          <t>IMSGEA</t>
+        </is>
+      </c>
+      <c r="L27" t="inlineStr">
+        <is>
+          <t>20-800570900</t>
+        </is>
+      </c>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>2026-06-11 00:00:00</t>
+        </is>
+      </c>
+      <c r="N27" t="inlineStr">
+        <is>
+          <t>2026-06-10 00:00:00</t>
+        </is>
+      </c>
+      <c r="O27" t="inlineStr">
+        <is>
+          <t>ADOLF FOHL GMBH &amp; CO.</t>
+        </is>
+      </c>
+      <c r="P27" t="inlineStr">
+        <is>
+          <t>ADOLF FOHL GMBH &amp; CO.</t>
+        </is>
+      </c>
+      <c r="Q27" t="inlineStr">
+        <is>
+          <t>2026-05-28 00:00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>2566081</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>EF4-0232237-6</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>Vessel, Container</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr"/>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>9903.03.01</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>SECTION 122 - 10% DUTY</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>003</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>9903.03.01</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>9903.82.01,8483.40.9000</t>
+        </is>
+      </c>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>IMS GEAR VIRGINIA LLC</t>
+        </is>
+      </c>
+      <c r="K28" t="inlineStr">
+        <is>
+          <t>IMSGEA</t>
+        </is>
+      </c>
+      <c r="L28" t="inlineStr">
+        <is>
+          <t>20-800570900</t>
+        </is>
+      </c>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>2026-06-11 00:00:00</t>
+        </is>
+      </c>
+      <c r="N28" t="inlineStr">
+        <is>
+          <t>2026-06-10 00:00:00</t>
+        </is>
+      </c>
+      <c r="O28" t="inlineStr">
+        <is>
+          <t>ADOLF FOHL GMBH &amp; CO.</t>
+        </is>
+      </c>
+      <c r="P28" t="inlineStr">
+        <is>
+          <t>ADOLF FOHL GMBH &amp; CO.</t>
+        </is>
+      </c>
+      <c r="Q28" t="inlineStr">
+        <is>
+          <t>2026-05-28 00:00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>2566081</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>EF4-0232237-6</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>Vessel, Container</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr"/>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>9903.03.01</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>SECTION 122 - 10% DUTY</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>004</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>9903.03.01</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>9903.82.01,8483.40.9000</t>
+        </is>
+      </c>
+      <c r="J29" t="inlineStr">
+        <is>
+          <t>IMS GEAR VIRGINIA LLC</t>
+        </is>
+      </c>
+      <c r="K29" t="inlineStr">
+        <is>
+          <t>IMSGEA</t>
+        </is>
+      </c>
+      <c r="L29" t="inlineStr">
+        <is>
+          <t>20-800570900</t>
+        </is>
+      </c>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>2026-06-11 00:00:00</t>
+        </is>
+      </c>
+      <c r="N29" t="inlineStr">
+        <is>
+          <t>2026-06-10 00:00:00</t>
+        </is>
+      </c>
+      <c r="O29" t="inlineStr">
+        <is>
+          <t>ADOLF FOHL GMBH &amp; CO.</t>
+        </is>
+      </c>
+      <c r="P29" t="inlineStr">
+        <is>
+          <t>ADOLF FOHL GMBH &amp; CO.</t>
+        </is>
+      </c>
+      <c r="Q29" t="inlineStr">
+        <is>
+          <t>2026-05-28 00:00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>2566081</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>EF4-0232237-6</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>Vessel, Container</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr"/>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>9903.03.01</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>SECTION 122 - 10% DUTY</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>005</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>9903.03.01</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>9903.82.01,8483.40.9000</t>
+        </is>
+      </c>
+      <c r="J30" t="inlineStr">
+        <is>
+          <t>IMS GEAR VIRGINIA LLC</t>
+        </is>
+      </c>
+      <c r="K30" t="inlineStr">
+        <is>
+          <t>IMSGEA</t>
+        </is>
+      </c>
+      <c r="L30" t="inlineStr">
+        <is>
+          <t>20-800570900</t>
+        </is>
+      </c>
+      <c r="M30" t="inlineStr">
+        <is>
+          <t>2026-06-11 00:00:00</t>
+        </is>
+      </c>
+      <c r="N30" t="inlineStr">
+        <is>
+          <t>2026-06-10 00:00:00</t>
+        </is>
+      </c>
+      <c r="O30" t="inlineStr">
+        <is>
+          <t>ADOLF FOHL GMBH &amp; CO.</t>
+        </is>
+      </c>
+      <c r="P30" t="inlineStr">
+        <is>
+          <t>ADOLF FOHL GMBH &amp; CO.</t>
+        </is>
+      </c>
+      <c r="Q30" t="inlineStr">
+        <is>
+          <t>2026-05-28 00:00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>2566081</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>EF4-0232237-6</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>Vessel, Container</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr"/>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>9903.03.01</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>SECTION 122 - 10% DUTY</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>006</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>9903.03.01</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>9903.82.01,8483.40.9000</t>
+        </is>
+      </c>
+      <c r="J31" t="inlineStr">
+        <is>
+          <t>IMS GEAR VIRGINIA LLC</t>
+        </is>
+      </c>
+      <c r="K31" t="inlineStr">
+        <is>
+          <t>IMSGEA</t>
+        </is>
+      </c>
+      <c r="L31" t="inlineStr">
+        <is>
+          <t>20-800570900</t>
+        </is>
+      </c>
+      <c r="M31" t="inlineStr">
+        <is>
+          <t>2026-06-11 00:00:00</t>
+        </is>
+      </c>
+      <c r="N31" t="inlineStr">
+        <is>
+          <t>2026-06-10 00:00:00</t>
+        </is>
+      </c>
+      <c r="O31" t="inlineStr">
+        <is>
+          <t>ADOLF FOHL GMBH &amp; CO.</t>
+        </is>
+      </c>
+      <c r="P31" t="inlineStr">
+        <is>
+          <t>ADOLF FOHL GMBH &amp; CO.</t>
+        </is>
+      </c>
+      <c r="Q31" t="inlineStr">
+        <is>
+          <t>2026-05-28 00:00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>4539450</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>EF4-0232402-6</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>Air, Non-container</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr"/>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>9903.03.03</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>S122 -EXCLUSION-EXEMPTED PRDTS</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>001</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>9903.03.03</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>9903.90.08,2931.90.9052</t>
+        </is>
+      </c>
+      <c r="J32" t="inlineStr">
+        <is>
+          <t>EREZTECH LLC</t>
+        </is>
+      </c>
+      <c r="K32" t="inlineStr">
+        <is>
+          <t>ERELLC01</t>
+        </is>
+      </c>
+      <c r="L32" t="inlineStr">
+        <is>
+          <t>27-437122900</t>
+        </is>
+      </c>
+      <c r="M32" t="inlineStr">
+        <is>
+          <t>2026-06-10 00:00:00</t>
+        </is>
+      </c>
+      <c r="N32" t="inlineStr">
+        <is>
+          <t>2026-06-10 00:00:00</t>
+        </is>
+      </c>
+      <c r="O32" t="inlineStr">
+        <is>
+          <t>SYNOR LTD</t>
+        </is>
+      </c>
+      <c r="P32" t="inlineStr">
+        <is>
+          <t>SYNOR LTD</t>
+        </is>
+      </c>
+      <c r="Q32" t="inlineStr">
+        <is>
+          <t>2026-06-10 00:00:00</t>
         </is>
       </c>
     </row>

--- a/trimika_data.xlsx
+++ b/trimika_data.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q32"/>
+  <dimension ref="A1:Q66"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3100,6 +3100,2828 @@
         </is>
       </c>
     </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>2565646</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>EF4-0231408-4</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>Vessel, Container</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr"/>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>9903.03.01</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>SECTION 122 - 10% DUTY</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>001</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>9903.03.01</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>5402.61.0000</t>
+        </is>
+      </c>
+      <c r="J33" t="inlineStr">
+        <is>
+          <t>HICKORY THROWING COMPANY</t>
+        </is>
+      </c>
+      <c r="K33" t="inlineStr">
+        <is>
+          <t>HICTHR</t>
+        </is>
+      </c>
+      <c r="L33" t="inlineStr">
+        <is>
+          <t>56-124106800</t>
+        </is>
+      </c>
+      <c r="M33" t="inlineStr">
+        <is>
+          <t>2026-06-11 00:00:00</t>
+        </is>
+      </c>
+      <c r="N33" t="inlineStr">
+        <is>
+          <t>2026-06-11 00:00:00</t>
+        </is>
+      </c>
+      <c r="O33" t="inlineStr">
+        <is>
+          <t>SARLA PERFORMANCE FIBERS LTD</t>
+        </is>
+      </c>
+      <c r="P33" t="inlineStr">
+        <is>
+          <t>SARLA PERFORMANCE FIBERS LTD</t>
+        </is>
+      </c>
+      <c r="Q33" t="inlineStr">
+        <is>
+          <t>2026-04-27 00:00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>2565646</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>EF4-0231408-4</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>Vessel, Container</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr"/>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>9903.03.01</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>SECTION 122 - 10% DUTY</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>002</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>9903.03.01</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>5402.61.0000</t>
+        </is>
+      </c>
+      <c r="J34" t="inlineStr">
+        <is>
+          <t>HICKORY THROWING COMPANY</t>
+        </is>
+      </c>
+      <c r="K34" t="inlineStr">
+        <is>
+          <t>HICTHR</t>
+        </is>
+      </c>
+      <c r="L34" t="inlineStr">
+        <is>
+          <t>56-124106800</t>
+        </is>
+      </c>
+      <c r="M34" t="inlineStr">
+        <is>
+          <t>2026-06-11 00:00:00</t>
+        </is>
+      </c>
+      <c r="N34" t="inlineStr">
+        <is>
+          <t>2026-06-11 00:00:00</t>
+        </is>
+      </c>
+      <c r="O34" t="inlineStr">
+        <is>
+          <t>SARLA PERFORMANCE FIBERS LTD</t>
+        </is>
+      </c>
+      <c r="P34" t="inlineStr">
+        <is>
+          <t>SARLA PERFORMANCE FIBERS LTD</t>
+        </is>
+      </c>
+      <c r="Q34" t="inlineStr">
+        <is>
+          <t>2026-04-27 00:00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>2565646</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>EF4-0231408-4</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>Vessel, Container</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr"/>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>9903.03.01</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>SECTION 122 - 10% DUTY</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>003</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>9903.03.01</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>5402.61.0000</t>
+        </is>
+      </c>
+      <c r="J35" t="inlineStr">
+        <is>
+          <t>HICKORY THROWING COMPANY</t>
+        </is>
+      </c>
+      <c r="K35" t="inlineStr">
+        <is>
+          <t>HICTHR</t>
+        </is>
+      </c>
+      <c r="L35" t="inlineStr">
+        <is>
+          <t>56-124106800</t>
+        </is>
+      </c>
+      <c r="M35" t="inlineStr">
+        <is>
+          <t>2026-06-11 00:00:00</t>
+        </is>
+      </c>
+      <c r="N35" t="inlineStr">
+        <is>
+          <t>2026-06-11 00:00:00</t>
+        </is>
+      </c>
+      <c r="O35" t="inlineStr">
+        <is>
+          <t>SARLA PERFORMANCE FIBERS LTD</t>
+        </is>
+      </c>
+      <c r="P35" t="inlineStr">
+        <is>
+          <t>SARLA PERFORMANCE FIBERS LTD</t>
+        </is>
+      </c>
+      <c r="Q35" t="inlineStr">
+        <is>
+          <t>2026-04-27 00:00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>2565646</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>EF4-0231408-4</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>Vessel, Container</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr"/>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>9903.03.01</t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>SECTION 122 - 10% DUTY</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>004</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>9903.03.01</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>5606.00.0010</t>
+        </is>
+      </c>
+      <c r="J36" t="inlineStr">
+        <is>
+          <t>HICKORY THROWING COMPANY</t>
+        </is>
+      </c>
+      <c r="K36" t="inlineStr">
+        <is>
+          <t>HICTHR</t>
+        </is>
+      </c>
+      <c r="L36" t="inlineStr">
+        <is>
+          <t>56-124106800</t>
+        </is>
+      </c>
+      <c r="M36" t="inlineStr">
+        <is>
+          <t>2026-06-11 00:00:00</t>
+        </is>
+      </c>
+      <c r="N36" t="inlineStr">
+        <is>
+          <t>2026-06-11 00:00:00</t>
+        </is>
+      </c>
+      <c r="O36" t="inlineStr">
+        <is>
+          <t>SARLA PERFORMANCE FIBERS LTD</t>
+        </is>
+      </c>
+      <c r="P36" t="inlineStr">
+        <is>
+          <t>SARLA PERFORMANCE FIBERS LTD</t>
+        </is>
+      </c>
+      <c r="Q36" t="inlineStr">
+        <is>
+          <t>2026-04-27 00:00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>2565646</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>EF4-0231408-4</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>Vessel, Container</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr"/>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>9903.03.01</t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>SECTION 122 - 10% DUTY</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>005</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>9903.03.01</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>5402.62.0000</t>
+        </is>
+      </c>
+      <c r="J37" t="inlineStr">
+        <is>
+          <t>HICKORY THROWING COMPANY</t>
+        </is>
+      </c>
+      <c r="K37" t="inlineStr">
+        <is>
+          <t>HICTHR</t>
+        </is>
+      </c>
+      <c r="L37" t="inlineStr">
+        <is>
+          <t>56-124106800</t>
+        </is>
+      </c>
+      <c r="M37" t="inlineStr">
+        <is>
+          <t>2026-06-11 00:00:00</t>
+        </is>
+      </c>
+      <c r="N37" t="inlineStr">
+        <is>
+          <t>2026-06-11 00:00:00</t>
+        </is>
+      </c>
+      <c r="O37" t="inlineStr">
+        <is>
+          <t>SARLA PERFORMANCE FIBERS LTD</t>
+        </is>
+      </c>
+      <c r="P37" t="inlineStr">
+        <is>
+          <t>SARLA PERFORMANCE FIBERS LTD</t>
+        </is>
+      </c>
+      <c r="Q37" t="inlineStr">
+        <is>
+          <t>2026-04-27 00:00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>2565646</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>EF4-0231408-4</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>Vessel, Container</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr"/>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>9903.03.01</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>SECTION 122 - 10% DUTY</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>006</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>9903.03.01</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>5402.52.9000</t>
+        </is>
+      </c>
+      <c r="J38" t="inlineStr">
+        <is>
+          <t>HICKORY THROWING COMPANY</t>
+        </is>
+      </c>
+      <c r="K38" t="inlineStr">
+        <is>
+          <t>HICTHR</t>
+        </is>
+      </c>
+      <c r="L38" t="inlineStr">
+        <is>
+          <t>56-124106800</t>
+        </is>
+      </c>
+      <c r="M38" t="inlineStr">
+        <is>
+          <t>2026-06-11 00:00:00</t>
+        </is>
+      </c>
+      <c r="N38" t="inlineStr">
+        <is>
+          <t>2026-06-11 00:00:00</t>
+        </is>
+      </c>
+      <c r="O38" t="inlineStr">
+        <is>
+          <t>SARLA PERFORMANCE FIBERS LTD</t>
+        </is>
+      </c>
+      <c r="P38" t="inlineStr">
+        <is>
+          <t>SARLA PERFORMANCE FIBERS LTD</t>
+        </is>
+      </c>
+      <c r="Q38" t="inlineStr">
+        <is>
+          <t>2026-04-27 00:00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>2565646</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>EF4-0231408-4</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>Vessel, Container</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr"/>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>9903.03.01</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>SECTION 122 - 10% DUTY</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>007</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>9903.03.01</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>5402.33.3000</t>
+        </is>
+      </c>
+      <c r="J39" t="inlineStr">
+        <is>
+          <t>HICKORY THROWING COMPANY</t>
+        </is>
+      </c>
+      <c r="K39" t="inlineStr">
+        <is>
+          <t>HICTHR</t>
+        </is>
+      </c>
+      <c r="L39" t="inlineStr">
+        <is>
+          <t>56-124106800</t>
+        </is>
+      </c>
+      <c r="M39" t="inlineStr">
+        <is>
+          <t>2026-06-11 00:00:00</t>
+        </is>
+      </c>
+      <c r="N39" t="inlineStr">
+        <is>
+          <t>2026-06-11 00:00:00</t>
+        </is>
+      </c>
+      <c r="O39" t="inlineStr">
+        <is>
+          <t>SARLA PERFORMANCE FIBERS LTD</t>
+        </is>
+      </c>
+      <c r="P39" t="inlineStr">
+        <is>
+          <t>SARLA PERFORMANCE FIBERS LTD</t>
+        </is>
+      </c>
+      <c r="Q39" t="inlineStr">
+        <is>
+          <t>2026-04-27 00:00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>2565646</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>EF4-0231408-4</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>Vessel, Container</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr"/>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>9903.03.01</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>SECTION 122 - 10% DUTY</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>008</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>9903.03.01</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>5402.33.3000</t>
+        </is>
+      </c>
+      <c r="J40" t="inlineStr">
+        <is>
+          <t>HICKORY THROWING COMPANY</t>
+        </is>
+      </c>
+      <c r="K40" t="inlineStr">
+        <is>
+          <t>HICTHR</t>
+        </is>
+      </c>
+      <c r="L40" t="inlineStr">
+        <is>
+          <t>56-124106800</t>
+        </is>
+      </c>
+      <c r="M40" t="inlineStr">
+        <is>
+          <t>2026-06-11 00:00:00</t>
+        </is>
+      </c>
+      <c r="N40" t="inlineStr">
+        <is>
+          <t>2026-06-11 00:00:00</t>
+        </is>
+      </c>
+      <c r="O40" t="inlineStr">
+        <is>
+          <t>SARLA PERFORMANCE FIBERS LTD</t>
+        </is>
+      </c>
+      <c r="P40" t="inlineStr">
+        <is>
+          <t>SARLA PERFORMANCE FIBERS LTD</t>
+        </is>
+      </c>
+      <c r="Q40" t="inlineStr">
+        <is>
+          <t>2026-04-27 00:00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>2565646</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>EF4-0231408-4</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>Vessel, Container</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr"/>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>9903.03.01</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>SECTION 122 - 10% DUTY</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>009</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>9903.03.01</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>5402.61.0000</t>
+        </is>
+      </c>
+      <c r="J41" t="inlineStr">
+        <is>
+          <t>HICKORY THROWING COMPANY</t>
+        </is>
+      </c>
+      <c r="K41" t="inlineStr">
+        <is>
+          <t>HICTHR</t>
+        </is>
+      </c>
+      <c r="L41" t="inlineStr">
+        <is>
+          <t>56-124106800</t>
+        </is>
+      </c>
+      <c r="M41" t="inlineStr">
+        <is>
+          <t>2026-06-11 00:00:00</t>
+        </is>
+      </c>
+      <c r="N41" t="inlineStr">
+        <is>
+          <t>2026-06-11 00:00:00</t>
+        </is>
+      </c>
+      <c r="O41" t="inlineStr">
+        <is>
+          <t>SARLA PERFORMANCE FIBERS LTD</t>
+        </is>
+      </c>
+      <c r="P41" t="inlineStr">
+        <is>
+          <t>SARLA PERFORMANCE FIBERS LTD</t>
+        </is>
+      </c>
+      <c r="Q41" t="inlineStr">
+        <is>
+          <t>2026-04-27 00:00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>2565646</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>EF4-0231408-4</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>Vessel, Container</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr"/>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>9903.03.01</t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>SECTION 122 - 10% DUTY</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>010</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>9903.03.01</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>5402.61.0000</t>
+        </is>
+      </c>
+      <c r="J42" t="inlineStr">
+        <is>
+          <t>HICKORY THROWING COMPANY</t>
+        </is>
+      </c>
+      <c r="K42" t="inlineStr">
+        <is>
+          <t>HICTHR</t>
+        </is>
+      </c>
+      <c r="L42" t="inlineStr">
+        <is>
+          <t>56-124106800</t>
+        </is>
+      </c>
+      <c r="M42" t="inlineStr">
+        <is>
+          <t>2026-06-11 00:00:00</t>
+        </is>
+      </c>
+      <c r="N42" t="inlineStr">
+        <is>
+          <t>2026-06-11 00:00:00</t>
+        </is>
+      </c>
+      <c r="O42" t="inlineStr">
+        <is>
+          <t>SARLA PERFORMANCE FIBERS LTD</t>
+        </is>
+      </c>
+      <c r="P42" t="inlineStr">
+        <is>
+          <t>SARLA PERFORMANCE FIBERS LTD</t>
+        </is>
+      </c>
+      <c r="Q42" t="inlineStr">
+        <is>
+          <t>2026-04-27 00:00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>2565646</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>EF4-0231408-4</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>Vessel, Container</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr"/>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>9903.03.01</t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>SECTION 122 - 10% DUTY</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>011</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>9903.03.01</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>5402.52.9000</t>
+        </is>
+      </c>
+      <c r="J43" t="inlineStr">
+        <is>
+          <t>HICKORY THROWING COMPANY</t>
+        </is>
+      </c>
+      <c r="K43" t="inlineStr">
+        <is>
+          <t>HICTHR</t>
+        </is>
+      </c>
+      <c r="L43" t="inlineStr">
+        <is>
+          <t>56-124106800</t>
+        </is>
+      </c>
+      <c r="M43" t="inlineStr">
+        <is>
+          <t>2026-06-11 00:00:00</t>
+        </is>
+      </c>
+      <c r="N43" t="inlineStr">
+        <is>
+          <t>2026-06-11 00:00:00</t>
+        </is>
+      </c>
+      <c r="O43" t="inlineStr">
+        <is>
+          <t>SARLA PERFORMANCE FIBERS LTD</t>
+        </is>
+      </c>
+      <c r="P43" t="inlineStr">
+        <is>
+          <t>SARLA PERFORMANCE FIBERS LTD</t>
+        </is>
+      </c>
+      <c r="Q43" t="inlineStr">
+        <is>
+          <t>2026-04-27 00:00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>2565646</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>EF4-0231408-4</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>Vessel, Container</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr"/>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>9903.03.01</t>
+        </is>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>SECTION 122 - 10% DUTY</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>012</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>9903.03.01</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>5402.51.0000</t>
+        </is>
+      </c>
+      <c r="J44" t="inlineStr">
+        <is>
+          <t>HICKORY THROWING COMPANY</t>
+        </is>
+      </c>
+      <c r="K44" t="inlineStr">
+        <is>
+          <t>HICTHR</t>
+        </is>
+      </c>
+      <c r="L44" t="inlineStr">
+        <is>
+          <t>56-124106800</t>
+        </is>
+      </c>
+      <c r="M44" t="inlineStr">
+        <is>
+          <t>2026-06-11 00:00:00</t>
+        </is>
+      </c>
+      <c r="N44" t="inlineStr">
+        <is>
+          <t>2026-06-11 00:00:00</t>
+        </is>
+      </c>
+      <c r="O44" t="inlineStr">
+        <is>
+          <t>SARLA PERFORMANCE FIBERS LTD</t>
+        </is>
+      </c>
+      <c r="P44" t="inlineStr">
+        <is>
+          <t>SARLA PERFORMANCE FIBERS LTD</t>
+        </is>
+      </c>
+      <c r="Q44" t="inlineStr">
+        <is>
+          <t>2026-04-27 00:00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>2565646</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>EF4-0231408-4</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>Vessel, Container</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr"/>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>9903.03.01</t>
+        </is>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>SECTION 122 - 10% DUTY</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>013</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>9903.03.01</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>5402.61.0000</t>
+        </is>
+      </c>
+      <c r="J45" t="inlineStr">
+        <is>
+          <t>HICKORY THROWING COMPANY</t>
+        </is>
+      </c>
+      <c r="K45" t="inlineStr">
+        <is>
+          <t>HICTHR</t>
+        </is>
+      </c>
+      <c r="L45" t="inlineStr">
+        <is>
+          <t>56-124106800</t>
+        </is>
+      </c>
+      <c r="M45" t="inlineStr">
+        <is>
+          <t>2026-06-11 00:00:00</t>
+        </is>
+      </c>
+      <c r="N45" t="inlineStr">
+        <is>
+          <t>2026-06-11 00:00:00</t>
+        </is>
+      </c>
+      <c r="O45" t="inlineStr">
+        <is>
+          <t>SARLA PERFORMANCE FIBERS LTD</t>
+        </is>
+      </c>
+      <c r="P45" t="inlineStr">
+        <is>
+          <t>SARLA PERFORMANCE FIBERS LTD</t>
+        </is>
+      </c>
+      <c r="Q45" t="inlineStr">
+        <is>
+          <t>2026-04-27 00:00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>2565646</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>EF4-0231408-4</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>Vessel, Container</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr"/>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>9903.03.01</t>
+        </is>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>SECTION 122 - 10% DUTY</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>014</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>9903.03.01</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>5606.00.0010</t>
+        </is>
+      </c>
+      <c r="J46" t="inlineStr">
+        <is>
+          <t>HICKORY THROWING COMPANY</t>
+        </is>
+      </c>
+      <c r="K46" t="inlineStr">
+        <is>
+          <t>HICTHR</t>
+        </is>
+      </c>
+      <c r="L46" t="inlineStr">
+        <is>
+          <t>56-124106800</t>
+        </is>
+      </c>
+      <c r="M46" t="inlineStr">
+        <is>
+          <t>2026-06-11 00:00:00</t>
+        </is>
+      </c>
+      <c r="N46" t="inlineStr">
+        <is>
+          <t>2026-06-11 00:00:00</t>
+        </is>
+      </c>
+      <c r="O46" t="inlineStr">
+        <is>
+          <t>SARLA PERFORMANCE FIBERS LTD</t>
+        </is>
+      </c>
+      <c r="P46" t="inlineStr">
+        <is>
+          <t>SARLA PERFORMANCE FIBERS LTD</t>
+        </is>
+      </c>
+      <c r="Q46" t="inlineStr">
+        <is>
+          <t>2026-04-27 00:00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>2565772</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>EF4-0231545-3</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>Vessel, Container</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr"/>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>9903.03.01</t>
+        </is>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>SECTION 122 - 10% DUTY</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>001</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>9903.03.01</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr">
+        <is>
+          <t>5603.14.9090</t>
+        </is>
+      </c>
+      <c r="J47" t="inlineStr">
+        <is>
+          <t>VEER CORPORATIONS INC</t>
+        </is>
+      </c>
+      <c r="K47" t="inlineStr">
+        <is>
+          <t>VEECOR01</t>
+        </is>
+      </c>
+      <c r="L47" t="inlineStr">
+        <is>
+          <t>99-106989200</t>
+        </is>
+      </c>
+      <c r="M47" t="inlineStr">
+        <is>
+          <t>2026-06-11 00:00:00</t>
+        </is>
+      </c>
+      <c r="N47" t="inlineStr">
+        <is>
+          <t>2026-06-11 00:00:00</t>
+        </is>
+      </c>
+      <c r="O47" t="inlineStr">
+        <is>
+          <t>VEER PLASTIC PVT LTD</t>
+        </is>
+      </c>
+      <c r="P47" t="inlineStr">
+        <is>
+          <t>VEER PLASTIC PVT LTD</t>
+        </is>
+      </c>
+      <c r="Q47" t="inlineStr">
+        <is>
+          <t>2026-05-03 00:00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>2565681</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>EF4-0231551-1</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>Vessel, Container</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>V0710311346</t>
+        </is>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>9903.03.01</t>
+        </is>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>SECTION 122 - 10% DUTY</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>001</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>9903.03.01</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr">
+        <is>
+          <t>5603.14.9090</t>
+        </is>
+      </c>
+      <c r="J48" t="inlineStr">
+        <is>
+          <t>VEER CORPORATIONS INC</t>
+        </is>
+      </c>
+      <c r="K48" t="inlineStr">
+        <is>
+          <t>VEECOR01</t>
+        </is>
+      </c>
+      <c r="L48" t="inlineStr">
+        <is>
+          <t>99-106989200</t>
+        </is>
+      </c>
+      <c r="M48" t="inlineStr">
+        <is>
+          <t>2026-06-03 00:00:00</t>
+        </is>
+      </c>
+      <c r="N48" t="inlineStr">
+        <is>
+          <t>2026-06-11 00:00:00</t>
+        </is>
+      </c>
+      <c r="O48" t="inlineStr">
+        <is>
+          <t>VEER PLASTIC PVT LTD</t>
+        </is>
+      </c>
+      <c r="P48" t="inlineStr">
+        <is>
+          <t>VEER PLASTIC PVT LTD</t>
+        </is>
+      </c>
+      <c r="Q48" t="inlineStr">
+        <is>
+          <t>2026-05-04 00:00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>2565767</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>EF4-0231554-5</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>Vessel, Container</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>V0710311346</t>
+        </is>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>9903.03.01</t>
+        </is>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>SECTION 122 - 10% DUTY</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>001</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>9903.03.01</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr">
+        <is>
+          <t>5603.14.9090</t>
+        </is>
+      </c>
+      <c r="J49" t="inlineStr">
+        <is>
+          <t>VEER CORPORATIONS INC</t>
+        </is>
+      </c>
+      <c r="K49" t="inlineStr">
+        <is>
+          <t>VEECOR01</t>
+        </is>
+      </c>
+      <c r="L49" t="inlineStr">
+        <is>
+          <t>99-106989200</t>
+        </is>
+      </c>
+      <c r="M49" t="inlineStr">
+        <is>
+          <t>2026-06-12 00:00:00</t>
+        </is>
+      </c>
+      <c r="N49" t="inlineStr">
+        <is>
+          <t>2026-06-11 00:00:00</t>
+        </is>
+      </c>
+      <c r="O49" t="inlineStr">
+        <is>
+          <t>VEER PLASTIC PVT LTD</t>
+        </is>
+      </c>
+      <c r="P49" t="inlineStr">
+        <is>
+          <t>VEER PLASTIC PVT LTD</t>
+        </is>
+      </c>
+      <c r="Q49" t="inlineStr">
+        <is>
+          <t>2026-05-03 00:00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>2565717</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>EF4-0231634-5</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>Vessel, Container</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr"/>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>9903.03.03</t>
+        </is>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>S122 -EXCLUSION-EXEMPTED PRDTS</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>001</t>
+        </is>
+      </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>9903.03.03</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr">
+        <is>
+          <t>1108.14.0000</t>
+        </is>
+      </c>
+      <c r="J50" t="inlineStr">
+        <is>
+          <t>ROYAL INGREDIENTS GROUP BV</t>
+        </is>
+      </c>
+      <c r="K50" t="inlineStr">
+        <is>
+          <t>ROYINGRE</t>
+        </is>
+      </c>
+      <c r="L50" t="inlineStr">
+        <is>
+          <t>074601-00962</t>
+        </is>
+      </c>
+      <c r="M50" t="inlineStr">
+        <is>
+          <t>2026-06-11 00:00:00</t>
+        </is>
+      </c>
+      <c r="N50" t="inlineStr">
+        <is>
+          <t>2026-06-11 00:00:00</t>
+        </is>
+      </c>
+      <c r="O50" t="inlineStr">
+        <is>
+          <t>SOUTHEAST ASIA ORGANIC CO.,LTD.</t>
+        </is>
+      </c>
+      <c r="P50" t="inlineStr">
+        <is>
+          <t>SOUTHEAST ASIA ORGANIC CO.,LTD.</t>
+        </is>
+      </c>
+      <c r="Q50" t="inlineStr">
+        <is>
+          <t>2026-05-01 00:00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>105504693</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>EF4-0231692-3</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>Vessel, Non-container</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr"/>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>9805.00.50</t>
+        </is>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>EFFECTS US GOV EMP&amp;FAMLY/EVACU</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>001</t>
+        </is>
+      </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>9805.00.50</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr"/>
+      <c r="J51" t="inlineStr">
+        <is>
+          <t>IFF, INC.</t>
+        </is>
+      </c>
+      <c r="K51" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="L51" t="inlineStr">
+        <is>
+          <t>58-149385700</t>
+        </is>
+      </c>
+      <c r="M51" t="inlineStr">
+        <is>
+          <t>2026-06-11 00:00:00</t>
+        </is>
+      </c>
+      <c r="N51" t="inlineStr">
+        <is>
+          <t>2026-06-11 00:00:00</t>
+        </is>
+      </c>
+      <c r="O51" t="inlineStr">
+        <is>
+          <t>VOLVO CAR INTERNATIONAL CORPORATION</t>
+        </is>
+      </c>
+      <c r="P51" t="inlineStr">
+        <is>
+          <t>VOLVO CAR INTERNATIONAL CORPORATION</t>
+        </is>
+      </c>
+      <c r="Q51" t="inlineStr">
+        <is>
+          <t>2026-05-07 00:00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>105504694</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>EF4-0231694-9</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>Vessel, Non-container</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr"/>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>9805.00.50</t>
+        </is>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>EFFECTS US GOV EMP&amp;FAMLY/EVACU</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>001</t>
+        </is>
+      </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>9805.00.50</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr"/>
+      <c r="J52" t="inlineStr">
+        <is>
+          <t>IFF, INC.</t>
+        </is>
+      </c>
+      <c r="K52" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="L52" t="inlineStr">
+        <is>
+          <t>58-149385700</t>
+        </is>
+      </c>
+      <c r="M52" t="inlineStr">
+        <is>
+          <t>2026-06-11 00:00:00</t>
+        </is>
+      </c>
+      <c r="N52" t="inlineStr">
+        <is>
+          <t>2026-06-11 00:00:00</t>
+        </is>
+      </c>
+      <c r="O52" t="inlineStr">
+        <is>
+          <t>VOLVO CAR INTERNATIONAL CORPORATION</t>
+        </is>
+      </c>
+      <c r="P52" t="inlineStr">
+        <is>
+          <t>VOLVO CAR INTERNATIONAL CORPORATION</t>
+        </is>
+      </c>
+      <c r="Q52" t="inlineStr">
+        <is>
+          <t>2026-05-06 00:00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>105504702</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>EF4-0231794-7</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>Vessel, Non-container</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr"/>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>9805.00.50</t>
+        </is>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>EFFECTS US GOV EMP&amp;FAMLY/EVACU</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>001</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>9805.00.50</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr"/>
+      <c r="J53" t="inlineStr">
+        <is>
+          <t>IFF, INC.</t>
+        </is>
+      </c>
+      <c r="K53" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="L53" t="inlineStr">
+        <is>
+          <t>58-149385700</t>
+        </is>
+      </c>
+      <c r="M53" t="inlineStr">
+        <is>
+          <t>2026-06-11 00:00:00</t>
+        </is>
+      </c>
+      <c r="N53" t="inlineStr">
+        <is>
+          <t>2026-06-11 00:00:00</t>
+        </is>
+      </c>
+      <c r="O53" t="inlineStr">
+        <is>
+          <t>VOLVO CAR INTERNATIONAL CORPORATION</t>
+        </is>
+      </c>
+      <c r="P53" t="inlineStr">
+        <is>
+          <t>VOLVO CAR INTERNATIONAL CORPORATION</t>
+        </is>
+      </c>
+      <c r="Q53" t="inlineStr">
+        <is>
+          <t>2026-05-08 00:00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>105504703</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>EF4-0231801-0</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>Vessel, Non-container</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr"/>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>9805.00.50</t>
+        </is>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>EFFECTS US GOV EMP&amp;FAMLY/EVACU</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>001</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>9805.00.50</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr"/>
+      <c r="J54" t="inlineStr">
+        <is>
+          <t>IFF, INC.</t>
+        </is>
+      </c>
+      <c r="K54" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="L54" t="inlineStr">
+        <is>
+          <t>58-149385700</t>
+        </is>
+      </c>
+      <c r="M54" t="inlineStr">
+        <is>
+          <t>2026-06-11 00:00:00</t>
+        </is>
+      </c>
+      <c r="N54" t="inlineStr">
+        <is>
+          <t>2026-06-11 00:00:00</t>
+        </is>
+      </c>
+      <c r="O54" t="inlineStr">
+        <is>
+          <t>VOLVO CAR INTERNATIONAL CORPORATION</t>
+        </is>
+      </c>
+      <c r="P54" t="inlineStr">
+        <is>
+          <t>VOLVO CAR INTERNATIONAL CORPORATION</t>
+        </is>
+      </c>
+      <c r="Q54" t="inlineStr">
+        <is>
+          <t>2026-05-08 00:00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>105504718</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>EF4-0231836-6</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>Vessel, Non-container</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr"/>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>9805.00.50</t>
+        </is>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>EFFECTS US GOV EMP&amp;FAMLY/EVACU</t>
+        </is>
+      </c>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>001</t>
+        </is>
+      </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>9805.00.50</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr"/>
+      <c r="J55" t="inlineStr">
+        <is>
+          <t>IFF, INC.</t>
+        </is>
+      </c>
+      <c r="K55" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="L55" t="inlineStr">
+        <is>
+          <t>58-149385700</t>
+        </is>
+      </c>
+      <c r="M55" t="inlineStr">
+        <is>
+          <t>2026-06-11 00:00:00</t>
+        </is>
+      </c>
+      <c r="N55" t="inlineStr">
+        <is>
+          <t>2026-06-11 00:00:00</t>
+        </is>
+      </c>
+      <c r="O55" t="inlineStr">
+        <is>
+          <t>VOLVO CAR INTERNATIONAL CORPORATION</t>
+        </is>
+      </c>
+      <c r="P55" t="inlineStr">
+        <is>
+          <t>VOLVO CAR INTERNATIONAL CORPORATION</t>
+        </is>
+      </c>
+      <c r="Q55" t="inlineStr">
+        <is>
+          <t>2026-05-12 00:00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>105504719</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>EF4-0231837-4</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>Vessel, Non-container</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr"/>
+      <c r="E56" t="inlineStr">
+        <is>
+          <t>9805.00.50</t>
+        </is>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>EFFECTS US GOV EMP&amp;FAMLY/EVACU</t>
+        </is>
+      </c>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>001</t>
+        </is>
+      </c>
+      <c r="H56" t="inlineStr">
+        <is>
+          <t>9805.00.50</t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr"/>
+      <c r="J56" t="inlineStr">
+        <is>
+          <t>IFF, INC.</t>
+        </is>
+      </c>
+      <c r="K56" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="L56" t="inlineStr">
+        <is>
+          <t>58-149385700</t>
+        </is>
+      </c>
+      <c r="M56" t="inlineStr">
+        <is>
+          <t>2026-06-11 00:00:00</t>
+        </is>
+      </c>
+      <c r="N56" t="inlineStr">
+        <is>
+          <t>2026-06-11 00:00:00</t>
+        </is>
+      </c>
+      <c r="O56" t="inlineStr">
+        <is>
+          <t>VOLVO CAR INTERNATIONAL CORPORATION</t>
+        </is>
+      </c>
+      <c r="P56" t="inlineStr">
+        <is>
+          <t>VOLVO CAR INTERNATIONAL CORPORATION</t>
+        </is>
+      </c>
+      <c r="Q56" t="inlineStr">
+        <is>
+          <t>2026-05-14 00:00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>2565843</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>EF4-0231944-8</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>Vessel, Container</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr"/>
+      <c r="E57" t="inlineStr">
+        <is>
+          <t>9903.03.01</t>
+        </is>
+      </c>
+      <c r="F57" t="inlineStr"/>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>001</t>
+        </is>
+      </c>
+      <c r="H57" t="inlineStr">
+        <is>
+          <t>9903.03.01</t>
+        </is>
+      </c>
+      <c r="I57" t="inlineStr">
+        <is>
+          <t>1108.13.0010</t>
+        </is>
+      </c>
+      <c r="J57" t="inlineStr">
+        <is>
+          <t>ROYAL INGREDIENTS GROUP BV</t>
+        </is>
+      </c>
+      <c r="K57" t="inlineStr">
+        <is>
+          <t>ROYINGRE</t>
+        </is>
+      </c>
+      <c r="L57" t="inlineStr">
+        <is>
+          <t>074601-00962</t>
+        </is>
+      </c>
+      <c r="M57" t="inlineStr">
+        <is>
+          <t>2026-06-11 00:00:00</t>
+        </is>
+      </c>
+      <c r="N57" t="inlineStr">
+        <is>
+          <t>2026-06-11 00:00:00</t>
+        </is>
+      </c>
+      <c r="O57" t="inlineStr">
+        <is>
+          <t>PRZEDSIEBIORSTWO PRZEMYSLU ZIEMNIAC</t>
+        </is>
+      </c>
+      <c r="P57" t="inlineStr">
+        <is>
+          <t>PRZEDSIEBIORSTWO PRZEMYSLU ZIEMNIACZANEGO PEPEES S.A.</t>
+        </is>
+      </c>
+      <c r="Q57" t="inlineStr">
+        <is>
+          <t>2026-05-16 00:00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>2565900</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>EF4-0232029-7</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>Vessel, Container</t>
+        </is>
+      </c>
+      <c r="D58" t="inlineStr"/>
+      <c r="E58" t="inlineStr">
+        <is>
+          <t>9903.03.06</t>
+        </is>
+      </c>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>S122 EXCL,IRN/STL/ALUM,DERIV</t>
+        </is>
+      </c>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>001</t>
+        </is>
+      </c>
+      <c r="H58" t="inlineStr">
+        <is>
+          <t>9903.03.06</t>
+        </is>
+      </c>
+      <c r="I58" t="inlineStr">
+        <is>
+          <t>9903.82.10,8428.33.0000</t>
+        </is>
+      </c>
+      <c r="J58" t="inlineStr">
+        <is>
+          <t>AUMUND CORPORATION</t>
+        </is>
+      </c>
+      <c r="K58" t="inlineStr">
+        <is>
+          <t>AUMCOR</t>
+        </is>
+      </c>
+      <c r="L58" t="inlineStr">
+        <is>
+          <t>58-138896800</t>
+        </is>
+      </c>
+      <c r="M58" t="inlineStr">
+        <is>
+          <t>2026-06-12 00:00:00</t>
+        </is>
+      </c>
+      <c r="N58" t="inlineStr">
+        <is>
+          <t>2026-06-11 00:00:00</t>
+        </is>
+      </c>
+      <c r="O58" t="inlineStr">
+        <is>
+          <t>AUMUND FOERDERTECHNIK GMBH</t>
+        </is>
+      </c>
+      <c r="P58" t="inlineStr">
+        <is>
+          <t>AUMUND FOERDERTECHNIK GMBH</t>
+        </is>
+      </c>
+      <c r="Q58" t="inlineStr">
+        <is>
+          <t>2026-05-18 00:00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>2565816</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>EF4-0232058-6</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>Vessel, Container</t>
+        </is>
+      </c>
+      <c r="D59" t="inlineStr"/>
+      <c r="E59" t="inlineStr">
+        <is>
+          <t>9903.03.01</t>
+        </is>
+      </c>
+      <c r="F59" t="inlineStr">
+        <is>
+          <t>SECTION 122 - 10% DUTY</t>
+        </is>
+      </c>
+      <c r="G59" t="inlineStr">
+        <is>
+          <t>001</t>
+        </is>
+      </c>
+      <c r="H59" t="inlineStr">
+        <is>
+          <t>9903.03.01</t>
+        </is>
+      </c>
+      <c r="I59" t="inlineStr">
+        <is>
+          <t>1109.00.9010</t>
+        </is>
+      </c>
+      <c r="J59" t="inlineStr">
+        <is>
+          <t>ROYAL INGREDIENTS GROUP BV</t>
+        </is>
+      </c>
+      <c r="K59" t="inlineStr">
+        <is>
+          <t>ROYINGRE</t>
+        </is>
+      </c>
+      <c r="L59" t="inlineStr">
+        <is>
+          <t>074601-00962</t>
+        </is>
+      </c>
+      <c r="M59" t="inlineStr">
+        <is>
+          <t>2026-06-10 00:00:00</t>
+        </is>
+      </c>
+      <c r="N59" t="inlineStr">
+        <is>
+          <t>2026-06-11 00:00:00</t>
+        </is>
+      </c>
+      <c r="O59" t="inlineStr">
+        <is>
+          <t>KROENER-STARKE BIO GMBH</t>
+        </is>
+      </c>
+      <c r="P59" t="inlineStr">
+        <is>
+          <t>KROENER-STARKE BIO GMBH</t>
+        </is>
+      </c>
+      <c r="Q59" t="inlineStr">
+        <is>
+          <t>2026-05-22 00:00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>2565857</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>EF4-0232060-2</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>Vessel, Container</t>
+        </is>
+      </c>
+      <c r="D60" t="inlineStr"/>
+      <c r="E60" t="inlineStr">
+        <is>
+          <t>9903.03.01</t>
+        </is>
+      </c>
+      <c r="F60" t="inlineStr">
+        <is>
+          <t>SECTION 122 - 10% DUTY</t>
+        </is>
+      </c>
+      <c r="G60" t="inlineStr">
+        <is>
+          <t>001</t>
+        </is>
+      </c>
+      <c r="H60" t="inlineStr">
+        <is>
+          <t>9903.03.01</t>
+        </is>
+      </c>
+      <c r="I60" t="inlineStr">
+        <is>
+          <t>1108.13.0010</t>
+        </is>
+      </c>
+      <c r="J60" t="inlineStr">
+        <is>
+          <t>ROYAL INGREDIENTS GROUP BV</t>
+        </is>
+      </c>
+      <c r="K60" t="inlineStr">
+        <is>
+          <t>ROYINGRE</t>
+        </is>
+      </c>
+      <c r="L60" t="inlineStr">
+        <is>
+          <t>074601-00962</t>
+        </is>
+      </c>
+      <c r="M60" t="inlineStr">
+        <is>
+          <t>2026-06-10 00:00:00</t>
+        </is>
+      </c>
+      <c r="N60" t="inlineStr">
+        <is>
+          <t>2026-06-11 00:00:00</t>
+        </is>
+      </c>
+      <c r="O60" t="inlineStr">
+        <is>
+          <t>AKV LANGHOLT AMBA</t>
+        </is>
+      </c>
+      <c r="P60" t="inlineStr">
+        <is>
+          <t>AKV LANGHOLT AMBA</t>
+        </is>
+      </c>
+      <c r="Q60" t="inlineStr">
+        <is>
+          <t>2026-05-08 00:00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>2566034</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>EF4-0232180-8</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>Vessel, Container</t>
+        </is>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>V1626455557</t>
+        </is>
+      </c>
+      <c r="E61" t="inlineStr">
+        <is>
+          <t>9903.03.01</t>
+        </is>
+      </c>
+      <c r="F61" t="inlineStr"/>
+      <c r="G61" t="inlineStr">
+        <is>
+          <t>001</t>
+        </is>
+      </c>
+      <c r="H61" t="inlineStr">
+        <is>
+          <t>9903.03.01</t>
+        </is>
+      </c>
+      <c r="I61" t="inlineStr">
+        <is>
+          <t>1108.11.0010</t>
+        </is>
+      </c>
+      <c r="J61" t="inlineStr">
+        <is>
+          <t>ROYAL INGREDIENTS GROUP BV</t>
+        </is>
+      </c>
+      <c r="K61" t="inlineStr">
+        <is>
+          <t>ROYINGRE</t>
+        </is>
+      </c>
+      <c r="L61" t="inlineStr">
+        <is>
+          <t>074601-00962</t>
+        </is>
+      </c>
+      <c r="M61" t="inlineStr">
+        <is>
+          <t>2026-06-11 00:00:00</t>
+        </is>
+      </c>
+      <c r="N61" t="inlineStr">
+        <is>
+          <t>2026-06-11 00:00:00</t>
+        </is>
+      </c>
+      <c r="O61" t="inlineStr">
+        <is>
+          <t>KROENER-STARKE BIO GMBH</t>
+        </is>
+      </c>
+      <c r="P61" t="inlineStr">
+        <is>
+          <t>KROENER-STARKE BIO GMBH</t>
+        </is>
+      </c>
+      <c r="Q61" t="inlineStr">
+        <is>
+          <t>2026-05-28 00:00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>2566053</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>EF4-0232278-0</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>Vessel, Container</t>
+        </is>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>V1626455557</t>
+        </is>
+      </c>
+      <c r="E62" t="inlineStr">
+        <is>
+          <t>9903.03.06</t>
+        </is>
+      </c>
+      <c r="F62" t="inlineStr">
+        <is>
+          <t>S122 EXCL,IRN/STL/ALUM,DERIV</t>
+        </is>
+      </c>
+      <c r="G62" t="inlineStr">
+        <is>
+          <t>001</t>
+        </is>
+      </c>
+      <c r="H62" t="inlineStr">
+        <is>
+          <t>9903.03.06</t>
+        </is>
+      </c>
+      <c r="I62" t="inlineStr">
+        <is>
+          <t>9903.74.11,9903.94.53,8708.29.5160</t>
+        </is>
+      </c>
+      <c r="J62" t="inlineStr">
+        <is>
+          <t>BORGERS USA CORP</t>
+        </is>
+      </c>
+      <c r="K62" t="inlineStr">
+        <is>
+          <t>BORUSA</t>
+        </is>
+      </c>
+      <c r="L62" t="inlineStr">
+        <is>
+          <t>65-117296500</t>
+        </is>
+      </c>
+      <c r="M62" t="inlineStr">
+        <is>
+          <t>2026-06-12 00:00:00</t>
+        </is>
+      </c>
+      <c r="N62" t="inlineStr">
+        <is>
+          <t>2026-06-11 00:00:00</t>
+        </is>
+      </c>
+      <c r="O62" t="inlineStr">
+        <is>
+          <t>AUTONEUM CZ S.R.O.</t>
+        </is>
+      </c>
+      <c r="P62" t="inlineStr">
+        <is>
+          <t>AUTONEUM CZ S.R.O.</t>
+        </is>
+      </c>
+      <c r="Q62" t="inlineStr">
+        <is>
+          <t>2026-06-01 00:00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>2566053</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>EF4-0232278-0</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>Vessel, Container</t>
+        </is>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>V1626455557</t>
+        </is>
+      </c>
+      <c r="E63" t="inlineStr">
+        <is>
+          <t>9903.03.06</t>
+        </is>
+      </c>
+      <c r="F63" t="inlineStr">
+        <is>
+          <t>S122 EXCL,IRN/STL/ALUM,DERIV</t>
+        </is>
+      </c>
+      <c r="G63" t="inlineStr">
+        <is>
+          <t>002</t>
+        </is>
+      </c>
+      <c r="H63" t="inlineStr">
+        <is>
+          <t>9903.03.06</t>
+        </is>
+      </c>
+      <c r="I63" t="inlineStr">
+        <is>
+          <t>9903.74.11,9903.94.53,8708.29.5160</t>
+        </is>
+      </c>
+      <c r="J63" t="inlineStr">
+        <is>
+          <t>BORGERS USA CORP</t>
+        </is>
+      </c>
+      <c r="K63" t="inlineStr">
+        <is>
+          <t>BORUSA</t>
+        </is>
+      </c>
+      <c r="L63" t="inlineStr">
+        <is>
+          <t>65-117296500</t>
+        </is>
+      </c>
+      <c r="M63" t="inlineStr">
+        <is>
+          <t>2026-06-12 00:00:00</t>
+        </is>
+      </c>
+      <c r="N63" t="inlineStr">
+        <is>
+          <t>2026-06-11 00:00:00</t>
+        </is>
+      </c>
+      <c r="O63" t="inlineStr">
+        <is>
+          <t>AUTONEUM CZ S.R.O.</t>
+        </is>
+      </c>
+      <c r="P63" t="inlineStr">
+        <is>
+          <t>AUTONEUM CZ S.R.O.</t>
+        </is>
+      </c>
+      <c r="Q63" t="inlineStr">
+        <is>
+          <t>2026-06-01 00:00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>2566053</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>EF4-0232278-0</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>Vessel, Container</t>
+        </is>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>V1626455557</t>
+        </is>
+      </c>
+      <c r="E64" t="inlineStr">
+        <is>
+          <t>9903.03.06</t>
+        </is>
+      </c>
+      <c r="F64" t="inlineStr">
+        <is>
+          <t>S122 EXCL,IRN/STL/ALUM,DERIV</t>
+        </is>
+      </c>
+      <c r="G64" t="inlineStr">
+        <is>
+          <t>003</t>
+        </is>
+      </c>
+      <c r="H64" t="inlineStr">
+        <is>
+          <t>9903.03.06</t>
+        </is>
+      </c>
+      <c r="I64" t="inlineStr">
+        <is>
+          <t>9903.74.11,9903.94.53,8708.29.5160</t>
+        </is>
+      </c>
+      <c r="J64" t="inlineStr">
+        <is>
+          <t>BORGERS USA CORP</t>
+        </is>
+      </c>
+      <c r="K64" t="inlineStr">
+        <is>
+          <t>BORUSA</t>
+        </is>
+      </c>
+      <c r="L64" t="inlineStr">
+        <is>
+          <t>65-117296500</t>
+        </is>
+      </c>
+      <c r="M64" t="inlineStr">
+        <is>
+          <t>2026-06-12 00:00:00</t>
+        </is>
+      </c>
+      <c r="N64" t="inlineStr">
+        <is>
+          <t>2026-06-11 00:00:00</t>
+        </is>
+      </c>
+      <c r="O64" t="inlineStr">
+        <is>
+          <t>AUTONEUM CZ S.R.O.</t>
+        </is>
+      </c>
+      <c r="P64" t="inlineStr">
+        <is>
+          <t>AUTONEUM CZ S.R.O.</t>
+        </is>
+      </c>
+      <c r="Q64" t="inlineStr">
+        <is>
+          <t>2026-06-01 00:00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>2566053</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>EF4-0232278-0</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>Vessel, Container</t>
+        </is>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>V1626455557</t>
+        </is>
+      </c>
+      <c r="E65" t="inlineStr">
+        <is>
+          <t>9903.03.06</t>
+        </is>
+      </c>
+      <c r="F65" t="inlineStr">
+        <is>
+          <t>S122 EXCL,IRN/STL/ALUM,DERIV</t>
+        </is>
+      </c>
+      <c r="G65" t="inlineStr">
+        <is>
+          <t>004</t>
+        </is>
+      </c>
+      <c r="H65" t="inlineStr">
+        <is>
+          <t>9903.03.06</t>
+        </is>
+      </c>
+      <c r="I65" t="inlineStr">
+        <is>
+          <t>9903.74.11,9903.94.53,8708.29.5160</t>
+        </is>
+      </c>
+      <c r="J65" t="inlineStr">
+        <is>
+          <t>BORGERS USA CORP</t>
+        </is>
+      </c>
+      <c r="K65" t="inlineStr">
+        <is>
+          <t>BORUSA</t>
+        </is>
+      </c>
+      <c r="L65" t="inlineStr">
+        <is>
+          <t>65-117296500</t>
+        </is>
+      </c>
+      <c r="M65" t="inlineStr">
+        <is>
+          <t>2026-06-12 00:00:00</t>
+        </is>
+      </c>
+      <c r="N65" t="inlineStr">
+        <is>
+          <t>2026-06-11 00:00:00</t>
+        </is>
+      </c>
+      <c r="O65" t="inlineStr">
+        <is>
+          <t>AUTONEUM CZ S.R.O.</t>
+        </is>
+      </c>
+      <c r="P65" t="inlineStr">
+        <is>
+          <t>AUTONEUM CZ S.R.O.</t>
+        </is>
+      </c>
+      <c r="Q65" t="inlineStr">
+        <is>
+          <t>2026-06-01 00:00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>2566053</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>EF4-0232278-0</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>Vessel, Container</t>
+        </is>
+      </c>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>V1626455557</t>
+        </is>
+      </c>
+      <c r="E66" t="inlineStr">
+        <is>
+          <t>9903.03.06</t>
+        </is>
+      </c>
+      <c r="F66" t="inlineStr">
+        <is>
+          <t>S122 EXCL,IRN/STL/ALUM,DERIV</t>
+        </is>
+      </c>
+      <c r="G66" t="inlineStr">
+        <is>
+          <t>005</t>
+        </is>
+      </c>
+      <c r="H66" t="inlineStr">
+        <is>
+          <t>9903.03.06</t>
+        </is>
+      </c>
+      <c r="I66" t="inlineStr">
+        <is>
+          <t>9903.74.11,9903.94.53,8708.29.5160</t>
+        </is>
+      </c>
+      <c r="J66" t="inlineStr">
+        <is>
+          <t>BORGERS USA CORP</t>
+        </is>
+      </c>
+      <c r="K66" t="inlineStr">
+        <is>
+          <t>BORUSA</t>
+        </is>
+      </c>
+      <c r="L66" t="inlineStr">
+        <is>
+          <t>65-117296500</t>
+        </is>
+      </c>
+      <c r="M66" t="inlineStr">
+        <is>
+          <t>2026-06-12 00:00:00</t>
+        </is>
+      </c>
+      <c r="N66" t="inlineStr">
+        <is>
+          <t>2026-06-11 00:00:00</t>
+        </is>
+      </c>
+      <c r="O66" t="inlineStr">
+        <is>
+          <t>AUTONEUM CZ S.R.O.</t>
+        </is>
+      </c>
+      <c r="P66" t="inlineStr">
+        <is>
+          <t>AUTONEUM CZ S.R.O.</t>
+        </is>
+      </c>
+      <c r="Q66" t="inlineStr">
+        <is>
+          <t>2026-06-01 00:00:00</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/trimika_data.xlsx
+++ b/trimika_data.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q66"/>
+  <dimension ref="A1:Q102"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5922,6 +5922,3026 @@
         </is>
       </c>
     </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>2565494</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>EF4-0231250-0</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>Vessel, Container</t>
+        </is>
+      </c>
+      <c r="D67" t="inlineStr"/>
+      <c r="E67" t="inlineStr">
+        <is>
+          <t>9903.03.01</t>
+        </is>
+      </c>
+      <c r="F67" t="inlineStr">
+        <is>
+          <t>SECTION 122 - 10% DUTY</t>
+        </is>
+      </c>
+      <c r="G67" t="inlineStr">
+        <is>
+          <t>001</t>
+        </is>
+      </c>
+      <c r="H67" t="inlineStr">
+        <is>
+          <t>9903.03.01</t>
+        </is>
+      </c>
+      <c r="I67" t="inlineStr">
+        <is>
+          <t>1109.00.9020</t>
+        </is>
+      </c>
+      <c r="J67" t="inlineStr">
+        <is>
+          <t>ROYAL INGREDIENTS GROUP BV</t>
+        </is>
+      </c>
+      <c r="K67" t="inlineStr">
+        <is>
+          <t>ROYINGRE</t>
+        </is>
+      </c>
+      <c r="L67" t="inlineStr">
+        <is>
+          <t>074601-00962</t>
+        </is>
+      </c>
+      <c r="M67" t="inlineStr">
+        <is>
+          <t>2026-06-12 00:00:00</t>
+        </is>
+      </c>
+      <c r="N67" t="inlineStr">
+        <is>
+          <t>2026-06-12 00:00:00</t>
+        </is>
+      </c>
+      <c r="O67" t="inlineStr">
+        <is>
+          <t>ROQUETTE FRERES</t>
+        </is>
+      </c>
+      <c r="P67" t="inlineStr">
+        <is>
+          <t>ROQUETTE FRERES</t>
+        </is>
+      </c>
+      <c r="Q67" t="inlineStr">
+        <is>
+          <t>2026-04-18 00:00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>2565534</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>EF4-0231273-2</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>Vessel, Container</t>
+        </is>
+      </c>
+      <c r="D68" t="inlineStr"/>
+      <c r="E68" t="inlineStr">
+        <is>
+          <t>9903.03.01</t>
+        </is>
+      </c>
+      <c r="F68" t="inlineStr">
+        <is>
+          <t>SECTION 122 - 10% DUTY</t>
+        </is>
+      </c>
+      <c r="G68" t="inlineStr">
+        <is>
+          <t>001</t>
+        </is>
+      </c>
+      <c r="H68" t="inlineStr">
+        <is>
+          <t>9903.03.01</t>
+        </is>
+      </c>
+      <c r="I68" t="inlineStr">
+        <is>
+          <t>1108.13.0010</t>
+        </is>
+      </c>
+      <c r="J68" t="inlineStr">
+        <is>
+          <t>ROYAL INGREDIENTS GROUP BV</t>
+        </is>
+      </c>
+      <c r="K68" t="inlineStr">
+        <is>
+          <t>ROYINGRE</t>
+        </is>
+      </c>
+      <c r="L68" t="inlineStr">
+        <is>
+          <t>074601-00962</t>
+        </is>
+      </c>
+      <c r="M68" t="inlineStr">
+        <is>
+          <t>2026-06-12 00:00:00</t>
+        </is>
+      </c>
+      <c r="N68" t="inlineStr">
+        <is>
+          <t>2026-06-12 00:00:00</t>
+        </is>
+      </c>
+      <c r="O68" t="inlineStr">
+        <is>
+          <t>AKV LANGHOLT AMBA</t>
+        </is>
+      </c>
+      <c r="P68" t="inlineStr">
+        <is>
+          <t>AKV LANGHOLT AMBA</t>
+        </is>
+      </c>
+      <c r="Q68" t="inlineStr">
+        <is>
+          <t>2026-04-20 00:00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>2565697</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>EF4-0231423-3</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>Vessel, Container</t>
+        </is>
+      </c>
+      <c r="D69" t="inlineStr"/>
+      <c r="E69" t="inlineStr">
+        <is>
+          <t>9903.03.01</t>
+        </is>
+      </c>
+      <c r="F69" t="inlineStr">
+        <is>
+          <t>SECTION 122 - 10% DUTY</t>
+        </is>
+      </c>
+      <c r="G69" t="inlineStr">
+        <is>
+          <t>001</t>
+        </is>
+      </c>
+      <c r="H69" t="inlineStr">
+        <is>
+          <t>9903.03.01</t>
+        </is>
+      </c>
+      <c r="I69" t="inlineStr">
+        <is>
+          <t>1108.13.0010</t>
+        </is>
+      </c>
+      <c r="J69" t="inlineStr">
+        <is>
+          <t>ROYAL INGREDIENTS GROUP BV</t>
+        </is>
+      </c>
+      <c r="K69" t="inlineStr">
+        <is>
+          <t>ROYINGRE</t>
+        </is>
+      </c>
+      <c r="L69" t="inlineStr">
+        <is>
+          <t>074601-00962</t>
+        </is>
+      </c>
+      <c r="M69" t="inlineStr">
+        <is>
+          <t>2026-06-12 00:00:00</t>
+        </is>
+      </c>
+      <c r="N69" t="inlineStr">
+        <is>
+          <t>2026-06-12 00:00:00</t>
+        </is>
+      </c>
+      <c r="O69" t="inlineStr">
+        <is>
+          <t>AKV LANGHOLT AMBA</t>
+        </is>
+      </c>
+      <c r="P69" t="inlineStr">
+        <is>
+          <t>AKV LANGHOLT AMBA</t>
+        </is>
+      </c>
+      <c r="Q69" t="inlineStr">
+        <is>
+          <t>2026-04-27 00:00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>2565660</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>EF4-0231430-8</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>Vessel, Container</t>
+        </is>
+      </c>
+      <c r="D70" t="inlineStr"/>
+      <c r="E70" t="inlineStr">
+        <is>
+          <t>9903.03.01</t>
+        </is>
+      </c>
+      <c r="F70" t="inlineStr">
+        <is>
+          <t>SECTION 122 - 10% DUTY</t>
+        </is>
+      </c>
+      <c r="G70" t="inlineStr">
+        <is>
+          <t>001</t>
+        </is>
+      </c>
+      <c r="H70" t="inlineStr">
+        <is>
+          <t>9903.03.01</t>
+        </is>
+      </c>
+      <c r="I70" t="inlineStr">
+        <is>
+          <t>5903.90.3090</t>
+        </is>
+      </c>
+      <c r="J70" t="inlineStr">
+        <is>
+          <t>VEER CORPORATIONS INC</t>
+        </is>
+      </c>
+      <c r="K70" t="inlineStr">
+        <is>
+          <t>VEECOR01</t>
+        </is>
+      </c>
+      <c r="L70" t="inlineStr">
+        <is>
+          <t>99-106989200</t>
+        </is>
+      </c>
+      <c r="M70" t="inlineStr">
+        <is>
+          <t>2026-06-14 00:00:00</t>
+        </is>
+      </c>
+      <c r="N70" t="inlineStr">
+        <is>
+          <t>2026-06-12 00:00:00</t>
+        </is>
+      </c>
+      <c r="O70" t="inlineStr">
+        <is>
+          <t>VEER PLASTIC PVT LTD</t>
+        </is>
+      </c>
+      <c r="P70" t="inlineStr">
+        <is>
+          <t>VEER PLASTIC PVT LTD</t>
+        </is>
+      </c>
+      <c r="Q70" t="inlineStr">
+        <is>
+          <t>2026-04-28 00:00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>2565924</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>EF4-0231960-4</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>Vessel, Container</t>
+        </is>
+      </c>
+      <c r="D71" t="inlineStr"/>
+      <c r="E71" t="inlineStr">
+        <is>
+          <t>9903.03.01</t>
+        </is>
+      </c>
+      <c r="F71" t="inlineStr">
+        <is>
+          <t>SECTION 122 - 10% DUTY</t>
+        </is>
+      </c>
+      <c r="G71" t="inlineStr">
+        <is>
+          <t>001</t>
+        </is>
+      </c>
+      <c r="H71" t="inlineStr">
+        <is>
+          <t>9903.03.01</t>
+        </is>
+      </c>
+      <c r="I71" t="inlineStr">
+        <is>
+          <t>1109.00.9020</t>
+        </is>
+      </c>
+      <c r="J71" t="inlineStr">
+        <is>
+          <t>ROYAL INGREDIENTS GROUP BV</t>
+        </is>
+      </c>
+      <c r="K71" t="inlineStr">
+        <is>
+          <t>ROYINGRE</t>
+        </is>
+      </c>
+      <c r="L71" t="inlineStr">
+        <is>
+          <t>074601-00962</t>
+        </is>
+      </c>
+      <c r="M71" t="inlineStr">
+        <is>
+          <t>2026-06-12 00:00:00</t>
+        </is>
+      </c>
+      <c r="N71" t="inlineStr">
+        <is>
+          <t>2026-06-12 00:00:00</t>
+        </is>
+      </c>
+      <c r="O71" t="inlineStr">
+        <is>
+          <t>JACKERING MUHLEN UND NAHRMITTELWERK</t>
+        </is>
+      </c>
+      <c r="P71" t="inlineStr">
+        <is>
+          <t>JACKERING MUHLEN UND NAHRMITTELWERKE GMBH</t>
+        </is>
+      </c>
+      <c r="Q71" t="inlineStr">
+        <is>
+          <t>2026-05-18 00:00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>2566052</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>EF4-0232193-1</t>
+        </is>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>Vessel, Container</t>
+        </is>
+      </c>
+      <c r="D72" t="inlineStr"/>
+      <c r="E72" t="inlineStr">
+        <is>
+          <t>9903.03.01</t>
+        </is>
+      </c>
+      <c r="F72" t="inlineStr">
+        <is>
+          <t>SECTION 122 - 10% DUTY</t>
+        </is>
+      </c>
+      <c r="G72" t="inlineStr">
+        <is>
+          <t>001</t>
+        </is>
+      </c>
+      <c r="H72" t="inlineStr">
+        <is>
+          <t>9903.03.01</t>
+        </is>
+      </c>
+      <c r="I72" t="inlineStr">
+        <is>
+          <t>3402.90.1000</t>
+        </is>
+      </c>
+      <c r="J72" t="inlineStr">
+        <is>
+          <t>FI-TECH INC</t>
+        </is>
+      </c>
+      <c r="K72" t="inlineStr">
+        <is>
+          <t>FITINC</t>
+        </is>
+      </c>
+      <c r="L72" t="inlineStr">
+        <is>
+          <t>54-091465000</t>
+        </is>
+      </c>
+      <c r="M72" t="inlineStr">
+        <is>
+          <t>2026-06-12 00:00:00</t>
+        </is>
+      </c>
+      <c r="N72" t="inlineStr">
+        <is>
+          <t>2026-06-12 00:00:00</t>
+        </is>
+      </c>
+      <c r="O72" t="inlineStr">
+        <is>
+          <t>SCHILL SEILACHER GMBH CO</t>
+        </is>
+      </c>
+      <c r="P72" t="inlineStr">
+        <is>
+          <t>SCHILL SEILACHER GMBH CO</t>
+        </is>
+      </c>
+      <c r="Q72" t="inlineStr">
+        <is>
+          <t>2026-05-28 00:00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>2566057</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>EF4-0232211-1</t>
+        </is>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>Vessel, Container</t>
+        </is>
+      </c>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>V1626460482</t>
+        </is>
+      </c>
+      <c r="E73" t="inlineStr">
+        <is>
+          <t>9903.03.01</t>
+        </is>
+      </c>
+      <c r="F73" t="inlineStr">
+        <is>
+          <t>SECTION 122 - 10% DUTY</t>
+        </is>
+      </c>
+      <c r="G73" t="inlineStr">
+        <is>
+          <t>001</t>
+        </is>
+      </c>
+      <c r="H73" t="inlineStr">
+        <is>
+          <t>9903.03.01</t>
+        </is>
+      </c>
+      <c r="I73" t="inlineStr">
+        <is>
+          <t>1109.00.9020</t>
+        </is>
+      </c>
+      <c r="J73" t="inlineStr">
+        <is>
+          <t>ROYAL INGREDIENTS GROUP BV</t>
+        </is>
+      </c>
+      <c r="K73" t="inlineStr">
+        <is>
+          <t>ROYINGRE</t>
+        </is>
+      </c>
+      <c r="L73" t="inlineStr">
+        <is>
+          <t>074601-00962</t>
+        </is>
+      </c>
+      <c r="M73" t="inlineStr">
+        <is>
+          <t>2026-06-14 00:00:00</t>
+        </is>
+      </c>
+      <c r="N73" t="inlineStr">
+        <is>
+          <t>2026-06-12 00:00:00</t>
+        </is>
+      </c>
+      <c r="O73" t="inlineStr">
+        <is>
+          <t>JACKERING MUHLEN UND NAHRMITTELWERK</t>
+        </is>
+      </c>
+      <c r="P73" t="inlineStr">
+        <is>
+          <t>JACKERING MUHLEN UND NAHRMITTELWERKE GMBH</t>
+        </is>
+      </c>
+      <c r="Q73" t="inlineStr">
+        <is>
+          <t>2026-05-30 00:00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>2566058</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>EF4-0232213-7</t>
+        </is>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>Vessel, Container</t>
+        </is>
+      </c>
+      <c r="D74" t="inlineStr">
+        <is>
+          <t>V1626460482</t>
+        </is>
+      </c>
+      <c r="E74" t="inlineStr">
+        <is>
+          <t>9903.03.01</t>
+        </is>
+      </c>
+      <c r="F74" t="inlineStr">
+        <is>
+          <t>SECTION 122 - 10% DUTY</t>
+        </is>
+      </c>
+      <c r="G74" t="inlineStr">
+        <is>
+          <t>001</t>
+        </is>
+      </c>
+      <c r="H74" t="inlineStr">
+        <is>
+          <t>9903.03.01</t>
+        </is>
+      </c>
+      <c r="I74" t="inlineStr">
+        <is>
+          <t>1109.00.9020</t>
+        </is>
+      </c>
+      <c r="J74" t="inlineStr">
+        <is>
+          <t>ROYAL INGREDIENTS GROUP BV</t>
+        </is>
+      </c>
+      <c r="K74" t="inlineStr">
+        <is>
+          <t>ROYINGRE</t>
+        </is>
+      </c>
+      <c r="L74" t="inlineStr">
+        <is>
+          <t>074601-00962</t>
+        </is>
+      </c>
+      <c r="M74" t="inlineStr">
+        <is>
+          <t>2026-06-14 00:00:00</t>
+        </is>
+      </c>
+      <c r="N74" t="inlineStr">
+        <is>
+          <t>2026-06-12 00:00:00</t>
+        </is>
+      </c>
+      <c r="O74" t="inlineStr">
+        <is>
+          <t>JACKERING MUHLEN UND NAHRMITTELWERK</t>
+        </is>
+      </c>
+      <c r="P74" t="inlineStr">
+        <is>
+          <t>JACKERING MUHLEN UND NAHRMITTELWERKE GMBH</t>
+        </is>
+      </c>
+      <c r="Q74" t="inlineStr">
+        <is>
+          <t>2026-05-30 00:00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>2566067</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>EF4-0232214-5</t>
+        </is>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>Vessel, Container</t>
+        </is>
+      </c>
+      <c r="D75" t="inlineStr">
+        <is>
+          <t>V1626460482</t>
+        </is>
+      </c>
+      <c r="E75" t="inlineStr">
+        <is>
+          <t>9903.03.01</t>
+        </is>
+      </c>
+      <c r="F75" t="inlineStr">
+        <is>
+          <t>SECTION 122 - 10% DUTY</t>
+        </is>
+      </c>
+      <c r="G75" t="inlineStr">
+        <is>
+          <t>001</t>
+        </is>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>9903.03.01</t>
+        </is>
+      </c>
+      <c r="I75" t="inlineStr">
+        <is>
+          <t>1109.00.9020</t>
+        </is>
+      </c>
+      <c r="J75" t="inlineStr">
+        <is>
+          <t>ROYAL INGREDIENTS GROUP BV</t>
+        </is>
+      </c>
+      <c r="K75" t="inlineStr">
+        <is>
+          <t>ROYINGRE</t>
+        </is>
+      </c>
+      <c r="L75" t="inlineStr">
+        <is>
+          <t>074601-00962</t>
+        </is>
+      </c>
+      <c r="M75" t="inlineStr">
+        <is>
+          <t>2026-06-14 00:00:00</t>
+        </is>
+      </c>
+      <c r="N75" t="inlineStr">
+        <is>
+          <t>2026-06-12 00:00:00</t>
+        </is>
+      </c>
+      <c r="O75" t="inlineStr">
+        <is>
+          <t>JACKERING MUHLEN UND NAHRMITTELWERK</t>
+        </is>
+      </c>
+      <c r="P75" t="inlineStr">
+        <is>
+          <t>JACKERING MUHLEN UND NAHRMITTELWERKE GMBH</t>
+        </is>
+      </c>
+      <c r="Q75" t="inlineStr">
+        <is>
+          <t>2026-05-30 00:00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>2566070</t>
+        </is>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>EF4-0232215-2</t>
+        </is>
+      </c>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>Vessel, Container</t>
+        </is>
+      </c>
+      <c r="D76" t="inlineStr">
+        <is>
+          <t>V1626460482</t>
+        </is>
+      </c>
+      <c r="E76" t="inlineStr">
+        <is>
+          <t>9903.03.01</t>
+        </is>
+      </c>
+      <c r="F76" t="inlineStr">
+        <is>
+          <t>SECTION 122 - 10% DUTY</t>
+        </is>
+      </c>
+      <c r="G76" t="inlineStr">
+        <is>
+          <t>001</t>
+        </is>
+      </c>
+      <c r="H76" t="inlineStr">
+        <is>
+          <t>9903.03.01</t>
+        </is>
+      </c>
+      <c r="I76" t="inlineStr">
+        <is>
+          <t>1109.00.9020</t>
+        </is>
+      </c>
+      <c r="J76" t="inlineStr">
+        <is>
+          <t>ROYAL INGREDIENTS GROUP BV</t>
+        </is>
+      </c>
+      <c r="K76" t="inlineStr">
+        <is>
+          <t>ROYINGRE</t>
+        </is>
+      </c>
+      <c r="L76" t="inlineStr">
+        <is>
+          <t>074601-00962</t>
+        </is>
+      </c>
+      <c r="M76" t="inlineStr">
+        <is>
+          <t>2026-06-14 00:00:00</t>
+        </is>
+      </c>
+      <c r="N76" t="inlineStr">
+        <is>
+          <t>2026-06-12 00:00:00</t>
+        </is>
+      </c>
+      <c r="O76" t="inlineStr">
+        <is>
+          <t>JACKERING MUHLEN UND NAHRMITTELWERK</t>
+        </is>
+      </c>
+      <c r="P76" t="inlineStr">
+        <is>
+          <t>JACKERING MUHLEN UND NAHRMITTELWERKE GMBH</t>
+        </is>
+      </c>
+      <c r="Q76" t="inlineStr">
+        <is>
+          <t>2026-05-30 00:00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>4539358</t>
+        </is>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>EF4-0232235-0</t>
+        </is>
+      </c>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>Air, Non-container</t>
+        </is>
+      </c>
+      <c r="D77" t="inlineStr">
+        <is>
+          <t>01650618422</t>
+        </is>
+      </c>
+      <c r="E77" t="inlineStr">
+        <is>
+          <t>9903.03.01</t>
+        </is>
+      </c>
+      <c r="F77" t="inlineStr">
+        <is>
+          <t>SECTION 122 - 10% DUTY</t>
+        </is>
+      </c>
+      <c r="G77" t="inlineStr">
+        <is>
+          <t>001</t>
+        </is>
+      </c>
+      <c r="H77" t="inlineStr">
+        <is>
+          <t>9903.03.01</t>
+        </is>
+      </c>
+      <c r="I77" t="inlineStr">
+        <is>
+          <t>3204.19.2020</t>
+        </is>
+      </c>
+      <c r="J77" t="inlineStr">
+        <is>
+          <t>COLORCHEM INTERNATIONAL CORP</t>
+        </is>
+      </c>
+      <c r="K77" t="inlineStr">
+        <is>
+          <t>COLORC01</t>
+        </is>
+      </c>
+      <c r="L77" t="inlineStr">
+        <is>
+          <t>58-241511400</t>
+        </is>
+      </c>
+      <c r="M77" t="inlineStr">
+        <is>
+          <t>2026-06-12 00:00:00</t>
+        </is>
+      </c>
+      <c r="N77" t="inlineStr">
+        <is>
+          <t>2026-06-12 00:00:00</t>
+        </is>
+      </c>
+      <c r="O77" t="inlineStr">
+        <is>
+          <t>PHILODEN INDUSTRIES PVT LTD</t>
+        </is>
+      </c>
+      <c r="P77" t="inlineStr">
+        <is>
+          <t>PHILODEN INDUSTRIES PVT LTD</t>
+        </is>
+      </c>
+      <c r="Q77" t="inlineStr">
+        <is>
+          <t>2026-06-12 00:00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>2566145</t>
+        </is>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>EF4-0232245-9</t>
+        </is>
+      </c>
+      <c r="C78" t="inlineStr">
+        <is>
+          <t>Vessel, Container</t>
+        </is>
+      </c>
+      <c r="D78" t="inlineStr">
+        <is>
+          <t>01650618422</t>
+        </is>
+      </c>
+      <c r="E78" t="inlineStr">
+        <is>
+          <t>9903.03.01</t>
+        </is>
+      </c>
+      <c r="F78" t="inlineStr">
+        <is>
+          <t>SECTION 122 - 10% DUTY</t>
+        </is>
+      </c>
+      <c r="G78" t="inlineStr">
+        <is>
+          <t>001</t>
+        </is>
+      </c>
+      <c r="H78" t="inlineStr">
+        <is>
+          <t>9903.03.01</t>
+        </is>
+      </c>
+      <c r="I78" t="inlineStr">
+        <is>
+          <t>1109.00.9010</t>
+        </is>
+      </c>
+      <c r="J78" t="inlineStr">
+        <is>
+          <t>ROYAL INGREDIENTS GROUP BV</t>
+        </is>
+      </c>
+      <c r="K78" t="inlineStr">
+        <is>
+          <t>ROYINGRE</t>
+        </is>
+      </c>
+      <c r="L78" t="inlineStr">
+        <is>
+          <t>074601-00962</t>
+        </is>
+      </c>
+      <c r="M78" t="inlineStr">
+        <is>
+          <t>2026-06-14 00:00:00</t>
+        </is>
+      </c>
+      <c r="N78" t="inlineStr">
+        <is>
+          <t>2026-06-12 00:00:00</t>
+        </is>
+      </c>
+      <c r="O78" t="inlineStr">
+        <is>
+          <t>KROENER-STARKE BIO GMBH</t>
+        </is>
+      </c>
+      <c r="P78" t="inlineStr">
+        <is>
+          <t>KROENER-STARKE BIO GMBH</t>
+        </is>
+      </c>
+      <c r="Q78" t="inlineStr">
+        <is>
+          <t>2026-06-01 00:00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>2566233</t>
+        </is>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>EF4-0232259-0</t>
+        </is>
+      </c>
+      <c r="C79" t="inlineStr">
+        <is>
+          <t>Vessel, Container</t>
+        </is>
+      </c>
+      <c r="D79" t="inlineStr"/>
+      <c r="E79" t="inlineStr">
+        <is>
+          <t>9903.03.01</t>
+        </is>
+      </c>
+      <c r="F79" t="inlineStr">
+        <is>
+          <t>SECTION 122 - 10% DUTY</t>
+        </is>
+      </c>
+      <c r="G79" t="inlineStr">
+        <is>
+          <t>001</t>
+        </is>
+      </c>
+      <c r="H79" t="inlineStr">
+        <is>
+          <t>9903.03.01</t>
+        </is>
+      </c>
+      <c r="I79" t="inlineStr">
+        <is>
+          <t>8421.99.0180</t>
+        </is>
+      </c>
+      <c r="J79" t="inlineStr">
+        <is>
+          <t>FI-TECH INC</t>
+        </is>
+      </c>
+      <c r="K79" t="inlineStr">
+        <is>
+          <t>FITINC</t>
+        </is>
+      </c>
+      <c r="L79" t="inlineStr">
+        <is>
+          <t>54-091465000</t>
+        </is>
+      </c>
+      <c r="M79" t="inlineStr">
+        <is>
+          <t>2026-06-12 00:00:00</t>
+        </is>
+      </c>
+      <c r="N79" t="inlineStr">
+        <is>
+          <t>2026-06-12 00:00:00</t>
+        </is>
+      </c>
+      <c r="O79" t="inlineStr">
+        <is>
+          <t>FILTERTECHNIK EUROPE GMBH &amp; CO KG</t>
+        </is>
+      </c>
+      <c r="P79" t="inlineStr">
+        <is>
+          <t>FILTERTECHNIK EUROPE GMBH &amp; CO KG</t>
+        </is>
+      </c>
+      <c r="Q79" t="inlineStr">
+        <is>
+          <t>2026-05-28 00:00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>2566233</t>
+        </is>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>EF4-0232259-0</t>
+        </is>
+      </c>
+      <c r="C80" t="inlineStr">
+        <is>
+          <t>Vessel, Container</t>
+        </is>
+      </c>
+      <c r="D80" t="inlineStr"/>
+      <c r="E80" t="inlineStr">
+        <is>
+          <t>9903.03.01</t>
+        </is>
+      </c>
+      <c r="F80" t="inlineStr">
+        <is>
+          <t>SECTION 122 - 10% DUTY</t>
+        </is>
+      </c>
+      <c r="G80" t="inlineStr">
+        <is>
+          <t>002</t>
+        </is>
+      </c>
+      <c r="H80" t="inlineStr">
+        <is>
+          <t>9903.03.01</t>
+        </is>
+      </c>
+      <c r="I80" t="inlineStr">
+        <is>
+          <t>8421.99.0180</t>
+        </is>
+      </c>
+      <c r="J80" t="inlineStr">
+        <is>
+          <t>FI-TECH INC</t>
+        </is>
+      </c>
+      <c r="K80" t="inlineStr">
+        <is>
+          <t>FITINC</t>
+        </is>
+      </c>
+      <c r="L80" t="inlineStr">
+        <is>
+          <t>54-091465000</t>
+        </is>
+      </c>
+      <c r="M80" t="inlineStr">
+        <is>
+          <t>2026-06-12 00:00:00</t>
+        </is>
+      </c>
+      <c r="N80" t="inlineStr">
+        <is>
+          <t>2026-06-12 00:00:00</t>
+        </is>
+      </c>
+      <c r="O80" t="inlineStr">
+        <is>
+          <t>WIREMESH-PRO TEC GMBH</t>
+        </is>
+      </c>
+      <c r="P80" t="inlineStr">
+        <is>
+          <t>WIREMESH-PRO TEC GMBH</t>
+        </is>
+      </c>
+      <c r="Q80" t="inlineStr">
+        <is>
+          <t>2026-05-28 00:00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>2566233</t>
+        </is>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>EF4-0232259-0</t>
+        </is>
+      </c>
+      <c r="C81" t="inlineStr">
+        <is>
+          <t>Vessel, Container</t>
+        </is>
+      </c>
+      <c r="D81" t="inlineStr"/>
+      <c r="E81" t="inlineStr">
+        <is>
+          <t>9903.03.01</t>
+        </is>
+      </c>
+      <c r="F81" t="inlineStr">
+        <is>
+          <t>SECTION 122 - 10% DUTY</t>
+        </is>
+      </c>
+      <c r="G81" t="inlineStr">
+        <is>
+          <t>003</t>
+        </is>
+      </c>
+      <c r="H81" t="inlineStr">
+        <is>
+          <t>9903.03.01</t>
+        </is>
+      </c>
+      <c r="I81" t="inlineStr">
+        <is>
+          <t>8421.99.0180</t>
+        </is>
+      </c>
+      <c r="J81" t="inlineStr">
+        <is>
+          <t>FI-TECH INC</t>
+        </is>
+      </c>
+      <c r="K81" t="inlineStr">
+        <is>
+          <t>FITINC</t>
+        </is>
+      </c>
+      <c r="L81" t="inlineStr">
+        <is>
+          <t>54-091465000</t>
+        </is>
+      </c>
+      <c r="M81" t="inlineStr">
+        <is>
+          <t>2026-06-12 00:00:00</t>
+        </is>
+      </c>
+      <c r="N81" t="inlineStr">
+        <is>
+          <t>2026-06-12 00:00:00</t>
+        </is>
+      </c>
+      <c r="O81" t="inlineStr">
+        <is>
+          <t>WIREMESH-PRO TEC GMBH</t>
+        </is>
+      </c>
+      <c r="P81" t="inlineStr">
+        <is>
+          <t>WIREMESH-PRO TEC GMBH</t>
+        </is>
+      </c>
+      <c r="Q81" t="inlineStr">
+        <is>
+          <t>2026-05-28 00:00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>2566233</t>
+        </is>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>EF4-0232259-0</t>
+        </is>
+      </c>
+      <c r="C82" t="inlineStr">
+        <is>
+          <t>Vessel, Container</t>
+        </is>
+      </c>
+      <c r="D82" t="inlineStr"/>
+      <c r="E82" t="inlineStr">
+        <is>
+          <t>9903.03.01</t>
+        </is>
+      </c>
+      <c r="F82" t="inlineStr">
+        <is>
+          <t>SECTION 122 - 10% DUTY</t>
+        </is>
+      </c>
+      <c r="G82" t="inlineStr">
+        <is>
+          <t>004</t>
+        </is>
+      </c>
+      <c r="H82" t="inlineStr">
+        <is>
+          <t>9903.03.01</t>
+        </is>
+      </c>
+      <c r="I82" t="inlineStr">
+        <is>
+          <t>8421.99.0180</t>
+        </is>
+      </c>
+      <c r="J82" t="inlineStr">
+        <is>
+          <t>FI-TECH INC</t>
+        </is>
+      </c>
+      <c r="K82" t="inlineStr">
+        <is>
+          <t>FITINC</t>
+        </is>
+      </c>
+      <c r="L82" t="inlineStr">
+        <is>
+          <t>54-091465000</t>
+        </is>
+      </c>
+      <c r="M82" t="inlineStr">
+        <is>
+          <t>2026-06-12 00:00:00</t>
+        </is>
+      </c>
+      <c r="N82" t="inlineStr">
+        <is>
+          <t>2026-06-12 00:00:00</t>
+        </is>
+      </c>
+      <c r="O82" t="inlineStr">
+        <is>
+          <t>WIREMESH-PRO TEC GMBH</t>
+        </is>
+      </c>
+      <c r="P82" t="inlineStr">
+        <is>
+          <t>WIREMESH-PRO TEC GMBH</t>
+        </is>
+      </c>
+      <c r="Q82" t="inlineStr">
+        <is>
+          <t>2026-05-28 00:00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>2566233</t>
+        </is>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>EF4-0232259-0</t>
+        </is>
+      </c>
+      <c r="C83" t="inlineStr">
+        <is>
+          <t>Vessel, Container</t>
+        </is>
+      </c>
+      <c r="D83" t="inlineStr"/>
+      <c r="E83" t="inlineStr">
+        <is>
+          <t>9903.03.01</t>
+        </is>
+      </c>
+      <c r="F83" t="inlineStr">
+        <is>
+          <t>SECTION 122 - 10% DUTY</t>
+        </is>
+      </c>
+      <c r="G83" t="inlineStr">
+        <is>
+          <t>005</t>
+        </is>
+      </c>
+      <c r="H83" t="inlineStr">
+        <is>
+          <t>9903.03.01</t>
+        </is>
+      </c>
+      <c r="I83" t="inlineStr">
+        <is>
+          <t>8421.99.0180</t>
+        </is>
+      </c>
+      <c r="J83" t="inlineStr">
+        <is>
+          <t>FI-TECH INC</t>
+        </is>
+      </c>
+      <c r="K83" t="inlineStr">
+        <is>
+          <t>FITINC</t>
+        </is>
+      </c>
+      <c r="L83" t="inlineStr">
+        <is>
+          <t>54-091465000</t>
+        </is>
+      </c>
+      <c r="M83" t="inlineStr">
+        <is>
+          <t>2026-06-12 00:00:00</t>
+        </is>
+      </c>
+      <c r="N83" t="inlineStr">
+        <is>
+          <t>2026-06-12 00:00:00</t>
+        </is>
+      </c>
+      <c r="O83" t="inlineStr">
+        <is>
+          <t>REIFENHAUSER REICOFIL GMBH &amp; CO. KG</t>
+        </is>
+      </c>
+      <c r="P83" t="inlineStr">
+        <is>
+          <t>REIFENHAUSER REICOFIL GMBH &amp; CO. KG</t>
+        </is>
+      </c>
+      <c r="Q83" t="inlineStr">
+        <is>
+          <t>2026-05-28 00:00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>2566233</t>
+        </is>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>EF4-0232259-0</t>
+        </is>
+      </c>
+      <c r="C84" t="inlineStr">
+        <is>
+          <t>Vessel, Container</t>
+        </is>
+      </c>
+      <c r="D84" t="inlineStr"/>
+      <c r="E84" t="inlineStr">
+        <is>
+          <t>9903.03.01</t>
+        </is>
+      </c>
+      <c r="F84" t="inlineStr">
+        <is>
+          <t>SECTION 122 - 10% DUTY</t>
+        </is>
+      </c>
+      <c r="G84" t="inlineStr">
+        <is>
+          <t>006</t>
+        </is>
+      </c>
+      <c r="H84" t="inlineStr">
+        <is>
+          <t>9903.03.01</t>
+        </is>
+      </c>
+      <c r="I84" t="inlineStr">
+        <is>
+          <t>8448.20.5090</t>
+        </is>
+      </c>
+      <c r="J84" t="inlineStr">
+        <is>
+          <t>FI-TECH INC</t>
+        </is>
+      </c>
+      <c r="K84" t="inlineStr">
+        <is>
+          <t>FITINC</t>
+        </is>
+      </c>
+      <c r="L84" t="inlineStr">
+        <is>
+          <t>54-091465000</t>
+        </is>
+      </c>
+      <c r="M84" t="inlineStr">
+        <is>
+          <t>2026-06-12 00:00:00</t>
+        </is>
+      </c>
+      <c r="N84" t="inlineStr">
+        <is>
+          <t>2026-06-12 00:00:00</t>
+        </is>
+      </c>
+      <c r="O84" t="inlineStr">
+        <is>
+          <t>REIFENHAUSER REICOFIL GMBH &amp; CO. KG</t>
+        </is>
+      </c>
+      <c r="P84" t="inlineStr">
+        <is>
+          <t>REIFENHAUSER REICOFIL GMBH &amp; CO. KG</t>
+        </is>
+      </c>
+      <c r="Q84" t="inlineStr">
+        <is>
+          <t>2026-05-28 00:00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>2566233</t>
+        </is>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>EF4-0232259-0</t>
+        </is>
+      </c>
+      <c r="C85" t="inlineStr">
+        <is>
+          <t>Vessel, Container</t>
+        </is>
+      </c>
+      <c r="D85" t="inlineStr"/>
+      <c r="E85" t="inlineStr">
+        <is>
+          <t>9903.03.01</t>
+        </is>
+      </c>
+      <c r="F85" t="inlineStr">
+        <is>
+          <t>SECTION 122 - 10% DUTY</t>
+        </is>
+      </c>
+      <c r="G85" t="inlineStr">
+        <is>
+          <t>007</t>
+        </is>
+      </c>
+      <c r="H85" t="inlineStr">
+        <is>
+          <t>9903.03.01</t>
+        </is>
+      </c>
+      <c r="I85" t="inlineStr">
+        <is>
+          <t>3402.90.5030</t>
+        </is>
+      </c>
+      <c r="J85" t="inlineStr">
+        <is>
+          <t>FI-TECH INC</t>
+        </is>
+      </c>
+      <c r="K85" t="inlineStr">
+        <is>
+          <t>FITINC</t>
+        </is>
+      </c>
+      <c r="L85" t="inlineStr">
+        <is>
+          <t>54-091465000</t>
+        </is>
+      </c>
+      <c r="M85" t="inlineStr">
+        <is>
+          <t>2026-06-12 00:00:00</t>
+        </is>
+      </c>
+      <c r="N85" t="inlineStr">
+        <is>
+          <t>2026-06-12 00:00:00</t>
+        </is>
+      </c>
+      <c r="O85" t="inlineStr">
+        <is>
+          <t>REIFENHAUSER REICOFIL GMBH &amp; CO. KG</t>
+        </is>
+      </c>
+      <c r="P85" t="inlineStr">
+        <is>
+          <t>REIFENHAUSER REICOFIL GMBH &amp; CO. KG</t>
+        </is>
+      </c>
+      <c r="Q85" t="inlineStr">
+        <is>
+          <t>2026-05-28 00:00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>2566233</t>
+        </is>
+      </c>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>EF4-0232259-0</t>
+        </is>
+      </c>
+      <c r="C86" t="inlineStr">
+        <is>
+          <t>Vessel, Container</t>
+        </is>
+      </c>
+      <c r="D86" t="inlineStr"/>
+      <c r="E86" t="inlineStr">
+        <is>
+          <t>9903.03.01</t>
+        </is>
+      </c>
+      <c r="F86" t="inlineStr">
+        <is>
+          <t>SECTION 122 - 10% DUTY</t>
+        </is>
+      </c>
+      <c r="G86" t="inlineStr">
+        <is>
+          <t>008</t>
+        </is>
+      </c>
+      <c r="H86" t="inlineStr">
+        <is>
+          <t>9903.03.01</t>
+        </is>
+      </c>
+      <c r="I86" t="inlineStr">
+        <is>
+          <t>8421.99.0180</t>
+        </is>
+      </c>
+      <c r="J86" t="inlineStr">
+        <is>
+          <t>FI-TECH INC</t>
+        </is>
+      </c>
+      <c r="K86" t="inlineStr">
+        <is>
+          <t>FITINC</t>
+        </is>
+      </c>
+      <c r="L86" t="inlineStr">
+        <is>
+          <t>54-091465000</t>
+        </is>
+      </c>
+      <c r="M86" t="inlineStr">
+        <is>
+          <t>2026-06-12 00:00:00</t>
+        </is>
+      </c>
+      <c r="N86" t="inlineStr">
+        <is>
+          <t>2026-06-12 00:00:00</t>
+        </is>
+      </c>
+      <c r="O86" t="inlineStr">
+        <is>
+          <t>REIFENHAUSER REICOFIL GMBH &amp; CO. KG</t>
+        </is>
+      </c>
+      <c r="P86" t="inlineStr">
+        <is>
+          <t>REIFENHAUSER REICOFIL GMBH &amp; CO. KG</t>
+        </is>
+      </c>
+      <c r="Q86" t="inlineStr">
+        <is>
+          <t>2026-05-28 00:00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>2566233</t>
+        </is>
+      </c>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>EF4-0232259-0</t>
+        </is>
+      </c>
+      <c r="C87" t="inlineStr">
+        <is>
+          <t>Vessel, Container</t>
+        </is>
+      </c>
+      <c r="D87" t="inlineStr"/>
+      <c r="E87" t="inlineStr">
+        <is>
+          <t>9903.03.01</t>
+        </is>
+      </c>
+      <c r="F87" t="inlineStr">
+        <is>
+          <t>SECTION 122 - 10% DUTY</t>
+        </is>
+      </c>
+      <c r="G87" t="inlineStr">
+        <is>
+          <t>009</t>
+        </is>
+      </c>
+      <c r="H87" t="inlineStr">
+        <is>
+          <t>9903.03.01</t>
+        </is>
+      </c>
+      <c r="I87" t="inlineStr">
+        <is>
+          <t>8421.99.0180</t>
+        </is>
+      </c>
+      <c r="J87" t="inlineStr">
+        <is>
+          <t>FI-TECH INC</t>
+        </is>
+      </c>
+      <c r="K87" t="inlineStr">
+        <is>
+          <t>FITINC</t>
+        </is>
+      </c>
+      <c r="L87" t="inlineStr">
+        <is>
+          <t>54-091465000</t>
+        </is>
+      </c>
+      <c r="M87" t="inlineStr">
+        <is>
+          <t>2026-06-12 00:00:00</t>
+        </is>
+      </c>
+      <c r="N87" t="inlineStr">
+        <is>
+          <t>2026-06-12 00:00:00</t>
+        </is>
+      </c>
+      <c r="O87" t="inlineStr">
+        <is>
+          <t>REIFENHAUSER REICOFIL GMBH &amp; CO. KG</t>
+        </is>
+      </c>
+      <c r="P87" t="inlineStr">
+        <is>
+          <t>REIFENHAUSER REICOFIL GMBH &amp; CO. KG</t>
+        </is>
+      </c>
+      <c r="Q87" t="inlineStr">
+        <is>
+          <t>2026-05-28 00:00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="inlineStr">
+        <is>
+          <t>2566233</t>
+        </is>
+      </c>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>EF4-0232259-0</t>
+        </is>
+      </c>
+      <c r="C88" t="inlineStr">
+        <is>
+          <t>Vessel, Container</t>
+        </is>
+      </c>
+      <c r="D88" t="inlineStr"/>
+      <c r="E88" t="inlineStr">
+        <is>
+          <t>9903.03.01</t>
+        </is>
+      </c>
+      <c r="F88" t="inlineStr">
+        <is>
+          <t>SECTION 122 - 10% DUTY</t>
+        </is>
+      </c>
+      <c r="G88" t="inlineStr">
+        <is>
+          <t>010</t>
+        </is>
+      </c>
+      <c r="H88" t="inlineStr">
+        <is>
+          <t>9903.03.01</t>
+        </is>
+      </c>
+      <c r="I88" t="inlineStr">
+        <is>
+          <t>5911.32.0080</t>
+        </is>
+      </c>
+      <c r="J88" t="inlineStr">
+        <is>
+          <t>FI-TECH INC</t>
+        </is>
+      </c>
+      <c r="K88" t="inlineStr">
+        <is>
+          <t>FITINC</t>
+        </is>
+      </c>
+      <c r="L88" t="inlineStr">
+        <is>
+          <t>54-091465000</t>
+        </is>
+      </c>
+      <c r="M88" t="inlineStr">
+        <is>
+          <t>2026-06-12 00:00:00</t>
+        </is>
+      </c>
+      <c r="N88" t="inlineStr">
+        <is>
+          <t>2026-06-12 00:00:00</t>
+        </is>
+      </c>
+      <c r="O88" t="inlineStr">
+        <is>
+          <t>REIFENHAUSER REICOFIL GMBH &amp; CO. KG</t>
+        </is>
+      </c>
+      <c r="P88" t="inlineStr">
+        <is>
+          <t>REIFENHAUSER REICOFIL GMBH &amp; CO. KG</t>
+        </is>
+      </c>
+      <c r="Q88" t="inlineStr">
+        <is>
+          <t>2026-05-28 00:00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="inlineStr">
+        <is>
+          <t>2566233</t>
+        </is>
+      </c>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>EF4-0232259-0</t>
+        </is>
+      </c>
+      <c r="C89" t="inlineStr">
+        <is>
+          <t>Vessel, Container</t>
+        </is>
+      </c>
+      <c r="D89" t="inlineStr"/>
+      <c r="E89" t="inlineStr">
+        <is>
+          <t>9903.03.01</t>
+        </is>
+      </c>
+      <c r="F89" t="inlineStr">
+        <is>
+          <t>SECTION 122 - 10% DUTY</t>
+        </is>
+      </c>
+      <c r="G89" t="inlineStr">
+        <is>
+          <t>011</t>
+        </is>
+      </c>
+      <c r="H89" t="inlineStr">
+        <is>
+          <t>9903.03.01</t>
+        </is>
+      </c>
+      <c r="I89" t="inlineStr">
+        <is>
+          <t>8477.90.8695</t>
+        </is>
+      </c>
+      <c r="J89" t="inlineStr">
+        <is>
+          <t>FI-TECH INC</t>
+        </is>
+      </c>
+      <c r="K89" t="inlineStr">
+        <is>
+          <t>FITINC</t>
+        </is>
+      </c>
+      <c r="L89" t="inlineStr">
+        <is>
+          <t>54-091465000</t>
+        </is>
+      </c>
+      <c r="M89" t="inlineStr">
+        <is>
+          <t>2026-06-12 00:00:00</t>
+        </is>
+      </c>
+      <c r="N89" t="inlineStr">
+        <is>
+          <t>2026-06-12 00:00:00</t>
+        </is>
+      </c>
+      <c r="O89" t="inlineStr">
+        <is>
+          <t>REIFENHAUSER REICOFIL GMBH &amp; CO. KG</t>
+        </is>
+      </c>
+      <c r="P89" t="inlineStr">
+        <is>
+          <t>REIFENHAUSER REICOFIL GMBH &amp; CO. KG</t>
+        </is>
+      </c>
+      <c r="Q89" t="inlineStr">
+        <is>
+          <t>2026-05-28 00:00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="inlineStr">
+        <is>
+          <t>2566233</t>
+        </is>
+      </c>
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>EF4-0232259-0</t>
+        </is>
+      </c>
+      <c r="C90" t="inlineStr">
+        <is>
+          <t>Vessel, Container</t>
+        </is>
+      </c>
+      <c r="D90" t="inlineStr"/>
+      <c r="E90" t="inlineStr">
+        <is>
+          <t>9903.03.01</t>
+        </is>
+      </c>
+      <c r="F90" t="inlineStr">
+        <is>
+          <t>SECTION 122 - 10% DUTY</t>
+        </is>
+      </c>
+      <c r="G90" t="inlineStr">
+        <is>
+          <t>012</t>
+        </is>
+      </c>
+      <c r="H90" t="inlineStr">
+        <is>
+          <t>9903.03.01</t>
+        </is>
+      </c>
+      <c r="I90" t="inlineStr">
+        <is>
+          <t>8448.32.0090</t>
+        </is>
+      </c>
+      <c r="J90" t="inlineStr">
+        <is>
+          <t>FI-TECH INC</t>
+        </is>
+      </c>
+      <c r="K90" t="inlineStr">
+        <is>
+          <t>FITINC</t>
+        </is>
+      </c>
+      <c r="L90" t="inlineStr">
+        <is>
+          <t>54-091465000</t>
+        </is>
+      </c>
+      <c r="M90" t="inlineStr">
+        <is>
+          <t>2026-06-12 00:00:00</t>
+        </is>
+      </c>
+      <c r="N90" t="inlineStr">
+        <is>
+          <t>2026-06-12 00:00:00</t>
+        </is>
+      </c>
+      <c r="O90" t="inlineStr">
+        <is>
+          <t>HASTEM GMBH</t>
+        </is>
+      </c>
+      <c r="P90" t="inlineStr">
+        <is>
+          <t>HASTEM GMBH</t>
+        </is>
+      </c>
+      <c r="Q90" t="inlineStr">
+        <is>
+          <t>2026-05-28 00:00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="inlineStr">
+        <is>
+          <t>2566233</t>
+        </is>
+      </c>
+      <c r="B91" t="inlineStr">
+        <is>
+          <t>EF4-0232259-0</t>
+        </is>
+      </c>
+      <c r="C91" t="inlineStr">
+        <is>
+          <t>Vessel, Container</t>
+        </is>
+      </c>
+      <c r="D91" t="inlineStr"/>
+      <c r="E91" t="inlineStr">
+        <is>
+          <t>9903.03.01</t>
+        </is>
+      </c>
+      <c r="F91" t="inlineStr">
+        <is>
+          <t>SECTION 122 - 10% DUTY</t>
+        </is>
+      </c>
+      <c r="G91" t="inlineStr">
+        <is>
+          <t>013</t>
+        </is>
+      </c>
+      <c r="H91" t="inlineStr">
+        <is>
+          <t>9903.03.01</t>
+        </is>
+      </c>
+      <c r="I91" t="inlineStr">
+        <is>
+          <t>8448.32.0090</t>
+        </is>
+      </c>
+      <c r="J91" t="inlineStr">
+        <is>
+          <t>FI-TECH INC</t>
+        </is>
+      </c>
+      <c r="K91" t="inlineStr">
+        <is>
+          <t>FITINC</t>
+        </is>
+      </c>
+      <c r="L91" t="inlineStr">
+        <is>
+          <t>54-091465000</t>
+        </is>
+      </c>
+      <c r="M91" t="inlineStr">
+        <is>
+          <t>2026-06-12 00:00:00</t>
+        </is>
+      </c>
+      <c r="N91" t="inlineStr">
+        <is>
+          <t>2026-06-12 00:00:00</t>
+        </is>
+      </c>
+      <c r="O91" t="inlineStr">
+        <is>
+          <t>HASTEM GMBH</t>
+        </is>
+      </c>
+      <c r="P91" t="inlineStr">
+        <is>
+          <t>HASTEM GMBH</t>
+        </is>
+      </c>
+      <c r="Q91" t="inlineStr">
+        <is>
+          <t>2026-05-28 00:00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="inlineStr">
+        <is>
+          <t>2566233</t>
+        </is>
+      </c>
+      <c r="B92" t="inlineStr">
+        <is>
+          <t>EF4-0232259-0</t>
+        </is>
+      </c>
+      <c r="C92" t="inlineStr">
+        <is>
+          <t>Vessel, Container</t>
+        </is>
+      </c>
+      <c r="D92" t="inlineStr"/>
+      <c r="E92" t="inlineStr">
+        <is>
+          <t>9903.03.01</t>
+        </is>
+      </c>
+      <c r="F92" t="inlineStr">
+        <is>
+          <t>SECTION 122 - 10% DUTY</t>
+        </is>
+      </c>
+      <c r="G92" t="inlineStr">
+        <is>
+          <t>014</t>
+        </is>
+      </c>
+      <c r="H92" t="inlineStr">
+        <is>
+          <t>9903.03.01</t>
+        </is>
+      </c>
+      <c r="I92" t="inlineStr">
+        <is>
+          <t>8453.90.5000</t>
+        </is>
+      </c>
+      <c r="J92" t="inlineStr">
+        <is>
+          <t>FI-TECH INC</t>
+        </is>
+      </c>
+      <c r="K92" t="inlineStr">
+        <is>
+          <t>FITINC</t>
+        </is>
+      </c>
+      <c r="L92" t="inlineStr">
+        <is>
+          <t>54-091465000</t>
+        </is>
+      </c>
+      <c r="M92" t="inlineStr">
+        <is>
+          <t>2026-06-12 00:00:00</t>
+        </is>
+      </c>
+      <c r="N92" t="inlineStr">
+        <is>
+          <t>2026-06-12 00:00:00</t>
+        </is>
+      </c>
+      <c r="O92" t="inlineStr">
+        <is>
+          <t>BRUCKNER AFTER SALES GMBH</t>
+        </is>
+      </c>
+      <c r="P92" t="inlineStr">
+        <is>
+          <t>BRUCKNER AFTER SALES GMBH</t>
+        </is>
+      </c>
+      <c r="Q92" t="inlineStr">
+        <is>
+          <t>2026-05-28 00:00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="inlineStr">
+        <is>
+          <t>2566233</t>
+        </is>
+      </c>
+      <c r="B93" t="inlineStr">
+        <is>
+          <t>EF4-0232259-0</t>
+        </is>
+      </c>
+      <c r="C93" t="inlineStr">
+        <is>
+          <t>Vessel, Container</t>
+        </is>
+      </c>
+      <c r="D93" t="inlineStr"/>
+      <c r="E93" t="inlineStr">
+        <is>
+          <t>9903.03.01</t>
+        </is>
+      </c>
+      <c r="F93" t="inlineStr">
+        <is>
+          <t>SECTION 122 - 10% DUTY</t>
+        </is>
+      </c>
+      <c r="G93" t="inlineStr">
+        <is>
+          <t>015</t>
+        </is>
+      </c>
+      <c r="H93" t="inlineStr">
+        <is>
+          <t>9903.03.01</t>
+        </is>
+      </c>
+      <c r="I93" t="inlineStr">
+        <is>
+          <t>8516.10.0080</t>
+        </is>
+      </c>
+      <c r="J93" t="inlineStr">
+        <is>
+          <t>FI-TECH INC</t>
+        </is>
+      </c>
+      <c r="K93" t="inlineStr">
+        <is>
+          <t>FITINC</t>
+        </is>
+      </c>
+      <c r="L93" t="inlineStr">
+        <is>
+          <t>54-091465000</t>
+        </is>
+      </c>
+      <c r="M93" t="inlineStr">
+        <is>
+          <t>2026-06-12 00:00:00</t>
+        </is>
+      </c>
+      <c r="N93" t="inlineStr">
+        <is>
+          <t>2026-06-12 00:00:00</t>
+        </is>
+      </c>
+      <c r="O93" t="inlineStr">
+        <is>
+          <t>BRUCKNER AFTER SALES GMBH</t>
+        </is>
+      </c>
+      <c r="P93" t="inlineStr">
+        <is>
+          <t>BRUCKNER AFTER SALES GMBH</t>
+        </is>
+      </c>
+      <c r="Q93" t="inlineStr">
+        <is>
+          <t>2026-05-28 00:00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="inlineStr">
+        <is>
+          <t>2566233</t>
+        </is>
+      </c>
+      <c r="B94" t="inlineStr">
+        <is>
+          <t>EF4-0232259-0</t>
+        </is>
+      </c>
+      <c r="C94" t="inlineStr">
+        <is>
+          <t>Vessel, Container</t>
+        </is>
+      </c>
+      <c r="D94" t="inlineStr"/>
+      <c r="E94" t="inlineStr">
+        <is>
+          <t>9903.03.01</t>
+        </is>
+      </c>
+      <c r="F94" t="inlineStr">
+        <is>
+          <t>SECTION 122 - 10% DUTY</t>
+        </is>
+      </c>
+      <c r="G94" t="inlineStr">
+        <is>
+          <t>016</t>
+        </is>
+      </c>
+      <c r="H94" t="inlineStr">
+        <is>
+          <t>9903.03.01</t>
+        </is>
+      </c>
+      <c r="I94" t="inlineStr">
+        <is>
+          <t>3403.99.0000</t>
+        </is>
+      </c>
+      <c r="J94" t="inlineStr">
+        <is>
+          <t>FI-TECH INC</t>
+        </is>
+      </c>
+      <c r="K94" t="inlineStr">
+        <is>
+          <t>FITINC</t>
+        </is>
+      </c>
+      <c r="L94" t="inlineStr">
+        <is>
+          <t>54-091465000</t>
+        </is>
+      </c>
+      <c r="M94" t="inlineStr">
+        <is>
+          <t>2026-06-12 00:00:00</t>
+        </is>
+      </c>
+      <c r="N94" t="inlineStr">
+        <is>
+          <t>2026-06-12 00:00:00</t>
+        </is>
+      </c>
+      <c r="O94" t="inlineStr">
+        <is>
+          <t>BRUCKNER AFTER SALES GMBH</t>
+        </is>
+      </c>
+      <c r="P94" t="inlineStr">
+        <is>
+          <t>BRUCKNER AFTER SALES GMBH</t>
+        </is>
+      </c>
+      <c r="Q94" t="inlineStr">
+        <is>
+          <t>2026-05-28 00:00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="inlineStr">
+        <is>
+          <t>2566233</t>
+        </is>
+      </c>
+      <c r="B95" t="inlineStr">
+        <is>
+          <t>EF4-0232259-0</t>
+        </is>
+      </c>
+      <c r="C95" t="inlineStr">
+        <is>
+          <t>Vessel, Container</t>
+        </is>
+      </c>
+      <c r="D95" t="inlineStr"/>
+      <c r="E95" t="inlineStr">
+        <is>
+          <t>9903.03.01</t>
+        </is>
+      </c>
+      <c r="F95" t="inlineStr">
+        <is>
+          <t>SECTION 122 - 10% DUTY</t>
+        </is>
+      </c>
+      <c r="G95" t="inlineStr">
+        <is>
+          <t>017</t>
+        </is>
+      </c>
+      <c r="H95" t="inlineStr">
+        <is>
+          <t>9903.03.01</t>
+        </is>
+      </c>
+      <c r="I95" t="inlineStr">
+        <is>
+          <t>8448.39.9000</t>
+        </is>
+      </c>
+      <c r="J95" t="inlineStr">
+        <is>
+          <t>FI-TECH INC</t>
+        </is>
+      </c>
+      <c r="K95" t="inlineStr">
+        <is>
+          <t>FITINC</t>
+        </is>
+      </c>
+      <c r="L95" t="inlineStr">
+        <is>
+          <t>54-091465000</t>
+        </is>
+      </c>
+      <c r="M95" t="inlineStr">
+        <is>
+          <t>2026-06-12 00:00:00</t>
+        </is>
+      </c>
+      <c r="N95" t="inlineStr">
+        <is>
+          <t>2026-06-12 00:00:00</t>
+        </is>
+      </c>
+      <c r="O95" t="inlineStr">
+        <is>
+          <t>ZENTES UNITEX GMBH</t>
+        </is>
+      </c>
+      <c r="P95" t="inlineStr">
+        <is>
+          <t>ZENTES UNITEX GMBH</t>
+        </is>
+      </c>
+      <c r="Q95" t="inlineStr">
+        <is>
+          <t>2026-05-28 00:00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="inlineStr">
+        <is>
+          <t>2566233</t>
+        </is>
+      </c>
+      <c r="B96" t="inlineStr">
+        <is>
+          <t>EF4-0232259-0</t>
+        </is>
+      </c>
+      <c r="C96" t="inlineStr">
+        <is>
+          <t>Vessel, Container</t>
+        </is>
+      </c>
+      <c r="D96" t="inlineStr"/>
+      <c r="E96" t="inlineStr">
+        <is>
+          <t>9903.03.01</t>
+        </is>
+      </c>
+      <c r="F96" t="inlineStr">
+        <is>
+          <t>SECTION 122 - 10% DUTY</t>
+        </is>
+      </c>
+      <c r="G96" t="inlineStr">
+        <is>
+          <t>018</t>
+        </is>
+      </c>
+      <c r="H96" t="inlineStr">
+        <is>
+          <t>9903.03.01</t>
+        </is>
+      </c>
+      <c r="I96" t="inlineStr">
+        <is>
+          <t>4811.49.3000</t>
+        </is>
+      </c>
+      <c r="J96" t="inlineStr">
+        <is>
+          <t>FI-TECH INC</t>
+        </is>
+      </c>
+      <c r="K96" t="inlineStr">
+        <is>
+          <t>FITINC</t>
+        </is>
+      </c>
+      <c r="L96" t="inlineStr">
+        <is>
+          <t>54-091465000</t>
+        </is>
+      </c>
+      <c r="M96" t="inlineStr">
+        <is>
+          <t>2026-06-12 00:00:00</t>
+        </is>
+      </c>
+      <c r="N96" t="inlineStr">
+        <is>
+          <t>2026-06-12 00:00:00</t>
+        </is>
+      </c>
+      <c r="O96" t="inlineStr">
+        <is>
+          <t>ZENTES UNITEX GMBH</t>
+        </is>
+      </c>
+      <c r="P96" t="inlineStr">
+        <is>
+          <t>ZENTES UNITEX GMBH</t>
+        </is>
+      </c>
+      <c r="Q96" t="inlineStr">
+        <is>
+          <t>2026-05-28 00:00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="inlineStr">
+        <is>
+          <t>2566233</t>
+        </is>
+      </c>
+      <c r="B97" t="inlineStr">
+        <is>
+          <t>EF4-0232259-0</t>
+        </is>
+      </c>
+      <c r="C97" t="inlineStr">
+        <is>
+          <t>Vessel, Container</t>
+        </is>
+      </c>
+      <c r="D97" t="inlineStr"/>
+      <c r="E97" t="inlineStr">
+        <is>
+          <t>9903.03.01</t>
+        </is>
+      </c>
+      <c r="F97" t="inlineStr">
+        <is>
+          <t>SECTION 122 - 10% DUTY</t>
+        </is>
+      </c>
+      <c r="G97" t="inlineStr">
+        <is>
+          <t>019</t>
+        </is>
+      </c>
+      <c r="H97" t="inlineStr">
+        <is>
+          <t>9903.03.01</t>
+        </is>
+      </c>
+      <c r="I97" t="inlineStr">
+        <is>
+          <t>4811.49.3000</t>
+        </is>
+      </c>
+      <c r="J97" t="inlineStr">
+        <is>
+          <t>FI-TECH INC</t>
+        </is>
+      </c>
+      <c r="K97" t="inlineStr">
+        <is>
+          <t>FITINC</t>
+        </is>
+      </c>
+      <c r="L97" t="inlineStr">
+        <is>
+          <t>54-091465000</t>
+        </is>
+      </c>
+      <c r="M97" t="inlineStr">
+        <is>
+          <t>2026-06-12 00:00:00</t>
+        </is>
+      </c>
+      <c r="N97" t="inlineStr">
+        <is>
+          <t>2026-06-12 00:00:00</t>
+        </is>
+      </c>
+      <c r="O97" t="inlineStr">
+        <is>
+          <t>ZENTES UNITEX GMBH</t>
+        </is>
+      </c>
+      <c r="P97" t="inlineStr">
+        <is>
+          <t>ZENTES UNITEX GMBH</t>
+        </is>
+      </c>
+      <c r="Q97" t="inlineStr">
+        <is>
+          <t>2026-05-28 00:00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="inlineStr">
+        <is>
+          <t>2565794</t>
+        </is>
+      </c>
+      <c r="B98" t="inlineStr">
+        <is>
+          <t>EF4-0232384-6</t>
+        </is>
+      </c>
+      <c r="C98" t="inlineStr">
+        <is>
+          <t>Vessel, Container</t>
+        </is>
+      </c>
+      <c r="D98" t="inlineStr">
+        <is>
+          <t>V0413916151</t>
+        </is>
+      </c>
+      <c r="E98" t="inlineStr">
+        <is>
+          <t>9903.03.06</t>
+        </is>
+      </c>
+      <c r="F98" t="inlineStr">
+        <is>
+          <t>S122 EXCL,IRN/STL/ALUM,DERIV</t>
+        </is>
+      </c>
+      <c r="G98" t="inlineStr">
+        <is>
+          <t>001</t>
+        </is>
+      </c>
+      <c r="H98" t="inlineStr">
+        <is>
+          <t>9903.03.06</t>
+        </is>
+      </c>
+      <c r="I98" t="inlineStr">
+        <is>
+          <t>9903.82.02,7223.00.1031</t>
+        </is>
+      </c>
+      <c r="J98" t="inlineStr">
+        <is>
+          <t>VENUS WIRE INDUSTRIES PRIVATE LTD</t>
+        </is>
+      </c>
+      <c r="K98" t="inlineStr">
+        <is>
+          <t>VENWIR</t>
+        </is>
+      </c>
+      <c r="L98" t="inlineStr">
+        <is>
+          <t>993901-03595</t>
+        </is>
+      </c>
+      <c r="M98" t="inlineStr">
+        <is>
+          <t>2026-06-12 00:00:00</t>
+        </is>
+      </c>
+      <c r="N98" t="inlineStr">
+        <is>
+          <t>2026-06-12 00:00:00</t>
+        </is>
+      </c>
+      <c r="O98" t="inlineStr">
+        <is>
+          <t>VENUS WIRE INDUSTRIES PRIVATE LIMIT</t>
+        </is>
+      </c>
+      <c r="P98" t="inlineStr">
+        <is>
+          <t>VENUS WIRE INDUSTRIES PRIVATE LIMITED</t>
+        </is>
+      </c>
+      <c r="Q98" t="inlineStr">
+        <is>
+          <t>2026-05-05 00:00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="inlineStr">
+        <is>
+          <t>2566107</t>
+        </is>
+      </c>
+      <c r="B99" t="inlineStr">
+        <is>
+          <t>EF4-0232386-1</t>
+        </is>
+      </c>
+      <c r="C99" t="inlineStr">
+        <is>
+          <t>Vessel, Container</t>
+        </is>
+      </c>
+      <c r="D99" t="inlineStr">
+        <is>
+          <t>V0413916151</t>
+        </is>
+      </c>
+      <c r="E99" t="inlineStr">
+        <is>
+          <t>9903.03.01</t>
+        </is>
+      </c>
+      <c r="F99" t="inlineStr">
+        <is>
+          <t>SECTION 122 - 10% DUTY</t>
+        </is>
+      </c>
+      <c r="G99" t="inlineStr">
+        <is>
+          <t>001</t>
+        </is>
+      </c>
+      <c r="H99" t="inlineStr">
+        <is>
+          <t>9903.03.01</t>
+        </is>
+      </c>
+      <c r="I99" t="inlineStr">
+        <is>
+          <t>5503.40.0000</t>
+        </is>
+      </c>
+      <c r="J99" t="inlineStr">
+        <is>
+          <t>FOOTING FIRST, LLC</t>
+        </is>
+      </c>
+      <c r="K99" t="inlineStr">
+        <is>
+          <t>FOOFIR</t>
+        </is>
+      </c>
+      <c r="L99" t="inlineStr">
+        <is>
+          <t>27-059921300</t>
+        </is>
+      </c>
+      <c r="M99" t="inlineStr">
+        <is>
+          <t>2026-06-12 00:00:00</t>
+        </is>
+      </c>
+      <c r="N99" t="inlineStr">
+        <is>
+          <t>2026-06-12 00:00:00</t>
+        </is>
+      </c>
+      <c r="O99" t="inlineStr">
+        <is>
+          <t>HAGELSON PLASTIK GERI DONUSUM VE NA</t>
+        </is>
+      </c>
+      <c r="P99" t="inlineStr">
+        <is>
+          <t>HAGELSON PLASTIK GERI DONUSUM VE NAKLIYE SANAYI TICARET ANONIM SIRKETI</t>
+        </is>
+      </c>
+      <c r="Q99" t="inlineStr">
+        <is>
+          <t>2026-05-25 00:00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="inlineStr">
+        <is>
+          <t>4539413</t>
+        </is>
+      </c>
+      <c r="B100" t="inlineStr">
+        <is>
+          <t>EF4-0232400-0</t>
+        </is>
+      </c>
+      <c r="C100" t="inlineStr">
+        <is>
+          <t>Air, Non-container</t>
+        </is>
+      </c>
+      <c r="D100" t="inlineStr"/>
+      <c r="E100" t="inlineStr">
+        <is>
+          <t>9903.03.01</t>
+        </is>
+      </c>
+      <c r="F100" t="inlineStr">
+        <is>
+          <t>SECTION 122 - 10% DUTY</t>
+        </is>
+      </c>
+      <c r="G100" t="inlineStr">
+        <is>
+          <t>001</t>
+        </is>
+      </c>
+      <c r="H100" t="inlineStr">
+        <is>
+          <t>9903.03.01</t>
+        </is>
+      </c>
+      <c r="I100" t="inlineStr">
+        <is>
+          <t>3405.20.0000</t>
+        </is>
+      </c>
+      <c r="J100" t="inlineStr">
+        <is>
+          <t>COVE HOME LLC</t>
+        </is>
+      </c>
+      <c r="K100" t="inlineStr">
+        <is>
+          <t>COVHOM01</t>
+        </is>
+      </c>
+      <c r="L100" t="inlineStr">
+        <is>
+          <t>30-136116600</t>
+        </is>
+      </c>
+      <c r="M100" t="inlineStr">
+        <is>
+          <t>2026-06-12 00:00:00</t>
+        </is>
+      </c>
+      <c r="N100" t="inlineStr">
+        <is>
+          <t>2026-06-12 00:00:00</t>
+        </is>
+      </c>
+      <c r="O100" t="inlineStr">
+        <is>
+          <t>CV. PRASDA BALI UTMA</t>
+        </is>
+      </c>
+      <c r="P100" t="inlineStr">
+        <is>
+          <t>CV. PRASDA BALI UTMA</t>
+        </is>
+      </c>
+      <c r="Q100" t="inlineStr">
+        <is>
+          <t>2026-06-12 00:00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="inlineStr">
+        <is>
+          <t>4539413</t>
+        </is>
+      </c>
+      <c r="B101" t="inlineStr">
+        <is>
+          <t>EF4-0232400-0</t>
+        </is>
+      </c>
+      <c r="C101" t="inlineStr">
+        <is>
+          <t>Air, Non-container</t>
+        </is>
+      </c>
+      <c r="D101" t="inlineStr"/>
+      <c r="E101" t="inlineStr">
+        <is>
+          <t>9903.03.01</t>
+        </is>
+      </c>
+      <c r="F101" t="inlineStr">
+        <is>
+          <t>SECTION 122 - 10% DUTY</t>
+        </is>
+      </c>
+      <c r="G101" t="inlineStr">
+        <is>
+          <t>002</t>
+        </is>
+      </c>
+      <c r="H101" t="inlineStr">
+        <is>
+          <t>9903.03.01</t>
+        </is>
+      </c>
+      <c r="I101" t="inlineStr">
+        <is>
+          <t>4419.20.9000</t>
+        </is>
+      </c>
+      <c r="J101" t="inlineStr">
+        <is>
+          <t>COVE HOME LLC</t>
+        </is>
+      </c>
+      <c r="K101" t="inlineStr">
+        <is>
+          <t>COVHOM01</t>
+        </is>
+      </c>
+      <c r="L101" t="inlineStr">
+        <is>
+          <t>30-136116600</t>
+        </is>
+      </c>
+      <c r="M101" t="inlineStr">
+        <is>
+          <t>2026-06-12 00:00:00</t>
+        </is>
+      </c>
+      <c r="N101" t="inlineStr">
+        <is>
+          <t>2026-06-12 00:00:00</t>
+        </is>
+      </c>
+      <c r="O101" t="inlineStr">
+        <is>
+          <t>CV. PRASDA BALI UTMA</t>
+        </is>
+      </c>
+      <c r="P101" t="inlineStr">
+        <is>
+          <t>CV. PRASDA BALI UTMA</t>
+        </is>
+      </c>
+      <c r="Q101" t="inlineStr">
+        <is>
+          <t>2026-06-12 00:00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="inlineStr">
+        <is>
+          <t>4539413</t>
+        </is>
+      </c>
+      <c r="B102" t="inlineStr">
+        <is>
+          <t>EF4-0232400-0</t>
+        </is>
+      </c>
+      <c r="C102" t="inlineStr">
+        <is>
+          <t>Air, Non-container</t>
+        </is>
+      </c>
+      <c r="D102" t="inlineStr"/>
+      <c r="E102" t="inlineStr">
+        <is>
+          <t>9903.03.01</t>
+        </is>
+      </c>
+      <c r="F102" t="inlineStr">
+        <is>
+          <t>SECTION 122 - 10% DUTY</t>
+        </is>
+      </c>
+      <c r="G102" t="inlineStr">
+        <is>
+          <t>003</t>
+        </is>
+      </c>
+      <c r="H102" t="inlineStr">
+        <is>
+          <t>9903.03.01</t>
+        </is>
+      </c>
+      <c r="I102" t="inlineStr">
+        <is>
+          <t>4202.22.1500</t>
+        </is>
+      </c>
+      <c r="J102" t="inlineStr">
+        <is>
+          <t>COVE HOME LLC</t>
+        </is>
+      </c>
+      <c r="K102" t="inlineStr">
+        <is>
+          <t>COVHOM01</t>
+        </is>
+      </c>
+      <c r="L102" t="inlineStr">
+        <is>
+          <t>30-136116600</t>
+        </is>
+      </c>
+      <c r="M102" t="inlineStr">
+        <is>
+          <t>2026-06-12 00:00:00</t>
+        </is>
+      </c>
+      <c r="N102" t="inlineStr">
+        <is>
+          <t>2026-06-12 00:00:00</t>
+        </is>
+      </c>
+      <c r="O102" t="inlineStr">
+        <is>
+          <t>CV. PRASDA BALI UTMA</t>
+        </is>
+      </c>
+      <c r="P102" t="inlineStr">
+        <is>
+          <t>CV. PRASDA BALI UTMA</t>
+        </is>
+      </c>
+      <c r="Q102" t="inlineStr">
+        <is>
+          <t>2026-06-12 00:00:00</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/trimika_data.xlsx
+++ b/trimika_data.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q102"/>
+  <dimension ref="A1:Q122"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -8942,6 +8942,1638 @@
         </is>
       </c>
     </row>
+    <row r="103">
+      <c r="A103" t="inlineStr">
+        <is>
+          <t>2565751</t>
+        </is>
+      </c>
+      <c r="B103" t="inlineStr">
+        <is>
+          <t>EF4-0231790-5</t>
+        </is>
+      </c>
+      <c r="C103" t="inlineStr">
+        <is>
+          <t>Vessel, Non-container</t>
+        </is>
+      </c>
+      <c r="D103" t="inlineStr"/>
+      <c r="E103" t="inlineStr">
+        <is>
+          <t>9903.03.06</t>
+        </is>
+      </c>
+      <c r="F103" t="inlineStr">
+        <is>
+          <t>S122 EXCL,IRN/STL/ALUM,DERIV</t>
+        </is>
+      </c>
+      <c r="G103" t="inlineStr">
+        <is>
+          <t>001</t>
+        </is>
+      </c>
+      <c r="H103" t="inlineStr">
+        <is>
+          <t>9903.03.06</t>
+        </is>
+      </c>
+      <c r="I103" t="inlineStr">
+        <is>
+          <t>9903.82.10,8428.33.0000</t>
+        </is>
+      </c>
+      <c r="J103" t="inlineStr">
+        <is>
+          <t>AUMUND CORPORATION</t>
+        </is>
+      </c>
+      <c r="K103" t="inlineStr">
+        <is>
+          <t>AUMCOR</t>
+        </is>
+      </c>
+      <c r="L103" t="inlineStr">
+        <is>
+          <t>58-138896800</t>
+        </is>
+      </c>
+      <c r="M103" t="inlineStr">
+        <is>
+          <t>2026-06-13 00:00:00</t>
+        </is>
+      </c>
+      <c r="N103" t="inlineStr">
+        <is>
+          <t>2026-06-13 00:00:00</t>
+        </is>
+      </c>
+      <c r="O103" t="inlineStr">
+        <is>
+          <t>AUMUND FOERDERTECHNIK GMBH</t>
+        </is>
+      </c>
+      <c r="P103" t="inlineStr">
+        <is>
+          <t>AUMUND FOERDERTECHNIK GMBH</t>
+        </is>
+      </c>
+      <c r="Q103" t="inlineStr">
+        <is>
+          <t>2026-05-11 00:00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="inlineStr">
+        <is>
+          <t>2565927</t>
+        </is>
+      </c>
+      <c r="B104" t="inlineStr">
+        <is>
+          <t>EF4-0231897-8</t>
+        </is>
+      </c>
+      <c r="C104" t="inlineStr">
+        <is>
+          <t>Vessel, Container</t>
+        </is>
+      </c>
+      <c r="D104" t="inlineStr"/>
+      <c r="E104" t="inlineStr">
+        <is>
+          <t>9903.03.01</t>
+        </is>
+      </c>
+      <c r="F104" t="inlineStr">
+        <is>
+          <t>SECTION 122 - 10% DUTY</t>
+        </is>
+      </c>
+      <c r="G104" t="inlineStr">
+        <is>
+          <t>001</t>
+        </is>
+      </c>
+      <c r="H104" t="inlineStr">
+        <is>
+          <t>9903.03.01</t>
+        </is>
+      </c>
+      <c r="I104" t="inlineStr">
+        <is>
+          <t>3920.62.0090</t>
+        </is>
+      </c>
+      <c r="J104" t="inlineStr">
+        <is>
+          <t>GULF ATLANTIC PACKAGING CORP</t>
+        </is>
+      </c>
+      <c r="K104" t="inlineStr">
+        <is>
+          <t>GULATL</t>
+        </is>
+      </c>
+      <c r="L104" t="inlineStr">
+        <is>
+          <t>58-184378700</t>
+        </is>
+      </c>
+      <c r="M104" t="inlineStr">
+        <is>
+          <t>2026-06-14 00:00:00</t>
+        </is>
+      </c>
+      <c r="N104" t="inlineStr">
+        <is>
+          <t>2026-06-13 00:00:00</t>
+        </is>
+      </c>
+      <c r="O104" t="inlineStr">
+        <is>
+          <t>CONSENT FZCO</t>
+        </is>
+      </c>
+      <c r="P104" t="inlineStr">
+        <is>
+          <t>CONSENT FZCO</t>
+        </is>
+      </c>
+      <c r="Q104" t="inlineStr">
+        <is>
+          <t>2026-05-16 00:00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="inlineStr">
+        <is>
+          <t>2566010</t>
+        </is>
+      </c>
+      <c r="B105" t="inlineStr">
+        <is>
+          <t>EF4-0231962-0</t>
+        </is>
+      </c>
+      <c r="C105" t="inlineStr">
+        <is>
+          <t>Vessel, Container</t>
+        </is>
+      </c>
+      <c r="D105" t="inlineStr"/>
+      <c r="E105" t="inlineStr">
+        <is>
+          <t>9903.03.01</t>
+        </is>
+      </c>
+      <c r="F105" t="inlineStr"/>
+      <c r="G105" t="inlineStr">
+        <is>
+          <t>001</t>
+        </is>
+      </c>
+      <c r="H105" t="inlineStr">
+        <is>
+          <t>9903.03.01</t>
+        </is>
+      </c>
+      <c r="I105" t="inlineStr">
+        <is>
+          <t>1108.13.0010</t>
+        </is>
+      </c>
+      <c r="J105" t="inlineStr">
+        <is>
+          <t>ROYAL INGREDIENTS GROUP BV</t>
+        </is>
+      </c>
+      <c r="K105" t="inlineStr">
+        <is>
+          <t>ROYINGRE</t>
+        </is>
+      </c>
+      <c r="L105" t="inlineStr">
+        <is>
+          <t>074601-00962</t>
+        </is>
+      </c>
+      <c r="M105" t="inlineStr">
+        <is>
+          <t>2026-06-14 00:00:00</t>
+        </is>
+      </c>
+      <c r="N105" t="inlineStr">
+        <is>
+          <t>2026-06-13 00:00:00</t>
+        </is>
+      </c>
+      <c r="O105" t="inlineStr">
+        <is>
+          <t>PRZEDSIEBIORSTWO PRZEMYSLU ZIEMNIAC</t>
+        </is>
+      </c>
+      <c r="P105" t="inlineStr">
+        <is>
+          <t>PRZEDSIEBIORSTWO PRZEMYSLU ZIEMNIACZANEGO PEPEES S.A.</t>
+        </is>
+      </c>
+      <c r="Q105" t="inlineStr">
+        <is>
+          <t>2026-05-17 00:00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="inlineStr">
+        <is>
+          <t>2565855</t>
+        </is>
+      </c>
+      <c r="B106" t="inlineStr">
+        <is>
+          <t>EF4-0232059-4</t>
+        </is>
+      </c>
+      <c r="C106" t="inlineStr">
+        <is>
+          <t>Vessel, Container</t>
+        </is>
+      </c>
+      <c r="D106" t="inlineStr">
+        <is>
+          <t>V1626451887</t>
+        </is>
+      </c>
+      <c r="E106" t="inlineStr">
+        <is>
+          <t>9903.03.01</t>
+        </is>
+      </c>
+      <c r="F106" t="inlineStr">
+        <is>
+          <t>SECTION 122 - 10% DUTY</t>
+        </is>
+      </c>
+      <c r="G106" t="inlineStr">
+        <is>
+          <t>001</t>
+        </is>
+      </c>
+      <c r="H106" t="inlineStr">
+        <is>
+          <t>9903.03.01</t>
+        </is>
+      </c>
+      <c r="I106" t="inlineStr">
+        <is>
+          <t>1108.13.0010</t>
+        </is>
+      </c>
+      <c r="J106" t="inlineStr">
+        <is>
+          <t>ROYAL INGREDIENTS GROUP BV</t>
+        </is>
+      </c>
+      <c r="K106" t="inlineStr">
+        <is>
+          <t>ROYINGRE</t>
+        </is>
+      </c>
+      <c r="L106" t="inlineStr">
+        <is>
+          <t>074601-00962</t>
+        </is>
+      </c>
+      <c r="M106" t="inlineStr">
+        <is>
+          <t>2026-06-02 00:00:00</t>
+        </is>
+      </c>
+      <c r="N106" t="inlineStr">
+        <is>
+          <t>2026-06-13 00:00:00</t>
+        </is>
+      </c>
+      <c r="O106" t="inlineStr">
+        <is>
+          <t>AKV LANGHOLT AMBA</t>
+        </is>
+      </c>
+      <c r="P106" t="inlineStr">
+        <is>
+          <t>AKV LANGHOLT AMBA</t>
+        </is>
+      </c>
+      <c r="Q106" t="inlineStr">
+        <is>
+          <t>2026-05-08 00:00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="inlineStr">
+        <is>
+          <t>2566011</t>
+        </is>
+      </c>
+      <c r="B107" t="inlineStr">
+        <is>
+          <t>EF4-0232062-8</t>
+        </is>
+      </c>
+      <c r="C107" t="inlineStr">
+        <is>
+          <t>Vessel, Container</t>
+        </is>
+      </c>
+      <c r="D107" t="inlineStr">
+        <is>
+          <t>V1626451887</t>
+        </is>
+      </c>
+      <c r="E107" t="inlineStr">
+        <is>
+          <t>9903.03.01</t>
+        </is>
+      </c>
+      <c r="F107" t="inlineStr"/>
+      <c r="G107" t="inlineStr">
+        <is>
+          <t>001</t>
+        </is>
+      </c>
+      <c r="H107" t="inlineStr">
+        <is>
+          <t>9903.03.01</t>
+        </is>
+      </c>
+      <c r="I107" t="inlineStr">
+        <is>
+          <t>1108.13.0010</t>
+        </is>
+      </c>
+      <c r="J107" t="inlineStr">
+        <is>
+          <t>ROYAL INGREDIENTS GROUP BV</t>
+        </is>
+      </c>
+      <c r="K107" t="inlineStr">
+        <is>
+          <t>ROYINGRE</t>
+        </is>
+      </c>
+      <c r="L107" t="inlineStr">
+        <is>
+          <t>074601-00962</t>
+        </is>
+      </c>
+      <c r="M107" t="inlineStr">
+        <is>
+          <t>2026-06-14 00:00:00</t>
+        </is>
+      </c>
+      <c r="N107" t="inlineStr">
+        <is>
+          <t>2026-06-13 00:00:00</t>
+        </is>
+      </c>
+      <c r="O107" t="inlineStr">
+        <is>
+          <t>PRZEDSIEBIORSTWO PRZEMYSLU ZIEMNIAC</t>
+        </is>
+      </c>
+      <c r="P107" t="inlineStr">
+        <is>
+          <t>PRZEDSIEBIORSTWO PRZEMYSLU ZIEMNIACZANEGO PEPEES S.A.</t>
+        </is>
+      </c>
+      <c r="Q107" t="inlineStr">
+        <is>
+          <t>2026-05-20 00:00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" t="inlineStr">
+        <is>
+          <t>2566028</t>
+        </is>
+      </c>
+      <c r="B108" t="inlineStr">
+        <is>
+          <t>EF4-0232065-1</t>
+        </is>
+      </c>
+      <c r="C108" t="inlineStr">
+        <is>
+          <t>Vessel, Container</t>
+        </is>
+      </c>
+      <c r="D108" t="inlineStr">
+        <is>
+          <t>V0710334942</t>
+        </is>
+      </c>
+      <c r="E108" t="inlineStr">
+        <is>
+          <t>9903.03.01</t>
+        </is>
+      </c>
+      <c r="F108" t="inlineStr"/>
+      <c r="G108" t="inlineStr">
+        <is>
+          <t>001</t>
+        </is>
+      </c>
+      <c r="H108" t="inlineStr">
+        <is>
+          <t>9903.03.01</t>
+        </is>
+      </c>
+      <c r="I108" t="inlineStr">
+        <is>
+          <t>1108.12.0010</t>
+        </is>
+      </c>
+      <c r="J108" t="inlineStr">
+        <is>
+          <t>ROYAL INGREDIENTS GROUP BV</t>
+        </is>
+      </c>
+      <c r="K108" t="inlineStr">
+        <is>
+          <t>ROYINGRE</t>
+        </is>
+      </c>
+      <c r="L108" t="inlineStr">
+        <is>
+          <t>074601-00962</t>
+        </is>
+      </c>
+      <c r="M108" t="inlineStr">
+        <is>
+          <t>2026-06-14 00:00:00</t>
+        </is>
+      </c>
+      <c r="N108" t="inlineStr">
+        <is>
+          <t>2026-06-13 00:00:00</t>
+        </is>
+      </c>
+      <c r="O108" t="inlineStr">
+        <is>
+          <t>TAT NISASTA INS SAN TIC AS</t>
+        </is>
+      </c>
+      <c r="P108" t="inlineStr">
+        <is>
+          <t>TAT NISASTA INS SAN TIC AS</t>
+        </is>
+      </c>
+      <c r="Q108" t="inlineStr">
+        <is>
+          <t>2026-05-23 00:00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" t="inlineStr">
+        <is>
+          <t>105504734</t>
+        </is>
+      </c>
+      <c r="B109" t="inlineStr">
+        <is>
+          <t>EF4-0232081-8</t>
+        </is>
+      </c>
+      <c r="C109" t="inlineStr">
+        <is>
+          <t>Vessel, Non-container</t>
+        </is>
+      </c>
+      <c r="D109" t="inlineStr"/>
+      <c r="E109" t="inlineStr">
+        <is>
+          <t>9805.00.50</t>
+        </is>
+      </c>
+      <c r="F109" t="inlineStr">
+        <is>
+          <t>EFFECTS US GOV EMP&amp;FAMLY/EVACU</t>
+        </is>
+      </c>
+      <c r="G109" t="inlineStr">
+        <is>
+          <t>001</t>
+        </is>
+      </c>
+      <c r="H109" t="inlineStr">
+        <is>
+          <t>9805.00.50</t>
+        </is>
+      </c>
+      <c r="I109" t="inlineStr"/>
+      <c r="J109" t="inlineStr">
+        <is>
+          <t>IFF, INC.</t>
+        </is>
+      </c>
+      <c r="K109" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="L109" t="inlineStr">
+        <is>
+          <t>58-149385700</t>
+        </is>
+      </c>
+      <c r="M109" t="inlineStr">
+        <is>
+          <t>2026-06-13 00:00:00</t>
+        </is>
+      </c>
+      <c r="N109" t="inlineStr">
+        <is>
+          <t>2026-06-13 00:00:00</t>
+        </is>
+      </c>
+      <c r="O109" t="inlineStr">
+        <is>
+          <t>VOLVO CAR INTERNATIONAL CORPORATION</t>
+        </is>
+      </c>
+      <c r="P109" t="inlineStr">
+        <is>
+          <t>VOLVO CAR INTERNATIONAL CORPORATION</t>
+        </is>
+      </c>
+      <c r="Q109" t="inlineStr">
+        <is>
+          <t>2026-05-26 00:00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" t="inlineStr">
+        <is>
+          <t>105504735</t>
+        </is>
+      </c>
+      <c r="B110" t="inlineStr">
+        <is>
+          <t>EF4-0232084-2</t>
+        </is>
+      </c>
+      <c r="C110" t="inlineStr">
+        <is>
+          <t>Vessel, Non-container</t>
+        </is>
+      </c>
+      <c r="D110" t="inlineStr"/>
+      <c r="E110" t="inlineStr">
+        <is>
+          <t>9805.00.50</t>
+        </is>
+      </c>
+      <c r="F110" t="inlineStr">
+        <is>
+          <t>EFFECTS US GOV EMP&amp;FAMLY/EVACU</t>
+        </is>
+      </c>
+      <c r="G110" t="inlineStr">
+        <is>
+          <t>001</t>
+        </is>
+      </c>
+      <c r="H110" t="inlineStr">
+        <is>
+          <t>9805.00.50</t>
+        </is>
+      </c>
+      <c r="I110" t="inlineStr"/>
+      <c r="J110" t="inlineStr">
+        <is>
+          <t>IFF, INC.</t>
+        </is>
+      </c>
+      <c r="K110" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="L110" t="inlineStr">
+        <is>
+          <t>58-149385700</t>
+        </is>
+      </c>
+      <c r="M110" t="inlineStr">
+        <is>
+          <t>2026-06-13 00:00:00</t>
+        </is>
+      </c>
+      <c r="N110" t="inlineStr">
+        <is>
+          <t>2026-06-13 00:00:00</t>
+        </is>
+      </c>
+      <c r="O110" t="inlineStr">
+        <is>
+          <t>VOLVO CAR INTERNATIONAL CORPORATION</t>
+        </is>
+      </c>
+      <c r="P110" t="inlineStr">
+        <is>
+          <t>VOLVO CAR INTERNATIONAL CORPORATION</t>
+        </is>
+      </c>
+      <c r="Q110" t="inlineStr">
+        <is>
+          <t>2026-05-26 00:00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" t="inlineStr">
+        <is>
+          <t>105504736</t>
+        </is>
+      </c>
+      <c r="B111" t="inlineStr">
+        <is>
+          <t>EF4-0232087-5</t>
+        </is>
+      </c>
+      <c r="C111" t="inlineStr">
+        <is>
+          <t>Vessel, Non-container</t>
+        </is>
+      </c>
+      <c r="D111" t="inlineStr"/>
+      <c r="E111" t="inlineStr">
+        <is>
+          <t>9805.00.50</t>
+        </is>
+      </c>
+      <c r="F111" t="inlineStr">
+        <is>
+          <t>EFFECTS US GOV EMP&amp;FAMLY/EVACU</t>
+        </is>
+      </c>
+      <c r="G111" t="inlineStr">
+        <is>
+          <t>001</t>
+        </is>
+      </c>
+      <c r="H111" t="inlineStr">
+        <is>
+          <t>9805.00.50</t>
+        </is>
+      </c>
+      <c r="I111" t="inlineStr"/>
+      <c r="J111" t="inlineStr">
+        <is>
+          <t>IFF, INC.</t>
+        </is>
+      </c>
+      <c r="K111" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="L111" t="inlineStr">
+        <is>
+          <t>58-149385700</t>
+        </is>
+      </c>
+      <c r="M111" t="inlineStr">
+        <is>
+          <t>2026-06-13 00:00:00</t>
+        </is>
+      </c>
+      <c r="N111" t="inlineStr">
+        <is>
+          <t>2026-06-13 00:00:00</t>
+        </is>
+      </c>
+      <c r="O111" t="inlineStr">
+        <is>
+          <t>VOLVO CAR INTERNATIONAL CORPORATION</t>
+        </is>
+      </c>
+      <c r="P111" t="inlineStr">
+        <is>
+          <t>VOLVO CAR INTERNATIONAL CORPORATION</t>
+        </is>
+      </c>
+      <c r="Q111" t="inlineStr">
+        <is>
+          <t>2026-05-26 00:00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" t="inlineStr">
+        <is>
+          <t>2565712</t>
+        </is>
+      </c>
+      <c r="B112" t="inlineStr">
+        <is>
+          <t>EF4-0232088-3</t>
+        </is>
+      </c>
+      <c r="C112" t="inlineStr">
+        <is>
+          <t>Vessel, Container</t>
+        </is>
+      </c>
+      <c r="D112" t="inlineStr"/>
+      <c r="E112" t="inlineStr">
+        <is>
+          <t>9903.03.06</t>
+        </is>
+      </c>
+      <c r="F112" t="inlineStr">
+        <is>
+          <t>S122 EXCL,IRN/STL/ALUM,DERIV</t>
+        </is>
+      </c>
+      <c r="G112" t="inlineStr">
+        <is>
+          <t>001</t>
+        </is>
+      </c>
+      <c r="H112" t="inlineStr">
+        <is>
+          <t>9903.03.06</t>
+        </is>
+      </c>
+      <c r="I112" t="inlineStr">
+        <is>
+          <t>9903.82.09,9403.20.0075</t>
+        </is>
+      </c>
+      <c r="J112" t="inlineStr">
+        <is>
+          <t>VISUAL CREATIONS, INC.</t>
+        </is>
+      </c>
+      <c r="K112" t="inlineStr">
+        <is>
+          <t>VISCRE</t>
+        </is>
+      </c>
+      <c r="L112" t="inlineStr">
+        <is>
+          <t>20-461602300</t>
+        </is>
+      </c>
+      <c r="M112" t="inlineStr">
+        <is>
+          <t>2026-06-14 00:00:00</t>
+        </is>
+      </c>
+      <c r="N112" t="inlineStr">
+        <is>
+          <t>2026-06-13 00:00:00</t>
+        </is>
+      </c>
+      <c r="O112" t="inlineStr">
+        <is>
+          <t>VIET MOI INDUSTRIAL COMPANY LIMITED</t>
+        </is>
+      </c>
+      <c r="P112" t="inlineStr">
+        <is>
+          <t>VIET MOI INDUSTRIAL COMPANY LIMITED</t>
+        </is>
+      </c>
+      <c r="Q112" t="inlineStr">
+        <is>
+          <t>2026-05-01 00:00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" t="inlineStr">
+        <is>
+          <t>2565712</t>
+        </is>
+      </c>
+      <c r="B113" t="inlineStr">
+        <is>
+          <t>EF4-0232088-3</t>
+        </is>
+      </c>
+      <c r="C113" t="inlineStr">
+        <is>
+          <t>Vessel, Container</t>
+        </is>
+      </c>
+      <c r="D113" t="inlineStr"/>
+      <c r="E113" t="inlineStr">
+        <is>
+          <t>9903.03.01</t>
+        </is>
+      </c>
+      <c r="F113" t="inlineStr">
+        <is>
+          <t>SECTION 122 - 10% DUTY</t>
+        </is>
+      </c>
+      <c r="G113" t="inlineStr">
+        <is>
+          <t>002</t>
+        </is>
+      </c>
+      <c r="H113" t="inlineStr">
+        <is>
+          <t>9903.03.01</t>
+        </is>
+      </c>
+      <c r="I113" t="inlineStr">
+        <is>
+          <t>9903.76.04,9403.60.8093</t>
+        </is>
+      </c>
+      <c r="J113" t="inlineStr">
+        <is>
+          <t>VISUAL CREATIONS, INC.</t>
+        </is>
+      </c>
+      <c r="K113" t="inlineStr">
+        <is>
+          <t>VISCRE</t>
+        </is>
+      </c>
+      <c r="L113" t="inlineStr">
+        <is>
+          <t>20-461602300</t>
+        </is>
+      </c>
+      <c r="M113" t="inlineStr">
+        <is>
+          <t>2026-06-14 00:00:00</t>
+        </is>
+      </c>
+      <c r="N113" t="inlineStr">
+        <is>
+          <t>2026-06-13 00:00:00</t>
+        </is>
+      </c>
+      <c r="O113" t="inlineStr">
+        <is>
+          <t>VIET MOI INDUSTRIAL COMPANY LIMITED</t>
+        </is>
+      </c>
+      <c r="P113" t="inlineStr">
+        <is>
+          <t>VIET MOI INDUSTRIAL COMPANY LIMITED</t>
+        </is>
+      </c>
+      <c r="Q113" t="inlineStr">
+        <is>
+          <t>2026-05-01 00:00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" t="inlineStr">
+        <is>
+          <t>2565712</t>
+        </is>
+      </c>
+      <c r="B114" t="inlineStr">
+        <is>
+          <t>EF4-0232088-3</t>
+        </is>
+      </c>
+      <c r="C114" t="inlineStr">
+        <is>
+          <t>Vessel, Container</t>
+        </is>
+      </c>
+      <c r="D114" t="inlineStr"/>
+      <c r="E114" t="inlineStr">
+        <is>
+          <t>9903.03.01</t>
+        </is>
+      </c>
+      <c r="F114" t="inlineStr">
+        <is>
+          <t>SECTION 122 - 10% DUTY</t>
+        </is>
+      </c>
+      <c r="G114" t="inlineStr">
+        <is>
+          <t>003</t>
+        </is>
+      </c>
+      <c r="H114" t="inlineStr">
+        <is>
+          <t>9903.03.01</t>
+        </is>
+      </c>
+      <c r="I114" t="inlineStr">
+        <is>
+          <t>9403.99.9045</t>
+        </is>
+      </c>
+      <c r="J114" t="inlineStr">
+        <is>
+          <t>VISUAL CREATIONS, INC.</t>
+        </is>
+      </c>
+      <c r="K114" t="inlineStr">
+        <is>
+          <t>VISCRE</t>
+        </is>
+      </c>
+      <c r="L114" t="inlineStr">
+        <is>
+          <t>20-461602300</t>
+        </is>
+      </c>
+      <c r="M114" t="inlineStr">
+        <is>
+          <t>2026-06-14 00:00:00</t>
+        </is>
+      </c>
+      <c r="N114" t="inlineStr">
+        <is>
+          <t>2026-06-13 00:00:00</t>
+        </is>
+      </c>
+      <c r="O114" t="inlineStr">
+        <is>
+          <t>VIET MOI INDUSTRIAL COMPANY LIMITED</t>
+        </is>
+      </c>
+      <c r="P114" t="inlineStr">
+        <is>
+          <t>VIET MOI INDUSTRIAL COMPANY LIMITED</t>
+        </is>
+      </c>
+      <c r="Q114" t="inlineStr">
+        <is>
+          <t>2026-05-01 00:00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" t="inlineStr">
+        <is>
+          <t>2565712</t>
+        </is>
+      </c>
+      <c r="B115" t="inlineStr">
+        <is>
+          <t>EF4-0232088-3</t>
+        </is>
+      </c>
+      <c r="C115" t="inlineStr">
+        <is>
+          <t>Vessel, Container</t>
+        </is>
+      </c>
+      <c r="D115" t="inlineStr"/>
+      <c r="E115" t="inlineStr">
+        <is>
+          <t>9903.03.01</t>
+        </is>
+      </c>
+      <c r="F115" t="inlineStr">
+        <is>
+          <t>SECTION 122 - 10% DUTY</t>
+        </is>
+      </c>
+      <c r="G115" t="inlineStr">
+        <is>
+          <t>004</t>
+        </is>
+      </c>
+      <c r="H115" t="inlineStr">
+        <is>
+          <t>9903.03.01</t>
+        </is>
+      </c>
+      <c r="I115" t="inlineStr">
+        <is>
+          <t>3926.90.9989</t>
+        </is>
+      </c>
+      <c r="J115" t="inlineStr">
+        <is>
+          <t>VISUAL CREATIONS, INC.</t>
+        </is>
+      </c>
+      <c r="K115" t="inlineStr">
+        <is>
+          <t>VISCRE</t>
+        </is>
+      </c>
+      <c r="L115" t="inlineStr">
+        <is>
+          <t>20-461602300</t>
+        </is>
+      </c>
+      <c r="M115" t="inlineStr">
+        <is>
+          <t>2026-06-14 00:00:00</t>
+        </is>
+      </c>
+      <c r="N115" t="inlineStr">
+        <is>
+          <t>2026-06-13 00:00:00</t>
+        </is>
+      </c>
+      <c r="O115" t="inlineStr">
+        <is>
+          <t>VIET MOI INDUSTRIAL COMPANY LIMITED</t>
+        </is>
+      </c>
+      <c r="P115" t="inlineStr">
+        <is>
+          <t>VIET MOI INDUSTRIAL COMPANY LIMITED</t>
+        </is>
+      </c>
+      <c r="Q115" t="inlineStr">
+        <is>
+          <t>2026-05-01 00:00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" t="inlineStr">
+        <is>
+          <t>105504738</t>
+        </is>
+      </c>
+      <c r="B116" t="inlineStr">
+        <is>
+          <t>EF4-0232095-8</t>
+        </is>
+      </c>
+      <c r="C116" t="inlineStr">
+        <is>
+          <t>Vessel, Non-container</t>
+        </is>
+      </c>
+      <c r="D116" t="inlineStr"/>
+      <c r="E116" t="inlineStr">
+        <is>
+          <t>9805.00.50</t>
+        </is>
+      </c>
+      <c r="F116" t="inlineStr">
+        <is>
+          <t>EFFECTS US GOV EMP&amp;FAMLY/EVACU</t>
+        </is>
+      </c>
+      <c r="G116" t="inlineStr">
+        <is>
+          <t>001</t>
+        </is>
+      </c>
+      <c r="H116" t="inlineStr">
+        <is>
+          <t>9805.00.50</t>
+        </is>
+      </c>
+      <c r="I116" t="inlineStr"/>
+      <c r="J116" t="inlineStr">
+        <is>
+          <t>IFF, INC.</t>
+        </is>
+      </c>
+      <c r="K116" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="L116" t="inlineStr">
+        <is>
+          <t>58-149385700</t>
+        </is>
+      </c>
+      <c r="M116" t="inlineStr">
+        <is>
+          <t>2026-06-13 00:00:00</t>
+        </is>
+      </c>
+      <c r="N116" t="inlineStr">
+        <is>
+          <t>2026-06-13 00:00:00</t>
+        </is>
+      </c>
+      <c r="O116" t="inlineStr">
+        <is>
+          <t>VOLVO CAR INTERNATIONAL CORPORATION</t>
+        </is>
+      </c>
+      <c r="P116" t="inlineStr">
+        <is>
+          <t>VOLVO CAR INTERNATIONAL CORPORATION</t>
+        </is>
+      </c>
+      <c r="Q116" t="inlineStr">
+        <is>
+          <t>2026-05-26 00:00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" t="inlineStr">
+        <is>
+          <t>105504739</t>
+        </is>
+      </c>
+      <c r="B117" t="inlineStr">
+        <is>
+          <t>EF4-0232096-6</t>
+        </is>
+      </c>
+      <c r="C117" t="inlineStr">
+        <is>
+          <t>Vessel, Non-container</t>
+        </is>
+      </c>
+      <c r="D117" t="inlineStr"/>
+      <c r="E117" t="inlineStr">
+        <is>
+          <t>9805.00.50</t>
+        </is>
+      </c>
+      <c r="F117" t="inlineStr">
+        <is>
+          <t>EFFECTS US GOV EMP&amp;FAMLY/EVACU</t>
+        </is>
+      </c>
+      <c r="G117" t="inlineStr">
+        <is>
+          <t>001</t>
+        </is>
+      </c>
+      <c r="H117" t="inlineStr">
+        <is>
+          <t>9805.00.50</t>
+        </is>
+      </c>
+      <c r="I117" t="inlineStr"/>
+      <c r="J117" t="inlineStr">
+        <is>
+          <t>IFF, INC.</t>
+        </is>
+      </c>
+      <c r="K117" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="L117" t="inlineStr">
+        <is>
+          <t>58-149385700</t>
+        </is>
+      </c>
+      <c r="M117" t="inlineStr">
+        <is>
+          <t>2026-06-13 00:00:00</t>
+        </is>
+      </c>
+      <c r="N117" t="inlineStr">
+        <is>
+          <t>2026-06-13 00:00:00</t>
+        </is>
+      </c>
+      <c r="O117" t="inlineStr">
+        <is>
+          <t>VOLVO CAR INTERNATIONAL CORPORATION</t>
+        </is>
+      </c>
+      <c r="P117" t="inlineStr">
+        <is>
+          <t>VOLVO CAR INTERNATIONAL CORPORATION</t>
+        </is>
+      </c>
+      <c r="Q117" t="inlineStr">
+        <is>
+          <t>2026-05-26 00:00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" t="inlineStr">
+        <is>
+          <t>105504740</t>
+        </is>
+      </c>
+      <c r="B118" t="inlineStr">
+        <is>
+          <t>EF4-0232098-2</t>
+        </is>
+      </c>
+      <c r="C118" t="inlineStr">
+        <is>
+          <t>Vessel, Non-container</t>
+        </is>
+      </c>
+      <c r="D118" t="inlineStr"/>
+      <c r="E118" t="inlineStr">
+        <is>
+          <t>9805.00.50</t>
+        </is>
+      </c>
+      <c r="F118" t="inlineStr">
+        <is>
+          <t>EFFECTS US GOV EMP&amp;FAMLY/EVACU</t>
+        </is>
+      </c>
+      <c r="G118" t="inlineStr">
+        <is>
+          <t>001</t>
+        </is>
+      </c>
+      <c r="H118" t="inlineStr">
+        <is>
+          <t>9805.00.50</t>
+        </is>
+      </c>
+      <c r="I118" t="inlineStr"/>
+      <c r="J118" t="inlineStr">
+        <is>
+          <t>IFF, INC.</t>
+        </is>
+      </c>
+      <c r="K118" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="L118" t="inlineStr">
+        <is>
+          <t>58-149385700</t>
+        </is>
+      </c>
+      <c r="M118" t="inlineStr">
+        <is>
+          <t>2026-06-13 00:00:00</t>
+        </is>
+      </c>
+      <c r="N118" t="inlineStr">
+        <is>
+          <t>2026-06-13 00:00:00</t>
+        </is>
+      </c>
+      <c r="O118" t="inlineStr">
+        <is>
+          <t>VOLVO CAR INTERNATIONAL CORPORATION</t>
+        </is>
+      </c>
+      <c r="P118" t="inlineStr">
+        <is>
+          <t>VOLVO CAR INTERNATIONAL CORPORATION</t>
+        </is>
+      </c>
+      <c r="Q118" t="inlineStr">
+        <is>
+          <t>2026-05-26 00:00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" t="inlineStr">
+        <is>
+          <t>105504741</t>
+        </is>
+      </c>
+      <c r="B119" t="inlineStr">
+        <is>
+          <t>EF4-0232100-6</t>
+        </is>
+      </c>
+      <c r="C119" t="inlineStr">
+        <is>
+          <t>Vessel, Non-container</t>
+        </is>
+      </c>
+      <c r="D119" t="inlineStr"/>
+      <c r="E119" t="inlineStr">
+        <is>
+          <t>9805.00.50</t>
+        </is>
+      </c>
+      <c r="F119" t="inlineStr">
+        <is>
+          <t>EFFECTS US GOV EMP&amp;FAMLY/EVACU</t>
+        </is>
+      </c>
+      <c r="G119" t="inlineStr">
+        <is>
+          <t>001</t>
+        </is>
+      </c>
+      <c r="H119" t="inlineStr">
+        <is>
+          <t>9805.00.50</t>
+        </is>
+      </c>
+      <c r="I119" t="inlineStr"/>
+      <c r="J119" t="inlineStr">
+        <is>
+          <t>IFF, INC.</t>
+        </is>
+      </c>
+      <c r="K119" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="L119" t="inlineStr">
+        <is>
+          <t>58-149385700</t>
+        </is>
+      </c>
+      <c r="M119" t="inlineStr">
+        <is>
+          <t>2026-06-13 00:00:00</t>
+        </is>
+      </c>
+      <c r="N119" t="inlineStr">
+        <is>
+          <t>2026-06-13 00:00:00</t>
+        </is>
+      </c>
+      <c r="O119" t="inlineStr">
+        <is>
+          <t>VOLVO CAR INTERNATIONAL CORPORATION</t>
+        </is>
+      </c>
+      <c r="P119" t="inlineStr">
+        <is>
+          <t>VOLVO CAR INTERNATIONAL CORPORATION</t>
+        </is>
+      </c>
+      <c r="Q119" t="inlineStr">
+        <is>
+          <t>2026-05-26 00:00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" t="inlineStr">
+        <is>
+          <t>105504747</t>
+        </is>
+      </c>
+      <c r="B120" t="inlineStr">
+        <is>
+          <t>EF4-0232107-1</t>
+        </is>
+      </c>
+      <c r="C120" t="inlineStr">
+        <is>
+          <t>Vessel, Non-container</t>
+        </is>
+      </c>
+      <c r="D120" t="inlineStr"/>
+      <c r="E120" t="inlineStr">
+        <is>
+          <t>9805.00.50</t>
+        </is>
+      </c>
+      <c r="F120" t="inlineStr">
+        <is>
+          <t>EFFECTS US GOV EMP&amp;FAMLY/EVACU</t>
+        </is>
+      </c>
+      <c r="G120" t="inlineStr">
+        <is>
+          <t>001</t>
+        </is>
+      </c>
+      <c r="H120" t="inlineStr">
+        <is>
+          <t>9805.00.50</t>
+        </is>
+      </c>
+      <c r="I120" t="inlineStr"/>
+      <c r="J120" t="inlineStr">
+        <is>
+          <t>IFF, INC.</t>
+        </is>
+      </c>
+      <c r="K120" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="L120" t="inlineStr">
+        <is>
+          <t>58-149385700</t>
+        </is>
+      </c>
+      <c r="M120" t="inlineStr">
+        <is>
+          <t>2026-06-13 00:00:00</t>
+        </is>
+      </c>
+      <c r="N120" t="inlineStr">
+        <is>
+          <t>2026-06-13 00:00:00</t>
+        </is>
+      </c>
+      <c r="O120" t="inlineStr">
+        <is>
+          <t>VOLVO CAR INTERNATIONAL CORPORATION</t>
+        </is>
+      </c>
+      <c r="P120" t="inlineStr">
+        <is>
+          <t>VOLVO CAR INTERNATIONAL CORPORATION</t>
+        </is>
+      </c>
+      <c r="Q120" t="inlineStr">
+        <is>
+          <t>2026-05-28 00:00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" t="inlineStr">
+        <is>
+          <t>2566131</t>
+        </is>
+      </c>
+      <c r="B121" t="inlineStr">
+        <is>
+          <t>EF4-0232126-1</t>
+        </is>
+      </c>
+      <c r="C121" t="inlineStr">
+        <is>
+          <t>Vessel, Container</t>
+        </is>
+      </c>
+      <c r="D121" t="inlineStr">
+        <is>
+          <t>V1626459831</t>
+        </is>
+      </c>
+      <c r="E121" t="inlineStr">
+        <is>
+          <t>9903.03.01</t>
+        </is>
+      </c>
+      <c r="F121" t="inlineStr"/>
+      <c r="G121" t="inlineStr">
+        <is>
+          <t>001</t>
+        </is>
+      </c>
+      <c r="H121" t="inlineStr">
+        <is>
+          <t>9903.03.01</t>
+        </is>
+      </c>
+      <c r="I121" t="inlineStr">
+        <is>
+          <t>1108.12.0010</t>
+        </is>
+      </c>
+      <c r="J121" t="inlineStr">
+        <is>
+          <t>ROYAL INGREDIENTS GROUP BV</t>
+        </is>
+      </c>
+      <c r="K121" t="inlineStr">
+        <is>
+          <t>ROYINGRE</t>
+        </is>
+      </c>
+      <c r="L121" t="inlineStr">
+        <is>
+          <t>074601-00962</t>
+        </is>
+      </c>
+      <c r="M121" t="inlineStr">
+        <is>
+          <t>2026-06-14 00:00:00</t>
+        </is>
+      </c>
+      <c r="N121" t="inlineStr">
+        <is>
+          <t>2026-06-13 00:00:00</t>
+        </is>
+      </c>
+      <c r="O121" t="inlineStr">
+        <is>
+          <t>TAT NISASTA INS SAN TIC AS</t>
+        </is>
+      </c>
+      <c r="P121" t="inlineStr">
+        <is>
+          <t>TAT NISASTA INS SAN TIC AS</t>
+        </is>
+      </c>
+      <c r="Q121" t="inlineStr">
+        <is>
+          <t>2026-05-23 00:00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" t="inlineStr">
+        <is>
+          <t>2565958</t>
+        </is>
+      </c>
+      <c r="B122" t="inlineStr">
+        <is>
+          <t>EF4-0232210-3</t>
+        </is>
+      </c>
+      <c r="C122" t="inlineStr">
+        <is>
+          <t>Vessel, Container</t>
+        </is>
+      </c>
+      <c r="D122" t="inlineStr">
+        <is>
+          <t>V1626459831</t>
+        </is>
+      </c>
+      <c r="E122" t="inlineStr">
+        <is>
+          <t>9903.03.06</t>
+        </is>
+      </c>
+      <c r="F122" t="inlineStr">
+        <is>
+          <t>S122 EXCL,IRN/STL/ALUM,DERIV</t>
+        </is>
+      </c>
+      <c r="G122" t="inlineStr">
+        <is>
+          <t>001</t>
+        </is>
+      </c>
+      <c r="H122" t="inlineStr">
+        <is>
+          <t>9903.03.06</t>
+        </is>
+      </c>
+      <c r="I122" t="inlineStr">
+        <is>
+          <t>9903.74.11,9903.94.53,8708.29.5160</t>
+        </is>
+      </c>
+      <c r="J122" t="inlineStr">
+        <is>
+          <t>BORGERS OHIO INC.</t>
+        </is>
+      </c>
+      <c r="K122" t="inlineStr">
+        <is>
+          <t>BORUSA02</t>
+        </is>
+      </c>
+      <c r="L122" t="inlineStr">
+        <is>
+          <t>30-084196200</t>
+        </is>
+      </c>
+      <c r="M122" t="inlineStr">
+        <is>
+          <t>2026-06-15 00:00:00</t>
+        </is>
+      </c>
+      <c r="N122" t="inlineStr">
+        <is>
+          <t>2026-06-13 00:00:00</t>
+        </is>
+      </c>
+      <c r="O122" t="inlineStr">
+        <is>
+          <t>AUTONEUM CZ S.R.O.</t>
+        </is>
+      </c>
+      <c r="P122" t="inlineStr">
+        <is>
+          <t>AUTONEUM CZ S.R.O.</t>
+        </is>
+      </c>
+      <c r="Q122" t="inlineStr">
+        <is>
+          <t>2026-05-28 00:00:00</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/trimika_data.xlsx
+++ b/trimika_data.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q122"/>
+  <dimension ref="A1:Q137"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5490,12 +5490,12 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>2566053</t>
+          <t>2565494</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>EF4-0232278-0</t>
+          <t>EF4-0231250-0</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
@@ -5503,19 +5503,15 @@
           <t>Vessel, Container</t>
         </is>
       </c>
-      <c r="D62" t="inlineStr">
-        <is>
-          <t>V1626455557</t>
-        </is>
-      </c>
+      <c r="D62" t="inlineStr"/>
       <c r="E62" t="inlineStr">
         <is>
-          <t>9903.03.06</t>
+          <t>9903.03.01</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>S122 EXCL,IRN/STL/ALUM,DERIV</t>
+          <t>SECTION 122 - 10% DUTY</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
@@ -5525,27 +5521,27 @@
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>9903.03.06</t>
+          <t>9903.03.01</t>
         </is>
       </c>
       <c r="I62" t="inlineStr">
         <is>
-          <t>9903.74.11,9903.94.53,8708.29.5160</t>
+          <t>1109.00.9020</t>
         </is>
       </c>
       <c r="J62" t="inlineStr">
         <is>
-          <t>BORGERS USA CORP</t>
+          <t>ROYAL INGREDIENTS GROUP BV</t>
         </is>
       </c>
       <c r="K62" t="inlineStr">
         <is>
-          <t>BORUSA</t>
+          <t>ROYINGRE</t>
         </is>
       </c>
       <c r="L62" t="inlineStr">
         <is>
-          <t>65-117296500</t>
+          <t>074601-00962</t>
         </is>
       </c>
       <c r="M62" t="inlineStr">
@@ -5555,34 +5551,34 @@
       </c>
       <c r="N62" t="inlineStr">
         <is>
-          <t>2026-06-11 00:00:00</t>
+          <t>2026-06-12 00:00:00</t>
         </is>
       </c>
       <c r="O62" t="inlineStr">
         <is>
-          <t>AUTONEUM CZ S.R.O.</t>
+          <t>ROQUETTE FRERES</t>
         </is>
       </c>
       <c r="P62" t="inlineStr">
         <is>
-          <t>AUTONEUM CZ S.R.O.</t>
+          <t>ROQUETTE FRERES</t>
         </is>
       </c>
       <c r="Q62" t="inlineStr">
         <is>
-          <t>2026-06-01 00:00:00</t>
+          <t>2026-04-18 00:00:00</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>2566053</t>
+          <t>2565534</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>EF4-0232278-0</t>
+          <t>EF4-0231273-2</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
@@ -5590,49 +5586,45 @@
           <t>Vessel, Container</t>
         </is>
       </c>
-      <c r="D63" t="inlineStr">
-        <is>
-          <t>V1626455557</t>
-        </is>
-      </c>
+      <c r="D63" t="inlineStr"/>
       <c r="E63" t="inlineStr">
         <is>
-          <t>9903.03.06</t>
+          <t>9903.03.01</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>S122 EXCL,IRN/STL/ALUM,DERIV</t>
+          <t>SECTION 122 - 10% DUTY</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>002</t>
+          <t>001</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>9903.03.06</t>
+          <t>9903.03.01</t>
         </is>
       </c>
       <c r="I63" t="inlineStr">
         <is>
-          <t>9903.74.11,9903.94.53,8708.29.5160</t>
+          <t>1108.13.0010</t>
         </is>
       </c>
       <c r="J63" t="inlineStr">
         <is>
-          <t>BORGERS USA CORP</t>
+          <t>ROYAL INGREDIENTS GROUP BV</t>
         </is>
       </c>
       <c r="K63" t="inlineStr">
         <is>
-          <t>BORUSA</t>
+          <t>ROYINGRE</t>
         </is>
       </c>
       <c r="L63" t="inlineStr">
         <is>
-          <t>65-117296500</t>
+          <t>074601-00962</t>
         </is>
       </c>
       <c r="M63" t="inlineStr">
@@ -5642,34 +5634,34 @@
       </c>
       <c r="N63" t="inlineStr">
         <is>
-          <t>2026-06-11 00:00:00</t>
+          <t>2026-06-12 00:00:00</t>
         </is>
       </c>
       <c r="O63" t="inlineStr">
         <is>
-          <t>AUTONEUM CZ S.R.O.</t>
+          <t>AKV LANGHOLT AMBA</t>
         </is>
       </c>
       <c r="P63" t="inlineStr">
         <is>
-          <t>AUTONEUM CZ S.R.O.</t>
+          <t>AKV LANGHOLT AMBA</t>
         </is>
       </c>
       <c r="Q63" t="inlineStr">
         <is>
-          <t>2026-06-01 00:00:00</t>
+          <t>2026-04-20 00:00:00</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>2566053</t>
+          <t>2565697</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>EF4-0232278-0</t>
+          <t>EF4-0231423-3</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
@@ -5677,49 +5669,45 @@
           <t>Vessel, Container</t>
         </is>
       </c>
-      <c r="D64" t="inlineStr">
-        <is>
-          <t>V1626455557</t>
-        </is>
-      </c>
+      <c r="D64" t="inlineStr"/>
       <c r="E64" t="inlineStr">
         <is>
-          <t>9903.03.06</t>
+          <t>9903.03.01</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>S122 EXCL,IRN/STL/ALUM,DERIV</t>
+          <t>SECTION 122 - 10% DUTY</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>003</t>
+          <t>001</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>9903.03.06</t>
+          <t>9903.03.01</t>
         </is>
       </c>
       <c r="I64" t="inlineStr">
         <is>
-          <t>9903.74.11,9903.94.53,8708.29.5160</t>
+          <t>1108.13.0010</t>
         </is>
       </c>
       <c r="J64" t="inlineStr">
         <is>
-          <t>BORGERS USA CORP</t>
+          <t>ROYAL INGREDIENTS GROUP BV</t>
         </is>
       </c>
       <c r="K64" t="inlineStr">
         <is>
-          <t>BORUSA</t>
+          <t>ROYINGRE</t>
         </is>
       </c>
       <c r="L64" t="inlineStr">
         <is>
-          <t>65-117296500</t>
+          <t>074601-00962</t>
         </is>
       </c>
       <c r="M64" t="inlineStr">
@@ -5729,34 +5717,34 @@
       </c>
       <c r="N64" t="inlineStr">
         <is>
-          <t>2026-06-11 00:00:00</t>
+          <t>2026-06-12 00:00:00</t>
         </is>
       </c>
       <c r="O64" t="inlineStr">
         <is>
-          <t>AUTONEUM CZ S.R.O.</t>
+          <t>AKV LANGHOLT AMBA</t>
         </is>
       </c>
       <c r="P64" t="inlineStr">
         <is>
-          <t>AUTONEUM CZ S.R.O.</t>
+          <t>AKV LANGHOLT AMBA</t>
         </is>
       </c>
       <c r="Q64" t="inlineStr">
         <is>
-          <t>2026-06-01 00:00:00</t>
+          <t>2026-04-27 00:00:00</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>2566053</t>
+          <t>2565660</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>EF4-0232278-0</t>
+          <t>EF4-0231430-8</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
@@ -5764,86 +5752,82 @@
           <t>Vessel, Container</t>
         </is>
       </c>
-      <c r="D65" t="inlineStr">
-        <is>
-          <t>V1626455557</t>
-        </is>
-      </c>
+      <c r="D65" t="inlineStr"/>
       <c r="E65" t="inlineStr">
         <is>
-          <t>9903.03.06</t>
+          <t>9903.03.01</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>S122 EXCL,IRN/STL/ALUM,DERIV</t>
+          <t>SECTION 122 - 10% DUTY</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>004</t>
+          <t>001</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>9903.03.06</t>
+          <t>9903.03.01</t>
         </is>
       </c>
       <c r="I65" t="inlineStr">
         <is>
-          <t>9903.74.11,9903.94.53,8708.29.5160</t>
+          <t>5903.90.3090</t>
         </is>
       </c>
       <c r="J65" t="inlineStr">
         <is>
-          <t>BORGERS USA CORP</t>
+          <t>VEER CORPORATIONS INC</t>
         </is>
       </c>
       <c r="K65" t="inlineStr">
         <is>
-          <t>BORUSA</t>
+          <t>VEECOR01</t>
         </is>
       </c>
       <c r="L65" t="inlineStr">
         <is>
-          <t>65-117296500</t>
+          <t>99-106989200</t>
         </is>
       </c>
       <c r="M65" t="inlineStr">
         <is>
+          <t>2026-06-14 00:00:00</t>
+        </is>
+      </c>
+      <c r="N65" t="inlineStr">
+        <is>
           <t>2026-06-12 00:00:00</t>
         </is>
       </c>
-      <c r="N65" t="inlineStr">
-        <is>
-          <t>2026-06-11 00:00:00</t>
-        </is>
-      </c>
       <c r="O65" t="inlineStr">
         <is>
-          <t>AUTONEUM CZ S.R.O.</t>
+          <t>VEER PLASTIC PVT LTD</t>
         </is>
       </c>
       <c r="P65" t="inlineStr">
         <is>
-          <t>AUTONEUM CZ S.R.O.</t>
+          <t>VEER PLASTIC PVT LTD</t>
         </is>
       </c>
       <c r="Q65" t="inlineStr">
         <is>
-          <t>2026-06-01 00:00:00</t>
+          <t>2026-04-28 00:00:00</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>2566053</t>
+          <t>2565924</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>EF4-0232278-0</t>
+          <t>EF4-0231960-4</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
@@ -5851,49 +5835,45 @@
           <t>Vessel, Container</t>
         </is>
       </c>
-      <c r="D66" t="inlineStr">
-        <is>
-          <t>V1626455557</t>
-        </is>
-      </c>
+      <c r="D66" t="inlineStr"/>
       <c r="E66" t="inlineStr">
         <is>
-          <t>9903.03.06</t>
+          <t>9903.03.01</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>S122 EXCL,IRN/STL/ALUM,DERIV</t>
+          <t>SECTION 122 - 10% DUTY</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>005</t>
+          <t>001</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>9903.03.06</t>
+          <t>9903.03.01</t>
         </is>
       </c>
       <c r="I66" t="inlineStr">
         <is>
-          <t>9903.74.11,9903.94.53,8708.29.5160</t>
+          <t>1109.00.9020</t>
         </is>
       </c>
       <c r="J66" t="inlineStr">
         <is>
-          <t>BORGERS USA CORP</t>
+          <t>ROYAL INGREDIENTS GROUP BV</t>
         </is>
       </c>
       <c r="K66" t="inlineStr">
         <is>
-          <t>BORUSA</t>
+          <t>ROYINGRE</t>
         </is>
       </c>
       <c r="L66" t="inlineStr">
         <is>
-          <t>65-117296500</t>
+          <t>074601-00962</t>
         </is>
       </c>
       <c r="M66" t="inlineStr">
@@ -5903,34 +5883,34 @@
       </c>
       <c r="N66" t="inlineStr">
         <is>
-          <t>2026-06-11 00:00:00</t>
+          <t>2026-06-12 00:00:00</t>
         </is>
       </c>
       <c r="O66" t="inlineStr">
         <is>
-          <t>AUTONEUM CZ S.R.O.</t>
+          <t>JACKERING MUHLEN UND NAHRMITTELWERK</t>
         </is>
       </c>
       <c r="P66" t="inlineStr">
         <is>
-          <t>AUTONEUM CZ S.R.O.</t>
+          <t>JACKERING MUHLEN UND NAHRMITTELWERKE GMBH</t>
         </is>
       </c>
       <c r="Q66" t="inlineStr">
         <is>
-          <t>2026-06-01 00:00:00</t>
+          <t>2026-05-18 00:00:00</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>2565494</t>
+          <t>2566052</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>EF4-0231250-0</t>
+          <t>EF4-0232193-1</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
@@ -5961,22 +5941,22 @@
       </c>
       <c r="I67" t="inlineStr">
         <is>
-          <t>1109.00.9020</t>
+          <t>3402.90.1000</t>
         </is>
       </c>
       <c r="J67" t="inlineStr">
         <is>
-          <t>ROYAL INGREDIENTS GROUP BV</t>
+          <t>FI-TECH INC</t>
         </is>
       </c>
       <c r="K67" t="inlineStr">
         <is>
-          <t>ROYINGRE</t>
+          <t>FITINC</t>
         </is>
       </c>
       <c r="L67" t="inlineStr">
         <is>
-          <t>074601-00962</t>
+          <t>54-091465000</t>
         </is>
       </c>
       <c r="M67" t="inlineStr">
@@ -5991,29 +5971,29 @@
       </c>
       <c r="O67" t="inlineStr">
         <is>
-          <t>ROQUETTE FRERES</t>
+          <t>SCHILL SEILACHER GMBH CO</t>
         </is>
       </c>
       <c r="P67" t="inlineStr">
         <is>
-          <t>ROQUETTE FRERES</t>
+          <t>SCHILL SEILACHER GMBH CO</t>
         </is>
       </c>
       <c r="Q67" t="inlineStr">
         <is>
-          <t>2026-04-18 00:00:00</t>
+          <t>2026-05-28 00:00:00</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>2565534</t>
+          <t>2566057</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>EF4-0231273-2</t>
+          <t>EF4-0232211-1</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
@@ -6021,7 +6001,11 @@
           <t>Vessel, Container</t>
         </is>
       </c>
-      <c r="D68" t="inlineStr"/>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>V1626460482</t>
+        </is>
+      </c>
       <c r="E68" t="inlineStr">
         <is>
           <t>9903.03.01</t>
@@ -6044,7 +6028,7 @@
       </c>
       <c r="I68" t="inlineStr">
         <is>
-          <t>1108.13.0010</t>
+          <t>1109.00.9020</t>
         </is>
       </c>
       <c r="J68" t="inlineStr">
@@ -6064,39 +6048,39 @@
       </c>
       <c r="M68" t="inlineStr">
         <is>
+          <t>2026-06-14 00:00:00</t>
+        </is>
+      </c>
+      <c r="N68" t="inlineStr">
+        <is>
           <t>2026-06-12 00:00:00</t>
         </is>
       </c>
-      <c r="N68" t="inlineStr">
-        <is>
-          <t>2026-06-12 00:00:00</t>
-        </is>
-      </c>
       <c r="O68" t="inlineStr">
         <is>
-          <t>AKV LANGHOLT AMBA</t>
+          <t>JACKERING MUHLEN UND NAHRMITTELWERK</t>
         </is>
       </c>
       <c r="P68" t="inlineStr">
         <is>
-          <t>AKV LANGHOLT AMBA</t>
+          <t>JACKERING MUHLEN UND NAHRMITTELWERKE GMBH</t>
         </is>
       </c>
       <c r="Q68" t="inlineStr">
         <is>
-          <t>2026-04-20 00:00:00</t>
+          <t>2026-05-30 00:00:00</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>2565697</t>
+          <t>2566058</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>EF4-0231423-3</t>
+          <t>EF4-0232213-7</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
@@ -6104,7 +6088,11 @@
           <t>Vessel, Container</t>
         </is>
       </c>
-      <c r="D69" t="inlineStr"/>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>V1626460482</t>
+        </is>
+      </c>
       <c r="E69" t="inlineStr">
         <is>
           <t>9903.03.01</t>
@@ -6127,7 +6115,7 @@
       </c>
       <c r="I69" t="inlineStr">
         <is>
-          <t>1108.13.0010</t>
+          <t>1109.00.9020</t>
         </is>
       </c>
       <c r="J69" t="inlineStr">
@@ -6147,39 +6135,39 @@
       </c>
       <c r="M69" t="inlineStr">
         <is>
+          <t>2026-06-14 00:00:00</t>
+        </is>
+      </c>
+      <c r="N69" t="inlineStr">
+        <is>
           <t>2026-06-12 00:00:00</t>
         </is>
       </c>
-      <c r="N69" t="inlineStr">
-        <is>
-          <t>2026-06-12 00:00:00</t>
-        </is>
-      </c>
       <c r="O69" t="inlineStr">
         <is>
-          <t>AKV LANGHOLT AMBA</t>
+          <t>JACKERING MUHLEN UND NAHRMITTELWERK</t>
         </is>
       </c>
       <c r="P69" t="inlineStr">
         <is>
-          <t>AKV LANGHOLT AMBA</t>
+          <t>JACKERING MUHLEN UND NAHRMITTELWERKE GMBH</t>
         </is>
       </c>
       <c r="Q69" t="inlineStr">
         <is>
-          <t>2026-04-27 00:00:00</t>
+          <t>2026-05-30 00:00:00</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>2565660</t>
+          <t>2566067</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>EF4-0231430-8</t>
+          <t>EF4-0232214-5</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
@@ -6187,7 +6175,11 @@
           <t>Vessel, Container</t>
         </is>
       </c>
-      <c r="D70" t="inlineStr"/>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>V1626460482</t>
+        </is>
+      </c>
       <c r="E70" t="inlineStr">
         <is>
           <t>9903.03.01</t>
@@ -6210,22 +6202,22 @@
       </c>
       <c r="I70" t="inlineStr">
         <is>
-          <t>5903.90.3090</t>
+          <t>1109.00.9020</t>
         </is>
       </c>
       <c r="J70" t="inlineStr">
         <is>
-          <t>VEER CORPORATIONS INC</t>
+          <t>ROYAL INGREDIENTS GROUP BV</t>
         </is>
       </c>
       <c r="K70" t="inlineStr">
         <is>
-          <t>VEECOR01</t>
+          <t>ROYINGRE</t>
         </is>
       </c>
       <c r="L70" t="inlineStr">
         <is>
-          <t>99-106989200</t>
+          <t>074601-00962</t>
         </is>
       </c>
       <c r="M70" t="inlineStr">
@@ -6240,29 +6232,29 @@
       </c>
       <c r="O70" t="inlineStr">
         <is>
-          <t>VEER PLASTIC PVT LTD</t>
+          <t>JACKERING MUHLEN UND NAHRMITTELWERK</t>
         </is>
       </c>
       <c r="P70" t="inlineStr">
         <is>
-          <t>VEER PLASTIC PVT LTD</t>
+          <t>JACKERING MUHLEN UND NAHRMITTELWERKE GMBH</t>
         </is>
       </c>
       <c r="Q70" t="inlineStr">
         <is>
-          <t>2026-04-28 00:00:00</t>
+          <t>2026-05-30 00:00:00</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>2565924</t>
+          <t>2566070</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>EF4-0231960-4</t>
+          <t>EF4-0232215-2</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
@@ -6270,7 +6262,11 @@
           <t>Vessel, Container</t>
         </is>
       </c>
-      <c r="D71" t="inlineStr"/>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>V1626460482</t>
+        </is>
+      </c>
       <c r="E71" t="inlineStr">
         <is>
           <t>9903.03.01</t>
@@ -6313,14 +6309,14 @@
       </c>
       <c r="M71" t="inlineStr">
         <is>
+          <t>2026-06-14 00:00:00</t>
+        </is>
+      </c>
+      <c r="N71" t="inlineStr">
+        <is>
           <t>2026-06-12 00:00:00</t>
         </is>
       </c>
-      <c r="N71" t="inlineStr">
-        <is>
-          <t>2026-06-12 00:00:00</t>
-        </is>
-      </c>
       <c r="O71" t="inlineStr">
         <is>
           <t>JACKERING MUHLEN UND NAHRMITTELWERK</t>
@@ -6333,27 +6329,31 @@
       </c>
       <c r="Q71" t="inlineStr">
         <is>
-          <t>2026-05-18 00:00:00</t>
+          <t>2026-05-30 00:00:00</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>2566052</t>
+          <t>4539358</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>EF4-0232193-1</t>
+          <t>EF4-0232235-0</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Vessel, Container</t>
-        </is>
-      </c>
-      <c r="D72" t="inlineStr"/>
+          <t>Air, Non-container</t>
+        </is>
+      </c>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>01650618422</t>
+        </is>
+      </c>
       <c r="E72" t="inlineStr">
         <is>
           <t>9903.03.01</t>
@@ -6376,22 +6376,22 @@
       </c>
       <c r="I72" t="inlineStr">
         <is>
-          <t>3402.90.1000</t>
+          <t>3204.19.2020</t>
         </is>
       </c>
       <c r="J72" t="inlineStr">
         <is>
-          <t>FI-TECH INC</t>
+          <t>COLORCHEM INTERNATIONAL CORP</t>
         </is>
       </c>
       <c r="K72" t="inlineStr">
         <is>
-          <t>FITINC</t>
+          <t>COLORC01</t>
         </is>
       </c>
       <c r="L72" t="inlineStr">
         <is>
-          <t>54-091465000</t>
+          <t>58-241511400</t>
         </is>
       </c>
       <c r="M72" t="inlineStr">
@@ -6406,29 +6406,29 @@
       </c>
       <c r="O72" t="inlineStr">
         <is>
-          <t>SCHILL SEILACHER GMBH CO</t>
+          <t>PHILODEN INDUSTRIES PVT LTD</t>
         </is>
       </c>
       <c r="P72" t="inlineStr">
         <is>
-          <t>SCHILL SEILACHER GMBH CO</t>
+          <t>PHILODEN INDUSTRIES PVT LTD</t>
         </is>
       </c>
       <c r="Q72" t="inlineStr">
         <is>
-          <t>2026-05-28 00:00:00</t>
+          <t>2026-06-12 00:00:00</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>2566057</t>
+          <t>2566145</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>EF4-0232211-1</t>
+          <t>EF4-0232245-9</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
@@ -6438,7 +6438,7 @@
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>V1626460482</t>
+          <t>01650618422</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
@@ -6463,7 +6463,7 @@
       </c>
       <c r="I73" t="inlineStr">
         <is>
-          <t>1109.00.9020</t>
+          <t>1109.00.9010</t>
         </is>
       </c>
       <c r="J73" t="inlineStr">
@@ -6493,29 +6493,29 @@
       </c>
       <c r="O73" t="inlineStr">
         <is>
-          <t>JACKERING MUHLEN UND NAHRMITTELWERK</t>
+          <t>KROENER-STARKE BIO GMBH</t>
         </is>
       </c>
       <c r="P73" t="inlineStr">
         <is>
-          <t>JACKERING MUHLEN UND NAHRMITTELWERKE GMBH</t>
+          <t>KROENER-STARKE BIO GMBH</t>
         </is>
       </c>
       <c r="Q73" t="inlineStr">
         <is>
-          <t>2026-05-30 00:00:00</t>
+          <t>2026-06-01 00:00:00</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>2566058</t>
+          <t>2566233</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>EF4-0232213-7</t>
+          <t>EF4-0232259-0</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
@@ -6523,11 +6523,7 @@
           <t>Vessel, Container</t>
         </is>
       </c>
-      <c r="D74" t="inlineStr">
-        <is>
-          <t>V1626460482</t>
-        </is>
-      </c>
+      <c r="D74" t="inlineStr"/>
       <c r="E74" t="inlineStr">
         <is>
           <t>9903.03.01</t>
@@ -6550,27 +6546,27 @@
       </c>
       <c r="I74" t="inlineStr">
         <is>
-          <t>1109.00.9020</t>
+          <t>8421.99.0180</t>
         </is>
       </c>
       <c r="J74" t="inlineStr">
         <is>
-          <t>ROYAL INGREDIENTS GROUP BV</t>
+          <t>FI-TECH INC</t>
         </is>
       </c>
       <c r="K74" t="inlineStr">
         <is>
-          <t>ROYINGRE</t>
+          <t>FITINC</t>
         </is>
       </c>
       <c r="L74" t="inlineStr">
         <is>
-          <t>074601-00962</t>
+          <t>54-091465000</t>
         </is>
       </c>
       <c r="M74" t="inlineStr">
         <is>
-          <t>2026-06-14 00:00:00</t>
+          <t>2026-06-12 00:00:00</t>
         </is>
       </c>
       <c r="N74" t="inlineStr">
@@ -6580,29 +6576,29 @@
       </c>
       <c r="O74" t="inlineStr">
         <is>
-          <t>JACKERING MUHLEN UND NAHRMITTELWERK</t>
+          <t>FILTERTECHNIK EUROPE GMBH &amp; CO KG</t>
         </is>
       </c>
       <c r="P74" t="inlineStr">
         <is>
-          <t>JACKERING MUHLEN UND NAHRMITTELWERKE GMBH</t>
+          <t>FILTERTECHNIK EUROPE GMBH &amp; CO KG</t>
         </is>
       </c>
       <c r="Q74" t="inlineStr">
         <is>
-          <t>2026-05-30 00:00:00</t>
+          <t>2026-05-28 00:00:00</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>2566067</t>
+          <t>2566233</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>EF4-0232214-5</t>
+          <t>EF4-0232259-0</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
@@ -6610,11 +6606,7 @@
           <t>Vessel, Container</t>
         </is>
       </c>
-      <c r="D75" t="inlineStr">
-        <is>
-          <t>V1626460482</t>
-        </is>
-      </c>
+      <c r="D75" t="inlineStr"/>
       <c r="E75" t="inlineStr">
         <is>
           <t>9903.03.01</t>
@@ -6627,7 +6619,7 @@
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>001</t>
+          <t>002</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
@@ -6637,27 +6629,27 @@
       </c>
       <c r="I75" t="inlineStr">
         <is>
-          <t>1109.00.9020</t>
+          <t>8421.99.0180</t>
         </is>
       </c>
       <c r="J75" t="inlineStr">
         <is>
-          <t>ROYAL INGREDIENTS GROUP BV</t>
+          <t>FI-TECH INC</t>
         </is>
       </c>
       <c r="K75" t="inlineStr">
         <is>
-          <t>ROYINGRE</t>
+          <t>FITINC</t>
         </is>
       </c>
       <c r="L75" t="inlineStr">
         <is>
-          <t>074601-00962</t>
+          <t>54-091465000</t>
         </is>
       </c>
       <c r="M75" t="inlineStr">
         <is>
-          <t>2026-06-14 00:00:00</t>
+          <t>2026-06-12 00:00:00</t>
         </is>
       </c>
       <c r="N75" t="inlineStr">
@@ -6667,29 +6659,29 @@
       </c>
       <c r="O75" t="inlineStr">
         <is>
-          <t>JACKERING MUHLEN UND NAHRMITTELWERK</t>
+          <t>WIREMESH-PRO TEC GMBH</t>
         </is>
       </c>
       <c r="P75" t="inlineStr">
         <is>
-          <t>JACKERING MUHLEN UND NAHRMITTELWERKE GMBH</t>
+          <t>WIREMESH-PRO TEC GMBH</t>
         </is>
       </c>
       <c r="Q75" t="inlineStr">
         <is>
-          <t>2026-05-30 00:00:00</t>
+          <t>2026-05-28 00:00:00</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>2566070</t>
+          <t>2566233</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>EF4-0232215-2</t>
+          <t>EF4-0232259-0</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
@@ -6697,11 +6689,7 @@
           <t>Vessel, Container</t>
         </is>
       </c>
-      <c r="D76" t="inlineStr">
-        <is>
-          <t>V1626460482</t>
-        </is>
-      </c>
+      <c r="D76" t="inlineStr"/>
       <c r="E76" t="inlineStr">
         <is>
           <t>9903.03.01</t>
@@ -6714,7 +6702,7 @@
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>001</t>
+          <t>003</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
@@ -6724,27 +6712,27 @@
       </c>
       <c r="I76" t="inlineStr">
         <is>
-          <t>1109.00.9020</t>
+          <t>8421.99.0180</t>
         </is>
       </c>
       <c r="J76" t="inlineStr">
         <is>
-          <t>ROYAL INGREDIENTS GROUP BV</t>
+          <t>FI-TECH INC</t>
         </is>
       </c>
       <c r="K76" t="inlineStr">
         <is>
-          <t>ROYINGRE</t>
+          <t>FITINC</t>
         </is>
       </c>
       <c r="L76" t="inlineStr">
         <is>
-          <t>074601-00962</t>
+          <t>54-091465000</t>
         </is>
       </c>
       <c r="M76" t="inlineStr">
         <is>
-          <t>2026-06-14 00:00:00</t>
+          <t>2026-06-12 00:00:00</t>
         </is>
       </c>
       <c r="N76" t="inlineStr">
@@ -6754,41 +6742,37 @@
       </c>
       <c r="O76" t="inlineStr">
         <is>
-          <t>JACKERING MUHLEN UND NAHRMITTELWERK</t>
+          <t>WIREMESH-PRO TEC GMBH</t>
         </is>
       </c>
       <c r="P76" t="inlineStr">
         <is>
-          <t>JACKERING MUHLEN UND NAHRMITTELWERKE GMBH</t>
+          <t>WIREMESH-PRO TEC GMBH</t>
         </is>
       </c>
       <c r="Q76" t="inlineStr">
         <is>
-          <t>2026-05-30 00:00:00</t>
+          <t>2026-05-28 00:00:00</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>4539358</t>
+          <t>2566233</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>EF4-0232235-0</t>
+          <t>EF4-0232259-0</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Air, Non-container</t>
-        </is>
-      </c>
-      <c r="D77" t="inlineStr">
-        <is>
-          <t>01650618422</t>
-        </is>
-      </c>
+          <t>Vessel, Container</t>
+        </is>
+      </c>
+      <c r="D77" t="inlineStr"/>
       <c r="E77" t="inlineStr">
         <is>
           <t>9903.03.01</t>
@@ -6801,7 +6785,7 @@
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>001</t>
+          <t>004</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
@@ -6811,22 +6795,22 @@
       </c>
       <c r="I77" t="inlineStr">
         <is>
-          <t>3204.19.2020</t>
+          <t>8421.99.0180</t>
         </is>
       </c>
       <c r="J77" t="inlineStr">
         <is>
-          <t>COLORCHEM INTERNATIONAL CORP</t>
+          <t>FI-TECH INC</t>
         </is>
       </c>
       <c r="K77" t="inlineStr">
         <is>
-          <t>COLORC01</t>
+          <t>FITINC</t>
         </is>
       </c>
       <c r="L77" t="inlineStr">
         <is>
-          <t>58-241511400</t>
+          <t>54-091465000</t>
         </is>
       </c>
       <c r="M77" t="inlineStr">
@@ -6841,29 +6825,29 @@
       </c>
       <c r="O77" t="inlineStr">
         <is>
-          <t>PHILODEN INDUSTRIES PVT LTD</t>
+          <t>WIREMESH-PRO TEC GMBH</t>
         </is>
       </c>
       <c r="P77" t="inlineStr">
         <is>
-          <t>PHILODEN INDUSTRIES PVT LTD</t>
+          <t>WIREMESH-PRO TEC GMBH</t>
         </is>
       </c>
       <c r="Q77" t="inlineStr">
         <is>
-          <t>2026-06-12 00:00:00</t>
+          <t>2026-05-28 00:00:00</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>2566145</t>
+          <t>2566233</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>EF4-0232245-9</t>
+          <t>EF4-0232259-0</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
@@ -6871,11 +6855,7 @@
           <t>Vessel, Container</t>
         </is>
       </c>
-      <c r="D78" t="inlineStr">
-        <is>
-          <t>01650618422</t>
-        </is>
-      </c>
+      <c r="D78" t="inlineStr"/>
       <c r="E78" t="inlineStr">
         <is>
           <t>9903.03.01</t>
@@ -6888,7 +6868,7 @@
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>001</t>
+          <t>005</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
@@ -6898,27 +6878,27 @@
       </c>
       <c r="I78" t="inlineStr">
         <is>
-          <t>1109.00.9010</t>
+          <t>8421.99.0180</t>
         </is>
       </c>
       <c r="J78" t="inlineStr">
         <is>
-          <t>ROYAL INGREDIENTS GROUP BV</t>
+          <t>FI-TECH INC</t>
         </is>
       </c>
       <c r="K78" t="inlineStr">
         <is>
-          <t>ROYINGRE</t>
+          <t>FITINC</t>
         </is>
       </c>
       <c r="L78" t="inlineStr">
         <is>
-          <t>074601-00962</t>
+          <t>54-091465000</t>
         </is>
       </c>
       <c r="M78" t="inlineStr">
         <is>
-          <t>2026-06-14 00:00:00</t>
+          <t>2026-06-12 00:00:00</t>
         </is>
       </c>
       <c r="N78" t="inlineStr">
@@ -6928,17 +6908,17 @@
       </c>
       <c r="O78" t="inlineStr">
         <is>
-          <t>KROENER-STARKE BIO GMBH</t>
+          <t>REIFENHAUSER REICOFIL GMBH &amp; CO. KG</t>
         </is>
       </c>
       <c r="P78" t="inlineStr">
         <is>
-          <t>KROENER-STARKE BIO GMBH</t>
+          <t>REIFENHAUSER REICOFIL GMBH &amp; CO. KG</t>
         </is>
       </c>
       <c r="Q78" t="inlineStr">
         <is>
-          <t>2026-06-01 00:00:00</t>
+          <t>2026-05-28 00:00:00</t>
         </is>
       </c>
     </row>
@@ -6971,7 +6951,7 @@
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>001</t>
+          <t>006</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
@@ -6981,7 +6961,7 @@
       </c>
       <c r="I79" t="inlineStr">
         <is>
-          <t>8421.99.0180</t>
+          <t>8448.20.5090</t>
         </is>
       </c>
       <c r="J79" t="inlineStr">
@@ -7011,12 +6991,12 @@
       </c>
       <c r="O79" t="inlineStr">
         <is>
-          <t>FILTERTECHNIK EUROPE GMBH &amp; CO KG</t>
+          <t>REIFENHAUSER REICOFIL GMBH &amp; CO. KG</t>
         </is>
       </c>
       <c r="P79" t="inlineStr">
         <is>
-          <t>FILTERTECHNIK EUROPE GMBH &amp; CO KG</t>
+          <t>REIFENHAUSER REICOFIL GMBH &amp; CO. KG</t>
         </is>
       </c>
       <c r="Q79" t="inlineStr">
@@ -7054,7 +7034,7 @@
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>002</t>
+          <t>007</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
@@ -7064,7 +7044,7 @@
       </c>
       <c r="I80" t="inlineStr">
         <is>
-          <t>8421.99.0180</t>
+          <t>3402.90.5030</t>
         </is>
       </c>
       <c r="J80" t="inlineStr">
@@ -7094,12 +7074,12 @@
       </c>
       <c r="O80" t="inlineStr">
         <is>
-          <t>WIREMESH-PRO TEC GMBH</t>
+          <t>REIFENHAUSER REICOFIL GMBH &amp; CO. KG</t>
         </is>
       </c>
       <c r="P80" t="inlineStr">
         <is>
-          <t>WIREMESH-PRO TEC GMBH</t>
+          <t>REIFENHAUSER REICOFIL GMBH &amp; CO. KG</t>
         </is>
       </c>
       <c r="Q80" t="inlineStr">
@@ -7137,7 +7117,7 @@
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>003</t>
+          <t>008</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
@@ -7177,12 +7157,12 @@
       </c>
       <c r="O81" t="inlineStr">
         <is>
-          <t>WIREMESH-PRO TEC GMBH</t>
+          <t>REIFENHAUSER REICOFIL GMBH &amp; CO. KG</t>
         </is>
       </c>
       <c r="P81" t="inlineStr">
         <is>
-          <t>WIREMESH-PRO TEC GMBH</t>
+          <t>REIFENHAUSER REICOFIL GMBH &amp; CO. KG</t>
         </is>
       </c>
       <c r="Q81" t="inlineStr">
@@ -7220,7 +7200,7 @@
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>004</t>
+          <t>009</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
@@ -7260,12 +7240,12 @@
       </c>
       <c r="O82" t="inlineStr">
         <is>
-          <t>WIREMESH-PRO TEC GMBH</t>
+          <t>REIFENHAUSER REICOFIL GMBH &amp; CO. KG</t>
         </is>
       </c>
       <c r="P82" t="inlineStr">
         <is>
-          <t>WIREMESH-PRO TEC GMBH</t>
+          <t>REIFENHAUSER REICOFIL GMBH &amp; CO. KG</t>
         </is>
       </c>
       <c r="Q82" t="inlineStr">
@@ -7303,7 +7283,7 @@
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>005</t>
+          <t>010</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
@@ -7313,7 +7293,7 @@
       </c>
       <c r="I83" t="inlineStr">
         <is>
-          <t>8421.99.0180</t>
+          <t>5911.32.0080</t>
         </is>
       </c>
       <c r="J83" t="inlineStr">
@@ -7386,7 +7366,7 @@
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>006</t>
+          <t>011</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
@@ -7396,7 +7376,7 @@
       </c>
       <c r="I84" t="inlineStr">
         <is>
-          <t>8448.20.5090</t>
+          <t>8477.90.8695</t>
         </is>
       </c>
       <c r="J84" t="inlineStr">
@@ -7469,7 +7449,7 @@
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>007</t>
+          <t>012</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
@@ -7479,7 +7459,7 @@
       </c>
       <c r="I85" t="inlineStr">
         <is>
-          <t>3402.90.5030</t>
+          <t>8448.32.0090</t>
         </is>
       </c>
       <c r="J85" t="inlineStr">
@@ -7509,12 +7489,12 @@
       </c>
       <c r="O85" t="inlineStr">
         <is>
-          <t>REIFENHAUSER REICOFIL GMBH &amp; CO. KG</t>
+          <t>HASTEM GMBH</t>
         </is>
       </c>
       <c r="P85" t="inlineStr">
         <is>
-          <t>REIFENHAUSER REICOFIL GMBH &amp; CO. KG</t>
+          <t>HASTEM GMBH</t>
         </is>
       </c>
       <c r="Q85" t="inlineStr">
@@ -7552,7 +7532,7 @@
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>008</t>
+          <t>013</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
@@ -7562,7 +7542,7 @@
       </c>
       <c r="I86" t="inlineStr">
         <is>
-          <t>8421.99.0180</t>
+          <t>8448.32.0090</t>
         </is>
       </c>
       <c r="J86" t="inlineStr">
@@ -7592,12 +7572,12 @@
       </c>
       <c r="O86" t="inlineStr">
         <is>
-          <t>REIFENHAUSER REICOFIL GMBH &amp; CO. KG</t>
+          <t>HASTEM GMBH</t>
         </is>
       </c>
       <c r="P86" t="inlineStr">
         <is>
-          <t>REIFENHAUSER REICOFIL GMBH &amp; CO. KG</t>
+          <t>HASTEM GMBH</t>
         </is>
       </c>
       <c r="Q86" t="inlineStr">
@@ -7635,7 +7615,7 @@
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>009</t>
+          <t>014</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
@@ -7645,7 +7625,7 @@
       </c>
       <c r="I87" t="inlineStr">
         <is>
-          <t>8421.99.0180</t>
+          <t>8453.90.5000</t>
         </is>
       </c>
       <c r="J87" t="inlineStr">
@@ -7675,12 +7655,12 @@
       </c>
       <c r="O87" t="inlineStr">
         <is>
-          <t>REIFENHAUSER REICOFIL GMBH &amp; CO. KG</t>
+          <t>BRUCKNER AFTER SALES GMBH</t>
         </is>
       </c>
       <c r="P87" t="inlineStr">
         <is>
-          <t>REIFENHAUSER REICOFIL GMBH &amp; CO. KG</t>
+          <t>BRUCKNER AFTER SALES GMBH</t>
         </is>
       </c>
       <c r="Q87" t="inlineStr">
@@ -7718,7 +7698,7 @@
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>010</t>
+          <t>015</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
@@ -7728,7 +7708,7 @@
       </c>
       <c r="I88" t="inlineStr">
         <is>
-          <t>5911.32.0080</t>
+          <t>8516.10.0080</t>
         </is>
       </c>
       <c r="J88" t="inlineStr">
@@ -7758,12 +7738,12 @@
       </c>
       <c r="O88" t="inlineStr">
         <is>
-          <t>REIFENHAUSER REICOFIL GMBH &amp; CO. KG</t>
+          <t>BRUCKNER AFTER SALES GMBH</t>
         </is>
       </c>
       <c r="P88" t="inlineStr">
         <is>
-          <t>REIFENHAUSER REICOFIL GMBH &amp; CO. KG</t>
+          <t>BRUCKNER AFTER SALES GMBH</t>
         </is>
       </c>
       <c r="Q88" t="inlineStr">
@@ -7801,7 +7781,7 @@
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>011</t>
+          <t>016</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
@@ -7811,7 +7791,7 @@
       </c>
       <c r="I89" t="inlineStr">
         <is>
-          <t>8477.90.8695</t>
+          <t>3403.99.0000</t>
         </is>
       </c>
       <c r="J89" t="inlineStr">
@@ -7841,12 +7821,12 @@
       </c>
       <c r="O89" t="inlineStr">
         <is>
-          <t>REIFENHAUSER REICOFIL GMBH &amp; CO. KG</t>
+          <t>BRUCKNER AFTER SALES GMBH</t>
         </is>
       </c>
       <c r="P89" t="inlineStr">
         <is>
-          <t>REIFENHAUSER REICOFIL GMBH &amp; CO. KG</t>
+          <t>BRUCKNER AFTER SALES GMBH</t>
         </is>
       </c>
       <c r="Q89" t="inlineStr">
@@ -7884,7 +7864,7 @@
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>012</t>
+          <t>017</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
@@ -7894,7 +7874,7 @@
       </c>
       <c r="I90" t="inlineStr">
         <is>
-          <t>8448.32.0090</t>
+          <t>8448.39.9000</t>
         </is>
       </c>
       <c r="J90" t="inlineStr">
@@ -7924,12 +7904,12 @@
       </c>
       <c r="O90" t="inlineStr">
         <is>
-          <t>HASTEM GMBH</t>
+          <t>ZENTES UNITEX GMBH</t>
         </is>
       </c>
       <c r="P90" t="inlineStr">
         <is>
-          <t>HASTEM GMBH</t>
+          <t>ZENTES UNITEX GMBH</t>
         </is>
       </c>
       <c r="Q90" t="inlineStr">
@@ -7967,7 +7947,7 @@
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>013</t>
+          <t>018</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
@@ -7977,7 +7957,7 @@
       </c>
       <c r="I91" t="inlineStr">
         <is>
-          <t>8448.32.0090</t>
+          <t>4811.49.3000</t>
         </is>
       </c>
       <c r="J91" t="inlineStr">
@@ -8007,12 +7987,12 @@
       </c>
       <c r="O91" t="inlineStr">
         <is>
-          <t>HASTEM GMBH</t>
+          <t>ZENTES UNITEX GMBH</t>
         </is>
       </c>
       <c r="P91" t="inlineStr">
         <is>
-          <t>HASTEM GMBH</t>
+          <t>ZENTES UNITEX GMBH</t>
         </is>
       </c>
       <c r="Q91" t="inlineStr">
@@ -8050,7 +8030,7 @@
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>014</t>
+          <t>019</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
@@ -8060,7 +8040,7 @@
       </c>
       <c r="I92" t="inlineStr">
         <is>
-          <t>8453.90.5000</t>
+          <t>4811.49.3000</t>
         </is>
       </c>
       <c r="J92" t="inlineStr">
@@ -8090,12 +8070,12 @@
       </c>
       <c r="O92" t="inlineStr">
         <is>
-          <t>BRUCKNER AFTER SALES GMBH</t>
+          <t>ZENTES UNITEX GMBH</t>
         </is>
       </c>
       <c r="P92" t="inlineStr">
         <is>
-          <t>BRUCKNER AFTER SALES GMBH</t>
+          <t>ZENTES UNITEX GMBH</t>
         </is>
       </c>
       <c r="Q92" t="inlineStr">
@@ -8107,12 +8087,12 @@
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>2566233</t>
+          <t>2565794</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>EF4-0232259-0</t>
+          <t>EF4-0232384-6</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
@@ -8120,45 +8100,49 @@
           <t>Vessel, Container</t>
         </is>
       </c>
-      <c r="D93" t="inlineStr"/>
+      <c r="D93" t="inlineStr">
+        <is>
+          <t>V0413916151</t>
+        </is>
+      </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>9903.03.01</t>
+          <t>9903.03.06</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>SECTION 122 - 10% DUTY</t>
+          <t>S122 EXCL,IRN/STL/ALUM,DERIV</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>015</t>
+          <t>001</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>9903.03.01</t>
+          <t>9903.03.06</t>
         </is>
       </c>
       <c r="I93" t="inlineStr">
         <is>
-          <t>8516.10.0080</t>
+          <t>9903.82.02,7223.00.1031</t>
         </is>
       </c>
       <c r="J93" t="inlineStr">
         <is>
-          <t>FI-TECH INC</t>
+          <t>VENUS WIRE INDUSTRIES PRIVATE LTD</t>
         </is>
       </c>
       <c r="K93" t="inlineStr">
         <is>
-          <t>FITINC</t>
+          <t>VENWIR</t>
         </is>
       </c>
       <c r="L93" t="inlineStr">
         <is>
-          <t>54-091465000</t>
+          <t>993901-03595</t>
         </is>
       </c>
       <c r="M93" t="inlineStr">
@@ -8173,29 +8157,29 @@
       </c>
       <c r="O93" t="inlineStr">
         <is>
-          <t>BRUCKNER AFTER SALES GMBH</t>
+          <t>VENUS WIRE INDUSTRIES PRIVATE LIMIT</t>
         </is>
       </c>
       <c r="P93" t="inlineStr">
         <is>
-          <t>BRUCKNER AFTER SALES GMBH</t>
+          <t>VENUS WIRE INDUSTRIES PRIVATE LIMITED</t>
         </is>
       </c>
       <c r="Q93" t="inlineStr">
         <is>
-          <t>2026-05-28 00:00:00</t>
+          <t>2026-05-05 00:00:00</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>2566233</t>
+          <t>2566107</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>EF4-0232259-0</t>
+          <t>EF4-0232386-1</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
@@ -8203,7 +8187,11 @@
           <t>Vessel, Container</t>
         </is>
       </c>
-      <c r="D94" t="inlineStr"/>
+      <c r="D94" t="inlineStr">
+        <is>
+          <t>V0413916151</t>
+        </is>
+      </c>
       <c r="E94" t="inlineStr">
         <is>
           <t>9903.03.01</t>
@@ -8216,7 +8204,7 @@
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>016</t>
+          <t>001</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
@@ -8226,22 +8214,22 @@
       </c>
       <c r="I94" t="inlineStr">
         <is>
-          <t>3403.99.0000</t>
+          <t>5503.40.0000</t>
         </is>
       </c>
       <c r="J94" t="inlineStr">
         <is>
-          <t>FI-TECH INC</t>
+          <t>FOOTING FIRST, LLC</t>
         </is>
       </c>
       <c r="K94" t="inlineStr">
         <is>
-          <t>FITINC</t>
+          <t>FOOFIR</t>
         </is>
       </c>
       <c r="L94" t="inlineStr">
         <is>
-          <t>54-091465000</t>
+          <t>27-059921300</t>
         </is>
       </c>
       <c r="M94" t="inlineStr">
@@ -8256,34 +8244,34 @@
       </c>
       <c r="O94" t="inlineStr">
         <is>
-          <t>BRUCKNER AFTER SALES GMBH</t>
+          <t>HAGELSON PLASTIK GERI DONUSUM VE NA</t>
         </is>
       </c>
       <c r="P94" t="inlineStr">
         <is>
-          <t>BRUCKNER AFTER SALES GMBH</t>
+          <t>HAGELSON PLASTIK GERI DONUSUM VE NAKLIYE SANAYI TICARET ANONIM SIRKETI</t>
         </is>
       </c>
       <c r="Q94" t="inlineStr">
         <is>
-          <t>2026-05-28 00:00:00</t>
+          <t>2026-05-25 00:00:00</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>2566233</t>
+          <t>4539413</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>EF4-0232259-0</t>
+          <t>EF4-0232400-0</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Vessel, Container</t>
+          <t>Air, Non-container</t>
         </is>
       </c>
       <c r="D95" t="inlineStr"/>
@@ -8299,7 +8287,7 @@
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>017</t>
+          <t>001</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
@@ -8309,22 +8297,22 @@
       </c>
       <c r="I95" t="inlineStr">
         <is>
-          <t>8448.39.9000</t>
+          <t>3405.20.0000</t>
         </is>
       </c>
       <c r="J95" t="inlineStr">
         <is>
-          <t>FI-TECH INC</t>
+          <t>COVE HOME LLC</t>
         </is>
       </c>
       <c r="K95" t="inlineStr">
         <is>
-          <t>FITINC</t>
+          <t>COVHOM01</t>
         </is>
       </c>
       <c r="L95" t="inlineStr">
         <is>
-          <t>54-091465000</t>
+          <t>30-136116600</t>
         </is>
       </c>
       <c r="M95" t="inlineStr">
@@ -8339,34 +8327,34 @@
       </c>
       <c r="O95" t="inlineStr">
         <is>
-          <t>ZENTES UNITEX GMBH</t>
+          <t>CV. PRASDA BALI UTMA</t>
         </is>
       </c>
       <c r="P95" t="inlineStr">
         <is>
-          <t>ZENTES UNITEX GMBH</t>
+          <t>CV. PRASDA BALI UTMA</t>
         </is>
       </c>
       <c r="Q95" t="inlineStr">
         <is>
-          <t>2026-05-28 00:00:00</t>
+          <t>2026-06-12 00:00:00</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>2566233</t>
+          <t>4539413</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>EF4-0232259-0</t>
+          <t>EF4-0232400-0</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Vessel, Container</t>
+          <t>Air, Non-container</t>
         </is>
       </c>
       <c r="D96" t="inlineStr"/>
@@ -8382,7 +8370,7 @@
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>018</t>
+          <t>002</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
@@ -8392,22 +8380,22 @@
       </c>
       <c r="I96" t="inlineStr">
         <is>
-          <t>4811.49.3000</t>
+          <t>4419.20.9000</t>
         </is>
       </c>
       <c r="J96" t="inlineStr">
         <is>
-          <t>FI-TECH INC</t>
+          <t>COVE HOME LLC</t>
         </is>
       </c>
       <c r="K96" t="inlineStr">
         <is>
-          <t>FITINC</t>
+          <t>COVHOM01</t>
         </is>
       </c>
       <c r="L96" t="inlineStr">
         <is>
-          <t>54-091465000</t>
+          <t>30-136116600</t>
         </is>
       </c>
       <c r="M96" t="inlineStr">
@@ -8422,34 +8410,34 @@
       </c>
       <c r="O96" t="inlineStr">
         <is>
-          <t>ZENTES UNITEX GMBH</t>
+          <t>CV. PRASDA BALI UTMA</t>
         </is>
       </c>
       <c r="P96" t="inlineStr">
         <is>
-          <t>ZENTES UNITEX GMBH</t>
+          <t>CV. PRASDA BALI UTMA</t>
         </is>
       </c>
       <c r="Q96" t="inlineStr">
         <is>
-          <t>2026-05-28 00:00:00</t>
+          <t>2026-06-12 00:00:00</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>2566233</t>
+          <t>4539413</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>EF4-0232259-0</t>
+          <t>EF4-0232400-0</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Vessel, Container</t>
+          <t>Air, Non-container</t>
         </is>
       </c>
       <c r="D97" t="inlineStr"/>
@@ -8465,7 +8453,7 @@
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>019</t>
+          <t>003</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
@@ -8475,22 +8463,22 @@
       </c>
       <c r="I97" t="inlineStr">
         <is>
-          <t>4811.49.3000</t>
+          <t>4202.22.1500</t>
         </is>
       </c>
       <c r="J97" t="inlineStr">
         <is>
-          <t>FI-TECH INC</t>
+          <t>COVE HOME LLC</t>
         </is>
       </c>
       <c r="K97" t="inlineStr">
         <is>
-          <t>FITINC</t>
+          <t>COVHOM01</t>
         </is>
       </c>
       <c r="L97" t="inlineStr">
         <is>
-          <t>54-091465000</t>
+          <t>30-136116600</t>
         </is>
       </c>
       <c r="M97" t="inlineStr">
@@ -8505,41 +8493,37 @@
       </c>
       <c r="O97" t="inlineStr">
         <is>
-          <t>ZENTES UNITEX GMBH</t>
+          <t>CV. PRASDA BALI UTMA</t>
         </is>
       </c>
       <c r="P97" t="inlineStr">
         <is>
-          <t>ZENTES UNITEX GMBH</t>
+          <t>CV. PRASDA BALI UTMA</t>
         </is>
       </c>
       <c r="Q97" t="inlineStr">
         <is>
-          <t>2026-05-28 00:00:00</t>
+          <t>2026-06-12 00:00:00</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>2565794</t>
+          <t>2565751</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>EF4-0232384-6</t>
+          <t>EF4-0231790-5</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Vessel, Container</t>
-        </is>
-      </c>
-      <c r="D98" t="inlineStr">
-        <is>
-          <t>V0413916151</t>
-        </is>
-      </c>
+          <t>Vessel, Non-container</t>
+        </is>
+      </c>
+      <c r="D98" t="inlineStr"/>
       <c r="E98" t="inlineStr">
         <is>
           <t>9903.03.06</t>
@@ -8562,59 +8546,59 @@
       </c>
       <c r="I98" t="inlineStr">
         <is>
-          <t>9903.82.02,7223.00.1031</t>
+          <t>9903.82.10,8428.33.0000</t>
         </is>
       </c>
       <c r="J98" t="inlineStr">
         <is>
-          <t>VENUS WIRE INDUSTRIES PRIVATE LTD</t>
+          <t>AUMUND CORPORATION</t>
         </is>
       </c>
       <c r="K98" t="inlineStr">
         <is>
-          <t>VENWIR</t>
+          <t>AUMCOR</t>
         </is>
       </c>
       <c r="L98" t="inlineStr">
         <is>
-          <t>993901-03595</t>
+          <t>58-138896800</t>
         </is>
       </c>
       <c r="M98" t="inlineStr">
         <is>
-          <t>2026-06-12 00:00:00</t>
+          <t>2026-06-13 00:00:00</t>
         </is>
       </c>
       <c r="N98" t="inlineStr">
         <is>
-          <t>2026-06-12 00:00:00</t>
+          <t>2026-06-13 00:00:00</t>
         </is>
       </c>
       <c r="O98" t="inlineStr">
         <is>
-          <t>VENUS WIRE INDUSTRIES PRIVATE LIMIT</t>
+          <t>AUMUND FOERDERTECHNIK GMBH</t>
         </is>
       </c>
       <c r="P98" t="inlineStr">
         <is>
-          <t>VENUS WIRE INDUSTRIES PRIVATE LIMITED</t>
+          <t>AUMUND FOERDERTECHNIK GMBH</t>
         </is>
       </c>
       <c r="Q98" t="inlineStr">
         <is>
-          <t>2026-05-05 00:00:00</t>
+          <t>2026-05-11 00:00:00</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>2566107</t>
+          <t>2565927</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>EF4-0232386-1</t>
+          <t>EF4-0231897-8</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
@@ -8622,11 +8606,7 @@
           <t>Vessel, Container</t>
         </is>
       </c>
-      <c r="D99" t="inlineStr">
-        <is>
-          <t>V0413916151</t>
-        </is>
-      </c>
+      <c r="D99" t="inlineStr"/>
       <c r="E99" t="inlineStr">
         <is>
           <t>9903.03.01</t>
@@ -8649,64 +8629,64 @@
       </c>
       <c r="I99" t="inlineStr">
         <is>
-          <t>5503.40.0000</t>
+          <t>3920.62.0090</t>
         </is>
       </c>
       <c r="J99" t="inlineStr">
         <is>
-          <t>FOOTING FIRST, LLC</t>
+          <t>GULF ATLANTIC PACKAGING CORP</t>
         </is>
       </c>
       <c r="K99" t="inlineStr">
         <is>
-          <t>FOOFIR</t>
+          <t>GULATL</t>
         </is>
       </c>
       <c r="L99" t="inlineStr">
         <is>
-          <t>27-059921300</t>
+          <t>58-184378700</t>
         </is>
       </c>
       <c r="M99" t="inlineStr">
         <is>
-          <t>2026-06-12 00:00:00</t>
+          <t>2026-06-14 00:00:00</t>
         </is>
       </c>
       <c r="N99" t="inlineStr">
         <is>
-          <t>2026-06-12 00:00:00</t>
+          <t>2026-06-13 00:00:00</t>
         </is>
       </c>
       <c r="O99" t="inlineStr">
         <is>
-          <t>HAGELSON PLASTIK GERI DONUSUM VE NA</t>
+          <t>CONSENT FZCO</t>
         </is>
       </c>
       <c r="P99" t="inlineStr">
         <is>
-          <t>HAGELSON PLASTIK GERI DONUSUM VE NAKLIYE SANAYI TICARET ANONIM SIRKETI</t>
+          <t>CONSENT FZCO</t>
         </is>
       </c>
       <c r="Q99" t="inlineStr">
         <is>
-          <t>2026-05-25 00:00:00</t>
+          <t>2026-05-16 00:00:00</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>4539413</t>
+          <t>2566010</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>EF4-0232400-0</t>
+          <t>EF4-0231962-0</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Air, Non-container</t>
+          <t>Vessel, Container</t>
         </is>
       </c>
       <c r="D100" t="inlineStr"/>
@@ -8715,11 +8695,7 @@
           <t>9903.03.01</t>
         </is>
       </c>
-      <c r="F100" t="inlineStr">
-        <is>
-          <t>SECTION 122 - 10% DUTY</t>
-        </is>
-      </c>
+      <c r="F100" t="inlineStr"/>
       <c r="G100" t="inlineStr">
         <is>
           <t>001</t>
@@ -8732,67 +8708,71 @@
       </c>
       <c r="I100" t="inlineStr">
         <is>
-          <t>3405.20.0000</t>
+          <t>1108.13.0010</t>
         </is>
       </c>
       <c r="J100" t="inlineStr">
         <is>
-          <t>COVE HOME LLC</t>
+          <t>ROYAL INGREDIENTS GROUP BV</t>
         </is>
       </c>
       <c r="K100" t="inlineStr">
         <is>
-          <t>COVHOM01</t>
+          <t>ROYINGRE</t>
         </is>
       </c>
       <c r="L100" t="inlineStr">
         <is>
-          <t>30-136116600</t>
+          <t>074601-00962</t>
         </is>
       </c>
       <c r="M100" t="inlineStr">
         <is>
-          <t>2026-06-12 00:00:00</t>
+          <t>2026-06-14 00:00:00</t>
         </is>
       </c>
       <c r="N100" t="inlineStr">
         <is>
-          <t>2026-06-12 00:00:00</t>
+          <t>2026-06-13 00:00:00</t>
         </is>
       </c>
       <c r="O100" t="inlineStr">
         <is>
-          <t>CV. PRASDA BALI UTMA</t>
+          <t>PRZEDSIEBIORSTWO PRZEMYSLU ZIEMNIAC</t>
         </is>
       </c>
       <c r="P100" t="inlineStr">
         <is>
-          <t>CV. PRASDA BALI UTMA</t>
+          <t>PRZEDSIEBIORSTWO PRZEMYSLU ZIEMNIACZANEGO PEPEES S.A.</t>
         </is>
       </c>
       <c r="Q100" t="inlineStr">
         <is>
-          <t>2026-06-12 00:00:00</t>
+          <t>2026-05-17 00:00:00</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>4539413</t>
+          <t>2565855</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>EF4-0232400-0</t>
+          <t>EF4-0232059-4</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Air, Non-container</t>
-        </is>
-      </c>
-      <c r="D101" t="inlineStr"/>
+          <t>Vessel, Container</t>
+        </is>
+      </c>
+      <c r="D101" t="inlineStr">
+        <is>
+          <t>V1626451887</t>
+        </is>
+      </c>
       <c r="E101" t="inlineStr">
         <is>
           <t>9903.03.01</t>
@@ -8805,7 +8785,7 @@
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>002</t>
+          <t>001</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
@@ -8815,80 +8795,80 @@
       </c>
       <c r="I101" t="inlineStr">
         <is>
-          <t>4419.20.9000</t>
+          <t>1108.13.0010</t>
         </is>
       </c>
       <c r="J101" t="inlineStr">
         <is>
-          <t>COVE HOME LLC</t>
+          <t>ROYAL INGREDIENTS GROUP BV</t>
         </is>
       </c>
       <c r="K101" t="inlineStr">
         <is>
-          <t>COVHOM01</t>
+          <t>ROYINGRE</t>
         </is>
       </c>
       <c r="L101" t="inlineStr">
         <is>
-          <t>30-136116600</t>
+          <t>074601-00962</t>
         </is>
       </c>
       <c r="M101" t="inlineStr">
         <is>
-          <t>2026-06-12 00:00:00</t>
+          <t>2026-06-02 00:00:00</t>
         </is>
       </c>
       <c r="N101" t="inlineStr">
         <is>
-          <t>2026-06-12 00:00:00</t>
+          <t>2026-06-13 00:00:00</t>
         </is>
       </c>
       <c r="O101" t="inlineStr">
         <is>
-          <t>CV. PRASDA BALI UTMA</t>
+          <t>AKV LANGHOLT AMBA</t>
         </is>
       </c>
       <c r="P101" t="inlineStr">
         <is>
-          <t>CV. PRASDA BALI UTMA</t>
+          <t>AKV LANGHOLT AMBA</t>
         </is>
       </c>
       <c r="Q101" t="inlineStr">
         <is>
-          <t>2026-06-12 00:00:00</t>
+          <t>2026-05-08 00:00:00</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>4539413</t>
+          <t>2566011</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>EF4-0232400-0</t>
+          <t>EF4-0232062-8</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Air, Non-container</t>
-        </is>
-      </c>
-      <c r="D102" t="inlineStr"/>
+          <t>Vessel, Container</t>
+        </is>
+      </c>
+      <c r="D102" t="inlineStr">
+        <is>
+          <t>V1626451887</t>
+        </is>
+      </c>
       <c r="E102" t="inlineStr">
         <is>
           <t>9903.03.01</t>
         </is>
       </c>
-      <c r="F102" t="inlineStr">
-        <is>
-          <t>SECTION 122 - 10% DUTY</t>
-        </is>
-      </c>
+      <c r="F102" t="inlineStr"/>
       <c r="G102" t="inlineStr">
         <is>
-          <t>003</t>
+          <t>001</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
@@ -8898,59 +8878,59 @@
       </c>
       <c r="I102" t="inlineStr">
         <is>
-          <t>4202.22.1500</t>
+          <t>1108.13.0010</t>
         </is>
       </c>
       <c r="J102" t="inlineStr">
         <is>
-          <t>COVE HOME LLC</t>
+          <t>ROYAL INGREDIENTS GROUP BV</t>
         </is>
       </c>
       <c r="K102" t="inlineStr">
         <is>
-          <t>COVHOM01</t>
+          <t>ROYINGRE</t>
         </is>
       </c>
       <c r="L102" t="inlineStr">
         <is>
-          <t>30-136116600</t>
+          <t>074601-00962</t>
         </is>
       </c>
       <c r="M102" t="inlineStr">
         <is>
-          <t>2026-06-12 00:00:00</t>
+          <t>2026-06-14 00:00:00</t>
         </is>
       </c>
       <c r="N102" t="inlineStr">
         <is>
-          <t>2026-06-12 00:00:00</t>
+          <t>2026-06-13 00:00:00</t>
         </is>
       </c>
       <c r="O102" t="inlineStr">
         <is>
-          <t>CV. PRASDA BALI UTMA</t>
+          <t>PRZEDSIEBIORSTWO PRZEMYSLU ZIEMNIAC</t>
         </is>
       </c>
       <c r="P102" t="inlineStr">
         <is>
-          <t>CV. PRASDA BALI UTMA</t>
+          <t>PRZEDSIEBIORSTWO PRZEMYSLU ZIEMNIACZANEGO PEPEES S.A.</t>
         </is>
       </c>
       <c r="Q102" t="inlineStr">
         <is>
-          <t>2026-06-12 00:00:00</t>
+          <t>2026-05-20 00:00:00</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>2565751</t>
+          <t>105504734</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>EF4-0231790-5</t>
+          <t>EF4-0232081-8</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
@@ -8961,12 +8941,12 @@
       <c r="D103" t="inlineStr"/>
       <c r="E103" t="inlineStr">
         <is>
-          <t>9903.03.06</t>
+          <t>9805.00.50</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>S122 EXCL,IRN/STL/ALUM,DERIV</t>
+          <t>EFFECTS US GOV EMP&amp;FAMLY/EVACU</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
@@ -8976,27 +8956,23 @@
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>9903.03.06</t>
-        </is>
-      </c>
-      <c r="I103" t="inlineStr">
-        <is>
-          <t>9903.82.10,8428.33.0000</t>
-        </is>
-      </c>
+          <t>9805.00.50</t>
+        </is>
+      </c>
+      <c r="I103" t="inlineStr"/>
       <c r="J103" t="inlineStr">
         <is>
-          <t>AUMUND CORPORATION</t>
+          <t>IFF, INC.</t>
         </is>
       </c>
       <c r="K103" t="inlineStr">
         <is>
-          <t>AUMCOR</t>
+          <t>10</t>
         </is>
       </c>
       <c r="L103" t="inlineStr">
         <is>
-          <t>58-138896800</t>
+          <t>58-149385700</t>
         </is>
       </c>
       <c r="M103" t="inlineStr">
@@ -9011,45 +8987,45 @@
       </c>
       <c r="O103" t="inlineStr">
         <is>
-          <t>AUMUND FOERDERTECHNIK GMBH</t>
+          <t>VOLVO CAR INTERNATIONAL CORPORATION</t>
         </is>
       </c>
       <c r="P103" t="inlineStr">
         <is>
-          <t>AUMUND FOERDERTECHNIK GMBH</t>
+          <t>VOLVO CAR INTERNATIONAL CORPORATION</t>
         </is>
       </c>
       <c r="Q103" t="inlineStr">
         <is>
-          <t>2026-05-11 00:00:00</t>
+          <t>2026-05-26 00:00:00</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>2565927</t>
+          <t>105504735</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>EF4-0231897-8</t>
+          <t>EF4-0232084-2</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Vessel, Container</t>
+          <t>Vessel, Non-container</t>
         </is>
       </c>
       <c r="D104" t="inlineStr"/>
       <c r="E104" t="inlineStr">
         <is>
-          <t>9903.03.01</t>
+          <t>9805.00.50</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>SECTION 122 - 10% DUTY</t>
+          <t>EFFECTS US GOV EMP&amp;FAMLY/EVACU</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
@@ -9059,32 +9035,28 @@
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>9903.03.01</t>
-        </is>
-      </c>
-      <c r="I104" t="inlineStr">
-        <is>
-          <t>3920.62.0090</t>
-        </is>
-      </c>
+          <t>9805.00.50</t>
+        </is>
+      </c>
+      <c r="I104" t="inlineStr"/>
       <c r="J104" t="inlineStr">
         <is>
-          <t>GULF ATLANTIC PACKAGING CORP</t>
+          <t>IFF, INC.</t>
         </is>
       </c>
       <c r="K104" t="inlineStr">
         <is>
-          <t>GULATL</t>
+          <t>10</t>
         </is>
       </c>
       <c r="L104" t="inlineStr">
         <is>
-          <t>58-184378700</t>
+          <t>58-149385700</t>
         </is>
       </c>
       <c r="M104" t="inlineStr">
         <is>
-          <t>2026-06-14 00:00:00</t>
+          <t>2026-06-13 00:00:00</t>
         </is>
       </c>
       <c r="N104" t="inlineStr">
@@ -9094,43 +9066,47 @@
       </c>
       <c r="O104" t="inlineStr">
         <is>
-          <t>CONSENT FZCO</t>
+          <t>VOLVO CAR INTERNATIONAL CORPORATION</t>
         </is>
       </c>
       <c r="P104" t="inlineStr">
         <is>
-          <t>CONSENT FZCO</t>
+          <t>VOLVO CAR INTERNATIONAL CORPORATION</t>
         </is>
       </c>
       <c r="Q104" t="inlineStr">
         <is>
-          <t>2026-05-16 00:00:00</t>
+          <t>2026-05-26 00:00:00</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>2566010</t>
+          <t>105504736</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>EF4-0231962-0</t>
+          <t>EF4-0232087-5</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Vessel, Container</t>
+          <t>Vessel, Non-container</t>
         </is>
       </c>
       <c r="D105" t="inlineStr"/>
       <c r="E105" t="inlineStr">
         <is>
-          <t>9903.03.01</t>
-        </is>
-      </c>
-      <c r="F105" t="inlineStr"/>
+          <t>9805.00.50</t>
+        </is>
+      </c>
+      <c r="F105" t="inlineStr">
+        <is>
+          <t>EFFECTS US GOV EMP&amp;FAMLY/EVACU</t>
+        </is>
+      </c>
       <c r="G105" t="inlineStr">
         <is>
           <t>001</t>
@@ -9138,32 +9114,28 @@
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>9903.03.01</t>
-        </is>
-      </c>
-      <c r="I105" t="inlineStr">
-        <is>
-          <t>1108.13.0010</t>
-        </is>
-      </c>
+          <t>9805.00.50</t>
+        </is>
+      </c>
+      <c r="I105" t="inlineStr"/>
       <c r="J105" t="inlineStr">
         <is>
-          <t>ROYAL INGREDIENTS GROUP BV</t>
+          <t>IFF, INC.</t>
         </is>
       </c>
       <c r="K105" t="inlineStr">
         <is>
-          <t>ROYINGRE</t>
+          <t>10</t>
         </is>
       </c>
       <c r="L105" t="inlineStr">
         <is>
-          <t>074601-00962</t>
+          <t>58-149385700</t>
         </is>
       </c>
       <c r="M105" t="inlineStr">
         <is>
-          <t>2026-06-14 00:00:00</t>
+          <t>2026-06-13 00:00:00</t>
         </is>
       </c>
       <c r="N105" t="inlineStr">
@@ -9173,29 +9145,29 @@
       </c>
       <c r="O105" t="inlineStr">
         <is>
-          <t>PRZEDSIEBIORSTWO PRZEMYSLU ZIEMNIAC</t>
+          <t>VOLVO CAR INTERNATIONAL CORPORATION</t>
         </is>
       </c>
       <c r="P105" t="inlineStr">
         <is>
-          <t>PRZEDSIEBIORSTWO PRZEMYSLU ZIEMNIACZANEGO PEPEES S.A.</t>
+          <t>VOLVO CAR INTERNATIONAL CORPORATION</t>
         </is>
       </c>
       <c r="Q105" t="inlineStr">
         <is>
-          <t>2026-05-17 00:00:00</t>
+          <t>2026-05-26 00:00:00</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>2565855</t>
+          <t>2565712</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>EF4-0232059-4</t>
+          <t>EF4-0232088-3</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
@@ -9203,19 +9175,15 @@
           <t>Vessel, Container</t>
         </is>
       </c>
-      <c r="D106" t="inlineStr">
-        <is>
-          <t>V1626451887</t>
-        </is>
-      </c>
+      <c r="D106" t="inlineStr"/>
       <c r="E106" t="inlineStr">
         <is>
-          <t>9903.03.01</t>
+          <t>9903.03.06</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>SECTION 122 - 10% DUTY</t>
+          <t>S122 EXCL,IRN/STL/ALUM,DERIV</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
@@ -9225,32 +9193,32 @@
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>9903.03.01</t>
+          <t>9903.03.06</t>
         </is>
       </c>
       <c r="I106" t="inlineStr">
         <is>
-          <t>1108.13.0010</t>
+          <t>9903.82.09,9403.20.0075</t>
         </is>
       </c>
       <c r="J106" t="inlineStr">
         <is>
-          <t>ROYAL INGREDIENTS GROUP BV</t>
+          <t>VISUAL CREATIONS, INC.</t>
         </is>
       </c>
       <c r="K106" t="inlineStr">
         <is>
-          <t>ROYINGRE</t>
+          <t>VISCRE</t>
         </is>
       </c>
       <c r="L106" t="inlineStr">
         <is>
-          <t>074601-00962</t>
+          <t>20-461602300</t>
         </is>
       </c>
       <c r="M106" t="inlineStr">
         <is>
-          <t>2026-06-02 00:00:00</t>
+          <t>2026-06-14 00:00:00</t>
         </is>
       </c>
       <c r="N106" t="inlineStr">
@@ -9260,29 +9228,29 @@
       </c>
       <c r="O106" t="inlineStr">
         <is>
-          <t>AKV LANGHOLT AMBA</t>
+          <t>VIET MOI INDUSTRIAL COMPANY LIMITED</t>
         </is>
       </c>
       <c r="P106" t="inlineStr">
         <is>
-          <t>AKV LANGHOLT AMBA</t>
+          <t>VIET MOI INDUSTRIAL COMPANY LIMITED</t>
         </is>
       </c>
       <c r="Q106" t="inlineStr">
         <is>
-          <t>2026-05-08 00:00:00</t>
+          <t>2026-05-01 00:00:00</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>2566011</t>
+          <t>2565712</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>EF4-0232062-8</t>
+          <t>EF4-0232088-3</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
@@ -9290,20 +9258,20 @@
           <t>Vessel, Container</t>
         </is>
       </c>
-      <c r="D107" t="inlineStr">
-        <is>
-          <t>V1626451887</t>
-        </is>
-      </c>
+      <c r="D107" t="inlineStr"/>
       <c r="E107" t="inlineStr">
         <is>
           <t>9903.03.01</t>
         </is>
       </c>
-      <c r="F107" t="inlineStr"/>
+      <c r="F107" t="inlineStr">
+        <is>
+          <t>SECTION 122 - 10% DUTY</t>
+        </is>
+      </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>001</t>
+          <t>002</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
@@ -9313,22 +9281,22 @@
       </c>
       <c r="I107" t="inlineStr">
         <is>
-          <t>1108.13.0010</t>
+          <t>9903.76.04,9403.60.8093</t>
         </is>
       </c>
       <c r="J107" t="inlineStr">
         <is>
-          <t>ROYAL INGREDIENTS GROUP BV</t>
+          <t>VISUAL CREATIONS, INC.</t>
         </is>
       </c>
       <c r="K107" t="inlineStr">
         <is>
-          <t>ROYINGRE</t>
+          <t>VISCRE</t>
         </is>
       </c>
       <c r="L107" t="inlineStr">
         <is>
-          <t>074601-00962</t>
+          <t>20-461602300</t>
         </is>
       </c>
       <c r="M107" t="inlineStr">
@@ -9343,29 +9311,29 @@
       </c>
       <c r="O107" t="inlineStr">
         <is>
-          <t>PRZEDSIEBIORSTWO PRZEMYSLU ZIEMNIAC</t>
+          <t>VIET MOI INDUSTRIAL COMPANY LIMITED</t>
         </is>
       </c>
       <c r="P107" t="inlineStr">
         <is>
-          <t>PRZEDSIEBIORSTWO PRZEMYSLU ZIEMNIACZANEGO PEPEES S.A.</t>
+          <t>VIET MOI INDUSTRIAL COMPANY LIMITED</t>
         </is>
       </c>
       <c r="Q107" t="inlineStr">
         <is>
-          <t>2026-05-20 00:00:00</t>
+          <t>2026-05-01 00:00:00</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>2566028</t>
+          <t>2565712</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>EF4-0232065-1</t>
+          <t>EF4-0232088-3</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
@@ -9373,20 +9341,20 @@
           <t>Vessel, Container</t>
         </is>
       </c>
-      <c r="D108" t="inlineStr">
-        <is>
-          <t>V0710334942</t>
-        </is>
-      </c>
+      <c r="D108" t="inlineStr"/>
       <c r="E108" t="inlineStr">
         <is>
           <t>9903.03.01</t>
         </is>
       </c>
-      <c r="F108" t="inlineStr"/>
+      <c r="F108" t="inlineStr">
+        <is>
+          <t>SECTION 122 - 10% DUTY</t>
+        </is>
+      </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>001</t>
+          <t>003</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
@@ -9396,22 +9364,22 @@
       </c>
       <c r="I108" t="inlineStr">
         <is>
-          <t>1108.12.0010</t>
+          <t>9403.99.9045</t>
         </is>
       </c>
       <c r="J108" t="inlineStr">
         <is>
-          <t>ROYAL INGREDIENTS GROUP BV</t>
+          <t>VISUAL CREATIONS, INC.</t>
         </is>
       </c>
       <c r="K108" t="inlineStr">
         <is>
-          <t>ROYINGRE</t>
+          <t>VISCRE</t>
         </is>
       </c>
       <c r="L108" t="inlineStr">
         <is>
-          <t>074601-00962</t>
+          <t>20-461602300</t>
         </is>
       </c>
       <c r="M108" t="inlineStr">
@@ -9426,108 +9394,112 @@
       </c>
       <c r="O108" t="inlineStr">
         <is>
-          <t>TAT NISASTA INS SAN TIC AS</t>
+          <t>VIET MOI INDUSTRIAL COMPANY LIMITED</t>
         </is>
       </c>
       <c r="P108" t="inlineStr">
         <is>
-          <t>TAT NISASTA INS SAN TIC AS</t>
+          <t>VIET MOI INDUSTRIAL COMPANY LIMITED</t>
         </is>
       </c>
       <c r="Q108" t="inlineStr">
         <is>
-          <t>2026-05-23 00:00:00</t>
+          <t>2026-05-01 00:00:00</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>105504734</t>
+          <t>2565712</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>EF4-0232081-8</t>
+          <t>EF4-0232088-3</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>Vessel, Non-container</t>
+          <t>Vessel, Container</t>
         </is>
       </c>
       <c r="D109" t="inlineStr"/>
       <c r="E109" t="inlineStr">
         <is>
-          <t>9805.00.50</t>
+          <t>9903.03.01</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>EFFECTS US GOV EMP&amp;FAMLY/EVACU</t>
+          <t>SECTION 122 - 10% DUTY</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>001</t>
+          <t>004</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>9805.00.50</t>
-        </is>
-      </c>
-      <c r="I109" t="inlineStr"/>
+          <t>9903.03.01</t>
+        </is>
+      </c>
+      <c r="I109" t="inlineStr">
+        <is>
+          <t>3926.90.9989</t>
+        </is>
+      </c>
       <c r="J109" t="inlineStr">
         <is>
-          <t>IFF, INC.</t>
+          <t>VISUAL CREATIONS, INC.</t>
         </is>
       </c>
       <c r="K109" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>VISCRE</t>
         </is>
       </c>
       <c r="L109" t="inlineStr">
         <is>
-          <t>58-149385700</t>
+          <t>20-461602300</t>
         </is>
       </c>
       <c r="M109" t="inlineStr">
         <is>
+          <t>2026-06-14 00:00:00</t>
+        </is>
+      </c>
+      <c r="N109" t="inlineStr">
+        <is>
           <t>2026-06-13 00:00:00</t>
         </is>
       </c>
-      <c r="N109" t="inlineStr">
-        <is>
-          <t>2026-06-13 00:00:00</t>
-        </is>
-      </c>
       <c r="O109" t="inlineStr">
         <is>
-          <t>VOLVO CAR INTERNATIONAL CORPORATION</t>
+          <t>VIET MOI INDUSTRIAL COMPANY LIMITED</t>
         </is>
       </c>
       <c r="P109" t="inlineStr">
         <is>
-          <t>VOLVO CAR INTERNATIONAL CORPORATION</t>
+          <t>VIET MOI INDUSTRIAL COMPANY LIMITED</t>
         </is>
       </c>
       <c r="Q109" t="inlineStr">
         <is>
-          <t>2026-05-26 00:00:00</t>
+          <t>2026-05-01 00:00:00</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>105504735</t>
+          <t>105504738</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>EF4-0232084-2</t>
+          <t>EF4-0232095-8</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
@@ -9601,12 +9573,12 @@
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>105504736</t>
+          <t>105504739</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>EF4-0232087-5</t>
+          <t>EF4-0232096-6</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
@@ -9680,28 +9652,28 @@
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>2565712</t>
+          <t>105504740</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>EF4-0232088-3</t>
+          <t>EF4-0232098-2</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>Vessel, Container</t>
+          <t>Vessel, Non-container</t>
         </is>
       </c>
       <c r="D112" t="inlineStr"/>
       <c r="E112" t="inlineStr">
         <is>
-          <t>9903.03.06</t>
+          <t>9805.00.50</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>S122 EXCL,IRN/STL/ALUM,DERIV</t>
+          <t>EFFECTS US GOV EMP&amp;FAMLY/EVACU</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
@@ -9711,32 +9683,28 @@
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>9903.03.06</t>
-        </is>
-      </c>
-      <c r="I112" t="inlineStr">
-        <is>
-          <t>9903.82.09,9403.20.0075</t>
-        </is>
-      </c>
+          <t>9805.00.50</t>
+        </is>
+      </c>
+      <c r="I112" t="inlineStr"/>
       <c r="J112" t="inlineStr">
         <is>
-          <t>VISUAL CREATIONS, INC.</t>
+          <t>IFF, INC.</t>
         </is>
       </c>
       <c r="K112" t="inlineStr">
         <is>
-          <t>VISCRE</t>
+          <t>10</t>
         </is>
       </c>
       <c r="L112" t="inlineStr">
         <is>
-          <t>20-461602300</t>
+          <t>58-149385700</t>
         </is>
       </c>
       <c r="M112" t="inlineStr">
         <is>
-          <t>2026-06-14 00:00:00</t>
+          <t>2026-06-13 00:00:00</t>
         </is>
       </c>
       <c r="N112" t="inlineStr">
@@ -9746,80 +9714,76 @@
       </c>
       <c r="O112" t="inlineStr">
         <is>
-          <t>VIET MOI INDUSTRIAL COMPANY LIMITED</t>
+          <t>VOLVO CAR INTERNATIONAL CORPORATION</t>
         </is>
       </c>
       <c r="P112" t="inlineStr">
         <is>
-          <t>VIET MOI INDUSTRIAL COMPANY LIMITED</t>
+          <t>VOLVO CAR INTERNATIONAL CORPORATION</t>
         </is>
       </c>
       <c r="Q112" t="inlineStr">
         <is>
-          <t>2026-05-01 00:00:00</t>
+          <t>2026-05-26 00:00:00</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>2565712</t>
+          <t>105504741</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>EF4-0232088-3</t>
+          <t>EF4-0232100-6</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>Vessel, Container</t>
+          <t>Vessel, Non-container</t>
         </is>
       </c>
       <c r="D113" t="inlineStr"/>
       <c r="E113" t="inlineStr">
         <is>
-          <t>9903.03.01</t>
+          <t>9805.00.50</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>SECTION 122 - 10% DUTY</t>
+          <t>EFFECTS US GOV EMP&amp;FAMLY/EVACU</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>002</t>
+          <t>001</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>9903.03.01</t>
-        </is>
-      </c>
-      <c r="I113" t="inlineStr">
-        <is>
-          <t>9903.76.04,9403.60.8093</t>
-        </is>
-      </c>
+          <t>9805.00.50</t>
+        </is>
+      </c>
+      <c r="I113" t="inlineStr"/>
       <c r="J113" t="inlineStr">
         <is>
-          <t>VISUAL CREATIONS, INC.</t>
+          <t>IFF, INC.</t>
         </is>
       </c>
       <c r="K113" t="inlineStr">
         <is>
-          <t>VISCRE</t>
+          <t>10</t>
         </is>
       </c>
       <c r="L113" t="inlineStr">
         <is>
-          <t>20-461602300</t>
+          <t>58-149385700</t>
         </is>
       </c>
       <c r="M113" t="inlineStr">
         <is>
-          <t>2026-06-14 00:00:00</t>
+          <t>2026-06-13 00:00:00</t>
         </is>
       </c>
       <c r="N113" t="inlineStr">
@@ -9829,80 +9793,76 @@
       </c>
       <c r="O113" t="inlineStr">
         <is>
-          <t>VIET MOI INDUSTRIAL COMPANY LIMITED</t>
+          <t>VOLVO CAR INTERNATIONAL CORPORATION</t>
         </is>
       </c>
       <c r="P113" t="inlineStr">
         <is>
-          <t>VIET MOI INDUSTRIAL COMPANY LIMITED</t>
+          <t>VOLVO CAR INTERNATIONAL CORPORATION</t>
         </is>
       </c>
       <c r="Q113" t="inlineStr">
         <is>
-          <t>2026-05-01 00:00:00</t>
+          <t>2026-05-26 00:00:00</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>2565712</t>
+          <t>105504747</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>EF4-0232088-3</t>
+          <t>EF4-0232107-1</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>Vessel, Container</t>
+          <t>Vessel, Non-container</t>
         </is>
       </c>
       <c r="D114" t="inlineStr"/>
       <c r="E114" t="inlineStr">
         <is>
-          <t>9903.03.01</t>
+          <t>9805.00.50</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>SECTION 122 - 10% DUTY</t>
+          <t>EFFECTS US GOV EMP&amp;FAMLY/EVACU</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>003</t>
+          <t>001</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>9903.03.01</t>
-        </is>
-      </c>
-      <c r="I114" t="inlineStr">
-        <is>
-          <t>9403.99.9045</t>
-        </is>
-      </c>
+          <t>9805.00.50</t>
+        </is>
+      </c>
+      <c r="I114" t="inlineStr"/>
       <c r="J114" t="inlineStr">
         <is>
-          <t>VISUAL CREATIONS, INC.</t>
+          <t>IFF, INC.</t>
         </is>
       </c>
       <c r="K114" t="inlineStr">
         <is>
-          <t>VISCRE</t>
+          <t>10</t>
         </is>
       </c>
       <c r="L114" t="inlineStr">
         <is>
-          <t>20-461602300</t>
+          <t>58-149385700</t>
         </is>
       </c>
       <c r="M114" t="inlineStr">
         <is>
-          <t>2026-06-14 00:00:00</t>
+          <t>2026-06-13 00:00:00</t>
         </is>
       </c>
       <c r="N114" t="inlineStr">
@@ -9912,29 +9872,29 @@
       </c>
       <c r="O114" t="inlineStr">
         <is>
-          <t>VIET MOI INDUSTRIAL COMPANY LIMITED</t>
+          <t>VOLVO CAR INTERNATIONAL CORPORATION</t>
         </is>
       </c>
       <c r="P114" t="inlineStr">
         <is>
-          <t>VIET MOI INDUSTRIAL COMPANY LIMITED</t>
+          <t>VOLVO CAR INTERNATIONAL CORPORATION</t>
         </is>
       </c>
       <c r="Q114" t="inlineStr">
         <is>
-          <t>2026-05-01 00:00:00</t>
+          <t>2026-05-28 00:00:00</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>2565712</t>
+          <t>2565958</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>EF4-0232088-3</t>
+          <t>EF4-0232210-3</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
@@ -9942,50 +9902,54 @@
           <t>Vessel, Container</t>
         </is>
       </c>
-      <c r="D115" t="inlineStr"/>
+      <c r="D115" t="inlineStr">
+        <is>
+          <t>V1626459831</t>
+        </is>
+      </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>9903.03.01</t>
+          <t>9903.03.06</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>SECTION 122 - 10% DUTY</t>
+          <t>S122 EXCL,IRN/STL/ALUM,DERIV</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>004</t>
+          <t>001</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>9903.03.01</t>
+          <t>9903.03.06</t>
         </is>
       </c>
       <c r="I115" t="inlineStr">
         <is>
-          <t>3926.90.9989</t>
+          <t>9903.74.11,9903.94.53,8708.29.5160</t>
         </is>
       </c>
       <c r="J115" t="inlineStr">
         <is>
-          <t>VISUAL CREATIONS, INC.</t>
+          <t>BORGERS OHIO INC.</t>
         </is>
       </c>
       <c r="K115" t="inlineStr">
         <is>
-          <t>VISCRE</t>
+          <t>BORUSA02</t>
         </is>
       </c>
       <c r="L115" t="inlineStr">
         <is>
-          <t>20-461602300</t>
+          <t>30-084196200</t>
         </is>
       </c>
       <c r="M115" t="inlineStr">
         <is>
-          <t>2026-06-14 00:00:00</t>
+          <t>2026-06-15 00:00:00</t>
         </is>
       </c>
       <c r="N115" t="inlineStr">
@@ -9995,45 +9959,45 @@
       </c>
       <c r="O115" t="inlineStr">
         <is>
-          <t>VIET MOI INDUSTRIAL COMPANY LIMITED</t>
+          <t>AUTONEUM CZ S.R.O.</t>
         </is>
       </c>
       <c r="P115" t="inlineStr">
         <is>
-          <t>VIET MOI INDUSTRIAL COMPANY LIMITED</t>
+          <t>AUTONEUM CZ S.R.O.</t>
         </is>
       </c>
       <c r="Q115" t="inlineStr">
         <is>
-          <t>2026-05-01 00:00:00</t>
+          <t>2026-05-28 00:00:00</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>105504738</t>
+          <t>2565664</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>EF4-0232095-8</t>
+          <t>EF4-0231432-4</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>Vessel, Non-container</t>
+          <t>Vessel, Container</t>
         </is>
       </c>
       <c r="D116" t="inlineStr"/>
       <c r="E116" t="inlineStr">
         <is>
-          <t>9805.00.50</t>
+          <t>9903.03.01</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>EFFECTS US GOV EMP&amp;FAMLY/EVACU</t>
+          <t>SECTION 122 - 10% DUTY</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
@@ -10043,76 +10007,80 @@
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>9805.00.50</t>
-        </is>
-      </c>
-      <c r="I116" t="inlineStr"/>
+          <t>9903.03.01</t>
+        </is>
+      </c>
+      <c r="I116" t="inlineStr">
+        <is>
+          <t>5903.90.3090</t>
+        </is>
+      </c>
       <c r="J116" t="inlineStr">
         <is>
-          <t>IFF, INC.</t>
+          <t>VEER CORPORATIONS INC</t>
         </is>
       </c>
       <c r="K116" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>VEECOR01</t>
         </is>
       </c>
       <c r="L116" t="inlineStr">
         <is>
-          <t>58-149385700</t>
+          <t>99-106989200</t>
         </is>
       </c>
       <c r="M116" t="inlineStr">
         <is>
-          <t>2026-06-13 00:00:00</t>
+          <t>2026-06-14 00:00:00</t>
         </is>
       </c>
       <c r="N116" t="inlineStr">
         <is>
-          <t>2026-06-13 00:00:00</t>
+          <t>2026-06-14 00:00:00</t>
         </is>
       </c>
       <c r="O116" t="inlineStr">
         <is>
-          <t>VOLVO CAR INTERNATIONAL CORPORATION</t>
+          <t>VEER PLASTIC PVT LTD</t>
         </is>
       </c>
       <c r="P116" t="inlineStr">
         <is>
-          <t>VOLVO CAR INTERNATIONAL CORPORATION</t>
+          <t>VEER PLASTIC PVT LTD</t>
         </is>
       </c>
       <c r="Q116" t="inlineStr">
         <is>
-          <t>2026-05-26 00:00:00</t>
+          <t>2026-04-27 00:00:00</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>105504739</t>
+          <t>2565647</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>EF4-0232096-6</t>
+          <t>EF4-0231683-2</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>Vessel, Non-container</t>
+          <t>Vessel, Container</t>
         </is>
       </c>
       <c r="D117" t="inlineStr"/>
       <c r="E117" t="inlineStr">
         <is>
-          <t>9805.00.50</t>
+          <t>9903.03.01</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>EFFECTS US GOV EMP&amp;FAMLY/EVACU</t>
+          <t>SECTION 122 - 10% DUTY</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
@@ -10122,297 +10090,313 @@
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>9805.00.50</t>
-        </is>
-      </c>
-      <c r="I117" t="inlineStr"/>
+          <t>9903.03.01</t>
+        </is>
+      </c>
+      <c r="I117" t="inlineStr">
+        <is>
+          <t>3305.10.0000</t>
+        </is>
+      </c>
       <c r="J117" t="inlineStr">
         <is>
-          <t>IFF, INC.</t>
+          <t>ETHIQUE CONSUMER PRODUCTS, INC</t>
         </is>
       </c>
       <c r="K117" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>ETHCO01</t>
         </is>
       </c>
       <c r="L117" t="inlineStr">
         <is>
-          <t>58-149385700</t>
+          <t>85-417193400</t>
         </is>
       </c>
       <c r="M117" t="inlineStr">
         <is>
-          <t>2026-06-13 00:00:00</t>
+          <t>2026-06-15 00:00:00</t>
         </is>
       </c>
       <c r="N117" t="inlineStr">
         <is>
-          <t>2026-06-13 00:00:00</t>
+          <t>2026-06-14 00:00:00</t>
         </is>
       </c>
       <c r="O117" t="inlineStr">
         <is>
-          <t>VOLVO CAR INTERNATIONAL CORPORATION</t>
+          <t>SHIELING LABORATORIES LTD</t>
         </is>
       </c>
       <c r="P117" t="inlineStr">
         <is>
-          <t>VOLVO CAR INTERNATIONAL CORPORATION</t>
+          <t>SHIELING LABORATORIES LTD</t>
         </is>
       </c>
       <c r="Q117" t="inlineStr">
         <is>
-          <t>2026-05-26 00:00:00</t>
+          <t>2026-05-05 00:00:00</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>105504740</t>
+          <t>2565647</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>EF4-0232098-2</t>
+          <t>EF4-0231683-2</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>Vessel, Non-container</t>
+          <t>Vessel, Container</t>
         </is>
       </c>
       <c r="D118" t="inlineStr"/>
       <c r="E118" t="inlineStr">
         <is>
-          <t>9805.00.50</t>
+          <t>9903.03.01</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>EFFECTS US GOV EMP&amp;FAMLY/EVACU</t>
+          <t>SECTION 122 - 10% DUTY</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>001</t>
+          <t>002</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>9805.00.50</t>
-        </is>
-      </c>
-      <c r="I118" t="inlineStr"/>
+          <t>9903.03.01</t>
+        </is>
+      </c>
+      <c r="I118" t="inlineStr">
+        <is>
+          <t>3305.90.0000</t>
+        </is>
+      </c>
       <c r="J118" t="inlineStr">
         <is>
-          <t>IFF, INC.</t>
+          <t>ETHIQUE CONSUMER PRODUCTS, INC</t>
         </is>
       </c>
       <c r="K118" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>ETHCO01</t>
         </is>
       </c>
       <c r="L118" t="inlineStr">
         <is>
-          <t>58-149385700</t>
+          <t>85-417193400</t>
         </is>
       </c>
       <c r="M118" t="inlineStr">
         <is>
-          <t>2026-06-13 00:00:00</t>
+          <t>2026-06-15 00:00:00</t>
         </is>
       </c>
       <c r="N118" t="inlineStr">
         <is>
-          <t>2026-06-13 00:00:00</t>
+          <t>2026-06-14 00:00:00</t>
         </is>
       </c>
       <c r="O118" t="inlineStr">
         <is>
-          <t>VOLVO CAR INTERNATIONAL CORPORATION</t>
+          <t>SHIELING LABORATORIES LTD</t>
         </is>
       </c>
       <c r="P118" t="inlineStr">
         <is>
-          <t>VOLVO CAR INTERNATIONAL CORPORATION</t>
+          <t>SHIELING LABORATORIES LTD</t>
         </is>
       </c>
       <c r="Q118" t="inlineStr">
         <is>
-          <t>2026-05-26 00:00:00</t>
+          <t>2026-05-05 00:00:00</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>105504741</t>
+          <t>2565647</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>EF4-0232100-6</t>
+          <t>EF4-0231683-2</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>Vessel, Non-container</t>
+          <t>Vessel, Container</t>
         </is>
       </c>
       <c r="D119" t="inlineStr"/>
       <c r="E119" t="inlineStr">
         <is>
-          <t>9805.00.50</t>
+          <t>9903.03.01</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>EFFECTS US GOV EMP&amp;FAMLY/EVACU</t>
+          <t>SECTION 122 - 10% DUTY</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>001</t>
+          <t>003</t>
         </is>
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>9805.00.50</t>
-        </is>
-      </c>
-      <c r="I119" t="inlineStr"/>
+          <t>9903.03.01</t>
+        </is>
+      </c>
+      <c r="I119" t="inlineStr">
+        <is>
+          <t>3307.20.0000</t>
+        </is>
+      </c>
       <c r="J119" t="inlineStr">
         <is>
-          <t>IFF, INC.</t>
+          <t>ETHIQUE CONSUMER PRODUCTS, INC</t>
         </is>
       </c>
       <c r="K119" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>ETHCO01</t>
         </is>
       </c>
       <c r="L119" t="inlineStr">
         <is>
-          <t>58-149385700</t>
+          <t>85-417193400</t>
         </is>
       </c>
       <c r="M119" t="inlineStr">
         <is>
-          <t>2026-06-13 00:00:00</t>
+          <t>2026-06-15 00:00:00</t>
         </is>
       </c>
       <c r="N119" t="inlineStr">
         <is>
-          <t>2026-06-13 00:00:00</t>
+          <t>2026-06-14 00:00:00</t>
         </is>
       </c>
       <c r="O119" t="inlineStr">
         <is>
-          <t>VOLVO CAR INTERNATIONAL CORPORATION</t>
+          <t>SHIELING LABORATORIES LTD</t>
         </is>
       </c>
       <c r="P119" t="inlineStr">
         <is>
-          <t>VOLVO CAR INTERNATIONAL CORPORATION</t>
+          <t>SHIELING LABORATORIES LTD</t>
         </is>
       </c>
       <c r="Q119" t="inlineStr">
         <is>
-          <t>2026-05-26 00:00:00</t>
+          <t>2026-05-05 00:00:00</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>105504747</t>
+          <t>2565647</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>EF4-0232107-1</t>
+          <t>EF4-0231683-2</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>Vessel, Non-container</t>
+          <t>Vessel, Container</t>
         </is>
       </c>
       <c r="D120" t="inlineStr"/>
       <c r="E120" t="inlineStr">
         <is>
-          <t>9805.00.50</t>
+          <t>9903.03.01</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>EFFECTS US GOV EMP&amp;FAMLY/EVACU</t>
+          <t>SECTION 122 - 10% DUTY</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>001</t>
+          <t>004</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>9805.00.50</t>
-        </is>
-      </c>
-      <c r="I120" t="inlineStr"/>
+          <t>9903.03.01</t>
+        </is>
+      </c>
+      <c r="I120" t="inlineStr">
+        <is>
+          <t>3305.10.0000</t>
+        </is>
+      </c>
       <c r="J120" t="inlineStr">
         <is>
-          <t>IFF, INC.</t>
+          <t>ETHIQUE CONSUMER PRODUCTS, INC</t>
         </is>
       </c>
       <c r="K120" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>ETHCO01</t>
         </is>
       </c>
       <c r="L120" t="inlineStr">
         <is>
-          <t>58-149385700</t>
+          <t>85-417193400</t>
         </is>
       </c>
       <c r="M120" t="inlineStr">
         <is>
-          <t>2026-06-13 00:00:00</t>
+          <t>2026-06-15 00:00:00</t>
         </is>
       </c>
       <c r="N120" t="inlineStr">
         <is>
-          <t>2026-06-13 00:00:00</t>
+          <t>2026-06-14 00:00:00</t>
         </is>
       </c>
       <c r="O120" t="inlineStr">
         <is>
-          <t>VOLVO CAR INTERNATIONAL CORPORATION</t>
+          <t>SHIELING LABORATORIES LTD</t>
         </is>
       </c>
       <c r="P120" t="inlineStr">
         <is>
-          <t>VOLVO CAR INTERNATIONAL CORPORATION</t>
+          <t>SHIELING LABORATORIES LTD</t>
         </is>
       </c>
       <c r="Q120" t="inlineStr">
         <is>
-          <t>2026-05-28 00:00:00</t>
+          <t>2026-05-05 00:00:00</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>2566131</t>
+          <t>2565873</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>EF4-0232126-1</t>
+          <t>EF4-0231852-3</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
@@ -10420,17 +10404,17 @@
           <t>Vessel, Container</t>
         </is>
       </c>
-      <c r="D121" t="inlineStr">
-        <is>
-          <t>V1626459831</t>
-        </is>
-      </c>
+      <c r="D121" t="inlineStr"/>
       <c r="E121" t="inlineStr">
         <is>
           <t>9903.03.01</t>
         </is>
       </c>
-      <c r="F121" t="inlineStr"/>
+      <c r="F121" t="inlineStr">
+        <is>
+          <t>SECTION 122 - 10% DUTY</t>
+        </is>
+      </c>
       <c r="G121" t="inlineStr">
         <is>
           <t>001</t>
@@ -10443,59 +10427,59 @@
       </c>
       <c r="I121" t="inlineStr">
         <is>
-          <t>1108.12.0010</t>
+          <t>9903.82.01,8431.20.0000</t>
         </is>
       </c>
       <c r="J121" t="inlineStr">
         <is>
-          <t>ROYAL INGREDIENTS GROUP BV</t>
+          <t>MALLAGHAN (GA) INC.</t>
         </is>
       </c>
       <c r="K121" t="inlineStr">
         <is>
-          <t>ROYINGRE</t>
+          <t>MALGA01</t>
         </is>
       </c>
       <c r="L121" t="inlineStr">
         <is>
-          <t>074601-00962</t>
+          <t>36-488102800</t>
         </is>
       </c>
       <c r="M121" t="inlineStr">
         <is>
+          <t>2026-06-15 00:00:00</t>
+        </is>
+      </c>
+      <c r="N121" t="inlineStr">
+        <is>
           <t>2026-06-14 00:00:00</t>
         </is>
       </c>
-      <c r="N121" t="inlineStr">
-        <is>
-          <t>2026-06-13 00:00:00</t>
-        </is>
-      </c>
       <c r="O121" t="inlineStr">
         <is>
-          <t>TAT NISASTA INS SAN TIC AS</t>
+          <t>MALLAGHAN ENGINEERING  LTD</t>
         </is>
       </c>
       <c r="P121" t="inlineStr">
         <is>
-          <t>TAT NISASTA INS SAN TIC AS</t>
+          <t>MALLAGHAN ENGINEERING  LTD</t>
         </is>
       </c>
       <c r="Q121" t="inlineStr">
         <is>
-          <t>2026-05-23 00:00:00</t>
+          <t>2026-05-12 00:00:00</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>2565958</t>
+          <t>2565888</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>EF4-0232210-3</t>
+          <t>EF4-0231959-6</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
@@ -10505,72 +10489,1333 @@
       </c>
       <c r="D122" t="inlineStr">
         <is>
+          <t>V0710337820</t>
+        </is>
+      </c>
+      <c r="E122" t="inlineStr">
+        <is>
+          <t>9903.03.01</t>
+        </is>
+      </c>
+      <c r="F122" t="inlineStr">
+        <is>
+          <t>SECTION 122 - 10% DUTY</t>
+        </is>
+      </c>
+      <c r="G122" t="inlineStr">
+        <is>
+          <t>001</t>
+        </is>
+      </c>
+      <c r="H122" t="inlineStr">
+        <is>
+          <t>9903.03.01</t>
+        </is>
+      </c>
+      <c r="I122" t="inlineStr">
+        <is>
+          <t>1108.13.0010</t>
+        </is>
+      </c>
+      <c r="J122" t="inlineStr">
+        <is>
+          <t>ROYAL INGREDIENTS GROUP BV</t>
+        </is>
+      </c>
+      <c r="K122" t="inlineStr">
+        <is>
+          <t>ROYINGRE</t>
+        </is>
+      </c>
+      <c r="L122" t="inlineStr">
+        <is>
+          <t>074601-00962</t>
+        </is>
+      </c>
+      <c r="M122" t="inlineStr">
+        <is>
+          <t>2026-06-14 00:00:00</t>
+        </is>
+      </c>
+      <c r="N122" t="inlineStr">
+        <is>
+          <t>2026-06-14 00:00:00</t>
+        </is>
+      </c>
+      <c r="O122" t="inlineStr">
+        <is>
+          <t>AKV LANGHOLT AMBA</t>
+        </is>
+      </c>
+      <c r="P122" t="inlineStr">
+        <is>
+          <t>AKV LANGHOLT AMBA</t>
+        </is>
+      </c>
+      <c r="Q122" t="inlineStr">
+        <is>
+          <t>2026-05-18 00:00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" t="inlineStr">
+        <is>
+          <t>2565945</t>
+        </is>
+      </c>
+      <c r="B123" t="inlineStr">
+        <is>
+          <t>EF4-0231961-2</t>
+        </is>
+      </c>
+      <c r="C123" t="inlineStr">
+        <is>
+          <t>Vessel, Container</t>
+        </is>
+      </c>
+      <c r="D123" t="inlineStr">
+        <is>
+          <t>V0710337820</t>
+        </is>
+      </c>
+      <c r="E123" t="inlineStr">
+        <is>
+          <t>9903.03.01</t>
+        </is>
+      </c>
+      <c r="F123" t="inlineStr"/>
+      <c r="G123" t="inlineStr">
+        <is>
+          <t>001</t>
+        </is>
+      </c>
+      <c r="H123" t="inlineStr">
+        <is>
+          <t>9903.03.01</t>
+        </is>
+      </c>
+      <c r="I123" t="inlineStr">
+        <is>
+          <t>1108.13.0010</t>
+        </is>
+      </c>
+      <c r="J123" t="inlineStr">
+        <is>
+          <t>ROYAL INGREDIENTS GROUP BV</t>
+        </is>
+      </c>
+      <c r="K123" t="inlineStr">
+        <is>
+          <t>ROYINGRE</t>
+        </is>
+      </c>
+      <c r="L123" t="inlineStr">
+        <is>
+          <t>074601-00962</t>
+        </is>
+      </c>
+      <c r="M123" t="inlineStr">
+        <is>
+          <t>2026-06-15 00:00:00</t>
+        </is>
+      </c>
+      <c r="N123" t="inlineStr">
+        <is>
+          <t>2026-06-14 00:00:00</t>
+        </is>
+      </c>
+      <c r="O123" t="inlineStr">
+        <is>
+          <t>PRZEDSIEBIORSTWO PRZEMYSLU ZIEMNIAC</t>
+        </is>
+      </c>
+      <c r="P123" t="inlineStr">
+        <is>
+          <t>PRZEDSIEBIORSTWO PRZEMYSLU ZIEMNIACZANEGO PEPEES S.A.</t>
+        </is>
+      </c>
+      <c r="Q123" t="inlineStr">
+        <is>
+          <t>2026-05-17 00:00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" t="inlineStr">
+        <is>
+          <t>2615692</t>
+        </is>
+      </c>
+      <c r="B124" t="inlineStr">
+        <is>
+          <t>EF4-0231982-8</t>
+        </is>
+      </c>
+      <c r="C124" t="inlineStr">
+        <is>
+          <t>Vessel, Non-container</t>
+        </is>
+      </c>
+      <c r="D124" t="inlineStr">
+        <is>
+          <t>V8N03137232</t>
+        </is>
+      </c>
+      <c r="E124" t="inlineStr">
+        <is>
+          <t>9903.88.15</t>
+        </is>
+      </c>
+      <c r="F124" t="inlineStr">
+        <is>
+          <t>ARTICLE OF CHINA,US NTE 20(R)</t>
+        </is>
+      </c>
+      <c r="G124" t="inlineStr">
+        <is>
+          <t>001</t>
+        </is>
+      </c>
+      <c r="H124" t="inlineStr">
+        <is>
+          <t>9903.88.15</t>
+        </is>
+      </c>
+      <c r="I124" t="inlineStr">
+        <is>
+          <t>9903.03.01,3926.90.9989</t>
+        </is>
+      </c>
+      <c r="J124" t="inlineStr">
+        <is>
+          <t>BORGERS OHIO INC.</t>
+        </is>
+      </c>
+      <c r="K124" t="inlineStr">
+        <is>
+          <t>BORUSA02</t>
+        </is>
+      </c>
+      <c r="L124" t="inlineStr">
+        <is>
+          <t>30-084196200</t>
+        </is>
+      </c>
+      <c r="M124" t="inlineStr">
+        <is>
+          <t>2026-06-04 00:00:00</t>
+        </is>
+      </c>
+      <c r="N124" t="inlineStr">
+        <is>
+          <t>2026-06-14 00:00:00</t>
+        </is>
+      </c>
+      <c r="O124" t="inlineStr">
+        <is>
+          <t>AUTONEUM (SHANGHAI) MANAGEMENT CO.</t>
+        </is>
+      </c>
+      <c r="P124" t="inlineStr">
+        <is>
+          <t>AUTONEUM (SHANGHAI) MANAGEMENT CO. LTD.</t>
+        </is>
+      </c>
+      <c r="Q124" t="inlineStr">
+        <is>
+          <t>2026-05-19 00:00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" t="inlineStr">
+        <is>
+          <t>2615692</t>
+        </is>
+      </c>
+      <c r="B125" t="inlineStr">
+        <is>
+          <t>EF4-0231982-8</t>
+        </is>
+      </c>
+      <c r="C125" t="inlineStr">
+        <is>
+          <t>Vessel, Non-container</t>
+        </is>
+      </c>
+      <c r="D125" t="inlineStr">
+        <is>
+          <t>V8N03137232</t>
+        </is>
+      </c>
+      <c r="E125" t="inlineStr">
+        <is>
+          <t>9903.88.15</t>
+        </is>
+      </c>
+      <c r="F125" t="inlineStr">
+        <is>
+          <t>ARTICLE OF CHINA,US NTE 20(R)</t>
+        </is>
+      </c>
+      <c r="G125" t="inlineStr">
+        <is>
+          <t>002</t>
+        </is>
+      </c>
+      <c r="H125" t="inlineStr">
+        <is>
+          <t>9903.88.15</t>
+        </is>
+      </c>
+      <c r="I125" t="inlineStr">
+        <is>
+          <t>9903.03.01,3926.30.5000</t>
+        </is>
+      </c>
+      <c r="J125" t="inlineStr">
+        <is>
+          <t>BORGERS OHIO INC.</t>
+        </is>
+      </c>
+      <c r="K125" t="inlineStr">
+        <is>
+          <t>BORUSA02</t>
+        </is>
+      </c>
+      <c r="L125" t="inlineStr">
+        <is>
+          <t>30-084196200</t>
+        </is>
+      </c>
+      <c r="M125" t="inlineStr">
+        <is>
+          <t>2026-06-04 00:00:00</t>
+        </is>
+      </c>
+      <c r="N125" t="inlineStr">
+        <is>
+          <t>2026-06-14 00:00:00</t>
+        </is>
+      </c>
+      <c r="O125" t="inlineStr">
+        <is>
+          <t>AUTONEUM (SHANGHAI) MANAGEMENT CO.</t>
+        </is>
+      </c>
+      <c r="P125" t="inlineStr">
+        <is>
+          <t>AUTONEUM (SHANGHAI) MANAGEMENT CO. LTD.</t>
+        </is>
+      </c>
+      <c r="Q125" t="inlineStr">
+        <is>
+          <t>2026-05-19 00:00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" t="inlineStr">
+        <is>
+          <t>2565999</t>
+        </is>
+      </c>
+      <c r="B126" t="inlineStr">
+        <is>
+          <t>EF4-0232009-9</t>
+        </is>
+      </c>
+      <c r="C126" t="inlineStr">
+        <is>
+          <t>Vessel, Container</t>
+        </is>
+      </c>
+      <c r="D126" t="inlineStr">
+        <is>
+          <t>V8N03137232</t>
+        </is>
+      </c>
+      <c r="E126" t="inlineStr">
+        <is>
+          <t>9903.03.01</t>
+        </is>
+      </c>
+      <c r="F126" t="inlineStr">
+        <is>
+          <t>SECTION 122 - 10% DUTY</t>
+        </is>
+      </c>
+      <c r="G126" t="inlineStr">
+        <is>
+          <t>001</t>
+        </is>
+      </c>
+      <c r="H126" t="inlineStr">
+        <is>
+          <t>9903.03.01</t>
+        </is>
+      </c>
+      <c r="I126" t="inlineStr">
+        <is>
+          <t>1806.90.9090</t>
+        </is>
+      </c>
+      <c r="J126" t="inlineStr">
+        <is>
+          <t>DOBLA USA MFG LLC</t>
+        </is>
+      </c>
+      <c r="K126" t="inlineStr">
+        <is>
+          <t>DOBUSA</t>
+        </is>
+      </c>
+      <c r="L126" t="inlineStr">
+        <is>
+          <t>41-218954800</t>
+        </is>
+      </c>
+      <c r="M126" t="inlineStr">
+        <is>
+          <t>2026-06-15 00:00:00</t>
+        </is>
+      </c>
+      <c r="N126" t="inlineStr">
+        <is>
+          <t>2026-06-14 00:00:00</t>
+        </is>
+      </c>
+      <c r="O126" t="inlineStr">
+        <is>
+          <t>DOBLA LOGISTICS BVBA</t>
+        </is>
+      </c>
+      <c r="P126" t="inlineStr">
+        <is>
+          <t>DOBLA LOGISTICS BVBA</t>
+        </is>
+      </c>
+      <c r="Q126" t="inlineStr">
+        <is>
+          <t>2026-05-19 00:00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" t="inlineStr">
+        <is>
+          <t>2565956</t>
+        </is>
+      </c>
+      <c r="B127" t="inlineStr">
+        <is>
+          <t>EF4-0232032-1</t>
+        </is>
+      </c>
+      <c r="C127" t="inlineStr">
+        <is>
+          <t>Vessel, Container</t>
+        </is>
+      </c>
+      <c r="D127" t="inlineStr"/>
+      <c r="E127" t="inlineStr">
+        <is>
+          <t>9903.03.01</t>
+        </is>
+      </c>
+      <c r="F127" t="inlineStr">
+        <is>
+          <t>SECTION 122 - 10% DUTY</t>
+        </is>
+      </c>
+      <c r="G127" t="inlineStr">
+        <is>
+          <t>001</t>
+        </is>
+      </c>
+      <c r="H127" t="inlineStr">
+        <is>
+          <t>9903.03.01</t>
+        </is>
+      </c>
+      <c r="I127" t="inlineStr">
+        <is>
+          <t>9903.82.01,8431.20.0000</t>
+        </is>
+      </c>
+      <c r="J127" t="inlineStr">
+        <is>
+          <t>MALLAGHAN (GA) INC.</t>
+        </is>
+      </c>
+      <c r="K127" t="inlineStr">
+        <is>
+          <t>MALGA01</t>
+        </is>
+      </c>
+      <c r="L127" t="inlineStr">
+        <is>
+          <t>36-488102800</t>
+        </is>
+      </c>
+      <c r="M127" t="inlineStr">
+        <is>
+          <t>2026-06-15 00:00:00</t>
+        </is>
+      </c>
+      <c r="N127" t="inlineStr">
+        <is>
+          <t>2026-06-14 00:00:00</t>
+        </is>
+      </c>
+      <c r="O127" t="inlineStr">
+        <is>
+          <t>MALLAGHAN ENGINEERING  LTD</t>
+        </is>
+      </c>
+      <c r="P127" t="inlineStr">
+        <is>
+          <t>MALLAGHAN ENGINEERING  LTD</t>
+        </is>
+      </c>
+      <c r="Q127" t="inlineStr">
+        <is>
+          <t>2026-05-19 00:00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" t="inlineStr">
+        <is>
+          <t>2566028</t>
+        </is>
+      </c>
+      <c r="B128" t="inlineStr">
+        <is>
+          <t>EF4-0232065-1</t>
+        </is>
+      </c>
+      <c r="C128" t="inlineStr">
+        <is>
+          <t>Vessel, Container</t>
+        </is>
+      </c>
+      <c r="D128" t="inlineStr"/>
+      <c r="E128" t="inlineStr">
+        <is>
+          <t>9903.03.01</t>
+        </is>
+      </c>
+      <c r="F128" t="inlineStr"/>
+      <c r="G128" t="inlineStr">
+        <is>
+          <t>001</t>
+        </is>
+      </c>
+      <c r="H128" t="inlineStr">
+        <is>
+          <t>9903.03.01</t>
+        </is>
+      </c>
+      <c r="I128" t="inlineStr">
+        <is>
+          <t>1108.12.0010</t>
+        </is>
+      </c>
+      <c r="J128" t="inlineStr">
+        <is>
+          <t>ROYAL INGREDIENTS GROUP BV</t>
+        </is>
+      </c>
+      <c r="K128" t="inlineStr">
+        <is>
+          <t>ROYINGRE</t>
+        </is>
+      </c>
+      <c r="L128" t="inlineStr">
+        <is>
+          <t>074601-00962</t>
+        </is>
+      </c>
+      <c r="M128" t="inlineStr">
+        <is>
+          <t>2026-06-14 00:00:00</t>
+        </is>
+      </c>
+      <c r="N128" t="inlineStr">
+        <is>
+          <t>2026-06-14 00:00:00</t>
+        </is>
+      </c>
+      <c r="O128" t="inlineStr">
+        <is>
+          <t>TAT NISASTA INS SAN TIC AS</t>
+        </is>
+      </c>
+      <c r="P128" t="inlineStr">
+        <is>
+          <t>TAT NISASTA INS SAN TIC AS</t>
+        </is>
+      </c>
+      <c r="Q128" t="inlineStr">
+        <is>
+          <t>2026-05-23 00:00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" t="inlineStr">
+        <is>
+          <t>2566055</t>
+        </is>
+      </c>
+      <c r="B129" t="inlineStr">
+        <is>
+          <t>EF4-0232124-6</t>
+        </is>
+      </c>
+      <c r="C129" t="inlineStr">
+        <is>
+          <t>Vessel, Container</t>
+        </is>
+      </c>
+      <c r="D129" t="inlineStr">
+        <is>
+          <t>V0710343679</t>
+        </is>
+      </c>
+      <c r="E129" t="inlineStr">
+        <is>
+          <t>9903.03.01</t>
+        </is>
+      </c>
+      <c r="F129" t="inlineStr">
+        <is>
+          <t>SECTION 122 - 10% DUTY</t>
+        </is>
+      </c>
+      <c r="G129" t="inlineStr">
+        <is>
+          <t>001</t>
+        </is>
+      </c>
+      <c r="H129" t="inlineStr">
+        <is>
+          <t>9903.03.01</t>
+        </is>
+      </c>
+      <c r="I129" t="inlineStr">
+        <is>
+          <t>1109.00.9020</t>
+        </is>
+      </c>
+      <c r="J129" t="inlineStr">
+        <is>
+          <t>ROYAL INGREDIENTS GROUP BV</t>
+        </is>
+      </c>
+      <c r="K129" t="inlineStr">
+        <is>
+          <t>ROYINGRE</t>
+        </is>
+      </c>
+      <c r="L129" t="inlineStr">
+        <is>
+          <t>074601-00962</t>
+        </is>
+      </c>
+      <c r="M129" t="inlineStr">
+        <is>
+          <t>2026-06-14 00:00:00</t>
+        </is>
+      </c>
+      <c r="N129" t="inlineStr">
+        <is>
+          <t>2026-06-14 00:00:00</t>
+        </is>
+      </c>
+      <c r="O129" t="inlineStr">
+        <is>
+          <t>JACKERING MUHLEN UND NAHRMITTELWERK</t>
+        </is>
+      </c>
+      <c r="P129" t="inlineStr">
+        <is>
+          <t>JACKERING MUHLEN UND NAHRMITTELWERKE GMBH</t>
+        </is>
+      </c>
+      <c r="Q129" t="inlineStr">
+        <is>
+          <t>2026-05-25 00:00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" t="inlineStr">
+        <is>
+          <t>2566131</t>
+        </is>
+      </c>
+      <c r="B130" t="inlineStr">
+        <is>
+          <t>EF4-0232126-1</t>
+        </is>
+      </c>
+      <c r="C130" t="inlineStr">
+        <is>
+          <t>Vessel, Container</t>
+        </is>
+      </c>
+      <c r="D130" t="inlineStr">
+        <is>
+          <t>V0710343679</t>
+        </is>
+      </c>
+      <c r="E130" t="inlineStr">
+        <is>
+          <t>9903.03.01</t>
+        </is>
+      </c>
+      <c r="F130" t="inlineStr"/>
+      <c r="G130" t="inlineStr">
+        <is>
+          <t>001</t>
+        </is>
+      </c>
+      <c r="H130" t="inlineStr">
+        <is>
+          <t>9903.03.01</t>
+        </is>
+      </c>
+      <c r="I130" t="inlineStr">
+        <is>
+          <t>1108.12.0010</t>
+        </is>
+      </c>
+      <c r="J130" t="inlineStr">
+        <is>
+          <t>ROYAL INGREDIENTS GROUP BV</t>
+        </is>
+      </c>
+      <c r="K130" t="inlineStr">
+        <is>
+          <t>ROYINGRE</t>
+        </is>
+      </c>
+      <c r="L130" t="inlineStr">
+        <is>
+          <t>074601-00962</t>
+        </is>
+      </c>
+      <c r="M130" t="inlineStr">
+        <is>
+          <t>2026-06-14 00:00:00</t>
+        </is>
+      </c>
+      <c r="N130" t="inlineStr">
+        <is>
+          <t>2026-06-14 00:00:00</t>
+        </is>
+      </c>
+      <c r="O130" t="inlineStr">
+        <is>
+          <t>TAT NISASTA INS SAN TIC AS</t>
+        </is>
+      </c>
+      <c r="P130" t="inlineStr">
+        <is>
+          <t>TAT NISASTA INS SAN TIC AS</t>
+        </is>
+      </c>
+      <c r="Q130" t="inlineStr">
+        <is>
+          <t>2026-05-23 00:00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" t="inlineStr">
+        <is>
+          <t>2566056</t>
+        </is>
+      </c>
+      <c r="B131" t="inlineStr">
+        <is>
+          <t>EF4-0232208-7</t>
+        </is>
+      </c>
+      <c r="C131" t="inlineStr">
+        <is>
+          <t>Vessel, Container</t>
+        </is>
+      </c>
+      <c r="D131" t="inlineStr">
+        <is>
           <t>V1626459831</t>
         </is>
       </c>
-      <c r="E122" t="inlineStr">
+      <c r="E131" t="inlineStr">
+        <is>
+          <t>9903.03.01</t>
+        </is>
+      </c>
+      <c r="F131" t="inlineStr">
+        <is>
+          <t>SECTION 122 - 10% DUTY</t>
+        </is>
+      </c>
+      <c r="G131" t="inlineStr">
+        <is>
+          <t>001</t>
+        </is>
+      </c>
+      <c r="H131" t="inlineStr">
+        <is>
+          <t>9903.03.01</t>
+        </is>
+      </c>
+      <c r="I131" t="inlineStr">
+        <is>
+          <t>1108.13.0010</t>
+        </is>
+      </c>
+      <c r="J131" t="inlineStr">
+        <is>
+          <t>ROYAL INGREDIENTS GROUP BV</t>
+        </is>
+      </c>
+      <c r="K131" t="inlineStr">
+        <is>
+          <t>ROYINGRE</t>
+        </is>
+      </c>
+      <c r="L131" t="inlineStr">
+        <is>
+          <t>074601-00962</t>
+        </is>
+      </c>
+      <c r="M131" t="inlineStr">
+        <is>
+          <t>2026-06-14 00:00:00</t>
+        </is>
+      </c>
+      <c r="N131" t="inlineStr">
+        <is>
+          <t>2026-06-14 00:00:00</t>
+        </is>
+      </c>
+      <c r="O131" t="inlineStr">
+        <is>
+          <t>AKV LANGHOLT AMBA</t>
+        </is>
+      </c>
+      <c r="P131" t="inlineStr">
+        <is>
+          <t>AKV LANGHOLT AMBA</t>
+        </is>
+      </c>
+      <c r="Q131" t="inlineStr">
+        <is>
+          <t>2026-05-25 00:00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" t="inlineStr">
+        <is>
+          <t>2566180</t>
+        </is>
+      </c>
+      <c r="B132" t="inlineStr">
+        <is>
+          <t>EF4-0232260-8</t>
+        </is>
+      </c>
+      <c r="C132" t="inlineStr">
+        <is>
+          <t>Vessel, Container</t>
+        </is>
+      </c>
+      <c r="D132" t="inlineStr"/>
+      <c r="E132" t="inlineStr">
+        <is>
+          <t>9903.03.01</t>
+        </is>
+      </c>
+      <c r="F132" t="inlineStr">
+        <is>
+          <t>SECTION 122 - 10% DUTY</t>
+        </is>
+      </c>
+      <c r="G132" t="inlineStr">
+        <is>
+          <t>001</t>
+        </is>
+      </c>
+      <c r="H132" t="inlineStr">
+        <is>
+          <t>9903.03.01</t>
+        </is>
+      </c>
+      <c r="I132" t="inlineStr">
+        <is>
+          <t>9903.82.01,8424.90.9080</t>
+        </is>
+      </c>
+      <c r="J132" t="inlineStr">
+        <is>
+          <t>EISENMANN OF SOUTH CAROLINA INC</t>
+        </is>
+      </c>
+      <c r="K132" t="inlineStr">
+        <is>
+          <t>EISINC03</t>
+        </is>
+      </c>
+      <c r="L132" t="inlineStr">
+        <is>
+          <t>86-240963300</t>
+        </is>
+      </c>
+      <c r="M132" t="inlineStr">
+        <is>
+          <t>2026-06-12 00:00:00</t>
+        </is>
+      </c>
+      <c r="N132" t="inlineStr">
+        <is>
+          <t>2026-06-14 00:00:00</t>
+        </is>
+      </c>
+      <c r="O132" t="inlineStr">
+        <is>
+          <t>EISENMANN GMBH</t>
+        </is>
+      </c>
+      <c r="P132" t="inlineStr">
+        <is>
+          <t>EISENMANN GMBH</t>
+        </is>
+      </c>
+      <c r="Q132" t="inlineStr">
+        <is>
+          <t>2026-06-01 00:00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" t="inlineStr">
+        <is>
+          <t>2566053</t>
+        </is>
+      </c>
+      <c r="B133" t="inlineStr">
+        <is>
+          <t>EF4-0232278-0</t>
+        </is>
+      </c>
+      <c r="C133" t="inlineStr">
+        <is>
+          <t>Vessel, Container</t>
+        </is>
+      </c>
+      <c r="D133" t="inlineStr"/>
+      <c r="E133" t="inlineStr">
         <is>
           <t>9903.03.06</t>
         </is>
       </c>
-      <c r="F122" t="inlineStr">
+      <c r="F133" t="inlineStr">
         <is>
           <t>S122 EXCL,IRN/STL/ALUM,DERIV</t>
         </is>
       </c>
-      <c r="G122" t="inlineStr">
+      <c r="G133" t="inlineStr">
         <is>
           <t>001</t>
         </is>
       </c>
-      <c r="H122" t="inlineStr">
+      <c r="H133" t="inlineStr">
         <is>
           <t>9903.03.06</t>
         </is>
       </c>
-      <c r="I122" t="inlineStr">
+      <c r="I133" t="inlineStr">
         <is>
           <t>9903.74.11,9903.94.53,8708.29.5160</t>
         </is>
       </c>
-      <c r="J122" t="inlineStr">
-        <is>
-          <t>BORGERS OHIO INC.</t>
-        </is>
-      </c>
-      <c r="K122" t="inlineStr">
-        <is>
-          <t>BORUSA02</t>
-        </is>
-      </c>
-      <c r="L122" t="inlineStr">
-        <is>
-          <t>30-084196200</t>
-        </is>
-      </c>
-      <c r="M122" t="inlineStr">
-        <is>
-          <t>2026-06-15 00:00:00</t>
-        </is>
-      </c>
-      <c r="N122" t="inlineStr">
-        <is>
-          <t>2026-06-13 00:00:00</t>
-        </is>
-      </c>
-      <c r="O122" t="inlineStr">
+      <c r="J133" t="inlineStr">
+        <is>
+          <t>BORGERS USA CORP</t>
+        </is>
+      </c>
+      <c r="K133" t="inlineStr">
+        <is>
+          <t>BORUSA</t>
+        </is>
+      </c>
+      <c r="L133" t="inlineStr">
+        <is>
+          <t>65-117296500</t>
+        </is>
+      </c>
+      <c r="M133" t="inlineStr">
+        <is>
+          <t>2026-06-12 00:00:00</t>
+        </is>
+      </c>
+      <c r="N133" t="inlineStr">
+        <is>
+          <t>2026-06-14 00:00:00</t>
+        </is>
+      </c>
+      <c r="O133" t="inlineStr">
         <is>
           <t>AUTONEUM CZ S.R.O.</t>
         </is>
       </c>
-      <c r="P122" t="inlineStr">
+      <c r="P133" t="inlineStr">
         <is>
           <t>AUTONEUM CZ S.R.O.</t>
         </is>
       </c>
-      <c r="Q122" t="inlineStr">
-        <is>
-          <t>2026-05-28 00:00:00</t>
+      <c r="Q133" t="inlineStr">
+        <is>
+          <t>2026-06-01 00:00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" t="inlineStr">
+        <is>
+          <t>2566053</t>
+        </is>
+      </c>
+      <c r="B134" t="inlineStr">
+        <is>
+          <t>EF4-0232278-0</t>
+        </is>
+      </c>
+      <c r="C134" t="inlineStr">
+        <is>
+          <t>Vessel, Container</t>
+        </is>
+      </c>
+      <c r="D134" t="inlineStr"/>
+      <c r="E134" t="inlineStr">
+        <is>
+          <t>9903.03.06</t>
+        </is>
+      </c>
+      <c r="F134" t="inlineStr">
+        <is>
+          <t>S122 EXCL,IRN/STL/ALUM,DERIV</t>
+        </is>
+      </c>
+      <c r="G134" t="inlineStr">
+        <is>
+          <t>002</t>
+        </is>
+      </c>
+      <c r="H134" t="inlineStr">
+        <is>
+          <t>9903.03.06</t>
+        </is>
+      </c>
+      <c r="I134" t="inlineStr">
+        <is>
+          <t>9903.74.11,9903.94.53,8708.29.5160</t>
+        </is>
+      </c>
+      <c r="J134" t="inlineStr">
+        <is>
+          <t>BORGERS USA CORP</t>
+        </is>
+      </c>
+      <c r="K134" t="inlineStr">
+        <is>
+          <t>BORUSA</t>
+        </is>
+      </c>
+      <c r="L134" t="inlineStr">
+        <is>
+          <t>65-117296500</t>
+        </is>
+      </c>
+      <c r="M134" t="inlineStr">
+        <is>
+          <t>2026-06-12 00:00:00</t>
+        </is>
+      </c>
+      <c r="N134" t="inlineStr">
+        <is>
+          <t>2026-06-14 00:00:00</t>
+        </is>
+      </c>
+      <c r="O134" t="inlineStr">
+        <is>
+          <t>AUTONEUM CZ S.R.O.</t>
+        </is>
+      </c>
+      <c r="P134" t="inlineStr">
+        <is>
+          <t>AUTONEUM CZ S.R.O.</t>
+        </is>
+      </c>
+      <c r="Q134" t="inlineStr">
+        <is>
+          <t>2026-06-01 00:00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" t="inlineStr">
+        <is>
+          <t>2566053</t>
+        </is>
+      </c>
+      <c r="B135" t="inlineStr">
+        <is>
+          <t>EF4-0232278-0</t>
+        </is>
+      </c>
+      <c r="C135" t="inlineStr">
+        <is>
+          <t>Vessel, Container</t>
+        </is>
+      </c>
+      <c r="D135" t="inlineStr"/>
+      <c r="E135" t="inlineStr">
+        <is>
+          <t>9903.03.06</t>
+        </is>
+      </c>
+      <c r="F135" t="inlineStr">
+        <is>
+          <t>S122 EXCL,IRN/STL/ALUM,DERIV</t>
+        </is>
+      </c>
+      <c r="G135" t="inlineStr">
+        <is>
+          <t>003</t>
+        </is>
+      </c>
+      <c r="H135" t="inlineStr">
+        <is>
+          <t>9903.03.06</t>
+        </is>
+      </c>
+      <c r="I135" t="inlineStr">
+        <is>
+          <t>9903.74.11,9903.94.53,8708.29.5160</t>
+        </is>
+      </c>
+      <c r="J135" t="inlineStr">
+        <is>
+          <t>BORGERS USA CORP</t>
+        </is>
+      </c>
+      <c r="K135" t="inlineStr">
+        <is>
+          <t>BORUSA</t>
+        </is>
+      </c>
+      <c r="L135" t="inlineStr">
+        <is>
+          <t>65-117296500</t>
+        </is>
+      </c>
+      <c r="M135" t="inlineStr">
+        <is>
+          <t>2026-06-12 00:00:00</t>
+        </is>
+      </c>
+      <c r="N135" t="inlineStr">
+        <is>
+          <t>2026-06-14 00:00:00</t>
+        </is>
+      </c>
+      <c r="O135" t="inlineStr">
+        <is>
+          <t>AUTONEUM CZ S.R.O.</t>
+        </is>
+      </c>
+      <c r="P135" t="inlineStr">
+        <is>
+          <t>AUTONEUM CZ S.R.O.</t>
+        </is>
+      </c>
+      <c r="Q135" t="inlineStr">
+        <is>
+          <t>2026-06-01 00:00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" t="inlineStr">
+        <is>
+          <t>2566053</t>
+        </is>
+      </c>
+      <c r="B136" t="inlineStr">
+        <is>
+          <t>EF4-0232278-0</t>
+        </is>
+      </c>
+      <c r="C136" t="inlineStr">
+        <is>
+          <t>Vessel, Container</t>
+        </is>
+      </c>
+      <c r="D136" t="inlineStr"/>
+      <c r="E136" t="inlineStr">
+        <is>
+          <t>9903.03.06</t>
+        </is>
+      </c>
+      <c r="F136" t="inlineStr">
+        <is>
+          <t>S122 EXCL,IRN/STL/ALUM,DERIV</t>
+        </is>
+      </c>
+      <c r="G136" t="inlineStr">
+        <is>
+          <t>004</t>
+        </is>
+      </c>
+      <c r="H136" t="inlineStr">
+        <is>
+          <t>9903.03.06</t>
+        </is>
+      </c>
+      <c r="I136" t="inlineStr">
+        <is>
+          <t>9903.74.11,9903.94.53,8708.29.5160</t>
+        </is>
+      </c>
+      <c r="J136" t="inlineStr">
+        <is>
+          <t>BORGERS USA CORP</t>
+        </is>
+      </c>
+      <c r="K136" t="inlineStr">
+        <is>
+          <t>BORUSA</t>
+        </is>
+      </c>
+      <c r="L136" t="inlineStr">
+        <is>
+          <t>65-117296500</t>
+        </is>
+      </c>
+      <c r="M136" t="inlineStr">
+        <is>
+          <t>2026-06-12 00:00:00</t>
+        </is>
+      </c>
+      <c r="N136" t="inlineStr">
+        <is>
+          <t>2026-06-14 00:00:00</t>
+        </is>
+      </c>
+      <c r="O136" t="inlineStr">
+        <is>
+          <t>AUTONEUM CZ S.R.O.</t>
+        </is>
+      </c>
+      <c r="P136" t="inlineStr">
+        <is>
+          <t>AUTONEUM CZ S.R.O.</t>
+        </is>
+      </c>
+      <c r="Q136" t="inlineStr">
+        <is>
+          <t>2026-06-01 00:00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" t="inlineStr">
+        <is>
+          <t>2566053</t>
+        </is>
+      </c>
+      <c r="B137" t="inlineStr">
+        <is>
+          <t>EF4-0232278-0</t>
+        </is>
+      </c>
+      <c r="C137" t="inlineStr">
+        <is>
+          <t>Vessel, Container</t>
+        </is>
+      </c>
+      <c r="D137" t="inlineStr"/>
+      <c r="E137" t="inlineStr">
+        <is>
+          <t>9903.03.06</t>
+        </is>
+      </c>
+      <c r="F137" t="inlineStr">
+        <is>
+          <t>S122 EXCL,IRN/STL/ALUM,DERIV</t>
+        </is>
+      </c>
+      <c r="G137" t="inlineStr">
+        <is>
+          <t>005</t>
+        </is>
+      </c>
+      <c r="H137" t="inlineStr">
+        <is>
+          <t>9903.03.06</t>
+        </is>
+      </c>
+      <c r="I137" t="inlineStr">
+        <is>
+          <t>9903.74.11,9903.94.53,8708.29.5160</t>
+        </is>
+      </c>
+      <c r="J137" t="inlineStr">
+        <is>
+          <t>BORGERS USA CORP</t>
+        </is>
+      </c>
+      <c r="K137" t="inlineStr">
+        <is>
+          <t>BORUSA</t>
+        </is>
+      </c>
+      <c r="L137" t="inlineStr">
+        <is>
+          <t>65-117296500</t>
+        </is>
+      </c>
+      <c r="M137" t="inlineStr">
+        <is>
+          <t>2026-06-12 00:00:00</t>
+        </is>
+      </c>
+      <c r="N137" t="inlineStr">
+        <is>
+          <t>2026-06-14 00:00:00</t>
+        </is>
+      </c>
+      <c r="O137" t="inlineStr">
+        <is>
+          <t>AUTONEUM CZ S.R.O.</t>
+        </is>
+      </c>
+      <c r="P137" t="inlineStr">
+        <is>
+          <t>AUTONEUM CZ S.R.O.</t>
+        </is>
+      </c>
+      <c r="Q137" t="inlineStr">
+        <is>
+          <t>2026-06-01 00:00:00</t>
         </is>
       </c>
     </row>

--- a/trimika_data.xlsx
+++ b/trimika_data.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q137"/>
+  <dimension ref="A1:Q164"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -9889,12 +9889,12 @@
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>2565958</t>
+          <t>2565664</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>EF4-0232210-3</t>
+          <t>EF4-0231432-4</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
@@ -9902,19 +9902,15 @@
           <t>Vessel, Container</t>
         </is>
       </c>
-      <c r="D115" t="inlineStr">
-        <is>
-          <t>V1626459831</t>
-        </is>
-      </c>
+      <c r="D115" t="inlineStr"/>
       <c r="E115" t="inlineStr">
         <is>
-          <t>9903.03.06</t>
+          <t>9903.03.01</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>S122 EXCL,IRN/STL/ALUM,DERIV</t>
+          <t>SECTION 122 - 10% DUTY</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
@@ -9924,64 +9920,64 @@
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>9903.03.06</t>
+          <t>9903.03.01</t>
         </is>
       </c>
       <c r="I115" t="inlineStr">
         <is>
-          <t>9903.74.11,9903.94.53,8708.29.5160</t>
+          <t>5903.90.3090</t>
         </is>
       </c>
       <c r="J115" t="inlineStr">
         <is>
-          <t>BORGERS OHIO INC.</t>
+          <t>VEER CORPORATIONS INC</t>
         </is>
       </c>
       <c r="K115" t="inlineStr">
         <is>
-          <t>BORUSA02</t>
+          <t>VEECOR01</t>
         </is>
       </c>
       <c r="L115" t="inlineStr">
         <is>
-          <t>30-084196200</t>
+          <t>99-106989200</t>
         </is>
       </c>
       <c r="M115" t="inlineStr">
         <is>
-          <t>2026-06-15 00:00:00</t>
+          <t>2026-06-14 00:00:00</t>
         </is>
       </c>
       <c r="N115" t="inlineStr">
         <is>
-          <t>2026-06-13 00:00:00</t>
+          <t>2026-06-14 00:00:00</t>
         </is>
       </c>
       <c r="O115" t="inlineStr">
         <is>
-          <t>AUTONEUM CZ S.R.O.</t>
+          <t>VEER PLASTIC PVT LTD</t>
         </is>
       </c>
       <c r="P115" t="inlineStr">
         <is>
-          <t>AUTONEUM CZ S.R.O.</t>
+          <t>VEER PLASTIC PVT LTD</t>
         </is>
       </c>
       <c r="Q115" t="inlineStr">
         <is>
-          <t>2026-05-28 00:00:00</t>
+          <t>2026-04-27 00:00:00</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>2565664</t>
+          <t>2565647</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>EF4-0231432-4</t>
+          <t>EF4-0231683-2</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
@@ -10012,47 +10008,47 @@
       </c>
       <c r="I116" t="inlineStr">
         <is>
-          <t>5903.90.3090</t>
+          <t>3305.10.0000</t>
         </is>
       </c>
       <c r="J116" t="inlineStr">
         <is>
-          <t>VEER CORPORATIONS INC</t>
+          <t>ETHIQUE CONSUMER PRODUCTS, INC</t>
         </is>
       </c>
       <c r="K116" t="inlineStr">
         <is>
-          <t>VEECOR01</t>
+          <t>ETHCO01</t>
         </is>
       </c>
       <c r="L116" t="inlineStr">
         <is>
-          <t>99-106989200</t>
+          <t>85-417193400</t>
         </is>
       </c>
       <c r="M116" t="inlineStr">
         <is>
+          <t>2026-06-15 00:00:00</t>
+        </is>
+      </c>
+      <c r="N116" t="inlineStr">
+        <is>
           <t>2026-06-14 00:00:00</t>
         </is>
       </c>
-      <c r="N116" t="inlineStr">
-        <is>
-          <t>2026-06-14 00:00:00</t>
-        </is>
-      </c>
       <c r="O116" t="inlineStr">
         <is>
-          <t>VEER PLASTIC PVT LTD</t>
+          <t>SHIELING LABORATORIES LTD</t>
         </is>
       </c>
       <c r="P116" t="inlineStr">
         <is>
-          <t>VEER PLASTIC PVT LTD</t>
+          <t>SHIELING LABORATORIES LTD</t>
         </is>
       </c>
       <c r="Q116" t="inlineStr">
         <is>
-          <t>2026-04-27 00:00:00</t>
+          <t>2026-05-05 00:00:00</t>
         </is>
       </c>
     </row>
@@ -10085,7 +10081,7 @@
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>001</t>
+          <t>002</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
@@ -10095,7 +10091,7 @@
       </c>
       <c r="I117" t="inlineStr">
         <is>
-          <t>3305.10.0000</t>
+          <t>3305.90.0000</t>
         </is>
       </c>
       <c r="J117" t="inlineStr">
@@ -10168,7 +10164,7 @@
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>002</t>
+          <t>003</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
@@ -10178,7 +10174,7 @@
       </c>
       <c r="I118" t="inlineStr">
         <is>
-          <t>3305.90.0000</t>
+          <t>3307.20.0000</t>
         </is>
       </c>
       <c r="J118" t="inlineStr">
@@ -10251,7 +10247,7 @@
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>003</t>
+          <t>004</t>
         </is>
       </c>
       <c r="H119" t="inlineStr">
@@ -10261,7 +10257,7 @@
       </c>
       <c r="I119" t="inlineStr">
         <is>
-          <t>3307.20.0000</t>
+          <t>3305.10.0000</t>
         </is>
       </c>
       <c r="J119" t="inlineStr">
@@ -10308,12 +10304,12 @@
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>2565647</t>
+          <t>2565873</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>EF4-0231683-2</t>
+          <t>EF4-0231852-3</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
@@ -10334,7 +10330,7 @@
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>004</t>
+          <t>001</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
@@ -10344,22 +10340,22 @@
       </c>
       <c r="I120" t="inlineStr">
         <is>
-          <t>3305.10.0000</t>
+          <t>9903.82.01,8431.20.0000</t>
         </is>
       </c>
       <c r="J120" t="inlineStr">
         <is>
-          <t>ETHIQUE CONSUMER PRODUCTS, INC</t>
+          <t>MALLAGHAN (GA) INC.</t>
         </is>
       </c>
       <c r="K120" t="inlineStr">
         <is>
-          <t>ETHCO01</t>
+          <t>MALGA01</t>
         </is>
       </c>
       <c r="L120" t="inlineStr">
         <is>
-          <t>85-417193400</t>
+          <t>36-488102800</t>
         </is>
       </c>
       <c r="M120" t="inlineStr">
@@ -10374,29 +10370,29 @@
       </c>
       <c r="O120" t="inlineStr">
         <is>
-          <t>SHIELING LABORATORIES LTD</t>
+          <t>MALLAGHAN ENGINEERING  LTD</t>
         </is>
       </c>
       <c r="P120" t="inlineStr">
         <is>
-          <t>SHIELING LABORATORIES LTD</t>
+          <t>MALLAGHAN ENGINEERING  LTD</t>
         </is>
       </c>
       <c r="Q120" t="inlineStr">
         <is>
-          <t>2026-05-05 00:00:00</t>
+          <t>2026-05-12 00:00:00</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>2565873</t>
+          <t>2565888</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>EF4-0231852-3</t>
+          <t>EF4-0231959-6</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
@@ -10404,7 +10400,11 @@
           <t>Vessel, Container</t>
         </is>
       </c>
-      <c r="D121" t="inlineStr"/>
+      <c r="D121" t="inlineStr">
+        <is>
+          <t>V0710337820</t>
+        </is>
+      </c>
       <c r="E121" t="inlineStr">
         <is>
           <t>9903.03.01</t>
@@ -10427,27 +10427,27 @@
       </c>
       <c r="I121" t="inlineStr">
         <is>
-          <t>9903.82.01,8431.20.0000</t>
+          <t>1108.13.0010</t>
         </is>
       </c>
       <c r="J121" t="inlineStr">
         <is>
-          <t>MALLAGHAN (GA) INC.</t>
+          <t>ROYAL INGREDIENTS GROUP BV</t>
         </is>
       </c>
       <c r="K121" t="inlineStr">
         <is>
-          <t>MALGA01</t>
+          <t>ROYINGRE</t>
         </is>
       </c>
       <c r="L121" t="inlineStr">
         <is>
-          <t>36-488102800</t>
+          <t>074601-00962</t>
         </is>
       </c>
       <c r="M121" t="inlineStr">
         <is>
-          <t>2026-06-15 00:00:00</t>
+          <t>2026-06-14 00:00:00</t>
         </is>
       </c>
       <c r="N121" t="inlineStr">
@@ -10457,29 +10457,29 @@
       </c>
       <c r="O121" t="inlineStr">
         <is>
-          <t>MALLAGHAN ENGINEERING  LTD</t>
+          <t>AKV LANGHOLT AMBA</t>
         </is>
       </c>
       <c r="P121" t="inlineStr">
         <is>
-          <t>MALLAGHAN ENGINEERING  LTD</t>
+          <t>AKV LANGHOLT AMBA</t>
         </is>
       </c>
       <c r="Q121" t="inlineStr">
         <is>
-          <t>2026-05-12 00:00:00</t>
+          <t>2026-05-18 00:00:00</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>2565888</t>
+          <t>2565945</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>EF4-0231959-6</t>
+          <t>EF4-0231961-2</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
@@ -10497,11 +10497,7 @@
           <t>9903.03.01</t>
         </is>
       </c>
-      <c r="F122" t="inlineStr">
-        <is>
-          <t>SECTION 122 - 10% DUTY</t>
-        </is>
-      </c>
+      <c r="F122" t="inlineStr"/>
       <c r="G122" t="inlineStr">
         <is>
           <t>001</t>
@@ -10534,57 +10530,61 @@
       </c>
       <c r="M122" t="inlineStr">
         <is>
+          <t>2026-06-15 00:00:00</t>
+        </is>
+      </c>
+      <c r="N122" t="inlineStr">
+        <is>
           <t>2026-06-14 00:00:00</t>
         </is>
       </c>
-      <c r="N122" t="inlineStr">
-        <is>
-          <t>2026-06-14 00:00:00</t>
-        </is>
-      </c>
       <c r="O122" t="inlineStr">
         <is>
-          <t>AKV LANGHOLT AMBA</t>
+          <t>PRZEDSIEBIORSTWO PRZEMYSLU ZIEMNIAC</t>
         </is>
       </c>
       <c r="P122" t="inlineStr">
         <is>
-          <t>AKV LANGHOLT AMBA</t>
+          <t>PRZEDSIEBIORSTWO PRZEMYSLU ZIEMNIACZANEGO PEPEES S.A.</t>
         </is>
       </c>
       <c r="Q122" t="inlineStr">
         <is>
-          <t>2026-05-18 00:00:00</t>
+          <t>2026-05-17 00:00:00</t>
         </is>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>2565945</t>
+          <t>2615692</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>EF4-0231961-2</t>
+          <t>EF4-0231982-8</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>Vessel, Container</t>
+          <t>Vessel, Non-container</t>
         </is>
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>V0710337820</t>
+          <t>V8N03137232</t>
         </is>
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>9903.03.01</t>
-        </is>
-      </c>
-      <c r="F123" t="inlineStr"/>
+          <t>9903.88.15</t>
+        </is>
+      </c>
+      <c r="F123" t="inlineStr">
+        <is>
+          <t>ARTICLE OF CHINA,US NTE 20(R)</t>
+        </is>
+      </c>
       <c r="G123" t="inlineStr">
         <is>
           <t>001</t>
@@ -10592,32 +10592,32 @@
       </c>
       <c r="H123" t="inlineStr">
         <is>
-          <t>9903.03.01</t>
+          <t>9903.88.15</t>
         </is>
       </c>
       <c r="I123" t="inlineStr">
         <is>
-          <t>1108.13.0010</t>
+          <t>9903.03.01,3926.90.9989</t>
         </is>
       </c>
       <c r="J123" t="inlineStr">
         <is>
-          <t>ROYAL INGREDIENTS GROUP BV</t>
+          <t>BORGERS OHIO INC.</t>
         </is>
       </c>
       <c r="K123" t="inlineStr">
         <is>
-          <t>ROYINGRE</t>
+          <t>BORUSA02</t>
         </is>
       </c>
       <c r="L123" t="inlineStr">
         <is>
-          <t>074601-00962</t>
+          <t>30-084196200</t>
         </is>
       </c>
       <c r="M123" t="inlineStr">
         <is>
-          <t>2026-06-15 00:00:00</t>
+          <t>2026-06-04 00:00:00</t>
         </is>
       </c>
       <c r="N123" t="inlineStr">
@@ -10627,17 +10627,17 @@
       </c>
       <c r="O123" t="inlineStr">
         <is>
-          <t>PRZEDSIEBIORSTWO PRZEMYSLU ZIEMNIAC</t>
+          <t>AUTONEUM (SHANGHAI) MANAGEMENT CO.</t>
         </is>
       </c>
       <c r="P123" t="inlineStr">
         <is>
-          <t>PRZEDSIEBIORSTWO PRZEMYSLU ZIEMNIACZANEGO PEPEES S.A.</t>
+          <t>AUTONEUM (SHANGHAI) MANAGEMENT CO. LTD.</t>
         </is>
       </c>
       <c r="Q123" t="inlineStr">
         <is>
-          <t>2026-05-17 00:00:00</t>
+          <t>2026-05-19 00:00:00</t>
         </is>
       </c>
     </row>
@@ -10674,7 +10674,7 @@
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>001</t>
+          <t>002</t>
         </is>
       </c>
       <c r="H124" t="inlineStr">
@@ -10684,7 +10684,7 @@
       </c>
       <c r="I124" t="inlineStr">
         <is>
-          <t>9903.03.01,3926.90.9989</t>
+          <t>9903.03.01,3926.30.5000</t>
         </is>
       </c>
       <c r="J124" t="inlineStr">
@@ -10731,17 +10731,17 @@
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>2615692</t>
+          <t>2565999</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>EF4-0231982-8</t>
+          <t>EF4-0232009-9</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>Vessel, Non-container</t>
+          <t>Vessel, Container</t>
         </is>
       </c>
       <c r="D125" t="inlineStr">
@@ -10751,47 +10751,47 @@
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>9903.88.15</t>
+          <t>9903.03.01</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>ARTICLE OF CHINA,US NTE 20(R)</t>
+          <t>SECTION 122 - 10% DUTY</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>002</t>
+          <t>001</t>
         </is>
       </c>
       <c r="H125" t="inlineStr">
         <is>
-          <t>9903.88.15</t>
+          <t>9903.03.01</t>
         </is>
       </c>
       <c r="I125" t="inlineStr">
         <is>
-          <t>9903.03.01,3926.30.5000</t>
+          <t>1806.90.9090</t>
         </is>
       </c>
       <c r="J125" t="inlineStr">
         <is>
-          <t>BORGERS OHIO INC.</t>
+          <t>DOBLA USA MFG LLC</t>
         </is>
       </c>
       <c r="K125" t="inlineStr">
         <is>
-          <t>BORUSA02</t>
+          <t>DOBUSA</t>
         </is>
       </c>
       <c r="L125" t="inlineStr">
         <is>
-          <t>30-084196200</t>
+          <t>41-218954800</t>
         </is>
       </c>
       <c r="M125" t="inlineStr">
         <is>
-          <t>2026-06-04 00:00:00</t>
+          <t>2026-06-15 00:00:00</t>
         </is>
       </c>
       <c r="N125" t="inlineStr">
@@ -10801,12 +10801,12 @@
       </c>
       <c r="O125" t="inlineStr">
         <is>
-          <t>AUTONEUM (SHANGHAI) MANAGEMENT CO.</t>
+          <t>DOBLA LOGISTICS BVBA</t>
         </is>
       </c>
       <c r="P125" t="inlineStr">
         <is>
-          <t>AUTONEUM (SHANGHAI) MANAGEMENT CO. LTD.</t>
+          <t>DOBLA LOGISTICS BVBA</t>
         </is>
       </c>
       <c r="Q125" t="inlineStr">
@@ -10818,12 +10818,12 @@
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>2565999</t>
+          <t>2565956</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>EF4-0232009-9</t>
+          <t>EF4-0232032-1</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
@@ -10831,11 +10831,7 @@
           <t>Vessel, Container</t>
         </is>
       </c>
-      <c r="D126" t="inlineStr">
-        <is>
-          <t>V8N03137232</t>
-        </is>
-      </c>
+      <c r="D126" t="inlineStr"/>
       <c r="E126" t="inlineStr">
         <is>
           <t>9903.03.01</t>
@@ -10858,22 +10854,22 @@
       </c>
       <c r="I126" t="inlineStr">
         <is>
-          <t>1806.90.9090</t>
+          <t>9903.82.01,8431.20.0000</t>
         </is>
       </c>
       <c r="J126" t="inlineStr">
         <is>
-          <t>DOBLA USA MFG LLC</t>
+          <t>MALLAGHAN (GA) INC.</t>
         </is>
       </c>
       <c r="K126" t="inlineStr">
         <is>
-          <t>DOBUSA</t>
+          <t>MALGA01</t>
         </is>
       </c>
       <c r="L126" t="inlineStr">
         <is>
-          <t>41-218954800</t>
+          <t>36-488102800</t>
         </is>
       </c>
       <c r="M126" t="inlineStr">
@@ -10888,12 +10884,12 @@
       </c>
       <c r="O126" t="inlineStr">
         <is>
-          <t>DOBLA LOGISTICS BVBA</t>
+          <t>MALLAGHAN ENGINEERING  LTD</t>
         </is>
       </c>
       <c r="P126" t="inlineStr">
         <is>
-          <t>DOBLA LOGISTICS BVBA</t>
+          <t>MALLAGHAN ENGINEERING  LTD</t>
         </is>
       </c>
       <c r="Q126" t="inlineStr">
@@ -10905,12 +10901,12 @@
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>2565956</t>
+          <t>2566028</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>EF4-0232032-1</t>
+          <t>EF4-0232065-1</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
@@ -10924,11 +10920,7 @@
           <t>9903.03.01</t>
         </is>
       </c>
-      <c r="F127" t="inlineStr">
-        <is>
-          <t>SECTION 122 - 10% DUTY</t>
-        </is>
-      </c>
+      <c r="F127" t="inlineStr"/>
       <c r="G127" t="inlineStr">
         <is>
           <t>001</t>
@@ -10941,27 +10933,27 @@
       </c>
       <c r="I127" t="inlineStr">
         <is>
-          <t>9903.82.01,8431.20.0000</t>
+          <t>1108.12.0010</t>
         </is>
       </c>
       <c r="J127" t="inlineStr">
         <is>
-          <t>MALLAGHAN (GA) INC.</t>
+          <t>ROYAL INGREDIENTS GROUP BV</t>
         </is>
       </c>
       <c r="K127" t="inlineStr">
         <is>
-          <t>MALGA01</t>
+          <t>ROYINGRE</t>
         </is>
       </c>
       <c r="L127" t="inlineStr">
         <is>
-          <t>36-488102800</t>
+          <t>074601-00962</t>
         </is>
       </c>
       <c r="M127" t="inlineStr">
         <is>
-          <t>2026-06-15 00:00:00</t>
+          <t>2026-06-14 00:00:00</t>
         </is>
       </c>
       <c r="N127" t="inlineStr">
@@ -10971,29 +10963,29 @@
       </c>
       <c r="O127" t="inlineStr">
         <is>
-          <t>MALLAGHAN ENGINEERING  LTD</t>
+          <t>TAT NISASTA INS SAN TIC AS</t>
         </is>
       </c>
       <c r="P127" t="inlineStr">
         <is>
-          <t>MALLAGHAN ENGINEERING  LTD</t>
+          <t>TAT NISASTA INS SAN TIC AS</t>
         </is>
       </c>
       <c r="Q127" t="inlineStr">
         <is>
-          <t>2026-05-19 00:00:00</t>
+          <t>2026-05-23 00:00:00</t>
         </is>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>2566028</t>
+          <t>2566055</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>EF4-0232065-1</t>
+          <t>EF4-0232124-6</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
@@ -11001,13 +10993,21 @@
           <t>Vessel, Container</t>
         </is>
       </c>
-      <c r="D128" t="inlineStr"/>
+      <c r="D128" t="inlineStr">
+        <is>
+          <t>V0710343679</t>
+        </is>
+      </c>
       <c r="E128" t="inlineStr">
         <is>
           <t>9903.03.01</t>
         </is>
       </c>
-      <c r="F128" t="inlineStr"/>
+      <c r="F128" t="inlineStr">
+        <is>
+          <t>SECTION 122 - 10% DUTY</t>
+        </is>
+      </c>
       <c r="G128" t="inlineStr">
         <is>
           <t>001</t>
@@ -11020,7 +11020,7 @@
       </c>
       <c r="I128" t="inlineStr">
         <is>
-          <t>1108.12.0010</t>
+          <t>1109.00.9020</t>
         </is>
       </c>
       <c r="J128" t="inlineStr">
@@ -11050,29 +11050,29 @@
       </c>
       <c r="O128" t="inlineStr">
         <is>
-          <t>TAT NISASTA INS SAN TIC AS</t>
+          <t>JACKERING MUHLEN UND NAHRMITTELWERK</t>
         </is>
       </c>
       <c r="P128" t="inlineStr">
         <is>
-          <t>TAT NISASTA INS SAN TIC AS</t>
+          <t>JACKERING MUHLEN UND NAHRMITTELWERKE GMBH</t>
         </is>
       </c>
       <c r="Q128" t="inlineStr">
         <is>
-          <t>2026-05-23 00:00:00</t>
+          <t>2026-05-25 00:00:00</t>
         </is>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>2566055</t>
+          <t>2566131</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>EF4-0232124-6</t>
+          <t>EF4-0232126-1</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
@@ -11090,11 +11090,7 @@
           <t>9903.03.01</t>
         </is>
       </c>
-      <c r="F129" t="inlineStr">
-        <is>
-          <t>SECTION 122 - 10% DUTY</t>
-        </is>
-      </c>
+      <c r="F129" t="inlineStr"/>
       <c r="G129" t="inlineStr">
         <is>
           <t>001</t>
@@ -11107,7 +11103,7 @@
       </c>
       <c r="I129" t="inlineStr">
         <is>
-          <t>1109.00.9020</t>
+          <t>1108.12.0010</t>
         </is>
       </c>
       <c r="J129" t="inlineStr">
@@ -11137,29 +11133,29 @@
       </c>
       <c r="O129" t="inlineStr">
         <is>
-          <t>JACKERING MUHLEN UND NAHRMITTELWERK</t>
+          <t>TAT NISASTA INS SAN TIC AS</t>
         </is>
       </c>
       <c r="P129" t="inlineStr">
         <is>
-          <t>JACKERING MUHLEN UND NAHRMITTELWERKE GMBH</t>
+          <t>TAT NISASTA INS SAN TIC AS</t>
         </is>
       </c>
       <c r="Q129" t="inlineStr">
         <is>
-          <t>2026-05-25 00:00:00</t>
+          <t>2026-05-23 00:00:00</t>
         </is>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>2566131</t>
+          <t>2566056</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>EF4-0232126-1</t>
+          <t>EF4-0232208-7</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
@@ -11169,7 +11165,7 @@
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t>V0710343679</t>
+          <t>V1626459831</t>
         </is>
       </c>
       <c r="E130" t="inlineStr">
@@ -11177,7 +11173,11 @@
           <t>9903.03.01</t>
         </is>
       </c>
-      <c r="F130" t="inlineStr"/>
+      <c r="F130" t="inlineStr">
+        <is>
+          <t>SECTION 122 - 10% DUTY</t>
+        </is>
+      </c>
       <c r="G130" t="inlineStr">
         <is>
           <t>001</t>
@@ -11190,7 +11190,7 @@
       </c>
       <c r="I130" t="inlineStr">
         <is>
-          <t>1108.12.0010</t>
+          <t>1108.13.0010</t>
         </is>
       </c>
       <c r="J130" t="inlineStr">
@@ -11220,29 +11220,29 @@
       </c>
       <c r="O130" t="inlineStr">
         <is>
-          <t>TAT NISASTA INS SAN TIC AS</t>
+          <t>AKV LANGHOLT AMBA</t>
         </is>
       </c>
       <c r="P130" t="inlineStr">
         <is>
-          <t>TAT NISASTA INS SAN TIC AS</t>
+          <t>AKV LANGHOLT AMBA</t>
         </is>
       </c>
       <c r="Q130" t="inlineStr">
         <is>
-          <t>2026-05-23 00:00:00</t>
+          <t>2026-05-25 00:00:00</t>
         </is>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>2566056</t>
+          <t>2566180</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>EF4-0232208-7</t>
+          <t>EF4-0232260-8</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
@@ -11250,11 +11250,7 @@
           <t>Vessel, Container</t>
         </is>
       </c>
-      <c r="D131" t="inlineStr">
-        <is>
-          <t>V1626459831</t>
-        </is>
-      </c>
+      <c r="D131" t="inlineStr"/>
       <c r="E131" t="inlineStr">
         <is>
           <t>9903.03.01</t>
@@ -11277,59 +11273,59 @@
       </c>
       <c r="I131" t="inlineStr">
         <is>
-          <t>1108.13.0010</t>
+          <t>9903.82.01,8424.90.9080</t>
         </is>
       </c>
       <c r="J131" t="inlineStr">
         <is>
-          <t>ROYAL INGREDIENTS GROUP BV</t>
+          <t>EISENMANN OF SOUTH CAROLINA INC</t>
         </is>
       </c>
       <c r="K131" t="inlineStr">
         <is>
-          <t>ROYINGRE</t>
+          <t>EISINC03</t>
         </is>
       </c>
       <c r="L131" t="inlineStr">
         <is>
-          <t>074601-00962</t>
+          <t>86-240963300</t>
         </is>
       </c>
       <c r="M131" t="inlineStr">
         <is>
+          <t>2026-06-12 00:00:00</t>
+        </is>
+      </c>
+      <c r="N131" t="inlineStr">
+        <is>
           <t>2026-06-14 00:00:00</t>
         </is>
       </c>
-      <c r="N131" t="inlineStr">
-        <is>
-          <t>2026-06-14 00:00:00</t>
-        </is>
-      </c>
       <c r="O131" t="inlineStr">
         <is>
-          <t>AKV LANGHOLT AMBA</t>
+          <t>EISENMANN GMBH</t>
         </is>
       </c>
       <c r="P131" t="inlineStr">
         <is>
-          <t>AKV LANGHOLT AMBA</t>
+          <t>EISENMANN GMBH</t>
         </is>
       </c>
       <c r="Q131" t="inlineStr">
         <is>
-          <t>2026-05-25 00:00:00</t>
+          <t>2026-06-01 00:00:00</t>
         </is>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>2566180</t>
+          <t>2566053</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>EF4-0232260-8</t>
+          <t>EF4-0232278-0</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
@@ -11340,12 +11336,12 @@
       <c r="D132" t="inlineStr"/>
       <c r="E132" t="inlineStr">
         <is>
-          <t>9903.03.01</t>
+          <t>9903.03.06</t>
         </is>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>SECTION 122 - 10% DUTY</t>
+          <t>S122 EXCL,IRN/STL/ALUM,DERIV</t>
         </is>
       </c>
       <c r="G132" t="inlineStr">
@@ -11355,27 +11351,27 @@
       </c>
       <c r="H132" t="inlineStr">
         <is>
-          <t>9903.03.01</t>
+          <t>9903.03.06</t>
         </is>
       </c>
       <c r="I132" t="inlineStr">
         <is>
-          <t>9903.82.01,8424.90.9080</t>
+          <t>9903.74.11,9903.94.53,8708.29.5160</t>
         </is>
       </c>
       <c r="J132" t="inlineStr">
         <is>
-          <t>EISENMANN OF SOUTH CAROLINA INC</t>
+          <t>BORGERS USA CORP</t>
         </is>
       </c>
       <c r="K132" t="inlineStr">
         <is>
-          <t>EISINC03</t>
+          <t>BORUSA</t>
         </is>
       </c>
       <c r="L132" t="inlineStr">
         <is>
-          <t>86-240963300</t>
+          <t>65-117296500</t>
         </is>
       </c>
       <c r="M132" t="inlineStr">
@@ -11390,12 +11386,12 @@
       </c>
       <c r="O132" t="inlineStr">
         <is>
-          <t>EISENMANN GMBH</t>
+          <t>AUTONEUM CZ S.R.O.</t>
         </is>
       </c>
       <c r="P132" t="inlineStr">
         <is>
-          <t>EISENMANN GMBH</t>
+          <t>AUTONEUM CZ S.R.O.</t>
         </is>
       </c>
       <c r="Q132" t="inlineStr">
@@ -11433,7 +11429,7 @@
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>001</t>
+          <t>002</t>
         </is>
       </c>
       <c r="H133" t="inlineStr">
@@ -11516,7 +11512,7 @@
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>002</t>
+          <t>003</t>
         </is>
       </c>
       <c r="H134" t="inlineStr">
@@ -11599,7 +11595,7 @@
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>003</t>
+          <t>004</t>
         </is>
       </c>
       <c r="H135" t="inlineStr">
@@ -11682,7 +11678,7 @@
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>004</t>
+          <t>005</t>
         </is>
       </c>
       <c r="H136" t="inlineStr">
@@ -11739,12 +11735,12 @@
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>2566053</t>
+          <t>2565851</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>EF4-0232278-0</t>
+          <t>EF4-0231710-3</t>
         </is>
       </c>
       <c r="C137" t="inlineStr">
@@ -11752,70 +11748,2403 @@
           <t>Vessel, Container</t>
         </is>
       </c>
-      <c r="D137" t="inlineStr"/>
+      <c r="D137" t="inlineStr">
+        <is>
+          <t>VA923744786</t>
+        </is>
+      </c>
       <c r="E137" t="inlineStr">
         <is>
+          <t>9903.03.01</t>
+        </is>
+      </c>
+      <c r="F137" t="inlineStr">
+        <is>
+          <t>SECTION 122 - 10% DUTY</t>
+        </is>
+      </c>
+      <c r="G137" t="inlineStr">
+        <is>
+          <t>001</t>
+        </is>
+      </c>
+      <c r="H137" t="inlineStr">
+        <is>
+          <t>9903.03.01</t>
+        </is>
+      </c>
+      <c r="I137" t="inlineStr">
+        <is>
+          <t>5903.90.3090</t>
+        </is>
+      </c>
+      <c r="J137" t="inlineStr">
+        <is>
+          <t>VEER CORPORATIONS INC</t>
+        </is>
+      </c>
+      <c r="K137" t="inlineStr">
+        <is>
+          <t>VEECOR01</t>
+        </is>
+      </c>
+      <c r="L137" t="inlineStr">
+        <is>
+          <t>99-106989200</t>
+        </is>
+      </c>
+      <c r="M137" t="inlineStr">
+        <is>
+          <t>2026-06-15 00:00:00</t>
+        </is>
+      </c>
+      <c r="N137" t="inlineStr">
+        <is>
+          <t>2026-06-15 00:00:00</t>
+        </is>
+      </c>
+      <c r="O137" t="inlineStr">
+        <is>
+          <t>VEER PLASTIC PVT LTD</t>
+        </is>
+      </c>
+      <c r="P137" t="inlineStr">
+        <is>
+          <t>VEER PLASTIC PVT LTD</t>
+        </is>
+      </c>
+      <c r="Q137" t="inlineStr">
+        <is>
+          <t>2026-05-06 00:00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" t="inlineStr">
+        <is>
+          <t>2565884</t>
+        </is>
+      </c>
+      <c r="B138" t="inlineStr">
+        <is>
+          <t>EF4-0231856-4</t>
+        </is>
+      </c>
+      <c r="C138" t="inlineStr">
+        <is>
+          <t>Vessel, Container</t>
+        </is>
+      </c>
+      <c r="D138" t="inlineStr">
+        <is>
+          <t>VA923744786</t>
+        </is>
+      </c>
+      <c r="E138" t="inlineStr">
+        <is>
+          <t>9903.03.03</t>
+        </is>
+      </c>
+      <c r="F138" t="inlineStr">
+        <is>
+          <t>S122 -EXCLUSION-EXEMPTED PRDTS</t>
+        </is>
+      </c>
+      <c r="G138" t="inlineStr">
+        <is>
+          <t>001</t>
+        </is>
+      </c>
+      <c r="H138" t="inlineStr">
+        <is>
+          <t>9903.03.03</t>
+        </is>
+      </c>
+      <c r="I138" t="inlineStr">
+        <is>
+          <t>2930.90.9231</t>
+        </is>
+      </c>
+      <c r="J138" t="inlineStr">
+        <is>
+          <t>CASTLE CHEMICALS LTD</t>
+        </is>
+      </c>
+      <c r="K138" t="inlineStr">
+        <is>
+          <t>CASCHE01</t>
+        </is>
+      </c>
+      <c r="L138" t="inlineStr">
+        <is>
+          <t>151704-07138</t>
+        </is>
+      </c>
+      <c r="M138" t="inlineStr">
+        <is>
+          <t>2026-06-15 00:00:00</t>
+        </is>
+      </c>
+      <c r="N138" t="inlineStr">
+        <is>
+          <t>2026-06-15 00:00:00</t>
+        </is>
+      </c>
+      <c r="O138" t="inlineStr">
+        <is>
+          <t>HUBEI JIANGHAN NEW MATERIALS CO</t>
+        </is>
+      </c>
+      <c r="P138" t="inlineStr">
+        <is>
+          <t>HUBEI JIANGHAN NEW MATERIALS CO</t>
+        </is>
+      </c>
+      <c r="Q138" t="inlineStr">
+        <is>
+          <t>2026-05-13 00:00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" t="inlineStr">
+        <is>
+          <t>2565885</t>
+        </is>
+      </c>
+      <c r="B139" t="inlineStr">
+        <is>
+          <t>EF4-0231857-2</t>
+        </is>
+      </c>
+      <c r="C139" t="inlineStr">
+        <is>
+          <t>Vessel, Container</t>
+        </is>
+      </c>
+      <c r="D139" t="inlineStr"/>
+      <c r="E139" t="inlineStr">
+        <is>
+          <t>9903.03.03</t>
+        </is>
+      </c>
+      <c r="F139" t="inlineStr">
+        <is>
+          <t>S122 -EXCLUSION-EXEMPTED PRDTS</t>
+        </is>
+      </c>
+      <c r="G139" t="inlineStr">
+        <is>
+          <t>001</t>
+        </is>
+      </c>
+      <c r="H139" t="inlineStr">
+        <is>
+          <t>9903.03.03</t>
+        </is>
+      </c>
+      <c r="I139" t="inlineStr">
+        <is>
+          <t>2930.90.9231</t>
+        </is>
+      </c>
+      <c r="J139" t="inlineStr">
+        <is>
+          <t>CASTLE CHEMICALS LTD</t>
+        </is>
+      </c>
+      <c r="K139" t="inlineStr">
+        <is>
+          <t>CASCHE01</t>
+        </is>
+      </c>
+      <c r="L139" t="inlineStr">
+        <is>
+          <t>151704-07138</t>
+        </is>
+      </c>
+      <c r="M139" t="inlineStr">
+        <is>
+          <t>2026-06-15 00:00:00</t>
+        </is>
+      </c>
+      <c r="N139" t="inlineStr">
+        <is>
+          <t>2026-06-15 00:00:00</t>
+        </is>
+      </c>
+      <c r="O139" t="inlineStr">
+        <is>
+          <t>HUBEI JIANGHAN NEW MATERIALS CO</t>
+        </is>
+      </c>
+      <c r="P139" t="inlineStr">
+        <is>
+          <t>HUBEI JIANGHAN NEW MATERIALS CO</t>
+        </is>
+      </c>
+      <c r="Q139" t="inlineStr">
+        <is>
+          <t>2026-05-13 00:00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" t="inlineStr">
+        <is>
+          <t>2565886</t>
+        </is>
+      </c>
+      <c r="B140" t="inlineStr">
+        <is>
+          <t>EF4-0231858-0</t>
+        </is>
+      </c>
+      <c r="C140" t="inlineStr">
+        <is>
+          <t>Vessel, Container</t>
+        </is>
+      </c>
+      <c r="D140" t="inlineStr"/>
+      <c r="E140" t="inlineStr">
+        <is>
+          <t>9903.03.03</t>
+        </is>
+      </c>
+      <c r="F140" t="inlineStr">
+        <is>
+          <t>S122 -EXCLUSION-EXEMPTED PRDTS</t>
+        </is>
+      </c>
+      <c r="G140" t="inlineStr">
+        <is>
+          <t>001</t>
+        </is>
+      </c>
+      <c r="H140" t="inlineStr">
+        <is>
+          <t>9903.03.03</t>
+        </is>
+      </c>
+      <c r="I140" t="inlineStr">
+        <is>
+          <t>2930.90.9231</t>
+        </is>
+      </c>
+      <c r="J140" t="inlineStr">
+        <is>
+          <t>CASTLE CHEMICALS LTD</t>
+        </is>
+      </c>
+      <c r="K140" t="inlineStr">
+        <is>
+          <t>CASCHE01</t>
+        </is>
+      </c>
+      <c r="L140" t="inlineStr">
+        <is>
+          <t>151704-07138</t>
+        </is>
+      </c>
+      <c r="M140" t="inlineStr">
+        <is>
+          <t>2026-06-15 00:00:00</t>
+        </is>
+      </c>
+      <c r="N140" t="inlineStr">
+        <is>
+          <t>2026-06-15 00:00:00</t>
+        </is>
+      </c>
+      <c r="O140" t="inlineStr">
+        <is>
+          <t>HUBEI JIANGHAN NEW MATERIALS CO</t>
+        </is>
+      </c>
+      <c r="P140" t="inlineStr">
+        <is>
+          <t>HUBEI JIANGHAN NEW MATERIALS CO</t>
+        </is>
+      </c>
+      <c r="Q140" t="inlineStr">
+        <is>
+          <t>2026-05-13 00:00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" t="inlineStr">
+        <is>
+          <t>2565875</t>
+        </is>
+      </c>
+      <c r="B141" t="inlineStr">
+        <is>
+          <t>EF4-0231949-7</t>
+        </is>
+      </c>
+      <c r="C141" t="inlineStr">
+        <is>
+          <t>Vessel, Container</t>
+        </is>
+      </c>
+      <c r="D141" t="inlineStr"/>
+      <c r="E141" t="inlineStr">
+        <is>
+          <t>9903.03.03</t>
+        </is>
+      </c>
+      <c r="F141" t="inlineStr">
+        <is>
+          <t>S122 -EXCLUSION-EXEMPTED PRDTS</t>
+        </is>
+      </c>
+      <c r="G141" t="inlineStr">
+        <is>
+          <t>001</t>
+        </is>
+      </c>
+      <c r="H141" t="inlineStr">
+        <is>
+          <t>9903.03.03</t>
+        </is>
+      </c>
+      <c r="I141" t="inlineStr">
+        <is>
+          <t>2931.49.0055</t>
+        </is>
+      </c>
+      <c r="J141" t="inlineStr">
+        <is>
+          <t>BRUHL CHEMICAL TRADE INC</t>
+        </is>
+      </c>
+      <c r="K141" t="inlineStr">
+        <is>
+          <t>BRUCHE02</t>
+        </is>
+      </c>
+      <c r="L141" t="inlineStr">
+        <is>
+          <t>83-155181000</t>
+        </is>
+      </c>
+      <c r="M141" t="inlineStr">
+        <is>
+          <t>2026-06-15 00:00:00</t>
+        </is>
+      </c>
+      <c r="N141" t="inlineStr">
+        <is>
+          <t>2026-06-15 00:00:00</t>
+        </is>
+      </c>
+      <c r="O141" t="inlineStr">
+        <is>
+          <t>HUBEI GURUN TECHNOLOGY CO. LTD</t>
+        </is>
+      </c>
+      <c r="P141" t="inlineStr">
+        <is>
+          <t>HUBEI GURUN TECHNOLOGY CO. LTD</t>
+        </is>
+      </c>
+      <c r="Q141" t="inlineStr">
+        <is>
+          <t>2026-05-13 00:00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" t="inlineStr">
+        <is>
+          <t>2565860</t>
+        </is>
+      </c>
+      <c r="B142" t="inlineStr">
+        <is>
+          <t>EF4-0232030-5</t>
+        </is>
+      </c>
+      <c r="C142" t="inlineStr">
+        <is>
+          <t>Vessel, Container</t>
+        </is>
+      </c>
+      <c r="D142" t="inlineStr"/>
+      <c r="E142" t="inlineStr">
+        <is>
           <t>9903.03.06</t>
         </is>
       </c>
-      <c r="F137" t="inlineStr">
+      <c r="F142" t="inlineStr">
         <is>
           <t>S122 EXCL,IRN/STL/ALUM,DERIV</t>
         </is>
       </c>
-      <c r="G137" t="inlineStr">
+      <c r="G142" t="inlineStr">
+        <is>
+          <t>001</t>
+        </is>
+      </c>
+      <c r="H142" t="inlineStr">
+        <is>
+          <t>9903.03.06</t>
+        </is>
+      </c>
+      <c r="I142" t="inlineStr">
+        <is>
+          <t>9903.82.10,8415.81.0130</t>
+        </is>
+      </c>
+      <c r="J142" t="inlineStr">
+        <is>
+          <t>SUNBELT RENTALS, INC.</t>
+        </is>
+      </c>
+      <c r="K142" t="inlineStr">
+        <is>
+          <t>SUNREN01</t>
+        </is>
+      </c>
+      <c r="L142" t="inlineStr">
+        <is>
+          <t>58-041519200</t>
+        </is>
+      </c>
+      <c r="M142" t="inlineStr">
+        <is>
+          <t>2026-06-15 00:00:00</t>
+        </is>
+      </c>
+      <c r="N142" t="inlineStr">
+        <is>
+          <t>2026-06-15 00:00:00</t>
+        </is>
+      </c>
+      <c r="O142" t="inlineStr">
+        <is>
+          <t>HEPHZIBAH CO LTD</t>
+        </is>
+      </c>
+      <c r="P142" t="inlineStr">
+        <is>
+          <t>HEPHZIBAH CO LTD</t>
+        </is>
+      </c>
+      <c r="Q142" t="inlineStr">
+        <is>
+          <t>2026-05-21 00:00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" t="inlineStr">
+        <is>
+          <t>2565860</t>
+        </is>
+      </c>
+      <c r="B143" t="inlineStr">
+        <is>
+          <t>EF4-0232030-5</t>
+        </is>
+      </c>
+      <c r="C143" t="inlineStr">
+        <is>
+          <t>Vessel, Container</t>
+        </is>
+      </c>
+      <c r="D143" t="inlineStr"/>
+      <c r="E143" t="inlineStr">
+        <is>
+          <t>9903.03.06</t>
+        </is>
+      </c>
+      <c r="F143" t="inlineStr">
+        <is>
+          <t>S122 EXCL,IRN/STL/ALUM,DERIV</t>
+        </is>
+      </c>
+      <c r="G143" t="inlineStr">
+        <is>
+          <t>002</t>
+        </is>
+      </c>
+      <c r="H143" t="inlineStr">
+        <is>
+          <t>9903.03.06</t>
+        </is>
+      </c>
+      <c r="I143" t="inlineStr">
+        <is>
+          <t>9903.82.10,8415.81.0130</t>
+        </is>
+      </c>
+      <c r="J143" t="inlineStr">
+        <is>
+          <t>SUNBELT RENTALS, INC.</t>
+        </is>
+      </c>
+      <c r="K143" t="inlineStr">
+        <is>
+          <t>SUNREN01</t>
+        </is>
+      </c>
+      <c r="L143" t="inlineStr">
+        <is>
+          <t>58-041519200</t>
+        </is>
+      </c>
+      <c r="M143" t="inlineStr">
+        <is>
+          <t>2026-06-15 00:00:00</t>
+        </is>
+      </c>
+      <c r="N143" t="inlineStr">
+        <is>
+          <t>2026-06-15 00:00:00</t>
+        </is>
+      </c>
+      <c r="O143" t="inlineStr">
+        <is>
+          <t>HEPHZIBAH CO LTD</t>
+        </is>
+      </c>
+      <c r="P143" t="inlineStr">
+        <is>
+          <t>HEPHZIBAH CO LTD</t>
+        </is>
+      </c>
+      <c r="Q143" t="inlineStr">
+        <is>
+          <t>2026-05-21 00:00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" t="inlineStr">
+        <is>
+          <t>2566066</t>
+        </is>
+      </c>
+      <c r="B144" t="inlineStr">
+        <is>
+          <t>EF4-0232182-4</t>
+        </is>
+      </c>
+      <c r="C144" t="inlineStr">
+        <is>
+          <t>Vessel, Container</t>
+        </is>
+      </c>
+      <c r="D144" t="inlineStr">
+        <is>
+          <t>V1626459823</t>
+        </is>
+      </c>
+      <c r="E144" t="inlineStr">
+        <is>
+          <t>9903.03.01</t>
+        </is>
+      </c>
+      <c r="F144" t="inlineStr">
+        <is>
+          <t>SECTION 122 - 10% DUTY</t>
+        </is>
+      </c>
+      <c r="G144" t="inlineStr">
+        <is>
+          <t>001</t>
+        </is>
+      </c>
+      <c r="H144" t="inlineStr">
+        <is>
+          <t>9903.03.01</t>
+        </is>
+      </c>
+      <c r="I144" t="inlineStr">
+        <is>
+          <t>1702.30.4085</t>
+        </is>
+      </c>
+      <c r="J144" t="inlineStr">
+        <is>
+          <t>ROYAL INGREDIENTS GROUP BV</t>
+        </is>
+      </c>
+      <c r="K144" t="inlineStr">
+        <is>
+          <t>ROYINGRE</t>
+        </is>
+      </c>
+      <c r="L144" t="inlineStr">
+        <is>
+          <t>074601-00962</t>
+        </is>
+      </c>
+      <c r="M144" t="inlineStr">
+        <is>
+          <t>2026-06-16 00:00:00</t>
+        </is>
+      </c>
+      <c r="N144" t="inlineStr">
+        <is>
+          <t>2026-06-15 00:00:00</t>
+        </is>
+      </c>
+      <c r="O144" t="inlineStr">
+        <is>
+          <t>AK NISASTA SANAYI VE TICARET AS</t>
+        </is>
+      </c>
+      <c r="P144" t="inlineStr">
+        <is>
+          <t>AK NISASTA SANAYI VE TICARET AS</t>
+        </is>
+      </c>
+      <c r="Q144" t="inlineStr">
+        <is>
+          <t>2026-05-27 00:00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" t="inlineStr">
+        <is>
+          <t>2565958</t>
+        </is>
+      </c>
+      <c r="B145" t="inlineStr">
+        <is>
+          <t>EF4-0232210-3</t>
+        </is>
+      </c>
+      <c r="C145" t="inlineStr">
+        <is>
+          <t>Vessel, Container</t>
+        </is>
+      </c>
+      <c r="D145" t="inlineStr">
+        <is>
+          <t>V1626459823</t>
+        </is>
+      </c>
+      <c r="E145" t="inlineStr">
+        <is>
+          <t>9903.03.06</t>
+        </is>
+      </c>
+      <c r="F145" t="inlineStr">
+        <is>
+          <t>S122 EXCL,IRN/STL/ALUM,DERIV</t>
+        </is>
+      </c>
+      <c r="G145" t="inlineStr">
+        <is>
+          <t>001</t>
+        </is>
+      </c>
+      <c r="H145" t="inlineStr">
+        <is>
+          <t>9903.03.06</t>
+        </is>
+      </c>
+      <c r="I145" t="inlineStr">
+        <is>
+          <t>9903.74.11,9903.94.53,8708.29.5160</t>
+        </is>
+      </c>
+      <c r="J145" t="inlineStr">
+        <is>
+          <t>BORGERS OHIO INC.</t>
+        </is>
+      </c>
+      <c r="K145" t="inlineStr">
+        <is>
+          <t>BORUSA02</t>
+        </is>
+      </c>
+      <c r="L145" t="inlineStr">
+        <is>
+          <t>30-084196200</t>
+        </is>
+      </c>
+      <c r="M145" t="inlineStr">
+        <is>
+          <t>2026-06-15 00:00:00</t>
+        </is>
+      </c>
+      <c r="N145" t="inlineStr">
+        <is>
+          <t>2026-06-15 00:00:00</t>
+        </is>
+      </c>
+      <c r="O145" t="inlineStr">
+        <is>
+          <t>AUTONEUM CZ S.R.O.</t>
+        </is>
+      </c>
+      <c r="P145" t="inlineStr">
+        <is>
+          <t>AUTONEUM CZ S.R.O.</t>
+        </is>
+      </c>
+      <c r="Q145" t="inlineStr">
+        <is>
+          <t>2026-05-28 00:00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" t="inlineStr">
+        <is>
+          <t>4539483</t>
+        </is>
+      </c>
+      <c r="B146" t="inlineStr">
+        <is>
+          <t>EF4-0232485-1</t>
+        </is>
+      </c>
+      <c r="C146" t="inlineStr">
+        <is>
+          <t>Air, Non-container</t>
+        </is>
+      </c>
+      <c r="D146" t="inlineStr">
+        <is>
+          <t>V9S19229198</t>
+        </is>
+      </c>
+      <c r="E146" t="inlineStr">
+        <is>
+          <t>9903.03.01</t>
+        </is>
+      </c>
+      <c r="F146" t="inlineStr">
+        <is>
+          <t>SECTION 122 - 10% DUTY</t>
+        </is>
+      </c>
+      <c r="G146" t="inlineStr">
+        <is>
+          <t>001</t>
+        </is>
+      </c>
+      <c r="H146" t="inlineStr">
+        <is>
+          <t>9903.03.01</t>
+        </is>
+      </c>
+      <c r="I146" t="inlineStr">
+        <is>
+          <t>8481.80.9050</t>
+        </is>
+      </c>
+      <c r="J146" t="inlineStr">
+        <is>
+          <t>EUROPEAN SPARE PARTS SERVICE INC</t>
+        </is>
+      </c>
+      <c r="K146" t="inlineStr">
+        <is>
+          <t>ESSEUR</t>
+        </is>
+      </c>
+      <c r="L146" t="inlineStr">
+        <is>
+          <t>58-181585100</t>
+        </is>
+      </c>
+      <c r="M146" t="inlineStr">
+        <is>
+          <t>2026-06-14 00:00:00</t>
+        </is>
+      </c>
+      <c r="N146" t="inlineStr">
+        <is>
+          <t>2026-06-15 00:00:00</t>
+        </is>
+      </c>
+      <c r="O146" t="inlineStr">
+        <is>
+          <t>HJK INTERNATIONAL GMBH</t>
+        </is>
+      </c>
+      <c r="P146" t="inlineStr">
+        <is>
+          <t>HJK INTERNATIONAL GMBH</t>
+        </is>
+      </c>
+      <c r="Q146" t="inlineStr">
+        <is>
+          <t>2026-06-12 00:00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" t="inlineStr">
+        <is>
+          <t>4539483</t>
+        </is>
+      </c>
+      <c r="B147" t="inlineStr">
+        <is>
+          <t>EF4-0232485-1</t>
+        </is>
+      </c>
+      <c r="C147" t="inlineStr">
+        <is>
+          <t>Air, Non-container</t>
+        </is>
+      </c>
+      <c r="D147" t="inlineStr">
+        <is>
+          <t>V9S19229198</t>
+        </is>
+      </c>
+      <c r="E147" t="inlineStr">
+        <is>
+          <t>9903.03.06</t>
+        </is>
+      </c>
+      <c r="F147" t="inlineStr">
+        <is>
+          <t>S122 EXCL,IRN/STL/ALUM,DERIV</t>
+        </is>
+      </c>
+      <c r="G147" t="inlineStr">
+        <is>
+          <t>002</t>
+        </is>
+      </c>
+      <c r="H147" t="inlineStr">
+        <is>
+          <t>9903.03.06</t>
+        </is>
+      </c>
+      <c r="I147" t="inlineStr">
+        <is>
+          <t>9903.82.10,8479.89.9599</t>
+        </is>
+      </c>
+      <c r="J147" t="inlineStr">
+        <is>
+          <t>EUROPEAN SPARE PARTS SERVICE INC</t>
+        </is>
+      </c>
+      <c r="K147" t="inlineStr">
+        <is>
+          <t>ESSEUR</t>
+        </is>
+      </c>
+      <c r="L147" t="inlineStr">
+        <is>
+          <t>58-181585100</t>
+        </is>
+      </c>
+      <c r="M147" t="inlineStr">
+        <is>
+          <t>2026-06-14 00:00:00</t>
+        </is>
+      </c>
+      <c r="N147" t="inlineStr">
+        <is>
+          <t>2026-06-15 00:00:00</t>
+        </is>
+      </c>
+      <c r="O147" t="inlineStr">
+        <is>
+          <t>HJK INTERNATIONAL GMBH</t>
+        </is>
+      </c>
+      <c r="P147" t="inlineStr">
+        <is>
+          <t>HJK INTERNATIONAL GMBH</t>
+        </is>
+      </c>
+      <c r="Q147" t="inlineStr">
+        <is>
+          <t>2026-06-12 00:00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" t="inlineStr">
+        <is>
+          <t>4539483</t>
+        </is>
+      </c>
+      <c r="B148" t="inlineStr">
+        <is>
+          <t>EF4-0232485-1</t>
+        </is>
+      </c>
+      <c r="C148" t="inlineStr">
+        <is>
+          <t>Air, Non-container</t>
+        </is>
+      </c>
+      <c r="D148" t="inlineStr">
+        <is>
+          <t>V9S19229198</t>
+        </is>
+      </c>
+      <c r="E148" t="inlineStr">
+        <is>
+          <t>9903.03.01</t>
+        </is>
+      </c>
+      <c r="F148" t="inlineStr">
+        <is>
+          <t>SECTION 122 - 10% DUTY</t>
+        </is>
+      </c>
+      <c r="G148" t="inlineStr">
+        <is>
+          <t>003</t>
+        </is>
+      </c>
+      <c r="H148" t="inlineStr">
+        <is>
+          <t>9903.03.01</t>
+        </is>
+      </c>
+      <c r="I148" t="inlineStr">
+        <is>
+          <t>8501.31.2000</t>
+        </is>
+      </c>
+      <c r="J148" t="inlineStr">
+        <is>
+          <t>EUROPEAN SPARE PARTS SERVICE INC</t>
+        </is>
+      </c>
+      <c r="K148" t="inlineStr">
+        <is>
+          <t>ESSEUR</t>
+        </is>
+      </c>
+      <c r="L148" t="inlineStr">
+        <is>
+          <t>58-181585100</t>
+        </is>
+      </c>
+      <c r="M148" t="inlineStr">
+        <is>
+          <t>2026-06-14 00:00:00</t>
+        </is>
+      </c>
+      <c r="N148" t="inlineStr">
+        <is>
+          <t>2026-06-15 00:00:00</t>
+        </is>
+      </c>
+      <c r="O148" t="inlineStr">
+        <is>
+          <t>HJK INTERNATIONAL GMBH</t>
+        </is>
+      </c>
+      <c r="P148" t="inlineStr">
+        <is>
+          <t>HJK INTERNATIONAL GMBH</t>
+        </is>
+      </c>
+      <c r="Q148" t="inlineStr">
+        <is>
+          <t>2026-06-12 00:00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" t="inlineStr">
+        <is>
+          <t>4539483</t>
+        </is>
+      </c>
+      <c r="B149" t="inlineStr">
+        <is>
+          <t>EF4-0232485-1</t>
+        </is>
+      </c>
+      <c r="C149" t="inlineStr">
+        <is>
+          <t>Air, Non-container</t>
+        </is>
+      </c>
+      <c r="D149" t="inlineStr">
+        <is>
+          <t>V9S19229198</t>
+        </is>
+      </c>
+      <c r="E149" t="inlineStr">
+        <is>
+          <t>9903.03.06</t>
+        </is>
+      </c>
+      <c r="F149" t="inlineStr">
+        <is>
+          <t>S122 EXCL,IRN/STL/ALUM,DERIV</t>
+        </is>
+      </c>
+      <c r="G149" t="inlineStr">
+        <is>
+          <t>004</t>
+        </is>
+      </c>
+      <c r="H149" t="inlineStr">
+        <is>
+          <t>9903.03.06</t>
+        </is>
+      </c>
+      <c r="I149" t="inlineStr">
+        <is>
+          <t>9903.82.02,7320.90.5060</t>
+        </is>
+      </c>
+      <c r="J149" t="inlineStr">
+        <is>
+          <t>EUROPEAN SPARE PARTS SERVICE INC</t>
+        </is>
+      </c>
+      <c r="K149" t="inlineStr">
+        <is>
+          <t>ESSEUR</t>
+        </is>
+      </c>
+      <c r="L149" t="inlineStr">
+        <is>
+          <t>58-181585100</t>
+        </is>
+      </c>
+      <c r="M149" t="inlineStr">
+        <is>
+          <t>2026-06-14 00:00:00</t>
+        </is>
+      </c>
+      <c r="N149" t="inlineStr">
+        <is>
+          <t>2026-06-15 00:00:00</t>
+        </is>
+      </c>
+      <c r="O149" t="inlineStr">
+        <is>
+          <t>HJK INTERNATIONAL GMBH</t>
+        </is>
+      </c>
+      <c r="P149" t="inlineStr">
+        <is>
+          <t>HJK INTERNATIONAL GMBH</t>
+        </is>
+      </c>
+      <c r="Q149" t="inlineStr">
+        <is>
+          <t>2026-06-12 00:00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" t="inlineStr">
+        <is>
+          <t>4539483</t>
+        </is>
+      </c>
+      <c r="B150" t="inlineStr">
+        <is>
+          <t>EF4-0232485-1</t>
+        </is>
+      </c>
+      <c r="C150" t="inlineStr">
+        <is>
+          <t>Air, Non-container</t>
+        </is>
+      </c>
+      <c r="D150" t="inlineStr">
+        <is>
+          <t>V9S19229198</t>
+        </is>
+      </c>
+      <c r="E150" t="inlineStr">
+        <is>
+          <t>9903.03.06</t>
+        </is>
+      </c>
+      <c r="F150" t="inlineStr">
+        <is>
+          <t>S122 EXCL,IRN/STL/ALUM,DERIV</t>
+        </is>
+      </c>
+      <c r="G150" t="inlineStr">
         <is>
           <t>005</t>
         </is>
       </c>
-      <c r="H137" t="inlineStr">
+      <c r="H150" t="inlineStr">
         <is>
           <t>9903.03.06</t>
         </is>
       </c>
-      <c r="I137" t="inlineStr">
-        <is>
-          <t>9903.74.11,9903.94.53,8708.29.5160</t>
-        </is>
-      </c>
-      <c r="J137" t="inlineStr">
-        <is>
-          <t>BORGERS USA CORP</t>
-        </is>
-      </c>
-      <c r="K137" t="inlineStr">
-        <is>
-          <t>BORUSA</t>
-        </is>
-      </c>
-      <c r="L137" t="inlineStr">
-        <is>
-          <t>65-117296500</t>
-        </is>
-      </c>
-      <c r="M137" t="inlineStr">
+      <c r="I150" t="inlineStr">
+        <is>
+          <t>9903.82.02,7320.90.5060</t>
+        </is>
+      </c>
+      <c r="J150" t="inlineStr">
+        <is>
+          <t>EUROPEAN SPARE PARTS SERVICE INC</t>
+        </is>
+      </c>
+      <c r="K150" t="inlineStr">
+        <is>
+          <t>ESSEUR</t>
+        </is>
+      </c>
+      <c r="L150" t="inlineStr">
+        <is>
+          <t>58-181585100</t>
+        </is>
+      </c>
+      <c r="M150" t="inlineStr">
+        <is>
+          <t>2026-06-14 00:00:00</t>
+        </is>
+      </c>
+      <c r="N150" t="inlineStr">
+        <is>
+          <t>2026-06-15 00:00:00</t>
+        </is>
+      </c>
+      <c r="O150" t="inlineStr">
+        <is>
+          <t>HJK INTERNATIONAL GMBH</t>
+        </is>
+      </c>
+      <c r="P150" t="inlineStr">
+        <is>
+          <t>HJK INTERNATIONAL GMBH</t>
+        </is>
+      </c>
+      <c r="Q150" t="inlineStr">
         <is>
           <t>2026-06-12 00:00:00</t>
         </is>
       </c>
-      <c r="N137" t="inlineStr">
+    </row>
+    <row r="151">
+      <c r="A151" t="inlineStr">
+        <is>
+          <t>4539483</t>
+        </is>
+      </c>
+      <c r="B151" t="inlineStr">
+        <is>
+          <t>EF4-0232485-1</t>
+        </is>
+      </c>
+      <c r="C151" t="inlineStr">
+        <is>
+          <t>Air, Non-container</t>
+        </is>
+      </c>
+      <c r="D151" t="inlineStr">
+        <is>
+          <t>V9S19229198</t>
+        </is>
+      </c>
+      <c r="E151" t="inlineStr">
+        <is>
+          <t>9903.03.01</t>
+        </is>
+      </c>
+      <c r="F151" t="inlineStr">
+        <is>
+          <t>SECTION 122 - 10% DUTY</t>
+        </is>
+      </c>
+      <c r="G151" t="inlineStr">
+        <is>
+          <t>006</t>
+        </is>
+      </c>
+      <c r="H151" t="inlineStr">
+        <is>
+          <t>9903.03.01</t>
+        </is>
+      </c>
+      <c r="I151" t="inlineStr">
+        <is>
+          <t>8443.91.3000</t>
+        </is>
+      </c>
+      <c r="J151" t="inlineStr">
+        <is>
+          <t>EUROPEAN SPARE PARTS SERVICE INC</t>
+        </is>
+      </c>
+      <c r="K151" t="inlineStr">
+        <is>
+          <t>ESSEUR</t>
+        </is>
+      </c>
+      <c r="L151" t="inlineStr">
+        <is>
+          <t>58-181585100</t>
+        </is>
+      </c>
+      <c r="M151" t="inlineStr">
         <is>
           <t>2026-06-14 00:00:00</t>
         </is>
       </c>
-      <c r="O137" t="inlineStr">
-        <is>
-          <t>AUTONEUM CZ S.R.O.</t>
-        </is>
-      </c>
-      <c r="P137" t="inlineStr">
-        <is>
-          <t>AUTONEUM CZ S.R.O.</t>
-        </is>
-      </c>
-      <c r="Q137" t="inlineStr">
-        <is>
-          <t>2026-06-01 00:00:00</t>
+      <c r="N151" t="inlineStr">
+        <is>
+          <t>2026-06-15 00:00:00</t>
+        </is>
+      </c>
+      <c r="O151" t="inlineStr">
+        <is>
+          <t>HJK INTERNATIONAL GMBH</t>
+        </is>
+      </c>
+      <c r="P151" t="inlineStr">
+        <is>
+          <t>HJK INTERNATIONAL GMBH</t>
+        </is>
+      </c>
+      <c r="Q151" t="inlineStr">
+        <is>
+          <t>2026-06-12 00:00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" t="inlineStr">
+        <is>
+          <t>4539483</t>
+        </is>
+      </c>
+      <c r="B152" t="inlineStr">
+        <is>
+          <t>EF4-0232485-1</t>
+        </is>
+      </c>
+      <c r="C152" t="inlineStr">
+        <is>
+          <t>Air, Non-container</t>
+        </is>
+      </c>
+      <c r="D152" t="inlineStr">
+        <is>
+          <t>V9S19229198</t>
+        </is>
+      </c>
+      <c r="E152" t="inlineStr">
+        <is>
+          <t>9903.03.01</t>
+        </is>
+      </c>
+      <c r="F152" t="inlineStr">
+        <is>
+          <t>SECTION 122 - 10% DUTY</t>
+        </is>
+      </c>
+      <c r="G152" t="inlineStr">
+        <is>
+          <t>007</t>
+        </is>
+      </c>
+      <c r="H152" t="inlineStr">
+        <is>
+          <t>9903.03.01</t>
+        </is>
+      </c>
+      <c r="I152" t="inlineStr">
+        <is>
+          <t>8443.91.3000</t>
+        </is>
+      </c>
+      <c r="J152" t="inlineStr">
+        <is>
+          <t>EUROPEAN SPARE PARTS SERVICE INC</t>
+        </is>
+      </c>
+      <c r="K152" t="inlineStr">
+        <is>
+          <t>ESSEUR</t>
+        </is>
+      </c>
+      <c r="L152" t="inlineStr">
+        <is>
+          <t>58-181585100</t>
+        </is>
+      </c>
+      <c r="M152" t="inlineStr">
+        <is>
+          <t>2026-06-14 00:00:00</t>
+        </is>
+      </c>
+      <c r="N152" t="inlineStr">
+        <is>
+          <t>2026-06-15 00:00:00</t>
+        </is>
+      </c>
+      <c r="O152" t="inlineStr">
+        <is>
+          <t>HJK INTERNATIONAL GMBH</t>
+        </is>
+      </c>
+      <c r="P152" t="inlineStr">
+        <is>
+          <t>HJK INTERNATIONAL GMBH</t>
+        </is>
+      </c>
+      <c r="Q152" t="inlineStr">
+        <is>
+          <t>2026-06-12 00:00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" t="inlineStr">
+        <is>
+          <t>4539483</t>
+        </is>
+      </c>
+      <c r="B153" t="inlineStr">
+        <is>
+          <t>EF4-0232485-1</t>
+        </is>
+      </c>
+      <c r="C153" t="inlineStr">
+        <is>
+          <t>Air, Non-container</t>
+        </is>
+      </c>
+      <c r="D153" t="inlineStr">
+        <is>
+          <t>V9S19229198</t>
+        </is>
+      </c>
+      <c r="E153" t="inlineStr">
+        <is>
+          <t>9903.03.01</t>
+        </is>
+      </c>
+      <c r="F153" t="inlineStr">
+        <is>
+          <t>SECTION 122 - 10% DUTY</t>
+        </is>
+      </c>
+      <c r="G153" t="inlineStr">
+        <is>
+          <t>008</t>
+        </is>
+      </c>
+      <c r="H153" t="inlineStr">
+        <is>
+          <t>9903.03.01</t>
+        </is>
+      </c>
+      <c r="I153" t="inlineStr">
+        <is>
+          <t>8414.59.6595</t>
+        </is>
+      </c>
+      <c r="J153" t="inlineStr">
+        <is>
+          <t>EUROPEAN SPARE PARTS SERVICE INC</t>
+        </is>
+      </c>
+      <c r="K153" t="inlineStr">
+        <is>
+          <t>ESSEUR</t>
+        </is>
+      </c>
+      <c r="L153" t="inlineStr">
+        <is>
+          <t>58-181585100</t>
+        </is>
+      </c>
+      <c r="M153" t="inlineStr">
+        <is>
+          <t>2026-06-14 00:00:00</t>
+        </is>
+      </c>
+      <c r="N153" t="inlineStr">
+        <is>
+          <t>2026-06-15 00:00:00</t>
+        </is>
+      </c>
+      <c r="O153" t="inlineStr">
+        <is>
+          <t>HJK INTERNATIONAL GMBH</t>
+        </is>
+      </c>
+      <c r="P153" t="inlineStr">
+        <is>
+          <t>HJK INTERNATIONAL GMBH</t>
+        </is>
+      </c>
+      <c r="Q153" t="inlineStr">
+        <is>
+          <t>2026-06-12 00:00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" t="inlineStr">
+        <is>
+          <t>4539483</t>
+        </is>
+      </c>
+      <c r="B154" t="inlineStr">
+        <is>
+          <t>EF4-0232485-1</t>
+        </is>
+      </c>
+      <c r="C154" t="inlineStr">
+        <is>
+          <t>Air, Non-container</t>
+        </is>
+      </c>
+      <c r="D154" t="inlineStr">
+        <is>
+          <t>V9S19229198</t>
+        </is>
+      </c>
+      <c r="E154" t="inlineStr">
+        <is>
+          <t>9903.03.06</t>
+        </is>
+      </c>
+      <c r="F154" t="inlineStr">
+        <is>
+          <t>S122 EXCL,IRN/STL/ALUM,DERIV</t>
+        </is>
+      </c>
+      <c r="G154" t="inlineStr">
+        <is>
+          <t>009</t>
+        </is>
+      </c>
+      <c r="H154" t="inlineStr">
+        <is>
+          <t>9903.03.06</t>
+        </is>
+      </c>
+      <c r="I154" t="inlineStr">
+        <is>
+          <t>9903.82.02,7320.90.5060</t>
+        </is>
+      </c>
+      <c r="J154" t="inlineStr">
+        <is>
+          <t>EUROPEAN SPARE PARTS SERVICE INC</t>
+        </is>
+      </c>
+      <c r="K154" t="inlineStr">
+        <is>
+          <t>ESSEUR</t>
+        </is>
+      </c>
+      <c r="L154" t="inlineStr">
+        <is>
+          <t>58-181585100</t>
+        </is>
+      </c>
+      <c r="M154" t="inlineStr">
+        <is>
+          <t>2026-06-14 00:00:00</t>
+        </is>
+      </c>
+      <c r="N154" t="inlineStr">
+        <is>
+          <t>2026-06-15 00:00:00</t>
+        </is>
+      </c>
+      <c r="O154" t="inlineStr">
+        <is>
+          <t>HJK INTERNATIONAL GMBH</t>
+        </is>
+      </c>
+      <c r="P154" t="inlineStr">
+        <is>
+          <t>HJK INTERNATIONAL GMBH</t>
+        </is>
+      </c>
+      <c r="Q154" t="inlineStr">
+        <is>
+          <t>2026-06-12 00:00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" t="inlineStr">
+        <is>
+          <t>4539483</t>
+        </is>
+      </c>
+      <c r="B155" t="inlineStr">
+        <is>
+          <t>EF4-0232485-1</t>
+        </is>
+      </c>
+      <c r="C155" t="inlineStr">
+        <is>
+          <t>Air, Non-container</t>
+        </is>
+      </c>
+      <c r="D155" t="inlineStr">
+        <is>
+          <t>V9S19229198</t>
+        </is>
+      </c>
+      <c r="E155" t="inlineStr">
+        <is>
+          <t>9903.03.01</t>
+        </is>
+      </c>
+      <c r="F155" t="inlineStr">
+        <is>
+          <t>SECTION 122 - 10% DUTY</t>
+        </is>
+      </c>
+      <c r="G155" t="inlineStr">
+        <is>
+          <t>010</t>
+        </is>
+      </c>
+      <c r="H155" t="inlineStr">
+        <is>
+          <t>9903.03.01</t>
+        </is>
+      </c>
+      <c r="I155" t="inlineStr">
+        <is>
+          <t>9903.94.06,8537.10.9160</t>
+        </is>
+      </c>
+      <c r="J155" t="inlineStr">
+        <is>
+          <t>EUROPEAN SPARE PARTS SERVICE INC</t>
+        </is>
+      </c>
+      <c r="K155" t="inlineStr">
+        <is>
+          <t>ESSEUR</t>
+        </is>
+      </c>
+      <c r="L155" t="inlineStr">
+        <is>
+          <t>58-181585100</t>
+        </is>
+      </c>
+      <c r="M155" t="inlineStr">
+        <is>
+          <t>2026-06-14 00:00:00</t>
+        </is>
+      </c>
+      <c r="N155" t="inlineStr">
+        <is>
+          <t>2026-06-15 00:00:00</t>
+        </is>
+      </c>
+      <c r="O155" t="inlineStr">
+        <is>
+          <t>HJK INTERNATIONAL GMBH</t>
+        </is>
+      </c>
+      <c r="P155" t="inlineStr">
+        <is>
+          <t>HJK INTERNATIONAL GMBH</t>
+        </is>
+      </c>
+      <c r="Q155" t="inlineStr">
+        <is>
+          <t>2026-06-12 00:00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156" t="inlineStr">
+        <is>
+          <t>4539483</t>
+        </is>
+      </c>
+      <c r="B156" t="inlineStr">
+        <is>
+          <t>EF4-0232485-1</t>
+        </is>
+      </c>
+      <c r="C156" t="inlineStr">
+        <is>
+          <t>Air, Non-container</t>
+        </is>
+      </c>
+      <c r="D156" t="inlineStr">
+        <is>
+          <t>V9S19229198</t>
+        </is>
+      </c>
+      <c r="E156" t="inlineStr">
+        <is>
+          <t>9903.03.01</t>
+        </is>
+      </c>
+      <c r="F156" t="inlineStr">
+        <is>
+          <t>SECTION 122 - 10% DUTY</t>
+        </is>
+      </c>
+      <c r="G156" t="inlineStr">
+        <is>
+          <t>011</t>
+        </is>
+      </c>
+      <c r="H156" t="inlineStr">
+        <is>
+          <t>9903.03.01</t>
+        </is>
+      </c>
+      <c r="I156" t="inlineStr">
+        <is>
+          <t>8443.91.3000</t>
+        </is>
+      </c>
+      <c r="J156" t="inlineStr">
+        <is>
+          <t>EUROPEAN SPARE PARTS SERVICE INC</t>
+        </is>
+      </c>
+      <c r="K156" t="inlineStr">
+        <is>
+          <t>ESSEUR</t>
+        </is>
+      </c>
+      <c r="L156" t="inlineStr">
+        <is>
+          <t>58-181585100</t>
+        </is>
+      </c>
+      <c r="M156" t="inlineStr">
+        <is>
+          <t>2026-06-14 00:00:00</t>
+        </is>
+      </c>
+      <c r="N156" t="inlineStr">
+        <is>
+          <t>2026-06-15 00:00:00</t>
+        </is>
+      </c>
+      <c r="O156" t="inlineStr">
+        <is>
+          <t>HJK INTERNATIONAL GMBH</t>
+        </is>
+      </c>
+      <c r="P156" t="inlineStr">
+        <is>
+          <t>HJK INTERNATIONAL GMBH</t>
+        </is>
+      </c>
+      <c r="Q156" t="inlineStr">
+        <is>
+          <t>2026-06-12 00:00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="157">
+      <c r="A157" t="inlineStr">
+        <is>
+          <t>4539483</t>
+        </is>
+      </c>
+      <c r="B157" t="inlineStr">
+        <is>
+          <t>EF4-0232485-1</t>
+        </is>
+      </c>
+      <c r="C157" t="inlineStr">
+        <is>
+          <t>Air, Non-container</t>
+        </is>
+      </c>
+      <c r="D157" t="inlineStr">
+        <is>
+          <t>V9S19229198</t>
+        </is>
+      </c>
+      <c r="E157" t="inlineStr">
+        <is>
+          <t>9903.03.01</t>
+        </is>
+      </c>
+      <c r="F157" t="inlineStr">
+        <is>
+          <t>SECTION 122 - 10% DUTY</t>
+        </is>
+      </c>
+      <c r="G157" t="inlineStr">
+        <is>
+          <t>012</t>
+        </is>
+      </c>
+      <c r="H157" t="inlineStr">
+        <is>
+          <t>9903.03.01</t>
+        </is>
+      </c>
+      <c r="I157" t="inlineStr">
+        <is>
+          <t>4016.93.5050</t>
+        </is>
+      </c>
+      <c r="J157" t="inlineStr">
+        <is>
+          <t>EUROPEAN SPARE PARTS SERVICE INC</t>
+        </is>
+      </c>
+      <c r="K157" t="inlineStr">
+        <is>
+          <t>ESSEUR</t>
+        </is>
+      </c>
+      <c r="L157" t="inlineStr">
+        <is>
+          <t>58-181585100</t>
+        </is>
+      </c>
+      <c r="M157" t="inlineStr">
+        <is>
+          <t>2026-06-14 00:00:00</t>
+        </is>
+      </c>
+      <c r="N157" t="inlineStr">
+        <is>
+          <t>2026-06-15 00:00:00</t>
+        </is>
+      </c>
+      <c r="O157" t="inlineStr">
+        <is>
+          <t>HJK INTERNATIONAL GMBH</t>
+        </is>
+      </c>
+      <c r="P157" t="inlineStr">
+        <is>
+          <t>HJK INTERNATIONAL GMBH</t>
+        </is>
+      </c>
+      <c r="Q157" t="inlineStr">
+        <is>
+          <t>2026-06-12 00:00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="158">
+      <c r="A158" t="inlineStr">
+        <is>
+          <t>4539483</t>
+        </is>
+      </c>
+      <c r="B158" t="inlineStr">
+        <is>
+          <t>EF4-0232485-1</t>
+        </is>
+      </c>
+      <c r="C158" t="inlineStr">
+        <is>
+          <t>Air, Non-container</t>
+        </is>
+      </c>
+      <c r="D158" t="inlineStr">
+        <is>
+          <t>V9S19229198</t>
+        </is>
+      </c>
+      <c r="E158" t="inlineStr">
+        <is>
+          <t>9903.03.01</t>
+        </is>
+      </c>
+      <c r="F158" t="inlineStr">
+        <is>
+          <t>SECTION 122 - 10% DUTY</t>
+        </is>
+      </c>
+      <c r="G158" t="inlineStr">
+        <is>
+          <t>013</t>
+        </is>
+      </c>
+      <c r="H158" t="inlineStr">
+        <is>
+          <t>9903.03.01</t>
+        </is>
+      </c>
+      <c r="I158" t="inlineStr">
+        <is>
+          <t>8481.80.9050</t>
+        </is>
+      </c>
+      <c r="J158" t="inlineStr">
+        <is>
+          <t>EUROPEAN SPARE PARTS SERVICE INC</t>
+        </is>
+      </c>
+      <c r="K158" t="inlineStr">
+        <is>
+          <t>ESSEUR</t>
+        </is>
+      </c>
+      <c r="L158" t="inlineStr">
+        <is>
+          <t>58-181585100</t>
+        </is>
+      </c>
+      <c r="M158" t="inlineStr">
+        <is>
+          <t>2026-06-14 00:00:00</t>
+        </is>
+      </c>
+      <c r="N158" t="inlineStr">
+        <is>
+          <t>2026-06-15 00:00:00</t>
+        </is>
+      </c>
+      <c r="O158" t="inlineStr">
+        <is>
+          <t>HJK INTERNATIONAL GMBH</t>
+        </is>
+      </c>
+      <c r="P158" t="inlineStr">
+        <is>
+          <t>HJK INTERNATIONAL GMBH</t>
+        </is>
+      </c>
+      <c r="Q158" t="inlineStr">
+        <is>
+          <t>2026-06-12 00:00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="159">
+      <c r="A159" t="inlineStr">
+        <is>
+          <t>4539483</t>
+        </is>
+      </c>
+      <c r="B159" t="inlineStr">
+        <is>
+          <t>EF4-0232485-1</t>
+        </is>
+      </c>
+      <c r="C159" t="inlineStr">
+        <is>
+          <t>Air, Non-container</t>
+        </is>
+      </c>
+      <c r="D159" t="inlineStr">
+        <is>
+          <t>V9S19229198</t>
+        </is>
+      </c>
+      <c r="E159" t="inlineStr">
+        <is>
+          <t>9903.03.01</t>
+        </is>
+      </c>
+      <c r="F159" t="inlineStr">
+        <is>
+          <t>SECTION 122 - 10% DUTY</t>
+        </is>
+      </c>
+      <c r="G159" t="inlineStr">
+        <is>
+          <t>014</t>
+        </is>
+      </c>
+      <c r="H159" t="inlineStr">
+        <is>
+          <t>9903.03.01</t>
+        </is>
+      </c>
+      <c r="I159" t="inlineStr">
+        <is>
+          <t>8443.91.3000</t>
+        </is>
+      </c>
+      <c r="J159" t="inlineStr">
+        <is>
+          <t>EUROPEAN SPARE PARTS SERVICE INC</t>
+        </is>
+      </c>
+      <c r="K159" t="inlineStr">
+        <is>
+          <t>ESSEUR</t>
+        </is>
+      </c>
+      <c r="L159" t="inlineStr">
+        <is>
+          <t>58-181585100</t>
+        </is>
+      </c>
+      <c r="M159" t="inlineStr">
+        <is>
+          <t>2026-06-14 00:00:00</t>
+        </is>
+      </c>
+      <c r="N159" t="inlineStr">
+        <is>
+          <t>2026-06-15 00:00:00</t>
+        </is>
+      </c>
+      <c r="O159" t="inlineStr">
+        <is>
+          <t>HJK INTERNATIONAL GMBH</t>
+        </is>
+      </c>
+      <c r="P159" t="inlineStr">
+        <is>
+          <t>HJK INTERNATIONAL GMBH</t>
+        </is>
+      </c>
+      <c r="Q159" t="inlineStr">
+        <is>
+          <t>2026-06-12 00:00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="160">
+      <c r="A160" t="inlineStr">
+        <is>
+          <t>4539483</t>
+        </is>
+      </c>
+      <c r="B160" t="inlineStr">
+        <is>
+          <t>EF4-0232485-1</t>
+        </is>
+      </c>
+      <c r="C160" t="inlineStr">
+        <is>
+          <t>Air, Non-container</t>
+        </is>
+      </c>
+      <c r="D160" t="inlineStr">
+        <is>
+          <t>V9S19229198</t>
+        </is>
+      </c>
+      <c r="E160" t="inlineStr">
+        <is>
+          <t>9903.03.01</t>
+        </is>
+      </c>
+      <c r="F160" t="inlineStr">
+        <is>
+          <t>SECTION 122 - 10% DUTY</t>
+        </is>
+      </c>
+      <c r="G160" t="inlineStr">
+        <is>
+          <t>015</t>
+        </is>
+      </c>
+      <c r="H160" t="inlineStr">
+        <is>
+          <t>9903.03.01</t>
+        </is>
+      </c>
+      <c r="I160" t="inlineStr">
+        <is>
+          <t>8443.91.3000</t>
+        </is>
+      </c>
+      <c r="J160" t="inlineStr">
+        <is>
+          <t>EUROPEAN SPARE PARTS SERVICE INC</t>
+        </is>
+      </c>
+      <c r="K160" t="inlineStr">
+        <is>
+          <t>ESSEUR</t>
+        </is>
+      </c>
+      <c r="L160" t="inlineStr">
+        <is>
+          <t>58-181585100</t>
+        </is>
+      </c>
+      <c r="M160" t="inlineStr">
+        <is>
+          <t>2026-06-14 00:00:00</t>
+        </is>
+      </c>
+      <c r="N160" t="inlineStr">
+        <is>
+          <t>2026-06-15 00:00:00</t>
+        </is>
+      </c>
+      <c r="O160" t="inlineStr">
+        <is>
+          <t>HJK INTERNATIONAL GMBH</t>
+        </is>
+      </c>
+      <c r="P160" t="inlineStr">
+        <is>
+          <t>HJK INTERNATIONAL GMBH</t>
+        </is>
+      </c>
+      <c r="Q160" t="inlineStr">
+        <is>
+          <t>2026-06-12 00:00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="161">
+      <c r="A161" t="inlineStr">
+        <is>
+          <t>4539483</t>
+        </is>
+      </c>
+      <c r="B161" t="inlineStr">
+        <is>
+          <t>EF4-0232485-1</t>
+        </is>
+      </c>
+      <c r="C161" t="inlineStr">
+        <is>
+          <t>Air, Non-container</t>
+        </is>
+      </c>
+      <c r="D161" t="inlineStr">
+        <is>
+          <t>V9S19229198</t>
+        </is>
+      </c>
+      <c r="E161" t="inlineStr">
+        <is>
+          <t>9903.03.01</t>
+        </is>
+      </c>
+      <c r="F161" t="inlineStr">
+        <is>
+          <t>SECTION 122 - 10% DUTY</t>
+        </is>
+      </c>
+      <c r="G161" t="inlineStr">
+        <is>
+          <t>016</t>
+        </is>
+      </c>
+      <c r="H161" t="inlineStr">
+        <is>
+          <t>9903.03.01</t>
+        </is>
+      </c>
+      <c r="I161" t="inlineStr">
+        <is>
+          <t>8443.91.3000</t>
+        </is>
+      </c>
+      <c r="J161" t="inlineStr">
+        <is>
+          <t>EUROPEAN SPARE PARTS SERVICE INC</t>
+        </is>
+      </c>
+      <c r="K161" t="inlineStr">
+        <is>
+          <t>ESSEUR</t>
+        </is>
+      </c>
+      <c r="L161" t="inlineStr">
+        <is>
+          <t>58-181585100</t>
+        </is>
+      </c>
+      <c r="M161" t="inlineStr">
+        <is>
+          <t>2026-06-14 00:00:00</t>
+        </is>
+      </c>
+      <c r="N161" t="inlineStr">
+        <is>
+          <t>2026-06-15 00:00:00</t>
+        </is>
+      </c>
+      <c r="O161" t="inlineStr">
+        <is>
+          <t>HJK INTERNATIONAL GMBH</t>
+        </is>
+      </c>
+      <c r="P161" t="inlineStr">
+        <is>
+          <t>HJK INTERNATIONAL GMBH</t>
+        </is>
+      </c>
+      <c r="Q161" t="inlineStr">
+        <is>
+          <t>2026-06-12 00:00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="162">
+      <c r="A162" t="inlineStr">
+        <is>
+          <t>4539483</t>
+        </is>
+      </c>
+      <c r="B162" t="inlineStr">
+        <is>
+          <t>EF4-0232485-1</t>
+        </is>
+      </c>
+      <c r="C162" t="inlineStr">
+        <is>
+          <t>Air, Non-container</t>
+        </is>
+      </c>
+      <c r="D162" t="inlineStr">
+        <is>
+          <t>V9S19229198</t>
+        </is>
+      </c>
+      <c r="E162" t="inlineStr">
+        <is>
+          <t>9903.03.01</t>
+        </is>
+      </c>
+      <c r="F162" t="inlineStr">
+        <is>
+          <t>SECTION 122 - 10% DUTY</t>
+        </is>
+      </c>
+      <c r="G162" t="inlineStr">
+        <is>
+          <t>017</t>
+        </is>
+      </c>
+      <c r="H162" t="inlineStr">
+        <is>
+          <t>9903.03.01</t>
+        </is>
+      </c>
+      <c r="I162" t="inlineStr">
+        <is>
+          <t>8504.40.9540</t>
+        </is>
+      </c>
+      <c r="J162" t="inlineStr">
+        <is>
+          <t>EUROPEAN SPARE PARTS SERVICE INC</t>
+        </is>
+      </c>
+      <c r="K162" t="inlineStr">
+        <is>
+          <t>ESSEUR</t>
+        </is>
+      </c>
+      <c r="L162" t="inlineStr">
+        <is>
+          <t>58-181585100</t>
+        </is>
+      </c>
+      <c r="M162" t="inlineStr">
+        <is>
+          <t>2026-06-14 00:00:00</t>
+        </is>
+      </c>
+      <c r="N162" t="inlineStr">
+        <is>
+          <t>2026-06-15 00:00:00</t>
+        </is>
+      </c>
+      <c r="O162" t="inlineStr">
+        <is>
+          <t>HJK INTERNATIONAL GMBH</t>
+        </is>
+      </c>
+      <c r="P162" t="inlineStr">
+        <is>
+          <t>HJK INTERNATIONAL GMBH</t>
+        </is>
+      </c>
+      <c r="Q162" t="inlineStr">
+        <is>
+          <t>2026-06-12 00:00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="163">
+      <c r="A163" t="inlineStr">
+        <is>
+          <t>4539483</t>
+        </is>
+      </c>
+      <c r="B163" t="inlineStr">
+        <is>
+          <t>EF4-0232485-1</t>
+        </is>
+      </c>
+      <c r="C163" t="inlineStr">
+        <is>
+          <t>Air, Non-container</t>
+        </is>
+      </c>
+      <c r="D163" t="inlineStr">
+        <is>
+          <t>V9S19229198</t>
+        </is>
+      </c>
+      <c r="E163" t="inlineStr">
+        <is>
+          <t>9903.03.06</t>
+        </is>
+      </c>
+      <c r="F163" t="inlineStr">
+        <is>
+          <t>S122 EXCL,IRN/STL/ALUM,DERIV</t>
+        </is>
+      </c>
+      <c r="G163" t="inlineStr">
+        <is>
+          <t>018</t>
+        </is>
+      </c>
+      <c r="H163" t="inlineStr">
+        <is>
+          <t>9903.03.06</t>
+        </is>
+      </c>
+      <c r="I163" t="inlineStr">
+        <is>
+          <t>9903.82.09,8302.10.6090</t>
+        </is>
+      </c>
+      <c r="J163" t="inlineStr">
+        <is>
+          <t>EUROPEAN SPARE PARTS SERVICE INC</t>
+        </is>
+      </c>
+      <c r="K163" t="inlineStr">
+        <is>
+          <t>ESSEUR</t>
+        </is>
+      </c>
+      <c r="L163" t="inlineStr">
+        <is>
+          <t>58-181585100</t>
+        </is>
+      </c>
+      <c r="M163" t="inlineStr">
+        <is>
+          <t>2026-06-14 00:00:00</t>
+        </is>
+      </c>
+      <c r="N163" t="inlineStr">
+        <is>
+          <t>2026-06-15 00:00:00</t>
+        </is>
+      </c>
+      <c r="O163" t="inlineStr">
+        <is>
+          <t>HJK INTERNATIONAL GMBH</t>
+        </is>
+      </c>
+      <c r="P163" t="inlineStr">
+        <is>
+          <t>HJK INTERNATIONAL GMBH</t>
+        </is>
+      </c>
+      <c r="Q163" t="inlineStr">
+        <is>
+          <t>2026-06-12 00:00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="164">
+      <c r="A164" t="inlineStr">
+        <is>
+          <t>4539483</t>
+        </is>
+      </c>
+      <c r="B164" t="inlineStr">
+        <is>
+          <t>EF4-0232485-1</t>
+        </is>
+      </c>
+      <c r="C164" t="inlineStr">
+        <is>
+          <t>Air, Non-container</t>
+        </is>
+      </c>
+      <c r="D164" t="inlineStr">
+        <is>
+          <t>V9S19229198</t>
+        </is>
+      </c>
+      <c r="E164" t="inlineStr">
+        <is>
+          <t>9903.03.01</t>
+        </is>
+      </c>
+      <c r="F164" t="inlineStr">
+        <is>
+          <t>SECTION 122 - 10% DUTY</t>
+        </is>
+      </c>
+      <c r="G164" t="inlineStr">
+        <is>
+          <t>019</t>
+        </is>
+      </c>
+      <c r="H164" t="inlineStr">
+        <is>
+          <t>9903.03.01</t>
+        </is>
+      </c>
+      <c r="I164" t="inlineStr">
+        <is>
+          <t>8443.91.3000</t>
+        </is>
+      </c>
+      <c r="J164" t="inlineStr">
+        <is>
+          <t>EUROPEAN SPARE PARTS SERVICE INC</t>
+        </is>
+      </c>
+      <c r="K164" t="inlineStr">
+        <is>
+          <t>ESSEUR</t>
+        </is>
+      </c>
+      <c r="L164" t="inlineStr">
+        <is>
+          <t>58-181585100</t>
+        </is>
+      </c>
+      <c r="M164" t="inlineStr">
+        <is>
+          <t>2026-06-14 00:00:00</t>
+        </is>
+      </c>
+      <c r="N164" t="inlineStr">
+        <is>
+          <t>2026-06-15 00:00:00</t>
+        </is>
+      </c>
+      <c r="O164" t="inlineStr">
+        <is>
+          <t>HJK INTERNATIONAL GMBH</t>
+        </is>
+      </c>
+      <c r="P164" t="inlineStr">
+        <is>
+          <t>HJK INTERNATIONAL GMBH</t>
+        </is>
+      </c>
+      <c r="Q164" t="inlineStr">
+        <is>
+          <t>2026-06-12 00:00:00</t>
         </is>
       </c>
     </row>

--- a/trimika_data.xlsx
+++ b/trimika_data.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q285"/>
+  <dimension ref="A1:Q306"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -24227,6 +24227,1781 @@
         </is>
       </c>
     </row>
+    <row r="286">
+      <c r="A286" t="inlineStr">
+        <is>
+          <t>2565718</t>
+        </is>
+      </c>
+      <c r="B286" t="inlineStr">
+        <is>
+          <t>EF4-0231703-8</t>
+        </is>
+      </c>
+      <c r="C286" t="inlineStr">
+        <is>
+          <t>Vessel, Container</t>
+        </is>
+      </c>
+      <c r="D286" t="inlineStr"/>
+      <c r="E286" t="inlineStr">
+        <is>
+          <t>9903.03.01</t>
+        </is>
+      </c>
+      <c r="F286" t="inlineStr">
+        <is>
+          <t>SECTION 122 - 10% DUTY</t>
+        </is>
+      </c>
+      <c r="G286" t="inlineStr">
+        <is>
+          <t>001</t>
+        </is>
+      </c>
+      <c r="H286" t="inlineStr">
+        <is>
+          <t>9903.03.01</t>
+        </is>
+      </c>
+      <c r="I286" t="inlineStr">
+        <is>
+          <t>3505.10.0092</t>
+        </is>
+      </c>
+      <c r="J286" t="inlineStr">
+        <is>
+          <t>ROYAL INGREDIENTS GROUP BV</t>
+        </is>
+      </c>
+      <c r="K286" t="inlineStr">
+        <is>
+          <t>ROYINGRE</t>
+        </is>
+      </c>
+      <c r="L286" t="inlineStr">
+        <is>
+          <t>074601-00962</t>
+        </is>
+      </c>
+      <c r="M286" t="inlineStr">
+        <is>
+          <t>2026-06-17 00:00:00</t>
+        </is>
+      </c>
+      <c r="N286" t="inlineStr">
+        <is>
+          <t>2026-06-17 00:00:00</t>
+        </is>
+      </c>
+      <c r="O286" t="inlineStr">
+        <is>
+          <t>EHM INTERTRADING CO LTD</t>
+        </is>
+      </c>
+      <c r="P286" t="inlineStr">
+        <is>
+          <t>EHM INTERTRADING CO LTD</t>
+        </is>
+      </c>
+      <c r="Q286" t="inlineStr">
+        <is>
+          <t>2026-05-01 00:00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="287">
+      <c r="A287" t="inlineStr">
+        <is>
+          <t>2565827</t>
+        </is>
+      </c>
+      <c r="B287" t="inlineStr">
+        <is>
+          <t>EF4-0231709-5</t>
+        </is>
+      </c>
+      <c r="C287" t="inlineStr">
+        <is>
+          <t>Vessel, Container</t>
+        </is>
+      </c>
+      <c r="D287" t="inlineStr"/>
+      <c r="E287" t="inlineStr">
+        <is>
+          <t>9903.03.01</t>
+        </is>
+      </c>
+      <c r="F287" t="inlineStr">
+        <is>
+          <t>SECTION 122 - 10% DUTY</t>
+        </is>
+      </c>
+      <c r="G287" t="inlineStr">
+        <is>
+          <t>001</t>
+        </is>
+      </c>
+      <c r="H287" t="inlineStr">
+        <is>
+          <t>9903.03.01</t>
+        </is>
+      </c>
+      <c r="I287" t="inlineStr">
+        <is>
+          <t>5903.90.3090</t>
+        </is>
+      </c>
+      <c r="J287" t="inlineStr">
+        <is>
+          <t>VEER CORPORATIONS INC</t>
+        </is>
+      </c>
+      <c r="K287" t="inlineStr">
+        <is>
+          <t>VEECOR01</t>
+        </is>
+      </c>
+      <c r="L287" t="inlineStr">
+        <is>
+          <t>99-106989200</t>
+        </is>
+      </c>
+      <c r="M287" t="inlineStr">
+        <is>
+          <t>2026-06-17 00:00:00</t>
+        </is>
+      </c>
+      <c r="N287" t="inlineStr">
+        <is>
+          <t>2026-06-17 00:00:00</t>
+        </is>
+      </c>
+      <c r="O287" t="inlineStr">
+        <is>
+          <t>VEER PLASTIC PVT LTD</t>
+        </is>
+      </c>
+      <c r="P287" t="inlineStr">
+        <is>
+          <t>VEER PLASTIC PVT LTD</t>
+        </is>
+      </c>
+      <c r="Q287" t="inlineStr">
+        <is>
+          <t>2026-05-10 00:00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="288">
+      <c r="A288" t="inlineStr">
+        <is>
+          <t>2565938</t>
+        </is>
+      </c>
+      <c r="B288" t="inlineStr">
+        <is>
+          <t>EF4-0231958-8</t>
+        </is>
+      </c>
+      <c r="C288" t="inlineStr">
+        <is>
+          <t>Vessel, Container</t>
+        </is>
+      </c>
+      <c r="D288" t="inlineStr"/>
+      <c r="E288" t="inlineStr">
+        <is>
+          <t>9903.03.06</t>
+        </is>
+      </c>
+      <c r="F288" t="inlineStr">
+        <is>
+          <t>S122 EXCL,IRN/STL/ALUM,DERIV</t>
+        </is>
+      </c>
+      <c r="G288" t="inlineStr">
+        <is>
+          <t>001</t>
+        </is>
+      </c>
+      <c r="H288" t="inlineStr">
+        <is>
+          <t>9903.03.06</t>
+        </is>
+      </c>
+      <c r="I288" t="inlineStr">
+        <is>
+          <t>9903.74.11,9903.94.53,8708.29.5160</t>
+        </is>
+      </c>
+      <c r="J288" t="inlineStr">
+        <is>
+          <t>HAGO AUTOMOTIVE CORP</t>
+        </is>
+      </c>
+      <c r="K288" t="inlineStr">
+        <is>
+          <t>HAGAUT02</t>
+        </is>
+      </c>
+      <c r="L288" t="inlineStr">
+        <is>
+          <t>47-447117700</t>
+        </is>
+      </c>
+      <c r="M288" t="inlineStr">
+        <is>
+          <t>2026-06-18 00:00:00</t>
+        </is>
+      </c>
+      <c r="N288" t="inlineStr">
+        <is>
+          <t>2026-06-17 00:00:00</t>
+        </is>
+      </c>
+      <c r="O288" t="inlineStr">
+        <is>
+          <t>WALOR VOEHRENBACH GMBH</t>
+        </is>
+      </c>
+      <c r="P288" t="inlineStr">
+        <is>
+          <t>WALOR VOEHRENBACH GMBH</t>
+        </is>
+      </c>
+      <c r="Q288" t="inlineStr">
+        <is>
+          <t>2026-05-19 00:00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="289">
+      <c r="A289" t="inlineStr">
+        <is>
+          <t>2565938</t>
+        </is>
+      </c>
+      <c r="B289" t="inlineStr">
+        <is>
+          <t>EF4-0231958-8</t>
+        </is>
+      </c>
+      <c r="C289" t="inlineStr">
+        <is>
+          <t>Vessel, Container</t>
+        </is>
+      </c>
+      <c r="D289" t="inlineStr"/>
+      <c r="E289" t="inlineStr">
+        <is>
+          <t>9903.03.06</t>
+        </is>
+      </c>
+      <c r="F289" t="inlineStr">
+        <is>
+          <t>S122 EXCL,IRN/STL/ALUM,DERIV</t>
+        </is>
+      </c>
+      <c r="G289" t="inlineStr">
+        <is>
+          <t>002</t>
+        </is>
+      </c>
+      <c r="H289" t="inlineStr">
+        <is>
+          <t>9903.03.06</t>
+        </is>
+      </c>
+      <c r="I289" t="inlineStr">
+        <is>
+          <t>9903.74.11,9903.94.53,8708.29.5160</t>
+        </is>
+      </c>
+      <c r="J289" t="inlineStr">
+        <is>
+          <t>HAGO AUTOMOTIVE CORP</t>
+        </is>
+      </c>
+      <c r="K289" t="inlineStr">
+        <is>
+          <t>HAGAUT02</t>
+        </is>
+      </c>
+      <c r="L289" t="inlineStr">
+        <is>
+          <t>47-447117700</t>
+        </is>
+      </c>
+      <c r="M289" t="inlineStr">
+        <is>
+          <t>2026-06-18 00:00:00</t>
+        </is>
+      </c>
+      <c r="N289" t="inlineStr">
+        <is>
+          <t>2026-06-17 00:00:00</t>
+        </is>
+      </c>
+      <c r="O289" t="inlineStr">
+        <is>
+          <t>WALOR VOEHRENBACH GMBH</t>
+        </is>
+      </c>
+      <c r="P289" t="inlineStr">
+        <is>
+          <t>WALOR VOEHRENBACH GMBH</t>
+        </is>
+      </c>
+      <c r="Q289" t="inlineStr">
+        <is>
+          <t>2026-05-19 00:00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="290">
+      <c r="A290" t="inlineStr">
+        <is>
+          <t>2565938</t>
+        </is>
+      </c>
+      <c r="B290" t="inlineStr">
+        <is>
+          <t>EF4-0231958-8</t>
+        </is>
+      </c>
+      <c r="C290" t="inlineStr">
+        <is>
+          <t>Vessel, Container</t>
+        </is>
+      </c>
+      <c r="D290" t="inlineStr"/>
+      <c r="E290" t="inlineStr">
+        <is>
+          <t>9903.03.06</t>
+        </is>
+      </c>
+      <c r="F290" t="inlineStr">
+        <is>
+          <t>S122 EXCL,IRN/STL/ALUM,DERIV</t>
+        </is>
+      </c>
+      <c r="G290" t="inlineStr">
+        <is>
+          <t>003</t>
+        </is>
+      </c>
+      <c r="H290" t="inlineStr">
+        <is>
+          <t>9903.03.06</t>
+        </is>
+      </c>
+      <c r="I290" t="inlineStr">
+        <is>
+          <t>9903.74.11,9903.94.53,8708.29.5160</t>
+        </is>
+      </c>
+      <c r="J290" t="inlineStr">
+        <is>
+          <t>HAGO AUTOMOTIVE CORP</t>
+        </is>
+      </c>
+      <c r="K290" t="inlineStr">
+        <is>
+          <t>HAGAUT02</t>
+        </is>
+      </c>
+      <c r="L290" t="inlineStr">
+        <is>
+          <t>47-447117700</t>
+        </is>
+      </c>
+      <c r="M290" t="inlineStr">
+        <is>
+          <t>2026-06-18 00:00:00</t>
+        </is>
+      </c>
+      <c r="N290" t="inlineStr">
+        <is>
+          <t>2026-06-17 00:00:00</t>
+        </is>
+      </c>
+      <c r="O290" t="inlineStr">
+        <is>
+          <t>WALOR VOEHRENBACH GMBH</t>
+        </is>
+      </c>
+      <c r="P290" t="inlineStr">
+        <is>
+          <t>WALOR VOEHRENBACH GMBH</t>
+        </is>
+      </c>
+      <c r="Q290" t="inlineStr">
+        <is>
+          <t>2026-05-19 00:00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="291">
+      <c r="A291" t="inlineStr">
+        <is>
+          <t>2565938</t>
+        </is>
+      </c>
+      <c r="B291" t="inlineStr">
+        <is>
+          <t>EF4-0231958-8</t>
+        </is>
+      </c>
+      <c r="C291" t="inlineStr">
+        <is>
+          <t>Vessel, Container</t>
+        </is>
+      </c>
+      <c r="D291" t="inlineStr"/>
+      <c r="E291" t="inlineStr">
+        <is>
+          <t>9903.03.06</t>
+        </is>
+      </c>
+      <c r="F291" t="inlineStr">
+        <is>
+          <t>S122 EXCL,IRN/STL/ALUM,DERIV</t>
+        </is>
+      </c>
+      <c r="G291" t="inlineStr">
+        <is>
+          <t>004</t>
+        </is>
+      </c>
+      <c r="H291" t="inlineStr">
+        <is>
+          <t>9903.03.06</t>
+        </is>
+      </c>
+      <c r="I291" t="inlineStr">
+        <is>
+          <t>9903.74.11,9903.94.53,8708.29.5160</t>
+        </is>
+      </c>
+      <c r="J291" t="inlineStr">
+        <is>
+          <t>HAGO AUTOMOTIVE CORP</t>
+        </is>
+      </c>
+      <c r="K291" t="inlineStr">
+        <is>
+          <t>HAGAUT02</t>
+        </is>
+      </c>
+      <c r="L291" t="inlineStr">
+        <is>
+          <t>47-447117700</t>
+        </is>
+      </c>
+      <c r="M291" t="inlineStr">
+        <is>
+          <t>2026-06-18 00:00:00</t>
+        </is>
+      </c>
+      <c r="N291" t="inlineStr">
+        <is>
+          <t>2026-06-17 00:00:00</t>
+        </is>
+      </c>
+      <c r="O291" t="inlineStr">
+        <is>
+          <t>WALOR VOEHRENBACH GMBH</t>
+        </is>
+      </c>
+      <c r="P291" t="inlineStr">
+        <is>
+          <t>WALOR VOEHRENBACH GMBH</t>
+        </is>
+      </c>
+      <c r="Q291" t="inlineStr">
+        <is>
+          <t>2026-05-19 00:00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="292">
+      <c r="A292" t="inlineStr">
+        <is>
+          <t>2565938</t>
+        </is>
+      </c>
+      <c r="B292" t="inlineStr">
+        <is>
+          <t>EF4-0231958-8</t>
+        </is>
+      </c>
+      <c r="C292" t="inlineStr">
+        <is>
+          <t>Vessel, Container</t>
+        </is>
+      </c>
+      <c r="D292" t="inlineStr"/>
+      <c r="E292" t="inlineStr">
+        <is>
+          <t>9903.03.06</t>
+        </is>
+      </c>
+      <c r="F292" t="inlineStr">
+        <is>
+          <t>S122 EXCL,IRN/STL/ALUM,DERIV</t>
+        </is>
+      </c>
+      <c r="G292" t="inlineStr">
+        <is>
+          <t>005</t>
+        </is>
+      </c>
+      <c r="H292" t="inlineStr">
+        <is>
+          <t>9903.03.06</t>
+        </is>
+      </c>
+      <c r="I292" t="inlineStr">
+        <is>
+          <t>9903.74.11,9903.94.53,8708.29.5160</t>
+        </is>
+      </c>
+      <c r="J292" t="inlineStr">
+        <is>
+          <t>HAGO AUTOMOTIVE CORP</t>
+        </is>
+      </c>
+      <c r="K292" t="inlineStr">
+        <is>
+          <t>HAGAUT02</t>
+        </is>
+      </c>
+      <c r="L292" t="inlineStr">
+        <is>
+          <t>47-447117700</t>
+        </is>
+      </c>
+      <c r="M292" t="inlineStr">
+        <is>
+          <t>2026-06-18 00:00:00</t>
+        </is>
+      </c>
+      <c r="N292" t="inlineStr">
+        <is>
+          <t>2026-06-17 00:00:00</t>
+        </is>
+      </c>
+      <c r="O292" t="inlineStr">
+        <is>
+          <t>WALOR VOEHRENBACH GMBH</t>
+        </is>
+      </c>
+      <c r="P292" t="inlineStr">
+        <is>
+          <t>WALOR VOEHRENBACH GMBH</t>
+        </is>
+      </c>
+      <c r="Q292" t="inlineStr">
+        <is>
+          <t>2026-05-19 00:00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="293">
+      <c r="A293" t="inlineStr">
+        <is>
+          <t>2565938</t>
+        </is>
+      </c>
+      <c r="B293" t="inlineStr">
+        <is>
+          <t>EF4-0231958-8</t>
+        </is>
+      </c>
+      <c r="C293" t="inlineStr">
+        <is>
+          <t>Vessel, Container</t>
+        </is>
+      </c>
+      <c r="D293" t="inlineStr"/>
+      <c r="E293" t="inlineStr">
+        <is>
+          <t>9903.03.06</t>
+        </is>
+      </c>
+      <c r="F293" t="inlineStr">
+        <is>
+          <t>S122 EXCL,IRN/STL/ALUM,DERIV</t>
+        </is>
+      </c>
+      <c r="G293" t="inlineStr">
+        <is>
+          <t>006</t>
+        </is>
+      </c>
+      <c r="H293" t="inlineStr">
+        <is>
+          <t>9903.03.06</t>
+        </is>
+      </c>
+      <c r="I293" t="inlineStr">
+        <is>
+          <t>9903.74.11,9903.94.53,8708.29.5160</t>
+        </is>
+      </c>
+      <c r="J293" t="inlineStr">
+        <is>
+          <t>HAGO AUTOMOTIVE CORP</t>
+        </is>
+      </c>
+      <c r="K293" t="inlineStr">
+        <is>
+          <t>HAGAUT02</t>
+        </is>
+      </c>
+      <c r="L293" t="inlineStr">
+        <is>
+          <t>47-447117700</t>
+        </is>
+      </c>
+      <c r="M293" t="inlineStr">
+        <is>
+          <t>2026-06-18 00:00:00</t>
+        </is>
+      </c>
+      <c r="N293" t="inlineStr">
+        <is>
+          <t>2026-06-17 00:00:00</t>
+        </is>
+      </c>
+      <c r="O293" t="inlineStr">
+        <is>
+          <t>WALOR VOEHRENBACH GMBH</t>
+        </is>
+      </c>
+      <c r="P293" t="inlineStr">
+        <is>
+          <t>WALOR VOEHRENBACH GMBH</t>
+        </is>
+      </c>
+      <c r="Q293" t="inlineStr">
+        <is>
+          <t>2026-05-19 00:00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="294">
+      <c r="A294" t="inlineStr">
+        <is>
+          <t>2565938</t>
+        </is>
+      </c>
+      <c r="B294" t="inlineStr">
+        <is>
+          <t>EF4-0231958-8</t>
+        </is>
+      </c>
+      <c r="C294" t="inlineStr">
+        <is>
+          <t>Vessel, Container</t>
+        </is>
+      </c>
+      <c r="D294" t="inlineStr"/>
+      <c r="E294" t="inlineStr">
+        <is>
+          <t>9903.03.06</t>
+        </is>
+      </c>
+      <c r="F294" t="inlineStr">
+        <is>
+          <t>S122 EXCL,IRN/STL/ALUM,DERIV</t>
+        </is>
+      </c>
+      <c r="G294" t="inlineStr">
+        <is>
+          <t>007</t>
+        </is>
+      </c>
+      <c r="H294" t="inlineStr">
+        <is>
+          <t>9903.03.06</t>
+        </is>
+      </c>
+      <c r="I294" t="inlineStr">
+        <is>
+          <t>9903.74.11,9903.94.53,8708.29.5160</t>
+        </is>
+      </c>
+      <c r="J294" t="inlineStr">
+        <is>
+          <t>HAGO AUTOMOTIVE CORP</t>
+        </is>
+      </c>
+      <c r="K294" t="inlineStr">
+        <is>
+          <t>HAGAUT02</t>
+        </is>
+      </c>
+      <c r="L294" t="inlineStr">
+        <is>
+          <t>47-447117700</t>
+        </is>
+      </c>
+      <c r="M294" t="inlineStr">
+        <is>
+          <t>2026-06-18 00:00:00</t>
+        </is>
+      </c>
+      <c r="N294" t="inlineStr">
+        <is>
+          <t>2026-06-17 00:00:00</t>
+        </is>
+      </c>
+      <c r="O294" t="inlineStr">
+        <is>
+          <t>WALOR VOEHRENBACH GMBH</t>
+        </is>
+      </c>
+      <c r="P294" t="inlineStr">
+        <is>
+          <t>WALOR VOEHRENBACH GMBH</t>
+        </is>
+      </c>
+      <c r="Q294" t="inlineStr">
+        <is>
+          <t>2026-05-19 00:00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="295">
+      <c r="A295" t="inlineStr">
+        <is>
+          <t>2615664</t>
+        </is>
+      </c>
+      <c r="B295" t="inlineStr">
+        <is>
+          <t>EF4-0231983-6</t>
+        </is>
+      </c>
+      <c r="C295" t="inlineStr">
+        <is>
+          <t>Vessel, Non-container</t>
+        </is>
+      </c>
+      <c r="D295" t="inlineStr"/>
+      <c r="E295" t="inlineStr">
+        <is>
+          <t>9903.88.01</t>
+        </is>
+      </c>
+      <c r="F295" t="inlineStr">
+        <is>
+          <t>ARTICLE OF CHINA,US NTE 20(A)</t>
+        </is>
+      </c>
+      <c r="G295" t="inlineStr">
+        <is>
+          <t>001</t>
+        </is>
+      </c>
+      <c r="H295" t="inlineStr">
+        <is>
+          <t>9903.88.01</t>
+        </is>
+      </c>
+      <c r="I295" t="inlineStr">
+        <is>
+          <t>9903.03.06,9903.82.09,8482.10.5012</t>
+        </is>
+      </c>
+      <c r="J295" t="inlineStr">
+        <is>
+          <t>VISUAL CREATIONS, INC.</t>
+        </is>
+      </c>
+      <c r="K295" t="inlineStr">
+        <is>
+          <t>VISCRE</t>
+        </is>
+      </c>
+      <c r="L295" t="inlineStr">
+        <is>
+          <t>20-461602300</t>
+        </is>
+      </c>
+      <c r="M295" t="inlineStr">
+        <is>
+          <t>2026-06-11 00:00:00</t>
+        </is>
+      </c>
+      <c r="N295" t="inlineStr">
+        <is>
+          <t>2026-06-17 00:00:00</t>
+        </is>
+      </c>
+      <c r="O295" t="inlineStr">
+        <is>
+          <t>LINYU HANDWARE MANUFACTURE CO LTD</t>
+        </is>
+      </c>
+      <c r="P295" t="inlineStr">
+        <is>
+          <t>LINYU HANDWARE MANUFACTURE CO LTD</t>
+        </is>
+      </c>
+      <c r="Q295" t="inlineStr">
+        <is>
+          <t>2026-05-15 00:00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="296">
+      <c r="A296" t="inlineStr">
+        <is>
+          <t>2565682</t>
+        </is>
+      </c>
+      <c r="B296" t="inlineStr">
+        <is>
+          <t>EF4-0231989-3</t>
+        </is>
+      </c>
+      <c r="C296" t="inlineStr">
+        <is>
+          <t>Vessel, Container</t>
+        </is>
+      </c>
+      <c r="D296" t="inlineStr"/>
+      <c r="E296" t="inlineStr">
+        <is>
+          <t>9903.88.03</t>
+        </is>
+      </c>
+      <c r="F296" t="inlineStr">
+        <is>
+          <t>ARTICLE OF CHINA,US NTE 20(F)</t>
+        </is>
+      </c>
+      <c r="G296" t="inlineStr">
+        <is>
+          <t>001</t>
+        </is>
+      </c>
+      <c r="H296" t="inlineStr">
+        <is>
+          <t>9903.88.03</t>
+        </is>
+      </c>
+      <c r="I296" t="inlineStr">
+        <is>
+          <t>9903.03.01,9403.99.9045</t>
+        </is>
+      </c>
+      <c r="J296" t="inlineStr">
+        <is>
+          <t>VISUAL CREATIONS, INC.</t>
+        </is>
+      </c>
+      <c r="K296" t="inlineStr">
+        <is>
+          <t>VISCRE</t>
+        </is>
+      </c>
+      <c r="L296" t="inlineStr">
+        <is>
+          <t>20-461602300</t>
+        </is>
+      </c>
+      <c r="M296" t="inlineStr">
+        <is>
+          <t>2026-06-19 00:00:00</t>
+        </is>
+      </c>
+      <c r="N296" t="inlineStr">
+        <is>
+          <t>2026-06-17 00:00:00</t>
+        </is>
+      </c>
+      <c r="O296" t="inlineStr">
+        <is>
+          <t>FUJIAN ANTAI NEW ENERGY TECH CO LTD</t>
+        </is>
+      </c>
+      <c r="P296" t="inlineStr">
+        <is>
+          <t>FUJIAN ANTAI NEW ENERGY TECH CO LTD</t>
+        </is>
+      </c>
+      <c r="Q296" t="inlineStr">
+        <is>
+          <t>2026-05-19 00:00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="297">
+      <c r="A297" t="inlineStr">
+        <is>
+          <t>2565682</t>
+        </is>
+      </c>
+      <c r="B297" t="inlineStr">
+        <is>
+          <t>EF4-0231989-3</t>
+        </is>
+      </c>
+      <c r="C297" t="inlineStr">
+        <is>
+          <t>Vessel, Container</t>
+        </is>
+      </c>
+      <c r="D297" t="inlineStr"/>
+      <c r="E297" t="inlineStr">
+        <is>
+          <t>9903.88.03</t>
+        </is>
+      </c>
+      <c r="F297" t="inlineStr">
+        <is>
+          <t>ARTICLE OF CHINA,US NTE 20(F)</t>
+        </is>
+      </c>
+      <c r="G297" t="inlineStr">
+        <is>
+          <t>002</t>
+        </is>
+      </c>
+      <c r="H297" t="inlineStr">
+        <is>
+          <t>9903.88.03</t>
+        </is>
+      </c>
+      <c r="I297" t="inlineStr">
+        <is>
+          <t>9903.03.01,9405.41.8440</t>
+        </is>
+      </c>
+      <c r="J297" t="inlineStr">
+        <is>
+          <t>VISUAL CREATIONS, INC.</t>
+        </is>
+      </c>
+      <c r="K297" t="inlineStr">
+        <is>
+          <t>VISCRE</t>
+        </is>
+      </c>
+      <c r="L297" t="inlineStr">
+        <is>
+          <t>20-461602300</t>
+        </is>
+      </c>
+      <c r="M297" t="inlineStr">
+        <is>
+          <t>2026-06-19 00:00:00</t>
+        </is>
+      </c>
+      <c r="N297" t="inlineStr">
+        <is>
+          <t>2026-06-17 00:00:00</t>
+        </is>
+      </c>
+      <c r="O297" t="inlineStr">
+        <is>
+          <t>FUJIAN ANTAI NEW ENERGY TECH CO LTD</t>
+        </is>
+      </c>
+      <c r="P297" t="inlineStr">
+        <is>
+          <t>FUJIAN ANTAI NEW ENERGY TECH CO LTD</t>
+        </is>
+      </c>
+      <c r="Q297" t="inlineStr">
+        <is>
+          <t>2026-05-19 00:00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="298">
+      <c r="A298" t="inlineStr">
+        <is>
+          <t>2565682</t>
+        </is>
+      </c>
+      <c r="B298" t="inlineStr">
+        <is>
+          <t>EF4-0231989-3</t>
+        </is>
+      </c>
+      <c r="C298" t="inlineStr">
+        <is>
+          <t>Vessel, Container</t>
+        </is>
+      </c>
+      <c r="D298" t="inlineStr"/>
+      <c r="E298" t="inlineStr">
+        <is>
+          <t>9903.88.15</t>
+        </is>
+      </c>
+      <c r="F298" t="inlineStr">
+        <is>
+          <t>ARTICLE OF CHINA,US NTE 20(R)</t>
+        </is>
+      </c>
+      <c r="G298" t="inlineStr">
+        <is>
+          <t>003</t>
+        </is>
+      </c>
+      <c r="H298" t="inlineStr">
+        <is>
+          <t>9903.88.15</t>
+        </is>
+      </c>
+      <c r="I298" t="inlineStr">
+        <is>
+          <t>9903.03.01,3926.90.9989</t>
+        </is>
+      </c>
+      <c r="J298" t="inlineStr">
+        <is>
+          <t>VISUAL CREATIONS, INC.</t>
+        </is>
+      </c>
+      <c r="K298" t="inlineStr">
+        <is>
+          <t>VISCRE</t>
+        </is>
+      </c>
+      <c r="L298" t="inlineStr">
+        <is>
+          <t>20-461602300</t>
+        </is>
+      </c>
+      <c r="M298" t="inlineStr">
+        <is>
+          <t>2026-06-19 00:00:00</t>
+        </is>
+      </c>
+      <c r="N298" t="inlineStr">
+        <is>
+          <t>2026-06-17 00:00:00</t>
+        </is>
+      </c>
+      <c r="O298" t="inlineStr">
+        <is>
+          <t>FUJIAN ANTAI NEW ENERGY TECH CO LTD</t>
+        </is>
+      </c>
+      <c r="P298" t="inlineStr">
+        <is>
+          <t>FUJIAN ANTAI NEW ENERGY TECH CO LTD</t>
+        </is>
+      </c>
+      <c r="Q298" t="inlineStr">
+        <is>
+          <t>2026-05-19 00:00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="299">
+      <c r="A299" t="inlineStr">
+        <is>
+          <t>2565800</t>
+        </is>
+      </c>
+      <c r="B299" t="inlineStr">
+        <is>
+          <t>EF4-0232068-5</t>
+        </is>
+      </c>
+      <c r="C299" t="inlineStr">
+        <is>
+          <t>Vessel, Container</t>
+        </is>
+      </c>
+      <c r="D299" t="inlineStr">
+        <is>
+          <t>V0413939047</t>
+        </is>
+      </c>
+      <c r="E299" t="inlineStr">
+        <is>
+          <t>9903.03.06</t>
+        </is>
+      </c>
+      <c r="F299" t="inlineStr">
+        <is>
+          <t>S122 EXCL,IRN/STL/ALUM,DERIV</t>
+        </is>
+      </c>
+      <c r="G299" t="inlineStr">
+        <is>
+          <t>001</t>
+        </is>
+      </c>
+      <c r="H299" t="inlineStr">
+        <is>
+          <t>9903.03.06</t>
+        </is>
+      </c>
+      <c r="I299" t="inlineStr">
+        <is>
+          <t>9903.82.02,7223.00.1031</t>
+        </is>
+      </c>
+      <c r="J299" t="inlineStr">
+        <is>
+          <t>VENUS WIRE INDUSTRIES PRIVATE LTD</t>
+        </is>
+      </c>
+      <c r="K299" t="inlineStr">
+        <is>
+          <t>VENWIR</t>
+        </is>
+      </c>
+      <c r="L299" t="inlineStr">
+        <is>
+          <t>993901-03595</t>
+        </is>
+      </c>
+      <c r="M299" t="inlineStr">
+        <is>
+          <t>2026-06-17 00:00:00</t>
+        </is>
+      </c>
+      <c r="N299" t="inlineStr">
+        <is>
+          <t>2026-06-17 00:00:00</t>
+        </is>
+      </c>
+      <c r="O299" t="inlineStr">
+        <is>
+          <t>VENUS WIRE INDUSTRIES PRIVATE LIMIT</t>
+        </is>
+      </c>
+      <c r="P299" t="inlineStr">
+        <is>
+          <t>VENUS WIRE INDUSTRIES PRIVATE LIMITED</t>
+        </is>
+      </c>
+      <c r="Q299" t="inlineStr">
+        <is>
+          <t>2026-05-11 00:00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="300">
+      <c r="A300" t="inlineStr">
+        <is>
+          <t>2566097</t>
+        </is>
+      </c>
+      <c r="B300" t="inlineStr">
+        <is>
+          <t>EF4-0232212-9</t>
+        </is>
+      </c>
+      <c r="C300" t="inlineStr">
+        <is>
+          <t>Vessel, Container</t>
+        </is>
+      </c>
+      <c r="D300" t="inlineStr">
+        <is>
+          <t>V0413939047</t>
+        </is>
+      </c>
+      <c r="E300" t="inlineStr">
+        <is>
+          <t>9903.03.01</t>
+        </is>
+      </c>
+      <c r="F300" t="inlineStr">
+        <is>
+          <t>SECTION 122 - 10% DUTY</t>
+        </is>
+      </c>
+      <c r="G300" t="inlineStr">
+        <is>
+          <t>001</t>
+        </is>
+      </c>
+      <c r="H300" t="inlineStr">
+        <is>
+          <t>9903.03.01</t>
+        </is>
+      </c>
+      <c r="I300" t="inlineStr">
+        <is>
+          <t>5704.90.0190</t>
+        </is>
+      </c>
+      <c r="J300" t="inlineStr">
+        <is>
+          <t>BORGERS OHIO INC.</t>
+        </is>
+      </c>
+      <c r="K300" t="inlineStr">
+        <is>
+          <t>BORUSA02</t>
+        </is>
+      </c>
+      <c r="L300" t="inlineStr">
+        <is>
+          <t>30-084196200</t>
+        </is>
+      </c>
+      <c r="M300" t="inlineStr">
+        <is>
+          <t>2026-06-17 00:00:00</t>
+        </is>
+      </c>
+      <c r="N300" t="inlineStr">
+        <is>
+          <t>2026-06-17 00:00:00</t>
+        </is>
+      </c>
+      <c r="O300" t="inlineStr">
+        <is>
+          <t>AUTONEUM GERMANY GMBH</t>
+        </is>
+      </c>
+      <c r="P300" t="inlineStr">
+        <is>
+          <t>AUTONEUM GERMANY GMBH</t>
+        </is>
+      </c>
+      <c r="Q300" t="inlineStr">
+        <is>
+          <t>2026-05-30 00:00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="301">
+      <c r="A301" t="inlineStr">
+        <is>
+          <t>2566097</t>
+        </is>
+      </c>
+      <c r="B301" t="inlineStr">
+        <is>
+          <t>EF4-0232212-9</t>
+        </is>
+      </c>
+      <c r="C301" t="inlineStr">
+        <is>
+          <t>Vessel, Container</t>
+        </is>
+      </c>
+      <c r="D301" t="inlineStr">
+        <is>
+          <t>V0413939047</t>
+        </is>
+      </c>
+      <c r="E301" t="inlineStr">
+        <is>
+          <t>9903.03.01</t>
+        </is>
+      </c>
+      <c r="F301" t="inlineStr">
+        <is>
+          <t>SECTION 122 - 10% DUTY</t>
+        </is>
+      </c>
+      <c r="G301" t="inlineStr">
+        <is>
+          <t>002</t>
+        </is>
+      </c>
+      <c r="H301" t="inlineStr">
+        <is>
+          <t>9903.03.01</t>
+        </is>
+      </c>
+      <c r="I301" t="inlineStr">
+        <is>
+          <t>5704.90.0190</t>
+        </is>
+      </c>
+      <c r="J301" t="inlineStr">
+        <is>
+          <t>BORGERS OHIO INC.</t>
+        </is>
+      </c>
+      <c r="K301" t="inlineStr">
+        <is>
+          <t>BORUSA02</t>
+        </is>
+      </c>
+      <c r="L301" t="inlineStr">
+        <is>
+          <t>30-084196200</t>
+        </is>
+      </c>
+      <c r="M301" t="inlineStr">
+        <is>
+          <t>2026-06-17 00:00:00</t>
+        </is>
+      </c>
+      <c r="N301" t="inlineStr">
+        <is>
+          <t>2026-06-17 00:00:00</t>
+        </is>
+      </c>
+      <c r="O301" t="inlineStr">
+        <is>
+          <t>AUTONEUM GERMANY GMBH</t>
+        </is>
+      </c>
+      <c r="P301" t="inlineStr">
+        <is>
+          <t>AUTONEUM GERMANY GMBH</t>
+        </is>
+      </c>
+      <c r="Q301" t="inlineStr">
+        <is>
+          <t>2026-05-30 00:00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="302">
+      <c r="A302" t="inlineStr">
+        <is>
+          <t>2566097</t>
+        </is>
+      </c>
+      <c r="B302" t="inlineStr">
+        <is>
+          <t>EF4-0232212-9</t>
+        </is>
+      </c>
+      <c r="C302" t="inlineStr">
+        <is>
+          <t>Vessel, Container</t>
+        </is>
+      </c>
+      <c r="D302" t="inlineStr">
+        <is>
+          <t>V0413939047</t>
+        </is>
+      </c>
+      <c r="E302" t="inlineStr">
+        <is>
+          <t>9903.03.01</t>
+        </is>
+      </c>
+      <c r="F302" t="inlineStr">
+        <is>
+          <t>SECTION 122 - 10% DUTY</t>
+        </is>
+      </c>
+      <c r="G302" t="inlineStr">
+        <is>
+          <t>003</t>
+        </is>
+      </c>
+      <c r="H302" t="inlineStr">
+        <is>
+          <t>9903.03.01</t>
+        </is>
+      </c>
+      <c r="I302" t="inlineStr">
+        <is>
+          <t>5704.90.0190</t>
+        </is>
+      </c>
+      <c r="J302" t="inlineStr">
+        <is>
+          <t>BORGERS OHIO INC.</t>
+        </is>
+      </c>
+      <c r="K302" t="inlineStr">
+        <is>
+          <t>BORUSA02</t>
+        </is>
+      </c>
+      <c r="L302" t="inlineStr">
+        <is>
+          <t>30-084196200</t>
+        </is>
+      </c>
+      <c r="M302" t="inlineStr">
+        <is>
+          <t>2026-06-17 00:00:00</t>
+        </is>
+      </c>
+      <c r="N302" t="inlineStr">
+        <is>
+          <t>2026-06-17 00:00:00</t>
+        </is>
+      </c>
+      <c r="O302" t="inlineStr">
+        <is>
+          <t>AUTONEUM GERMANY GMBH</t>
+        </is>
+      </c>
+      <c r="P302" t="inlineStr">
+        <is>
+          <t>AUTONEUM GERMANY GMBH</t>
+        </is>
+      </c>
+      <c r="Q302" t="inlineStr">
+        <is>
+          <t>2026-05-30 00:00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="303">
+      <c r="A303" t="inlineStr">
+        <is>
+          <t>2565838</t>
+        </is>
+      </c>
+      <c r="B303" t="inlineStr">
+        <is>
+          <t>EF4-0232439-8</t>
+        </is>
+      </c>
+      <c r="C303" t="inlineStr">
+        <is>
+          <t>Vessel, Container</t>
+        </is>
+      </c>
+      <c r="D303" t="inlineStr">
+        <is>
+          <t>V0413931663</t>
+        </is>
+      </c>
+      <c r="E303" t="inlineStr">
+        <is>
+          <t>9903.03.06</t>
+        </is>
+      </c>
+      <c r="F303" t="inlineStr">
+        <is>
+          <t>S122 EXCL,IRN/STL/ALUM,DERIV</t>
+        </is>
+      </c>
+      <c r="G303" t="inlineStr">
+        <is>
+          <t>001</t>
+        </is>
+      </c>
+      <c r="H303" t="inlineStr">
+        <is>
+          <t>9903.03.06</t>
+        </is>
+      </c>
+      <c r="I303" t="inlineStr">
+        <is>
+          <t>9903.82.02,7222.20.0062</t>
+        </is>
+      </c>
+      <c r="J303" t="inlineStr">
+        <is>
+          <t>MESHA STEELS  LLC</t>
+        </is>
+      </c>
+      <c r="K303" t="inlineStr">
+        <is>
+          <t>MESSTE</t>
+        </is>
+      </c>
+      <c r="L303" t="inlineStr">
+        <is>
+          <t>20-274801900</t>
+        </is>
+      </c>
+      <c r="M303" t="inlineStr">
+        <is>
+          <t>2026-06-17 00:00:00</t>
+        </is>
+      </c>
+      <c r="N303" t="inlineStr">
+        <is>
+          <t>2026-06-17 00:00:00</t>
+        </is>
+      </c>
+      <c r="O303" t="inlineStr">
+        <is>
+          <t>BHANSALI BRIGHT BARS PVT. LTD.</t>
+        </is>
+      </c>
+      <c r="P303" t="inlineStr">
+        <is>
+          <t>BHANSALI BRIGHT BARS PVT. LTD.</t>
+        </is>
+      </c>
+      <c r="Q303" t="inlineStr">
+        <is>
+          <t>2026-05-05 00:00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="304">
+      <c r="A304" t="inlineStr">
+        <is>
+          <t>2565907</t>
+        </is>
+      </c>
+      <c r="B304" t="inlineStr">
+        <is>
+          <t>EF4-0232496-8</t>
+        </is>
+      </c>
+      <c r="C304" t="inlineStr">
+        <is>
+          <t>Vessel, Container</t>
+        </is>
+      </c>
+      <c r="D304" t="inlineStr">
+        <is>
+          <t>V0413937900</t>
+        </is>
+      </c>
+      <c r="E304" t="inlineStr">
+        <is>
+          <t>9903.03.06</t>
+        </is>
+      </c>
+      <c r="F304" t="inlineStr">
+        <is>
+          <t>S122 EXCL,IRN/STL/ALUM,DERIV</t>
+        </is>
+      </c>
+      <c r="G304" t="inlineStr">
+        <is>
+          <t>001</t>
+        </is>
+      </c>
+      <c r="H304" t="inlineStr">
+        <is>
+          <t>9903.03.06</t>
+        </is>
+      </c>
+      <c r="I304" t="inlineStr">
+        <is>
+          <t>9903.82.02,7222.20.0043</t>
+        </is>
+      </c>
+      <c r="J304" t="inlineStr">
+        <is>
+          <t>MESHA STEELS  LLC</t>
+        </is>
+      </c>
+      <c r="K304" t="inlineStr">
+        <is>
+          <t>MESSTE</t>
+        </is>
+      </c>
+      <c r="L304" t="inlineStr">
+        <is>
+          <t>20-274801900</t>
+        </is>
+      </c>
+      <c r="M304" t="inlineStr">
+        <is>
+          <t>2026-06-17 00:00:00</t>
+        </is>
+      </c>
+      <c r="N304" t="inlineStr">
+        <is>
+          <t>2026-06-17 00:00:00</t>
+        </is>
+      </c>
+      <c r="O304" t="inlineStr">
+        <is>
+          <t>BHANSALI BRIGHT BARS PVT. LTD.</t>
+        </is>
+      </c>
+      <c r="P304" t="inlineStr">
+        <is>
+          <t>BHANSALI BRIGHT BARS PVT. LTD.</t>
+        </is>
+      </c>
+      <c r="Q304" t="inlineStr">
+        <is>
+          <t>2026-05-11 00:00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="305">
+      <c r="A305" t="inlineStr">
+        <is>
+          <t>2565907</t>
+        </is>
+      </c>
+      <c r="B305" t="inlineStr">
+        <is>
+          <t>EF4-0232496-8</t>
+        </is>
+      </c>
+      <c r="C305" t="inlineStr">
+        <is>
+          <t>Vessel, Container</t>
+        </is>
+      </c>
+      <c r="D305" t="inlineStr">
+        <is>
+          <t>V0413937900</t>
+        </is>
+      </c>
+      <c r="E305" t="inlineStr">
+        <is>
+          <t>9903.03.06</t>
+        </is>
+      </c>
+      <c r="F305" t="inlineStr">
+        <is>
+          <t>S122 EXCL,IRN/STL/ALUM,DERIV</t>
+        </is>
+      </c>
+      <c r="G305" t="inlineStr">
+        <is>
+          <t>002</t>
+        </is>
+      </c>
+      <c r="H305" t="inlineStr">
+        <is>
+          <t>9903.03.06</t>
+        </is>
+      </c>
+      <c r="I305" t="inlineStr">
+        <is>
+          <t>9903.82.02,7222.20.0073</t>
+        </is>
+      </c>
+      <c r="J305" t="inlineStr">
+        <is>
+          <t>MESHA STEELS  LLC</t>
+        </is>
+      </c>
+      <c r="K305" t="inlineStr">
+        <is>
+          <t>MESSTE</t>
+        </is>
+      </c>
+      <c r="L305" t="inlineStr">
+        <is>
+          <t>20-274801900</t>
+        </is>
+      </c>
+      <c r="M305" t="inlineStr">
+        <is>
+          <t>2026-06-17 00:00:00</t>
+        </is>
+      </c>
+      <c r="N305" t="inlineStr">
+        <is>
+          <t>2026-06-17 00:00:00</t>
+        </is>
+      </c>
+      <c r="O305" t="inlineStr">
+        <is>
+          <t>BHANSALI BRIGHT BARS PVT. LTD.</t>
+        </is>
+      </c>
+      <c r="P305" t="inlineStr">
+        <is>
+          <t>BHANSALI BRIGHT BARS PVT. LTD.</t>
+        </is>
+      </c>
+      <c r="Q305" t="inlineStr">
+        <is>
+          <t>2026-05-11 00:00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="306">
+      <c r="A306" t="inlineStr">
+        <is>
+          <t>2615809</t>
+        </is>
+      </c>
+      <c r="B306" t="inlineStr">
+        <is>
+          <t>EF4-0232557-7</t>
+        </is>
+      </c>
+      <c r="C306" t="inlineStr">
+        <is>
+          <t>Truck, Non-container</t>
+        </is>
+      </c>
+      <c r="D306" t="inlineStr">
+        <is>
+          <t>V0413937900</t>
+        </is>
+      </c>
+      <c r="E306" t="inlineStr">
+        <is>
+          <t>9903.03.01</t>
+        </is>
+      </c>
+      <c r="F306" t="inlineStr">
+        <is>
+          <t>SECTION 122 - 10% DUTY</t>
+        </is>
+      </c>
+      <c r="G306" t="inlineStr">
+        <is>
+          <t>001</t>
+        </is>
+      </c>
+      <c r="H306" t="inlineStr">
+        <is>
+          <t>9903.03.01</t>
+        </is>
+      </c>
+      <c r="I306" t="inlineStr">
+        <is>
+          <t>8483.40.5010</t>
+        </is>
+      </c>
+      <c r="J306" t="inlineStr">
+        <is>
+          <t>AUMUND CORPORATION</t>
+        </is>
+      </c>
+      <c r="K306" t="inlineStr">
+        <is>
+          <t>AUMCOR</t>
+        </is>
+      </c>
+      <c r="L306" t="inlineStr">
+        <is>
+          <t>58-138896800</t>
+        </is>
+      </c>
+      <c r="M306" t="inlineStr">
+        <is>
+          <t>2026-06-16 00:00:00</t>
+        </is>
+      </c>
+      <c r="N306" t="inlineStr">
+        <is>
+          <t>2026-06-17 00:00:00</t>
+        </is>
+      </c>
+      <c r="O306" t="inlineStr">
+        <is>
+          <t>AUMUND FOERDERTECHNIK GMBH</t>
+        </is>
+      </c>
+      <c r="P306" t="inlineStr">
+        <is>
+          <t>AUMUND FOERDERTECHNIK GMBH</t>
+        </is>
+      </c>
+      <c r="Q306" t="inlineStr">
+        <is>
+          <t>2026-06-16 00:00:00</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/trimika_data.xlsx
+++ b/trimika_data.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q306"/>
+  <dimension ref="A1:Q323"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -26002,6 +26002,1417 @@
         </is>
       </c>
     </row>
+    <row r="307">
+      <c r="A307" t="inlineStr">
+        <is>
+          <t>2565634</t>
+        </is>
+      </c>
+      <c r="B307" t="inlineStr">
+        <is>
+          <t>EF4-0231631-1</t>
+        </is>
+      </c>
+      <c r="C307" t="inlineStr">
+        <is>
+          <t>Vessel, Container</t>
+        </is>
+      </c>
+      <c r="D307" t="inlineStr"/>
+      <c r="E307" t="inlineStr">
+        <is>
+          <t>9903.03.01</t>
+        </is>
+      </c>
+      <c r="F307" t="inlineStr">
+        <is>
+          <t>SECTION 122 - 10% DUTY</t>
+        </is>
+      </c>
+      <c r="G307" t="inlineStr">
+        <is>
+          <t>001</t>
+        </is>
+      </c>
+      <c r="H307" t="inlineStr">
+        <is>
+          <t>9903.03.01</t>
+        </is>
+      </c>
+      <c r="I307" t="inlineStr">
+        <is>
+          <t>8438.90.9060</t>
+        </is>
+      </c>
+      <c r="J307" t="inlineStr">
+        <is>
+          <t>CANTRELL GAINCO GROUP INC</t>
+        </is>
+      </c>
+      <c r="K307" t="inlineStr">
+        <is>
+          <t>CANGAI01</t>
+        </is>
+      </c>
+      <c r="L307" t="inlineStr">
+        <is>
+          <t>31-151121700</t>
+        </is>
+      </c>
+      <c r="M307" t="inlineStr">
+        <is>
+          <t>2026-06-18 00:00:00</t>
+        </is>
+      </c>
+      <c r="N307" t="inlineStr">
+        <is>
+          <t>2026-06-18 00:00:00</t>
+        </is>
+      </c>
+      <c r="O307" t="inlineStr">
+        <is>
+          <t>O E CO LTD</t>
+        </is>
+      </c>
+      <c r="P307" t="inlineStr">
+        <is>
+          <t>O E CO LTD</t>
+        </is>
+      </c>
+      <c r="Q307" t="inlineStr">
+        <is>
+          <t>2026-05-05 00:00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="308">
+      <c r="A308" t="inlineStr">
+        <is>
+          <t>2565782</t>
+        </is>
+      </c>
+      <c r="B308" t="inlineStr">
+        <is>
+          <t>EF4-0231677-4</t>
+        </is>
+      </c>
+      <c r="C308" t="inlineStr">
+        <is>
+          <t>Vessel, Container</t>
+        </is>
+      </c>
+      <c r="D308" t="inlineStr"/>
+      <c r="E308" t="inlineStr">
+        <is>
+          <t>9903.03.01</t>
+        </is>
+      </c>
+      <c r="F308" t="inlineStr">
+        <is>
+          <t>SECTION 122 - 10% DUTY</t>
+        </is>
+      </c>
+      <c r="G308" t="inlineStr">
+        <is>
+          <t>001</t>
+        </is>
+      </c>
+      <c r="H308" t="inlineStr">
+        <is>
+          <t>9903.03.01</t>
+        </is>
+      </c>
+      <c r="I308" t="inlineStr">
+        <is>
+          <t>3505.10.0092</t>
+        </is>
+      </c>
+      <c r="J308" t="inlineStr">
+        <is>
+          <t>ROYAL INGREDIENTS GROUP BV</t>
+        </is>
+      </c>
+      <c r="K308" t="inlineStr">
+        <is>
+          <t>ROYINGRE</t>
+        </is>
+      </c>
+      <c r="L308" t="inlineStr">
+        <is>
+          <t>074601-00962</t>
+        </is>
+      </c>
+      <c r="M308" t="inlineStr">
+        <is>
+          <t>2026-06-18 00:00:00</t>
+        </is>
+      </c>
+      <c r="N308" t="inlineStr">
+        <is>
+          <t>2026-06-18 00:00:00</t>
+        </is>
+      </c>
+      <c r="O308" t="inlineStr">
+        <is>
+          <t>EHM INTERTRADING CO LTD</t>
+        </is>
+      </c>
+      <c r="P308" t="inlineStr">
+        <is>
+          <t>EHM INTERTRADING CO LTD</t>
+        </is>
+      </c>
+      <c r="Q308" t="inlineStr">
+        <is>
+          <t>2026-05-05 00:00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="309">
+      <c r="A309" t="inlineStr">
+        <is>
+          <t>2565784</t>
+        </is>
+      </c>
+      <c r="B309" t="inlineStr">
+        <is>
+          <t>EF4-0231678-2</t>
+        </is>
+      </c>
+      <c r="C309" t="inlineStr">
+        <is>
+          <t>Vessel, Container</t>
+        </is>
+      </c>
+      <c r="D309" t="inlineStr"/>
+      <c r="E309" t="inlineStr">
+        <is>
+          <t>9903.03.01</t>
+        </is>
+      </c>
+      <c r="F309" t="inlineStr">
+        <is>
+          <t>SECTION 122 - 10% DUTY</t>
+        </is>
+      </c>
+      <c r="G309" t="inlineStr">
+        <is>
+          <t>001</t>
+        </is>
+      </c>
+      <c r="H309" t="inlineStr">
+        <is>
+          <t>9903.03.01</t>
+        </is>
+      </c>
+      <c r="I309" t="inlineStr">
+        <is>
+          <t>3505.10.0092</t>
+        </is>
+      </c>
+      <c r="J309" t="inlineStr">
+        <is>
+          <t>ROYAL INGREDIENTS GROUP BV</t>
+        </is>
+      </c>
+      <c r="K309" t="inlineStr">
+        <is>
+          <t>ROYINGRE</t>
+        </is>
+      </c>
+      <c r="L309" t="inlineStr">
+        <is>
+          <t>074601-00962</t>
+        </is>
+      </c>
+      <c r="M309" t="inlineStr">
+        <is>
+          <t>2026-06-18 00:00:00</t>
+        </is>
+      </c>
+      <c r="N309" t="inlineStr">
+        <is>
+          <t>2026-06-18 00:00:00</t>
+        </is>
+      </c>
+      <c r="O309" t="inlineStr">
+        <is>
+          <t>EHM INTERTRADING CO LTD</t>
+        </is>
+      </c>
+      <c r="P309" t="inlineStr">
+        <is>
+          <t>EHM INTERTRADING CO LTD</t>
+        </is>
+      </c>
+      <c r="Q309" t="inlineStr">
+        <is>
+          <t>2026-05-05 00:00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="310">
+      <c r="A310" t="inlineStr">
+        <is>
+          <t>2565894</t>
+        </is>
+      </c>
+      <c r="B310" t="inlineStr">
+        <is>
+          <t>EF4-0232004-0</t>
+        </is>
+      </c>
+      <c r="C310" t="inlineStr">
+        <is>
+          <t>Vessel, Container</t>
+        </is>
+      </c>
+      <c r="D310" t="inlineStr"/>
+      <c r="E310" t="inlineStr">
+        <is>
+          <t>9903.03.03</t>
+        </is>
+      </c>
+      <c r="F310" t="inlineStr">
+        <is>
+          <t>S122 -EXCLUSION-EXEMPTED PRDTS</t>
+        </is>
+      </c>
+      <c r="G310" t="inlineStr">
+        <is>
+          <t>001</t>
+        </is>
+      </c>
+      <c r="H310" t="inlineStr">
+        <is>
+          <t>9903.03.03</t>
+        </is>
+      </c>
+      <c r="I310" t="inlineStr">
+        <is>
+          <t>2930.90.9231</t>
+        </is>
+      </c>
+      <c r="J310" t="inlineStr">
+        <is>
+          <t>CASTLE CHEMICALS LTD</t>
+        </is>
+      </c>
+      <c r="K310" t="inlineStr">
+        <is>
+          <t>CASCHE01</t>
+        </is>
+      </c>
+      <c r="L310" t="inlineStr">
+        <is>
+          <t>151704-07138</t>
+        </is>
+      </c>
+      <c r="M310" t="inlineStr">
+        <is>
+          <t>2026-06-18 00:00:00</t>
+        </is>
+      </c>
+      <c r="N310" t="inlineStr">
+        <is>
+          <t>2026-06-18 00:00:00</t>
+        </is>
+      </c>
+      <c r="O310" t="inlineStr">
+        <is>
+          <t>HUBEI JIANGHAN NEW MATERIALS CO LTD</t>
+        </is>
+      </c>
+      <c r="P310" t="inlineStr">
+        <is>
+          <t>HUBEI JIANGHAN NEW MATERIALS CO LTD</t>
+        </is>
+      </c>
+      <c r="Q310" t="inlineStr">
+        <is>
+          <t>2026-04-30 00:00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="311">
+      <c r="A311" t="inlineStr">
+        <is>
+          <t>2566078</t>
+        </is>
+      </c>
+      <c r="B311" t="inlineStr">
+        <is>
+          <t>EF4-0232219-4</t>
+        </is>
+      </c>
+      <c r="C311" t="inlineStr">
+        <is>
+          <t>Vessel, Non-container</t>
+        </is>
+      </c>
+      <c r="D311" t="inlineStr"/>
+      <c r="E311" t="inlineStr">
+        <is>
+          <t>9903.03.01</t>
+        </is>
+      </c>
+      <c r="F311" t="inlineStr">
+        <is>
+          <t>SECTION 122 - 10% DUTY</t>
+        </is>
+      </c>
+      <c r="G311" t="inlineStr">
+        <is>
+          <t>001</t>
+        </is>
+      </c>
+      <c r="H311" t="inlineStr">
+        <is>
+          <t>9903.03.01</t>
+        </is>
+      </c>
+      <c r="I311" t="inlineStr">
+        <is>
+          <t>8474.10.0010</t>
+        </is>
+      </c>
+      <c r="J311" t="inlineStr">
+        <is>
+          <t>EDGE INNOVATE (NI) LTD</t>
+        </is>
+      </c>
+      <c r="K311" t="inlineStr">
+        <is>
+          <t>EDGINN01</t>
+        </is>
+      </c>
+      <c r="L311" t="inlineStr">
+        <is>
+          <t>135501-01432</t>
+        </is>
+      </c>
+      <c r="M311" t="inlineStr">
+        <is>
+          <t>2026-06-17 00:00:00</t>
+        </is>
+      </c>
+      <c r="N311" t="inlineStr">
+        <is>
+          <t>2026-06-18 00:00:00</t>
+        </is>
+      </c>
+      <c r="O311" t="inlineStr">
+        <is>
+          <t>EDGE INNOVATE (NI) LTD</t>
+        </is>
+      </c>
+      <c r="P311" t="inlineStr">
+        <is>
+          <t>EDGE INNOVATE (NI) LTD</t>
+        </is>
+      </c>
+      <c r="Q311" t="inlineStr">
+        <is>
+          <t>2026-05-29 00:00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="312">
+      <c r="A312" t="inlineStr">
+        <is>
+          <t>2565937</t>
+        </is>
+      </c>
+      <c r="B312" t="inlineStr">
+        <is>
+          <t>EF4-0232258-2</t>
+        </is>
+      </c>
+      <c r="C312" t="inlineStr">
+        <is>
+          <t>Vessel, Container</t>
+        </is>
+      </c>
+      <c r="D312" t="inlineStr"/>
+      <c r="E312" t="inlineStr">
+        <is>
+          <t>9903.03.06</t>
+        </is>
+      </c>
+      <c r="F312" t="inlineStr">
+        <is>
+          <t>S122 EXCL,IRN/STL/ALUM,DERIV</t>
+        </is>
+      </c>
+      <c r="G312" t="inlineStr">
+        <is>
+          <t>001</t>
+        </is>
+      </c>
+      <c r="H312" t="inlineStr">
+        <is>
+          <t>9903.03.06</t>
+        </is>
+      </c>
+      <c r="I312" t="inlineStr">
+        <is>
+          <t>9903.82.22,8431.20.0000</t>
+        </is>
+      </c>
+      <c r="J312" t="inlineStr">
+        <is>
+          <t>MALLAGHAN (GA) INC.</t>
+        </is>
+      </c>
+      <c r="K312" t="inlineStr">
+        <is>
+          <t>MALGA01</t>
+        </is>
+      </c>
+      <c r="L312" t="inlineStr">
+        <is>
+          <t>36-488102800</t>
+        </is>
+      </c>
+      <c r="M312" t="inlineStr">
+        <is>
+          <t>2026-06-20 00:00:00</t>
+        </is>
+      </c>
+      <c r="N312" t="inlineStr">
+        <is>
+          <t>2026-06-18 00:00:00</t>
+        </is>
+      </c>
+      <c r="O312" t="inlineStr">
+        <is>
+          <t>MALLAGHAN ENGINEERING  LTD</t>
+        </is>
+      </c>
+      <c r="P312" t="inlineStr">
+        <is>
+          <t>MALLAGHAN ENGINEERING  LTD</t>
+        </is>
+      </c>
+      <c r="Q312" t="inlineStr">
+        <is>
+          <t>2026-05-17 00:00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="313">
+      <c r="A313" t="inlineStr">
+        <is>
+          <t>2565937</t>
+        </is>
+      </c>
+      <c r="B313" t="inlineStr">
+        <is>
+          <t>EF4-0232258-2</t>
+        </is>
+      </c>
+      <c r="C313" t="inlineStr">
+        <is>
+          <t>Vessel, Container</t>
+        </is>
+      </c>
+      <c r="D313" t="inlineStr"/>
+      <c r="E313" t="inlineStr">
+        <is>
+          <t>9903.03.06</t>
+        </is>
+      </c>
+      <c r="F313" t="inlineStr">
+        <is>
+          <t>S122 EXCL,IRN/STL/ALUM,DERIV</t>
+        </is>
+      </c>
+      <c r="G313" t="inlineStr">
+        <is>
+          <t>002</t>
+        </is>
+      </c>
+      <c r="H313" t="inlineStr">
+        <is>
+          <t>9903.03.06</t>
+        </is>
+      </c>
+      <c r="I313" t="inlineStr">
+        <is>
+          <t>9903.82.22,8431.20.0000</t>
+        </is>
+      </c>
+      <c r="J313" t="inlineStr">
+        <is>
+          <t>MALLAGHAN (GA) INC.</t>
+        </is>
+      </c>
+      <c r="K313" t="inlineStr">
+        <is>
+          <t>MALGA01</t>
+        </is>
+      </c>
+      <c r="L313" t="inlineStr">
+        <is>
+          <t>36-488102800</t>
+        </is>
+      </c>
+      <c r="M313" t="inlineStr">
+        <is>
+          <t>2026-06-20 00:00:00</t>
+        </is>
+      </c>
+      <c r="N313" t="inlineStr">
+        <is>
+          <t>2026-06-18 00:00:00</t>
+        </is>
+      </c>
+      <c r="O313" t="inlineStr">
+        <is>
+          <t>MALLAGHAN ENGINEERING  LTD</t>
+        </is>
+      </c>
+      <c r="P313" t="inlineStr">
+        <is>
+          <t>MALLAGHAN ENGINEERING  LTD</t>
+        </is>
+      </c>
+      <c r="Q313" t="inlineStr">
+        <is>
+          <t>2026-05-17 00:00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="314">
+      <c r="A314" t="inlineStr">
+        <is>
+          <t>2565937</t>
+        </is>
+      </c>
+      <c r="B314" t="inlineStr">
+        <is>
+          <t>EF4-0232258-2</t>
+        </is>
+      </c>
+      <c r="C314" t="inlineStr">
+        <is>
+          <t>Vessel, Container</t>
+        </is>
+      </c>
+      <c r="D314" t="inlineStr"/>
+      <c r="E314" t="inlineStr">
+        <is>
+          <t>9903.03.06</t>
+        </is>
+      </c>
+      <c r="F314" t="inlineStr">
+        <is>
+          <t>S122 EXCL,IRN/STL/ALUM,DERIV</t>
+        </is>
+      </c>
+      <c r="G314" t="inlineStr">
+        <is>
+          <t>003</t>
+        </is>
+      </c>
+      <c r="H314" t="inlineStr">
+        <is>
+          <t>9903.03.06</t>
+        </is>
+      </c>
+      <c r="I314" t="inlineStr">
+        <is>
+          <t>9903.82.22,8431.20.0000</t>
+        </is>
+      </c>
+      <c r="J314" t="inlineStr">
+        <is>
+          <t>MALLAGHAN (GA) INC.</t>
+        </is>
+      </c>
+      <c r="K314" t="inlineStr">
+        <is>
+          <t>MALGA01</t>
+        </is>
+      </c>
+      <c r="L314" t="inlineStr">
+        <is>
+          <t>36-488102800</t>
+        </is>
+      </c>
+      <c r="M314" t="inlineStr">
+        <is>
+          <t>2026-06-20 00:00:00</t>
+        </is>
+      </c>
+      <c r="N314" t="inlineStr">
+        <is>
+          <t>2026-06-18 00:00:00</t>
+        </is>
+      </c>
+      <c r="O314" t="inlineStr">
+        <is>
+          <t>MALLAGHAN ENGINEERING  LTD</t>
+        </is>
+      </c>
+      <c r="P314" t="inlineStr">
+        <is>
+          <t>MALLAGHAN ENGINEERING  LTD</t>
+        </is>
+      </c>
+      <c r="Q314" t="inlineStr">
+        <is>
+          <t>2026-05-17 00:00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="315">
+      <c r="A315" t="inlineStr">
+        <is>
+          <t>2566105</t>
+        </is>
+      </c>
+      <c r="B315" t="inlineStr">
+        <is>
+          <t>EF4-0232283-0</t>
+        </is>
+      </c>
+      <c r="C315" t="inlineStr">
+        <is>
+          <t>Vessel, Container</t>
+        </is>
+      </c>
+      <c r="D315" t="inlineStr"/>
+      <c r="E315" t="inlineStr">
+        <is>
+          <t>9903.03.01</t>
+        </is>
+      </c>
+      <c r="F315" t="inlineStr">
+        <is>
+          <t>SECTION 122 - 10% DUTY</t>
+        </is>
+      </c>
+      <c r="G315" t="inlineStr">
+        <is>
+          <t>001</t>
+        </is>
+      </c>
+      <c r="H315" t="inlineStr">
+        <is>
+          <t>9903.03.01</t>
+        </is>
+      </c>
+      <c r="I315" t="inlineStr">
+        <is>
+          <t>3920.61.0000</t>
+        </is>
+      </c>
+      <c r="J315" t="inlineStr">
+        <is>
+          <t>TUBUS BAUER GMBH</t>
+        </is>
+      </c>
+      <c r="K315" t="inlineStr">
+        <is>
+          <t>TUBBAU01</t>
+        </is>
+      </c>
+      <c r="L315" t="inlineStr">
+        <is>
+          <t>091601-00584</t>
+        </is>
+      </c>
+      <c r="M315" t="inlineStr">
+        <is>
+          <t>2026-06-18 00:00:00</t>
+        </is>
+      </c>
+      <c r="N315" t="inlineStr">
+        <is>
+          <t>2026-06-18 00:00:00</t>
+        </is>
+      </c>
+      <c r="O315" t="inlineStr">
+        <is>
+          <t>TUBUS BAUER GMBH</t>
+        </is>
+      </c>
+      <c r="P315" t="inlineStr">
+        <is>
+          <t>TUBUS BAUER GMBH</t>
+        </is>
+      </c>
+      <c r="Q315" t="inlineStr">
+        <is>
+          <t>2026-06-02 00:00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="316">
+      <c r="A316" t="inlineStr">
+        <is>
+          <t>2566265</t>
+        </is>
+      </c>
+      <c r="B316" t="inlineStr">
+        <is>
+          <t>EF4-0232362-2</t>
+        </is>
+      </c>
+      <c r="C316" t="inlineStr">
+        <is>
+          <t>Vessel, Container</t>
+        </is>
+      </c>
+      <c r="D316" t="inlineStr"/>
+      <c r="E316" t="inlineStr">
+        <is>
+          <t>9903.03.01</t>
+        </is>
+      </c>
+      <c r="F316" t="inlineStr">
+        <is>
+          <t>SECTION 122 - 10% DUTY</t>
+        </is>
+      </c>
+      <c r="G316" t="inlineStr">
+        <is>
+          <t>001</t>
+        </is>
+      </c>
+      <c r="H316" t="inlineStr">
+        <is>
+          <t>9903.03.01</t>
+        </is>
+      </c>
+      <c r="I316" t="inlineStr">
+        <is>
+          <t>9903.82.01,8424.90.9080</t>
+        </is>
+      </c>
+      <c r="J316" t="inlineStr">
+        <is>
+          <t>EISENMANN OF SOUTH CAROLINA INC</t>
+        </is>
+      </c>
+      <c r="K316" t="inlineStr">
+        <is>
+          <t>EISINC03</t>
+        </is>
+      </c>
+      <c r="L316" t="inlineStr">
+        <is>
+          <t>86-240963300</t>
+        </is>
+      </c>
+      <c r="M316" t="inlineStr">
+        <is>
+          <t>2026-06-21 00:00:00</t>
+        </is>
+      </c>
+      <c r="N316" t="inlineStr">
+        <is>
+          <t>2026-06-18 00:00:00</t>
+        </is>
+      </c>
+      <c r="O316" t="inlineStr">
+        <is>
+          <t>EISENMANN GMBH</t>
+        </is>
+      </c>
+      <c r="P316" t="inlineStr">
+        <is>
+          <t>EISENMANN GMBH</t>
+        </is>
+      </c>
+      <c r="Q316" t="inlineStr">
+        <is>
+          <t>2026-06-06 00:00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="317">
+      <c r="A317" t="inlineStr">
+        <is>
+          <t>2566155</t>
+        </is>
+      </c>
+      <c r="B317" t="inlineStr">
+        <is>
+          <t>EF4-0232431-5</t>
+        </is>
+      </c>
+      <c r="C317" t="inlineStr">
+        <is>
+          <t>Vessel, Container</t>
+        </is>
+      </c>
+      <c r="D317" t="inlineStr"/>
+      <c r="E317" t="inlineStr">
+        <is>
+          <t>9903.03.06</t>
+        </is>
+      </c>
+      <c r="F317" t="inlineStr">
+        <is>
+          <t>S122 EXCL,IRN/STL/ALUM,DERIV</t>
+        </is>
+      </c>
+      <c r="G317" t="inlineStr">
+        <is>
+          <t>001</t>
+        </is>
+      </c>
+      <c r="H317" t="inlineStr">
+        <is>
+          <t>9903.03.06</t>
+        </is>
+      </c>
+      <c r="I317" t="inlineStr">
+        <is>
+          <t>9903.74.11,9903.94.53,8708.29.5160</t>
+        </is>
+      </c>
+      <c r="J317" t="inlineStr">
+        <is>
+          <t>BORGERS USA CORP</t>
+        </is>
+      </c>
+      <c r="K317" t="inlineStr">
+        <is>
+          <t>BORUSA</t>
+        </is>
+      </c>
+      <c r="L317" t="inlineStr">
+        <is>
+          <t>65-117296500</t>
+        </is>
+      </c>
+      <c r="M317" t="inlineStr">
+        <is>
+          <t>2026-06-18 00:00:00</t>
+        </is>
+      </c>
+      <c r="N317" t="inlineStr">
+        <is>
+          <t>2026-06-18 00:00:00</t>
+        </is>
+      </c>
+      <c r="O317" t="inlineStr">
+        <is>
+          <t>AUTONEUM CZ S.R.O.</t>
+        </is>
+      </c>
+      <c r="P317" t="inlineStr">
+        <is>
+          <t>AUTONEUM CZ S.R.O.</t>
+        </is>
+      </c>
+      <c r="Q317" t="inlineStr">
+        <is>
+          <t>2026-06-06 00:00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="318">
+      <c r="A318" t="inlineStr">
+        <is>
+          <t>2566155</t>
+        </is>
+      </c>
+      <c r="B318" t="inlineStr">
+        <is>
+          <t>EF4-0232431-5</t>
+        </is>
+      </c>
+      <c r="C318" t="inlineStr">
+        <is>
+          <t>Vessel, Container</t>
+        </is>
+      </c>
+      <c r="D318" t="inlineStr"/>
+      <c r="E318" t="inlineStr">
+        <is>
+          <t>9903.03.06</t>
+        </is>
+      </c>
+      <c r="F318" t="inlineStr">
+        <is>
+          <t>S122 EXCL,IRN/STL/ALUM,DERIV</t>
+        </is>
+      </c>
+      <c r="G318" t="inlineStr">
+        <is>
+          <t>002</t>
+        </is>
+      </c>
+      <c r="H318" t="inlineStr">
+        <is>
+          <t>9903.03.06</t>
+        </is>
+      </c>
+      <c r="I318" t="inlineStr">
+        <is>
+          <t>9903.74.11,9903.94.53,8708.29.5160</t>
+        </is>
+      </c>
+      <c r="J318" t="inlineStr">
+        <is>
+          <t>BORGERS USA CORP</t>
+        </is>
+      </c>
+      <c r="K318" t="inlineStr">
+        <is>
+          <t>BORUSA</t>
+        </is>
+      </c>
+      <c r="L318" t="inlineStr">
+        <is>
+          <t>65-117296500</t>
+        </is>
+      </c>
+      <c r="M318" t="inlineStr">
+        <is>
+          <t>2026-06-18 00:00:00</t>
+        </is>
+      </c>
+      <c r="N318" t="inlineStr">
+        <is>
+          <t>2026-06-18 00:00:00</t>
+        </is>
+      </c>
+      <c r="O318" t="inlineStr">
+        <is>
+          <t>AUTONEUM CZ S.R.O.</t>
+        </is>
+      </c>
+      <c r="P318" t="inlineStr">
+        <is>
+          <t>AUTONEUM CZ S.R.O.</t>
+        </is>
+      </c>
+      <c r="Q318" t="inlineStr">
+        <is>
+          <t>2026-06-06 00:00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="319">
+      <c r="A319" t="inlineStr">
+        <is>
+          <t>2566155</t>
+        </is>
+      </c>
+      <c r="B319" t="inlineStr">
+        <is>
+          <t>EF4-0232431-5</t>
+        </is>
+      </c>
+      <c r="C319" t="inlineStr">
+        <is>
+          <t>Vessel, Container</t>
+        </is>
+      </c>
+      <c r="D319" t="inlineStr"/>
+      <c r="E319" t="inlineStr">
+        <is>
+          <t>9903.03.06</t>
+        </is>
+      </c>
+      <c r="F319" t="inlineStr">
+        <is>
+          <t>S122 EXCL,IRN/STL/ALUM,DERIV</t>
+        </is>
+      </c>
+      <c r="G319" t="inlineStr">
+        <is>
+          <t>003</t>
+        </is>
+      </c>
+      <c r="H319" t="inlineStr">
+        <is>
+          <t>9903.03.06</t>
+        </is>
+      </c>
+      <c r="I319" t="inlineStr">
+        <is>
+          <t>9903.74.11,9903.94.53,8708.29.5160</t>
+        </is>
+      </c>
+      <c r="J319" t="inlineStr">
+        <is>
+          <t>BORGERS USA CORP</t>
+        </is>
+      </c>
+      <c r="K319" t="inlineStr">
+        <is>
+          <t>BORUSA</t>
+        </is>
+      </c>
+      <c r="L319" t="inlineStr">
+        <is>
+          <t>65-117296500</t>
+        </is>
+      </c>
+      <c r="M319" t="inlineStr">
+        <is>
+          <t>2026-06-18 00:00:00</t>
+        </is>
+      </c>
+      <c r="N319" t="inlineStr">
+        <is>
+          <t>2026-06-18 00:00:00</t>
+        </is>
+      </c>
+      <c r="O319" t="inlineStr">
+        <is>
+          <t>AUTONEUM CZ S.R.O.</t>
+        </is>
+      </c>
+      <c r="P319" t="inlineStr">
+        <is>
+          <t>AUTONEUM CZ S.R.O.</t>
+        </is>
+      </c>
+      <c r="Q319" t="inlineStr">
+        <is>
+          <t>2026-06-06 00:00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="320">
+      <c r="A320" t="inlineStr">
+        <is>
+          <t>2566155</t>
+        </is>
+      </c>
+      <c r="B320" t="inlineStr">
+        <is>
+          <t>EF4-0232431-5</t>
+        </is>
+      </c>
+      <c r="C320" t="inlineStr">
+        <is>
+          <t>Vessel, Container</t>
+        </is>
+      </c>
+      <c r="D320" t="inlineStr"/>
+      <c r="E320" t="inlineStr">
+        <is>
+          <t>9903.03.06</t>
+        </is>
+      </c>
+      <c r="F320" t="inlineStr">
+        <is>
+          <t>S122 EXCL,IRN/STL/ALUM,DERIV</t>
+        </is>
+      </c>
+      <c r="G320" t="inlineStr">
+        <is>
+          <t>004</t>
+        </is>
+      </c>
+      <c r="H320" t="inlineStr">
+        <is>
+          <t>9903.03.06</t>
+        </is>
+      </c>
+      <c r="I320" t="inlineStr">
+        <is>
+          <t>9903.74.11,9903.94.53,8708.29.5160</t>
+        </is>
+      </c>
+      <c r="J320" t="inlineStr">
+        <is>
+          <t>BORGERS USA CORP</t>
+        </is>
+      </c>
+      <c r="K320" t="inlineStr">
+        <is>
+          <t>BORUSA</t>
+        </is>
+      </c>
+      <c r="L320" t="inlineStr">
+        <is>
+          <t>65-117296500</t>
+        </is>
+      </c>
+      <c r="M320" t="inlineStr">
+        <is>
+          <t>2026-06-18 00:00:00</t>
+        </is>
+      </c>
+      <c r="N320" t="inlineStr">
+        <is>
+          <t>2026-06-18 00:00:00</t>
+        </is>
+      </c>
+      <c r="O320" t="inlineStr">
+        <is>
+          <t>AUTONEUM CZ S.R.O.</t>
+        </is>
+      </c>
+      <c r="P320" t="inlineStr">
+        <is>
+          <t>AUTONEUM CZ S.R.O.</t>
+        </is>
+      </c>
+      <c r="Q320" t="inlineStr">
+        <is>
+          <t>2026-06-06 00:00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="321">
+      <c r="A321" t="inlineStr">
+        <is>
+          <t>4539433</t>
+        </is>
+      </c>
+      <c r="B321" t="inlineStr">
+        <is>
+          <t>EF4-0232434-9</t>
+        </is>
+      </c>
+      <c r="C321" t="inlineStr">
+        <is>
+          <t>Air, Non-container</t>
+        </is>
+      </c>
+      <c r="D321" t="inlineStr"/>
+      <c r="E321" t="inlineStr">
+        <is>
+          <t>9903.88.03</t>
+        </is>
+      </c>
+      <c r="F321" t="inlineStr">
+        <is>
+          <t>ARTICLE OF CHINA,US NTE 20(F)</t>
+        </is>
+      </c>
+      <c r="G321" t="inlineStr">
+        <is>
+          <t>001</t>
+        </is>
+      </c>
+      <c r="H321" t="inlineStr">
+        <is>
+          <t>9903.88.03</t>
+        </is>
+      </c>
+      <c r="I321" t="inlineStr">
+        <is>
+          <t>9903.03.03,2926.90.4300</t>
+        </is>
+      </c>
+      <c r="J321" t="inlineStr">
+        <is>
+          <t>MAYZO INC</t>
+        </is>
+      </c>
+      <c r="K321" t="inlineStr">
+        <is>
+          <t>MAYINC</t>
+        </is>
+      </c>
+      <c r="L321" t="inlineStr">
+        <is>
+          <t>62-129031200</t>
+        </is>
+      </c>
+      <c r="M321" t="inlineStr">
+        <is>
+          <t>2026-06-17 00:00:00</t>
+        </is>
+      </c>
+      <c r="N321" t="inlineStr">
+        <is>
+          <t>2026-06-18 00:00:00</t>
+        </is>
+      </c>
+      <c r="O321" t="inlineStr">
+        <is>
+          <t>HANGZHOU DISHENG IMPORT &amp; EXPORT</t>
+        </is>
+      </c>
+      <c r="P321" t="inlineStr">
+        <is>
+          <t>HANGZHOU DISHENG IMPORT &amp; EXPORT</t>
+        </is>
+      </c>
+      <c r="Q321" t="inlineStr">
+        <is>
+          <t>2026-06-17 00:00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="322">
+      <c r="A322" t="inlineStr">
+        <is>
+          <t>2565798</t>
+        </is>
+      </c>
+      <c r="B322" t="inlineStr">
+        <is>
+          <t>EF4-0232494-3</t>
+        </is>
+      </c>
+      <c r="C322" t="inlineStr">
+        <is>
+          <t>Vessel, Container</t>
+        </is>
+      </c>
+      <c r="D322" t="inlineStr"/>
+      <c r="E322" t="inlineStr">
+        <is>
+          <t>9903.03.06</t>
+        </is>
+      </c>
+      <c r="F322" t="inlineStr">
+        <is>
+          <t>S122 EXCL,IRN/STL/ALUM,DERIV</t>
+        </is>
+      </c>
+      <c r="G322" t="inlineStr">
+        <is>
+          <t>001</t>
+        </is>
+      </c>
+      <c r="H322" t="inlineStr">
+        <is>
+          <t>9903.03.06</t>
+        </is>
+      </c>
+      <c r="I322" t="inlineStr">
+        <is>
+          <t>9903.82.02,7222.20.0064</t>
+        </is>
+      </c>
+      <c r="J322" t="inlineStr">
+        <is>
+          <t>MESHA STEELS  LLC</t>
+        </is>
+      </c>
+      <c r="K322" t="inlineStr">
+        <is>
+          <t>MESSTE</t>
+        </is>
+      </c>
+      <c r="L322" t="inlineStr">
+        <is>
+          <t>20-274801900</t>
+        </is>
+      </c>
+      <c r="M322" t="inlineStr">
+        <is>
+          <t>2026-06-18 00:00:00</t>
+        </is>
+      </c>
+      <c r="N322" t="inlineStr">
+        <is>
+          <t>2026-06-18 00:00:00</t>
+        </is>
+      </c>
+      <c r="O322" t="inlineStr">
+        <is>
+          <t>BHANSALI BRIGHT BARS PVT. LTD.</t>
+        </is>
+      </c>
+      <c r="P322" t="inlineStr">
+        <is>
+          <t>BHANSALI BRIGHT BARS PVT. LTD.</t>
+        </is>
+      </c>
+      <c r="Q322" t="inlineStr">
+        <is>
+          <t>2026-05-12 00:00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="323">
+      <c r="A323" t="inlineStr">
+        <is>
+          <t>2565799</t>
+        </is>
+      </c>
+      <c r="B323" t="inlineStr">
+        <is>
+          <t>EF4-0232495-0</t>
+        </is>
+      </c>
+      <c r="C323" t="inlineStr">
+        <is>
+          <t>Vessel, Container</t>
+        </is>
+      </c>
+      <c r="D323" t="inlineStr"/>
+      <c r="E323" t="inlineStr">
+        <is>
+          <t>9903.03.06</t>
+        </is>
+      </c>
+      <c r="F323" t="inlineStr">
+        <is>
+          <t>S122 EXCL,IRN/STL/ALUM,DERIV</t>
+        </is>
+      </c>
+      <c r="G323" t="inlineStr">
+        <is>
+          <t>001</t>
+        </is>
+      </c>
+      <c r="H323" t="inlineStr">
+        <is>
+          <t>9903.03.06</t>
+        </is>
+      </c>
+      <c r="I323" t="inlineStr">
+        <is>
+          <t>9903.82.02,7222.20.0062</t>
+        </is>
+      </c>
+      <c r="J323" t="inlineStr">
+        <is>
+          <t>MESHA STEELS  LLC</t>
+        </is>
+      </c>
+      <c r="K323" t="inlineStr">
+        <is>
+          <t>MESSTE</t>
+        </is>
+      </c>
+      <c r="L323" t="inlineStr">
+        <is>
+          <t>20-274801900</t>
+        </is>
+      </c>
+      <c r="M323" t="inlineStr">
+        <is>
+          <t>2026-06-18 00:00:00</t>
+        </is>
+      </c>
+      <c r="N323" t="inlineStr">
+        <is>
+          <t>2026-06-18 00:00:00</t>
+        </is>
+      </c>
+      <c r="O323" t="inlineStr">
+        <is>
+          <t>BHANSALI BRIGHT BARS PVT. LTD.</t>
+        </is>
+      </c>
+      <c r="P323" t="inlineStr">
+        <is>
+          <t>BHANSALI BRIGHT BARS PVT. LTD.</t>
+        </is>
+      </c>
+      <c r="Q323" t="inlineStr">
+        <is>
+          <t>2026-05-12 00:00:00</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/trimika_data.xlsx
+++ b/trimika_data.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q323"/>
+  <dimension ref="A1:Q340"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -24977,28 +24977,28 @@
     <row r="295">
       <c r="A295" t="inlineStr">
         <is>
-          <t>2615664</t>
+          <t>2565682</t>
         </is>
       </c>
       <c r="B295" t="inlineStr">
         <is>
-          <t>EF4-0231983-6</t>
+          <t>EF4-0231989-3</t>
         </is>
       </c>
       <c r="C295" t="inlineStr">
         <is>
-          <t>Vessel, Non-container</t>
+          <t>Vessel, Container</t>
         </is>
       </c>
       <c r="D295" t="inlineStr"/>
       <c r="E295" t="inlineStr">
         <is>
-          <t>9903.88.01</t>
+          <t>9903.88.03</t>
         </is>
       </c>
       <c r="F295" t="inlineStr">
         <is>
-          <t>ARTICLE OF CHINA,US NTE 20(A)</t>
+          <t>ARTICLE OF CHINA,US NTE 20(F)</t>
         </is>
       </c>
       <c r="G295" t="inlineStr">
@@ -25008,12 +25008,12 @@
       </c>
       <c r="H295" t="inlineStr">
         <is>
-          <t>9903.88.01</t>
+          <t>9903.88.03</t>
         </is>
       </c>
       <c r="I295" t="inlineStr">
         <is>
-          <t>9903.03.06,9903.82.09,8482.10.5012</t>
+          <t>9903.03.01,9403.99.9045</t>
         </is>
       </c>
       <c r="J295" t="inlineStr">
@@ -25033,7 +25033,7 @@
       </c>
       <c r="M295" t="inlineStr">
         <is>
-          <t>2026-06-11 00:00:00</t>
+          <t>2026-06-19 00:00:00</t>
         </is>
       </c>
       <c r="N295" t="inlineStr">
@@ -25043,17 +25043,17 @@
       </c>
       <c r="O295" t="inlineStr">
         <is>
-          <t>LINYU HANDWARE MANUFACTURE CO LTD</t>
+          <t>FUJIAN ANTAI NEW ENERGY TECH CO LTD</t>
         </is>
       </c>
       <c r="P295" t="inlineStr">
         <is>
-          <t>LINYU HANDWARE MANUFACTURE CO LTD</t>
+          <t>FUJIAN ANTAI NEW ENERGY TECH CO LTD</t>
         </is>
       </c>
       <c r="Q295" t="inlineStr">
         <is>
-          <t>2026-05-15 00:00:00</t>
+          <t>2026-05-19 00:00:00</t>
         </is>
       </c>
     </row>
@@ -25086,7 +25086,7 @@
       </c>
       <c r="G296" t="inlineStr">
         <is>
-          <t>001</t>
+          <t>002</t>
         </is>
       </c>
       <c r="H296" t="inlineStr">
@@ -25096,7 +25096,7 @@
       </c>
       <c r="I296" t="inlineStr">
         <is>
-          <t>9903.03.01,9403.99.9045</t>
+          <t>9903.03.01,9405.41.8440</t>
         </is>
       </c>
       <c r="J296" t="inlineStr">
@@ -25159,27 +25159,27 @@
       <c r="D297" t="inlineStr"/>
       <c r="E297" t="inlineStr">
         <is>
-          <t>9903.88.03</t>
+          <t>9903.88.15</t>
         </is>
       </c>
       <c r="F297" t="inlineStr">
         <is>
-          <t>ARTICLE OF CHINA,US NTE 20(F)</t>
+          <t>ARTICLE OF CHINA,US NTE 20(R)</t>
         </is>
       </c>
       <c r="G297" t="inlineStr">
         <is>
-          <t>002</t>
+          <t>003</t>
         </is>
       </c>
       <c r="H297" t="inlineStr">
         <is>
-          <t>9903.88.03</t>
+          <t>9903.88.15</t>
         </is>
       </c>
       <c r="I297" t="inlineStr">
         <is>
-          <t>9903.03.01,9405.41.8440</t>
+          <t>9903.03.01,3926.90.9989</t>
         </is>
       </c>
       <c r="J297" t="inlineStr">
@@ -25226,12 +25226,12 @@
     <row r="298">
       <c r="A298" t="inlineStr">
         <is>
-          <t>2565682</t>
+          <t>2565800</t>
         </is>
       </c>
       <c r="B298" t="inlineStr">
         <is>
-          <t>EF4-0231989-3</t>
+          <t>EF4-0232068-5</t>
         </is>
       </c>
       <c r="C298" t="inlineStr">
@@ -25239,50 +25239,54 @@
           <t>Vessel, Container</t>
         </is>
       </c>
-      <c r="D298" t="inlineStr"/>
+      <c r="D298" t="inlineStr">
+        <is>
+          <t>V0413939047</t>
+        </is>
+      </c>
       <c r="E298" t="inlineStr">
         <is>
-          <t>9903.88.15</t>
+          <t>9903.03.06</t>
         </is>
       </c>
       <c r="F298" t="inlineStr">
         <is>
-          <t>ARTICLE OF CHINA,US NTE 20(R)</t>
+          <t>S122 EXCL,IRN/STL/ALUM,DERIV</t>
         </is>
       </c>
       <c r="G298" t="inlineStr">
         <is>
-          <t>003</t>
+          <t>001</t>
         </is>
       </c>
       <c r="H298" t="inlineStr">
         <is>
-          <t>9903.88.15</t>
+          <t>9903.03.06</t>
         </is>
       </c>
       <c r="I298" t="inlineStr">
         <is>
-          <t>9903.03.01,3926.90.9989</t>
+          <t>9903.82.02,7223.00.1031</t>
         </is>
       </c>
       <c r="J298" t="inlineStr">
         <is>
-          <t>VISUAL CREATIONS, INC.</t>
+          <t>VENUS WIRE INDUSTRIES PRIVATE LTD</t>
         </is>
       </c>
       <c r="K298" t="inlineStr">
         <is>
-          <t>VISCRE</t>
+          <t>VENWIR</t>
         </is>
       </c>
       <c r="L298" t="inlineStr">
         <is>
-          <t>20-461602300</t>
+          <t>993901-03595</t>
         </is>
       </c>
       <c r="M298" t="inlineStr">
         <is>
-          <t>2026-06-19 00:00:00</t>
+          <t>2026-06-17 00:00:00</t>
         </is>
       </c>
       <c r="N298" t="inlineStr">
@@ -25292,29 +25296,29 @@
       </c>
       <c r="O298" t="inlineStr">
         <is>
-          <t>FUJIAN ANTAI NEW ENERGY TECH CO LTD</t>
+          <t>VENUS WIRE INDUSTRIES PRIVATE LIMIT</t>
         </is>
       </c>
       <c r="P298" t="inlineStr">
         <is>
-          <t>FUJIAN ANTAI NEW ENERGY TECH CO LTD</t>
+          <t>VENUS WIRE INDUSTRIES PRIVATE LIMITED</t>
         </is>
       </c>
       <c r="Q298" t="inlineStr">
         <is>
-          <t>2026-05-19 00:00:00</t>
+          <t>2026-05-11 00:00:00</t>
         </is>
       </c>
     </row>
     <row r="299">
       <c r="A299" t="inlineStr">
         <is>
-          <t>2565800</t>
+          <t>2566097</t>
         </is>
       </c>
       <c r="B299" t="inlineStr">
         <is>
-          <t>EF4-0232068-5</t>
+          <t>EF4-0232212-9</t>
         </is>
       </c>
       <c r="C299" t="inlineStr">
@@ -25329,12 +25333,12 @@
       </c>
       <c r="E299" t="inlineStr">
         <is>
-          <t>9903.03.06</t>
+          <t>9903.03.01</t>
         </is>
       </c>
       <c r="F299" t="inlineStr">
         <is>
-          <t>S122 EXCL,IRN/STL/ALUM,DERIV</t>
+          <t>SECTION 122 - 10% DUTY</t>
         </is>
       </c>
       <c r="G299" t="inlineStr">
@@ -25344,27 +25348,27 @@
       </c>
       <c r="H299" t="inlineStr">
         <is>
-          <t>9903.03.06</t>
+          <t>9903.03.01</t>
         </is>
       </c>
       <c r="I299" t="inlineStr">
         <is>
-          <t>9903.82.02,7223.00.1031</t>
+          <t>5704.90.0190</t>
         </is>
       </c>
       <c r="J299" t="inlineStr">
         <is>
-          <t>VENUS WIRE INDUSTRIES PRIVATE LTD</t>
+          <t>BORGERS OHIO INC.</t>
         </is>
       </c>
       <c r="K299" t="inlineStr">
         <is>
-          <t>VENWIR</t>
+          <t>BORUSA02</t>
         </is>
       </c>
       <c r="L299" t="inlineStr">
         <is>
-          <t>993901-03595</t>
+          <t>30-084196200</t>
         </is>
       </c>
       <c r="M299" t="inlineStr">
@@ -25379,17 +25383,17 @@
       </c>
       <c r="O299" t="inlineStr">
         <is>
-          <t>VENUS WIRE INDUSTRIES PRIVATE LIMIT</t>
+          <t>AUTONEUM GERMANY GMBH</t>
         </is>
       </c>
       <c r="P299" t="inlineStr">
         <is>
-          <t>VENUS WIRE INDUSTRIES PRIVATE LIMITED</t>
+          <t>AUTONEUM GERMANY GMBH</t>
         </is>
       </c>
       <c r="Q299" t="inlineStr">
         <is>
-          <t>2026-05-11 00:00:00</t>
+          <t>2026-05-30 00:00:00</t>
         </is>
       </c>
     </row>
@@ -25426,7 +25430,7 @@
       </c>
       <c r="G300" t="inlineStr">
         <is>
-          <t>001</t>
+          <t>002</t>
         </is>
       </c>
       <c r="H300" t="inlineStr">
@@ -25513,7 +25517,7 @@
       </c>
       <c r="G301" t="inlineStr">
         <is>
-          <t>002</t>
+          <t>003</t>
         </is>
       </c>
       <c r="H301" t="inlineStr">
@@ -25570,12 +25574,12 @@
     <row r="302">
       <c r="A302" t="inlineStr">
         <is>
-          <t>2566097</t>
+          <t>2565838</t>
         </is>
       </c>
       <c r="B302" t="inlineStr">
         <is>
-          <t>EF4-0232212-9</t>
+          <t>EF4-0232439-8</t>
         </is>
       </c>
       <c r="C302" t="inlineStr">
@@ -25585,47 +25589,47 @@
       </c>
       <c r="D302" t="inlineStr">
         <is>
-          <t>V0413939047</t>
+          <t>V0413931663</t>
         </is>
       </c>
       <c r="E302" t="inlineStr">
         <is>
-          <t>9903.03.01</t>
+          <t>9903.03.06</t>
         </is>
       </c>
       <c r="F302" t="inlineStr">
         <is>
-          <t>SECTION 122 - 10% DUTY</t>
+          <t>S122 EXCL,IRN/STL/ALUM,DERIV</t>
         </is>
       </c>
       <c r="G302" t="inlineStr">
         <is>
-          <t>003</t>
+          <t>001</t>
         </is>
       </c>
       <c r="H302" t="inlineStr">
         <is>
-          <t>9903.03.01</t>
+          <t>9903.03.06</t>
         </is>
       </c>
       <c r="I302" t="inlineStr">
         <is>
-          <t>5704.90.0190</t>
+          <t>9903.82.02,7222.20.0062</t>
         </is>
       </c>
       <c r="J302" t="inlineStr">
         <is>
-          <t>BORGERS OHIO INC.</t>
+          <t>MESHA STEELS  LLC</t>
         </is>
       </c>
       <c r="K302" t="inlineStr">
         <is>
-          <t>BORUSA02</t>
+          <t>MESSTE</t>
         </is>
       </c>
       <c r="L302" t="inlineStr">
         <is>
-          <t>30-084196200</t>
+          <t>20-274801900</t>
         </is>
       </c>
       <c r="M302" t="inlineStr">
@@ -25640,29 +25644,29 @@
       </c>
       <c r="O302" t="inlineStr">
         <is>
-          <t>AUTONEUM GERMANY GMBH</t>
+          <t>BHANSALI BRIGHT BARS PVT. LTD.</t>
         </is>
       </c>
       <c r="P302" t="inlineStr">
         <is>
-          <t>AUTONEUM GERMANY GMBH</t>
+          <t>BHANSALI BRIGHT BARS PVT. LTD.</t>
         </is>
       </c>
       <c r="Q302" t="inlineStr">
         <is>
-          <t>2026-05-30 00:00:00</t>
+          <t>2026-05-05 00:00:00</t>
         </is>
       </c>
     </row>
     <row r="303">
       <c r="A303" t="inlineStr">
         <is>
-          <t>2565838</t>
+          <t>2565907</t>
         </is>
       </c>
       <c r="B303" t="inlineStr">
         <is>
-          <t>EF4-0232439-8</t>
+          <t>EF4-0232496-8</t>
         </is>
       </c>
       <c r="C303" t="inlineStr">
@@ -25672,7 +25676,7 @@
       </c>
       <c r="D303" t="inlineStr">
         <is>
-          <t>V0413931663</t>
+          <t>V0413937900</t>
         </is>
       </c>
       <c r="E303" t="inlineStr">
@@ -25697,7 +25701,7 @@
       </c>
       <c r="I303" t="inlineStr">
         <is>
-          <t>9903.82.02,7222.20.0062</t>
+          <t>9903.82.02,7222.20.0043</t>
         </is>
       </c>
       <c r="J303" t="inlineStr">
@@ -25737,7 +25741,7 @@
       </c>
       <c r="Q303" t="inlineStr">
         <is>
-          <t>2026-05-05 00:00:00</t>
+          <t>2026-05-11 00:00:00</t>
         </is>
       </c>
     </row>
@@ -25774,7 +25778,7 @@
       </c>
       <c r="G304" t="inlineStr">
         <is>
-          <t>001</t>
+          <t>002</t>
         </is>
       </c>
       <c r="H304" t="inlineStr">
@@ -25784,7 +25788,7 @@
       </c>
       <c r="I304" t="inlineStr">
         <is>
-          <t>9903.82.02,7222.20.0043</t>
+          <t>9903.82.02,7222.20.0073</t>
         </is>
       </c>
       <c r="J304" t="inlineStr">
@@ -25831,17 +25835,17 @@
     <row r="305">
       <c r="A305" t="inlineStr">
         <is>
-          <t>2565907</t>
+          <t>2615809</t>
         </is>
       </c>
       <c r="B305" t="inlineStr">
         <is>
-          <t>EF4-0232496-8</t>
+          <t>EF4-0232557-7</t>
         </is>
       </c>
       <c r="C305" t="inlineStr">
         <is>
-          <t>Vessel, Container</t>
+          <t>Truck, Non-container</t>
         </is>
       </c>
       <c r="D305" t="inlineStr">
@@ -25851,91 +25855,87 @@
       </c>
       <c r="E305" t="inlineStr">
         <is>
-          <t>9903.03.06</t>
+          <t>9903.03.01</t>
         </is>
       </c>
       <c r="F305" t="inlineStr">
         <is>
-          <t>S122 EXCL,IRN/STL/ALUM,DERIV</t>
+          <t>SECTION 122 - 10% DUTY</t>
         </is>
       </c>
       <c r="G305" t="inlineStr">
         <is>
-          <t>002</t>
+          <t>001</t>
         </is>
       </c>
       <c r="H305" t="inlineStr">
         <is>
-          <t>9903.03.06</t>
+          <t>9903.03.01</t>
         </is>
       </c>
       <c r="I305" t="inlineStr">
         <is>
-          <t>9903.82.02,7222.20.0073</t>
+          <t>8483.40.5010</t>
         </is>
       </c>
       <c r="J305" t="inlineStr">
         <is>
-          <t>MESHA STEELS  LLC</t>
+          <t>AUMUND CORPORATION</t>
         </is>
       </c>
       <c r="K305" t="inlineStr">
         <is>
-          <t>MESSTE</t>
+          <t>AUMCOR</t>
         </is>
       </c>
       <c r="L305" t="inlineStr">
         <is>
-          <t>20-274801900</t>
+          <t>58-138896800</t>
         </is>
       </c>
       <c r="M305" t="inlineStr">
         <is>
+          <t>2026-06-16 00:00:00</t>
+        </is>
+      </c>
+      <c r="N305" t="inlineStr">
+        <is>
           <t>2026-06-17 00:00:00</t>
         </is>
       </c>
-      <c r="N305" t="inlineStr">
-        <is>
-          <t>2026-06-17 00:00:00</t>
-        </is>
-      </c>
       <c r="O305" t="inlineStr">
         <is>
-          <t>BHANSALI BRIGHT BARS PVT. LTD.</t>
+          <t>AUMUND FOERDERTECHNIK GMBH</t>
         </is>
       </c>
       <c r="P305" t="inlineStr">
         <is>
-          <t>BHANSALI BRIGHT BARS PVT. LTD.</t>
+          <t>AUMUND FOERDERTECHNIK GMBH</t>
         </is>
       </c>
       <c r="Q305" t="inlineStr">
         <is>
-          <t>2026-05-11 00:00:00</t>
+          <t>2026-06-16 00:00:00</t>
         </is>
       </c>
     </row>
     <row r="306">
       <c r="A306" t="inlineStr">
         <is>
-          <t>2615809</t>
+          <t>2565634</t>
         </is>
       </c>
       <c r="B306" t="inlineStr">
         <is>
-          <t>EF4-0232557-7</t>
+          <t>EF4-0231631-1</t>
         </is>
       </c>
       <c r="C306" t="inlineStr">
         <is>
-          <t>Truck, Non-container</t>
-        </is>
-      </c>
-      <c r="D306" t="inlineStr">
-        <is>
-          <t>V0413937900</t>
-        </is>
-      </c>
+          <t>Vessel, Container</t>
+        </is>
+      </c>
+      <c r="D306" t="inlineStr"/>
       <c r="E306" t="inlineStr">
         <is>
           <t>9903.03.01</t>
@@ -25958,59 +25958,59 @@
       </c>
       <c r="I306" t="inlineStr">
         <is>
-          <t>8483.40.5010</t>
+          <t>8438.90.9060</t>
         </is>
       </c>
       <c r="J306" t="inlineStr">
         <is>
-          <t>AUMUND CORPORATION</t>
+          <t>CANTRELL GAINCO GROUP INC</t>
         </is>
       </c>
       <c r="K306" t="inlineStr">
         <is>
-          <t>AUMCOR</t>
+          <t>CANGAI01</t>
         </is>
       </c>
       <c r="L306" t="inlineStr">
         <is>
-          <t>58-138896800</t>
+          <t>31-151121700</t>
         </is>
       </c>
       <c r="M306" t="inlineStr">
         <is>
-          <t>2026-06-16 00:00:00</t>
+          <t>2026-06-18 00:00:00</t>
         </is>
       </c>
       <c r="N306" t="inlineStr">
         <is>
-          <t>2026-06-17 00:00:00</t>
+          <t>2026-06-18 00:00:00</t>
         </is>
       </c>
       <c r="O306" t="inlineStr">
         <is>
-          <t>AUMUND FOERDERTECHNIK GMBH</t>
+          <t>O E CO LTD</t>
         </is>
       </c>
       <c r="P306" t="inlineStr">
         <is>
-          <t>AUMUND FOERDERTECHNIK GMBH</t>
+          <t>O E CO LTD</t>
         </is>
       </c>
       <c r="Q306" t="inlineStr">
         <is>
-          <t>2026-06-16 00:00:00</t>
+          <t>2026-05-05 00:00:00</t>
         </is>
       </c>
     </row>
     <row r="307">
       <c r="A307" t="inlineStr">
         <is>
-          <t>2565634</t>
+          <t>2565782</t>
         </is>
       </c>
       <c r="B307" t="inlineStr">
         <is>
-          <t>EF4-0231631-1</t>
+          <t>EF4-0231677-4</t>
         </is>
       </c>
       <c r="C307" t="inlineStr">
@@ -26041,22 +26041,22 @@
       </c>
       <c r="I307" t="inlineStr">
         <is>
-          <t>8438.90.9060</t>
+          <t>3505.10.0092</t>
         </is>
       </c>
       <c r="J307" t="inlineStr">
         <is>
-          <t>CANTRELL GAINCO GROUP INC</t>
+          <t>ROYAL INGREDIENTS GROUP BV</t>
         </is>
       </c>
       <c r="K307" t="inlineStr">
         <is>
-          <t>CANGAI01</t>
+          <t>ROYINGRE</t>
         </is>
       </c>
       <c r="L307" t="inlineStr">
         <is>
-          <t>31-151121700</t>
+          <t>074601-00962</t>
         </is>
       </c>
       <c r="M307" t="inlineStr">
@@ -26071,12 +26071,12 @@
       </c>
       <c r="O307" t="inlineStr">
         <is>
-          <t>O E CO LTD</t>
+          <t>EHM INTERTRADING CO LTD</t>
         </is>
       </c>
       <c r="P307" t="inlineStr">
         <is>
-          <t>O E CO LTD</t>
+          <t>EHM INTERTRADING CO LTD</t>
         </is>
       </c>
       <c r="Q307" t="inlineStr">
@@ -26088,12 +26088,12 @@
     <row r="308">
       <c r="A308" t="inlineStr">
         <is>
-          <t>2565782</t>
+          <t>2565784</t>
         </is>
       </c>
       <c r="B308" t="inlineStr">
         <is>
-          <t>EF4-0231677-4</t>
+          <t>EF4-0231678-2</t>
         </is>
       </c>
       <c r="C308" t="inlineStr">
@@ -26171,12 +26171,12 @@
     <row r="309">
       <c r="A309" t="inlineStr">
         <is>
-          <t>2565784</t>
+          <t>2565894</t>
         </is>
       </c>
       <c r="B309" t="inlineStr">
         <is>
-          <t>EF4-0231678-2</t>
+          <t>EF4-0232004-0</t>
         </is>
       </c>
       <c r="C309" t="inlineStr">
@@ -26187,12 +26187,12 @@
       <c r="D309" t="inlineStr"/>
       <c r="E309" t="inlineStr">
         <is>
-          <t>9903.03.01</t>
+          <t>9903.03.03</t>
         </is>
       </c>
       <c r="F309" t="inlineStr">
         <is>
-          <t>SECTION 122 - 10% DUTY</t>
+          <t>S122 -EXCLUSION-EXEMPTED PRDTS</t>
         </is>
       </c>
       <c r="G309" t="inlineStr">
@@ -26202,27 +26202,27 @@
       </c>
       <c r="H309" t="inlineStr">
         <is>
-          <t>9903.03.01</t>
+          <t>9903.03.03</t>
         </is>
       </c>
       <c r="I309" t="inlineStr">
         <is>
-          <t>3505.10.0092</t>
+          <t>2930.90.9231</t>
         </is>
       </c>
       <c r="J309" t="inlineStr">
         <is>
-          <t>ROYAL INGREDIENTS GROUP BV</t>
+          <t>CASTLE CHEMICALS LTD</t>
         </is>
       </c>
       <c r="K309" t="inlineStr">
         <is>
-          <t>ROYINGRE</t>
+          <t>CASCHE01</t>
         </is>
       </c>
       <c r="L309" t="inlineStr">
         <is>
-          <t>074601-00962</t>
+          <t>151704-07138</t>
         </is>
       </c>
       <c r="M309" t="inlineStr">
@@ -26237,45 +26237,45 @@
       </c>
       <c r="O309" t="inlineStr">
         <is>
-          <t>EHM INTERTRADING CO LTD</t>
+          <t>HUBEI JIANGHAN NEW MATERIALS CO LTD</t>
         </is>
       </c>
       <c r="P309" t="inlineStr">
         <is>
-          <t>EHM INTERTRADING CO LTD</t>
+          <t>HUBEI JIANGHAN NEW MATERIALS CO LTD</t>
         </is>
       </c>
       <c r="Q309" t="inlineStr">
         <is>
-          <t>2026-05-05 00:00:00</t>
+          <t>2026-04-30 00:00:00</t>
         </is>
       </c>
     </row>
     <row r="310">
       <c r="A310" t="inlineStr">
         <is>
-          <t>2565894</t>
+          <t>2566078</t>
         </is>
       </c>
       <c r="B310" t="inlineStr">
         <is>
-          <t>EF4-0232004-0</t>
+          <t>EF4-0232219-4</t>
         </is>
       </c>
       <c r="C310" t="inlineStr">
         <is>
-          <t>Vessel, Container</t>
+          <t>Vessel, Non-container</t>
         </is>
       </c>
       <c r="D310" t="inlineStr"/>
       <c r="E310" t="inlineStr">
         <is>
-          <t>9903.03.03</t>
+          <t>9903.03.01</t>
         </is>
       </c>
       <c r="F310" t="inlineStr">
         <is>
-          <t>S122 -EXCLUSION-EXEMPTED PRDTS</t>
+          <t>SECTION 122 - 10% DUTY</t>
         </is>
       </c>
       <c r="G310" t="inlineStr">
@@ -26285,80 +26285,80 @@
       </c>
       <c r="H310" t="inlineStr">
         <is>
-          <t>9903.03.03</t>
+          <t>9903.03.01</t>
         </is>
       </c>
       <c r="I310" t="inlineStr">
         <is>
-          <t>2930.90.9231</t>
+          <t>8474.10.0010</t>
         </is>
       </c>
       <c r="J310" t="inlineStr">
         <is>
-          <t>CASTLE CHEMICALS LTD</t>
+          <t>EDGE INNOVATE (NI) LTD</t>
         </is>
       </c>
       <c r="K310" t="inlineStr">
         <is>
-          <t>CASCHE01</t>
+          <t>EDGINN01</t>
         </is>
       </c>
       <c r="L310" t="inlineStr">
         <is>
-          <t>151704-07138</t>
+          <t>135501-01432</t>
         </is>
       </c>
       <c r="M310" t="inlineStr">
         <is>
+          <t>2026-06-17 00:00:00</t>
+        </is>
+      </c>
+      <c r="N310" t="inlineStr">
+        <is>
           <t>2026-06-18 00:00:00</t>
         </is>
       </c>
-      <c r="N310" t="inlineStr">
-        <is>
-          <t>2026-06-18 00:00:00</t>
-        </is>
-      </c>
       <c r="O310" t="inlineStr">
         <is>
-          <t>HUBEI JIANGHAN NEW MATERIALS CO LTD</t>
+          <t>EDGE INNOVATE (NI) LTD</t>
         </is>
       </c>
       <c r="P310" t="inlineStr">
         <is>
-          <t>HUBEI JIANGHAN NEW MATERIALS CO LTD</t>
+          <t>EDGE INNOVATE (NI) LTD</t>
         </is>
       </c>
       <c r="Q310" t="inlineStr">
         <is>
-          <t>2026-04-30 00:00:00</t>
+          <t>2026-05-29 00:00:00</t>
         </is>
       </c>
     </row>
     <row r="311">
       <c r="A311" t="inlineStr">
         <is>
-          <t>2566078</t>
+          <t>2565937</t>
         </is>
       </c>
       <c r="B311" t="inlineStr">
         <is>
-          <t>EF4-0232219-4</t>
+          <t>EF4-0232258-2</t>
         </is>
       </c>
       <c r="C311" t="inlineStr">
         <is>
-          <t>Vessel, Non-container</t>
+          <t>Vessel, Container</t>
         </is>
       </c>
       <c r="D311" t="inlineStr"/>
       <c r="E311" t="inlineStr">
         <is>
-          <t>9903.03.01</t>
+          <t>9903.03.06</t>
         </is>
       </c>
       <c r="F311" t="inlineStr">
         <is>
-          <t>SECTION 122 - 10% DUTY</t>
+          <t>S122 EXCL,IRN/STL/ALUM,DERIV</t>
         </is>
       </c>
       <c r="G311" t="inlineStr">
@@ -26368,32 +26368,32 @@
       </c>
       <c r="H311" t="inlineStr">
         <is>
-          <t>9903.03.01</t>
+          <t>9903.03.06</t>
         </is>
       </c>
       <c r="I311" t="inlineStr">
         <is>
-          <t>8474.10.0010</t>
+          <t>9903.82.22,8431.20.0000</t>
         </is>
       </c>
       <c r="J311" t="inlineStr">
         <is>
-          <t>EDGE INNOVATE (NI) LTD</t>
+          <t>MALLAGHAN (GA) INC.</t>
         </is>
       </c>
       <c r="K311" t="inlineStr">
         <is>
-          <t>EDGINN01</t>
+          <t>MALGA01</t>
         </is>
       </c>
       <c r="L311" t="inlineStr">
         <is>
-          <t>135501-01432</t>
+          <t>36-488102800</t>
         </is>
       </c>
       <c r="M311" t="inlineStr">
         <is>
-          <t>2026-06-17 00:00:00</t>
+          <t>2026-06-20 00:00:00</t>
         </is>
       </c>
       <c r="N311" t="inlineStr">
@@ -26403,17 +26403,17 @@
       </c>
       <c r="O311" t="inlineStr">
         <is>
-          <t>EDGE INNOVATE (NI) LTD</t>
+          <t>MALLAGHAN ENGINEERING  LTD</t>
         </is>
       </c>
       <c r="P311" t="inlineStr">
         <is>
-          <t>EDGE INNOVATE (NI) LTD</t>
+          <t>MALLAGHAN ENGINEERING  LTD</t>
         </is>
       </c>
       <c r="Q311" t="inlineStr">
         <is>
-          <t>2026-05-29 00:00:00</t>
+          <t>2026-05-17 00:00:00</t>
         </is>
       </c>
     </row>
@@ -26446,7 +26446,7 @@
       </c>
       <c r="G312" t="inlineStr">
         <is>
-          <t>001</t>
+          <t>002</t>
         </is>
       </c>
       <c r="H312" t="inlineStr">
@@ -26529,7 +26529,7 @@
       </c>
       <c r="G313" t="inlineStr">
         <is>
-          <t>002</t>
+          <t>003</t>
         </is>
       </c>
       <c r="H313" t="inlineStr">
@@ -26586,12 +26586,12 @@
     <row r="314">
       <c r="A314" t="inlineStr">
         <is>
-          <t>2565937</t>
+          <t>2566105</t>
         </is>
       </c>
       <c r="B314" t="inlineStr">
         <is>
-          <t>EF4-0232258-2</t>
+          <t>EF4-0232283-0</t>
         </is>
       </c>
       <c r="C314" t="inlineStr">
@@ -26602,47 +26602,47 @@
       <c r="D314" t="inlineStr"/>
       <c r="E314" t="inlineStr">
         <is>
-          <t>9903.03.06</t>
+          <t>9903.03.01</t>
         </is>
       </c>
       <c r="F314" t="inlineStr">
         <is>
-          <t>S122 EXCL,IRN/STL/ALUM,DERIV</t>
+          <t>SECTION 122 - 10% DUTY</t>
         </is>
       </c>
       <c r="G314" t="inlineStr">
         <is>
-          <t>003</t>
+          <t>001</t>
         </is>
       </c>
       <c r="H314" t="inlineStr">
         <is>
-          <t>9903.03.06</t>
+          <t>9903.03.01</t>
         </is>
       </c>
       <c r="I314" t="inlineStr">
         <is>
-          <t>9903.82.22,8431.20.0000</t>
+          <t>3920.61.0000</t>
         </is>
       </c>
       <c r="J314" t="inlineStr">
         <is>
-          <t>MALLAGHAN (GA) INC.</t>
+          <t>TUBUS BAUER GMBH</t>
         </is>
       </c>
       <c r="K314" t="inlineStr">
         <is>
-          <t>MALGA01</t>
+          <t>TUBBAU01</t>
         </is>
       </c>
       <c r="L314" t="inlineStr">
         <is>
-          <t>36-488102800</t>
+          <t>091601-00584</t>
         </is>
       </c>
       <c r="M314" t="inlineStr">
         <is>
-          <t>2026-06-20 00:00:00</t>
+          <t>2026-06-18 00:00:00</t>
         </is>
       </c>
       <c r="N314" t="inlineStr">
@@ -26652,29 +26652,29 @@
       </c>
       <c r="O314" t="inlineStr">
         <is>
-          <t>MALLAGHAN ENGINEERING  LTD</t>
+          <t>TUBUS BAUER GMBH</t>
         </is>
       </c>
       <c r="P314" t="inlineStr">
         <is>
-          <t>MALLAGHAN ENGINEERING  LTD</t>
+          <t>TUBUS BAUER GMBH</t>
         </is>
       </c>
       <c r="Q314" t="inlineStr">
         <is>
-          <t>2026-05-17 00:00:00</t>
+          <t>2026-06-02 00:00:00</t>
         </is>
       </c>
     </row>
     <row r="315">
       <c r="A315" t="inlineStr">
         <is>
-          <t>2566105</t>
+          <t>2566265</t>
         </is>
       </c>
       <c r="B315" t="inlineStr">
         <is>
-          <t>EF4-0232283-0</t>
+          <t>EF4-0232362-2</t>
         </is>
       </c>
       <c r="C315" t="inlineStr">
@@ -26705,59 +26705,59 @@
       </c>
       <c r="I315" t="inlineStr">
         <is>
-          <t>3920.61.0000</t>
+          <t>9903.82.01,8424.90.9080</t>
         </is>
       </c>
       <c r="J315" t="inlineStr">
         <is>
-          <t>TUBUS BAUER GMBH</t>
+          <t>EISENMANN OF SOUTH CAROLINA INC</t>
         </is>
       </c>
       <c r="K315" t="inlineStr">
         <is>
-          <t>TUBBAU01</t>
+          <t>EISINC03</t>
         </is>
       </c>
       <c r="L315" t="inlineStr">
         <is>
-          <t>091601-00584</t>
+          <t>86-240963300</t>
         </is>
       </c>
       <c r="M315" t="inlineStr">
         <is>
+          <t>2026-06-21 00:00:00</t>
+        </is>
+      </c>
+      <c r="N315" t="inlineStr">
+        <is>
           <t>2026-06-18 00:00:00</t>
         </is>
       </c>
-      <c r="N315" t="inlineStr">
-        <is>
-          <t>2026-06-18 00:00:00</t>
-        </is>
-      </c>
       <c r="O315" t="inlineStr">
         <is>
-          <t>TUBUS BAUER GMBH</t>
+          <t>EISENMANN GMBH</t>
         </is>
       </c>
       <c r="P315" t="inlineStr">
         <is>
-          <t>TUBUS BAUER GMBH</t>
+          <t>EISENMANN GMBH</t>
         </is>
       </c>
       <c r="Q315" t="inlineStr">
         <is>
-          <t>2026-06-02 00:00:00</t>
+          <t>2026-06-06 00:00:00</t>
         </is>
       </c>
     </row>
     <row r="316">
       <c r="A316" t="inlineStr">
         <is>
-          <t>2566265</t>
+          <t>2566155</t>
         </is>
       </c>
       <c r="B316" t="inlineStr">
         <is>
-          <t>EF4-0232362-2</t>
+          <t>EF4-0232431-5</t>
         </is>
       </c>
       <c r="C316" t="inlineStr">
@@ -26768,12 +26768,12 @@
       <c r="D316" t="inlineStr"/>
       <c r="E316" t="inlineStr">
         <is>
-          <t>9903.03.01</t>
+          <t>9903.03.06</t>
         </is>
       </c>
       <c r="F316" t="inlineStr">
         <is>
-          <t>SECTION 122 - 10% DUTY</t>
+          <t>S122 EXCL,IRN/STL/ALUM,DERIV</t>
         </is>
       </c>
       <c r="G316" t="inlineStr">
@@ -26783,32 +26783,32 @@
       </c>
       <c r="H316" t="inlineStr">
         <is>
-          <t>9903.03.01</t>
+          <t>9903.03.06</t>
         </is>
       </c>
       <c r="I316" t="inlineStr">
         <is>
-          <t>9903.82.01,8424.90.9080</t>
+          <t>9903.74.11,9903.94.53,8708.29.5160</t>
         </is>
       </c>
       <c r="J316" t="inlineStr">
         <is>
-          <t>EISENMANN OF SOUTH CAROLINA INC</t>
+          <t>BORGERS USA CORP</t>
         </is>
       </c>
       <c r="K316" t="inlineStr">
         <is>
-          <t>EISINC03</t>
+          <t>BORUSA</t>
         </is>
       </c>
       <c r="L316" t="inlineStr">
         <is>
-          <t>86-240963300</t>
+          <t>65-117296500</t>
         </is>
       </c>
       <c r="M316" t="inlineStr">
         <is>
-          <t>2026-06-21 00:00:00</t>
+          <t>2026-06-18 00:00:00</t>
         </is>
       </c>
       <c r="N316" t="inlineStr">
@@ -26818,12 +26818,12 @@
       </c>
       <c r="O316" t="inlineStr">
         <is>
-          <t>EISENMANN GMBH</t>
+          <t>AUTONEUM CZ S.R.O.</t>
         </is>
       </c>
       <c r="P316" t="inlineStr">
         <is>
-          <t>EISENMANN GMBH</t>
+          <t>AUTONEUM CZ S.R.O.</t>
         </is>
       </c>
       <c r="Q316" t="inlineStr">
@@ -26861,7 +26861,7 @@
       </c>
       <c r="G317" t="inlineStr">
         <is>
-          <t>001</t>
+          <t>002</t>
         </is>
       </c>
       <c r="H317" t="inlineStr">
@@ -26944,7 +26944,7 @@
       </c>
       <c r="G318" t="inlineStr">
         <is>
-          <t>002</t>
+          <t>003</t>
         </is>
       </c>
       <c r="H318" t="inlineStr">
@@ -27027,7 +27027,7 @@
       </c>
       <c r="G319" t="inlineStr">
         <is>
-          <t>003</t>
+          <t>004</t>
         </is>
       </c>
       <c r="H319" t="inlineStr">
@@ -27084,111 +27084,111 @@
     <row r="320">
       <c r="A320" t="inlineStr">
         <is>
-          <t>2566155</t>
+          <t>4539433</t>
         </is>
       </c>
       <c r="B320" t="inlineStr">
         <is>
-          <t>EF4-0232431-5</t>
+          <t>EF4-0232434-9</t>
         </is>
       </c>
       <c r="C320" t="inlineStr">
         <is>
-          <t>Vessel, Container</t>
+          <t>Air, Non-container</t>
         </is>
       </c>
       <c r="D320" t="inlineStr"/>
       <c r="E320" t="inlineStr">
         <is>
-          <t>9903.03.06</t>
+          <t>9903.88.03</t>
         </is>
       </c>
       <c r="F320" t="inlineStr">
         <is>
-          <t>S122 EXCL,IRN/STL/ALUM,DERIV</t>
+          <t>ARTICLE OF CHINA,US NTE 20(F)</t>
         </is>
       </c>
       <c r="G320" t="inlineStr">
         <is>
-          <t>004</t>
+          <t>001</t>
         </is>
       </c>
       <c r="H320" t="inlineStr">
         <is>
-          <t>9903.03.06</t>
+          <t>9903.88.03</t>
         </is>
       </c>
       <c r="I320" t="inlineStr">
         <is>
-          <t>9903.74.11,9903.94.53,8708.29.5160</t>
+          <t>9903.03.03,2926.90.4300</t>
         </is>
       </c>
       <c r="J320" t="inlineStr">
         <is>
-          <t>BORGERS USA CORP</t>
+          <t>MAYZO INC</t>
         </is>
       </c>
       <c r="K320" t="inlineStr">
         <is>
-          <t>BORUSA</t>
+          <t>MAYINC</t>
         </is>
       </c>
       <c r="L320" t="inlineStr">
         <is>
-          <t>65-117296500</t>
+          <t>62-129031200</t>
         </is>
       </c>
       <c r="M320" t="inlineStr">
         <is>
+          <t>2026-06-17 00:00:00</t>
+        </is>
+      </c>
+      <c r="N320" t="inlineStr">
+        <is>
           <t>2026-06-18 00:00:00</t>
         </is>
       </c>
-      <c r="N320" t="inlineStr">
-        <is>
-          <t>2026-06-18 00:00:00</t>
-        </is>
-      </c>
       <c r="O320" t="inlineStr">
         <is>
-          <t>AUTONEUM CZ S.R.O.</t>
+          <t>HANGZHOU DISHENG IMPORT &amp; EXPORT</t>
         </is>
       </c>
       <c r="P320" t="inlineStr">
         <is>
-          <t>AUTONEUM CZ S.R.O.</t>
+          <t>HANGZHOU DISHENG IMPORT &amp; EXPORT</t>
         </is>
       </c>
       <c r="Q320" t="inlineStr">
         <is>
-          <t>2026-06-06 00:00:00</t>
+          <t>2026-06-17 00:00:00</t>
         </is>
       </c>
     </row>
     <row r="321">
       <c r="A321" t="inlineStr">
         <is>
-          <t>4539433</t>
+          <t>2565798</t>
         </is>
       </c>
       <c r="B321" t="inlineStr">
         <is>
-          <t>EF4-0232434-9</t>
+          <t>EF4-0232494-3</t>
         </is>
       </c>
       <c r="C321" t="inlineStr">
         <is>
-          <t>Air, Non-container</t>
+          <t>Vessel, Container</t>
         </is>
       </c>
       <c r="D321" t="inlineStr"/>
       <c r="E321" t="inlineStr">
         <is>
-          <t>9903.88.03</t>
+          <t>9903.03.06</t>
         </is>
       </c>
       <c r="F321" t="inlineStr">
         <is>
-          <t>ARTICLE OF CHINA,US NTE 20(F)</t>
+          <t>S122 EXCL,IRN/STL/ALUM,DERIV</t>
         </is>
       </c>
       <c r="G321" t="inlineStr">
@@ -27198,32 +27198,32 @@
       </c>
       <c r="H321" t="inlineStr">
         <is>
-          <t>9903.88.03</t>
+          <t>9903.03.06</t>
         </is>
       </c>
       <c r="I321" t="inlineStr">
         <is>
-          <t>9903.03.03,2926.90.4300</t>
+          <t>9903.82.02,7222.20.0064</t>
         </is>
       </c>
       <c r="J321" t="inlineStr">
         <is>
-          <t>MAYZO INC</t>
+          <t>MESHA STEELS  LLC</t>
         </is>
       </c>
       <c r="K321" t="inlineStr">
         <is>
-          <t>MAYINC</t>
+          <t>MESSTE</t>
         </is>
       </c>
       <c r="L321" t="inlineStr">
         <is>
-          <t>62-129031200</t>
+          <t>20-274801900</t>
         </is>
       </c>
       <c r="M321" t="inlineStr">
         <is>
-          <t>2026-06-17 00:00:00</t>
+          <t>2026-06-18 00:00:00</t>
         </is>
       </c>
       <c r="N321" t="inlineStr">
@@ -27233,29 +27233,29 @@
       </c>
       <c r="O321" t="inlineStr">
         <is>
-          <t>HANGZHOU DISHENG IMPORT &amp; EXPORT</t>
+          <t>BHANSALI BRIGHT BARS PVT. LTD.</t>
         </is>
       </c>
       <c r="P321" t="inlineStr">
         <is>
-          <t>HANGZHOU DISHENG IMPORT &amp; EXPORT</t>
+          <t>BHANSALI BRIGHT BARS PVT. LTD.</t>
         </is>
       </c>
       <c r="Q321" t="inlineStr">
         <is>
-          <t>2026-06-17 00:00:00</t>
+          <t>2026-05-12 00:00:00</t>
         </is>
       </c>
     </row>
     <row r="322">
       <c r="A322" t="inlineStr">
         <is>
-          <t>2565798</t>
+          <t>2565799</t>
         </is>
       </c>
       <c r="B322" t="inlineStr">
         <is>
-          <t>EF4-0232494-3</t>
+          <t>EF4-0232495-0</t>
         </is>
       </c>
       <c r="C322" t="inlineStr">
@@ -27286,7 +27286,7 @@
       </c>
       <c r="I322" t="inlineStr">
         <is>
-          <t>9903.82.02,7222.20.0064</t>
+          <t>9903.82.02,7222.20.0062</t>
         </is>
       </c>
       <c r="J322" t="inlineStr">
@@ -27333,12 +27333,12 @@
     <row r="323">
       <c r="A323" t="inlineStr">
         <is>
-          <t>2565799</t>
+          <t>2565760</t>
         </is>
       </c>
       <c r="B323" t="inlineStr">
         <is>
-          <t>EF4-0232495-0</t>
+          <t>EF4-0231661-8</t>
         </is>
       </c>
       <c r="C323" t="inlineStr">
@@ -27349,67 +27349,1498 @@
       <c r="D323" t="inlineStr"/>
       <c r="E323" t="inlineStr">
         <is>
+          <t>9903.88.15</t>
+        </is>
+      </c>
+      <c r="F323" t="inlineStr">
+        <is>
+          <t>ARTICLE OF CHINA,US NTE 20(R)</t>
+        </is>
+      </c>
+      <c r="G323" t="inlineStr">
+        <is>
+          <t>001</t>
+        </is>
+      </c>
+      <c r="H323" t="inlineStr">
+        <is>
+          <t>9903.88.15</t>
+        </is>
+      </c>
+      <c r="I323" t="inlineStr">
+        <is>
+          <t>9903.03.06,9903.82.09,8302.42.3015</t>
+        </is>
+      </c>
+      <c r="J323" t="inlineStr">
+        <is>
+          <t>GRASS AMERICA INC</t>
+        </is>
+      </c>
+      <c r="K323" t="inlineStr">
+        <is>
+          <t>GRAAME</t>
+        </is>
+      </c>
+      <c r="L323" t="inlineStr">
+        <is>
+          <t>51-066023000</t>
+        </is>
+      </c>
+      <c r="M323" t="inlineStr">
+        <is>
+          <t>2026-06-20 00:00:00</t>
+        </is>
+      </c>
+      <c r="N323" t="inlineStr">
+        <is>
+          <t>2026-06-20 00:00:00</t>
+        </is>
+      </c>
+      <c r="O323" t="inlineStr">
+        <is>
+          <t>SACA PRECISION LTD</t>
+        </is>
+      </c>
+      <c r="P323" t="inlineStr">
+        <is>
+          <t>SACA PRECISION LTD</t>
+        </is>
+      </c>
+      <c r="Q323" t="inlineStr">
+        <is>
+          <t>2026-05-05 00:00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="324">
+      <c r="A324" t="inlineStr">
+        <is>
+          <t>2565760</t>
+        </is>
+      </c>
+      <c r="B324" t="inlineStr">
+        <is>
+          <t>EF4-0231661-8</t>
+        </is>
+      </c>
+      <c r="C324" t="inlineStr">
+        <is>
+          <t>Vessel, Container</t>
+        </is>
+      </c>
+      <c r="D324" t="inlineStr"/>
+      <c r="E324" t="inlineStr">
+        <is>
+          <t>9903.88.15</t>
+        </is>
+      </c>
+      <c r="F324" t="inlineStr">
+        <is>
+          <t>ARTICLE OF CHINA,US NTE 20(R)</t>
+        </is>
+      </c>
+      <c r="G324" t="inlineStr">
+        <is>
+          <t>002</t>
+        </is>
+      </c>
+      <c r="H324" t="inlineStr">
+        <is>
+          <t>9903.88.15</t>
+        </is>
+      </c>
+      <c r="I324" t="inlineStr">
+        <is>
+          <t>9903.03.01,3926.30.5000</t>
+        </is>
+      </c>
+      <c r="J324" t="inlineStr">
+        <is>
+          <t>GRASS AMERICA INC</t>
+        </is>
+      </c>
+      <c r="K324" t="inlineStr">
+        <is>
+          <t>GRAAME</t>
+        </is>
+      </c>
+      <c r="L324" t="inlineStr">
+        <is>
+          <t>51-066023000</t>
+        </is>
+      </c>
+      <c r="M324" t="inlineStr">
+        <is>
+          <t>2026-06-20 00:00:00</t>
+        </is>
+      </c>
+      <c r="N324" t="inlineStr">
+        <is>
+          <t>2026-06-20 00:00:00</t>
+        </is>
+      </c>
+      <c r="O324" t="inlineStr">
+        <is>
+          <t>SACA PRECISION LTD</t>
+        </is>
+      </c>
+      <c r="P324" t="inlineStr">
+        <is>
+          <t>SACA PRECISION LTD</t>
+        </is>
+      </c>
+      <c r="Q324" t="inlineStr">
+        <is>
+          <t>2026-05-05 00:00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="325">
+      <c r="A325" t="inlineStr">
+        <is>
+          <t>2615656</t>
+        </is>
+      </c>
+      <c r="B325" t="inlineStr">
+        <is>
+          <t>EF4-0231976-0</t>
+        </is>
+      </c>
+      <c r="C325" t="inlineStr">
+        <is>
+          <t>Vessel, Non-container</t>
+        </is>
+      </c>
+      <c r="D325" t="inlineStr"/>
+      <c r="E325" t="inlineStr">
+        <is>
+          <t>9903.88.15</t>
+        </is>
+      </c>
+      <c r="F325" t="inlineStr">
+        <is>
+          <t>ARTICLE OF CHINA,US NTE 20(R)</t>
+        </is>
+      </c>
+      <c r="G325" t="inlineStr">
+        <is>
+          <t>001</t>
+        </is>
+      </c>
+      <c r="H325" t="inlineStr">
+        <is>
+          <t>9903.88.15</t>
+        </is>
+      </c>
+      <c r="I325" t="inlineStr">
+        <is>
+          <t>9903.03.01,3926.90.9989</t>
+        </is>
+      </c>
+      <c r="J325" t="inlineStr">
+        <is>
+          <t>VISUAL CREATIONS, INC.</t>
+        </is>
+      </c>
+      <c r="K325" t="inlineStr">
+        <is>
+          <t>VISCRE</t>
+        </is>
+      </c>
+      <c r="L325" t="inlineStr">
+        <is>
+          <t>20-461602300</t>
+        </is>
+      </c>
+      <c r="M325" t="inlineStr">
+        <is>
+          <t>2026-06-20 00:00:00</t>
+        </is>
+      </c>
+      <c r="N325" t="inlineStr">
+        <is>
+          <t>2026-06-20 00:00:00</t>
+        </is>
+      </c>
+      <c r="O325" t="inlineStr">
+        <is>
+          <t>NINGBO SMART HIGH TECH INDUSTRIES L</t>
+        </is>
+      </c>
+      <c r="P325" t="inlineStr">
+        <is>
+          <t>NINGBO SMART HIGH TECH INDUSTRIES LTD</t>
+        </is>
+      </c>
+      <c r="Q325" t="inlineStr">
+        <is>
+          <t>2026-05-12 00:00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="326">
+      <c r="A326" t="inlineStr">
+        <is>
+          <t>2615664</t>
+        </is>
+      </c>
+      <c r="B326" t="inlineStr">
+        <is>
+          <t>EF4-0231983-6</t>
+        </is>
+      </c>
+      <c r="C326" t="inlineStr">
+        <is>
+          <t>Vessel, Non-container</t>
+        </is>
+      </c>
+      <c r="D326" t="inlineStr"/>
+      <c r="E326" t="inlineStr">
+        <is>
+          <t>9903.88.01</t>
+        </is>
+      </c>
+      <c r="F326" t="inlineStr">
+        <is>
+          <t>ARTICLE OF CHINA,US NTE 20(A)</t>
+        </is>
+      </c>
+      <c r="G326" t="inlineStr">
+        <is>
+          <t>001</t>
+        </is>
+      </c>
+      <c r="H326" t="inlineStr">
+        <is>
+          <t>9903.88.01</t>
+        </is>
+      </c>
+      <c r="I326" t="inlineStr">
+        <is>
+          <t>9903.03.06,9903.82.09,8482.10.5012</t>
+        </is>
+      </c>
+      <c r="J326" t="inlineStr">
+        <is>
+          <t>VISUAL CREATIONS, INC.</t>
+        </is>
+      </c>
+      <c r="K326" t="inlineStr">
+        <is>
+          <t>VISCRE</t>
+        </is>
+      </c>
+      <c r="L326" t="inlineStr">
+        <is>
+          <t>20-461602300</t>
+        </is>
+      </c>
+      <c r="M326" t="inlineStr">
+        <is>
+          <t>2026-06-11 00:00:00</t>
+        </is>
+      </c>
+      <c r="N326" t="inlineStr">
+        <is>
+          <t>2026-06-20 00:00:00</t>
+        </is>
+      </c>
+      <c r="O326" t="inlineStr">
+        <is>
+          <t>LINYU HANDWARE MANUFACTURE CO LTD</t>
+        </is>
+      </c>
+      <c r="P326" t="inlineStr">
+        <is>
+          <t>LINYU HANDWARE MANUFACTURE CO LTD</t>
+        </is>
+      </c>
+      <c r="Q326" t="inlineStr">
+        <is>
+          <t>2026-05-15 00:00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="327">
+      <c r="A327" t="inlineStr">
+        <is>
+          <t>2565923</t>
+        </is>
+      </c>
+      <c r="B327" t="inlineStr">
+        <is>
+          <t>EF4-0232195-6</t>
+        </is>
+      </c>
+      <c r="C327" t="inlineStr">
+        <is>
+          <t>Vessel, Container</t>
+        </is>
+      </c>
+      <c r="D327" t="inlineStr"/>
+      <c r="E327" t="inlineStr">
+        <is>
+          <t>9903.91.01</t>
+        </is>
+      </c>
+      <c r="F327" t="inlineStr">
+        <is>
+          <t>ARTS, PRDS OF CN SUB(B)US NT31</t>
+        </is>
+      </c>
+      <c r="G327" t="inlineStr">
+        <is>
+          <t>001</t>
+        </is>
+      </c>
+      <c r="H327" t="inlineStr">
+        <is>
+          <t>9903.91.01</t>
+        </is>
+      </c>
+      <c r="I327" t="inlineStr">
+        <is>
+          <t>9903.03.06,9903.82.02,7228.30.6000</t>
+        </is>
+      </c>
+      <c r="J327" t="inlineStr">
+        <is>
+          <t>MAHA USA LLC</t>
+        </is>
+      </c>
+      <c r="K327" t="inlineStr">
+        <is>
+          <t>MAHUSA</t>
+        </is>
+      </c>
+      <c r="L327" t="inlineStr">
+        <is>
+          <t>52-213556300</t>
+        </is>
+      </c>
+      <c r="M327" t="inlineStr">
+        <is>
+          <t>2026-06-20 00:00:00</t>
+        </is>
+      </c>
+      <c r="N327" t="inlineStr">
+        <is>
+          <t>2026-06-20 00:00:00</t>
+        </is>
+      </c>
+      <c r="O327" t="inlineStr">
+        <is>
+          <t>THYSSENKRUPP SCHULTE GMBH</t>
+        </is>
+      </c>
+      <c r="P327" t="inlineStr">
+        <is>
+          <t>THYSSENKRUPP SCHULTE GMBH</t>
+        </is>
+      </c>
+      <c r="Q327" t="inlineStr">
+        <is>
+          <t>2026-05-27 00:00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="328">
+      <c r="A328" t="inlineStr">
+        <is>
+          <t>2565923</t>
+        </is>
+      </c>
+      <c r="B328" t="inlineStr">
+        <is>
+          <t>EF4-0232195-6</t>
+        </is>
+      </c>
+      <c r="C328" t="inlineStr">
+        <is>
+          <t>Vessel, Container</t>
+        </is>
+      </c>
+      <c r="D328" t="inlineStr"/>
+      <c r="E328" t="inlineStr">
+        <is>
           <t>9903.03.06</t>
         </is>
       </c>
-      <c r="F323" t="inlineStr">
+      <c r="F328" t="inlineStr">
         <is>
           <t>S122 EXCL,IRN/STL/ALUM,DERIV</t>
         </is>
       </c>
-      <c r="G323" t="inlineStr">
+      <c r="G328" t="inlineStr">
+        <is>
+          <t>002</t>
+        </is>
+      </c>
+      <c r="H328" t="inlineStr">
+        <is>
+          <t>9903.03.06</t>
+        </is>
+      </c>
+      <c r="I328" t="inlineStr">
+        <is>
+          <t>9903.82.02,7215.50.0016</t>
+        </is>
+      </c>
+      <c r="J328" t="inlineStr">
+        <is>
+          <t>MAHA USA LLC</t>
+        </is>
+      </c>
+      <c r="K328" t="inlineStr">
+        <is>
+          <t>MAHUSA</t>
+        </is>
+      </c>
+      <c r="L328" t="inlineStr">
+        <is>
+          <t>52-213556300</t>
+        </is>
+      </c>
+      <c r="M328" t="inlineStr">
+        <is>
+          <t>2026-06-20 00:00:00</t>
+        </is>
+      </c>
+      <c r="N328" t="inlineStr">
+        <is>
+          <t>2026-06-20 00:00:00</t>
+        </is>
+      </c>
+      <c r="O328" t="inlineStr">
+        <is>
+          <t>THYSSENKRUPP SCHULTE GMBH</t>
+        </is>
+      </c>
+      <c r="P328" t="inlineStr">
+        <is>
+          <t>THYSSENKRUPP SCHULTE GMBH</t>
+        </is>
+      </c>
+      <c r="Q328" t="inlineStr">
+        <is>
+          <t>2026-05-27 00:00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="329">
+      <c r="A329" t="inlineStr">
+        <is>
+          <t>2565923</t>
+        </is>
+      </c>
+      <c r="B329" t="inlineStr">
+        <is>
+          <t>EF4-0232195-6</t>
+        </is>
+      </c>
+      <c r="C329" t="inlineStr">
+        <is>
+          <t>Vessel, Container</t>
+        </is>
+      </c>
+      <c r="D329" t="inlineStr"/>
+      <c r="E329" t="inlineStr">
+        <is>
+          <t>9903.03.06</t>
+        </is>
+      </c>
+      <c r="F329" t="inlineStr">
+        <is>
+          <t>S122 EXCL,IRN/STL/ALUM,DERIV</t>
+        </is>
+      </c>
+      <c r="G329" t="inlineStr">
+        <is>
+          <t>003</t>
+        </is>
+      </c>
+      <c r="H329" t="inlineStr">
+        <is>
+          <t>9903.03.06</t>
+        </is>
+      </c>
+      <c r="I329" t="inlineStr">
+        <is>
+          <t>9903.82.02,7216.33.0090</t>
+        </is>
+      </c>
+      <c r="J329" t="inlineStr">
+        <is>
+          <t>MAHA USA LLC</t>
+        </is>
+      </c>
+      <c r="K329" t="inlineStr">
+        <is>
+          <t>MAHUSA</t>
+        </is>
+      </c>
+      <c r="L329" t="inlineStr">
+        <is>
+          <t>52-213556300</t>
+        </is>
+      </c>
+      <c r="M329" t="inlineStr">
+        <is>
+          <t>2026-06-20 00:00:00</t>
+        </is>
+      </c>
+      <c r="N329" t="inlineStr">
+        <is>
+          <t>2026-06-20 00:00:00</t>
+        </is>
+      </c>
+      <c r="O329" t="inlineStr">
+        <is>
+          <t>THYSSENKRUPP SCHULTE GMBH</t>
+        </is>
+      </c>
+      <c r="P329" t="inlineStr">
+        <is>
+          <t>THYSSENKRUPP SCHULTE GMBH</t>
+        </is>
+      </c>
+      <c r="Q329" t="inlineStr">
+        <is>
+          <t>2026-05-27 00:00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="330">
+      <c r="A330" t="inlineStr">
+        <is>
+          <t>2566178</t>
+        </is>
+      </c>
+      <c r="B330" t="inlineStr">
+        <is>
+          <t>EF4-0232247-5</t>
+        </is>
+      </c>
+      <c r="C330" t="inlineStr">
+        <is>
+          <t>Vessel, Container</t>
+        </is>
+      </c>
+      <c r="D330" t="inlineStr"/>
+      <c r="E330" t="inlineStr">
+        <is>
+          <t>9903.03.01</t>
+        </is>
+      </c>
+      <c r="F330" t="inlineStr">
+        <is>
+          <t>SECTION 122 - 10% DUTY</t>
+        </is>
+      </c>
+      <c r="G330" t="inlineStr">
         <is>
           <t>001</t>
         </is>
       </c>
-      <c r="H323" t="inlineStr">
-        <is>
-          <t>9903.03.06</t>
-        </is>
-      </c>
-      <c r="I323" t="inlineStr">
-        <is>
-          <t>9903.82.02,7222.20.0062</t>
-        </is>
-      </c>
-      <c r="J323" t="inlineStr">
-        <is>
-          <t>MESHA STEELS  LLC</t>
-        </is>
-      </c>
-      <c r="K323" t="inlineStr">
-        <is>
-          <t>MESSTE</t>
-        </is>
-      </c>
-      <c r="L323" t="inlineStr">
-        <is>
-          <t>20-274801900</t>
-        </is>
-      </c>
-      <c r="M323" t="inlineStr">
-        <is>
-          <t>2026-06-18 00:00:00</t>
-        </is>
-      </c>
-      <c r="N323" t="inlineStr">
-        <is>
-          <t>2026-06-18 00:00:00</t>
-        </is>
-      </c>
-      <c r="O323" t="inlineStr">
-        <is>
-          <t>BHANSALI BRIGHT BARS PVT. LTD.</t>
-        </is>
-      </c>
-      <c r="P323" t="inlineStr">
-        <is>
-          <t>BHANSALI BRIGHT BARS PVT. LTD.</t>
-        </is>
-      </c>
-      <c r="Q323" t="inlineStr">
-        <is>
-          <t>2026-05-12 00:00:00</t>
+      <c r="H330" t="inlineStr">
+        <is>
+          <t>9903.03.01</t>
+        </is>
+      </c>
+      <c r="I330" t="inlineStr">
+        <is>
+          <t>1108.13.0010</t>
+        </is>
+      </c>
+      <c r="J330" t="inlineStr">
+        <is>
+          <t>ROYAL INGREDIENTS GROUP BV</t>
+        </is>
+      </c>
+      <c r="K330" t="inlineStr">
+        <is>
+          <t>ROYINGRE</t>
+        </is>
+      </c>
+      <c r="L330" t="inlineStr">
+        <is>
+          <t>074601-00962</t>
+        </is>
+      </c>
+      <c r="M330" t="inlineStr">
+        <is>
+          <t>2026-06-20 00:00:00</t>
+        </is>
+      </c>
+      <c r="N330" t="inlineStr">
+        <is>
+          <t>2026-06-20 00:00:00</t>
+        </is>
+      </c>
+      <c r="O330" t="inlineStr">
+        <is>
+          <t>AKV LANGHOLT AMBA</t>
+        </is>
+      </c>
+      <c r="P330" t="inlineStr">
+        <is>
+          <t>AKV LANGHOLT AMBA</t>
+        </is>
+      </c>
+      <c r="Q330" t="inlineStr">
+        <is>
+          <t>2026-06-01 00:00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="331">
+      <c r="A331" t="inlineStr">
+        <is>
+          <t>2566229</t>
+        </is>
+      </c>
+      <c r="B331" t="inlineStr">
+        <is>
+          <t>EF4-0232249-1</t>
+        </is>
+      </c>
+      <c r="C331" t="inlineStr">
+        <is>
+          <t>Vessel, Container</t>
+        </is>
+      </c>
+      <c r="D331" t="inlineStr">
+        <is>
+          <t>V0710338448</t>
+        </is>
+      </c>
+      <c r="E331" t="inlineStr">
+        <is>
+          <t>9903.03.01</t>
+        </is>
+      </c>
+      <c r="F331" t="inlineStr">
+        <is>
+          <t>SECTION 122 - 10% DUTY</t>
+        </is>
+      </c>
+      <c r="G331" t="inlineStr">
+        <is>
+          <t>001</t>
+        </is>
+      </c>
+      <c r="H331" t="inlineStr">
+        <is>
+          <t>9903.03.01</t>
+        </is>
+      </c>
+      <c r="I331" t="inlineStr">
+        <is>
+          <t>1108.13.0010</t>
+        </is>
+      </c>
+      <c r="J331" t="inlineStr">
+        <is>
+          <t>ROYAL INGREDIENTS GROUP BV</t>
+        </is>
+      </c>
+      <c r="K331" t="inlineStr">
+        <is>
+          <t>ROYINGRE</t>
+        </is>
+      </c>
+      <c r="L331" t="inlineStr">
+        <is>
+          <t>074601-00962</t>
+        </is>
+      </c>
+      <c r="M331" t="inlineStr">
+        <is>
+          <t>2026-06-20 00:00:00</t>
+        </is>
+      </c>
+      <c r="N331" t="inlineStr">
+        <is>
+          <t>2026-06-20 00:00:00</t>
+        </is>
+      </c>
+      <c r="O331" t="inlineStr">
+        <is>
+          <t>AKV LANGHOLT AMBA</t>
+        </is>
+      </c>
+      <c r="P331" t="inlineStr">
+        <is>
+          <t>AKV LANGHOLT AMBA</t>
+        </is>
+      </c>
+      <c r="Q331" t="inlineStr">
+        <is>
+          <t>2026-06-01 00:00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="332">
+      <c r="A332" t="inlineStr">
+        <is>
+          <t>2566177</t>
+        </is>
+      </c>
+      <c r="B332" t="inlineStr">
+        <is>
+          <t>EF4-0232275-6</t>
+        </is>
+      </c>
+      <c r="C332" t="inlineStr">
+        <is>
+          <t>Vessel, Container</t>
+        </is>
+      </c>
+      <c r="D332" t="inlineStr">
+        <is>
+          <t>V0710338448</t>
+        </is>
+      </c>
+      <c r="E332" t="inlineStr">
+        <is>
+          <t>9903.03.01</t>
+        </is>
+      </c>
+      <c r="F332" t="inlineStr">
+        <is>
+          <t>SECTION 122 - 10% DUTY</t>
+        </is>
+      </c>
+      <c r="G332" t="inlineStr">
+        <is>
+          <t>001</t>
+        </is>
+      </c>
+      <c r="H332" t="inlineStr">
+        <is>
+          <t>9903.03.01</t>
+        </is>
+      </c>
+      <c r="I332" t="inlineStr">
+        <is>
+          <t>1108.13.0010</t>
+        </is>
+      </c>
+      <c r="J332" t="inlineStr">
+        <is>
+          <t>ROYAL INGREDIENTS GROUP BV</t>
+        </is>
+      </c>
+      <c r="K332" t="inlineStr">
+        <is>
+          <t>ROYINGRE</t>
+        </is>
+      </c>
+      <c r="L332" t="inlineStr">
+        <is>
+          <t>074601-00962</t>
+        </is>
+      </c>
+      <c r="M332" t="inlineStr">
+        <is>
+          <t>2026-06-20 00:00:00</t>
+        </is>
+      </c>
+      <c r="N332" t="inlineStr">
+        <is>
+          <t>2026-06-20 00:00:00</t>
+        </is>
+      </c>
+      <c r="O332" t="inlineStr">
+        <is>
+          <t>AKV LANGHOLT AMBA</t>
+        </is>
+      </c>
+      <c r="P332" t="inlineStr">
+        <is>
+          <t>AKV LANGHOLT AMBA</t>
+        </is>
+      </c>
+      <c r="Q332" t="inlineStr">
+        <is>
+          <t>2026-06-01 00:00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="333">
+      <c r="A333" t="inlineStr">
+        <is>
+          <t>2566051</t>
+        </is>
+      </c>
+      <c r="B333" t="inlineStr">
+        <is>
+          <t>EF4-0232281-4</t>
+        </is>
+      </c>
+      <c r="C333" t="inlineStr">
+        <is>
+          <t>Vessel, Container</t>
+        </is>
+      </c>
+      <c r="D333" t="inlineStr">
+        <is>
+          <t>V0710349973</t>
+        </is>
+      </c>
+      <c r="E333" t="inlineStr">
+        <is>
+          <t>9903.03.01</t>
+        </is>
+      </c>
+      <c r="F333" t="inlineStr">
+        <is>
+          <t>SECTION 122 - 10% DUTY</t>
+        </is>
+      </c>
+      <c r="G333" t="inlineStr">
+        <is>
+          <t>001</t>
+        </is>
+      </c>
+      <c r="H333" t="inlineStr">
+        <is>
+          <t>9903.03.01</t>
+        </is>
+      </c>
+      <c r="I333" t="inlineStr">
+        <is>
+          <t>4811.59.4040</t>
+        </is>
+      </c>
+      <c r="J333" t="inlineStr">
+        <is>
+          <t>BAUSCHLINNEMANN NORTH AMERICA</t>
+        </is>
+      </c>
+      <c r="K333" t="inlineStr">
+        <is>
+          <t>BAULIN</t>
+        </is>
+      </c>
+      <c r="L333" t="inlineStr">
+        <is>
+          <t>56-193913400</t>
+        </is>
+      </c>
+      <c r="M333" t="inlineStr">
+        <is>
+          <t>2026-06-21 00:00:00</t>
+        </is>
+      </c>
+      <c r="N333" t="inlineStr">
+        <is>
+          <t>2026-06-20 00:00:00</t>
+        </is>
+      </c>
+      <c r="O333" t="inlineStr">
+        <is>
+          <t>SURTECO GMBH</t>
+        </is>
+      </c>
+      <c r="P333" t="inlineStr">
+        <is>
+          <t>SURTECO GMBH</t>
+        </is>
+      </c>
+      <c r="Q333" t="inlineStr">
+        <is>
+          <t>2026-06-01 00:00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="334">
+      <c r="A334" t="inlineStr">
+        <is>
+          <t>2566051</t>
+        </is>
+      </c>
+      <c r="B334" t="inlineStr">
+        <is>
+          <t>EF4-0232281-4</t>
+        </is>
+      </c>
+      <c r="C334" t="inlineStr">
+        <is>
+          <t>Vessel, Container</t>
+        </is>
+      </c>
+      <c r="D334" t="inlineStr">
+        <is>
+          <t>V0710349973</t>
+        </is>
+      </c>
+      <c r="E334" t="inlineStr">
+        <is>
+          <t>9903.03.01</t>
+        </is>
+      </c>
+      <c r="F334" t="inlineStr">
+        <is>
+          <t>SECTION 122 - 10% DUTY</t>
+        </is>
+      </c>
+      <c r="G334" t="inlineStr">
+        <is>
+          <t>002</t>
+        </is>
+      </c>
+      <c r="H334" t="inlineStr">
+        <is>
+          <t>9903.03.01</t>
+        </is>
+      </c>
+      <c r="I334" t="inlineStr">
+        <is>
+          <t>4811.59.4040</t>
+        </is>
+      </c>
+      <c r="J334" t="inlineStr">
+        <is>
+          <t>BAUSCHLINNEMANN NORTH AMERICA</t>
+        </is>
+      </c>
+      <c r="K334" t="inlineStr">
+        <is>
+          <t>BAULIN</t>
+        </is>
+      </c>
+      <c r="L334" t="inlineStr">
+        <is>
+          <t>56-193913400</t>
+        </is>
+      </c>
+      <c r="M334" t="inlineStr">
+        <is>
+          <t>2026-06-21 00:00:00</t>
+        </is>
+      </c>
+      <c r="N334" t="inlineStr">
+        <is>
+          <t>2026-06-20 00:00:00</t>
+        </is>
+      </c>
+      <c r="O334" t="inlineStr">
+        <is>
+          <t>SURTECO GMBH</t>
+        </is>
+      </c>
+      <c r="P334" t="inlineStr">
+        <is>
+          <t>SURTECO GMBH</t>
+        </is>
+      </c>
+      <c r="Q334" t="inlineStr">
+        <is>
+          <t>2026-06-01 00:00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="335">
+      <c r="A335" t="inlineStr">
+        <is>
+          <t>2566051</t>
+        </is>
+      </c>
+      <c r="B335" t="inlineStr">
+        <is>
+          <t>EF4-0232281-4</t>
+        </is>
+      </c>
+      <c r="C335" t="inlineStr">
+        <is>
+          <t>Vessel, Container</t>
+        </is>
+      </c>
+      <c r="D335" t="inlineStr">
+        <is>
+          <t>V0710349973</t>
+        </is>
+      </c>
+      <c r="E335" t="inlineStr">
+        <is>
+          <t>9903.03.01</t>
+        </is>
+      </c>
+      <c r="F335" t="inlineStr">
+        <is>
+          <t>SECTION 122 - 10% DUTY</t>
+        </is>
+      </c>
+      <c r="G335" t="inlineStr">
+        <is>
+          <t>003</t>
+        </is>
+      </c>
+      <c r="H335" t="inlineStr">
+        <is>
+          <t>9903.03.01</t>
+        </is>
+      </c>
+      <c r="I335" t="inlineStr">
+        <is>
+          <t>4811.59.4040</t>
+        </is>
+      </c>
+      <c r="J335" t="inlineStr">
+        <is>
+          <t>BAUSCHLINNEMANN NORTH AMERICA</t>
+        </is>
+      </c>
+      <c r="K335" t="inlineStr">
+        <is>
+          <t>BAULIN</t>
+        </is>
+      </c>
+      <c r="L335" t="inlineStr">
+        <is>
+          <t>56-193913400</t>
+        </is>
+      </c>
+      <c r="M335" t="inlineStr">
+        <is>
+          <t>2026-06-21 00:00:00</t>
+        </is>
+      </c>
+      <c r="N335" t="inlineStr">
+        <is>
+          <t>2026-06-20 00:00:00</t>
+        </is>
+      </c>
+      <c r="O335" t="inlineStr">
+        <is>
+          <t>SURTECO GMBH</t>
+        </is>
+      </c>
+      <c r="P335" t="inlineStr">
+        <is>
+          <t>SURTECO GMBH</t>
+        </is>
+      </c>
+      <c r="Q335" t="inlineStr">
+        <is>
+          <t>2026-06-01 00:00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="336">
+      <c r="A336" t="inlineStr">
+        <is>
+          <t>2566100</t>
+        </is>
+      </c>
+      <c r="B336" t="inlineStr">
+        <is>
+          <t>EF4-0232282-2</t>
+        </is>
+      </c>
+      <c r="C336" t="inlineStr">
+        <is>
+          <t>Vessel, Container</t>
+        </is>
+      </c>
+      <c r="D336" t="inlineStr"/>
+      <c r="E336" t="inlineStr">
+        <is>
+          <t>9903.03.01</t>
+        </is>
+      </c>
+      <c r="F336" t="inlineStr">
+        <is>
+          <t>SECTION 122 - 10% DUTY</t>
+        </is>
+      </c>
+      <c r="G336" t="inlineStr">
+        <is>
+          <t>001</t>
+        </is>
+      </c>
+      <c r="H336" t="inlineStr">
+        <is>
+          <t>9903.03.01</t>
+        </is>
+      </c>
+      <c r="I336" t="inlineStr">
+        <is>
+          <t>4811.59.4040</t>
+        </is>
+      </c>
+      <c r="J336" t="inlineStr">
+        <is>
+          <t>BAUSCHLINNEMANN NORTH AMERICA</t>
+        </is>
+      </c>
+      <c r="K336" t="inlineStr">
+        <is>
+          <t>BAULIN</t>
+        </is>
+      </c>
+      <c r="L336" t="inlineStr">
+        <is>
+          <t>56-193913400</t>
+        </is>
+      </c>
+      <c r="M336" t="inlineStr">
+        <is>
+          <t>2026-06-21 00:00:00</t>
+        </is>
+      </c>
+      <c r="N336" t="inlineStr">
+        <is>
+          <t>2026-06-20 00:00:00</t>
+        </is>
+      </c>
+      <c r="O336" t="inlineStr">
+        <is>
+          <t>SURTECO GMBH</t>
+        </is>
+      </c>
+      <c r="P336" t="inlineStr">
+        <is>
+          <t>SURTECO GMBH</t>
+        </is>
+      </c>
+      <c r="Q336" t="inlineStr">
+        <is>
+          <t>2026-06-01 00:00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="337">
+      <c r="A337" t="inlineStr">
+        <is>
+          <t>2566100</t>
+        </is>
+      </c>
+      <c r="B337" t="inlineStr">
+        <is>
+          <t>EF4-0232282-2</t>
+        </is>
+      </c>
+      <c r="C337" t="inlineStr">
+        <is>
+          <t>Vessel, Container</t>
+        </is>
+      </c>
+      <c r="D337" t="inlineStr"/>
+      <c r="E337" t="inlineStr">
+        <is>
+          <t>9903.03.01</t>
+        </is>
+      </c>
+      <c r="F337" t="inlineStr">
+        <is>
+          <t>SECTION 122 - 10% DUTY</t>
+        </is>
+      </c>
+      <c r="G337" t="inlineStr">
+        <is>
+          <t>002</t>
+        </is>
+      </c>
+      <c r="H337" t="inlineStr">
+        <is>
+          <t>9903.03.01</t>
+        </is>
+      </c>
+      <c r="I337" t="inlineStr">
+        <is>
+          <t>4811.59.4040</t>
+        </is>
+      </c>
+      <c r="J337" t="inlineStr">
+        <is>
+          <t>BAUSCHLINNEMANN NORTH AMERICA</t>
+        </is>
+      </c>
+      <c r="K337" t="inlineStr">
+        <is>
+          <t>BAULIN</t>
+        </is>
+      </c>
+      <c r="L337" t="inlineStr">
+        <is>
+          <t>56-193913400</t>
+        </is>
+      </c>
+      <c r="M337" t="inlineStr">
+        <is>
+          <t>2026-06-21 00:00:00</t>
+        </is>
+      </c>
+      <c r="N337" t="inlineStr">
+        <is>
+          <t>2026-06-20 00:00:00</t>
+        </is>
+      </c>
+      <c r="O337" t="inlineStr">
+        <is>
+          <t>SURTECO GMBH</t>
+        </is>
+      </c>
+      <c r="P337" t="inlineStr">
+        <is>
+          <t>SURTECO GMBH</t>
+        </is>
+      </c>
+      <c r="Q337" t="inlineStr">
+        <is>
+          <t>2026-06-01 00:00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="338">
+      <c r="A338" t="inlineStr">
+        <is>
+          <t>2566100</t>
+        </is>
+      </c>
+      <c r="B338" t="inlineStr">
+        <is>
+          <t>EF4-0232282-2</t>
+        </is>
+      </c>
+      <c r="C338" t="inlineStr">
+        <is>
+          <t>Vessel, Container</t>
+        </is>
+      </c>
+      <c r="D338" t="inlineStr"/>
+      <c r="E338" t="inlineStr">
+        <is>
+          <t>9903.03.01</t>
+        </is>
+      </c>
+      <c r="F338" t="inlineStr">
+        <is>
+          <t>SECTION 122 - 10% DUTY</t>
+        </is>
+      </c>
+      <c r="G338" t="inlineStr">
+        <is>
+          <t>003</t>
+        </is>
+      </c>
+      <c r="H338" t="inlineStr">
+        <is>
+          <t>9903.03.01</t>
+        </is>
+      </c>
+      <c r="I338" t="inlineStr">
+        <is>
+          <t>4811.59.4040</t>
+        </is>
+      </c>
+      <c r="J338" t="inlineStr">
+        <is>
+          <t>BAUSCHLINNEMANN NORTH AMERICA</t>
+        </is>
+      </c>
+      <c r="K338" t="inlineStr">
+        <is>
+          <t>BAULIN</t>
+        </is>
+      </c>
+      <c r="L338" t="inlineStr">
+        <is>
+          <t>56-193913400</t>
+        </is>
+      </c>
+      <c r="M338" t="inlineStr">
+        <is>
+          <t>2026-06-21 00:00:00</t>
+        </is>
+      </c>
+      <c r="N338" t="inlineStr">
+        <is>
+          <t>2026-06-20 00:00:00</t>
+        </is>
+      </c>
+      <c r="O338" t="inlineStr">
+        <is>
+          <t>SURTECO GMBH</t>
+        </is>
+      </c>
+      <c r="P338" t="inlineStr">
+        <is>
+          <t>SURTECO GMBH</t>
+        </is>
+      </c>
+      <c r="Q338" t="inlineStr">
+        <is>
+          <t>2026-06-01 00:00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="339">
+      <c r="A339" t="inlineStr">
+        <is>
+          <t>2615771</t>
+        </is>
+      </c>
+      <c r="B339" t="inlineStr">
+        <is>
+          <t>EF4-0232406-7</t>
+        </is>
+      </c>
+      <c r="C339" t="inlineStr">
+        <is>
+          <t>Vessel, Non-container</t>
+        </is>
+      </c>
+      <c r="D339" t="inlineStr"/>
+      <c r="E339" t="inlineStr">
+        <is>
+          <t>9903.03.01</t>
+        </is>
+      </c>
+      <c r="F339" t="inlineStr">
+        <is>
+          <t>SECTION 122 - 10% DUTY</t>
+        </is>
+      </c>
+      <c r="G339" t="inlineStr">
+        <is>
+          <t>001</t>
+        </is>
+      </c>
+      <c r="H339" t="inlineStr">
+        <is>
+          <t>9903.03.01</t>
+        </is>
+      </c>
+      <c r="I339" t="inlineStr">
+        <is>
+          <t>8210.00.0000</t>
+        </is>
+      </c>
+      <c r="J339" t="inlineStr">
+        <is>
+          <t>COVE HOME LLC</t>
+        </is>
+      </c>
+      <c r="K339" t="inlineStr">
+        <is>
+          <t>COVHOM01</t>
+        </is>
+      </c>
+      <c r="L339" t="inlineStr">
+        <is>
+          <t>30-136116600</t>
+        </is>
+      </c>
+      <c r="M339" t="inlineStr">
+        <is>
+          <t>2026-06-20 00:00:00</t>
+        </is>
+      </c>
+      <c r="N339" t="inlineStr">
+        <is>
+          <t>2026-06-20 00:00:00</t>
+        </is>
+      </c>
+      <c r="O339" t="inlineStr">
+        <is>
+          <t>P. IONNOU G ZARKADIS QE</t>
+        </is>
+      </c>
+      <c r="P339" t="inlineStr">
+        <is>
+          <t>P. IONNOU G ZARKADIS QE</t>
+        </is>
+      </c>
+      <c r="Q339" t="inlineStr">
+        <is>
+          <t>2026-06-06 00:00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="340">
+      <c r="A340" t="inlineStr">
+        <is>
+          <t>2615771</t>
+        </is>
+      </c>
+      <c r="B340" t="inlineStr">
+        <is>
+          <t>EF4-0232406-7</t>
+        </is>
+      </c>
+      <c r="C340" t="inlineStr">
+        <is>
+          <t>Vessel, Non-container</t>
+        </is>
+      </c>
+      <c r="D340" t="inlineStr"/>
+      <c r="E340" t="inlineStr">
+        <is>
+          <t>9903.03.01</t>
+        </is>
+      </c>
+      <c r="F340" t="inlineStr">
+        <is>
+          <t>SECTION 122 - 10% DUTY</t>
+        </is>
+      </c>
+      <c r="G340" t="inlineStr">
+        <is>
+          <t>002</t>
+        </is>
+      </c>
+      <c r="H340" t="inlineStr">
+        <is>
+          <t>9903.03.01</t>
+        </is>
+      </c>
+      <c r="I340" t="inlineStr">
+        <is>
+          <t>8210.00.0000</t>
+        </is>
+      </c>
+      <c r="J340" t="inlineStr">
+        <is>
+          <t>COVE HOME LLC</t>
+        </is>
+      </c>
+      <c r="K340" t="inlineStr">
+        <is>
+          <t>COVHOM01</t>
+        </is>
+      </c>
+      <c r="L340" t="inlineStr">
+        <is>
+          <t>30-136116600</t>
+        </is>
+      </c>
+      <c r="M340" t="inlineStr">
+        <is>
+          <t>2026-06-20 00:00:00</t>
+        </is>
+      </c>
+      <c r="N340" t="inlineStr">
+        <is>
+          <t>2026-06-20 00:00:00</t>
+        </is>
+      </c>
+      <c r="O340" t="inlineStr">
+        <is>
+          <t>P. IONNOU G ZARKADIS QE</t>
+        </is>
+      </c>
+      <c r="P340" t="inlineStr">
+        <is>
+          <t>P. IONNOU G ZARKADIS QE</t>
+        </is>
+      </c>
+      <c r="Q340" t="inlineStr">
+        <is>
+          <t>2026-06-06 00:00:00</t>
         </is>
       </c>
     </row>

--- a/trimika_data.xlsx
+++ b/trimika_data.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q340"/>
+  <dimension ref="A1:Q353"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -27665,12 +27665,12 @@
     <row r="327">
       <c r="A327" t="inlineStr">
         <is>
-          <t>2565923</t>
+          <t>2566178</t>
         </is>
       </c>
       <c r="B327" t="inlineStr">
         <is>
-          <t>EF4-0232195-6</t>
+          <t>EF4-0232247-5</t>
         </is>
       </c>
       <c r="C327" t="inlineStr">
@@ -27681,12 +27681,12 @@
       <c r="D327" t="inlineStr"/>
       <c r="E327" t="inlineStr">
         <is>
-          <t>9903.91.01</t>
+          <t>9903.03.01</t>
         </is>
       </c>
       <c r="F327" t="inlineStr">
         <is>
-          <t>ARTS, PRDS OF CN SUB(B)US NT31</t>
+          <t>SECTION 122 - 10% DUTY</t>
         </is>
       </c>
       <c r="G327" t="inlineStr">
@@ -27696,27 +27696,27 @@
       </c>
       <c r="H327" t="inlineStr">
         <is>
-          <t>9903.91.01</t>
+          <t>9903.03.01</t>
         </is>
       </c>
       <c r="I327" t="inlineStr">
         <is>
-          <t>9903.03.06,9903.82.02,7228.30.6000</t>
+          <t>1108.13.0010</t>
         </is>
       </c>
       <c r="J327" t="inlineStr">
         <is>
-          <t>MAHA USA LLC</t>
+          <t>ROYAL INGREDIENTS GROUP BV</t>
         </is>
       </c>
       <c r="K327" t="inlineStr">
         <is>
-          <t>MAHUSA</t>
+          <t>ROYINGRE</t>
         </is>
       </c>
       <c r="L327" t="inlineStr">
         <is>
-          <t>52-213556300</t>
+          <t>074601-00962</t>
         </is>
       </c>
       <c r="M327" t="inlineStr">
@@ -27731,29 +27731,29 @@
       </c>
       <c r="O327" t="inlineStr">
         <is>
-          <t>THYSSENKRUPP SCHULTE GMBH</t>
+          <t>AKV LANGHOLT AMBA</t>
         </is>
       </c>
       <c r="P327" t="inlineStr">
         <is>
-          <t>THYSSENKRUPP SCHULTE GMBH</t>
+          <t>AKV LANGHOLT AMBA</t>
         </is>
       </c>
       <c r="Q327" t="inlineStr">
         <is>
-          <t>2026-05-27 00:00:00</t>
+          <t>2026-06-01 00:00:00</t>
         </is>
       </c>
     </row>
     <row r="328">
       <c r="A328" t="inlineStr">
         <is>
-          <t>2565923</t>
+          <t>2566229</t>
         </is>
       </c>
       <c r="B328" t="inlineStr">
         <is>
-          <t>EF4-0232195-6</t>
+          <t>EF4-0232249-1</t>
         </is>
       </c>
       <c r="C328" t="inlineStr">
@@ -27761,45 +27761,49 @@
           <t>Vessel, Container</t>
         </is>
       </c>
-      <c r="D328" t="inlineStr"/>
+      <c r="D328" t="inlineStr">
+        <is>
+          <t>V0710338448</t>
+        </is>
+      </c>
       <c r="E328" t="inlineStr">
         <is>
-          <t>9903.03.06</t>
+          <t>9903.03.01</t>
         </is>
       </c>
       <c r="F328" t="inlineStr">
         <is>
-          <t>S122 EXCL,IRN/STL/ALUM,DERIV</t>
+          <t>SECTION 122 - 10% DUTY</t>
         </is>
       </c>
       <c r="G328" t="inlineStr">
         <is>
-          <t>002</t>
+          <t>001</t>
         </is>
       </c>
       <c r="H328" t="inlineStr">
         <is>
-          <t>9903.03.06</t>
+          <t>9903.03.01</t>
         </is>
       </c>
       <c r="I328" t="inlineStr">
         <is>
-          <t>9903.82.02,7215.50.0016</t>
+          <t>1108.13.0010</t>
         </is>
       </c>
       <c r="J328" t="inlineStr">
         <is>
-          <t>MAHA USA LLC</t>
+          <t>ROYAL INGREDIENTS GROUP BV</t>
         </is>
       </c>
       <c r="K328" t="inlineStr">
         <is>
-          <t>MAHUSA</t>
+          <t>ROYINGRE</t>
         </is>
       </c>
       <c r="L328" t="inlineStr">
         <is>
-          <t>52-213556300</t>
+          <t>074601-00962</t>
         </is>
       </c>
       <c r="M328" t="inlineStr">
@@ -27814,29 +27818,29 @@
       </c>
       <c r="O328" t="inlineStr">
         <is>
-          <t>THYSSENKRUPP SCHULTE GMBH</t>
+          <t>AKV LANGHOLT AMBA</t>
         </is>
       </c>
       <c r="P328" t="inlineStr">
         <is>
-          <t>THYSSENKRUPP SCHULTE GMBH</t>
+          <t>AKV LANGHOLT AMBA</t>
         </is>
       </c>
       <c r="Q328" t="inlineStr">
         <is>
-          <t>2026-05-27 00:00:00</t>
+          <t>2026-06-01 00:00:00</t>
         </is>
       </c>
     </row>
     <row r="329">
       <c r="A329" t="inlineStr">
         <is>
-          <t>2565923</t>
+          <t>2566177</t>
         </is>
       </c>
       <c r="B329" t="inlineStr">
         <is>
-          <t>EF4-0232195-6</t>
+          <t>EF4-0232275-6</t>
         </is>
       </c>
       <c r="C329" t="inlineStr">
@@ -27844,45 +27848,49 @@
           <t>Vessel, Container</t>
         </is>
       </c>
-      <c r="D329" t="inlineStr"/>
+      <c r="D329" t="inlineStr">
+        <is>
+          <t>V0710338448</t>
+        </is>
+      </c>
       <c r="E329" t="inlineStr">
         <is>
-          <t>9903.03.06</t>
+          <t>9903.03.01</t>
         </is>
       </c>
       <c r="F329" t="inlineStr">
         <is>
-          <t>S122 EXCL,IRN/STL/ALUM,DERIV</t>
+          <t>SECTION 122 - 10% DUTY</t>
         </is>
       </c>
       <c r="G329" t="inlineStr">
         <is>
-          <t>003</t>
+          <t>001</t>
         </is>
       </c>
       <c r="H329" t="inlineStr">
         <is>
-          <t>9903.03.06</t>
+          <t>9903.03.01</t>
         </is>
       </c>
       <c r="I329" t="inlineStr">
         <is>
-          <t>9903.82.02,7216.33.0090</t>
+          <t>1108.13.0010</t>
         </is>
       </c>
       <c r="J329" t="inlineStr">
         <is>
-          <t>MAHA USA LLC</t>
+          <t>ROYAL INGREDIENTS GROUP BV</t>
         </is>
       </c>
       <c r="K329" t="inlineStr">
         <is>
-          <t>MAHUSA</t>
+          <t>ROYINGRE</t>
         </is>
       </c>
       <c r="L329" t="inlineStr">
         <is>
-          <t>52-213556300</t>
+          <t>074601-00962</t>
         </is>
       </c>
       <c r="M329" t="inlineStr">
@@ -27897,29 +27905,29 @@
       </c>
       <c r="O329" t="inlineStr">
         <is>
-          <t>THYSSENKRUPP SCHULTE GMBH</t>
+          <t>AKV LANGHOLT AMBA</t>
         </is>
       </c>
       <c r="P329" t="inlineStr">
         <is>
-          <t>THYSSENKRUPP SCHULTE GMBH</t>
+          <t>AKV LANGHOLT AMBA</t>
         </is>
       </c>
       <c r="Q329" t="inlineStr">
         <is>
-          <t>2026-05-27 00:00:00</t>
+          <t>2026-06-01 00:00:00</t>
         </is>
       </c>
     </row>
     <row r="330">
       <c r="A330" t="inlineStr">
         <is>
-          <t>2566178</t>
+          <t>2566051</t>
         </is>
       </c>
       <c r="B330" t="inlineStr">
         <is>
-          <t>EF4-0232247-5</t>
+          <t>EF4-0232281-4</t>
         </is>
       </c>
       <c r="C330" t="inlineStr">
@@ -27927,7 +27935,11 @@
           <t>Vessel, Container</t>
         </is>
       </c>
-      <c r="D330" t="inlineStr"/>
+      <c r="D330" t="inlineStr">
+        <is>
+          <t>V0710349973</t>
+        </is>
+      </c>
       <c r="E330" t="inlineStr">
         <is>
           <t>9903.03.01</t>
@@ -27950,42 +27962,42 @@
       </c>
       <c r="I330" t="inlineStr">
         <is>
-          <t>1108.13.0010</t>
+          <t>4811.59.4040</t>
         </is>
       </c>
       <c r="J330" t="inlineStr">
         <is>
-          <t>ROYAL INGREDIENTS GROUP BV</t>
+          <t>BAUSCHLINNEMANN NORTH AMERICA</t>
         </is>
       </c>
       <c r="K330" t="inlineStr">
         <is>
-          <t>ROYINGRE</t>
+          <t>BAULIN</t>
         </is>
       </c>
       <c r="L330" t="inlineStr">
         <is>
-          <t>074601-00962</t>
+          <t>56-193913400</t>
         </is>
       </c>
       <c r="M330" t="inlineStr">
         <is>
+          <t>2026-06-21 00:00:00</t>
+        </is>
+      </c>
+      <c r="N330" t="inlineStr">
+        <is>
           <t>2026-06-20 00:00:00</t>
         </is>
       </c>
-      <c r="N330" t="inlineStr">
-        <is>
-          <t>2026-06-20 00:00:00</t>
-        </is>
-      </c>
       <c r="O330" t="inlineStr">
         <is>
-          <t>AKV LANGHOLT AMBA</t>
+          <t>SURTECO GMBH</t>
         </is>
       </c>
       <c r="P330" t="inlineStr">
         <is>
-          <t>AKV LANGHOLT AMBA</t>
+          <t>SURTECO GMBH</t>
         </is>
       </c>
       <c r="Q330" t="inlineStr">
@@ -27997,12 +28009,12 @@
     <row r="331">
       <c r="A331" t="inlineStr">
         <is>
-          <t>2566229</t>
+          <t>2566051</t>
         </is>
       </c>
       <c r="B331" t="inlineStr">
         <is>
-          <t>EF4-0232249-1</t>
+          <t>EF4-0232281-4</t>
         </is>
       </c>
       <c r="C331" t="inlineStr">
@@ -28012,7 +28024,7 @@
       </c>
       <c r="D331" t="inlineStr">
         <is>
-          <t>V0710338448</t>
+          <t>V0710349973</t>
         </is>
       </c>
       <c r="E331" t="inlineStr">
@@ -28027,7 +28039,7 @@
       </c>
       <c r="G331" t="inlineStr">
         <is>
-          <t>001</t>
+          <t>002</t>
         </is>
       </c>
       <c r="H331" t="inlineStr">
@@ -28037,42 +28049,42 @@
       </c>
       <c r="I331" t="inlineStr">
         <is>
-          <t>1108.13.0010</t>
+          <t>4811.59.4040</t>
         </is>
       </c>
       <c r="J331" t="inlineStr">
         <is>
-          <t>ROYAL INGREDIENTS GROUP BV</t>
+          <t>BAUSCHLINNEMANN NORTH AMERICA</t>
         </is>
       </c>
       <c r="K331" t="inlineStr">
         <is>
-          <t>ROYINGRE</t>
+          <t>BAULIN</t>
         </is>
       </c>
       <c r="L331" t="inlineStr">
         <is>
-          <t>074601-00962</t>
+          <t>56-193913400</t>
         </is>
       </c>
       <c r="M331" t="inlineStr">
         <is>
+          <t>2026-06-21 00:00:00</t>
+        </is>
+      </c>
+      <c r="N331" t="inlineStr">
+        <is>
           <t>2026-06-20 00:00:00</t>
         </is>
       </c>
-      <c r="N331" t="inlineStr">
-        <is>
-          <t>2026-06-20 00:00:00</t>
-        </is>
-      </c>
       <c r="O331" t="inlineStr">
         <is>
-          <t>AKV LANGHOLT AMBA</t>
+          <t>SURTECO GMBH</t>
         </is>
       </c>
       <c r="P331" t="inlineStr">
         <is>
-          <t>AKV LANGHOLT AMBA</t>
+          <t>SURTECO GMBH</t>
         </is>
       </c>
       <c r="Q331" t="inlineStr">
@@ -28084,12 +28096,12 @@
     <row r="332">
       <c r="A332" t="inlineStr">
         <is>
-          <t>2566177</t>
+          <t>2566051</t>
         </is>
       </c>
       <c r="B332" t="inlineStr">
         <is>
-          <t>EF4-0232275-6</t>
+          <t>EF4-0232281-4</t>
         </is>
       </c>
       <c r="C332" t="inlineStr">
@@ -28099,7 +28111,7 @@
       </c>
       <c r="D332" t="inlineStr">
         <is>
-          <t>V0710338448</t>
+          <t>V0710349973</t>
         </is>
       </c>
       <c r="E332" t="inlineStr">
@@ -28114,7 +28126,7 @@
       </c>
       <c r="G332" t="inlineStr">
         <is>
-          <t>001</t>
+          <t>003</t>
         </is>
       </c>
       <c r="H332" t="inlineStr">
@@ -28124,42 +28136,42 @@
       </c>
       <c r="I332" t="inlineStr">
         <is>
-          <t>1108.13.0010</t>
+          <t>4811.59.4040</t>
         </is>
       </c>
       <c r="J332" t="inlineStr">
         <is>
-          <t>ROYAL INGREDIENTS GROUP BV</t>
+          <t>BAUSCHLINNEMANN NORTH AMERICA</t>
         </is>
       </c>
       <c r="K332" t="inlineStr">
         <is>
-          <t>ROYINGRE</t>
+          <t>BAULIN</t>
         </is>
       </c>
       <c r="L332" t="inlineStr">
         <is>
-          <t>074601-00962</t>
+          <t>56-193913400</t>
         </is>
       </c>
       <c r="M332" t="inlineStr">
         <is>
+          <t>2026-06-21 00:00:00</t>
+        </is>
+      </c>
+      <c r="N332" t="inlineStr">
+        <is>
           <t>2026-06-20 00:00:00</t>
         </is>
       </c>
-      <c r="N332" t="inlineStr">
-        <is>
-          <t>2026-06-20 00:00:00</t>
-        </is>
-      </c>
       <c r="O332" t="inlineStr">
         <is>
-          <t>AKV LANGHOLT AMBA</t>
+          <t>SURTECO GMBH</t>
         </is>
       </c>
       <c r="P332" t="inlineStr">
         <is>
-          <t>AKV LANGHOLT AMBA</t>
+          <t>SURTECO GMBH</t>
         </is>
       </c>
       <c r="Q332" t="inlineStr">
@@ -28171,12 +28183,12 @@
     <row r="333">
       <c r="A333" t="inlineStr">
         <is>
-          <t>2566051</t>
+          <t>2566100</t>
         </is>
       </c>
       <c r="B333" t="inlineStr">
         <is>
-          <t>EF4-0232281-4</t>
+          <t>EF4-0232282-2</t>
         </is>
       </c>
       <c r="C333" t="inlineStr">
@@ -28184,11 +28196,7 @@
           <t>Vessel, Container</t>
         </is>
       </c>
-      <c r="D333" t="inlineStr">
-        <is>
-          <t>V0710349973</t>
-        </is>
-      </c>
+      <c r="D333" t="inlineStr"/>
       <c r="E333" t="inlineStr">
         <is>
           <t>9903.03.01</t>
@@ -28258,12 +28266,12 @@
     <row r="334">
       <c r="A334" t="inlineStr">
         <is>
-          <t>2566051</t>
+          <t>2566100</t>
         </is>
       </c>
       <c r="B334" t="inlineStr">
         <is>
-          <t>EF4-0232281-4</t>
+          <t>EF4-0232282-2</t>
         </is>
       </c>
       <c r="C334" t="inlineStr">
@@ -28271,11 +28279,7 @@
           <t>Vessel, Container</t>
         </is>
       </c>
-      <c r="D334" t="inlineStr">
-        <is>
-          <t>V0710349973</t>
-        </is>
-      </c>
+      <c r="D334" t="inlineStr"/>
       <c r="E334" t="inlineStr">
         <is>
           <t>9903.03.01</t>
@@ -28345,12 +28349,12 @@
     <row r="335">
       <c r="A335" t="inlineStr">
         <is>
-          <t>2566051</t>
+          <t>2566100</t>
         </is>
       </c>
       <c r="B335" t="inlineStr">
         <is>
-          <t>EF4-0232281-4</t>
+          <t>EF4-0232282-2</t>
         </is>
       </c>
       <c r="C335" t="inlineStr">
@@ -28358,11 +28362,7 @@
           <t>Vessel, Container</t>
         </is>
       </c>
-      <c r="D335" t="inlineStr">
-        <is>
-          <t>V0710349973</t>
-        </is>
-      </c>
+      <c r="D335" t="inlineStr"/>
       <c r="E335" t="inlineStr">
         <is>
           <t>9903.03.01</t>
@@ -28432,17 +28432,17 @@
     <row r="336">
       <c r="A336" t="inlineStr">
         <is>
-          <t>2566100</t>
+          <t>2615771</t>
         </is>
       </c>
       <c r="B336" t="inlineStr">
         <is>
-          <t>EF4-0232282-2</t>
+          <t>EF4-0232406-7</t>
         </is>
       </c>
       <c r="C336" t="inlineStr">
         <is>
-          <t>Vessel, Container</t>
+          <t>Vessel, Non-container</t>
         </is>
       </c>
       <c r="D336" t="inlineStr"/>
@@ -28468,27 +28468,27 @@
       </c>
       <c r="I336" t="inlineStr">
         <is>
-          <t>4811.59.4040</t>
+          <t>8210.00.0000</t>
         </is>
       </c>
       <c r="J336" t="inlineStr">
         <is>
-          <t>BAUSCHLINNEMANN NORTH AMERICA</t>
+          <t>COVE HOME LLC</t>
         </is>
       </c>
       <c r="K336" t="inlineStr">
         <is>
-          <t>BAULIN</t>
+          <t>COVHOM01</t>
         </is>
       </c>
       <c r="L336" t="inlineStr">
         <is>
-          <t>56-193913400</t>
+          <t>30-136116600</t>
         </is>
       </c>
       <c r="M336" t="inlineStr">
         <is>
-          <t>2026-06-21 00:00:00</t>
+          <t>2026-06-20 00:00:00</t>
         </is>
       </c>
       <c r="N336" t="inlineStr">
@@ -28498,34 +28498,34 @@
       </c>
       <c r="O336" t="inlineStr">
         <is>
-          <t>SURTECO GMBH</t>
+          <t>P. IONNOU G ZARKADIS QE</t>
         </is>
       </c>
       <c r="P336" t="inlineStr">
         <is>
-          <t>SURTECO GMBH</t>
+          <t>P. IONNOU G ZARKADIS QE</t>
         </is>
       </c>
       <c r="Q336" t="inlineStr">
         <is>
-          <t>2026-06-01 00:00:00</t>
+          <t>2026-06-06 00:00:00</t>
         </is>
       </c>
     </row>
     <row r="337">
       <c r="A337" t="inlineStr">
         <is>
-          <t>2566100</t>
+          <t>2615771</t>
         </is>
       </c>
       <c r="B337" t="inlineStr">
         <is>
-          <t>EF4-0232282-2</t>
+          <t>EF4-0232406-7</t>
         </is>
       </c>
       <c r="C337" t="inlineStr">
         <is>
-          <t>Vessel, Container</t>
+          <t>Vessel, Non-container</t>
         </is>
       </c>
       <c r="D337" t="inlineStr"/>
@@ -28551,27 +28551,27 @@
       </c>
       <c r="I337" t="inlineStr">
         <is>
-          <t>4811.59.4040</t>
+          <t>8210.00.0000</t>
         </is>
       </c>
       <c r="J337" t="inlineStr">
         <is>
-          <t>BAUSCHLINNEMANN NORTH AMERICA</t>
+          <t>COVE HOME LLC</t>
         </is>
       </c>
       <c r="K337" t="inlineStr">
         <is>
-          <t>BAULIN</t>
+          <t>COVHOM01</t>
         </is>
       </c>
       <c r="L337" t="inlineStr">
         <is>
-          <t>56-193913400</t>
+          <t>30-136116600</t>
         </is>
       </c>
       <c r="M337" t="inlineStr">
         <is>
-          <t>2026-06-21 00:00:00</t>
+          <t>2026-06-20 00:00:00</t>
         </is>
       </c>
       <c r="N337" t="inlineStr">
@@ -28581,29 +28581,29 @@
       </c>
       <c r="O337" t="inlineStr">
         <is>
-          <t>SURTECO GMBH</t>
+          <t>P. IONNOU G ZARKADIS QE</t>
         </is>
       </c>
       <c r="P337" t="inlineStr">
         <is>
-          <t>SURTECO GMBH</t>
+          <t>P. IONNOU G ZARKADIS QE</t>
         </is>
       </c>
       <c r="Q337" t="inlineStr">
         <is>
-          <t>2026-06-01 00:00:00</t>
+          <t>2026-06-06 00:00:00</t>
         </is>
       </c>
     </row>
     <row r="338">
       <c r="A338" t="inlineStr">
         <is>
-          <t>2566100</t>
+          <t>2565847</t>
         </is>
       </c>
       <c r="B338" t="inlineStr">
         <is>
-          <t>EF4-0232282-2</t>
+          <t>EF4-0231725-1</t>
         </is>
       </c>
       <c r="C338" t="inlineStr">
@@ -28624,7 +28624,7 @@
       </c>
       <c r="G338" t="inlineStr">
         <is>
-          <t>003</t>
+          <t>001</t>
         </is>
       </c>
       <c r="H338" t="inlineStr">
@@ -28634,64 +28634,64 @@
       </c>
       <c r="I338" t="inlineStr">
         <is>
-          <t>4811.59.4040</t>
+          <t>5407.20.0000</t>
         </is>
       </c>
       <c r="J338" t="inlineStr">
         <is>
-          <t>BAUSCHLINNEMANN NORTH AMERICA</t>
+          <t>VEER CORPORATIONS INC</t>
         </is>
       </c>
       <c r="K338" t="inlineStr">
         <is>
-          <t>BAULIN</t>
+          <t>VEECOR01</t>
         </is>
       </c>
       <c r="L338" t="inlineStr">
         <is>
-          <t>56-193913400</t>
+          <t>99-106989200</t>
         </is>
       </c>
       <c r="M338" t="inlineStr">
         <is>
+          <t>2026-06-19 00:00:00</t>
+        </is>
+      </c>
+      <c r="N338" t="inlineStr">
+        <is>
           <t>2026-06-21 00:00:00</t>
         </is>
       </c>
-      <c r="N338" t="inlineStr">
-        <is>
-          <t>2026-06-20 00:00:00</t>
-        </is>
-      </c>
       <c r="O338" t="inlineStr">
         <is>
-          <t>SURTECO GMBH</t>
+          <t>VEER PLASTIC PVT LTD</t>
         </is>
       </c>
       <c r="P338" t="inlineStr">
         <is>
-          <t>SURTECO GMBH</t>
+          <t>VEER PLASTIC PVT LTD</t>
         </is>
       </c>
       <c r="Q338" t="inlineStr">
         <is>
-          <t>2026-06-01 00:00:00</t>
+          <t>2026-05-06 00:00:00</t>
         </is>
       </c>
     </row>
     <row r="339">
       <c r="A339" t="inlineStr">
         <is>
-          <t>2615771</t>
+          <t>2565848</t>
         </is>
       </c>
       <c r="B339" t="inlineStr">
         <is>
-          <t>EF4-0232406-7</t>
+          <t>EF4-0231726-9</t>
         </is>
       </c>
       <c r="C339" t="inlineStr">
         <is>
-          <t>Vessel, Non-container</t>
+          <t>Vessel, Container</t>
         </is>
       </c>
       <c r="D339" t="inlineStr"/>
@@ -28717,64 +28717,64 @@
       </c>
       <c r="I339" t="inlineStr">
         <is>
-          <t>8210.00.0000</t>
+          <t>5603.14.9090</t>
         </is>
       </c>
       <c r="J339" t="inlineStr">
         <is>
-          <t>COVE HOME LLC</t>
+          <t>VEER CORPORATIONS INC</t>
         </is>
       </c>
       <c r="K339" t="inlineStr">
         <is>
-          <t>COVHOM01</t>
+          <t>VEECOR01</t>
         </is>
       </c>
       <c r="L339" t="inlineStr">
         <is>
-          <t>30-136116600</t>
+          <t>99-106989200</t>
         </is>
       </c>
       <c r="M339" t="inlineStr">
         <is>
-          <t>2026-06-20 00:00:00</t>
+          <t>2026-06-19 00:00:00</t>
         </is>
       </c>
       <c r="N339" t="inlineStr">
         <is>
-          <t>2026-06-20 00:00:00</t>
+          <t>2026-06-21 00:00:00</t>
         </is>
       </c>
       <c r="O339" t="inlineStr">
         <is>
-          <t>P. IONNOU G ZARKADIS QE</t>
+          <t>VEER PLASTIC PVT LTD</t>
         </is>
       </c>
       <c r="P339" t="inlineStr">
         <is>
-          <t>P. IONNOU G ZARKADIS QE</t>
+          <t>VEER PLASTIC PVT LTD</t>
         </is>
       </c>
       <c r="Q339" t="inlineStr">
         <is>
-          <t>2026-06-06 00:00:00</t>
+          <t>2026-05-11 00:00:00</t>
         </is>
       </c>
     </row>
     <row r="340">
       <c r="A340" t="inlineStr">
         <is>
-          <t>2615771</t>
+          <t>2565849</t>
         </is>
       </c>
       <c r="B340" t="inlineStr">
         <is>
-          <t>EF4-0232406-7</t>
+          <t>EF4-0231727-7</t>
         </is>
       </c>
       <c r="C340" t="inlineStr">
         <is>
-          <t>Vessel, Non-container</t>
+          <t>Vessel, Container</t>
         </is>
       </c>
       <c r="D340" t="inlineStr"/>
@@ -28790,55 +28790,1142 @@
       </c>
       <c r="G340" t="inlineStr">
         <is>
+          <t>001</t>
+        </is>
+      </c>
+      <c r="H340" t="inlineStr">
+        <is>
+          <t>9903.03.01</t>
+        </is>
+      </c>
+      <c r="I340" t="inlineStr">
+        <is>
+          <t>5407.20.0000</t>
+        </is>
+      </c>
+      <c r="J340" t="inlineStr">
+        <is>
+          <t>VEER CORPORATIONS INC</t>
+        </is>
+      </c>
+      <c r="K340" t="inlineStr">
+        <is>
+          <t>VEECOR01</t>
+        </is>
+      </c>
+      <c r="L340" t="inlineStr">
+        <is>
+          <t>99-106989200</t>
+        </is>
+      </c>
+      <c r="M340" t="inlineStr">
+        <is>
+          <t>2026-06-19 00:00:00</t>
+        </is>
+      </c>
+      <c r="N340" t="inlineStr">
+        <is>
+          <t>2026-06-21 00:00:00</t>
+        </is>
+      </c>
+      <c r="O340" t="inlineStr">
+        <is>
+          <t>VEER PLASTIC PVT LTD</t>
+        </is>
+      </c>
+      <c r="P340" t="inlineStr">
+        <is>
+          <t>VEER PLASTIC PVT LTD</t>
+        </is>
+      </c>
+      <c r="Q340" t="inlineStr">
+        <is>
+          <t>2026-05-11 00:00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="341">
+      <c r="A341" t="inlineStr">
+        <is>
+          <t>2565891</t>
+        </is>
+      </c>
+      <c r="B341" t="inlineStr">
+        <is>
+          <t>EF4-0231922-4</t>
+        </is>
+      </c>
+      <c r="C341" t="inlineStr">
+        <is>
+          <t>Vessel, Container</t>
+        </is>
+      </c>
+      <c r="D341" t="inlineStr"/>
+      <c r="E341" t="inlineStr">
+        <is>
+          <t>9903.03.01</t>
+        </is>
+      </c>
+      <c r="F341" t="inlineStr">
+        <is>
+          <t>SECTION 122 - 10% DUTY</t>
+        </is>
+      </c>
+      <c r="G341" t="inlineStr">
+        <is>
+          <t>001</t>
+        </is>
+      </c>
+      <c r="H341" t="inlineStr">
+        <is>
+          <t>9903.03.01</t>
+        </is>
+      </c>
+      <c r="I341" t="inlineStr">
+        <is>
+          <t>1109.00.9020</t>
+        </is>
+      </c>
+      <c r="J341" t="inlineStr">
+        <is>
+          <t>ROYAL INGREDIENTS GROUP BV</t>
+        </is>
+      </c>
+      <c r="K341" t="inlineStr">
+        <is>
+          <t>ROYINGRE</t>
+        </is>
+      </c>
+      <c r="L341" t="inlineStr">
+        <is>
+          <t>074601-00962</t>
+        </is>
+      </c>
+      <c r="M341" t="inlineStr">
+        <is>
+          <t>2026-06-20 00:00:00</t>
+        </is>
+      </c>
+      <c r="N341" t="inlineStr">
+        <is>
+          <t>2026-06-21 00:00:00</t>
+        </is>
+      </c>
+      <c r="O341" t="inlineStr">
+        <is>
+          <t>SEDAMYL UK</t>
+        </is>
+      </c>
+      <c r="P341" t="inlineStr">
+        <is>
+          <t>SEDAMYL UK</t>
+        </is>
+      </c>
+      <c r="Q341" t="inlineStr">
+        <is>
+          <t>2026-05-16 00:00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="342">
+      <c r="A342" t="inlineStr">
+        <is>
+          <t>2565934</t>
+        </is>
+      </c>
+      <c r="B342" t="inlineStr">
+        <is>
+          <t>EF4-0231991-9</t>
+        </is>
+      </c>
+      <c r="C342" t="inlineStr">
+        <is>
+          <t>Vessel, Container</t>
+        </is>
+      </c>
+      <c r="D342" t="inlineStr">
+        <is>
+          <t>V0710339289</t>
+        </is>
+      </c>
+      <c r="E342" t="inlineStr">
+        <is>
+          <t>9903.03.01</t>
+        </is>
+      </c>
+      <c r="F342" t="inlineStr">
+        <is>
+          <t>SECTION 122 - 10% DUTY</t>
+        </is>
+      </c>
+      <c r="G342" t="inlineStr">
+        <is>
+          <t>001</t>
+        </is>
+      </c>
+      <c r="H342" t="inlineStr">
+        <is>
+          <t>9903.03.01</t>
+        </is>
+      </c>
+      <c r="I342" t="inlineStr">
+        <is>
+          <t>1108.13.0010</t>
+        </is>
+      </c>
+      <c r="J342" t="inlineStr">
+        <is>
+          <t>ROYAL INGREDIENTS GROUP BV</t>
+        </is>
+      </c>
+      <c r="K342" t="inlineStr">
+        <is>
+          <t>ROYINGRE</t>
+        </is>
+      </c>
+      <c r="L342" t="inlineStr">
+        <is>
+          <t>074601-00962</t>
+        </is>
+      </c>
+      <c r="M342" t="inlineStr">
+        <is>
+          <t>2026-06-07 00:00:00</t>
+        </is>
+      </c>
+      <c r="N342" t="inlineStr">
+        <is>
+          <t>2026-06-21 00:00:00</t>
+        </is>
+      </c>
+      <c r="O342" t="inlineStr">
+        <is>
+          <t>AKV LANGHOLT AMBA</t>
+        </is>
+      </c>
+      <c r="P342" t="inlineStr">
+        <is>
+          <t>AKV LANGHOLT AMBA</t>
+        </is>
+      </c>
+      <c r="Q342" t="inlineStr">
+        <is>
+          <t>2026-05-18 00:00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="343">
+      <c r="A343" t="inlineStr">
+        <is>
+          <t>2566075</t>
+        </is>
+      </c>
+      <c r="B343" t="inlineStr">
+        <is>
+          <t>EF4-0232185-7</t>
+        </is>
+      </c>
+      <c r="C343" t="inlineStr">
+        <is>
+          <t>Vessel, Container</t>
+        </is>
+      </c>
+      <c r="D343" t="inlineStr">
+        <is>
+          <t>V0710339289</t>
+        </is>
+      </c>
+      <c r="E343" t="inlineStr">
+        <is>
+          <t>9903.03.01</t>
+        </is>
+      </c>
+      <c r="F343" t="inlineStr">
+        <is>
+          <t>SECTION 122 - 10% DUTY</t>
+        </is>
+      </c>
+      <c r="G343" t="inlineStr">
+        <is>
+          <t>001</t>
+        </is>
+      </c>
+      <c r="H343" t="inlineStr">
+        <is>
+          <t>9903.03.01</t>
+        </is>
+      </c>
+      <c r="I343" t="inlineStr">
+        <is>
+          <t>9903.82.01,8431.20.0000</t>
+        </is>
+      </c>
+      <c r="J343" t="inlineStr">
+        <is>
+          <t>MALLAGHAN (GA) INC.</t>
+        </is>
+      </c>
+      <c r="K343" t="inlineStr">
+        <is>
+          <t>MALGA01</t>
+        </is>
+      </c>
+      <c r="L343" t="inlineStr">
+        <is>
+          <t>36-488102800</t>
+        </is>
+      </c>
+      <c r="M343" t="inlineStr">
+        <is>
+          <t>2026-06-22 00:00:00</t>
+        </is>
+      </c>
+      <c r="N343" t="inlineStr">
+        <is>
+          <t>2026-06-21 00:00:00</t>
+        </is>
+      </c>
+      <c r="O343" t="inlineStr">
+        <is>
+          <t>MALLAGHAN ENGINEERING  LTD</t>
+        </is>
+      </c>
+      <c r="P343" t="inlineStr">
+        <is>
+          <t>MALLAGHAN ENGINEERING  LTD</t>
+        </is>
+      </c>
+      <c r="Q343" t="inlineStr">
+        <is>
+          <t>2026-05-28 00:00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="344">
+      <c r="A344" t="inlineStr">
+        <is>
+          <t>2566102</t>
+        </is>
+      </c>
+      <c r="B344" t="inlineStr">
+        <is>
+          <t>EF4-0232187-3</t>
+        </is>
+      </c>
+      <c r="C344" t="inlineStr">
+        <is>
+          <t>Vessel, Container</t>
+        </is>
+      </c>
+      <c r="D344" t="inlineStr"/>
+      <c r="E344" t="inlineStr">
+        <is>
+          <t>9903.03.06</t>
+        </is>
+      </c>
+      <c r="F344" t="inlineStr">
+        <is>
+          <t>S122 EXCL,IRN/STL/ALUM,DERIV</t>
+        </is>
+      </c>
+      <c r="G344" t="inlineStr">
+        <is>
+          <t>001</t>
+        </is>
+      </c>
+      <c r="H344" t="inlineStr">
+        <is>
+          <t>9903.03.06</t>
+        </is>
+      </c>
+      <c r="I344" t="inlineStr">
+        <is>
+          <t>9903.82.22,8431.20.0000</t>
+        </is>
+      </c>
+      <c r="J344" t="inlineStr">
+        <is>
+          <t>MALLAGHAN (GA) INC.</t>
+        </is>
+      </c>
+      <c r="K344" t="inlineStr">
+        <is>
+          <t>MALGA01</t>
+        </is>
+      </c>
+      <c r="L344" t="inlineStr">
+        <is>
+          <t>36-488102800</t>
+        </is>
+      </c>
+      <c r="M344" t="inlineStr">
+        <is>
+          <t>2026-06-22 00:00:00</t>
+        </is>
+      </c>
+      <c r="N344" t="inlineStr">
+        <is>
+          <t>2026-06-21 00:00:00</t>
+        </is>
+      </c>
+      <c r="O344" t="inlineStr">
+        <is>
+          <t>MALLAGHAN ENGINEERING  LTD</t>
+        </is>
+      </c>
+      <c r="P344" t="inlineStr">
+        <is>
+          <t>MALLAGHAN ENGINEERING  LTD</t>
+        </is>
+      </c>
+      <c r="Q344" t="inlineStr">
+        <is>
+          <t>2026-05-28 00:00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="345">
+      <c r="A345" t="inlineStr">
+        <is>
+          <t>2565923</t>
+        </is>
+      </c>
+      <c r="B345" t="inlineStr">
+        <is>
+          <t>EF4-0232195-6</t>
+        </is>
+      </c>
+      <c r="C345" t="inlineStr">
+        <is>
+          <t>Vessel, Container</t>
+        </is>
+      </c>
+      <c r="D345" t="inlineStr"/>
+      <c r="E345" t="inlineStr">
+        <is>
+          <t>9903.91.01</t>
+        </is>
+      </c>
+      <c r="F345" t="inlineStr">
+        <is>
+          <t>ARTS, PRDS OF CN SUB(B)US NT31</t>
+        </is>
+      </c>
+      <c r="G345" t="inlineStr">
+        <is>
+          <t>001</t>
+        </is>
+      </c>
+      <c r="H345" t="inlineStr">
+        <is>
+          <t>9903.91.01</t>
+        </is>
+      </c>
+      <c r="I345" t="inlineStr">
+        <is>
+          <t>9903.03.06,9903.82.02,7228.30.6000</t>
+        </is>
+      </c>
+      <c r="J345" t="inlineStr">
+        <is>
+          <t>MAHA USA LLC</t>
+        </is>
+      </c>
+      <c r="K345" t="inlineStr">
+        <is>
+          <t>MAHUSA</t>
+        </is>
+      </c>
+      <c r="L345" t="inlineStr">
+        <is>
+          <t>52-213556300</t>
+        </is>
+      </c>
+      <c r="M345" t="inlineStr">
+        <is>
+          <t>2026-06-20 00:00:00</t>
+        </is>
+      </c>
+      <c r="N345" t="inlineStr">
+        <is>
+          <t>2026-06-21 00:00:00</t>
+        </is>
+      </c>
+      <c r="O345" t="inlineStr">
+        <is>
+          <t>THYSSENKRUPP SCHULTE GMBH</t>
+        </is>
+      </c>
+      <c r="P345" t="inlineStr">
+        <is>
+          <t>THYSSENKRUPP SCHULTE GMBH</t>
+        </is>
+      </c>
+      <c r="Q345" t="inlineStr">
+        <is>
+          <t>2026-05-27 00:00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="346">
+      <c r="A346" t="inlineStr">
+        <is>
+          <t>2565923</t>
+        </is>
+      </c>
+      <c r="B346" t="inlineStr">
+        <is>
+          <t>EF4-0232195-6</t>
+        </is>
+      </c>
+      <c r="C346" t="inlineStr">
+        <is>
+          <t>Vessel, Container</t>
+        </is>
+      </c>
+      <c r="D346" t="inlineStr"/>
+      <c r="E346" t="inlineStr">
+        <is>
+          <t>9903.03.06</t>
+        </is>
+      </c>
+      <c r="F346" t="inlineStr">
+        <is>
+          <t>S122 EXCL,IRN/STL/ALUM,DERIV</t>
+        </is>
+      </c>
+      <c r="G346" t="inlineStr">
+        <is>
           <t>002</t>
         </is>
       </c>
-      <c r="H340" t="inlineStr">
-        <is>
-          <t>9903.03.01</t>
-        </is>
-      </c>
-      <c r="I340" t="inlineStr">
-        <is>
-          <t>8210.00.0000</t>
-        </is>
-      </c>
-      <c r="J340" t="inlineStr">
-        <is>
-          <t>COVE HOME LLC</t>
-        </is>
-      </c>
-      <c r="K340" t="inlineStr">
-        <is>
-          <t>COVHOM01</t>
-        </is>
-      </c>
-      <c r="L340" t="inlineStr">
-        <is>
-          <t>30-136116600</t>
-        </is>
-      </c>
-      <c r="M340" t="inlineStr">
+      <c r="H346" t="inlineStr">
+        <is>
+          <t>9903.03.06</t>
+        </is>
+      </c>
+      <c r="I346" t="inlineStr">
+        <is>
+          <t>9903.82.02,7215.50.0016</t>
+        </is>
+      </c>
+      <c r="J346" t="inlineStr">
+        <is>
+          <t>MAHA USA LLC</t>
+        </is>
+      </c>
+      <c r="K346" t="inlineStr">
+        <is>
+          <t>MAHUSA</t>
+        </is>
+      </c>
+      <c r="L346" t="inlineStr">
+        <is>
+          <t>52-213556300</t>
+        </is>
+      </c>
+      <c r="M346" t="inlineStr">
         <is>
           <t>2026-06-20 00:00:00</t>
         </is>
       </c>
-      <c r="N340" t="inlineStr">
+      <c r="N346" t="inlineStr">
+        <is>
+          <t>2026-06-21 00:00:00</t>
+        </is>
+      </c>
+      <c r="O346" t="inlineStr">
+        <is>
+          <t>THYSSENKRUPP SCHULTE GMBH</t>
+        </is>
+      </c>
+      <c r="P346" t="inlineStr">
+        <is>
+          <t>THYSSENKRUPP SCHULTE GMBH</t>
+        </is>
+      </c>
+      <c r="Q346" t="inlineStr">
+        <is>
+          <t>2026-05-27 00:00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="347">
+      <c r="A347" t="inlineStr">
+        <is>
+          <t>2565923</t>
+        </is>
+      </c>
+      <c r="B347" t="inlineStr">
+        <is>
+          <t>EF4-0232195-6</t>
+        </is>
+      </c>
+      <c r="C347" t="inlineStr">
+        <is>
+          <t>Vessel, Container</t>
+        </is>
+      </c>
+      <c r="D347" t="inlineStr"/>
+      <c r="E347" t="inlineStr">
+        <is>
+          <t>9903.03.06</t>
+        </is>
+      </c>
+      <c r="F347" t="inlineStr">
+        <is>
+          <t>S122 EXCL,IRN/STL/ALUM,DERIV</t>
+        </is>
+      </c>
+      <c r="G347" t="inlineStr">
+        <is>
+          <t>003</t>
+        </is>
+      </c>
+      <c r="H347" t="inlineStr">
+        <is>
+          <t>9903.03.06</t>
+        </is>
+      </c>
+      <c r="I347" t="inlineStr">
+        <is>
+          <t>9903.82.02,7216.33.0090</t>
+        </is>
+      </c>
+      <c r="J347" t="inlineStr">
+        <is>
+          <t>MAHA USA LLC</t>
+        </is>
+      </c>
+      <c r="K347" t="inlineStr">
+        <is>
+          <t>MAHUSA</t>
+        </is>
+      </c>
+      <c r="L347" t="inlineStr">
+        <is>
+          <t>52-213556300</t>
+        </is>
+      </c>
+      <c r="M347" t="inlineStr">
         <is>
           <t>2026-06-20 00:00:00</t>
         </is>
       </c>
-      <c r="O340" t="inlineStr">
-        <is>
-          <t>P. IONNOU G ZARKADIS QE</t>
-        </is>
-      </c>
-      <c r="P340" t="inlineStr">
-        <is>
-          <t>P. IONNOU G ZARKADIS QE</t>
-        </is>
-      </c>
-      <c r="Q340" t="inlineStr">
+      <c r="N347" t="inlineStr">
+        <is>
+          <t>2026-06-21 00:00:00</t>
+        </is>
+      </c>
+      <c r="O347" t="inlineStr">
+        <is>
+          <t>THYSSENKRUPP SCHULTE GMBH</t>
+        </is>
+      </c>
+      <c r="P347" t="inlineStr">
+        <is>
+          <t>THYSSENKRUPP SCHULTE GMBH</t>
+        </is>
+      </c>
+      <c r="Q347" t="inlineStr">
+        <is>
+          <t>2026-05-27 00:00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="348">
+      <c r="A348" t="inlineStr">
+        <is>
+          <t>2566146</t>
+        </is>
+      </c>
+      <c r="B348" t="inlineStr">
+        <is>
+          <t>EF4-0232246-7</t>
+        </is>
+      </c>
+      <c r="C348" t="inlineStr">
+        <is>
+          <t>Vessel, Container</t>
+        </is>
+      </c>
+      <c r="D348" t="inlineStr"/>
+      <c r="E348" t="inlineStr">
+        <is>
+          <t>9903.03.01</t>
+        </is>
+      </c>
+      <c r="F348" t="inlineStr">
+        <is>
+          <t>SECTION 122 - 10% DUTY</t>
+        </is>
+      </c>
+      <c r="G348" t="inlineStr">
+        <is>
+          <t>001</t>
+        </is>
+      </c>
+      <c r="H348" t="inlineStr">
+        <is>
+          <t>9903.03.01</t>
+        </is>
+      </c>
+      <c r="I348" t="inlineStr">
+        <is>
+          <t>1109.00.9010</t>
+        </is>
+      </c>
+      <c r="J348" t="inlineStr">
+        <is>
+          <t>ROYAL INGREDIENTS GROUP BV</t>
+        </is>
+      </c>
+      <c r="K348" t="inlineStr">
+        <is>
+          <t>ROYINGRE</t>
+        </is>
+      </c>
+      <c r="L348" t="inlineStr">
+        <is>
+          <t>074601-00962</t>
+        </is>
+      </c>
+      <c r="M348" t="inlineStr">
+        <is>
+          <t>2026-06-22 00:00:00</t>
+        </is>
+      </c>
+      <c r="N348" t="inlineStr">
+        <is>
+          <t>2026-06-21 00:00:00</t>
+        </is>
+      </c>
+      <c r="O348" t="inlineStr">
+        <is>
+          <t>KROENER-STARKE BIO GMBH</t>
+        </is>
+      </c>
+      <c r="P348" t="inlineStr">
+        <is>
+          <t>KROENER-STARKE BIO GMBH</t>
+        </is>
+      </c>
+      <c r="Q348" t="inlineStr">
+        <is>
+          <t>2026-06-01 00:00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="349">
+      <c r="A349" t="inlineStr">
+        <is>
+          <t>2566173</t>
+        </is>
+      </c>
+      <c r="B349" t="inlineStr">
+        <is>
+          <t>EF4-0232274-9</t>
+        </is>
+      </c>
+      <c r="C349" t="inlineStr">
+        <is>
+          <t>Vessel, Container</t>
+        </is>
+      </c>
+      <c r="D349" t="inlineStr"/>
+      <c r="E349" t="inlineStr">
+        <is>
+          <t>9903.03.01</t>
+        </is>
+      </c>
+      <c r="F349" t="inlineStr">
+        <is>
+          <t>SECTION 122 - 10% DUTY</t>
+        </is>
+      </c>
+      <c r="G349" t="inlineStr">
+        <is>
+          <t>001</t>
+        </is>
+      </c>
+      <c r="H349" t="inlineStr">
+        <is>
+          <t>9903.03.01</t>
+        </is>
+      </c>
+      <c r="I349" t="inlineStr">
+        <is>
+          <t>1109.00.9020</t>
+        </is>
+      </c>
+      <c r="J349" t="inlineStr">
+        <is>
+          <t>ROYAL INGREDIENTS GROUP BV</t>
+        </is>
+      </c>
+      <c r="K349" t="inlineStr">
+        <is>
+          <t>ROYINGRE</t>
+        </is>
+      </c>
+      <c r="L349" t="inlineStr">
+        <is>
+          <t>074601-00962</t>
+        </is>
+      </c>
+      <c r="M349" t="inlineStr">
+        <is>
+          <t>2026-06-21 00:00:00</t>
+        </is>
+      </c>
+      <c r="N349" t="inlineStr">
+        <is>
+          <t>2026-06-21 00:00:00</t>
+        </is>
+      </c>
+      <c r="O349" t="inlineStr">
+        <is>
+          <t>JACKERING MUHLEN UND NAHRMITTELWERK</t>
+        </is>
+      </c>
+      <c r="P349" t="inlineStr">
+        <is>
+          <t>JACKERING MUHLEN UND NAHRMITTELWERKE GMBH</t>
+        </is>
+      </c>
+      <c r="Q349" t="inlineStr">
+        <is>
+          <t>2026-06-01 00:00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="350">
+      <c r="A350" t="inlineStr">
+        <is>
+          <t>2565864</t>
+        </is>
+      </c>
+      <c r="B350" t="inlineStr">
+        <is>
+          <t>EF4-0232315-0</t>
+        </is>
+      </c>
+      <c r="C350" t="inlineStr">
+        <is>
+          <t>Vessel, Container</t>
+        </is>
+      </c>
+      <c r="D350" t="inlineStr"/>
+      <c r="E350" t="inlineStr">
+        <is>
+          <t>9903.03.01</t>
+        </is>
+      </c>
+      <c r="F350" t="inlineStr">
+        <is>
+          <t>SECTION 122 - 10% DUTY</t>
+        </is>
+      </c>
+      <c r="G350" t="inlineStr">
+        <is>
+          <t>001</t>
+        </is>
+      </c>
+      <c r="H350" t="inlineStr">
+        <is>
+          <t>9903.03.01</t>
+        </is>
+      </c>
+      <c r="I350" t="inlineStr">
+        <is>
+          <t>1109.00.9020</t>
+        </is>
+      </c>
+      <c r="J350" t="inlineStr">
+        <is>
+          <t>ROYAL INGREDIENTS GROUP BV</t>
+        </is>
+      </c>
+      <c r="K350" t="inlineStr">
+        <is>
+          <t>ROYINGRE</t>
+        </is>
+      </c>
+      <c r="L350" t="inlineStr">
+        <is>
+          <t>074601-00962</t>
+        </is>
+      </c>
+      <c r="M350" t="inlineStr">
+        <is>
+          <t>2026-06-20 00:00:00</t>
+        </is>
+      </c>
+      <c r="N350" t="inlineStr">
+        <is>
+          <t>2026-06-21 00:00:00</t>
+        </is>
+      </c>
+      <c r="O350" t="inlineStr">
+        <is>
+          <t>ROQUETTE FRERES</t>
+        </is>
+      </c>
+      <c r="P350" t="inlineStr">
+        <is>
+          <t>ROQUETTE FRERES</t>
+        </is>
+      </c>
+      <c r="Q350" t="inlineStr">
+        <is>
+          <t>2026-05-14 00:00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="351">
+      <c r="A351" t="inlineStr">
+        <is>
+          <t>2566183</t>
+        </is>
+      </c>
+      <c r="B351" t="inlineStr">
+        <is>
+          <t>EF4-0232343-2</t>
+        </is>
+      </c>
+      <c r="C351" t="inlineStr">
+        <is>
+          <t>Vessel, Container</t>
+        </is>
+      </c>
+      <c r="D351" t="inlineStr"/>
+      <c r="E351" t="inlineStr">
+        <is>
+          <t>9903.03.01</t>
+        </is>
+      </c>
+      <c r="F351" t="inlineStr">
+        <is>
+          <t>SECTION 122 - 10% DUTY</t>
+        </is>
+      </c>
+      <c r="G351" t="inlineStr">
+        <is>
+          <t>001</t>
+        </is>
+      </c>
+      <c r="H351" t="inlineStr">
+        <is>
+          <t>9903.03.01</t>
+        </is>
+      </c>
+      <c r="I351" t="inlineStr">
+        <is>
+          <t>2106.90.9998</t>
+        </is>
+      </c>
+      <c r="J351" t="inlineStr">
+        <is>
+          <t>DOBLA USA MFG LLC</t>
+        </is>
+      </c>
+      <c r="K351" t="inlineStr">
+        <is>
+          <t>DOBUSA</t>
+        </is>
+      </c>
+      <c r="L351" t="inlineStr">
+        <is>
+          <t>41-218954800</t>
+        </is>
+      </c>
+      <c r="M351" t="inlineStr">
+        <is>
+          <t>2026-06-21 00:00:00</t>
+        </is>
+      </c>
+      <c r="N351" t="inlineStr">
+        <is>
+          <t>2026-06-21 00:00:00</t>
+        </is>
+      </c>
+      <c r="O351" t="inlineStr">
+        <is>
+          <t>IRCA SRL</t>
+        </is>
+      </c>
+      <c r="P351" t="inlineStr">
+        <is>
+          <t>IRCA SRL</t>
+        </is>
+      </c>
+      <c r="Q351" t="inlineStr">
+        <is>
+          <t>2026-06-04 00:00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="352">
+      <c r="A352" t="inlineStr">
+        <is>
+          <t>2566264</t>
+        </is>
+      </c>
+      <c r="B352" t="inlineStr">
+        <is>
+          <t>EF4-0232584-1</t>
+        </is>
+      </c>
+      <c r="C352" t="inlineStr">
+        <is>
+          <t>Vessel, Container</t>
+        </is>
+      </c>
+      <c r="D352" t="inlineStr"/>
+      <c r="E352" t="inlineStr">
+        <is>
+          <t>9903.03.01</t>
+        </is>
+      </c>
+      <c r="F352" t="inlineStr">
+        <is>
+          <t>SECTION 122 - 10% DUTY</t>
+        </is>
+      </c>
+      <c r="G352" t="inlineStr">
+        <is>
+          <t>001</t>
+        </is>
+      </c>
+      <c r="H352" t="inlineStr">
+        <is>
+          <t>9903.03.01</t>
+        </is>
+      </c>
+      <c r="I352" t="inlineStr">
+        <is>
+          <t>3815.90.5000</t>
+        </is>
+      </c>
+      <c r="J352" t="inlineStr">
+        <is>
+          <t>JOBACHEM CORPORATION</t>
+        </is>
+      </c>
+      <c r="K352" t="inlineStr">
+        <is>
+          <t>JOBLP01</t>
+        </is>
+      </c>
+      <c r="L352" t="inlineStr">
+        <is>
+          <t>32-052169200</t>
+        </is>
+      </c>
+      <c r="M352" t="inlineStr">
+        <is>
+          <t>2026-06-22 00:00:00</t>
+        </is>
+      </c>
+      <c r="N352" t="inlineStr">
+        <is>
+          <t>2026-06-21 00:00:00</t>
+        </is>
+      </c>
+      <c r="O352" t="inlineStr">
+        <is>
+          <t>JOBACHEM GMBH</t>
+        </is>
+      </c>
+      <c r="P352" t="inlineStr">
+        <is>
+          <t>JOBACHEM GMBH</t>
+        </is>
+      </c>
+      <c r="Q352" t="inlineStr">
+        <is>
+          <t>2026-06-06 00:00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="353">
+      <c r="A353" t="inlineStr">
+        <is>
+          <t>2566264</t>
+        </is>
+      </c>
+      <c r="B353" t="inlineStr">
+        <is>
+          <t>EF4-0232584-1</t>
+        </is>
+      </c>
+      <c r="C353" t="inlineStr">
+        <is>
+          <t>Vessel, Container</t>
+        </is>
+      </c>
+      <c r="D353" t="inlineStr"/>
+      <c r="E353" t="inlineStr">
+        <is>
+          <t>9903.03.01</t>
+        </is>
+      </c>
+      <c r="F353" t="inlineStr">
+        <is>
+          <t>SECTION 122 - 10% DUTY</t>
+        </is>
+      </c>
+      <c r="G353" t="inlineStr">
+        <is>
+          <t>002</t>
+        </is>
+      </c>
+      <c r="H353" t="inlineStr">
+        <is>
+          <t>9903.03.01</t>
+        </is>
+      </c>
+      <c r="I353" t="inlineStr">
+        <is>
+          <t>2916.14.2050</t>
+        </is>
+      </c>
+      <c r="J353" t="inlineStr">
+        <is>
+          <t>JOBACHEM CORPORATION</t>
+        </is>
+      </c>
+      <c r="K353" t="inlineStr">
+        <is>
+          <t>JOBLP01</t>
+        </is>
+      </c>
+      <c r="L353" t="inlineStr">
+        <is>
+          <t>32-052169200</t>
+        </is>
+      </c>
+      <c r="M353" t="inlineStr">
+        <is>
+          <t>2026-06-22 00:00:00</t>
+        </is>
+      </c>
+      <c r="N353" t="inlineStr">
+        <is>
+          <t>2026-06-21 00:00:00</t>
+        </is>
+      </c>
+      <c r="O353" t="inlineStr">
+        <is>
+          <t>JOBACHEM GMBH</t>
+        </is>
+      </c>
+      <c r="P353" t="inlineStr">
+        <is>
+          <t>JOBACHEM GMBH</t>
+        </is>
+      </c>
+      <c r="Q353" t="inlineStr">
         <is>
           <t>2026-06-06 00:00:00</t>
         </is>

--- a/trimika_data.xlsx
+++ b/trimika_data.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q353"/>
+  <dimension ref="A1:Q370"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -25661,17 +25661,17 @@
     <row r="303">
       <c r="A303" t="inlineStr">
         <is>
-          <t>2565907</t>
+          <t>2615809</t>
         </is>
       </c>
       <c r="B303" t="inlineStr">
         <is>
-          <t>EF4-0232496-8</t>
+          <t>EF4-0232557-7</t>
         </is>
       </c>
       <c r="C303" t="inlineStr">
         <is>
-          <t>Vessel, Container</t>
+          <t>Truck, Non-container</t>
         </is>
       </c>
       <c r="D303" t="inlineStr">
@@ -25681,12 +25681,12 @@
       </c>
       <c r="E303" t="inlineStr">
         <is>
-          <t>9903.03.06</t>
+          <t>9903.03.01</t>
         </is>
       </c>
       <c r="F303" t="inlineStr">
         <is>
-          <t>S122 EXCL,IRN/STL/ALUM,DERIV</t>
+          <t>SECTION 122 - 10% DUTY</t>
         </is>
       </c>
       <c r="G303" t="inlineStr">
@@ -25696,64 +25696,64 @@
       </c>
       <c r="H303" t="inlineStr">
         <is>
-          <t>9903.03.06</t>
+          <t>9903.03.01</t>
         </is>
       </c>
       <c r="I303" t="inlineStr">
         <is>
-          <t>9903.82.02,7222.20.0043</t>
+          <t>8483.40.5010</t>
         </is>
       </c>
       <c r="J303" t="inlineStr">
         <is>
-          <t>MESHA STEELS  LLC</t>
+          <t>AUMUND CORPORATION</t>
         </is>
       </c>
       <c r="K303" t="inlineStr">
         <is>
-          <t>MESSTE</t>
+          <t>AUMCOR</t>
         </is>
       </c>
       <c r="L303" t="inlineStr">
         <is>
-          <t>20-274801900</t>
+          <t>58-138896800</t>
         </is>
       </c>
       <c r="M303" t="inlineStr">
         <is>
+          <t>2026-06-16 00:00:00</t>
+        </is>
+      </c>
+      <c r="N303" t="inlineStr">
+        <is>
           <t>2026-06-17 00:00:00</t>
         </is>
       </c>
-      <c r="N303" t="inlineStr">
-        <is>
-          <t>2026-06-17 00:00:00</t>
-        </is>
-      </c>
       <c r="O303" t="inlineStr">
         <is>
-          <t>BHANSALI BRIGHT BARS PVT. LTD.</t>
+          <t>AUMUND FOERDERTECHNIK GMBH</t>
         </is>
       </c>
       <c r="P303" t="inlineStr">
         <is>
-          <t>BHANSALI BRIGHT BARS PVT. LTD.</t>
+          <t>AUMUND FOERDERTECHNIK GMBH</t>
         </is>
       </c>
       <c r="Q303" t="inlineStr">
         <is>
-          <t>2026-05-11 00:00:00</t>
+          <t>2026-06-16 00:00:00</t>
         </is>
       </c>
     </row>
     <row r="304">
       <c r="A304" t="inlineStr">
         <is>
-          <t>2565907</t>
+          <t>2565634</t>
         </is>
       </c>
       <c r="B304" t="inlineStr">
         <is>
-          <t>EF4-0232496-8</t>
+          <t>EF4-0231631-1</t>
         </is>
       </c>
       <c r="C304" t="inlineStr">
@@ -25761,98 +25761,90 @@
           <t>Vessel, Container</t>
         </is>
       </c>
-      <c r="D304" t="inlineStr">
-        <is>
-          <t>V0413937900</t>
-        </is>
-      </c>
+      <c r="D304" t="inlineStr"/>
       <c r="E304" t="inlineStr">
         <is>
-          <t>9903.03.06</t>
+          <t>9903.03.01</t>
         </is>
       </c>
       <c r="F304" t="inlineStr">
         <is>
-          <t>S122 EXCL,IRN/STL/ALUM,DERIV</t>
+          <t>SECTION 122 - 10% DUTY</t>
         </is>
       </c>
       <c r="G304" t="inlineStr">
         <is>
-          <t>002</t>
+          <t>001</t>
         </is>
       </c>
       <c r="H304" t="inlineStr">
         <is>
-          <t>9903.03.06</t>
+          <t>9903.03.01</t>
         </is>
       </c>
       <c r="I304" t="inlineStr">
         <is>
-          <t>9903.82.02,7222.20.0073</t>
+          <t>8438.90.9060</t>
         </is>
       </c>
       <c r="J304" t="inlineStr">
         <is>
-          <t>MESHA STEELS  LLC</t>
+          <t>CANTRELL GAINCO GROUP INC</t>
         </is>
       </c>
       <c r="K304" t="inlineStr">
         <is>
-          <t>MESSTE</t>
+          <t>CANGAI01</t>
         </is>
       </c>
       <c r="L304" t="inlineStr">
         <is>
-          <t>20-274801900</t>
+          <t>31-151121700</t>
         </is>
       </c>
       <c r="M304" t="inlineStr">
         <is>
-          <t>2026-06-17 00:00:00</t>
+          <t>2026-06-18 00:00:00</t>
         </is>
       </c>
       <c r="N304" t="inlineStr">
         <is>
-          <t>2026-06-17 00:00:00</t>
+          <t>2026-06-18 00:00:00</t>
         </is>
       </c>
       <c r="O304" t="inlineStr">
         <is>
-          <t>BHANSALI BRIGHT BARS PVT. LTD.</t>
+          <t>O E CO LTD</t>
         </is>
       </c>
       <c r="P304" t="inlineStr">
         <is>
-          <t>BHANSALI BRIGHT BARS PVT. LTD.</t>
+          <t>O E CO LTD</t>
         </is>
       </c>
       <c r="Q304" t="inlineStr">
         <is>
-          <t>2026-05-11 00:00:00</t>
+          <t>2026-05-05 00:00:00</t>
         </is>
       </c>
     </row>
     <row r="305">
       <c r="A305" t="inlineStr">
         <is>
-          <t>2615809</t>
+          <t>2565782</t>
         </is>
       </c>
       <c r="B305" t="inlineStr">
         <is>
-          <t>EF4-0232557-7</t>
+          <t>EF4-0231677-4</t>
         </is>
       </c>
       <c r="C305" t="inlineStr">
         <is>
-          <t>Truck, Non-container</t>
-        </is>
-      </c>
-      <c r="D305" t="inlineStr">
-        <is>
-          <t>V0413937900</t>
-        </is>
-      </c>
+          <t>Vessel, Container</t>
+        </is>
+      </c>
+      <c r="D305" t="inlineStr"/>
       <c r="E305" t="inlineStr">
         <is>
           <t>9903.03.01</t>
@@ -25875,59 +25867,59 @@
       </c>
       <c r="I305" t="inlineStr">
         <is>
-          <t>8483.40.5010</t>
+          <t>3505.10.0092</t>
         </is>
       </c>
       <c r="J305" t="inlineStr">
         <is>
-          <t>AUMUND CORPORATION</t>
+          <t>ROYAL INGREDIENTS GROUP BV</t>
         </is>
       </c>
       <c r="K305" t="inlineStr">
         <is>
-          <t>AUMCOR</t>
+          <t>ROYINGRE</t>
         </is>
       </c>
       <c r="L305" t="inlineStr">
         <is>
-          <t>58-138896800</t>
+          <t>074601-00962</t>
         </is>
       </c>
       <c r="M305" t="inlineStr">
         <is>
-          <t>2026-06-16 00:00:00</t>
+          <t>2026-06-18 00:00:00</t>
         </is>
       </c>
       <c r="N305" t="inlineStr">
         <is>
-          <t>2026-06-17 00:00:00</t>
+          <t>2026-06-18 00:00:00</t>
         </is>
       </c>
       <c r="O305" t="inlineStr">
         <is>
-          <t>AUMUND FOERDERTECHNIK GMBH</t>
+          <t>EHM INTERTRADING CO LTD</t>
         </is>
       </c>
       <c r="P305" t="inlineStr">
         <is>
-          <t>AUMUND FOERDERTECHNIK GMBH</t>
+          <t>EHM INTERTRADING CO LTD</t>
         </is>
       </c>
       <c r="Q305" t="inlineStr">
         <is>
-          <t>2026-06-16 00:00:00</t>
+          <t>2026-05-05 00:00:00</t>
         </is>
       </c>
     </row>
     <row r="306">
       <c r="A306" t="inlineStr">
         <is>
-          <t>2565634</t>
+          <t>2565784</t>
         </is>
       </c>
       <c r="B306" t="inlineStr">
         <is>
-          <t>EF4-0231631-1</t>
+          <t>EF4-0231678-2</t>
         </is>
       </c>
       <c r="C306" t="inlineStr">
@@ -25958,22 +25950,22 @@
       </c>
       <c r="I306" t="inlineStr">
         <is>
-          <t>8438.90.9060</t>
+          <t>3505.10.0092</t>
         </is>
       </c>
       <c r="J306" t="inlineStr">
         <is>
-          <t>CANTRELL GAINCO GROUP INC</t>
+          <t>ROYAL INGREDIENTS GROUP BV</t>
         </is>
       </c>
       <c r="K306" t="inlineStr">
         <is>
-          <t>CANGAI01</t>
+          <t>ROYINGRE</t>
         </is>
       </c>
       <c r="L306" t="inlineStr">
         <is>
-          <t>31-151121700</t>
+          <t>074601-00962</t>
         </is>
       </c>
       <c r="M306" t="inlineStr">
@@ -25988,12 +25980,12 @@
       </c>
       <c r="O306" t="inlineStr">
         <is>
-          <t>O E CO LTD</t>
+          <t>EHM INTERTRADING CO LTD</t>
         </is>
       </c>
       <c r="P306" t="inlineStr">
         <is>
-          <t>O E CO LTD</t>
+          <t>EHM INTERTRADING CO LTD</t>
         </is>
       </c>
       <c r="Q306" t="inlineStr">
@@ -26005,12 +25997,12 @@
     <row r="307">
       <c r="A307" t="inlineStr">
         <is>
-          <t>2565782</t>
+          <t>2565894</t>
         </is>
       </c>
       <c r="B307" t="inlineStr">
         <is>
-          <t>EF4-0231677-4</t>
+          <t>EF4-0232004-0</t>
         </is>
       </c>
       <c r="C307" t="inlineStr">
@@ -26021,12 +26013,12 @@
       <c r="D307" t="inlineStr"/>
       <c r="E307" t="inlineStr">
         <is>
-          <t>9903.03.01</t>
+          <t>9903.03.03</t>
         </is>
       </c>
       <c r="F307" t="inlineStr">
         <is>
-          <t>SECTION 122 - 10% DUTY</t>
+          <t>S122 -EXCLUSION-EXEMPTED PRDTS</t>
         </is>
       </c>
       <c r="G307" t="inlineStr">
@@ -26036,27 +26028,27 @@
       </c>
       <c r="H307" t="inlineStr">
         <is>
-          <t>9903.03.01</t>
+          <t>9903.03.03</t>
         </is>
       </c>
       <c r="I307" t="inlineStr">
         <is>
-          <t>3505.10.0092</t>
+          <t>2930.90.9231</t>
         </is>
       </c>
       <c r="J307" t="inlineStr">
         <is>
-          <t>ROYAL INGREDIENTS GROUP BV</t>
+          <t>CASTLE CHEMICALS LTD</t>
         </is>
       </c>
       <c r="K307" t="inlineStr">
         <is>
-          <t>ROYINGRE</t>
+          <t>CASCHE01</t>
         </is>
       </c>
       <c r="L307" t="inlineStr">
         <is>
-          <t>074601-00962</t>
+          <t>151704-07138</t>
         </is>
       </c>
       <c r="M307" t="inlineStr">
@@ -26071,34 +26063,34 @@
       </c>
       <c r="O307" t="inlineStr">
         <is>
-          <t>EHM INTERTRADING CO LTD</t>
+          <t>HUBEI JIANGHAN NEW MATERIALS CO LTD</t>
         </is>
       </c>
       <c r="P307" t="inlineStr">
         <is>
-          <t>EHM INTERTRADING CO LTD</t>
+          <t>HUBEI JIANGHAN NEW MATERIALS CO LTD</t>
         </is>
       </c>
       <c r="Q307" t="inlineStr">
         <is>
-          <t>2026-05-05 00:00:00</t>
+          <t>2026-04-30 00:00:00</t>
         </is>
       </c>
     </row>
     <row r="308">
       <c r="A308" t="inlineStr">
         <is>
-          <t>2565784</t>
+          <t>2566078</t>
         </is>
       </c>
       <c r="B308" t="inlineStr">
         <is>
-          <t>EF4-0231678-2</t>
+          <t>EF4-0232219-4</t>
         </is>
       </c>
       <c r="C308" t="inlineStr">
         <is>
-          <t>Vessel, Container</t>
+          <t>Vessel, Non-container</t>
         </is>
       </c>
       <c r="D308" t="inlineStr"/>
@@ -26124,59 +26116,59 @@
       </c>
       <c r="I308" t="inlineStr">
         <is>
-          <t>3505.10.0092</t>
+          <t>8474.10.0010</t>
         </is>
       </c>
       <c r="J308" t="inlineStr">
         <is>
-          <t>ROYAL INGREDIENTS GROUP BV</t>
+          <t>EDGE INNOVATE (NI) LTD</t>
         </is>
       </c>
       <c r="K308" t="inlineStr">
         <is>
-          <t>ROYINGRE</t>
+          <t>EDGINN01</t>
         </is>
       </c>
       <c r="L308" t="inlineStr">
         <is>
-          <t>074601-00962</t>
+          <t>135501-01432</t>
         </is>
       </c>
       <c r="M308" t="inlineStr">
         <is>
+          <t>2026-06-17 00:00:00</t>
+        </is>
+      </c>
+      <c r="N308" t="inlineStr">
+        <is>
           <t>2026-06-18 00:00:00</t>
         </is>
       </c>
-      <c r="N308" t="inlineStr">
-        <is>
-          <t>2026-06-18 00:00:00</t>
-        </is>
-      </c>
       <c r="O308" t="inlineStr">
         <is>
-          <t>EHM INTERTRADING CO LTD</t>
+          <t>EDGE INNOVATE (NI) LTD</t>
         </is>
       </c>
       <c r="P308" t="inlineStr">
         <is>
-          <t>EHM INTERTRADING CO LTD</t>
+          <t>EDGE INNOVATE (NI) LTD</t>
         </is>
       </c>
       <c r="Q308" t="inlineStr">
         <is>
-          <t>2026-05-05 00:00:00</t>
+          <t>2026-05-29 00:00:00</t>
         </is>
       </c>
     </row>
     <row r="309">
       <c r="A309" t="inlineStr">
         <is>
-          <t>2565894</t>
+          <t>2565937</t>
         </is>
       </c>
       <c r="B309" t="inlineStr">
         <is>
-          <t>EF4-0232004-0</t>
+          <t>EF4-0232258-2</t>
         </is>
       </c>
       <c r="C309" t="inlineStr">
@@ -26187,12 +26179,12 @@
       <c r="D309" t="inlineStr"/>
       <c r="E309" t="inlineStr">
         <is>
-          <t>9903.03.03</t>
+          <t>9903.03.06</t>
         </is>
       </c>
       <c r="F309" t="inlineStr">
         <is>
-          <t>S122 -EXCLUSION-EXEMPTED PRDTS</t>
+          <t>S122 EXCL,IRN/STL/ALUM,DERIV</t>
         </is>
       </c>
       <c r="G309" t="inlineStr">
@@ -26202,115 +26194,115 @@
       </c>
       <c r="H309" t="inlineStr">
         <is>
-          <t>9903.03.03</t>
+          <t>9903.03.06</t>
         </is>
       </c>
       <c r="I309" t="inlineStr">
         <is>
-          <t>2930.90.9231</t>
+          <t>9903.82.22,8431.20.0000</t>
         </is>
       </c>
       <c r="J309" t="inlineStr">
         <is>
-          <t>CASTLE CHEMICALS LTD</t>
+          <t>MALLAGHAN (GA) INC.</t>
         </is>
       </c>
       <c r="K309" t="inlineStr">
         <is>
-          <t>CASCHE01</t>
+          <t>MALGA01</t>
         </is>
       </c>
       <c r="L309" t="inlineStr">
         <is>
-          <t>151704-07138</t>
+          <t>36-488102800</t>
         </is>
       </c>
       <c r="M309" t="inlineStr">
         <is>
+          <t>2026-06-20 00:00:00</t>
+        </is>
+      </c>
+      <c r="N309" t="inlineStr">
+        <is>
           <t>2026-06-18 00:00:00</t>
         </is>
       </c>
-      <c r="N309" t="inlineStr">
-        <is>
-          <t>2026-06-18 00:00:00</t>
-        </is>
-      </c>
       <c r="O309" t="inlineStr">
         <is>
-          <t>HUBEI JIANGHAN NEW MATERIALS CO LTD</t>
+          <t>MALLAGHAN ENGINEERING  LTD</t>
         </is>
       </c>
       <c r="P309" t="inlineStr">
         <is>
-          <t>HUBEI JIANGHAN NEW MATERIALS CO LTD</t>
+          <t>MALLAGHAN ENGINEERING  LTD</t>
         </is>
       </c>
       <c r="Q309" t="inlineStr">
         <is>
-          <t>2026-04-30 00:00:00</t>
+          <t>2026-05-17 00:00:00</t>
         </is>
       </c>
     </row>
     <row r="310">
       <c r="A310" t="inlineStr">
         <is>
-          <t>2566078</t>
+          <t>2565937</t>
         </is>
       </c>
       <c r="B310" t="inlineStr">
         <is>
-          <t>EF4-0232219-4</t>
+          <t>EF4-0232258-2</t>
         </is>
       </c>
       <c r="C310" t="inlineStr">
         <is>
-          <t>Vessel, Non-container</t>
+          <t>Vessel, Container</t>
         </is>
       </c>
       <c r="D310" t="inlineStr"/>
       <c r="E310" t="inlineStr">
         <is>
-          <t>9903.03.01</t>
+          <t>9903.03.06</t>
         </is>
       </c>
       <c r="F310" t="inlineStr">
         <is>
-          <t>SECTION 122 - 10% DUTY</t>
+          <t>S122 EXCL,IRN/STL/ALUM,DERIV</t>
         </is>
       </c>
       <c r="G310" t="inlineStr">
         <is>
-          <t>001</t>
+          <t>002</t>
         </is>
       </c>
       <c r="H310" t="inlineStr">
         <is>
-          <t>9903.03.01</t>
+          <t>9903.03.06</t>
         </is>
       </c>
       <c r="I310" t="inlineStr">
         <is>
-          <t>8474.10.0010</t>
+          <t>9903.82.22,8431.20.0000</t>
         </is>
       </c>
       <c r="J310" t="inlineStr">
         <is>
-          <t>EDGE INNOVATE (NI) LTD</t>
+          <t>MALLAGHAN (GA) INC.</t>
         </is>
       </c>
       <c r="K310" t="inlineStr">
         <is>
-          <t>EDGINN01</t>
+          <t>MALGA01</t>
         </is>
       </c>
       <c r="L310" t="inlineStr">
         <is>
-          <t>135501-01432</t>
+          <t>36-488102800</t>
         </is>
       </c>
       <c r="M310" t="inlineStr">
         <is>
-          <t>2026-06-17 00:00:00</t>
+          <t>2026-06-20 00:00:00</t>
         </is>
       </c>
       <c r="N310" t="inlineStr">
@@ -26320,17 +26312,17 @@
       </c>
       <c r="O310" t="inlineStr">
         <is>
-          <t>EDGE INNOVATE (NI) LTD</t>
+          <t>MALLAGHAN ENGINEERING  LTD</t>
         </is>
       </c>
       <c r="P310" t="inlineStr">
         <is>
-          <t>EDGE INNOVATE (NI) LTD</t>
+          <t>MALLAGHAN ENGINEERING  LTD</t>
         </is>
       </c>
       <c r="Q310" t="inlineStr">
         <is>
-          <t>2026-05-29 00:00:00</t>
+          <t>2026-05-17 00:00:00</t>
         </is>
       </c>
     </row>
@@ -26363,7 +26355,7 @@
       </c>
       <c r="G311" t="inlineStr">
         <is>
-          <t>001</t>
+          <t>003</t>
         </is>
       </c>
       <c r="H311" t="inlineStr">
@@ -26420,12 +26412,12 @@
     <row r="312">
       <c r="A312" t="inlineStr">
         <is>
-          <t>2565937</t>
+          <t>2566105</t>
         </is>
       </c>
       <c r="B312" t="inlineStr">
         <is>
-          <t>EF4-0232258-2</t>
+          <t>EF4-0232283-0</t>
         </is>
       </c>
       <c r="C312" t="inlineStr">
@@ -26436,47 +26428,47 @@
       <c r="D312" t="inlineStr"/>
       <c r="E312" t="inlineStr">
         <is>
-          <t>9903.03.06</t>
+          <t>9903.03.01</t>
         </is>
       </c>
       <c r="F312" t="inlineStr">
         <is>
-          <t>S122 EXCL,IRN/STL/ALUM,DERIV</t>
+          <t>SECTION 122 - 10% DUTY</t>
         </is>
       </c>
       <c r="G312" t="inlineStr">
         <is>
-          <t>002</t>
+          <t>001</t>
         </is>
       </c>
       <c r="H312" t="inlineStr">
         <is>
-          <t>9903.03.06</t>
+          <t>9903.03.01</t>
         </is>
       </c>
       <c r="I312" t="inlineStr">
         <is>
-          <t>9903.82.22,8431.20.0000</t>
+          <t>3920.61.0000</t>
         </is>
       </c>
       <c r="J312" t="inlineStr">
         <is>
-          <t>MALLAGHAN (GA) INC.</t>
+          <t>TUBUS BAUER GMBH</t>
         </is>
       </c>
       <c r="K312" t="inlineStr">
         <is>
-          <t>MALGA01</t>
+          <t>TUBBAU01</t>
         </is>
       </c>
       <c r="L312" t="inlineStr">
         <is>
-          <t>36-488102800</t>
+          <t>091601-00584</t>
         </is>
       </c>
       <c r="M312" t="inlineStr">
         <is>
-          <t>2026-06-20 00:00:00</t>
+          <t>2026-06-18 00:00:00</t>
         </is>
       </c>
       <c r="N312" t="inlineStr">
@@ -26486,29 +26478,29 @@
       </c>
       <c r="O312" t="inlineStr">
         <is>
-          <t>MALLAGHAN ENGINEERING  LTD</t>
+          <t>TUBUS BAUER GMBH</t>
         </is>
       </c>
       <c r="P312" t="inlineStr">
         <is>
-          <t>MALLAGHAN ENGINEERING  LTD</t>
+          <t>TUBUS BAUER GMBH</t>
         </is>
       </c>
       <c r="Q312" t="inlineStr">
         <is>
-          <t>2026-05-17 00:00:00</t>
+          <t>2026-06-02 00:00:00</t>
         </is>
       </c>
     </row>
     <row r="313">
       <c r="A313" t="inlineStr">
         <is>
-          <t>2565937</t>
+          <t>2566265</t>
         </is>
       </c>
       <c r="B313" t="inlineStr">
         <is>
-          <t>EF4-0232258-2</t>
+          <t>EF4-0232362-2</t>
         </is>
       </c>
       <c r="C313" t="inlineStr">
@@ -26519,47 +26511,47 @@
       <c r="D313" t="inlineStr"/>
       <c r="E313" t="inlineStr">
         <is>
-          <t>9903.03.06</t>
+          <t>9903.03.01</t>
         </is>
       </c>
       <c r="F313" t="inlineStr">
         <is>
-          <t>S122 EXCL,IRN/STL/ALUM,DERIV</t>
+          <t>SECTION 122 - 10% DUTY</t>
         </is>
       </c>
       <c r="G313" t="inlineStr">
         <is>
-          <t>003</t>
+          <t>001</t>
         </is>
       </c>
       <c r="H313" t="inlineStr">
         <is>
-          <t>9903.03.06</t>
+          <t>9903.03.01</t>
         </is>
       </c>
       <c r="I313" t="inlineStr">
         <is>
-          <t>9903.82.22,8431.20.0000</t>
+          <t>9903.82.01,8424.90.9080</t>
         </is>
       </c>
       <c r="J313" t="inlineStr">
         <is>
-          <t>MALLAGHAN (GA) INC.</t>
+          <t>EISENMANN OF SOUTH CAROLINA INC</t>
         </is>
       </c>
       <c r="K313" t="inlineStr">
         <is>
-          <t>MALGA01</t>
+          <t>EISINC03</t>
         </is>
       </c>
       <c r="L313" t="inlineStr">
         <is>
-          <t>36-488102800</t>
+          <t>86-240963300</t>
         </is>
       </c>
       <c r="M313" t="inlineStr">
         <is>
-          <t>2026-06-20 00:00:00</t>
+          <t>2026-06-21 00:00:00</t>
         </is>
       </c>
       <c r="N313" t="inlineStr">
@@ -26569,29 +26561,29 @@
       </c>
       <c r="O313" t="inlineStr">
         <is>
-          <t>MALLAGHAN ENGINEERING  LTD</t>
+          <t>EISENMANN GMBH</t>
         </is>
       </c>
       <c r="P313" t="inlineStr">
         <is>
-          <t>MALLAGHAN ENGINEERING  LTD</t>
+          <t>EISENMANN GMBH</t>
         </is>
       </c>
       <c r="Q313" t="inlineStr">
         <is>
-          <t>2026-05-17 00:00:00</t>
+          <t>2026-06-06 00:00:00</t>
         </is>
       </c>
     </row>
     <row r="314">
       <c r="A314" t="inlineStr">
         <is>
-          <t>2566105</t>
+          <t>2566155</t>
         </is>
       </c>
       <c r="B314" t="inlineStr">
         <is>
-          <t>EF4-0232283-0</t>
+          <t>EF4-0232431-5</t>
         </is>
       </c>
       <c r="C314" t="inlineStr">
@@ -26602,12 +26594,12 @@
       <c r="D314" t="inlineStr"/>
       <c r="E314" t="inlineStr">
         <is>
-          <t>9903.03.01</t>
+          <t>9903.03.06</t>
         </is>
       </c>
       <c r="F314" t="inlineStr">
         <is>
-          <t>SECTION 122 - 10% DUTY</t>
+          <t>S122 EXCL,IRN/STL/ALUM,DERIV</t>
         </is>
       </c>
       <c r="G314" t="inlineStr">
@@ -26617,27 +26609,27 @@
       </c>
       <c r="H314" t="inlineStr">
         <is>
-          <t>9903.03.01</t>
+          <t>9903.03.06</t>
         </is>
       </c>
       <c r="I314" t="inlineStr">
         <is>
-          <t>3920.61.0000</t>
+          <t>9903.74.11,9903.94.53,8708.29.5160</t>
         </is>
       </c>
       <c r="J314" t="inlineStr">
         <is>
-          <t>TUBUS BAUER GMBH</t>
+          <t>BORGERS USA CORP</t>
         </is>
       </c>
       <c r="K314" t="inlineStr">
         <is>
-          <t>TUBBAU01</t>
+          <t>BORUSA</t>
         </is>
       </c>
       <c r="L314" t="inlineStr">
         <is>
-          <t>091601-00584</t>
+          <t>65-117296500</t>
         </is>
       </c>
       <c r="M314" t="inlineStr">
@@ -26652,29 +26644,29 @@
       </c>
       <c r="O314" t="inlineStr">
         <is>
-          <t>TUBUS BAUER GMBH</t>
+          <t>AUTONEUM CZ S.R.O.</t>
         </is>
       </c>
       <c r="P314" t="inlineStr">
         <is>
-          <t>TUBUS BAUER GMBH</t>
+          <t>AUTONEUM CZ S.R.O.</t>
         </is>
       </c>
       <c r="Q314" t="inlineStr">
         <is>
-          <t>2026-06-02 00:00:00</t>
+          <t>2026-06-06 00:00:00</t>
         </is>
       </c>
     </row>
     <row r="315">
       <c r="A315" t="inlineStr">
         <is>
-          <t>2566265</t>
+          <t>2566155</t>
         </is>
       </c>
       <c r="B315" t="inlineStr">
         <is>
-          <t>EF4-0232362-2</t>
+          <t>EF4-0232431-5</t>
         </is>
       </c>
       <c r="C315" t="inlineStr">
@@ -26685,47 +26677,47 @@
       <c r="D315" t="inlineStr"/>
       <c r="E315" t="inlineStr">
         <is>
-          <t>9903.03.01</t>
+          <t>9903.03.06</t>
         </is>
       </c>
       <c r="F315" t="inlineStr">
         <is>
-          <t>SECTION 122 - 10% DUTY</t>
+          <t>S122 EXCL,IRN/STL/ALUM,DERIV</t>
         </is>
       </c>
       <c r="G315" t="inlineStr">
         <is>
-          <t>001</t>
+          <t>002</t>
         </is>
       </c>
       <c r="H315" t="inlineStr">
         <is>
-          <t>9903.03.01</t>
+          <t>9903.03.06</t>
         </is>
       </c>
       <c r="I315" t="inlineStr">
         <is>
-          <t>9903.82.01,8424.90.9080</t>
+          <t>9903.74.11,9903.94.53,8708.29.5160</t>
         </is>
       </c>
       <c r="J315" t="inlineStr">
         <is>
-          <t>EISENMANN OF SOUTH CAROLINA INC</t>
+          <t>BORGERS USA CORP</t>
         </is>
       </c>
       <c r="K315" t="inlineStr">
         <is>
-          <t>EISINC03</t>
+          <t>BORUSA</t>
         </is>
       </c>
       <c r="L315" t="inlineStr">
         <is>
-          <t>86-240963300</t>
+          <t>65-117296500</t>
         </is>
       </c>
       <c r="M315" t="inlineStr">
         <is>
-          <t>2026-06-21 00:00:00</t>
+          <t>2026-06-18 00:00:00</t>
         </is>
       </c>
       <c r="N315" t="inlineStr">
@@ -26735,12 +26727,12 @@
       </c>
       <c r="O315" t="inlineStr">
         <is>
-          <t>EISENMANN GMBH</t>
+          <t>AUTONEUM CZ S.R.O.</t>
         </is>
       </c>
       <c r="P315" t="inlineStr">
         <is>
-          <t>EISENMANN GMBH</t>
+          <t>AUTONEUM CZ S.R.O.</t>
         </is>
       </c>
       <c r="Q315" t="inlineStr">
@@ -26778,7 +26770,7 @@
       </c>
       <c r="G316" t="inlineStr">
         <is>
-          <t>001</t>
+          <t>003</t>
         </is>
       </c>
       <c r="H316" t="inlineStr">
@@ -26861,7 +26853,7 @@
       </c>
       <c r="G317" t="inlineStr">
         <is>
-          <t>002</t>
+          <t>004</t>
         </is>
       </c>
       <c r="H317" t="inlineStr">
@@ -26918,95 +26910,95 @@
     <row r="318">
       <c r="A318" t="inlineStr">
         <is>
-          <t>2566155</t>
+          <t>4539433</t>
         </is>
       </c>
       <c r="B318" t="inlineStr">
         <is>
-          <t>EF4-0232431-5</t>
+          <t>EF4-0232434-9</t>
         </is>
       </c>
       <c r="C318" t="inlineStr">
         <is>
-          <t>Vessel, Container</t>
+          <t>Air, Non-container</t>
         </is>
       </c>
       <c r="D318" t="inlineStr"/>
       <c r="E318" t="inlineStr">
         <is>
-          <t>9903.03.06</t>
+          <t>9903.88.03</t>
         </is>
       </c>
       <c r="F318" t="inlineStr">
         <is>
-          <t>S122 EXCL,IRN/STL/ALUM,DERIV</t>
+          <t>ARTICLE OF CHINA,US NTE 20(F)</t>
         </is>
       </c>
       <c r="G318" t="inlineStr">
         <is>
-          <t>003</t>
+          <t>001</t>
         </is>
       </c>
       <c r="H318" t="inlineStr">
         <is>
-          <t>9903.03.06</t>
+          <t>9903.88.03</t>
         </is>
       </c>
       <c r="I318" t="inlineStr">
         <is>
-          <t>9903.74.11,9903.94.53,8708.29.5160</t>
+          <t>9903.03.03,2926.90.4300</t>
         </is>
       </c>
       <c r="J318" t="inlineStr">
         <is>
-          <t>BORGERS USA CORP</t>
+          <t>MAYZO INC</t>
         </is>
       </c>
       <c r="K318" t="inlineStr">
         <is>
-          <t>BORUSA</t>
+          <t>MAYINC</t>
         </is>
       </c>
       <c r="L318" t="inlineStr">
         <is>
-          <t>65-117296500</t>
+          <t>62-129031200</t>
         </is>
       </c>
       <c r="M318" t="inlineStr">
         <is>
+          <t>2026-06-17 00:00:00</t>
+        </is>
+      </c>
+      <c r="N318" t="inlineStr">
+        <is>
           <t>2026-06-18 00:00:00</t>
         </is>
       </c>
-      <c r="N318" t="inlineStr">
-        <is>
-          <t>2026-06-18 00:00:00</t>
-        </is>
-      </c>
       <c r="O318" t="inlineStr">
         <is>
-          <t>AUTONEUM CZ S.R.O.</t>
+          <t>HANGZHOU DISHENG IMPORT &amp; EXPORT</t>
         </is>
       </c>
       <c r="P318" t="inlineStr">
         <is>
-          <t>AUTONEUM CZ S.R.O.</t>
+          <t>HANGZHOU DISHENG IMPORT &amp; EXPORT</t>
         </is>
       </c>
       <c r="Q318" t="inlineStr">
         <is>
-          <t>2026-06-06 00:00:00</t>
+          <t>2026-06-17 00:00:00</t>
         </is>
       </c>
     </row>
     <row r="319">
       <c r="A319" t="inlineStr">
         <is>
-          <t>2566155</t>
+          <t>2565798</t>
         </is>
       </c>
       <c r="B319" t="inlineStr">
         <is>
-          <t>EF4-0232431-5</t>
+          <t>EF4-0232494-3</t>
         </is>
       </c>
       <c r="C319" t="inlineStr">
@@ -27027,7 +27019,7 @@
       </c>
       <c r="G319" t="inlineStr">
         <is>
-          <t>004</t>
+          <t>001</t>
         </is>
       </c>
       <c r="H319" t="inlineStr">
@@ -27037,22 +27029,22 @@
       </c>
       <c r="I319" t="inlineStr">
         <is>
-          <t>9903.74.11,9903.94.53,8708.29.5160</t>
+          <t>9903.82.02,7222.20.0064</t>
         </is>
       </c>
       <c r="J319" t="inlineStr">
         <is>
-          <t>BORGERS USA CORP</t>
+          <t>MESHA STEELS  LLC</t>
         </is>
       </c>
       <c r="K319" t="inlineStr">
         <is>
-          <t>BORUSA</t>
+          <t>MESSTE</t>
         </is>
       </c>
       <c r="L319" t="inlineStr">
         <is>
-          <t>65-117296500</t>
+          <t>20-274801900</t>
         </is>
       </c>
       <c r="M319" t="inlineStr">
@@ -27067,45 +27059,45 @@
       </c>
       <c r="O319" t="inlineStr">
         <is>
-          <t>AUTONEUM CZ S.R.O.</t>
+          <t>BHANSALI BRIGHT BARS PVT. LTD.</t>
         </is>
       </c>
       <c r="P319" t="inlineStr">
         <is>
-          <t>AUTONEUM CZ S.R.O.</t>
+          <t>BHANSALI BRIGHT BARS PVT. LTD.</t>
         </is>
       </c>
       <c r="Q319" t="inlineStr">
         <is>
-          <t>2026-06-06 00:00:00</t>
+          <t>2026-05-12 00:00:00</t>
         </is>
       </c>
     </row>
     <row r="320">
       <c r="A320" t="inlineStr">
         <is>
-          <t>4539433</t>
+          <t>2565799</t>
         </is>
       </c>
       <c r="B320" t="inlineStr">
         <is>
-          <t>EF4-0232434-9</t>
+          <t>EF4-0232495-0</t>
         </is>
       </c>
       <c r="C320" t="inlineStr">
         <is>
-          <t>Air, Non-container</t>
+          <t>Vessel, Container</t>
         </is>
       </c>
       <c r="D320" t="inlineStr"/>
       <c r="E320" t="inlineStr">
         <is>
-          <t>9903.88.03</t>
+          <t>9903.03.06</t>
         </is>
       </c>
       <c r="F320" t="inlineStr">
         <is>
-          <t>ARTICLE OF CHINA,US NTE 20(F)</t>
+          <t>S122 EXCL,IRN/STL/ALUM,DERIV</t>
         </is>
       </c>
       <c r="G320" t="inlineStr">
@@ -27115,32 +27107,32 @@
       </c>
       <c r="H320" t="inlineStr">
         <is>
-          <t>9903.88.03</t>
+          <t>9903.03.06</t>
         </is>
       </c>
       <c r="I320" t="inlineStr">
         <is>
-          <t>9903.03.03,2926.90.4300</t>
+          <t>9903.82.02,7222.20.0062</t>
         </is>
       </c>
       <c r="J320" t="inlineStr">
         <is>
-          <t>MAYZO INC</t>
+          <t>MESHA STEELS  LLC</t>
         </is>
       </c>
       <c r="K320" t="inlineStr">
         <is>
-          <t>MAYINC</t>
+          <t>MESSTE</t>
         </is>
       </c>
       <c r="L320" t="inlineStr">
         <is>
-          <t>62-129031200</t>
+          <t>20-274801900</t>
         </is>
       </c>
       <c r="M320" t="inlineStr">
         <is>
-          <t>2026-06-17 00:00:00</t>
+          <t>2026-06-18 00:00:00</t>
         </is>
       </c>
       <c r="N320" t="inlineStr">
@@ -27150,29 +27142,29 @@
       </c>
       <c r="O320" t="inlineStr">
         <is>
-          <t>HANGZHOU DISHENG IMPORT &amp; EXPORT</t>
+          <t>BHANSALI BRIGHT BARS PVT. LTD.</t>
         </is>
       </c>
       <c r="P320" t="inlineStr">
         <is>
-          <t>HANGZHOU DISHENG IMPORT &amp; EXPORT</t>
+          <t>BHANSALI BRIGHT BARS PVT. LTD.</t>
         </is>
       </c>
       <c r="Q320" t="inlineStr">
         <is>
-          <t>2026-06-17 00:00:00</t>
+          <t>2026-05-12 00:00:00</t>
         </is>
       </c>
     </row>
     <row r="321">
       <c r="A321" t="inlineStr">
         <is>
-          <t>2565798</t>
+          <t>2565760</t>
         </is>
       </c>
       <c r="B321" t="inlineStr">
         <is>
-          <t>EF4-0232494-3</t>
+          <t>EF4-0231661-8</t>
         </is>
       </c>
       <c r="C321" t="inlineStr">
@@ -27183,12 +27175,12 @@
       <c r="D321" t="inlineStr"/>
       <c r="E321" t="inlineStr">
         <is>
-          <t>9903.03.06</t>
+          <t>9903.88.15</t>
         </is>
       </c>
       <c r="F321" t="inlineStr">
         <is>
-          <t>S122 EXCL,IRN/STL/ALUM,DERIV</t>
+          <t>ARTICLE OF CHINA,US NTE 20(R)</t>
         </is>
       </c>
       <c r="G321" t="inlineStr">
@@ -27198,64 +27190,64 @@
       </c>
       <c r="H321" t="inlineStr">
         <is>
-          <t>9903.03.06</t>
+          <t>9903.88.15</t>
         </is>
       </c>
       <c r="I321" t="inlineStr">
         <is>
-          <t>9903.82.02,7222.20.0064</t>
+          <t>9903.03.06,9903.82.09,8302.42.3015</t>
         </is>
       </c>
       <c r="J321" t="inlineStr">
         <is>
-          <t>MESHA STEELS  LLC</t>
+          <t>GRASS AMERICA INC</t>
         </is>
       </c>
       <c r="K321" t="inlineStr">
         <is>
-          <t>MESSTE</t>
+          <t>GRAAME</t>
         </is>
       </c>
       <c r="L321" t="inlineStr">
         <is>
-          <t>20-274801900</t>
+          <t>51-066023000</t>
         </is>
       </c>
       <c r="M321" t="inlineStr">
         <is>
-          <t>2026-06-18 00:00:00</t>
+          <t>2026-06-20 00:00:00</t>
         </is>
       </c>
       <c r="N321" t="inlineStr">
         <is>
-          <t>2026-06-18 00:00:00</t>
+          <t>2026-06-20 00:00:00</t>
         </is>
       </c>
       <c r="O321" t="inlineStr">
         <is>
-          <t>BHANSALI BRIGHT BARS PVT. LTD.</t>
+          <t>SACA PRECISION LTD</t>
         </is>
       </c>
       <c r="P321" t="inlineStr">
         <is>
-          <t>BHANSALI BRIGHT BARS PVT. LTD.</t>
+          <t>SACA PRECISION LTD</t>
         </is>
       </c>
       <c r="Q321" t="inlineStr">
         <is>
-          <t>2026-05-12 00:00:00</t>
+          <t>2026-05-05 00:00:00</t>
         </is>
       </c>
     </row>
     <row r="322">
       <c r="A322" t="inlineStr">
         <is>
-          <t>2565799</t>
+          <t>2565760</t>
         </is>
       </c>
       <c r="B322" t="inlineStr">
         <is>
-          <t>EF4-0232495-0</t>
+          <t>EF4-0231661-8</t>
         </is>
       </c>
       <c r="C322" t="inlineStr">
@@ -27266,84 +27258,84 @@
       <c r="D322" t="inlineStr"/>
       <c r="E322" t="inlineStr">
         <is>
-          <t>9903.03.06</t>
+          <t>9903.88.15</t>
         </is>
       </c>
       <c r="F322" t="inlineStr">
         <is>
-          <t>S122 EXCL,IRN/STL/ALUM,DERIV</t>
+          <t>ARTICLE OF CHINA,US NTE 20(R)</t>
         </is>
       </c>
       <c r="G322" t="inlineStr">
         <is>
-          <t>001</t>
+          <t>002</t>
         </is>
       </c>
       <c r="H322" t="inlineStr">
         <is>
-          <t>9903.03.06</t>
+          <t>9903.88.15</t>
         </is>
       </c>
       <c r="I322" t="inlineStr">
         <is>
-          <t>9903.82.02,7222.20.0062</t>
+          <t>9903.03.01,3926.30.5000</t>
         </is>
       </c>
       <c r="J322" t="inlineStr">
         <is>
-          <t>MESHA STEELS  LLC</t>
+          <t>GRASS AMERICA INC</t>
         </is>
       </c>
       <c r="K322" t="inlineStr">
         <is>
-          <t>MESSTE</t>
+          <t>GRAAME</t>
         </is>
       </c>
       <c r="L322" t="inlineStr">
         <is>
-          <t>20-274801900</t>
+          <t>51-066023000</t>
         </is>
       </c>
       <c r="M322" t="inlineStr">
         <is>
-          <t>2026-06-18 00:00:00</t>
+          <t>2026-06-20 00:00:00</t>
         </is>
       </c>
       <c r="N322" t="inlineStr">
         <is>
-          <t>2026-06-18 00:00:00</t>
+          <t>2026-06-20 00:00:00</t>
         </is>
       </c>
       <c r="O322" t="inlineStr">
         <is>
-          <t>BHANSALI BRIGHT BARS PVT. LTD.</t>
+          <t>SACA PRECISION LTD</t>
         </is>
       </c>
       <c r="P322" t="inlineStr">
         <is>
-          <t>BHANSALI BRIGHT BARS PVT. LTD.</t>
+          <t>SACA PRECISION LTD</t>
         </is>
       </c>
       <c r="Q322" t="inlineStr">
         <is>
-          <t>2026-05-12 00:00:00</t>
+          <t>2026-05-05 00:00:00</t>
         </is>
       </c>
     </row>
     <row r="323">
       <c r="A323" t="inlineStr">
         <is>
-          <t>2565760</t>
+          <t>2615656</t>
         </is>
       </c>
       <c r="B323" t="inlineStr">
         <is>
-          <t>EF4-0231661-8</t>
+          <t>EF4-0231976-0</t>
         </is>
       </c>
       <c r="C323" t="inlineStr">
         <is>
-          <t>Vessel, Container</t>
+          <t>Vessel, Non-container</t>
         </is>
       </c>
       <c r="D323" t="inlineStr"/>
@@ -27369,22 +27361,22 @@
       </c>
       <c r="I323" t="inlineStr">
         <is>
-          <t>9903.03.06,9903.82.09,8302.42.3015</t>
+          <t>9903.03.01,3926.90.9989</t>
         </is>
       </c>
       <c r="J323" t="inlineStr">
         <is>
-          <t>GRASS AMERICA INC</t>
+          <t>VISUAL CREATIONS, INC.</t>
         </is>
       </c>
       <c r="K323" t="inlineStr">
         <is>
-          <t>GRAAME</t>
+          <t>VISCRE</t>
         </is>
       </c>
       <c r="L323" t="inlineStr">
         <is>
-          <t>51-066023000</t>
+          <t>20-461602300</t>
         </is>
       </c>
       <c r="M323" t="inlineStr">
@@ -27399,128 +27391,128 @@
       </c>
       <c r="O323" t="inlineStr">
         <is>
-          <t>SACA PRECISION LTD</t>
+          <t>NINGBO SMART HIGH TECH INDUSTRIES L</t>
         </is>
       </c>
       <c r="P323" t="inlineStr">
         <is>
-          <t>SACA PRECISION LTD</t>
+          <t>NINGBO SMART HIGH TECH INDUSTRIES LTD</t>
         </is>
       </c>
       <c r="Q323" t="inlineStr">
         <is>
-          <t>2026-05-05 00:00:00</t>
+          <t>2026-05-12 00:00:00</t>
         </is>
       </c>
     </row>
     <row r="324">
       <c r="A324" t="inlineStr">
         <is>
-          <t>2565760</t>
+          <t>2615664</t>
         </is>
       </c>
       <c r="B324" t="inlineStr">
         <is>
-          <t>EF4-0231661-8</t>
+          <t>EF4-0231983-6</t>
         </is>
       </c>
       <c r="C324" t="inlineStr">
         <is>
-          <t>Vessel, Container</t>
+          <t>Vessel, Non-container</t>
         </is>
       </c>
       <c r="D324" t="inlineStr"/>
       <c r="E324" t="inlineStr">
         <is>
-          <t>9903.88.15</t>
+          <t>9903.88.01</t>
         </is>
       </c>
       <c r="F324" t="inlineStr">
         <is>
-          <t>ARTICLE OF CHINA,US NTE 20(R)</t>
+          <t>ARTICLE OF CHINA,US NTE 20(A)</t>
         </is>
       </c>
       <c r="G324" t="inlineStr">
         <is>
-          <t>002</t>
+          <t>001</t>
         </is>
       </c>
       <c r="H324" t="inlineStr">
         <is>
-          <t>9903.88.15</t>
+          <t>9903.88.01</t>
         </is>
       </c>
       <c r="I324" t="inlineStr">
         <is>
-          <t>9903.03.01,3926.30.5000</t>
+          <t>9903.03.06,9903.82.09,8482.10.5012</t>
         </is>
       </c>
       <c r="J324" t="inlineStr">
         <is>
-          <t>GRASS AMERICA INC</t>
+          <t>VISUAL CREATIONS, INC.</t>
         </is>
       </c>
       <c r="K324" t="inlineStr">
         <is>
-          <t>GRAAME</t>
+          <t>VISCRE</t>
         </is>
       </c>
       <c r="L324" t="inlineStr">
         <is>
-          <t>51-066023000</t>
+          <t>20-461602300</t>
         </is>
       </c>
       <c r="M324" t="inlineStr">
         <is>
+          <t>2026-06-11 00:00:00</t>
+        </is>
+      </c>
+      <c r="N324" t="inlineStr">
+        <is>
           <t>2026-06-20 00:00:00</t>
         </is>
       </c>
-      <c r="N324" t="inlineStr">
-        <is>
-          <t>2026-06-20 00:00:00</t>
-        </is>
-      </c>
       <c r="O324" t="inlineStr">
         <is>
-          <t>SACA PRECISION LTD</t>
+          <t>LINYU HANDWARE MANUFACTURE CO LTD</t>
         </is>
       </c>
       <c r="P324" t="inlineStr">
         <is>
-          <t>SACA PRECISION LTD</t>
+          <t>LINYU HANDWARE MANUFACTURE CO LTD</t>
         </is>
       </c>
       <c r="Q324" t="inlineStr">
         <is>
-          <t>2026-05-05 00:00:00</t>
+          <t>2026-05-15 00:00:00</t>
         </is>
       </c>
     </row>
     <row r="325">
       <c r="A325" t="inlineStr">
         <is>
-          <t>2615656</t>
+          <t>2566178</t>
         </is>
       </c>
       <c r="B325" t="inlineStr">
         <is>
-          <t>EF4-0231976-0</t>
+          <t>EF4-0232247-5</t>
         </is>
       </c>
       <c r="C325" t="inlineStr">
         <is>
-          <t>Vessel, Non-container</t>
+          <t>Vessel, Container</t>
         </is>
       </c>
       <c r="D325" t="inlineStr"/>
       <c r="E325" t="inlineStr">
         <is>
-          <t>9903.88.15</t>
+          <t>9903.03.01</t>
         </is>
       </c>
       <c r="F325" t="inlineStr">
         <is>
-          <t>ARTICLE OF CHINA,US NTE 20(R)</t>
+          <t>SECTION 122 - 10% DUTY</t>
         </is>
       </c>
       <c r="G325" t="inlineStr">
@@ -27530,27 +27522,27 @@
       </c>
       <c r="H325" t="inlineStr">
         <is>
-          <t>9903.88.15</t>
+          <t>9903.03.01</t>
         </is>
       </c>
       <c r="I325" t="inlineStr">
         <is>
-          <t>9903.03.01,3926.90.9989</t>
+          <t>1108.13.0010</t>
         </is>
       </c>
       <c r="J325" t="inlineStr">
         <is>
-          <t>VISUAL CREATIONS, INC.</t>
+          <t>ROYAL INGREDIENTS GROUP BV</t>
         </is>
       </c>
       <c r="K325" t="inlineStr">
         <is>
-          <t>VISCRE</t>
+          <t>ROYINGRE</t>
         </is>
       </c>
       <c r="L325" t="inlineStr">
         <is>
-          <t>20-461602300</t>
+          <t>074601-00962</t>
         </is>
       </c>
       <c r="M325" t="inlineStr">
@@ -27565,45 +27557,49 @@
       </c>
       <c r="O325" t="inlineStr">
         <is>
-          <t>NINGBO SMART HIGH TECH INDUSTRIES L</t>
+          <t>AKV LANGHOLT AMBA</t>
         </is>
       </c>
       <c r="P325" t="inlineStr">
         <is>
-          <t>NINGBO SMART HIGH TECH INDUSTRIES LTD</t>
+          <t>AKV LANGHOLT AMBA</t>
         </is>
       </c>
       <c r="Q325" t="inlineStr">
         <is>
-          <t>2026-05-12 00:00:00</t>
+          <t>2026-06-01 00:00:00</t>
         </is>
       </c>
     </row>
     <row r="326">
       <c r="A326" t="inlineStr">
         <is>
-          <t>2615664</t>
+          <t>2566229</t>
         </is>
       </c>
       <c r="B326" t="inlineStr">
         <is>
-          <t>EF4-0231983-6</t>
+          <t>EF4-0232249-1</t>
         </is>
       </c>
       <c r="C326" t="inlineStr">
         <is>
-          <t>Vessel, Non-container</t>
-        </is>
-      </c>
-      <c r="D326" t="inlineStr"/>
+          <t>Vessel, Container</t>
+        </is>
+      </c>
+      <c r="D326" t="inlineStr">
+        <is>
+          <t>V0710338448</t>
+        </is>
+      </c>
       <c r="E326" t="inlineStr">
         <is>
-          <t>9903.88.01</t>
+          <t>9903.03.01</t>
         </is>
       </c>
       <c r="F326" t="inlineStr">
         <is>
-          <t>ARTICLE OF CHINA,US NTE 20(A)</t>
+          <t>SECTION 122 - 10% DUTY</t>
         </is>
       </c>
       <c r="G326" t="inlineStr">
@@ -27613,32 +27609,32 @@
       </c>
       <c r="H326" t="inlineStr">
         <is>
-          <t>9903.88.01</t>
+          <t>9903.03.01</t>
         </is>
       </c>
       <c r="I326" t="inlineStr">
         <is>
-          <t>9903.03.06,9903.82.09,8482.10.5012</t>
+          <t>1108.13.0010</t>
         </is>
       </c>
       <c r="J326" t="inlineStr">
         <is>
-          <t>VISUAL CREATIONS, INC.</t>
+          <t>ROYAL INGREDIENTS GROUP BV</t>
         </is>
       </c>
       <c r="K326" t="inlineStr">
         <is>
-          <t>VISCRE</t>
+          <t>ROYINGRE</t>
         </is>
       </c>
       <c r="L326" t="inlineStr">
         <is>
-          <t>20-461602300</t>
+          <t>074601-00962</t>
         </is>
       </c>
       <c r="M326" t="inlineStr">
         <is>
-          <t>2026-06-11 00:00:00</t>
+          <t>2026-06-20 00:00:00</t>
         </is>
       </c>
       <c r="N326" t="inlineStr">
@@ -27648,29 +27644,29 @@
       </c>
       <c r="O326" t="inlineStr">
         <is>
-          <t>LINYU HANDWARE MANUFACTURE CO LTD</t>
+          <t>AKV LANGHOLT AMBA</t>
         </is>
       </c>
       <c r="P326" t="inlineStr">
         <is>
-          <t>LINYU HANDWARE MANUFACTURE CO LTD</t>
+          <t>AKV LANGHOLT AMBA</t>
         </is>
       </c>
       <c r="Q326" t="inlineStr">
         <is>
-          <t>2026-05-15 00:00:00</t>
+          <t>2026-06-01 00:00:00</t>
         </is>
       </c>
     </row>
     <row r="327">
       <c r="A327" t="inlineStr">
         <is>
-          <t>2566178</t>
+          <t>2566177</t>
         </is>
       </c>
       <c r="B327" t="inlineStr">
         <is>
-          <t>EF4-0232247-5</t>
+          <t>EF4-0232275-6</t>
         </is>
       </c>
       <c r="C327" t="inlineStr">
@@ -27678,7 +27674,11 @@
           <t>Vessel, Container</t>
         </is>
       </c>
-      <c r="D327" t="inlineStr"/>
+      <c r="D327" t="inlineStr">
+        <is>
+          <t>V0710338448</t>
+        </is>
+      </c>
       <c r="E327" t="inlineStr">
         <is>
           <t>9903.03.01</t>
@@ -27748,12 +27748,12 @@
     <row r="328">
       <c r="A328" t="inlineStr">
         <is>
-          <t>2566229</t>
+          <t>2566051</t>
         </is>
       </c>
       <c r="B328" t="inlineStr">
         <is>
-          <t>EF4-0232249-1</t>
+          <t>EF4-0232281-4</t>
         </is>
       </c>
       <c r="C328" t="inlineStr">
@@ -27763,7 +27763,7 @@
       </c>
       <c r="D328" t="inlineStr">
         <is>
-          <t>V0710338448</t>
+          <t>V0710349973</t>
         </is>
       </c>
       <c r="E328" t="inlineStr">
@@ -27788,42 +27788,42 @@
       </c>
       <c r="I328" t="inlineStr">
         <is>
-          <t>1108.13.0010</t>
+          <t>4811.59.4040</t>
         </is>
       </c>
       <c r="J328" t="inlineStr">
         <is>
-          <t>ROYAL INGREDIENTS GROUP BV</t>
+          <t>BAUSCHLINNEMANN NORTH AMERICA</t>
         </is>
       </c>
       <c r="K328" t="inlineStr">
         <is>
-          <t>ROYINGRE</t>
+          <t>BAULIN</t>
         </is>
       </c>
       <c r="L328" t="inlineStr">
         <is>
-          <t>074601-00962</t>
+          <t>56-193913400</t>
         </is>
       </c>
       <c r="M328" t="inlineStr">
         <is>
+          <t>2026-06-21 00:00:00</t>
+        </is>
+      </c>
+      <c r="N328" t="inlineStr">
+        <is>
           <t>2026-06-20 00:00:00</t>
         </is>
       </c>
-      <c r="N328" t="inlineStr">
-        <is>
-          <t>2026-06-20 00:00:00</t>
-        </is>
-      </c>
       <c r="O328" t="inlineStr">
         <is>
-          <t>AKV LANGHOLT AMBA</t>
+          <t>SURTECO GMBH</t>
         </is>
       </c>
       <c r="P328" t="inlineStr">
         <is>
-          <t>AKV LANGHOLT AMBA</t>
+          <t>SURTECO GMBH</t>
         </is>
       </c>
       <c r="Q328" t="inlineStr">
@@ -27835,12 +27835,12 @@
     <row r="329">
       <c r="A329" t="inlineStr">
         <is>
-          <t>2566177</t>
+          <t>2566051</t>
         </is>
       </c>
       <c r="B329" t="inlineStr">
         <is>
-          <t>EF4-0232275-6</t>
+          <t>EF4-0232281-4</t>
         </is>
       </c>
       <c r="C329" t="inlineStr">
@@ -27850,7 +27850,7 @@
       </c>
       <c r="D329" t="inlineStr">
         <is>
-          <t>V0710338448</t>
+          <t>V0710349973</t>
         </is>
       </c>
       <c r="E329" t="inlineStr">
@@ -27865,7 +27865,7 @@
       </c>
       <c r="G329" t="inlineStr">
         <is>
-          <t>001</t>
+          <t>002</t>
         </is>
       </c>
       <c r="H329" t="inlineStr">
@@ -27875,42 +27875,42 @@
       </c>
       <c r="I329" t="inlineStr">
         <is>
-          <t>1108.13.0010</t>
+          <t>4811.59.4040</t>
         </is>
       </c>
       <c r="J329" t="inlineStr">
         <is>
-          <t>ROYAL INGREDIENTS GROUP BV</t>
+          <t>BAUSCHLINNEMANN NORTH AMERICA</t>
         </is>
       </c>
       <c r="K329" t="inlineStr">
         <is>
-          <t>ROYINGRE</t>
+          <t>BAULIN</t>
         </is>
       </c>
       <c r="L329" t="inlineStr">
         <is>
-          <t>074601-00962</t>
+          <t>56-193913400</t>
         </is>
       </c>
       <c r="M329" t="inlineStr">
         <is>
+          <t>2026-06-21 00:00:00</t>
+        </is>
+      </c>
+      <c r="N329" t="inlineStr">
+        <is>
           <t>2026-06-20 00:00:00</t>
         </is>
       </c>
-      <c r="N329" t="inlineStr">
-        <is>
-          <t>2026-06-20 00:00:00</t>
-        </is>
-      </c>
       <c r="O329" t="inlineStr">
         <is>
-          <t>AKV LANGHOLT AMBA</t>
+          <t>SURTECO GMBH</t>
         </is>
       </c>
       <c r="P329" t="inlineStr">
         <is>
-          <t>AKV LANGHOLT AMBA</t>
+          <t>SURTECO GMBH</t>
         </is>
       </c>
       <c r="Q329" t="inlineStr">
@@ -27952,7 +27952,7 @@
       </c>
       <c r="G330" t="inlineStr">
         <is>
-          <t>001</t>
+          <t>003</t>
         </is>
       </c>
       <c r="H330" t="inlineStr">
@@ -28009,12 +28009,12 @@
     <row r="331">
       <c r="A331" t="inlineStr">
         <is>
-          <t>2566051</t>
+          <t>2566100</t>
         </is>
       </c>
       <c r="B331" t="inlineStr">
         <is>
-          <t>EF4-0232281-4</t>
+          <t>EF4-0232282-2</t>
         </is>
       </c>
       <c r="C331" t="inlineStr">
@@ -28022,11 +28022,7 @@
           <t>Vessel, Container</t>
         </is>
       </c>
-      <c r="D331" t="inlineStr">
-        <is>
-          <t>V0710349973</t>
-        </is>
-      </c>
+      <c r="D331" t="inlineStr"/>
       <c r="E331" t="inlineStr">
         <is>
           <t>9903.03.01</t>
@@ -28039,7 +28035,7 @@
       </c>
       <c r="G331" t="inlineStr">
         <is>
-          <t>002</t>
+          <t>001</t>
         </is>
       </c>
       <c r="H331" t="inlineStr">
@@ -28096,12 +28092,12 @@
     <row r="332">
       <c r="A332" t="inlineStr">
         <is>
-          <t>2566051</t>
+          <t>2566100</t>
         </is>
       </c>
       <c r="B332" t="inlineStr">
         <is>
-          <t>EF4-0232281-4</t>
+          <t>EF4-0232282-2</t>
         </is>
       </c>
       <c r="C332" t="inlineStr">
@@ -28109,11 +28105,7 @@
           <t>Vessel, Container</t>
         </is>
       </c>
-      <c r="D332" t="inlineStr">
-        <is>
-          <t>V0710349973</t>
-        </is>
-      </c>
+      <c r="D332" t="inlineStr"/>
       <c r="E332" t="inlineStr">
         <is>
           <t>9903.03.01</t>
@@ -28126,7 +28118,7 @@
       </c>
       <c r="G332" t="inlineStr">
         <is>
-          <t>003</t>
+          <t>002</t>
         </is>
       </c>
       <c r="H332" t="inlineStr">
@@ -28209,7 +28201,7 @@
       </c>
       <c r="G333" t="inlineStr">
         <is>
-          <t>001</t>
+          <t>003</t>
         </is>
       </c>
       <c r="H333" t="inlineStr">
@@ -28266,17 +28258,17 @@
     <row r="334">
       <c r="A334" t="inlineStr">
         <is>
-          <t>2566100</t>
+          <t>2615771</t>
         </is>
       </c>
       <c r="B334" t="inlineStr">
         <is>
-          <t>EF4-0232282-2</t>
+          <t>EF4-0232406-7</t>
         </is>
       </c>
       <c r="C334" t="inlineStr">
         <is>
-          <t>Vessel, Container</t>
+          <t>Vessel, Non-container</t>
         </is>
       </c>
       <c r="D334" t="inlineStr"/>
@@ -28292,7 +28284,7 @@
       </c>
       <c r="G334" t="inlineStr">
         <is>
-          <t>002</t>
+          <t>001</t>
         </is>
       </c>
       <c r="H334" t="inlineStr">
@@ -28302,27 +28294,27 @@
       </c>
       <c r="I334" t="inlineStr">
         <is>
-          <t>4811.59.4040</t>
+          <t>8210.00.0000</t>
         </is>
       </c>
       <c r="J334" t="inlineStr">
         <is>
-          <t>BAUSCHLINNEMANN NORTH AMERICA</t>
+          <t>COVE HOME LLC</t>
         </is>
       </c>
       <c r="K334" t="inlineStr">
         <is>
-          <t>BAULIN</t>
+          <t>COVHOM01</t>
         </is>
       </c>
       <c r="L334" t="inlineStr">
         <is>
-          <t>56-193913400</t>
+          <t>30-136116600</t>
         </is>
       </c>
       <c r="M334" t="inlineStr">
         <is>
-          <t>2026-06-21 00:00:00</t>
+          <t>2026-06-20 00:00:00</t>
         </is>
       </c>
       <c r="N334" t="inlineStr">
@@ -28332,34 +28324,34 @@
       </c>
       <c r="O334" t="inlineStr">
         <is>
-          <t>SURTECO GMBH</t>
+          <t>P. IONNOU G ZARKADIS QE</t>
         </is>
       </c>
       <c r="P334" t="inlineStr">
         <is>
-          <t>SURTECO GMBH</t>
+          <t>P. IONNOU G ZARKADIS QE</t>
         </is>
       </c>
       <c r="Q334" t="inlineStr">
         <is>
-          <t>2026-06-01 00:00:00</t>
+          <t>2026-06-06 00:00:00</t>
         </is>
       </c>
     </row>
     <row r="335">
       <c r="A335" t="inlineStr">
         <is>
-          <t>2566100</t>
+          <t>2615771</t>
         </is>
       </c>
       <c r="B335" t="inlineStr">
         <is>
-          <t>EF4-0232282-2</t>
+          <t>EF4-0232406-7</t>
         </is>
       </c>
       <c r="C335" t="inlineStr">
         <is>
-          <t>Vessel, Container</t>
+          <t>Vessel, Non-container</t>
         </is>
       </c>
       <c r="D335" t="inlineStr"/>
@@ -28375,7 +28367,7 @@
       </c>
       <c r="G335" t="inlineStr">
         <is>
-          <t>003</t>
+          <t>002</t>
         </is>
       </c>
       <c r="H335" t="inlineStr">
@@ -28385,27 +28377,27 @@
       </c>
       <c r="I335" t="inlineStr">
         <is>
-          <t>4811.59.4040</t>
+          <t>8210.00.0000</t>
         </is>
       </c>
       <c r="J335" t="inlineStr">
         <is>
-          <t>BAUSCHLINNEMANN NORTH AMERICA</t>
+          <t>COVE HOME LLC</t>
         </is>
       </c>
       <c r="K335" t="inlineStr">
         <is>
-          <t>BAULIN</t>
+          <t>COVHOM01</t>
         </is>
       </c>
       <c r="L335" t="inlineStr">
         <is>
-          <t>56-193913400</t>
+          <t>30-136116600</t>
         </is>
       </c>
       <c r="M335" t="inlineStr">
         <is>
-          <t>2026-06-21 00:00:00</t>
+          <t>2026-06-20 00:00:00</t>
         </is>
       </c>
       <c r="N335" t="inlineStr">
@@ -28415,34 +28407,34 @@
       </c>
       <c r="O335" t="inlineStr">
         <is>
-          <t>SURTECO GMBH</t>
+          <t>P. IONNOU G ZARKADIS QE</t>
         </is>
       </c>
       <c r="P335" t="inlineStr">
         <is>
-          <t>SURTECO GMBH</t>
+          <t>P. IONNOU G ZARKADIS QE</t>
         </is>
       </c>
       <c r="Q335" t="inlineStr">
         <is>
-          <t>2026-06-01 00:00:00</t>
+          <t>2026-06-06 00:00:00</t>
         </is>
       </c>
     </row>
     <row r="336">
       <c r="A336" t="inlineStr">
         <is>
-          <t>2615771</t>
+          <t>2565847</t>
         </is>
       </c>
       <c r="B336" t="inlineStr">
         <is>
-          <t>EF4-0232406-7</t>
+          <t>EF4-0231725-1</t>
         </is>
       </c>
       <c r="C336" t="inlineStr">
         <is>
-          <t>Vessel, Non-container</t>
+          <t>Vessel, Container</t>
         </is>
       </c>
       <c r="D336" t="inlineStr"/>
@@ -28468,64 +28460,64 @@
       </c>
       <c r="I336" t="inlineStr">
         <is>
-          <t>8210.00.0000</t>
+          <t>5407.20.0000</t>
         </is>
       </c>
       <c r="J336" t="inlineStr">
         <is>
-          <t>COVE HOME LLC</t>
+          <t>VEER CORPORATIONS INC</t>
         </is>
       </c>
       <c r="K336" t="inlineStr">
         <is>
-          <t>COVHOM01</t>
+          <t>VEECOR01</t>
         </is>
       </c>
       <c r="L336" t="inlineStr">
         <is>
-          <t>30-136116600</t>
+          <t>99-106989200</t>
         </is>
       </c>
       <c r="M336" t="inlineStr">
         <is>
-          <t>2026-06-20 00:00:00</t>
+          <t>2026-06-19 00:00:00</t>
         </is>
       </c>
       <c r="N336" t="inlineStr">
         <is>
-          <t>2026-06-20 00:00:00</t>
+          <t>2026-06-21 00:00:00</t>
         </is>
       </c>
       <c r="O336" t="inlineStr">
         <is>
-          <t>P. IONNOU G ZARKADIS QE</t>
+          <t>VEER PLASTIC PVT LTD</t>
         </is>
       </c>
       <c r="P336" t="inlineStr">
         <is>
-          <t>P. IONNOU G ZARKADIS QE</t>
+          <t>VEER PLASTIC PVT LTD</t>
         </is>
       </c>
       <c r="Q336" t="inlineStr">
         <is>
-          <t>2026-06-06 00:00:00</t>
+          <t>2026-05-06 00:00:00</t>
         </is>
       </c>
     </row>
     <row r="337">
       <c r="A337" t="inlineStr">
         <is>
-          <t>2615771</t>
+          <t>2565848</t>
         </is>
       </c>
       <c r="B337" t="inlineStr">
         <is>
-          <t>EF4-0232406-7</t>
+          <t>EF4-0231726-9</t>
         </is>
       </c>
       <c r="C337" t="inlineStr">
         <is>
-          <t>Vessel, Non-container</t>
+          <t>Vessel, Container</t>
         </is>
       </c>
       <c r="D337" t="inlineStr"/>
@@ -28541,7 +28533,7 @@
       </c>
       <c r="G337" t="inlineStr">
         <is>
-          <t>002</t>
+          <t>001</t>
         </is>
       </c>
       <c r="H337" t="inlineStr">
@@ -28551,59 +28543,59 @@
       </c>
       <c r="I337" t="inlineStr">
         <is>
-          <t>8210.00.0000</t>
+          <t>5603.14.9090</t>
         </is>
       </c>
       <c r="J337" t="inlineStr">
         <is>
-          <t>COVE HOME LLC</t>
+          <t>VEER CORPORATIONS INC</t>
         </is>
       </c>
       <c r="K337" t="inlineStr">
         <is>
-          <t>COVHOM01</t>
+          <t>VEECOR01</t>
         </is>
       </c>
       <c r="L337" t="inlineStr">
         <is>
-          <t>30-136116600</t>
+          <t>99-106989200</t>
         </is>
       </c>
       <c r="M337" t="inlineStr">
         <is>
-          <t>2026-06-20 00:00:00</t>
+          <t>2026-06-19 00:00:00</t>
         </is>
       </c>
       <c r="N337" t="inlineStr">
         <is>
-          <t>2026-06-20 00:00:00</t>
+          <t>2026-06-21 00:00:00</t>
         </is>
       </c>
       <c r="O337" t="inlineStr">
         <is>
-          <t>P. IONNOU G ZARKADIS QE</t>
+          <t>VEER PLASTIC PVT LTD</t>
         </is>
       </c>
       <c r="P337" t="inlineStr">
         <is>
-          <t>P. IONNOU G ZARKADIS QE</t>
+          <t>VEER PLASTIC PVT LTD</t>
         </is>
       </c>
       <c r="Q337" t="inlineStr">
         <is>
-          <t>2026-06-06 00:00:00</t>
+          <t>2026-05-11 00:00:00</t>
         </is>
       </c>
     </row>
     <row r="338">
       <c r="A338" t="inlineStr">
         <is>
-          <t>2565847</t>
+          <t>2565849</t>
         </is>
       </c>
       <c r="B338" t="inlineStr">
         <is>
-          <t>EF4-0231725-1</t>
+          <t>EF4-0231727-7</t>
         </is>
       </c>
       <c r="C338" t="inlineStr">
@@ -28674,19 +28666,19 @@
       </c>
       <c r="Q338" t="inlineStr">
         <is>
-          <t>2026-05-06 00:00:00</t>
+          <t>2026-05-11 00:00:00</t>
         </is>
       </c>
     </row>
     <row r="339">
       <c r="A339" t="inlineStr">
         <is>
-          <t>2565848</t>
+          <t>2565891</t>
         </is>
       </c>
       <c r="B339" t="inlineStr">
         <is>
-          <t>EF4-0231726-9</t>
+          <t>EF4-0231922-4</t>
         </is>
       </c>
       <c r="C339" t="inlineStr">
@@ -28717,27 +28709,27 @@
       </c>
       <c r="I339" t="inlineStr">
         <is>
-          <t>5603.14.9090</t>
+          <t>1109.00.9020</t>
         </is>
       </c>
       <c r="J339" t="inlineStr">
         <is>
-          <t>VEER CORPORATIONS INC</t>
+          <t>ROYAL INGREDIENTS GROUP BV</t>
         </is>
       </c>
       <c r="K339" t="inlineStr">
         <is>
-          <t>VEECOR01</t>
+          <t>ROYINGRE</t>
         </is>
       </c>
       <c r="L339" t="inlineStr">
         <is>
-          <t>99-106989200</t>
+          <t>074601-00962</t>
         </is>
       </c>
       <c r="M339" t="inlineStr">
         <is>
-          <t>2026-06-19 00:00:00</t>
+          <t>2026-06-20 00:00:00</t>
         </is>
       </c>
       <c r="N339" t="inlineStr">
@@ -28747,29 +28739,29 @@
       </c>
       <c r="O339" t="inlineStr">
         <is>
-          <t>VEER PLASTIC PVT LTD</t>
+          <t>SEDAMYL UK</t>
         </is>
       </c>
       <c r="P339" t="inlineStr">
         <is>
-          <t>VEER PLASTIC PVT LTD</t>
+          <t>SEDAMYL UK</t>
         </is>
       </c>
       <c r="Q339" t="inlineStr">
         <is>
-          <t>2026-05-11 00:00:00</t>
+          <t>2026-05-16 00:00:00</t>
         </is>
       </c>
     </row>
     <row r="340">
       <c r="A340" t="inlineStr">
         <is>
-          <t>2565849</t>
+          <t>2565934</t>
         </is>
       </c>
       <c r="B340" t="inlineStr">
         <is>
-          <t>EF4-0231727-7</t>
+          <t>EF4-0231991-9</t>
         </is>
       </c>
       <c r="C340" t="inlineStr">
@@ -28777,7 +28769,11 @@
           <t>Vessel, Container</t>
         </is>
       </c>
-      <c r="D340" t="inlineStr"/>
+      <c r="D340" t="inlineStr">
+        <is>
+          <t>V0710339289</t>
+        </is>
+      </c>
       <c r="E340" t="inlineStr">
         <is>
           <t>9903.03.01</t>
@@ -28800,27 +28796,27 @@
       </c>
       <c r="I340" t="inlineStr">
         <is>
-          <t>5407.20.0000</t>
+          <t>1108.13.0010</t>
         </is>
       </c>
       <c r="J340" t="inlineStr">
         <is>
-          <t>VEER CORPORATIONS INC</t>
+          <t>ROYAL INGREDIENTS GROUP BV</t>
         </is>
       </c>
       <c r="K340" t="inlineStr">
         <is>
-          <t>VEECOR01</t>
+          <t>ROYINGRE</t>
         </is>
       </c>
       <c r="L340" t="inlineStr">
         <is>
-          <t>99-106989200</t>
+          <t>074601-00962</t>
         </is>
       </c>
       <c r="M340" t="inlineStr">
         <is>
-          <t>2026-06-19 00:00:00</t>
+          <t>2026-06-07 00:00:00</t>
         </is>
       </c>
       <c r="N340" t="inlineStr">
@@ -28830,29 +28826,29 @@
       </c>
       <c r="O340" t="inlineStr">
         <is>
-          <t>VEER PLASTIC PVT LTD</t>
+          <t>AKV LANGHOLT AMBA</t>
         </is>
       </c>
       <c r="P340" t="inlineStr">
         <is>
-          <t>VEER PLASTIC PVT LTD</t>
+          <t>AKV LANGHOLT AMBA</t>
         </is>
       </c>
       <c r="Q340" t="inlineStr">
         <is>
-          <t>2026-05-11 00:00:00</t>
+          <t>2026-05-18 00:00:00</t>
         </is>
       </c>
     </row>
     <row r="341">
       <c r="A341" t="inlineStr">
         <is>
-          <t>2565891</t>
+          <t>2566075</t>
         </is>
       </c>
       <c r="B341" t="inlineStr">
         <is>
-          <t>EF4-0231922-4</t>
+          <t>EF4-0232185-7</t>
         </is>
       </c>
       <c r="C341" t="inlineStr">
@@ -28860,7 +28856,11 @@
           <t>Vessel, Container</t>
         </is>
       </c>
-      <c r="D341" t="inlineStr"/>
+      <c r="D341" t="inlineStr">
+        <is>
+          <t>V0710339289</t>
+        </is>
+      </c>
       <c r="E341" t="inlineStr">
         <is>
           <t>9903.03.01</t>
@@ -28883,27 +28883,27 @@
       </c>
       <c r="I341" t="inlineStr">
         <is>
-          <t>1109.00.9020</t>
+          <t>9903.82.01,8431.20.0000</t>
         </is>
       </c>
       <c r="J341" t="inlineStr">
         <is>
-          <t>ROYAL INGREDIENTS GROUP BV</t>
+          <t>MALLAGHAN (GA) INC.</t>
         </is>
       </c>
       <c r="K341" t="inlineStr">
         <is>
-          <t>ROYINGRE</t>
+          <t>MALGA01</t>
         </is>
       </c>
       <c r="L341" t="inlineStr">
         <is>
-          <t>074601-00962</t>
+          <t>36-488102800</t>
         </is>
       </c>
       <c r="M341" t="inlineStr">
         <is>
-          <t>2026-06-20 00:00:00</t>
+          <t>2026-06-22 00:00:00</t>
         </is>
       </c>
       <c r="N341" t="inlineStr">
@@ -28913,29 +28913,29 @@
       </c>
       <c r="O341" t="inlineStr">
         <is>
-          <t>SEDAMYL UK</t>
+          <t>MALLAGHAN ENGINEERING  LTD</t>
         </is>
       </c>
       <c r="P341" t="inlineStr">
         <is>
-          <t>SEDAMYL UK</t>
+          <t>MALLAGHAN ENGINEERING  LTD</t>
         </is>
       </c>
       <c r="Q341" t="inlineStr">
         <is>
-          <t>2026-05-16 00:00:00</t>
+          <t>2026-05-28 00:00:00</t>
         </is>
       </c>
     </row>
     <row r="342">
       <c r="A342" t="inlineStr">
         <is>
-          <t>2565934</t>
+          <t>2566102</t>
         </is>
       </c>
       <c r="B342" t="inlineStr">
         <is>
-          <t>EF4-0231991-9</t>
+          <t>EF4-0232187-3</t>
         </is>
       </c>
       <c r="C342" t="inlineStr">
@@ -28943,19 +28943,15 @@
           <t>Vessel, Container</t>
         </is>
       </c>
-      <c r="D342" t="inlineStr">
-        <is>
-          <t>V0710339289</t>
-        </is>
-      </c>
+      <c r="D342" t="inlineStr"/>
       <c r="E342" t="inlineStr">
         <is>
-          <t>9903.03.01</t>
+          <t>9903.03.06</t>
         </is>
       </c>
       <c r="F342" t="inlineStr">
         <is>
-          <t>SECTION 122 - 10% DUTY</t>
+          <t>S122 EXCL,IRN/STL/ALUM,DERIV</t>
         </is>
       </c>
       <c r="G342" t="inlineStr">
@@ -28965,32 +28961,32 @@
       </c>
       <c r="H342" t="inlineStr">
         <is>
-          <t>9903.03.01</t>
+          <t>9903.03.06</t>
         </is>
       </c>
       <c r="I342" t="inlineStr">
         <is>
-          <t>1108.13.0010</t>
+          <t>9903.82.22,8431.20.0000</t>
         </is>
       </c>
       <c r="J342" t="inlineStr">
         <is>
-          <t>ROYAL INGREDIENTS GROUP BV</t>
+          <t>MALLAGHAN (GA) INC.</t>
         </is>
       </c>
       <c r="K342" t="inlineStr">
         <is>
-          <t>ROYINGRE</t>
+          <t>MALGA01</t>
         </is>
       </c>
       <c r="L342" t="inlineStr">
         <is>
-          <t>074601-00962</t>
+          <t>36-488102800</t>
         </is>
       </c>
       <c r="M342" t="inlineStr">
         <is>
-          <t>2026-06-07 00:00:00</t>
+          <t>2026-06-22 00:00:00</t>
         </is>
       </c>
       <c r="N342" t="inlineStr">
@@ -29000,29 +28996,29 @@
       </c>
       <c r="O342" t="inlineStr">
         <is>
-          <t>AKV LANGHOLT AMBA</t>
+          <t>MALLAGHAN ENGINEERING  LTD</t>
         </is>
       </c>
       <c r="P342" t="inlineStr">
         <is>
-          <t>AKV LANGHOLT AMBA</t>
+          <t>MALLAGHAN ENGINEERING  LTD</t>
         </is>
       </c>
       <c r="Q342" t="inlineStr">
         <is>
-          <t>2026-05-18 00:00:00</t>
+          <t>2026-05-28 00:00:00</t>
         </is>
       </c>
     </row>
     <row r="343">
       <c r="A343" t="inlineStr">
         <is>
-          <t>2566075</t>
+          <t>2565923</t>
         </is>
       </c>
       <c r="B343" t="inlineStr">
         <is>
-          <t>EF4-0232185-7</t>
+          <t>EF4-0232195-6</t>
         </is>
       </c>
       <c r="C343" t="inlineStr">
@@ -29030,19 +29026,15 @@
           <t>Vessel, Container</t>
         </is>
       </c>
-      <c r="D343" t="inlineStr">
-        <is>
-          <t>V0710339289</t>
-        </is>
-      </c>
+      <c r="D343" t="inlineStr"/>
       <c r="E343" t="inlineStr">
         <is>
-          <t>9903.03.01</t>
+          <t>9903.91.01</t>
         </is>
       </c>
       <c r="F343" t="inlineStr">
         <is>
-          <t>SECTION 122 - 10% DUTY</t>
+          <t>ARTS, PRDS OF CN SUB(B)US NT31</t>
         </is>
       </c>
       <c r="G343" t="inlineStr">
@@ -29052,32 +29044,32 @@
       </c>
       <c r="H343" t="inlineStr">
         <is>
-          <t>9903.03.01</t>
+          <t>9903.91.01</t>
         </is>
       </c>
       <c r="I343" t="inlineStr">
         <is>
-          <t>9903.82.01,8431.20.0000</t>
+          <t>9903.03.06,9903.82.02,7228.30.6000</t>
         </is>
       </c>
       <c r="J343" t="inlineStr">
         <is>
-          <t>MALLAGHAN (GA) INC.</t>
+          <t>MAHA USA LLC</t>
         </is>
       </c>
       <c r="K343" t="inlineStr">
         <is>
-          <t>MALGA01</t>
+          <t>MAHUSA</t>
         </is>
       </c>
       <c r="L343" t="inlineStr">
         <is>
-          <t>36-488102800</t>
+          <t>52-213556300</t>
         </is>
       </c>
       <c r="M343" t="inlineStr">
         <is>
-          <t>2026-06-22 00:00:00</t>
+          <t>2026-06-20 00:00:00</t>
         </is>
       </c>
       <c r="N343" t="inlineStr">
@@ -29087,29 +29079,29 @@
       </c>
       <c r="O343" t="inlineStr">
         <is>
-          <t>MALLAGHAN ENGINEERING  LTD</t>
+          <t>THYSSENKRUPP SCHULTE GMBH</t>
         </is>
       </c>
       <c r="P343" t="inlineStr">
         <is>
-          <t>MALLAGHAN ENGINEERING  LTD</t>
+          <t>THYSSENKRUPP SCHULTE GMBH</t>
         </is>
       </c>
       <c r="Q343" t="inlineStr">
         <is>
-          <t>2026-05-28 00:00:00</t>
+          <t>2026-05-27 00:00:00</t>
         </is>
       </c>
     </row>
     <row r="344">
       <c r="A344" t="inlineStr">
         <is>
-          <t>2566102</t>
+          <t>2565923</t>
         </is>
       </c>
       <c r="B344" t="inlineStr">
         <is>
-          <t>EF4-0232187-3</t>
+          <t>EF4-0232195-6</t>
         </is>
       </c>
       <c r="C344" t="inlineStr">
@@ -29130,7 +29122,7 @@
       </c>
       <c r="G344" t="inlineStr">
         <is>
-          <t>001</t>
+          <t>002</t>
         </is>
       </c>
       <c r="H344" t="inlineStr">
@@ -29140,27 +29132,27 @@
       </c>
       <c r="I344" t="inlineStr">
         <is>
-          <t>9903.82.22,8431.20.0000</t>
+          <t>9903.82.02,7215.50.0016</t>
         </is>
       </c>
       <c r="J344" t="inlineStr">
         <is>
-          <t>MALLAGHAN (GA) INC.</t>
+          <t>MAHA USA LLC</t>
         </is>
       </c>
       <c r="K344" t="inlineStr">
         <is>
-          <t>MALGA01</t>
+          <t>MAHUSA</t>
         </is>
       </c>
       <c r="L344" t="inlineStr">
         <is>
-          <t>36-488102800</t>
+          <t>52-213556300</t>
         </is>
       </c>
       <c r="M344" t="inlineStr">
         <is>
-          <t>2026-06-22 00:00:00</t>
+          <t>2026-06-20 00:00:00</t>
         </is>
       </c>
       <c r="N344" t="inlineStr">
@@ -29170,17 +29162,17 @@
       </c>
       <c r="O344" t="inlineStr">
         <is>
-          <t>MALLAGHAN ENGINEERING  LTD</t>
+          <t>THYSSENKRUPP SCHULTE GMBH</t>
         </is>
       </c>
       <c r="P344" t="inlineStr">
         <is>
-          <t>MALLAGHAN ENGINEERING  LTD</t>
+          <t>THYSSENKRUPP SCHULTE GMBH</t>
         </is>
       </c>
       <c r="Q344" t="inlineStr">
         <is>
-          <t>2026-05-28 00:00:00</t>
+          <t>2026-05-27 00:00:00</t>
         </is>
       </c>
     </row>
@@ -29203,27 +29195,27 @@
       <c r="D345" t="inlineStr"/>
       <c r="E345" t="inlineStr">
         <is>
-          <t>9903.91.01</t>
+          <t>9903.03.06</t>
         </is>
       </c>
       <c r="F345" t="inlineStr">
         <is>
-          <t>ARTS, PRDS OF CN SUB(B)US NT31</t>
+          <t>S122 EXCL,IRN/STL/ALUM,DERIV</t>
         </is>
       </c>
       <c r="G345" t="inlineStr">
         <is>
-          <t>001</t>
+          <t>003</t>
         </is>
       </c>
       <c r="H345" t="inlineStr">
         <is>
-          <t>9903.91.01</t>
+          <t>9903.03.06</t>
         </is>
       </c>
       <c r="I345" t="inlineStr">
         <is>
-          <t>9903.03.06,9903.82.02,7228.30.6000</t>
+          <t>9903.82.02,7216.33.0090</t>
         </is>
       </c>
       <c r="J345" t="inlineStr">
@@ -29270,12 +29262,12 @@
     <row r="346">
       <c r="A346" t="inlineStr">
         <is>
-          <t>2565923</t>
+          <t>2566146</t>
         </is>
       </c>
       <c r="B346" t="inlineStr">
         <is>
-          <t>EF4-0232195-6</t>
+          <t>EF4-0232246-7</t>
         </is>
       </c>
       <c r="C346" t="inlineStr">
@@ -29286,47 +29278,47 @@
       <c r="D346" t="inlineStr"/>
       <c r="E346" t="inlineStr">
         <is>
-          <t>9903.03.06</t>
+          <t>9903.03.01</t>
         </is>
       </c>
       <c r="F346" t="inlineStr">
         <is>
-          <t>S122 EXCL,IRN/STL/ALUM,DERIV</t>
+          <t>SECTION 122 - 10% DUTY</t>
         </is>
       </c>
       <c r="G346" t="inlineStr">
         <is>
-          <t>002</t>
+          <t>001</t>
         </is>
       </c>
       <c r="H346" t="inlineStr">
         <is>
-          <t>9903.03.06</t>
+          <t>9903.03.01</t>
         </is>
       </c>
       <c r="I346" t="inlineStr">
         <is>
-          <t>9903.82.02,7215.50.0016</t>
+          <t>1109.00.9010</t>
         </is>
       </c>
       <c r="J346" t="inlineStr">
         <is>
-          <t>MAHA USA LLC</t>
+          <t>ROYAL INGREDIENTS GROUP BV</t>
         </is>
       </c>
       <c r="K346" t="inlineStr">
         <is>
-          <t>MAHUSA</t>
+          <t>ROYINGRE</t>
         </is>
       </c>
       <c r="L346" t="inlineStr">
         <is>
-          <t>52-213556300</t>
+          <t>074601-00962</t>
         </is>
       </c>
       <c r="M346" t="inlineStr">
         <is>
-          <t>2026-06-20 00:00:00</t>
+          <t>2026-06-22 00:00:00</t>
         </is>
       </c>
       <c r="N346" t="inlineStr">
@@ -29336,29 +29328,29 @@
       </c>
       <c r="O346" t="inlineStr">
         <is>
-          <t>THYSSENKRUPP SCHULTE GMBH</t>
+          <t>KROENER-STARKE BIO GMBH</t>
         </is>
       </c>
       <c r="P346" t="inlineStr">
         <is>
-          <t>THYSSENKRUPP SCHULTE GMBH</t>
+          <t>KROENER-STARKE BIO GMBH</t>
         </is>
       </c>
       <c r="Q346" t="inlineStr">
         <is>
-          <t>2026-05-27 00:00:00</t>
+          <t>2026-06-01 00:00:00</t>
         </is>
       </c>
     </row>
     <row r="347">
       <c r="A347" t="inlineStr">
         <is>
-          <t>2565923</t>
+          <t>2566173</t>
         </is>
       </c>
       <c r="B347" t="inlineStr">
         <is>
-          <t>EF4-0232195-6</t>
+          <t>EF4-0232274-9</t>
         </is>
       </c>
       <c r="C347" t="inlineStr">
@@ -29369,47 +29361,47 @@
       <c r="D347" t="inlineStr"/>
       <c r="E347" t="inlineStr">
         <is>
-          <t>9903.03.06</t>
+          <t>9903.03.01</t>
         </is>
       </c>
       <c r="F347" t="inlineStr">
         <is>
-          <t>S122 EXCL,IRN/STL/ALUM,DERIV</t>
+          <t>SECTION 122 - 10% DUTY</t>
         </is>
       </c>
       <c r="G347" t="inlineStr">
         <is>
-          <t>003</t>
+          <t>001</t>
         </is>
       </c>
       <c r="H347" t="inlineStr">
         <is>
-          <t>9903.03.06</t>
+          <t>9903.03.01</t>
         </is>
       </c>
       <c r="I347" t="inlineStr">
         <is>
-          <t>9903.82.02,7216.33.0090</t>
+          <t>1109.00.9020</t>
         </is>
       </c>
       <c r="J347" t="inlineStr">
         <is>
-          <t>MAHA USA LLC</t>
+          <t>ROYAL INGREDIENTS GROUP BV</t>
         </is>
       </c>
       <c r="K347" t="inlineStr">
         <is>
-          <t>MAHUSA</t>
+          <t>ROYINGRE</t>
         </is>
       </c>
       <c r="L347" t="inlineStr">
         <is>
-          <t>52-213556300</t>
+          <t>074601-00962</t>
         </is>
       </c>
       <c r="M347" t="inlineStr">
         <is>
-          <t>2026-06-20 00:00:00</t>
+          <t>2026-06-21 00:00:00</t>
         </is>
       </c>
       <c r="N347" t="inlineStr">
@@ -29419,29 +29411,29 @@
       </c>
       <c r="O347" t="inlineStr">
         <is>
-          <t>THYSSENKRUPP SCHULTE GMBH</t>
+          <t>JACKERING MUHLEN UND NAHRMITTELWERK</t>
         </is>
       </c>
       <c r="P347" t="inlineStr">
         <is>
-          <t>THYSSENKRUPP SCHULTE GMBH</t>
+          <t>JACKERING MUHLEN UND NAHRMITTELWERKE GMBH</t>
         </is>
       </c>
       <c r="Q347" t="inlineStr">
         <is>
-          <t>2026-05-27 00:00:00</t>
+          <t>2026-06-01 00:00:00</t>
         </is>
       </c>
     </row>
     <row r="348">
       <c r="A348" t="inlineStr">
         <is>
-          <t>2566146</t>
+          <t>2565864</t>
         </is>
       </c>
       <c r="B348" t="inlineStr">
         <is>
-          <t>EF4-0232246-7</t>
+          <t>EF4-0232315-0</t>
         </is>
       </c>
       <c r="C348" t="inlineStr">
@@ -29472,7 +29464,7 @@
       </c>
       <c r="I348" t="inlineStr">
         <is>
-          <t>1109.00.9010</t>
+          <t>1109.00.9020</t>
         </is>
       </c>
       <c r="J348" t="inlineStr">
@@ -29492,7 +29484,7 @@
       </c>
       <c r="M348" t="inlineStr">
         <is>
-          <t>2026-06-22 00:00:00</t>
+          <t>2026-06-20 00:00:00</t>
         </is>
       </c>
       <c r="N348" t="inlineStr">
@@ -29502,29 +29494,29 @@
       </c>
       <c r="O348" t="inlineStr">
         <is>
-          <t>KROENER-STARKE BIO GMBH</t>
+          <t>ROQUETTE FRERES</t>
         </is>
       </c>
       <c r="P348" t="inlineStr">
         <is>
-          <t>KROENER-STARKE BIO GMBH</t>
+          <t>ROQUETTE FRERES</t>
         </is>
       </c>
       <c r="Q348" t="inlineStr">
         <is>
-          <t>2026-06-01 00:00:00</t>
+          <t>2026-05-14 00:00:00</t>
         </is>
       </c>
     </row>
     <row r="349">
       <c r="A349" t="inlineStr">
         <is>
-          <t>2566173</t>
+          <t>2566183</t>
         </is>
       </c>
       <c r="B349" t="inlineStr">
         <is>
-          <t>EF4-0232274-9</t>
+          <t>EF4-0232343-2</t>
         </is>
       </c>
       <c r="C349" t="inlineStr">
@@ -29555,22 +29547,22 @@
       </c>
       <c r="I349" t="inlineStr">
         <is>
-          <t>1109.00.9020</t>
+          <t>2106.90.9998</t>
         </is>
       </c>
       <c r="J349" t="inlineStr">
         <is>
-          <t>ROYAL INGREDIENTS GROUP BV</t>
+          <t>DOBLA USA MFG LLC</t>
         </is>
       </c>
       <c r="K349" t="inlineStr">
         <is>
-          <t>ROYINGRE</t>
+          <t>DOBUSA</t>
         </is>
       </c>
       <c r="L349" t="inlineStr">
         <is>
-          <t>074601-00962</t>
+          <t>41-218954800</t>
         </is>
       </c>
       <c r="M349" t="inlineStr">
@@ -29585,29 +29577,29 @@
       </c>
       <c r="O349" t="inlineStr">
         <is>
-          <t>JACKERING MUHLEN UND NAHRMITTELWERK</t>
+          <t>IRCA SRL</t>
         </is>
       </c>
       <c r="P349" t="inlineStr">
         <is>
-          <t>JACKERING MUHLEN UND NAHRMITTELWERKE GMBH</t>
+          <t>IRCA SRL</t>
         </is>
       </c>
       <c r="Q349" t="inlineStr">
         <is>
-          <t>2026-06-01 00:00:00</t>
+          <t>2026-06-04 00:00:00</t>
         </is>
       </c>
     </row>
     <row r="350">
       <c r="A350" t="inlineStr">
         <is>
-          <t>2565864</t>
+          <t>2566264</t>
         </is>
       </c>
       <c r="B350" t="inlineStr">
         <is>
-          <t>EF4-0232315-0</t>
+          <t>EF4-0232584-1</t>
         </is>
       </c>
       <c r="C350" t="inlineStr">
@@ -29638,27 +29630,27 @@
       </c>
       <c r="I350" t="inlineStr">
         <is>
-          <t>1109.00.9020</t>
+          <t>3815.90.5000</t>
         </is>
       </c>
       <c r="J350" t="inlineStr">
         <is>
-          <t>ROYAL INGREDIENTS GROUP BV</t>
+          <t>JOBACHEM CORPORATION</t>
         </is>
       </c>
       <c r="K350" t="inlineStr">
         <is>
-          <t>ROYINGRE</t>
+          <t>JOBLP01</t>
         </is>
       </c>
       <c r="L350" t="inlineStr">
         <is>
-          <t>074601-00962</t>
+          <t>32-052169200</t>
         </is>
       </c>
       <c r="M350" t="inlineStr">
         <is>
-          <t>2026-06-20 00:00:00</t>
+          <t>2026-06-22 00:00:00</t>
         </is>
       </c>
       <c r="N350" t="inlineStr">
@@ -29668,29 +29660,29 @@
       </c>
       <c r="O350" t="inlineStr">
         <is>
-          <t>ROQUETTE FRERES</t>
+          <t>JOBACHEM GMBH</t>
         </is>
       </c>
       <c r="P350" t="inlineStr">
         <is>
-          <t>ROQUETTE FRERES</t>
+          <t>JOBACHEM GMBH</t>
         </is>
       </c>
       <c r="Q350" t="inlineStr">
         <is>
-          <t>2026-05-14 00:00:00</t>
+          <t>2026-06-06 00:00:00</t>
         </is>
       </c>
     </row>
     <row r="351">
       <c r="A351" t="inlineStr">
         <is>
-          <t>2566183</t>
+          <t>2566264</t>
         </is>
       </c>
       <c r="B351" t="inlineStr">
         <is>
-          <t>EF4-0232343-2</t>
+          <t>EF4-0232584-1</t>
         </is>
       </c>
       <c r="C351" t="inlineStr">
@@ -29711,7 +29703,7 @@
       </c>
       <c r="G351" t="inlineStr">
         <is>
-          <t>001</t>
+          <t>002</t>
         </is>
       </c>
       <c r="H351" t="inlineStr">
@@ -29721,59 +29713,59 @@
       </c>
       <c r="I351" t="inlineStr">
         <is>
-          <t>2106.90.9998</t>
+          <t>2916.14.2050</t>
         </is>
       </c>
       <c r="J351" t="inlineStr">
         <is>
-          <t>DOBLA USA MFG LLC</t>
+          <t>JOBACHEM CORPORATION</t>
         </is>
       </c>
       <c r="K351" t="inlineStr">
         <is>
-          <t>DOBUSA</t>
+          <t>JOBLP01</t>
         </is>
       </c>
       <c r="L351" t="inlineStr">
         <is>
-          <t>41-218954800</t>
+          <t>32-052169200</t>
         </is>
       </c>
       <c r="M351" t="inlineStr">
         <is>
+          <t>2026-06-22 00:00:00</t>
+        </is>
+      </c>
+      <c r="N351" t="inlineStr">
+        <is>
           <t>2026-06-21 00:00:00</t>
         </is>
       </c>
-      <c r="N351" t="inlineStr">
-        <is>
-          <t>2026-06-21 00:00:00</t>
-        </is>
-      </c>
       <c r="O351" t="inlineStr">
         <is>
-          <t>IRCA SRL</t>
+          <t>JOBACHEM GMBH</t>
         </is>
       </c>
       <c r="P351" t="inlineStr">
         <is>
-          <t>IRCA SRL</t>
+          <t>JOBACHEM GMBH</t>
         </is>
       </c>
       <c r="Q351" t="inlineStr">
         <is>
-          <t>2026-06-04 00:00:00</t>
+          <t>2026-06-06 00:00:00</t>
         </is>
       </c>
     </row>
     <row r="352">
       <c r="A352" t="inlineStr">
         <is>
-          <t>2566264</t>
+          <t>2565444</t>
         </is>
       </c>
       <c r="B352" t="inlineStr">
         <is>
-          <t>EF4-0232584-1</t>
+          <t>EF4-0231090-0</t>
         </is>
       </c>
       <c r="C352" t="inlineStr">
@@ -29804,22 +29796,22 @@
       </c>
       <c r="I352" t="inlineStr">
         <is>
-          <t>3815.90.5000</t>
+          <t>5903.90.3090</t>
         </is>
       </c>
       <c r="J352" t="inlineStr">
         <is>
-          <t>JOBACHEM CORPORATION</t>
+          <t>VEER CORPORATIONS INC</t>
         </is>
       </c>
       <c r="K352" t="inlineStr">
         <is>
-          <t>JOBLP01</t>
+          <t>VEECOR01</t>
         </is>
       </c>
       <c r="L352" t="inlineStr">
         <is>
-          <t>32-052169200</t>
+          <t>99-106989200</t>
         </is>
       </c>
       <c r="M352" t="inlineStr">
@@ -29829,34 +29821,34 @@
       </c>
       <c r="N352" t="inlineStr">
         <is>
-          <t>2026-06-21 00:00:00</t>
+          <t>2026-06-22 00:00:00</t>
         </is>
       </c>
       <c r="O352" t="inlineStr">
         <is>
-          <t>JOBACHEM GMBH</t>
+          <t>VEER PLASTIC PVT LTD</t>
         </is>
       </c>
       <c r="P352" t="inlineStr">
         <is>
-          <t>JOBACHEM GMBH</t>
+          <t>VEER PLASTIC PVT LTD</t>
         </is>
       </c>
       <c r="Q352" t="inlineStr">
         <is>
-          <t>2026-06-06 00:00:00</t>
+          <t>2026-04-10 00:00:00</t>
         </is>
       </c>
     </row>
     <row r="353">
       <c r="A353" t="inlineStr">
         <is>
-          <t>2566264</t>
+          <t>2566049</t>
         </is>
       </c>
       <c r="B353" t="inlineStr">
         <is>
-          <t>EF4-0232584-1</t>
+          <t>EF4-0231964-6</t>
         </is>
       </c>
       <c r="C353" t="inlineStr">
@@ -29867,67 +29859,1510 @@
       <c r="D353" t="inlineStr"/>
       <c r="E353" t="inlineStr">
         <is>
-          <t>9903.03.01</t>
+          <t>9903.88.15</t>
         </is>
       </c>
       <c r="F353" t="inlineStr">
         <is>
+          <t>ARTICLE OF CHINA,US NTE 20(R)</t>
+        </is>
+      </c>
+      <c r="G353" t="inlineStr">
+        <is>
+          <t>001</t>
+        </is>
+      </c>
+      <c r="H353" t="inlineStr">
+        <is>
+          <t>9903.88.15</t>
+        </is>
+      </c>
+      <c r="I353" t="inlineStr">
+        <is>
+          <t>9903.03.01,3926.30.5000</t>
+        </is>
+      </c>
+      <c r="J353" t="inlineStr">
+        <is>
+          <t>BORGERS USA CORP</t>
+        </is>
+      </c>
+      <c r="K353" t="inlineStr">
+        <is>
+          <t>BORUSA</t>
+        </is>
+      </c>
+      <c r="L353" t="inlineStr">
+        <is>
+          <t>65-117296500</t>
+        </is>
+      </c>
+      <c r="M353" t="inlineStr">
+        <is>
+          <t>2026-06-22 00:00:00</t>
+        </is>
+      </c>
+      <c r="N353" t="inlineStr">
+        <is>
+          <t>2026-06-22 00:00:00</t>
+        </is>
+      </c>
+      <c r="O353" t="inlineStr">
+        <is>
+          <t>AUTONEUM (SHANGHAI) MANAGEMENT CO.</t>
+        </is>
+      </c>
+      <c r="P353" t="inlineStr">
+        <is>
+          <t>AUTONEUM (SHANGHAI) MANAGEMENT CO. LTD.</t>
+        </is>
+      </c>
+      <c r="Q353" t="inlineStr">
+        <is>
+          <t>2026-05-17 00:00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="354">
+      <c r="A354" t="inlineStr">
+        <is>
+          <t>2566049</t>
+        </is>
+      </c>
+      <c r="B354" t="inlineStr">
+        <is>
+          <t>EF4-0231964-6</t>
+        </is>
+      </c>
+      <c r="C354" t="inlineStr">
+        <is>
+          <t>Vessel, Container</t>
+        </is>
+      </c>
+      <c r="D354" t="inlineStr"/>
+      <c r="E354" t="inlineStr">
+        <is>
+          <t>9903.88.15</t>
+        </is>
+      </c>
+      <c r="F354" t="inlineStr">
+        <is>
+          <t>ARTICLE OF CHINA,US NTE 20(R)</t>
+        </is>
+      </c>
+      <c r="G354" t="inlineStr">
+        <is>
+          <t>002</t>
+        </is>
+      </c>
+      <c r="H354" t="inlineStr">
+        <is>
+          <t>9903.88.15</t>
+        </is>
+      </c>
+      <c r="I354" t="inlineStr">
+        <is>
+          <t>9903.03.01,3926.90.9989</t>
+        </is>
+      </c>
+      <c r="J354" t="inlineStr">
+        <is>
+          <t>BORGERS USA CORP</t>
+        </is>
+      </c>
+      <c r="K354" t="inlineStr">
+        <is>
+          <t>BORUSA</t>
+        </is>
+      </c>
+      <c r="L354" t="inlineStr">
+        <is>
+          <t>65-117296500</t>
+        </is>
+      </c>
+      <c r="M354" t="inlineStr">
+        <is>
+          <t>2026-06-22 00:00:00</t>
+        </is>
+      </c>
+      <c r="N354" t="inlineStr">
+        <is>
+          <t>2026-06-22 00:00:00</t>
+        </is>
+      </c>
+      <c r="O354" t="inlineStr">
+        <is>
+          <t>AUTONEUM (SHANGHAI) MANAGEMENT CO.</t>
+        </is>
+      </c>
+      <c r="P354" t="inlineStr">
+        <is>
+          <t>AUTONEUM (SHANGHAI) MANAGEMENT CO. LTD.</t>
+        </is>
+      </c>
+      <c r="Q354" t="inlineStr">
+        <is>
+          <t>2026-05-17 00:00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="355">
+      <c r="A355" t="inlineStr">
+        <is>
+          <t>2566049</t>
+        </is>
+      </c>
+      <c r="B355" t="inlineStr">
+        <is>
+          <t>EF4-0231964-6</t>
+        </is>
+      </c>
+      <c r="C355" t="inlineStr">
+        <is>
+          <t>Vessel, Container</t>
+        </is>
+      </c>
+      <c r="D355" t="inlineStr"/>
+      <c r="E355" t="inlineStr">
+        <is>
+          <t>9903.88.03</t>
+        </is>
+      </c>
+      <c r="F355" t="inlineStr">
+        <is>
+          <t>ARTICLE OF CHINA,US NTE 20(F)</t>
+        </is>
+      </c>
+      <c r="G355" t="inlineStr">
+        <is>
+          <t>003</t>
+        </is>
+      </c>
+      <c r="H355" t="inlineStr">
+        <is>
+          <t>9903.88.03</t>
+        </is>
+      </c>
+      <c r="I355" t="inlineStr">
+        <is>
+          <t>9903.03.06,9903.74.11,9903.94.05,8708.29.5160</t>
+        </is>
+      </c>
+      <c r="J355" t="inlineStr">
+        <is>
+          <t>BORGERS USA CORP</t>
+        </is>
+      </c>
+      <c r="K355" t="inlineStr">
+        <is>
+          <t>BORUSA</t>
+        </is>
+      </c>
+      <c r="L355" t="inlineStr">
+        <is>
+          <t>65-117296500</t>
+        </is>
+      </c>
+      <c r="M355" t="inlineStr">
+        <is>
+          <t>2026-06-22 00:00:00</t>
+        </is>
+      </c>
+      <c r="N355" t="inlineStr">
+        <is>
+          <t>2026-06-22 00:00:00</t>
+        </is>
+      </c>
+      <c r="O355" t="inlineStr">
+        <is>
+          <t>AUTONEUM (SHANGHAI) MANAGEMENT CO.</t>
+        </is>
+      </c>
+      <c r="P355" t="inlineStr">
+        <is>
+          <t>AUTONEUM (SHANGHAI) MANAGEMENT CO. LTD.</t>
+        </is>
+      </c>
+      <c r="Q355" t="inlineStr">
+        <is>
+          <t>2026-05-17 00:00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="356">
+      <c r="A356" t="inlineStr">
+        <is>
+          <t>2566049</t>
+        </is>
+      </c>
+      <c r="B356" t="inlineStr">
+        <is>
+          <t>EF4-0231964-6</t>
+        </is>
+      </c>
+      <c r="C356" t="inlineStr">
+        <is>
+          <t>Vessel, Container</t>
+        </is>
+      </c>
+      <c r="D356" t="inlineStr"/>
+      <c r="E356" t="inlineStr">
+        <is>
+          <t>9903.88.15</t>
+        </is>
+      </c>
+      <c r="F356" t="inlineStr">
+        <is>
+          <t>ARTICLE OF CHINA,US NTE 20(R)</t>
+        </is>
+      </c>
+      <c r="G356" t="inlineStr">
+        <is>
+          <t>004</t>
+        </is>
+      </c>
+      <c r="H356" t="inlineStr">
+        <is>
+          <t>9903.88.15</t>
+        </is>
+      </c>
+      <c r="I356" t="inlineStr">
+        <is>
+          <t>9903.03.06,9903.74.11,9903.94.05,8302.10.3000</t>
+        </is>
+      </c>
+      <c r="J356" t="inlineStr">
+        <is>
+          <t>BORGERS USA CORP</t>
+        </is>
+      </c>
+      <c r="K356" t="inlineStr">
+        <is>
+          <t>BORUSA</t>
+        </is>
+      </c>
+      <c r="L356" t="inlineStr">
+        <is>
+          <t>65-117296500</t>
+        </is>
+      </c>
+      <c r="M356" t="inlineStr">
+        <is>
+          <t>2026-06-22 00:00:00</t>
+        </is>
+      </c>
+      <c r="N356" t="inlineStr">
+        <is>
+          <t>2026-06-22 00:00:00</t>
+        </is>
+      </c>
+      <c r="O356" t="inlineStr">
+        <is>
+          <t>AUTONEUM (SHANGHAI) MANAGEMENT CO.</t>
+        </is>
+      </c>
+      <c r="P356" t="inlineStr">
+        <is>
+          <t>AUTONEUM (SHANGHAI) MANAGEMENT CO. LTD.</t>
+        </is>
+      </c>
+      <c r="Q356" t="inlineStr">
+        <is>
+          <t>2026-05-17 00:00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="357">
+      <c r="A357" t="inlineStr">
+        <is>
+          <t>2565952</t>
+        </is>
+      </c>
+      <c r="B357" t="inlineStr">
+        <is>
+          <t>EF4-0232005-7</t>
+        </is>
+      </c>
+      <c r="C357" t="inlineStr">
+        <is>
+          <t>Vessel, Container</t>
+        </is>
+      </c>
+      <c r="D357" t="inlineStr"/>
+      <c r="E357" t="inlineStr">
+        <is>
+          <t>9903.03.03</t>
+        </is>
+      </c>
+      <c r="F357" t="inlineStr">
+        <is>
+          <t>S122 -EXCLUSION-EXEMPTED PRDTS</t>
+        </is>
+      </c>
+      <c r="G357" t="inlineStr">
+        <is>
+          <t>001</t>
+        </is>
+      </c>
+      <c r="H357" t="inlineStr">
+        <is>
+          <t>9903.03.03</t>
+        </is>
+      </c>
+      <c r="I357" t="inlineStr">
+        <is>
+          <t>2930.90.9231</t>
+        </is>
+      </c>
+      <c r="J357" t="inlineStr">
+        <is>
+          <t>CASTLE CHEMICALS LTD</t>
+        </is>
+      </c>
+      <c r="K357" t="inlineStr">
+        <is>
+          <t>CASCHE01</t>
+        </is>
+      </c>
+      <c r="L357" t="inlineStr">
+        <is>
+          <t>151704-07138</t>
+        </is>
+      </c>
+      <c r="M357" t="inlineStr">
+        <is>
+          <t>2026-06-22 00:00:00</t>
+        </is>
+      </c>
+      <c r="N357" t="inlineStr">
+        <is>
+          <t>2026-06-22 00:00:00</t>
+        </is>
+      </c>
+      <c r="O357" t="inlineStr">
+        <is>
+          <t>HUBEI JIANGHAN NEW MATERIALS CO</t>
+        </is>
+      </c>
+      <c r="P357" t="inlineStr">
+        <is>
+          <t>HUBEI JIANGHAN NEW MATERIALS CO</t>
+        </is>
+      </c>
+      <c r="Q357" t="inlineStr">
+        <is>
+          <t>2026-05-19 00:00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="358">
+      <c r="A358" t="inlineStr">
+        <is>
+          <t>2565953</t>
+        </is>
+      </c>
+      <c r="B358" t="inlineStr">
+        <is>
+          <t>EF4-0232006-5</t>
+        </is>
+      </c>
+      <c r="C358" t="inlineStr">
+        <is>
+          <t>Vessel, Container</t>
+        </is>
+      </c>
+      <c r="D358" t="inlineStr"/>
+      <c r="E358" t="inlineStr">
+        <is>
+          <t>9903.03.03</t>
+        </is>
+      </c>
+      <c r="F358" t="inlineStr">
+        <is>
+          <t>S122 -EXCLUSION-EXEMPTED PRDTS</t>
+        </is>
+      </c>
+      <c r="G358" t="inlineStr">
+        <is>
+          <t>001</t>
+        </is>
+      </c>
+      <c r="H358" t="inlineStr">
+        <is>
+          <t>9903.03.03</t>
+        </is>
+      </c>
+      <c r="I358" t="inlineStr">
+        <is>
+          <t>2930.90.9231</t>
+        </is>
+      </c>
+      <c r="J358" t="inlineStr">
+        <is>
+          <t>CASTLE CHEMICALS LTD</t>
+        </is>
+      </c>
+      <c r="K358" t="inlineStr">
+        <is>
+          <t>CASCHE01</t>
+        </is>
+      </c>
+      <c r="L358" t="inlineStr">
+        <is>
+          <t>151704-07138</t>
+        </is>
+      </c>
+      <c r="M358" t="inlineStr">
+        <is>
+          <t>2026-06-22 00:00:00</t>
+        </is>
+      </c>
+      <c r="N358" t="inlineStr">
+        <is>
+          <t>2026-06-22 00:00:00</t>
+        </is>
+      </c>
+      <c r="O358" t="inlineStr">
+        <is>
+          <t>HUBEI JIANGHAN NEW MATERIALS CO</t>
+        </is>
+      </c>
+      <c r="P358" t="inlineStr">
+        <is>
+          <t>HUBEI JIANGHAN NEW MATERIALS CO</t>
+        </is>
+      </c>
+      <c r="Q358" t="inlineStr">
+        <is>
+          <t>2026-05-19 00:00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="359">
+      <c r="A359" t="inlineStr">
+        <is>
+          <t>2565954</t>
+        </is>
+      </c>
+      <c r="B359" t="inlineStr">
+        <is>
+          <t>EF4-0232007-3</t>
+        </is>
+      </c>
+      <c r="C359" t="inlineStr">
+        <is>
+          <t>Vessel, Container</t>
+        </is>
+      </c>
+      <c r="D359" t="inlineStr"/>
+      <c r="E359" t="inlineStr">
+        <is>
+          <t>9903.03.03</t>
+        </is>
+      </c>
+      <c r="F359" t="inlineStr">
+        <is>
+          <t>S122 -EXCLUSION-EXEMPTED PRDTS</t>
+        </is>
+      </c>
+      <c r="G359" t="inlineStr">
+        <is>
+          <t>001</t>
+        </is>
+      </c>
+      <c r="H359" t="inlineStr">
+        <is>
+          <t>9903.03.03</t>
+        </is>
+      </c>
+      <c r="I359" t="inlineStr">
+        <is>
+          <t>2930.90.9231</t>
+        </is>
+      </c>
+      <c r="J359" t="inlineStr">
+        <is>
+          <t>CASTLE CHEMICALS LTD</t>
+        </is>
+      </c>
+      <c r="K359" t="inlineStr">
+        <is>
+          <t>CASCHE01</t>
+        </is>
+      </c>
+      <c r="L359" t="inlineStr">
+        <is>
+          <t>151704-07138</t>
+        </is>
+      </c>
+      <c r="M359" t="inlineStr">
+        <is>
+          <t>2026-06-22 00:00:00</t>
+        </is>
+      </c>
+      <c r="N359" t="inlineStr">
+        <is>
+          <t>2026-06-22 00:00:00</t>
+        </is>
+      </c>
+      <c r="O359" t="inlineStr">
+        <is>
+          <t>HUBEI JIANGHAN NEW MATERIALS CO</t>
+        </is>
+      </c>
+      <c r="P359" t="inlineStr">
+        <is>
+          <t>HUBEI JIANGHAN NEW MATERIALS CO</t>
+        </is>
+      </c>
+      <c r="Q359" t="inlineStr">
+        <is>
+          <t>2026-05-19 00:00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="360">
+      <c r="A360" t="inlineStr">
+        <is>
+          <t>2565955</t>
+        </is>
+      </c>
+      <c r="B360" t="inlineStr">
+        <is>
+          <t>EF4-0232008-1</t>
+        </is>
+      </c>
+      <c r="C360" t="inlineStr">
+        <is>
+          <t>Vessel, Container</t>
+        </is>
+      </c>
+      <c r="D360" t="inlineStr"/>
+      <c r="E360" t="inlineStr">
+        <is>
+          <t>9903.03.03</t>
+        </is>
+      </c>
+      <c r="F360" t="inlineStr">
+        <is>
+          <t>S122 -EXCLUSION-EXEMPTED PRDTS</t>
+        </is>
+      </c>
+      <c r="G360" t="inlineStr">
+        <is>
+          <t>001</t>
+        </is>
+      </c>
+      <c r="H360" t="inlineStr">
+        <is>
+          <t>9903.03.03</t>
+        </is>
+      </c>
+      <c r="I360" t="inlineStr">
+        <is>
+          <t>2930.90.9231</t>
+        </is>
+      </c>
+      <c r="J360" t="inlineStr">
+        <is>
+          <t>CASTLE CHEMICALS LTD</t>
+        </is>
+      </c>
+      <c r="K360" t="inlineStr">
+        <is>
+          <t>CASCHE01</t>
+        </is>
+      </c>
+      <c r="L360" t="inlineStr">
+        <is>
+          <t>151704-07138</t>
+        </is>
+      </c>
+      <c r="M360" t="inlineStr">
+        <is>
+          <t>2026-06-22 00:00:00</t>
+        </is>
+      </c>
+      <c r="N360" t="inlineStr">
+        <is>
+          <t>2026-06-22 00:00:00</t>
+        </is>
+      </c>
+      <c r="O360" t="inlineStr">
+        <is>
+          <t>HUBEI JIANGHAN NEW MATERIALS CO</t>
+        </is>
+      </c>
+      <c r="P360" t="inlineStr">
+        <is>
+          <t>HUBEI JIANGHAN NEW MATERIALS CO</t>
+        </is>
+      </c>
+      <c r="Q360" t="inlineStr">
+        <is>
+          <t>2026-05-19 00:00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="361">
+      <c r="A361" t="inlineStr">
+        <is>
+          <t>2566243</t>
+        </is>
+      </c>
+      <c r="B361" t="inlineStr">
+        <is>
+          <t>EF4-0232301-0</t>
+        </is>
+      </c>
+      <c r="C361" t="inlineStr">
+        <is>
+          <t>Vessel, Container</t>
+        </is>
+      </c>
+      <c r="D361" t="inlineStr"/>
+      <c r="E361" t="inlineStr">
+        <is>
+          <t>9903.03.01</t>
+        </is>
+      </c>
+      <c r="F361" t="inlineStr">
+        <is>
           <t>SECTION 122 - 10% DUTY</t>
         </is>
       </c>
-      <c r="G353" t="inlineStr">
+      <c r="G361" t="inlineStr">
+        <is>
+          <t>001</t>
+        </is>
+      </c>
+      <c r="H361" t="inlineStr">
+        <is>
+          <t>9903.03.01</t>
+        </is>
+      </c>
+      <c r="I361" t="inlineStr">
+        <is>
+          <t>3920.20.0055</t>
+        </is>
+      </c>
+      <c r="J361" t="inlineStr">
+        <is>
+          <t>GULF ATLANTIC PACKAGING CORP</t>
+        </is>
+      </c>
+      <c r="K361" t="inlineStr">
+        <is>
+          <t>GULATL</t>
+        </is>
+      </c>
+      <c r="L361" t="inlineStr">
+        <is>
+          <t>58-184378700</t>
+        </is>
+      </c>
+      <c r="M361" t="inlineStr">
+        <is>
+          <t>2026-06-22 00:00:00</t>
+        </is>
+      </c>
+      <c r="N361" t="inlineStr">
+        <is>
+          <t>2026-06-22 00:00:00</t>
+        </is>
+      </c>
+      <c r="O361" t="inlineStr">
+        <is>
+          <t>SEKISUI JUSHI BV</t>
+        </is>
+      </c>
+      <c r="P361" t="inlineStr">
+        <is>
+          <t>SEKISUI JUSHI BV</t>
+        </is>
+      </c>
+      <c r="Q361" t="inlineStr">
+        <is>
+          <t>2026-05-30 00:00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="362">
+      <c r="A362" t="inlineStr">
+        <is>
+          <t>2566128</t>
+        </is>
+      </c>
+      <c r="B362" t="inlineStr">
+        <is>
+          <t>EF4-0232453-9</t>
+        </is>
+      </c>
+      <c r="C362" t="inlineStr">
+        <is>
+          <t>Vessel, Container</t>
+        </is>
+      </c>
+      <c r="D362" t="inlineStr">
+        <is>
+          <t>V1626463577</t>
+        </is>
+      </c>
+      <c r="E362" t="inlineStr">
+        <is>
+          <t>9903.03.01</t>
+        </is>
+      </c>
+      <c r="F362" t="inlineStr"/>
+      <c r="G362" t="inlineStr">
+        <is>
+          <t>001</t>
+        </is>
+      </c>
+      <c r="H362" t="inlineStr">
+        <is>
+          <t>9903.03.01</t>
+        </is>
+      </c>
+      <c r="I362" t="inlineStr">
+        <is>
+          <t>1108.12.0010</t>
+        </is>
+      </c>
+      <c r="J362" t="inlineStr">
+        <is>
+          <t>ROYAL INGREDIENTS GROUP BV</t>
+        </is>
+      </c>
+      <c r="K362" t="inlineStr">
+        <is>
+          <t>ROYINGRE</t>
+        </is>
+      </c>
+      <c r="L362" t="inlineStr">
+        <is>
+          <t>074601-00962</t>
+        </is>
+      </c>
+      <c r="M362" t="inlineStr">
+        <is>
+          <t>2026-06-22 00:00:00</t>
+        </is>
+      </c>
+      <c r="N362" t="inlineStr">
+        <is>
+          <t>2026-06-22 00:00:00</t>
+        </is>
+      </c>
+      <c r="O362" t="inlineStr">
+        <is>
+          <t>TAT NISASTA INS SAN TIC AS</t>
+        </is>
+      </c>
+      <c r="P362" t="inlineStr">
+        <is>
+          <t>TAT NISASTA INS SAN TIC AS</t>
+        </is>
+      </c>
+      <c r="Q362" t="inlineStr">
+        <is>
+          <t>2026-05-30 00:00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="363">
+      <c r="A363" t="inlineStr">
+        <is>
+          <t>4539472</t>
+        </is>
+      </c>
+      <c r="B363" t="inlineStr">
+        <is>
+          <t>EF4-0232482-8</t>
+        </is>
+      </c>
+      <c r="C363" t="inlineStr">
+        <is>
+          <t>Air, Non-container</t>
+        </is>
+      </c>
+      <c r="D363" t="inlineStr">
+        <is>
+          <t>V1626463577</t>
+        </is>
+      </c>
+      <c r="E363" t="inlineStr">
+        <is>
+          <t>9903.03.01</t>
+        </is>
+      </c>
+      <c r="F363" t="inlineStr">
+        <is>
+          <t>SECTION 122 - 10% DUTY</t>
+        </is>
+      </c>
+      <c r="G363" t="inlineStr">
+        <is>
+          <t>001</t>
+        </is>
+      </c>
+      <c r="H363" t="inlineStr">
+        <is>
+          <t>9903.03.01</t>
+        </is>
+      </c>
+      <c r="I363" t="inlineStr">
+        <is>
+          <t>9026.20.4000</t>
+        </is>
+      </c>
+      <c r="J363" t="inlineStr">
+        <is>
+          <t>JRCRUZ CORP</t>
+        </is>
+      </c>
+      <c r="K363" t="inlineStr">
+        <is>
+          <t>JRCCOR01</t>
+        </is>
+      </c>
+      <c r="L363" t="inlineStr">
+        <is>
+          <t>22-337379600</t>
+        </is>
+      </c>
+      <c r="M363" t="inlineStr">
+        <is>
+          <t>2026-06-20 00:00:00</t>
+        </is>
+      </c>
+      <c r="N363" t="inlineStr">
+        <is>
+          <t>2026-06-22 00:00:00</t>
+        </is>
+      </c>
+      <c r="O363" t="inlineStr">
+        <is>
+          <t>JACKCONTROL AG</t>
+        </is>
+      </c>
+      <c r="P363" t="inlineStr">
+        <is>
+          <t>JACKCONTROL AG</t>
+        </is>
+      </c>
+      <c r="Q363" t="inlineStr">
+        <is>
+          <t>2026-06-20 00:00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="364">
+      <c r="A364" t="inlineStr">
+        <is>
+          <t>2565907</t>
+        </is>
+      </c>
+      <c r="B364" t="inlineStr">
+        <is>
+          <t>EF4-0232496-8</t>
+        </is>
+      </c>
+      <c r="C364" t="inlineStr">
+        <is>
+          <t>Vessel, Container</t>
+        </is>
+      </c>
+      <c r="D364" t="inlineStr">
+        <is>
+          <t>V0413937900</t>
+        </is>
+      </c>
+      <c r="E364" t="inlineStr">
+        <is>
+          <t>9903.03.06</t>
+        </is>
+      </c>
+      <c r="F364" t="inlineStr">
+        <is>
+          <t>S122 EXCL,IRN/STL/ALUM,DERIV</t>
+        </is>
+      </c>
+      <c r="G364" t="inlineStr">
+        <is>
+          <t>001</t>
+        </is>
+      </c>
+      <c r="H364" t="inlineStr">
+        <is>
+          <t>9903.03.06</t>
+        </is>
+      </c>
+      <c r="I364" t="inlineStr">
+        <is>
+          <t>9903.82.02,7222.20.0043</t>
+        </is>
+      </c>
+      <c r="J364" t="inlineStr">
+        <is>
+          <t>MESHA STEELS  LLC</t>
+        </is>
+      </c>
+      <c r="K364" t="inlineStr">
+        <is>
+          <t>MESSTE</t>
+        </is>
+      </c>
+      <c r="L364" t="inlineStr">
+        <is>
+          <t>20-274801900</t>
+        </is>
+      </c>
+      <c r="M364" t="inlineStr">
+        <is>
+          <t>2026-06-17 00:00:00</t>
+        </is>
+      </c>
+      <c r="N364" t="inlineStr">
+        <is>
+          <t>2026-06-22 00:00:00</t>
+        </is>
+      </c>
+      <c r="O364" t="inlineStr">
+        <is>
+          <t>BHANSALI BRIGHT BARS PVT. LTD.</t>
+        </is>
+      </c>
+      <c r="P364" t="inlineStr">
+        <is>
+          <t>BHANSALI BRIGHT BARS PVT. LTD.</t>
+        </is>
+      </c>
+      <c r="Q364" t="inlineStr">
+        <is>
+          <t>2026-05-11 00:00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="365">
+      <c r="A365" t="inlineStr">
+        <is>
+          <t>2565907</t>
+        </is>
+      </c>
+      <c r="B365" t="inlineStr">
+        <is>
+          <t>EF4-0232496-8</t>
+        </is>
+      </c>
+      <c r="C365" t="inlineStr">
+        <is>
+          <t>Vessel, Container</t>
+        </is>
+      </c>
+      <c r="D365" t="inlineStr">
+        <is>
+          <t>V0413937900</t>
+        </is>
+      </c>
+      <c r="E365" t="inlineStr">
+        <is>
+          <t>9903.03.06</t>
+        </is>
+      </c>
+      <c r="F365" t="inlineStr">
+        <is>
+          <t>S122 EXCL,IRN/STL/ALUM,DERIV</t>
+        </is>
+      </c>
+      <c r="G365" t="inlineStr">
         <is>
           <t>002</t>
         </is>
       </c>
-      <c r="H353" t="inlineStr">
-        <is>
-          <t>9903.03.01</t>
-        </is>
-      </c>
-      <c r="I353" t="inlineStr">
-        <is>
-          <t>2916.14.2050</t>
-        </is>
-      </c>
-      <c r="J353" t="inlineStr">
-        <is>
-          <t>JOBACHEM CORPORATION</t>
-        </is>
-      </c>
-      <c r="K353" t="inlineStr">
-        <is>
-          <t>JOBLP01</t>
-        </is>
-      </c>
-      <c r="L353" t="inlineStr">
-        <is>
-          <t>32-052169200</t>
-        </is>
-      </c>
-      <c r="M353" t="inlineStr">
+      <c r="H365" t="inlineStr">
+        <is>
+          <t>9903.03.06</t>
+        </is>
+      </c>
+      <c r="I365" t="inlineStr">
+        <is>
+          <t>9903.82.02,7222.20.0073</t>
+        </is>
+      </c>
+      <c r="J365" t="inlineStr">
+        <is>
+          <t>MESHA STEELS  LLC</t>
+        </is>
+      </c>
+      <c r="K365" t="inlineStr">
+        <is>
+          <t>MESSTE</t>
+        </is>
+      </c>
+      <c r="L365" t="inlineStr">
+        <is>
+          <t>20-274801900</t>
+        </is>
+      </c>
+      <c r="M365" t="inlineStr">
+        <is>
+          <t>2026-06-17 00:00:00</t>
+        </is>
+      </c>
+      <c r="N365" t="inlineStr">
         <is>
           <t>2026-06-22 00:00:00</t>
         </is>
       </c>
-      <c r="N353" t="inlineStr">
-        <is>
-          <t>2026-06-21 00:00:00</t>
-        </is>
-      </c>
-      <c r="O353" t="inlineStr">
-        <is>
-          <t>JOBACHEM GMBH</t>
-        </is>
-      </c>
-      <c r="P353" t="inlineStr">
-        <is>
-          <t>JOBACHEM GMBH</t>
-        </is>
-      </c>
-      <c r="Q353" t="inlineStr">
-        <is>
-          <t>2026-06-06 00:00:00</t>
+      <c r="O365" t="inlineStr">
+        <is>
+          <t>BHANSALI BRIGHT BARS PVT. LTD.</t>
+        </is>
+      </c>
+      <c r="P365" t="inlineStr">
+        <is>
+          <t>BHANSALI BRIGHT BARS PVT. LTD.</t>
+        </is>
+      </c>
+      <c r="Q365" t="inlineStr">
+        <is>
+          <t>2026-05-11 00:00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="366">
+      <c r="A366" t="inlineStr">
+        <is>
+          <t>2566336</t>
+        </is>
+      </c>
+      <c r="B366" t="inlineStr">
+        <is>
+          <t>EF4-0232529-6</t>
+        </is>
+      </c>
+      <c r="C366" t="inlineStr">
+        <is>
+          <t>Vessel, Container</t>
+        </is>
+      </c>
+      <c r="D366" t="inlineStr">
+        <is>
+          <t>V0413937900</t>
+        </is>
+      </c>
+      <c r="E366" t="inlineStr">
+        <is>
+          <t>9903.03.01</t>
+        </is>
+      </c>
+      <c r="F366" t="inlineStr">
+        <is>
+          <t>SECTION 122 - 10% DUTY</t>
+        </is>
+      </c>
+      <c r="G366" t="inlineStr">
+        <is>
+          <t>001</t>
+        </is>
+      </c>
+      <c r="H366" t="inlineStr">
+        <is>
+          <t>9903.03.01</t>
+        </is>
+      </c>
+      <c r="I366" t="inlineStr">
+        <is>
+          <t>8422.30.9130</t>
+        </is>
+      </c>
+      <c r="J366" t="inlineStr">
+        <is>
+          <t>MANKIEWICZ COATINGS, LLC</t>
+        </is>
+      </c>
+      <c r="K366" t="inlineStr">
+        <is>
+          <t>MANCOAT</t>
+        </is>
+      </c>
+      <c r="L366" t="inlineStr">
+        <is>
+          <t>56-202308900</t>
+        </is>
+      </c>
+      <c r="M366" t="inlineStr">
+        <is>
+          <t>2026-06-22 00:00:00</t>
+        </is>
+      </c>
+      <c r="N366" t="inlineStr">
+        <is>
+          <t>2026-06-22 00:00:00</t>
+        </is>
+      </c>
+      <c r="O366" t="inlineStr">
+        <is>
+          <t>MANKIEWICZ GEBR. &amp; CO.</t>
+        </is>
+      </c>
+      <c r="P366" t="inlineStr">
+        <is>
+          <t>MANKIEWICZ GEBR. &amp; CO.</t>
+        </is>
+      </c>
+      <c r="Q366" t="inlineStr">
+        <is>
+          <t>2026-06-13 00:00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="367">
+      <c r="A367" t="inlineStr">
+        <is>
+          <t>2566336</t>
+        </is>
+      </c>
+      <c r="B367" t="inlineStr">
+        <is>
+          <t>EF4-0232529-6</t>
+        </is>
+      </c>
+      <c r="C367" t="inlineStr">
+        <is>
+          <t>Vessel, Container</t>
+        </is>
+      </c>
+      <c r="D367" t="inlineStr">
+        <is>
+          <t>V0413937900</t>
+        </is>
+      </c>
+      <c r="E367" t="inlineStr">
+        <is>
+          <t>9903.03.06</t>
+        </is>
+      </c>
+      <c r="F367" t="inlineStr">
+        <is>
+          <t>S122 EXCL,IRN/STL/ALUM,DERIV</t>
+        </is>
+      </c>
+      <c r="G367" t="inlineStr">
+        <is>
+          <t>002</t>
+        </is>
+      </c>
+      <c r="H367" t="inlineStr">
+        <is>
+          <t>9903.03.06</t>
+        </is>
+      </c>
+      <c r="I367" t="inlineStr">
+        <is>
+          <t>9903.82.02,7309.00.0030</t>
+        </is>
+      </c>
+      <c r="J367" t="inlineStr">
+        <is>
+          <t>MANKIEWICZ COATINGS, LLC</t>
+        </is>
+      </c>
+      <c r="K367" t="inlineStr">
+        <is>
+          <t>MANCOAT</t>
+        </is>
+      </c>
+      <c r="L367" t="inlineStr">
+        <is>
+          <t>56-202308900</t>
+        </is>
+      </c>
+      <c r="M367" t="inlineStr">
+        <is>
+          <t>2026-06-22 00:00:00</t>
+        </is>
+      </c>
+      <c r="N367" t="inlineStr">
+        <is>
+          <t>2026-06-22 00:00:00</t>
+        </is>
+      </c>
+      <c r="O367" t="inlineStr">
+        <is>
+          <t>MANKIEWICZ GEBR. &amp; CO.</t>
+        </is>
+      </c>
+      <c r="P367" t="inlineStr">
+        <is>
+          <t>MANKIEWICZ GEBR. &amp; CO.</t>
+        </is>
+      </c>
+      <c r="Q367" t="inlineStr">
+        <is>
+          <t>2026-06-13 00:00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="368">
+      <c r="A368" t="inlineStr">
+        <is>
+          <t>2566336</t>
+        </is>
+      </c>
+      <c r="B368" t="inlineStr">
+        <is>
+          <t>EF4-0232529-6</t>
+        </is>
+      </c>
+      <c r="C368" t="inlineStr">
+        <is>
+          <t>Vessel, Container</t>
+        </is>
+      </c>
+      <c r="D368" t="inlineStr">
+        <is>
+          <t>V0413937900</t>
+        </is>
+      </c>
+      <c r="E368" t="inlineStr">
+        <is>
+          <t>9903.03.01</t>
+        </is>
+      </c>
+      <c r="F368" t="inlineStr">
+        <is>
+          <t>SECTION 122 - 10% DUTY</t>
+        </is>
+      </c>
+      <c r="G368" t="inlineStr">
+        <is>
+          <t>003</t>
+        </is>
+      </c>
+      <c r="H368" t="inlineStr">
+        <is>
+          <t>9903.03.01</t>
+        </is>
+      </c>
+      <c r="I368" t="inlineStr">
+        <is>
+          <t>8479.82.0040</t>
+        </is>
+      </c>
+      <c r="J368" t="inlineStr">
+        <is>
+          <t>MANKIEWICZ COATINGS, LLC</t>
+        </is>
+      </c>
+      <c r="K368" t="inlineStr">
+        <is>
+          <t>MANCOAT</t>
+        </is>
+      </c>
+      <c r="L368" t="inlineStr">
+        <is>
+          <t>56-202308900</t>
+        </is>
+      </c>
+      <c r="M368" t="inlineStr">
+        <is>
+          <t>2026-06-22 00:00:00</t>
+        </is>
+      </c>
+      <c r="N368" t="inlineStr">
+        <is>
+          <t>2026-06-22 00:00:00</t>
+        </is>
+      </c>
+      <c r="O368" t="inlineStr">
+        <is>
+          <t>MANKIEWICZ GEBR. &amp; CO.</t>
+        </is>
+      </c>
+      <c r="P368" t="inlineStr">
+        <is>
+          <t>MANKIEWICZ GEBR. &amp; CO.</t>
+        </is>
+      </c>
+      <c r="Q368" t="inlineStr">
+        <is>
+          <t>2026-06-13 00:00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="369">
+      <c r="A369" t="inlineStr">
+        <is>
+          <t>2566336</t>
+        </is>
+      </c>
+      <c r="B369" t="inlineStr">
+        <is>
+          <t>EF4-0232529-6</t>
+        </is>
+      </c>
+      <c r="C369" t="inlineStr">
+        <is>
+          <t>Vessel, Container</t>
+        </is>
+      </c>
+      <c r="D369" t="inlineStr">
+        <is>
+          <t>V0413937900</t>
+        </is>
+      </c>
+      <c r="E369" t="inlineStr">
+        <is>
+          <t>9903.03.06</t>
+        </is>
+      </c>
+      <c r="F369" t="inlineStr">
+        <is>
+          <t>S122 EXCL,IRN/STL/ALUM,DERIV</t>
+        </is>
+      </c>
+      <c r="G369" t="inlineStr">
+        <is>
+          <t>004</t>
+        </is>
+      </c>
+      <c r="H369" t="inlineStr">
+        <is>
+          <t>9903.03.06</t>
+        </is>
+      </c>
+      <c r="I369" t="inlineStr">
+        <is>
+          <t>9903.82.02,7309.00.0030</t>
+        </is>
+      </c>
+      <c r="J369" t="inlineStr">
+        <is>
+          <t>MANKIEWICZ COATINGS, LLC</t>
+        </is>
+      </c>
+      <c r="K369" t="inlineStr">
+        <is>
+          <t>MANCOAT</t>
+        </is>
+      </c>
+      <c r="L369" t="inlineStr">
+        <is>
+          <t>56-202308900</t>
+        </is>
+      </c>
+      <c r="M369" t="inlineStr">
+        <is>
+          <t>2026-06-22 00:00:00</t>
+        </is>
+      </c>
+      <c r="N369" t="inlineStr">
+        <is>
+          <t>2026-06-22 00:00:00</t>
+        </is>
+      </c>
+      <c r="O369" t="inlineStr">
+        <is>
+          <t>MANKIEWICZ GEBR. &amp; CO.</t>
+        </is>
+      </c>
+      <c r="P369" t="inlineStr">
+        <is>
+          <t>MANKIEWICZ GEBR. &amp; CO.</t>
+        </is>
+      </c>
+      <c r="Q369" t="inlineStr">
+        <is>
+          <t>2026-06-13 00:00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="370">
+      <c r="A370" t="inlineStr">
+        <is>
+          <t>2566336</t>
+        </is>
+      </c>
+      <c r="B370" t="inlineStr">
+        <is>
+          <t>EF4-0232529-6</t>
+        </is>
+      </c>
+      <c r="C370" t="inlineStr">
+        <is>
+          <t>Vessel, Container</t>
+        </is>
+      </c>
+      <c r="D370" t="inlineStr">
+        <is>
+          <t>V0413937900</t>
+        </is>
+      </c>
+      <c r="E370" t="inlineStr">
+        <is>
+          <t>9903.03.01</t>
+        </is>
+      </c>
+      <c r="F370" t="inlineStr">
+        <is>
+          <t>SECTION 122 - 10% DUTY</t>
+        </is>
+      </c>
+      <c r="G370" t="inlineStr">
+        <is>
+          <t>005</t>
+        </is>
+      </c>
+      <c r="H370" t="inlineStr">
+        <is>
+          <t>9903.03.01</t>
+        </is>
+      </c>
+      <c r="I370" t="inlineStr">
+        <is>
+          <t>8479.82.0040</t>
+        </is>
+      </c>
+      <c r="J370" t="inlineStr">
+        <is>
+          <t>MANKIEWICZ COATINGS, LLC</t>
+        </is>
+      </c>
+      <c r="K370" t="inlineStr">
+        <is>
+          <t>MANCOAT</t>
+        </is>
+      </c>
+      <c r="L370" t="inlineStr">
+        <is>
+          <t>56-202308900</t>
+        </is>
+      </c>
+      <c r="M370" t="inlineStr">
+        <is>
+          <t>2026-06-22 00:00:00</t>
+        </is>
+      </c>
+      <c r="N370" t="inlineStr">
+        <is>
+          <t>2026-06-22 00:00:00</t>
+        </is>
+      </c>
+      <c r="O370" t="inlineStr">
+        <is>
+          <t>MANKIEWICZ GEBR. &amp; CO.</t>
+        </is>
+      </c>
+      <c r="P370" t="inlineStr">
+        <is>
+          <t>MANKIEWICZ GEBR. &amp; CO.</t>
+        </is>
+      </c>
+      <c r="Q370" t="inlineStr">
+        <is>
+          <t>2026-06-13 00:00:00</t>
         </is>
       </c>
     </row>

--- a/trimika_data.xlsx
+++ b/trimika_data.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q370"/>
+  <dimension ref="A1:Q379"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -15088,12 +15088,12 @@
     <row r="176">
       <c r="A176" t="inlineStr">
         <is>
-          <t>2566066</t>
+          <t>2615746</t>
         </is>
       </c>
       <c r="B176" t="inlineStr">
         <is>
-          <t>EF4-0232182-4</t>
+          <t>EF4-0232312-7</t>
         </is>
       </c>
       <c r="C176" t="inlineStr">
@@ -15103,7 +15103,7 @@
       </c>
       <c r="D176" t="inlineStr">
         <is>
-          <t>V0710334850</t>
+          <t>V1626459823</t>
         </is>
       </c>
       <c r="E176" t="inlineStr">
@@ -15128,22 +15128,22 @@
       </c>
       <c r="I176" t="inlineStr">
         <is>
-          <t>1702.30.4085</t>
+          <t>8412.80.1000</t>
         </is>
       </c>
       <c r="J176" t="inlineStr">
         <is>
-          <t>ROYAL INGREDIENTS GROUP BV</t>
+          <t>BORGERS USA CORP</t>
         </is>
       </c>
       <c r="K176" t="inlineStr">
         <is>
-          <t>ROYINGRE</t>
+          <t>BORUSA</t>
         </is>
       </c>
       <c r="L176" t="inlineStr">
         <is>
-          <t>074601-00962</t>
+          <t>65-117296500</t>
         </is>
       </c>
       <c r="M176" t="inlineStr">
@@ -15158,17 +15158,17 @@
       </c>
       <c r="O176" t="inlineStr">
         <is>
-          <t>AK NISASTA SANAYI VE TICARET AS</t>
+          <t>FKT GMBH</t>
         </is>
       </c>
       <c r="P176" t="inlineStr">
         <is>
-          <t>AK NISASTA SANAYI VE TICARET AS</t>
+          <t>FKT GMBH</t>
         </is>
       </c>
       <c r="Q176" t="inlineStr">
         <is>
-          <t>2026-05-27 00:00:00</t>
+          <t>2026-06-05 00:00:00</t>
         </is>
       </c>
     </row>
@@ -15195,27 +15195,27 @@
       </c>
       <c r="E177" t="inlineStr">
         <is>
-          <t>9903.03.01</t>
+          <t>9903.03.06</t>
         </is>
       </c>
       <c r="F177" t="inlineStr">
         <is>
-          <t>SECTION 122 - 10% DUTY</t>
+          <t>S122 EXCL,IRN/STL/ALUM,DERIV</t>
         </is>
       </c>
       <c r="G177" t="inlineStr">
         <is>
-          <t>001</t>
+          <t>002</t>
         </is>
       </c>
       <c r="H177" t="inlineStr">
         <is>
-          <t>9903.03.01</t>
+          <t>9903.03.06</t>
         </is>
       </c>
       <c r="I177" t="inlineStr">
         <is>
-          <t>8412.80.1000</t>
+          <t>9903.82.10,8479.90.9596</t>
         </is>
       </c>
       <c r="J177" t="inlineStr">
@@ -15282,27 +15282,27 @@
       </c>
       <c r="E178" t="inlineStr">
         <is>
-          <t>9903.03.06</t>
+          <t>9903.03.01</t>
         </is>
       </c>
       <c r="F178" t="inlineStr">
         <is>
-          <t>S122 EXCL,IRN/STL/ALUM,DERIV</t>
+          <t>SECTION 122 - 10% DUTY</t>
         </is>
       </c>
       <c r="G178" t="inlineStr">
         <is>
-          <t>002</t>
+          <t>003</t>
         </is>
       </c>
       <c r="H178" t="inlineStr">
         <is>
-          <t>9903.03.06</t>
+          <t>9903.03.01</t>
         </is>
       </c>
       <c r="I178" t="inlineStr">
         <is>
-          <t>9903.82.10,8479.90.9596</t>
+          <t>8412.80.1000</t>
         </is>
       </c>
       <c r="J178" t="inlineStr">
@@ -15349,12 +15349,12 @@
     <row r="179">
       <c r="A179" t="inlineStr">
         <is>
-          <t>2615746</t>
+          <t>2566191</t>
         </is>
       </c>
       <c r="B179" t="inlineStr">
         <is>
-          <t>EF4-0232312-7</t>
+          <t>EF4-0232317-6</t>
         </is>
       </c>
       <c r="C179" t="inlineStr">
@@ -15362,11 +15362,7 @@
           <t>Vessel, Container</t>
         </is>
       </c>
-      <c r="D179" t="inlineStr">
-        <is>
-          <t>V1626459823</t>
-        </is>
-      </c>
+      <c r="D179" t="inlineStr"/>
       <c r="E179" t="inlineStr">
         <is>
           <t>9903.03.01</t>
@@ -15379,7 +15375,7 @@
       </c>
       <c r="G179" t="inlineStr">
         <is>
-          <t>003</t>
+          <t>001</t>
         </is>
       </c>
       <c r="H179" t="inlineStr">
@@ -15389,22 +15385,22 @@
       </c>
       <c r="I179" t="inlineStr">
         <is>
-          <t>8412.80.1000</t>
+          <t>1109.00.9020</t>
         </is>
       </c>
       <c r="J179" t="inlineStr">
         <is>
-          <t>BORGERS USA CORP</t>
+          <t>ROYAL INGREDIENTS GROUP BV</t>
         </is>
       </c>
       <c r="K179" t="inlineStr">
         <is>
-          <t>BORUSA</t>
+          <t>ROYINGRE</t>
         </is>
       </c>
       <c r="L179" t="inlineStr">
         <is>
-          <t>65-117296500</t>
+          <t>074601-00962</t>
         </is>
       </c>
       <c r="M179" t="inlineStr">
@@ -15419,29 +15415,29 @@
       </c>
       <c r="O179" t="inlineStr">
         <is>
-          <t>FKT GMBH</t>
+          <t>JACKERING MUHLEN UND NAHRMITTELWERK</t>
         </is>
       </c>
       <c r="P179" t="inlineStr">
         <is>
-          <t>FKT GMBH</t>
+          <t>JACKERING MUHLEN UND NAHRMITTELWERKE GMBH</t>
         </is>
       </c>
       <c r="Q179" t="inlineStr">
         <is>
-          <t>2026-06-05 00:00:00</t>
+          <t>2026-06-03 00:00:00</t>
         </is>
       </c>
     </row>
     <row r="180">
       <c r="A180" t="inlineStr">
         <is>
-          <t>2566191</t>
+          <t>2566270</t>
         </is>
       </c>
       <c r="B180" t="inlineStr">
         <is>
-          <t>EF4-0232317-6</t>
+          <t>EF4-0232359-8</t>
         </is>
       </c>
       <c r="C180" t="inlineStr">
@@ -15472,22 +15468,22 @@
       </c>
       <c r="I180" t="inlineStr">
         <is>
-          <t>1109.00.9020</t>
+          <t>3208.20.0000</t>
         </is>
       </c>
       <c r="J180" t="inlineStr">
         <is>
-          <t>ROYAL INGREDIENTS GROUP BV</t>
+          <t>MANKIEWICZ COATINGS, LLC</t>
         </is>
       </c>
       <c r="K180" t="inlineStr">
         <is>
-          <t>ROYINGRE</t>
+          <t>MANCOAT</t>
         </is>
       </c>
       <c r="L180" t="inlineStr">
         <is>
-          <t>074601-00962</t>
+          <t>56-202308900</t>
         </is>
       </c>
       <c r="M180" t="inlineStr">
@@ -15502,17 +15498,17 @@
       </c>
       <c r="O180" t="inlineStr">
         <is>
-          <t>JACKERING MUHLEN UND NAHRMITTELWERK</t>
+          <t>RUDT INDUSTRIELACKE GMBH</t>
         </is>
       </c>
       <c r="P180" t="inlineStr">
         <is>
-          <t>JACKERING MUHLEN UND NAHRMITTELWERKE GMBH</t>
+          <t>RUDT INDUSTRIELACKE GMBH</t>
         </is>
       </c>
       <c r="Q180" t="inlineStr">
         <is>
-          <t>2026-06-03 00:00:00</t>
+          <t>2026-06-05 00:00:00</t>
         </is>
       </c>
     </row>
@@ -15545,7 +15541,7 @@
       </c>
       <c r="G181" t="inlineStr">
         <is>
-          <t>001</t>
+          <t>002</t>
         </is>
       </c>
       <c r="H181" t="inlineStr">
@@ -15628,7 +15624,7 @@
       </c>
       <c r="G182" t="inlineStr">
         <is>
-          <t>002</t>
+          <t>003</t>
         </is>
       </c>
       <c r="H182" t="inlineStr">
@@ -15711,7 +15707,7 @@
       </c>
       <c r="G183" t="inlineStr">
         <is>
-          <t>003</t>
+          <t>004</t>
         </is>
       </c>
       <c r="H183" t="inlineStr">
@@ -15794,7 +15790,7 @@
       </c>
       <c r="G184" t="inlineStr">
         <is>
-          <t>004</t>
+          <t>005</t>
         </is>
       </c>
       <c r="H184" t="inlineStr">
@@ -15877,7 +15873,7 @@
       </c>
       <c r="G185" t="inlineStr">
         <is>
-          <t>005</t>
+          <t>006</t>
         </is>
       </c>
       <c r="H185" t="inlineStr">
@@ -15960,7 +15956,7 @@
       </c>
       <c r="G186" t="inlineStr">
         <is>
-          <t>006</t>
+          <t>007</t>
         </is>
       </c>
       <c r="H186" t="inlineStr">
@@ -16043,7 +16039,7 @@
       </c>
       <c r="G187" t="inlineStr">
         <is>
-          <t>007</t>
+          <t>008</t>
         </is>
       </c>
       <c r="H187" t="inlineStr">
@@ -16053,7 +16049,7 @@
       </c>
       <c r="I187" t="inlineStr">
         <is>
-          <t>3208.20.0000</t>
+          <t>3208.90.0000</t>
         </is>
       </c>
       <c r="J187" t="inlineStr">
@@ -16126,7 +16122,7 @@
       </c>
       <c r="G188" t="inlineStr">
         <is>
-          <t>008</t>
+          <t>009</t>
         </is>
       </c>
       <c r="H188" t="inlineStr">
@@ -16136,7 +16132,7 @@
       </c>
       <c r="I188" t="inlineStr">
         <is>
-          <t>3208.90.0000</t>
+          <t>3208.20.0000</t>
         </is>
       </c>
       <c r="J188" t="inlineStr">
@@ -16209,7 +16205,7 @@
       </c>
       <c r="G189" t="inlineStr">
         <is>
-          <t>009</t>
+          <t>010</t>
         </is>
       </c>
       <c r="H189" t="inlineStr">
@@ -16219,7 +16215,7 @@
       </c>
       <c r="I189" t="inlineStr">
         <is>
-          <t>3208.20.0000</t>
+          <t>3208.10.0000</t>
         </is>
       </c>
       <c r="J189" t="inlineStr">
@@ -16292,7 +16288,7 @@
       </c>
       <c r="G190" t="inlineStr">
         <is>
-          <t>010</t>
+          <t>011</t>
         </is>
       </c>
       <c r="H190" t="inlineStr">
@@ -16302,7 +16298,7 @@
       </c>
       <c r="I190" t="inlineStr">
         <is>
-          <t>3208.10.0000</t>
+          <t>3208.20.0000</t>
         </is>
       </c>
       <c r="J190" t="inlineStr">
@@ -16375,7 +16371,7 @@
       </c>
       <c r="G191" t="inlineStr">
         <is>
-          <t>011</t>
+          <t>012</t>
         </is>
       </c>
       <c r="H191" t="inlineStr">
@@ -16458,7 +16454,7 @@
       </c>
       <c r="G192" t="inlineStr">
         <is>
-          <t>012</t>
+          <t>013</t>
         </is>
       </c>
       <c r="H192" t="inlineStr">
@@ -16498,12 +16494,12 @@
       </c>
       <c r="O192" t="inlineStr">
         <is>
-          <t>RUDT INDUSTRIELACKE GMBH</t>
+          <t>FINALIN GMBH</t>
         </is>
       </c>
       <c r="P192" t="inlineStr">
         <is>
-          <t>RUDT INDUSTRIELACKE GMBH</t>
+          <t>FINALIN GMBH</t>
         </is>
       </c>
       <c r="Q192" t="inlineStr">
@@ -16541,7 +16537,7 @@
       </c>
       <c r="G193" t="inlineStr">
         <is>
-          <t>013</t>
+          <t>014</t>
         </is>
       </c>
       <c r="H193" t="inlineStr">
@@ -16551,7 +16547,7 @@
       </c>
       <c r="I193" t="inlineStr">
         <is>
-          <t>3208.20.0000</t>
+          <t>3208.10.0000</t>
         </is>
       </c>
       <c r="J193" t="inlineStr">
@@ -16624,7 +16620,7 @@
       </c>
       <c r="G194" t="inlineStr">
         <is>
-          <t>014</t>
+          <t>015</t>
         </is>
       </c>
       <c r="H194" t="inlineStr">
@@ -16697,27 +16693,27 @@
       <c r="D195" t="inlineStr"/>
       <c r="E195" t="inlineStr">
         <is>
-          <t>9903.03.01</t>
+          <t>9903.03.03</t>
         </is>
       </c>
       <c r="F195" t="inlineStr">
         <is>
-          <t>SECTION 122 - 10% DUTY</t>
+          <t>S122 -EXCLUSION-EXEMPTED PRDTS</t>
         </is>
       </c>
       <c r="G195" t="inlineStr">
         <is>
-          <t>015</t>
+          <t>016</t>
         </is>
       </c>
       <c r="H195" t="inlineStr">
         <is>
-          <t>9903.03.01</t>
+          <t>9903.03.03</t>
         </is>
       </c>
       <c r="I195" t="inlineStr">
         <is>
-          <t>3208.10.0000</t>
+          <t>3911.90.2500</t>
         </is>
       </c>
       <c r="J195" t="inlineStr">
@@ -16780,27 +16776,27 @@
       <c r="D196" t="inlineStr"/>
       <c r="E196" t="inlineStr">
         <is>
-          <t>9903.03.03</t>
+          <t>9903.03.01</t>
         </is>
       </c>
       <c r="F196" t="inlineStr">
         <is>
-          <t>S122 -EXCLUSION-EXEMPTED PRDTS</t>
+          <t>SECTION 122 - 10% DUTY</t>
         </is>
       </c>
       <c r="G196" t="inlineStr">
         <is>
-          <t>016</t>
+          <t>017</t>
         </is>
       </c>
       <c r="H196" t="inlineStr">
         <is>
-          <t>9903.03.03</t>
+          <t>9903.03.01</t>
         </is>
       </c>
       <c r="I196" t="inlineStr">
         <is>
-          <t>3911.90.2500</t>
+          <t>3209.90.0000</t>
         </is>
       </c>
       <c r="J196" t="inlineStr">
@@ -16863,27 +16859,27 @@
       <c r="D197" t="inlineStr"/>
       <c r="E197" t="inlineStr">
         <is>
-          <t>9903.03.01</t>
+          <t>9903.03.03</t>
         </is>
       </c>
       <c r="F197" t="inlineStr">
         <is>
-          <t>SECTION 122 - 10% DUTY</t>
+          <t>S122 -EXCLUSION-EXEMPTED PRDTS</t>
         </is>
       </c>
       <c r="G197" t="inlineStr">
         <is>
-          <t>017</t>
+          <t>018</t>
         </is>
       </c>
       <c r="H197" t="inlineStr">
         <is>
-          <t>9903.03.01</t>
+          <t>9903.03.03</t>
         </is>
       </c>
       <c r="I197" t="inlineStr">
         <is>
-          <t>3209.90.0000</t>
+          <t>3911.90.2500</t>
         </is>
       </c>
       <c r="J197" t="inlineStr">
@@ -16946,27 +16942,27 @@
       <c r="D198" t="inlineStr"/>
       <c r="E198" t="inlineStr">
         <is>
-          <t>9903.03.03</t>
+          <t>9903.03.01</t>
         </is>
       </c>
       <c r="F198" t="inlineStr">
         <is>
-          <t>S122 -EXCLUSION-EXEMPTED PRDTS</t>
+          <t>SECTION 122 - 10% DUTY</t>
         </is>
       </c>
       <c r="G198" t="inlineStr">
         <is>
-          <t>018</t>
+          <t>019</t>
         </is>
       </c>
       <c r="H198" t="inlineStr">
         <is>
-          <t>9903.03.03</t>
+          <t>9903.03.01</t>
         </is>
       </c>
       <c r="I198" t="inlineStr">
         <is>
-          <t>3911.90.2500</t>
+          <t>3208.90.0000</t>
         </is>
       </c>
       <c r="J198" t="inlineStr">
@@ -17029,27 +17025,27 @@
       <c r="D199" t="inlineStr"/>
       <c r="E199" t="inlineStr">
         <is>
-          <t>9903.03.01</t>
+          <t>9903.03.03</t>
         </is>
       </c>
       <c r="F199" t="inlineStr">
         <is>
-          <t>SECTION 122 - 10% DUTY</t>
+          <t>S122 -EXCLUSION-EXEMPTED PRDTS</t>
         </is>
       </c>
       <c r="G199" t="inlineStr">
         <is>
-          <t>019</t>
+          <t>020</t>
         </is>
       </c>
       <c r="H199" t="inlineStr">
         <is>
-          <t>9903.03.01</t>
+          <t>9903.03.03</t>
         </is>
       </c>
       <c r="I199" t="inlineStr">
         <is>
-          <t>3208.90.0000</t>
+          <t>3911.90.2500</t>
         </is>
       </c>
       <c r="J199" t="inlineStr">
@@ -17112,27 +17108,27 @@
       <c r="D200" t="inlineStr"/>
       <c r="E200" t="inlineStr">
         <is>
-          <t>9903.03.03</t>
+          <t>9903.03.01</t>
         </is>
       </c>
       <c r="F200" t="inlineStr">
         <is>
-          <t>S122 -EXCLUSION-EXEMPTED PRDTS</t>
+          <t>SECTION 122 - 10% DUTY</t>
         </is>
       </c>
       <c r="G200" t="inlineStr">
         <is>
-          <t>020</t>
+          <t>021</t>
         </is>
       </c>
       <c r="H200" t="inlineStr">
         <is>
-          <t>9903.03.03</t>
+          <t>9903.03.01</t>
         </is>
       </c>
       <c r="I200" t="inlineStr">
         <is>
-          <t>3911.90.2500</t>
+          <t>3208.10.0000</t>
         </is>
       </c>
       <c r="J200" t="inlineStr">
@@ -17205,7 +17201,7 @@
       </c>
       <c r="G201" t="inlineStr">
         <is>
-          <t>021</t>
+          <t>022</t>
         </is>
       </c>
       <c r="H201" t="inlineStr">
@@ -17215,7 +17211,7 @@
       </c>
       <c r="I201" t="inlineStr">
         <is>
-          <t>3208.10.0000</t>
+          <t>3814.00.1000</t>
         </is>
       </c>
       <c r="J201" t="inlineStr">
@@ -17278,27 +17274,27 @@
       <c r="D202" t="inlineStr"/>
       <c r="E202" t="inlineStr">
         <is>
-          <t>9903.03.01</t>
+          <t>9903.03.03</t>
         </is>
       </c>
       <c r="F202" t="inlineStr">
         <is>
-          <t>SECTION 122 - 10% DUTY</t>
+          <t>S122 -EXCLUSION-EXEMPTED PRDTS</t>
         </is>
       </c>
       <c r="G202" t="inlineStr">
         <is>
-          <t>022</t>
+          <t>023</t>
         </is>
       </c>
       <c r="H202" t="inlineStr">
         <is>
-          <t>9903.03.01</t>
+          <t>9903.03.03</t>
         </is>
       </c>
       <c r="I202" t="inlineStr">
         <is>
-          <t>3814.00.1000</t>
+          <t>3911.90.2500</t>
         </is>
       </c>
       <c r="J202" t="inlineStr">
@@ -17361,27 +17357,27 @@
       <c r="D203" t="inlineStr"/>
       <c r="E203" t="inlineStr">
         <is>
-          <t>9903.03.03</t>
+          <t>9903.03.01</t>
         </is>
       </c>
       <c r="F203" t="inlineStr">
         <is>
-          <t>S122 -EXCLUSION-EXEMPTED PRDTS</t>
+          <t>SECTION 122 - 10% DUTY</t>
         </is>
       </c>
       <c r="G203" t="inlineStr">
         <is>
-          <t>023</t>
+          <t>024</t>
         </is>
       </c>
       <c r="H203" t="inlineStr">
         <is>
-          <t>9903.03.03</t>
+          <t>9903.03.01</t>
         </is>
       </c>
       <c r="I203" t="inlineStr">
         <is>
-          <t>3911.90.2500</t>
+          <t>3814.00.1000</t>
         </is>
       </c>
       <c r="J203" t="inlineStr">
@@ -17454,7 +17450,7 @@
       </c>
       <c r="G204" t="inlineStr">
         <is>
-          <t>024</t>
+          <t>025</t>
         </is>
       </c>
       <c r="H204" t="inlineStr">
@@ -17537,7 +17533,7 @@
       </c>
       <c r="G205" t="inlineStr">
         <is>
-          <t>025</t>
+          <t>026</t>
         </is>
       </c>
       <c r="H205" t="inlineStr">
@@ -17610,27 +17606,27 @@
       <c r="D206" t="inlineStr"/>
       <c r="E206" t="inlineStr">
         <is>
-          <t>9903.03.01</t>
+          <t>9903.03.03</t>
         </is>
       </c>
       <c r="F206" t="inlineStr">
         <is>
-          <t>SECTION 122 - 10% DUTY</t>
+          <t>S122 -EXCLUSION-EXEMPTED PRDTS</t>
         </is>
       </c>
       <c r="G206" t="inlineStr">
         <is>
-          <t>026</t>
+          <t>027</t>
         </is>
       </c>
       <c r="H206" t="inlineStr">
         <is>
-          <t>9903.03.01</t>
+          <t>9903.03.03</t>
         </is>
       </c>
       <c r="I206" t="inlineStr">
         <is>
-          <t>3814.00.1000</t>
+          <t>3911.90.2500</t>
         </is>
       </c>
       <c r="J206" t="inlineStr">
@@ -17693,27 +17689,27 @@
       <c r="D207" t="inlineStr"/>
       <c r="E207" t="inlineStr">
         <is>
-          <t>9903.03.03</t>
+          <t>9903.03.01</t>
         </is>
       </c>
       <c r="F207" t="inlineStr">
         <is>
-          <t>S122 -EXCLUSION-EXEMPTED PRDTS</t>
+          <t>SECTION 122 - 10% DUTY</t>
         </is>
       </c>
       <c r="G207" t="inlineStr">
         <is>
-          <t>027</t>
+          <t>028</t>
         </is>
       </c>
       <c r="H207" t="inlineStr">
         <is>
-          <t>9903.03.03</t>
+          <t>9903.03.01</t>
         </is>
       </c>
       <c r="I207" t="inlineStr">
         <is>
-          <t>3911.90.2500</t>
+          <t>3208.10.0000</t>
         </is>
       </c>
       <c r="J207" t="inlineStr">
@@ -17786,7 +17782,7 @@
       </c>
       <c r="G208" t="inlineStr">
         <is>
-          <t>028</t>
+          <t>029</t>
         </is>
       </c>
       <c r="H208" t="inlineStr">
@@ -17869,7 +17865,7 @@
       </c>
       <c r="G209" t="inlineStr">
         <is>
-          <t>029</t>
+          <t>030</t>
         </is>
       </c>
       <c r="H209" t="inlineStr">
@@ -17952,7 +17948,7 @@
       </c>
       <c r="G210" t="inlineStr">
         <is>
-          <t>030</t>
+          <t>031</t>
         </is>
       </c>
       <c r="H210" t="inlineStr">
@@ -18035,7 +18031,7 @@
       </c>
       <c r="G211" t="inlineStr">
         <is>
-          <t>031</t>
+          <t>032</t>
         </is>
       </c>
       <c r="H211" t="inlineStr">
@@ -18118,7 +18114,7 @@
       </c>
       <c r="G212" t="inlineStr">
         <is>
-          <t>032</t>
+          <t>033</t>
         </is>
       </c>
       <c r="H212" t="inlineStr">
@@ -18201,7 +18197,7 @@
       </c>
       <c r="G213" t="inlineStr">
         <is>
-          <t>033</t>
+          <t>034</t>
         </is>
       </c>
       <c r="H213" t="inlineStr">
@@ -18284,7 +18280,7 @@
       </c>
       <c r="G214" t="inlineStr">
         <is>
-          <t>034</t>
+          <t>035</t>
         </is>
       </c>
       <c r="H214" t="inlineStr">
@@ -18367,7 +18363,7 @@
       </c>
       <c r="G215" t="inlineStr">
         <is>
-          <t>035</t>
+          <t>036</t>
         </is>
       </c>
       <c r="H215" t="inlineStr">
@@ -18450,7 +18446,7 @@
       </c>
       <c r="G216" t="inlineStr">
         <is>
-          <t>036</t>
+          <t>037</t>
         </is>
       </c>
       <c r="H216" t="inlineStr">
@@ -18533,7 +18529,7 @@
       </c>
       <c r="G217" t="inlineStr">
         <is>
-          <t>037</t>
+          <t>038</t>
         </is>
       </c>
       <c r="H217" t="inlineStr">
@@ -18543,7 +18539,7 @@
       </c>
       <c r="I217" t="inlineStr">
         <is>
-          <t>3208.10.0000</t>
+          <t>3209.90.0000</t>
         </is>
       </c>
       <c r="J217" t="inlineStr">
@@ -18616,7 +18612,7 @@
       </c>
       <c r="G218" t="inlineStr">
         <is>
-          <t>038</t>
+          <t>039</t>
         </is>
       </c>
       <c r="H218" t="inlineStr">
@@ -18626,7 +18622,7 @@
       </c>
       <c r="I218" t="inlineStr">
         <is>
-          <t>3209.90.0000</t>
+          <t>3208.20.0000</t>
         </is>
       </c>
       <c r="J218" t="inlineStr">
@@ -18699,7 +18695,7 @@
       </c>
       <c r="G219" t="inlineStr">
         <is>
-          <t>039</t>
+          <t>040</t>
         </is>
       </c>
       <c r="H219" t="inlineStr">
@@ -18709,7 +18705,7 @@
       </c>
       <c r="I219" t="inlineStr">
         <is>
-          <t>3208.20.0000</t>
+          <t>3214.10.0090</t>
         </is>
       </c>
       <c r="J219" t="inlineStr">
@@ -18782,7 +18778,7 @@
       </c>
       <c r="G220" t="inlineStr">
         <is>
-          <t>040</t>
+          <t>041</t>
         </is>
       </c>
       <c r="H220" t="inlineStr">
@@ -18792,7 +18788,7 @@
       </c>
       <c r="I220" t="inlineStr">
         <is>
-          <t>3214.10.0090</t>
+          <t>3208.20.0000</t>
         </is>
       </c>
       <c r="J220" t="inlineStr">
@@ -18865,7 +18861,7 @@
       </c>
       <c r="G221" t="inlineStr">
         <is>
-          <t>041</t>
+          <t>042</t>
         </is>
       </c>
       <c r="H221" t="inlineStr">
@@ -18948,7 +18944,7 @@
       </c>
       <c r="G222" t="inlineStr">
         <is>
-          <t>042</t>
+          <t>043</t>
         </is>
       </c>
       <c r="H222" t="inlineStr">
@@ -19031,7 +19027,7 @@
       </c>
       <c r="G223" t="inlineStr">
         <is>
-          <t>043</t>
+          <t>044</t>
         </is>
       </c>
       <c r="H223" t="inlineStr">
@@ -19114,7 +19110,7 @@
       </c>
       <c r="G224" t="inlineStr">
         <is>
-          <t>044</t>
+          <t>045</t>
         </is>
       </c>
       <c r="H224" t="inlineStr">
@@ -19197,7 +19193,7 @@
       </c>
       <c r="G225" t="inlineStr">
         <is>
-          <t>045</t>
+          <t>046</t>
         </is>
       </c>
       <c r="H225" t="inlineStr">
@@ -19280,7 +19276,7 @@
       </c>
       <c r="G226" t="inlineStr">
         <is>
-          <t>046</t>
+          <t>047</t>
         </is>
       </c>
       <c r="H226" t="inlineStr">
@@ -19363,7 +19359,7 @@
       </c>
       <c r="G227" t="inlineStr">
         <is>
-          <t>047</t>
+          <t>048</t>
         </is>
       </c>
       <c r="H227" t="inlineStr">
@@ -19446,7 +19442,7 @@
       </c>
       <c r="G228" t="inlineStr">
         <is>
-          <t>048</t>
+          <t>049</t>
         </is>
       </c>
       <c r="H228" t="inlineStr">
@@ -19529,7 +19525,7 @@
       </c>
       <c r="G229" t="inlineStr">
         <is>
-          <t>049</t>
+          <t>050</t>
         </is>
       </c>
       <c r="H229" t="inlineStr">
@@ -19539,7 +19535,7 @@
       </c>
       <c r="I229" t="inlineStr">
         <is>
-          <t>3208.20.0000</t>
+          <t>3208.10.0000</t>
         </is>
       </c>
       <c r="J229" t="inlineStr">
@@ -19612,7 +19608,7 @@
       </c>
       <c r="G230" t="inlineStr">
         <is>
-          <t>050</t>
+          <t>051</t>
         </is>
       </c>
       <c r="H230" t="inlineStr">
@@ -19622,7 +19618,7 @@
       </c>
       <c r="I230" t="inlineStr">
         <is>
-          <t>3208.10.0000</t>
+          <t>3208.20.0000</t>
         </is>
       </c>
       <c r="J230" t="inlineStr">
@@ -19695,7 +19691,7 @@
       </c>
       <c r="G231" t="inlineStr">
         <is>
-          <t>051</t>
+          <t>052</t>
         </is>
       </c>
       <c r="H231" t="inlineStr">
@@ -19778,7 +19774,7 @@
       </c>
       <c r="G232" t="inlineStr">
         <is>
-          <t>052</t>
+          <t>053</t>
         </is>
       </c>
       <c r="H232" t="inlineStr">
@@ -19788,7 +19784,7 @@
       </c>
       <c r="I232" t="inlineStr">
         <is>
-          <t>3208.20.0000</t>
+          <t>3208.10.0000</t>
         </is>
       </c>
       <c r="J232" t="inlineStr">
@@ -19861,7 +19857,7 @@
       </c>
       <c r="G233" t="inlineStr">
         <is>
-          <t>053</t>
+          <t>054</t>
         </is>
       </c>
       <c r="H233" t="inlineStr">
@@ -19944,7 +19940,7 @@
       </c>
       <c r="G234" t="inlineStr">
         <is>
-          <t>054</t>
+          <t>055</t>
         </is>
       </c>
       <c r="H234" t="inlineStr">
@@ -19954,7 +19950,7 @@
       </c>
       <c r="I234" t="inlineStr">
         <is>
-          <t>3208.10.0000</t>
+          <t>3814.00.1000</t>
         </is>
       </c>
       <c r="J234" t="inlineStr">
@@ -20027,7 +20023,7 @@
       </c>
       <c r="G235" t="inlineStr">
         <is>
-          <t>055</t>
+          <t>056</t>
         </is>
       </c>
       <c r="H235" t="inlineStr">
@@ -20037,7 +20033,7 @@
       </c>
       <c r="I235" t="inlineStr">
         <is>
-          <t>3814.00.1000</t>
+          <t>3208.20.0000</t>
         </is>
       </c>
       <c r="J235" t="inlineStr">
@@ -20110,7 +20106,7 @@
       </c>
       <c r="G236" t="inlineStr">
         <is>
-          <t>056</t>
+          <t>057</t>
         </is>
       </c>
       <c r="H236" t="inlineStr">
@@ -20193,7 +20189,7 @@
       </c>
       <c r="G237" t="inlineStr">
         <is>
-          <t>057</t>
+          <t>058</t>
         </is>
       </c>
       <c r="H237" t="inlineStr">
@@ -20276,7 +20272,7 @@
       </c>
       <c r="G238" t="inlineStr">
         <is>
-          <t>058</t>
+          <t>059</t>
         </is>
       </c>
       <c r="H238" t="inlineStr">
@@ -20286,7 +20282,7 @@
       </c>
       <c r="I238" t="inlineStr">
         <is>
-          <t>3208.20.0000</t>
+          <t>3209.90.0000</t>
         </is>
       </c>
       <c r="J238" t="inlineStr">
@@ -20359,7 +20355,7 @@
       </c>
       <c r="G239" t="inlineStr">
         <is>
-          <t>059</t>
+          <t>060</t>
         </is>
       </c>
       <c r="H239" t="inlineStr">
@@ -20369,7 +20365,7 @@
       </c>
       <c r="I239" t="inlineStr">
         <is>
-          <t>3209.90.0000</t>
+          <t>3208.20.0000</t>
         </is>
       </c>
       <c r="J239" t="inlineStr">
@@ -20432,27 +20428,27 @@
       <c r="D240" t="inlineStr"/>
       <c r="E240" t="inlineStr">
         <is>
-          <t>9903.03.01</t>
+          <t>9903.03.03</t>
         </is>
       </c>
       <c r="F240" t="inlineStr">
         <is>
-          <t>SECTION 122 - 10% DUTY</t>
+          <t>S122 -EXCLUSION-EXEMPTED PRDTS</t>
         </is>
       </c>
       <c r="G240" t="inlineStr">
         <is>
-          <t>060</t>
+          <t>061</t>
         </is>
       </c>
       <c r="H240" t="inlineStr">
         <is>
-          <t>9903.03.01</t>
+          <t>9903.03.03</t>
         </is>
       </c>
       <c r="I240" t="inlineStr">
         <is>
-          <t>3208.20.0000</t>
+          <t>3911.90.2500</t>
         </is>
       </c>
       <c r="J240" t="inlineStr">
@@ -20515,27 +20511,27 @@
       <c r="D241" t="inlineStr"/>
       <c r="E241" t="inlineStr">
         <is>
-          <t>9903.03.03</t>
+          <t>9903.03.01</t>
         </is>
       </c>
       <c r="F241" t="inlineStr">
         <is>
-          <t>S122 -EXCLUSION-EXEMPTED PRDTS</t>
+          <t>SECTION 122 - 10% DUTY</t>
         </is>
       </c>
       <c r="G241" t="inlineStr">
         <is>
-          <t>061</t>
+          <t>062</t>
         </is>
       </c>
       <c r="H241" t="inlineStr">
         <is>
-          <t>9903.03.03</t>
+          <t>9903.03.01</t>
         </is>
       </c>
       <c r="I241" t="inlineStr">
         <is>
-          <t>3911.90.2500</t>
+          <t>3208.10.0000</t>
         </is>
       </c>
       <c r="J241" t="inlineStr">
@@ -20608,7 +20604,7 @@
       </c>
       <c r="G242" t="inlineStr">
         <is>
-          <t>062</t>
+          <t>063</t>
         </is>
       </c>
       <c r="H242" t="inlineStr">
@@ -20618,7 +20614,7 @@
       </c>
       <c r="I242" t="inlineStr">
         <is>
-          <t>3208.10.0000</t>
+          <t>3209.90.0000</t>
         </is>
       </c>
       <c r="J242" t="inlineStr">
@@ -20648,12 +20644,12 @@
       </c>
       <c r="O242" t="inlineStr">
         <is>
-          <t>FINALIN GMBH</t>
+          <t>NORIX LACKFABRIK GMBH</t>
         </is>
       </c>
       <c r="P242" t="inlineStr">
         <is>
-          <t>FINALIN GMBH</t>
+          <t>NORIX LACKFABRIK GMBH</t>
         </is>
       </c>
       <c r="Q242" t="inlineStr">
@@ -20691,7 +20687,7 @@
       </c>
       <c r="G243" t="inlineStr">
         <is>
-          <t>063</t>
+          <t>064</t>
         </is>
       </c>
       <c r="H243" t="inlineStr">
@@ -20774,7 +20770,7 @@
       </c>
       <c r="G244" t="inlineStr">
         <is>
-          <t>064</t>
+          <t>065</t>
         </is>
       </c>
       <c r="H244" t="inlineStr">
@@ -20857,7 +20853,7 @@
       </c>
       <c r="G245" t="inlineStr">
         <is>
-          <t>065</t>
+          <t>066</t>
         </is>
       </c>
       <c r="H245" t="inlineStr">
@@ -20867,7 +20863,7 @@
       </c>
       <c r="I245" t="inlineStr">
         <is>
-          <t>3209.90.0000</t>
+          <t>3209.10.0000</t>
         </is>
       </c>
       <c r="J245" t="inlineStr">
@@ -20940,7 +20936,7 @@
       </c>
       <c r="G246" t="inlineStr">
         <is>
-          <t>066</t>
+          <t>067</t>
         </is>
       </c>
       <c r="H246" t="inlineStr">
@@ -20950,7 +20946,7 @@
       </c>
       <c r="I246" t="inlineStr">
         <is>
-          <t>3209.10.0000</t>
+          <t>3209.90.0000</t>
         </is>
       </c>
       <c r="J246" t="inlineStr">
@@ -21023,7 +21019,7 @@
       </c>
       <c r="G247" t="inlineStr">
         <is>
-          <t>067</t>
+          <t>068</t>
         </is>
       </c>
       <c r="H247" t="inlineStr">
@@ -21106,7 +21102,7 @@
       </c>
       <c r="G248" t="inlineStr">
         <is>
-          <t>068</t>
+          <t>069</t>
         </is>
       </c>
       <c r="H248" t="inlineStr">
@@ -21189,7 +21185,7 @@
       </c>
       <c r="G249" t="inlineStr">
         <is>
-          <t>069</t>
+          <t>070</t>
         </is>
       </c>
       <c r="H249" t="inlineStr">
@@ -21199,7 +21195,7 @@
       </c>
       <c r="I249" t="inlineStr">
         <is>
-          <t>3209.90.0000</t>
+          <t>3208.20.0000</t>
         </is>
       </c>
       <c r="J249" t="inlineStr">
@@ -21272,7 +21268,7 @@
       </c>
       <c r="G250" t="inlineStr">
         <is>
-          <t>070</t>
+          <t>071</t>
         </is>
       </c>
       <c r="H250" t="inlineStr">
@@ -21282,7 +21278,7 @@
       </c>
       <c r="I250" t="inlineStr">
         <is>
-          <t>3208.20.0000</t>
+          <t>3208.90.0000</t>
         </is>
       </c>
       <c r="J250" t="inlineStr">
@@ -21312,12 +21308,12 @@
       </c>
       <c r="O250" t="inlineStr">
         <is>
-          <t>NORIX LACKFABRIK GMBH</t>
+          <t>FINALIN GMBH</t>
         </is>
       </c>
       <c r="P250" t="inlineStr">
         <is>
-          <t>NORIX LACKFABRIK GMBH</t>
+          <t>FINALIN GMBH</t>
         </is>
       </c>
       <c r="Q250" t="inlineStr">
@@ -21355,7 +21351,7 @@
       </c>
       <c r="G251" t="inlineStr">
         <is>
-          <t>071</t>
+          <t>072</t>
         </is>
       </c>
       <c r="H251" t="inlineStr">
@@ -21365,7 +21361,7 @@
       </c>
       <c r="I251" t="inlineStr">
         <is>
-          <t>3208.90.0000</t>
+          <t>3208.10.0000</t>
         </is>
       </c>
       <c r="J251" t="inlineStr">
@@ -21438,7 +21434,7 @@
       </c>
       <c r="G252" t="inlineStr">
         <is>
-          <t>072</t>
+          <t>073</t>
         </is>
       </c>
       <c r="H252" t="inlineStr">
@@ -21448,7 +21444,7 @@
       </c>
       <c r="I252" t="inlineStr">
         <is>
-          <t>3208.10.0000</t>
+          <t>3208.20.0000</t>
         </is>
       </c>
       <c r="J252" t="inlineStr">
@@ -21521,7 +21517,7 @@
       </c>
       <c r="G253" t="inlineStr">
         <is>
-          <t>073</t>
+          <t>074</t>
         </is>
       </c>
       <c r="H253" t="inlineStr">
@@ -21531,7 +21527,7 @@
       </c>
       <c r="I253" t="inlineStr">
         <is>
-          <t>3208.20.0000</t>
+          <t>3208.10.0000</t>
         </is>
       </c>
       <c r="J253" t="inlineStr">
@@ -21604,7 +21600,7 @@
       </c>
       <c r="G254" t="inlineStr">
         <is>
-          <t>074</t>
+          <t>075</t>
         </is>
       </c>
       <c r="H254" t="inlineStr">
@@ -21614,7 +21610,7 @@
       </c>
       <c r="I254" t="inlineStr">
         <is>
-          <t>3208.10.0000</t>
+          <t>3208.20.0000</t>
         </is>
       </c>
       <c r="J254" t="inlineStr">
@@ -21687,7 +21683,7 @@
       </c>
       <c r="G255" t="inlineStr">
         <is>
-          <t>075</t>
+          <t>076</t>
         </is>
       </c>
       <c r="H255" t="inlineStr">
@@ -21770,7 +21766,7 @@
       </c>
       <c r="G256" t="inlineStr">
         <is>
-          <t>076</t>
+          <t>077</t>
         </is>
       </c>
       <c r="H256" t="inlineStr">
@@ -21827,12 +21823,12 @@
     <row r="257">
       <c r="A257" t="inlineStr">
         <is>
-          <t>2566270</t>
+          <t>2566329</t>
         </is>
       </c>
       <c r="B257" t="inlineStr">
         <is>
-          <t>EF4-0232359-8</t>
+          <t>EF4-0232388-7</t>
         </is>
       </c>
       <c r="C257" t="inlineStr">
@@ -21853,7 +21849,7 @@
       </c>
       <c r="G257" t="inlineStr">
         <is>
-          <t>077</t>
+          <t>001</t>
         </is>
       </c>
       <c r="H257" t="inlineStr">
@@ -21863,7 +21859,7 @@
       </c>
       <c r="I257" t="inlineStr">
         <is>
-          <t>3208.20.0000</t>
+          <t>3920.61.0000</t>
         </is>
       </c>
       <c r="J257" t="inlineStr">
@@ -21893,12 +21889,12 @@
       </c>
       <c r="O257" t="inlineStr">
         <is>
-          <t>FINALIN GMBH</t>
+          <t>MANKIEWICZ GEBR. &amp; CO.</t>
         </is>
       </c>
       <c r="P257" t="inlineStr">
         <is>
-          <t>FINALIN GMBH</t>
+          <t>MANKIEWICZ GEBR. &amp; CO.</t>
         </is>
       </c>
       <c r="Q257" t="inlineStr">
@@ -21936,7 +21932,7 @@
       </c>
       <c r="G258" t="inlineStr">
         <is>
-          <t>001</t>
+          <t>002</t>
         </is>
       </c>
       <c r="H258" t="inlineStr">
@@ -21946,7 +21942,7 @@
       </c>
       <c r="I258" t="inlineStr">
         <is>
-          <t>3920.61.0000</t>
+          <t>2518.10.0000</t>
         </is>
       </c>
       <c r="J258" t="inlineStr">
@@ -21976,12 +21972,12 @@
       </c>
       <c r="O258" t="inlineStr">
         <is>
-          <t>MANKIEWICZ GEBR. &amp; CO.</t>
+          <t>FINALIN GMBH</t>
         </is>
       </c>
       <c r="P258" t="inlineStr">
         <is>
-          <t>MANKIEWICZ GEBR. &amp; CO.</t>
+          <t>FINALIN GMBH</t>
         </is>
       </c>
       <c r="Q258" t="inlineStr">
@@ -22019,7 +22015,7 @@
       </c>
       <c r="G259" t="inlineStr">
         <is>
-          <t>002</t>
+          <t>003</t>
         </is>
       </c>
       <c r="H259" t="inlineStr">
@@ -22029,7 +22025,7 @@
       </c>
       <c r="I259" t="inlineStr">
         <is>
-          <t>2518.10.0000</t>
+          <t>2836.50.0000</t>
         </is>
       </c>
       <c r="J259" t="inlineStr">
@@ -22102,7 +22098,7 @@
       </c>
       <c r="G260" t="inlineStr">
         <is>
-          <t>003</t>
+          <t>004</t>
         </is>
       </c>
       <c r="H260" t="inlineStr">
@@ -22112,7 +22108,7 @@
       </c>
       <c r="I260" t="inlineStr">
         <is>
-          <t>2836.50.0000</t>
+          <t>2526.20.0000</t>
         </is>
       </c>
       <c r="J260" t="inlineStr">
@@ -22185,7 +22181,7 @@
       </c>
       <c r="G261" t="inlineStr">
         <is>
-          <t>004</t>
+          <t>005</t>
         </is>
       </c>
       <c r="H261" t="inlineStr">
@@ -22195,7 +22191,7 @@
       </c>
       <c r="I261" t="inlineStr">
         <is>
-          <t>2526.20.0000</t>
+          <t>3403.99.0000</t>
         </is>
       </c>
       <c r="J261" t="inlineStr">
@@ -22258,29 +22254,25 @@
       <c r="D262" t="inlineStr"/>
       <c r="E262" t="inlineStr">
         <is>
-          <t>9903.03.01</t>
+          <t>2508.40.0150</t>
         </is>
       </c>
       <c r="F262" t="inlineStr">
         <is>
-          <t>SECTION 122 - 10% DUTY</t>
+          <t>OTHR CLAYS,WHE OR NOT CALC</t>
         </is>
       </c>
       <c r="G262" t="inlineStr">
         <is>
-          <t>005</t>
+          <t>006</t>
         </is>
       </c>
       <c r="H262" t="inlineStr">
         <is>
-          <t>9903.03.01</t>
-        </is>
-      </c>
-      <c r="I262" t="inlineStr">
-        <is>
-          <t>3403.99.0000</t>
-        </is>
-      </c>
+          <t>2508.40.0150</t>
+        </is>
+      </c>
+      <c r="I262" t="inlineStr"/>
       <c r="J262" t="inlineStr">
         <is>
           <t>MANKIEWICZ COATINGS, LLC</t>
@@ -22341,25 +22333,29 @@
       <c r="D263" t="inlineStr"/>
       <c r="E263" t="inlineStr">
         <is>
-          <t>2508.40.0150</t>
+          <t>9903.03.01</t>
         </is>
       </c>
       <c r="F263" t="inlineStr">
         <is>
-          <t>OTHR CLAYS,WHE OR NOT CALC</t>
+          <t>SECTION 122 - 10% DUTY</t>
         </is>
       </c>
       <c r="G263" t="inlineStr">
         <is>
-          <t>006</t>
+          <t>007</t>
         </is>
       </c>
       <c r="H263" t="inlineStr">
         <is>
-          <t>2508.40.0150</t>
-        </is>
-      </c>
-      <c r="I263" t="inlineStr"/>
+          <t>9903.03.01</t>
+        </is>
+      </c>
+      <c r="I263" t="inlineStr">
+        <is>
+          <t>2915.39.1000</t>
+        </is>
+      </c>
       <c r="J263" t="inlineStr">
         <is>
           <t>MANKIEWICZ COATINGS, LLC</t>
@@ -22430,7 +22426,7 @@
       </c>
       <c r="G264" t="inlineStr">
         <is>
-          <t>007</t>
+          <t>008</t>
         </is>
       </c>
       <c r="H264" t="inlineStr">
@@ -22440,7 +22436,7 @@
       </c>
       <c r="I264" t="inlineStr">
         <is>
-          <t>2915.39.1000</t>
+          <t>3214.10.0090</t>
         </is>
       </c>
       <c r="J264" t="inlineStr">
@@ -22513,7 +22509,7 @@
       </c>
       <c r="G265" t="inlineStr">
         <is>
-          <t>008</t>
+          <t>009</t>
         </is>
       </c>
       <c r="H265" t="inlineStr">
@@ -22523,7 +22519,7 @@
       </c>
       <c r="I265" t="inlineStr">
         <is>
-          <t>3214.10.0090</t>
+          <t>3208.90.0000</t>
         </is>
       </c>
       <c r="J265" t="inlineStr">
@@ -22596,7 +22592,7 @@
       </c>
       <c r="G266" t="inlineStr">
         <is>
-          <t>009</t>
+          <t>010</t>
         </is>
       </c>
       <c r="H266" t="inlineStr">
@@ -22606,7 +22602,7 @@
       </c>
       <c r="I266" t="inlineStr">
         <is>
-          <t>3208.90.0000</t>
+          <t>3214.10.0090</t>
         </is>
       </c>
       <c r="J266" t="inlineStr">
@@ -22679,7 +22675,7 @@
       </c>
       <c r="G267" t="inlineStr">
         <is>
-          <t>010</t>
+          <t>011</t>
         </is>
       </c>
       <c r="H267" t="inlineStr">
@@ -22752,27 +22748,27 @@
       <c r="D268" t="inlineStr"/>
       <c r="E268" t="inlineStr">
         <is>
-          <t>9903.03.01</t>
+          <t>9903.03.03</t>
         </is>
       </c>
       <c r="F268" t="inlineStr">
         <is>
-          <t>SECTION 122 - 10% DUTY</t>
+          <t>S122 -EXCLUSION-EXEMPTED PRDTS</t>
         </is>
       </c>
       <c r="G268" t="inlineStr">
         <is>
-          <t>011</t>
+          <t>012</t>
         </is>
       </c>
       <c r="H268" t="inlineStr">
         <is>
-          <t>9903.03.01</t>
+          <t>9903.03.03</t>
         </is>
       </c>
       <c r="I268" t="inlineStr">
         <is>
-          <t>3214.10.0090</t>
+          <t>3911.90.2500</t>
         </is>
       </c>
       <c r="J268" t="inlineStr">
@@ -22845,7 +22841,7 @@
       </c>
       <c r="G269" t="inlineStr">
         <is>
-          <t>012</t>
+          <t>013</t>
         </is>
       </c>
       <c r="H269" t="inlineStr">
@@ -22918,27 +22914,27 @@
       <c r="D270" t="inlineStr"/>
       <c r="E270" t="inlineStr">
         <is>
-          <t>9903.03.03</t>
+          <t>9903.03.01</t>
         </is>
       </c>
       <c r="F270" t="inlineStr">
         <is>
-          <t>S122 -EXCLUSION-EXEMPTED PRDTS</t>
+          <t>SECTION 122 - 10% DUTY</t>
         </is>
       </c>
       <c r="G270" t="inlineStr">
         <is>
-          <t>013</t>
+          <t>014</t>
         </is>
       </c>
       <c r="H270" t="inlineStr">
         <is>
-          <t>9903.03.03</t>
+          <t>9903.03.01</t>
         </is>
       </c>
       <c r="I270" t="inlineStr">
         <is>
-          <t>3911.90.2500</t>
+          <t>3209.90.0000</t>
         </is>
       </c>
       <c r="J270" t="inlineStr">
@@ -22968,12 +22964,12 @@
       </c>
       <c r="O270" t="inlineStr">
         <is>
-          <t>FINALIN GMBH</t>
+          <t>NORIX LACKFABRIK GMBH</t>
         </is>
       </c>
       <c r="P270" t="inlineStr">
         <is>
-          <t>FINALIN GMBH</t>
+          <t>NORIX LACKFABRIK GMBH</t>
         </is>
       </c>
       <c r="Q270" t="inlineStr">
@@ -23011,7 +23007,7 @@
       </c>
       <c r="G271" t="inlineStr">
         <is>
-          <t>014</t>
+          <t>015</t>
         </is>
       </c>
       <c r="H271" t="inlineStr">
@@ -23094,7 +23090,7 @@
       </c>
       <c r="G272" t="inlineStr">
         <is>
-          <t>015</t>
+          <t>016</t>
         </is>
       </c>
       <c r="H272" t="inlineStr">
@@ -23104,7 +23100,7 @@
       </c>
       <c r="I272" t="inlineStr">
         <is>
-          <t>3209.90.0000</t>
+          <t>3209.10.0000</t>
         </is>
       </c>
       <c r="J272" t="inlineStr">
@@ -23177,7 +23173,7 @@
       </c>
       <c r="G273" t="inlineStr">
         <is>
-          <t>016</t>
+          <t>017</t>
         </is>
       </c>
       <c r="H273" t="inlineStr">
@@ -23187,7 +23183,7 @@
       </c>
       <c r="I273" t="inlineStr">
         <is>
-          <t>3209.10.0000</t>
+          <t>3209.90.0000</t>
         </is>
       </c>
       <c r="J273" t="inlineStr">
@@ -23260,7 +23256,7 @@
       </c>
       <c r="G274" t="inlineStr">
         <is>
-          <t>017</t>
+          <t>018</t>
         </is>
       </c>
       <c r="H274" t="inlineStr">
@@ -23343,7 +23339,7 @@
       </c>
       <c r="G275" t="inlineStr">
         <is>
-          <t>018</t>
+          <t>019</t>
         </is>
       </c>
       <c r="H275" t="inlineStr">
@@ -23426,7 +23422,7 @@
       </c>
       <c r="G276" t="inlineStr">
         <is>
-          <t>019</t>
+          <t>020</t>
         </is>
       </c>
       <c r="H276" t="inlineStr">
@@ -23509,7 +23505,7 @@
       </c>
       <c r="G277" t="inlineStr">
         <is>
-          <t>020</t>
+          <t>021</t>
         </is>
       </c>
       <c r="H277" t="inlineStr">
@@ -23592,7 +23588,7 @@
       </c>
       <c r="G278" t="inlineStr">
         <is>
-          <t>021</t>
+          <t>022</t>
         </is>
       </c>
       <c r="H278" t="inlineStr">
@@ -23665,27 +23661,27 @@
       <c r="D279" t="inlineStr"/>
       <c r="E279" t="inlineStr">
         <is>
-          <t>9903.03.01</t>
+          <t>9903.03.03</t>
         </is>
       </c>
       <c r="F279" t="inlineStr">
         <is>
-          <t>SECTION 122 - 10% DUTY</t>
+          <t>S122 -EXCLUSION-EXEMPTED PRDTS</t>
         </is>
       </c>
       <c r="G279" t="inlineStr">
         <is>
-          <t>022</t>
+          <t>023</t>
         </is>
       </c>
       <c r="H279" t="inlineStr">
         <is>
-          <t>9903.03.01</t>
+          <t>9903.03.03</t>
         </is>
       </c>
       <c r="I279" t="inlineStr">
         <is>
-          <t>3209.90.0000</t>
+          <t>3911.90.2500</t>
         </is>
       </c>
       <c r="J279" t="inlineStr">
@@ -23715,12 +23711,12 @@
       </c>
       <c r="O279" t="inlineStr">
         <is>
-          <t>NORIX LACKFABRIK GMBH</t>
+          <t>FINALIN GMBH</t>
         </is>
       </c>
       <c r="P279" t="inlineStr">
         <is>
-          <t>NORIX LACKFABRIK GMBH</t>
+          <t>FINALIN GMBH</t>
         </is>
       </c>
       <c r="Q279" t="inlineStr">
@@ -23748,27 +23744,27 @@
       <c r="D280" t="inlineStr"/>
       <c r="E280" t="inlineStr">
         <is>
-          <t>9903.03.03</t>
+          <t>9903.03.01</t>
         </is>
       </c>
       <c r="F280" t="inlineStr">
         <is>
-          <t>S122 -EXCLUSION-EXEMPTED PRDTS</t>
+          <t>SECTION 122 - 10% DUTY</t>
         </is>
       </c>
       <c r="G280" t="inlineStr">
         <is>
-          <t>023</t>
+          <t>024</t>
         </is>
       </c>
       <c r="H280" t="inlineStr">
         <is>
-          <t>9903.03.03</t>
+          <t>9903.03.01</t>
         </is>
       </c>
       <c r="I280" t="inlineStr">
         <is>
-          <t>3911.90.2500</t>
+          <t>3208.20.0000</t>
         </is>
       </c>
       <c r="J280" t="inlineStr">
@@ -23841,7 +23837,7 @@
       </c>
       <c r="G281" t="inlineStr">
         <is>
-          <t>024</t>
+          <t>025</t>
         </is>
       </c>
       <c r="H281" t="inlineStr">
@@ -23851,7 +23847,7 @@
       </c>
       <c r="I281" t="inlineStr">
         <is>
-          <t>3208.20.0000</t>
+          <t>3209.90.0000</t>
         </is>
       </c>
       <c r="J281" t="inlineStr">
@@ -23898,12 +23894,12 @@
     <row r="282">
       <c r="A282" t="inlineStr">
         <is>
-          <t>2566329</t>
+          <t>2566263</t>
         </is>
       </c>
       <c r="B282" t="inlineStr">
         <is>
-          <t>EF4-0232388-7</t>
+          <t>EF4-0232389-5</t>
         </is>
       </c>
       <c r="C282" t="inlineStr">
@@ -23924,7 +23920,7 @@
       </c>
       <c r="G282" t="inlineStr">
         <is>
-          <t>025</t>
+          <t>001</t>
         </is>
       </c>
       <c r="H282" t="inlineStr">
@@ -23934,22 +23930,22 @@
       </c>
       <c r="I282" t="inlineStr">
         <is>
-          <t>3209.90.0000</t>
+          <t>8474.10.0010</t>
         </is>
       </c>
       <c r="J282" t="inlineStr">
         <is>
-          <t>MANKIEWICZ COATINGS, LLC</t>
+          <t>EDGE INNOVATE (NI) LTD</t>
         </is>
       </c>
       <c r="K282" t="inlineStr">
         <is>
-          <t>MANCOAT</t>
+          <t>EDGINN01</t>
         </is>
       </c>
       <c r="L282" t="inlineStr">
         <is>
-          <t>56-202308900</t>
+          <t>135501-01432</t>
         </is>
       </c>
       <c r="M282" t="inlineStr">
@@ -23964,17 +23960,17 @@
       </c>
       <c r="O282" t="inlineStr">
         <is>
-          <t>FINALIN GMBH</t>
+          <t>EDGE INNOVATE (NI) LTD</t>
         </is>
       </c>
       <c r="P282" t="inlineStr">
         <is>
-          <t>FINALIN GMBH</t>
+          <t>EDGE INNOVATE (NI) LTD</t>
         </is>
       </c>
       <c r="Q282" t="inlineStr">
         <is>
-          <t>2026-06-05 00:00:00</t>
+          <t>2026-06-07 00:00:00</t>
         </is>
       </c>
     </row>
@@ -24007,7 +24003,7 @@
       </c>
       <c r="G283" t="inlineStr">
         <is>
-          <t>001</t>
+          <t>002</t>
         </is>
       </c>
       <c r="H283" t="inlineStr">
@@ -24090,7 +24086,7 @@
       </c>
       <c r="G284" t="inlineStr">
         <is>
-          <t>002</t>
+          <t>003</t>
         </is>
       </c>
       <c r="H284" t="inlineStr">
@@ -24147,12 +24143,12 @@
     <row r="285">
       <c r="A285" t="inlineStr">
         <is>
-          <t>2566263</t>
+          <t>2565718</t>
         </is>
       </c>
       <c r="B285" t="inlineStr">
         <is>
-          <t>EF4-0232389-5</t>
+          <t>EF4-0231703-8</t>
         </is>
       </c>
       <c r="C285" t="inlineStr">
@@ -24173,7 +24169,7 @@
       </c>
       <c r="G285" t="inlineStr">
         <is>
-          <t>003</t>
+          <t>001</t>
         </is>
       </c>
       <c r="H285" t="inlineStr">
@@ -24183,59 +24179,59 @@
       </c>
       <c r="I285" t="inlineStr">
         <is>
-          <t>8474.10.0010</t>
+          <t>3505.10.0092</t>
         </is>
       </c>
       <c r="J285" t="inlineStr">
         <is>
-          <t>EDGE INNOVATE (NI) LTD</t>
+          <t>ROYAL INGREDIENTS GROUP BV</t>
         </is>
       </c>
       <c r="K285" t="inlineStr">
         <is>
-          <t>EDGINN01</t>
+          <t>ROYINGRE</t>
         </is>
       </c>
       <c r="L285" t="inlineStr">
         <is>
-          <t>135501-01432</t>
+          <t>074601-00962</t>
         </is>
       </c>
       <c r="M285" t="inlineStr">
         <is>
-          <t>2026-06-16 00:00:00</t>
+          <t>2026-06-17 00:00:00</t>
         </is>
       </c>
       <c r="N285" t="inlineStr">
         <is>
-          <t>2026-06-16 00:00:00</t>
+          <t>2026-06-17 00:00:00</t>
         </is>
       </c>
       <c r="O285" t="inlineStr">
         <is>
-          <t>EDGE INNOVATE (NI) LTD</t>
+          <t>EHM INTERTRADING CO LTD</t>
         </is>
       </c>
       <c r="P285" t="inlineStr">
         <is>
-          <t>EDGE INNOVATE (NI) LTD</t>
+          <t>EHM INTERTRADING CO LTD</t>
         </is>
       </c>
       <c r="Q285" t="inlineStr">
         <is>
-          <t>2026-06-07 00:00:00</t>
+          <t>2026-05-01 00:00:00</t>
         </is>
       </c>
     </row>
     <row r="286">
       <c r="A286" t="inlineStr">
         <is>
-          <t>2565718</t>
+          <t>2565827</t>
         </is>
       </c>
       <c r="B286" t="inlineStr">
         <is>
-          <t>EF4-0231703-8</t>
+          <t>EF4-0231709-5</t>
         </is>
       </c>
       <c r="C286" t="inlineStr">
@@ -24266,22 +24262,22 @@
       </c>
       <c r="I286" t="inlineStr">
         <is>
-          <t>3505.10.0092</t>
+          <t>5903.90.3090</t>
         </is>
       </c>
       <c r="J286" t="inlineStr">
         <is>
-          <t>ROYAL INGREDIENTS GROUP BV</t>
+          <t>VEER CORPORATIONS INC</t>
         </is>
       </c>
       <c r="K286" t="inlineStr">
         <is>
-          <t>ROYINGRE</t>
+          <t>VEECOR01</t>
         </is>
       </c>
       <c r="L286" t="inlineStr">
         <is>
-          <t>074601-00962</t>
+          <t>99-106989200</t>
         </is>
       </c>
       <c r="M286" t="inlineStr">
@@ -24296,29 +24292,29 @@
       </c>
       <c r="O286" t="inlineStr">
         <is>
-          <t>EHM INTERTRADING CO LTD</t>
+          <t>VEER PLASTIC PVT LTD</t>
         </is>
       </c>
       <c r="P286" t="inlineStr">
         <is>
-          <t>EHM INTERTRADING CO LTD</t>
+          <t>VEER PLASTIC PVT LTD</t>
         </is>
       </c>
       <c r="Q286" t="inlineStr">
         <is>
-          <t>2026-05-01 00:00:00</t>
+          <t>2026-05-10 00:00:00</t>
         </is>
       </c>
     </row>
     <row r="287">
       <c r="A287" t="inlineStr">
         <is>
-          <t>2565827</t>
+          <t>2565938</t>
         </is>
       </c>
       <c r="B287" t="inlineStr">
         <is>
-          <t>EF4-0231709-5</t>
+          <t>EF4-0231958-8</t>
         </is>
       </c>
       <c r="C287" t="inlineStr">
@@ -24329,12 +24325,12 @@
       <c r="D287" t="inlineStr"/>
       <c r="E287" t="inlineStr">
         <is>
-          <t>9903.03.01</t>
+          <t>9903.03.06</t>
         </is>
       </c>
       <c r="F287" t="inlineStr">
         <is>
-          <t>SECTION 122 - 10% DUTY</t>
+          <t>S122 EXCL,IRN/STL/ALUM,DERIV</t>
         </is>
       </c>
       <c r="G287" t="inlineStr">
@@ -24344,52 +24340,52 @@
       </c>
       <c r="H287" t="inlineStr">
         <is>
-          <t>9903.03.01</t>
+          <t>9903.03.06</t>
         </is>
       </c>
       <c r="I287" t="inlineStr">
         <is>
-          <t>5903.90.3090</t>
+          <t>9903.74.11,9903.94.53,8708.29.5160</t>
         </is>
       </c>
       <c r="J287" t="inlineStr">
         <is>
-          <t>VEER CORPORATIONS INC</t>
+          <t>HAGO AUTOMOTIVE CORP</t>
         </is>
       </c>
       <c r="K287" t="inlineStr">
         <is>
-          <t>VEECOR01</t>
+          <t>HAGAUT02</t>
         </is>
       </c>
       <c r="L287" t="inlineStr">
         <is>
-          <t>99-106989200</t>
+          <t>47-447117700</t>
         </is>
       </c>
       <c r="M287" t="inlineStr">
         <is>
+          <t>2026-06-18 00:00:00</t>
+        </is>
+      </c>
+      <c r="N287" t="inlineStr">
+        <is>
           <t>2026-06-17 00:00:00</t>
         </is>
       </c>
-      <c r="N287" t="inlineStr">
-        <is>
-          <t>2026-06-17 00:00:00</t>
-        </is>
-      </c>
       <c r="O287" t="inlineStr">
         <is>
-          <t>VEER PLASTIC PVT LTD</t>
+          <t>WALOR VOEHRENBACH GMBH</t>
         </is>
       </c>
       <c r="P287" t="inlineStr">
         <is>
-          <t>VEER PLASTIC PVT LTD</t>
+          <t>WALOR VOEHRENBACH GMBH</t>
         </is>
       </c>
       <c r="Q287" t="inlineStr">
         <is>
-          <t>2026-05-10 00:00:00</t>
+          <t>2026-05-19 00:00:00</t>
         </is>
       </c>
     </row>
@@ -24422,7 +24418,7 @@
       </c>
       <c r="G288" t="inlineStr">
         <is>
-          <t>001</t>
+          <t>002</t>
         </is>
       </c>
       <c r="H288" t="inlineStr">
@@ -24505,7 +24501,7 @@
       </c>
       <c r="G289" t="inlineStr">
         <is>
-          <t>002</t>
+          <t>003</t>
         </is>
       </c>
       <c r="H289" t="inlineStr">
@@ -24588,7 +24584,7 @@
       </c>
       <c r="G290" t="inlineStr">
         <is>
-          <t>003</t>
+          <t>004</t>
         </is>
       </c>
       <c r="H290" t="inlineStr">
@@ -24671,7 +24667,7 @@
       </c>
       <c r="G291" t="inlineStr">
         <is>
-          <t>004</t>
+          <t>005</t>
         </is>
       </c>
       <c r="H291" t="inlineStr">
@@ -24754,7 +24750,7 @@
       </c>
       <c r="G292" t="inlineStr">
         <is>
-          <t>005</t>
+          <t>006</t>
         </is>
       </c>
       <c r="H292" t="inlineStr">
@@ -24837,7 +24833,7 @@
       </c>
       <c r="G293" t="inlineStr">
         <is>
-          <t>006</t>
+          <t>007</t>
         </is>
       </c>
       <c r="H293" t="inlineStr">
@@ -24894,12 +24890,12 @@
     <row r="294">
       <c r="A294" t="inlineStr">
         <is>
-          <t>2565938</t>
+          <t>2565682</t>
         </is>
       </c>
       <c r="B294" t="inlineStr">
         <is>
-          <t>EF4-0231958-8</t>
+          <t>EF4-0231989-3</t>
         </is>
       </c>
       <c r="C294" t="inlineStr">
@@ -24910,47 +24906,47 @@
       <c r="D294" t="inlineStr"/>
       <c r="E294" t="inlineStr">
         <is>
-          <t>9903.03.06</t>
+          <t>9903.88.03</t>
         </is>
       </c>
       <c r="F294" t="inlineStr">
         <is>
-          <t>S122 EXCL,IRN/STL/ALUM,DERIV</t>
+          <t>ARTICLE OF CHINA,US NTE 20(F)</t>
         </is>
       </c>
       <c r="G294" t="inlineStr">
         <is>
-          <t>007</t>
+          <t>001</t>
         </is>
       </c>
       <c r="H294" t="inlineStr">
         <is>
-          <t>9903.03.06</t>
+          <t>9903.88.03</t>
         </is>
       </c>
       <c r="I294" t="inlineStr">
         <is>
-          <t>9903.74.11,9903.94.53,8708.29.5160</t>
+          <t>9903.03.01,9403.99.9045</t>
         </is>
       </c>
       <c r="J294" t="inlineStr">
         <is>
-          <t>HAGO AUTOMOTIVE CORP</t>
+          <t>VISUAL CREATIONS, INC.</t>
         </is>
       </c>
       <c r="K294" t="inlineStr">
         <is>
-          <t>HAGAUT02</t>
+          <t>VISCRE</t>
         </is>
       </c>
       <c r="L294" t="inlineStr">
         <is>
-          <t>47-447117700</t>
+          <t>20-461602300</t>
         </is>
       </c>
       <c r="M294" t="inlineStr">
         <is>
-          <t>2026-06-18 00:00:00</t>
+          <t>2026-06-19 00:00:00</t>
         </is>
       </c>
       <c r="N294" t="inlineStr">
@@ -24960,12 +24956,12 @@
       </c>
       <c r="O294" t="inlineStr">
         <is>
-          <t>WALOR VOEHRENBACH GMBH</t>
+          <t>FUJIAN ANTAI NEW ENERGY TECH CO LTD</t>
         </is>
       </c>
       <c r="P294" t="inlineStr">
         <is>
-          <t>WALOR VOEHRENBACH GMBH</t>
+          <t>FUJIAN ANTAI NEW ENERGY TECH CO LTD</t>
         </is>
       </c>
       <c r="Q294" t="inlineStr">
@@ -25003,7 +24999,7 @@
       </c>
       <c r="G295" t="inlineStr">
         <is>
-          <t>001</t>
+          <t>002</t>
         </is>
       </c>
       <c r="H295" t="inlineStr">
@@ -25013,7 +25009,7 @@
       </c>
       <c r="I295" t="inlineStr">
         <is>
-          <t>9903.03.01,9403.99.9045</t>
+          <t>9903.03.01,9405.41.8440</t>
         </is>
       </c>
       <c r="J295" t="inlineStr">
@@ -25076,27 +25072,27 @@
       <c r="D296" t="inlineStr"/>
       <c r="E296" t="inlineStr">
         <is>
-          <t>9903.88.03</t>
+          <t>9903.88.15</t>
         </is>
       </c>
       <c r="F296" t="inlineStr">
         <is>
-          <t>ARTICLE OF CHINA,US NTE 20(F)</t>
+          <t>ARTICLE OF CHINA,US NTE 20(R)</t>
         </is>
       </c>
       <c r="G296" t="inlineStr">
         <is>
-          <t>002</t>
+          <t>003</t>
         </is>
       </c>
       <c r="H296" t="inlineStr">
         <is>
-          <t>9903.88.03</t>
+          <t>9903.88.15</t>
         </is>
       </c>
       <c r="I296" t="inlineStr">
         <is>
-          <t>9903.03.01,9405.41.8440</t>
+          <t>9903.03.01,3926.90.9989</t>
         </is>
       </c>
       <c r="J296" t="inlineStr">
@@ -25143,12 +25139,12 @@
     <row r="297">
       <c r="A297" t="inlineStr">
         <is>
-          <t>2565682</t>
+          <t>2566097</t>
         </is>
       </c>
       <c r="B297" t="inlineStr">
         <is>
-          <t>EF4-0231989-3</t>
+          <t>EF4-0232212-9</t>
         </is>
       </c>
       <c r="C297" t="inlineStr">
@@ -25156,50 +25152,54 @@
           <t>Vessel, Container</t>
         </is>
       </c>
-      <c r="D297" t="inlineStr"/>
+      <c r="D297" t="inlineStr">
+        <is>
+          <t>V0413939047</t>
+        </is>
+      </c>
       <c r="E297" t="inlineStr">
         <is>
-          <t>9903.88.15</t>
+          <t>9903.03.01</t>
         </is>
       </c>
       <c r="F297" t="inlineStr">
         <is>
-          <t>ARTICLE OF CHINA,US NTE 20(R)</t>
+          <t>SECTION 122 - 10% DUTY</t>
         </is>
       </c>
       <c r="G297" t="inlineStr">
         <is>
-          <t>003</t>
+          <t>001</t>
         </is>
       </c>
       <c r="H297" t="inlineStr">
         <is>
-          <t>9903.88.15</t>
+          <t>9903.03.01</t>
         </is>
       </c>
       <c r="I297" t="inlineStr">
         <is>
-          <t>9903.03.01,3926.90.9989</t>
+          <t>5704.90.0190</t>
         </is>
       </c>
       <c r="J297" t="inlineStr">
         <is>
-          <t>VISUAL CREATIONS, INC.</t>
+          <t>BORGERS OHIO INC.</t>
         </is>
       </c>
       <c r="K297" t="inlineStr">
         <is>
-          <t>VISCRE</t>
+          <t>BORUSA02</t>
         </is>
       </c>
       <c r="L297" t="inlineStr">
         <is>
-          <t>20-461602300</t>
+          <t>30-084196200</t>
         </is>
       </c>
       <c r="M297" t="inlineStr">
         <is>
-          <t>2026-06-19 00:00:00</t>
+          <t>2026-06-17 00:00:00</t>
         </is>
       </c>
       <c r="N297" t="inlineStr">
@@ -25209,29 +25209,29 @@
       </c>
       <c r="O297" t="inlineStr">
         <is>
-          <t>FUJIAN ANTAI NEW ENERGY TECH CO LTD</t>
+          <t>AUTONEUM GERMANY GMBH</t>
         </is>
       </c>
       <c r="P297" t="inlineStr">
         <is>
-          <t>FUJIAN ANTAI NEW ENERGY TECH CO LTD</t>
+          <t>AUTONEUM GERMANY GMBH</t>
         </is>
       </c>
       <c r="Q297" t="inlineStr">
         <is>
-          <t>2026-05-19 00:00:00</t>
+          <t>2026-05-30 00:00:00</t>
         </is>
       </c>
     </row>
     <row r="298">
       <c r="A298" t="inlineStr">
         <is>
-          <t>2565800</t>
+          <t>2566097</t>
         </is>
       </c>
       <c r="B298" t="inlineStr">
         <is>
-          <t>EF4-0232068-5</t>
+          <t>EF4-0232212-9</t>
         </is>
       </c>
       <c r="C298" t="inlineStr">
@@ -25246,42 +25246,42 @@
       </c>
       <c r="E298" t="inlineStr">
         <is>
-          <t>9903.03.06</t>
+          <t>9903.03.01</t>
         </is>
       </c>
       <c r="F298" t="inlineStr">
         <is>
-          <t>S122 EXCL,IRN/STL/ALUM,DERIV</t>
+          <t>SECTION 122 - 10% DUTY</t>
         </is>
       </c>
       <c r="G298" t="inlineStr">
         <is>
-          <t>001</t>
+          <t>002</t>
         </is>
       </c>
       <c r="H298" t="inlineStr">
         <is>
-          <t>9903.03.06</t>
+          <t>9903.03.01</t>
         </is>
       </c>
       <c r="I298" t="inlineStr">
         <is>
-          <t>9903.82.02,7223.00.1031</t>
+          <t>5704.90.0190</t>
         </is>
       </c>
       <c r="J298" t="inlineStr">
         <is>
-          <t>VENUS WIRE INDUSTRIES PRIVATE LTD</t>
+          <t>BORGERS OHIO INC.</t>
         </is>
       </c>
       <c r="K298" t="inlineStr">
         <is>
-          <t>VENWIR</t>
+          <t>BORUSA02</t>
         </is>
       </c>
       <c r="L298" t="inlineStr">
         <is>
-          <t>993901-03595</t>
+          <t>30-084196200</t>
         </is>
       </c>
       <c r="M298" t="inlineStr">
@@ -25296,17 +25296,17 @@
       </c>
       <c r="O298" t="inlineStr">
         <is>
-          <t>VENUS WIRE INDUSTRIES PRIVATE LIMIT</t>
+          <t>AUTONEUM GERMANY GMBH</t>
         </is>
       </c>
       <c r="P298" t="inlineStr">
         <is>
-          <t>VENUS WIRE INDUSTRIES PRIVATE LIMITED</t>
+          <t>AUTONEUM GERMANY GMBH</t>
         </is>
       </c>
       <c r="Q298" t="inlineStr">
         <is>
-          <t>2026-05-11 00:00:00</t>
+          <t>2026-05-30 00:00:00</t>
         </is>
       </c>
     </row>
@@ -25343,7 +25343,7 @@
       </c>
       <c r="G299" t="inlineStr">
         <is>
-          <t>001</t>
+          <t>003</t>
         </is>
       </c>
       <c r="H299" t="inlineStr">
@@ -25400,12 +25400,12 @@
     <row r="300">
       <c r="A300" t="inlineStr">
         <is>
-          <t>2566097</t>
+          <t>2565838</t>
         </is>
       </c>
       <c r="B300" t="inlineStr">
         <is>
-          <t>EF4-0232212-9</t>
+          <t>EF4-0232439-8</t>
         </is>
       </c>
       <c r="C300" t="inlineStr">
@@ -25415,47 +25415,47 @@
       </c>
       <c r="D300" t="inlineStr">
         <is>
-          <t>V0413939047</t>
+          <t>V0413931663</t>
         </is>
       </c>
       <c r="E300" t="inlineStr">
         <is>
-          <t>9903.03.01</t>
+          <t>9903.03.06</t>
         </is>
       </c>
       <c r="F300" t="inlineStr">
         <is>
-          <t>SECTION 122 - 10% DUTY</t>
+          <t>S122 EXCL,IRN/STL/ALUM,DERIV</t>
         </is>
       </c>
       <c r="G300" t="inlineStr">
         <is>
-          <t>002</t>
+          <t>001</t>
         </is>
       </c>
       <c r="H300" t="inlineStr">
         <is>
-          <t>9903.03.01</t>
+          <t>9903.03.06</t>
         </is>
       </c>
       <c r="I300" t="inlineStr">
         <is>
-          <t>5704.90.0190</t>
+          <t>9903.82.02,7222.20.0062</t>
         </is>
       </c>
       <c r="J300" t="inlineStr">
         <is>
-          <t>BORGERS OHIO INC.</t>
+          <t>MESHA STEELS  LLC</t>
         </is>
       </c>
       <c r="K300" t="inlineStr">
         <is>
-          <t>BORUSA02</t>
+          <t>MESSTE</t>
         </is>
       </c>
       <c r="L300" t="inlineStr">
         <is>
-          <t>30-084196200</t>
+          <t>20-274801900</t>
         </is>
       </c>
       <c r="M300" t="inlineStr">
@@ -25470,39 +25470,39 @@
       </c>
       <c r="O300" t="inlineStr">
         <is>
-          <t>AUTONEUM GERMANY GMBH</t>
+          <t>BHANSALI BRIGHT BARS PVT. LTD.</t>
         </is>
       </c>
       <c r="P300" t="inlineStr">
         <is>
-          <t>AUTONEUM GERMANY GMBH</t>
+          <t>BHANSALI BRIGHT BARS PVT. LTD.</t>
         </is>
       </c>
       <c r="Q300" t="inlineStr">
         <is>
-          <t>2026-05-30 00:00:00</t>
+          <t>2026-05-05 00:00:00</t>
         </is>
       </c>
     </row>
     <row r="301">
       <c r="A301" t="inlineStr">
         <is>
-          <t>2566097</t>
+          <t>2615809</t>
         </is>
       </c>
       <c r="B301" t="inlineStr">
         <is>
-          <t>EF4-0232212-9</t>
+          <t>EF4-0232557-7</t>
         </is>
       </c>
       <c r="C301" t="inlineStr">
         <is>
-          <t>Vessel, Container</t>
+          <t>Truck, Non-container</t>
         </is>
       </c>
       <c r="D301" t="inlineStr">
         <is>
-          <t>V0413939047</t>
+          <t>V0413937900</t>
         </is>
       </c>
       <c r="E301" t="inlineStr">
@@ -25517,7 +25517,7 @@
       </c>
       <c r="G301" t="inlineStr">
         <is>
-          <t>003</t>
+          <t>001</t>
         </is>
       </c>
       <c r="H301" t="inlineStr">
@@ -25527,59 +25527,59 @@
       </c>
       <c r="I301" t="inlineStr">
         <is>
-          <t>5704.90.0190</t>
+          <t>8483.40.5010</t>
         </is>
       </c>
       <c r="J301" t="inlineStr">
         <is>
-          <t>BORGERS OHIO INC.</t>
+          <t>AUMUND CORPORATION</t>
         </is>
       </c>
       <c r="K301" t="inlineStr">
         <is>
-          <t>BORUSA02</t>
+          <t>AUMCOR</t>
         </is>
       </c>
       <c r="L301" t="inlineStr">
         <is>
-          <t>30-084196200</t>
+          <t>58-138896800</t>
         </is>
       </c>
       <c r="M301" t="inlineStr">
         <is>
+          <t>2026-06-16 00:00:00</t>
+        </is>
+      </c>
+      <c r="N301" t="inlineStr">
+        <is>
           <t>2026-06-17 00:00:00</t>
         </is>
       </c>
-      <c r="N301" t="inlineStr">
-        <is>
-          <t>2026-06-17 00:00:00</t>
-        </is>
-      </c>
       <c r="O301" t="inlineStr">
         <is>
-          <t>AUTONEUM GERMANY GMBH</t>
+          <t>AUMUND FOERDERTECHNIK GMBH</t>
         </is>
       </c>
       <c r="P301" t="inlineStr">
         <is>
-          <t>AUTONEUM GERMANY GMBH</t>
+          <t>AUMUND FOERDERTECHNIK GMBH</t>
         </is>
       </c>
       <c r="Q301" t="inlineStr">
         <is>
-          <t>2026-05-30 00:00:00</t>
+          <t>2026-06-16 00:00:00</t>
         </is>
       </c>
     </row>
     <row r="302">
       <c r="A302" t="inlineStr">
         <is>
-          <t>2565838</t>
+          <t>2565634</t>
         </is>
       </c>
       <c r="B302" t="inlineStr">
         <is>
-          <t>EF4-0232439-8</t>
+          <t>EF4-0231631-1</t>
         </is>
       </c>
       <c r="C302" t="inlineStr">
@@ -25587,19 +25587,15 @@
           <t>Vessel, Container</t>
         </is>
       </c>
-      <c r="D302" t="inlineStr">
-        <is>
-          <t>V0413931663</t>
-        </is>
-      </c>
+      <c r="D302" t="inlineStr"/>
       <c r="E302" t="inlineStr">
         <is>
-          <t>9903.03.06</t>
+          <t>9903.03.01</t>
         </is>
       </c>
       <c r="F302" t="inlineStr">
         <is>
-          <t>S122 EXCL,IRN/STL/ALUM,DERIV</t>
+          <t>SECTION 122 - 10% DUTY</t>
         </is>
       </c>
       <c r="G302" t="inlineStr">
@@ -25609,47 +25605,47 @@
       </c>
       <c r="H302" t="inlineStr">
         <is>
-          <t>9903.03.06</t>
+          <t>9903.03.01</t>
         </is>
       </c>
       <c r="I302" t="inlineStr">
         <is>
-          <t>9903.82.02,7222.20.0062</t>
+          <t>8438.90.9060</t>
         </is>
       </c>
       <c r="J302" t="inlineStr">
         <is>
-          <t>MESHA STEELS  LLC</t>
+          <t>CANTRELL GAINCO GROUP INC</t>
         </is>
       </c>
       <c r="K302" t="inlineStr">
         <is>
-          <t>MESSTE</t>
+          <t>CANGAI01</t>
         </is>
       </c>
       <c r="L302" t="inlineStr">
         <is>
-          <t>20-274801900</t>
+          <t>31-151121700</t>
         </is>
       </c>
       <c r="M302" t="inlineStr">
         <is>
-          <t>2026-06-17 00:00:00</t>
+          <t>2026-06-18 00:00:00</t>
         </is>
       </c>
       <c r="N302" t="inlineStr">
         <is>
-          <t>2026-06-17 00:00:00</t>
+          <t>2026-06-18 00:00:00</t>
         </is>
       </c>
       <c r="O302" t="inlineStr">
         <is>
-          <t>BHANSALI BRIGHT BARS PVT. LTD.</t>
+          <t>O E CO LTD</t>
         </is>
       </c>
       <c r="P302" t="inlineStr">
         <is>
-          <t>BHANSALI BRIGHT BARS PVT. LTD.</t>
+          <t>O E CO LTD</t>
         </is>
       </c>
       <c r="Q302" t="inlineStr">
@@ -25661,24 +25657,20 @@
     <row r="303">
       <c r="A303" t="inlineStr">
         <is>
-          <t>2615809</t>
+          <t>2565782</t>
         </is>
       </c>
       <c r="B303" t="inlineStr">
         <is>
-          <t>EF4-0232557-7</t>
+          <t>EF4-0231677-4</t>
         </is>
       </c>
       <c r="C303" t="inlineStr">
         <is>
-          <t>Truck, Non-container</t>
-        </is>
-      </c>
-      <c r="D303" t="inlineStr">
-        <is>
-          <t>V0413937900</t>
-        </is>
-      </c>
+          <t>Vessel, Container</t>
+        </is>
+      </c>
+      <c r="D303" t="inlineStr"/>
       <c r="E303" t="inlineStr">
         <is>
           <t>9903.03.01</t>
@@ -25701,59 +25693,59 @@
       </c>
       <c r="I303" t="inlineStr">
         <is>
-          <t>8483.40.5010</t>
+          <t>3505.10.0092</t>
         </is>
       </c>
       <c r="J303" t="inlineStr">
         <is>
-          <t>AUMUND CORPORATION</t>
+          <t>ROYAL INGREDIENTS GROUP BV</t>
         </is>
       </c>
       <c r="K303" t="inlineStr">
         <is>
-          <t>AUMCOR</t>
+          <t>ROYINGRE</t>
         </is>
       </c>
       <c r="L303" t="inlineStr">
         <is>
-          <t>58-138896800</t>
+          <t>074601-00962</t>
         </is>
       </c>
       <c r="M303" t="inlineStr">
         <is>
-          <t>2026-06-16 00:00:00</t>
+          <t>2026-06-18 00:00:00</t>
         </is>
       </c>
       <c r="N303" t="inlineStr">
         <is>
-          <t>2026-06-17 00:00:00</t>
+          <t>2026-06-18 00:00:00</t>
         </is>
       </c>
       <c r="O303" t="inlineStr">
         <is>
-          <t>AUMUND FOERDERTECHNIK GMBH</t>
+          <t>EHM INTERTRADING CO LTD</t>
         </is>
       </c>
       <c r="P303" t="inlineStr">
         <is>
-          <t>AUMUND FOERDERTECHNIK GMBH</t>
+          <t>EHM INTERTRADING CO LTD</t>
         </is>
       </c>
       <c r="Q303" t="inlineStr">
         <is>
-          <t>2026-06-16 00:00:00</t>
+          <t>2026-05-05 00:00:00</t>
         </is>
       </c>
     </row>
     <row r="304">
       <c r="A304" t="inlineStr">
         <is>
-          <t>2565634</t>
+          <t>2565784</t>
         </is>
       </c>
       <c r="B304" t="inlineStr">
         <is>
-          <t>EF4-0231631-1</t>
+          <t>EF4-0231678-2</t>
         </is>
       </c>
       <c r="C304" t="inlineStr">
@@ -25784,22 +25776,22 @@
       </c>
       <c r="I304" t="inlineStr">
         <is>
-          <t>8438.90.9060</t>
+          <t>3505.10.0092</t>
         </is>
       </c>
       <c r="J304" t="inlineStr">
         <is>
-          <t>CANTRELL GAINCO GROUP INC</t>
+          <t>ROYAL INGREDIENTS GROUP BV</t>
         </is>
       </c>
       <c r="K304" t="inlineStr">
         <is>
-          <t>CANGAI01</t>
+          <t>ROYINGRE</t>
         </is>
       </c>
       <c r="L304" t="inlineStr">
         <is>
-          <t>31-151121700</t>
+          <t>074601-00962</t>
         </is>
       </c>
       <c r="M304" t="inlineStr">
@@ -25814,12 +25806,12 @@
       </c>
       <c r="O304" t="inlineStr">
         <is>
-          <t>O E CO LTD</t>
+          <t>EHM INTERTRADING CO LTD</t>
         </is>
       </c>
       <c r="P304" t="inlineStr">
         <is>
-          <t>O E CO LTD</t>
+          <t>EHM INTERTRADING CO LTD</t>
         </is>
       </c>
       <c r="Q304" t="inlineStr">
@@ -25831,12 +25823,12 @@
     <row r="305">
       <c r="A305" t="inlineStr">
         <is>
-          <t>2565782</t>
+          <t>2565894</t>
         </is>
       </c>
       <c r="B305" t="inlineStr">
         <is>
-          <t>EF4-0231677-4</t>
+          <t>EF4-0232004-0</t>
         </is>
       </c>
       <c r="C305" t="inlineStr">
@@ -25847,12 +25839,12 @@
       <c r="D305" t="inlineStr"/>
       <c r="E305" t="inlineStr">
         <is>
-          <t>9903.03.01</t>
+          <t>9903.03.03</t>
         </is>
       </c>
       <c r="F305" t="inlineStr">
         <is>
-          <t>SECTION 122 - 10% DUTY</t>
+          <t>S122 -EXCLUSION-EXEMPTED PRDTS</t>
         </is>
       </c>
       <c r="G305" t="inlineStr">
@@ -25862,27 +25854,27 @@
       </c>
       <c r="H305" t="inlineStr">
         <is>
-          <t>9903.03.01</t>
+          <t>9903.03.03</t>
         </is>
       </c>
       <c r="I305" t="inlineStr">
         <is>
-          <t>3505.10.0092</t>
+          <t>2930.90.9231</t>
         </is>
       </c>
       <c r="J305" t="inlineStr">
         <is>
-          <t>ROYAL INGREDIENTS GROUP BV</t>
+          <t>CASTLE CHEMICALS LTD</t>
         </is>
       </c>
       <c r="K305" t="inlineStr">
         <is>
-          <t>ROYINGRE</t>
+          <t>CASCHE01</t>
         </is>
       </c>
       <c r="L305" t="inlineStr">
         <is>
-          <t>074601-00962</t>
+          <t>151704-07138</t>
         </is>
       </c>
       <c r="M305" t="inlineStr">
@@ -25897,34 +25889,34 @@
       </c>
       <c r="O305" t="inlineStr">
         <is>
-          <t>EHM INTERTRADING CO LTD</t>
+          <t>HUBEI JIANGHAN NEW MATERIALS CO LTD</t>
         </is>
       </c>
       <c r="P305" t="inlineStr">
         <is>
-          <t>EHM INTERTRADING CO LTD</t>
+          <t>HUBEI JIANGHAN NEW MATERIALS CO LTD</t>
         </is>
       </c>
       <c r="Q305" t="inlineStr">
         <is>
-          <t>2026-05-05 00:00:00</t>
+          <t>2026-04-30 00:00:00</t>
         </is>
       </c>
     </row>
     <row r="306">
       <c r="A306" t="inlineStr">
         <is>
-          <t>2565784</t>
+          <t>2566078</t>
         </is>
       </c>
       <c r="B306" t="inlineStr">
         <is>
-          <t>EF4-0231678-2</t>
+          <t>EF4-0232219-4</t>
         </is>
       </c>
       <c r="C306" t="inlineStr">
         <is>
-          <t>Vessel, Container</t>
+          <t>Vessel, Non-container</t>
         </is>
       </c>
       <c r="D306" t="inlineStr"/>
@@ -25950,59 +25942,59 @@
       </c>
       <c r="I306" t="inlineStr">
         <is>
-          <t>3505.10.0092</t>
+          <t>8474.10.0010</t>
         </is>
       </c>
       <c r="J306" t="inlineStr">
         <is>
-          <t>ROYAL INGREDIENTS GROUP BV</t>
+          <t>EDGE INNOVATE (NI) LTD</t>
         </is>
       </c>
       <c r="K306" t="inlineStr">
         <is>
-          <t>ROYINGRE</t>
+          <t>EDGINN01</t>
         </is>
       </c>
       <c r="L306" t="inlineStr">
         <is>
-          <t>074601-00962</t>
+          <t>135501-01432</t>
         </is>
       </c>
       <c r="M306" t="inlineStr">
         <is>
+          <t>2026-06-17 00:00:00</t>
+        </is>
+      </c>
+      <c r="N306" t="inlineStr">
+        <is>
           <t>2026-06-18 00:00:00</t>
         </is>
       </c>
-      <c r="N306" t="inlineStr">
-        <is>
-          <t>2026-06-18 00:00:00</t>
-        </is>
-      </c>
       <c r="O306" t="inlineStr">
         <is>
-          <t>EHM INTERTRADING CO LTD</t>
+          <t>EDGE INNOVATE (NI) LTD</t>
         </is>
       </c>
       <c r="P306" t="inlineStr">
         <is>
-          <t>EHM INTERTRADING CO LTD</t>
+          <t>EDGE INNOVATE (NI) LTD</t>
         </is>
       </c>
       <c r="Q306" t="inlineStr">
         <is>
-          <t>2026-05-05 00:00:00</t>
+          <t>2026-05-29 00:00:00</t>
         </is>
       </c>
     </row>
     <row r="307">
       <c r="A307" t="inlineStr">
         <is>
-          <t>2565894</t>
+          <t>2565937</t>
         </is>
       </c>
       <c r="B307" t="inlineStr">
         <is>
-          <t>EF4-0232004-0</t>
+          <t>EF4-0232258-2</t>
         </is>
       </c>
       <c r="C307" t="inlineStr">
@@ -26013,12 +26005,12 @@
       <c r="D307" t="inlineStr"/>
       <c r="E307" t="inlineStr">
         <is>
-          <t>9903.03.03</t>
+          <t>9903.03.06</t>
         </is>
       </c>
       <c r="F307" t="inlineStr">
         <is>
-          <t>S122 -EXCLUSION-EXEMPTED PRDTS</t>
+          <t>S122 EXCL,IRN/STL/ALUM,DERIV</t>
         </is>
       </c>
       <c r="G307" t="inlineStr">
@@ -26028,115 +26020,115 @@
       </c>
       <c r="H307" t="inlineStr">
         <is>
-          <t>9903.03.03</t>
+          <t>9903.03.06</t>
         </is>
       </c>
       <c r="I307" t="inlineStr">
         <is>
-          <t>2930.90.9231</t>
+          <t>9903.82.22,8431.20.0000</t>
         </is>
       </c>
       <c r="J307" t="inlineStr">
         <is>
-          <t>CASTLE CHEMICALS LTD</t>
+          <t>MALLAGHAN (GA) INC.</t>
         </is>
       </c>
       <c r="K307" t="inlineStr">
         <is>
-          <t>CASCHE01</t>
+          <t>MALGA01</t>
         </is>
       </c>
       <c r="L307" t="inlineStr">
         <is>
-          <t>151704-07138</t>
+          <t>36-488102800</t>
         </is>
       </c>
       <c r="M307" t="inlineStr">
         <is>
+          <t>2026-06-20 00:00:00</t>
+        </is>
+      </c>
+      <c r="N307" t="inlineStr">
+        <is>
           <t>2026-06-18 00:00:00</t>
         </is>
       </c>
-      <c r="N307" t="inlineStr">
-        <is>
-          <t>2026-06-18 00:00:00</t>
-        </is>
-      </c>
       <c r="O307" t="inlineStr">
         <is>
-          <t>HUBEI JIANGHAN NEW MATERIALS CO LTD</t>
+          <t>MALLAGHAN ENGINEERING  LTD</t>
         </is>
       </c>
       <c r="P307" t="inlineStr">
         <is>
-          <t>HUBEI JIANGHAN NEW MATERIALS CO LTD</t>
+          <t>MALLAGHAN ENGINEERING  LTD</t>
         </is>
       </c>
       <c r="Q307" t="inlineStr">
         <is>
-          <t>2026-04-30 00:00:00</t>
+          <t>2026-05-17 00:00:00</t>
         </is>
       </c>
     </row>
     <row r="308">
       <c r="A308" t="inlineStr">
         <is>
-          <t>2566078</t>
+          <t>2565937</t>
         </is>
       </c>
       <c r="B308" t="inlineStr">
         <is>
-          <t>EF4-0232219-4</t>
+          <t>EF4-0232258-2</t>
         </is>
       </c>
       <c r="C308" t="inlineStr">
         <is>
-          <t>Vessel, Non-container</t>
+          <t>Vessel, Container</t>
         </is>
       </c>
       <c r="D308" t="inlineStr"/>
       <c r="E308" t="inlineStr">
         <is>
-          <t>9903.03.01</t>
+          <t>9903.03.06</t>
         </is>
       </c>
       <c r="F308" t="inlineStr">
         <is>
-          <t>SECTION 122 - 10% DUTY</t>
+          <t>S122 EXCL,IRN/STL/ALUM,DERIV</t>
         </is>
       </c>
       <c r="G308" t="inlineStr">
         <is>
-          <t>001</t>
+          <t>002</t>
         </is>
       </c>
       <c r="H308" t="inlineStr">
         <is>
-          <t>9903.03.01</t>
+          <t>9903.03.06</t>
         </is>
       </c>
       <c r="I308" t="inlineStr">
         <is>
-          <t>8474.10.0010</t>
+          <t>9903.82.22,8431.20.0000</t>
         </is>
       </c>
       <c r="J308" t="inlineStr">
         <is>
-          <t>EDGE INNOVATE (NI) LTD</t>
+          <t>MALLAGHAN (GA) INC.</t>
         </is>
       </c>
       <c r="K308" t="inlineStr">
         <is>
-          <t>EDGINN01</t>
+          <t>MALGA01</t>
         </is>
       </c>
       <c r="L308" t="inlineStr">
         <is>
-          <t>135501-01432</t>
+          <t>36-488102800</t>
         </is>
       </c>
       <c r="M308" t="inlineStr">
         <is>
-          <t>2026-06-17 00:00:00</t>
+          <t>2026-06-20 00:00:00</t>
         </is>
       </c>
       <c r="N308" t="inlineStr">
@@ -26146,17 +26138,17 @@
       </c>
       <c r="O308" t="inlineStr">
         <is>
-          <t>EDGE INNOVATE (NI) LTD</t>
+          <t>MALLAGHAN ENGINEERING  LTD</t>
         </is>
       </c>
       <c r="P308" t="inlineStr">
         <is>
-          <t>EDGE INNOVATE (NI) LTD</t>
+          <t>MALLAGHAN ENGINEERING  LTD</t>
         </is>
       </c>
       <c r="Q308" t="inlineStr">
         <is>
-          <t>2026-05-29 00:00:00</t>
+          <t>2026-05-17 00:00:00</t>
         </is>
       </c>
     </row>
@@ -26189,7 +26181,7 @@
       </c>
       <c r="G309" t="inlineStr">
         <is>
-          <t>001</t>
+          <t>003</t>
         </is>
       </c>
       <c r="H309" t="inlineStr">
@@ -26246,12 +26238,12 @@
     <row r="310">
       <c r="A310" t="inlineStr">
         <is>
-          <t>2565937</t>
+          <t>2566105</t>
         </is>
       </c>
       <c r="B310" t="inlineStr">
         <is>
-          <t>EF4-0232258-2</t>
+          <t>EF4-0232283-0</t>
         </is>
       </c>
       <c r="C310" t="inlineStr">
@@ -26262,47 +26254,47 @@
       <c r="D310" t="inlineStr"/>
       <c r="E310" t="inlineStr">
         <is>
-          <t>9903.03.06</t>
+          <t>9903.03.01</t>
         </is>
       </c>
       <c r="F310" t="inlineStr">
         <is>
-          <t>S122 EXCL,IRN/STL/ALUM,DERIV</t>
+          <t>SECTION 122 - 10% DUTY</t>
         </is>
       </c>
       <c r="G310" t="inlineStr">
         <is>
-          <t>002</t>
+          <t>001</t>
         </is>
       </c>
       <c r="H310" t="inlineStr">
         <is>
-          <t>9903.03.06</t>
+          <t>9903.03.01</t>
         </is>
       </c>
       <c r="I310" t="inlineStr">
         <is>
-          <t>9903.82.22,8431.20.0000</t>
+          <t>3920.61.0000</t>
         </is>
       </c>
       <c r="J310" t="inlineStr">
         <is>
-          <t>MALLAGHAN (GA) INC.</t>
+          <t>TUBUS BAUER GMBH</t>
         </is>
       </c>
       <c r="K310" t="inlineStr">
         <is>
-          <t>MALGA01</t>
+          <t>TUBBAU01</t>
         </is>
       </c>
       <c r="L310" t="inlineStr">
         <is>
-          <t>36-488102800</t>
+          <t>091601-00584</t>
         </is>
       </c>
       <c r="M310" t="inlineStr">
         <is>
-          <t>2026-06-20 00:00:00</t>
+          <t>2026-06-18 00:00:00</t>
         </is>
       </c>
       <c r="N310" t="inlineStr">
@@ -26312,29 +26304,29 @@
       </c>
       <c r="O310" t="inlineStr">
         <is>
-          <t>MALLAGHAN ENGINEERING  LTD</t>
+          <t>TUBUS BAUER GMBH</t>
         </is>
       </c>
       <c r="P310" t="inlineStr">
         <is>
-          <t>MALLAGHAN ENGINEERING  LTD</t>
+          <t>TUBUS BAUER GMBH</t>
         </is>
       </c>
       <c r="Q310" t="inlineStr">
         <is>
-          <t>2026-05-17 00:00:00</t>
+          <t>2026-06-02 00:00:00</t>
         </is>
       </c>
     </row>
     <row r="311">
       <c r="A311" t="inlineStr">
         <is>
-          <t>2565937</t>
+          <t>2566265</t>
         </is>
       </c>
       <c r="B311" t="inlineStr">
         <is>
-          <t>EF4-0232258-2</t>
+          <t>EF4-0232362-2</t>
         </is>
       </c>
       <c r="C311" t="inlineStr">
@@ -26345,47 +26337,47 @@
       <c r="D311" t="inlineStr"/>
       <c r="E311" t="inlineStr">
         <is>
-          <t>9903.03.06</t>
+          <t>9903.03.01</t>
         </is>
       </c>
       <c r="F311" t="inlineStr">
         <is>
-          <t>S122 EXCL,IRN/STL/ALUM,DERIV</t>
+          <t>SECTION 122 - 10% DUTY</t>
         </is>
       </c>
       <c r="G311" t="inlineStr">
         <is>
-          <t>003</t>
+          <t>001</t>
         </is>
       </c>
       <c r="H311" t="inlineStr">
         <is>
-          <t>9903.03.06</t>
+          <t>9903.03.01</t>
         </is>
       </c>
       <c r="I311" t="inlineStr">
         <is>
-          <t>9903.82.22,8431.20.0000</t>
+          <t>9903.82.01,8424.90.9080</t>
         </is>
       </c>
       <c r="J311" t="inlineStr">
         <is>
-          <t>MALLAGHAN (GA) INC.</t>
+          <t>EISENMANN OF SOUTH CAROLINA INC</t>
         </is>
       </c>
       <c r="K311" t="inlineStr">
         <is>
-          <t>MALGA01</t>
+          <t>EISINC03</t>
         </is>
       </c>
       <c r="L311" t="inlineStr">
         <is>
-          <t>36-488102800</t>
+          <t>86-240963300</t>
         </is>
       </c>
       <c r="M311" t="inlineStr">
         <is>
-          <t>2026-06-20 00:00:00</t>
+          <t>2026-06-21 00:00:00</t>
         </is>
       </c>
       <c r="N311" t="inlineStr">
@@ -26395,29 +26387,29 @@
       </c>
       <c r="O311" t="inlineStr">
         <is>
-          <t>MALLAGHAN ENGINEERING  LTD</t>
+          <t>EISENMANN GMBH</t>
         </is>
       </c>
       <c r="P311" t="inlineStr">
         <is>
-          <t>MALLAGHAN ENGINEERING  LTD</t>
+          <t>EISENMANN GMBH</t>
         </is>
       </c>
       <c r="Q311" t="inlineStr">
         <is>
-          <t>2026-05-17 00:00:00</t>
+          <t>2026-06-06 00:00:00</t>
         </is>
       </c>
     </row>
     <row r="312">
       <c r="A312" t="inlineStr">
         <is>
-          <t>2566105</t>
+          <t>2566155</t>
         </is>
       </c>
       <c r="B312" t="inlineStr">
         <is>
-          <t>EF4-0232283-0</t>
+          <t>EF4-0232431-5</t>
         </is>
       </c>
       <c r="C312" t="inlineStr">
@@ -26428,12 +26420,12 @@
       <c r="D312" t="inlineStr"/>
       <c r="E312" t="inlineStr">
         <is>
-          <t>9903.03.01</t>
+          <t>9903.03.06</t>
         </is>
       </c>
       <c r="F312" t="inlineStr">
         <is>
-          <t>SECTION 122 - 10% DUTY</t>
+          <t>S122 EXCL,IRN/STL/ALUM,DERIV</t>
         </is>
       </c>
       <c r="G312" t="inlineStr">
@@ -26443,27 +26435,27 @@
       </c>
       <c r="H312" t="inlineStr">
         <is>
-          <t>9903.03.01</t>
+          <t>9903.03.06</t>
         </is>
       </c>
       <c r="I312" t="inlineStr">
         <is>
-          <t>3920.61.0000</t>
+          <t>9903.74.11,9903.94.53,8708.29.5160</t>
         </is>
       </c>
       <c r="J312" t="inlineStr">
         <is>
-          <t>TUBUS BAUER GMBH</t>
+          <t>BORGERS USA CORP</t>
         </is>
       </c>
       <c r="K312" t="inlineStr">
         <is>
-          <t>TUBBAU01</t>
+          <t>BORUSA</t>
         </is>
       </c>
       <c r="L312" t="inlineStr">
         <is>
-          <t>091601-00584</t>
+          <t>65-117296500</t>
         </is>
       </c>
       <c r="M312" t="inlineStr">
@@ -26478,29 +26470,29 @@
       </c>
       <c r="O312" t="inlineStr">
         <is>
-          <t>TUBUS BAUER GMBH</t>
+          <t>AUTONEUM CZ S.R.O.</t>
         </is>
       </c>
       <c r="P312" t="inlineStr">
         <is>
-          <t>TUBUS BAUER GMBH</t>
+          <t>AUTONEUM CZ S.R.O.</t>
         </is>
       </c>
       <c r="Q312" t="inlineStr">
         <is>
-          <t>2026-06-02 00:00:00</t>
+          <t>2026-06-06 00:00:00</t>
         </is>
       </c>
     </row>
     <row r="313">
       <c r="A313" t="inlineStr">
         <is>
-          <t>2566265</t>
+          <t>2566155</t>
         </is>
       </c>
       <c r="B313" t="inlineStr">
         <is>
-          <t>EF4-0232362-2</t>
+          <t>EF4-0232431-5</t>
         </is>
       </c>
       <c r="C313" t="inlineStr">
@@ -26511,47 +26503,47 @@
       <c r="D313" t="inlineStr"/>
       <c r="E313" t="inlineStr">
         <is>
-          <t>9903.03.01</t>
+          <t>9903.03.06</t>
         </is>
       </c>
       <c r="F313" t="inlineStr">
         <is>
-          <t>SECTION 122 - 10% DUTY</t>
+          <t>S122 EXCL,IRN/STL/ALUM,DERIV</t>
         </is>
       </c>
       <c r="G313" t="inlineStr">
         <is>
-          <t>001</t>
+          <t>002</t>
         </is>
       </c>
       <c r="H313" t="inlineStr">
         <is>
-          <t>9903.03.01</t>
+          <t>9903.03.06</t>
         </is>
       </c>
       <c r="I313" t="inlineStr">
         <is>
-          <t>9903.82.01,8424.90.9080</t>
+          <t>9903.74.11,9903.94.53,8708.29.5160</t>
         </is>
       </c>
       <c r="J313" t="inlineStr">
         <is>
-          <t>EISENMANN OF SOUTH CAROLINA INC</t>
+          <t>BORGERS USA CORP</t>
         </is>
       </c>
       <c r="K313" t="inlineStr">
         <is>
-          <t>EISINC03</t>
+          <t>BORUSA</t>
         </is>
       </c>
       <c r="L313" t="inlineStr">
         <is>
-          <t>86-240963300</t>
+          <t>65-117296500</t>
         </is>
       </c>
       <c r="M313" t="inlineStr">
         <is>
-          <t>2026-06-21 00:00:00</t>
+          <t>2026-06-18 00:00:00</t>
         </is>
       </c>
       <c r="N313" t="inlineStr">
@@ -26561,12 +26553,12 @@
       </c>
       <c r="O313" t="inlineStr">
         <is>
-          <t>EISENMANN GMBH</t>
+          <t>AUTONEUM CZ S.R.O.</t>
         </is>
       </c>
       <c r="P313" t="inlineStr">
         <is>
-          <t>EISENMANN GMBH</t>
+          <t>AUTONEUM CZ S.R.O.</t>
         </is>
       </c>
       <c r="Q313" t="inlineStr">
@@ -26604,7 +26596,7 @@
       </c>
       <c r="G314" t="inlineStr">
         <is>
-          <t>001</t>
+          <t>003</t>
         </is>
       </c>
       <c r="H314" t="inlineStr">
@@ -26687,7 +26679,7 @@
       </c>
       <c r="G315" t="inlineStr">
         <is>
-          <t>002</t>
+          <t>004</t>
         </is>
       </c>
       <c r="H315" t="inlineStr">
@@ -26744,95 +26736,95 @@
     <row r="316">
       <c r="A316" t="inlineStr">
         <is>
-          <t>2566155</t>
+          <t>4539433</t>
         </is>
       </c>
       <c r="B316" t="inlineStr">
         <is>
-          <t>EF4-0232431-5</t>
+          <t>EF4-0232434-9</t>
         </is>
       </c>
       <c r="C316" t="inlineStr">
         <is>
-          <t>Vessel, Container</t>
+          <t>Air, Non-container</t>
         </is>
       </c>
       <c r="D316" t="inlineStr"/>
       <c r="E316" t="inlineStr">
         <is>
-          <t>9903.03.06</t>
+          <t>9903.88.03</t>
         </is>
       </c>
       <c r="F316" t="inlineStr">
         <is>
-          <t>S122 EXCL,IRN/STL/ALUM,DERIV</t>
+          <t>ARTICLE OF CHINA,US NTE 20(F)</t>
         </is>
       </c>
       <c r="G316" t="inlineStr">
         <is>
-          <t>003</t>
+          <t>001</t>
         </is>
       </c>
       <c r="H316" t="inlineStr">
         <is>
-          <t>9903.03.06</t>
+          <t>9903.88.03</t>
         </is>
       </c>
       <c r="I316" t="inlineStr">
         <is>
-          <t>9903.74.11,9903.94.53,8708.29.5160</t>
+          <t>9903.03.03,2926.90.4300</t>
         </is>
       </c>
       <c r="J316" t="inlineStr">
         <is>
-          <t>BORGERS USA CORP</t>
+          <t>MAYZO INC</t>
         </is>
       </c>
       <c r="K316" t="inlineStr">
         <is>
-          <t>BORUSA</t>
+          <t>MAYINC</t>
         </is>
       </c>
       <c r="L316" t="inlineStr">
         <is>
-          <t>65-117296500</t>
+          <t>62-129031200</t>
         </is>
       </c>
       <c r="M316" t="inlineStr">
         <is>
+          <t>2026-06-17 00:00:00</t>
+        </is>
+      </c>
+      <c r="N316" t="inlineStr">
+        <is>
           <t>2026-06-18 00:00:00</t>
         </is>
       </c>
-      <c r="N316" t="inlineStr">
-        <is>
-          <t>2026-06-18 00:00:00</t>
-        </is>
-      </c>
       <c r="O316" t="inlineStr">
         <is>
-          <t>AUTONEUM CZ S.R.O.</t>
+          <t>HANGZHOU DISHENG IMPORT &amp; EXPORT</t>
         </is>
       </c>
       <c r="P316" t="inlineStr">
         <is>
-          <t>AUTONEUM CZ S.R.O.</t>
+          <t>HANGZHOU DISHENG IMPORT &amp; EXPORT</t>
         </is>
       </c>
       <c r="Q316" t="inlineStr">
         <is>
-          <t>2026-06-06 00:00:00</t>
+          <t>2026-06-17 00:00:00</t>
         </is>
       </c>
     </row>
     <row r="317">
       <c r="A317" t="inlineStr">
         <is>
-          <t>2566155</t>
+          <t>2565798</t>
         </is>
       </c>
       <c r="B317" t="inlineStr">
         <is>
-          <t>EF4-0232431-5</t>
+          <t>EF4-0232494-3</t>
         </is>
       </c>
       <c r="C317" t="inlineStr">
@@ -26853,7 +26845,7 @@
       </c>
       <c r="G317" t="inlineStr">
         <is>
-          <t>004</t>
+          <t>001</t>
         </is>
       </c>
       <c r="H317" t="inlineStr">
@@ -26863,22 +26855,22 @@
       </c>
       <c r="I317" t="inlineStr">
         <is>
-          <t>9903.74.11,9903.94.53,8708.29.5160</t>
+          <t>9903.82.02,7222.20.0064</t>
         </is>
       </c>
       <c r="J317" t="inlineStr">
         <is>
-          <t>BORGERS USA CORP</t>
+          <t>MESHA STEELS  LLC</t>
         </is>
       </c>
       <c r="K317" t="inlineStr">
         <is>
-          <t>BORUSA</t>
+          <t>MESSTE</t>
         </is>
       </c>
       <c r="L317" t="inlineStr">
         <is>
-          <t>65-117296500</t>
+          <t>20-274801900</t>
         </is>
       </c>
       <c r="M317" t="inlineStr">
@@ -26893,45 +26885,45 @@
       </c>
       <c r="O317" t="inlineStr">
         <is>
-          <t>AUTONEUM CZ S.R.O.</t>
+          <t>BHANSALI BRIGHT BARS PVT. LTD.</t>
         </is>
       </c>
       <c r="P317" t="inlineStr">
         <is>
-          <t>AUTONEUM CZ S.R.O.</t>
+          <t>BHANSALI BRIGHT BARS PVT. LTD.</t>
         </is>
       </c>
       <c r="Q317" t="inlineStr">
         <is>
-          <t>2026-06-06 00:00:00</t>
+          <t>2026-05-12 00:00:00</t>
         </is>
       </c>
     </row>
     <row r="318">
       <c r="A318" t="inlineStr">
         <is>
-          <t>4539433</t>
+          <t>2565799</t>
         </is>
       </c>
       <c r="B318" t="inlineStr">
         <is>
-          <t>EF4-0232434-9</t>
+          <t>EF4-0232495-0</t>
         </is>
       </c>
       <c r="C318" t="inlineStr">
         <is>
-          <t>Air, Non-container</t>
+          <t>Vessel, Container</t>
         </is>
       </c>
       <c r="D318" t="inlineStr"/>
       <c r="E318" t="inlineStr">
         <is>
-          <t>9903.88.03</t>
+          <t>9903.03.06</t>
         </is>
       </c>
       <c r="F318" t="inlineStr">
         <is>
-          <t>ARTICLE OF CHINA,US NTE 20(F)</t>
+          <t>S122 EXCL,IRN/STL/ALUM,DERIV</t>
         </is>
       </c>
       <c r="G318" t="inlineStr">
@@ -26941,32 +26933,32 @@
       </c>
       <c r="H318" t="inlineStr">
         <is>
-          <t>9903.88.03</t>
+          <t>9903.03.06</t>
         </is>
       </c>
       <c r="I318" t="inlineStr">
         <is>
-          <t>9903.03.03,2926.90.4300</t>
+          <t>9903.82.02,7222.20.0062</t>
         </is>
       </c>
       <c r="J318" t="inlineStr">
         <is>
-          <t>MAYZO INC</t>
+          <t>MESHA STEELS  LLC</t>
         </is>
       </c>
       <c r="K318" t="inlineStr">
         <is>
-          <t>MAYINC</t>
+          <t>MESSTE</t>
         </is>
       </c>
       <c r="L318" t="inlineStr">
         <is>
-          <t>62-129031200</t>
+          <t>20-274801900</t>
         </is>
       </c>
       <c r="M318" t="inlineStr">
         <is>
-          <t>2026-06-17 00:00:00</t>
+          <t>2026-06-18 00:00:00</t>
         </is>
       </c>
       <c r="N318" t="inlineStr">
@@ -26976,29 +26968,29 @@
       </c>
       <c r="O318" t="inlineStr">
         <is>
-          <t>HANGZHOU DISHENG IMPORT &amp; EXPORT</t>
+          <t>BHANSALI BRIGHT BARS PVT. LTD.</t>
         </is>
       </c>
       <c r="P318" t="inlineStr">
         <is>
-          <t>HANGZHOU DISHENG IMPORT &amp; EXPORT</t>
+          <t>BHANSALI BRIGHT BARS PVT. LTD.</t>
         </is>
       </c>
       <c r="Q318" t="inlineStr">
         <is>
-          <t>2026-06-17 00:00:00</t>
+          <t>2026-05-12 00:00:00</t>
         </is>
       </c>
     </row>
     <row r="319">
       <c r="A319" t="inlineStr">
         <is>
-          <t>2565798</t>
+          <t>2565760</t>
         </is>
       </c>
       <c r="B319" t="inlineStr">
         <is>
-          <t>EF4-0232494-3</t>
+          <t>EF4-0231661-8</t>
         </is>
       </c>
       <c r="C319" t="inlineStr">
@@ -27009,12 +27001,12 @@
       <c r="D319" t="inlineStr"/>
       <c r="E319" t="inlineStr">
         <is>
-          <t>9903.03.06</t>
+          <t>9903.88.15</t>
         </is>
       </c>
       <c r="F319" t="inlineStr">
         <is>
-          <t>S122 EXCL,IRN/STL/ALUM,DERIV</t>
+          <t>ARTICLE OF CHINA,US NTE 20(R)</t>
         </is>
       </c>
       <c r="G319" t="inlineStr">
@@ -27024,64 +27016,64 @@
       </c>
       <c r="H319" t="inlineStr">
         <is>
-          <t>9903.03.06</t>
+          <t>9903.88.15</t>
         </is>
       </c>
       <c r="I319" t="inlineStr">
         <is>
-          <t>9903.82.02,7222.20.0064</t>
+          <t>9903.03.06,9903.82.09,8302.42.3015</t>
         </is>
       </c>
       <c r="J319" t="inlineStr">
         <is>
-          <t>MESHA STEELS  LLC</t>
+          <t>GRASS AMERICA INC</t>
         </is>
       </c>
       <c r="K319" t="inlineStr">
         <is>
-          <t>MESSTE</t>
+          <t>GRAAME</t>
         </is>
       </c>
       <c r="L319" t="inlineStr">
         <is>
-          <t>20-274801900</t>
+          <t>51-066023000</t>
         </is>
       </c>
       <c r="M319" t="inlineStr">
         <is>
-          <t>2026-06-18 00:00:00</t>
+          <t>2026-06-20 00:00:00</t>
         </is>
       </c>
       <c r="N319" t="inlineStr">
         <is>
-          <t>2026-06-18 00:00:00</t>
+          <t>2026-06-20 00:00:00</t>
         </is>
       </c>
       <c r="O319" t="inlineStr">
         <is>
-          <t>BHANSALI BRIGHT BARS PVT. LTD.</t>
+          <t>SACA PRECISION LTD</t>
         </is>
       </c>
       <c r="P319" t="inlineStr">
         <is>
-          <t>BHANSALI BRIGHT BARS PVT. LTD.</t>
+          <t>SACA PRECISION LTD</t>
         </is>
       </c>
       <c r="Q319" t="inlineStr">
         <is>
-          <t>2026-05-12 00:00:00</t>
+          <t>2026-05-05 00:00:00</t>
         </is>
       </c>
     </row>
     <row r="320">
       <c r="A320" t="inlineStr">
         <is>
-          <t>2565799</t>
+          <t>2565760</t>
         </is>
       </c>
       <c r="B320" t="inlineStr">
         <is>
-          <t>EF4-0232495-0</t>
+          <t>EF4-0231661-8</t>
         </is>
       </c>
       <c r="C320" t="inlineStr">
@@ -27092,84 +27084,84 @@
       <c r="D320" t="inlineStr"/>
       <c r="E320" t="inlineStr">
         <is>
-          <t>9903.03.06</t>
+          <t>9903.88.15</t>
         </is>
       </c>
       <c r="F320" t="inlineStr">
         <is>
-          <t>S122 EXCL,IRN/STL/ALUM,DERIV</t>
+          <t>ARTICLE OF CHINA,US NTE 20(R)</t>
         </is>
       </c>
       <c r="G320" t="inlineStr">
         <is>
-          <t>001</t>
+          <t>002</t>
         </is>
       </c>
       <c r="H320" t="inlineStr">
         <is>
-          <t>9903.03.06</t>
+          <t>9903.88.15</t>
         </is>
       </c>
       <c r="I320" t="inlineStr">
         <is>
-          <t>9903.82.02,7222.20.0062</t>
+          <t>9903.03.01,3926.30.5000</t>
         </is>
       </c>
       <c r="J320" t="inlineStr">
         <is>
-          <t>MESHA STEELS  LLC</t>
+          <t>GRASS AMERICA INC</t>
         </is>
       </c>
       <c r="K320" t="inlineStr">
         <is>
-          <t>MESSTE</t>
+          <t>GRAAME</t>
         </is>
       </c>
       <c r="L320" t="inlineStr">
         <is>
-          <t>20-274801900</t>
+          <t>51-066023000</t>
         </is>
       </c>
       <c r="M320" t="inlineStr">
         <is>
-          <t>2026-06-18 00:00:00</t>
+          <t>2026-06-20 00:00:00</t>
         </is>
       </c>
       <c r="N320" t="inlineStr">
         <is>
-          <t>2026-06-18 00:00:00</t>
+          <t>2026-06-20 00:00:00</t>
         </is>
       </c>
       <c r="O320" t="inlineStr">
         <is>
-          <t>BHANSALI BRIGHT BARS PVT. LTD.</t>
+          <t>SACA PRECISION LTD</t>
         </is>
       </c>
       <c r="P320" t="inlineStr">
         <is>
-          <t>BHANSALI BRIGHT BARS PVT. LTD.</t>
+          <t>SACA PRECISION LTD</t>
         </is>
       </c>
       <c r="Q320" t="inlineStr">
         <is>
-          <t>2026-05-12 00:00:00</t>
+          <t>2026-05-05 00:00:00</t>
         </is>
       </c>
     </row>
     <row r="321">
       <c r="A321" t="inlineStr">
         <is>
-          <t>2565760</t>
+          <t>2615656</t>
         </is>
       </c>
       <c r="B321" t="inlineStr">
         <is>
-          <t>EF4-0231661-8</t>
+          <t>EF4-0231976-0</t>
         </is>
       </c>
       <c r="C321" t="inlineStr">
         <is>
-          <t>Vessel, Container</t>
+          <t>Vessel, Non-container</t>
         </is>
       </c>
       <c r="D321" t="inlineStr"/>
@@ -27195,22 +27187,22 @@
       </c>
       <c r="I321" t="inlineStr">
         <is>
-          <t>9903.03.06,9903.82.09,8302.42.3015</t>
+          <t>9903.03.01,3926.90.9989</t>
         </is>
       </c>
       <c r="J321" t="inlineStr">
         <is>
-          <t>GRASS AMERICA INC</t>
+          <t>VISUAL CREATIONS, INC.</t>
         </is>
       </c>
       <c r="K321" t="inlineStr">
         <is>
-          <t>GRAAME</t>
+          <t>VISCRE</t>
         </is>
       </c>
       <c r="L321" t="inlineStr">
         <is>
-          <t>51-066023000</t>
+          <t>20-461602300</t>
         </is>
       </c>
       <c r="M321" t="inlineStr">
@@ -27225,128 +27217,128 @@
       </c>
       <c r="O321" t="inlineStr">
         <is>
-          <t>SACA PRECISION LTD</t>
+          <t>NINGBO SMART HIGH TECH INDUSTRIES L</t>
         </is>
       </c>
       <c r="P321" t="inlineStr">
         <is>
-          <t>SACA PRECISION LTD</t>
+          <t>NINGBO SMART HIGH TECH INDUSTRIES LTD</t>
         </is>
       </c>
       <c r="Q321" t="inlineStr">
         <is>
-          <t>2026-05-05 00:00:00</t>
+          <t>2026-05-12 00:00:00</t>
         </is>
       </c>
     </row>
     <row r="322">
       <c r="A322" t="inlineStr">
         <is>
-          <t>2565760</t>
+          <t>2615664</t>
         </is>
       </c>
       <c r="B322" t="inlineStr">
         <is>
-          <t>EF4-0231661-8</t>
+          <t>EF4-0231983-6</t>
         </is>
       </c>
       <c r="C322" t="inlineStr">
         <is>
-          <t>Vessel, Container</t>
+          <t>Vessel, Non-container</t>
         </is>
       </c>
       <c r="D322" t="inlineStr"/>
       <c r="E322" t="inlineStr">
         <is>
-          <t>9903.88.15</t>
+          <t>9903.88.01</t>
         </is>
       </c>
       <c r="F322" t="inlineStr">
         <is>
-          <t>ARTICLE OF CHINA,US NTE 20(R)</t>
+          <t>ARTICLE OF CHINA,US NTE 20(A)</t>
         </is>
       </c>
       <c r="G322" t="inlineStr">
         <is>
-          <t>002</t>
+          <t>001</t>
         </is>
       </c>
       <c r="H322" t="inlineStr">
         <is>
-          <t>9903.88.15</t>
+          <t>9903.88.01</t>
         </is>
       </c>
       <c r="I322" t="inlineStr">
         <is>
-          <t>9903.03.01,3926.30.5000</t>
+          <t>9903.03.06,9903.82.09,8482.10.5012</t>
         </is>
       </c>
       <c r="J322" t="inlineStr">
         <is>
-          <t>GRASS AMERICA INC</t>
+          <t>VISUAL CREATIONS, INC.</t>
         </is>
       </c>
       <c r="K322" t="inlineStr">
         <is>
-          <t>GRAAME</t>
+          <t>VISCRE</t>
         </is>
       </c>
       <c r="L322" t="inlineStr">
         <is>
-          <t>51-066023000</t>
+          <t>20-461602300</t>
         </is>
       </c>
       <c r="M322" t="inlineStr">
         <is>
+          <t>2026-06-11 00:00:00</t>
+        </is>
+      </c>
+      <c r="N322" t="inlineStr">
+        <is>
           <t>2026-06-20 00:00:00</t>
         </is>
       </c>
-      <c r="N322" t="inlineStr">
-        <is>
-          <t>2026-06-20 00:00:00</t>
-        </is>
-      </c>
       <c r="O322" t="inlineStr">
         <is>
-          <t>SACA PRECISION LTD</t>
+          <t>LINYU HANDWARE MANUFACTURE CO LTD</t>
         </is>
       </c>
       <c r="P322" t="inlineStr">
         <is>
-          <t>SACA PRECISION LTD</t>
+          <t>LINYU HANDWARE MANUFACTURE CO LTD</t>
         </is>
       </c>
       <c r="Q322" t="inlineStr">
         <is>
-          <t>2026-05-05 00:00:00</t>
+          <t>2026-05-15 00:00:00</t>
         </is>
       </c>
     </row>
     <row r="323">
       <c r="A323" t="inlineStr">
         <is>
-          <t>2615656</t>
+          <t>2566178</t>
         </is>
       </c>
       <c r="B323" t="inlineStr">
         <is>
-          <t>EF4-0231976-0</t>
+          <t>EF4-0232247-5</t>
         </is>
       </c>
       <c r="C323" t="inlineStr">
         <is>
-          <t>Vessel, Non-container</t>
+          <t>Vessel, Container</t>
         </is>
       </c>
       <c r="D323" t="inlineStr"/>
       <c r="E323" t="inlineStr">
         <is>
-          <t>9903.88.15</t>
+          <t>9903.03.01</t>
         </is>
       </c>
       <c r="F323" t="inlineStr">
         <is>
-          <t>ARTICLE OF CHINA,US NTE 20(R)</t>
+          <t>SECTION 122 - 10% DUTY</t>
         </is>
       </c>
       <c r="G323" t="inlineStr">
@@ -27356,27 +27348,27 @@
       </c>
       <c r="H323" t="inlineStr">
         <is>
-          <t>9903.88.15</t>
+          <t>9903.03.01</t>
         </is>
       </c>
       <c r="I323" t="inlineStr">
         <is>
-          <t>9903.03.01,3926.90.9989</t>
+          <t>1108.13.0010</t>
         </is>
       </c>
       <c r="J323" t="inlineStr">
         <is>
-          <t>VISUAL CREATIONS, INC.</t>
+          <t>ROYAL INGREDIENTS GROUP BV</t>
         </is>
       </c>
       <c r="K323" t="inlineStr">
         <is>
-          <t>VISCRE</t>
+          <t>ROYINGRE</t>
         </is>
       </c>
       <c r="L323" t="inlineStr">
         <is>
-          <t>20-461602300</t>
+          <t>074601-00962</t>
         </is>
       </c>
       <c r="M323" t="inlineStr">
@@ -27391,45 +27383,49 @@
       </c>
       <c r="O323" t="inlineStr">
         <is>
-          <t>NINGBO SMART HIGH TECH INDUSTRIES L</t>
+          <t>AKV LANGHOLT AMBA</t>
         </is>
       </c>
       <c r="P323" t="inlineStr">
         <is>
-          <t>NINGBO SMART HIGH TECH INDUSTRIES LTD</t>
+          <t>AKV LANGHOLT AMBA</t>
         </is>
       </c>
       <c r="Q323" t="inlineStr">
         <is>
-          <t>2026-05-12 00:00:00</t>
+          <t>2026-06-01 00:00:00</t>
         </is>
       </c>
     </row>
     <row r="324">
       <c r="A324" t="inlineStr">
         <is>
-          <t>2615664</t>
+          <t>2566229</t>
         </is>
       </c>
       <c r="B324" t="inlineStr">
         <is>
-          <t>EF4-0231983-6</t>
+          <t>EF4-0232249-1</t>
         </is>
       </c>
       <c r="C324" t="inlineStr">
         <is>
-          <t>Vessel, Non-container</t>
-        </is>
-      </c>
-      <c r="D324" t="inlineStr"/>
+          <t>Vessel, Container</t>
+        </is>
+      </c>
+      <c r="D324" t="inlineStr">
+        <is>
+          <t>V0710338448</t>
+        </is>
+      </c>
       <c r="E324" t="inlineStr">
         <is>
-          <t>9903.88.01</t>
+          <t>9903.03.01</t>
         </is>
       </c>
       <c r="F324" t="inlineStr">
         <is>
-          <t>ARTICLE OF CHINA,US NTE 20(A)</t>
+          <t>SECTION 122 - 10% DUTY</t>
         </is>
       </c>
       <c r="G324" t="inlineStr">
@@ -27439,32 +27435,32 @@
       </c>
       <c r="H324" t="inlineStr">
         <is>
-          <t>9903.88.01</t>
+          <t>9903.03.01</t>
         </is>
       </c>
       <c r="I324" t="inlineStr">
         <is>
-          <t>9903.03.06,9903.82.09,8482.10.5012</t>
+          <t>1108.13.0010</t>
         </is>
       </c>
       <c r="J324" t="inlineStr">
         <is>
-          <t>VISUAL CREATIONS, INC.</t>
+          <t>ROYAL INGREDIENTS GROUP BV</t>
         </is>
       </c>
       <c r="K324" t="inlineStr">
         <is>
-          <t>VISCRE</t>
+          <t>ROYINGRE</t>
         </is>
       </c>
       <c r="L324" t="inlineStr">
         <is>
-          <t>20-461602300</t>
+          <t>074601-00962</t>
         </is>
       </c>
       <c r="M324" t="inlineStr">
         <is>
-          <t>2026-06-11 00:00:00</t>
+          <t>2026-06-20 00:00:00</t>
         </is>
       </c>
       <c r="N324" t="inlineStr">
@@ -27474,29 +27470,29 @@
       </c>
       <c r="O324" t="inlineStr">
         <is>
-          <t>LINYU HANDWARE MANUFACTURE CO LTD</t>
+          <t>AKV LANGHOLT AMBA</t>
         </is>
       </c>
       <c r="P324" t="inlineStr">
         <is>
-          <t>LINYU HANDWARE MANUFACTURE CO LTD</t>
+          <t>AKV LANGHOLT AMBA</t>
         </is>
       </c>
       <c r="Q324" t="inlineStr">
         <is>
-          <t>2026-05-15 00:00:00</t>
+          <t>2026-06-01 00:00:00</t>
         </is>
       </c>
     </row>
     <row r="325">
       <c r="A325" t="inlineStr">
         <is>
-          <t>2566178</t>
+          <t>2566177</t>
         </is>
       </c>
       <c r="B325" t="inlineStr">
         <is>
-          <t>EF4-0232247-5</t>
+          <t>EF4-0232275-6</t>
         </is>
       </c>
       <c r="C325" t="inlineStr">
@@ -27504,7 +27500,11 @@
           <t>Vessel, Container</t>
         </is>
       </c>
-      <c r="D325" t="inlineStr"/>
+      <c r="D325" t="inlineStr">
+        <is>
+          <t>V0710338448</t>
+        </is>
+      </c>
       <c r="E325" t="inlineStr">
         <is>
           <t>9903.03.01</t>
@@ -27574,12 +27574,12 @@
     <row r="326">
       <c r="A326" t="inlineStr">
         <is>
-          <t>2566229</t>
+          <t>2566051</t>
         </is>
       </c>
       <c r="B326" t="inlineStr">
         <is>
-          <t>EF4-0232249-1</t>
+          <t>EF4-0232281-4</t>
         </is>
       </c>
       <c r="C326" t="inlineStr">
@@ -27589,7 +27589,7 @@
       </c>
       <c r="D326" t="inlineStr">
         <is>
-          <t>V0710338448</t>
+          <t>V0710349973</t>
         </is>
       </c>
       <c r="E326" t="inlineStr">
@@ -27614,42 +27614,42 @@
       </c>
       <c r="I326" t="inlineStr">
         <is>
-          <t>1108.13.0010</t>
+          <t>4811.59.4040</t>
         </is>
       </c>
       <c r="J326" t="inlineStr">
         <is>
-          <t>ROYAL INGREDIENTS GROUP BV</t>
+          <t>BAUSCHLINNEMANN NORTH AMERICA</t>
         </is>
       </c>
       <c r="K326" t="inlineStr">
         <is>
-          <t>ROYINGRE</t>
+          <t>BAULIN</t>
         </is>
       </c>
       <c r="L326" t="inlineStr">
         <is>
-          <t>074601-00962</t>
+          <t>56-193913400</t>
         </is>
       </c>
       <c r="M326" t="inlineStr">
         <is>
+          <t>2026-06-21 00:00:00</t>
+        </is>
+      </c>
+      <c r="N326" t="inlineStr">
+        <is>
           <t>2026-06-20 00:00:00</t>
         </is>
       </c>
-      <c r="N326" t="inlineStr">
-        <is>
-          <t>2026-06-20 00:00:00</t>
-        </is>
-      </c>
       <c r="O326" t="inlineStr">
         <is>
-          <t>AKV LANGHOLT AMBA</t>
+          <t>SURTECO GMBH</t>
         </is>
       </c>
       <c r="P326" t="inlineStr">
         <is>
-          <t>AKV LANGHOLT AMBA</t>
+          <t>SURTECO GMBH</t>
         </is>
       </c>
       <c r="Q326" t="inlineStr">
@@ -27661,12 +27661,12 @@
     <row r="327">
       <c r="A327" t="inlineStr">
         <is>
-          <t>2566177</t>
+          <t>2566051</t>
         </is>
       </c>
       <c r="B327" t="inlineStr">
         <is>
-          <t>EF4-0232275-6</t>
+          <t>EF4-0232281-4</t>
         </is>
       </c>
       <c r="C327" t="inlineStr">
@@ -27676,7 +27676,7 @@
       </c>
       <c r="D327" t="inlineStr">
         <is>
-          <t>V0710338448</t>
+          <t>V0710349973</t>
         </is>
       </c>
       <c r="E327" t="inlineStr">
@@ -27691,7 +27691,7 @@
       </c>
       <c r="G327" t="inlineStr">
         <is>
-          <t>001</t>
+          <t>002</t>
         </is>
       </c>
       <c r="H327" t="inlineStr">
@@ -27701,42 +27701,42 @@
       </c>
       <c r="I327" t="inlineStr">
         <is>
-          <t>1108.13.0010</t>
+          <t>4811.59.4040</t>
         </is>
       </c>
       <c r="J327" t="inlineStr">
         <is>
-          <t>ROYAL INGREDIENTS GROUP BV</t>
+          <t>BAUSCHLINNEMANN NORTH AMERICA</t>
         </is>
       </c>
       <c r="K327" t="inlineStr">
         <is>
-          <t>ROYINGRE</t>
+          <t>BAULIN</t>
         </is>
       </c>
       <c r="L327" t="inlineStr">
         <is>
-          <t>074601-00962</t>
+          <t>56-193913400</t>
         </is>
       </c>
       <c r="M327" t="inlineStr">
         <is>
+          <t>2026-06-21 00:00:00</t>
+        </is>
+      </c>
+      <c r="N327" t="inlineStr">
+        <is>
           <t>2026-06-20 00:00:00</t>
         </is>
       </c>
-      <c r="N327" t="inlineStr">
-        <is>
-          <t>2026-06-20 00:00:00</t>
-        </is>
-      </c>
       <c r="O327" t="inlineStr">
         <is>
-          <t>AKV LANGHOLT AMBA</t>
+          <t>SURTECO GMBH</t>
         </is>
       </c>
       <c r="P327" t="inlineStr">
         <is>
-          <t>AKV LANGHOLT AMBA</t>
+          <t>SURTECO GMBH</t>
         </is>
       </c>
       <c r="Q327" t="inlineStr">
@@ -27778,7 +27778,7 @@
       </c>
       <c r="G328" t="inlineStr">
         <is>
-          <t>001</t>
+          <t>003</t>
         </is>
       </c>
       <c r="H328" t="inlineStr">
@@ -27835,12 +27835,12 @@
     <row r="329">
       <c r="A329" t="inlineStr">
         <is>
-          <t>2566051</t>
+          <t>2566100</t>
         </is>
       </c>
       <c r="B329" t="inlineStr">
         <is>
-          <t>EF4-0232281-4</t>
+          <t>EF4-0232282-2</t>
         </is>
       </c>
       <c r="C329" t="inlineStr">
@@ -27848,11 +27848,7 @@
           <t>Vessel, Container</t>
         </is>
       </c>
-      <c r="D329" t="inlineStr">
-        <is>
-          <t>V0710349973</t>
-        </is>
-      </c>
+      <c r="D329" t="inlineStr"/>
       <c r="E329" t="inlineStr">
         <is>
           <t>9903.03.01</t>
@@ -27865,7 +27861,7 @@
       </c>
       <c r="G329" t="inlineStr">
         <is>
-          <t>002</t>
+          <t>001</t>
         </is>
       </c>
       <c r="H329" t="inlineStr">
@@ -27922,12 +27918,12 @@
     <row r="330">
       <c r="A330" t="inlineStr">
         <is>
-          <t>2566051</t>
+          <t>2566100</t>
         </is>
       </c>
       <c r="B330" t="inlineStr">
         <is>
-          <t>EF4-0232281-4</t>
+          <t>EF4-0232282-2</t>
         </is>
       </c>
       <c r="C330" t="inlineStr">
@@ -27935,11 +27931,7 @@
           <t>Vessel, Container</t>
         </is>
       </c>
-      <c r="D330" t="inlineStr">
-        <is>
-          <t>V0710349973</t>
-        </is>
-      </c>
+      <c r="D330" t="inlineStr"/>
       <c r="E330" t="inlineStr">
         <is>
           <t>9903.03.01</t>
@@ -27952,7 +27944,7 @@
       </c>
       <c r="G330" t="inlineStr">
         <is>
-          <t>003</t>
+          <t>002</t>
         </is>
       </c>
       <c r="H330" t="inlineStr">
@@ -28035,7 +28027,7 @@
       </c>
       <c r="G331" t="inlineStr">
         <is>
-          <t>001</t>
+          <t>003</t>
         </is>
       </c>
       <c r="H331" t="inlineStr">
@@ -28092,17 +28084,17 @@
     <row r="332">
       <c r="A332" t="inlineStr">
         <is>
-          <t>2566100</t>
+          <t>2615771</t>
         </is>
       </c>
       <c r="B332" t="inlineStr">
         <is>
-          <t>EF4-0232282-2</t>
+          <t>EF4-0232406-7</t>
         </is>
       </c>
       <c r="C332" t="inlineStr">
         <is>
-          <t>Vessel, Container</t>
+          <t>Vessel, Non-container</t>
         </is>
       </c>
       <c r="D332" t="inlineStr"/>
@@ -28118,7 +28110,7 @@
       </c>
       <c r="G332" t="inlineStr">
         <is>
-          <t>002</t>
+          <t>001</t>
         </is>
       </c>
       <c r="H332" t="inlineStr">
@@ -28128,27 +28120,27 @@
       </c>
       <c r="I332" t="inlineStr">
         <is>
-          <t>4811.59.4040</t>
+          <t>8210.00.0000</t>
         </is>
       </c>
       <c r="J332" t="inlineStr">
         <is>
-          <t>BAUSCHLINNEMANN NORTH AMERICA</t>
+          <t>COVE HOME LLC</t>
         </is>
       </c>
       <c r="K332" t="inlineStr">
         <is>
-          <t>BAULIN</t>
+          <t>COVHOM01</t>
         </is>
       </c>
       <c r="L332" t="inlineStr">
         <is>
-          <t>56-193913400</t>
+          <t>30-136116600</t>
         </is>
       </c>
       <c r="M332" t="inlineStr">
         <is>
-          <t>2026-06-21 00:00:00</t>
+          <t>2026-06-20 00:00:00</t>
         </is>
       </c>
       <c r="N332" t="inlineStr">
@@ -28158,34 +28150,34 @@
       </c>
       <c r="O332" t="inlineStr">
         <is>
-          <t>SURTECO GMBH</t>
+          <t>P. IONNOU G ZARKADIS QE</t>
         </is>
       </c>
       <c r="P332" t="inlineStr">
         <is>
-          <t>SURTECO GMBH</t>
+          <t>P. IONNOU G ZARKADIS QE</t>
         </is>
       </c>
       <c r="Q332" t="inlineStr">
         <is>
-          <t>2026-06-01 00:00:00</t>
+          <t>2026-06-06 00:00:00</t>
         </is>
       </c>
     </row>
     <row r="333">
       <c r="A333" t="inlineStr">
         <is>
-          <t>2566100</t>
+          <t>2615771</t>
         </is>
       </c>
       <c r="B333" t="inlineStr">
         <is>
-          <t>EF4-0232282-2</t>
+          <t>EF4-0232406-7</t>
         </is>
       </c>
       <c r="C333" t="inlineStr">
         <is>
-          <t>Vessel, Container</t>
+          <t>Vessel, Non-container</t>
         </is>
       </c>
       <c r="D333" t="inlineStr"/>
@@ -28201,7 +28193,7 @@
       </c>
       <c r="G333" t="inlineStr">
         <is>
-          <t>003</t>
+          <t>002</t>
         </is>
       </c>
       <c r="H333" t="inlineStr">
@@ -28211,27 +28203,27 @@
       </c>
       <c r="I333" t="inlineStr">
         <is>
-          <t>4811.59.4040</t>
+          <t>8210.00.0000</t>
         </is>
       </c>
       <c r="J333" t="inlineStr">
         <is>
-          <t>BAUSCHLINNEMANN NORTH AMERICA</t>
+          <t>COVE HOME LLC</t>
         </is>
       </c>
       <c r="K333" t="inlineStr">
         <is>
-          <t>BAULIN</t>
+          <t>COVHOM01</t>
         </is>
       </c>
       <c r="L333" t="inlineStr">
         <is>
-          <t>56-193913400</t>
+          <t>30-136116600</t>
         </is>
       </c>
       <c r="M333" t="inlineStr">
         <is>
-          <t>2026-06-21 00:00:00</t>
+          <t>2026-06-20 00:00:00</t>
         </is>
       </c>
       <c r="N333" t="inlineStr">
@@ -28241,34 +28233,34 @@
       </c>
       <c r="O333" t="inlineStr">
         <is>
-          <t>SURTECO GMBH</t>
+          <t>P. IONNOU G ZARKADIS QE</t>
         </is>
       </c>
       <c r="P333" t="inlineStr">
         <is>
-          <t>SURTECO GMBH</t>
+          <t>P. IONNOU G ZARKADIS QE</t>
         </is>
       </c>
       <c r="Q333" t="inlineStr">
         <is>
-          <t>2026-06-01 00:00:00</t>
+          <t>2026-06-06 00:00:00</t>
         </is>
       </c>
     </row>
     <row r="334">
       <c r="A334" t="inlineStr">
         <is>
-          <t>2615771</t>
+          <t>2565847</t>
         </is>
       </c>
       <c r="B334" t="inlineStr">
         <is>
-          <t>EF4-0232406-7</t>
+          <t>EF4-0231725-1</t>
         </is>
       </c>
       <c r="C334" t="inlineStr">
         <is>
-          <t>Vessel, Non-container</t>
+          <t>Vessel, Container</t>
         </is>
       </c>
       <c r="D334" t="inlineStr"/>
@@ -28294,64 +28286,64 @@
       </c>
       <c r="I334" t="inlineStr">
         <is>
-          <t>8210.00.0000</t>
+          <t>5407.20.0000</t>
         </is>
       </c>
       <c r="J334" t="inlineStr">
         <is>
-          <t>COVE HOME LLC</t>
+          <t>VEER CORPORATIONS INC</t>
         </is>
       </c>
       <c r="K334" t="inlineStr">
         <is>
-          <t>COVHOM01</t>
+          <t>VEECOR01</t>
         </is>
       </c>
       <c r="L334" t="inlineStr">
         <is>
-          <t>30-136116600</t>
+          <t>99-106989200</t>
         </is>
       </c>
       <c r="M334" t="inlineStr">
         <is>
-          <t>2026-06-20 00:00:00</t>
+          <t>2026-06-19 00:00:00</t>
         </is>
       </c>
       <c r="N334" t="inlineStr">
         <is>
-          <t>2026-06-20 00:00:00</t>
+          <t>2026-06-21 00:00:00</t>
         </is>
       </c>
       <c r="O334" t="inlineStr">
         <is>
-          <t>P. IONNOU G ZARKADIS QE</t>
+          <t>VEER PLASTIC PVT LTD</t>
         </is>
       </c>
       <c r="P334" t="inlineStr">
         <is>
-          <t>P. IONNOU G ZARKADIS QE</t>
+          <t>VEER PLASTIC PVT LTD</t>
         </is>
       </c>
       <c r="Q334" t="inlineStr">
         <is>
-          <t>2026-06-06 00:00:00</t>
+          <t>2026-05-06 00:00:00</t>
         </is>
       </c>
     </row>
     <row r="335">
       <c r="A335" t="inlineStr">
         <is>
-          <t>2615771</t>
+          <t>2565848</t>
         </is>
       </c>
       <c r="B335" t="inlineStr">
         <is>
-          <t>EF4-0232406-7</t>
+          <t>EF4-0231726-9</t>
         </is>
       </c>
       <c r="C335" t="inlineStr">
         <is>
-          <t>Vessel, Non-container</t>
+          <t>Vessel, Container</t>
         </is>
       </c>
       <c r="D335" t="inlineStr"/>
@@ -28367,7 +28359,7 @@
       </c>
       <c r="G335" t="inlineStr">
         <is>
-          <t>002</t>
+          <t>001</t>
         </is>
       </c>
       <c r="H335" t="inlineStr">
@@ -28377,59 +28369,59 @@
       </c>
       <c r="I335" t="inlineStr">
         <is>
-          <t>8210.00.0000</t>
+          <t>5603.14.9090</t>
         </is>
       </c>
       <c r="J335" t="inlineStr">
         <is>
-          <t>COVE HOME LLC</t>
+          <t>VEER CORPORATIONS INC</t>
         </is>
       </c>
       <c r="K335" t="inlineStr">
         <is>
-          <t>COVHOM01</t>
+          <t>VEECOR01</t>
         </is>
       </c>
       <c r="L335" t="inlineStr">
         <is>
-          <t>30-136116600</t>
+          <t>99-106989200</t>
         </is>
       </c>
       <c r="M335" t="inlineStr">
         <is>
-          <t>2026-06-20 00:00:00</t>
+          <t>2026-06-19 00:00:00</t>
         </is>
       </c>
       <c r="N335" t="inlineStr">
         <is>
-          <t>2026-06-20 00:00:00</t>
+          <t>2026-06-21 00:00:00</t>
         </is>
       </c>
       <c r="O335" t="inlineStr">
         <is>
-          <t>P. IONNOU G ZARKADIS QE</t>
+          <t>VEER PLASTIC PVT LTD</t>
         </is>
       </c>
       <c r="P335" t="inlineStr">
         <is>
-          <t>P. IONNOU G ZARKADIS QE</t>
+          <t>VEER PLASTIC PVT LTD</t>
         </is>
       </c>
       <c r="Q335" t="inlineStr">
         <is>
-          <t>2026-06-06 00:00:00</t>
+          <t>2026-05-11 00:00:00</t>
         </is>
       </c>
     </row>
     <row r="336">
       <c r="A336" t="inlineStr">
         <is>
-          <t>2565847</t>
+          <t>2565849</t>
         </is>
       </c>
       <c r="B336" t="inlineStr">
         <is>
-          <t>EF4-0231725-1</t>
+          <t>EF4-0231727-7</t>
         </is>
       </c>
       <c r="C336" t="inlineStr">
@@ -28500,19 +28492,19 @@
       </c>
       <c r="Q336" t="inlineStr">
         <is>
-          <t>2026-05-06 00:00:00</t>
+          <t>2026-05-11 00:00:00</t>
         </is>
       </c>
     </row>
     <row r="337">
       <c r="A337" t="inlineStr">
         <is>
-          <t>2565848</t>
+          <t>2565891</t>
         </is>
       </c>
       <c r="B337" t="inlineStr">
         <is>
-          <t>EF4-0231726-9</t>
+          <t>EF4-0231922-4</t>
         </is>
       </c>
       <c r="C337" t="inlineStr">
@@ -28543,27 +28535,27 @@
       </c>
       <c r="I337" t="inlineStr">
         <is>
-          <t>5603.14.9090</t>
+          <t>1109.00.9020</t>
         </is>
       </c>
       <c r="J337" t="inlineStr">
         <is>
-          <t>VEER CORPORATIONS INC</t>
+          <t>ROYAL INGREDIENTS GROUP BV</t>
         </is>
       </c>
       <c r="K337" t="inlineStr">
         <is>
-          <t>VEECOR01</t>
+          <t>ROYINGRE</t>
         </is>
       </c>
       <c r="L337" t="inlineStr">
         <is>
-          <t>99-106989200</t>
+          <t>074601-00962</t>
         </is>
       </c>
       <c r="M337" t="inlineStr">
         <is>
-          <t>2026-06-19 00:00:00</t>
+          <t>2026-06-20 00:00:00</t>
         </is>
       </c>
       <c r="N337" t="inlineStr">
@@ -28573,29 +28565,29 @@
       </c>
       <c r="O337" t="inlineStr">
         <is>
-          <t>VEER PLASTIC PVT LTD</t>
+          <t>SEDAMYL UK</t>
         </is>
       </c>
       <c r="P337" t="inlineStr">
         <is>
-          <t>VEER PLASTIC PVT LTD</t>
+          <t>SEDAMYL UK</t>
         </is>
       </c>
       <c r="Q337" t="inlineStr">
         <is>
-          <t>2026-05-11 00:00:00</t>
+          <t>2026-05-16 00:00:00</t>
         </is>
       </c>
     </row>
     <row r="338">
       <c r="A338" t="inlineStr">
         <is>
-          <t>2565849</t>
+          <t>2565934</t>
         </is>
       </c>
       <c r="B338" t="inlineStr">
         <is>
-          <t>EF4-0231727-7</t>
+          <t>EF4-0231991-9</t>
         </is>
       </c>
       <c r="C338" t="inlineStr">
@@ -28603,7 +28595,11 @@
           <t>Vessel, Container</t>
         </is>
       </c>
-      <c r="D338" t="inlineStr"/>
+      <c r="D338" t="inlineStr">
+        <is>
+          <t>V0710339289</t>
+        </is>
+      </c>
       <c r="E338" t="inlineStr">
         <is>
           <t>9903.03.01</t>
@@ -28626,27 +28622,27 @@
       </c>
       <c r="I338" t="inlineStr">
         <is>
-          <t>5407.20.0000</t>
+          <t>1108.13.0010</t>
         </is>
       </c>
       <c r="J338" t="inlineStr">
         <is>
-          <t>VEER CORPORATIONS INC</t>
+          <t>ROYAL INGREDIENTS GROUP BV</t>
         </is>
       </c>
       <c r="K338" t="inlineStr">
         <is>
-          <t>VEECOR01</t>
+          <t>ROYINGRE</t>
         </is>
       </c>
       <c r="L338" t="inlineStr">
         <is>
-          <t>99-106989200</t>
+          <t>074601-00962</t>
         </is>
       </c>
       <c r="M338" t="inlineStr">
         <is>
-          <t>2026-06-19 00:00:00</t>
+          <t>2026-06-07 00:00:00</t>
         </is>
       </c>
       <c r="N338" t="inlineStr">
@@ -28656,29 +28652,29 @@
       </c>
       <c r="O338" t="inlineStr">
         <is>
-          <t>VEER PLASTIC PVT LTD</t>
+          <t>AKV LANGHOLT AMBA</t>
         </is>
       </c>
       <c r="P338" t="inlineStr">
         <is>
-          <t>VEER PLASTIC PVT LTD</t>
+          <t>AKV LANGHOLT AMBA</t>
         </is>
       </c>
       <c r="Q338" t="inlineStr">
         <is>
-          <t>2026-05-11 00:00:00</t>
+          <t>2026-05-18 00:00:00</t>
         </is>
       </c>
     </row>
     <row r="339">
       <c r="A339" t="inlineStr">
         <is>
-          <t>2565891</t>
+          <t>2566075</t>
         </is>
       </c>
       <c r="B339" t="inlineStr">
         <is>
-          <t>EF4-0231922-4</t>
+          <t>EF4-0232185-7</t>
         </is>
       </c>
       <c r="C339" t="inlineStr">
@@ -28686,7 +28682,11 @@
           <t>Vessel, Container</t>
         </is>
       </c>
-      <c r="D339" t="inlineStr"/>
+      <c r="D339" t="inlineStr">
+        <is>
+          <t>V0710339289</t>
+        </is>
+      </c>
       <c r="E339" t="inlineStr">
         <is>
           <t>9903.03.01</t>
@@ -28709,27 +28709,27 @@
       </c>
       <c r="I339" t="inlineStr">
         <is>
-          <t>1109.00.9020</t>
+          <t>9903.82.01,8431.20.0000</t>
         </is>
       </c>
       <c r="J339" t="inlineStr">
         <is>
-          <t>ROYAL INGREDIENTS GROUP BV</t>
+          <t>MALLAGHAN (GA) INC.</t>
         </is>
       </c>
       <c r="K339" t="inlineStr">
         <is>
-          <t>ROYINGRE</t>
+          <t>MALGA01</t>
         </is>
       </c>
       <c r="L339" t="inlineStr">
         <is>
-          <t>074601-00962</t>
+          <t>36-488102800</t>
         </is>
       </c>
       <c r="M339" t="inlineStr">
         <is>
-          <t>2026-06-20 00:00:00</t>
+          <t>2026-06-22 00:00:00</t>
         </is>
       </c>
       <c r="N339" t="inlineStr">
@@ -28739,29 +28739,29 @@
       </c>
       <c r="O339" t="inlineStr">
         <is>
-          <t>SEDAMYL UK</t>
+          <t>MALLAGHAN ENGINEERING  LTD</t>
         </is>
       </c>
       <c r="P339" t="inlineStr">
         <is>
-          <t>SEDAMYL UK</t>
+          <t>MALLAGHAN ENGINEERING  LTD</t>
         </is>
       </c>
       <c r="Q339" t="inlineStr">
         <is>
-          <t>2026-05-16 00:00:00</t>
+          <t>2026-05-28 00:00:00</t>
         </is>
       </c>
     </row>
     <row r="340">
       <c r="A340" t="inlineStr">
         <is>
-          <t>2565934</t>
+          <t>2566102</t>
         </is>
       </c>
       <c r="B340" t="inlineStr">
         <is>
-          <t>EF4-0231991-9</t>
+          <t>EF4-0232187-3</t>
         </is>
       </c>
       <c r="C340" t="inlineStr">
@@ -28769,19 +28769,15 @@
           <t>Vessel, Container</t>
         </is>
       </c>
-      <c r="D340" t="inlineStr">
-        <is>
-          <t>V0710339289</t>
-        </is>
-      </c>
+      <c r="D340" t="inlineStr"/>
       <c r="E340" t="inlineStr">
         <is>
-          <t>9903.03.01</t>
+          <t>9903.03.06</t>
         </is>
       </c>
       <c r="F340" t="inlineStr">
         <is>
-          <t>SECTION 122 - 10% DUTY</t>
+          <t>S122 EXCL,IRN/STL/ALUM,DERIV</t>
         </is>
       </c>
       <c r="G340" t="inlineStr">
@@ -28791,32 +28787,32 @@
       </c>
       <c r="H340" t="inlineStr">
         <is>
-          <t>9903.03.01</t>
+          <t>9903.03.06</t>
         </is>
       </c>
       <c r="I340" t="inlineStr">
         <is>
-          <t>1108.13.0010</t>
+          <t>9903.82.22,8431.20.0000</t>
         </is>
       </c>
       <c r="J340" t="inlineStr">
         <is>
-          <t>ROYAL INGREDIENTS GROUP BV</t>
+          <t>MALLAGHAN (GA) INC.</t>
         </is>
       </c>
       <c r="K340" t="inlineStr">
         <is>
-          <t>ROYINGRE</t>
+          <t>MALGA01</t>
         </is>
       </c>
       <c r="L340" t="inlineStr">
         <is>
-          <t>074601-00962</t>
+          <t>36-488102800</t>
         </is>
       </c>
       <c r="M340" t="inlineStr">
         <is>
-          <t>2026-06-07 00:00:00</t>
+          <t>2026-06-22 00:00:00</t>
         </is>
       </c>
       <c r="N340" t="inlineStr">
@@ -28826,29 +28822,29 @@
       </c>
       <c r="O340" t="inlineStr">
         <is>
-          <t>AKV LANGHOLT AMBA</t>
+          <t>MALLAGHAN ENGINEERING  LTD</t>
         </is>
       </c>
       <c r="P340" t="inlineStr">
         <is>
-          <t>AKV LANGHOLT AMBA</t>
+          <t>MALLAGHAN ENGINEERING  LTD</t>
         </is>
       </c>
       <c r="Q340" t="inlineStr">
         <is>
-          <t>2026-05-18 00:00:00</t>
+          <t>2026-05-28 00:00:00</t>
         </is>
       </c>
     </row>
     <row r="341">
       <c r="A341" t="inlineStr">
         <is>
-          <t>2566075</t>
+          <t>2565923</t>
         </is>
       </c>
       <c r="B341" t="inlineStr">
         <is>
-          <t>EF4-0232185-7</t>
+          <t>EF4-0232195-6</t>
         </is>
       </c>
       <c r="C341" t="inlineStr">
@@ -28856,19 +28852,15 @@
           <t>Vessel, Container</t>
         </is>
       </c>
-      <c r="D341" t="inlineStr">
-        <is>
-          <t>V0710339289</t>
-        </is>
-      </c>
+      <c r="D341" t="inlineStr"/>
       <c r="E341" t="inlineStr">
         <is>
-          <t>9903.03.01</t>
+          <t>9903.91.01</t>
         </is>
       </c>
       <c r="F341" t="inlineStr">
         <is>
-          <t>SECTION 122 - 10% DUTY</t>
+          <t>ARTS, PRDS OF CN SUB(B)US NT31</t>
         </is>
       </c>
       <c r="G341" t="inlineStr">
@@ -28878,32 +28870,32 @@
       </c>
       <c r="H341" t="inlineStr">
         <is>
-          <t>9903.03.01</t>
+          <t>9903.91.01</t>
         </is>
       </c>
       <c r="I341" t="inlineStr">
         <is>
-          <t>9903.82.01,8431.20.0000</t>
+          <t>9903.03.06,9903.82.02,7228.30.6000</t>
         </is>
       </c>
       <c r="J341" t="inlineStr">
         <is>
-          <t>MALLAGHAN (GA) INC.</t>
+          <t>MAHA USA LLC</t>
         </is>
       </c>
       <c r="K341" t="inlineStr">
         <is>
-          <t>MALGA01</t>
+          <t>MAHUSA</t>
         </is>
       </c>
       <c r="L341" t="inlineStr">
         <is>
-          <t>36-488102800</t>
+          <t>52-213556300</t>
         </is>
       </c>
       <c r="M341" t="inlineStr">
         <is>
-          <t>2026-06-22 00:00:00</t>
+          <t>2026-06-20 00:00:00</t>
         </is>
       </c>
       <c r="N341" t="inlineStr">
@@ -28913,29 +28905,29 @@
       </c>
       <c r="O341" t="inlineStr">
         <is>
-          <t>MALLAGHAN ENGINEERING  LTD</t>
+          <t>THYSSENKRUPP SCHULTE GMBH</t>
         </is>
       </c>
       <c r="P341" t="inlineStr">
         <is>
-          <t>MALLAGHAN ENGINEERING  LTD</t>
+          <t>THYSSENKRUPP SCHULTE GMBH</t>
         </is>
       </c>
       <c r="Q341" t="inlineStr">
         <is>
-          <t>2026-05-28 00:00:00</t>
+          <t>2026-05-27 00:00:00</t>
         </is>
       </c>
     </row>
     <row r="342">
       <c r="A342" t="inlineStr">
         <is>
-          <t>2566102</t>
+          <t>2565923</t>
         </is>
       </c>
       <c r="B342" t="inlineStr">
         <is>
-          <t>EF4-0232187-3</t>
+          <t>EF4-0232195-6</t>
         </is>
       </c>
       <c r="C342" t="inlineStr">
@@ -28956,7 +28948,7 @@
       </c>
       <c r="G342" t="inlineStr">
         <is>
-          <t>001</t>
+          <t>002</t>
         </is>
       </c>
       <c r="H342" t="inlineStr">
@@ -28966,27 +28958,27 @@
       </c>
       <c r="I342" t="inlineStr">
         <is>
-          <t>9903.82.22,8431.20.0000</t>
+          <t>9903.82.02,7215.50.0016</t>
         </is>
       </c>
       <c r="J342" t="inlineStr">
         <is>
-          <t>MALLAGHAN (GA) INC.</t>
+          <t>MAHA USA LLC</t>
         </is>
       </c>
       <c r="K342" t="inlineStr">
         <is>
-          <t>MALGA01</t>
+          <t>MAHUSA</t>
         </is>
       </c>
       <c r="L342" t="inlineStr">
         <is>
-          <t>36-488102800</t>
+          <t>52-213556300</t>
         </is>
       </c>
       <c r="M342" t="inlineStr">
         <is>
-          <t>2026-06-22 00:00:00</t>
+          <t>2026-06-20 00:00:00</t>
         </is>
       </c>
       <c r="N342" t="inlineStr">
@@ -28996,17 +28988,17 @@
       </c>
       <c r="O342" t="inlineStr">
         <is>
-          <t>MALLAGHAN ENGINEERING  LTD</t>
+          <t>THYSSENKRUPP SCHULTE GMBH</t>
         </is>
       </c>
       <c r="P342" t="inlineStr">
         <is>
-          <t>MALLAGHAN ENGINEERING  LTD</t>
+          <t>THYSSENKRUPP SCHULTE GMBH</t>
         </is>
       </c>
       <c r="Q342" t="inlineStr">
         <is>
-          <t>2026-05-28 00:00:00</t>
+          <t>2026-05-27 00:00:00</t>
         </is>
       </c>
     </row>
@@ -29029,27 +29021,27 @@
       <c r="D343" t="inlineStr"/>
       <c r="E343" t="inlineStr">
         <is>
-          <t>9903.91.01</t>
+          <t>9903.03.06</t>
         </is>
       </c>
       <c r="F343" t="inlineStr">
         <is>
-          <t>ARTS, PRDS OF CN SUB(B)US NT31</t>
+          <t>S122 EXCL,IRN/STL/ALUM,DERIV</t>
         </is>
       </c>
       <c r="G343" t="inlineStr">
         <is>
-          <t>001</t>
+          <t>003</t>
         </is>
       </c>
       <c r="H343" t="inlineStr">
         <is>
-          <t>9903.91.01</t>
+          <t>9903.03.06</t>
         </is>
       </c>
       <c r="I343" t="inlineStr">
         <is>
-          <t>9903.03.06,9903.82.02,7228.30.6000</t>
+          <t>9903.82.02,7216.33.0090</t>
         </is>
       </c>
       <c r="J343" t="inlineStr">
@@ -29096,12 +29088,12 @@
     <row r="344">
       <c r="A344" t="inlineStr">
         <is>
-          <t>2565923</t>
+          <t>2566146</t>
         </is>
       </c>
       <c r="B344" t="inlineStr">
         <is>
-          <t>EF4-0232195-6</t>
+          <t>EF4-0232246-7</t>
         </is>
       </c>
       <c r="C344" t="inlineStr">
@@ -29112,47 +29104,47 @@
       <c r="D344" t="inlineStr"/>
       <c r="E344" t="inlineStr">
         <is>
-          <t>9903.03.06</t>
+          <t>9903.03.01</t>
         </is>
       </c>
       <c r="F344" t="inlineStr">
         <is>
-          <t>S122 EXCL,IRN/STL/ALUM,DERIV</t>
+          <t>SECTION 122 - 10% DUTY</t>
         </is>
       </c>
       <c r="G344" t="inlineStr">
         <is>
-          <t>002</t>
+          <t>001</t>
         </is>
       </c>
       <c r="H344" t="inlineStr">
         <is>
-          <t>9903.03.06</t>
+          <t>9903.03.01</t>
         </is>
       </c>
       <c r="I344" t="inlineStr">
         <is>
-          <t>9903.82.02,7215.50.0016</t>
+          <t>1109.00.9010</t>
         </is>
       </c>
       <c r="J344" t="inlineStr">
         <is>
-          <t>MAHA USA LLC</t>
+          <t>ROYAL INGREDIENTS GROUP BV</t>
         </is>
       </c>
       <c r="K344" t="inlineStr">
         <is>
-          <t>MAHUSA</t>
+          <t>ROYINGRE</t>
         </is>
       </c>
       <c r="L344" t="inlineStr">
         <is>
-          <t>52-213556300</t>
+          <t>074601-00962</t>
         </is>
       </c>
       <c r="M344" t="inlineStr">
         <is>
-          <t>2026-06-20 00:00:00</t>
+          <t>2026-06-22 00:00:00</t>
         </is>
       </c>
       <c r="N344" t="inlineStr">
@@ -29162,29 +29154,29 @@
       </c>
       <c r="O344" t="inlineStr">
         <is>
-          <t>THYSSENKRUPP SCHULTE GMBH</t>
+          <t>KROENER-STARKE BIO GMBH</t>
         </is>
       </c>
       <c r="P344" t="inlineStr">
         <is>
-          <t>THYSSENKRUPP SCHULTE GMBH</t>
+          <t>KROENER-STARKE BIO GMBH</t>
         </is>
       </c>
       <c r="Q344" t="inlineStr">
         <is>
-          <t>2026-05-27 00:00:00</t>
+          <t>2026-06-01 00:00:00</t>
         </is>
       </c>
     </row>
     <row r="345">
       <c r="A345" t="inlineStr">
         <is>
-          <t>2565923</t>
+          <t>2566173</t>
         </is>
       </c>
       <c r="B345" t="inlineStr">
         <is>
-          <t>EF4-0232195-6</t>
+          <t>EF4-0232274-9</t>
         </is>
       </c>
       <c r="C345" t="inlineStr">
@@ -29195,47 +29187,47 @@
       <c r="D345" t="inlineStr"/>
       <c r="E345" t="inlineStr">
         <is>
-          <t>9903.03.06</t>
+          <t>9903.03.01</t>
         </is>
       </c>
       <c r="F345" t="inlineStr">
         <is>
-          <t>S122 EXCL,IRN/STL/ALUM,DERIV</t>
+          <t>SECTION 122 - 10% DUTY</t>
         </is>
       </c>
       <c r="G345" t="inlineStr">
         <is>
-          <t>003</t>
+          <t>001</t>
         </is>
       </c>
       <c r="H345" t="inlineStr">
         <is>
-          <t>9903.03.06</t>
+          <t>9903.03.01</t>
         </is>
       </c>
       <c r="I345" t="inlineStr">
         <is>
-          <t>9903.82.02,7216.33.0090</t>
+          <t>1109.00.9020</t>
         </is>
       </c>
       <c r="J345" t="inlineStr">
         <is>
-          <t>MAHA USA LLC</t>
+          <t>ROYAL INGREDIENTS GROUP BV</t>
         </is>
       </c>
       <c r="K345" t="inlineStr">
         <is>
-          <t>MAHUSA</t>
+          <t>ROYINGRE</t>
         </is>
       </c>
       <c r="L345" t="inlineStr">
         <is>
-          <t>52-213556300</t>
+          <t>074601-00962</t>
         </is>
       </c>
       <c r="M345" t="inlineStr">
         <is>
-          <t>2026-06-20 00:00:00</t>
+          <t>2026-06-21 00:00:00</t>
         </is>
       </c>
       <c r="N345" t="inlineStr">
@@ -29245,29 +29237,29 @@
       </c>
       <c r="O345" t="inlineStr">
         <is>
-          <t>THYSSENKRUPP SCHULTE GMBH</t>
+          <t>JACKERING MUHLEN UND NAHRMITTELWERK</t>
         </is>
       </c>
       <c r="P345" t="inlineStr">
         <is>
-          <t>THYSSENKRUPP SCHULTE GMBH</t>
+          <t>JACKERING MUHLEN UND NAHRMITTELWERKE GMBH</t>
         </is>
       </c>
       <c r="Q345" t="inlineStr">
         <is>
-          <t>2026-05-27 00:00:00</t>
+          <t>2026-06-01 00:00:00</t>
         </is>
       </c>
     </row>
     <row r="346">
       <c r="A346" t="inlineStr">
         <is>
-          <t>2566146</t>
+          <t>2565864</t>
         </is>
       </c>
       <c r="B346" t="inlineStr">
         <is>
-          <t>EF4-0232246-7</t>
+          <t>EF4-0232315-0</t>
         </is>
       </c>
       <c r="C346" t="inlineStr">
@@ -29298,7 +29290,7 @@
       </c>
       <c r="I346" t="inlineStr">
         <is>
-          <t>1109.00.9010</t>
+          <t>1109.00.9020</t>
         </is>
       </c>
       <c r="J346" t="inlineStr">
@@ -29318,7 +29310,7 @@
       </c>
       <c r="M346" t="inlineStr">
         <is>
-          <t>2026-06-22 00:00:00</t>
+          <t>2026-06-20 00:00:00</t>
         </is>
       </c>
       <c r="N346" t="inlineStr">
@@ -29328,29 +29320,29 @@
       </c>
       <c r="O346" t="inlineStr">
         <is>
-          <t>KROENER-STARKE BIO GMBH</t>
+          <t>ROQUETTE FRERES</t>
         </is>
       </c>
       <c r="P346" t="inlineStr">
         <is>
-          <t>KROENER-STARKE BIO GMBH</t>
+          <t>ROQUETTE FRERES</t>
         </is>
       </c>
       <c r="Q346" t="inlineStr">
         <is>
-          <t>2026-06-01 00:00:00</t>
+          <t>2026-05-14 00:00:00</t>
         </is>
       </c>
     </row>
     <row r="347">
       <c r="A347" t="inlineStr">
         <is>
-          <t>2566173</t>
+          <t>2566183</t>
         </is>
       </c>
       <c r="B347" t="inlineStr">
         <is>
-          <t>EF4-0232274-9</t>
+          <t>EF4-0232343-2</t>
         </is>
       </c>
       <c r="C347" t="inlineStr">
@@ -29381,22 +29373,22 @@
       </c>
       <c r="I347" t="inlineStr">
         <is>
-          <t>1109.00.9020</t>
+          <t>2106.90.9998</t>
         </is>
       </c>
       <c r="J347" t="inlineStr">
         <is>
-          <t>ROYAL INGREDIENTS GROUP BV</t>
+          <t>DOBLA USA MFG LLC</t>
         </is>
       </c>
       <c r="K347" t="inlineStr">
         <is>
-          <t>ROYINGRE</t>
+          <t>DOBUSA</t>
         </is>
       </c>
       <c r="L347" t="inlineStr">
         <is>
-          <t>074601-00962</t>
+          <t>41-218954800</t>
         </is>
       </c>
       <c r="M347" t="inlineStr">
@@ -29411,29 +29403,29 @@
       </c>
       <c r="O347" t="inlineStr">
         <is>
-          <t>JACKERING MUHLEN UND NAHRMITTELWERK</t>
+          <t>IRCA SRL</t>
         </is>
       </c>
       <c r="P347" t="inlineStr">
         <is>
-          <t>JACKERING MUHLEN UND NAHRMITTELWERKE GMBH</t>
+          <t>IRCA SRL</t>
         </is>
       </c>
       <c r="Q347" t="inlineStr">
         <is>
-          <t>2026-06-01 00:00:00</t>
+          <t>2026-06-04 00:00:00</t>
         </is>
       </c>
     </row>
     <row r="348">
       <c r="A348" t="inlineStr">
         <is>
-          <t>2565864</t>
+          <t>2566264</t>
         </is>
       </c>
       <c r="B348" t="inlineStr">
         <is>
-          <t>EF4-0232315-0</t>
+          <t>EF4-0232584-1</t>
         </is>
       </c>
       <c r="C348" t="inlineStr">
@@ -29464,27 +29456,27 @@
       </c>
       <c r="I348" t="inlineStr">
         <is>
-          <t>1109.00.9020</t>
+          <t>3815.90.5000</t>
         </is>
       </c>
       <c r="J348" t="inlineStr">
         <is>
-          <t>ROYAL INGREDIENTS GROUP BV</t>
+          <t>JOBACHEM CORPORATION</t>
         </is>
       </c>
       <c r="K348" t="inlineStr">
         <is>
-          <t>ROYINGRE</t>
+          <t>JOBLP01</t>
         </is>
       </c>
       <c r="L348" t="inlineStr">
         <is>
-          <t>074601-00962</t>
+          <t>32-052169200</t>
         </is>
       </c>
       <c r="M348" t="inlineStr">
         <is>
-          <t>2026-06-20 00:00:00</t>
+          <t>2026-06-22 00:00:00</t>
         </is>
       </c>
       <c r="N348" t="inlineStr">
@@ -29494,29 +29486,29 @@
       </c>
       <c r="O348" t="inlineStr">
         <is>
-          <t>ROQUETTE FRERES</t>
+          <t>JOBACHEM GMBH</t>
         </is>
       </c>
       <c r="P348" t="inlineStr">
         <is>
-          <t>ROQUETTE FRERES</t>
+          <t>JOBACHEM GMBH</t>
         </is>
       </c>
       <c r="Q348" t="inlineStr">
         <is>
-          <t>2026-05-14 00:00:00</t>
+          <t>2026-06-06 00:00:00</t>
         </is>
       </c>
     </row>
     <row r="349">
       <c r="A349" t="inlineStr">
         <is>
-          <t>2566183</t>
+          <t>2566264</t>
         </is>
       </c>
       <c r="B349" t="inlineStr">
         <is>
-          <t>EF4-0232343-2</t>
+          <t>EF4-0232584-1</t>
         </is>
       </c>
       <c r="C349" t="inlineStr">
@@ -29537,7 +29529,7 @@
       </c>
       <c r="G349" t="inlineStr">
         <is>
-          <t>001</t>
+          <t>002</t>
         </is>
       </c>
       <c r="H349" t="inlineStr">
@@ -29547,59 +29539,59 @@
       </c>
       <c r="I349" t="inlineStr">
         <is>
-          <t>2106.90.9998</t>
+          <t>2916.14.2050</t>
         </is>
       </c>
       <c r="J349" t="inlineStr">
         <is>
-          <t>DOBLA USA MFG LLC</t>
+          <t>JOBACHEM CORPORATION</t>
         </is>
       </c>
       <c r="K349" t="inlineStr">
         <is>
-          <t>DOBUSA</t>
+          <t>JOBLP01</t>
         </is>
       </c>
       <c r="L349" t="inlineStr">
         <is>
-          <t>41-218954800</t>
+          <t>32-052169200</t>
         </is>
       </c>
       <c r="M349" t="inlineStr">
         <is>
+          <t>2026-06-22 00:00:00</t>
+        </is>
+      </c>
+      <c r="N349" t="inlineStr">
+        <is>
           <t>2026-06-21 00:00:00</t>
         </is>
       </c>
-      <c r="N349" t="inlineStr">
-        <is>
-          <t>2026-06-21 00:00:00</t>
-        </is>
-      </c>
       <c r="O349" t="inlineStr">
         <is>
-          <t>IRCA SRL</t>
+          <t>JOBACHEM GMBH</t>
         </is>
       </c>
       <c r="P349" t="inlineStr">
         <is>
-          <t>IRCA SRL</t>
+          <t>JOBACHEM GMBH</t>
         </is>
       </c>
       <c r="Q349" t="inlineStr">
         <is>
-          <t>2026-06-04 00:00:00</t>
+          <t>2026-06-06 00:00:00</t>
         </is>
       </c>
     </row>
     <row r="350">
       <c r="A350" t="inlineStr">
         <is>
-          <t>2566264</t>
+          <t>2565444</t>
         </is>
       </c>
       <c r="B350" t="inlineStr">
         <is>
-          <t>EF4-0232584-1</t>
+          <t>EF4-0231090-0</t>
         </is>
       </c>
       <c r="C350" t="inlineStr">
@@ -29630,22 +29622,22 @@
       </c>
       <c r="I350" t="inlineStr">
         <is>
-          <t>3815.90.5000</t>
+          <t>5903.90.3090</t>
         </is>
       </c>
       <c r="J350" t="inlineStr">
         <is>
-          <t>JOBACHEM CORPORATION</t>
+          <t>VEER CORPORATIONS INC</t>
         </is>
       </c>
       <c r="K350" t="inlineStr">
         <is>
-          <t>JOBLP01</t>
+          <t>VEECOR01</t>
         </is>
       </c>
       <c r="L350" t="inlineStr">
         <is>
-          <t>32-052169200</t>
+          <t>99-106989200</t>
         </is>
       </c>
       <c r="M350" t="inlineStr">
@@ -29655,34 +29647,34 @@
       </c>
       <c r="N350" t="inlineStr">
         <is>
-          <t>2026-06-21 00:00:00</t>
+          <t>2026-06-22 00:00:00</t>
         </is>
       </c>
       <c r="O350" t="inlineStr">
         <is>
-          <t>JOBACHEM GMBH</t>
+          <t>VEER PLASTIC PVT LTD</t>
         </is>
       </c>
       <c r="P350" t="inlineStr">
         <is>
-          <t>JOBACHEM GMBH</t>
+          <t>VEER PLASTIC PVT LTD</t>
         </is>
       </c>
       <c r="Q350" t="inlineStr">
         <is>
-          <t>2026-06-06 00:00:00</t>
+          <t>2026-04-10 00:00:00</t>
         </is>
       </c>
     </row>
     <row r="351">
       <c r="A351" t="inlineStr">
         <is>
-          <t>2566264</t>
+          <t>2566049</t>
         </is>
       </c>
       <c r="B351" t="inlineStr">
         <is>
-          <t>EF4-0232584-1</t>
+          <t>EF4-0231964-6</t>
         </is>
       </c>
       <c r="C351" t="inlineStr">
@@ -29693,42 +29685,42 @@
       <c r="D351" t="inlineStr"/>
       <c r="E351" t="inlineStr">
         <is>
-          <t>9903.03.01</t>
+          <t>9903.88.15</t>
         </is>
       </c>
       <c r="F351" t="inlineStr">
         <is>
-          <t>SECTION 122 - 10% DUTY</t>
+          <t>ARTICLE OF CHINA,US NTE 20(R)</t>
         </is>
       </c>
       <c r="G351" t="inlineStr">
         <is>
-          <t>002</t>
+          <t>001</t>
         </is>
       </c>
       <c r="H351" t="inlineStr">
         <is>
-          <t>9903.03.01</t>
+          <t>9903.88.15</t>
         </is>
       </c>
       <c r="I351" t="inlineStr">
         <is>
-          <t>2916.14.2050</t>
+          <t>9903.03.01,3926.30.5000</t>
         </is>
       </c>
       <c r="J351" t="inlineStr">
         <is>
-          <t>JOBACHEM CORPORATION</t>
+          <t>BORGERS USA CORP</t>
         </is>
       </c>
       <c r="K351" t="inlineStr">
         <is>
-          <t>JOBLP01</t>
+          <t>BORUSA</t>
         </is>
       </c>
       <c r="L351" t="inlineStr">
         <is>
-          <t>32-052169200</t>
+          <t>65-117296500</t>
         </is>
       </c>
       <c r="M351" t="inlineStr">
@@ -29738,34 +29730,34 @@
       </c>
       <c r="N351" t="inlineStr">
         <is>
-          <t>2026-06-21 00:00:00</t>
+          <t>2026-06-22 00:00:00</t>
         </is>
       </c>
       <c r="O351" t="inlineStr">
         <is>
-          <t>JOBACHEM GMBH</t>
+          <t>AUTONEUM (SHANGHAI) MANAGEMENT CO.</t>
         </is>
       </c>
       <c r="P351" t="inlineStr">
         <is>
-          <t>JOBACHEM GMBH</t>
+          <t>AUTONEUM (SHANGHAI) MANAGEMENT CO. LTD.</t>
         </is>
       </c>
       <c r="Q351" t="inlineStr">
         <is>
-          <t>2026-06-06 00:00:00</t>
+          <t>2026-05-17 00:00:00</t>
         </is>
       </c>
     </row>
     <row r="352">
       <c r="A352" t="inlineStr">
         <is>
-          <t>2565444</t>
+          <t>2566049</t>
         </is>
       </c>
       <c r="B352" t="inlineStr">
         <is>
-          <t>EF4-0231090-0</t>
+          <t>EF4-0231964-6</t>
         </is>
       </c>
       <c r="C352" t="inlineStr">
@@ -29776,42 +29768,42 @@
       <c r="D352" t="inlineStr"/>
       <c r="E352" t="inlineStr">
         <is>
-          <t>9903.03.01</t>
+          <t>9903.88.15</t>
         </is>
       </c>
       <c r="F352" t="inlineStr">
         <is>
-          <t>SECTION 122 - 10% DUTY</t>
+          <t>ARTICLE OF CHINA,US NTE 20(R)</t>
         </is>
       </c>
       <c r="G352" t="inlineStr">
         <is>
-          <t>001</t>
+          <t>002</t>
         </is>
       </c>
       <c r="H352" t="inlineStr">
         <is>
-          <t>9903.03.01</t>
+          <t>9903.88.15</t>
         </is>
       </c>
       <c r="I352" t="inlineStr">
         <is>
-          <t>5903.90.3090</t>
+          <t>9903.03.01,3926.90.9989</t>
         </is>
       </c>
       <c r="J352" t="inlineStr">
         <is>
-          <t>VEER CORPORATIONS INC</t>
+          <t>BORGERS USA CORP</t>
         </is>
       </c>
       <c r="K352" t="inlineStr">
         <is>
-          <t>VEECOR01</t>
+          <t>BORUSA</t>
         </is>
       </c>
       <c r="L352" t="inlineStr">
         <is>
-          <t>99-106989200</t>
+          <t>65-117296500</t>
         </is>
       </c>
       <c r="M352" t="inlineStr">
@@ -29826,17 +29818,17 @@
       </c>
       <c r="O352" t="inlineStr">
         <is>
-          <t>VEER PLASTIC PVT LTD</t>
+          <t>AUTONEUM (SHANGHAI) MANAGEMENT CO.</t>
         </is>
       </c>
       <c r="P352" t="inlineStr">
         <is>
-          <t>VEER PLASTIC PVT LTD</t>
+          <t>AUTONEUM (SHANGHAI) MANAGEMENT CO. LTD.</t>
         </is>
       </c>
       <c r="Q352" t="inlineStr">
         <is>
-          <t>2026-04-10 00:00:00</t>
+          <t>2026-05-17 00:00:00</t>
         </is>
       </c>
     </row>
@@ -29859,27 +29851,27 @@
       <c r="D353" t="inlineStr"/>
       <c r="E353" t="inlineStr">
         <is>
-          <t>9903.88.15</t>
+          <t>9903.88.03</t>
         </is>
       </c>
       <c r="F353" t="inlineStr">
         <is>
-          <t>ARTICLE OF CHINA,US NTE 20(R)</t>
+          <t>ARTICLE OF CHINA,US NTE 20(F)</t>
         </is>
       </c>
       <c r="G353" t="inlineStr">
         <is>
-          <t>001</t>
+          <t>003</t>
         </is>
       </c>
       <c r="H353" t="inlineStr">
         <is>
-          <t>9903.88.15</t>
+          <t>9903.88.03</t>
         </is>
       </c>
       <c r="I353" t="inlineStr">
         <is>
-          <t>9903.03.01,3926.30.5000</t>
+          <t>9903.03.06,9903.74.11,9903.94.05,8708.29.5160</t>
         </is>
       </c>
       <c r="J353" t="inlineStr">
@@ -29952,7 +29944,7 @@
       </c>
       <c r="G354" t="inlineStr">
         <is>
-          <t>002</t>
+          <t>004</t>
         </is>
       </c>
       <c r="H354" t="inlineStr">
@@ -29962,7 +29954,7 @@
       </c>
       <c r="I354" t="inlineStr">
         <is>
-          <t>9903.03.01,3926.90.9989</t>
+          <t>9903.03.06,9903.74.11,9903.94.05,8302.10.3000</t>
         </is>
       </c>
       <c r="J354" t="inlineStr">
@@ -30009,12 +30001,12 @@
     <row r="355">
       <c r="A355" t="inlineStr">
         <is>
-          <t>2566049</t>
+          <t>2565952</t>
         </is>
       </c>
       <c r="B355" t="inlineStr">
         <is>
-          <t>EF4-0231964-6</t>
+          <t>EF4-0232005-7</t>
         </is>
       </c>
       <c r="C355" t="inlineStr">
@@ -30025,42 +30017,42 @@
       <c r="D355" t="inlineStr"/>
       <c r="E355" t="inlineStr">
         <is>
-          <t>9903.88.03</t>
+          <t>9903.03.03</t>
         </is>
       </c>
       <c r="F355" t="inlineStr">
         <is>
-          <t>ARTICLE OF CHINA,US NTE 20(F)</t>
+          <t>S122 -EXCLUSION-EXEMPTED PRDTS</t>
         </is>
       </c>
       <c r="G355" t="inlineStr">
         <is>
-          <t>003</t>
+          <t>001</t>
         </is>
       </c>
       <c r="H355" t="inlineStr">
         <is>
-          <t>9903.88.03</t>
+          <t>9903.03.03</t>
         </is>
       </c>
       <c r="I355" t="inlineStr">
         <is>
-          <t>9903.03.06,9903.74.11,9903.94.05,8708.29.5160</t>
+          <t>2930.90.9231</t>
         </is>
       </c>
       <c r="J355" t="inlineStr">
         <is>
-          <t>BORGERS USA CORP</t>
+          <t>CASTLE CHEMICALS LTD</t>
         </is>
       </c>
       <c r="K355" t="inlineStr">
         <is>
-          <t>BORUSA</t>
+          <t>CASCHE01</t>
         </is>
       </c>
       <c r="L355" t="inlineStr">
         <is>
-          <t>65-117296500</t>
+          <t>151704-07138</t>
         </is>
       </c>
       <c r="M355" t="inlineStr">
@@ -30075,29 +30067,29 @@
       </c>
       <c r="O355" t="inlineStr">
         <is>
-          <t>AUTONEUM (SHANGHAI) MANAGEMENT CO.</t>
+          <t>HUBEI JIANGHAN NEW MATERIALS CO</t>
         </is>
       </c>
       <c r="P355" t="inlineStr">
         <is>
-          <t>AUTONEUM (SHANGHAI) MANAGEMENT CO. LTD.</t>
+          <t>HUBEI JIANGHAN NEW MATERIALS CO</t>
         </is>
       </c>
       <c r="Q355" t="inlineStr">
         <is>
-          <t>2026-05-17 00:00:00</t>
+          <t>2026-05-19 00:00:00</t>
         </is>
       </c>
     </row>
     <row r="356">
       <c r="A356" t="inlineStr">
         <is>
-          <t>2566049</t>
+          <t>2565953</t>
         </is>
       </c>
       <c r="B356" t="inlineStr">
         <is>
-          <t>EF4-0231964-6</t>
+          <t>EF4-0232006-5</t>
         </is>
       </c>
       <c r="C356" t="inlineStr">
@@ -30108,42 +30100,42 @@
       <c r="D356" t="inlineStr"/>
       <c r="E356" t="inlineStr">
         <is>
-          <t>9903.88.15</t>
+          <t>9903.03.03</t>
         </is>
       </c>
       <c r="F356" t="inlineStr">
         <is>
-          <t>ARTICLE OF CHINA,US NTE 20(R)</t>
+          <t>S122 -EXCLUSION-EXEMPTED PRDTS</t>
         </is>
       </c>
       <c r="G356" t="inlineStr">
         <is>
-          <t>004</t>
+          <t>001</t>
         </is>
       </c>
       <c r="H356" t="inlineStr">
         <is>
-          <t>9903.88.15</t>
+          <t>9903.03.03</t>
         </is>
       </c>
       <c r="I356" t="inlineStr">
         <is>
-          <t>9903.03.06,9903.74.11,9903.94.05,8302.10.3000</t>
+          <t>2930.90.9231</t>
         </is>
       </c>
       <c r="J356" t="inlineStr">
         <is>
-          <t>BORGERS USA CORP</t>
+          <t>CASTLE CHEMICALS LTD</t>
         </is>
       </c>
       <c r="K356" t="inlineStr">
         <is>
-          <t>BORUSA</t>
+          <t>CASCHE01</t>
         </is>
       </c>
       <c r="L356" t="inlineStr">
         <is>
-          <t>65-117296500</t>
+          <t>151704-07138</t>
         </is>
       </c>
       <c r="M356" t="inlineStr">
@@ -30158,29 +30150,29 @@
       </c>
       <c r="O356" t="inlineStr">
         <is>
-          <t>AUTONEUM (SHANGHAI) MANAGEMENT CO.</t>
+          <t>HUBEI JIANGHAN NEW MATERIALS CO</t>
         </is>
       </c>
       <c r="P356" t="inlineStr">
         <is>
-          <t>AUTONEUM (SHANGHAI) MANAGEMENT CO. LTD.</t>
+          <t>HUBEI JIANGHAN NEW MATERIALS CO</t>
         </is>
       </c>
       <c r="Q356" t="inlineStr">
         <is>
-          <t>2026-05-17 00:00:00</t>
+          <t>2026-05-19 00:00:00</t>
         </is>
       </c>
     </row>
     <row r="357">
       <c r="A357" t="inlineStr">
         <is>
-          <t>2565952</t>
+          <t>2565954</t>
         </is>
       </c>
       <c r="B357" t="inlineStr">
         <is>
-          <t>EF4-0232005-7</t>
+          <t>EF4-0232007-3</t>
         </is>
       </c>
       <c r="C357" t="inlineStr">
@@ -30258,12 +30250,12 @@
     <row r="358">
       <c r="A358" t="inlineStr">
         <is>
-          <t>2565953</t>
+          <t>2565955</t>
         </is>
       </c>
       <c r="B358" t="inlineStr">
         <is>
-          <t>EF4-0232006-5</t>
+          <t>EF4-0232008-1</t>
         </is>
       </c>
       <c r="C358" t="inlineStr">
@@ -30341,12 +30333,12 @@
     <row r="359">
       <c r="A359" t="inlineStr">
         <is>
-          <t>2565954</t>
+          <t>2566243</t>
         </is>
       </c>
       <c r="B359" t="inlineStr">
         <is>
-          <t>EF4-0232007-3</t>
+          <t>EF4-0232301-0</t>
         </is>
       </c>
       <c r="C359" t="inlineStr">
@@ -30357,12 +30349,12 @@
       <c r="D359" t="inlineStr"/>
       <c r="E359" t="inlineStr">
         <is>
-          <t>9903.03.03</t>
+          <t>9903.03.01</t>
         </is>
       </c>
       <c r="F359" t="inlineStr">
         <is>
-          <t>S122 -EXCLUSION-EXEMPTED PRDTS</t>
+          <t>SECTION 122 - 10% DUTY</t>
         </is>
       </c>
       <c r="G359" t="inlineStr">
@@ -30372,27 +30364,27 @@
       </c>
       <c r="H359" t="inlineStr">
         <is>
-          <t>9903.03.03</t>
+          <t>9903.03.01</t>
         </is>
       </c>
       <c r="I359" t="inlineStr">
         <is>
-          <t>2930.90.9231</t>
+          <t>3920.20.0055</t>
         </is>
       </c>
       <c r="J359" t="inlineStr">
         <is>
-          <t>CASTLE CHEMICALS LTD</t>
+          <t>GULF ATLANTIC PACKAGING CORP</t>
         </is>
       </c>
       <c r="K359" t="inlineStr">
         <is>
-          <t>CASCHE01</t>
+          <t>GULATL</t>
         </is>
       </c>
       <c r="L359" t="inlineStr">
         <is>
-          <t>151704-07138</t>
+          <t>58-184378700</t>
         </is>
       </c>
       <c r="M359" t="inlineStr">
@@ -30407,29 +30399,29 @@
       </c>
       <c r="O359" t="inlineStr">
         <is>
-          <t>HUBEI JIANGHAN NEW MATERIALS CO</t>
+          <t>SEKISUI JUSHI BV</t>
         </is>
       </c>
       <c r="P359" t="inlineStr">
         <is>
-          <t>HUBEI JIANGHAN NEW MATERIALS CO</t>
+          <t>SEKISUI JUSHI BV</t>
         </is>
       </c>
       <c r="Q359" t="inlineStr">
         <is>
-          <t>2026-05-19 00:00:00</t>
+          <t>2026-05-30 00:00:00</t>
         </is>
       </c>
     </row>
     <row r="360">
       <c r="A360" t="inlineStr">
         <is>
-          <t>2565955</t>
+          <t>2566128</t>
         </is>
       </c>
       <c r="B360" t="inlineStr">
         <is>
-          <t>EF4-0232008-1</t>
+          <t>EF4-0232453-9</t>
         </is>
       </c>
       <c r="C360" t="inlineStr">
@@ -30437,17 +30429,17 @@
           <t>Vessel, Container</t>
         </is>
       </c>
-      <c r="D360" t="inlineStr"/>
+      <c r="D360" t="inlineStr">
+        <is>
+          <t>V1626463577</t>
+        </is>
+      </c>
       <c r="E360" t="inlineStr">
         <is>
-          <t>9903.03.03</t>
-        </is>
-      </c>
-      <c r="F360" t="inlineStr">
-        <is>
-          <t>S122 -EXCLUSION-EXEMPTED PRDTS</t>
-        </is>
-      </c>
+          <t>9903.03.01</t>
+        </is>
+      </c>
+      <c r="F360" t="inlineStr"/>
       <c r="G360" t="inlineStr">
         <is>
           <t>001</t>
@@ -30455,27 +30447,27 @@
       </c>
       <c r="H360" t="inlineStr">
         <is>
-          <t>9903.03.03</t>
+          <t>9903.03.01</t>
         </is>
       </c>
       <c r="I360" t="inlineStr">
         <is>
-          <t>2930.90.9231</t>
+          <t>1108.12.0010</t>
         </is>
       </c>
       <c r="J360" t="inlineStr">
         <is>
-          <t>CASTLE CHEMICALS LTD</t>
+          <t>ROYAL INGREDIENTS GROUP BV</t>
         </is>
       </c>
       <c r="K360" t="inlineStr">
         <is>
-          <t>CASCHE01</t>
+          <t>ROYINGRE</t>
         </is>
       </c>
       <c r="L360" t="inlineStr">
         <is>
-          <t>151704-07138</t>
+          <t>074601-00962</t>
         </is>
       </c>
       <c r="M360" t="inlineStr">
@@ -30490,37 +30482,41 @@
       </c>
       <c r="O360" t="inlineStr">
         <is>
-          <t>HUBEI JIANGHAN NEW MATERIALS CO</t>
+          <t>TAT NISASTA INS SAN TIC AS</t>
         </is>
       </c>
       <c r="P360" t="inlineStr">
         <is>
-          <t>HUBEI JIANGHAN NEW MATERIALS CO</t>
+          <t>TAT NISASTA INS SAN TIC AS</t>
         </is>
       </c>
       <c r="Q360" t="inlineStr">
         <is>
-          <t>2026-05-19 00:00:00</t>
+          <t>2026-05-30 00:00:00</t>
         </is>
       </c>
     </row>
     <row r="361">
       <c r="A361" t="inlineStr">
         <is>
-          <t>2566243</t>
+          <t>4539472</t>
         </is>
       </c>
       <c r="B361" t="inlineStr">
         <is>
-          <t>EF4-0232301-0</t>
+          <t>EF4-0232482-8</t>
         </is>
       </c>
       <c r="C361" t="inlineStr">
         <is>
-          <t>Vessel, Container</t>
-        </is>
-      </c>
-      <c r="D361" t="inlineStr"/>
+          <t>Air, Non-container</t>
+        </is>
+      </c>
+      <c r="D361" t="inlineStr">
+        <is>
+          <t>V1626463577</t>
+        </is>
+      </c>
       <c r="E361" t="inlineStr">
         <is>
           <t>9903.03.01</t>
@@ -30543,59 +30539,59 @@
       </c>
       <c r="I361" t="inlineStr">
         <is>
-          <t>3920.20.0055</t>
+          <t>9026.20.4000</t>
         </is>
       </c>
       <c r="J361" t="inlineStr">
         <is>
-          <t>GULF ATLANTIC PACKAGING CORP</t>
+          <t>JRCRUZ CORP</t>
         </is>
       </c>
       <c r="K361" t="inlineStr">
         <is>
-          <t>GULATL</t>
+          <t>JRCCOR01</t>
         </is>
       </c>
       <c r="L361" t="inlineStr">
         <is>
-          <t>58-184378700</t>
+          <t>22-337379600</t>
         </is>
       </c>
       <c r="M361" t="inlineStr">
         <is>
+          <t>2026-06-20 00:00:00</t>
+        </is>
+      </c>
+      <c r="N361" t="inlineStr">
+        <is>
           <t>2026-06-22 00:00:00</t>
         </is>
       </c>
-      <c r="N361" t="inlineStr">
-        <is>
-          <t>2026-06-22 00:00:00</t>
-        </is>
-      </c>
       <c r="O361" t="inlineStr">
         <is>
-          <t>SEKISUI JUSHI BV</t>
+          <t>JACKCONTROL AG</t>
         </is>
       </c>
       <c r="P361" t="inlineStr">
         <is>
-          <t>SEKISUI JUSHI BV</t>
+          <t>JACKCONTROL AG</t>
         </is>
       </c>
       <c r="Q361" t="inlineStr">
         <is>
-          <t>2026-05-30 00:00:00</t>
+          <t>2026-06-20 00:00:00</t>
         </is>
       </c>
     </row>
     <row r="362">
       <c r="A362" t="inlineStr">
         <is>
-          <t>2566128</t>
+          <t>2565907</t>
         </is>
       </c>
       <c r="B362" t="inlineStr">
         <is>
-          <t>EF4-0232453-9</t>
+          <t>EF4-0232496-8</t>
         </is>
       </c>
       <c r="C362" t="inlineStr">
@@ -30605,15 +30601,19 @@
       </c>
       <c r="D362" t="inlineStr">
         <is>
-          <t>V1626463577</t>
+          <t>V0413937900</t>
         </is>
       </c>
       <c r="E362" t="inlineStr">
         <is>
-          <t>9903.03.01</t>
-        </is>
-      </c>
-      <c r="F362" t="inlineStr"/>
+          <t>9903.03.06</t>
+        </is>
+      </c>
+      <c r="F362" t="inlineStr">
+        <is>
+          <t>S122 EXCL,IRN/STL/ALUM,DERIV</t>
+        </is>
+      </c>
       <c r="G362" t="inlineStr">
         <is>
           <t>001</t>
@@ -30621,119 +30621,119 @@
       </c>
       <c r="H362" t="inlineStr">
         <is>
-          <t>9903.03.01</t>
+          <t>9903.03.06</t>
         </is>
       </c>
       <c r="I362" t="inlineStr">
         <is>
-          <t>1108.12.0010</t>
+          <t>9903.82.02,7222.20.0043</t>
         </is>
       </c>
       <c r="J362" t="inlineStr">
         <is>
-          <t>ROYAL INGREDIENTS GROUP BV</t>
+          <t>MESHA STEELS  LLC</t>
         </is>
       </c>
       <c r="K362" t="inlineStr">
         <is>
-          <t>ROYINGRE</t>
+          <t>MESSTE</t>
         </is>
       </c>
       <c r="L362" t="inlineStr">
         <is>
-          <t>074601-00962</t>
+          <t>20-274801900</t>
         </is>
       </c>
       <c r="M362" t="inlineStr">
         <is>
+          <t>2026-06-17 00:00:00</t>
+        </is>
+      </c>
+      <c r="N362" t="inlineStr">
+        <is>
           <t>2026-06-22 00:00:00</t>
         </is>
       </c>
-      <c r="N362" t="inlineStr">
-        <is>
-          <t>2026-06-22 00:00:00</t>
-        </is>
-      </c>
       <c r="O362" t="inlineStr">
         <is>
-          <t>TAT NISASTA INS SAN TIC AS</t>
+          <t>BHANSALI BRIGHT BARS PVT. LTD.</t>
         </is>
       </c>
       <c r="P362" t="inlineStr">
         <is>
-          <t>TAT NISASTA INS SAN TIC AS</t>
+          <t>BHANSALI BRIGHT BARS PVT. LTD.</t>
         </is>
       </c>
       <c r="Q362" t="inlineStr">
         <is>
-          <t>2026-05-30 00:00:00</t>
+          <t>2026-05-11 00:00:00</t>
         </is>
       </c>
     </row>
     <row r="363">
       <c r="A363" t="inlineStr">
         <is>
-          <t>4539472</t>
+          <t>2565907</t>
         </is>
       </c>
       <c r="B363" t="inlineStr">
         <is>
-          <t>EF4-0232482-8</t>
+          <t>EF4-0232496-8</t>
         </is>
       </c>
       <c r="C363" t="inlineStr">
         <is>
-          <t>Air, Non-container</t>
+          <t>Vessel, Container</t>
         </is>
       </c>
       <c r="D363" t="inlineStr">
         <is>
-          <t>V1626463577</t>
+          <t>V0413937900</t>
         </is>
       </c>
       <c r="E363" t="inlineStr">
         <is>
-          <t>9903.03.01</t>
+          <t>9903.03.06</t>
         </is>
       </c>
       <c r="F363" t="inlineStr">
         <is>
-          <t>SECTION 122 - 10% DUTY</t>
+          <t>S122 EXCL,IRN/STL/ALUM,DERIV</t>
         </is>
       </c>
       <c r="G363" t="inlineStr">
         <is>
-          <t>001</t>
+          <t>002</t>
         </is>
       </c>
       <c r="H363" t="inlineStr">
         <is>
-          <t>9903.03.01</t>
+          <t>9903.03.06</t>
         </is>
       </c>
       <c r="I363" t="inlineStr">
         <is>
-          <t>9026.20.4000</t>
+          <t>9903.82.02,7222.20.0073</t>
         </is>
       </c>
       <c r="J363" t="inlineStr">
         <is>
-          <t>JRCRUZ CORP</t>
+          <t>MESHA STEELS  LLC</t>
         </is>
       </c>
       <c r="K363" t="inlineStr">
         <is>
-          <t>JRCCOR01</t>
+          <t>MESSTE</t>
         </is>
       </c>
       <c r="L363" t="inlineStr">
         <is>
-          <t>22-337379600</t>
+          <t>20-274801900</t>
         </is>
       </c>
       <c r="M363" t="inlineStr">
         <is>
-          <t>2026-06-20 00:00:00</t>
+          <t>2026-06-17 00:00:00</t>
         </is>
       </c>
       <c r="N363" t="inlineStr">
@@ -30743,29 +30743,29 @@
       </c>
       <c r="O363" t="inlineStr">
         <is>
-          <t>JACKCONTROL AG</t>
+          <t>BHANSALI BRIGHT BARS PVT. LTD.</t>
         </is>
       </c>
       <c r="P363" t="inlineStr">
         <is>
-          <t>JACKCONTROL AG</t>
+          <t>BHANSALI BRIGHT BARS PVT. LTD.</t>
         </is>
       </c>
       <c r="Q363" t="inlineStr">
         <is>
-          <t>2026-06-20 00:00:00</t>
+          <t>2026-05-11 00:00:00</t>
         </is>
       </c>
     </row>
     <row r="364">
       <c r="A364" t="inlineStr">
         <is>
-          <t>2565907</t>
+          <t>2566336</t>
         </is>
       </c>
       <c r="B364" t="inlineStr">
         <is>
-          <t>EF4-0232496-8</t>
+          <t>EF4-0232529-6</t>
         </is>
       </c>
       <c r="C364" t="inlineStr">
@@ -30780,12 +30780,12 @@
       </c>
       <c r="E364" t="inlineStr">
         <is>
-          <t>9903.03.06</t>
+          <t>9903.03.01</t>
         </is>
       </c>
       <c r="F364" t="inlineStr">
         <is>
-          <t>S122 EXCL,IRN/STL/ALUM,DERIV</t>
+          <t>SECTION 122 - 10% DUTY</t>
         </is>
       </c>
       <c r="G364" t="inlineStr">
@@ -30795,32 +30795,32 @@
       </c>
       <c r="H364" t="inlineStr">
         <is>
-          <t>9903.03.06</t>
+          <t>9903.03.01</t>
         </is>
       </c>
       <c r="I364" t="inlineStr">
         <is>
-          <t>9903.82.02,7222.20.0043</t>
+          <t>8422.30.9130</t>
         </is>
       </c>
       <c r="J364" t="inlineStr">
         <is>
-          <t>MESHA STEELS  LLC</t>
+          <t>MANKIEWICZ COATINGS, LLC</t>
         </is>
       </c>
       <c r="K364" t="inlineStr">
         <is>
-          <t>MESSTE</t>
+          <t>MANCOAT</t>
         </is>
       </c>
       <c r="L364" t="inlineStr">
         <is>
-          <t>20-274801900</t>
+          <t>56-202308900</t>
         </is>
       </c>
       <c r="M364" t="inlineStr">
         <is>
-          <t>2026-06-17 00:00:00</t>
+          <t>2026-06-22 00:00:00</t>
         </is>
       </c>
       <c r="N364" t="inlineStr">
@@ -30830,29 +30830,29 @@
       </c>
       <c r="O364" t="inlineStr">
         <is>
-          <t>BHANSALI BRIGHT BARS PVT. LTD.</t>
+          <t>MANKIEWICZ GEBR. &amp; CO.</t>
         </is>
       </c>
       <c r="P364" t="inlineStr">
         <is>
-          <t>BHANSALI BRIGHT BARS PVT. LTD.</t>
+          <t>MANKIEWICZ GEBR. &amp; CO.</t>
         </is>
       </c>
       <c r="Q364" t="inlineStr">
         <is>
-          <t>2026-05-11 00:00:00</t>
+          <t>2026-06-13 00:00:00</t>
         </is>
       </c>
     </row>
     <row r="365">
       <c r="A365" t="inlineStr">
         <is>
-          <t>2565907</t>
+          <t>2566336</t>
         </is>
       </c>
       <c r="B365" t="inlineStr">
         <is>
-          <t>EF4-0232496-8</t>
+          <t>EF4-0232529-6</t>
         </is>
       </c>
       <c r="C365" t="inlineStr">
@@ -30887,27 +30887,27 @@
       </c>
       <c r="I365" t="inlineStr">
         <is>
-          <t>9903.82.02,7222.20.0073</t>
+          <t>9903.82.02,7309.00.0030</t>
         </is>
       </c>
       <c r="J365" t="inlineStr">
         <is>
-          <t>MESHA STEELS  LLC</t>
+          <t>MANKIEWICZ COATINGS, LLC</t>
         </is>
       </c>
       <c r="K365" t="inlineStr">
         <is>
-          <t>MESSTE</t>
+          <t>MANCOAT</t>
         </is>
       </c>
       <c r="L365" t="inlineStr">
         <is>
-          <t>20-274801900</t>
+          <t>56-202308900</t>
         </is>
       </c>
       <c r="M365" t="inlineStr">
         <is>
-          <t>2026-06-17 00:00:00</t>
+          <t>2026-06-22 00:00:00</t>
         </is>
       </c>
       <c r="N365" t="inlineStr">
@@ -30917,17 +30917,17 @@
       </c>
       <c r="O365" t="inlineStr">
         <is>
-          <t>BHANSALI BRIGHT BARS PVT. LTD.</t>
+          <t>MANKIEWICZ GEBR. &amp; CO.</t>
         </is>
       </c>
       <c r="P365" t="inlineStr">
         <is>
-          <t>BHANSALI BRIGHT BARS PVT. LTD.</t>
+          <t>MANKIEWICZ GEBR. &amp; CO.</t>
         </is>
       </c>
       <c r="Q365" t="inlineStr">
         <is>
-          <t>2026-05-11 00:00:00</t>
+          <t>2026-06-13 00:00:00</t>
         </is>
       </c>
     </row>
@@ -30964,7 +30964,7 @@
       </c>
       <c r="G366" t="inlineStr">
         <is>
-          <t>001</t>
+          <t>003</t>
         </is>
       </c>
       <c r="H366" t="inlineStr">
@@ -30974,7 +30974,7 @@
       </c>
       <c r="I366" t="inlineStr">
         <is>
-          <t>8422.30.9130</t>
+          <t>8479.82.0040</t>
         </is>
       </c>
       <c r="J366" t="inlineStr">
@@ -31051,7 +31051,7 @@
       </c>
       <c r="G367" t="inlineStr">
         <is>
-          <t>002</t>
+          <t>004</t>
         </is>
       </c>
       <c r="H367" t="inlineStr">
@@ -31138,7 +31138,7 @@
       </c>
       <c r="G368" t="inlineStr">
         <is>
-          <t>003</t>
+          <t>005</t>
         </is>
       </c>
       <c r="H368" t="inlineStr">
@@ -31195,12 +31195,12 @@
     <row r="369">
       <c r="A369" t="inlineStr">
         <is>
-          <t>2566336</t>
+          <t>2565800</t>
         </is>
       </c>
       <c r="B369" t="inlineStr">
         <is>
-          <t>EF4-0232529-6</t>
+          <t>EF4-0232068-5</t>
         </is>
       </c>
       <c r="C369" t="inlineStr">
@@ -31210,7 +31210,7 @@
       </c>
       <c r="D369" t="inlineStr">
         <is>
-          <t>V0413937900</t>
+          <t>165922433</t>
         </is>
       </c>
       <c r="E369" t="inlineStr">
@@ -31225,7 +31225,7 @@
       </c>
       <c r="G369" t="inlineStr">
         <is>
-          <t>004</t>
+          <t>001</t>
         </is>
       </c>
       <c r="H369" t="inlineStr">
@@ -31235,59 +31235,59 @@
       </c>
       <c r="I369" t="inlineStr">
         <is>
-          <t>9903.82.02,7309.00.0030</t>
+          <t>9903.82.02,7223.00.1031</t>
         </is>
       </c>
       <c r="J369" t="inlineStr">
         <is>
-          <t>MANKIEWICZ COATINGS, LLC</t>
+          <t>VENUS WIRE INDUSTRIES PRIVATE LTD</t>
         </is>
       </c>
       <c r="K369" t="inlineStr">
         <is>
-          <t>MANCOAT</t>
+          <t>VENWIR</t>
         </is>
       </c>
       <c r="L369" t="inlineStr">
         <is>
-          <t>56-202308900</t>
+          <t>993901-03595</t>
         </is>
       </c>
       <c r="M369" t="inlineStr">
         <is>
-          <t>2026-06-22 00:00:00</t>
+          <t>2026-06-17 00:00:00</t>
         </is>
       </c>
       <c r="N369" t="inlineStr">
         <is>
-          <t>2026-06-22 00:00:00</t>
+          <t>2026-06-23 00:00:00</t>
         </is>
       </c>
       <c r="O369" t="inlineStr">
         <is>
-          <t>MANKIEWICZ GEBR. &amp; CO.</t>
+          <t>VENUS WIRE INDUSTRIES PRIVATE LIMIT</t>
         </is>
       </c>
       <c r="P369" t="inlineStr">
         <is>
-          <t>MANKIEWICZ GEBR. &amp; CO.</t>
+          <t>VENUS WIRE INDUSTRIES PRIVATE LIMITED</t>
         </is>
       </c>
       <c r="Q369" t="inlineStr">
         <is>
-          <t>2026-06-13 00:00:00</t>
+          <t>2026-05-11 00:00:00</t>
         </is>
       </c>
     </row>
     <row r="370">
       <c r="A370" t="inlineStr">
         <is>
-          <t>2566336</t>
+          <t>2566066</t>
         </is>
       </c>
       <c r="B370" t="inlineStr">
         <is>
-          <t>EF4-0232529-6</t>
+          <t>EF4-0232182-4</t>
         </is>
       </c>
       <c r="C370" t="inlineStr">
@@ -31297,7 +31297,7 @@
       </c>
       <c r="D370" t="inlineStr">
         <is>
-          <t>V0413937900</t>
+          <t>V0413939047</t>
         </is>
       </c>
       <c r="E370" t="inlineStr">
@@ -31312,7 +31312,7 @@
       </c>
       <c r="G370" t="inlineStr">
         <is>
-          <t>005</t>
+          <t>001</t>
         </is>
       </c>
       <c r="H370" t="inlineStr">
@@ -31322,47 +31322,830 @@
       </c>
       <c r="I370" t="inlineStr">
         <is>
-          <t>8479.82.0040</t>
+          <t>1702.30.4085</t>
         </is>
       </c>
       <c r="J370" t="inlineStr">
         <is>
-          <t>MANKIEWICZ COATINGS, LLC</t>
+          <t>ROYAL INGREDIENTS GROUP BV</t>
         </is>
       </c>
       <c r="K370" t="inlineStr">
         <is>
-          <t>MANCOAT</t>
+          <t>ROYINGRE</t>
         </is>
       </c>
       <c r="L370" t="inlineStr">
         <is>
-          <t>56-202308900</t>
+          <t>074601-00962</t>
         </is>
       </c>
       <c r="M370" t="inlineStr">
         <is>
+          <t>2026-06-16 00:00:00</t>
+        </is>
+      </c>
+      <c r="N370" t="inlineStr">
+        <is>
+          <t>2026-06-23 00:00:00</t>
+        </is>
+      </c>
+      <c r="O370" t="inlineStr">
+        <is>
+          <t>AK NISASTA SANAYI VE TICARET AS</t>
+        </is>
+      </c>
+      <c r="P370" t="inlineStr">
+        <is>
+          <t>AK NISASTA SANAYI VE TICARET AS</t>
+        </is>
+      </c>
+      <c r="Q370" t="inlineStr">
+        <is>
+          <t>2026-05-27 00:00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="371">
+      <c r="A371" t="inlineStr">
+        <is>
+          <t>2566295</t>
+        </is>
+      </c>
+      <c r="B371" t="inlineStr">
+        <is>
+          <t>EF4-0232493-5</t>
+        </is>
+      </c>
+      <c r="C371" t="inlineStr">
+        <is>
+          <t>Vessel, Container</t>
+        </is>
+      </c>
+      <c r="D371" t="inlineStr">
+        <is>
+          <t>V1626459823</t>
+        </is>
+      </c>
+      <c r="E371" t="inlineStr">
+        <is>
+          <t>9903.03.01</t>
+        </is>
+      </c>
+      <c r="F371" t="inlineStr">
+        <is>
+          <t>SECTION 122 - 10% DUTY</t>
+        </is>
+      </c>
+      <c r="G371" t="inlineStr">
+        <is>
+          <t>001</t>
+        </is>
+      </c>
+      <c r="H371" t="inlineStr">
+        <is>
+          <t>9903.03.01</t>
+        </is>
+      </c>
+      <c r="I371" t="inlineStr">
+        <is>
+          <t>1109.00.9020</t>
+        </is>
+      </c>
+      <c r="J371" t="inlineStr">
+        <is>
+          <t>ROYAL INGREDIENTS GROUP BV</t>
+        </is>
+      </c>
+      <c r="K371" t="inlineStr">
+        <is>
+          <t>ROYINGRE</t>
+        </is>
+      </c>
+      <c r="L371" t="inlineStr">
+        <is>
+          <t>074601-00962</t>
+        </is>
+      </c>
+      <c r="M371" t="inlineStr">
+        <is>
+          <t>2026-06-23 00:00:00</t>
+        </is>
+      </c>
+      <c r="N371" t="inlineStr">
+        <is>
+          <t>2026-06-23 00:00:00</t>
+        </is>
+      </c>
+      <c r="O371" t="inlineStr">
+        <is>
+          <t>JACKERING MUHLEN UND NAHRMITTELWERK</t>
+        </is>
+      </c>
+      <c r="P371" t="inlineStr">
+        <is>
+          <t>JACKERING MUHLEN UND NAHRMITTELWERKE GMBH</t>
+        </is>
+      </c>
+      <c r="Q371" t="inlineStr">
+        <is>
+          <t>2026-06-11 00:00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="372">
+      <c r="A372" t="inlineStr">
+        <is>
+          <t>2566237</t>
+        </is>
+      </c>
+      <c r="B372" t="inlineStr">
+        <is>
+          <t>EF4-0232521-3</t>
+        </is>
+      </c>
+      <c r="C372" t="inlineStr">
+        <is>
+          <t>Vessel, Container</t>
+        </is>
+      </c>
+      <c r="D372" t="inlineStr">
+        <is>
+          <t>VA923813227</t>
+        </is>
+      </c>
+      <c r="E372" t="inlineStr">
+        <is>
+          <t>9903.03.01</t>
+        </is>
+      </c>
+      <c r="F372" t="inlineStr">
+        <is>
+          <t>SECTION 122 - 10% DUTY</t>
+        </is>
+      </c>
+      <c r="G372" t="inlineStr">
+        <is>
+          <t>001</t>
+        </is>
+      </c>
+      <c r="H372" t="inlineStr">
+        <is>
+          <t>9903.03.01</t>
+        </is>
+      </c>
+      <c r="I372" t="inlineStr">
+        <is>
+          <t>3604.10.9010</t>
+        </is>
+      </c>
+      <c r="J372" t="inlineStr">
+        <is>
+          <t>AMERICAN FIREWORKS COMPANY</t>
+        </is>
+      </c>
+      <c r="K372" t="inlineStr">
+        <is>
+          <t>AMEFIR01</t>
+        </is>
+      </c>
+      <c r="L372" t="inlineStr">
+        <is>
+          <t>34-006522000</t>
+        </is>
+      </c>
+      <c r="M372" t="inlineStr">
+        <is>
           <t>2026-06-22 00:00:00</t>
         </is>
       </c>
-      <c r="N370" t="inlineStr">
+      <c r="N372" t="inlineStr">
+        <is>
+          <t>2026-06-23 00:00:00</t>
+        </is>
+      </c>
+      <c r="O372" t="inlineStr">
+        <is>
+          <t>JIANGXI PANDA FIREWORKS CO. LTD.</t>
+        </is>
+      </c>
+      <c r="P372" t="inlineStr">
+        <is>
+          <t>JIANGXI PANDA FIREWORKS CO. LTD.</t>
+        </is>
+      </c>
+      <c r="Q372" t="inlineStr">
+        <is>
+          <t>2026-06-11 00:00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="373">
+      <c r="A373" t="inlineStr">
+        <is>
+          <t>2566237</t>
+        </is>
+      </c>
+      <c r="B373" t="inlineStr">
+        <is>
+          <t>EF4-0232521-3</t>
+        </is>
+      </c>
+      <c r="C373" t="inlineStr">
+        <is>
+          <t>Vessel, Container</t>
+        </is>
+      </c>
+      <c r="D373" t="inlineStr">
+        <is>
+          <t>VA923813227</t>
+        </is>
+      </c>
+      <c r="E373" t="inlineStr">
+        <is>
+          <t>9903.03.01</t>
+        </is>
+      </c>
+      <c r="F373" t="inlineStr">
+        <is>
+          <t>SECTION 122 - 10% DUTY</t>
+        </is>
+      </c>
+      <c r="G373" t="inlineStr">
+        <is>
+          <t>002</t>
+        </is>
+      </c>
+      <c r="H373" t="inlineStr">
+        <is>
+          <t>9903.03.01</t>
+        </is>
+      </c>
+      <c r="I373" t="inlineStr">
+        <is>
+          <t>3604.10.9050</t>
+        </is>
+      </c>
+      <c r="J373" t="inlineStr">
+        <is>
+          <t>AMERICAN FIREWORKS COMPANY</t>
+        </is>
+      </c>
+      <c r="K373" t="inlineStr">
+        <is>
+          <t>AMEFIR01</t>
+        </is>
+      </c>
+      <c r="L373" t="inlineStr">
+        <is>
+          <t>34-006522000</t>
+        </is>
+      </c>
+      <c r="M373" t="inlineStr">
         <is>
           <t>2026-06-22 00:00:00</t>
         </is>
       </c>
-      <c r="O370" t="inlineStr">
-        <is>
-          <t>MANKIEWICZ GEBR. &amp; CO.</t>
-        </is>
-      </c>
-      <c r="P370" t="inlineStr">
-        <is>
-          <t>MANKIEWICZ GEBR. &amp; CO.</t>
-        </is>
-      </c>
-      <c r="Q370" t="inlineStr">
-        <is>
-          <t>2026-06-13 00:00:00</t>
+      <c r="N373" t="inlineStr">
+        <is>
+          <t>2026-06-23 00:00:00</t>
+        </is>
+      </c>
+      <c r="O373" t="inlineStr">
+        <is>
+          <t>JIANGXI PANDA FIREWORKS CO. LTD.</t>
+        </is>
+      </c>
+      <c r="P373" t="inlineStr">
+        <is>
+          <t>JIANGXI PANDA FIREWORKS CO. LTD.</t>
+        </is>
+      </c>
+      <c r="Q373" t="inlineStr">
+        <is>
+          <t>2026-06-11 00:00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="374">
+      <c r="A374" t="inlineStr">
+        <is>
+          <t>2566246</t>
+        </is>
+      </c>
+      <c r="B374" t="inlineStr">
+        <is>
+          <t>EF4-0232522-1</t>
+        </is>
+      </c>
+      <c r="C374" t="inlineStr">
+        <is>
+          <t>Vessel, Container</t>
+        </is>
+      </c>
+      <c r="D374" t="inlineStr">
+        <is>
+          <t>VA923813227</t>
+        </is>
+      </c>
+      <c r="E374" t="inlineStr">
+        <is>
+          <t>9903.03.01</t>
+        </is>
+      </c>
+      <c r="F374" t="inlineStr">
+        <is>
+          <t>SECTION 122 - 10% DUTY</t>
+        </is>
+      </c>
+      <c r="G374" t="inlineStr">
+        <is>
+          <t>001</t>
+        </is>
+      </c>
+      <c r="H374" t="inlineStr">
+        <is>
+          <t>9903.03.01</t>
+        </is>
+      </c>
+      <c r="I374" t="inlineStr">
+        <is>
+          <t>3604.10.9050</t>
+        </is>
+      </c>
+      <c r="J374" t="inlineStr">
+        <is>
+          <t>AMERICAN FIREWORKS COMPANY</t>
+        </is>
+      </c>
+      <c r="K374" t="inlineStr">
+        <is>
+          <t>AMEFIR01</t>
+        </is>
+      </c>
+      <c r="L374" t="inlineStr">
+        <is>
+          <t>34-006522000</t>
+        </is>
+      </c>
+      <c r="M374" t="inlineStr">
+        <is>
+          <t>2026-06-22 00:00:00</t>
+        </is>
+      </c>
+      <c r="N374" t="inlineStr">
+        <is>
+          <t>2026-06-23 00:00:00</t>
+        </is>
+      </c>
+      <c r="O374" t="inlineStr">
+        <is>
+          <t>JIANGXI PANDA FIREWORKS CO. LTD.</t>
+        </is>
+      </c>
+      <c r="P374" t="inlineStr">
+        <is>
+          <t>JIANGXI PANDA FIREWORKS CO. LTD.</t>
+        </is>
+      </c>
+      <c r="Q374" t="inlineStr">
+        <is>
+          <t>2026-06-11 00:00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="375">
+      <c r="A375" t="inlineStr">
+        <is>
+          <t>2566246</t>
+        </is>
+      </c>
+      <c r="B375" t="inlineStr">
+        <is>
+          <t>EF4-0232522-1</t>
+        </is>
+      </c>
+      <c r="C375" t="inlineStr">
+        <is>
+          <t>Vessel, Container</t>
+        </is>
+      </c>
+      <c r="D375" t="inlineStr">
+        <is>
+          <t>VA923813227</t>
+        </is>
+      </c>
+      <c r="E375" t="inlineStr">
+        <is>
+          <t>9903.03.01</t>
+        </is>
+      </c>
+      <c r="F375" t="inlineStr">
+        <is>
+          <t>SECTION 122 - 10% DUTY</t>
+        </is>
+      </c>
+      <c r="G375" t="inlineStr">
+        <is>
+          <t>002</t>
+        </is>
+      </c>
+      <c r="H375" t="inlineStr">
+        <is>
+          <t>9903.03.01</t>
+        </is>
+      </c>
+      <c r="I375" t="inlineStr">
+        <is>
+          <t>3604.10.9010</t>
+        </is>
+      </c>
+      <c r="J375" t="inlineStr">
+        <is>
+          <t>AMERICAN FIREWORKS COMPANY</t>
+        </is>
+      </c>
+      <c r="K375" t="inlineStr">
+        <is>
+          <t>AMEFIR01</t>
+        </is>
+      </c>
+      <c r="L375" t="inlineStr">
+        <is>
+          <t>34-006522000</t>
+        </is>
+      </c>
+      <c r="M375" t="inlineStr">
+        <is>
+          <t>2026-06-22 00:00:00</t>
+        </is>
+      </c>
+      <c r="N375" t="inlineStr">
+        <is>
+          <t>2026-06-23 00:00:00</t>
+        </is>
+      </c>
+      <c r="O375" t="inlineStr">
+        <is>
+          <t>JIANGXI PANDA FIREWORKS CO. LTD.</t>
+        </is>
+      </c>
+      <c r="P375" t="inlineStr">
+        <is>
+          <t>JIANGXI PANDA FIREWORKS CO. LTD.</t>
+        </is>
+      </c>
+      <c r="Q375" t="inlineStr">
+        <is>
+          <t>2026-06-11 00:00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="376">
+      <c r="A376" t="inlineStr">
+        <is>
+          <t>2566111</t>
+        </is>
+      </c>
+      <c r="B376" t="inlineStr">
+        <is>
+          <t>EF4-0232544-5</t>
+        </is>
+      </c>
+      <c r="C376" t="inlineStr">
+        <is>
+          <t>Vessel, Container</t>
+        </is>
+      </c>
+      <c r="D376" t="inlineStr">
+        <is>
+          <t>VA923813219</t>
+        </is>
+      </c>
+      <c r="E376" t="inlineStr">
+        <is>
+          <t>9903.03.06</t>
+        </is>
+      </c>
+      <c r="F376" t="inlineStr">
+        <is>
+          <t>S122 EXCL,IRN/STL/ALUM,DERIV</t>
+        </is>
+      </c>
+      <c r="G376" t="inlineStr">
+        <is>
+          <t>001</t>
+        </is>
+      </c>
+      <c r="H376" t="inlineStr">
+        <is>
+          <t>9903.03.06</t>
+        </is>
+      </c>
+      <c r="I376" t="inlineStr">
+        <is>
+          <t>9903.82.02,7223.00.1061</t>
+        </is>
+      </c>
+      <c r="J376" t="inlineStr">
+        <is>
+          <t>VENUS WIRE INDUSTRIES PRIVATE LTD</t>
+        </is>
+      </c>
+      <c r="K376" t="inlineStr">
+        <is>
+          <t>VENWIR</t>
+        </is>
+      </c>
+      <c r="L376" t="inlineStr">
+        <is>
+          <t>993901-03595</t>
+        </is>
+      </c>
+      <c r="M376" t="inlineStr">
+        <is>
+          <t>2026-06-23 00:00:00</t>
+        </is>
+      </c>
+      <c r="N376" t="inlineStr">
+        <is>
+          <t>2026-06-23 00:00:00</t>
+        </is>
+      </c>
+      <c r="O376" t="inlineStr">
+        <is>
+          <t>PRECISION METALS</t>
+        </is>
+      </c>
+      <c r="P376" t="inlineStr">
+        <is>
+          <t>PRECISION METALS</t>
+        </is>
+      </c>
+      <c r="Q376" t="inlineStr">
+        <is>
+          <t>2026-05-23 00:00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="377">
+      <c r="A377" t="inlineStr">
+        <is>
+          <t>2566111</t>
+        </is>
+      </c>
+      <c r="B377" t="inlineStr">
+        <is>
+          <t>EF4-0232544-5</t>
+        </is>
+      </c>
+      <c r="C377" t="inlineStr">
+        <is>
+          <t>Vessel, Container</t>
+        </is>
+      </c>
+      <c r="D377" t="inlineStr">
+        <is>
+          <t>VA923813219</t>
+        </is>
+      </c>
+      <c r="E377" t="inlineStr">
+        <is>
+          <t>9903.03.06</t>
+        </is>
+      </c>
+      <c r="F377" t="inlineStr">
+        <is>
+          <t>S122 EXCL,IRN/STL/ALUM,DERIV</t>
+        </is>
+      </c>
+      <c r="G377" t="inlineStr">
+        <is>
+          <t>002</t>
+        </is>
+      </c>
+      <c r="H377" t="inlineStr">
+        <is>
+          <t>9903.03.06</t>
+        </is>
+      </c>
+      <c r="I377" t="inlineStr">
+        <is>
+          <t>9903.82.02,7223.00.1076</t>
+        </is>
+      </c>
+      <c r="J377" t="inlineStr">
+        <is>
+          <t>VENUS WIRE INDUSTRIES PRIVATE LTD</t>
+        </is>
+      </c>
+      <c r="K377" t="inlineStr">
+        <is>
+          <t>VENWIR</t>
+        </is>
+      </c>
+      <c r="L377" t="inlineStr">
+        <is>
+          <t>993901-03595</t>
+        </is>
+      </c>
+      <c r="M377" t="inlineStr">
+        <is>
+          <t>2026-06-23 00:00:00</t>
+        </is>
+      </c>
+      <c r="N377" t="inlineStr">
+        <is>
+          <t>2026-06-23 00:00:00</t>
+        </is>
+      </c>
+      <c r="O377" t="inlineStr">
+        <is>
+          <t>PRECISION METALS</t>
+        </is>
+      </c>
+      <c r="P377" t="inlineStr">
+        <is>
+          <t>PRECISION METALS</t>
+        </is>
+      </c>
+      <c r="Q377" t="inlineStr">
+        <is>
+          <t>2026-05-23 00:00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="378">
+      <c r="A378" t="inlineStr">
+        <is>
+          <t>4539506</t>
+        </is>
+      </c>
+      <c r="B378" t="inlineStr">
+        <is>
+          <t>EF4-0232622-9</t>
+        </is>
+      </c>
+      <c r="C378" t="inlineStr">
+        <is>
+          <t>Air, Non-container</t>
+        </is>
+      </c>
+      <c r="D378" t="inlineStr">
+        <is>
+          <t>V0710322558</t>
+        </is>
+      </c>
+      <c r="E378" t="inlineStr">
+        <is>
+          <t>9903.03.01</t>
+        </is>
+      </c>
+      <c r="F378" t="inlineStr">
+        <is>
+          <t>SECTION 122 - 10% DUTY</t>
+        </is>
+      </c>
+      <c r="G378" t="inlineStr">
+        <is>
+          <t>001</t>
+        </is>
+      </c>
+      <c r="H378" t="inlineStr">
+        <is>
+          <t>9903.03.01</t>
+        </is>
+      </c>
+      <c r="I378" t="inlineStr">
+        <is>
+          <t>9401.99.1085</t>
+        </is>
+      </c>
+      <c r="J378" t="inlineStr">
+        <is>
+          <t>ALBAFORM INC</t>
+        </is>
+      </c>
+      <c r="K378" t="inlineStr">
+        <is>
+          <t>ALBINC01</t>
+        </is>
+      </c>
+      <c r="L378" t="inlineStr">
+        <is>
+          <t>35-243920800</t>
+        </is>
+      </c>
+      <c r="M378" t="inlineStr">
+        <is>
+          <t>2026-06-23 00:00:00</t>
+        </is>
+      </c>
+      <c r="N378" t="inlineStr">
+        <is>
+          <t>2026-06-23 00:00:00</t>
+        </is>
+      </c>
+      <c r="O378" t="inlineStr">
+        <is>
+          <t>ALBAFORM S.R.O</t>
+        </is>
+      </c>
+      <c r="P378" t="inlineStr">
+        <is>
+          <t>ALBAFORM S.R.O</t>
+        </is>
+      </c>
+      <c r="Q378" t="inlineStr">
+        <is>
+          <t>2026-06-23 00:00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="379">
+      <c r="A379" t="inlineStr">
+        <is>
+          <t>4539548</t>
+        </is>
+      </c>
+      <c r="B379" t="inlineStr">
+        <is>
+          <t>EF4-0232745-8</t>
+        </is>
+      </c>
+      <c r="C379" t="inlineStr">
+        <is>
+          <t>Air, Non-container</t>
+        </is>
+      </c>
+      <c r="D379" t="inlineStr">
+        <is>
+          <t>708088895</t>
+        </is>
+      </c>
+      <c r="E379" t="inlineStr">
+        <is>
+          <t>9903.03.01</t>
+        </is>
+      </c>
+      <c r="F379" t="inlineStr">
+        <is>
+          <t>SECTION 122 - 10% DUTY</t>
+        </is>
+      </c>
+      <c r="G379" t="inlineStr">
+        <is>
+          <t>001</t>
+        </is>
+      </c>
+      <c r="H379" t="inlineStr">
+        <is>
+          <t>9903.03.01</t>
+        </is>
+      </c>
+      <c r="I379" t="inlineStr">
+        <is>
+          <t>8438.90.9060</t>
+        </is>
+      </c>
+      <c r="J379" t="inlineStr">
+        <is>
+          <t>CANTRELL GAINCO GROUP INC</t>
+        </is>
+      </c>
+      <c r="K379" t="inlineStr">
+        <is>
+          <t>CANGAI01</t>
+        </is>
+      </c>
+      <c r="L379" t="inlineStr">
+        <is>
+          <t>31-151121700</t>
+        </is>
+      </c>
+      <c r="M379" t="inlineStr">
+        <is>
+          <t>2026-06-22 00:00:00</t>
+        </is>
+      </c>
+      <c r="N379" t="inlineStr">
+        <is>
+          <t>2026-06-23 00:00:00</t>
+        </is>
+      </c>
+      <c r="O379" t="inlineStr">
+        <is>
+          <t>O E CO LTD</t>
+        </is>
+      </c>
+      <c r="P379" t="inlineStr">
+        <is>
+          <t>O E CO LTD</t>
+        </is>
+      </c>
+      <c r="Q379" t="inlineStr">
+        <is>
+          <t>2026-06-22 00:00:00</t>
         </is>
       </c>
     </row>

--- a/trimika_data.xlsx
+++ b/trimika_data.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q379"/>
+  <dimension ref="A1:Q390"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -32149,6 +32149,931 @@
         </is>
       </c>
     </row>
+    <row r="380">
+      <c r="A380" t="inlineStr">
+        <is>
+          <t>2565850</t>
+        </is>
+      </c>
+      <c r="B380" t="inlineStr">
+        <is>
+          <t>EF4-0231705-3</t>
+        </is>
+      </c>
+      <c r="C380" t="inlineStr">
+        <is>
+          <t>Vessel, Container</t>
+        </is>
+      </c>
+      <c r="D380" t="inlineStr"/>
+      <c r="E380" t="inlineStr">
+        <is>
+          <t>9903.03.01</t>
+        </is>
+      </c>
+      <c r="F380" t="inlineStr">
+        <is>
+          <t>SECTION 122 - 10% DUTY</t>
+        </is>
+      </c>
+      <c r="G380" t="inlineStr">
+        <is>
+          <t>001</t>
+        </is>
+      </c>
+      <c r="H380" t="inlineStr">
+        <is>
+          <t>9903.03.01</t>
+        </is>
+      </c>
+      <c r="I380" t="inlineStr">
+        <is>
+          <t>5407.20.0000</t>
+        </is>
+      </c>
+      <c r="J380" t="inlineStr">
+        <is>
+          <t>VEER CORPORATIONS INC</t>
+        </is>
+      </c>
+      <c r="K380" t="inlineStr">
+        <is>
+          <t>VEECOR01</t>
+        </is>
+      </c>
+      <c r="L380" t="inlineStr">
+        <is>
+          <t>99-106989200</t>
+        </is>
+      </c>
+      <c r="M380" t="inlineStr">
+        <is>
+          <t>2026-06-25 00:00:00</t>
+        </is>
+      </c>
+      <c r="N380" t="inlineStr">
+        <is>
+          <t>2026-06-24 00:00:00</t>
+        </is>
+      </c>
+      <c r="O380" t="inlineStr">
+        <is>
+          <t>VEER PLASTIC PVT LTD</t>
+        </is>
+      </c>
+      <c r="P380" t="inlineStr">
+        <is>
+          <t>VEER PLASTIC PVT LTD</t>
+        </is>
+      </c>
+      <c r="Q380" t="inlineStr">
+        <is>
+          <t>2026-05-10 00:00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="381">
+      <c r="A381" t="inlineStr">
+        <is>
+          <t>2565826</t>
+        </is>
+      </c>
+      <c r="B381" t="inlineStr">
+        <is>
+          <t>EF4-0231707-9</t>
+        </is>
+      </c>
+      <c r="C381" t="inlineStr">
+        <is>
+          <t>Vessel, Container</t>
+        </is>
+      </c>
+      <c r="D381" t="inlineStr"/>
+      <c r="E381" t="inlineStr">
+        <is>
+          <t>9903.03.01</t>
+        </is>
+      </c>
+      <c r="F381" t="inlineStr">
+        <is>
+          <t>SECTION 122 - 10% DUTY</t>
+        </is>
+      </c>
+      <c r="G381" t="inlineStr">
+        <is>
+          <t>001</t>
+        </is>
+      </c>
+      <c r="H381" t="inlineStr">
+        <is>
+          <t>9903.03.01</t>
+        </is>
+      </c>
+      <c r="I381" t="inlineStr">
+        <is>
+          <t>5407.20.0000</t>
+        </is>
+      </c>
+      <c r="J381" t="inlineStr">
+        <is>
+          <t>VEER CORPORATIONS INC</t>
+        </is>
+      </c>
+      <c r="K381" t="inlineStr">
+        <is>
+          <t>VEECOR01</t>
+        </is>
+      </c>
+      <c r="L381" t="inlineStr">
+        <is>
+          <t>99-106989200</t>
+        </is>
+      </c>
+      <c r="M381" t="inlineStr">
+        <is>
+          <t>2026-06-24 00:00:00</t>
+        </is>
+      </c>
+      <c r="N381" t="inlineStr">
+        <is>
+          <t>2026-06-24 00:00:00</t>
+        </is>
+      </c>
+      <c r="O381" t="inlineStr">
+        <is>
+          <t>VEER PLASTIC PVT LTD</t>
+        </is>
+      </c>
+      <c r="P381" t="inlineStr">
+        <is>
+          <t>VEER PLASTIC PVT LTD</t>
+        </is>
+      </c>
+      <c r="Q381" t="inlineStr">
+        <is>
+          <t>2026-04-21 00:00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="382">
+      <c r="A382" t="inlineStr">
+        <is>
+          <t>2565828</t>
+        </is>
+      </c>
+      <c r="B382" t="inlineStr">
+        <is>
+          <t>EF4-0231712-9</t>
+        </is>
+      </c>
+      <c r="C382" t="inlineStr">
+        <is>
+          <t>Vessel, Container</t>
+        </is>
+      </c>
+      <c r="D382" t="inlineStr"/>
+      <c r="E382" t="inlineStr">
+        <is>
+          <t>9903.03.01</t>
+        </is>
+      </c>
+      <c r="F382" t="inlineStr">
+        <is>
+          <t>SECTION 122 - 10% DUTY</t>
+        </is>
+      </c>
+      <c r="G382" t="inlineStr">
+        <is>
+          <t>001</t>
+        </is>
+      </c>
+      <c r="H382" t="inlineStr">
+        <is>
+          <t>9903.03.01</t>
+        </is>
+      </c>
+      <c r="I382" t="inlineStr">
+        <is>
+          <t>5407.20.0000</t>
+        </is>
+      </c>
+      <c r="J382" t="inlineStr">
+        <is>
+          <t>VEER CORPORATIONS INC</t>
+        </is>
+      </c>
+      <c r="K382" t="inlineStr">
+        <is>
+          <t>VEECOR01</t>
+        </is>
+      </c>
+      <c r="L382" t="inlineStr">
+        <is>
+          <t>99-106989200</t>
+        </is>
+      </c>
+      <c r="M382" t="inlineStr">
+        <is>
+          <t>2026-06-24 00:00:00</t>
+        </is>
+      </c>
+      <c r="N382" t="inlineStr">
+        <is>
+          <t>2026-06-24 00:00:00</t>
+        </is>
+      </c>
+      <c r="O382" t="inlineStr">
+        <is>
+          <t>VEER PLASTIC PVT LTD</t>
+        </is>
+      </c>
+      <c r="P382" t="inlineStr">
+        <is>
+          <t>VEER PLASTIC PVT LTD</t>
+        </is>
+      </c>
+      <c r="Q382" t="inlineStr">
+        <is>
+          <t>2026-05-10 00:00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="383">
+      <c r="A383" t="inlineStr">
+        <is>
+          <t>2565829</t>
+        </is>
+      </c>
+      <c r="B383" t="inlineStr">
+        <is>
+          <t>EF4-0231713-7</t>
+        </is>
+      </c>
+      <c r="C383" t="inlineStr">
+        <is>
+          <t>Vessel, Container</t>
+        </is>
+      </c>
+      <c r="D383" t="inlineStr"/>
+      <c r="E383" t="inlineStr">
+        <is>
+          <t>9903.03.01</t>
+        </is>
+      </c>
+      <c r="F383" t="inlineStr">
+        <is>
+          <t>SECTION 122 - 10% DUTY</t>
+        </is>
+      </c>
+      <c r="G383" t="inlineStr">
+        <is>
+          <t>001</t>
+        </is>
+      </c>
+      <c r="H383" t="inlineStr">
+        <is>
+          <t>9903.03.01</t>
+        </is>
+      </c>
+      <c r="I383" t="inlineStr">
+        <is>
+          <t>5407.20.0000</t>
+        </is>
+      </c>
+      <c r="J383" t="inlineStr">
+        <is>
+          <t>VEER CORPORATIONS INC</t>
+        </is>
+      </c>
+      <c r="K383" t="inlineStr">
+        <is>
+          <t>VEECOR01</t>
+        </is>
+      </c>
+      <c r="L383" t="inlineStr">
+        <is>
+          <t>99-106989200</t>
+        </is>
+      </c>
+      <c r="M383" t="inlineStr">
+        <is>
+          <t>2026-06-24 00:00:00</t>
+        </is>
+      </c>
+      <c r="N383" t="inlineStr">
+        <is>
+          <t>2026-06-24 00:00:00</t>
+        </is>
+      </c>
+      <c r="O383" t="inlineStr">
+        <is>
+          <t>VEER PLASTIC PVT LTD</t>
+        </is>
+      </c>
+      <c r="P383" t="inlineStr">
+        <is>
+          <t>VEER PLASTIC PVT LTD</t>
+        </is>
+      </c>
+      <c r="Q383" t="inlineStr">
+        <is>
+          <t>2026-05-10 00:00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="384">
+      <c r="A384" t="inlineStr">
+        <is>
+          <t>2565908</t>
+        </is>
+      </c>
+      <c r="B384" t="inlineStr">
+        <is>
+          <t>EF4-0232026-3</t>
+        </is>
+      </c>
+      <c r="C384" t="inlineStr">
+        <is>
+          <t>Vessel, Container</t>
+        </is>
+      </c>
+      <c r="D384" t="inlineStr"/>
+      <c r="E384" t="inlineStr">
+        <is>
+          <t>9903.03.06</t>
+        </is>
+      </c>
+      <c r="F384" t="inlineStr">
+        <is>
+          <t>S122 EXCL,IRN/STL/ALUM,DERIV</t>
+        </is>
+      </c>
+      <c r="G384" t="inlineStr">
+        <is>
+          <t>001</t>
+        </is>
+      </c>
+      <c r="H384" t="inlineStr">
+        <is>
+          <t>9903.03.06</t>
+        </is>
+      </c>
+      <c r="I384" t="inlineStr">
+        <is>
+          <t>9903.82.02,7223.00.1061</t>
+        </is>
+      </c>
+      <c r="J384" t="inlineStr">
+        <is>
+          <t>VENUS WIRE INDUSTRIES PRIVATE LTD</t>
+        </is>
+      </c>
+      <c r="K384" t="inlineStr">
+        <is>
+          <t>VENWIR</t>
+        </is>
+      </c>
+      <c r="L384" t="inlineStr">
+        <is>
+          <t>993901-03595</t>
+        </is>
+      </c>
+      <c r="M384" t="inlineStr">
+        <is>
+          <t>2026-06-24 00:00:00</t>
+        </is>
+      </c>
+      <c r="N384" t="inlineStr">
+        <is>
+          <t>2026-06-24 00:00:00</t>
+        </is>
+      </c>
+      <c r="O384" t="inlineStr">
+        <is>
+          <t>PRECISION METALS</t>
+        </is>
+      </c>
+      <c r="P384" t="inlineStr">
+        <is>
+          <t>PRECISION METALS</t>
+        </is>
+      </c>
+      <c r="Q384" t="inlineStr">
+        <is>
+          <t>2026-05-09 00:00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="385">
+      <c r="A385" t="inlineStr">
+        <is>
+          <t>2566016</t>
+        </is>
+      </c>
+      <c r="B385" t="inlineStr">
+        <is>
+          <t>EF4-0232063-6</t>
+        </is>
+      </c>
+      <c r="C385" t="inlineStr">
+        <is>
+          <t>Vessel, Container</t>
+        </is>
+      </c>
+      <c r="D385" t="inlineStr"/>
+      <c r="E385" t="inlineStr">
+        <is>
+          <t>9903.03.01</t>
+        </is>
+      </c>
+      <c r="F385" t="inlineStr">
+        <is>
+          <t>SECTION 122 - 10% DUTY</t>
+        </is>
+      </c>
+      <c r="G385" t="inlineStr">
+        <is>
+          <t>001</t>
+        </is>
+      </c>
+      <c r="H385" t="inlineStr">
+        <is>
+          <t>9903.03.01</t>
+        </is>
+      </c>
+      <c r="I385" t="inlineStr">
+        <is>
+          <t>1108.13.0010</t>
+        </is>
+      </c>
+      <c r="J385" t="inlineStr">
+        <is>
+          <t>ROYAL INGREDIENTS GROUP BV</t>
+        </is>
+      </c>
+      <c r="K385" t="inlineStr">
+        <is>
+          <t>ROYINGRE</t>
+        </is>
+      </c>
+      <c r="L385" t="inlineStr">
+        <is>
+          <t>074601-00962</t>
+        </is>
+      </c>
+      <c r="M385" t="inlineStr">
+        <is>
+          <t>2026-06-24 00:00:00</t>
+        </is>
+      </c>
+      <c r="N385" t="inlineStr">
+        <is>
+          <t>2026-06-24 00:00:00</t>
+        </is>
+      </c>
+      <c r="O385" t="inlineStr">
+        <is>
+          <t>AKV LANGHOLT AMBA</t>
+        </is>
+      </c>
+      <c r="P385" t="inlineStr">
+        <is>
+          <t>AKV LANGHOLT AMBA</t>
+        </is>
+      </c>
+      <c r="Q385" t="inlineStr">
+        <is>
+          <t>2026-05-24 00:00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="386">
+      <c r="A386" t="inlineStr">
+        <is>
+          <t>2566041</t>
+        </is>
+      </c>
+      <c r="B386" t="inlineStr">
+        <is>
+          <t>EF4-0232085-9</t>
+        </is>
+      </c>
+      <c r="C386" t="inlineStr">
+        <is>
+          <t>Vessel, Container</t>
+        </is>
+      </c>
+      <c r="D386" t="inlineStr"/>
+      <c r="E386" t="inlineStr">
+        <is>
+          <t>9903.88.15</t>
+        </is>
+      </c>
+      <c r="F386" t="inlineStr">
+        <is>
+          <t>ARTICLE OF CHINA,US NTE 20(R)</t>
+        </is>
+      </c>
+      <c r="G386" t="inlineStr">
+        <is>
+          <t>001</t>
+        </is>
+      </c>
+      <c r="H386" t="inlineStr">
+        <is>
+          <t>9903.88.15</t>
+        </is>
+      </c>
+      <c r="I386" t="inlineStr">
+        <is>
+          <t>9903.03.06,9903.82.09,8302.42.3015</t>
+        </is>
+      </c>
+      <c r="J386" t="inlineStr">
+        <is>
+          <t>GRASS AMERICA INC</t>
+        </is>
+      </c>
+      <c r="K386" t="inlineStr">
+        <is>
+          <t>GRAAME</t>
+        </is>
+      </c>
+      <c r="L386" t="inlineStr">
+        <is>
+          <t>51-066023000</t>
+        </is>
+      </c>
+      <c r="M386" t="inlineStr">
+        <is>
+          <t>2026-06-24 00:00:00</t>
+        </is>
+      </c>
+      <c r="N386" t="inlineStr">
+        <is>
+          <t>2026-06-24 00:00:00</t>
+        </is>
+      </c>
+      <c r="O386" t="inlineStr">
+        <is>
+          <t>SACA PRECISION LTD</t>
+        </is>
+      </c>
+      <c r="P386" t="inlineStr">
+        <is>
+          <t>SACA PRECISION LTD</t>
+        </is>
+      </c>
+      <c r="Q386" t="inlineStr">
+        <is>
+          <t>2026-05-21 00:00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="387">
+      <c r="A387" t="inlineStr">
+        <is>
+          <t>2565946</t>
+        </is>
+      </c>
+      <c r="B387" t="inlineStr">
+        <is>
+          <t>EF4-0232241-8</t>
+        </is>
+      </c>
+      <c r="C387" t="inlineStr">
+        <is>
+          <t>Vessel, Container</t>
+        </is>
+      </c>
+      <c r="D387" t="inlineStr">
+        <is>
+          <t>V1626464484</t>
+        </is>
+      </c>
+      <c r="E387" t="inlineStr">
+        <is>
+          <t>9903.03.01</t>
+        </is>
+      </c>
+      <c r="F387" t="inlineStr"/>
+      <c r="G387" t="inlineStr">
+        <is>
+          <t>001</t>
+        </is>
+      </c>
+      <c r="H387" t="inlineStr">
+        <is>
+          <t>9903.03.01</t>
+        </is>
+      </c>
+      <c r="I387" t="inlineStr">
+        <is>
+          <t>1108.13.0010</t>
+        </is>
+      </c>
+      <c r="J387" t="inlineStr">
+        <is>
+          <t>ROYAL INGREDIENTS GROUP BV</t>
+        </is>
+      </c>
+      <c r="K387" t="inlineStr">
+        <is>
+          <t>ROYINGRE</t>
+        </is>
+      </c>
+      <c r="L387" t="inlineStr">
+        <is>
+          <t>074601-00962</t>
+        </is>
+      </c>
+      <c r="M387" t="inlineStr">
+        <is>
+          <t>2026-06-24 00:00:00</t>
+        </is>
+      </c>
+      <c r="N387" t="inlineStr">
+        <is>
+          <t>2026-06-24 00:00:00</t>
+        </is>
+      </c>
+      <c r="O387" t="inlineStr">
+        <is>
+          <t>PRZEDSIEBIORSTWO PRZEMYSLU ZIEMNIAC</t>
+        </is>
+      </c>
+      <c r="P387" t="inlineStr">
+        <is>
+          <t>PRZEDSIEBIORSTWO PRZEMYSLU ZIEMNIACZANEGO PEPEES S.A.</t>
+        </is>
+      </c>
+      <c r="Q387" t="inlineStr">
+        <is>
+          <t>2026-05-31 00:00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="388">
+      <c r="A388" t="inlineStr">
+        <is>
+          <t>4539555</t>
+        </is>
+      </c>
+      <c r="B388" t="inlineStr">
+        <is>
+          <t>EF4-0232777-1</t>
+        </is>
+      </c>
+      <c r="C388" t="inlineStr">
+        <is>
+          <t>Air, Non-container</t>
+        </is>
+      </c>
+      <c r="D388" t="inlineStr">
+        <is>
+          <t>V1626464484</t>
+        </is>
+      </c>
+      <c r="E388" t="inlineStr">
+        <is>
+          <t>9903.03.01</t>
+        </is>
+      </c>
+      <c r="F388" t="inlineStr">
+        <is>
+          <t>SECTION 122 - 10% DUTY</t>
+        </is>
+      </c>
+      <c r="G388" t="inlineStr">
+        <is>
+          <t>001</t>
+        </is>
+      </c>
+      <c r="H388" t="inlineStr">
+        <is>
+          <t>9903.03.01</t>
+        </is>
+      </c>
+      <c r="I388" t="inlineStr">
+        <is>
+          <t>3926.90.6090</t>
+        </is>
+      </c>
+      <c r="J388" t="inlineStr">
+        <is>
+          <t>ESBAND USA INC</t>
+        </is>
+      </c>
+      <c r="K388" t="inlineStr">
+        <is>
+          <t>ESBUSA01</t>
+        </is>
+      </c>
+      <c r="L388" t="inlineStr">
+        <is>
+          <t>87-443503100</t>
+        </is>
+      </c>
+      <c r="M388" t="inlineStr">
+        <is>
+          <t>2026-06-20 00:00:00</t>
+        </is>
+      </c>
+      <c r="N388" t="inlineStr">
+        <is>
+          <t>2026-06-24 00:00:00</t>
+        </is>
+      </c>
+      <c r="O388" t="inlineStr">
+        <is>
+          <t>MAX SCHLATTERER</t>
+        </is>
+      </c>
+      <c r="P388" t="inlineStr">
+        <is>
+          <t>MAX SCHLATTERER</t>
+        </is>
+      </c>
+      <c r="Q388" t="inlineStr">
+        <is>
+          <t>2026-06-20 00:00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="389">
+      <c r="A389" t="inlineStr">
+        <is>
+          <t>4539555</t>
+        </is>
+      </c>
+      <c r="B389" t="inlineStr">
+        <is>
+          <t>EF4-0232777-1</t>
+        </is>
+      </c>
+      <c r="C389" t="inlineStr">
+        <is>
+          <t>Air, Non-container</t>
+        </is>
+      </c>
+      <c r="D389" t="inlineStr">
+        <is>
+          <t>V1626464484</t>
+        </is>
+      </c>
+      <c r="E389" t="inlineStr">
+        <is>
+          <t>9903.03.01</t>
+        </is>
+      </c>
+      <c r="F389" t="inlineStr">
+        <is>
+          <t>SECTION 122 - 10% DUTY</t>
+        </is>
+      </c>
+      <c r="G389" t="inlineStr">
+        <is>
+          <t>002</t>
+        </is>
+      </c>
+      <c r="H389" t="inlineStr">
+        <is>
+          <t>9903.03.01</t>
+        </is>
+      </c>
+      <c r="I389" t="inlineStr">
+        <is>
+          <t>4010.35.9000</t>
+        </is>
+      </c>
+      <c r="J389" t="inlineStr">
+        <is>
+          <t>ESBAND USA INC</t>
+        </is>
+      </c>
+      <c r="K389" t="inlineStr">
+        <is>
+          <t>ESBUSA01</t>
+        </is>
+      </c>
+      <c r="L389" t="inlineStr">
+        <is>
+          <t>87-443503100</t>
+        </is>
+      </c>
+      <c r="M389" t="inlineStr">
+        <is>
+          <t>2026-06-20 00:00:00</t>
+        </is>
+      </c>
+      <c r="N389" t="inlineStr">
+        <is>
+          <t>2026-06-24 00:00:00</t>
+        </is>
+      </c>
+      <c r="O389" t="inlineStr">
+        <is>
+          <t>MAX SCHLATTERER</t>
+        </is>
+      </c>
+      <c r="P389" t="inlineStr">
+        <is>
+          <t>MAX SCHLATTERER</t>
+        </is>
+      </c>
+      <c r="Q389" t="inlineStr">
+        <is>
+          <t>2026-06-20 00:00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="390">
+      <c r="A390" t="inlineStr">
+        <is>
+          <t>4539555</t>
+        </is>
+      </c>
+      <c r="B390" t="inlineStr">
+        <is>
+          <t>EF4-0232777-1</t>
+        </is>
+      </c>
+      <c r="C390" t="inlineStr">
+        <is>
+          <t>Air, Non-container</t>
+        </is>
+      </c>
+      <c r="D390" t="inlineStr">
+        <is>
+          <t>V1626464484</t>
+        </is>
+      </c>
+      <c r="E390" t="inlineStr">
+        <is>
+          <t>9903.03.01</t>
+        </is>
+      </c>
+      <c r="F390" t="inlineStr">
+        <is>
+          <t>SECTION 122 - 10% DUTY</t>
+        </is>
+      </c>
+      <c r="G390" t="inlineStr">
+        <is>
+          <t>003</t>
+        </is>
+      </c>
+      <c r="H390" t="inlineStr">
+        <is>
+          <t>9903.03.01</t>
+        </is>
+      </c>
+      <c r="I390" t="inlineStr">
+        <is>
+          <t>5910.00.1090</t>
+        </is>
+      </c>
+      <c r="J390" t="inlineStr">
+        <is>
+          <t>ESBAND USA INC</t>
+        </is>
+      </c>
+      <c r="K390" t="inlineStr">
+        <is>
+          <t>ESBUSA01</t>
+        </is>
+      </c>
+      <c r="L390" t="inlineStr">
+        <is>
+          <t>87-443503100</t>
+        </is>
+      </c>
+      <c r="M390" t="inlineStr">
+        <is>
+          <t>2026-06-20 00:00:00</t>
+        </is>
+      </c>
+      <c r="N390" t="inlineStr">
+        <is>
+          <t>2026-06-24 00:00:00</t>
+        </is>
+      </c>
+      <c r="O390" t="inlineStr">
+        <is>
+          <t>MAX SCHLATTERER</t>
+        </is>
+      </c>
+      <c r="P390" t="inlineStr">
+        <is>
+          <t>MAX SCHLATTERER</t>
+        </is>
+      </c>
+      <c r="Q390" t="inlineStr">
+        <is>
+          <t>2026-06-20 00:00:00</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/trimika_data.xlsx
+++ b/trimika_data.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q390"/>
+  <dimension ref="A1:Q412"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -33074,6 +33074,1808 @@
         </is>
       </c>
     </row>
+    <row r="391">
+      <c r="A391" t="inlineStr">
+        <is>
+          <t>2565903</t>
+        </is>
+      </c>
+      <c r="B391" t="inlineStr">
+        <is>
+          <t>EF4-0231899-4</t>
+        </is>
+      </c>
+      <c r="C391" t="inlineStr">
+        <is>
+          <t>Vessel, Container</t>
+        </is>
+      </c>
+      <c r="D391" t="inlineStr"/>
+      <c r="E391" t="inlineStr">
+        <is>
+          <t>9903.03.01</t>
+        </is>
+      </c>
+      <c r="F391" t="inlineStr">
+        <is>
+          <t>SECTION 122 - 10% DUTY</t>
+        </is>
+      </c>
+      <c r="G391" t="inlineStr">
+        <is>
+          <t>001</t>
+        </is>
+      </c>
+      <c r="H391" t="inlineStr">
+        <is>
+          <t>9903.03.01</t>
+        </is>
+      </c>
+      <c r="I391" t="inlineStr">
+        <is>
+          <t>5903.90.3090</t>
+        </is>
+      </c>
+      <c r="J391" t="inlineStr">
+        <is>
+          <t>VEER CORPORATIONS INC</t>
+        </is>
+      </c>
+      <c r="K391" t="inlineStr">
+        <is>
+          <t>VEECOR01</t>
+        </is>
+      </c>
+      <c r="L391" t="inlineStr">
+        <is>
+          <t>99-106989200</t>
+        </is>
+      </c>
+      <c r="M391" t="inlineStr">
+        <is>
+          <t>2026-06-25 00:00:00</t>
+        </is>
+      </c>
+      <c r="N391" t="inlineStr">
+        <is>
+          <t>2026-06-25 00:00:00</t>
+        </is>
+      </c>
+      <c r="O391" t="inlineStr">
+        <is>
+          <t>VEER PLASTIC PVT LTD</t>
+        </is>
+      </c>
+      <c r="P391" t="inlineStr">
+        <is>
+          <t>VEER PLASTIC PVT LTD</t>
+        </is>
+      </c>
+      <c r="Q391" t="inlineStr">
+        <is>
+          <t>2026-05-14 00:00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="392">
+      <c r="A392" t="inlineStr">
+        <is>
+          <t>2566026</t>
+        </is>
+      </c>
+      <c r="B392" t="inlineStr">
+        <is>
+          <t>EF4-0232031-3</t>
+        </is>
+      </c>
+      <c r="C392" t="inlineStr">
+        <is>
+          <t>Vessel, Container</t>
+        </is>
+      </c>
+      <c r="D392" t="inlineStr">
+        <is>
+          <t>V2108743882</t>
+        </is>
+      </c>
+      <c r="E392" t="inlineStr">
+        <is>
+          <t>9903.03.01</t>
+        </is>
+      </c>
+      <c r="F392" t="inlineStr">
+        <is>
+          <t>SECTION 122 - 10% DUTY</t>
+        </is>
+      </c>
+      <c r="G392" t="inlineStr">
+        <is>
+          <t>001</t>
+        </is>
+      </c>
+      <c r="H392" t="inlineStr">
+        <is>
+          <t>9903.03.01</t>
+        </is>
+      </c>
+      <c r="I392" t="inlineStr">
+        <is>
+          <t>8436.80.0020</t>
+        </is>
+      </c>
+      <c r="J392" t="inlineStr">
+        <is>
+          <t>MDE MACHINERY INC</t>
+        </is>
+      </c>
+      <c r="K392" t="inlineStr">
+        <is>
+          <t>MDEMAC02</t>
+        </is>
+      </c>
+      <c r="L392" t="inlineStr">
+        <is>
+          <t>38-438331300</t>
+        </is>
+      </c>
+      <c r="M392" t="inlineStr">
+        <is>
+          <t>2026-06-17 00:00:00</t>
+        </is>
+      </c>
+      <c r="N392" t="inlineStr">
+        <is>
+          <t>2026-06-25 00:00:00</t>
+        </is>
+      </c>
+      <c r="O392" t="inlineStr">
+        <is>
+          <t>MDE MACHINERY LTD</t>
+        </is>
+      </c>
+      <c r="P392" t="inlineStr">
+        <is>
+          <t>MDE MACHINERY LTD</t>
+        </is>
+      </c>
+      <c r="Q392" t="inlineStr">
+        <is>
+          <t>2026-05-19 00:00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="393">
+      <c r="A393" t="inlineStr">
+        <is>
+          <t>2565097</t>
+        </is>
+      </c>
+      <c r="B393" t="inlineStr">
+        <is>
+          <t>EF4-0232240-0</t>
+        </is>
+      </c>
+      <c r="C393" t="inlineStr">
+        <is>
+          <t>Vessel, Container</t>
+        </is>
+      </c>
+      <c r="D393" t="inlineStr">
+        <is>
+          <t>V2108743882</t>
+        </is>
+      </c>
+      <c r="E393" t="inlineStr">
+        <is>
+          <t>9903.03.01</t>
+        </is>
+      </c>
+      <c r="F393" t="inlineStr"/>
+      <c r="G393" t="inlineStr">
+        <is>
+          <t>001</t>
+        </is>
+      </c>
+      <c r="H393" t="inlineStr">
+        <is>
+          <t>9903.03.01</t>
+        </is>
+      </c>
+      <c r="I393" t="inlineStr">
+        <is>
+          <t>1108.12.0010</t>
+        </is>
+      </c>
+      <c r="J393" t="inlineStr">
+        <is>
+          <t>ROYAL INGREDIENTS GROUP BV</t>
+        </is>
+      </c>
+      <c r="K393" t="inlineStr">
+        <is>
+          <t>ROYINGRE</t>
+        </is>
+      </c>
+      <c r="L393" t="inlineStr">
+        <is>
+          <t>074601-00962</t>
+        </is>
+      </c>
+      <c r="M393" t="inlineStr">
+        <is>
+          <t>2026-06-25 00:00:00</t>
+        </is>
+      </c>
+      <c r="N393" t="inlineStr">
+        <is>
+          <t>2026-06-25 00:00:00</t>
+        </is>
+      </c>
+      <c r="O393" t="inlineStr">
+        <is>
+          <t>TAT NISASTA INS SAN TIC AS</t>
+        </is>
+      </c>
+      <c r="P393" t="inlineStr">
+        <is>
+          <t>TAT NISASTA INS SAN TIC AS</t>
+        </is>
+      </c>
+      <c r="Q393" t="inlineStr">
+        <is>
+          <t>2026-03-16 00:00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="394">
+      <c r="A394" t="inlineStr">
+        <is>
+          <t>2566241</t>
+        </is>
+      </c>
+      <c r="B394" t="inlineStr">
+        <is>
+          <t>EF4-0232379-6</t>
+        </is>
+      </c>
+      <c r="C394" t="inlineStr">
+        <is>
+          <t>Vessel, Container</t>
+        </is>
+      </c>
+      <c r="D394" t="inlineStr"/>
+      <c r="E394" t="inlineStr">
+        <is>
+          <t>9903.03.01</t>
+        </is>
+      </c>
+      <c r="F394" t="inlineStr">
+        <is>
+          <t>SECTION 122 - 10% DUTY</t>
+        </is>
+      </c>
+      <c r="G394" t="inlineStr">
+        <is>
+          <t>001</t>
+        </is>
+      </c>
+      <c r="H394" t="inlineStr">
+        <is>
+          <t>9903.03.01</t>
+        </is>
+      </c>
+      <c r="I394" t="inlineStr">
+        <is>
+          <t>6913.90.1000</t>
+        </is>
+      </c>
+      <c r="J394" t="inlineStr">
+        <is>
+          <t>MESO CASA LLC</t>
+        </is>
+      </c>
+      <c r="K394" t="inlineStr">
+        <is>
+          <t>MESCAS01</t>
+        </is>
+      </c>
+      <c r="L394" t="inlineStr">
+        <is>
+          <t>93-375253000</t>
+        </is>
+      </c>
+      <c r="M394" t="inlineStr">
+        <is>
+          <t>2026-06-18 00:00:00</t>
+        </is>
+      </c>
+      <c r="N394" t="inlineStr">
+        <is>
+          <t>2026-06-25 00:00:00</t>
+        </is>
+      </c>
+      <c r="O394" t="inlineStr">
+        <is>
+          <t>ATUTO S DE R.L.</t>
+        </is>
+      </c>
+      <c r="P394" t="inlineStr">
+        <is>
+          <t>ATUTO S DE R.L.</t>
+        </is>
+      </c>
+      <c r="Q394" t="inlineStr">
+        <is>
+          <t>2026-06-05 00:00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="395">
+      <c r="A395" t="inlineStr">
+        <is>
+          <t>2566241</t>
+        </is>
+      </c>
+      <c r="B395" t="inlineStr">
+        <is>
+          <t>EF4-0232379-6</t>
+        </is>
+      </c>
+      <c r="C395" t="inlineStr">
+        <is>
+          <t>Vessel, Container</t>
+        </is>
+      </c>
+      <c r="D395" t="inlineStr"/>
+      <c r="E395" t="inlineStr">
+        <is>
+          <t>9903.03.01</t>
+        </is>
+      </c>
+      <c r="F395" t="inlineStr">
+        <is>
+          <t>SECTION 122 - 10% DUTY</t>
+        </is>
+      </c>
+      <c r="G395" t="inlineStr">
+        <is>
+          <t>002</t>
+        </is>
+      </c>
+      <c r="H395" t="inlineStr">
+        <is>
+          <t>9903.03.01</t>
+        </is>
+      </c>
+      <c r="I395" t="inlineStr">
+        <is>
+          <t>4420.11.0090</t>
+        </is>
+      </c>
+      <c r="J395" t="inlineStr">
+        <is>
+          <t>MESO CASA LLC</t>
+        </is>
+      </c>
+      <c r="K395" t="inlineStr">
+        <is>
+          <t>MESCAS01</t>
+        </is>
+      </c>
+      <c r="L395" t="inlineStr">
+        <is>
+          <t>93-375253000</t>
+        </is>
+      </c>
+      <c r="M395" t="inlineStr">
+        <is>
+          <t>2026-06-18 00:00:00</t>
+        </is>
+      </c>
+      <c r="N395" t="inlineStr">
+        <is>
+          <t>2026-06-25 00:00:00</t>
+        </is>
+      </c>
+      <c r="O395" t="inlineStr">
+        <is>
+          <t>ATUTO S DE R.L.</t>
+        </is>
+      </c>
+      <c r="P395" t="inlineStr">
+        <is>
+          <t>ATUTO S DE R.L.</t>
+        </is>
+      </c>
+      <c r="Q395" t="inlineStr">
+        <is>
+          <t>2026-06-05 00:00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="396">
+      <c r="A396" t="inlineStr">
+        <is>
+          <t>2566258</t>
+        </is>
+      </c>
+      <c r="B396" t="inlineStr">
+        <is>
+          <t>EF4-0232463-8</t>
+        </is>
+      </c>
+      <c r="C396" t="inlineStr">
+        <is>
+          <t>Vessel, Container</t>
+        </is>
+      </c>
+      <c r="D396" t="inlineStr"/>
+      <c r="E396" t="inlineStr">
+        <is>
+          <t>9903.03.01</t>
+        </is>
+      </c>
+      <c r="F396" t="inlineStr">
+        <is>
+          <t>SECTION 122 - 10% DUTY</t>
+        </is>
+      </c>
+      <c r="G396" t="inlineStr">
+        <is>
+          <t>001</t>
+        </is>
+      </c>
+      <c r="H396" t="inlineStr">
+        <is>
+          <t>9903.03.01</t>
+        </is>
+      </c>
+      <c r="I396" t="inlineStr">
+        <is>
+          <t>3920.61.0000</t>
+        </is>
+      </c>
+      <c r="J396" t="inlineStr">
+        <is>
+          <t>TUBUS BAUER GMBH</t>
+        </is>
+      </c>
+      <c r="K396" t="inlineStr">
+        <is>
+          <t>TUBBAU01</t>
+        </is>
+      </c>
+      <c r="L396" t="inlineStr">
+        <is>
+          <t>091601-00584</t>
+        </is>
+      </c>
+      <c r="M396" t="inlineStr">
+        <is>
+          <t>2026-06-25 00:00:00</t>
+        </is>
+      </c>
+      <c r="N396" t="inlineStr">
+        <is>
+          <t>2026-06-25 00:00:00</t>
+        </is>
+      </c>
+      <c r="O396" t="inlineStr">
+        <is>
+          <t>TUBUS BAUER GMBH</t>
+        </is>
+      </c>
+      <c r="P396" t="inlineStr">
+        <is>
+          <t>TUBUS BAUER GMBH</t>
+        </is>
+      </c>
+      <c r="Q396" t="inlineStr">
+        <is>
+          <t>2026-06-09 00:00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="397">
+      <c r="A397" t="inlineStr">
+        <is>
+          <t>105504778</t>
+        </is>
+      </c>
+      <c r="B397" t="inlineStr">
+        <is>
+          <t>EF4-0232476-0</t>
+        </is>
+      </c>
+      <c r="C397" t="inlineStr">
+        <is>
+          <t>Vessel, Non-container</t>
+        </is>
+      </c>
+      <c r="D397" t="inlineStr"/>
+      <c r="E397" t="inlineStr">
+        <is>
+          <t>9805.00.50</t>
+        </is>
+      </c>
+      <c r="F397" t="inlineStr">
+        <is>
+          <t>EFFECTS US GOV EMP&amp;FAMLY/EVACU</t>
+        </is>
+      </c>
+      <c r="G397" t="inlineStr">
+        <is>
+          <t>001</t>
+        </is>
+      </c>
+      <c r="H397" t="inlineStr">
+        <is>
+          <t>9805.00.50</t>
+        </is>
+      </c>
+      <c r="I397" t="inlineStr"/>
+      <c r="J397" t="inlineStr">
+        <is>
+          <t>IFF, INC.</t>
+        </is>
+      </c>
+      <c r="K397" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="L397" t="inlineStr">
+        <is>
+          <t>58-149385700</t>
+        </is>
+      </c>
+      <c r="M397" t="inlineStr">
+        <is>
+          <t>2026-06-26 00:00:00</t>
+        </is>
+      </c>
+      <c r="N397" t="inlineStr">
+        <is>
+          <t>2026-06-25 00:00:00</t>
+        </is>
+      </c>
+      <c r="O397" t="inlineStr">
+        <is>
+          <t>VOLVO CAR INTERNATIONAL CORPORATION</t>
+        </is>
+      </c>
+      <c r="P397" t="inlineStr">
+        <is>
+          <t>VOLVO CAR INTERNATIONAL CORPORATION</t>
+        </is>
+      </c>
+      <c r="Q397" t="inlineStr">
+        <is>
+          <t>2026-06-12 00:00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="398">
+      <c r="A398" t="inlineStr">
+        <is>
+          <t>105504780</t>
+        </is>
+      </c>
+      <c r="B398" t="inlineStr">
+        <is>
+          <t>EF4-0232486-9</t>
+        </is>
+      </c>
+      <c r="C398" t="inlineStr">
+        <is>
+          <t>Vessel, Non-container</t>
+        </is>
+      </c>
+      <c r="D398" t="inlineStr"/>
+      <c r="E398" t="inlineStr">
+        <is>
+          <t>9805.00.50</t>
+        </is>
+      </c>
+      <c r="F398" t="inlineStr">
+        <is>
+          <t>EFFECTS US GOV EMP&amp;FAMLY/EVACU</t>
+        </is>
+      </c>
+      <c r="G398" t="inlineStr">
+        <is>
+          <t>001</t>
+        </is>
+      </c>
+      <c r="H398" t="inlineStr">
+        <is>
+          <t>9805.00.50</t>
+        </is>
+      </c>
+      <c r="I398" t="inlineStr"/>
+      <c r="J398" t="inlineStr">
+        <is>
+          <t>IFF, INC.</t>
+        </is>
+      </c>
+      <c r="K398" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="L398" t="inlineStr">
+        <is>
+          <t>58-149385700</t>
+        </is>
+      </c>
+      <c r="M398" t="inlineStr">
+        <is>
+          <t>2026-06-26 00:00:00</t>
+        </is>
+      </c>
+      <c r="N398" t="inlineStr">
+        <is>
+          <t>2026-06-25 00:00:00</t>
+        </is>
+      </c>
+      <c r="O398" t="inlineStr">
+        <is>
+          <t>VOLVO CAR INTERNATIONAL CORPORATION</t>
+        </is>
+      </c>
+      <c r="P398" t="inlineStr">
+        <is>
+          <t>VOLVO CAR INTERNATIONAL CORPORATION</t>
+        </is>
+      </c>
+      <c r="Q398" t="inlineStr">
+        <is>
+          <t>2026-06-16 00:00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="399">
+      <c r="A399" t="inlineStr">
+        <is>
+          <t>2566249</t>
+        </is>
+      </c>
+      <c r="B399" t="inlineStr">
+        <is>
+          <t>EF4-0232524-7</t>
+        </is>
+      </c>
+      <c r="C399" t="inlineStr">
+        <is>
+          <t>Vessel, Container</t>
+        </is>
+      </c>
+      <c r="D399" t="inlineStr"/>
+      <c r="E399" t="inlineStr">
+        <is>
+          <t>9903.03.06</t>
+        </is>
+      </c>
+      <c r="F399" t="inlineStr">
+        <is>
+          <t>S122 EXCL,IRN/STL/ALUM,DERIV</t>
+        </is>
+      </c>
+      <c r="G399" t="inlineStr">
+        <is>
+          <t>001</t>
+        </is>
+      </c>
+      <c r="H399" t="inlineStr">
+        <is>
+          <t>9903.03.06</t>
+        </is>
+      </c>
+      <c r="I399" t="inlineStr">
+        <is>
+          <t>9903.74.11,9903.94.53,8708.29.5160</t>
+        </is>
+      </c>
+      <c r="J399" t="inlineStr">
+        <is>
+          <t>BORGERS USA CORP</t>
+        </is>
+      </c>
+      <c r="K399" t="inlineStr">
+        <is>
+          <t>BORUSA</t>
+        </is>
+      </c>
+      <c r="L399" t="inlineStr">
+        <is>
+          <t>65-117296500</t>
+        </is>
+      </c>
+      <c r="M399" t="inlineStr">
+        <is>
+          <t>2026-06-27 00:00:00</t>
+        </is>
+      </c>
+      <c r="N399" t="inlineStr">
+        <is>
+          <t>2026-06-25 00:00:00</t>
+        </is>
+      </c>
+      <c r="O399" t="inlineStr">
+        <is>
+          <t>AUTONEUM CZ S.R.O.</t>
+        </is>
+      </c>
+      <c r="P399" t="inlineStr">
+        <is>
+          <t>AUTONEUM CZ S.R.O.</t>
+        </is>
+      </c>
+      <c r="Q399" t="inlineStr">
+        <is>
+          <t>2026-06-14 00:00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="400">
+      <c r="A400" t="inlineStr">
+        <is>
+          <t>2566249</t>
+        </is>
+      </c>
+      <c r="B400" t="inlineStr">
+        <is>
+          <t>EF4-0232524-7</t>
+        </is>
+      </c>
+      <c r="C400" t="inlineStr">
+        <is>
+          <t>Vessel, Container</t>
+        </is>
+      </c>
+      <c r="D400" t="inlineStr"/>
+      <c r="E400" t="inlineStr">
+        <is>
+          <t>9903.03.06</t>
+        </is>
+      </c>
+      <c r="F400" t="inlineStr">
+        <is>
+          <t>S122 EXCL,IRN/STL/ALUM,DERIV</t>
+        </is>
+      </c>
+      <c r="G400" t="inlineStr">
+        <is>
+          <t>002</t>
+        </is>
+      </c>
+      <c r="H400" t="inlineStr">
+        <is>
+          <t>9903.03.06</t>
+        </is>
+      </c>
+      <c r="I400" t="inlineStr">
+        <is>
+          <t>9903.74.11,9903.94.53,8708.29.5160</t>
+        </is>
+      </c>
+      <c r="J400" t="inlineStr">
+        <is>
+          <t>BORGERS USA CORP</t>
+        </is>
+      </c>
+      <c r="K400" t="inlineStr">
+        <is>
+          <t>BORUSA</t>
+        </is>
+      </c>
+      <c r="L400" t="inlineStr">
+        <is>
+          <t>65-117296500</t>
+        </is>
+      </c>
+      <c r="M400" t="inlineStr">
+        <is>
+          <t>2026-06-27 00:00:00</t>
+        </is>
+      </c>
+      <c r="N400" t="inlineStr">
+        <is>
+          <t>2026-06-25 00:00:00</t>
+        </is>
+      </c>
+      <c r="O400" t="inlineStr">
+        <is>
+          <t>AUTONEUM CZ S.R.O.</t>
+        </is>
+      </c>
+      <c r="P400" t="inlineStr">
+        <is>
+          <t>AUTONEUM CZ S.R.O.</t>
+        </is>
+      </c>
+      <c r="Q400" t="inlineStr">
+        <is>
+          <t>2026-06-14 00:00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="401">
+      <c r="A401" t="inlineStr">
+        <is>
+          <t>2566249</t>
+        </is>
+      </c>
+      <c r="B401" t="inlineStr">
+        <is>
+          <t>EF4-0232524-7</t>
+        </is>
+      </c>
+      <c r="C401" t="inlineStr">
+        <is>
+          <t>Vessel, Container</t>
+        </is>
+      </c>
+      <c r="D401" t="inlineStr"/>
+      <c r="E401" t="inlineStr">
+        <is>
+          <t>9903.03.06</t>
+        </is>
+      </c>
+      <c r="F401" t="inlineStr">
+        <is>
+          <t>S122 EXCL,IRN/STL/ALUM,DERIV</t>
+        </is>
+      </c>
+      <c r="G401" t="inlineStr">
+        <is>
+          <t>003</t>
+        </is>
+      </c>
+      <c r="H401" t="inlineStr">
+        <is>
+          <t>9903.03.06</t>
+        </is>
+      </c>
+      <c r="I401" t="inlineStr">
+        <is>
+          <t>9903.74.11,9903.94.53,8708.29.5160</t>
+        </is>
+      </c>
+      <c r="J401" t="inlineStr">
+        <is>
+          <t>BORGERS USA CORP</t>
+        </is>
+      </c>
+      <c r="K401" t="inlineStr">
+        <is>
+          <t>BORUSA</t>
+        </is>
+      </c>
+      <c r="L401" t="inlineStr">
+        <is>
+          <t>65-117296500</t>
+        </is>
+      </c>
+      <c r="M401" t="inlineStr">
+        <is>
+          <t>2026-06-27 00:00:00</t>
+        </is>
+      </c>
+      <c r="N401" t="inlineStr">
+        <is>
+          <t>2026-06-25 00:00:00</t>
+        </is>
+      </c>
+      <c r="O401" t="inlineStr">
+        <is>
+          <t>AUTONEUM CZ S.R.O.</t>
+        </is>
+      </c>
+      <c r="P401" t="inlineStr">
+        <is>
+          <t>AUTONEUM CZ S.R.O.</t>
+        </is>
+      </c>
+      <c r="Q401" t="inlineStr">
+        <is>
+          <t>2026-06-14 00:00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="402">
+      <c r="A402" t="inlineStr">
+        <is>
+          <t>2566249</t>
+        </is>
+      </c>
+      <c r="B402" t="inlineStr">
+        <is>
+          <t>EF4-0232524-7</t>
+        </is>
+      </c>
+      <c r="C402" t="inlineStr">
+        <is>
+          <t>Vessel, Container</t>
+        </is>
+      </c>
+      <c r="D402" t="inlineStr"/>
+      <c r="E402" t="inlineStr">
+        <is>
+          <t>9903.03.06</t>
+        </is>
+      </c>
+      <c r="F402" t="inlineStr">
+        <is>
+          <t>S122 EXCL,IRN/STL/ALUM,DERIV</t>
+        </is>
+      </c>
+      <c r="G402" t="inlineStr">
+        <is>
+          <t>004</t>
+        </is>
+      </c>
+      <c r="H402" t="inlineStr">
+        <is>
+          <t>9903.03.06</t>
+        </is>
+      </c>
+      <c r="I402" t="inlineStr">
+        <is>
+          <t>9903.74.11,9903.94.53,8708.29.5160</t>
+        </is>
+      </c>
+      <c r="J402" t="inlineStr">
+        <is>
+          <t>BORGERS USA CORP</t>
+        </is>
+      </c>
+      <c r="K402" t="inlineStr">
+        <is>
+          <t>BORUSA</t>
+        </is>
+      </c>
+      <c r="L402" t="inlineStr">
+        <is>
+          <t>65-117296500</t>
+        </is>
+      </c>
+      <c r="M402" t="inlineStr">
+        <is>
+          <t>2026-06-27 00:00:00</t>
+        </is>
+      </c>
+      <c r="N402" t="inlineStr">
+        <is>
+          <t>2026-06-25 00:00:00</t>
+        </is>
+      </c>
+      <c r="O402" t="inlineStr">
+        <is>
+          <t>AUTONEUM CZ S.R.O.</t>
+        </is>
+      </c>
+      <c r="P402" t="inlineStr">
+        <is>
+          <t>AUTONEUM CZ S.R.O.</t>
+        </is>
+      </c>
+      <c r="Q402" t="inlineStr">
+        <is>
+          <t>2026-06-14 00:00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="403">
+      <c r="A403" t="inlineStr">
+        <is>
+          <t>105504788</t>
+        </is>
+      </c>
+      <c r="B403" t="inlineStr">
+        <is>
+          <t>EF4-0232545-2</t>
+        </is>
+      </c>
+      <c r="C403" t="inlineStr">
+        <is>
+          <t>Vessel, Non-container</t>
+        </is>
+      </c>
+      <c r="D403" t="inlineStr"/>
+      <c r="E403" t="inlineStr">
+        <is>
+          <t>9805.00.50</t>
+        </is>
+      </c>
+      <c r="F403" t="inlineStr">
+        <is>
+          <t>EFFECTS US GOV EMP&amp;FAMLY/EVACU</t>
+        </is>
+      </c>
+      <c r="G403" t="inlineStr">
+        <is>
+          <t>001</t>
+        </is>
+      </c>
+      <c r="H403" t="inlineStr">
+        <is>
+          <t>9805.00.50</t>
+        </is>
+      </c>
+      <c r="I403" t="inlineStr"/>
+      <c r="J403" t="inlineStr">
+        <is>
+          <t>IFF, INC.</t>
+        </is>
+      </c>
+      <c r="K403" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="L403" t="inlineStr">
+        <is>
+          <t>58-149385700</t>
+        </is>
+      </c>
+      <c r="M403" t="inlineStr">
+        <is>
+          <t>2026-06-26 00:00:00</t>
+        </is>
+      </c>
+      <c r="N403" t="inlineStr">
+        <is>
+          <t>2026-06-25 00:00:00</t>
+        </is>
+      </c>
+      <c r="O403" t="inlineStr">
+        <is>
+          <t>VOLVO CARS GHENT</t>
+        </is>
+      </c>
+      <c r="P403" t="inlineStr">
+        <is>
+          <t>VOLVO CARS GHENT</t>
+        </is>
+      </c>
+      <c r="Q403" t="inlineStr">
+        <is>
+          <t>2026-06-12 00:00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="404">
+      <c r="A404" t="inlineStr">
+        <is>
+          <t>105504789</t>
+        </is>
+      </c>
+      <c r="B404" t="inlineStr">
+        <is>
+          <t>EF4-0232555-1</t>
+        </is>
+      </c>
+      <c r="C404" t="inlineStr">
+        <is>
+          <t>Vessel, Non-container</t>
+        </is>
+      </c>
+      <c r="D404" t="inlineStr"/>
+      <c r="E404" t="inlineStr">
+        <is>
+          <t>9805.00.50</t>
+        </is>
+      </c>
+      <c r="F404" t="inlineStr">
+        <is>
+          <t>EFFECTS US GOV EMP&amp;FAMLY/EVACU</t>
+        </is>
+      </c>
+      <c r="G404" t="inlineStr">
+        <is>
+          <t>001</t>
+        </is>
+      </c>
+      <c r="H404" t="inlineStr">
+        <is>
+          <t>9805.00.50</t>
+        </is>
+      </c>
+      <c r="I404" t="inlineStr"/>
+      <c r="J404" t="inlineStr">
+        <is>
+          <t>IFF, INC.</t>
+        </is>
+      </c>
+      <c r="K404" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="L404" t="inlineStr">
+        <is>
+          <t>58-149385700</t>
+        </is>
+      </c>
+      <c r="M404" t="inlineStr">
+        <is>
+          <t>2026-06-26 00:00:00</t>
+        </is>
+      </c>
+      <c r="N404" t="inlineStr">
+        <is>
+          <t>2026-06-25 00:00:00</t>
+        </is>
+      </c>
+      <c r="O404" t="inlineStr">
+        <is>
+          <t>VOLVO CARS GHENT</t>
+        </is>
+      </c>
+      <c r="P404" t="inlineStr">
+        <is>
+          <t>VOLVO CARS GHENT</t>
+        </is>
+      </c>
+      <c r="Q404" t="inlineStr">
+        <is>
+          <t>2026-06-12 00:00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="405">
+      <c r="A405" t="inlineStr">
+        <is>
+          <t>105504791</t>
+        </is>
+      </c>
+      <c r="B405" t="inlineStr">
+        <is>
+          <t>EF4-0232565-0</t>
+        </is>
+      </c>
+      <c r="C405" t="inlineStr">
+        <is>
+          <t>Vessel, Non-container</t>
+        </is>
+      </c>
+      <c r="D405" t="inlineStr"/>
+      <c r="E405" t="inlineStr">
+        <is>
+          <t>9805.00.50</t>
+        </is>
+      </c>
+      <c r="F405" t="inlineStr">
+        <is>
+          <t>EFFECTS US GOV EMP&amp;FAMLY/EVACU</t>
+        </is>
+      </c>
+      <c r="G405" t="inlineStr">
+        <is>
+          <t>001</t>
+        </is>
+      </c>
+      <c r="H405" t="inlineStr">
+        <is>
+          <t>9805.00.50</t>
+        </is>
+      </c>
+      <c r="I405" t="inlineStr"/>
+      <c r="J405" t="inlineStr">
+        <is>
+          <t>IFF, INC.</t>
+        </is>
+      </c>
+      <c r="K405" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="L405" t="inlineStr">
+        <is>
+          <t>58-149385700</t>
+        </is>
+      </c>
+      <c r="M405" t="inlineStr">
+        <is>
+          <t>2026-06-26 00:00:00</t>
+        </is>
+      </c>
+      <c r="N405" t="inlineStr">
+        <is>
+          <t>2026-06-25 00:00:00</t>
+        </is>
+      </c>
+      <c r="O405" t="inlineStr">
+        <is>
+          <t>VOLVO CAR INTERNATIONAL CORPORATION</t>
+        </is>
+      </c>
+      <c r="P405" t="inlineStr">
+        <is>
+          <t>VOLVO CAR INTERNATIONAL CORPORATION</t>
+        </is>
+      </c>
+      <c r="Q405" t="inlineStr">
+        <is>
+          <t>2026-06-12 00:00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="406">
+      <c r="A406" t="inlineStr">
+        <is>
+          <t>105504792</t>
+        </is>
+      </c>
+      <c r="B406" t="inlineStr">
+        <is>
+          <t>EF4-0232567-6</t>
+        </is>
+      </c>
+      <c r="C406" t="inlineStr">
+        <is>
+          <t>Vessel, Non-container</t>
+        </is>
+      </c>
+      <c r="D406" t="inlineStr"/>
+      <c r="E406" t="inlineStr">
+        <is>
+          <t>9805.00.50</t>
+        </is>
+      </c>
+      <c r="F406" t="inlineStr">
+        <is>
+          <t>EFFECTS US GOV EMP&amp;FAMLY/EVACU</t>
+        </is>
+      </c>
+      <c r="G406" t="inlineStr">
+        <is>
+          <t>001</t>
+        </is>
+      </c>
+      <c r="H406" t="inlineStr">
+        <is>
+          <t>9805.00.50</t>
+        </is>
+      </c>
+      <c r="I406" t="inlineStr"/>
+      <c r="J406" t="inlineStr">
+        <is>
+          <t>IFF, INC.</t>
+        </is>
+      </c>
+      <c r="K406" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="L406" t="inlineStr">
+        <is>
+          <t>58-149385700</t>
+        </is>
+      </c>
+      <c r="M406" t="inlineStr">
+        <is>
+          <t>2026-06-26 00:00:00</t>
+        </is>
+      </c>
+      <c r="N406" t="inlineStr">
+        <is>
+          <t>2026-06-25 00:00:00</t>
+        </is>
+      </c>
+      <c r="O406" t="inlineStr">
+        <is>
+          <t>VOLVO CAR INTERNATIONAL CORPORATION</t>
+        </is>
+      </c>
+      <c r="P406" t="inlineStr">
+        <is>
+          <t>VOLVO CAR INTERNATIONAL CORPORATION</t>
+        </is>
+      </c>
+      <c r="Q406" t="inlineStr">
+        <is>
+          <t>2026-06-12 00:00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="407">
+      <c r="A407" t="inlineStr">
+        <is>
+          <t>105504793</t>
+        </is>
+      </c>
+      <c r="B407" t="inlineStr">
+        <is>
+          <t>EF4-0232569-2</t>
+        </is>
+      </c>
+      <c r="C407" t="inlineStr">
+        <is>
+          <t>Vessel, Non-container</t>
+        </is>
+      </c>
+      <c r="D407" t="inlineStr"/>
+      <c r="E407" t="inlineStr">
+        <is>
+          <t>9805.00.50</t>
+        </is>
+      </c>
+      <c r="F407" t="inlineStr">
+        <is>
+          <t>EFFECTS US GOV EMP&amp;FAMLY/EVACU</t>
+        </is>
+      </c>
+      <c r="G407" t="inlineStr">
+        <is>
+          <t>001</t>
+        </is>
+      </c>
+      <c r="H407" t="inlineStr">
+        <is>
+          <t>9805.00.50</t>
+        </is>
+      </c>
+      <c r="I407" t="inlineStr"/>
+      <c r="J407" t="inlineStr">
+        <is>
+          <t>IFF, INC.</t>
+        </is>
+      </c>
+      <c r="K407" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="L407" t="inlineStr">
+        <is>
+          <t>58-149385700</t>
+        </is>
+      </c>
+      <c r="M407" t="inlineStr">
+        <is>
+          <t>2026-06-26 00:00:00</t>
+        </is>
+      </c>
+      <c r="N407" t="inlineStr">
+        <is>
+          <t>2026-06-25 00:00:00</t>
+        </is>
+      </c>
+      <c r="O407" t="inlineStr">
+        <is>
+          <t>VOLVO CAR INTERNATIONAL CORPORATION</t>
+        </is>
+      </c>
+      <c r="P407" t="inlineStr">
+        <is>
+          <t>VOLVO CAR INTERNATIONAL CORPORATION</t>
+        </is>
+      </c>
+      <c r="Q407" t="inlineStr">
+        <is>
+          <t>2026-06-12 00:00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="408">
+      <c r="A408" t="inlineStr">
+        <is>
+          <t>105504795</t>
+        </is>
+      </c>
+      <c r="B408" t="inlineStr">
+        <is>
+          <t>EF4-0232583-3</t>
+        </is>
+      </c>
+      <c r="C408" t="inlineStr">
+        <is>
+          <t>Vessel, Non-container</t>
+        </is>
+      </c>
+      <c r="D408" t="inlineStr"/>
+      <c r="E408" t="inlineStr">
+        <is>
+          <t>9805.00.50</t>
+        </is>
+      </c>
+      <c r="F408" t="inlineStr">
+        <is>
+          <t>EFFECTS US GOV EMP&amp;FAMLY/EVACU</t>
+        </is>
+      </c>
+      <c r="G408" t="inlineStr">
+        <is>
+          <t>001</t>
+        </is>
+      </c>
+      <c r="H408" t="inlineStr">
+        <is>
+          <t>9805.00.50</t>
+        </is>
+      </c>
+      <c r="I408" t="inlineStr"/>
+      <c r="J408" t="inlineStr">
+        <is>
+          <t>IFF, INC.</t>
+        </is>
+      </c>
+      <c r="K408" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="L408" t="inlineStr">
+        <is>
+          <t>58-149385700</t>
+        </is>
+      </c>
+      <c r="M408" t="inlineStr">
+        <is>
+          <t>2026-06-26 00:00:00</t>
+        </is>
+      </c>
+      <c r="N408" t="inlineStr">
+        <is>
+          <t>2026-06-25 00:00:00</t>
+        </is>
+      </c>
+      <c r="O408" t="inlineStr">
+        <is>
+          <t>VOLVO CAR INTERNATIONAL CORPORATION</t>
+        </is>
+      </c>
+      <c r="P408" t="inlineStr">
+        <is>
+          <t>VOLVO CAR INTERNATIONAL CORPORATION</t>
+        </is>
+      </c>
+      <c r="Q408" t="inlineStr">
+        <is>
+          <t>2026-06-12 00:00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="409">
+      <c r="A409" t="inlineStr">
+        <is>
+          <t>105504796</t>
+        </is>
+      </c>
+      <c r="B409" t="inlineStr">
+        <is>
+          <t>EF4-0232585-8</t>
+        </is>
+      </c>
+      <c r="C409" t="inlineStr">
+        <is>
+          <t>Vessel, Non-container</t>
+        </is>
+      </c>
+      <c r="D409" t="inlineStr"/>
+      <c r="E409" t="inlineStr">
+        <is>
+          <t>9805.00.50</t>
+        </is>
+      </c>
+      <c r="F409" t="inlineStr">
+        <is>
+          <t>EFFECTS US GOV EMP&amp;FAMLY/EVACU</t>
+        </is>
+      </c>
+      <c r="G409" t="inlineStr">
+        <is>
+          <t>001</t>
+        </is>
+      </c>
+      <c r="H409" t="inlineStr">
+        <is>
+          <t>9805.00.50</t>
+        </is>
+      </c>
+      <c r="I409" t="inlineStr"/>
+      <c r="J409" t="inlineStr">
+        <is>
+          <t>IFF, INC.</t>
+        </is>
+      </c>
+      <c r="K409" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="L409" t="inlineStr">
+        <is>
+          <t>58-149385700</t>
+        </is>
+      </c>
+      <c r="M409" t="inlineStr">
+        <is>
+          <t>2026-06-26 00:00:00</t>
+        </is>
+      </c>
+      <c r="N409" t="inlineStr">
+        <is>
+          <t>2026-06-25 00:00:00</t>
+        </is>
+      </c>
+      <c r="O409" t="inlineStr">
+        <is>
+          <t>VOLVO CARS GHENT</t>
+        </is>
+      </c>
+      <c r="P409" t="inlineStr">
+        <is>
+          <t>VOLVO CARS GHENT</t>
+        </is>
+      </c>
+      <c r="Q409" t="inlineStr">
+        <is>
+          <t>2026-06-12 00:00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="410">
+      <c r="A410" t="inlineStr">
+        <is>
+          <t>2566322</t>
+        </is>
+      </c>
+      <c r="B410" t="inlineStr">
+        <is>
+          <t>EF4-0232612-0</t>
+        </is>
+      </c>
+      <c r="C410" t="inlineStr">
+        <is>
+          <t>Vessel, Container</t>
+        </is>
+      </c>
+      <c r="D410" t="inlineStr"/>
+      <c r="E410" t="inlineStr">
+        <is>
+          <t>9903.03.01</t>
+        </is>
+      </c>
+      <c r="F410" t="inlineStr">
+        <is>
+          <t>SECTION 122 - 10% DUTY</t>
+        </is>
+      </c>
+      <c r="G410" t="inlineStr">
+        <is>
+          <t>001</t>
+        </is>
+      </c>
+      <c r="H410" t="inlineStr">
+        <is>
+          <t>9903.03.01</t>
+        </is>
+      </c>
+      <c r="I410" t="inlineStr">
+        <is>
+          <t>8419.19.0120</t>
+        </is>
+      </c>
+      <c r="J410" t="inlineStr">
+        <is>
+          <t>THERMAL PROCESS DEVELOPMENT LLC</t>
+        </is>
+      </c>
+      <c r="K410" t="inlineStr">
+        <is>
+          <t>THEPRO01</t>
+        </is>
+      </c>
+      <c r="L410" t="inlineStr">
+        <is>
+          <t>82-175198100</t>
+        </is>
+      </c>
+      <c r="M410" t="inlineStr">
+        <is>
+          <t>2026-06-27 00:00:00</t>
+        </is>
+      </c>
+      <c r="N410" t="inlineStr">
+        <is>
+          <t>2026-06-25 00:00:00</t>
+        </is>
+      </c>
+      <c r="O410" t="inlineStr">
+        <is>
+          <t>INTEC ENGINEERING GMBH</t>
+        </is>
+      </c>
+      <c r="P410" t="inlineStr">
+        <is>
+          <t>INTEC ENGINEERING GMBH</t>
+        </is>
+      </c>
+      <c r="Q410" t="inlineStr">
+        <is>
+          <t>2026-06-14 00:00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="411">
+      <c r="A411" t="inlineStr">
+        <is>
+          <t>4539557</t>
+        </is>
+      </c>
+      <c r="B411" t="inlineStr">
+        <is>
+          <t>EF4-0232785-4</t>
+        </is>
+      </c>
+      <c r="C411" t="inlineStr">
+        <is>
+          <t>Air, Non-container</t>
+        </is>
+      </c>
+      <c r="D411" t="inlineStr">
+        <is>
+          <t>709758804</t>
+        </is>
+      </c>
+      <c r="E411" t="inlineStr">
+        <is>
+          <t>9903.03.01</t>
+        </is>
+      </c>
+      <c r="F411" t="inlineStr">
+        <is>
+          <t>SECTION 122 - 10% DUTY</t>
+        </is>
+      </c>
+      <c r="G411" t="inlineStr">
+        <is>
+          <t>001</t>
+        </is>
+      </c>
+      <c r="H411" t="inlineStr">
+        <is>
+          <t>9903.03.01</t>
+        </is>
+      </c>
+      <c r="I411" t="inlineStr">
+        <is>
+          <t>8438.90.9060</t>
+        </is>
+      </c>
+      <c r="J411" t="inlineStr">
+        <is>
+          <t>CANTRELL GAINCO GROUP INC</t>
+        </is>
+      </c>
+      <c r="K411" t="inlineStr">
+        <is>
+          <t>CANGAI01</t>
+        </is>
+      </c>
+      <c r="L411" t="inlineStr">
+        <is>
+          <t>31-151121700</t>
+        </is>
+      </c>
+      <c r="M411" t="inlineStr">
+        <is>
+          <t>2026-06-24 00:00:00</t>
+        </is>
+      </c>
+      <c r="N411" t="inlineStr">
+        <is>
+          <t>2026-06-25 00:00:00</t>
+        </is>
+      </c>
+      <c r="O411" t="inlineStr">
+        <is>
+          <t>O E CO LTD</t>
+        </is>
+      </c>
+      <c r="P411" t="inlineStr">
+        <is>
+          <t>O E CO LTD</t>
+        </is>
+      </c>
+      <c r="Q411" t="inlineStr">
+        <is>
+          <t>2026-06-24 00:00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="412">
+      <c r="A412" t="inlineStr">
+        <is>
+          <t>4539561</t>
+        </is>
+      </c>
+      <c r="B412" t="inlineStr">
+        <is>
+          <t>EF4-0232788-8</t>
+        </is>
+      </c>
+      <c r="C412" t="inlineStr">
+        <is>
+          <t>Air, Non-container</t>
+        </is>
+      </c>
+      <c r="D412" t="inlineStr">
+        <is>
+          <t>709758804</t>
+        </is>
+      </c>
+      <c r="E412" t="inlineStr">
+        <is>
+          <t>9903.03.01</t>
+        </is>
+      </c>
+      <c r="F412" t="inlineStr">
+        <is>
+          <t>SECTION 122 - 10% DUTY</t>
+        </is>
+      </c>
+      <c r="G412" t="inlineStr">
+        <is>
+          <t>001</t>
+        </is>
+      </c>
+      <c r="H412" t="inlineStr">
+        <is>
+          <t>9903.03.01</t>
+        </is>
+      </c>
+      <c r="I412" t="inlineStr">
+        <is>
+          <t>4010.19.9100</t>
+        </is>
+      </c>
+      <c r="J412" t="inlineStr">
+        <is>
+          <t>CANTRELL GAINCO GROUP INC</t>
+        </is>
+      </c>
+      <c r="K412" t="inlineStr">
+        <is>
+          <t>CANGAI01</t>
+        </is>
+      </c>
+      <c r="L412" t="inlineStr">
+        <is>
+          <t>31-151121700</t>
+        </is>
+      </c>
+      <c r="M412" t="inlineStr">
+        <is>
+          <t>2026-06-23 00:00:00</t>
+        </is>
+      </c>
+      <c r="N412" t="inlineStr">
+        <is>
+          <t>2026-06-25 00:00:00</t>
+        </is>
+      </c>
+      <c r="O412" t="inlineStr">
+        <is>
+          <t>MANIFATTURE TECNICHE INDUSTRIALI SA</t>
+        </is>
+      </c>
+      <c r="P412" t="inlineStr">
+        <is>
+          <t>MANIFATTURE TECNICHE INDUSTRIALI SA</t>
+        </is>
+      </c>
+      <c r="Q412" t="inlineStr">
+        <is>
+          <t>2026-06-23 00:00:00</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/trimika_data.xlsx
+++ b/trimika_data.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q412"/>
+  <dimension ref="A1:Q415"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -34876,6 +34876,255 @@
         </is>
       </c>
     </row>
+    <row r="413">
+      <c r="A413" t="inlineStr">
+        <is>
+          <t>2566151</t>
+        </is>
+      </c>
+      <c r="B413" t="inlineStr">
+        <is>
+          <t>EF4-0232363-0</t>
+        </is>
+      </c>
+      <c r="C413" t="inlineStr">
+        <is>
+          <t>Vessel, Container</t>
+        </is>
+      </c>
+      <c r="D413" t="inlineStr"/>
+      <c r="E413" t="inlineStr">
+        <is>
+          <t>9903.03.01</t>
+        </is>
+      </c>
+      <c r="F413" t="inlineStr">
+        <is>
+          <t>SECTION 122 - 10% DUTY</t>
+        </is>
+      </c>
+      <c r="G413" t="inlineStr">
+        <is>
+          <t>001</t>
+        </is>
+      </c>
+      <c r="H413" t="inlineStr">
+        <is>
+          <t>9903.03.01</t>
+        </is>
+      </c>
+      <c r="I413" t="inlineStr">
+        <is>
+          <t>1109.00.9020</t>
+        </is>
+      </c>
+      <c r="J413" t="inlineStr">
+        <is>
+          <t>ROYAL INGREDIENTS GROUP BV</t>
+        </is>
+      </c>
+      <c r="K413" t="inlineStr">
+        <is>
+          <t>ROYINGRE</t>
+        </is>
+      </c>
+      <c r="L413" t="inlineStr">
+        <is>
+          <t>074601-00962</t>
+        </is>
+      </c>
+      <c r="M413" t="inlineStr">
+        <is>
+          <t>2026-06-29 00:00:00</t>
+        </is>
+      </c>
+      <c r="N413" t="inlineStr">
+        <is>
+          <t>2026-06-26 00:00:00</t>
+        </is>
+      </c>
+      <c r="O413" t="inlineStr">
+        <is>
+          <t>SEDAMYL UK</t>
+        </is>
+      </c>
+      <c r="P413" t="inlineStr">
+        <is>
+          <t>SEDAMYL UK</t>
+        </is>
+      </c>
+      <c r="Q413" t="inlineStr">
+        <is>
+          <t>2026-06-07 00:00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="414">
+      <c r="A414" t="inlineStr">
+        <is>
+          <t>2566238</t>
+        </is>
+      </c>
+      <c r="B414" t="inlineStr">
+        <is>
+          <t>EF4-0232707-8</t>
+        </is>
+      </c>
+      <c r="C414" t="inlineStr">
+        <is>
+          <t>Vessel, Container</t>
+        </is>
+      </c>
+      <c r="D414" t="inlineStr"/>
+      <c r="E414" t="inlineStr">
+        <is>
+          <t>9903.03.01</t>
+        </is>
+      </c>
+      <c r="F414" t="inlineStr">
+        <is>
+          <t>SECTION 122 - 10% DUTY</t>
+        </is>
+      </c>
+      <c r="G414" t="inlineStr">
+        <is>
+          <t>001</t>
+        </is>
+      </c>
+      <c r="H414" t="inlineStr">
+        <is>
+          <t>9903.03.01</t>
+        </is>
+      </c>
+      <c r="I414" t="inlineStr">
+        <is>
+          <t>1109.00.9020</t>
+        </is>
+      </c>
+      <c r="J414" t="inlineStr">
+        <is>
+          <t>ROYAL INGREDIENTS GROUP BV</t>
+        </is>
+      </c>
+      <c r="K414" t="inlineStr">
+        <is>
+          <t>ROYINGRE</t>
+        </is>
+      </c>
+      <c r="L414" t="inlineStr">
+        <is>
+          <t>074601-00962</t>
+        </is>
+      </c>
+      <c r="M414" t="inlineStr">
+        <is>
+          <t>2026-06-29 00:00:00</t>
+        </is>
+      </c>
+      <c r="N414" t="inlineStr">
+        <is>
+          <t>2026-06-26 00:00:00</t>
+        </is>
+      </c>
+      <c r="O414" t="inlineStr">
+        <is>
+          <t>CARGILL BARBY</t>
+        </is>
+      </c>
+      <c r="P414" t="inlineStr">
+        <is>
+          <t>CARGILL BARBY</t>
+        </is>
+      </c>
+      <c r="Q414" t="inlineStr">
+        <is>
+          <t>2026-06-19 00:00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="415">
+      <c r="A415" t="inlineStr">
+        <is>
+          <t>2566351</t>
+        </is>
+      </c>
+      <c r="B415" t="inlineStr">
+        <is>
+          <t>EF4-0232708-6</t>
+        </is>
+      </c>
+      <c r="C415" t="inlineStr">
+        <is>
+          <t>Vessel, Container</t>
+        </is>
+      </c>
+      <c r="D415" t="inlineStr"/>
+      <c r="E415" t="inlineStr">
+        <is>
+          <t>9903.03.01</t>
+        </is>
+      </c>
+      <c r="F415" t="inlineStr">
+        <is>
+          <t>SECTION 122 - 10% DUTY</t>
+        </is>
+      </c>
+      <c r="G415" t="inlineStr">
+        <is>
+          <t>001</t>
+        </is>
+      </c>
+      <c r="H415" t="inlineStr">
+        <is>
+          <t>9903.03.01</t>
+        </is>
+      </c>
+      <c r="I415" t="inlineStr">
+        <is>
+          <t>1109.00.9020</t>
+        </is>
+      </c>
+      <c r="J415" t="inlineStr">
+        <is>
+          <t>ROYAL INGREDIENTS GROUP BV</t>
+        </is>
+      </c>
+      <c r="K415" t="inlineStr">
+        <is>
+          <t>ROYINGRE</t>
+        </is>
+      </c>
+      <c r="L415" t="inlineStr">
+        <is>
+          <t>074601-00962</t>
+        </is>
+      </c>
+      <c r="M415" t="inlineStr">
+        <is>
+          <t>2026-06-29 00:00:00</t>
+        </is>
+      </c>
+      <c r="N415" t="inlineStr">
+        <is>
+          <t>2026-06-26 00:00:00</t>
+        </is>
+      </c>
+      <c r="O415" t="inlineStr">
+        <is>
+          <t>CARGILL BARBY</t>
+        </is>
+      </c>
+      <c r="P415" t="inlineStr">
+        <is>
+          <t>CARGILL BARBY</t>
+        </is>
+      </c>
+      <c r="Q415" t="inlineStr">
+        <is>
+          <t>2026-06-19 00:00:00</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/trimika_data.xlsx
+++ b/trimika_data.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q423"/>
+  <dimension ref="A1:Q433"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -35813,6 +35813,856 @@
         </is>
       </c>
     </row>
+    <row r="424">
+      <c r="A424" t="inlineStr">
+        <is>
+          <t>2565881</t>
+        </is>
+      </c>
+      <c r="B424" t="inlineStr">
+        <is>
+          <t>EF4-0231827-5</t>
+        </is>
+      </c>
+      <c r="C424" t="inlineStr">
+        <is>
+          <t>Vessel, Container</t>
+        </is>
+      </c>
+      <c r="D424" t="inlineStr"/>
+      <c r="E424" t="inlineStr">
+        <is>
+          <t>9903.88.15</t>
+        </is>
+      </c>
+      <c r="F424" t="inlineStr">
+        <is>
+          <t>ARTICLE OF CHINA,US NTE 20(R)</t>
+        </is>
+      </c>
+      <c r="G424" t="inlineStr">
+        <is>
+          <t>001</t>
+        </is>
+      </c>
+      <c r="H424" t="inlineStr">
+        <is>
+          <t>9903.88.15</t>
+        </is>
+      </c>
+      <c r="I424" t="inlineStr">
+        <is>
+          <t>9903.03.06,9903.82.09,8302.42.3065</t>
+        </is>
+      </c>
+      <c r="J424" t="inlineStr">
+        <is>
+          <t>GRASS AMERICA INC</t>
+        </is>
+      </c>
+      <c r="K424" t="inlineStr">
+        <is>
+          <t>GRAAME</t>
+        </is>
+      </c>
+      <c r="L424" t="inlineStr">
+        <is>
+          <t>51-066023000</t>
+        </is>
+      </c>
+      <c r="M424" t="inlineStr">
+        <is>
+          <t>2026-06-25 00:00:00</t>
+        </is>
+      </c>
+      <c r="N424" t="inlineStr">
+        <is>
+          <t>2026-06-28 00:00:00</t>
+        </is>
+      </c>
+      <c r="O424" t="inlineStr">
+        <is>
+          <t>BAIHUI ENTERPRISE(KAISI)</t>
+        </is>
+      </c>
+      <c r="P424" t="inlineStr">
+        <is>
+          <t>BAIHUI ENTERPRISE(KAISI)</t>
+        </is>
+      </c>
+      <c r="Q424" t="inlineStr">
+        <is>
+          <t>2026-05-12 00:00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="425">
+      <c r="A425" t="inlineStr">
+        <is>
+          <t>2565881</t>
+        </is>
+      </c>
+      <c r="B425" t="inlineStr">
+        <is>
+          <t>EF4-0231827-5</t>
+        </is>
+      </c>
+      <c r="C425" t="inlineStr">
+        <is>
+          <t>Vessel, Container</t>
+        </is>
+      </c>
+      <c r="D425" t="inlineStr"/>
+      <c r="E425" t="inlineStr">
+        <is>
+          <t>9903.88.15</t>
+        </is>
+      </c>
+      <c r="F425" t="inlineStr">
+        <is>
+          <t>ARTICLE OF CHINA,US NTE 20(R)</t>
+        </is>
+      </c>
+      <c r="G425" t="inlineStr">
+        <is>
+          <t>002</t>
+        </is>
+      </c>
+      <c r="H425" t="inlineStr">
+        <is>
+          <t>9903.88.15</t>
+        </is>
+      </c>
+      <c r="I425" t="inlineStr">
+        <is>
+          <t>9903.03.01,3926.30.5000</t>
+        </is>
+      </c>
+      <c r="J425" t="inlineStr">
+        <is>
+          <t>GRASS AMERICA INC</t>
+        </is>
+      </c>
+      <c r="K425" t="inlineStr">
+        <is>
+          <t>GRAAME</t>
+        </is>
+      </c>
+      <c r="L425" t="inlineStr">
+        <is>
+          <t>51-066023000</t>
+        </is>
+      </c>
+      <c r="M425" t="inlineStr">
+        <is>
+          <t>2026-06-25 00:00:00</t>
+        </is>
+      </c>
+      <c r="N425" t="inlineStr">
+        <is>
+          <t>2026-06-28 00:00:00</t>
+        </is>
+      </c>
+      <c r="O425" t="inlineStr">
+        <is>
+          <t>BAIHUI ENTERPRISE(KAISI)</t>
+        </is>
+      </c>
+      <c r="P425" t="inlineStr">
+        <is>
+          <t>BAIHUI ENTERPRISE(KAISI)</t>
+        </is>
+      </c>
+      <c r="Q425" t="inlineStr">
+        <is>
+          <t>2026-05-12 00:00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="426">
+      <c r="A426" t="inlineStr">
+        <is>
+          <t>2566043</t>
+        </is>
+      </c>
+      <c r="B426" t="inlineStr">
+        <is>
+          <t>EF4-0232123-8</t>
+        </is>
+      </c>
+      <c r="C426" t="inlineStr">
+        <is>
+          <t>Vessel, Container</t>
+        </is>
+      </c>
+      <c r="D426" t="inlineStr"/>
+      <c r="E426" t="inlineStr">
+        <is>
+          <t>9903.03.01</t>
+        </is>
+      </c>
+      <c r="F426" t="inlineStr">
+        <is>
+          <t>SECTION 122 - 10% DUTY</t>
+        </is>
+      </c>
+      <c r="G426" t="inlineStr">
+        <is>
+          <t>001</t>
+        </is>
+      </c>
+      <c r="H426" t="inlineStr">
+        <is>
+          <t>9903.03.01</t>
+        </is>
+      </c>
+      <c r="I426" t="inlineStr">
+        <is>
+          <t>1108.13.0010</t>
+        </is>
+      </c>
+      <c r="J426" t="inlineStr">
+        <is>
+          <t>ROYAL INGREDIENTS GROUP BV</t>
+        </is>
+      </c>
+      <c r="K426" t="inlineStr">
+        <is>
+          <t>ROYINGRE</t>
+        </is>
+      </c>
+      <c r="L426" t="inlineStr">
+        <is>
+          <t>074601-00962</t>
+        </is>
+      </c>
+      <c r="M426" t="inlineStr">
+        <is>
+          <t>2026-06-28 00:00:00</t>
+        </is>
+      </c>
+      <c r="N426" t="inlineStr">
+        <is>
+          <t>2026-06-28 00:00:00</t>
+        </is>
+      </c>
+      <c r="O426" t="inlineStr">
+        <is>
+          <t>AKV LANGHOLT AMBA</t>
+        </is>
+      </c>
+      <c r="P426" t="inlineStr">
+        <is>
+          <t>AKV LANGHOLT AMBA</t>
+        </is>
+      </c>
+      <c r="Q426" t="inlineStr">
+        <is>
+          <t>2026-05-24 00:00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="427">
+      <c r="A427" t="inlineStr">
+        <is>
+          <t>2566085</t>
+        </is>
+      </c>
+      <c r="B427" t="inlineStr">
+        <is>
+          <t>EF4-0232125-3</t>
+        </is>
+      </c>
+      <c r="C427" t="inlineStr">
+        <is>
+          <t>Vessel, Container</t>
+        </is>
+      </c>
+      <c r="D427" t="inlineStr">
+        <is>
+          <t>V0710342853</t>
+        </is>
+      </c>
+      <c r="E427" t="inlineStr">
+        <is>
+          <t>9903.03.01</t>
+        </is>
+      </c>
+      <c r="F427" t="inlineStr">
+        <is>
+          <t>SECTION 122 - 10% DUTY</t>
+        </is>
+      </c>
+      <c r="G427" t="inlineStr">
+        <is>
+          <t>001</t>
+        </is>
+      </c>
+      <c r="H427" t="inlineStr">
+        <is>
+          <t>9903.03.01</t>
+        </is>
+      </c>
+      <c r="I427" t="inlineStr">
+        <is>
+          <t>1108.13.0010</t>
+        </is>
+      </c>
+      <c r="J427" t="inlineStr">
+        <is>
+          <t>ROYAL INGREDIENTS GROUP BV</t>
+        </is>
+      </c>
+      <c r="K427" t="inlineStr">
+        <is>
+          <t>ROYINGRE</t>
+        </is>
+      </c>
+      <c r="L427" t="inlineStr">
+        <is>
+          <t>074601-00962</t>
+        </is>
+      </c>
+      <c r="M427" t="inlineStr">
+        <is>
+          <t>2026-06-28 00:00:00</t>
+        </is>
+      </c>
+      <c r="N427" t="inlineStr">
+        <is>
+          <t>2026-06-28 00:00:00</t>
+        </is>
+      </c>
+      <c r="O427" t="inlineStr">
+        <is>
+          <t>AKV LANGHOLT AMBA</t>
+        </is>
+      </c>
+      <c r="P427" t="inlineStr">
+        <is>
+          <t>AKV LANGHOLT AMBA</t>
+        </is>
+      </c>
+      <c r="Q427" t="inlineStr">
+        <is>
+          <t>2026-05-25 00:00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="428">
+      <c r="A428" t="inlineStr">
+        <is>
+          <t>2566136</t>
+        </is>
+      </c>
+      <c r="B428" t="inlineStr">
+        <is>
+          <t>EF4-0232217-8</t>
+        </is>
+      </c>
+      <c r="C428" t="inlineStr">
+        <is>
+          <t>Vessel, Container</t>
+        </is>
+      </c>
+      <c r="D428" t="inlineStr">
+        <is>
+          <t>V0710342853</t>
+        </is>
+      </c>
+      <c r="E428" t="inlineStr">
+        <is>
+          <t>9903.03.01</t>
+        </is>
+      </c>
+      <c r="F428" t="inlineStr">
+        <is>
+          <t>SECTION 122 - 10% DUTY</t>
+        </is>
+      </c>
+      <c r="G428" t="inlineStr">
+        <is>
+          <t>001</t>
+        </is>
+      </c>
+      <c r="H428" t="inlineStr">
+        <is>
+          <t>9903.03.01</t>
+        </is>
+      </c>
+      <c r="I428" t="inlineStr">
+        <is>
+          <t>1109.00.9020</t>
+        </is>
+      </c>
+      <c r="J428" t="inlineStr">
+        <is>
+          <t>ROYAL INGREDIENTS GROUP BV</t>
+        </is>
+      </c>
+      <c r="K428" t="inlineStr">
+        <is>
+          <t>ROYINGRE</t>
+        </is>
+      </c>
+      <c r="L428" t="inlineStr">
+        <is>
+          <t>074601-00962</t>
+        </is>
+      </c>
+      <c r="M428" t="inlineStr">
+        <is>
+          <t>2026-06-28 00:00:00</t>
+        </is>
+      </c>
+      <c r="N428" t="inlineStr">
+        <is>
+          <t>2026-06-28 00:00:00</t>
+        </is>
+      </c>
+      <c r="O428" t="inlineStr">
+        <is>
+          <t>ROQUETTE FRERES</t>
+        </is>
+      </c>
+      <c r="P428" t="inlineStr">
+        <is>
+          <t>ROQUETTE FRERES</t>
+        </is>
+      </c>
+      <c r="Q428" t="inlineStr">
+        <is>
+          <t>2026-05-30 00:00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="429">
+      <c r="A429" t="inlineStr">
+        <is>
+          <t>2566037</t>
+        </is>
+      </c>
+      <c r="B429" t="inlineStr">
+        <is>
+          <t>EF4-0232303-6</t>
+        </is>
+      </c>
+      <c r="C429" t="inlineStr">
+        <is>
+          <t>Vessel, Container</t>
+        </is>
+      </c>
+      <c r="D429" t="inlineStr">
+        <is>
+          <t>V1P06267054</t>
+        </is>
+      </c>
+      <c r="E429" t="inlineStr">
+        <is>
+          <t>9903.03.03</t>
+        </is>
+      </c>
+      <c r="F429" t="inlineStr">
+        <is>
+          <t>S122 -EXCLUSION-EXEMPTED PRDTS</t>
+        </is>
+      </c>
+      <c r="G429" t="inlineStr">
+        <is>
+          <t>001</t>
+        </is>
+      </c>
+      <c r="H429" t="inlineStr">
+        <is>
+          <t>9903.03.03</t>
+        </is>
+      </c>
+      <c r="I429" t="inlineStr">
+        <is>
+          <t>1108.14.0000</t>
+        </is>
+      </c>
+      <c r="J429" t="inlineStr">
+        <is>
+          <t>ROYAL INGREDIENTS GROUP BV</t>
+        </is>
+      </c>
+      <c r="K429" t="inlineStr">
+        <is>
+          <t>ROYINGRE</t>
+        </is>
+      </c>
+      <c r="L429" t="inlineStr">
+        <is>
+          <t>074601-00962</t>
+        </is>
+      </c>
+      <c r="M429" t="inlineStr">
+        <is>
+          <t>2026-06-30 00:00:00</t>
+        </is>
+      </c>
+      <c r="N429" t="inlineStr">
+        <is>
+          <t>2026-06-28 00:00:00</t>
+        </is>
+      </c>
+      <c r="O429" t="inlineStr">
+        <is>
+          <t>SANGUAN WONGSE STARCH CO., LTD.</t>
+        </is>
+      </c>
+      <c r="P429" t="inlineStr">
+        <is>
+          <t>SANGUAN WONGSE STARCH CO., LTD.</t>
+        </is>
+      </c>
+      <c r="Q429" t="inlineStr">
+        <is>
+          <t>2026-05-23 00:00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="430">
+      <c r="A430" t="inlineStr">
+        <is>
+          <t>2566247</t>
+        </is>
+      </c>
+      <c r="B430" t="inlineStr">
+        <is>
+          <t>EF4-0232455-4</t>
+        </is>
+      </c>
+      <c r="C430" t="inlineStr">
+        <is>
+          <t>Vessel, Container</t>
+        </is>
+      </c>
+      <c r="D430" t="inlineStr">
+        <is>
+          <t>V1P06267054</t>
+        </is>
+      </c>
+      <c r="E430" t="inlineStr">
+        <is>
+          <t>9903.03.01</t>
+        </is>
+      </c>
+      <c r="F430" t="inlineStr">
+        <is>
+          <t>SECTION 122 - 10% DUTY</t>
+        </is>
+      </c>
+      <c r="G430" t="inlineStr">
+        <is>
+          <t>001</t>
+        </is>
+      </c>
+      <c r="H430" t="inlineStr">
+        <is>
+          <t>9903.03.01</t>
+        </is>
+      </c>
+      <c r="I430" t="inlineStr">
+        <is>
+          <t>1109.00.9020</t>
+        </is>
+      </c>
+      <c r="J430" t="inlineStr">
+        <is>
+          <t>ROYAL INGREDIENTS GROUP BV</t>
+        </is>
+      </c>
+      <c r="K430" t="inlineStr">
+        <is>
+          <t>ROYINGRE</t>
+        </is>
+      </c>
+      <c r="L430" t="inlineStr">
+        <is>
+          <t>074601-00962</t>
+        </is>
+      </c>
+      <c r="M430" t="inlineStr">
+        <is>
+          <t>2026-06-28 00:00:00</t>
+        </is>
+      </c>
+      <c r="N430" t="inlineStr">
+        <is>
+          <t>2026-06-28 00:00:00</t>
+        </is>
+      </c>
+      <c r="O430" t="inlineStr">
+        <is>
+          <t>JACKERING MUHLEN UND NAHRMITTELWERK</t>
+        </is>
+      </c>
+      <c r="P430" t="inlineStr">
+        <is>
+          <t>JACKERING MUHLEN UND NAHRMITTELWERKE GMBH</t>
+        </is>
+      </c>
+      <c r="Q430" t="inlineStr">
+        <is>
+          <t>2026-06-08 00:00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="431">
+      <c r="A431" t="inlineStr">
+        <is>
+          <t>2566232</t>
+        </is>
+      </c>
+      <c r="B431" t="inlineStr">
+        <is>
+          <t>EF4-0232576-7</t>
+        </is>
+      </c>
+      <c r="C431" t="inlineStr">
+        <is>
+          <t>Vessel, Container</t>
+        </is>
+      </c>
+      <c r="D431" t="inlineStr"/>
+      <c r="E431" t="inlineStr">
+        <is>
+          <t>9903.03.01</t>
+        </is>
+      </c>
+      <c r="F431" t="inlineStr">
+        <is>
+          <t>SECTION 122 - 10% DUTY</t>
+        </is>
+      </c>
+      <c r="G431" t="inlineStr">
+        <is>
+          <t>001</t>
+        </is>
+      </c>
+      <c r="H431" t="inlineStr">
+        <is>
+          <t>9903.03.01</t>
+        </is>
+      </c>
+      <c r="I431" t="inlineStr">
+        <is>
+          <t>3920.20.0055</t>
+        </is>
+      </c>
+      <c r="J431" t="inlineStr">
+        <is>
+          <t>TEUFELBERGER G.E.S.M.B.H</t>
+        </is>
+      </c>
+      <c r="K431" t="inlineStr">
+        <is>
+          <t>TEUSEI01</t>
+        </is>
+      </c>
+      <c r="L431" t="inlineStr">
+        <is>
+          <t>181704-13780</t>
+        </is>
+      </c>
+      <c r="M431" t="inlineStr">
+        <is>
+          <t>2026-06-28 00:00:00</t>
+        </is>
+      </c>
+      <c r="N431" t="inlineStr">
+        <is>
+          <t>2026-06-28 00:00:00</t>
+        </is>
+      </c>
+      <c r="O431" t="inlineStr">
+        <is>
+          <t>TEUFELBERGER GMBH</t>
+        </is>
+      </c>
+      <c r="P431" t="inlineStr">
+        <is>
+          <t>TEUFELBERGER GMBH</t>
+        </is>
+      </c>
+      <c r="Q431" t="inlineStr">
+        <is>
+          <t>2026-06-14 00:00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="432">
+      <c r="A432" t="inlineStr">
+        <is>
+          <t>4539529</t>
+        </is>
+      </c>
+      <c r="B432" t="inlineStr">
+        <is>
+          <t>EF4-0232822-5</t>
+        </is>
+      </c>
+      <c r="C432" t="inlineStr">
+        <is>
+          <t>Air, Non-container</t>
+        </is>
+      </c>
+      <c r="D432" t="inlineStr"/>
+      <c r="E432" t="inlineStr">
+        <is>
+          <t>9903.88.03</t>
+        </is>
+      </c>
+      <c r="F432" t="inlineStr">
+        <is>
+          <t>ARTICLE OF CHINA,US NTE 20(F)</t>
+        </is>
+      </c>
+      <c r="G432" t="inlineStr">
+        <is>
+          <t>001</t>
+        </is>
+      </c>
+      <c r="H432" t="inlineStr">
+        <is>
+          <t>9903.88.03</t>
+        </is>
+      </c>
+      <c r="I432" t="inlineStr">
+        <is>
+          <t>9903.03.01,9403.99.9045</t>
+        </is>
+      </c>
+      <c r="J432" t="inlineStr">
+        <is>
+          <t>VISUAL CREATIONS, INC.</t>
+        </is>
+      </c>
+      <c r="K432" t="inlineStr">
+        <is>
+          <t>VISCRE</t>
+        </is>
+      </c>
+      <c r="L432" t="inlineStr">
+        <is>
+          <t>20-461602300</t>
+        </is>
+      </c>
+      <c r="M432" t="inlineStr">
+        <is>
+          <t>2026-06-26 00:00:00</t>
+        </is>
+      </c>
+      <c r="N432" t="inlineStr">
+        <is>
+          <t>2026-06-28 00:00:00</t>
+        </is>
+      </c>
+      <c r="O432" t="inlineStr">
+        <is>
+          <t>XIAMEN CUBES INDUSTRIAL &amp; TRADING C</t>
+        </is>
+      </c>
+      <c r="P432" t="inlineStr">
+        <is>
+          <t>XIAMEN CUBES INDUSTRIAL &amp; TRADING C</t>
+        </is>
+      </c>
+      <c r="Q432" t="inlineStr">
+        <is>
+          <t>2026-06-26 00:00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="433">
+      <c r="A433" t="inlineStr">
+        <is>
+          <t>4539572</t>
+        </is>
+      </c>
+      <c r="B433" t="inlineStr">
+        <is>
+          <t>EF4-0232838-1</t>
+        </is>
+      </c>
+      <c r="C433" t="inlineStr">
+        <is>
+          <t>Air, Non-container</t>
+        </is>
+      </c>
+      <c r="D433" t="inlineStr">
+        <is>
+          <t>711583181</t>
+        </is>
+      </c>
+      <c r="E433" t="inlineStr">
+        <is>
+          <t>9903.03.01</t>
+        </is>
+      </c>
+      <c r="F433" t="inlineStr">
+        <is>
+          <t>SECTION 122 - 10% DUTY</t>
+        </is>
+      </c>
+      <c r="G433" t="inlineStr">
+        <is>
+          <t>001</t>
+        </is>
+      </c>
+      <c r="H433" t="inlineStr">
+        <is>
+          <t>9903.03.01</t>
+        </is>
+      </c>
+      <c r="I433" t="inlineStr">
+        <is>
+          <t>8438.90.9060</t>
+        </is>
+      </c>
+      <c r="J433" t="inlineStr">
+        <is>
+          <t>CANTRELL GAINCO GROUP INC</t>
+        </is>
+      </c>
+      <c r="K433" t="inlineStr">
+        <is>
+          <t>CANGAI01</t>
+        </is>
+      </c>
+      <c r="L433" t="inlineStr">
+        <is>
+          <t>31-151121700</t>
+        </is>
+      </c>
+      <c r="M433" t="inlineStr">
+        <is>
+          <t>2026-06-26 00:00:00</t>
+        </is>
+      </c>
+      <c r="N433" t="inlineStr">
+        <is>
+          <t>2026-06-28 00:00:00</t>
+        </is>
+      </c>
+      <c r="O433" t="inlineStr">
+        <is>
+          <t>O E CO LTD</t>
+        </is>
+      </c>
+      <c r="P433" t="inlineStr">
+        <is>
+          <t>O E CO LTD</t>
+        </is>
+      </c>
+      <c r="Q433" t="inlineStr">
+        <is>
+          <t>2026-06-26 00:00:00</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/trimika_data.xlsx
+++ b/trimika_data.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q770"/>
+  <dimension ref="A1:Q786"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -36330,28 +36330,28 @@
     <row r="430">
       <c r="A430" t="inlineStr">
         <is>
-          <t>2566232</t>
+          <t>4539529</t>
         </is>
       </c>
       <c r="B430" t="inlineStr">
         <is>
-          <t>EF4-0232576-7</t>
+          <t>EF4-0232822-5</t>
         </is>
       </c>
       <c r="C430" t="inlineStr">
         <is>
-          <t>Vessel, Container</t>
+          <t>Air, Non-container</t>
         </is>
       </c>
       <c r="D430" t="inlineStr"/>
       <c r="E430" t="inlineStr">
         <is>
-          <t>9903.03.01</t>
+          <t>9903.88.03</t>
         </is>
       </c>
       <c r="F430" t="inlineStr">
         <is>
-          <t>SECTION 122 - 10% DUTY</t>
+          <t>ARTICLE OF CHINA,US NTE 20(F)</t>
         </is>
       </c>
       <c r="G430" t="inlineStr">
@@ -36361,64 +36361,64 @@
       </c>
       <c r="H430" t="inlineStr">
         <is>
-          <t>9903.03.01</t>
+          <t>9903.88.03</t>
         </is>
       </c>
       <c r="I430" t="inlineStr">
         <is>
-          <t>3920.20.0055</t>
+          <t>9903.03.01,9403.99.9045</t>
         </is>
       </c>
       <c r="J430" t="inlineStr">
         <is>
-          <t>TEUFELBERGER G.E.S.M.B.H</t>
+          <t>VISUAL CREATIONS, INC.</t>
         </is>
       </c>
       <c r="K430" t="inlineStr">
         <is>
-          <t>TEUSEI01</t>
+          <t>VISCRE</t>
         </is>
       </c>
       <c r="L430" t="inlineStr">
         <is>
-          <t>181704-13780</t>
+          <t>20-461602300</t>
         </is>
       </c>
       <c r="M430" t="inlineStr">
         <is>
+          <t>2026-06-26 00:00:00</t>
+        </is>
+      </c>
+      <c r="N430" t="inlineStr">
+        <is>
           <t>2026-06-28 00:00:00</t>
         </is>
       </c>
-      <c r="N430" t="inlineStr">
-        <is>
-          <t>2026-06-28 00:00:00</t>
-        </is>
-      </c>
       <c r="O430" t="inlineStr">
         <is>
-          <t>TEUFELBERGER GMBH</t>
+          <t>XIAMEN CUBES INDUSTRIAL &amp; TRADING C</t>
         </is>
       </c>
       <c r="P430" t="inlineStr">
         <is>
-          <t>TEUFELBERGER GMBH</t>
+          <t>XIAMEN CUBES INDUSTRIAL &amp; TRADING C</t>
         </is>
       </c>
       <c r="Q430" t="inlineStr">
         <is>
-          <t>2026-06-14 00:00:00</t>
+          <t>2026-06-26 00:00:00</t>
         </is>
       </c>
     </row>
     <row r="431">
       <c r="A431" t="inlineStr">
         <is>
-          <t>4539529</t>
+          <t>4539572</t>
         </is>
       </c>
       <c r="B431" t="inlineStr">
         <is>
-          <t>EF4-0232822-5</t>
+          <t>EF4-0232838-1</t>
         </is>
       </c>
       <c r="C431" t="inlineStr">
@@ -36426,15 +36426,19 @@
           <t>Air, Non-container</t>
         </is>
       </c>
-      <c r="D431" t="inlineStr"/>
+      <c r="D431" t="inlineStr">
+        <is>
+          <t>711583181</t>
+        </is>
+      </c>
       <c r="E431" t="inlineStr">
         <is>
-          <t>9903.88.03</t>
+          <t>9903.03.01</t>
         </is>
       </c>
       <c r="F431" t="inlineStr">
         <is>
-          <t>ARTICLE OF CHINA,US NTE 20(F)</t>
+          <t>SECTION 122 - 10% DUTY</t>
         </is>
       </c>
       <c r="G431" t="inlineStr">
@@ -36444,27 +36448,27 @@
       </c>
       <c r="H431" t="inlineStr">
         <is>
-          <t>9903.88.03</t>
+          <t>9903.03.01</t>
         </is>
       </c>
       <c r="I431" t="inlineStr">
         <is>
-          <t>9903.03.01,9403.99.9045</t>
+          <t>8438.90.9060</t>
         </is>
       </c>
       <c r="J431" t="inlineStr">
         <is>
-          <t>VISUAL CREATIONS, INC.</t>
+          <t>CANTRELL GAINCO GROUP INC</t>
         </is>
       </c>
       <c r="K431" t="inlineStr">
         <is>
-          <t>VISCRE</t>
+          <t>CANGAI01</t>
         </is>
       </c>
       <c r="L431" t="inlineStr">
         <is>
-          <t>20-461602300</t>
+          <t>31-151121700</t>
         </is>
       </c>
       <c r="M431" t="inlineStr">
@@ -36479,12 +36483,12 @@
       </c>
       <c r="O431" t="inlineStr">
         <is>
-          <t>XIAMEN CUBES INDUSTRIAL &amp; TRADING C</t>
+          <t>O E CO LTD</t>
         </is>
       </c>
       <c r="P431" t="inlineStr">
         <is>
-          <t>XIAMEN CUBES INDUSTRIAL &amp; TRADING C</t>
+          <t>O E CO LTD</t>
         </is>
       </c>
       <c r="Q431" t="inlineStr">
@@ -36496,24 +36500,20 @@
     <row r="432">
       <c r="A432" t="inlineStr">
         <is>
-          <t>4539572</t>
+          <t>2615655-1</t>
         </is>
       </c>
       <c r="B432" t="inlineStr">
         <is>
-          <t>EF4-0232838-1</t>
+          <t>EF4-0231809-3</t>
         </is>
       </c>
       <c r="C432" t="inlineStr">
         <is>
-          <t>Air, Non-container</t>
-        </is>
-      </c>
-      <c r="D432" t="inlineStr">
-        <is>
-          <t>711583181</t>
-        </is>
-      </c>
+          <t>Vessel, Non-container</t>
+        </is>
+      </c>
+      <c r="D432" t="inlineStr"/>
       <c r="E432" t="inlineStr">
         <is>
           <t>9903.03.01</t>
@@ -36536,47 +36536,47 @@
       </c>
       <c r="I432" t="inlineStr">
         <is>
-          <t>8438.90.9060</t>
+          <t>3926.90.4590</t>
         </is>
       </c>
       <c r="J432" t="inlineStr">
         <is>
-          <t>CANTRELL GAINCO GROUP INC</t>
+          <t>VIELER INTERNATIONAL LP</t>
         </is>
       </c>
       <c r="K432" t="inlineStr">
         <is>
-          <t>CANGAI01</t>
+          <t>VIEINT</t>
         </is>
       </c>
       <c r="L432" t="inlineStr">
         <is>
-          <t>31-151121700</t>
+          <t>58-255440400</t>
         </is>
       </c>
       <c r="M432" t="inlineStr">
         <is>
-          <t>2026-06-26 00:00:00</t>
+          <t>2026-06-18 00:00:00</t>
         </is>
       </c>
       <c r="N432" t="inlineStr">
         <is>
-          <t>2026-06-28 00:00:00</t>
+          <t>2026-06-29 00:00:00</t>
         </is>
       </c>
       <c r="O432" t="inlineStr">
         <is>
-          <t>O E CO LTD</t>
+          <t>VIELER INTERNATIONAL GMBH + CO. KG</t>
         </is>
       </c>
       <c r="P432" t="inlineStr">
         <is>
-          <t>O E CO LTD</t>
+          <t>VIELER INTERNATIONAL GMBH + CO. KG</t>
         </is>
       </c>
       <c r="Q432" t="inlineStr">
         <is>
-          <t>2026-06-26 00:00:00</t>
+          <t>2026-05-27 00:00:00</t>
         </is>
       </c>
     </row>
@@ -36609,7 +36609,7 @@
       </c>
       <c r="G433" t="inlineStr">
         <is>
-          <t>001</t>
+          <t>002</t>
         </is>
       </c>
       <c r="H433" t="inlineStr">
@@ -36682,27 +36682,27 @@
       <c r="D434" t="inlineStr"/>
       <c r="E434" t="inlineStr">
         <is>
-          <t>9903.03.01</t>
+          <t>9903.03.06</t>
         </is>
       </c>
       <c r="F434" t="inlineStr">
         <is>
-          <t>SECTION 122 - 10% DUTY</t>
+          <t>S122 EXCL,IRN/STL/ALUM,DERIV</t>
         </is>
       </c>
       <c r="G434" t="inlineStr">
         <is>
-          <t>002</t>
+          <t>003</t>
         </is>
       </c>
       <c r="H434" t="inlineStr">
         <is>
-          <t>9903.03.01</t>
+          <t>9903.03.06</t>
         </is>
       </c>
       <c r="I434" t="inlineStr">
         <is>
-          <t>3926.90.4590</t>
+          <t>9903.82.09,8302.42.3065</t>
         </is>
       </c>
       <c r="J434" t="inlineStr">
@@ -36775,7 +36775,7 @@
       </c>
       <c r="G435" t="inlineStr">
         <is>
-          <t>003</t>
+          <t>004</t>
         </is>
       </c>
       <c r="H435" t="inlineStr">
@@ -36858,7 +36858,7 @@
       </c>
       <c r="G436" t="inlineStr">
         <is>
-          <t>004</t>
+          <t>005</t>
         </is>
       </c>
       <c r="H436" t="inlineStr">
@@ -36941,7 +36941,7 @@
       </c>
       <c r="G437" t="inlineStr">
         <is>
-          <t>005</t>
+          <t>006</t>
         </is>
       </c>
       <c r="H437" t="inlineStr">
@@ -37024,7 +37024,7 @@
       </c>
       <c r="G438" t="inlineStr">
         <is>
-          <t>006</t>
+          <t>007</t>
         </is>
       </c>
       <c r="H438" t="inlineStr">
@@ -37107,7 +37107,7 @@
       </c>
       <c r="G439" t="inlineStr">
         <is>
-          <t>007</t>
+          <t>008</t>
         </is>
       </c>
       <c r="H439" t="inlineStr">
@@ -37190,7 +37190,7 @@
       </c>
       <c r="G440" t="inlineStr">
         <is>
-          <t>008</t>
+          <t>009</t>
         </is>
       </c>
       <c r="H440" t="inlineStr">
@@ -37273,7 +37273,7 @@
       </c>
       <c r="G441" t="inlineStr">
         <is>
-          <t>009</t>
+          <t>010</t>
         </is>
       </c>
       <c r="H441" t="inlineStr">
@@ -37356,7 +37356,7 @@
       </c>
       <c r="G442" t="inlineStr">
         <is>
-          <t>010</t>
+          <t>011</t>
         </is>
       </c>
       <c r="H442" t="inlineStr">
@@ -37439,7 +37439,7 @@
       </c>
       <c r="G443" t="inlineStr">
         <is>
-          <t>011</t>
+          <t>012</t>
         </is>
       </c>
       <c r="H443" t="inlineStr">
@@ -37522,7 +37522,7 @@
       </c>
       <c r="G444" t="inlineStr">
         <is>
-          <t>012</t>
+          <t>013</t>
         </is>
       </c>
       <c r="H444" t="inlineStr">
@@ -37605,7 +37605,7 @@
       </c>
       <c r="G445" t="inlineStr">
         <is>
-          <t>013</t>
+          <t>014</t>
         </is>
       </c>
       <c r="H445" t="inlineStr">
@@ -37688,7 +37688,7 @@
       </c>
       <c r="G446" t="inlineStr">
         <is>
-          <t>014</t>
+          <t>015</t>
         </is>
       </c>
       <c r="H446" t="inlineStr">
@@ -37698,7 +37698,7 @@
       </c>
       <c r="I446" t="inlineStr">
         <is>
-          <t>9903.82.09,8302.42.3065</t>
+          <t>9903.82.09,8302.42.3010</t>
         </is>
       </c>
       <c r="J446" t="inlineStr">
@@ -37771,7 +37771,7 @@
       </c>
       <c r="G447" t="inlineStr">
         <is>
-          <t>015</t>
+          <t>016</t>
         </is>
       </c>
       <c r="H447" t="inlineStr">
@@ -37781,7 +37781,7 @@
       </c>
       <c r="I447" t="inlineStr">
         <is>
-          <t>9903.82.09,8302.42.3010</t>
+          <t>9903.82.09,8302.42.3065</t>
         </is>
       </c>
       <c r="J447" t="inlineStr">
@@ -37854,7 +37854,7 @@
       </c>
       <c r="G448" t="inlineStr">
         <is>
-          <t>016</t>
+          <t>017</t>
         </is>
       </c>
       <c r="H448" t="inlineStr">
@@ -37937,7 +37937,7 @@
       </c>
       <c r="G449" t="inlineStr">
         <is>
-          <t>017</t>
+          <t>018</t>
         </is>
       </c>
       <c r="H449" t="inlineStr">
@@ -38020,7 +38020,7 @@
       </c>
       <c r="G450" t="inlineStr">
         <is>
-          <t>018</t>
+          <t>019</t>
         </is>
       </c>
       <c r="H450" t="inlineStr">
@@ -38030,7 +38030,7 @@
       </c>
       <c r="I450" t="inlineStr">
         <is>
-          <t>9903.82.09,8302.42.3065</t>
+          <t>9903.82.02,7604.29.1090</t>
         </is>
       </c>
       <c r="J450" t="inlineStr">
@@ -38103,7 +38103,7 @@
       </c>
       <c r="G451" t="inlineStr">
         <is>
-          <t>019</t>
+          <t>020</t>
         </is>
       </c>
       <c r="H451" t="inlineStr">
@@ -38113,7 +38113,7 @@
       </c>
       <c r="I451" t="inlineStr">
         <is>
-          <t>9903.82.02,7604.29.1090</t>
+          <t>9903.82.09,8302.42.3065</t>
         </is>
       </c>
       <c r="J451" t="inlineStr">
@@ -38176,27 +38176,27 @@
       <c r="D452" t="inlineStr"/>
       <c r="E452" t="inlineStr">
         <is>
-          <t>9903.03.06</t>
+          <t>9903.03.01</t>
         </is>
       </c>
       <c r="F452" t="inlineStr">
         <is>
-          <t>S122 EXCL,IRN/STL/ALUM,DERIV</t>
+          <t>SECTION 122 - 10% DUTY</t>
         </is>
       </c>
       <c r="G452" t="inlineStr">
         <is>
-          <t>020</t>
+          <t>021</t>
         </is>
       </c>
       <c r="H452" t="inlineStr">
         <is>
-          <t>9903.03.06</t>
+          <t>9903.03.01</t>
         </is>
       </c>
       <c r="I452" t="inlineStr">
         <is>
-          <t>9903.82.09,8302.42.3065</t>
+          <t>9403.99.1085</t>
         </is>
       </c>
       <c r="J452" t="inlineStr">
@@ -38259,27 +38259,27 @@
       <c r="D453" t="inlineStr"/>
       <c r="E453" t="inlineStr">
         <is>
-          <t>9903.03.01</t>
+          <t>9903.03.06</t>
         </is>
       </c>
       <c r="F453" t="inlineStr">
         <is>
-          <t>SECTION 122 - 10% DUTY</t>
+          <t>S122 EXCL,IRN/STL/ALUM,DERIV</t>
         </is>
       </c>
       <c r="G453" t="inlineStr">
         <is>
-          <t>021</t>
+          <t>022</t>
         </is>
       </c>
       <c r="H453" t="inlineStr">
         <is>
-          <t>9903.03.01</t>
+          <t>9903.03.06</t>
         </is>
       </c>
       <c r="I453" t="inlineStr">
         <is>
-          <t>9403.99.1085</t>
+          <t>9903.82.09,8302.42.3065</t>
         </is>
       </c>
       <c r="J453" t="inlineStr">
@@ -38352,7 +38352,7 @@
       </c>
       <c r="G454" t="inlineStr">
         <is>
-          <t>022</t>
+          <t>023</t>
         </is>
       </c>
       <c r="H454" t="inlineStr">
@@ -38435,7 +38435,7 @@
       </c>
       <c r="G455" t="inlineStr">
         <is>
-          <t>023</t>
+          <t>024</t>
         </is>
       </c>
       <c r="H455" t="inlineStr">
@@ -38518,7 +38518,7 @@
       </c>
       <c r="G456" t="inlineStr">
         <is>
-          <t>024</t>
+          <t>025</t>
         </is>
       </c>
       <c r="H456" t="inlineStr">
@@ -38601,7 +38601,7 @@
       </c>
       <c r="G457" t="inlineStr">
         <is>
-          <t>025</t>
+          <t>026</t>
         </is>
       </c>
       <c r="H457" t="inlineStr">
@@ -38684,7 +38684,7 @@
       </c>
       <c r="G458" t="inlineStr">
         <is>
-          <t>026</t>
+          <t>027</t>
         </is>
       </c>
       <c r="H458" t="inlineStr">
@@ -38694,7 +38694,7 @@
       </c>
       <c r="I458" t="inlineStr">
         <is>
-          <t>9903.82.09,8302.42.3065</t>
+          <t>9903.82.02,7604.29.1090</t>
         </is>
       </c>
       <c r="J458" t="inlineStr">
@@ -38767,7 +38767,7 @@
       </c>
       <c r="G459" t="inlineStr">
         <is>
-          <t>027</t>
+          <t>028</t>
         </is>
       </c>
       <c r="H459" t="inlineStr">
@@ -38850,7 +38850,7 @@
       </c>
       <c r="G460" t="inlineStr">
         <is>
-          <t>028</t>
+          <t>029</t>
         </is>
       </c>
       <c r="H460" t="inlineStr">
@@ -38860,7 +38860,7 @@
       </c>
       <c r="I460" t="inlineStr">
         <is>
-          <t>9903.82.02,7604.29.1090</t>
+          <t>9903.82.02,7604.21.0090</t>
         </is>
       </c>
       <c r="J460" t="inlineStr">
@@ -38933,7 +38933,7 @@
       </c>
       <c r="G461" t="inlineStr">
         <is>
-          <t>029</t>
+          <t>030</t>
         </is>
       </c>
       <c r="H461" t="inlineStr">
@@ -38943,7 +38943,7 @@
       </c>
       <c r="I461" t="inlineStr">
         <is>
-          <t>9903.82.02,7604.21.0090</t>
+          <t>9903.82.02,7604.29.1090</t>
         </is>
       </c>
       <c r="J461" t="inlineStr">
@@ -39016,7 +39016,7 @@
       </c>
       <c r="G462" t="inlineStr">
         <is>
-          <t>030</t>
+          <t>031</t>
         </is>
       </c>
       <c r="H462" t="inlineStr">
@@ -39099,7 +39099,7 @@
       </c>
       <c r="G463" t="inlineStr">
         <is>
-          <t>031</t>
+          <t>032</t>
         </is>
       </c>
       <c r="H463" t="inlineStr">
@@ -39182,7 +39182,7 @@
       </c>
       <c r="G464" t="inlineStr">
         <is>
-          <t>032</t>
+          <t>033</t>
         </is>
       </c>
       <c r="H464" t="inlineStr">
@@ -39265,7 +39265,7 @@
       </c>
       <c r="G465" t="inlineStr">
         <is>
-          <t>033</t>
+          <t>034</t>
         </is>
       </c>
       <c r="H465" t="inlineStr">
@@ -39275,7 +39275,7 @@
       </c>
       <c r="I465" t="inlineStr">
         <is>
-          <t>9903.82.02,7604.29.1090</t>
+          <t>9903.82.02,7604.21.0090</t>
         </is>
       </c>
       <c r="J465" t="inlineStr">
@@ -39338,27 +39338,27 @@
       <c r="D466" t="inlineStr"/>
       <c r="E466" t="inlineStr">
         <is>
-          <t>9903.03.06</t>
+          <t>9903.03.01</t>
         </is>
       </c>
       <c r="F466" t="inlineStr">
         <is>
-          <t>S122 EXCL,IRN/STL/ALUM,DERIV</t>
+          <t>SECTION 122 - 10% DUTY</t>
         </is>
       </c>
       <c r="G466" t="inlineStr">
         <is>
-          <t>034</t>
+          <t>035</t>
         </is>
       </c>
       <c r="H466" t="inlineStr">
         <is>
-          <t>9903.03.06</t>
+          <t>9903.03.01</t>
         </is>
       </c>
       <c r="I466" t="inlineStr">
         <is>
-          <t>9903.82.02,7604.21.0090</t>
+          <t>3926.90.4590</t>
         </is>
       </c>
       <c r="J466" t="inlineStr">
@@ -39421,27 +39421,27 @@
       <c r="D467" t="inlineStr"/>
       <c r="E467" t="inlineStr">
         <is>
-          <t>9903.03.01</t>
+          <t>9903.03.06</t>
         </is>
       </c>
       <c r="F467" t="inlineStr">
         <is>
-          <t>SECTION 122 - 10% DUTY</t>
+          <t>S122 EXCL,IRN/STL/ALUM,DERIV</t>
         </is>
       </c>
       <c r="G467" t="inlineStr">
         <is>
-          <t>035</t>
+          <t>036</t>
         </is>
       </c>
       <c r="H467" t="inlineStr">
         <is>
-          <t>9903.03.01</t>
+          <t>9903.03.06</t>
         </is>
       </c>
       <c r="I467" t="inlineStr">
         <is>
-          <t>3926.90.4590</t>
+          <t>9903.82.02,7604.21.0090</t>
         </is>
       </c>
       <c r="J467" t="inlineStr">
@@ -39514,7 +39514,7 @@
       </c>
       <c r="G468" t="inlineStr">
         <is>
-          <t>036</t>
+          <t>037</t>
         </is>
       </c>
       <c r="H468" t="inlineStr">
@@ -39597,7 +39597,7 @@
       </c>
       <c r="G469" t="inlineStr">
         <is>
-          <t>037</t>
+          <t>038</t>
         </is>
       </c>
       <c r="H469" t="inlineStr">
@@ -39607,7 +39607,7 @@
       </c>
       <c r="I469" t="inlineStr">
         <is>
-          <t>9903.82.02,7604.21.0090</t>
+          <t>9903.82.02,7604.29.1090</t>
         </is>
       </c>
       <c r="J469" t="inlineStr">
@@ -39680,7 +39680,7 @@
       </c>
       <c r="G470" t="inlineStr">
         <is>
-          <t>038</t>
+          <t>039</t>
         </is>
       </c>
       <c r="H470" t="inlineStr">
@@ -39690,7 +39690,7 @@
       </c>
       <c r="I470" t="inlineStr">
         <is>
-          <t>9903.82.02,7604.29.1090</t>
+          <t>9903.82.02,7318.15.8030</t>
         </is>
       </c>
       <c r="J470" t="inlineStr">
@@ -39763,7 +39763,7 @@
       </c>
       <c r="G471" t="inlineStr">
         <is>
-          <t>039</t>
+          <t>040</t>
         </is>
       </c>
       <c r="H471" t="inlineStr">
@@ -39773,7 +39773,7 @@
       </c>
       <c r="I471" t="inlineStr">
         <is>
-          <t>9903.82.02,7318.15.8030</t>
+          <t>9903.82.02,7318.15.6010</t>
         </is>
       </c>
       <c r="J471" t="inlineStr">
@@ -39846,7 +39846,7 @@
       </c>
       <c r="G472" t="inlineStr">
         <is>
-          <t>040</t>
+          <t>041</t>
         </is>
       </c>
       <c r="H472" t="inlineStr">
@@ -39856,7 +39856,7 @@
       </c>
       <c r="I472" t="inlineStr">
         <is>
-          <t>9903.82.02,7318.15.6010</t>
+          <t>9903.82.02,7318.15.8030</t>
         </is>
       </c>
       <c r="J472" t="inlineStr">
@@ -39929,7 +39929,7 @@
       </c>
       <c r="G473" t="inlineStr">
         <is>
-          <t>041</t>
+          <t>042</t>
         </is>
       </c>
       <c r="H473" t="inlineStr">
@@ -40012,7 +40012,7 @@
       </c>
       <c r="G474" t="inlineStr">
         <is>
-          <t>042</t>
+          <t>043</t>
         </is>
       </c>
       <c r="H474" t="inlineStr">
@@ -40022,7 +40022,7 @@
       </c>
       <c r="I474" t="inlineStr">
         <is>
-          <t>9903.82.02,7318.15.8030</t>
+          <t>9903.82.02,7318.29.0000</t>
         </is>
       </c>
       <c r="J474" t="inlineStr">
@@ -40095,7 +40095,7 @@
       </c>
       <c r="G475" t="inlineStr">
         <is>
-          <t>043</t>
+          <t>044</t>
         </is>
       </c>
       <c r="H475" t="inlineStr">
@@ -40105,7 +40105,7 @@
       </c>
       <c r="I475" t="inlineStr">
         <is>
-          <t>9903.82.02,7318.29.0000</t>
+          <t>9903.82.09,8302.42.3065</t>
         </is>
       </c>
       <c r="J475" t="inlineStr">
@@ -40178,7 +40178,7 @@
       </c>
       <c r="G476" t="inlineStr">
         <is>
-          <t>044</t>
+          <t>045</t>
         </is>
       </c>
       <c r="H476" t="inlineStr">
@@ -40188,7 +40188,7 @@
       </c>
       <c r="I476" t="inlineStr">
         <is>
-          <t>9903.82.09,8302.42.3065</t>
+          <t>9903.82.02,7318.29.0000</t>
         </is>
       </c>
       <c r="J476" t="inlineStr">
@@ -40261,7 +40261,7 @@
       </c>
       <c r="G477" t="inlineStr">
         <is>
-          <t>045</t>
+          <t>046</t>
         </is>
       </c>
       <c r="H477" t="inlineStr">
@@ -40271,7 +40271,7 @@
       </c>
       <c r="I477" t="inlineStr">
         <is>
-          <t>9903.82.02,7318.29.0000</t>
+          <t>9903.82.02,7318.15.8069</t>
         </is>
       </c>
       <c r="J477" t="inlineStr">
@@ -40344,7 +40344,7 @@
       </c>
       <c r="G478" t="inlineStr">
         <is>
-          <t>046</t>
+          <t>047</t>
         </is>
       </c>
       <c r="H478" t="inlineStr">
@@ -40354,7 +40354,7 @@
       </c>
       <c r="I478" t="inlineStr">
         <is>
-          <t>9903.82.02,7318.15.8069</t>
+          <t>9903.82.02,7318.29.0000</t>
         </is>
       </c>
       <c r="J478" t="inlineStr">
@@ -40427,7 +40427,7 @@
       </c>
       <c r="G479" t="inlineStr">
         <is>
-          <t>047</t>
+          <t>048</t>
         </is>
       </c>
       <c r="H479" t="inlineStr">
@@ -40437,7 +40437,7 @@
       </c>
       <c r="I479" t="inlineStr">
         <is>
-          <t>9903.82.02,7318.29.0000</t>
+          <t>9903.82.02,7307.92.3030</t>
         </is>
       </c>
       <c r="J479" t="inlineStr">
@@ -40510,7 +40510,7 @@
       </c>
       <c r="G480" t="inlineStr">
         <is>
-          <t>048</t>
+          <t>049</t>
         </is>
       </c>
       <c r="H480" t="inlineStr">
@@ -40520,7 +40520,7 @@
       </c>
       <c r="I480" t="inlineStr">
         <is>
-          <t>9903.82.02,7307.92.3030</t>
+          <t>9903.82.09,8302.42.3065</t>
         </is>
       </c>
       <c r="J480" t="inlineStr">
@@ -40593,7 +40593,7 @@
       </c>
       <c r="G481" t="inlineStr">
         <is>
-          <t>049</t>
+          <t>050</t>
         </is>
       </c>
       <c r="H481" t="inlineStr">
@@ -40603,7 +40603,7 @@
       </c>
       <c r="I481" t="inlineStr">
         <is>
-          <t>9903.82.09,8302.42.3065</t>
+          <t>9903.82.02,7320.90.5060</t>
         </is>
       </c>
       <c r="J481" t="inlineStr">
@@ -40676,7 +40676,7 @@
       </c>
       <c r="G482" t="inlineStr">
         <is>
-          <t>050</t>
+          <t>051</t>
         </is>
       </c>
       <c r="H482" t="inlineStr">
@@ -40749,27 +40749,27 @@
       <c r="D483" t="inlineStr"/>
       <c r="E483" t="inlineStr">
         <is>
-          <t>9903.03.06</t>
+          <t>9903.03.01</t>
         </is>
       </c>
       <c r="F483" t="inlineStr">
         <is>
-          <t>S122 EXCL,IRN/STL/ALUM,DERIV</t>
+          <t>SECTION 122 - 10% DUTY</t>
         </is>
       </c>
       <c r="G483" t="inlineStr">
         <is>
-          <t>051</t>
+          <t>052</t>
         </is>
       </c>
       <c r="H483" t="inlineStr">
         <is>
-          <t>9903.03.06</t>
+          <t>9903.03.01</t>
         </is>
       </c>
       <c r="I483" t="inlineStr">
         <is>
-          <t>9903.82.02,7320.90.5060</t>
+          <t>3926.90.9989</t>
         </is>
       </c>
       <c r="J483" t="inlineStr">
@@ -40832,27 +40832,27 @@
       <c r="D484" t="inlineStr"/>
       <c r="E484" t="inlineStr">
         <is>
-          <t>9903.03.01</t>
+          <t>9903.03.06</t>
         </is>
       </c>
       <c r="F484" t="inlineStr">
         <is>
-          <t>SECTION 122 - 10% DUTY</t>
+          <t>S122 EXCL,IRN/STL/ALUM,DERIV</t>
         </is>
       </c>
       <c r="G484" t="inlineStr">
         <is>
-          <t>052</t>
+          <t>053</t>
         </is>
       </c>
       <c r="H484" t="inlineStr">
         <is>
-          <t>9903.03.01</t>
+          <t>9903.03.06</t>
         </is>
       </c>
       <c r="I484" t="inlineStr">
         <is>
-          <t>3926.90.9989</t>
+          <t>9903.82.09,8302.42.3065</t>
         </is>
       </c>
       <c r="J484" t="inlineStr">
@@ -40925,7 +40925,7 @@
       </c>
       <c r="G485" t="inlineStr">
         <is>
-          <t>053</t>
+          <t>054</t>
         </is>
       </c>
       <c r="H485" t="inlineStr">
@@ -41008,7 +41008,7 @@
       </c>
       <c r="G486" t="inlineStr">
         <is>
-          <t>054</t>
+          <t>055</t>
         </is>
       </c>
       <c r="H486" t="inlineStr">
@@ -41091,7 +41091,7 @@
       </c>
       <c r="G487" t="inlineStr">
         <is>
-          <t>055</t>
+          <t>056</t>
         </is>
       </c>
       <c r="H487" t="inlineStr">
@@ -41101,7 +41101,7 @@
       </c>
       <c r="I487" t="inlineStr">
         <is>
-          <t>9903.82.09,8302.42.3065</t>
+          <t>9903.82.09,8302.42.3010</t>
         </is>
       </c>
       <c r="J487" t="inlineStr">
@@ -41174,7 +41174,7 @@
       </c>
       <c r="G488" t="inlineStr">
         <is>
-          <t>056</t>
+          <t>057</t>
         </is>
       </c>
       <c r="H488" t="inlineStr">
@@ -41257,7 +41257,7 @@
       </c>
       <c r="G489" t="inlineStr">
         <is>
-          <t>057</t>
+          <t>058</t>
         </is>
       </c>
       <c r="H489" t="inlineStr">
@@ -41340,7 +41340,7 @@
       </c>
       <c r="G490" t="inlineStr">
         <is>
-          <t>058</t>
+          <t>059</t>
         </is>
       </c>
       <c r="H490" t="inlineStr">
@@ -41423,7 +41423,7 @@
       </c>
       <c r="G491" t="inlineStr">
         <is>
-          <t>059</t>
+          <t>060</t>
         </is>
       </c>
       <c r="H491" t="inlineStr">
@@ -41506,7 +41506,7 @@
       </c>
       <c r="G492" t="inlineStr">
         <is>
-          <t>060</t>
+          <t>061</t>
         </is>
       </c>
       <c r="H492" t="inlineStr">
@@ -41589,7 +41589,7 @@
       </c>
       <c r="G493" t="inlineStr">
         <is>
-          <t>061</t>
+          <t>062</t>
         </is>
       </c>
       <c r="H493" t="inlineStr">
@@ -41672,7 +41672,7 @@
       </c>
       <c r="G494" t="inlineStr">
         <is>
-          <t>062</t>
+          <t>063</t>
         </is>
       </c>
       <c r="H494" t="inlineStr">
@@ -41755,7 +41755,7 @@
       </c>
       <c r="G495" t="inlineStr">
         <is>
-          <t>063</t>
+          <t>064</t>
         </is>
       </c>
       <c r="H495" t="inlineStr">
@@ -41838,7 +41838,7 @@
       </c>
       <c r="G496" t="inlineStr">
         <is>
-          <t>064</t>
+          <t>065</t>
         </is>
       </c>
       <c r="H496" t="inlineStr">
@@ -41921,7 +41921,7 @@
       </c>
       <c r="G497" t="inlineStr">
         <is>
-          <t>065</t>
+          <t>066</t>
         </is>
       </c>
       <c r="H497" t="inlineStr">
@@ -41931,7 +41931,7 @@
       </c>
       <c r="I497" t="inlineStr">
         <is>
-          <t>9903.82.09,8302.42.3010</t>
+          <t>9903.82.02,7604.29.1090</t>
         </is>
       </c>
       <c r="J497" t="inlineStr">
@@ -42004,7 +42004,7 @@
       </c>
       <c r="G498" t="inlineStr">
         <is>
-          <t>066</t>
+          <t>067</t>
         </is>
       </c>
       <c r="H498" t="inlineStr">
@@ -42014,7 +42014,7 @@
       </c>
       <c r="I498" t="inlineStr">
         <is>
-          <t>9903.82.02,7604.29.1090</t>
+          <t>9903.82.09,8302.42.3065</t>
         </is>
       </c>
       <c r="J498" t="inlineStr">
@@ -42087,7 +42087,7 @@
       </c>
       <c r="G499" t="inlineStr">
         <is>
-          <t>067</t>
+          <t>068</t>
         </is>
       </c>
       <c r="H499" t="inlineStr">
@@ -42097,7 +42097,7 @@
       </c>
       <c r="I499" t="inlineStr">
         <is>
-          <t>9903.82.09,8302.42.3065</t>
+          <t>9903.82.09,8302.42.3010</t>
         </is>
       </c>
       <c r="J499" t="inlineStr">
@@ -42170,7 +42170,7 @@
       </c>
       <c r="G500" t="inlineStr">
         <is>
-          <t>068</t>
+          <t>069</t>
         </is>
       </c>
       <c r="H500" t="inlineStr">
@@ -42180,7 +42180,7 @@
       </c>
       <c r="I500" t="inlineStr">
         <is>
-          <t>9903.82.09,8302.42.3010</t>
+          <t>9903.82.09,8302.42.3065</t>
         </is>
       </c>
       <c r="J500" t="inlineStr">
@@ -42253,7 +42253,7 @@
       </c>
       <c r="G501" t="inlineStr">
         <is>
-          <t>069</t>
+          <t>070</t>
         </is>
       </c>
       <c r="H501" t="inlineStr">
@@ -42336,7 +42336,7 @@
       </c>
       <c r="G502" t="inlineStr">
         <is>
-          <t>070</t>
+          <t>071</t>
         </is>
       </c>
       <c r="H502" t="inlineStr">
@@ -42346,7 +42346,7 @@
       </c>
       <c r="I502" t="inlineStr">
         <is>
-          <t>9903.82.09,8302.42.3065</t>
+          <t>9903.82.09,8302.42.3010</t>
         </is>
       </c>
       <c r="J502" t="inlineStr">
@@ -42419,7 +42419,7 @@
       </c>
       <c r="G503" t="inlineStr">
         <is>
-          <t>071</t>
+          <t>072</t>
         </is>
       </c>
       <c r="H503" t="inlineStr">
@@ -42429,7 +42429,7 @@
       </c>
       <c r="I503" t="inlineStr">
         <is>
-          <t>9903.82.09,8302.42.3010</t>
+          <t>9903.82.02,7604.29.1090</t>
         </is>
       </c>
       <c r="J503" t="inlineStr">
@@ -42502,7 +42502,7 @@
       </c>
       <c r="G504" t="inlineStr">
         <is>
-          <t>072</t>
+          <t>073</t>
         </is>
       </c>
       <c r="H504" t="inlineStr">
@@ -42512,7 +42512,7 @@
       </c>
       <c r="I504" t="inlineStr">
         <is>
-          <t>9903.82.02,7604.29.1090</t>
+          <t>9903.82.09,8302.42.3010</t>
         </is>
       </c>
       <c r="J504" t="inlineStr">
@@ -42585,7 +42585,7 @@
       </c>
       <c r="G505" t="inlineStr">
         <is>
-          <t>073</t>
+          <t>074</t>
         </is>
       </c>
       <c r="H505" t="inlineStr">
@@ -42668,7 +42668,7 @@
       </c>
       <c r="G506" t="inlineStr">
         <is>
-          <t>074</t>
+          <t>075</t>
         </is>
       </c>
       <c r="H506" t="inlineStr">
@@ -42678,7 +42678,7 @@
       </c>
       <c r="I506" t="inlineStr">
         <is>
-          <t>9903.82.09,8302.42.3010</t>
+          <t>9903.82.02,7318.21.0090</t>
         </is>
       </c>
       <c r="J506" t="inlineStr">
@@ -42751,7 +42751,7 @@
       </c>
       <c r="G507" t="inlineStr">
         <is>
-          <t>075</t>
+          <t>076</t>
         </is>
       </c>
       <c r="H507" t="inlineStr">
@@ -42761,7 +42761,7 @@
       </c>
       <c r="I507" t="inlineStr">
         <is>
-          <t>9903.82.02,7318.21.0090</t>
+          <t>9903.82.09,8302.42.3065</t>
         </is>
       </c>
       <c r="J507" t="inlineStr">
@@ -42834,7 +42834,7 @@
       </c>
       <c r="G508" t="inlineStr">
         <is>
-          <t>076</t>
+          <t>077</t>
         </is>
       </c>
       <c r="H508" t="inlineStr">
@@ -42917,7 +42917,7 @@
       </c>
       <c r="G509" t="inlineStr">
         <is>
-          <t>077</t>
+          <t>078</t>
         </is>
       </c>
       <c r="H509" t="inlineStr">
@@ -43000,7 +43000,7 @@
       </c>
       <c r="G510" t="inlineStr">
         <is>
-          <t>078</t>
+          <t>079</t>
         </is>
       </c>
       <c r="H510" t="inlineStr">
@@ -43083,7 +43083,7 @@
       </c>
       <c r="G511" t="inlineStr">
         <is>
-          <t>079</t>
+          <t>080</t>
         </is>
       </c>
       <c r="H511" t="inlineStr">
@@ -43093,7 +43093,7 @@
       </c>
       <c r="I511" t="inlineStr">
         <is>
-          <t>9903.82.09,8302.42.3065</t>
+          <t>9903.82.09,8302.42.3010</t>
         </is>
       </c>
       <c r="J511" t="inlineStr">
@@ -43166,7 +43166,7 @@
       </c>
       <c r="G512" t="inlineStr">
         <is>
-          <t>080</t>
+          <t>081</t>
         </is>
       </c>
       <c r="H512" t="inlineStr">
@@ -43249,7 +43249,7 @@
       </c>
       <c r="G513" t="inlineStr">
         <is>
-          <t>081</t>
+          <t>082</t>
         </is>
       </c>
       <c r="H513" t="inlineStr">
@@ -43332,7 +43332,7 @@
       </c>
       <c r="G514" t="inlineStr">
         <is>
-          <t>082</t>
+          <t>083</t>
         </is>
       </c>
       <c r="H514" t="inlineStr">
@@ -43342,7 +43342,7 @@
       </c>
       <c r="I514" t="inlineStr">
         <is>
-          <t>9903.82.09,8302.42.3010</t>
+          <t>9903.82.09,8302.42.3065</t>
         </is>
       </c>
       <c r="J514" t="inlineStr">
@@ -43415,7 +43415,7 @@
       </c>
       <c r="G515" t="inlineStr">
         <is>
-          <t>083</t>
+          <t>084</t>
         </is>
       </c>
       <c r="H515" t="inlineStr">
@@ -43425,7 +43425,7 @@
       </c>
       <c r="I515" t="inlineStr">
         <is>
-          <t>9903.82.09,8302.42.3065</t>
+          <t>9903.82.02,7604.21.0090</t>
         </is>
       </c>
       <c r="J515" t="inlineStr">
@@ -43498,7 +43498,7 @@
       </c>
       <c r="G516" t="inlineStr">
         <is>
-          <t>084</t>
+          <t>085</t>
         </is>
       </c>
       <c r="H516" t="inlineStr">
@@ -43508,7 +43508,7 @@
       </c>
       <c r="I516" t="inlineStr">
         <is>
-          <t>9903.82.02,7604.21.0090</t>
+          <t>9903.82.02,7318.22.0000</t>
         </is>
       </c>
       <c r="J516" t="inlineStr">
@@ -43581,7 +43581,7 @@
       </c>
       <c r="G517" t="inlineStr">
         <is>
-          <t>085</t>
+          <t>086</t>
         </is>
       </c>
       <c r="H517" t="inlineStr">
@@ -43664,7 +43664,7 @@
       </c>
       <c r="G518" t="inlineStr">
         <is>
-          <t>086</t>
+          <t>087</t>
         </is>
       </c>
       <c r="H518" t="inlineStr">
@@ -43674,7 +43674,7 @@
       </c>
       <c r="I518" t="inlineStr">
         <is>
-          <t>9903.82.02,7318.22.0000</t>
+          <t>9903.82.02,7307.92.3030</t>
         </is>
       </c>
       <c r="J518" t="inlineStr">
@@ -43747,7 +43747,7 @@
       </c>
       <c r="G519" t="inlineStr">
         <is>
-          <t>087</t>
+          <t>088</t>
         </is>
       </c>
       <c r="H519" t="inlineStr">
@@ -43830,7 +43830,7 @@
       </c>
       <c r="G520" t="inlineStr">
         <is>
-          <t>088</t>
+          <t>089</t>
         </is>
       </c>
       <c r="H520" t="inlineStr">
@@ -43840,7 +43840,7 @@
       </c>
       <c r="I520" t="inlineStr">
         <is>
-          <t>9903.82.02,7307.92.3030</t>
+          <t>9903.82.02,7318.29.0000</t>
         </is>
       </c>
       <c r="J520" t="inlineStr">
@@ -43903,27 +43903,27 @@
       <c r="D521" t="inlineStr"/>
       <c r="E521" t="inlineStr">
         <is>
-          <t>9903.03.06</t>
+          <t>9903.03.01</t>
         </is>
       </c>
       <c r="F521" t="inlineStr">
         <is>
-          <t>S122 EXCL,IRN/STL/ALUM,DERIV</t>
+          <t>SECTION 122 - 10% DUTY</t>
         </is>
       </c>
       <c r="G521" t="inlineStr">
         <is>
-          <t>089</t>
+          <t>090</t>
         </is>
       </c>
       <c r="H521" t="inlineStr">
         <is>
-          <t>9903.03.06</t>
+          <t>9903.03.01</t>
         </is>
       </c>
       <c r="I521" t="inlineStr">
         <is>
-          <t>9903.82.02,7318.29.0000</t>
+          <t>3926.90.9989</t>
         </is>
       </c>
       <c r="J521" t="inlineStr">
@@ -43996,7 +43996,7 @@
       </c>
       <c r="G522" t="inlineStr">
         <is>
-          <t>090</t>
+          <t>091</t>
         </is>
       </c>
       <c r="H522" t="inlineStr">
@@ -44079,7 +44079,7 @@
       </c>
       <c r="G523" t="inlineStr">
         <is>
-          <t>091</t>
+          <t>092</t>
         </is>
       </c>
       <c r="H523" t="inlineStr">
@@ -44089,7 +44089,7 @@
       </c>
       <c r="I523" t="inlineStr">
         <is>
-          <t>3926.90.9989</t>
+          <t>7616.10.1000</t>
         </is>
       </c>
       <c r="J523" t="inlineStr">
@@ -44152,27 +44152,27 @@
       <c r="D524" t="inlineStr"/>
       <c r="E524" t="inlineStr">
         <is>
-          <t>9903.03.01</t>
+          <t>9903.03.06</t>
         </is>
       </c>
       <c r="F524" t="inlineStr">
         <is>
-          <t>SECTION 122 - 10% DUTY</t>
+          <t>S122 EXCL,IRN/STL/ALUM,DERIV</t>
         </is>
       </c>
       <c r="G524" t="inlineStr">
         <is>
-          <t>092</t>
+          <t>093</t>
         </is>
       </c>
       <c r="H524" t="inlineStr">
         <is>
-          <t>9903.03.01</t>
+          <t>9903.03.06</t>
         </is>
       </c>
       <c r="I524" t="inlineStr">
         <is>
-          <t>7616.10.1000</t>
+          <t>9903.82.02,7307.92.3030</t>
         </is>
       </c>
       <c r="J524" t="inlineStr">
@@ -44245,7 +44245,7 @@
       </c>
       <c r="G525" t="inlineStr">
         <is>
-          <t>093</t>
+          <t>094</t>
         </is>
       </c>
       <c r="H525" t="inlineStr">
@@ -44328,7 +44328,7 @@
       </c>
       <c r="G526" t="inlineStr">
         <is>
-          <t>094</t>
+          <t>095</t>
         </is>
       </c>
       <c r="H526" t="inlineStr">
@@ -44338,7 +44338,7 @@
       </c>
       <c r="I526" t="inlineStr">
         <is>
-          <t>9903.82.02,7307.92.3030</t>
+          <t>9903.82.09,8302.42.3065</t>
         </is>
       </c>
       <c r="J526" t="inlineStr">
@@ -44411,7 +44411,7 @@
       </c>
       <c r="G527" t="inlineStr">
         <is>
-          <t>095</t>
+          <t>096</t>
         </is>
       </c>
       <c r="H527" t="inlineStr">
@@ -44494,7 +44494,7 @@
       </c>
       <c r="G528" t="inlineStr">
         <is>
-          <t>096</t>
+          <t>097</t>
         </is>
       </c>
       <c r="H528" t="inlineStr">
@@ -44504,7 +44504,7 @@
       </c>
       <c r="I528" t="inlineStr">
         <is>
-          <t>9903.82.09,8302.42.3065</t>
+          <t>9903.82.02,7318.15.8030</t>
         </is>
       </c>
       <c r="J528" t="inlineStr">
@@ -44577,7 +44577,7 @@
       </c>
       <c r="G529" t="inlineStr">
         <is>
-          <t>097</t>
+          <t>098</t>
         </is>
       </c>
       <c r="H529" t="inlineStr">
@@ -44587,7 +44587,7 @@
       </c>
       <c r="I529" t="inlineStr">
         <is>
-          <t>9903.82.02,7318.15.8030</t>
+          <t>9903.82.09,8302.42.3065</t>
         </is>
       </c>
       <c r="J529" t="inlineStr">
@@ -44660,7 +44660,7 @@
       </c>
       <c r="G530" t="inlineStr">
         <is>
-          <t>098</t>
+          <t>099</t>
         </is>
       </c>
       <c r="H530" t="inlineStr">
@@ -44743,7 +44743,7 @@
       </c>
       <c r="G531" t="inlineStr">
         <is>
-          <t>099</t>
+          <t>100</t>
         </is>
       </c>
       <c r="H531" t="inlineStr">
@@ -44826,7 +44826,7 @@
       </c>
       <c r="G532" t="inlineStr">
         <is>
-          <t>100</t>
+          <t>101</t>
         </is>
       </c>
       <c r="H532" t="inlineStr">
@@ -44909,7 +44909,7 @@
       </c>
       <c r="G533" t="inlineStr">
         <is>
-          <t>101</t>
+          <t>102</t>
         </is>
       </c>
       <c r="H533" t="inlineStr">
@@ -44992,7 +44992,7 @@
       </c>
       <c r="G534" t="inlineStr">
         <is>
-          <t>102</t>
+          <t>103</t>
         </is>
       </c>
       <c r="H534" t="inlineStr">
@@ -45075,7 +45075,7 @@
       </c>
       <c r="G535" t="inlineStr">
         <is>
-          <t>103</t>
+          <t>104</t>
         </is>
       </c>
       <c r="H535" t="inlineStr">
@@ -45158,7 +45158,7 @@
       </c>
       <c r="G536" t="inlineStr">
         <is>
-          <t>104</t>
+          <t>105</t>
         </is>
       </c>
       <c r="H536" t="inlineStr">
@@ -45168,7 +45168,7 @@
       </c>
       <c r="I536" t="inlineStr">
         <is>
-          <t>9903.82.09,8302.42.3065</t>
+          <t>9903.82.02,7307.92.3030</t>
         </is>
       </c>
       <c r="J536" t="inlineStr">
@@ -45241,7 +45241,7 @@
       </c>
       <c r="G537" t="inlineStr">
         <is>
-          <t>105</t>
+          <t>106</t>
         </is>
       </c>
       <c r="H537" t="inlineStr">
@@ -45251,7 +45251,7 @@
       </c>
       <c r="I537" t="inlineStr">
         <is>
-          <t>9903.82.02,7307.92.3030</t>
+          <t>9903.82.09,8302.42.3065</t>
         </is>
       </c>
       <c r="J537" t="inlineStr">
@@ -45324,7 +45324,7 @@
       </c>
       <c r="G538" t="inlineStr">
         <is>
-          <t>106</t>
+          <t>107</t>
         </is>
       </c>
       <c r="H538" t="inlineStr">
@@ -45407,7 +45407,7 @@
       </c>
       <c r="G539" t="inlineStr">
         <is>
-          <t>107</t>
+          <t>108</t>
         </is>
       </c>
       <c r="H539" t="inlineStr">
@@ -45490,7 +45490,7 @@
       </c>
       <c r="G540" t="inlineStr">
         <is>
-          <t>108</t>
+          <t>109</t>
         </is>
       </c>
       <c r="H540" t="inlineStr">
@@ -45563,27 +45563,27 @@
       <c r="D541" t="inlineStr"/>
       <c r="E541" t="inlineStr">
         <is>
-          <t>9903.03.06</t>
+          <t>9903.03.01</t>
         </is>
       </c>
       <c r="F541" t="inlineStr">
         <is>
-          <t>S122 EXCL,IRN/STL/ALUM,DERIV</t>
+          <t>SECTION 122 - 10% DUTY</t>
         </is>
       </c>
       <c r="G541" t="inlineStr">
         <is>
-          <t>109</t>
+          <t>110</t>
         </is>
       </c>
       <c r="H541" t="inlineStr">
         <is>
-          <t>9903.03.06</t>
+          <t>9903.03.01</t>
         </is>
       </c>
       <c r="I541" t="inlineStr">
         <is>
-          <t>9903.82.09,8302.42.3065</t>
+          <t>9403.99.1085</t>
         </is>
       </c>
       <c r="J541" t="inlineStr">
@@ -45630,12 +45630,12 @@
     <row r="542">
       <c r="A542" t="inlineStr">
         <is>
-          <t>2615655-1</t>
+          <t>2615655-2</t>
         </is>
       </c>
       <c r="B542" t="inlineStr">
         <is>
-          <t>EF4-0231809-3</t>
+          <t>EF4-0231820-0</t>
         </is>
       </c>
       <c r="C542" t="inlineStr">
@@ -45646,42 +45646,42 @@
       <c r="D542" t="inlineStr"/>
       <c r="E542" t="inlineStr">
         <is>
-          <t>9903.03.01</t>
+          <t>9903.88.03</t>
         </is>
       </c>
       <c r="F542" t="inlineStr">
         <is>
-          <t>SECTION 122 - 10% DUTY</t>
+          <t>ARTICLE OF CHINA,US NTE 20(F)</t>
         </is>
       </c>
       <c r="G542" t="inlineStr">
         <is>
-          <t>110</t>
+          <t>001</t>
         </is>
       </c>
       <c r="H542" t="inlineStr">
         <is>
-          <t>9903.03.01</t>
+          <t>9903.88.03</t>
         </is>
       </c>
       <c r="I542" t="inlineStr">
         <is>
-          <t>9403.99.1085</t>
+          <t>9903.03.06,9903.82.02,7318.15.8055</t>
         </is>
       </c>
       <c r="J542" t="inlineStr">
         <is>
-          <t>VIELER INTERNATIONAL LP</t>
+          <t>EUROLINK FSS LLC</t>
         </is>
       </c>
       <c r="K542" t="inlineStr">
         <is>
-          <t>VIEINT</t>
+          <t>SUPLIN</t>
         </is>
       </c>
       <c r="L542" t="inlineStr">
         <is>
-          <t>58-255440400</t>
+          <t>57-112314200</t>
         </is>
       </c>
       <c r="M542" t="inlineStr">
@@ -45696,12 +45696,12 @@
       </c>
       <c r="O542" t="inlineStr">
         <is>
-          <t>VIELER INTERNATIONAL GMBH + CO. KG</t>
+          <t>WASI GMBH</t>
         </is>
       </c>
       <c r="P542" t="inlineStr">
         <is>
-          <t>VIELER INTERNATIONAL GMBH + CO. KG</t>
+          <t>WASI GMBH</t>
         </is>
       </c>
       <c r="Q542" t="inlineStr">
@@ -45739,7 +45739,7 @@
       </c>
       <c r="G543" t="inlineStr">
         <is>
-          <t>001</t>
+          <t>002</t>
         </is>
       </c>
       <c r="H543" t="inlineStr">
@@ -45812,27 +45812,27 @@
       <c r="D544" t="inlineStr"/>
       <c r="E544" t="inlineStr">
         <is>
-          <t>9903.88.03</t>
+          <t>9903.03.06</t>
         </is>
       </c>
       <c r="F544" t="inlineStr">
         <is>
-          <t>ARTICLE OF CHINA,US NTE 20(F)</t>
+          <t>S122 EXCL,IRN/STL/ALUM,DERIV</t>
         </is>
       </c>
       <c r="G544" t="inlineStr">
         <is>
-          <t>002</t>
+          <t>003</t>
         </is>
       </c>
       <c r="H544" t="inlineStr">
         <is>
-          <t>9903.88.03</t>
+          <t>9903.03.06</t>
         </is>
       </c>
       <c r="I544" t="inlineStr">
         <is>
-          <t>9903.03.06,9903.82.02,7318.15.8055</t>
+          <t>9903.82.02,7318.15.8030</t>
         </is>
       </c>
       <c r="J544" t="inlineStr">
@@ -45895,27 +45895,27 @@
       <c r="D545" t="inlineStr"/>
       <c r="E545" t="inlineStr">
         <is>
-          <t>9903.03.06</t>
+          <t>9903.88.15</t>
         </is>
       </c>
       <c r="F545" t="inlineStr">
         <is>
-          <t>S122 EXCL,IRN/STL/ALUM,DERIV</t>
+          <t>ARTICLE OF CHINA,US NTE 20(R)</t>
         </is>
       </c>
       <c r="G545" t="inlineStr">
         <is>
-          <t>003</t>
+          <t>004</t>
         </is>
       </c>
       <c r="H545" t="inlineStr">
         <is>
-          <t>9903.03.06</t>
+          <t>9903.88.15</t>
         </is>
       </c>
       <c r="I545" t="inlineStr">
         <is>
-          <t>9903.82.02,7318.15.8030</t>
+          <t>9903.03.06,9903.82.02,7318.16.0060</t>
         </is>
       </c>
       <c r="J545" t="inlineStr">
@@ -45978,27 +45978,27 @@
       <c r="D546" t="inlineStr"/>
       <c r="E546" t="inlineStr">
         <is>
-          <t>9903.88.15</t>
+          <t>9903.88.03</t>
         </is>
       </c>
       <c r="F546" t="inlineStr">
         <is>
-          <t>ARTICLE OF CHINA,US NTE 20(R)</t>
+          <t>ARTICLE OF CHINA,US NTE 20(F)</t>
         </is>
       </c>
       <c r="G546" t="inlineStr">
         <is>
-          <t>004</t>
+          <t>005</t>
         </is>
       </c>
       <c r="H546" t="inlineStr">
         <is>
-          <t>9903.88.15</t>
+          <t>9903.88.03</t>
         </is>
       </c>
       <c r="I546" t="inlineStr">
         <is>
-          <t>9903.03.06,9903.82.02,7318.16.0060</t>
+          <t>9903.03.06,9903.82.02,7318.22.0000</t>
         </is>
       </c>
       <c r="J546" t="inlineStr">
@@ -46071,7 +46071,7 @@
       </c>
       <c r="G547" t="inlineStr">
         <is>
-          <t>005</t>
+          <t>006</t>
         </is>
       </c>
       <c r="H547" t="inlineStr">
@@ -46081,7 +46081,7 @@
       </c>
       <c r="I547" t="inlineStr">
         <is>
-          <t>9903.03.06,9903.82.02,7318.22.0000</t>
+          <t>9903.03.06,9903.82.02,7318.15.8030</t>
         </is>
       </c>
       <c r="J547" t="inlineStr">
@@ -46111,12 +46111,12 @@
       </c>
       <c r="O547" t="inlineStr">
         <is>
-          <t>WASI GMBH</t>
+          <t>SCHAFER &amp; PETERS GMBH</t>
         </is>
       </c>
       <c r="P547" t="inlineStr">
         <is>
-          <t>WASI GMBH</t>
+          <t>SCHAFER &amp; PETERS GMBH</t>
         </is>
       </c>
       <c r="Q547" t="inlineStr">
@@ -46154,7 +46154,7 @@
       </c>
       <c r="G548" t="inlineStr">
         <is>
-          <t>006</t>
+          <t>007</t>
         </is>
       </c>
       <c r="H548" t="inlineStr">
@@ -46237,7 +46237,7 @@
       </c>
       <c r="G549" t="inlineStr">
         <is>
-          <t>007</t>
+          <t>008</t>
         </is>
       </c>
       <c r="H549" t="inlineStr">
@@ -46310,27 +46310,27 @@
       <c r="D550" t="inlineStr"/>
       <c r="E550" t="inlineStr">
         <is>
-          <t>9903.88.03</t>
+          <t>9903.03.06</t>
         </is>
       </c>
       <c r="F550" t="inlineStr">
         <is>
-          <t>ARTICLE OF CHINA,US NTE 20(F)</t>
+          <t>S122 EXCL,IRN/STL/ALUM,DERIV</t>
         </is>
       </c>
       <c r="G550" t="inlineStr">
         <is>
-          <t>008</t>
+          <t>009</t>
         </is>
       </c>
       <c r="H550" t="inlineStr">
         <is>
-          <t>9903.88.03</t>
+          <t>9903.03.06</t>
         </is>
       </c>
       <c r="I550" t="inlineStr">
         <is>
-          <t>9903.03.06,9903.82.02,7318.15.8030</t>
+          <t>9903.82.02,7318.22.0000</t>
         </is>
       </c>
       <c r="J550" t="inlineStr">
@@ -46393,27 +46393,27 @@
       <c r="D551" t="inlineStr"/>
       <c r="E551" t="inlineStr">
         <is>
-          <t>9903.03.06</t>
+          <t>9903.88.03</t>
         </is>
       </c>
       <c r="F551" t="inlineStr">
         <is>
-          <t>S122 EXCL,IRN/STL/ALUM,DERIV</t>
+          <t>ARTICLE OF CHINA,US NTE 20(F)</t>
         </is>
       </c>
       <c r="G551" t="inlineStr">
         <is>
-          <t>009</t>
+          <t>010</t>
         </is>
       </c>
       <c r="H551" t="inlineStr">
         <is>
-          <t>9903.03.06</t>
+          <t>9903.88.03</t>
         </is>
       </c>
       <c r="I551" t="inlineStr">
         <is>
-          <t>9903.82.02,7318.22.0000</t>
+          <t>9903.03.06,9903.82.02,7318.15.2010</t>
         </is>
       </c>
       <c r="J551" t="inlineStr">
@@ -46486,7 +46486,7 @@
       </c>
       <c r="G552" t="inlineStr">
         <is>
-          <t>010</t>
+          <t>011</t>
         </is>
       </c>
       <c r="H552" t="inlineStr">
@@ -46496,7 +46496,7 @@
       </c>
       <c r="I552" t="inlineStr">
         <is>
-          <t>9903.03.06,9903.82.02,7318.15.2010</t>
+          <t>9903.03.06,9903.82.02,7318.15.8030</t>
         </is>
       </c>
       <c r="J552" t="inlineStr">
@@ -46569,7 +46569,7 @@
       </c>
       <c r="G553" t="inlineStr">
         <is>
-          <t>011</t>
+          <t>012</t>
         </is>
       </c>
       <c r="H553" t="inlineStr">
@@ -46579,7 +46579,7 @@
       </c>
       <c r="I553" t="inlineStr">
         <is>
-          <t>9903.03.06,9903.82.02,7318.15.8030</t>
+          <t>9903.03.06,9903.82.02,7318.15.8055</t>
         </is>
       </c>
       <c r="J553" t="inlineStr">
@@ -46642,27 +46642,27 @@
       <c r="D554" t="inlineStr"/>
       <c r="E554" t="inlineStr">
         <is>
-          <t>9903.88.03</t>
+          <t>9903.88.15</t>
         </is>
       </c>
       <c r="F554" t="inlineStr">
         <is>
-          <t>ARTICLE OF CHINA,US NTE 20(F)</t>
+          <t>ARTICLE OF CHINA,US NTE 20(R)</t>
         </is>
       </c>
       <c r="G554" t="inlineStr">
         <is>
-          <t>012</t>
+          <t>013</t>
         </is>
       </c>
       <c r="H554" t="inlineStr">
         <is>
-          <t>9903.88.03</t>
+          <t>9903.88.15</t>
         </is>
       </c>
       <c r="I554" t="inlineStr">
         <is>
-          <t>9903.03.06,9903.82.02,7318.15.8055</t>
+          <t>9903.03.06,9903.82.02,7318.16.0060</t>
         </is>
       </c>
       <c r="J554" t="inlineStr">
@@ -46725,27 +46725,27 @@
       <c r="D555" t="inlineStr"/>
       <c r="E555" t="inlineStr">
         <is>
-          <t>9903.88.15</t>
+          <t>9903.88.03</t>
         </is>
       </c>
       <c r="F555" t="inlineStr">
         <is>
-          <t>ARTICLE OF CHINA,US NTE 20(R)</t>
+          <t>ARTICLE OF CHINA,US NTE 20(F)</t>
         </is>
       </c>
       <c r="G555" t="inlineStr">
         <is>
-          <t>013</t>
+          <t>014</t>
         </is>
       </c>
       <c r="H555" t="inlineStr">
         <is>
-          <t>9903.88.15</t>
+          <t>9903.88.03</t>
         </is>
       </c>
       <c r="I555" t="inlineStr">
         <is>
-          <t>9903.03.06,9903.82.02,7318.16.0060</t>
+          <t>9903.03.06,9903.82.02,7318.15.8055</t>
         </is>
       </c>
       <c r="J555" t="inlineStr">
@@ -46818,7 +46818,7 @@
       </c>
       <c r="G556" t="inlineStr">
         <is>
-          <t>014</t>
+          <t>015</t>
         </is>
       </c>
       <c r="H556" t="inlineStr">
@@ -46828,7 +46828,7 @@
       </c>
       <c r="I556" t="inlineStr">
         <is>
-          <t>9903.03.06,9903.82.02,7318.15.8055</t>
+          <t>9903.03.06,9903.82.02,7318.15.8030</t>
         </is>
       </c>
       <c r="J556" t="inlineStr">
@@ -46901,7 +46901,7 @@
       </c>
       <c r="G557" t="inlineStr">
         <is>
-          <t>015</t>
+          <t>016</t>
         </is>
       </c>
       <c r="H557" t="inlineStr">
@@ -46911,7 +46911,7 @@
       </c>
       <c r="I557" t="inlineStr">
         <is>
-          <t>9903.03.06,9903.82.02,7318.15.8030</t>
+          <t>9903.03.06,9903.82.02,7318.15.2051</t>
         </is>
       </c>
       <c r="J557" t="inlineStr">
@@ -46974,27 +46974,27 @@
       <c r="D558" t="inlineStr"/>
       <c r="E558" t="inlineStr">
         <is>
-          <t>9903.88.03</t>
+          <t>9903.03.06</t>
         </is>
       </c>
       <c r="F558" t="inlineStr">
         <is>
-          <t>ARTICLE OF CHINA,US NTE 20(F)</t>
+          <t>S122 EXCL,IRN/STL/ALUM,DERIV</t>
         </is>
       </c>
       <c r="G558" t="inlineStr">
         <is>
-          <t>016</t>
+          <t>017</t>
         </is>
       </c>
       <c r="H558" t="inlineStr">
         <is>
-          <t>9903.88.03</t>
+          <t>9903.03.06</t>
         </is>
       </c>
       <c r="I558" t="inlineStr">
         <is>
-          <t>9903.03.06,9903.82.02,7318.15.2051</t>
+          <t>9903.82.02,7318.15.8082</t>
         </is>
       </c>
       <c r="J558" t="inlineStr">
@@ -47057,27 +47057,27 @@
       <c r="D559" t="inlineStr"/>
       <c r="E559" t="inlineStr">
         <is>
-          <t>9903.03.06</t>
+          <t>9903.88.03</t>
         </is>
       </c>
       <c r="F559" t="inlineStr">
         <is>
-          <t>S122 EXCL,IRN/STL/ALUM,DERIV</t>
+          <t>ARTICLE OF CHINA,US NTE 20(F)</t>
         </is>
       </c>
       <c r="G559" t="inlineStr">
         <is>
-          <t>017</t>
+          <t>018</t>
         </is>
       </c>
       <c r="H559" t="inlineStr">
         <is>
-          <t>9903.03.06</t>
+          <t>9903.88.03</t>
         </is>
       </c>
       <c r="I559" t="inlineStr">
         <is>
-          <t>9903.82.02,7318.15.8082</t>
+          <t>9903.03.06,9903.82.02,7318.15.4000</t>
         </is>
       </c>
       <c r="J559" t="inlineStr">
@@ -47150,7 +47150,7 @@
       </c>
       <c r="G560" t="inlineStr">
         <is>
-          <t>018</t>
+          <t>019</t>
         </is>
       </c>
       <c r="H560" t="inlineStr">
@@ -47160,7 +47160,7 @@
       </c>
       <c r="I560" t="inlineStr">
         <is>
-          <t>9903.03.06,9903.82.02,7318.15.4000</t>
+          <t>9903.03.06,9903.82.02,7318.22.0000</t>
         </is>
       </c>
       <c r="J560" t="inlineStr">
@@ -47233,7 +47233,7 @@
       </c>
       <c r="G561" t="inlineStr">
         <is>
-          <t>019</t>
+          <t>020</t>
         </is>
       </c>
       <c r="H561" t="inlineStr">
@@ -47243,7 +47243,7 @@
       </c>
       <c r="I561" t="inlineStr">
         <is>
-          <t>9903.03.06,9903.82.02,7318.22.0000</t>
+          <t>9903.03.06,9903.82.02,7318.15.8030</t>
         </is>
       </c>
       <c r="J561" t="inlineStr">
@@ -47316,7 +47316,7 @@
       </c>
       <c r="G562" t="inlineStr">
         <is>
-          <t>020</t>
+          <t>021</t>
         </is>
       </c>
       <c r="H562" t="inlineStr">
@@ -47326,7 +47326,7 @@
       </c>
       <c r="I562" t="inlineStr">
         <is>
-          <t>9903.03.06,9903.82.02,7318.15.8030</t>
+          <t>9903.03.06,9903.82.02,7318.15.8055</t>
         </is>
       </c>
       <c r="J562" t="inlineStr">
@@ -47399,7 +47399,7 @@
       </c>
       <c r="G563" t="inlineStr">
         <is>
-          <t>021</t>
+          <t>022</t>
         </is>
       </c>
       <c r="H563" t="inlineStr">
@@ -47409,7 +47409,7 @@
       </c>
       <c r="I563" t="inlineStr">
         <is>
-          <t>9903.03.06,9903.82.02,7318.15.8055</t>
+          <t>9903.03.06,9903.82.02,7318.15.8020</t>
         </is>
       </c>
       <c r="J563" t="inlineStr">
@@ -47472,27 +47472,27 @@
       <c r="D564" t="inlineStr"/>
       <c r="E564" t="inlineStr">
         <is>
-          <t>9903.88.03</t>
+          <t>9903.03.06</t>
         </is>
       </c>
       <c r="F564" t="inlineStr">
         <is>
-          <t>ARTICLE OF CHINA,US NTE 20(F)</t>
+          <t>S122 EXCL,IRN/STL/ALUM,DERIV</t>
         </is>
       </c>
       <c r="G564" t="inlineStr">
         <is>
-          <t>022</t>
+          <t>023</t>
         </is>
       </c>
       <c r="H564" t="inlineStr">
         <is>
-          <t>9903.88.03</t>
+          <t>9903.03.06</t>
         </is>
       </c>
       <c r="I564" t="inlineStr">
         <is>
-          <t>9903.03.06,9903.82.02,7318.15.8020</t>
+          <t>9903.82.02,7318.15.8030</t>
         </is>
       </c>
       <c r="J564" t="inlineStr">
@@ -47555,27 +47555,27 @@
       <c r="D565" t="inlineStr"/>
       <c r="E565" t="inlineStr">
         <is>
-          <t>9903.03.06</t>
+          <t>9903.88.03</t>
         </is>
       </c>
       <c r="F565" t="inlineStr">
         <is>
-          <t>S122 EXCL,IRN/STL/ALUM,DERIV</t>
+          <t>ARTICLE OF CHINA,US NTE 20(F)</t>
         </is>
       </c>
       <c r="G565" t="inlineStr">
         <is>
-          <t>023</t>
+          <t>024</t>
         </is>
       </c>
       <c r="H565" t="inlineStr">
         <is>
-          <t>9903.03.06</t>
+          <t>9903.88.03</t>
         </is>
       </c>
       <c r="I565" t="inlineStr">
         <is>
-          <t>9903.82.02,7318.15.8030</t>
+          <t>9903.03.06,9903.82.02,7318.15.2051</t>
         </is>
       </c>
       <c r="J565" t="inlineStr">
@@ -47638,27 +47638,27 @@
       <c r="D566" t="inlineStr"/>
       <c r="E566" t="inlineStr">
         <is>
-          <t>9903.88.03</t>
+          <t>9903.03.06</t>
         </is>
       </c>
       <c r="F566" t="inlineStr">
         <is>
-          <t>ARTICLE OF CHINA,US NTE 20(F)</t>
+          <t>S122 EXCL,IRN/STL/ALUM,DERIV</t>
         </is>
       </c>
       <c r="G566" t="inlineStr">
         <is>
-          <t>024</t>
+          <t>025</t>
         </is>
       </c>
       <c r="H566" t="inlineStr">
         <is>
-          <t>9903.88.03</t>
+          <t>9903.03.06</t>
         </is>
       </c>
       <c r="I566" t="inlineStr">
         <is>
-          <t>9903.03.06,9903.82.02,7318.15.2051</t>
+          <t>9903.82.02,7318.15.5030</t>
         </is>
       </c>
       <c r="J566" t="inlineStr">
@@ -47721,27 +47721,27 @@
       <c r="D567" t="inlineStr"/>
       <c r="E567" t="inlineStr">
         <is>
-          <t>9903.03.06</t>
+          <t>9903.88.03</t>
         </is>
       </c>
       <c r="F567" t="inlineStr">
         <is>
-          <t>S122 EXCL,IRN/STL/ALUM,DERIV</t>
+          <t>ARTICLE OF CHINA,US NTE 20(F)</t>
         </is>
       </c>
       <c r="G567" t="inlineStr">
         <is>
-          <t>025</t>
+          <t>026</t>
         </is>
       </c>
       <c r="H567" t="inlineStr">
         <is>
-          <t>9903.03.06</t>
+          <t>9903.88.03</t>
         </is>
       </c>
       <c r="I567" t="inlineStr">
         <is>
-          <t>9903.82.02,7318.15.5030</t>
+          <t>9903.03.06,9903.82.02,7318.15.5030</t>
         </is>
       </c>
       <c r="J567" t="inlineStr">
@@ -47804,27 +47804,27 @@
       <c r="D568" t="inlineStr"/>
       <c r="E568" t="inlineStr">
         <is>
-          <t>9903.88.03</t>
+          <t>9903.03.06</t>
         </is>
       </c>
       <c r="F568" t="inlineStr">
         <is>
-          <t>ARTICLE OF CHINA,US NTE 20(F)</t>
+          <t>S122 EXCL,IRN/STL/ALUM,DERIV</t>
         </is>
       </c>
       <c r="G568" t="inlineStr">
         <is>
-          <t>026</t>
+          <t>027</t>
         </is>
       </c>
       <c r="H568" t="inlineStr">
         <is>
-          <t>9903.88.03</t>
+          <t>9903.03.06</t>
         </is>
       </c>
       <c r="I568" t="inlineStr">
         <is>
-          <t>9903.03.06,9903.82.02,7318.15.5030</t>
+          <t>9903.82.02,7318.29.0000</t>
         </is>
       </c>
       <c r="J568" t="inlineStr">
@@ -47897,7 +47897,7 @@
       </c>
       <c r="G569" t="inlineStr">
         <is>
-          <t>027</t>
+          <t>028</t>
         </is>
       </c>
       <c r="H569" t="inlineStr">
@@ -47907,7 +47907,7 @@
       </c>
       <c r="I569" t="inlineStr">
         <is>
-          <t>9903.82.02,7318.29.0000</t>
+          <t>9903.82.02,7318.24.0000</t>
         </is>
       </c>
       <c r="J569" t="inlineStr">
@@ -47980,7 +47980,7 @@
       </c>
       <c r="G570" t="inlineStr">
         <is>
-          <t>028</t>
+          <t>029</t>
         </is>
       </c>
       <c r="H570" t="inlineStr">
@@ -47990,7 +47990,7 @@
       </c>
       <c r="I570" t="inlineStr">
         <is>
-          <t>9903.82.02,7318.24.0000</t>
+          <t>9903.82.02,7318.29.0000</t>
         </is>
       </c>
       <c r="J570" t="inlineStr">
@@ -48063,7 +48063,7 @@
       </c>
       <c r="G571" t="inlineStr">
         <is>
-          <t>029</t>
+          <t>030</t>
         </is>
       </c>
       <c r="H571" t="inlineStr">
@@ -48073,7 +48073,7 @@
       </c>
       <c r="I571" t="inlineStr">
         <is>
-          <t>9903.82.02,7318.29.0000</t>
+          <t>9903.82.02,7318.15.8066</t>
         </is>
       </c>
       <c r="J571" t="inlineStr">
@@ -48103,12 +48103,12 @@
       </c>
       <c r="O571" t="inlineStr">
         <is>
-          <t>SCHAFER &amp; PETERS GMBH</t>
+          <t>EUROBOLT BV</t>
         </is>
       </c>
       <c r="P571" t="inlineStr">
         <is>
-          <t>SCHAFER &amp; PETERS GMBH</t>
+          <t>EUROBOLT BV</t>
         </is>
       </c>
       <c r="Q571" t="inlineStr">
@@ -48146,7 +48146,7 @@
       </c>
       <c r="G572" t="inlineStr">
         <is>
-          <t>030</t>
+          <t>031</t>
         </is>
       </c>
       <c r="H572" t="inlineStr">
@@ -48156,7 +48156,7 @@
       </c>
       <c r="I572" t="inlineStr">
         <is>
-          <t>9903.82.02,7318.15.8066</t>
+          <t>9903.82.02,7318.22.0000</t>
         </is>
       </c>
       <c r="J572" t="inlineStr">
@@ -48229,7 +48229,7 @@
       </c>
       <c r="G573" t="inlineStr">
         <is>
-          <t>031</t>
+          <t>032</t>
         </is>
       </c>
       <c r="H573" t="inlineStr">
@@ -48239,7 +48239,7 @@
       </c>
       <c r="I573" t="inlineStr">
         <is>
-          <t>9903.82.02,7318.22.0000</t>
+          <t>9903.82.02,7318.15.8066</t>
         </is>
       </c>
       <c r="J573" t="inlineStr">
@@ -48312,7 +48312,7 @@
       </c>
       <c r="G574" t="inlineStr">
         <is>
-          <t>032</t>
+          <t>033</t>
         </is>
       </c>
       <c r="H574" t="inlineStr">
@@ -48395,7 +48395,7 @@
       </c>
       <c r="G575" t="inlineStr">
         <is>
-          <t>033</t>
+          <t>034</t>
         </is>
       </c>
       <c r="H575" t="inlineStr">
@@ -48405,7 +48405,7 @@
       </c>
       <c r="I575" t="inlineStr">
         <is>
-          <t>9903.82.02,7318.15.8066</t>
+          <t>9903.82.02,7318.15.6040</t>
         </is>
       </c>
       <c r="J575" t="inlineStr">
@@ -48478,7 +48478,7 @@
       </c>
       <c r="G576" t="inlineStr">
         <is>
-          <t>034</t>
+          <t>035</t>
         </is>
       </c>
       <c r="H576" t="inlineStr">
@@ -48488,7 +48488,7 @@
       </c>
       <c r="I576" t="inlineStr">
         <is>
-          <t>9903.82.02,7318.15.6040</t>
+          <t>9903.82.02,7318.15.8066</t>
         </is>
       </c>
       <c r="J576" t="inlineStr">
@@ -48561,7 +48561,7 @@
       </c>
       <c r="G577" t="inlineStr">
         <is>
-          <t>035</t>
+          <t>036</t>
         </is>
       </c>
       <c r="H577" t="inlineStr">
@@ -48644,7 +48644,7 @@
       </c>
       <c r="G578" t="inlineStr">
         <is>
-          <t>036</t>
+          <t>037</t>
         </is>
       </c>
       <c r="H578" t="inlineStr">
@@ -48727,7 +48727,7 @@
       </c>
       <c r="G579" t="inlineStr">
         <is>
-          <t>037</t>
+          <t>038</t>
         </is>
       </c>
       <c r="H579" t="inlineStr">
@@ -48810,7 +48810,7 @@
       </c>
       <c r="G580" t="inlineStr">
         <is>
-          <t>038</t>
+          <t>039</t>
         </is>
       </c>
       <c r="H580" t="inlineStr">
@@ -48820,7 +48820,7 @@
       </c>
       <c r="I580" t="inlineStr">
         <is>
-          <t>9903.82.02,7318.15.8066</t>
+          <t>9903.82.02,7318.22.0000</t>
         </is>
       </c>
       <c r="J580" t="inlineStr">
@@ -48893,7 +48893,7 @@
       </c>
       <c r="G581" t="inlineStr">
         <is>
-          <t>039</t>
+          <t>040</t>
         </is>
       </c>
       <c r="H581" t="inlineStr">
@@ -48903,7 +48903,7 @@
       </c>
       <c r="I581" t="inlineStr">
         <is>
-          <t>9903.82.02,7318.22.0000</t>
+          <t>9903.82.02,7318.15.4000</t>
         </is>
       </c>
       <c r="J581" t="inlineStr">
@@ -48976,7 +48976,7 @@
       </c>
       <c r="G582" t="inlineStr">
         <is>
-          <t>040</t>
+          <t>041</t>
         </is>
       </c>
       <c r="H582" t="inlineStr">
@@ -48986,7 +48986,7 @@
       </c>
       <c r="I582" t="inlineStr">
         <is>
-          <t>9903.82.02,7318.15.4000</t>
+          <t>9903.82.02,7318.15.8066</t>
         </is>
       </c>
       <c r="J582" t="inlineStr">
@@ -49059,7 +49059,7 @@
       </c>
       <c r="G583" t="inlineStr">
         <is>
-          <t>041</t>
+          <t>042</t>
         </is>
       </c>
       <c r="H583" t="inlineStr">
@@ -49069,7 +49069,7 @@
       </c>
       <c r="I583" t="inlineStr">
         <is>
-          <t>9903.82.02,7318.15.8066</t>
+          <t>9903.82.02,7318.22.0000</t>
         </is>
       </c>
       <c r="J583" t="inlineStr">
@@ -49142,7 +49142,7 @@
       </c>
       <c r="G584" t="inlineStr">
         <is>
-          <t>042</t>
+          <t>043</t>
         </is>
       </c>
       <c r="H584" t="inlineStr">
@@ -49225,7 +49225,7 @@
       </c>
       <c r="G585" t="inlineStr">
         <is>
-          <t>043</t>
+          <t>044</t>
         </is>
       </c>
       <c r="H585" t="inlineStr">
@@ -49298,27 +49298,27 @@
       <c r="D586" t="inlineStr"/>
       <c r="E586" t="inlineStr">
         <is>
-          <t>9903.03.06</t>
+          <t>9903.88.03</t>
         </is>
       </c>
       <c r="F586" t="inlineStr">
         <is>
-          <t>S122 EXCL,IRN/STL/ALUM,DERIV</t>
+          <t>ARTICLE OF CHINA,US NTE 20(F)</t>
         </is>
       </c>
       <c r="G586" t="inlineStr">
         <is>
-          <t>044</t>
+          <t>045</t>
         </is>
       </c>
       <c r="H586" t="inlineStr">
         <is>
-          <t>9903.03.06</t>
+          <t>9903.88.03</t>
         </is>
       </c>
       <c r="I586" t="inlineStr">
         <is>
-          <t>9903.82.02,7318.22.0000</t>
+          <t>9903.03.06,9903.82.02,7318.15.8066</t>
         </is>
       </c>
       <c r="J586" t="inlineStr">
@@ -49381,27 +49381,27 @@
       <c r="D587" t="inlineStr"/>
       <c r="E587" t="inlineStr">
         <is>
-          <t>9903.88.03</t>
+          <t>9903.03.06</t>
         </is>
       </c>
       <c r="F587" t="inlineStr">
         <is>
-          <t>ARTICLE OF CHINA,US NTE 20(F)</t>
+          <t>S122 EXCL,IRN/STL/ALUM,DERIV</t>
         </is>
       </c>
       <c r="G587" t="inlineStr">
         <is>
-          <t>045</t>
+          <t>046</t>
         </is>
       </c>
       <c r="H587" t="inlineStr">
         <is>
-          <t>9903.88.03</t>
+          <t>9903.03.06</t>
         </is>
       </c>
       <c r="I587" t="inlineStr">
         <is>
-          <t>9903.03.06,9903.82.02,7318.15.8066</t>
+          <t>9903.82.02,7318.15.8066</t>
         </is>
       </c>
       <c r="J587" t="inlineStr">
@@ -49464,27 +49464,27 @@
       <c r="D588" t="inlineStr"/>
       <c r="E588" t="inlineStr">
         <is>
-          <t>9903.03.06</t>
+          <t>9903.88.15</t>
         </is>
       </c>
       <c r="F588" t="inlineStr">
         <is>
-          <t>S122 EXCL,IRN/STL/ALUM,DERIV</t>
+          <t>ARTICLE OF CHINA,US NTE 20(R)</t>
         </is>
       </c>
       <c r="G588" t="inlineStr">
         <is>
-          <t>046</t>
+          <t>047</t>
         </is>
       </c>
       <c r="H588" t="inlineStr">
         <is>
-          <t>9903.03.06</t>
+          <t>9903.88.15</t>
         </is>
       </c>
       <c r="I588" t="inlineStr">
         <is>
-          <t>9903.82.02,7318.15.8066</t>
+          <t>9903.03.06,9903.82.02,7318.16.0085</t>
         </is>
       </c>
       <c r="J588" t="inlineStr">
@@ -49547,27 +49547,27 @@
       <c r="D589" t="inlineStr"/>
       <c r="E589" t="inlineStr">
         <is>
-          <t>9903.88.15</t>
+          <t>9903.03.06</t>
         </is>
       </c>
       <c r="F589" t="inlineStr">
         <is>
-          <t>ARTICLE OF CHINA,US NTE 20(R)</t>
+          <t>S122 EXCL,IRN/STL/ALUM,DERIV</t>
         </is>
       </c>
       <c r="G589" t="inlineStr">
         <is>
-          <t>047</t>
+          <t>048</t>
         </is>
       </c>
       <c r="H589" t="inlineStr">
         <is>
-          <t>9903.88.15</t>
+          <t>9903.03.06</t>
         </is>
       </c>
       <c r="I589" t="inlineStr">
         <is>
-          <t>9903.03.06,9903.82.02,7318.16.0085</t>
+          <t>9903.82.02,7318.16.0085</t>
         </is>
       </c>
       <c r="J589" t="inlineStr">
@@ -49640,7 +49640,7 @@
       </c>
       <c r="G590" t="inlineStr">
         <is>
-          <t>048</t>
+          <t>049</t>
         </is>
       </c>
       <c r="H590" t="inlineStr">
@@ -49650,7 +49650,7 @@
       </c>
       <c r="I590" t="inlineStr">
         <is>
-          <t>9903.82.02,7318.16.0085</t>
+          <t>9903.82.02,7318.15.8066</t>
         </is>
       </c>
       <c r="J590" t="inlineStr">
@@ -49723,7 +49723,7 @@
       </c>
       <c r="G591" t="inlineStr">
         <is>
-          <t>049</t>
+          <t>050</t>
         </is>
       </c>
       <c r="H591" t="inlineStr">
@@ -49806,7 +49806,7 @@
       </c>
       <c r="G592" t="inlineStr">
         <is>
-          <t>050</t>
+          <t>051</t>
         </is>
       </c>
       <c r="H592" t="inlineStr">
@@ -49816,7 +49816,7 @@
       </c>
       <c r="I592" t="inlineStr">
         <is>
-          <t>9903.82.02,7318.15.8066</t>
+          <t>9903.82.02,7318.16.0085</t>
         </is>
       </c>
       <c r="J592" t="inlineStr">
@@ -49889,7 +49889,7 @@
       </c>
       <c r="G593" t="inlineStr">
         <is>
-          <t>051</t>
+          <t>052</t>
         </is>
       </c>
       <c r="H593" t="inlineStr">
@@ -49899,7 +49899,7 @@
       </c>
       <c r="I593" t="inlineStr">
         <is>
-          <t>9903.82.02,7318.16.0085</t>
+          <t>9903.82.02,7318.15.8066</t>
         </is>
       </c>
       <c r="J593" t="inlineStr">
@@ -49962,27 +49962,27 @@
       <c r="D594" t="inlineStr"/>
       <c r="E594" t="inlineStr">
         <is>
-          <t>9903.03.06</t>
+          <t>9903.88.15</t>
         </is>
       </c>
       <c r="F594" t="inlineStr">
         <is>
-          <t>S122 EXCL,IRN/STL/ALUM,DERIV</t>
+          <t>ARTICLE OF CHINA,US NTE 20(R)</t>
         </is>
       </c>
       <c r="G594" t="inlineStr">
         <is>
-          <t>052</t>
+          <t>053</t>
         </is>
       </c>
       <c r="H594" t="inlineStr">
         <is>
-          <t>9903.03.06</t>
+          <t>9903.88.15</t>
         </is>
       </c>
       <c r="I594" t="inlineStr">
         <is>
-          <t>9903.82.02,7318.15.8066</t>
+          <t>9903.03.06,9903.82.02,7318.16.0085</t>
         </is>
       </c>
       <c r="J594" t="inlineStr">
@@ -50045,27 +50045,27 @@
       <c r="D595" t="inlineStr"/>
       <c r="E595" t="inlineStr">
         <is>
-          <t>9903.88.15</t>
+          <t>9903.88.03</t>
         </is>
       </c>
       <c r="F595" t="inlineStr">
         <is>
-          <t>ARTICLE OF CHINA,US NTE 20(R)</t>
+          <t>ARTICLE OF CHINA,US NTE 20(F)</t>
         </is>
       </c>
       <c r="G595" t="inlineStr">
         <is>
-          <t>053</t>
+          <t>054</t>
         </is>
       </c>
       <c r="H595" t="inlineStr">
         <is>
-          <t>9903.88.15</t>
+          <t>9903.88.03</t>
         </is>
       </c>
       <c r="I595" t="inlineStr">
         <is>
-          <t>9903.03.06,9903.82.02,7318.16.0085</t>
+          <t>9903.03.06,9903.82.02,7318.15.6040</t>
         </is>
       </c>
       <c r="J595" t="inlineStr">
@@ -50128,27 +50128,27 @@
       <c r="D596" t="inlineStr"/>
       <c r="E596" t="inlineStr">
         <is>
-          <t>9903.88.03</t>
+          <t>9903.03.06</t>
         </is>
       </c>
       <c r="F596" t="inlineStr">
         <is>
-          <t>ARTICLE OF CHINA,US NTE 20(F)</t>
+          <t>S122 EXCL,IRN/STL/ALUM,DERIV</t>
         </is>
       </c>
       <c r="G596" t="inlineStr">
         <is>
-          <t>054</t>
+          <t>055</t>
         </is>
       </c>
       <c r="H596" t="inlineStr">
         <is>
-          <t>9903.88.03</t>
+          <t>9903.03.06</t>
         </is>
       </c>
       <c r="I596" t="inlineStr">
         <is>
-          <t>9903.03.06,9903.82.02,7318.15.6040</t>
+          <t>9903.82.02,7318.15.8066</t>
         </is>
       </c>
       <c r="J596" t="inlineStr">
@@ -50221,7 +50221,7 @@
       </c>
       <c r="G597" t="inlineStr">
         <is>
-          <t>055</t>
+          <t>056</t>
         </is>
       </c>
       <c r="H597" t="inlineStr">
@@ -50304,7 +50304,7 @@
       </c>
       <c r="G598" t="inlineStr">
         <is>
-          <t>056</t>
+          <t>057</t>
         </is>
       </c>
       <c r="H598" t="inlineStr">
@@ -50377,27 +50377,27 @@
       <c r="D599" t="inlineStr"/>
       <c r="E599" t="inlineStr">
         <is>
-          <t>9903.03.06</t>
+          <t>9903.88.03</t>
         </is>
       </c>
       <c r="F599" t="inlineStr">
         <is>
-          <t>S122 EXCL,IRN/STL/ALUM,DERIV</t>
+          <t>ARTICLE OF CHINA,US NTE 20(F)</t>
         </is>
       </c>
       <c r="G599" t="inlineStr">
         <is>
-          <t>057</t>
+          <t>058</t>
         </is>
       </c>
       <c r="H599" t="inlineStr">
         <is>
-          <t>9903.03.06</t>
+          <t>9903.88.03</t>
         </is>
       </c>
       <c r="I599" t="inlineStr">
         <is>
-          <t>9903.82.02,7318.15.8066</t>
+          <t>9903.03.06,9903.82.02,7318.22.0000</t>
         </is>
       </c>
       <c r="J599" t="inlineStr">
@@ -50460,27 +50460,27 @@
       <c r="D600" t="inlineStr"/>
       <c r="E600" t="inlineStr">
         <is>
-          <t>9903.88.03</t>
+          <t>9903.03.06</t>
         </is>
       </c>
       <c r="F600" t="inlineStr">
         <is>
-          <t>ARTICLE OF CHINA,US NTE 20(F)</t>
+          <t>S122 EXCL,IRN/STL/ALUM,DERIV</t>
         </is>
       </c>
       <c r="G600" t="inlineStr">
         <is>
-          <t>058</t>
+          <t>059</t>
         </is>
       </c>
       <c r="H600" t="inlineStr">
         <is>
-          <t>9903.88.03</t>
+          <t>9903.03.06</t>
         </is>
       </c>
       <c r="I600" t="inlineStr">
         <is>
-          <t>9903.03.06,9903.82.02,7318.22.0000</t>
+          <t>9903.82.02,7318.22.0000</t>
         </is>
       </c>
       <c r="J600" t="inlineStr">
@@ -50553,7 +50553,7 @@
       </c>
       <c r="G601" t="inlineStr">
         <is>
-          <t>059</t>
+          <t>060</t>
         </is>
       </c>
       <c r="H601" t="inlineStr">
@@ -50626,27 +50626,27 @@
       <c r="D602" t="inlineStr"/>
       <c r="E602" t="inlineStr">
         <is>
-          <t>9903.03.06</t>
+          <t>9903.88.03</t>
         </is>
       </c>
       <c r="F602" t="inlineStr">
         <is>
-          <t>S122 EXCL,IRN/STL/ALUM,DERIV</t>
+          <t>ARTICLE OF CHINA,US NTE 20(F)</t>
         </is>
       </c>
       <c r="G602" t="inlineStr">
         <is>
-          <t>060</t>
+          <t>061</t>
         </is>
       </c>
       <c r="H602" t="inlineStr">
         <is>
-          <t>9903.03.06</t>
+          <t>9903.88.03</t>
         </is>
       </c>
       <c r="I602" t="inlineStr">
         <is>
-          <t>9903.82.02,7318.22.0000</t>
+          <t>9903.03.06,9903.82.02,7318.15.8045</t>
         </is>
       </c>
       <c r="J602" t="inlineStr">
@@ -50709,27 +50709,27 @@
       <c r="D603" t="inlineStr"/>
       <c r="E603" t="inlineStr">
         <is>
-          <t>9903.88.03</t>
+          <t>9903.03.06</t>
         </is>
       </c>
       <c r="F603" t="inlineStr">
         <is>
-          <t>ARTICLE OF CHINA,US NTE 20(F)</t>
+          <t>S122 EXCL,IRN/STL/ALUM,DERIV</t>
         </is>
       </c>
       <c r="G603" t="inlineStr">
         <is>
-          <t>061</t>
+          <t>062</t>
         </is>
       </c>
       <c r="H603" t="inlineStr">
         <is>
-          <t>9903.88.03</t>
+          <t>9903.03.06</t>
         </is>
       </c>
       <c r="I603" t="inlineStr">
         <is>
-          <t>9903.03.06,9903.82.02,7318.15.8045</t>
+          <t>9903.82.02,7318.16.0085</t>
         </is>
       </c>
       <c r="J603" t="inlineStr">
@@ -50792,27 +50792,27 @@
       <c r="D604" t="inlineStr"/>
       <c r="E604" t="inlineStr">
         <is>
-          <t>9903.03.06</t>
+          <t>9903.88.03</t>
         </is>
       </c>
       <c r="F604" t="inlineStr">
         <is>
-          <t>S122 EXCL,IRN/STL/ALUM,DERIV</t>
+          <t>ARTICLE OF CHINA,US NTE 20(F)</t>
         </is>
       </c>
       <c r="G604" t="inlineStr">
         <is>
-          <t>062</t>
+          <t>063</t>
         </is>
       </c>
       <c r="H604" t="inlineStr">
         <is>
-          <t>9903.03.06</t>
+          <t>9903.88.03</t>
         </is>
       </c>
       <c r="I604" t="inlineStr">
         <is>
-          <t>9903.82.02,7318.16.0085</t>
+          <t>9903.03.06,9903.82.02,7318.15.8045</t>
         </is>
       </c>
       <c r="J604" t="inlineStr">
@@ -50842,12 +50842,12 @@
       </c>
       <c r="O604" t="inlineStr">
         <is>
-          <t>EUROBOLT BV</t>
+          <t>REYHER GMBH</t>
         </is>
       </c>
       <c r="P604" t="inlineStr">
         <is>
-          <t>EUROBOLT BV</t>
+          <t>REYHER GMBH</t>
         </is>
       </c>
       <c r="Q604" t="inlineStr">
@@ -50885,7 +50885,7 @@
       </c>
       <c r="G605" t="inlineStr">
         <is>
-          <t>063</t>
+          <t>064</t>
         </is>
       </c>
       <c r="H605" t="inlineStr">
@@ -50968,7 +50968,7 @@
       </c>
       <c r="G606" t="inlineStr">
         <is>
-          <t>064</t>
+          <t>065</t>
         </is>
       </c>
       <c r="H606" t="inlineStr">
@@ -51051,7 +51051,7 @@
       </c>
       <c r="G607" t="inlineStr">
         <is>
-          <t>065</t>
+          <t>066</t>
         </is>
       </c>
       <c r="H607" t="inlineStr">
@@ -51124,27 +51124,27 @@
       <c r="D608" t="inlineStr"/>
       <c r="E608" t="inlineStr">
         <is>
-          <t>9903.88.03</t>
+          <t>9903.03.06</t>
         </is>
       </c>
       <c r="F608" t="inlineStr">
         <is>
-          <t>ARTICLE OF CHINA,US NTE 20(F)</t>
+          <t>S122 EXCL,IRN/STL/ALUM,DERIV</t>
         </is>
       </c>
       <c r="G608" t="inlineStr">
         <is>
-          <t>066</t>
+          <t>067</t>
         </is>
       </c>
       <c r="H608" t="inlineStr">
         <is>
-          <t>9903.88.03</t>
+          <t>9903.03.06</t>
         </is>
       </c>
       <c r="I608" t="inlineStr">
         <is>
-          <t>9903.03.06,9903.82.02,7318.15.8045</t>
+          <t>9903.82.02,7318.15.8045</t>
         </is>
       </c>
       <c r="J608" t="inlineStr">
@@ -51217,7 +51217,7 @@
       </c>
       <c r="G609" t="inlineStr">
         <is>
-          <t>067</t>
+          <t>068</t>
         </is>
       </c>
       <c r="H609" t="inlineStr">
@@ -51227,7 +51227,7 @@
       </c>
       <c r="I609" t="inlineStr">
         <is>
-          <t>9903.82.02,7318.15.8045</t>
+          <t>9903.82.02,7318.21.0090</t>
         </is>
       </c>
       <c r="J609" t="inlineStr">
@@ -51300,7 +51300,7 @@
       </c>
       <c r="G610" t="inlineStr">
         <is>
-          <t>068</t>
+          <t>069</t>
         </is>
       </c>
       <c r="H610" t="inlineStr">
@@ -51310,7 +51310,7 @@
       </c>
       <c r="I610" t="inlineStr">
         <is>
-          <t>9903.82.02,7318.21.0090</t>
+          <t>9903.82.02,7318.29.0000</t>
         </is>
       </c>
       <c r="J610" t="inlineStr">
@@ -51383,7 +51383,7 @@
       </c>
       <c r="G611" t="inlineStr">
         <is>
-          <t>069</t>
+          <t>070</t>
         </is>
       </c>
       <c r="H611" t="inlineStr">
@@ -51393,7 +51393,7 @@
       </c>
       <c r="I611" t="inlineStr">
         <is>
-          <t>9903.82.02,7318.29.0000</t>
+          <t>9903.82.02,7318.16.0085</t>
         </is>
       </c>
       <c r="J611" t="inlineStr">
@@ -51466,7 +51466,7 @@
       </c>
       <c r="G612" t="inlineStr">
         <is>
-          <t>070</t>
+          <t>071</t>
         </is>
       </c>
       <c r="H612" t="inlineStr">
@@ -51476,7 +51476,7 @@
       </c>
       <c r="I612" t="inlineStr">
         <is>
-          <t>9903.82.02,7318.16.0085</t>
+          <t>9903.82.02,7318.15.8069</t>
         </is>
       </c>
       <c r="J612" t="inlineStr">
@@ -51539,27 +51539,27 @@
       <c r="D613" t="inlineStr"/>
       <c r="E613" t="inlineStr">
         <is>
-          <t>9903.03.06</t>
+          <t>9903.88.15</t>
         </is>
       </c>
       <c r="F613" t="inlineStr">
         <is>
-          <t>S122 EXCL,IRN/STL/ALUM,DERIV</t>
+          <t>ARTICLE OF CHINA,US NTE 20(R)</t>
         </is>
       </c>
       <c r="G613" t="inlineStr">
         <is>
-          <t>071</t>
+          <t>072</t>
         </is>
       </c>
       <c r="H613" t="inlineStr">
         <is>
-          <t>9903.03.06</t>
+          <t>9903.88.15</t>
         </is>
       </c>
       <c r="I613" t="inlineStr">
         <is>
-          <t>9903.82.02,7318.15.8069</t>
+          <t>9903.03.06,9903.82.02,7318.16.0085</t>
         </is>
       </c>
       <c r="J613" t="inlineStr">
@@ -51622,27 +51622,27 @@
       <c r="D614" t="inlineStr"/>
       <c r="E614" t="inlineStr">
         <is>
-          <t>9903.88.15</t>
+          <t>9903.88.03</t>
         </is>
       </c>
       <c r="F614" t="inlineStr">
         <is>
-          <t>ARTICLE OF CHINA,US NTE 20(R)</t>
+          <t>ARTICLE OF CHINA,US NTE 20(F)</t>
         </is>
       </c>
       <c r="G614" t="inlineStr">
         <is>
-          <t>072</t>
+          <t>073</t>
         </is>
       </c>
       <c r="H614" t="inlineStr">
         <is>
-          <t>9903.88.15</t>
+          <t>9903.88.03</t>
         </is>
       </c>
       <c r="I614" t="inlineStr">
         <is>
-          <t>9903.03.06,9903.82.02,7318.16.0085</t>
+          <t>9903.03.06,9903.82.02,7318.11.0000</t>
         </is>
       </c>
       <c r="J614" t="inlineStr">
@@ -51715,7 +51715,7 @@
       </c>
       <c r="G615" t="inlineStr">
         <is>
-          <t>073</t>
+          <t>074</t>
         </is>
       </c>
       <c r="H615" t="inlineStr">
@@ -51725,7 +51725,7 @@
       </c>
       <c r="I615" t="inlineStr">
         <is>
-          <t>9903.03.06,9903.82.02,7318.11.0000</t>
+          <t>9903.03.06,9903.82.02,7415.33.8010</t>
         </is>
       </c>
       <c r="J615" t="inlineStr">
@@ -51788,27 +51788,27 @@
       <c r="D616" t="inlineStr"/>
       <c r="E616" t="inlineStr">
         <is>
-          <t>9903.88.03</t>
+          <t>9903.03.06</t>
         </is>
       </c>
       <c r="F616" t="inlineStr">
         <is>
-          <t>ARTICLE OF CHINA,US NTE 20(F)</t>
+          <t>S122 EXCL,IRN/STL/ALUM,DERIV</t>
         </is>
       </c>
       <c r="G616" t="inlineStr">
         <is>
-          <t>074</t>
+          <t>075</t>
         </is>
       </c>
       <c r="H616" t="inlineStr">
         <is>
-          <t>9903.88.03</t>
+          <t>9903.03.06</t>
         </is>
       </c>
       <c r="I616" t="inlineStr">
         <is>
-          <t>9903.03.06,9903.82.02,7415.33.8010</t>
+          <t>9903.82.02,7415.33.8010</t>
         </is>
       </c>
       <c r="J616" t="inlineStr">
@@ -51871,27 +51871,27 @@
       <c r="D617" t="inlineStr"/>
       <c r="E617" t="inlineStr">
         <is>
-          <t>9903.03.06</t>
+          <t>9903.88.15</t>
         </is>
       </c>
       <c r="F617" t="inlineStr">
         <is>
-          <t>S122 EXCL,IRN/STL/ALUM,DERIV</t>
+          <t>ARTICLE OF CHINA,US NTE 20(R)</t>
         </is>
       </c>
       <c r="G617" t="inlineStr">
         <is>
-          <t>075</t>
+          <t>076</t>
         </is>
       </c>
       <c r="H617" t="inlineStr">
         <is>
-          <t>9903.03.06</t>
+          <t>9903.88.15</t>
         </is>
       </c>
       <c r="I617" t="inlineStr">
         <is>
-          <t>9903.82.02,7415.33.8010</t>
+          <t>9903.03.06,9903.82.02,7318.16.0085</t>
         </is>
       </c>
       <c r="J617" t="inlineStr">
@@ -51954,27 +51954,27 @@
       <c r="D618" t="inlineStr"/>
       <c r="E618" t="inlineStr">
         <is>
-          <t>9903.88.15</t>
+          <t>9903.03.06</t>
         </is>
       </c>
       <c r="F618" t="inlineStr">
         <is>
-          <t>ARTICLE OF CHINA,US NTE 20(R)</t>
+          <t>S122 EXCL,IRN/STL/ALUM,DERIV</t>
         </is>
       </c>
       <c r="G618" t="inlineStr">
         <is>
-          <t>076</t>
+          <t>077</t>
         </is>
       </c>
       <c r="H618" t="inlineStr">
         <is>
-          <t>9903.88.15</t>
+          <t>9903.03.06</t>
         </is>
       </c>
       <c r="I618" t="inlineStr">
         <is>
-          <t>9903.03.06,9903.82.02,7318.16.0085</t>
+          <t>9903.82.02,7318.15.8066</t>
         </is>
       </c>
       <c r="J618" t="inlineStr">
@@ -52047,7 +52047,7 @@
       </c>
       <c r="G619" t="inlineStr">
         <is>
-          <t>077</t>
+          <t>078</t>
         </is>
       </c>
       <c r="H619" t="inlineStr">
@@ -52057,7 +52057,7 @@
       </c>
       <c r="I619" t="inlineStr">
         <is>
-          <t>9903.82.02,7318.15.8066</t>
+          <t>9903.82.02,7318.15.8030</t>
         </is>
       </c>
       <c r="J619" t="inlineStr">
@@ -52120,27 +52120,27 @@
       <c r="D620" t="inlineStr"/>
       <c r="E620" t="inlineStr">
         <is>
-          <t>9903.03.06</t>
+          <t>9903.88.03</t>
         </is>
       </c>
       <c r="F620" t="inlineStr">
         <is>
-          <t>S122 EXCL,IRN/STL/ALUM,DERIV</t>
+          <t>ARTICLE OF CHINA,US NTE 20(F)</t>
         </is>
       </c>
       <c r="G620" t="inlineStr">
         <is>
-          <t>078</t>
+          <t>079</t>
         </is>
       </c>
       <c r="H620" t="inlineStr">
         <is>
-          <t>9903.03.06</t>
+          <t>9903.88.03</t>
         </is>
       </c>
       <c r="I620" t="inlineStr">
         <is>
-          <t>9903.82.02,7318.15.8030</t>
+          <t>9903.03.06,9903.82.02,7318.22.0000</t>
         </is>
       </c>
       <c r="J620" t="inlineStr">
@@ -52213,7 +52213,7 @@
       </c>
       <c r="G621" t="inlineStr">
         <is>
-          <t>079</t>
+          <t>080</t>
         </is>
       </c>
       <c r="H621" t="inlineStr">
@@ -52223,7 +52223,7 @@
       </c>
       <c r="I621" t="inlineStr">
         <is>
-          <t>9903.03.06,9903.82.02,7318.22.0000</t>
+          <t>9903.03.06,9903.82.02,7318.29.0000</t>
         </is>
       </c>
       <c r="J621" t="inlineStr">
@@ -52286,27 +52286,27 @@
       <c r="D622" t="inlineStr"/>
       <c r="E622" t="inlineStr">
         <is>
-          <t>9903.88.03</t>
+          <t>9903.03.06</t>
         </is>
       </c>
       <c r="F622" t="inlineStr">
         <is>
-          <t>ARTICLE OF CHINA,US NTE 20(F)</t>
+          <t>S122 EXCL,IRN/STL/ALUM,DERIV</t>
         </is>
       </c>
       <c r="G622" t="inlineStr">
         <is>
-          <t>080</t>
+          <t>081</t>
         </is>
       </c>
       <c r="H622" t="inlineStr">
         <is>
-          <t>9903.88.03</t>
+          <t>9903.03.06</t>
         </is>
       </c>
       <c r="I622" t="inlineStr">
         <is>
-          <t>9903.03.06,9903.82.02,7318.29.0000</t>
+          <t>9903.82.02,7318.15.2010</t>
         </is>
       </c>
       <c r="J622" t="inlineStr">
@@ -52379,7 +52379,7 @@
       </c>
       <c r="G623" t="inlineStr">
         <is>
-          <t>081</t>
+          <t>082</t>
         </is>
       </c>
       <c r="H623" t="inlineStr">
@@ -52389,7 +52389,7 @@
       </c>
       <c r="I623" t="inlineStr">
         <is>
-          <t>9903.82.02,7318.15.2010</t>
+          <t>9903.82.02,7318.14.1030</t>
         </is>
       </c>
       <c r="J623" t="inlineStr">
@@ -52462,7 +52462,7 @@
       </c>
       <c r="G624" t="inlineStr">
         <is>
-          <t>082</t>
+          <t>083</t>
         </is>
       </c>
       <c r="H624" t="inlineStr">
@@ -52472,7 +52472,7 @@
       </c>
       <c r="I624" t="inlineStr">
         <is>
-          <t>9903.82.02,7318.14.1030</t>
+          <t>9903.82.02,7318.22.0000</t>
         </is>
       </c>
       <c r="J624" t="inlineStr">
@@ -52535,27 +52535,27 @@
       <c r="D625" t="inlineStr"/>
       <c r="E625" t="inlineStr">
         <is>
-          <t>9903.03.06</t>
+          <t>9903.88.03</t>
         </is>
       </c>
       <c r="F625" t="inlineStr">
         <is>
-          <t>S122 EXCL,IRN/STL/ALUM,DERIV</t>
+          <t>ARTICLE OF CHINA,US NTE 20(F)</t>
         </is>
       </c>
       <c r="G625" t="inlineStr">
         <is>
-          <t>083</t>
+          <t>084</t>
         </is>
       </c>
       <c r="H625" t="inlineStr">
         <is>
-          <t>9903.03.06</t>
+          <t>9903.88.03</t>
         </is>
       </c>
       <c r="I625" t="inlineStr">
         <is>
-          <t>9903.82.02,7318.22.0000</t>
+          <t>9903.03.06,9903.82.02,7318.15.8066</t>
         </is>
       </c>
       <c r="J625" t="inlineStr">
@@ -52618,27 +52618,27 @@
       <c r="D626" t="inlineStr"/>
       <c r="E626" t="inlineStr">
         <is>
-          <t>9903.88.03</t>
+          <t>9903.03.06</t>
         </is>
       </c>
       <c r="F626" t="inlineStr">
         <is>
-          <t>ARTICLE OF CHINA,US NTE 20(F)</t>
+          <t>S122 EXCL,IRN/STL/ALUM,DERIV</t>
         </is>
       </c>
       <c r="G626" t="inlineStr">
         <is>
-          <t>084</t>
+          <t>085</t>
         </is>
       </c>
       <c r="H626" t="inlineStr">
         <is>
-          <t>9903.88.03</t>
+          <t>9903.03.06</t>
         </is>
       </c>
       <c r="I626" t="inlineStr">
         <is>
-          <t>9903.03.06,9903.82.02,7318.15.8066</t>
+          <t>9903.82.02,7318.15.2030</t>
         </is>
       </c>
       <c r="J626" t="inlineStr">
@@ -52711,7 +52711,7 @@
       </c>
       <c r="G627" t="inlineStr">
         <is>
-          <t>085</t>
+          <t>086</t>
         </is>
       </c>
       <c r="H627" t="inlineStr">
@@ -52794,7 +52794,7 @@
       </c>
       <c r="G628" t="inlineStr">
         <is>
-          <t>086</t>
+          <t>087</t>
         </is>
       </c>
       <c r="H628" t="inlineStr">
@@ -52877,7 +52877,7 @@
       </c>
       <c r="G629" t="inlineStr">
         <is>
-          <t>087</t>
+          <t>088</t>
         </is>
       </c>
       <c r="H629" t="inlineStr">
@@ -52960,7 +52960,7 @@
       </c>
       <c r="G630" t="inlineStr">
         <is>
-          <t>088</t>
+          <t>089</t>
         </is>
       </c>
       <c r="H630" t="inlineStr">
@@ -53043,7 +53043,7 @@
       </c>
       <c r="G631" t="inlineStr">
         <is>
-          <t>089</t>
+          <t>090</t>
         </is>
       </c>
       <c r="H631" t="inlineStr">
@@ -53126,7 +53126,7 @@
       </c>
       <c r="G632" t="inlineStr">
         <is>
-          <t>090</t>
+          <t>091</t>
         </is>
       </c>
       <c r="H632" t="inlineStr">
@@ -53209,7 +53209,7 @@
       </c>
       <c r="G633" t="inlineStr">
         <is>
-          <t>091</t>
+          <t>092</t>
         </is>
       </c>
       <c r="H633" t="inlineStr">
@@ -53219,7 +53219,7 @@
       </c>
       <c r="I633" t="inlineStr">
         <is>
-          <t>9903.82.02,7318.15.2030</t>
+          <t>9903.82.02,7318.16.0085</t>
         </is>
       </c>
       <c r="J633" t="inlineStr">
@@ -53292,7 +53292,7 @@
       </c>
       <c r="G634" t="inlineStr">
         <is>
-          <t>092</t>
+          <t>093</t>
         </is>
       </c>
       <c r="H634" t="inlineStr">
@@ -53375,7 +53375,7 @@
       </c>
       <c r="G635" t="inlineStr">
         <is>
-          <t>093</t>
+          <t>094</t>
         </is>
       </c>
       <c r="H635" t="inlineStr">
@@ -53458,7 +53458,7 @@
       </c>
       <c r="G636" t="inlineStr">
         <is>
-          <t>094</t>
+          <t>095</t>
         </is>
       </c>
       <c r="H636" t="inlineStr">
@@ -53468,7 +53468,7 @@
       </c>
       <c r="I636" t="inlineStr">
         <is>
-          <t>9903.82.02,7318.16.0085</t>
+          <t>9903.82.02,7318.22.0000</t>
         </is>
       </c>
       <c r="J636" t="inlineStr">
@@ -53541,7 +53541,7 @@
       </c>
       <c r="G637" t="inlineStr">
         <is>
-          <t>095</t>
+          <t>096</t>
         </is>
       </c>
       <c r="H637" t="inlineStr">
@@ -53624,7 +53624,7 @@
       </c>
       <c r="G638" t="inlineStr">
         <is>
-          <t>096</t>
+          <t>097</t>
         </is>
       </c>
       <c r="H638" t="inlineStr">
@@ -53634,7 +53634,7 @@
       </c>
       <c r="I638" t="inlineStr">
         <is>
-          <t>9903.82.02,7318.22.0000</t>
+          <t>9903.82.02,7318.15.2055</t>
         </is>
       </c>
       <c r="J638" t="inlineStr">
@@ -53707,7 +53707,7 @@
       </c>
       <c r="G639" t="inlineStr">
         <is>
-          <t>097</t>
+          <t>098</t>
         </is>
       </c>
       <c r="H639" t="inlineStr">
@@ -53780,27 +53780,27 @@
       <c r="D640" t="inlineStr"/>
       <c r="E640" t="inlineStr">
         <is>
-          <t>9903.03.06</t>
+          <t>9903.88.03</t>
         </is>
       </c>
       <c r="F640" t="inlineStr">
         <is>
-          <t>S122 EXCL,IRN/STL/ALUM,DERIV</t>
+          <t>ARTICLE OF CHINA,US NTE 20(F)</t>
         </is>
       </c>
       <c r="G640" t="inlineStr">
         <is>
-          <t>098</t>
+          <t>099</t>
         </is>
       </c>
       <c r="H640" t="inlineStr">
         <is>
-          <t>9903.03.06</t>
+          <t>9903.88.03</t>
         </is>
       </c>
       <c r="I640" t="inlineStr">
         <is>
-          <t>9903.82.02,7318.15.2055</t>
+          <t>9903.03.06,9903.82.02,7318.22.0000</t>
         </is>
       </c>
       <c r="J640" t="inlineStr">
@@ -53873,7 +53873,7 @@
       </c>
       <c r="G641" t="inlineStr">
         <is>
-          <t>099</t>
+          <t>100</t>
         </is>
       </c>
       <c r="H641" t="inlineStr">
@@ -53883,7 +53883,7 @@
       </c>
       <c r="I641" t="inlineStr">
         <is>
-          <t>9903.03.06,9903.82.02,7318.22.0000</t>
+          <t>9903.03.06,9903.82.02,7415.33.8010</t>
         </is>
       </c>
       <c r="J641" t="inlineStr">
@@ -53956,7 +53956,7 @@
       </c>
       <c r="G642" t="inlineStr">
         <is>
-          <t>100</t>
+          <t>101</t>
         </is>
       </c>
       <c r="H642" t="inlineStr">
@@ -53966,7 +53966,7 @@
       </c>
       <c r="I642" t="inlineStr">
         <is>
-          <t>9903.03.06,9903.82.02,7415.33.8010</t>
+          <t>9903.03.06,9903.82.02,7318.15.8055</t>
         </is>
       </c>
       <c r="J642" t="inlineStr">
@@ -54029,27 +54029,27 @@
       <c r="D643" t="inlineStr"/>
       <c r="E643" t="inlineStr">
         <is>
-          <t>9903.88.03</t>
+          <t>9903.03.06</t>
         </is>
       </c>
       <c r="F643" t="inlineStr">
         <is>
-          <t>ARTICLE OF CHINA,US NTE 20(F)</t>
+          <t>S122 EXCL,IRN/STL/ALUM,DERIV</t>
         </is>
       </c>
       <c r="G643" t="inlineStr">
         <is>
-          <t>101</t>
+          <t>102</t>
         </is>
       </c>
       <c r="H643" t="inlineStr">
         <is>
-          <t>9903.88.03</t>
+          <t>9903.03.06</t>
         </is>
       </c>
       <c r="I643" t="inlineStr">
         <is>
-          <t>9903.03.06,9903.82.02,7318.15.8055</t>
+          <t>9903.82.02,7318.15.6040</t>
         </is>
       </c>
       <c r="J643" t="inlineStr">
@@ -54122,7 +54122,7 @@
       </c>
       <c r="G644" t="inlineStr">
         <is>
-          <t>102</t>
+          <t>103</t>
         </is>
       </c>
       <c r="H644" t="inlineStr">
@@ -54132,7 +54132,7 @@
       </c>
       <c r="I644" t="inlineStr">
         <is>
-          <t>9903.82.02,7318.15.6040</t>
+          <t>9903.82.02,7318.15.8045</t>
         </is>
       </c>
       <c r="J644" t="inlineStr">
@@ -54195,27 +54195,27 @@
       <c r="D645" t="inlineStr"/>
       <c r="E645" t="inlineStr">
         <is>
-          <t>9903.03.06</t>
+          <t>9903.88.03</t>
         </is>
       </c>
       <c r="F645" t="inlineStr">
         <is>
-          <t>S122 EXCL,IRN/STL/ALUM,DERIV</t>
+          <t>ARTICLE OF CHINA,US NTE 20(F)</t>
         </is>
       </c>
       <c r="G645" t="inlineStr">
         <is>
-          <t>103</t>
+          <t>104</t>
         </is>
       </c>
       <c r="H645" t="inlineStr">
         <is>
-          <t>9903.03.06</t>
+          <t>9903.88.03</t>
         </is>
       </c>
       <c r="I645" t="inlineStr">
         <is>
-          <t>9903.82.02,7318.15.8045</t>
+          <t>9903.03.06,9903.82.02,7318.15.4000</t>
         </is>
       </c>
       <c r="J645" t="inlineStr">
@@ -54278,27 +54278,27 @@
       <c r="D646" t="inlineStr"/>
       <c r="E646" t="inlineStr">
         <is>
-          <t>9903.88.03</t>
+          <t>9903.03.06</t>
         </is>
       </c>
       <c r="F646" t="inlineStr">
         <is>
-          <t>ARTICLE OF CHINA,US NTE 20(F)</t>
+          <t>S122 EXCL,IRN/STL/ALUM,DERIV</t>
         </is>
       </c>
       <c r="G646" t="inlineStr">
         <is>
-          <t>104</t>
+          <t>105</t>
         </is>
       </c>
       <c r="H646" t="inlineStr">
         <is>
-          <t>9903.88.03</t>
+          <t>9903.03.06</t>
         </is>
       </c>
       <c r="I646" t="inlineStr">
         <is>
-          <t>9903.03.06,9903.82.02,7318.15.4000</t>
+          <t>9903.82.02,7318.15.8020</t>
         </is>
       </c>
       <c r="J646" t="inlineStr">
@@ -54371,7 +54371,7 @@
       </c>
       <c r="G647" t="inlineStr">
         <is>
-          <t>105</t>
+          <t>106</t>
         </is>
       </c>
       <c r="H647" t="inlineStr">
@@ -54381,7 +54381,7 @@
       </c>
       <c r="I647" t="inlineStr">
         <is>
-          <t>9903.82.02,7318.15.8020</t>
+          <t>9903.82.02,7318.15.8066</t>
         </is>
       </c>
       <c r="J647" t="inlineStr">
@@ -54444,27 +54444,27 @@
       <c r="D648" t="inlineStr"/>
       <c r="E648" t="inlineStr">
         <is>
-          <t>9903.03.06</t>
+          <t>9903.88.03</t>
         </is>
       </c>
       <c r="F648" t="inlineStr">
         <is>
-          <t>S122 EXCL,IRN/STL/ALUM,DERIV</t>
+          <t>ARTICLE OF CHINA,US NTE 20(F)</t>
         </is>
       </c>
       <c r="G648" t="inlineStr">
         <is>
-          <t>106</t>
+          <t>107</t>
         </is>
       </c>
       <c r="H648" t="inlineStr">
         <is>
-          <t>9903.03.06</t>
+          <t>9903.88.03</t>
         </is>
       </c>
       <c r="I648" t="inlineStr">
         <is>
-          <t>9903.82.02,7318.15.8066</t>
+          <t>9903.03.06,9903.82.02,7318.22.0000</t>
         </is>
       </c>
       <c r="J648" t="inlineStr">
@@ -54537,7 +54537,7 @@
       </c>
       <c r="G649" t="inlineStr">
         <is>
-          <t>107</t>
+          <t>108</t>
         </is>
       </c>
       <c r="H649" t="inlineStr">
@@ -54547,7 +54547,7 @@
       </c>
       <c r="I649" t="inlineStr">
         <is>
-          <t>9903.03.06,9903.82.02,7318.22.0000</t>
+          <t>9903.03.06,9903.82.02,7318.15.8055</t>
         </is>
       </c>
       <c r="J649" t="inlineStr">
@@ -54610,27 +54610,27 @@
       <c r="D650" t="inlineStr"/>
       <c r="E650" t="inlineStr">
         <is>
-          <t>9903.88.03</t>
+          <t>9903.03.06</t>
         </is>
       </c>
       <c r="F650" t="inlineStr">
         <is>
-          <t>ARTICLE OF CHINA,US NTE 20(F)</t>
+          <t>S122 EXCL,IRN/STL/ALUM,DERIV</t>
         </is>
       </c>
       <c r="G650" t="inlineStr">
         <is>
-          <t>108</t>
+          <t>109</t>
         </is>
       </c>
       <c r="H650" t="inlineStr">
         <is>
-          <t>9903.88.03</t>
+          <t>9903.03.06</t>
         </is>
       </c>
       <c r="I650" t="inlineStr">
         <is>
-          <t>9903.03.06,9903.82.02,7318.15.8055</t>
+          <t>9903.82.02,7318.14.1060</t>
         </is>
       </c>
       <c r="J650" t="inlineStr">
@@ -54693,27 +54693,27 @@
       <c r="D651" t="inlineStr"/>
       <c r="E651" t="inlineStr">
         <is>
-          <t>9903.03.06</t>
+          <t>9903.88.03</t>
         </is>
       </c>
       <c r="F651" t="inlineStr">
         <is>
-          <t>S122 EXCL,IRN/STL/ALUM,DERIV</t>
+          <t>ARTICLE OF CHINA,US NTE 20(F)</t>
         </is>
       </c>
       <c r="G651" t="inlineStr">
         <is>
-          <t>109</t>
+          <t>110</t>
         </is>
       </c>
       <c r="H651" t="inlineStr">
         <is>
-          <t>9903.03.06</t>
+          <t>9903.88.03</t>
         </is>
       </c>
       <c r="I651" t="inlineStr">
         <is>
-          <t>9903.82.02,7318.14.1060</t>
+          <t>9903.03.06,9903.82.02,7318.22.0000</t>
         </is>
       </c>
       <c r="J651" t="inlineStr">
@@ -54776,27 +54776,27 @@
       <c r="D652" t="inlineStr"/>
       <c r="E652" t="inlineStr">
         <is>
-          <t>9903.88.03</t>
+          <t>9903.03.06</t>
         </is>
       </c>
       <c r="F652" t="inlineStr">
         <is>
-          <t>ARTICLE OF CHINA,US NTE 20(F)</t>
+          <t>S122 EXCL,IRN/STL/ALUM,DERIV</t>
         </is>
       </c>
       <c r="G652" t="inlineStr">
         <is>
-          <t>110</t>
+          <t>111</t>
         </is>
       </c>
       <c r="H652" t="inlineStr">
         <is>
-          <t>9903.88.03</t>
+          <t>9903.03.06</t>
         </is>
       </c>
       <c r="I652" t="inlineStr">
         <is>
-          <t>9903.03.06,9903.82.02,7318.22.0000</t>
+          <t>9903.82.02,7318.15.8066</t>
         </is>
       </c>
       <c r="J652" t="inlineStr">
@@ -54869,7 +54869,7 @@
       </c>
       <c r="G653" t="inlineStr">
         <is>
-          <t>111</t>
+          <t>112</t>
         </is>
       </c>
       <c r="H653" t="inlineStr">
@@ -54879,7 +54879,7 @@
       </c>
       <c r="I653" t="inlineStr">
         <is>
-          <t>9903.82.02,7318.15.8066</t>
+          <t>9903.82.02,7318.29.0000</t>
         </is>
       </c>
       <c r="J653" t="inlineStr">
@@ -54952,7 +54952,7 @@
       </c>
       <c r="G654" t="inlineStr">
         <is>
-          <t>112</t>
+          <t>113</t>
         </is>
       </c>
       <c r="H654" t="inlineStr">
@@ -55025,27 +55025,27 @@
       <c r="D655" t="inlineStr"/>
       <c r="E655" t="inlineStr">
         <is>
-          <t>9903.03.06</t>
+          <t>9903.88.03</t>
         </is>
       </c>
       <c r="F655" t="inlineStr">
         <is>
-          <t>S122 EXCL,IRN/STL/ALUM,DERIV</t>
+          <t>ARTICLE OF CHINA,US NTE 20(F)</t>
         </is>
       </c>
       <c r="G655" t="inlineStr">
         <is>
-          <t>113</t>
+          <t>114</t>
         </is>
       </c>
       <c r="H655" t="inlineStr">
         <is>
-          <t>9903.03.06</t>
+          <t>9903.88.03</t>
         </is>
       </c>
       <c r="I655" t="inlineStr">
         <is>
-          <t>9903.82.02,7318.29.0000</t>
+          <t>9903.03.06,9903.82.02,7318.22.0000</t>
         </is>
       </c>
       <c r="J655" t="inlineStr">
@@ -55108,27 +55108,27 @@
       <c r="D656" t="inlineStr"/>
       <c r="E656" t="inlineStr">
         <is>
-          <t>9903.88.03</t>
+          <t>9903.03.06</t>
         </is>
       </c>
       <c r="F656" t="inlineStr">
         <is>
-          <t>ARTICLE OF CHINA,US NTE 20(F)</t>
+          <t>S122 EXCL,IRN/STL/ALUM,DERIV</t>
         </is>
       </c>
       <c r="G656" t="inlineStr">
         <is>
-          <t>114</t>
+          <t>115</t>
         </is>
       </c>
       <c r="H656" t="inlineStr">
         <is>
-          <t>9903.88.03</t>
+          <t>9903.03.06</t>
         </is>
       </c>
       <c r="I656" t="inlineStr">
         <is>
-          <t>9903.03.06,9903.82.02,7318.22.0000</t>
+          <t>9903.82.02,7318.15.6040</t>
         </is>
       </c>
       <c r="J656" t="inlineStr">
@@ -55191,27 +55191,27 @@
       <c r="D657" t="inlineStr"/>
       <c r="E657" t="inlineStr">
         <is>
-          <t>9903.03.06</t>
+          <t>9903.88.03</t>
         </is>
       </c>
       <c r="F657" t="inlineStr">
         <is>
-          <t>S122 EXCL,IRN/STL/ALUM,DERIV</t>
+          <t>ARTICLE OF CHINA,US NTE 20(F)</t>
         </is>
       </c>
       <c r="G657" t="inlineStr">
         <is>
-          <t>115</t>
+          <t>116</t>
         </is>
       </c>
       <c r="H657" t="inlineStr">
         <is>
-          <t>9903.03.06</t>
+          <t>9903.88.03</t>
         </is>
       </c>
       <c r="I657" t="inlineStr">
         <is>
-          <t>9903.82.02,7318.15.6040</t>
+          <t>9903.03.06,9903.82.02,7318.22.0000</t>
         </is>
       </c>
       <c r="J657" t="inlineStr">
@@ -55274,27 +55274,27 @@
       <c r="D658" t="inlineStr"/>
       <c r="E658" t="inlineStr">
         <is>
-          <t>9903.88.03</t>
+          <t>9903.03.06</t>
         </is>
       </c>
       <c r="F658" t="inlineStr">
         <is>
-          <t>ARTICLE OF CHINA,US NTE 20(F)</t>
+          <t>S122 EXCL,IRN/STL/ALUM,DERIV</t>
         </is>
       </c>
       <c r="G658" t="inlineStr">
         <is>
-          <t>116</t>
+          <t>117</t>
         </is>
       </c>
       <c r="H658" t="inlineStr">
         <is>
-          <t>9903.88.03</t>
+          <t>9903.03.06</t>
         </is>
       </c>
       <c r="I658" t="inlineStr">
         <is>
-          <t>9903.03.06,9903.82.02,7318.22.0000</t>
+          <t>9903.82.02,7318.15.8066</t>
         </is>
       </c>
       <c r="J658" t="inlineStr">
@@ -55367,7 +55367,7 @@
       </c>
       <c r="G659" t="inlineStr">
         <is>
-          <t>117</t>
+          <t>118</t>
         </is>
       </c>
       <c r="H659" t="inlineStr">
@@ -55377,7 +55377,7 @@
       </c>
       <c r="I659" t="inlineStr">
         <is>
-          <t>9903.82.02,7318.15.8066</t>
+          <t>9903.82.02,7318.29.0000</t>
         </is>
       </c>
       <c r="J659" t="inlineStr">
@@ -55450,7 +55450,7 @@
       </c>
       <c r="G660" t="inlineStr">
         <is>
-          <t>118</t>
+          <t>119</t>
         </is>
       </c>
       <c r="H660" t="inlineStr">
@@ -55460,7 +55460,7 @@
       </c>
       <c r="I660" t="inlineStr">
         <is>
-          <t>9903.82.02,7318.29.0000</t>
+          <t>9903.82.02,7318.22.0000</t>
         </is>
       </c>
       <c r="J660" t="inlineStr">
@@ -55523,27 +55523,27 @@
       <c r="D661" t="inlineStr"/>
       <c r="E661" t="inlineStr">
         <is>
-          <t>9903.03.06</t>
+          <t>9903.88.15</t>
         </is>
       </c>
       <c r="F661" t="inlineStr">
         <is>
-          <t>S122 EXCL,IRN/STL/ALUM,DERIV</t>
+          <t>ARTICLE OF CHINA,US NTE 20(R)</t>
         </is>
       </c>
       <c r="G661" t="inlineStr">
         <is>
-          <t>119</t>
+          <t>120</t>
         </is>
       </c>
       <c r="H661" t="inlineStr">
         <is>
-          <t>9903.03.06</t>
+          <t>9903.88.15</t>
         </is>
       </c>
       <c r="I661" t="inlineStr">
         <is>
-          <t>9903.82.02,7318.22.0000</t>
+          <t>9903.03.06,9903.82.02,7318.16.0085</t>
         </is>
       </c>
       <c r="J661" t="inlineStr">
@@ -55606,27 +55606,27 @@
       <c r="D662" t="inlineStr"/>
       <c r="E662" t="inlineStr">
         <is>
-          <t>9903.88.15</t>
+          <t>9903.88.03</t>
         </is>
       </c>
       <c r="F662" t="inlineStr">
         <is>
-          <t>ARTICLE OF CHINA,US NTE 20(R)</t>
+          <t>ARTICLE OF CHINA,US NTE 20(F)</t>
         </is>
       </c>
       <c r="G662" t="inlineStr">
         <is>
-          <t>120</t>
+          <t>121</t>
         </is>
       </c>
       <c r="H662" t="inlineStr">
         <is>
-          <t>9903.88.15</t>
+          <t>9903.88.03</t>
         </is>
       </c>
       <c r="I662" t="inlineStr">
         <is>
-          <t>9903.03.06,9903.82.02,7318.16.0085</t>
+          <t>9903.03.06,9903.82.02,7318.29.0000</t>
         </is>
       </c>
       <c r="J662" t="inlineStr">
@@ -55689,27 +55689,27 @@
       <c r="D663" t="inlineStr"/>
       <c r="E663" t="inlineStr">
         <is>
-          <t>9903.88.03</t>
+          <t>9903.88.15</t>
         </is>
       </c>
       <c r="F663" t="inlineStr">
         <is>
-          <t>ARTICLE OF CHINA,US NTE 20(F)</t>
+          <t>ARTICLE OF CHINA,US NTE 20(R)</t>
         </is>
       </c>
       <c r="G663" t="inlineStr">
         <is>
-          <t>121</t>
+          <t>122</t>
         </is>
       </c>
       <c r="H663" t="inlineStr">
         <is>
-          <t>9903.88.03</t>
+          <t>9903.88.15</t>
         </is>
       </c>
       <c r="I663" t="inlineStr">
         <is>
-          <t>9903.03.06,9903.82.02,7318.29.0000</t>
+          <t>9903.03.06,9903.82.02,7318.16.0085</t>
         </is>
       </c>
       <c r="J663" t="inlineStr">
@@ -55772,27 +55772,27 @@
       <c r="D664" t="inlineStr"/>
       <c r="E664" t="inlineStr">
         <is>
-          <t>9903.88.15</t>
+          <t>9903.03.06</t>
         </is>
       </c>
       <c r="F664" t="inlineStr">
         <is>
-          <t>ARTICLE OF CHINA,US NTE 20(R)</t>
+          <t>S122 EXCL,IRN/STL/ALUM,DERIV</t>
         </is>
       </c>
       <c r="G664" t="inlineStr">
         <is>
-          <t>122</t>
+          <t>123</t>
         </is>
       </c>
       <c r="H664" t="inlineStr">
         <is>
-          <t>9903.88.15</t>
+          <t>9903.03.06</t>
         </is>
       </c>
       <c r="I664" t="inlineStr">
         <is>
-          <t>9903.03.06,9903.82.02,7318.16.0085</t>
+          <t>9903.82.02,7318.15.8066</t>
         </is>
       </c>
       <c r="J664" t="inlineStr">
@@ -55822,12 +55822,12 @@
       </c>
       <c r="O664" t="inlineStr">
         <is>
-          <t>REYHER GMBH</t>
+          <t>ACHILLES SEIBERT GMBH</t>
         </is>
       </c>
       <c r="P664" t="inlineStr">
         <is>
-          <t>REYHER GMBH</t>
+          <t>ACHILLES SEIBERT GMBH</t>
         </is>
       </c>
       <c r="Q664" t="inlineStr">
@@ -55865,7 +55865,7 @@
       </c>
       <c r="G665" t="inlineStr">
         <is>
-          <t>123</t>
+          <t>124</t>
         </is>
       </c>
       <c r="H665" t="inlineStr">
@@ -55948,7 +55948,7 @@
       </c>
       <c r="G666" t="inlineStr">
         <is>
-          <t>124</t>
+          <t>125</t>
         </is>
       </c>
       <c r="H666" t="inlineStr">
@@ -56031,7 +56031,7 @@
       </c>
       <c r="G667" t="inlineStr">
         <is>
-          <t>125</t>
+          <t>126</t>
         </is>
       </c>
       <c r="H667" t="inlineStr">
@@ -56114,7 +56114,7 @@
       </c>
       <c r="G668" t="inlineStr">
         <is>
-          <t>126</t>
+          <t>127</t>
         </is>
       </c>
       <c r="H668" t="inlineStr">
@@ -56197,7 +56197,7 @@
       </c>
       <c r="G669" t="inlineStr">
         <is>
-          <t>127</t>
+          <t>128</t>
         </is>
       </c>
       <c r="H669" t="inlineStr">
@@ -56280,7 +56280,7 @@
       </c>
       <c r="G670" t="inlineStr">
         <is>
-          <t>128</t>
+          <t>129</t>
         </is>
       </c>
       <c r="H670" t="inlineStr">
@@ -56363,7 +56363,7 @@
       </c>
       <c r="G671" t="inlineStr">
         <is>
-          <t>129</t>
+          <t>130</t>
         </is>
       </c>
       <c r="H671" t="inlineStr">
@@ -56446,7 +56446,7 @@
       </c>
       <c r="G672" t="inlineStr">
         <is>
-          <t>130</t>
+          <t>131</t>
         </is>
       </c>
       <c r="H672" t="inlineStr">
@@ -56519,27 +56519,27 @@
       <c r="D673" t="inlineStr"/>
       <c r="E673" t="inlineStr">
         <is>
-          <t>9903.03.06</t>
+          <t>9903.88.03</t>
         </is>
       </c>
       <c r="F673" t="inlineStr">
         <is>
-          <t>S122 EXCL,IRN/STL/ALUM,DERIV</t>
+          <t>ARTICLE OF CHINA,US NTE 20(F)</t>
         </is>
       </c>
       <c r="G673" t="inlineStr">
         <is>
-          <t>131</t>
+          <t>132</t>
         </is>
       </c>
       <c r="H673" t="inlineStr">
         <is>
-          <t>9903.03.06</t>
+          <t>9903.88.03</t>
         </is>
       </c>
       <c r="I673" t="inlineStr">
         <is>
-          <t>9903.82.02,7318.15.8066</t>
+          <t>9903.03.06,9903.82.02,7318.15.8066</t>
         </is>
       </c>
       <c r="J673" t="inlineStr">
@@ -56602,27 +56602,27 @@
       <c r="D674" t="inlineStr"/>
       <c r="E674" t="inlineStr">
         <is>
-          <t>9903.88.03</t>
+          <t>9903.03.06</t>
         </is>
       </c>
       <c r="F674" t="inlineStr">
         <is>
-          <t>ARTICLE OF CHINA,US NTE 20(F)</t>
+          <t>S122 EXCL,IRN/STL/ALUM,DERIV</t>
         </is>
       </c>
       <c r="G674" t="inlineStr">
         <is>
-          <t>132</t>
+          <t>133</t>
         </is>
       </c>
       <c r="H674" t="inlineStr">
         <is>
-          <t>9903.88.03</t>
+          <t>9903.03.06</t>
         </is>
       </c>
       <c r="I674" t="inlineStr">
         <is>
-          <t>9903.03.06,9903.82.02,7318.15.8066</t>
+          <t>9903.82.02,7318.15.8066</t>
         </is>
       </c>
       <c r="J674" t="inlineStr">
@@ -56695,7 +56695,7 @@
       </c>
       <c r="G675" t="inlineStr">
         <is>
-          <t>133</t>
+          <t>134</t>
         </is>
       </c>
       <c r="H675" t="inlineStr">
@@ -56778,7 +56778,7 @@
       </c>
       <c r="G676" t="inlineStr">
         <is>
-          <t>134</t>
+          <t>135</t>
         </is>
       </c>
       <c r="H676" t="inlineStr">
@@ -56861,7 +56861,7 @@
       </c>
       <c r="G677" t="inlineStr">
         <is>
-          <t>135</t>
+          <t>136</t>
         </is>
       </c>
       <c r="H677" t="inlineStr">
@@ -56871,7 +56871,7 @@
       </c>
       <c r="I677" t="inlineStr">
         <is>
-          <t>9903.82.02,7318.15.8066</t>
+          <t>9903.82.02,7318.15.6080</t>
         </is>
       </c>
       <c r="J677" t="inlineStr">
@@ -56944,7 +56944,7 @@
       </c>
       <c r="G678" t="inlineStr">
         <is>
-          <t>136</t>
+          <t>137</t>
         </is>
       </c>
       <c r="H678" t="inlineStr">
@@ -56954,7 +56954,7 @@
       </c>
       <c r="I678" t="inlineStr">
         <is>
-          <t>9903.82.02,7318.15.6080</t>
+          <t>9903.82.02,7318.15.8066</t>
         </is>
       </c>
       <c r="J678" t="inlineStr">
@@ -57027,7 +57027,7 @@
       </c>
       <c r="G679" t="inlineStr">
         <is>
-          <t>137</t>
+          <t>138</t>
         </is>
       </c>
       <c r="H679" t="inlineStr">
@@ -57110,7 +57110,7 @@
       </c>
       <c r="G680" t="inlineStr">
         <is>
-          <t>138</t>
+          <t>139</t>
         </is>
       </c>
       <c r="H680" t="inlineStr">
@@ -57193,7 +57193,7 @@
       </c>
       <c r="G681" t="inlineStr">
         <is>
-          <t>139</t>
+          <t>140</t>
         </is>
       </c>
       <c r="H681" t="inlineStr">
@@ -57266,27 +57266,27 @@
       <c r="D682" t="inlineStr"/>
       <c r="E682" t="inlineStr">
         <is>
-          <t>9903.03.06</t>
+          <t>9903.88.03</t>
         </is>
       </c>
       <c r="F682" t="inlineStr">
         <is>
-          <t>S122 EXCL,IRN/STL/ALUM,DERIV</t>
+          <t>ARTICLE OF CHINA,US NTE 20(F)</t>
         </is>
       </c>
       <c r="G682" t="inlineStr">
         <is>
-          <t>140</t>
+          <t>141</t>
         </is>
       </c>
       <c r="H682" t="inlineStr">
         <is>
-          <t>9903.03.06</t>
+          <t>9903.88.03</t>
         </is>
       </c>
       <c r="I682" t="inlineStr">
         <is>
-          <t>9903.82.02,7318.15.8066</t>
+          <t>9903.03.06,9903.82.02,7318.15.8066</t>
         </is>
       </c>
       <c r="J682" t="inlineStr">
@@ -57349,27 +57349,27 @@
       <c r="D683" t="inlineStr"/>
       <c r="E683" t="inlineStr">
         <is>
-          <t>9903.88.03</t>
+          <t>9903.03.06</t>
         </is>
       </c>
       <c r="F683" t="inlineStr">
         <is>
-          <t>ARTICLE OF CHINA,US NTE 20(F)</t>
+          <t>S122 EXCL,IRN/STL/ALUM,DERIV</t>
         </is>
       </c>
       <c r="G683" t="inlineStr">
         <is>
-          <t>141</t>
+          <t>142</t>
         </is>
       </c>
       <c r="H683" t="inlineStr">
         <is>
-          <t>9903.88.03</t>
+          <t>9903.03.06</t>
         </is>
       </c>
       <c r="I683" t="inlineStr">
         <is>
-          <t>9903.03.06,9903.82.02,7318.15.8066</t>
+          <t>9903.82.02,7318.15.8066</t>
         </is>
       </c>
       <c r="J683" t="inlineStr">
@@ -57442,7 +57442,7 @@
       </c>
       <c r="G684" t="inlineStr">
         <is>
-          <t>142</t>
+          <t>143</t>
         </is>
       </c>
       <c r="H684" t="inlineStr">
@@ -57525,7 +57525,7 @@
       </c>
       <c r="G685" t="inlineStr">
         <is>
-          <t>143</t>
+          <t>144</t>
         </is>
       </c>
       <c r="H685" t="inlineStr">
@@ -57535,7 +57535,7 @@
       </c>
       <c r="I685" t="inlineStr">
         <is>
-          <t>9903.82.02,7318.15.8066</t>
+          <t>9903.82.02,7318.15.8045</t>
         </is>
       </c>
       <c r="J685" t="inlineStr">
@@ -57608,7 +57608,7 @@
       </c>
       <c r="G686" t="inlineStr">
         <is>
-          <t>144</t>
+          <t>145</t>
         </is>
       </c>
       <c r="H686" t="inlineStr">
@@ -57618,7 +57618,7 @@
       </c>
       <c r="I686" t="inlineStr">
         <is>
-          <t>9903.82.02,7318.15.8045</t>
+          <t>9903.82.02,7318.15.6040</t>
         </is>
       </c>
       <c r="J686" t="inlineStr">
@@ -57691,7 +57691,7 @@
       </c>
       <c r="G687" t="inlineStr">
         <is>
-          <t>145</t>
+          <t>146</t>
         </is>
       </c>
       <c r="H687" t="inlineStr">
@@ -57701,7 +57701,7 @@
       </c>
       <c r="I687" t="inlineStr">
         <is>
-          <t>9903.82.02,7318.15.6040</t>
+          <t>9903.82.02,7318.15.8066</t>
         </is>
       </c>
       <c r="J687" t="inlineStr">
@@ -57774,7 +57774,7 @@
       </c>
       <c r="G688" t="inlineStr">
         <is>
-          <t>146</t>
+          <t>147</t>
         </is>
       </c>
       <c r="H688" t="inlineStr">
@@ -57857,7 +57857,7 @@
       </c>
       <c r="G689" t="inlineStr">
         <is>
-          <t>147</t>
+          <t>148</t>
         </is>
       </c>
       <c r="H689" t="inlineStr">
@@ -57940,7 +57940,7 @@
       </c>
       <c r="G690" t="inlineStr">
         <is>
-          <t>148</t>
+          <t>149</t>
         </is>
       </c>
       <c r="H690" t="inlineStr">
@@ -57950,7 +57950,7 @@
       </c>
       <c r="I690" t="inlineStr">
         <is>
-          <t>9903.82.02,7318.15.8066</t>
+          <t>9903.82.02,7318.15.8045</t>
         </is>
       </c>
       <c r="J690" t="inlineStr">
@@ -57980,12 +57980,12 @@
       </c>
       <c r="O690" t="inlineStr">
         <is>
-          <t>ACHILLES SEIBERT GMBH</t>
+          <t>PRK TECHNOLOGIES GMBH</t>
         </is>
       </c>
       <c r="P690" t="inlineStr">
         <is>
-          <t>ACHILLES SEIBERT GMBH</t>
+          <t>PRK TECHNOLOGIES GMBH</t>
         </is>
       </c>
       <c r="Q690" t="inlineStr">
@@ -58023,7 +58023,7 @@
       </c>
       <c r="G691" t="inlineStr">
         <is>
-          <t>149</t>
+          <t>150</t>
         </is>
       </c>
       <c r="H691" t="inlineStr">
@@ -58106,7 +58106,7 @@
       </c>
       <c r="G692" t="inlineStr">
         <is>
-          <t>150</t>
+          <t>151</t>
         </is>
       </c>
       <c r="H692" t="inlineStr">
@@ -58163,12 +58163,12 @@
     <row r="693">
       <c r="A693" t="inlineStr">
         <is>
-          <t>2615655-2</t>
+          <t>2615655-7</t>
         </is>
       </c>
       <c r="B693" t="inlineStr">
         <is>
-          <t>EF4-0231820-0</t>
+          <t>EF4-0231821-8</t>
         </is>
       </c>
       <c r="C693" t="inlineStr">
@@ -58189,7 +58189,7 @@
       </c>
       <c r="G693" t="inlineStr">
         <is>
-          <t>151</t>
+          <t>001</t>
         </is>
       </c>
       <c r="H693" t="inlineStr">
@@ -58199,22 +58199,22 @@
       </c>
       <c r="I693" t="inlineStr">
         <is>
-          <t>9903.82.02,7318.15.8045</t>
+          <t>9903.82.10,8431.39.0010</t>
         </is>
       </c>
       <c r="J693" t="inlineStr">
         <is>
-          <t>EUROLINK FSS LLC</t>
+          <t>AUMUND CORPORATION</t>
         </is>
       </c>
       <c r="K693" t="inlineStr">
         <is>
-          <t>SUPLIN</t>
+          <t>AUMCOR</t>
         </is>
       </c>
       <c r="L693" t="inlineStr">
         <is>
-          <t>57-112314200</t>
+          <t>58-138896800</t>
         </is>
       </c>
       <c r="M693" t="inlineStr">
@@ -58229,12 +58229,12 @@
       </c>
       <c r="O693" t="inlineStr">
         <is>
-          <t>PRK TECHNOLOGIES GMBH</t>
+          <t>AUMUND FOERDERTECHNIK GMBH</t>
         </is>
       </c>
       <c r="P693" t="inlineStr">
         <is>
-          <t>PRK TECHNOLOGIES GMBH</t>
+          <t>AUMUND FOERDERTECHNIK GMBH</t>
         </is>
       </c>
       <c r="Q693" t="inlineStr">
@@ -58272,7 +58272,7 @@
       </c>
       <c r="G694" t="inlineStr">
         <is>
-          <t>001</t>
+          <t>002</t>
         </is>
       </c>
       <c r="H694" t="inlineStr">
@@ -58282,7 +58282,7 @@
       </c>
       <c r="I694" t="inlineStr">
         <is>
-          <t>9903.82.10,8431.39.0010</t>
+          <t>9903.82.02,7318.15.2095</t>
         </is>
       </c>
       <c r="J694" t="inlineStr">
@@ -58355,7 +58355,7 @@
       </c>
       <c r="G695" t="inlineStr">
         <is>
-          <t>002</t>
+          <t>003</t>
         </is>
       </c>
       <c r="H695" t="inlineStr">
@@ -58365,7 +58365,7 @@
       </c>
       <c r="I695" t="inlineStr">
         <is>
-          <t>9903.82.02,7318.15.2095</t>
+          <t>9903.82.02,7318.16.0085</t>
         </is>
       </c>
       <c r="J695" t="inlineStr">
@@ -58438,7 +58438,7 @@
       </c>
       <c r="G696" t="inlineStr">
         <is>
-          <t>003</t>
+          <t>004</t>
         </is>
       </c>
       <c r="H696" t="inlineStr">
@@ -58448,7 +58448,7 @@
       </c>
       <c r="I696" t="inlineStr">
         <is>
-          <t>9903.82.02,7318.16.0085</t>
+          <t>9903.82.02,7318.22.0000</t>
         </is>
       </c>
       <c r="J696" t="inlineStr">
@@ -58495,12 +58495,12 @@
     <row r="697">
       <c r="A697" t="inlineStr">
         <is>
-          <t>2615655-7</t>
+          <t>2615655-8</t>
         </is>
       </c>
       <c r="B697" t="inlineStr">
         <is>
-          <t>EF4-0231821-8</t>
+          <t>EF4-0231822-6</t>
         </is>
       </c>
       <c r="C697" t="inlineStr">
@@ -58521,7 +58521,7 @@
       </c>
       <c r="G697" t="inlineStr">
         <is>
-          <t>004</t>
+          <t>001</t>
         </is>
       </c>
       <c r="H697" t="inlineStr">
@@ -58531,7 +58531,7 @@
       </c>
       <c r="I697" t="inlineStr">
         <is>
-          <t>9903.82.02,7318.22.0000</t>
+          <t>9903.82.10,8431.39.0010</t>
         </is>
       </c>
       <c r="J697" t="inlineStr">
@@ -58578,12 +58578,12 @@
     <row r="698">
       <c r="A698" t="inlineStr">
         <is>
-          <t>2615655-8</t>
+          <t>261565511</t>
         </is>
       </c>
       <c r="B698" t="inlineStr">
         <is>
-          <t>EF4-0231822-6</t>
+          <t>EF4-0231974-5</t>
         </is>
       </c>
       <c r="C698" t="inlineStr">
@@ -58614,27 +58614,27 @@
       </c>
       <c r="I698" t="inlineStr">
         <is>
-          <t>9903.82.10,8431.39.0010</t>
+          <t>9903.82.09,8483.30.4040</t>
         </is>
       </c>
       <c r="J698" t="inlineStr">
         <is>
-          <t>AUMUND CORPORATION</t>
+          <t>AFC LS LLC</t>
         </is>
       </c>
       <c r="K698" t="inlineStr">
         <is>
-          <t>AUMCOR</t>
+          <t>AFCLS01</t>
         </is>
       </c>
       <c r="L698" t="inlineStr">
         <is>
-          <t>58-138896800</t>
+          <t>27-072036900</t>
         </is>
       </c>
       <c r="M698" t="inlineStr">
         <is>
-          <t>2026-06-18 00:00:00</t>
+          <t>2026-06-14 00:00:00</t>
         </is>
       </c>
       <c r="N698" t="inlineStr">
@@ -58644,12 +58644,12 @@
       </c>
       <c r="O698" t="inlineStr">
         <is>
-          <t>AUMUND FOERDERTECHNIK GMBH</t>
+          <t>HFB WALZLAGER GEHAUSETECHNIK</t>
         </is>
       </c>
       <c r="P698" t="inlineStr">
         <is>
-          <t>AUMUND FOERDERTECHNIK GMBH</t>
+          <t>HFB WALZLAGER GEHAUSETECHNIK</t>
         </is>
       </c>
       <c r="Q698" t="inlineStr">
@@ -58677,27 +58677,27 @@
       <c r="D699" t="inlineStr"/>
       <c r="E699" t="inlineStr">
         <is>
-          <t>9903.03.06</t>
+          <t>9903.03.01</t>
         </is>
       </c>
       <c r="F699" t="inlineStr">
         <is>
-          <t>S122 EXCL,IRN/STL/ALUM,DERIV</t>
+          <t>SECTION 122 - 10% DUTY</t>
         </is>
       </c>
       <c r="G699" t="inlineStr">
         <is>
-          <t>001</t>
+          <t>002</t>
         </is>
       </c>
       <c r="H699" t="inlineStr">
         <is>
-          <t>9903.03.06</t>
+          <t>9903.03.01</t>
         </is>
       </c>
       <c r="I699" t="inlineStr">
         <is>
-          <t>9903.82.09,8483.30.4040</t>
+          <t>8482.30.0080</t>
         </is>
       </c>
       <c r="J699" t="inlineStr">
@@ -58760,27 +58760,27 @@
       <c r="D700" t="inlineStr"/>
       <c r="E700" t="inlineStr">
         <is>
-          <t>9903.03.01</t>
+          <t>9903.03.06</t>
         </is>
       </c>
       <c r="F700" t="inlineStr">
         <is>
-          <t>SECTION 122 - 10% DUTY</t>
+          <t>S122 EXCL,IRN/STL/ALUM,DERIV</t>
         </is>
       </c>
       <c r="G700" t="inlineStr">
         <is>
-          <t>002</t>
+          <t>003</t>
         </is>
       </c>
       <c r="H700" t="inlineStr">
         <is>
-          <t>9903.03.01</t>
+          <t>9903.03.06</t>
         </is>
       </c>
       <c r="I700" t="inlineStr">
         <is>
-          <t>8482.30.0080</t>
+          <t>9903.82.09,8482.99.6510</t>
         </is>
       </c>
       <c r="J700" t="inlineStr">
@@ -58853,7 +58853,7 @@
       </c>
       <c r="G701" t="inlineStr">
         <is>
-          <t>003</t>
+          <t>004</t>
         </is>
       </c>
       <c r="H701" t="inlineStr">
@@ -58863,7 +58863,7 @@
       </c>
       <c r="I701" t="inlineStr">
         <is>
-          <t>9903.82.09,8482.99.6510</t>
+          <t>9903.82.09,8483.30.4040</t>
         </is>
       </c>
       <c r="J701" t="inlineStr">
@@ -58926,27 +58926,27 @@
       <c r="D702" t="inlineStr"/>
       <c r="E702" t="inlineStr">
         <is>
-          <t>9903.03.06</t>
+          <t>9903.03.01</t>
         </is>
       </c>
       <c r="F702" t="inlineStr">
         <is>
-          <t>S122 EXCL,IRN/STL/ALUM,DERIV</t>
+          <t>SECTION 122 - 10% DUTY</t>
         </is>
       </c>
       <c r="G702" t="inlineStr">
         <is>
-          <t>004</t>
+          <t>005</t>
         </is>
       </c>
       <c r="H702" t="inlineStr">
         <is>
-          <t>9903.03.06</t>
+          <t>9903.03.01</t>
         </is>
       </c>
       <c r="I702" t="inlineStr">
         <is>
-          <t>9903.82.09,8483.30.4040</t>
+          <t>8482.30.0080</t>
         </is>
       </c>
       <c r="J702" t="inlineStr">
@@ -59009,27 +59009,27 @@
       <c r="D703" t="inlineStr"/>
       <c r="E703" t="inlineStr">
         <is>
-          <t>9903.03.01</t>
+          <t>9903.03.06</t>
         </is>
       </c>
       <c r="F703" t="inlineStr">
         <is>
-          <t>SECTION 122 - 10% DUTY</t>
+          <t>S122 EXCL,IRN/STL/ALUM,DERIV</t>
         </is>
       </c>
       <c r="G703" t="inlineStr">
         <is>
-          <t>005</t>
+          <t>006</t>
         </is>
       </c>
       <c r="H703" t="inlineStr">
         <is>
-          <t>9903.03.01</t>
+          <t>9903.03.06</t>
         </is>
       </c>
       <c r="I703" t="inlineStr">
         <is>
-          <t>8482.30.0080</t>
+          <t>9903.82.09,8482.99.6510</t>
         </is>
       </c>
       <c r="J703" t="inlineStr">
@@ -59076,12 +59076,12 @@
     <row r="704">
       <c r="A704" t="inlineStr">
         <is>
-          <t>261565511</t>
+          <t>2615703</t>
         </is>
       </c>
       <c r="B704" t="inlineStr">
         <is>
-          <t>EF4-0231974-5</t>
+          <t>EF4-0232045-3</t>
         </is>
       </c>
       <c r="C704" t="inlineStr">
@@ -59089,50 +59089,54 @@
           <t>Vessel, Non-container</t>
         </is>
       </c>
-      <c r="D704" t="inlineStr"/>
+      <c r="D704" t="inlineStr">
+        <is>
+          <t>165938054</t>
+        </is>
+      </c>
       <c r="E704" t="inlineStr">
         <is>
-          <t>9903.03.06</t>
+          <t>9903.91.01</t>
         </is>
       </c>
       <c r="F704" t="inlineStr">
         <is>
-          <t>S122 EXCL,IRN/STL/ALUM,DERIV</t>
+          <t>ARTS, PRDS OF CN SUB(B)US NT31</t>
         </is>
       </c>
       <c r="G704" t="inlineStr">
         <is>
-          <t>006</t>
+          <t>001</t>
         </is>
       </c>
       <c r="H704" t="inlineStr">
         <is>
-          <t>9903.03.06</t>
+          <t>9903.91.01</t>
         </is>
       </c>
       <c r="I704" t="inlineStr">
         <is>
-          <t>9903.82.09,8482.99.6510</t>
+          <t>9903.03.06,9903.82.02,7219.33.0070</t>
         </is>
       </c>
       <c r="J704" t="inlineStr">
         <is>
-          <t>AFC LS LLC</t>
+          <t>SOUTHERN PRECISION MACHINING, LLC</t>
         </is>
       </c>
       <c r="K704" t="inlineStr">
         <is>
-          <t>AFCLS01</t>
+          <t>SOUPRE01</t>
         </is>
       </c>
       <c r="L704" t="inlineStr">
         <is>
-          <t>27-072036900</t>
+          <t>33-354197700</t>
         </is>
       </c>
       <c r="M704" t="inlineStr">
         <is>
-          <t>2026-06-14 00:00:00</t>
+          <t>2026-06-27 00:00:00</t>
         </is>
       </c>
       <c r="N704" t="inlineStr">
@@ -59142,17 +59146,17 @@
       </c>
       <c r="O704" t="inlineStr">
         <is>
-          <t>HFB WALZLAGER GEHAUSETECHNIK</t>
+          <t>FUJIAN TSINGTUO INDUSTRIAL CO LTD</t>
         </is>
       </c>
       <c r="P704" t="inlineStr">
         <is>
-          <t>HFB WALZLAGER GEHAUSETECHNIK</t>
+          <t>FUJIAN TSINGTUO INDUSTRIAL CO LTD</t>
         </is>
       </c>
       <c r="Q704" t="inlineStr">
         <is>
-          <t>2026-05-27 00:00:00</t>
+          <t>2026-06-01 00:00:00</t>
         </is>
       </c>
     </row>
@@ -59189,7 +59193,7 @@
       </c>
       <c r="G705" t="inlineStr">
         <is>
-          <t>001</t>
+          <t>002</t>
         </is>
       </c>
       <c r="H705" t="inlineStr">
@@ -59199,7 +59203,7 @@
       </c>
       <c r="I705" t="inlineStr">
         <is>
-          <t>9903.03.06,9903.82.02,7219.33.0070</t>
+          <t>9903.03.06,9903.82.02,7219.23.0060</t>
         </is>
       </c>
       <c r="J705" t="inlineStr">
@@ -59276,7 +59280,7 @@
       </c>
       <c r="G706" t="inlineStr">
         <is>
-          <t>002</t>
+          <t>003</t>
         </is>
       </c>
       <c r="H706" t="inlineStr">
@@ -59363,7 +59367,7 @@
       </c>
       <c r="G707" t="inlineStr">
         <is>
-          <t>003</t>
+          <t>004</t>
         </is>
       </c>
       <c r="H707" t="inlineStr">
@@ -59420,12 +59424,12 @@
     <row r="708">
       <c r="A708" t="inlineStr">
         <is>
-          <t>2615703</t>
+          <t>2615705-2</t>
         </is>
       </c>
       <c r="B708" t="inlineStr">
         <is>
-          <t>EF4-0232045-3</t>
+          <t>EF4-0232161-8</t>
         </is>
       </c>
       <c r="C708" t="inlineStr">
@@ -59440,47 +59444,47 @@
       </c>
       <c r="E708" t="inlineStr">
         <is>
-          <t>9903.91.01</t>
+          <t>9903.03.06</t>
         </is>
       </c>
       <c r="F708" t="inlineStr">
         <is>
-          <t>ARTS, PRDS OF CN SUB(B)US NT31</t>
+          <t>S122 EXCL,IRN/STL/ALUM,DERIV</t>
         </is>
       </c>
       <c r="G708" t="inlineStr">
         <is>
-          <t>004</t>
+          <t>001</t>
         </is>
       </c>
       <c r="H708" t="inlineStr">
         <is>
-          <t>9903.91.01</t>
+          <t>9903.03.06</t>
         </is>
       </c>
       <c r="I708" t="inlineStr">
         <is>
-          <t>9903.03.06,9903.82.02,7219.23.0060</t>
+          <t>9903.82.02,7315.82.7000</t>
         </is>
       </c>
       <c r="J708" t="inlineStr">
         <is>
-          <t>SOUTHERN PRECISION MACHINING, LLC</t>
+          <t>CANTRELL GAINCO GROUP INC</t>
         </is>
       </c>
       <c r="K708" t="inlineStr">
         <is>
-          <t>SOUPRE01</t>
+          <t>CANGAI01</t>
         </is>
       </c>
       <c r="L708" t="inlineStr">
         <is>
-          <t>33-354197700</t>
+          <t>31-151121700</t>
         </is>
       </c>
       <c r="M708" t="inlineStr">
         <is>
-          <t>2026-06-27 00:00:00</t>
+          <t>2026-07-01 00:00:00</t>
         </is>
       </c>
       <c r="N708" t="inlineStr">
@@ -59490,17 +59494,17 @@
       </c>
       <c r="O708" t="inlineStr">
         <is>
-          <t>FUJIAN TSINGTUO INDUSTRIAL CO LTD</t>
+          <t>ROTTGERS KETTEN GMBH</t>
         </is>
       </c>
       <c r="P708" t="inlineStr">
         <is>
-          <t>FUJIAN TSINGTUO INDUSTRIAL CO LTD</t>
+          <t>ROTTGERS KETTEN GMBH</t>
         </is>
       </c>
       <c r="Q708" t="inlineStr">
         <is>
-          <t>2026-06-01 00:00:00</t>
+          <t>2026-06-11 00:00:00</t>
         </is>
       </c>
     </row>
@@ -59537,7 +59541,7 @@
       </c>
       <c r="G709" t="inlineStr">
         <is>
-          <t>001</t>
+          <t>002</t>
         </is>
       </c>
       <c r="H709" t="inlineStr">
@@ -59547,7 +59551,7 @@
       </c>
       <c r="I709" t="inlineStr">
         <is>
-          <t>9903.82.02,7315.82.7000</t>
+          <t>9903.82.02,7315.82.3000</t>
         </is>
       </c>
       <c r="J709" t="inlineStr">
@@ -59624,7 +59628,7 @@
       </c>
       <c r="G710" t="inlineStr">
         <is>
-          <t>002</t>
+          <t>003</t>
         </is>
       </c>
       <c r="H710" t="inlineStr">
@@ -59711,7 +59715,7 @@
       </c>
       <c r="G711" t="inlineStr">
         <is>
-          <t>003</t>
+          <t>004</t>
         </is>
       </c>
       <c r="H711" t="inlineStr">
@@ -59798,7 +59802,7 @@
       </c>
       <c r="G712" t="inlineStr">
         <is>
-          <t>004</t>
+          <t>005</t>
         </is>
       </c>
       <c r="H712" t="inlineStr">
@@ -59855,67 +59859,63 @@
     <row r="713">
       <c r="A713" t="inlineStr">
         <is>
-          <t>2615705-2</t>
+          <t>2566071</t>
         </is>
       </c>
       <c r="B713" t="inlineStr">
         <is>
-          <t>EF4-0232161-8</t>
+          <t>EF4-0232189-9</t>
         </is>
       </c>
       <c r="C713" t="inlineStr">
         <is>
-          <t>Vessel, Non-container</t>
-        </is>
-      </c>
-      <c r="D713" t="inlineStr">
-        <is>
-          <t>165938054</t>
-        </is>
-      </c>
+          <t>Vessel, Container</t>
+        </is>
+      </c>
+      <c r="D713" t="inlineStr"/>
       <c r="E713" t="inlineStr">
         <is>
-          <t>9903.03.06</t>
+          <t>9903.03.03</t>
         </is>
       </c>
       <c r="F713" t="inlineStr">
         <is>
-          <t>S122 EXCL,IRN/STL/ALUM,DERIV</t>
+          <t>S122 -EXCLUSION-EXEMPTED PRDTS</t>
         </is>
       </c>
       <c r="G713" t="inlineStr">
         <is>
-          <t>005</t>
+          <t>001</t>
         </is>
       </c>
       <c r="H713" t="inlineStr">
         <is>
-          <t>9903.03.06</t>
+          <t>9903.03.03</t>
         </is>
       </c>
       <c r="I713" t="inlineStr">
         <is>
-          <t>9903.82.02,7315.82.3000</t>
+          <t>2930.90.9231</t>
         </is>
       </c>
       <c r="J713" t="inlineStr">
         <is>
-          <t>CANTRELL GAINCO GROUP INC</t>
+          <t>CASTLE CHEMICALS LTD</t>
         </is>
       </c>
       <c r="K713" t="inlineStr">
         <is>
-          <t>CANGAI01</t>
+          <t>CASCHE01</t>
         </is>
       </c>
       <c r="L713" t="inlineStr">
         <is>
-          <t>31-151121700</t>
+          <t>151704-07138</t>
         </is>
       </c>
       <c r="M713" t="inlineStr">
         <is>
-          <t>2026-07-01 00:00:00</t>
+          <t>2026-06-29 00:00:00</t>
         </is>
       </c>
       <c r="N713" t="inlineStr">
@@ -59925,29 +59925,29 @@
       </c>
       <c r="O713" t="inlineStr">
         <is>
-          <t>ROTTGERS KETTEN GMBH</t>
+          <t>HUBEI JIANGHAN NEW MATERIALS CO LTD</t>
         </is>
       </c>
       <c r="P713" t="inlineStr">
         <is>
-          <t>ROTTGERS KETTEN GMBH</t>
+          <t>HUBEI JIANGHAN NEW MATERIALS CO LTD</t>
         </is>
       </c>
       <c r="Q713" t="inlineStr">
         <is>
-          <t>2026-06-11 00:00:00</t>
+          <t>2026-05-27 00:00:00</t>
         </is>
       </c>
     </row>
     <row r="714">
       <c r="A714" t="inlineStr">
         <is>
-          <t>2566071</t>
+          <t>2566072</t>
         </is>
       </c>
       <c r="B714" t="inlineStr">
         <is>
-          <t>EF4-0232189-9</t>
+          <t>EF4-0232190-7</t>
         </is>
       </c>
       <c r="C714" t="inlineStr">
@@ -60025,28 +60025,32 @@
     <row r="715">
       <c r="A715" t="inlineStr">
         <is>
-          <t>2566072</t>
+          <t>2615752</t>
         </is>
       </c>
       <c r="B715" t="inlineStr">
         <is>
-          <t>EF4-0232190-7</t>
+          <t>EF4-0232314-3</t>
         </is>
       </c>
       <c r="C715" t="inlineStr">
         <is>
-          <t>Vessel, Container</t>
-        </is>
-      </c>
-      <c r="D715" t="inlineStr"/>
+          <t>Vessel, Non-container</t>
+        </is>
+      </c>
+      <c r="D715" t="inlineStr">
+        <is>
+          <t>233390404</t>
+        </is>
+      </c>
       <c r="E715" t="inlineStr">
         <is>
-          <t>9903.03.03</t>
+          <t>9903.88.03</t>
         </is>
       </c>
       <c r="F715" t="inlineStr">
         <is>
-          <t>S122 -EXCLUSION-EXEMPTED PRDTS</t>
+          <t>ARTICLE OF CHINA,US NTE 20(F)</t>
         </is>
       </c>
       <c r="G715" t="inlineStr">
@@ -60056,52 +60060,52 @@
       </c>
       <c r="H715" t="inlineStr">
         <is>
-          <t>9903.03.03</t>
+          <t>9903.88.03</t>
         </is>
       </c>
       <c r="I715" t="inlineStr">
         <is>
-          <t>2930.90.9231</t>
+          <t>9903.03.01,8208.20.0060</t>
         </is>
       </c>
       <c r="J715" t="inlineStr">
         <is>
-          <t>CASTLE CHEMICALS LTD</t>
+          <t>CB MANUFACTURING &amp; SALES CO INC</t>
         </is>
       </c>
       <c r="K715" t="inlineStr">
         <is>
-          <t>CASCHE01</t>
+          <t>CBMAN01</t>
         </is>
       </c>
       <c r="L715" t="inlineStr">
         <is>
-          <t>151704-07138</t>
+          <t>34-101525000</t>
         </is>
       </c>
       <c r="M715" t="inlineStr">
         <is>
+          <t>2026-06-27 00:00:00</t>
+        </is>
+      </c>
+      <c r="N715" t="inlineStr">
+        <is>
           <t>2026-06-29 00:00:00</t>
         </is>
       </c>
-      <c r="N715" t="inlineStr">
-        <is>
-          <t>2026-06-29 00:00:00</t>
-        </is>
-      </c>
       <c r="O715" t="inlineStr">
         <is>
-          <t>HUBEI JIANGHAN NEW MATERIALS CO LTD</t>
+          <t>ZHUZHOU ROCKKING ENGINEERING MACHIN</t>
         </is>
       </c>
       <c r="P715" t="inlineStr">
         <is>
-          <t>HUBEI JIANGHAN NEW MATERIALS CO LTD</t>
+          <t>ZHUZHOU ROCKKING ENGINEERING MACHIN</t>
         </is>
       </c>
       <c r="Q715" t="inlineStr">
         <is>
-          <t>2026-05-27 00:00:00</t>
+          <t>2026-06-01 00:00:00</t>
         </is>
       </c>
     </row>
@@ -60138,7 +60142,7 @@
       </c>
       <c r="G716" t="inlineStr">
         <is>
-          <t>001</t>
+          <t>002</t>
         </is>
       </c>
       <c r="H716" t="inlineStr">
@@ -60148,7 +60152,7 @@
       </c>
       <c r="I716" t="inlineStr">
         <is>
-          <t>9903.03.01,8208.20.0060</t>
+          <t>9903.03.01,8208.90.6000</t>
         </is>
       </c>
       <c r="J716" t="inlineStr">
@@ -60225,7 +60229,7 @@
       </c>
       <c r="G717" t="inlineStr">
         <is>
-          <t>002</t>
+          <t>003</t>
         </is>
       </c>
       <c r="H717" t="inlineStr">
@@ -60282,17 +60286,17 @@
     <row r="718">
       <c r="A718" t="inlineStr">
         <is>
-          <t>2615752</t>
+          <t>2615781</t>
         </is>
       </c>
       <c r="B718" t="inlineStr">
         <is>
-          <t>EF4-0232314-3</t>
+          <t>EF4-0232587-4</t>
         </is>
       </c>
       <c r="C718" t="inlineStr">
         <is>
-          <t>Vessel, Non-container</t>
+          <t>Vessel, Container</t>
         </is>
       </c>
       <c r="D718" t="inlineStr">
@@ -60302,47 +60306,47 @@
       </c>
       <c r="E718" t="inlineStr">
         <is>
-          <t>9903.88.03</t>
+          <t>9903.88.15</t>
         </is>
       </c>
       <c r="F718" t="inlineStr">
         <is>
-          <t>ARTICLE OF CHINA,US NTE 20(F)</t>
+          <t>ARTICLE OF CHINA,US NTE 20(R)</t>
         </is>
       </c>
       <c r="G718" t="inlineStr">
         <is>
-          <t>003</t>
+          <t>001</t>
         </is>
       </c>
       <c r="H718" t="inlineStr">
         <is>
-          <t>9903.88.03</t>
+          <t>9903.88.15</t>
         </is>
       </c>
       <c r="I718" t="inlineStr">
         <is>
-          <t>9903.03.01,8208.90.6000</t>
+          <t>9903.03.01,3926.90.9989</t>
         </is>
       </c>
       <c r="J718" t="inlineStr">
         <is>
-          <t>CB MANUFACTURING &amp; SALES CO INC</t>
+          <t>BORGERS OHIO INC.</t>
         </is>
       </c>
       <c r="K718" t="inlineStr">
         <is>
-          <t>CBMAN01</t>
+          <t>BORUSA02</t>
         </is>
       </c>
       <c r="L718" t="inlineStr">
         <is>
-          <t>34-101525000</t>
+          <t>30-084196200</t>
         </is>
       </c>
       <c r="M718" t="inlineStr">
         <is>
-          <t>2026-06-27 00:00:00</t>
+          <t>2026-06-28 00:00:00</t>
         </is>
       </c>
       <c r="N718" t="inlineStr">
@@ -60352,17 +60356,17 @@
       </c>
       <c r="O718" t="inlineStr">
         <is>
-          <t>ZHUZHOU ROCKKING ENGINEERING MACHIN</t>
+          <t>AUTONEUM (SHANGHAI) MANAGEMENT CO.</t>
         </is>
       </c>
       <c r="P718" t="inlineStr">
         <is>
-          <t>ZHUZHOU ROCKKING ENGINEERING MACHIN</t>
+          <t>AUTONEUM (SHANGHAI) MANAGEMENT CO. LTD.</t>
         </is>
       </c>
       <c r="Q718" t="inlineStr">
         <is>
-          <t>2026-06-01 00:00:00</t>
+          <t>2026-06-13 00:00:00</t>
         </is>
       </c>
     </row>
@@ -60399,7 +60403,7 @@
       </c>
       <c r="G719" t="inlineStr">
         <is>
-          <t>001</t>
+          <t>002</t>
         </is>
       </c>
       <c r="H719" t="inlineStr">
@@ -60486,7 +60490,7 @@
       </c>
       <c r="G720" t="inlineStr">
         <is>
-          <t>002</t>
+          <t>003</t>
         </is>
       </c>
       <c r="H720" t="inlineStr">
@@ -60496,7 +60500,7 @@
       </c>
       <c r="I720" t="inlineStr">
         <is>
-          <t>9903.03.01,3926.90.9989</t>
+          <t>9903.03.01,3926.30.5000</t>
         </is>
       </c>
       <c r="J720" t="inlineStr">
@@ -60573,7 +60577,7 @@
       </c>
       <c r="G721" t="inlineStr">
         <is>
-          <t>003</t>
+          <t>004</t>
         </is>
       </c>
       <c r="H721" t="inlineStr">
@@ -60583,7 +60587,7 @@
       </c>
       <c r="I721" t="inlineStr">
         <is>
-          <t>9903.03.01,3926.30.5000</t>
+          <t>9903.03.01,3926.90.9989</t>
         </is>
       </c>
       <c r="J721" t="inlineStr">
@@ -60660,7 +60664,7 @@
       </c>
       <c r="G722" t="inlineStr">
         <is>
-          <t>004</t>
+          <t>005</t>
         </is>
       </c>
       <c r="H722" t="inlineStr">
@@ -60747,7 +60751,7 @@
       </c>
       <c r="G723" t="inlineStr">
         <is>
-          <t>005</t>
+          <t>006</t>
         </is>
       </c>
       <c r="H723" t="inlineStr">
@@ -60757,7 +60761,7 @@
       </c>
       <c r="I723" t="inlineStr">
         <is>
-          <t>9903.03.01,3926.90.9989</t>
+          <t>9903.03.01,3926.30.5000</t>
         </is>
       </c>
       <c r="J723" t="inlineStr">
@@ -60834,7 +60838,7 @@
       </c>
       <c r="G724" t="inlineStr">
         <is>
-          <t>006</t>
+          <t>007</t>
         </is>
       </c>
       <c r="H724" t="inlineStr">
@@ -60921,7 +60925,7 @@
       </c>
       <c r="G725" t="inlineStr">
         <is>
-          <t>007</t>
+          <t>008</t>
         </is>
       </c>
       <c r="H725" t="inlineStr">
@@ -61008,7 +61012,7 @@
       </c>
       <c r="G726" t="inlineStr">
         <is>
-          <t>008</t>
+          <t>009</t>
         </is>
       </c>
       <c r="H726" t="inlineStr">
@@ -61095,7 +61099,7 @@
       </c>
       <c r="G727" t="inlineStr">
         <is>
-          <t>009</t>
+          <t>010</t>
         </is>
       </c>
       <c r="H727" t="inlineStr">
@@ -61152,12 +61156,12 @@
     <row r="728">
       <c r="A728" t="inlineStr">
         <is>
-          <t>2615781</t>
+          <t>2566482</t>
         </is>
       </c>
       <c r="B728" t="inlineStr">
         <is>
-          <t>EF4-0232587-4</t>
+          <t>EF4-0232721-9</t>
         </is>
       </c>
       <c r="C728" t="inlineStr">
@@ -61167,52 +61171,52 @@
       </c>
       <c r="D728" t="inlineStr">
         <is>
-          <t>233390404</t>
+          <t>V8N03155507</t>
         </is>
       </c>
       <c r="E728" t="inlineStr">
         <is>
-          <t>9903.88.15</t>
+          <t>9903.03.01</t>
         </is>
       </c>
       <c r="F728" t="inlineStr">
         <is>
-          <t>ARTICLE OF CHINA,US NTE 20(R)</t>
+          <t>SECTION 122 - 10% DUTY</t>
         </is>
       </c>
       <c r="G728" t="inlineStr">
         <is>
-          <t>010</t>
+          <t>001</t>
         </is>
       </c>
       <c r="H728" t="inlineStr">
         <is>
-          <t>9903.88.15</t>
+          <t>9903.03.01</t>
         </is>
       </c>
       <c r="I728" t="inlineStr">
         <is>
-          <t>9903.03.01,3926.30.5000</t>
+          <t>3214.10.0090</t>
         </is>
       </c>
       <c r="J728" t="inlineStr">
         <is>
-          <t>BORGERS OHIO INC.</t>
+          <t>MANKIEWICZ COATINGS, LLC</t>
         </is>
       </c>
       <c r="K728" t="inlineStr">
         <is>
-          <t>BORUSA02</t>
+          <t>MANCOAT</t>
         </is>
       </c>
       <c r="L728" t="inlineStr">
         <is>
-          <t>30-084196200</t>
+          <t>56-202308900</t>
         </is>
       </c>
       <c r="M728" t="inlineStr">
         <is>
-          <t>2026-06-28 00:00:00</t>
+          <t>2026-06-30 00:00:00</t>
         </is>
       </c>
       <c r="N728" t="inlineStr">
@@ -61222,17 +61226,17 @@
       </c>
       <c r="O728" t="inlineStr">
         <is>
-          <t>AUTONEUM (SHANGHAI) MANAGEMENT CO.</t>
+          <t>FINALIN GMBH</t>
         </is>
       </c>
       <c r="P728" t="inlineStr">
         <is>
-          <t>AUTONEUM (SHANGHAI) MANAGEMENT CO. LTD.</t>
+          <t>FINALIN GMBH</t>
         </is>
       </c>
       <c r="Q728" t="inlineStr">
         <is>
-          <t>2026-06-13 00:00:00</t>
+          <t>2026-06-20 00:00:00</t>
         </is>
       </c>
     </row>
@@ -61269,7 +61273,7 @@
       </c>
       <c r="G729" t="inlineStr">
         <is>
-          <t>001</t>
+          <t>002</t>
         </is>
       </c>
       <c r="H729" t="inlineStr">
@@ -61279,7 +61283,7 @@
       </c>
       <c r="I729" t="inlineStr">
         <is>
-          <t>3214.10.0090</t>
+          <t>3208.20.0000</t>
         </is>
       </c>
       <c r="J729" t="inlineStr">
@@ -61356,7 +61360,7 @@
       </c>
       <c r="G730" t="inlineStr">
         <is>
-          <t>002</t>
+          <t>003</t>
         </is>
       </c>
       <c r="H730" t="inlineStr">
@@ -61366,7 +61370,7 @@
       </c>
       <c r="I730" t="inlineStr">
         <is>
-          <t>3208.20.0000</t>
+          <t>3814.00.1000</t>
         </is>
       </c>
       <c r="J730" t="inlineStr">
@@ -61443,7 +61447,7 @@
       </c>
       <c r="G731" t="inlineStr">
         <is>
-          <t>003</t>
+          <t>004</t>
         </is>
       </c>
       <c r="H731" t="inlineStr">
@@ -61453,7 +61457,7 @@
       </c>
       <c r="I731" t="inlineStr">
         <is>
-          <t>3814.00.1000</t>
+          <t>3208.10.0000</t>
         </is>
       </c>
       <c r="J731" t="inlineStr">
@@ -61530,7 +61534,7 @@
       </c>
       <c r="G732" t="inlineStr">
         <is>
-          <t>004</t>
+          <t>005</t>
         </is>
       </c>
       <c r="H732" t="inlineStr">
@@ -61540,7 +61544,7 @@
       </c>
       <c r="I732" t="inlineStr">
         <is>
-          <t>3208.10.0000</t>
+          <t>3208.20.0000</t>
         </is>
       </c>
       <c r="J732" t="inlineStr">
@@ -61617,7 +61621,7 @@
       </c>
       <c r="G733" t="inlineStr">
         <is>
-          <t>005</t>
+          <t>006</t>
         </is>
       </c>
       <c r="H733" t="inlineStr">
@@ -61704,7 +61708,7 @@
       </c>
       <c r="G734" t="inlineStr">
         <is>
-          <t>006</t>
+          <t>007</t>
         </is>
       </c>
       <c r="H734" t="inlineStr">
@@ -61791,7 +61795,7 @@
       </c>
       <c r="G735" t="inlineStr">
         <is>
-          <t>007</t>
+          <t>008</t>
         </is>
       </c>
       <c r="H735" t="inlineStr">
@@ -61878,7 +61882,7 @@
       </c>
       <c r="G736" t="inlineStr">
         <is>
-          <t>008</t>
+          <t>009</t>
         </is>
       </c>
       <c r="H736" t="inlineStr">
@@ -61888,7 +61892,7 @@
       </c>
       <c r="I736" t="inlineStr">
         <is>
-          <t>3208.20.0000</t>
+          <t>3208.10.0000</t>
         </is>
       </c>
       <c r="J736" t="inlineStr">
@@ -61965,7 +61969,7 @@
       </c>
       <c r="G737" t="inlineStr">
         <is>
-          <t>009</t>
+          <t>010</t>
         </is>
       </c>
       <c r="H737" t="inlineStr">
@@ -61975,7 +61979,7 @@
       </c>
       <c r="I737" t="inlineStr">
         <is>
-          <t>3208.10.0000</t>
+          <t>3214.10.0090</t>
         </is>
       </c>
       <c r="J737" t="inlineStr">
@@ -62052,7 +62056,7 @@
       </c>
       <c r="G738" t="inlineStr">
         <is>
-          <t>010</t>
+          <t>011</t>
         </is>
       </c>
       <c r="H738" t="inlineStr">
@@ -62062,7 +62066,7 @@
       </c>
       <c r="I738" t="inlineStr">
         <is>
-          <t>3214.10.0090</t>
+          <t>3208.20.0000</t>
         </is>
       </c>
       <c r="J738" t="inlineStr">
@@ -62139,7 +62143,7 @@
       </c>
       <c r="G739" t="inlineStr">
         <is>
-          <t>011</t>
+          <t>012</t>
         </is>
       </c>
       <c r="H739" t="inlineStr">
@@ -62226,7 +62230,7 @@
       </c>
       <c r="G740" t="inlineStr">
         <is>
-          <t>012</t>
+          <t>013</t>
         </is>
       </c>
       <c r="H740" t="inlineStr">
@@ -62236,7 +62240,7 @@
       </c>
       <c r="I740" t="inlineStr">
         <is>
-          <t>3208.20.0000</t>
+          <t>3209.10.0000</t>
         </is>
       </c>
       <c r="J740" t="inlineStr">
@@ -62266,12 +62270,12 @@
       </c>
       <c r="O740" t="inlineStr">
         <is>
-          <t>FINALIN GMBH</t>
+          <t>NORIX LACKFABRIK GMBH</t>
         </is>
       </c>
       <c r="P740" t="inlineStr">
         <is>
-          <t>FINALIN GMBH</t>
+          <t>NORIX LACKFABRIK GMBH</t>
         </is>
       </c>
       <c r="Q740" t="inlineStr">
@@ -62313,7 +62317,7 @@
       </c>
       <c r="G741" t="inlineStr">
         <is>
-          <t>013</t>
+          <t>014</t>
         </is>
       </c>
       <c r="H741" t="inlineStr">
@@ -62323,7 +62327,7 @@
       </c>
       <c r="I741" t="inlineStr">
         <is>
-          <t>3209.10.0000</t>
+          <t>3209.90.0000</t>
         </is>
       </c>
       <c r="J741" t="inlineStr">
@@ -62400,7 +62404,7 @@
       </c>
       <c r="G742" t="inlineStr">
         <is>
-          <t>014</t>
+          <t>015</t>
         </is>
       </c>
       <c r="H742" t="inlineStr">
@@ -62487,7 +62491,7 @@
       </c>
       <c r="G743" t="inlineStr">
         <is>
-          <t>015</t>
+          <t>016</t>
         </is>
       </c>
       <c r="H743" t="inlineStr">
@@ -62574,7 +62578,7 @@
       </c>
       <c r="G744" t="inlineStr">
         <is>
-          <t>016</t>
+          <t>017</t>
         </is>
       </c>
       <c r="H744" t="inlineStr">
@@ -62661,7 +62665,7 @@
       </c>
       <c r="G745" t="inlineStr">
         <is>
-          <t>017</t>
+          <t>018</t>
         </is>
       </c>
       <c r="H745" t="inlineStr">
@@ -62748,7 +62752,7 @@
       </c>
       <c r="G746" t="inlineStr">
         <is>
-          <t>018</t>
+          <t>019</t>
         </is>
       </c>
       <c r="H746" t="inlineStr">
@@ -62835,7 +62839,7 @@
       </c>
       <c r="G747" t="inlineStr">
         <is>
-          <t>019</t>
+          <t>020</t>
         </is>
       </c>
       <c r="H747" t="inlineStr">
@@ -62845,7 +62849,7 @@
       </c>
       <c r="I747" t="inlineStr">
         <is>
-          <t>3209.90.0000</t>
+          <t>3824.99.9397</t>
         </is>
       </c>
       <c r="J747" t="inlineStr">
@@ -62875,12 +62879,12 @@
       </c>
       <c r="O747" t="inlineStr">
         <is>
-          <t>NORIX LACKFABRIK GMBH</t>
+          <t>FINALIN GMBH</t>
         </is>
       </c>
       <c r="P747" t="inlineStr">
         <is>
-          <t>NORIX LACKFABRIK GMBH</t>
+          <t>FINALIN GMBH</t>
         </is>
       </c>
       <c r="Q747" t="inlineStr">
@@ -62892,12 +62896,12 @@
     <row r="748">
       <c r="A748" t="inlineStr">
         <is>
-          <t>2566482</t>
+          <t>2566485</t>
         </is>
       </c>
       <c r="B748" t="inlineStr">
         <is>
-          <t>EF4-0232721-9</t>
+          <t>EF4-0232726-8</t>
         </is>
       </c>
       <c r="C748" t="inlineStr">
@@ -62905,11 +62909,7 @@
           <t>Vessel, Container</t>
         </is>
       </c>
-      <c r="D748" t="inlineStr">
-        <is>
-          <t>V8N03155507</t>
-        </is>
-      </c>
+      <c r="D748" t="inlineStr"/>
       <c r="E748" t="inlineStr">
         <is>
           <t>9903.03.01</t>
@@ -62922,7 +62922,7 @@
       </c>
       <c r="G748" t="inlineStr">
         <is>
-          <t>020</t>
+          <t>001</t>
         </is>
       </c>
       <c r="H748" t="inlineStr">
@@ -62932,7 +62932,7 @@
       </c>
       <c r="I748" t="inlineStr">
         <is>
-          <t>3824.99.9397</t>
+          <t>3214.10.0090</t>
         </is>
       </c>
       <c r="J748" t="inlineStr">
@@ -63005,7 +63005,7 @@
       </c>
       <c r="G749" t="inlineStr">
         <is>
-          <t>001</t>
+          <t>002</t>
         </is>
       </c>
       <c r="H749" t="inlineStr">
@@ -63088,7 +63088,7 @@
       </c>
       <c r="G750" t="inlineStr">
         <is>
-          <t>002</t>
+          <t>003</t>
         </is>
       </c>
       <c r="H750" t="inlineStr">
@@ -63171,7 +63171,7 @@
       </c>
       <c r="G751" t="inlineStr">
         <is>
-          <t>003</t>
+          <t>004</t>
         </is>
       </c>
       <c r="H751" t="inlineStr">
@@ -63254,7 +63254,7 @@
       </c>
       <c r="G752" t="inlineStr">
         <is>
-          <t>004</t>
+          <t>005</t>
         </is>
       </c>
       <c r="H752" t="inlineStr">
@@ -63311,12 +63311,12 @@
     <row r="753">
       <c r="A753" t="inlineStr">
         <is>
-          <t>2566485</t>
+          <t>2615796</t>
         </is>
       </c>
       <c r="B753" t="inlineStr">
         <is>
-          <t>EF4-0232726-8</t>
+          <t>EF4-0232739-1</t>
         </is>
       </c>
       <c r="C753" t="inlineStr">
@@ -63337,7 +63337,7 @@
       </c>
       <c r="G753" t="inlineStr">
         <is>
-          <t>005</t>
+          <t>001</t>
         </is>
       </c>
       <c r="H753" t="inlineStr">
@@ -63347,27 +63347,27 @@
       </c>
       <c r="I753" t="inlineStr">
         <is>
-          <t>3214.10.0090</t>
+          <t>2916.14.2050</t>
         </is>
       </c>
       <c r="J753" t="inlineStr">
         <is>
-          <t>MANKIEWICZ COATINGS, LLC</t>
+          <t>TRENCHLESS PRODUCTS</t>
         </is>
       </c>
       <c r="K753" t="inlineStr">
         <is>
-          <t>MANCOAT</t>
+          <t>TREPRO01</t>
         </is>
       </c>
       <c r="L753" t="inlineStr">
         <is>
-          <t>56-202308900</t>
+          <t>83-157973900</t>
         </is>
       </c>
       <c r="M753" t="inlineStr">
         <is>
-          <t>2026-06-30 00:00:00</t>
+          <t>2026-06-29 00:00:00</t>
         </is>
       </c>
       <c r="N753" t="inlineStr">
@@ -63377,45 +63377,45 @@
       </c>
       <c r="O753" t="inlineStr">
         <is>
-          <t>FINALIN GMBH</t>
+          <t>POLINVENT KFT.</t>
         </is>
       </c>
       <c r="P753" t="inlineStr">
         <is>
-          <t>FINALIN GMBH</t>
+          <t>POLINVENT KFT.</t>
         </is>
       </c>
       <c r="Q753" t="inlineStr">
         <is>
-          <t>2026-06-20 00:00:00</t>
+          <t>2026-06-14 00:00:00</t>
         </is>
       </c>
     </row>
     <row r="754">
       <c r="A754" t="inlineStr">
         <is>
-          <t>2615796</t>
+          <t>105504831</t>
         </is>
       </c>
       <c r="B754" t="inlineStr">
         <is>
-          <t>EF4-0232739-1</t>
+          <t>EF4-0232809-2</t>
         </is>
       </c>
       <c r="C754" t="inlineStr">
         <is>
-          <t>Vessel, Container</t>
+          <t>Air, Non-container</t>
         </is>
       </c>
       <c r="D754" t="inlineStr"/>
       <c r="E754" t="inlineStr">
         <is>
-          <t>9903.03.01</t>
+          <t>9817.85.01</t>
         </is>
       </c>
       <c r="F754" t="inlineStr">
         <is>
-          <t>SECTION 122 - 10% DUTY</t>
+          <t>PROTOTYPES, TESTING/EVALUATION</t>
         </is>
       </c>
       <c r="G754" t="inlineStr">
@@ -63425,52 +63425,52 @@
       </c>
       <c r="H754" t="inlineStr">
         <is>
-          <t>9903.03.01</t>
+          <t>9817.85.01</t>
         </is>
       </c>
       <c r="I754" t="inlineStr">
         <is>
-          <t>2916.14.2050</t>
+          <t>9903.03.06,9903.94.51,8703.23.0160</t>
         </is>
       </c>
       <c r="J754" t="inlineStr">
         <is>
-          <t>TRENCHLESS PRODUCTS</t>
+          <t>PORSCHE MOTORSPORT NORTH AMERICA</t>
         </is>
       </c>
       <c r="K754" t="inlineStr">
         <is>
-          <t>TREPRO01</t>
+          <t>PORMOT01</t>
         </is>
       </c>
       <c r="L754" t="inlineStr">
         <is>
-          <t>83-157973900</t>
+          <t>23-234420600</t>
         </is>
       </c>
       <c r="M754" t="inlineStr">
         <is>
+          <t>2026-06-28 00:00:00</t>
+        </is>
+      </c>
+      <c r="N754" t="inlineStr">
+        <is>
           <t>2026-06-29 00:00:00</t>
         </is>
       </c>
-      <c r="N754" t="inlineStr">
-        <is>
-          <t>2026-06-29 00:00:00</t>
-        </is>
-      </c>
       <c r="O754" t="inlineStr">
         <is>
-          <t>POLINVENT KFT.</t>
+          <t>VOLKSWAGEN SLOVAKIA A.S</t>
         </is>
       </c>
       <c r="P754" t="inlineStr">
         <is>
-          <t>POLINVENT KFT.</t>
+          <t>VOLKSWAGEN SLOVAKIA A.S</t>
         </is>
       </c>
       <c r="Q754" t="inlineStr">
         <is>
-          <t>2026-06-14 00:00:00</t>
+          <t>2026-06-28 00:00:00</t>
         </is>
       </c>
     </row>
@@ -63503,7 +63503,7 @@
       </c>
       <c r="G755" t="inlineStr">
         <is>
-          <t>001</t>
+          <t>002</t>
         </is>
       </c>
       <c r="H755" t="inlineStr">
@@ -63513,7 +63513,7 @@
       </c>
       <c r="I755" t="inlineStr">
         <is>
-          <t>9903.03.06,9903.94.51,8703.23.0160</t>
+          <t>9903.03.06,9903.94.51,8703.24.0160</t>
         </is>
       </c>
       <c r="J755" t="inlineStr">
@@ -63586,7 +63586,7 @@
       </c>
       <c r="G756" t="inlineStr">
         <is>
-          <t>002</t>
+          <t>003</t>
         </is>
       </c>
       <c r="H756" t="inlineStr">
@@ -63596,7 +63596,7 @@
       </c>
       <c r="I756" t="inlineStr">
         <is>
-          <t>9903.03.06,9903.94.51,8703.24.0160</t>
+          <t>9903.03.06,9903.94.51,8703.80.0060</t>
         </is>
       </c>
       <c r="J756" t="inlineStr">
@@ -63643,95 +63643,99 @@
     <row r="757">
       <c r="A757" t="inlineStr">
         <is>
-          <t>105504831</t>
+          <t>2565738</t>
         </is>
       </c>
       <c r="B757" t="inlineStr">
         <is>
-          <t>EF4-0232809-2</t>
+          <t>EF4-0231594-1</t>
         </is>
       </c>
       <c r="C757" t="inlineStr">
         <is>
-          <t>Air, Non-container</t>
-        </is>
-      </c>
-      <c r="D757" t="inlineStr"/>
+          <t>Vessel, Container</t>
+        </is>
+      </c>
+      <c r="D757" t="inlineStr">
+        <is>
+          <t>V8N61688878</t>
+        </is>
+      </c>
       <c r="E757" t="inlineStr">
         <is>
-          <t>9817.85.01</t>
+          <t>9903.03.03</t>
         </is>
       </c>
       <c r="F757" t="inlineStr">
         <is>
-          <t>PROTOTYPES, TESTING/EVALUATION</t>
+          <t>S122 -EXCLUSION-EXEMPTED PRDTS</t>
         </is>
       </c>
       <c r="G757" t="inlineStr">
         <is>
-          <t>003</t>
+          <t>001</t>
         </is>
       </c>
       <c r="H757" t="inlineStr">
         <is>
-          <t>9817.85.01</t>
+          <t>9903.03.03</t>
         </is>
       </c>
       <c r="I757" t="inlineStr">
         <is>
-          <t>9903.03.06,9903.94.51,8703.80.0060</t>
+          <t>1108.14.0000</t>
         </is>
       </c>
       <c r="J757" t="inlineStr">
         <is>
-          <t>PORSCHE MOTORSPORT NORTH AMERICA</t>
+          <t>ROYAL INGREDIENTS GROUP BV</t>
         </is>
       </c>
       <c r="K757" t="inlineStr">
         <is>
-          <t>PORMOT01</t>
+          <t>ROYINGRE</t>
         </is>
       </c>
       <c r="L757" t="inlineStr">
         <is>
-          <t>23-234420600</t>
+          <t>074601-00962</t>
         </is>
       </c>
       <c r="M757" t="inlineStr">
         <is>
-          <t>2026-06-28 00:00:00</t>
+          <t>2026-06-19 00:00:00</t>
         </is>
       </c>
       <c r="N757" t="inlineStr">
         <is>
-          <t>2026-06-29 00:00:00</t>
+          <t>2026-06-30 00:00:00</t>
         </is>
       </c>
       <c r="O757" t="inlineStr">
         <is>
-          <t>VOLKSWAGEN SLOVAKIA A.S</t>
+          <t>THANAWAT INTER STARCH CO., LTD.</t>
         </is>
       </c>
       <c r="P757" t="inlineStr">
         <is>
-          <t>VOLKSWAGEN SLOVAKIA A.S</t>
+          <t>THANAWAT INTER STARCH CO., LTD.</t>
         </is>
       </c>
       <c r="Q757" t="inlineStr">
         <is>
-          <t>2026-06-28 00:00:00</t>
+          <t>2026-05-05 00:00:00</t>
         </is>
       </c>
     </row>
     <row r="758">
       <c r="A758" t="inlineStr">
         <is>
-          <t>2565738</t>
+          <t>2565909</t>
         </is>
       </c>
       <c r="B758" t="inlineStr">
         <is>
-          <t>EF4-0231594-1</t>
+          <t>EF4-0231945-5</t>
         </is>
       </c>
       <c r="C758" t="inlineStr">
@@ -63746,12 +63750,12 @@
       </c>
       <c r="E758" t="inlineStr">
         <is>
-          <t>9903.03.03</t>
+          <t>9903.03.01</t>
         </is>
       </c>
       <c r="F758" t="inlineStr">
         <is>
-          <t>S122 -EXCLUSION-EXEMPTED PRDTS</t>
+          <t>SECTION 122 - 10% DUTY</t>
         </is>
       </c>
       <c r="G758" t="inlineStr">
@@ -63761,12 +63765,12 @@
       </c>
       <c r="H758" t="inlineStr">
         <is>
-          <t>9903.03.03</t>
+          <t>9903.03.01</t>
         </is>
       </c>
       <c r="I758" t="inlineStr">
         <is>
-          <t>1108.14.0000</t>
+          <t>3505.10.0092</t>
         </is>
       </c>
       <c r="J758" t="inlineStr">
@@ -63786,7 +63790,7 @@
       </c>
       <c r="M758" t="inlineStr">
         <is>
-          <t>2026-06-19 00:00:00</t>
+          <t>2026-06-30 00:00:00</t>
         </is>
       </c>
       <c r="N758" t="inlineStr">
@@ -63796,29 +63800,29 @@
       </c>
       <c r="O758" t="inlineStr">
         <is>
-          <t>THANAWAT INTER STARCH CO., LTD.</t>
+          <t>SANGUAN WONGSE STARCH CO., LTD.</t>
         </is>
       </c>
       <c r="P758" t="inlineStr">
         <is>
-          <t>THANAWAT INTER STARCH CO., LTD.</t>
+          <t>SANGUAN WONGSE STARCH CO., LTD.</t>
         </is>
       </c>
       <c r="Q758" t="inlineStr">
         <is>
-          <t>2026-05-05 00:00:00</t>
+          <t>2026-05-15 00:00:00</t>
         </is>
       </c>
     </row>
     <row r="759">
       <c r="A759" t="inlineStr">
         <is>
-          <t>2565909</t>
+          <t>2566018</t>
         </is>
       </c>
       <c r="B759" t="inlineStr">
         <is>
-          <t>EF4-0231945-5</t>
+          <t>EF4-0232021-4</t>
         </is>
       </c>
       <c r="C759" t="inlineStr">
@@ -63826,19 +63830,15 @@
           <t>Vessel, Container</t>
         </is>
       </c>
-      <c r="D759" t="inlineStr">
-        <is>
-          <t>V8N61688878</t>
-        </is>
-      </c>
+      <c r="D759" t="inlineStr"/>
       <c r="E759" t="inlineStr">
         <is>
-          <t>9903.03.01</t>
+          <t>9903.03.03</t>
         </is>
       </c>
       <c r="F759" t="inlineStr">
         <is>
-          <t>SECTION 122 - 10% DUTY</t>
+          <t>S122 -EXCLUSION-EXEMPTED PRDTS</t>
         </is>
       </c>
       <c r="G759" t="inlineStr">
@@ -63848,12 +63848,12 @@
       </c>
       <c r="H759" t="inlineStr">
         <is>
-          <t>9903.03.01</t>
+          <t>9903.03.03</t>
         </is>
       </c>
       <c r="I759" t="inlineStr">
         <is>
-          <t>3505.10.0092</t>
+          <t>1108.14.0000</t>
         </is>
       </c>
       <c r="J759" t="inlineStr">
@@ -63893,19 +63893,19 @@
       </c>
       <c r="Q759" t="inlineStr">
         <is>
-          <t>2026-05-15 00:00:00</t>
+          <t>2026-05-19 00:00:00</t>
         </is>
       </c>
     </row>
     <row r="760">
       <c r="A760" t="inlineStr">
         <is>
-          <t>2566018</t>
+          <t>2566167</t>
         </is>
       </c>
       <c r="B760" t="inlineStr">
         <is>
-          <t>EF4-0232021-4</t>
+          <t>EF4-0232220-2</t>
         </is>
       </c>
       <c r="C760" t="inlineStr">
@@ -63916,12 +63916,12 @@
       <c r="D760" t="inlineStr"/>
       <c r="E760" t="inlineStr">
         <is>
-          <t>9903.03.03</t>
+          <t>9903.03.06</t>
         </is>
       </c>
       <c r="F760" t="inlineStr">
         <is>
-          <t>S122 -EXCLUSION-EXEMPTED PRDTS</t>
+          <t>S122 EXCL,IRN/STL/ALUM,DERIV</t>
         </is>
       </c>
       <c r="G760" t="inlineStr">
@@ -63931,64 +63931,64 @@
       </c>
       <c r="H760" t="inlineStr">
         <is>
-          <t>9903.03.03</t>
+          <t>9903.03.06</t>
         </is>
       </c>
       <c r="I760" t="inlineStr">
         <is>
-          <t>1108.14.0000</t>
+          <t>9903.82.22,8427.20.8020</t>
         </is>
       </c>
       <c r="J760" t="inlineStr">
         <is>
-          <t>ROYAL INGREDIENTS GROUP BV</t>
+          <t>MALLAGHAN (GA) INC.</t>
         </is>
       </c>
       <c r="K760" t="inlineStr">
         <is>
-          <t>ROYINGRE</t>
+          <t>MALGA01</t>
         </is>
       </c>
       <c r="L760" t="inlineStr">
         <is>
-          <t>074601-00962</t>
+          <t>36-488102800</t>
         </is>
       </c>
       <c r="M760" t="inlineStr">
         <is>
+          <t>2026-06-29 00:00:00</t>
+        </is>
+      </c>
+      <c r="N760" t="inlineStr">
+        <is>
           <t>2026-06-30 00:00:00</t>
         </is>
       </c>
-      <c r="N760" t="inlineStr">
-        <is>
-          <t>2026-06-30 00:00:00</t>
-        </is>
-      </c>
       <c r="O760" t="inlineStr">
         <is>
-          <t>SANGUAN WONGSE STARCH CO., LTD.</t>
+          <t>MALLAGHAN ENGINEERING  LTD</t>
         </is>
       </c>
       <c r="P760" t="inlineStr">
         <is>
-          <t>SANGUAN WONGSE STARCH CO., LTD.</t>
+          <t>MALLAGHAN ENGINEERING  LTD</t>
         </is>
       </c>
       <c r="Q760" t="inlineStr">
         <is>
-          <t>2026-05-19 00:00:00</t>
+          <t>2026-05-29 00:00:00</t>
         </is>
       </c>
     </row>
     <row r="761">
       <c r="A761" t="inlineStr">
         <is>
-          <t>2566167</t>
+          <t>2566128</t>
         </is>
       </c>
       <c r="B761" t="inlineStr">
         <is>
-          <t>EF4-0232220-2</t>
+          <t>EF4-0232453-9</t>
         </is>
       </c>
       <c r="C761" t="inlineStr">
@@ -63996,17 +63996,17 @@
           <t>Vessel, Container</t>
         </is>
       </c>
-      <c r="D761" t="inlineStr"/>
+      <c r="D761" t="inlineStr">
+        <is>
+          <t>V1626463577</t>
+        </is>
+      </c>
       <c r="E761" t="inlineStr">
         <is>
-          <t>9903.03.06</t>
-        </is>
-      </c>
-      <c r="F761" t="inlineStr">
-        <is>
-          <t>S122 EXCL,IRN/STL/ALUM,DERIV</t>
-        </is>
-      </c>
+          <t>9903.03.01</t>
+        </is>
+      </c>
+      <c r="F761" t="inlineStr"/>
       <c r="G761" t="inlineStr">
         <is>
           <t>001</t>
@@ -64014,32 +64014,32 @@
       </c>
       <c r="H761" t="inlineStr">
         <is>
-          <t>9903.03.06</t>
+          <t>9903.03.01</t>
         </is>
       </c>
       <c r="I761" t="inlineStr">
         <is>
-          <t>9903.82.22,8427.20.8020</t>
+          <t>1108.12.0010</t>
         </is>
       </c>
       <c r="J761" t="inlineStr">
         <is>
-          <t>MALLAGHAN (GA) INC.</t>
+          <t>ROYAL INGREDIENTS GROUP BV</t>
         </is>
       </c>
       <c r="K761" t="inlineStr">
         <is>
-          <t>MALGA01</t>
+          <t>ROYINGRE</t>
         </is>
       </c>
       <c r="L761" t="inlineStr">
         <is>
-          <t>36-488102800</t>
+          <t>074601-00962</t>
         </is>
       </c>
       <c r="M761" t="inlineStr">
         <is>
-          <t>2026-06-29 00:00:00</t>
+          <t>2026-06-22 00:00:00</t>
         </is>
       </c>
       <c r="N761" t="inlineStr">
@@ -64049,29 +64049,29 @@
       </c>
       <c r="O761" t="inlineStr">
         <is>
-          <t>MALLAGHAN ENGINEERING  LTD</t>
+          <t>TAT NISASTA INS SAN TIC AS</t>
         </is>
       </c>
       <c r="P761" t="inlineStr">
         <is>
-          <t>MALLAGHAN ENGINEERING  LTD</t>
+          <t>TAT NISASTA INS SAN TIC AS</t>
         </is>
       </c>
       <c r="Q761" t="inlineStr">
         <is>
-          <t>2026-05-29 00:00:00</t>
+          <t>2026-05-30 00:00:00</t>
         </is>
       </c>
     </row>
     <row r="762">
       <c r="A762" t="inlineStr">
         <is>
-          <t>2566128</t>
+          <t>2566251</t>
         </is>
       </c>
       <c r="B762" t="inlineStr">
         <is>
-          <t>EF4-0232453-9</t>
+          <t>EF4-0232519-7</t>
         </is>
       </c>
       <c r="C762" t="inlineStr">
@@ -64089,7 +64089,11 @@
           <t>9903.03.01</t>
         </is>
       </c>
-      <c r="F762" t="inlineStr"/>
+      <c r="F762" t="inlineStr">
+        <is>
+          <t>SECTION 122 - 10% DUTY</t>
+        </is>
+      </c>
       <c r="G762" t="inlineStr">
         <is>
           <t>001</t>
@@ -64102,27 +64106,27 @@
       </c>
       <c r="I762" t="inlineStr">
         <is>
-          <t>1108.12.0010</t>
+          <t>4811.59.4040</t>
         </is>
       </c>
       <c r="J762" t="inlineStr">
         <is>
-          <t>ROYAL INGREDIENTS GROUP BV</t>
+          <t>BAUSCHLINNEMANN NORTH AMERICA</t>
         </is>
       </c>
       <c r="K762" t="inlineStr">
         <is>
-          <t>ROYINGRE</t>
+          <t>BAULIN</t>
         </is>
       </c>
       <c r="L762" t="inlineStr">
         <is>
-          <t>074601-00962</t>
+          <t>56-193913400</t>
         </is>
       </c>
       <c r="M762" t="inlineStr">
         <is>
-          <t>2026-06-22 00:00:00</t>
+          <t>2026-07-01 00:00:00</t>
         </is>
       </c>
       <c r="N762" t="inlineStr">
@@ -64132,29 +64136,29 @@
       </c>
       <c r="O762" t="inlineStr">
         <is>
-          <t>TAT NISASTA INS SAN TIC AS</t>
+          <t>SURTECO GMBH</t>
         </is>
       </c>
       <c r="P762" t="inlineStr">
         <is>
-          <t>TAT NISASTA INS SAN TIC AS</t>
+          <t>SURTECO GMBH</t>
         </is>
       </c>
       <c r="Q762" t="inlineStr">
         <is>
-          <t>2026-05-30 00:00:00</t>
+          <t>2026-06-11 00:00:00</t>
         </is>
       </c>
     </row>
     <row r="763">
       <c r="A763" t="inlineStr">
         <is>
-          <t>2566251</t>
+          <t>2566084</t>
         </is>
       </c>
       <c r="B763" t="inlineStr">
         <is>
-          <t>EF4-0232519-7</t>
+          <t>EF4-0232543-7</t>
         </is>
       </c>
       <c r="C763" t="inlineStr">
@@ -64164,17 +64168,17 @@
       </c>
       <c r="D763" t="inlineStr">
         <is>
-          <t>V1626463577</t>
+          <t>V0710340071</t>
         </is>
       </c>
       <c r="E763" t="inlineStr">
         <is>
-          <t>9903.03.01</t>
+          <t>9903.03.06</t>
         </is>
       </c>
       <c r="F763" t="inlineStr">
         <is>
-          <t>SECTION 122 - 10% DUTY</t>
+          <t>S122 EXCL,IRN/STL/ALUM,DERIV</t>
         </is>
       </c>
       <c r="G763" t="inlineStr">
@@ -64184,27 +64188,27 @@
       </c>
       <c r="H763" t="inlineStr">
         <is>
-          <t>9903.03.01</t>
+          <t>9903.03.06</t>
         </is>
       </c>
       <c r="I763" t="inlineStr">
         <is>
-          <t>4811.59.4040</t>
+          <t>9903.82.02,7223.00.1031</t>
         </is>
       </c>
       <c r="J763" t="inlineStr">
         <is>
-          <t>BAUSCHLINNEMANN NORTH AMERICA</t>
+          <t>VENUS WIRE INDUSTRIES PRIVATE LTD</t>
         </is>
       </c>
       <c r="K763" t="inlineStr">
         <is>
-          <t>BAULIN</t>
+          <t>VENWIR</t>
         </is>
       </c>
       <c r="L763" t="inlineStr">
         <is>
-          <t>56-193913400</t>
+          <t>993901-03595</t>
         </is>
       </c>
       <c r="M763" t="inlineStr">
@@ -64219,29 +64223,29 @@
       </c>
       <c r="O763" t="inlineStr">
         <is>
-          <t>SURTECO GMBH</t>
+          <t>PRECISION METALS</t>
         </is>
       </c>
       <c r="P763" t="inlineStr">
         <is>
-          <t>SURTECO GMBH</t>
+          <t>PRECISION METALS</t>
         </is>
       </c>
       <c r="Q763" t="inlineStr">
         <is>
-          <t>2026-06-11 00:00:00</t>
+          <t>2026-05-23 00:00:00</t>
         </is>
       </c>
     </row>
     <row r="764">
       <c r="A764" t="inlineStr">
         <is>
-          <t>2566084</t>
+          <t>2566120</t>
         </is>
       </c>
       <c r="B764" t="inlineStr">
         <is>
-          <t>EF4-0232543-7</t>
+          <t>EF4-0232546-0</t>
         </is>
       </c>
       <c r="C764" t="inlineStr">
@@ -64316,19 +64320,19 @@
       </c>
       <c r="Q764" t="inlineStr">
         <is>
-          <t>2026-05-23 00:00:00</t>
+          <t>2026-05-30 00:00:00</t>
         </is>
       </c>
     </row>
     <row r="765">
       <c r="A765" t="inlineStr">
         <is>
-          <t>2566120</t>
+          <t>2566275</t>
         </is>
       </c>
       <c r="B765" t="inlineStr">
         <is>
-          <t>EF4-0232546-0</t>
+          <t>EF4-0232553-6</t>
         </is>
       </c>
       <c r="C765" t="inlineStr">
@@ -64343,12 +64347,12 @@
       </c>
       <c r="E765" t="inlineStr">
         <is>
-          <t>9903.03.06</t>
+          <t>9903.03.01</t>
         </is>
       </c>
       <c r="F765" t="inlineStr">
         <is>
-          <t>S122 EXCL,IRN/STL/ALUM,DERIV</t>
+          <t>SECTION 122 - 10% DUTY</t>
         </is>
       </c>
       <c r="G765" t="inlineStr">
@@ -64358,32 +64362,32 @@
       </c>
       <c r="H765" t="inlineStr">
         <is>
-          <t>9903.03.06</t>
+          <t>9903.03.01</t>
         </is>
       </c>
       <c r="I765" t="inlineStr">
         <is>
-          <t>9903.82.02,7223.00.1031</t>
+          <t>8515.21.0000</t>
         </is>
       </c>
       <c r="J765" t="inlineStr">
         <is>
-          <t>VENUS WIRE INDUSTRIES PRIVATE LTD</t>
+          <t>KUKA SYSTEMS GMBH</t>
         </is>
       </c>
       <c r="K765" t="inlineStr">
         <is>
-          <t>VENWIR</t>
+          <t>KUKSYS04</t>
         </is>
       </c>
       <c r="L765" t="inlineStr">
         <is>
-          <t>993901-03595</t>
+          <t>051704-00238</t>
         </is>
       </c>
       <c r="M765" t="inlineStr">
         <is>
-          <t>2026-07-01 00:00:00</t>
+          <t>2026-06-30 00:00:00</t>
         </is>
       </c>
       <c r="N765" t="inlineStr">
@@ -64393,29 +64397,29 @@
       </c>
       <c r="O765" t="inlineStr">
         <is>
-          <t>PRECISION METALS</t>
+          <t>KUKA DEUTSCHLAND</t>
         </is>
       </c>
       <c r="P765" t="inlineStr">
         <is>
-          <t>PRECISION METALS</t>
+          <t>KUKA DEUTSCHLAND</t>
         </is>
       </c>
       <c r="Q765" t="inlineStr">
         <is>
-          <t>2026-05-30 00:00:00</t>
+          <t>2026-06-11 00:00:00</t>
         </is>
       </c>
     </row>
     <row r="766">
       <c r="A766" t="inlineStr">
         <is>
-          <t>2566275</t>
+          <t>2566409</t>
         </is>
       </c>
       <c r="B766" t="inlineStr">
         <is>
-          <t>EF4-0232553-6</t>
+          <t>EF4-0232675-7</t>
         </is>
       </c>
       <c r="C766" t="inlineStr">
@@ -64423,11 +64427,7 @@
           <t>Vessel, Container</t>
         </is>
       </c>
-      <c r="D766" t="inlineStr">
-        <is>
-          <t>V0710340071</t>
-        </is>
-      </c>
+      <c r="D766" t="inlineStr"/>
       <c r="E766" t="inlineStr">
         <is>
           <t>9903.03.01</t>
@@ -64450,22 +64450,22 @@
       </c>
       <c r="I766" t="inlineStr">
         <is>
-          <t>8515.21.0000</t>
+          <t>1109.00.9020</t>
         </is>
       </c>
       <c r="J766" t="inlineStr">
         <is>
-          <t>KUKA SYSTEMS GMBH</t>
+          <t>ROYAL INGREDIENTS GROUP BV</t>
         </is>
       </c>
       <c r="K766" t="inlineStr">
         <is>
-          <t>KUKSYS04</t>
+          <t>ROYINGRE</t>
         </is>
       </c>
       <c r="L766" t="inlineStr">
         <is>
-          <t>051704-00238</t>
+          <t>074601-00962</t>
         </is>
       </c>
       <c r="M766" t="inlineStr">
@@ -64480,29 +64480,29 @@
       </c>
       <c r="O766" t="inlineStr">
         <is>
-          <t>KUKA DEUTSCHLAND</t>
+          <t>JACKERING MUHLEN UND NAHRMITTELWERK</t>
         </is>
       </c>
       <c r="P766" t="inlineStr">
         <is>
-          <t>KUKA DEUTSCHLAND</t>
+          <t>JACKERING MUHLEN UND NAHRMITTELWERKE GMBH</t>
         </is>
       </c>
       <c r="Q766" t="inlineStr">
         <is>
-          <t>2026-06-11 00:00:00</t>
+          <t>2026-06-17 00:00:00</t>
         </is>
       </c>
     </row>
     <row r="767">
       <c r="A767" t="inlineStr">
         <is>
-          <t>2566409</t>
+          <t>2566418</t>
         </is>
       </c>
       <c r="B767" t="inlineStr">
         <is>
-          <t>EF4-0232675-7</t>
+          <t>EF4-0232678-1</t>
         </is>
       </c>
       <c r="C767" t="inlineStr">
@@ -64580,12 +64580,12 @@
     <row r="768">
       <c r="A768" t="inlineStr">
         <is>
-          <t>2566418</t>
+          <t>2615790</t>
         </is>
       </c>
       <c r="B768" t="inlineStr">
         <is>
-          <t>EF4-0232678-1</t>
+          <t>EF4-0232737-5</t>
         </is>
       </c>
       <c r="C768" t="inlineStr">
@@ -64616,22 +64616,22 @@
       </c>
       <c r="I768" t="inlineStr">
         <is>
-          <t>1109.00.9020</t>
+          <t>8501.53.4080</t>
         </is>
       </c>
       <c r="J768" t="inlineStr">
         <is>
-          <t>ROYAL INGREDIENTS GROUP BV</t>
+          <t>FI-TECH INC</t>
         </is>
       </c>
       <c r="K768" t="inlineStr">
         <is>
-          <t>ROYINGRE</t>
+          <t>FITINC</t>
         </is>
       </c>
       <c r="L768" t="inlineStr">
         <is>
-          <t>074601-00962</t>
+          <t>54-091465000</t>
         </is>
       </c>
       <c r="M768" t="inlineStr">
@@ -64646,12 +64646,12 @@
       </c>
       <c r="O768" t="inlineStr">
         <is>
-          <t>JACKERING MUHLEN UND NAHRMITTELWERK</t>
+          <t>REIFENHAUSER REICOFIL GMBH &amp; CO. KG</t>
         </is>
       </c>
       <c r="P768" t="inlineStr">
         <is>
-          <t>JACKERING MUHLEN UND NAHRMITTELWERKE GMBH</t>
+          <t>REIFENHAUSER REICOFIL GMBH &amp; CO. KG</t>
         </is>
       </c>
       <c r="Q768" t="inlineStr">
@@ -64689,7 +64689,7 @@
       </c>
       <c r="G769" t="inlineStr">
         <is>
-          <t>001</t>
+          <t>002</t>
         </is>
       </c>
       <c r="H769" t="inlineStr">
@@ -64699,7 +64699,7 @@
       </c>
       <c r="I769" t="inlineStr">
         <is>
-          <t>8501.53.4080</t>
+          <t>8420.91.9000</t>
         </is>
       </c>
       <c r="J769" t="inlineStr">
@@ -64746,12 +64746,12 @@
     <row r="770">
       <c r="A770" t="inlineStr">
         <is>
-          <t>2615790</t>
+          <t>2565942</t>
         </is>
       </c>
       <c r="B770" t="inlineStr">
         <is>
-          <t>EF4-0232737-5</t>
+          <t>EF4-0231987-7</t>
         </is>
       </c>
       <c r="C770" t="inlineStr">
@@ -64762,67 +64762,1403 @@
       <c r="D770" t="inlineStr"/>
       <c r="E770" t="inlineStr">
         <is>
-          <t>9903.03.01</t>
+          <t>9903.88.15</t>
         </is>
       </c>
       <c r="F770" t="inlineStr">
         <is>
+          <t>ARTICLE OF CHINA,US NTE 20(R)</t>
+        </is>
+      </c>
+      <c r="G770" t="inlineStr">
+        <is>
+          <t>001</t>
+        </is>
+      </c>
+      <c r="H770" t="inlineStr">
+        <is>
+          <t>9903.88.15</t>
+        </is>
+      </c>
+      <c r="I770" t="inlineStr">
+        <is>
+          <t>9903.03.06,9903.82.09,8302.42.3015</t>
+        </is>
+      </c>
+      <c r="J770" t="inlineStr">
+        <is>
+          <t>GRASS AMERICA INC</t>
+        </is>
+      </c>
+      <c r="K770" t="inlineStr">
+        <is>
+          <t>GRAAME</t>
+        </is>
+      </c>
+      <c r="L770" t="inlineStr">
+        <is>
+          <t>51-066023000</t>
+        </is>
+      </c>
+      <c r="M770" t="inlineStr">
+        <is>
+          <t>2026-06-30 00:00:00</t>
+        </is>
+      </c>
+      <c r="N770" t="inlineStr">
+        <is>
+          <t>2026-07-01 00:00:00</t>
+        </is>
+      </c>
+      <c r="O770" t="inlineStr">
+        <is>
+          <t>SACA PRECISION LTD</t>
+        </is>
+      </c>
+      <c r="P770" t="inlineStr">
+        <is>
+          <t>SACA PRECISION LTD</t>
+        </is>
+      </c>
+      <c r="Q770" t="inlineStr">
+        <is>
+          <t>2026-05-19 00:00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="771">
+      <c r="A771" t="inlineStr">
+        <is>
+          <t>2565942</t>
+        </is>
+      </c>
+      <c r="B771" t="inlineStr">
+        <is>
+          <t>EF4-0231987-7</t>
+        </is>
+      </c>
+      <c r="C771" t="inlineStr">
+        <is>
+          <t>Vessel, Container</t>
+        </is>
+      </c>
+      <c r="D771" t="inlineStr"/>
+      <c r="E771" t="inlineStr">
+        <is>
+          <t>9903.88.15</t>
+        </is>
+      </c>
+      <c r="F771" t="inlineStr">
+        <is>
+          <t>ARTICLE OF CHINA,US NTE 20(R)</t>
+        </is>
+      </c>
+      <c r="G771" t="inlineStr">
+        <is>
+          <t>002</t>
+        </is>
+      </c>
+      <c r="H771" t="inlineStr">
+        <is>
+          <t>9903.88.15</t>
+        </is>
+      </c>
+      <c r="I771" t="inlineStr">
+        <is>
+          <t>9903.03.01,3926.30.5000</t>
+        </is>
+      </c>
+      <c r="J771" t="inlineStr">
+        <is>
+          <t>GRASS AMERICA INC</t>
+        </is>
+      </c>
+      <c r="K771" t="inlineStr">
+        <is>
+          <t>GRAAME</t>
+        </is>
+      </c>
+      <c r="L771" t="inlineStr">
+        <is>
+          <t>51-066023000</t>
+        </is>
+      </c>
+      <c r="M771" t="inlineStr">
+        <is>
+          <t>2026-06-30 00:00:00</t>
+        </is>
+      </c>
+      <c r="N771" t="inlineStr">
+        <is>
+          <t>2026-07-01 00:00:00</t>
+        </is>
+      </c>
+      <c r="O771" t="inlineStr">
+        <is>
+          <t>SACA PRECISION LTD</t>
+        </is>
+      </c>
+      <c r="P771" t="inlineStr">
+        <is>
+          <t>SACA PRECISION LTD</t>
+        </is>
+      </c>
+      <c r="Q771" t="inlineStr">
+        <is>
+          <t>2026-05-19 00:00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="772">
+      <c r="A772" t="inlineStr">
+        <is>
+          <t>2566073</t>
+        </is>
+      </c>
+      <c r="B772" t="inlineStr">
+        <is>
+          <t>EF4-0232230-1</t>
+        </is>
+      </c>
+      <c r="C772" t="inlineStr">
+        <is>
+          <t>Vessel, Container</t>
+        </is>
+      </c>
+      <c r="D772" t="inlineStr"/>
+      <c r="E772" t="inlineStr">
+        <is>
+          <t>9903.03.06</t>
+        </is>
+      </c>
+      <c r="F772" t="inlineStr">
+        <is>
+          <t>S122 EXCL,IRN/STL/ALUM,DERIV</t>
+        </is>
+      </c>
+      <c r="G772" t="inlineStr">
+        <is>
+          <t>001</t>
+        </is>
+      </c>
+      <c r="H772" t="inlineStr">
+        <is>
+          <t>9903.03.06</t>
+        </is>
+      </c>
+      <c r="I772" t="inlineStr">
+        <is>
+          <t>9903.74.11,9903.94.53,8708.29.5160</t>
+        </is>
+      </c>
+      <c r="J772" t="inlineStr">
+        <is>
+          <t>HAGO AUTOMOTIVE CORP</t>
+        </is>
+      </c>
+      <c r="K772" t="inlineStr">
+        <is>
+          <t>HAGAUT02</t>
+        </is>
+      </c>
+      <c r="L772" t="inlineStr">
+        <is>
+          <t>47-447117700</t>
+        </is>
+      </c>
+      <c r="M772" t="inlineStr">
+        <is>
+          <t>2026-06-20 00:00:00</t>
+        </is>
+      </c>
+      <c r="N772" t="inlineStr">
+        <is>
+          <t>2026-07-01 00:00:00</t>
+        </is>
+      </c>
+      <c r="O772" t="inlineStr">
+        <is>
+          <t>WALOR VOEHRENBACH GMBH</t>
+        </is>
+      </c>
+      <c r="P772" t="inlineStr">
+        <is>
+          <t>WALOR VOEHRENBACH GMBH</t>
+        </is>
+      </c>
+      <c r="Q772" t="inlineStr">
+        <is>
+          <t>2026-05-30 00:00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="773">
+      <c r="A773" t="inlineStr">
+        <is>
+          <t>2566073</t>
+        </is>
+      </c>
+      <c r="B773" t="inlineStr">
+        <is>
+          <t>EF4-0232230-1</t>
+        </is>
+      </c>
+      <c r="C773" t="inlineStr">
+        <is>
+          <t>Vessel, Container</t>
+        </is>
+      </c>
+      <c r="D773" t="inlineStr"/>
+      <c r="E773" t="inlineStr">
+        <is>
+          <t>9903.03.06</t>
+        </is>
+      </c>
+      <c r="F773" t="inlineStr">
+        <is>
+          <t>S122 EXCL,IRN/STL/ALUM,DERIV</t>
+        </is>
+      </c>
+      <c r="G773" t="inlineStr">
+        <is>
+          <t>002</t>
+        </is>
+      </c>
+      <c r="H773" t="inlineStr">
+        <is>
+          <t>9903.03.06</t>
+        </is>
+      </c>
+      <c r="I773" t="inlineStr">
+        <is>
+          <t>9903.74.11,9903.94.53,8708.29.5160</t>
+        </is>
+      </c>
+      <c r="J773" t="inlineStr">
+        <is>
+          <t>HAGO AUTOMOTIVE CORP</t>
+        </is>
+      </c>
+      <c r="K773" t="inlineStr">
+        <is>
+          <t>HAGAUT02</t>
+        </is>
+      </c>
+      <c r="L773" t="inlineStr">
+        <is>
+          <t>47-447117700</t>
+        </is>
+      </c>
+      <c r="M773" t="inlineStr">
+        <is>
+          <t>2026-06-20 00:00:00</t>
+        </is>
+      </c>
+      <c r="N773" t="inlineStr">
+        <is>
+          <t>2026-07-01 00:00:00</t>
+        </is>
+      </c>
+      <c r="O773" t="inlineStr">
+        <is>
+          <t>WALOR VOEHRENBACH GMBH</t>
+        </is>
+      </c>
+      <c r="P773" t="inlineStr">
+        <is>
+          <t>WALOR VOEHRENBACH GMBH</t>
+        </is>
+      </c>
+      <c r="Q773" t="inlineStr">
+        <is>
+          <t>2026-05-30 00:00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="774">
+      <c r="A774" t="inlineStr">
+        <is>
+          <t>2566073</t>
+        </is>
+      </c>
+      <c r="B774" t="inlineStr">
+        <is>
+          <t>EF4-0232230-1</t>
+        </is>
+      </c>
+      <c r="C774" t="inlineStr">
+        <is>
+          <t>Vessel, Container</t>
+        </is>
+      </c>
+      <c r="D774" t="inlineStr"/>
+      <c r="E774" t="inlineStr">
+        <is>
+          <t>9903.03.06</t>
+        </is>
+      </c>
+      <c r="F774" t="inlineStr">
+        <is>
+          <t>S122 EXCL,IRN/STL/ALUM,DERIV</t>
+        </is>
+      </c>
+      <c r="G774" t="inlineStr">
+        <is>
+          <t>003</t>
+        </is>
+      </c>
+      <c r="H774" t="inlineStr">
+        <is>
+          <t>9903.03.06</t>
+        </is>
+      </c>
+      <c r="I774" t="inlineStr">
+        <is>
+          <t>9903.74.11,9903.94.53,8708.29.5160</t>
+        </is>
+      </c>
+      <c r="J774" t="inlineStr">
+        <is>
+          <t>HAGO AUTOMOTIVE CORP</t>
+        </is>
+      </c>
+      <c r="K774" t="inlineStr">
+        <is>
+          <t>HAGAUT02</t>
+        </is>
+      </c>
+      <c r="L774" t="inlineStr">
+        <is>
+          <t>47-447117700</t>
+        </is>
+      </c>
+      <c r="M774" t="inlineStr">
+        <is>
+          <t>2026-06-20 00:00:00</t>
+        </is>
+      </c>
+      <c r="N774" t="inlineStr">
+        <is>
+          <t>2026-07-01 00:00:00</t>
+        </is>
+      </c>
+      <c r="O774" t="inlineStr">
+        <is>
+          <t>WALOR VOEHRENBACH GMBH</t>
+        </is>
+      </c>
+      <c r="P774" t="inlineStr">
+        <is>
+          <t>WALOR VOEHRENBACH GMBH</t>
+        </is>
+      </c>
+      <c r="Q774" t="inlineStr">
+        <is>
+          <t>2026-05-30 00:00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="775">
+      <c r="A775" t="inlineStr">
+        <is>
+          <t>2566073</t>
+        </is>
+      </c>
+      <c r="B775" t="inlineStr">
+        <is>
+          <t>EF4-0232230-1</t>
+        </is>
+      </c>
+      <c r="C775" t="inlineStr">
+        <is>
+          <t>Vessel, Container</t>
+        </is>
+      </c>
+      <c r="D775" t="inlineStr"/>
+      <c r="E775" t="inlineStr">
+        <is>
+          <t>9903.03.06</t>
+        </is>
+      </c>
+      <c r="F775" t="inlineStr">
+        <is>
+          <t>S122 EXCL,IRN/STL/ALUM,DERIV</t>
+        </is>
+      </c>
+      <c r="G775" t="inlineStr">
+        <is>
+          <t>004</t>
+        </is>
+      </c>
+      <c r="H775" t="inlineStr">
+        <is>
+          <t>9903.03.06</t>
+        </is>
+      </c>
+      <c r="I775" t="inlineStr">
+        <is>
+          <t>9903.74.11,9903.94.53,8708.29.5160</t>
+        </is>
+      </c>
+      <c r="J775" t="inlineStr">
+        <is>
+          <t>HAGO AUTOMOTIVE CORP</t>
+        </is>
+      </c>
+      <c r="K775" t="inlineStr">
+        <is>
+          <t>HAGAUT02</t>
+        </is>
+      </c>
+      <c r="L775" t="inlineStr">
+        <is>
+          <t>47-447117700</t>
+        </is>
+      </c>
+      <c r="M775" t="inlineStr">
+        <is>
+          <t>2026-06-20 00:00:00</t>
+        </is>
+      </c>
+      <c r="N775" t="inlineStr">
+        <is>
+          <t>2026-07-01 00:00:00</t>
+        </is>
+      </c>
+      <c r="O775" t="inlineStr">
+        <is>
+          <t>WALOR VOEHRENBACH GMBH</t>
+        </is>
+      </c>
+      <c r="P775" t="inlineStr">
+        <is>
+          <t>WALOR VOEHRENBACH GMBH</t>
+        </is>
+      </c>
+      <c r="Q775" t="inlineStr">
+        <is>
+          <t>2026-05-30 00:00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="776">
+      <c r="A776" t="inlineStr">
+        <is>
+          <t>2566073</t>
+        </is>
+      </c>
+      <c r="B776" t="inlineStr">
+        <is>
+          <t>EF4-0232230-1</t>
+        </is>
+      </c>
+      <c r="C776" t="inlineStr">
+        <is>
+          <t>Vessel, Container</t>
+        </is>
+      </c>
+      <c r="D776" t="inlineStr"/>
+      <c r="E776" t="inlineStr">
+        <is>
+          <t>9903.03.06</t>
+        </is>
+      </c>
+      <c r="F776" t="inlineStr">
+        <is>
+          <t>S122 EXCL,IRN/STL/ALUM,DERIV</t>
+        </is>
+      </c>
+      <c r="G776" t="inlineStr">
+        <is>
+          <t>005</t>
+        </is>
+      </c>
+      <c r="H776" t="inlineStr">
+        <is>
+          <t>9903.03.06</t>
+        </is>
+      </c>
+      <c r="I776" t="inlineStr">
+        <is>
+          <t>9903.74.11,9903.94.53,8708.29.5160</t>
+        </is>
+      </c>
+      <c r="J776" t="inlineStr">
+        <is>
+          <t>HAGO AUTOMOTIVE CORP</t>
+        </is>
+      </c>
+      <c r="K776" t="inlineStr">
+        <is>
+          <t>HAGAUT02</t>
+        </is>
+      </c>
+      <c r="L776" t="inlineStr">
+        <is>
+          <t>47-447117700</t>
+        </is>
+      </c>
+      <c r="M776" t="inlineStr">
+        <is>
+          <t>2026-06-20 00:00:00</t>
+        </is>
+      </c>
+      <c r="N776" t="inlineStr">
+        <is>
+          <t>2026-07-01 00:00:00</t>
+        </is>
+      </c>
+      <c r="O776" t="inlineStr">
+        <is>
+          <t>WALOR VOEHRENBACH GMBH</t>
+        </is>
+      </c>
+      <c r="P776" t="inlineStr">
+        <is>
+          <t>WALOR VOEHRENBACH GMBH</t>
+        </is>
+      </c>
+      <c r="Q776" t="inlineStr">
+        <is>
+          <t>2026-05-30 00:00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="777">
+      <c r="A777" t="inlineStr">
+        <is>
+          <t>2566073</t>
+        </is>
+      </c>
+      <c r="B777" t="inlineStr">
+        <is>
+          <t>EF4-0232230-1</t>
+        </is>
+      </c>
+      <c r="C777" t="inlineStr">
+        <is>
+          <t>Vessel, Container</t>
+        </is>
+      </c>
+      <c r="D777" t="inlineStr"/>
+      <c r="E777" t="inlineStr">
+        <is>
+          <t>9903.03.06</t>
+        </is>
+      </c>
+      <c r="F777" t="inlineStr">
+        <is>
+          <t>S122 EXCL,IRN/STL/ALUM,DERIV</t>
+        </is>
+      </c>
+      <c r="G777" t="inlineStr">
+        <is>
+          <t>006</t>
+        </is>
+      </c>
+      <c r="H777" t="inlineStr">
+        <is>
+          <t>9903.03.06</t>
+        </is>
+      </c>
+      <c r="I777" t="inlineStr">
+        <is>
+          <t>9903.74.11,9903.94.53,8708.29.5160</t>
+        </is>
+      </c>
+      <c r="J777" t="inlineStr">
+        <is>
+          <t>HAGO AUTOMOTIVE CORP</t>
+        </is>
+      </c>
+      <c r="K777" t="inlineStr">
+        <is>
+          <t>HAGAUT02</t>
+        </is>
+      </c>
+      <c r="L777" t="inlineStr">
+        <is>
+          <t>47-447117700</t>
+        </is>
+      </c>
+      <c r="M777" t="inlineStr">
+        <is>
+          <t>2026-06-20 00:00:00</t>
+        </is>
+      </c>
+      <c r="N777" t="inlineStr">
+        <is>
+          <t>2026-07-01 00:00:00</t>
+        </is>
+      </c>
+      <c r="O777" t="inlineStr">
+        <is>
+          <t>WALOR VOEHRENBACH GMBH</t>
+        </is>
+      </c>
+      <c r="P777" t="inlineStr">
+        <is>
+          <t>WALOR VOEHRENBACH GMBH</t>
+        </is>
+      </c>
+      <c r="Q777" t="inlineStr">
+        <is>
+          <t>2026-05-30 00:00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="778">
+      <c r="A778" t="inlineStr">
+        <is>
+          <t>2566029</t>
+        </is>
+      </c>
+      <c r="B778" t="inlineStr">
+        <is>
+          <t>EF4-0232254-1</t>
+        </is>
+      </c>
+      <c r="C778" t="inlineStr">
+        <is>
+          <t>Vessel, Container</t>
+        </is>
+      </c>
+      <c r="D778" t="inlineStr"/>
+      <c r="E778" t="inlineStr">
+        <is>
+          <t>9903.03.06</t>
+        </is>
+      </c>
+      <c r="F778" t="inlineStr">
+        <is>
+          <t>S122 EXCL,IRN/STL/ALUM,DERIV</t>
+        </is>
+      </c>
+      <c r="G778" t="inlineStr">
+        <is>
+          <t>001</t>
+        </is>
+      </c>
+      <c r="H778" t="inlineStr">
+        <is>
+          <t>9903.03.06</t>
+        </is>
+      </c>
+      <c r="I778" t="inlineStr">
+        <is>
+          <t>9903.82.09,9403.20.0075</t>
+        </is>
+      </c>
+      <c r="J778" t="inlineStr">
+        <is>
+          <t>VISUAL CREATIONS, INC.</t>
+        </is>
+      </c>
+      <c r="K778" t="inlineStr">
+        <is>
+          <t>VISCRE</t>
+        </is>
+      </c>
+      <c r="L778" t="inlineStr">
+        <is>
+          <t>20-461602300</t>
+        </is>
+      </c>
+      <c r="M778" t="inlineStr">
+        <is>
+          <t>2026-06-30 00:00:00</t>
+        </is>
+      </c>
+      <c r="N778" t="inlineStr">
+        <is>
+          <t>2026-07-01 00:00:00</t>
+        </is>
+      </c>
+      <c r="O778" t="inlineStr">
+        <is>
+          <t>VIET MOI INDUSTRIAL COMPANY LIMITED</t>
+        </is>
+      </c>
+      <c r="P778" t="inlineStr">
+        <is>
+          <t>VIET MOI INDUSTRIAL COMPANY LIMITED</t>
+        </is>
+      </c>
+      <c r="Q778" t="inlineStr">
+        <is>
+          <t>2026-05-23 00:00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="779">
+      <c r="A779" t="inlineStr">
+        <is>
+          <t>2566029</t>
+        </is>
+      </c>
+      <c r="B779" t="inlineStr">
+        <is>
+          <t>EF4-0232254-1</t>
+        </is>
+      </c>
+      <c r="C779" t="inlineStr">
+        <is>
+          <t>Vessel, Container</t>
+        </is>
+      </c>
+      <c r="D779" t="inlineStr"/>
+      <c r="E779" t="inlineStr">
+        <is>
+          <t>9903.03.01</t>
+        </is>
+      </c>
+      <c r="F779" t="inlineStr">
+        <is>
           <t>SECTION 122 - 10% DUTY</t>
         </is>
       </c>
-      <c r="G770" t="inlineStr">
+      <c r="G779" t="inlineStr">
         <is>
           <t>002</t>
         </is>
       </c>
-      <c r="H770" t="inlineStr">
-        <is>
-          <t>9903.03.01</t>
-        </is>
-      </c>
-      <c r="I770" t="inlineStr">
-        <is>
-          <t>8420.91.9000</t>
-        </is>
-      </c>
-      <c r="J770" t="inlineStr">
-        <is>
-          <t>FI-TECH INC</t>
-        </is>
-      </c>
-      <c r="K770" t="inlineStr">
-        <is>
-          <t>FITINC</t>
-        </is>
-      </c>
-      <c r="L770" t="inlineStr">
-        <is>
-          <t>54-091465000</t>
-        </is>
-      </c>
-      <c r="M770" t="inlineStr">
+      <c r="H779" t="inlineStr">
+        <is>
+          <t>9903.03.01</t>
+        </is>
+      </c>
+      <c r="I779" t="inlineStr">
+        <is>
+          <t>9903.76.04,9403.60.8093</t>
+        </is>
+      </c>
+      <c r="J779" t="inlineStr">
+        <is>
+          <t>VISUAL CREATIONS, INC.</t>
+        </is>
+      </c>
+      <c r="K779" t="inlineStr">
+        <is>
+          <t>VISCRE</t>
+        </is>
+      </c>
+      <c r="L779" t="inlineStr">
+        <is>
+          <t>20-461602300</t>
+        </is>
+      </c>
+      <c r="M779" t="inlineStr">
         <is>
           <t>2026-06-30 00:00:00</t>
         </is>
       </c>
-      <c r="N770" t="inlineStr">
+      <c r="N779" t="inlineStr">
+        <is>
+          <t>2026-07-01 00:00:00</t>
+        </is>
+      </c>
+      <c r="O779" t="inlineStr">
+        <is>
+          <t>VIET MOI INDUSTRIAL COMPANY LIMITED</t>
+        </is>
+      </c>
+      <c r="P779" t="inlineStr">
+        <is>
+          <t>VIET MOI INDUSTRIAL COMPANY LIMITED</t>
+        </is>
+      </c>
+      <c r="Q779" t="inlineStr">
+        <is>
+          <t>2026-05-23 00:00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="780">
+      <c r="A780" t="inlineStr">
+        <is>
+          <t>2566029</t>
+        </is>
+      </c>
+      <c r="B780" t="inlineStr">
+        <is>
+          <t>EF4-0232254-1</t>
+        </is>
+      </c>
+      <c r="C780" t="inlineStr">
+        <is>
+          <t>Vessel, Container</t>
+        </is>
+      </c>
+      <c r="D780" t="inlineStr"/>
+      <c r="E780" t="inlineStr">
+        <is>
+          <t>9903.03.01</t>
+        </is>
+      </c>
+      <c r="F780" t="inlineStr">
+        <is>
+          <t>SECTION 122 - 10% DUTY</t>
+        </is>
+      </c>
+      <c r="G780" t="inlineStr">
+        <is>
+          <t>003</t>
+        </is>
+      </c>
+      <c r="H780" t="inlineStr">
+        <is>
+          <t>9903.03.01</t>
+        </is>
+      </c>
+      <c r="I780" t="inlineStr">
+        <is>
+          <t>9403.99.9045</t>
+        </is>
+      </c>
+      <c r="J780" t="inlineStr">
+        <is>
+          <t>VISUAL CREATIONS, INC.</t>
+        </is>
+      </c>
+      <c r="K780" t="inlineStr">
+        <is>
+          <t>VISCRE</t>
+        </is>
+      </c>
+      <c r="L780" t="inlineStr">
+        <is>
+          <t>20-461602300</t>
+        </is>
+      </c>
+      <c r="M780" t="inlineStr">
         <is>
           <t>2026-06-30 00:00:00</t>
         </is>
       </c>
-      <c r="O770" t="inlineStr">
-        <is>
-          <t>REIFENHAUSER REICOFIL GMBH &amp; CO. KG</t>
-        </is>
-      </c>
-      <c r="P770" t="inlineStr">
-        <is>
-          <t>REIFENHAUSER REICOFIL GMBH &amp; CO. KG</t>
-        </is>
-      </c>
-      <c r="Q770" t="inlineStr">
-        <is>
-          <t>2026-06-17 00:00:00</t>
+      <c r="N780" t="inlineStr">
+        <is>
+          <t>2026-07-01 00:00:00</t>
+        </is>
+      </c>
+      <c r="O780" t="inlineStr">
+        <is>
+          <t>VIET MOI INDUSTRIAL COMPANY LIMITED</t>
+        </is>
+      </c>
+      <c r="P780" t="inlineStr">
+        <is>
+          <t>VIET MOI INDUSTRIAL COMPANY LIMITED</t>
+        </is>
+      </c>
+      <c r="Q780" t="inlineStr">
+        <is>
+          <t>2026-05-23 00:00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="781">
+      <c r="A781" t="inlineStr">
+        <is>
+          <t>2566029</t>
+        </is>
+      </c>
+      <c r="B781" t="inlineStr">
+        <is>
+          <t>EF4-0232254-1</t>
+        </is>
+      </c>
+      <c r="C781" t="inlineStr">
+        <is>
+          <t>Vessel, Container</t>
+        </is>
+      </c>
+      <c r="D781" t="inlineStr"/>
+      <c r="E781" t="inlineStr">
+        <is>
+          <t>9903.03.01</t>
+        </is>
+      </c>
+      <c r="F781" t="inlineStr">
+        <is>
+          <t>SECTION 122 - 10% DUTY</t>
+        </is>
+      </c>
+      <c r="G781" t="inlineStr">
+        <is>
+          <t>004</t>
+        </is>
+      </c>
+      <c r="H781" t="inlineStr">
+        <is>
+          <t>9903.03.01</t>
+        </is>
+      </c>
+      <c r="I781" t="inlineStr">
+        <is>
+          <t>9403.99.3080</t>
+        </is>
+      </c>
+      <c r="J781" t="inlineStr">
+        <is>
+          <t>VISUAL CREATIONS, INC.</t>
+        </is>
+      </c>
+      <c r="K781" t="inlineStr">
+        <is>
+          <t>VISCRE</t>
+        </is>
+      </c>
+      <c r="L781" t="inlineStr">
+        <is>
+          <t>20-461602300</t>
+        </is>
+      </c>
+      <c r="M781" t="inlineStr">
+        <is>
+          <t>2026-06-30 00:00:00</t>
+        </is>
+      </c>
+      <c r="N781" t="inlineStr">
+        <is>
+          <t>2026-07-01 00:00:00</t>
+        </is>
+      </c>
+      <c r="O781" t="inlineStr">
+        <is>
+          <t>VIET MOI INDUSTRIAL COMPANY LIMITED</t>
+        </is>
+      </c>
+      <c r="P781" t="inlineStr">
+        <is>
+          <t>VIET MOI INDUSTRIAL COMPANY LIMITED</t>
+        </is>
+      </c>
+      <c r="Q781" t="inlineStr">
+        <is>
+          <t>2026-05-23 00:00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="782">
+      <c r="A782" t="inlineStr">
+        <is>
+          <t>2566029</t>
+        </is>
+      </c>
+      <c r="B782" t="inlineStr">
+        <is>
+          <t>EF4-0232254-1</t>
+        </is>
+      </c>
+      <c r="C782" t="inlineStr">
+        <is>
+          <t>Vessel, Container</t>
+        </is>
+      </c>
+      <c r="D782" t="inlineStr"/>
+      <c r="E782" t="inlineStr">
+        <is>
+          <t>9903.03.01</t>
+        </is>
+      </c>
+      <c r="F782" t="inlineStr">
+        <is>
+          <t>SECTION 122 - 10% DUTY</t>
+        </is>
+      </c>
+      <c r="G782" t="inlineStr">
+        <is>
+          <t>005</t>
+        </is>
+      </c>
+      <c r="H782" t="inlineStr">
+        <is>
+          <t>9903.03.01</t>
+        </is>
+      </c>
+      <c r="I782" t="inlineStr">
+        <is>
+          <t>9903.76.04,9403.91.0080</t>
+        </is>
+      </c>
+      <c r="J782" t="inlineStr">
+        <is>
+          <t>VISUAL CREATIONS, INC.</t>
+        </is>
+      </c>
+      <c r="K782" t="inlineStr">
+        <is>
+          <t>VISCRE</t>
+        </is>
+      </c>
+      <c r="L782" t="inlineStr">
+        <is>
+          <t>20-461602300</t>
+        </is>
+      </c>
+      <c r="M782" t="inlineStr">
+        <is>
+          <t>2026-06-30 00:00:00</t>
+        </is>
+      </c>
+      <c r="N782" t="inlineStr">
+        <is>
+          <t>2026-07-01 00:00:00</t>
+        </is>
+      </c>
+      <c r="O782" t="inlineStr">
+        <is>
+          <t>VIET MOI INDUSTRIAL COMPANY LIMITED</t>
+        </is>
+      </c>
+      <c r="P782" t="inlineStr">
+        <is>
+          <t>VIET MOI INDUSTRIAL COMPANY LIMITED</t>
+        </is>
+      </c>
+      <c r="Q782" t="inlineStr">
+        <is>
+          <t>2026-05-23 00:00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="783">
+      <c r="A783" t="inlineStr">
+        <is>
+          <t>2566239</t>
+        </is>
+      </c>
+      <c r="B783" t="inlineStr">
+        <is>
+          <t>EF4-0232286-3</t>
+        </is>
+      </c>
+      <c r="C783" t="inlineStr">
+        <is>
+          <t>Vessel, Container</t>
+        </is>
+      </c>
+      <c r="D783" t="inlineStr"/>
+      <c r="E783" t="inlineStr">
+        <is>
+          <t>9903.03.01</t>
+        </is>
+      </c>
+      <c r="F783" t="inlineStr">
+        <is>
+          <t>SECTION 122 - 10% DUTY</t>
+        </is>
+      </c>
+      <c r="G783" t="inlineStr">
+        <is>
+          <t>001</t>
+        </is>
+      </c>
+      <c r="H783" t="inlineStr">
+        <is>
+          <t>9903.03.01</t>
+        </is>
+      </c>
+      <c r="I783" t="inlineStr">
+        <is>
+          <t>4412.52.3105</t>
+        </is>
+      </c>
+      <c r="J783" t="inlineStr">
+        <is>
+          <t>BARLINEK USA CORP</t>
+        </is>
+      </c>
+      <c r="K783" t="inlineStr">
+        <is>
+          <t>BARUSA01</t>
+        </is>
+      </c>
+      <c r="L783" t="inlineStr">
+        <is>
+          <t>38-411880600</t>
+        </is>
+      </c>
+      <c r="M783" t="inlineStr">
+        <is>
+          <t>2026-07-01 00:00:00</t>
+        </is>
+      </c>
+      <c r="N783" t="inlineStr">
+        <is>
+          <t>2026-07-01 00:00:00</t>
+        </is>
+      </c>
+      <c r="O783" t="inlineStr">
+        <is>
+          <t>BARLINEK S.A.</t>
+        </is>
+      </c>
+      <c r="P783" t="inlineStr">
+        <is>
+          <t>BARLINEK S.A.</t>
+        </is>
+      </c>
+      <c r="Q783" t="inlineStr">
+        <is>
+          <t>2026-06-01 00:00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="784">
+      <c r="A784" t="inlineStr">
+        <is>
+          <t>2566232</t>
+        </is>
+      </c>
+      <c r="B784" t="inlineStr">
+        <is>
+          <t>EF4-0232576-7</t>
+        </is>
+      </c>
+      <c r="C784" t="inlineStr">
+        <is>
+          <t>Vessel, Container</t>
+        </is>
+      </c>
+      <c r="D784" t="inlineStr"/>
+      <c r="E784" t="inlineStr">
+        <is>
+          <t>9903.03.01</t>
+        </is>
+      </c>
+      <c r="F784" t="inlineStr">
+        <is>
+          <t>SECTION 122 - 10% DUTY</t>
+        </is>
+      </c>
+      <c r="G784" t="inlineStr">
+        <is>
+          <t>001</t>
+        </is>
+      </c>
+      <c r="H784" t="inlineStr">
+        <is>
+          <t>9903.03.01</t>
+        </is>
+      </c>
+      <c r="I784" t="inlineStr">
+        <is>
+          <t>3920.20.0055</t>
+        </is>
+      </c>
+      <c r="J784" t="inlineStr">
+        <is>
+          <t>TEUFELBERGER G.E.S.M.B.H</t>
+        </is>
+      </c>
+      <c r="K784" t="inlineStr">
+        <is>
+          <t>TEUSEI01</t>
+        </is>
+      </c>
+      <c r="L784" t="inlineStr">
+        <is>
+          <t>181704-13780</t>
+        </is>
+      </c>
+      <c r="M784" t="inlineStr">
+        <is>
+          <t>2026-06-28 00:00:00</t>
+        </is>
+      </c>
+      <c r="N784" t="inlineStr">
+        <is>
+          <t>2026-07-01 00:00:00</t>
+        </is>
+      </c>
+      <c r="O784" t="inlineStr">
+        <is>
+          <t>TEUFELBERGER GMBH</t>
+        </is>
+      </c>
+      <c r="P784" t="inlineStr">
+        <is>
+          <t>TEUFELBERGER GMBH</t>
+        </is>
+      </c>
+      <c r="Q784" t="inlineStr">
+        <is>
+          <t>2026-06-14 00:00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="785">
+      <c r="A785" t="inlineStr">
+        <is>
+          <t>4539584</t>
+        </is>
+      </c>
+      <c r="B785" t="inlineStr">
+        <is>
+          <t>EF4-0232901-7</t>
+        </is>
+      </c>
+      <c r="C785" t="inlineStr">
+        <is>
+          <t>Air, Non-container</t>
+        </is>
+      </c>
+      <c r="D785" t="inlineStr">
+        <is>
+          <t>713235457</t>
+        </is>
+      </c>
+      <c r="E785" t="inlineStr">
+        <is>
+          <t>9903.03.01</t>
+        </is>
+      </c>
+      <c r="F785" t="inlineStr">
+        <is>
+          <t>SECTION 122 - 10% DUTY</t>
+        </is>
+      </c>
+      <c r="G785" t="inlineStr">
+        <is>
+          <t>001</t>
+        </is>
+      </c>
+      <c r="H785" t="inlineStr">
+        <is>
+          <t>9903.03.01</t>
+        </is>
+      </c>
+      <c r="I785" t="inlineStr">
+        <is>
+          <t>8438.90.9060</t>
+        </is>
+      </c>
+      <c r="J785" t="inlineStr">
+        <is>
+          <t>CANTRELL GAINCO GROUP INC</t>
+        </is>
+      </c>
+      <c r="K785" t="inlineStr">
+        <is>
+          <t>CANGAI01</t>
+        </is>
+      </c>
+      <c r="L785" t="inlineStr">
+        <is>
+          <t>31-151121700</t>
+        </is>
+      </c>
+      <c r="M785" t="inlineStr">
+        <is>
+          <t>2026-06-29 00:00:00</t>
+        </is>
+      </c>
+      <c r="N785" t="inlineStr">
+        <is>
+          <t>2026-07-01 00:00:00</t>
+        </is>
+      </c>
+      <c r="O785" t="inlineStr">
+        <is>
+          <t>O E CO LTD</t>
+        </is>
+      </c>
+      <c r="P785" t="inlineStr">
+        <is>
+          <t>O E CO LTD</t>
+        </is>
+      </c>
+      <c r="Q785" t="inlineStr">
+        <is>
+          <t>2026-06-26 00:00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="786">
+      <c r="A786" t="inlineStr">
+        <is>
+          <t>4539590</t>
+        </is>
+      </c>
+      <c r="B786" t="inlineStr">
+        <is>
+          <t>EF4-0232918-1</t>
+        </is>
+      </c>
+      <c r="C786" t="inlineStr">
+        <is>
+          <t>Air, Non-container</t>
+        </is>
+      </c>
+      <c r="D786" t="inlineStr">
+        <is>
+          <t>713235457</t>
+        </is>
+      </c>
+      <c r="E786" t="inlineStr">
+        <is>
+          <t>9903.03.01</t>
+        </is>
+      </c>
+      <c r="F786" t="inlineStr">
+        <is>
+          <t>SECTION 122 - 10% DUTY</t>
+        </is>
+      </c>
+      <c r="G786" t="inlineStr">
+        <is>
+          <t>001</t>
+        </is>
+      </c>
+      <c r="H786" t="inlineStr">
+        <is>
+          <t>9903.03.01</t>
+        </is>
+      </c>
+      <c r="I786" t="inlineStr">
+        <is>
+          <t>8438.90.9060</t>
+        </is>
+      </c>
+      <c r="J786" t="inlineStr">
+        <is>
+          <t>CANTRELL GAINCO GROUP INC</t>
+        </is>
+      </c>
+      <c r="K786" t="inlineStr">
+        <is>
+          <t>CANGAI01</t>
+        </is>
+      </c>
+      <c r="L786" t="inlineStr">
+        <is>
+          <t>31-151121700</t>
+        </is>
+      </c>
+      <c r="M786" t="inlineStr">
+        <is>
+          <t>2026-06-30 00:00:00</t>
+        </is>
+      </c>
+      <c r="N786" t="inlineStr">
+        <is>
+          <t>2026-07-01 00:00:00</t>
+        </is>
+      </c>
+      <c r="O786" t="inlineStr">
+        <is>
+          <t>O E CO LTD</t>
+        </is>
+      </c>
+      <c r="P786" t="inlineStr">
+        <is>
+          <t>O E CO LTD</t>
+        </is>
+      </c>
+      <c r="Q786" t="inlineStr">
+        <is>
+          <t>2026-06-30 00:00:00</t>
         </is>
       </c>
     </row>

--- a/trimika_data.xlsx
+++ b/trimika_data.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q786"/>
+  <dimension ref="A1:Q801"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -66162,6 +66162,1251 @@
         </is>
       </c>
     </row>
+    <row r="787">
+      <c r="A787" t="inlineStr">
+        <is>
+          <t>2566022</t>
+        </is>
+      </c>
+      <c r="B787" t="inlineStr">
+        <is>
+          <t>EF4-0232169-1</t>
+        </is>
+      </c>
+      <c r="C787" t="inlineStr">
+        <is>
+          <t>Vessel, Container</t>
+        </is>
+      </c>
+      <c r="D787" t="inlineStr"/>
+      <c r="E787" t="inlineStr">
+        <is>
+          <t>9903.03.01</t>
+        </is>
+      </c>
+      <c r="F787" t="inlineStr">
+        <is>
+          <t>SECTION 122 - 10% DUTY</t>
+        </is>
+      </c>
+      <c r="G787" t="inlineStr">
+        <is>
+          <t>001</t>
+        </is>
+      </c>
+      <c r="H787" t="inlineStr">
+        <is>
+          <t>9903.03.01</t>
+        </is>
+      </c>
+      <c r="I787" t="inlineStr">
+        <is>
+          <t>3920.62.0090</t>
+        </is>
+      </c>
+      <c r="J787" t="inlineStr">
+        <is>
+          <t>GULF ATLANTIC PACKAGING CORP</t>
+        </is>
+      </c>
+      <c r="K787" t="inlineStr">
+        <is>
+          <t>GULATL</t>
+        </is>
+      </c>
+      <c r="L787" t="inlineStr">
+        <is>
+          <t>58-184378700</t>
+        </is>
+      </c>
+      <c r="M787" t="inlineStr">
+        <is>
+          <t>2026-07-02 00:00:00</t>
+        </is>
+      </c>
+      <c r="N787" t="inlineStr">
+        <is>
+          <t>2026-07-02 00:00:00</t>
+        </is>
+      </c>
+      <c r="O787" t="inlineStr">
+        <is>
+          <t>CONSENT FZCO</t>
+        </is>
+      </c>
+      <c r="P787" t="inlineStr">
+        <is>
+          <t>CONSENT FZCO</t>
+        </is>
+      </c>
+      <c r="Q787" t="inlineStr">
+        <is>
+          <t>2026-05-27 00:00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="788">
+      <c r="A788" t="inlineStr">
+        <is>
+          <t>2566099</t>
+        </is>
+      </c>
+      <c r="B788" t="inlineStr">
+        <is>
+          <t>EF4-0232186-5</t>
+        </is>
+      </c>
+      <c r="C788" t="inlineStr">
+        <is>
+          <t>Vessel, Container</t>
+        </is>
+      </c>
+      <c r="D788" t="inlineStr"/>
+      <c r="E788" t="inlineStr">
+        <is>
+          <t>9903.03.06</t>
+        </is>
+      </c>
+      <c r="F788" t="inlineStr">
+        <is>
+          <t>S122 EXCL,IRN/STL/ALUM,DERIV</t>
+        </is>
+      </c>
+      <c r="G788" t="inlineStr">
+        <is>
+          <t>001</t>
+        </is>
+      </c>
+      <c r="H788" t="inlineStr">
+        <is>
+          <t>9903.03.06</t>
+        </is>
+      </c>
+      <c r="I788" t="inlineStr">
+        <is>
+          <t>9903.82.22,8431.20.0000</t>
+        </is>
+      </c>
+      <c r="J788" t="inlineStr">
+        <is>
+          <t>MALLAGHAN (GA) INC.</t>
+        </is>
+      </c>
+      <c r="K788" t="inlineStr">
+        <is>
+          <t>MALGA01</t>
+        </is>
+      </c>
+      <c r="L788" t="inlineStr">
+        <is>
+          <t>36-488102800</t>
+        </is>
+      </c>
+      <c r="M788" t="inlineStr">
+        <is>
+          <t>2026-07-05 00:00:00</t>
+        </is>
+      </c>
+      <c r="N788" t="inlineStr">
+        <is>
+          <t>2026-07-02 00:00:00</t>
+        </is>
+      </c>
+      <c r="O788" t="inlineStr">
+        <is>
+          <t>MALLAGHAN ENGINEERING  LTD</t>
+        </is>
+      </c>
+      <c r="P788" t="inlineStr">
+        <is>
+          <t>MALLAGHAN ENGINEERING  LTD</t>
+        </is>
+      </c>
+      <c r="Q788" t="inlineStr">
+        <is>
+          <t>2026-05-28 00:00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="789">
+      <c r="A789" t="inlineStr">
+        <is>
+          <t>2566099</t>
+        </is>
+      </c>
+      <c r="B789" t="inlineStr">
+        <is>
+          <t>EF4-0232186-5</t>
+        </is>
+      </c>
+      <c r="C789" t="inlineStr">
+        <is>
+          <t>Vessel, Container</t>
+        </is>
+      </c>
+      <c r="D789" t="inlineStr"/>
+      <c r="E789" t="inlineStr">
+        <is>
+          <t>9903.03.06</t>
+        </is>
+      </c>
+      <c r="F789" t="inlineStr">
+        <is>
+          <t>S122 EXCL,IRN/STL/ALUM,DERIV</t>
+        </is>
+      </c>
+      <c r="G789" t="inlineStr">
+        <is>
+          <t>002</t>
+        </is>
+      </c>
+      <c r="H789" t="inlineStr">
+        <is>
+          <t>9903.03.06</t>
+        </is>
+      </c>
+      <c r="I789" t="inlineStr">
+        <is>
+          <t>9903.82.22,8431.20.0000</t>
+        </is>
+      </c>
+      <c r="J789" t="inlineStr">
+        <is>
+          <t>MALLAGHAN (GA) INC.</t>
+        </is>
+      </c>
+      <c r="K789" t="inlineStr">
+        <is>
+          <t>MALGA01</t>
+        </is>
+      </c>
+      <c r="L789" t="inlineStr">
+        <is>
+          <t>36-488102800</t>
+        </is>
+      </c>
+      <c r="M789" t="inlineStr">
+        <is>
+          <t>2026-07-05 00:00:00</t>
+        </is>
+      </c>
+      <c r="N789" t="inlineStr">
+        <is>
+          <t>2026-07-02 00:00:00</t>
+        </is>
+      </c>
+      <c r="O789" t="inlineStr">
+        <is>
+          <t>MALLAGHAN ENGINEERING  LTD</t>
+        </is>
+      </c>
+      <c r="P789" t="inlineStr">
+        <is>
+          <t>MALLAGHAN ENGINEERING  LTD</t>
+        </is>
+      </c>
+      <c r="Q789" t="inlineStr">
+        <is>
+          <t>2026-05-28 00:00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="790">
+      <c r="A790" t="inlineStr">
+        <is>
+          <t>2565995</t>
+        </is>
+      </c>
+      <c r="B790" t="inlineStr">
+        <is>
+          <t>EF4-0232279-8</t>
+        </is>
+      </c>
+      <c r="C790" t="inlineStr">
+        <is>
+          <t>Vessel, Container</t>
+        </is>
+      </c>
+      <c r="D790" t="inlineStr"/>
+      <c r="E790" t="inlineStr">
+        <is>
+          <t>9903.88.03</t>
+        </is>
+      </c>
+      <c r="F790" t="inlineStr">
+        <is>
+          <t>ARTICLE OF CHINA,US NTE 20(F)</t>
+        </is>
+      </c>
+      <c r="G790" t="inlineStr">
+        <is>
+          <t>001</t>
+        </is>
+      </c>
+      <c r="H790" t="inlineStr">
+        <is>
+          <t>9903.88.03</t>
+        </is>
+      </c>
+      <c r="I790" t="inlineStr">
+        <is>
+          <t>9903.03.01,9403.99.9045</t>
+        </is>
+      </c>
+      <c r="J790" t="inlineStr">
+        <is>
+          <t>VISUAL CREATIONS, INC.</t>
+        </is>
+      </c>
+      <c r="K790" t="inlineStr">
+        <is>
+          <t>VISCRE</t>
+        </is>
+      </c>
+      <c r="L790" t="inlineStr">
+        <is>
+          <t>20-461602300</t>
+        </is>
+      </c>
+      <c r="M790" t="inlineStr">
+        <is>
+          <t>2026-07-04 00:00:00</t>
+        </is>
+      </c>
+      <c r="N790" t="inlineStr">
+        <is>
+          <t>2026-07-02 00:00:00</t>
+        </is>
+      </c>
+      <c r="O790" t="inlineStr">
+        <is>
+          <t>FUJIAN ANTAI NEW ENERGY TECH CO LTD</t>
+        </is>
+      </c>
+      <c r="P790" t="inlineStr">
+        <is>
+          <t>FUJIAN ANTAI NEW ENERGY TECH CO LTD</t>
+        </is>
+      </c>
+      <c r="Q790" t="inlineStr">
+        <is>
+          <t>2026-06-02 00:00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="791">
+      <c r="A791" t="inlineStr">
+        <is>
+          <t>2565995</t>
+        </is>
+      </c>
+      <c r="B791" t="inlineStr">
+        <is>
+          <t>EF4-0232279-8</t>
+        </is>
+      </c>
+      <c r="C791" t="inlineStr">
+        <is>
+          <t>Vessel, Container</t>
+        </is>
+      </c>
+      <c r="D791" t="inlineStr"/>
+      <c r="E791" t="inlineStr">
+        <is>
+          <t>9903.88.15</t>
+        </is>
+      </c>
+      <c r="F791" t="inlineStr">
+        <is>
+          <t>ARTICLE OF CHINA,US NTE 20(R)</t>
+        </is>
+      </c>
+      <c r="G791" t="inlineStr">
+        <is>
+          <t>002</t>
+        </is>
+      </c>
+      <c r="H791" t="inlineStr">
+        <is>
+          <t>9903.88.15</t>
+        </is>
+      </c>
+      <c r="I791" t="inlineStr">
+        <is>
+          <t>9903.03.01,3926.90.9989</t>
+        </is>
+      </c>
+      <c r="J791" t="inlineStr">
+        <is>
+          <t>VISUAL CREATIONS, INC.</t>
+        </is>
+      </c>
+      <c r="K791" t="inlineStr">
+        <is>
+          <t>VISCRE</t>
+        </is>
+      </c>
+      <c r="L791" t="inlineStr">
+        <is>
+          <t>20-461602300</t>
+        </is>
+      </c>
+      <c r="M791" t="inlineStr">
+        <is>
+          <t>2026-07-04 00:00:00</t>
+        </is>
+      </c>
+      <c r="N791" t="inlineStr">
+        <is>
+          <t>2026-07-02 00:00:00</t>
+        </is>
+      </c>
+      <c r="O791" t="inlineStr">
+        <is>
+          <t>FUJIAN ANTAI NEW ENERGY TECH CO LTD</t>
+        </is>
+      </c>
+      <c r="P791" t="inlineStr">
+        <is>
+          <t>FUJIAN ANTAI NEW ENERGY TECH CO LTD</t>
+        </is>
+      </c>
+      <c r="Q791" t="inlineStr">
+        <is>
+          <t>2026-06-02 00:00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="792">
+      <c r="A792" t="inlineStr">
+        <is>
+          <t>2565996</t>
+        </is>
+      </c>
+      <c r="B792" t="inlineStr">
+        <is>
+          <t>EF4-0232280-6</t>
+        </is>
+      </c>
+      <c r="C792" t="inlineStr">
+        <is>
+          <t>Vessel, Container</t>
+        </is>
+      </c>
+      <c r="D792" t="inlineStr"/>
+      <c r="E792" t="inlineStr">
+        <is>
+          <t>9903.88.15</t>
+        </is>
+      </c>
+      <c r="F792" t="inlineStr">
+        <is>
+          <t>ARTICLE OF CHINA,US NTE 20(R)</t>
+        </is>
+      </c>
+      <c r="G792" t="inlineStr">
+        <is>
+          <t>001</t>
+        </is>
+      </c>
+      <c r="H792" t="inlineStr">
+        <is>
+          <t>9903.88.15</t>
+        </is>
+      </c>
+      <c r="I792" t="inlineStr">
+        <is>
+          <t>9903.03.01,3926.90.9989</t>
+        </is>
+      </c>
+      <c r="J792" t="inlineStr">
+        <is>
+          <t>VISUAL CREATIONS, INC.</t>
+        </is>
+      </c>
+      <c r="K792" t="inlineStr">
+        <is>
+          <t>VISCRE</t>
+        </is>
+      </c>
+      <c r="L792" t="inlineStr">
+        <is>
+          <t>20-461602300</t>
+        </is>
+      </c>
+      <c r="M792" t="inlineStr">
+        <is>
+          <t>2026-07-04 00:00:00</t>
+        </is>
+      </c>
+      <c r="N792" t="inlineStr">
+        <is>
+          <t>2026-07-02 00:00:00</t>
+        </is>
+      </c>
+      <c r="O792" t="inlineStr">
+        <is>
+          <t>FUJIAN ANTAI NEW ENERGY TECH CO LTD</t>
+        </is>
+      </c>
+      <c r="P792" t="inlineStr">
+        <is>
+          <t>FUJIAN ANTAI NEW ENERGY TECH CO LTD</t>
+        </is>
+      </c>
+      <c r="Q792" t="inlineStr">
+        <is>
+          <t>2026-06-02 00:00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="793">
+      <c r="A793" t="inlineStr">
+        <is>
+          <t>2565996</t>
+        </is>
+      </c>
+      <c r="B793" t="inlineStr">
+        <is>
+          <t>EF4-0232280-6</t>
+        </is>
+      </c>
+      <c r="C793" t="inlineStr">
+        <is>
+          <t>Vessel, Container</t>
+        </is>
+      </c>
+      <c r="D793" t="inlineStr"/>
+      <c r="E793" t="inlineStr">
+        <is>
+          <t>9903.88.03</t>
+        </is>
+      </c>
+      <c r="F793" t="inlineStr">
+        <is>
+          <t>ARTICLE OF CHINA,US NTE 20(F)</t>
+        </is>
+      </c>
+      <c r="G793" t="inlineStr">
+        <is>
+          <t>002</t>
+        </is>
+      </c>
+      <c r="H793" t="inlineStr">
+        <is>
+          <t>9903.88.03</t>
+        </is>
+      </c>
+      <c r="I793" t="inlineStr">
+        <is>
+          <t>9903.03.01,9403.99.9045</t>
+        </is>
+      </c>
+      <c r="J793" t="inlineStr">
+        <is>
+          <t>VISUAL CREATIONS, INC.</t>
+        </is>
+      </c>
+      <c r="K793" t="inlineStr">
+        <is>
+          <t>VISCRE</t>
+        </is>
+      </c>
+      <c r="L793" t="inlineStr">
+        <is>
+          <t>20-461602300</t>
+        </is>
+      </c>
+      <c r="M793" t="inlineStr">
+        <is>
+          <t>2026-07-04 00:00:00</t>
+        </is>
+      </c>
+      <c r="N793" t="inlineStr">
+        <is>
+          <t>2026-07-02 00:00:00</t>
+        </is>
+      </c>
+      <c r="O793" t="inlineStr">
+        <is>
+          <t>FUJIAN ANTAI NEW ENERGY TECH CO LTD</t>
+        </is>
+      </c>
+      <c r="P793" t="inlineStr">
+        <is>
+          <t>FUJIAN ANTAI NEW ENERGY TECH CO LTD</t>
+        </is>
+      </c>
+      <c r="Q793" t="inlineStr">
+        <is>
+          <t>2026-06-02 00:00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="794">
+      <c r="A794" t="inlineStr">
+        <is>
+          <t>2565996</t>
+        </is>
+      </c>
+      <c r="B794" t="inlineStr">
+        <is>
+          <t>EF4-0232280-6</t>
+        </is>
+      </c>
+      <c r="C794" t="inlineStr">
+        <is>
+          <t>Vessel, Container</t>
+        </is>
+      </c>
+      <c r="D794" t="inlineStr"/>
+      <c r="E794" t="inlineStr">
+        <is>
+          <t>9903.88.15</t>
+        </is>
+      </c>
+      <c r="F794" t="inlineStr">
+        <is>
+          <t>ARTICLE OF CHINA,US NTE 20(R)</t>
+        </is>
+      </c>
+      <c r="G794" t="inlineStr">
+        <is>
+          <t>003</t>
+        </is>
+      </c>
+      <c r="H794" t="inlineStr">
+        <is>
+          <t>9903.88.15</t>
+        </is>
+      </c>
+      <c r="I794" t="inlineStr">
+        <is>
+          <t>9903.03.06,9903.82.09,8302.42.3065</t>
+        </is>
+      </c>
+      <c r="J794" t="inlineStr">
+        <is>
+          <t>VISUAL CREATIONS, INC.</t>
+        </is>
+      </c>
+      <c r="K794" t="inlineStr">
+        <is>
+          <t>VISCRE</t>
+        </is>
+      </c>
+      <c r="L794" t="inlineStr">
+        <is>
+          <t>20-461602300</t>
+        </is>
+      </c>
+      <c r="M794" t="inlineStr">
+        <is>
+          <t>2026-07-04 00:00:00</t>
+        </is>
+      </c>
+      <c r="N794" t="inlineStr">
+        <is>
+          <t>2026-07-02 00:00:00</t>
+        </is>
+      </c>
+      <c r="O794" t="inlineStr">
+        <is>
+          <t>FUJIAN ANTAI NEW ENERGY TECH CO LTD</t>
+        </is>
+      </c>
+      <c r="P794" t="inlineStr">
+        <is>
+          <t>FUJIAN ANTAI NEW ENERGY TECH CO LTD</t>
+        </is>
+      </c>
+      <c r="Q794" t="inlineStr">
+        <is>
+          <t>2026-06-02 00:00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="795">
+      <c r="A795" t="inlineStr">
+        <is>
+          <t>2565996</t>
+        </is>
+      </c>
+      <c r="B795" t="inlineStr">
+        <is>
+          <t>EF4-0232280-6</t>
+        </is>
+      </c>
+      <c r="C795" t="inlineStr">
+        <is>
+          <t>Vessel, Container</t>
+        </is>
+      </c>
+      <c r="D795" t="inlineStr"/>
+      <c r="E795" t="inlineStr">
+        <is>
+          <t>9903.88.03</t>
+        </is>
+      </c>
+      <c r="F795" t="inlineStr">
+        <is>
+          <t>ARTICLE OF CHINA,US NTE 20(F)</t>
+        </is>
+      </c>
+      <c r="G795" t="inlineStr">
+        <is>
+          <t>004</t>
+        </is>
+      </c>
+      <c r="H795" t="inlineStr">
+        <is>
+          <t>9903.88.03</t>
+        </is>
+      </c>
+      <c r="I795" t="inlineStr">
+        <is>
+          <t>9903.03.06,9903.82.09,9403.20.0075</t>
+        </is>
+      </c>
+      <c r="J795" t="inlineStr">
+        <is>
+          <t>VISUAL CREATIONS, INC.</t>
+        </is>
+      </c>
+      <c r="K795" t="inlineStr">
+        <is>
+          <t>VISCRE</t>
+        </is>
+      </c>
+      <c r="L795" t="inlineStr">
+        <is>
+          <t>20-461602300</t>
+        </is>
+      </c>
+      <c r="M795" t="inlineStr">
+        <is>
+          <t>2026-07-04 00:00:00</t>
+        </is>
+      </c>
+      <c r="N795" t="inlineStr">
+        <is>
+          <t>2026-07-02 00:00:00</t>
+        </is>
+      </c>
+      <c r="O795" t="inlineStr">
+        <is>
+          <t>FUJIAN ANTAI NEW ENERGY TECH CO LTD</t>
+        </is>
+      </c>
+      <c r="P795" t="inlineStr">
+        <is>
+          <t>FUJIAN ANTAI NEW ENERGY TECH CO LTD</t>
+        </is>
+      </c>
+      <c r="Q795" t="inlineStr">
+        <is>
+          <t>2026-06-02 00:00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="796">
+      <c r="A796" t="inlineStr">
+        <is>
+          <t>2565996</t>
+        </is>
+      </c>
+      <c r="B796" t="inlineStr">
+        <is>
+          <t>EF4-0232280-6</t>
+        </is>
+      </c>
+      <c r="C796" t="inlineStr">
+        <is>
+          <t>Vessel, Container</t>
+        </is>
+      </c>
+      <c r="D796" t="inlineStr"/>
+      <c r="E796" t="inlineStr">
+        <is>
+          <t>9903.88.03</t>
+        </is>
+      </c>
+      <c r="F796" t="inlineStr">
+        <is>
+          <t>ARTICLE OF CHINA,US NTE 20(F)</t>
+        </is>
+      </c>
+      <c r="G796" t="inlineStr">
+        <is>
+          <t>005</t>
+        </is>
+      </c>
+      <c r="H796" t="inlineStr">
+        <is>
+          <t>9903.88.03</t>
+        </is>
+      </c>
+      <c r="I796" t="inlineStr">
+        <is>
+          <t>9903.03.01,9903.76.04,9403.91.0080</t>
+        </is>
+      </c>
+      <c r="J796" t="inlineStr">
+        <is>
+          <t>VISUAL CREATIONS, INC.</t>
+        </is>
+      </c>
+      <c r="K796" t="inlineStr">
+        <is>
+          <t>VISCRE</t>
+        </is>
+      </c>
+      <c r="L796" t="inlineStr">
+        <is>
+          <t>20-461602300</t>
+        </is>
+      </c>
+      <c r="M796" t="inlineStr">
+        <is>
+          <t>2026-07-04 00:00:00</t>
+        </is>
+      </c>
+      <c r="N796" t="inlineStr">
+        <is>
+          <t>2026-07-02 00:00:00</t>
+        </is>
+      </c>
+      <c r="O796" t="inlineStr">
+        <is>
+          <t>FUJIAN ANTAI NEW ENERGY TECH CO LTD</t>
+        </is>
+      </c>
+      <c r="P796" t="inlineStr">
+        <is>
+          <t>FUJIAN ANTAI NEW ENERGY TECH CO LTD</t>
+        </is>
+      </c>
+      <c r="Q796" t="inlineStr">
+        <is>
+          <t>2026-06-02 00:00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="797">
+      <c r="A797" t="inlineStr">
+        <is>
+          <t>2566367</t>
+        </is>
+      </c>
+      <c r="B797" t="inlineStr">
+        <is>
+          <t>EF4-0232744-1</t>
+        </is>
+      </c>
+      <c r="C797" t="inlineStr">
+        <is>
+          <t>Vessel, Container</t>
+        </is>
+      </c>
+      <c r="D797" t="inlineStr"/>
+      <c r="E797" t="inlineStr">
+        <is>
+          <t>9903.03.06</t>
+        </is>
+      </c>
+      <c r="F797" t="inlineStr">
+        <is>
+          <t>S122 EXCL,IRN/STL/ALUM,DERIV</t>
+        </is>
+      </c>
+      <c r="G797" t="inlineStr">
+        <is>
+          <t>001</t>
+        </is>
+      </c>
+      <c r="H797" t="inlineStr">
+        <is>
+          <t>9903.03.06</t>
+        </is>
+      </c>
+      <c r="I797" t="inlineStr">
+        <is>
+          <t>9903.74.11,9903.94.53,8708.29.5190</t>
+        </is>
+      </c>
+      <c r="J797" t="inlineStr">
+        <is>
+          <t>BORGERS USA CORP</t>
+        </is>
+      </c>
+      <c r="K797" t="inlineStr">
+        <is>
+          <t>BORUSA</t>
+        </is>
+      </c>
+      <c r="L797" t="inlineStr">
+        <is>
+          <t>65-117296500</t>
+        </is>
+      </c>
+      <c r="M797" t="inlineStr">
+        <is>
+          <t>2026-07-02 00:00:00</t>
+        </is>
+      </c>
+      <c r="N797" t="inlineStr">
+        <is>
+          <t>2026-07-02 00:00:00</t>
+        </is>
+      </c>
+      <c r="O797" t="inlineStr">
+        <is>
+          <t>AUTONEUM CZ S.R.O.</t>
+        </is>
+      </c>
+      <c r="P797" t="inlineStr">
+        <is>
+          <t>AUTONEUM CZ S.R.O.</t>
+        </is>
+      </c>
+      <c r="Q797" t="inlineStr">
+        <is>
+          <t>2026-06-20 00:00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="798">
+      <c r="A798" t="inlineStr">
+        <is>
+          <t>2566367</t>
+        </is>
+      </c>
+      <c r="B798" t="inlineStr">
+        <is>
+          <t>EF4-0232744-1</t>
+        </is>
+      </c>
+      <c r="C798" t="inlineStr">
+        <is>
+          <t>Vessel, Container</t>
+        </is>
+      </c>
+      <c r="D798" t="inlineStr"/>
+      <c r="E798" t="inlineStr">
+        <is>
+          <t>9903.03.06</t>
+        </is>
+      </c>
+      <c r="F798" t="inlineStr">
+        <is>
+          <t>S122 EXCL,IRN/STL/ALUM,DERIV</t>
+        </is>
+      </c>
+      <c r="G798" t="inlineStr">
+        <is>
+          <t>002</t>
+        </is>
+      </c>
+      <c r="H798" t="inlineStr">
+        <is>
+          <t>9903.03.06</t>
+        </is>
+      </c>
+      <c r="I798" t="inlineStr">
+        <is>
+          <t>9903.74.11,9903.94.53,8708.29.5190</t>
+        </is>
+      </c>
+      <c r="J798" t="inlineStr">
+        <is>
+          <t>BORGERS USA CORP</t>
+        </is>
+      </c>
+      <c r="K798" t="inlineStr">
+        <is>
+          <t>BORUSA</t>
+        </is>
+      </c>
+      <c r="L798" t="inlineStr">
+        <is>
+          <t>65-117296500</t>
+        </is>
+      </c>
+      <c r="M798" t="inlineStr">
+        <is>
+          <t>2026-07-02 00:00:00</t>
+        </is>
+      </c>
+      <c r="N798" t="inlineStr">
+        <is>
+          <t>2026-07-02 00:00:00</t>
+        </is>
+      </c>
+      <c r="O798" t="inlineStr">
+        <is>
+          <t>AUTONEUM CZ S.R.O.</t>
+        </is>
+      </c>
+      <c r="P798" t="inlineStr">
+        <is>
+          <t>AUTONEUM CZ S.R.O.</t>
+        </is>
+      </c>
+      <c r="Q798" t="inlineStr">
+        <is>
+          <t>2026-06-20 00:00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="799">
+      <c r="A799" t="inlineStr">
+        <is>
+          <t>2566367</t>
+        </is>
+      </c>
+      <c r="B799" t="inlineStr">
+        <is>
+          <t>EF4-0232744-1</t>
+        </is>
+      </c>
+      <c r="C799" t="inlineStr">
+        <is>
+          <t>Vessel, Container</t>
+        </is>
+      </c>
+      <c r="D799" t="inlineStr"/>
+      <c r="E799" t="inlineStr">
+        <is>
+          <t>9903.03.06</t>
+        </is>
+      </c>
+      <c r="F799" t="inlineStr">
+        <is>
+          <t>S122 EXCL,IRN/STL/ALUM,DERIV</t>
+        </is>
+      </c>
+      <c r="G799" t="inlineStr">
+        <is>
+          <t>003</t>
+        </is>
+      </c>
+      <c r="H799" t="inlineStr">
+        <is>
+          <t>9903.03.06</t>
+        </is>
+      </c>
+      <c r="I799" t="inlineStr">
+        <is>
+          <t>9903.74.11,9903.94.53,8708.29.5190</t>
+        </is>
+      </c>
+      <c r="J799" t="inlineStr">
+        <is>
+          <t>BORGERS USA CORP</t>
+        </is>
+      </c>
+      <c r="K799" t="inlineStr">
+        <is>
+          <t>BORUSA</t>
+        </is>
+      </c>
+      <c r="L799" t="inlineStr">
+        <is>
+          <t>65-117296500</t>
+        </is>
+      </c>
+      <c r="M799" t="inlineStr">
+        <is>
+          <t>2026-07-02 00:00:00</t>
+        </is>
+      </c>
+      <c r="N799" t="inlineStr">
+        <is>
+          <t>2026-07-02 00:00:00</t>
+        </is>
+      </c>
+      <c r="O799" t="inlineStr">
+        <is>
+          <t>AUTONEUM CZ S.R.O.</t>
+        </is>
+      </c>
+      <c r="P799" t="inlineStr">
+        <is>
+          <t>AUTONEUM CZ S.R.O.</t>
+        </is>
+      </c>
+      <c r="Q799" t="inlineStr">
+        <is>
+          <t>2026-06-20 00:00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="800">
+      <c r="A800" t="inlineStr">
+        <is>
+          <t>2566367</t>
+        </is>
+      </c>
+      <c r="B800" t="inlineStr">
+        <is>
+          <t>EF4-0232744-1</t>
+        </is>
+      </c>
+      <c r="C800" t="inlineStr">
+        <is>
+          <t>Vessel, Container</t>
+        </is>
+      </c>
+      <c r="D800" t="inlineStr"/>
+      <c r="E800" t="inlineStr">
+        <is>
+          <t>9903.03.06</t>
+        </is>
+      </c>
+      <c r="F800" t="inlineStr">
+        <is>
+          <t>S122 EXCL,IRN/STL/ALUM,DERIV</t>
+        </is>
+      </c>
+      <c r="G800" t="inlineStr">
+        <is>
+          <t>004</t>
+        </is>
+      </c>
+      <c r="H800" t="inlineStr">
+        <is>
+          <t>9903.03.06</t>
+        </is>
+      </c>
+      <c r="I800" t="inlineStr">
+        <is>
+          <t>9903.74.11,9903.94.53,8708.29.5190</t>
+        </is>
+      </c>
+      <c r="J800" t="inlineStr">
+        <is>
+          <t>BORGERS USA CORP</t>
+        </is>
+      </c>
+      <c r="K800" t="inlineStr">
+        <is>
+          <t>BORUSA</t>
+        </is>
+      </c>
+      <c r="L800" t="inlineStr">
+        <is>
+          <t>65-117296500</t>
+        </is>
+      </c>
+      <c r="M800" t="inlineStr">
+        <is>
+          <t>2026-07-02 00:00:00</t>
+        </is>
+      </c>
+      <c r="N800" t="inlineStr">
+        <is>
+          <t>2026-07-02 00:00:00</t>
+        </is>
+      </c>
+      <c r="O800" t="inlineStr">
+        <is>
+          <t>AUTONEUM CZ S.R.O.</t>
+        </is>
+      </c>
+      <c r="P800" t="inlineStr">
+        <is>
+          <t>AUTONEUM CZ S.R.O.</t>
+        </is>
+      </c>
+      <c r="Q800" t="inlineStr">
+        <is>
+          <t>2026-06-20 00:00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="801">
+      <c r="A801" t="inlineStr">
+        <is>
+          <t>2566367</t>
+        </is>
+      </c>
+      <c r="B801" t="inlineStr">
+        <is>
+          <t>EF4-0232744-1</t>
+        </is>
+      </c>
+      <c r="C801" t="inlineStr">
+        <is>
+          <t>Vessel, Container</t>
+        </is>
+      </c>
+      <c r="D801" t="inlineStr"/>
+      <c r="E801" t="inlineStr">
+        <is>
+          <t>9903.03.06</t>
+        </is>
+      </c>
+      <c r="F801" t="inlineStr">
+        <is>
+          <t>S122 EXCL,IRN/STL/ALUM,DERIV</t>
+        </is>
+      </c>
+      <c r="G801" t="inlineStr">
+        <is>
+          <t>005</t>
+        </is>
+      </c>
+      <c r="H801" t="inlineStr">
+        <is>
+          <t>9903.03.06</t>
+        </is>
+      </c>
+      <c r="I801" t="inlineStr">
+        <is>
+          <t>9903.74.11,9903.94.53,8708.29.5190</t>
+        </is>
+      </c>
+      <c r="J801" t="inlineStr">
+        <is>
+          <t>BORGERS USA CORP</t>
+        </is>
+      </c>
+      <c r="K801" t="inlineStr">
+        <is>
+          <t>BORUSA</t>
+        </is>
+      </c>
+      <c r="L801" t="inlineStr">
+        <is>
+          <t>65-117296500</t>
+        </is>
+      </c>
+      <c r="M801" t="inlineStr">
+        <is>
+          <t>2026-07-02 00:00:00</t>
+        </is>
+      </c>
+      <c r="N801" t="inlineStr">
+        <is>
+          <t>2026-07-02 00:00:00</t>
+        </is>
+      </c>
+      <c r="O801" t="inlineStr">
+        <is>
+          <t>AUTONEUM CZ S.R.O.</t>
+        </is>
+      </c>
+      <c r="P801" t="inlineStr">
+        <is>
+          <t>AUTONEUM CZ S.R.O.</t>
+        </is>
+      </c>
+      <c r="Q801" t="inlineStr">
+        <is>
+          <t>2026-06-20 00:00:00</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/trimika_data.xlsx
+++ b/trimika_data.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q801"/>
+  <dimension ref="A1:Q804"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -66414,12 +66414,12 @@
     <row r="790">
       <c r="A790" t="inlineStr">
         <is>
-          <t>2565995</t>
+          <t>2566367</t>
         </is>
       </c>
       <c r="B790" t="inlineStr">
         <is>
-          <t>EF4-0232279-8</t>
+          <t>EF4-0232744-1</t>
         </is>
       </c>
       <c r="C790" t="inlineStr">
@@ -66430,12 +66430,12 @@
       <c r="D790" t="inlineStr"/>
       <c r="E790" t="inlineStr">
         <is>
-          <t>9903.88.03</t>
+          <t>9903.03.06</t>
         </is>
       </c>
       <c r="F790" t="inlineStr">
         <is>
-          <t>ARTICLE OF CHINA,US NTE 20(F)</t>
+          <t>S122 EXCL,IRN/STL/ALUM,DERIV</t>
         </is>
       </c>
       <c r="G790" t="inlineStr">
@@ -66445,32 +66445,32 @@
       </c>
       <c r="H790" t="inlineStr">
         <is>
-          <t>9903.88.03</t>
+          <t>9903.03.06</t>
         </is>
       </c>
       <c r="I790" t="inlineStr">
         <is>
-          <t>9903.03.01,9403.99.9045</t>
+          <t>9903.74.11,9903.94.53,8708.29.5190</t>
         </is>
       </c>
       <c r="J790" t="inlineStr">
         <is>
-          <t>VISUAL CREATIONS, INC.</t>
+          <t>BORGERS USA CORP</t>
         </is>
       </c>
       <c r="K790" t="inlineStr">
         <is>
-          <t>VISCRE</t>
+          <t>BORUSA</t>
         </is>
       </c>
       <c r="L790" t="inlineStr">
         <is>
-          <t>20-461602300</t>
+          <t>65-117296500</t>
         </is>
       </c>
       <c r="M790" t="inlineStr">
         <is>
-          <t>2026-07-04 00:00:00</t>
+          <t>2026-07-02 00:00:00</t>
         </is>
       </c>
       <c r="N790" t="inlineStr">
@@ -66480,29 +66480,29 @@
       </c>
       <c r="O790" t="inlineStr">
         <is>
-          <t>FUJIAN ANTAI NEW ENERGY TECH CO LTD</t>
+          <t>AUTONEUM CZ S.R.O.</t>
         </is>
       </c>
       <c r="P790" t="inlineStr">
         <is>
-          <t>FUJIAN ANTAI NEW ENERGY TECH CO LTD</t>
+          <t>AUTONEUM CZ S.R.O.</t>
         </is>
       </c>
       <c r="Q790" t="inlineStr">
         <is>
-          <t>2026-06-02 00:00:00</t>
+          <t>2026-06-20 00:00:00</t>
         </is>
       </c>
     </row>
     <row r="791">
       <c r="A791" t="inlineStr">
         <is>
-          <t>2565995</t>
+          <t>2566367</t>
         </is>
       </c>
       <c r="B791" t="inlineStr">
         <is>
-          <t>EF4-0232279-8</t>
+          <t>EF4-0232744-1</t>
         </is>
       </c>
       <c r="C791" t="inlineStr">
@@ -66513,12 +66513,12 @@
       <c r="D791" t="inlineStr"/>
       <c r="E791" t="inlineStr">
         <is>
-          <t>9903.88.15</t>
+          <t>9903.03.06</t>
         </is>
       </c>
       <c r="F791" t="inlineStr">
         <is>
-          <t>ARTICLE OF CHINA,US NTE 20(R)</t>
+          <t>S122 EXCL,IRN/STL/ALUM,DERIV</t>
         </is>
       </c>
       <c r="G791" t="inlineStr">
@@ -66528,32 +66528,32 @@
       </c>
       <c r="H791" t="inlineStr">
         <is>
-          <t>9903.88.15</t>
+          <t>9903.03.06</t>
         </is>
       </c>
       <c r="I791" t="inlineStr">
         <is>
-          <t>9903.03.01,3926.90.9989</t>
+          <t>9903.74.11,9903.94.53,8708.29.5190</t>
         </is>
       </c>
       <c r="J791" t="inlineStr">
         <is>
-          <t>VISUAL CREATIONS, INC.</t>
+          <t>BORGERS USA CORP</t>
         </is>
       </c>
       <c r="K791" t="inlineStr">
         <is>
-          <t>VISCRE</t>
+          <t>BORUSA</t>
         </is>
       </c>
       <c r="L791" t="inlineStr">
         <is>
-          <t>20-461602300</t>
+          <t>65-117296500</t>
         </is>
       </c>
       <c r="M791" t="inlineStr">
         <is>
-          <t>2026-07-04 00:00:00</t>
+          <t>2026-07-02 00:00:00</t>
         </is>
       </c>
       <c r="N791" t="inlineStr">
@@ -66563,29 +66563,29 @@
       </c>
       <c r="O791" t="inlineStr">
         <is>
-          <t>FUJIAN ANTAI NEW ENERGY TECH CO LTD</t>
+          <t>AUTONEUM CZ S.R.O.</t>
         </is>
       </c>
       <c r="P791" t="inlineStr">
         <is>
-          <t>FUJIAN ANTAI NEW ENERGY TECH CO LTD</t>
+          <t>AUTONEUM CZ S.R.O.</t>
         </is>
       </c>
       <c r="Q791" t="inlineStr">
         <is>
-          <t>2026-06-02 00:00:00</t>
+          <t>2026-06-20 00:00:00</t>
         </is>
       </c>
     </row>
     <row r="792">
       <c r="A792" t="inlineStr">
         <is>
-          <t>2565996</t>
+          <t>2566367</t>
         </is>
       </c>
       <c r="B792" t="inlineStr">
         <is>
-          <t>EF4-0232280-6</t>
+          <t>EF4-0232744-1</t>
         </is>
       </c>
       <c r="C792" t="inlineStr">
@@ -66596,47 +66596,47 @@
       <c r="D792" t="inlineStr"/>
       <c r="E792" t="inlineStr">
         <is>
-          <t>9903.88.15</t>
+          <t>9903.03.06</t>
         </is>
       </c>
       <c r="F792" t="inlineStr">
         <is>
-          <t>ARTICLE OF CHINA,US NTE 20(R)</t>
+          <t>S122 EXCL,IRN/STL/ALUM,DERIV</t>
         </is>
       </c>
       <c r="G792" t="inlineStr">
         <is>
-          <t>001</t>
+          <t>003</t>
         </is>
       </c>
       <c r="H792" t="inlineStr">
         <is>
-          <t>9903.88.15</t>
+          <t>9903.03.06</t>
         </is>
       </c>
       <c r="I792" t="inlineStr">
         <is>
-          <t>9903.03.01,3926.90.9989</t>
+          <t>9903.74.11,9903.94.53,8708.29.5190</t>
         </is>
       </c>
       <c r="J792" t="inlineStr">
         <is>
-          <t>VISUAL CREATIONS, INC.</t>
+          <t>BORGERS USA CORP</t>
         </is>
       </c>
       <c r="K792" t="inlineStr">
         <is>
-          <t>VISCRE</t>
+          <t>BORUSA</t>
         </is>
       </c>
       <c r="L792" t="inlineStr">
         <is>
-          <t>20-461602300</t>
+          <t>65-117296500</t>
         </is>
       </c>
       <c r="M792" t="inlineStr">
         <is>
-          <t>2026-07-04 00:00:00</t>
+          <t>2026-07-02 00:00:00</t>
         </is>
       </c>
       <c r="N792" t="inlineStr">
@@ -66646,29 +66646,29 @@
       </c>
       <c r="O792" t="inlineStr">
         <is>
-          <t>FUJIAN ANTAI NEW ENERGY TECH CO LTD</t>
+          <t>AUTONEUM CZ S.R.O.</t>
         </is>
       </c>
       <c r="P792" t="inlineStr">
         <is>
-          <t>FUJIAN ANTAI NEW ENERGY TECH CO LTD</t>
+          <t>AUTONEUM CZ S.R.O.</t>
         </is>
       </c>
       <c r="Q792" t="inlineStr">
         <is>
-          <t>2026-06-02 00:00:00</t>
+          <t>2026-06-20 00:00:00</t>
         </is>
       </c>
     </row>
     <row r="793">
       <c r="A793" t="inlineStr">
         <is>
-          <t>2565996</t>
+          <t>2566367</t>
         </is>
       </c>
       <c r="B793" t="inlineStr">
         <is>
-          <t>EF4-0232280-6</t>
+          <t>EF4-0232744-1</t>
         </is>
       </c>
       <c r="C793" t="inlineStr">
@@ -66679,47 +66679,47 @@
       <c r="D793" t="inlineStr"/>
       <c r="E793" t="inlineStr">
         <is>
-          <t>9903.88.03</t>
+          <t>9903.03.06</t>
         </is>
       </c>
       <c r="F793" t="inlineStr">
         <is>
-          <t>ARTICLE OF CHINA,US NTE 20(F)</t>
+          <t>S122 EXCL,IRN/STL/ALUM,DERIV</t>
         </is>
       </c>
       <c r="G793" t="inlineStr">
         <is>
-          <t>002</t>
+          <t>004</t>
         </is>
       </c>
       <c r="H793" t="inlineStr">
         <is>
-          <t>9903.88.03</t>
+          <t>9903.03.06</t>
         </is>
       </c>
       <c r="I793" t="inlineStr">
         <is>
-          <t>9903.03.01,9403.99.9045</t>
+          <t>9903.74.11,9903.94.53,8708.29.5190</t>
         </is>
       </c>
       <c r="J793" t="inlineStr">
         <is>
-          <t>VISUAL CREATIONS, INC.</t>
+          <t>BORGERS USA CORP</t>
         </is>
       </c>
       <c r="K793" t="inlineStr">
         <is>
-          <t>VISCRE</t>
+          <t>BORUSA</t>
         </is>
       </c>
       <c r="L793" t="inlineStr">
         <is>
-          <t>20-461602300</t>
+          <t>65-117296500</t>
         </is>
       </c>
       <c r="M793" t="inlineStr">
         <is>
-          <t>2026-07-04 00:00:00</t>
+          <t>2026-07-02 00:00:00</t>
         </is>
       </c>
       <c r="N793" t="inlineStr">
@@ -66729,29 +66729,29 @@
       </c>
       <c r="O793" t="inlineStr">
         <is>
-          <t>FUJIAN ANTAI NEW ENERGY TECH CO LTD</t>
+          <t>AUTONEUM CZ S.R.O.</t>
         </is>
       </c>
       <c r="P793" t="inlineStr">
         <is>
-          <t>FUJIAN ANTAI NEW ENERGY TECH CO LTD</t>
+          <t>AUTONEUM CZ S.R.O.</t>
         </is>
       </c>
       <c r="Q793" t="inlineStr">
         <is>
-          <t>2026-06-02 00:00:00</t>
+          <t>2026-06-20 00:00:00</t>
         </is>
       </c>
     </row>
     <row r="794">
       <c r="A794" t="inlineStr">
         <is>
-          <t>2565996</t>
+          <t>2566367</t>
         </is>
       </c>
       <c r="B794" t="inlineStr">
         <is>
-          <t>EF4-0232280-6</t>
+          <t>EF4-0232744-1</t>
         </is>
       </c>
       <c r="C794" t="inlineStr">
@@ -66762,47 +66762,47 @@
       <c r="D794" t="inlineStr"/>
       <c r="E794" t="inlineStr">
         <is>
-          <t>9903.88.15</t>
+          <t>9903.03.06</t>
         </is>
       </c>
       <c r="F794" t="inlineStr">
         <is>
-          <t>ARTICLE OF CHINA,US NTE 20(R)</t>
+          <t>S122 EXCL,IRN/STL/ALUM,DERIV</t>
         </is>
       </c>
       <c r="G794" t="inlineStr">
         <is>
-          <t>003</t>
+          <t>005</t>
         </is>
       </c>
       <c r="H794" t="inlineStr">
         <is>
-          <t>9903.88.15</t>
+          <t>9903.03.06</t>
         </is>
       </c>
       <c r="I794" t="inlineStr">
         <is>
-          <t>9903.03.06,9903.82.09,8302.42.3065</t>
+          <t>9903.74.11,9903.94.53,8708.29.5190</t>
         </is>
       </c>
       <c r="J794" t="inlineStr">
         <is>
-          <t>VISUAL CREATIONS, INC.</t>
+          <t>BORGERS USA CORP</t>
         </is>
       </c>
       <c r="K794" t="inlineStr">
         <is>
-          <t>VISCRE</t>
+          <t>BORUSA</t>
         </is>
       </c>
       <c r="L794" t="inlineStr">
         <is>
-          <t>20-461602300</t>
+          <t>65-117296500</t>
         </is>
       </c>
       <c r="M794" t="inlineStr">
         <is>
-          <t>2026-07-04 00:00:00</t>
+          <t>2026-07-02 00:00:00</t>
         </is>
       </c>
       <c r="N794" t="inlineStr">
@@ -66812,29 +66812,29 @@
       </c>
       <c r="O794" t="inlineStr">
         <is>
-          <t>FUJIAN ANTAI NEW ENERGY TECH CO LTD</t>
+          <t>AUTONEUM CZ S.R.O.</t>
         </is>
       </c>
       <c r="P794" t="inlineStr">
         <is>
-          <t>FUJIAN ANTAI NEW ENERGY TECH CO LTD</t>
+          <t>AUTONEUM CZ S.R.O.</t>
         </is>
       </c>
       <c r="Q794" t="inlineStr">
         <is>
-          <t>2026-06-02 00:00:00</t>
+          <t>2026-06-20 00:00:00</t>
         </is>
       </c>
     </row>
     <row r="795">
       <c r="A795" t="inlineStr">
         <is>
-          <t>2565996</t>
+          <t>2565995</t>
         </is>
       </c>
       <c r="B795" t="inlineStr">
         <is>
-          <t>EF4-0232280-6</t>
+          <t>EF4-0232279-8</t>
         </is>
       </c>
       <c r="C795" t="inlineStr">
@@ -66855,7 +66855,7 @@
       </c>
       <c r="G795" t="inlineStr">
         <is>
-          <t>004</t>
+          <t>001</t>
         </is>
       </c>
       <c r="H795" t="inlineStr">
@@ -66865,7 +66865,7 @@
       </c>
       <c r="I795" t="inlineStr">
         <is>
-          <t>9903.03.06,9903.82.09,9403.20.0075</t>
+          <t>9903.03.01,9403.99.9045</t>
         </is>
       </c>
       <c r="J795" t="inlineStr">
@@ -66890,7 +66890,7 @@
       </c>
       <c r="N795" t="inlineStr">
         <is>
-          <t>2026-07-02 00:00:00</t>
+          <t>2026-07-04 00:00:00</t>
         </is>
       </c>
       <c r="O795" t="inlineStr">
@@ -66912,12 +66912,12 @@
     <row r="796">
       <c r="A796" t="inlineStr">
         <is>
-          <t>2565996</t>
+          <t>2565995</t>
         </is>
       </c>
       <c r="B796" t="inlineStr">
         <is>
-          <t>EF4-0232280-6</t>
+          <t>EF4-0232279-8</t>
         </is>
       </c>
       <c r="C796" t="inlineStr">
@@ -66928,27 +66928,27 @@
       <c r="D796" t="inlineStr"/>
       <c r="E796" t="inlineStr">
         <is>
-          <t>9903.88.03</t>
+          <t>9903.88.15</t>
         </is>
       </c>
       <c r="F796" t="inlineStr">
         <is>
-          <t>ARTICLE OF CHINA,US NTE 20(F)</t>
+          <t>ARTICLE OF CHINA,US NTE 20(R)</t>
         </is>
       </c>
       <c r="G796" t="inlineStr">
         <is>
-          <t>005</t>
+          <t>002</t>
         </is>
       </c>
       <c r="H796" t="inlineStr">
         <is>
-          <t>9903.88.03</t>
+          <t>9903.88.15</t>
         </is>
       </c>
       <c r="I796" t="inlineStr">
         <is>
-          <t>9903.03.01,9903.76.04,9403.91.0080</t>
+          <t>9903.03.01,3926.90.9989</t>
         </is>
       </c>
       <c r="J796" t="inlineStr">
@@ -66973,7 +66973,7 @@
       </c>
       <c r="N796" t="inlineStr">
         <is>
-          <t>2026-07-02 00:00:00</t>
+          <t>2026-07-04 00:00:00</t>
         </is>
       </c>
       <c r="O796" t="inlineStr">
@@ -66995,12 +66995,12 @@
     <row r="797">
       <c r="A797" t="inlineStr">
         <is>
-          <t>2566367</t>
+          <t>2565996</t>
         </is>
       </c>
       <c r="B797" t="inlineStr">
         <is>
-          <t>EF4-0232744-1</t>
+          <t>EF4-0232280-6</t>
         </is>
       </c>
       <c r="C797" t="inlineStr">
@@ -67011,12 +67011,12 @@
       <c r="D797" t="inlineStr"/>
       <c r="E797" t="inlineStr">
         <is>
-          <t>9903.03.06</t>
+          <t>9903.88.15</t>
         </is>
       </c>
       <c r="F797" t="inlineStr">
         <is>
-          <t>S122 EXCL,IRN/STL/ALUM,DERIV</t>
+          <t>ARTICLE OF CHINA,US NTE 20(R)</t>
         </is>
       </c>
       <c r="G797" t="inlineStr">
@@ -67026,64 +67026,64 @@
       </c>
       <c r="H797" t="inlineStr">
         <is>
-          <t>9903.03.06</t>
+          <t>9903.88.15</t>
         </is>
       </c>
       <c r="I797" t="inlineStr">
         <is>
-          <t>9903.74.11,9903.94.53,8708.29.5190</t>
+          <t>9903.03.01,3926.90.9989</t>
         </is>
       </c>
       <c r="J797" t="inlineStr">
         <is>
-          <t>BORGERS USA CORP</t>
+          <t>VISUAL CREATIONS, INC.</t>
         </is>
       </c>
       <c r="K797" t="inlineStr">
         <is>
-          <t>BORUSA</t>
+          <t>VISCRE</t>
         </is>
       </c>
       <c r="L797" t="inlineStr">
         <is>
-          <t>65-117296500</t>
+          <t>20-461602300</t>
         </is>
       </c>
       <c r="M797" t="inlineStr">
         <is>
-          <t>2026-07-02 00:00:00</t>
+          <t>2026-07-04 00:00:00</t>
         </is>
       </c>
       <c r="N797" t="inlineStr">
         <is>
-          <t>2026-07-02 00:00:00</t>
+          <t>2026-07-04 00:00:00</t>
         </is>
       </c>
       <c r="O797" t="inlineStr">
         <is>
-          <t>AUTONEUM CZ S.R.O.</t>
+          <t>FUJIAN ANTAI NEW ENERGY TECH CO LTD</t>
         </is>
       </c>
       <c r="P797" t="inlineStr">
         <is>
-          <t>AUTONEUM CZ S.R.O.</t>
+          <t>FUJIAN ANTAI NEW ENERGY TECH CO LTD</t>
         </is>
       </c>
       <c r="Q797" t="inlineStr">
         <is>
-          <t>2026-06-20 00:00:00</t>
+          <t>2026-06-02 00:00:00</t>
         </is>
       </c>
     </row>
     <row r="798">
       <c r="A798" t="inlineStr">
         <is>
-          <t>2566367</t>
+          <t>2565996</t>
         </is>
       </c>
       <c r="B798" t="inlineStr">
         <is>
-          <t>EF4-0232744-1</t>
+          <t>EF4-0232280-6</t>
         </is>
       </c>
       <c r="C798" t="inlineStr">
@@ -67094,12 +67094,12 @@
       <c r="D798" t="inlineStr"/>
       <c r="E798" t="inlineStr">
         <is>
-          <t>9903.03.06</t>
+          <t>9903.88.03</t>
         </is>
       </c>
       <c r="F798" t="inlineStr">
         <is>
-          <t>S122 EXCL,IRN/STL/ALUM,DERIV</t>
+          <t>ARTICLE OF CHINA,US NTE 20(F)</t>
         </is>
       </c>
       <c r="G798" t="inlineStr">
@@ -67109,64 +67109,64 @@
       </c>
       <c r="H798" t="inlineStr">
         <is>
-          <t>9903.03.06</t>
+          <t>9903.88.03</t>
         </is>
       </c>
       <c r="I798" t="inlineStr">
         <is>
-          <t>9903.74.11,9903.94.53,8708.29.5190</t>
+          <t>9903.03.01,9403.99.9045</t>
         </is>
       </c>
       <c r="J798" t="inlineStr">
         <is>
-          <t>BORGERS USA CORP</t>
+          <t>VISUAL CREATIONS, INC.</t>
         </is>
       </c>
       <c r="K798" t="inlineStr">
         <is>
-          <t>BORUSA</t>
+          <t>VISCRE</t>
         </is>
       </c>
       <c r="L798" t="inlineStr">
         <is>
-          <t>65-117296500</t>
+          <t>20-461602300</t>
         </is>
       </c>
       <c r="M798" t="inlineStr">
         <is>
-          <t>2026-07-02 00:00:00</t>
+          <t>2026-07-04 00:00:00</t>
         </is>
       </c>
       <c r="N798" t="inlineStr">
         <is>
-          <t>2026-07-02 00:00:00</t>
+          <t>2026-07-04 00:00:00</t>
         </is>
       </c>
       <c r="O798" t="inlineStr">
         <is>
-          <t>AUTONEUM CZ S.R.O.</t>
+          <t>FUJIAN ANTAI NEW ENERGY TECH CO LTD</t>
         </is>
       </c>
       <c r="P798" t="inlineStr">
         <is>
-          <t>AUTONEUM CZ S.R.O.</t>
+          <t>FUJIAN ANTAI NEW ENERGY TECH CO LTD</t>
         </is>
       </c>
       <c r="Q798" t="inlineStr">
         <is>
-          <t>2026-06-20 00:00:00</t>
+          <t>2026-06-02 00:00:00</t>
         </is>
       </c>
     </row>
     <row r="799">
       <c r="A799" t="inlineStr">
         <is>
-          <t>2566367</t>
+          <t>2565996</t>
         </is>
       </c>
       <c r="B799" t="inlineStr">
         <is>
-          <t>EF4-0232744-1</t>
+          <t>EF4-0232280-6</t>
         </is>
       </c>
       <c r="C799" t="inlineStr">
@@ -67177,12 +67177,12 @@
       <c r="D799" t="inlineStr"/>
       <c r="E799" t="inlineStr">
         <is>
-          <t>9903.03.06</t>
+          <t>9903.88.15</t>
         </is>
       </c>
       <c r="F799" t="inlineStr">
         <is>
-          <t>S122 EXCL,IRN/STL/ALUM,DERIV</t>
+          <t>ARTICLE OF CHINA,US NTE 20(R)</t>
         </is>
       </c>
       <c r="G799" t="inlineStr">
@@ -67192,64 +67192,64 @@
       </c>
       <c r="H799" t="inlineStr">
         <is>
-          <t>9903.03.06</t>
+          <t>9903.88.15</t>
         </is>
       </c>
       <c r="I799" t="inlineStr">
         <is>
-          <t>9903.74.11,9903.94.53,8708.29.5190</t>
+          <t>9903.03.06,9903.82.09,8302.42.3065</t>
         </is>
       </c>
       <c r="J799" t="inlineStr">
         <is>
-          <t>BORGERS USA CORP</t>
+          <t>VISUAL CREATIONS, INC.</t>
         </is>
       </c>
       <c r="K799" t="inlineStr">
         <is>
-          <t>BORUSA</t>
+          <t>VISCRE</t>
         </is>
       </c>
       <c r="L799" t="inlineStr">
         <is>
-          <t>65-117296500</t>
+          <t>20-461602300</t>
         </is>
       </c>
       <c r="M799" t="inlineStr">
         <is>
-          <t>2026-07-02 00:00:00</t>
+          <t>2026-07-04 00:00:00</t>
         </is>
       </c>
       <c r="N799" t="inlineStr">
         <is>
-          <t>2026-07-02 00:00:00</t>
+          <t>2026-07-04 00:00:00</t>
         </is>
       </c>
       <c r="O799" t="inlineStr">
         <is>
-          <t>AUTONEUM CZ S.R.O.</t>
+          <t>FUJIAN ANTAI NEW ENERGY TECH CO LTD</t>
         </is>
       </c>
       <c r="P799" t="inlineStr">
         <is>
-          <t>AUTONEUM CZ S.R.O.</t>
+          <t>FUJIAN ANTAI NEW ENERGY TECH CO LTD</t>
         </is>
       </c>
       <c r="Q799" t="inlineStr">
         <is>
-          <t>2026-06-20 00:00:00</t>
+          <t>2026-06-02 00:00:00</t>
         </is>
       </c>
     </row>
     <row r="800">
       <c r="A800" t="inlineStr">
         <is>
-          <t>2566367</t>
+          <t>2565996</t>
         </is>
       </c>
       <c r="B800" t="inlineStr">
         <is>
-          <t>EF4-0232744-1</t>
+          <t>EF4-0232280-6</t>
         </is>
       </c>
       <c r="C800" t="inlineStr">
@@ -67260,12 +67260,12 @@
       <c r="D800" t="inlineStr"/>
       <c r="E800" t="inlineStr">
         <is>
-          <t>9903.03.06</t>
+          <t>9903.88.03</t>
         </is>
       </c>
       <c r="F800" t="inlineStr">
         <is>
-          <t>S122 EXCL,IRN/STL/ALUM,DERIV</t>
+          <t>ARTICLE OF CHINA,US NTE 20(F)</t>
         </is>
       </c>
       <c r="G800" t="inlineStr">
@@ -67275,64 +67275,64 @@
       </c>
       <c r="H800" t="inlineStr">
         <is>
-          <t>9903.03.06</t>
+          <t>9903.88.03</t>
         </is>
       </c>
       <c r="I800" t="inlineStr">
         <is>
-          <t>9903.74.11,9903.94.53,8708.29.5190</t>
+          <t>9903.03.06,9903.82.09,9403.20.0075</t>
         </is>
       </c>
       <c r="J800" t="inlineStr">
         <is>
-          <t>BORGERS USA CORP</t>
+          <t>VISUAL CREATIONS, INC.</t>
         </is>
       </c>
       <c r="K800" t="inlineStr">
         <is>
-          <t>BORUSA</t>
+          <t>VISCRE</t>
         </is>
       </c>
       <c r="L800" t="inlineStr">
         <is>
-          <t>65-117296500</t>
+          <t>20-461602300</t>
         </is>
       </c>
       <c r="M800" t="inlineStr">
         <is>
-          <t>2026-07-02 00:00:00</t>
+          <t>2026-07-04 00:00:00</t>
         </is>
       </c>
       <c r="N800" t="inlineStr">
         <is>
-          <t>2026-07-02 00:00:00</t>
+          <t>2026-07-04 00:00:00</t>
         </is>
       </c>
       <c r="O800" t="inlineStr">
         <is>
-          <t>AUTONEUM CZ S.R.O.</t>
+          <t>FUJIAN ANTAI NEW ENERGY TECH CO LTD</t>
         </is>
       </c>
       <c r="P800" t="inlineStr">
         <is>
-          <t>AUTONEUM CZ S.R.O.</t>
+          <t>FUJIAN ANTAI NEW ENERGY TECH CO LTD</t>
         </is>
       </c>
       <c r="Q800" t="inlineStr">
         <is>
-          <t>2026-06-20 00:00:00</t>
+          <t>2026-06-02 00:00:00</t>
         </is>
       </c>
     </row>
     <row r="801">
       <c r="A801" t="inlineStr">
         <is>
-          <t>2566367</t>
+          <t>2565996</t>
         </is>
       </c>
       <c r="B801" t="inlineStr">
         <is>
-          <t>EF4-0232744-1</t>
+          <t>EF4-0232280-6</t>
         </is>
       </c>
       <c r="C801" t="inlineStr">
@@ -67343,12 +67343,12 @@
       <c r="D801" t="inlineStr"/>
       <c r="E801" t="inlineStr">
         <is>
-          <t>9903.03.06</t>
+          <t>9903.88.03</t>
         </is>
       </c>
       <c r="F801" t="inlineStr">
         <is>
-          <t>S122 EXCL,IRN/STL/ALUM,DERIV</t>
+          <t>ARTICLE OF CHINA,US NTE 20(F)</t>
         </is>
       </c>
       <c r="G801" t="inlineStr">
@@ -67358,52 +67358,301 @@
       </c>
       <c r="H801" t="inlineStr">
         <is>
-          <t>9903.03.06</t>
+          <t>9903.88.03</t>
         </is>
       </c>
       <c r="I801" t="inlineStr">
         <is>
-          <t>9903.74.11,9903.94.53,8708.29.5190</t>
+          <t>9903.03.01,9903.76.04,9403.91.0080</t>
         </is>
       </c>
       <c r="J801" t="inlineStr">
         <is>
-          <t>BORGERS USA CORP</t>
+          <t>VISUAL CREATIONS, INC.</t>
         </is>
       </c>
       <c r="K801" t="inlineStr">
         <is>
-          <t>BORUSA</t>
+          <t>VISCRE</t>
         </is>
       </c>
       <c r="L801" t="inlineStr">
         <is>
-          <t>65-117296500</t>
+          <t>20-461602300</t>
         </is>
       </c>
       <c r="M801" t="inlineStr">
         <is>
-          <t>2026-07-02 00:00:00</t>
+          <t>2026-07-04 00:00:00</t>
         </is>
       </c>
       <c r="N801" t="inlineStr">
         <is>
-          <t>2026-07-02 00:00:00</t>
+          <t>2026-07-04 00:00:00</t>
         </is>
       </c>
       <c r="O801" t="inlineStr">
         <is>
-          <t>AUTONEUM CZ S.R.O.</t>
+          <t>FUJIAN ANTAI NEW ENERGY TECH CO LTD</t>
         </is>
       </c>
       <c r="P801" t="inlineStr">
         <is>
-          <t>AUTONEUM CZ S.R.O.</t>
+          <t>FUJIAN ANTAI NEW ENERGY TECH CO LTD</t>
         </is>
       </c>
       <c r="Q801" t="inlineStr">
         <is>
-          <t>2026-06-20 00:00:00</t>
+          <t>2026-06-02 00:00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="802">
+      <c r="A802" t="inlineStr">
+        <is>
+          <t>2566192</t>
+        </is>
+      </c>
+      <c r="B802" t="inlineStr">
+        <is>
+          <t>EF4-0232351-5</t>
+        </is>
+      </c>
+      <c r="C802" t="inlineStr">
+        <is>
+          <t>Vessel, Container</t>
+        </is>
+      </c>
+      <c r="D802" t="inlineStr"/>
+      <c r="E802" t="inlineStr">
+        <is>
+          <t>9903.03.03</t>
+        </is>
+      </c>
+      <c r="F802" t="inlineStr">
+        <is>
+          <t>S122 -EXCLUSION-EXEMPTED PRDTS</t>
+        </is>
+      </c>
+      <c r="G802" t="inlineStr">
+        <is>
+          <t>001</t>
+        </is>
+      </c>
+      <c r="H802" t="inlineStr">
+        <is>
+          <t>9903.03.03</t>
+        </is>
+      </c>
+      <c r="I802" t="inlineStr">
+        <is>
+          <t>1108.14.0000</t>
+        </is>
+      </c>
+      <c r="J802" t="inlineStr">
+        <is>
+          <t>ROYAL INGREDIENTS GROUP BV</t>
+        </is>
+      </c>
+      <c r="K802" t="inlineStr">
+        <is>
+          <t>ROYINGRE</t>
+        </is>
+      </c>
+      <c r="L802" t="inlineStr">
+        <is>
+          <t>074601-00962</t>
+        </is>
+      </c>
+      <c r="M802" t="inlineStr">
+        <is>
+          <t>2026-07-03 00:00:00</t>
+        </is>
+      </c>
+      <c r="N802" t="inlineStr">
+        <is>
+          <t>2026-07-04 00:00:00</t>
+        </is>
+      </c>
+      <c r="O802" t="inlineStr">
+        <is>
+          <t>SANGUAN WONGSE STARCH CO., LTD.</t>
+        </is>
+      </c>
+      <c r="P802" t="inlineStr">
+        <is>
+          <t>SANGUAN WONGSE STARCH CO., LTD.</t>
+        </is>
+      </c>
+      <c r="Q802" t="inlineStr">
+        <is>
+          <t>2026-06-05 00:00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="803">
+      <c r="A803" t="inlineStr">
+        <is>
+          <t>2566349</t>
+        </is>
+      </c>
+      <c r="B803" t="inlineStr">
+        <is>
+          <t>EF4-0232573-4</t>
+        </is>
+      </c>
+      <c r="C803" t="inlineStr">
+        <is>
+          <t>Vessel, Container</t>
+        </is>
+      </c>
+      <c r="D803" t="inlineStr"/>
+      <c r="E803" t="inlineStr">
+        <is>
+          <t>9903.03.01</t>
+        </is>
+      </c>
+      <c r="F803" t="inlineStr"/>
+      <c r="G803" t="inlineStr">
+        <is>
+          <t>001</t>
+        </is>
+      </c>
+      <c r="H803" t="inlineStr">
+        <is>
+          <t>9903.03.01</t>
+        </is>
+      </c>
+      <c r="I803" t="inlineStr">
+        <is>
+          <t>1108.12.0010</t>
+        </is>
+      </c>
+      <c r="J803" t="inlineStr">
+        <is>
+          <t>ROYAL INGREDIENTS GROUP BV</t>
+        </is>
+      </c>
+      <c r="K803" t="inlineStr">
+        <is>
+          <t>ROYINGRE</t>
+        </is>
+      </c>
+      <c r="L803" t="inlineStr">
+        <is>
+          <t>074601-00962</t>
+        </is>
+      </c>
+      <c r="M803" t="inlineStr">
+        <is>
+          <t>2026-07-05 00:00:00</t>
+        </is>
+      </c>
+      <c r="N803" t="inlineStr">
+        <is>
+          <t>2026-07-04 00:00:00</t>
+        </is>
+      </c>
+      <c r="O803" t="inlineStr">
+        <is>
+          <t>TAT NISASTA INS SAN TIC AS</t>
+        </is>
+      </c>
+      <c r="P803" t="inlineStr">
+        <is>
+          <t>TAT NISASTA INS SAN TIC AS</t>
+        </is>
+      </c>
+      <c r="Q803" t="inlineStr">
+        <is>
+          <t>2026-06-13 00:00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="804">
+      <c r="A804" t="inlineStr">
+        <is>
+          <t>2566272</t>
+        </is>
+      </c>
+      <c r="B804" t="inlineStr">
+        <is>
+          <t>EF4-0232670-8</t>
+        </is>
+      </c>
+      <c r="C804" t="inlineStr">
+        <is>
+          <t>Vessel, Container</t>
+        </is>
+      </c>
+      <c r="D804" t="inlineStr">
+        <is>
+          <t>V1626472883</t>
+        </is>
+      </c>
+      <c r="E804" t="inlineStr">
+        <is>
+          <t>9903.03.01</t>
+        </is>
+      </c>
+      <c r="F804" t="inlineStr">
+        <is>
+          <t>SECTION 122 - 10% DUTY</t>
+        </is>
+      </c>
+      <c r="G804" t="inlineStr">
+        <is>
+          <t>001</t>
+        </is>
+      </c>
+      <c r="H804" t="inlineStr">
+        <is>
+          <t>9903.03.01</t>
+        </is>
+      </c>
+      <c r="I804" t="inlineStr">
+        <is>
+          <t>1702.30.4085</t>
+        </is>
+      </c>
+      <c r="J804" t="inlineStr">
+        <is>
+          <t>ROYAL INGREDIENTS GROUP BV</t>
+        </is>
+      </c>
+      <c r="K804" t="inlineStr">
+        <is>
+          <t>ROYINGRE</t>
+        </is>
+      </c>
+      <c r="L804" t="inlineStr">
+        <is>
+          <t>074601-00962</t>
+        </is>
+      </c>
+      <c r="M804" t="inlineStr">
+        <is>
+          <t>2026-07-05 00:00:00</t>
+        </is>
+      </c>
+      <c r="N804" t="inlineStr">
+        <is>
+          <t>2026-07-04 00:00:00</t>
+        </is>
+      </c>
+      <c r="O804" t="inlineStr">
+        <is>
+          <t>AK NISASTA SANAYI VE TICARET AS</t>
+        </is>
+      </c>
+      <c r="P804" t="inlineStr">
+        <is>
+          <t>AK NISASTA SANAYI VE TICARET AS</t>
+        </is>
+      </c>
+      <c r="Q804" t="inlineStr">
+        <is>
+          <t>2026-06-19 00:00:00</t>
         </is>
       </c>
     </row>

--- a/trimika_data.xlsx
+++ b/trimika_data.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q804"/>
+  <dimension ref="A1:Q828"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -67656,6 +67656,2018 @@
         </is>
       </c>
     </row>
+    <row r="805">
+      <c r="A805" t="inlineStr">
+        <is>
+          <t>2565992</t>
+        </is>
+      </c>
+      <c r="B805" t="inlineStr">
+        <is>
+          <t>EF4-0232152-7</t>
+        </is>
+      </c>
+      <c r="C805" t="inlineStr">
+        <is>
+          <t>Vessel, Container</t>
+        </is>
+      </c>
+      <c r="D805" t="inlineStr"/>
+      <c r="E805" t="inlineStr">
+        <is>
+          <t>9903.03.01</t>
+        </is>
+      </c>
+      <c r="F805" t="inlineStr">
+        <is>
+          <t>SECTION 122 - 10% DUTY</t>
+        </is>
+      </c>
+      <c r="G805" t="inlineStr">
+        <is>
+          <t>001</t>
+        </is>
+      </c>
+      <c r="H805" t="inlineStr">
+        <is>
+          <t>9903.03.01</t>
+        </is>
+      </c>
+      <c r="I805" t="inlineStr">
+        <is>
+          <t>5903.90.3090</t>
+        </is>
+      </c>
+      <c r="J805" t="inlineStr">
+        <is>
+          <t>VEER CORPORATIONS INC</t>
+        </is>
+      </c>
+      <c r="K805" t="inlineStr">
+        <is>
+          <t>VEECOR01</t>
+        </is>
+      </c>
+      <c r="L805" t="inlineStr">
+        <is>
+          <t>99-106989200</t>
+        </is>
+      </c>
+      <c r="M805" t="inlineStr">
+        <is>
+          <t>2026-07-05 00:00:00</t>
+        </is>
+      </c>
+      <c r="N805" t="inlineStr">
+        <is>
+          <t>2026-07-06 00:00:00</t>
+        </is>
+      </c>
+      <c r="O805" t="inlineStr">
+        <is>
+          <t>VEER PLASTIC PVT LTD</t>
+        </is>
+      </c>
+      <c r="P805" t="inlineStr">
+        <is>
+          <t>VEER PLASTIC PVT LTD</t>
+        </is>
+      </c>
+      <c r="Q805" t="inlineStr">
+        <is>
+          <t>2026-05-27 00:00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="806">
+      <c r="A806" t="inlineStr">
+        <is>
+          <t>2566077</t>
+        </is>
+      </c>
+      <c r="B806" t="inlineStr">
+        <is>
+          <t>EF4-0232194-9</t>
+        </is>
+      </c>
+      <c r="C806" t="inlineStr">
+        <is>
+          <t>Vessel, Container</t>
+        </is>
+      </c>
+      <c r="D806" t="inlineStr"/>
+      <c r="E806" t="inlineStr">
+        <is>
+          <t>9903.03.01</t>
+        </is>
+      </c>
+      <c r="F806" t="inlineStr">
+        <is>
+          <t>SECTION 122 - 10% DUTY</t>
+        </is>
+      </c>
+      <c r="G806" t="inlineStr">
+        <is>
+          <t>001</t>
+        </is>
+      </c>
+      <c r="H806" t="inlineStr">
+        <is>
+          <t>9903.03.01</t>
+        </is>
+      </c>
+      <c r="I806" t="inlineStr">
+        <is>
+          <t>5407.20.0000</t>
+        </is>
+      </c>
+      <c r="J806" t="inlineStr">
+        <is>
+          <t>VEER CORPORATIONS INC</t>
+        </is>
+      </c>
+      <c r="K806" t="inlineStr">
+        <is>
+          <t>VEECOR01</t>
+        </is>
+      </c>
+      <c r="L806" t="inlineStr">
+        <is>
+          <t>99-106989200</t>
+        </is>
+      </c>
+      <c r="M806" t="inlineStr">
+        <is>
+          <t>2026-07-06 00:00:00</t>
+        </is>
+      </c>
+      <c r="N806" t="inlineStr">
+        <is>
+          <t>2026-07-06 00:00:00</t>
+        </is>
+      </c>
+      <c r="O806" t="inlineStr">
+        <is>
+          <t>VEER PLASTIC PVT LTD</t>
+        </is>
+      </c>
+      <c r="P806" t="inlineStr">
+        <is>
+          <t>VEER PLASTIC PVT LTD</t>
+        </is>
+      </c>
+      <c r="Q806" t="inlineStr">
+        <is>
+          <t>2026-05-27 00:00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="807">
+      <c r="A807" t="inlineStr">
+        <is>
+          <t>2566118</t>
+        </is>
+      </c>
+      <c r="B807" t="inlineStr">
+        <is>
+          <t>EF4-0232255-8</t>
+        </is>
+      </c>
+      <c r="C807" t="inlineStr">
+        <is>
+          <t>Vessel, Container</t>
+        </is>
+      </c>
+      <c r="D807" t="inlineStr"/>
+      <c r="E807" t="inlineStr">
+        <is>
+          <t>9903.88.15</t>
+        </is>
+      </c>
+      <c r="F807" t="inlineStr">
+        <is>
+          <t>ARTICLE OF CHINA,US NTE 20(R)</t>
+        </is>
+      </c>
+      <c r="G807" t="inlineStr">
+        <is>
+          <t>001</t>
+        </is>
+      </c>
+      <c r="H807" t="inlineStr">
+        <is>
+          <t>9903.88.15</t>
+        </is>
+      </c>
+      <c r="I807" t="inlineStr">
+        <is>
+          <t>9903.03.06,9903.82.09,8302.42.3065</t>
+        </is>
+      </c>
+      <c r="J807" t="inlineStr">
+        <is>
+          <t>VISUAL CREATIONS, INC.</t>
+        </is>
+      </c>
+      <c r="K807" t="inlineStr">
+        <is>
+          <t>VISCRE</t>
+        </is>
+      </c>
+      <c r="L807" t="inlineStr">
+        <is>
+          <t>20-461602300</t>
+        </is>
+      </c>
+      <c r="M807" t="inlineStr">
+        <is>
+          <t>2026-07-05 00:00:00</t>
+        </is>
+      </c>
+      <c r="N807" t="inlineStr">
+        <is>
+          <t>2026-07-06 00:00:00</t>
+        </is>
+      </c>
+      <c r="O807" t="inlineStr">
+        <is>
+          <t>FUJIAN ANTAI NEW ENERGY TECH CO LTD</t>
+        </is>
+      </c>
+      <c r="P807" t="inlineStr">
+        <is>
+          <t>FUJIAN ANTAI NEW ENERGY TECH CO LTD</t>
+        </is>
+      </c>
+      <c r="Q807" t="inlineStr">
+        <is>
+          <t>2026-05-31 00:00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="808">
+      <c r="A808" t="inlineStr">
+        <is>
+          <t>2566118</t>
+        </is>
+      </c>
+      <c r="B808" t="inlineStr">
+        <is>
+          <t>EF4-0232255-8</t>
+        </is>
+      </c>
+      <c r="C808" t="inlineStr">
+        <is>
+          <t>Vessel, Container</t>
+        </is>
+      </c>
+      <c r="D808" t="inlineStr"/>
+      <c r="E808" t="inlineStr">
+        <is>
+          <t>9903.88.03</t>
+        </is>
+      </c>
+      <c r="F808" t="inlineStr">
+        <is>
+          <t>ARTICLE OF CHINA,US NTE 20(F)</t>
+        </is>
+      </c>
+      <c r="G808" t="inlineStr">
+        <is>
+          <t>002</t>
+        </is>
+      </c>
+      <c r="H808" t="inlineStr">
+        <is>
+          <t>9903.88.03</t>
+        </is>
+      </c>
+      <c r="I808" t="inlineStr">
+        <is>
+          <t>9903.03.01,9403.99.9045</t>
+        </is>
+      </c>
+      <c r="J808" t="inlineStr">
+        <is>
+          <t>VISUAL CREATIONS, INC.</t>
+        </is>
+      </c>
+      <c r="K808" t="inlineStr">
+        <is>
+          <t>VISCRE</t>
+        </is>
+      </c>
+      <c r="L808" t="inlineStr">
+        <is>
+          <t>20-461602300</t>
+        </is>
+      </c>
+      <c r="M808" t="inlineStr">
+        <is>
+          <t>2026-07-05 00:00:00</t>
+        </is>
+      </c>
+      <c r="N808" t="inlineStr">
+        <is>
+          <t>2026-07-06 00:00:00</t>
+        </is>
+      </c>
+      <c r="O808" t="inlineStr">
+        <is>
+          <t>FUJIAN ANTAI NEW ENERGY TECH CO LTD</t>
+        </is>
+      </c>
+      <c r="P808" t="inlineStr">
+        <is>
+          <t>FUJIAN ANTAI NEW ENERGY TECH CO LTD</t>
+        </is>
+      </c>
+      <c r="Q808" t="inlineStr">
+        <is>
+          <t>2026-05-31 00:00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="809">
+      <c r="A809" t="inlineStr">
+        <is>
+          <t>2566118</t>
+        </is>
+      </c>
+      <c r="B809" t="inlineStr">
+        <is>
+          <t>EF4-0232255-8</t>
+        </is>
+      </c>
+      <c r="C809" t="inlineStr">
+        <is>
+          <t>Vessel, Container</t>
+        </is>
+      </c>
+      <c r="D809" t="inlineStr"/>
+      <c r="E809" t="inlineStr">
+        <is>
+          <t>9903.88.03</t>
+        </is>
+      </c>
+      <c r="F809" t="inlineStr">
+        <is>
+          <t>ARTICLE OF CHINA,US NTE 20(F)</t>
+        </is>
+      </c>
+      <c r="G809" t="inlineStr">
+        <is>
+          <t>003</t>
+        </is>
+      </c>
+      <c r="H809" t="inlineStr">
+        <is>
+          <t>9903.88.03</t>
+        </is>
+      </c>
+      <c r="I809" t="inlineStr">
+        <is>
+          <t>9903.03.01,9903.76.04,9403.91.0080</t>
+        </is>
+      </c>
+      <c r="J809" t="inlineStr">
+        <is>
+          <t>VISUAL CREATIONS, INC.</t>
+        </is>
+      </c>
+      <c r="K809" t="inlineStr">
+        <is>
+          <t>VISCRE</t>
+        </is>
+      </c>
+      <c r="L809" t="inlineStr">
+        <is>
+          <t>20-461602300</t>
+        </is>
+      </c>
+      <c r="M809" t="inlineStr">
+        <is>
+          <t>2026-07-05 00:00:00</t>
+        </is>
+      </c>
+      <c r="N809" t="inlineStr">
+        <is>
+          <t>2026-07-06 00:00:00</t>
+        </is>
+      </c>
+      <c r="O809" t="inlineStr">
+        <is>
+          <t>FUJIAN ANTAI NEW ENERGY TECH CO LTD</t>
+        </is>
+      </c>
+      <c r="P809" t="inlineStr">
+        <is>
+          <t>FUJIAN ANTAI NEW ENERGY TECH CO LTD</t>
+        </is>
+      </c>
+      <c r="Q809" t="inlineStr">
+        <is>
+          <t>2026-05-31 00:00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="810">
+      <c r="A810" t="inlineStr">
+        <is>
+          <t>2566127</t>
+        </is>
+      </c>
+      <c r="B810" t="inlineStr">
+        <is>
+          <t>EF4-0232257-4</t>
+        </is>
+      </c>
+      <c r="C810" t="inlineStr">
+        <is>
+          <t>Vessel, Container</t>
+        </is>
+      </c>
+      <c r="D810" t="inlineStr"/>
+      <c r="E810" t="inlineStr">
+        <is>
+          <t>9903.88.03</t>
+        </is>
+      </c>
+      <c r="F810" t="inlineStr">
+        <is>
+          <t>ARTICLE OF CHINA,US NTE 20(F)</t>
+        </is>
+      </c>
+      <c r="G810" t="inlineStr">
+        <is>
+          <t>001</t>
+        </is>
+      </c>
+      <c r="H810" t="inlineStr">
+        <is>
+          <t>9903.88.03</t>
+        </is>
+      </c>
+      <c r="I810" t="inlineStr">
+        <is>
+          <t>9903.03.01,9403.99.9045</t>
+        </is>
+      </c>
+      <c r="J810" t="inlineStr">
+        <is>
+          <t>VISUAL CREATIONS, INC.</t>
+        </is>
+      </c>
+      <c r="K810" t="inlineStr">
+        <is>
+          <t>VISCRE</t>
+        </is>
+      </c>
+      <c r="L810" t="inlineStr">
+        <is>
+          <t>20-461602300</t>
+        </is>
+      </c>
+      <c r="M810" t="inlineStr">
+        <is>
+          <t>2026-07-05 00:00:00</t>
+        </is>
+      </c>
+      <c r="N810" t="inlineStr">
+        <is>
+          <t>2026-07-06 00:00:00</t>
+        </is>
+      </c>
+      <c r="O810" t="inlineStr">
+        <is>
+          <t>FUJIAN ANTAI NEW ENERGY TECH CO LTD</t>
+        </is>
+      </c>
+      <c r="P810" t="inlineStr">
+        <is>
+          <t>FUJIAN ANTAI NEW ENERGY TECH CO LTD</t>
+        </is>
+      </c>
+      <c r="Q810" t="inlineStr">
+        <is>
+          <t>2026-05-31 00:00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="811">
+      <c r="A811" t="inlineStr">
+        <is>
+          <t>2566127</t>
+        </is>
+      </c>
+      <c r="B811" t="inlineStr">
+        <is>
+          <t>EF4-0232257-4</t>
+        </is>
+      </c>
+      <c r="C811" t="inlineStr">
+        <is>
+          <t>Vessel, Container</t>
+        </is>
+      </c>
+      <c r="D811" t="inlineStr"/>
+      <c r="E811" t="inlineStr">
+        <is>
+          <t>9903.88.03</t>
+        </is>
+      </c>
+      <c r="F811" t="inlineStr">
+        <is>
+          <t>ARTICLE OF CHINA,US NTE 20(F)</t>
+        </is>
+      </c>
+      <c r="G811" t="inlineStr">
+        <is>
+          <t>002</t>
+        </is>
+      </c>
+      <c r="H811" t="inlineStr">
+        <is>
+          <t>9903.88.03</t>
+        </is>
+      </c>
+      <c r="I811" t="inlineStr">
+        <is>
+          <t>9903.03.06,9903.82.02,7318.19.0000</t>
+        </is>
+      </c>
+      <c r="J811" t="inlineStr">
+        <is>
+          <t>VISUAL CREATIONS, INC.</t>
+        </is>
+      </c>
+      <c r="K811" t="inlineStr">
+        <is>
+          <t>VISCRE</t>
+        </is>
+      </c>
+      <c r="L811" t="inlineStr">
+        <is>
+          <t>20-461602300</t>
+        </is>
+      </c>
+      <c r="M811" t="inlineStr">
+        <is>
+          <t>2026-07-05 00:00:00</t>
+        </is>
+      </c>
+      <c r="N811" t="inlineStr">
+        <is>
+          <t>2026-07-06 00:00:00</t>
+        </is>
+      </c>
+      <c r="O811" t="inlineStr">
+        <is>
+          <t>FUJIAN ANTAI NEW ENERGY TECH CO LTD</t>
+        </is>
+      </c>
+      <c r="P811" t="inlineStr">
+        <is>
+          <t>FUJIAN ANTAI NEW ENERGY TECH CO LTD</t>
+        </is>
+      </c>
+      <c r="Q811" t="inlineStr">
+        <is>
+          <t>2026-05-31 00:00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="812">
+      <c r="A812" t="inlineStr">
+        <is>
+          <t>2566127</t>
+        </is>
+      </c>
+      <c r="B812" t="inlineStr">
+        <is>
+          <t>EF4-0232257-4</t>
+        </is>
+      </c>
+      <c r="C812" t="inlineStr">
+        <is>
+          <t>Vessel, Container</t>
+        </is>
+      </c>
+      <c r="D812" t="inlineStr"/>
+      <c r="E812" t="inlineStr">
+        <is>
+          <t>9903.88.03</t>
+        </is>
+      </c>
+      <c r="F812" t="inlineStr">
+        <is>
+          <t>ARTICLE OF CHINA,US NTE 20(F)</t>
+        </is>
+      </c>
+      <c r="G812" t="inlineStr">
+        <is>
+          <t>003</t>
+        </is>
+      </c>
+      <c r="H812" t="inlineStr">
+        <is>
+          <t>9903.88.03</t>
+        </is>
+      </c>
+      <c r="I812" t="inlineStr">
+        <is>
+          <t>9903.03.01,9405.42.8440</t>
+        </is>
+      </c>
+      <c r="J812" t="inlineStr">
+        <is>
+          <t>VISUAL CREATIONS, INC.</t>
+        </is>
+      </c>
+      <c r="K812" t="inlineStr">
+        <is>
+          <t>VISCRE</t>
+        </is>
+      </c>
+      <c r="L812" t="inlineStr">
+        <is>
+          <t>20-461602300</t>
+        </is>
+      </c>
+      <c r="M812" t="inlineStr">
+        <is>
+          <t>2026-07-05 00:00:00</t>
+        </is>
+      </c>
+      <c r="N812" t="inlineStr">
+        <is>
+          <t>2026-07-06 00:00:00</t>
+        </is>
+      </c>
+      <c r="O812" t="inlineStr">
+        <is>
+          <t>FUJIAN ANTAI NEW ENERGY TECH CO LTD</t>
+        </is>
+      </c>
+      <c r="P812" t="inlineStr">
+        <is>
+          <t>FUJIAN ANTAI NEW ENERGY TECH CO LTD</t>
+        </is>
+      </c>
+      <c r="Q812" t="inlineStr">
+        <is>
+          <t>2026-05-31 00:00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="813">
+      <c r="A813" t="inlineStr">
+        <is>
+          <t>2566127</t>
+        </is>
+      </c>
+      <c r="B813" t="inlineStr">
+        <is>
+          <t>EF4-0232257-4</t>
+        </is>
+      </c>
+      <c r="C813" t="inlineStr">
+        <is>
+          <t>Vessel, Container</t>
+        </is>
+      </c>
+      <c r="D813" t="inlineStr"/>
+      <c r="E813" t="inlineStr">
+        <is>
+          <t>9903.88.03</t>
+        </is>
+      </c>
+      <c r="F813" t="inlineStr">
+        <is>
+          <t>ARTICLE OF CHINA,US NTE 20(F)</t>
+        </is>
+      </c>
+      <c r="G813" t="inlineStr">
+        <is>
+          <t>004</t>
+        </is>
+      </c>
+      <c r="H813" t="inlineStr">
+        <is>
+          <t>9903.88.03</t>
+        </is>
+      </c>
+      <c r="I813" t="inlineStr">
+        <is>
+          <t>9903.03.01,9903.76.04,9403.60.8093</t>
+        </is>
+      </c>
+      <c r="J813" t="inlineStr">
+        <is>
+          <t>VISUAL CREATIONS, INC.</t>
+        </is>
+      </c>
+      <c r="K813" t="inlineStr">
+        <is>
+          <t>VISCRE</t>
+        </is>
+      </c>
+      <c r="L813" t="inlineStr">
+        <is>
+          <t>20-461602300</t>
+        </is>
+      </c>
+      <c r="M813" t="inlineStr">
+        <is>
+          <t>2026-07-05 00:00:00</t>
+        </is>
+      </c>
+      <c r="N813" t="inlineStr">
+        <is>
+          <t>2026-07-06 00:00:00</t>
+        </is>
+      </c>
+      <c r="O813" t="inlineStr">
+        <is>
+          <t>FUJIAN ANTAI NEW ENERGY TECH CO LTD</t>
+        </is>
+      </c>
+      <c r="P813" t="inlineStr">
+        <is>
+          <t>FUJIAN ANTAI NEW ENERGY TECH CO LTD</t>
+        </is>
+      </c>
+      <c r="Q813" t="inlineStr">
+        <is>
+          <t>2026-05-31 00:00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="814">
+      <c r="A814" t="inlineStr">
+        <is>
+          <t>2566127</t>
+        </is>
+      </c>
+      <c r="B814" t="inlineStr">
+        <is>
+          <t>EF4-0232257-4</t>
+        </is>
+      </c>
+      <c r="C814" t="inlineStr">
+        <is>
+          <t>Vessel, Container</t>
+        </is>
+      </c>
+      <c r="D814" t="inlineStr"/>
+      <c r="E814" t="inlineStr">
+        <is>
+          <t>9903.88.02</t>
+        </is>
+      </c>
+      <c r="F814" t="inlineStr">
+        <is>
+          <t>ARTICLE OF CHINA,US NTE 20(C)</t>
+        </is>
+      </c>
+      <c r="G814" t="inlineStr">
+        <is>
+          <t>005</t>
+        </is>
+      </c>
+      <c r="H814" t="inlineStr">
+        <is>
+          <t>9903.88.02</t>
+        </is>
+      </c>
+      <c r="I814" t="inlineStr">
+        <is>
+          <t>9903.03.01,8536.30.8000</t>
+        </is>
+      </c>
+      <c r="J814" t="inlineStr">
+        <is>
+          <t>VISUAL CREATIONS, INC.</t>
+        </is>
+      </c>
+      <c r="K814" t="inlineStr">
+        <is>
+          <t>VISCRE</t>
+        </is>
+      </c>
+      <c r="L814" t="inlineStr">
+        <is>
+          <t>20-461602300</t>
+        </is>
+      </c>
+      <c r="M814" t="inlineStr">
+        <is>
+          <t>2026-07-05 00:00:00</t>
+        </is>
+      </c>
+      <c r="N814" t="inlineStr">
+        <is>
+          <t>2026-07-06 00:00:00</t>
+        </is>
+      </c>
+      <c r="O814" t="inlineStr">
+        <is>
+          <t>FUJIAN ANTAI NEW ENERGY TECH CO LTD</t>
+        </is>
+      </c>
+      <c r="P814" t="inlineStr">
+        <is>
+          <t>FUJIAN ANTAI NEW ENERGY TECH CO LTD</t>
+        </is>
+      </c>
+      <c r="Q814" t="inlineStr">
+        <is>
+          <t>2026-05-31 00:00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="815">
+      <c r="A815" t="inlineStr">
+        <is>
+          <t>2566127</t>
+        </is>
+      </c>
+      <c r="B815" t="inlineStr">
+        <is>
+          <t>EF4-0232257-4</t>
+        </is>
+      </c>
+      <c r="C815" t="inlineStr">
+        <is>
+          <t>Vessel, Container</t>
+        </is>
+      </c>
+      <c r="D815" t="inlineStr"/>
+      <c r="E815" t="inlineStr">
+        <is>
+          <t>9903.88.15</t>
+        </is>
+      </c>
+      <c r="F815" t="inlineStr">
+        <is>
+          <t>ARTICLE OF CHINA,US NTE 20(R)</t>
+        </is>
+      </c>
+      <c r="G815" t="inlineStr">
+        <is>
+          <t>006</t>
+        </is>
+      </c>
+      <c r="H815" t="inlineStr">
+        <is>
+          <t>9903.88.15</t>
+        </is>
+      </c>
+      <c r="I815" t="inlineStr">
+        <is>
+          <t>9903.03.01,3926.90.9989</t>
+        </is>
+      </c>
+      <c r="J815" t="inlineStr">
+        <is>
+          <t>VISUAL CREATIONS, INC.</t>
+        </is>
+      </c>
+      <c r="K815" t="inlineStr">
+        <is>
+          <t>VISCRE</t>
+        </is>
+      </c>
+      <c r="L815" t="inlineStr">
+        <is>
+          <t>20-461602300</t>
+        </is>
+      </c>
+      <c r="M815" t="inlineStr">
+        <is>
+          <t>2026-07-05 00:00:00</t>
+        </is>
+      </c>
+      <c r="N815" t="inlineStr">
+        <is>
+          <t>2026-07-06 00:00:00</t>
+        </is>
+      </c>
+      <c r="O815" t="inlineStr">
+        <is>
+          <t>FUJIAN ANTAI NEW ENERGY TECH CO LTD</t>
+        </is>
+      </c>
+      <c r="P815" t="inlineStr">
+        <is>
+          <t>FUJIAN ANTAI NEW ENERGY TECH CO LTD</t>
+        </is>
+      </c>
+      <c r="Q815" t="inlineStr">
+        <is>
+          <t>2026-05-31 00:00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="816">
+      <c r="A816" t="inlineStr">
+        <is>
+          <t>2566127</t>
+        </is>
+      </c>
+      <c r="B816" t="inlineStr">
+        <is>
+          <t>EF4-0232257-4</t>
+        </is>
+      </c>
+      <c r="C816" t="inlineStr">
+        <is>
+          <t>Vessel, Container</t>
+        </is>
+      </c>
+      <c r="D816" t="inlineStr"/>
+      <c r="E816" t="inlineStr">
+        <is>
+          <t>9903.88.03</t>
+        </is>
+      </c>
+      <c r="F816" t="inlineStr">
+        <is>
+          <t>ARTICLE OF CHINA,US NTE 20(F)</t>
+        </is>
+      </c>
+      <c r="G816" t="inlineStr">
+        <is>
+          <t>007</t>
+        </is>
+      </c>
+      <c r="H816" t="inlineStr">
+        <is>
+          <t>9903.88.03</t>
+        </is>
+      </c>
+      <c r="I816" t="inlineStr">
+        <is>
+          <t>9903.03.01,9405.41.8440</t>
+        </is>
+      </c>
+      <c r="J816" t="inlineStr">
+        <is>
+          <t>VISUAL CREATIONS, INC.</t>
+        </is>
+      </c>
+      <c r="K816" t="inlineStr">
+        <is>
+          <t>VISCRE</t>
+        </is>
+      </c>
+      <c r="L816" t="inlineStr">
+        <is>
+          <t>20-461602300</t>
+        </is>
+      </c>
+      <c r="M816" t="inlineStr">
+        <is>
+          <t>2026-07-05 00:00:00</t>
+        </is>
+      </c>
+      <c r="N816" t="inlineStr">
+        <is>
+          <t>2026-07-06 00:00:00</t>
+        </is>
+      </c>
+      <c r="O816" t="inlineStr">
+        <is>
+          <t>FUJIAN ANTAI NEW ENERGY TECH CO LTD</t>
+        </is>
+      </c>
+      <c r="P816" t="inlineStr">
+        <is>
+          <t>FUJIAN ANTAI NEW ENERGY TECH CO LTD</t>
+        </is>
+      </c>
+      <c r="Q816" t="inlineStr">
+        <is>
+          <t>2026-05-31 00:00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="817">
+      <c r="A817" t="inlineStr">
+        <is>
+          <t>2566127</t>
+        </is>
+      </c>
+      <c r="B817" t="inlineStr">
+        <is>
+          <t>EF4-0232257-4</t>
+        </is>
+      </c>
+      <c r="C817" t="inlineStr">
+        <is>
+          <t>Vessel, Container</t>
+        </is>
+      </c>
+      <c r="D817" t="inlineStr"/>
+      <c r="E817" t="inlineStr">
+        <is>
+          <t>9903.88.15</t>
+        </is>
+      </c>
+      <c r="F817" t="inlineStr">
+        <is>
+          <t>ARTICLE OF CHINA,US NTE 20(R)</t>
+        </is>
+      </c>
+      <c r="G817" t="inlineStr">
+        <is>
+          <t>008</t>
+        </is>
+      </c>
+      <c r="H817" t="inlineStr">
+        <is>
+          <t>9903.88.15</t>
+        </is>
+      </c>
+      <c r="I817" t="inlineStr">
+        <is>
+          <t>9903.03.06,9903.82.09,8302.42.3065</t>
+        </is>
+      </c>
+      <c r="J817" t="inlineStr">
+        <is>
+          <t>VISUAL CREATIONS, INC.</t>
+        </is>
+      </c>
+      <c r="K817" t="inlineStr">
+        <is>
+          <t>VISCRE</t>
+        </is>
+      </c>
+      <c r="L817" t="inlineStr">
+        <is>
+          <t>20-461602300</t>
+        </is>
+      </c>
+      <c r="M817" t="inlineStr">
+        <is>
+          <t>2026-07-05 00:00:00</t>
+        </is>
+      </c>
+      <c r="N817" t="inlineStr">
+        <is>
+          <t>2026-07-06 00:00:00</t>
+        </is>
+      </c>
+      <c r="O817" t="inlineStr">
+        <is>
+          <t>FUJIAN ANTAI NEW ENERGY TECH CO LTD</t>
+        </is>
+      </c>
+      <c r="P817" t="inlineStr">
+        <is>
+          <t>FUJIAN ANTAI NEW ENERGY TECH CO LTD</t>
+        </is>
+      </c>
+      <c r="Q817" t="inlineStr">
+        <is>
+          <t>2026-05-31 00:00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="818">
+      <c r="A818" t="inlineStr">
+        <is>
+          <t>2566127</t>
+        </is>
+      </c>
+      <c r="B818" t="inlineStr">
+        <is>
+          <t>EF4-0232257-4</t>
+        </is>
+      </c>
+      <c r="C818" t="inlineStr">
+        <is>
+          <t>Vessel, Container</t>
+        </is>
+      </c>
+      <c r="D818" t="inlineStr"/>
+      <c r="E818" t="inlineStr">
+        <is>
+          <t>9903.88.03</t>
+        </is>
+      </c>
+      <c r="F818" t="inlineStr">
+        <is>
+          <t>ARTICLE OF CHINA,US NTE 20(F)</t>
+        </is>
+      </c>
+      <c r="G818" t="inlineStr">
+        <is>
+          <t>009</t>
+        </is>
+      </c>
+      <c r="H818" t="inlineStr">
+        <is>
+          <t>9903.88.03</t>
+        </is>
+      </c>
+      <c r="I818" t="inlineStr">
+        <is>
+          <t>9903.03.06,9903.82.09,9403.20.0075</t>
+        </is>
+      </c>
+      <c r="J818" t="inlineStr">
+        <is>
+          <t>VISUAL CREATIONS, INC.</t>
+        </is>
+      </c>
+      <c r="K818" t="inlineStr">
+        <is>
+          <t>VISCRE</t>
+        </is>
+      </c>
+      <c r="L818" t="inlineStr">
+        <is>
+          <t>20-461602300</t>
+        </is>
+      </c>
+      <c r="M818" t="inlineStr">
+        <is>
+          <t>2026-07-05 00:00:00</t>
+        </is>
+      </c>
+      <c r="N818" t="inlineStr">
+        <is>
+          <t>2026-07-06 00:00:00</t>
+        </is>
+      </c>
+      <c r="O818" t="inlineStr">
+        <is>
+          <t>FUJIAN ANTAI NEW ENERGY TECH CO LTD</t>
+        </is>
+      </c>
+      <c r="P818" t="inlineStr">
+        <is>
+          <t>FUJIAN ANTAI NEW ENERGY TECH CO LTD</t>
+        </is>
+      </c>
+      <c r="Q818" t="inlineStr">
+        <is>
+          <t>2026-05-31 00:00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="819">
+      <c r="A819" t="inlineStr">
+        <is>
+          <t>2566098</t>
+        </is>
+      </c>
+      <c r="B819" t="inlineStr">
+        <is>
+          <t>EF4-0232438-0</t>
+        </is>
+      </c>
+      <c r="C819" t="inlineStr">
+        <is>
+          <t>Vessel, Container</t>
+        </is>
+      </c>
+      <c r="D819" t="inlineStr"/>
+      <c r="E819" t="inlineStr">
+        <is>
+          <t>9903.03.01</t>
+        </is>
+      </c>
+      <c r="F819" t="inlineStr"/>
+      <c r="G819" t="inlineStr">
+        <is>
+          <t>001</t>
+        </is>
+      </c>
+      <c r="H819" t="inlineStr">
+        <is>
+          <t>9903.03.01</t>
+        </is>
+      </c>
+      <c r="I819" t="inlineStr">
+        <is>
+          <t>1108.12.0010</t>
+        </is>
+      </c>
+      <c r="J819" t="inlineStr">
+        <is>
+          <t>ROYAL INGREDIENTS GROUP BV</t>
+        </is>
+      </c>
+      <c r="K819" t="inlineStr">
+        <is>
+          <t>ROYINGRE</t>
+        </is>
+      </c>
+      <c r="L819" t="inlineStr">
+        <is>
+          <t>074601-00962</t>
+        </is>
+      </c>
+      <c r="M819" t="inlineStr">
+        <is>
+          <t>2026-07-05 00:00:00</t>
+        </is>
+      </c>
+      <c r="N819" t="inlineStr">
+        <is>
+          <t>2026-07-06 00:00:00</t>
+        </is>
+      </c>
+      <c r="O819" t="inlineStr">
+        <is>
+          <t>TAT NISASTA INS SAN TIC AS</t>
+        </is>
+      </c>
+      <c r="P819" t="inlineStr">
+        <is>
+          <t>TAT NISASTA INS SAN TIC AS</t>
+        </is>
+      </c>
+      <c r="Q819" t="inlineStr">
+        <is>
+          <t>2026-06-07 00:00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="820">
+      <c r="A820" t="inlineStr">
+        <is>
+          <t>2566326</t>
+        </is>
+      </c>
+      <c r="B820" t="inlineStr">
+        <is>
+          <t>EF4-0232459-6</t>
+        </is>
+      </c>
+      <c r="C820" t="inlineStr">
+        <is>
+          <t>Vessel, Container</t>
+        </is>
+      </c>
+      <c r="D820" t="inlineStr"/>
+      <c r="E820" t="inlineStr">
+        <is>
+          <t>9903.03.01</t>
+        </is>
+      </c>
+      <c r="F820" t="inlineStr">
+        <is>
+          <t>SECTION 122 - 10% DUTY</t>
+        </is>
+      </c>
+      <c r="G820" t="inlineStr">
+        <is>
+          <t>001</t>
+        </is>
+      </c>
+      <c r="H820" t="inlineStr">
+        <is>
+          <t>9903.03.01</t>
+        </is>
+      </c>
+      <c r="I820" t="inlineStr">
+        <is>
+          <t>4409.29.0655</t>
+        </is>
+      </c>
+      <c r="J820" t="inlineStr">
+        <is>
+          <t>AUTHENTIC SURFACES LLC</t>
+        </is>
+      </c>
+      <c r="K820" t="inlineStr">
+        <is>
+          <t>AUTSUR01</t>
+        </is>
+      </c>
+      <c r="L820" t="inlineStr">
+        <is>
+          <t>86-279678900</t>
+        </is>
+      </c>
+      <c r="M820" t="inlineStr">
+        <is>
+          <t>2026-07-04 00:00:00</t>
+        </is>
+      </c>
+      <c r="N820" t="inlineStr">
+        <is>
+          <t>2026-07-06 00:00:00</t>
+        </is>
+      </c>
+      <c r="O820" t="inlineStr">
+        <is>
+          <t>CHENE DE L'EST</t>
+        </is>
+      </c>
+      <c r="P820" t="inlineStr">
+        <is>
+          <t>CHENE DE L'EST</t>
+        </is>
+      </c>
+      <c r="Q820" t="inlineStr">
+        <is>
+          <t>2026-06-08 00:00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="821">
+      <c r="A821" t="inlineStr">
+        <is>
+          <t>2566274</t>
+        </is>
+      </c>
+      <c r="B821" t="inlineStr">
+        <is>
+          <t>EF4-0232541-1</t>
+        </is>
+      </c>
+      <c r="C821" t="inlineStr">
+        <is>
+          <t>Vessel, Container</t>
+        </is>
+      </c>
+      <c r="D821" t="inlineStr">
+        <is>
+          <t>V1626485778</t>
+        </is>
+      </c>
+      <c r="E821" t="inlineStr">
+        <is>
+          <t>9903.03.01</t>
+        </is>
+      </c>
+      <c r="F821" t="inlineStr">
+        <is>
+          <t>SECTION 122 - 10% DUTY</t>
+        </is>
+      </c>
+      <c r="G821" t="inlineStr">
+        <is>
+          <t>001</t>
+        </is>
+      </c>
+      <c r="H821" t="inlineStr">
+        <is>
+          <t>9903.03.01</t>
+        </is>
+      </c>
+      <c r="I821" t="inlineStr">
+        <is>
+          <t>1702.30.4085</t>
+        </is>
+      </c>
+      <c r="J821" t="inlineStr">
+        <is>
+          <t>ROYAL INGREDIENTS GROUP BV</t>
+        </is>
+      </c>
+      <c r="K821" t="inlineStr">
+        <is>
+          <t>ROYINGRE</t>
+        </is>
+      </c>
+      <c r="L821" t="inlineStr">
+        <is>
+          <t>074601-00962</t>
+        </is>
+      </c>
+      <c r="M821" t="inlineStr">
+        <is>
+          <t>2026-07-01 00:00:00</t>
+        </is>
+      </c>
+      <c r="N821" t="inlineStr">
+        <is>
+          <t>2026-07-06 00:00:00</t>
+        </is>
+      </c>
+      <c r="O821" t="inlineStr">
+        <is>
+          <t>AK NISASTA SANAYI VE TICARET AS</t>
+        </is>
+      </c>
+      <c r="P821" t="inlineStr">
+        <is>
+          <t>AK NISASTA SANAYI VE TICARET AS</t>
+        </is>
+      </c>
+      <c r="Q821" t="inlineStr">
+        <is>
+          <t>2026-06-12 00:00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="822">
+      <c r="A822" t="inlineStr">
+        <is>
+          <t>2566271</t>
+        </is>
+      </c>
+      <c r="B822" t="inlineStr">
+        <is>
+          <t>EF4-0232613-8</t>
+        </is>
+      </c>
+      <c r="C822" t="inlineStr">
+        <is>
+          <t>Vessel, Non-container</t>
+        </is>
+      </c>
+      <c r="D822" t="inlineStr">
+        <is>
+          <t>V1626485778</t>
+        </is>
+      </c>
+      <c r="E822" t="inlineStr">
+        <is>
+          <t>9903.03.06</t>
+        </is>
+      </c>
+      <c r="F822" t="inlineStr">
+        <is>
+          <t>S122 EXCL,IRN/STL/ALUM,DERIV</t>
+        </is>
+      </c>
+      <c r="G822" t="inlineStr">
+        <is>
+          <t>001</t>
+        </is>
+      </c>
+      <c r="H822" t="inlineStr">
+        <is>
+          <t>9903.03.06</t>
+        </is>
+      </c>
+      <c r="I822" t="inlineStr">
+        <is>
+          <t>9903.82.22,8427.90.0090</t>
+        </is>
+      </c>
+      <c r="J822" t="inlineStr">
+        <is>
+          <t>MALLAGHAN (GA) INC.</t>
+        </is>
+      </c>
+      <c r="K822" t="inlineStr">
+        <is>
+          <t>MALGA01</t>
+        </is>
+      </c>
+      <c r="L822" t="inlineStr">
+        <is>
+          <t>36-488102800</t>
+        </is>
+      </c>
+      <c r="M822" t="inlineStr">
+        <is>
+          <t>2026-07-04 00:00:00</t>
+        </is>
+      </c>
+      <c r="N822" t="inlineStr">
+        <is>
+          <t>2026-07-06 00:00:00</t>
+        </is>
+      </c>
+      <c r="O822" t="inlineStr">
+        <is>
+          <t>MALLAGHAN ENGINEERING  LTD</t>
+        </is>
+      </c>
+      <c r="P822" t="inlineStr">
+        <is>
+          <t>MALLAGHAN ENGINEERING  LTD</t>
+        </is>
+      </c>
+      <c r="Q822" t="inlineStr">
+        <is>
+          <t>2026-06-14 00:00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="823">
+      <c r="A823" t="inlineStr">
+        <is>
+          <t>2566271</t>
+        </is>
+      </c>
+      <c r="B823" t="inlineStr">
+        <is>
+          <t>EF4-0232613-8</t>
+        </is>
+      </c>
+      <c r="C823" t="inlineStr">
+        <is>
+          <t>Vessel, Non-container</t>
+        </is>
+      </c>
+      <c r="D823" t="inlineStr">
+        <is>
+          <t>V1626485778</t>
+        </is>
+      </c>
+      <c r="E823" t="inlineStr">
+        <is>
+          <t>9903.03.06</t>
+        </is>
+      </c>
+      <c r="F823" t="inlineStr">
+        <is>
+          <t>S122 EXCL,IRN/STL/ALUM,DERIV</t>
+        </is>
+      </c>
+      <c r="G823" t="inlineStr">
+        <is>
+          <t>002</t>
+        </is>
+      </c>
+      <c r="H823" t="inlineStr">
+        <is>
+          <t>9903.03.06</t>
+        </is>
+      </c>
+      <c r="I823" t="inlineStr">
+        <is>
+          <t>9903.82.22,8427.90.0090</t>
+        </is>
+      </c>
+      <c r="J823" t="inlineStr">
+        <is>
+          <t>MALLAGHAN (GA) INC.</t>
+        </is>
+      </c>
+      <c r="K823" t="inlineStr">
+        <is>
+          <t>MALGA01</t>
+        </is>
+      </c>
+      <c r="L823" t="inlineStr">
+        <is>
+          <t>36-488102800</t>
+        </is>
+      </c>
+      <c r="M823" t="inlineStr">
+        <is>
+          <t>2026-07-04 00:00:00</t>
+        </is>
+      </c>
+      <c r="N823" t="inlineStr">
+        <is>
+          <t>2026-07-06 00:00:00</t>
+        </is>
+      </c>
+      <c r="O823" t="inlineStr">
+        <is>
+          <t>MALLAGHAN ENGINEERING  LTD</t>
+        </is>
+      </c>
+      <c r="P823" t="inlineStr">
+        <is>
+          <t>MALLAGHAN ENGINEERING  LTD</t>
+        </is>
+      </c>
+      <c r="Q823" t="inlineStr">
+        <is>
+          <t>2026-06-14 00:00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="824">
+      <c r="A824" t="inlineStr">
+        <is>
+          <t>2566271</t>
+        </is>
+      </c>
+      <c r="B824" t="inlineStr">
+        <is>
+          <t>EF4-0232613-8</t>
+        </is>
+      </c>
+      <c r="C824" t="inlineStr">
+        <is>
+          <t>Vessel, Non-container</t>
+        </is>
+      </c>
+      <c r="D824" t="inlineStr">
+        <is>
+          <t>V1626485778</t>
+        </is>
+      </c>
+      <c r="E824" t="inlineStr">
+        <is>
+          <t>9903.03.06</t>
+        </is>
+      </c>
+      <c r="F824" t="inlineStr">
+        <is>
+          <t>S122 EXCL,IRN/STL/ALUM,DERIV</t>
+        </is>
+      </c>
+      <c r="G824" t="inlineStr">
+        <is>
+          <t>003</t>
+        </is>
+      </c>
+      <c r="H824" t="inlineStr">
+        <is>
+          <t>9903.03.06</t>
+        </is>
+      </c>
+      <c r="I824" t="inlineStr">
+        <is>
+          <t>9903.82.22,8427.90.0090</t>
+        </is>
+      </c>
+      <c r="J824" t="inlineStr">
+        <is>
+          <t>MALLAGHAN (GA) INC.</t>
+        </is>
+      </c>
+      <c r="K824" t="inlineStr">
+        <is>
+          <t>MALGA01</t>
+        </is>
+      </c>
+      <c r="L824" t="inlineStr">
+        <is>
+          <t>36-488102800</t>
+        </is>
+      </c>
+      <c r="M824" t="inlineStr">
+        <is>
+          <t>2026-07-04 00:00:00</t>
+        </is>
+      </c>
+      <c r="N824" t="inlineStr">
+        <is>
+          <t>2026-07-06 00:00:00</t>
+        </is>
+      </c>
+      <c r="O824" t="inlineStr">
+        <is>
+          <t>MALLAGHAN ENGINEERING  LTD</t>
+        </is>
+      </c>
+      <c r="P824" t="inlineStr">
+        <is>
+          <t>MALLAGHAN ENGINEERING  LTD</t>
+        </is>
+      </c>
+      <c r="Q824" t="inlineStr">
+        <is>
+          <t>2026-06-14 00:00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="825">
+      <c r="A825" t="inlineStr">
+        <is>
+          <t>2566271</t>
+        </is>
+      </c>
+      <c r="B825" t="inlineStr">
+        <is>
+          <t>EF4-0232613-8</t>
+        </is>
+      </c>
+      <c r="C825" t="inlineStr">
+        <is>
+          <t>Vessel, Non-container</t>
+        </is>
+      </c>
+      <c r="D825" t="inlineStr">
+        <is>
+          <t>V1626485778</t>
+        </is>
+      </c>
+      <c r="E825" t="inlineStr">
+        <is>
+          <t>9903.03.06</t>
+        </is>
+      </c>
+      <c r="F825" t="inlineStr">
+        <is>
+          <t>S122 EXCL,IRN/STL/ALUM,DERIV</t>
+        </is>
+      </c>
+      <c r="G825" t="inlineStr">
+        <is>
+          <t>004</t>
+        </is>
+      </c>
+      <c r="H825" t="inlineStr">
+        <is>
+          <t>9903.03.06</t>
+        </is>
+      </c>
+      <c r="I825" t="inlineStr">
+        <is>
+          <t>9903.82.22,8427.90.0090</t>
+        </is>
+      </c>
+      <c r="J825" t="inlineStr">
+        <is>
+          <t>MALLAGHAN (GA) INC.</t>
+        </is>
+      </c>
+      <c r="K825" t="inlineStr">
+        <is>
+          <t>MALGA01</t>
+        </is>
+      </c>
+      <c r="L825" t="inlineStr">
+        <is>
+          <t>36-488102800</t>
+        </is>
+      </c>
+      <c r="M825" t="inlineStr">
+        <is>
+          <t>2026-07-04 00:00:00</t>
+        </is>
+      </c>
+      <c r="N825" t="inlineStr">
+        <is>
+          <t>2026-07-06 00:00:00</t>
+        </is>
+      </c>
+      <c r="O825" t="inlineStr">
+        <is>
+          <t>MALLAGHAN ENGINEERING  LTD</t>
+        </is>
+      </c>
+      <c r="P825" t="inlineStr">
+        <is>
+          <t>MALLAGHAN ENGINEERING  LTD</t>
+        </is>
+      </c>
+      <c r="Q825" t="inlineStr">
+        <is>
+          <t>2026-06-14 00:00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="826">
+      <c r="A826" t="inlineStr">
+        <is>
+          <t>2566271</t>
+        </is>
+      </c>
+      <c r="B826" t="inlineStr">
+        <is>
+          <t>EF4-0232613-8</t>
+        </is>
+      </c>
+      <c r="C826" t="inlineStr">
+        <is>
+          <t>Vessel, Non-container</t>
+        </is>
+      </c>
+      <c r="D826" t="inlineStr">
+        <is>
+          <t>V1626485778</t>
+        </is>
+      </c>
+      <c r="E826" t="inlineStr">
+        <is>
+          <t>9903.03.06</t>
+        </is>
+      </c>
+      <c r="F826" t="inlineStr">
+        <is>
+          <t>S122 EXCL,IRN/STL/ALUM,DERIV</t>
+        </is>
+      </c>
+      <c r="G826" t="inlineStr">
+        <is>
+          <t>005</t>
+        </is>
+      </c>
+      <c r="H826" t="inlineStr">
+        <is>
+          <t>9903.03.06</t>
+        </is>
+      </c>
+      <c r="I826" t="inlineStr">
+        <is>
+          <t>9903.82.22,8427.90.0090</t>
+        </is>
+      </c>
+      <c r="J826" t="inlineStr">
+        <is>
+          <t>MALLAGHAN (GA) INC.</t>
+        </is>
+      </c>
+      <c r="K826" t="inlineStr">
+        <is>
+          <t>MALGA01</t>
+        </is>
+      </c>
+      <c r="L826" t="inlineStr">
+        <is>
+          <t>36-488102800</t>
+        </is>
+      </c>
+      <c r="M826" t="inlineStr">
+        <is>
+          <t>2026-07-04 00:00:00</t>
+        </is>
+      </c>
+      <c r="N826" t="inlineStr">
+        <is>
+          <t>2026-07-06 00:00:00</t>
+        </is>
+      </c>
+      <c r="O826" t="inlineStr">
+        <is>
+          <t>MALLAGHAN ENGINEERING  LTD</t>
+        </is>
+      </c>
+      <c r="P826" t="inlineStr">
+        <is>
+          <t>MALLAGHAN ENGINEERING  LTD</t>
+        </is>
+      </c>
+      <c r="Q826" t="inlineStr">
+        <is>
+          <t>2026-06-14 00:00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="827">
+      <c r="A827" t="inlineStr">
+        <is>
+          <t>105504864</t>
+        </is>
+      </c>
+      <c r="B827" t="inlineStr">
+        <is>
+          <t>EF4-0232978-5</t>
+        </is>
+      </c>
+      <c r="C827" t="inlineStr">
+        <is>
+          <t>Air, Non-container</t>
+        </is>
+      </c>
+      <c r="D827" t="inlineStr"/>
+      <c r="E827" t="inlineStr">
+        <is>
+          <t>9817.85.01</t>
+        </is>
+      </c>
+      <c r="F827" t="inlineStr">
+        <is>
+          <t>PROTOTYPES, TESTING/EVALUATION</t>
+        </is>
+      </c>
+      <c r="G827" t="inlineStr">
+        <is>
+          <t>001</t>
+        </is>
+      </c>
+      <c r="H827" t="inlineStr">
+        <is>
+          <t>9817.85.01</t>
+        </is>
+      </c>
+      <c r="I827" t="inlineStr">
+        <is>
+          <t>9903.03.06,9903.94.51,8703.23.0160</t>
+        </is>
+      </c>
+      <c r="J827" t="inlineStr">
+        <is>
+          <t>PORSCHE MOTORSPORT NORTH AMERICA</t>
+        </is>
+      </c>
+      <c r="K827" t="inlineStr">
+        <is>
+          <t>PORMOT01</t>
+        </is>
+      </c>
+      <c r="L827" t="inlineStr">
+        <is>
+          <t>23-234420600</t>
+        </is>
+      </c>
+      <c r="M827" t="inlineStr">
+        <is>
+          <t>2026-07-05 00:00:00</t>
+        </is>
+      </c>
+      <c r="N827" t="inlineStr">
+        <is>
+          <t>2026-07-06 00:00:00</t>
+        </is>
+      </c>
+      <c r="O827" t="inlineStr">
+        <is>
+          <t>VOLKSWAGEN SLOVAKIA A.S</t>
+        </is>
+      </c>
+      <c r="P827" t="inlineStr">
+        <is>
+          <t>VOLKSWAGEN SLOVAKIA A.S</t>
+        </is>
+      </c>
+      <c r="Q827" t="inlineStr">
+        <is>
+          <t>2026-07-05 00:00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="828">
+      <c r="A828" t="inlineStr">
+        <is>
+          <t>105504866</t>
+        </is>
+      </c>
+      <c r="B828" t="inlineStr">
+        <is>
+          <t>EF4-0232983-5</t>
+        </is>
+      </c>
+      <c r="C828" t="inlineStr">
+        <is>
+          <t>Air, Non-container</t>
+        </is>
+      </c>
+      <c r="D828" t="inlineStr"/>
+      <c r="E828" t="inlineStr">
+        <is>
+          <t>9817.85.01</t>
+        </is>
+      </c>
+      <c r="F828" t="inlineStr">
+        <is>
+          <t>PROTOTYPES, TESTING/EVALUATION</t>
+        </is>
+      </c>
+      <c r="G828" t="inlineStr">
+        <is>
+          <t>001</t>
+        </is>
+      </c>
+      <c r="H828" t="inlineStr">
+        <is>
+          <t>9817.85.01</t>
+        </is>
+      </c>
+      <c r="I828" t="inlineStr">
+        <is>
+          <t>9903.03.06,9903.94.51,8703.60.0030</t>
+        </is>
+      </c>
+      <c r="J828" t="inlineStr">
+        <is>
+          <t>PORSCHE MOTORSPORT NORTH AMERICA</t>
+        </is>
+      </c>
+      <c r="K828" t="inlineStr">
+        <is>
+          <t>PORMOT01</t>
+        </is>
+      </c>
+      <c r="L828" t="inlineStr">
+        <is>
+          <t>23-234420600</t>
+        </is>
+      </c>
+      <c r="M828" t="inlineStr">
+        <is>
+          <t>2026-07-05 00:00:00</t>
+        </is>
+      </c>
+      <c r="N828" t="inlineStr">
+        <is>
+          <t>2026-07-06 00:00:00</t>
+        </is>
+      </c>
+      <c r="O828" t="inlineStr">
+        <is>
+          <t>VOLKSWAGEN SLOVAKIA A.S</t>
+        </is>
+      </c>
+      <c r="P828" t="inlineStr">
+        <is>
+          <t>VOLKSWAGEN SLOVAKIA A.S</t>
+        </is>
+      </c>
+      <c r="Q828" t="inlineStr">
+        <is>
+          <t>2026-07-05 00:00:00</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/trimika_data.xlsx
+++ b/trimika_data.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q828"/>
+  <dimension ref="A1:Q859"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -69668,6 +69668,2667 @@
         </is>
       </c>
     </row>
+    <row r="829">
+      <c r="A829" t="inlineStr">
+        <is>
+          <t>2565921</t>
+        </is>
+      </c>
+      <c r="B829" t="inlineStr">
+        <is>
+          <t>EF4-0231891-1</t>
+        </is>
+      </c>
+      <c r="C829" t="inlineStr">
+        <is>
+          <t>Vessel, Container</t>
+        </is>
+      </c>
+      <c r="D829" t="inlineStr">
+        <is>
+          <t>165925675</t>
+        </is>
+      </c>
+      <c r="E829" t="inlineStr">
+        <is>
+          <t>9803.00.50</t>
+        </is>
+      </c>
+      <c r="F829" t="inlineStr">
+        <is>
+          <t>SUBSTANTIAL CONTAINERS US&amp;INTL</t>
+        </is>
+      </c>
+      <c r="G829" t="inlineStr">
+        <is>
+          <t>001</t>
+        </is>
+      </c>
+      <c r="H829" t="inlineStr">
+        <is>
+          <t>9803.00.50</t>
+        </is>
+      </c>
+      <c r="I829" t="inlineStr"/>
+      <c r="J829" t="inlineStr">
+        <is>
+          <t>MEBROM LLC</t>
+        </is>
+      </c>
+      <c r="K829" t="inlineStr">
+        <is>
+          <t>MEBLLC01</t>
+        </is>
+      </c>
+      <c r="L829" t="inlineStr">
+        <is>
+          <t>84-463527000</t>
+        </is>
+      </c>
+      <c r="M829" t="inlineStr">
+        <is>
+          <t>2026-07-07 00:00:00</t>
+        </is>
+      </c>
+      <c r="N829" t="inlineStr">
+        <is>
+          <t>2026-07-07 00:00:00</t>
+        </is>
+      </c>
+      <c r="O829" t="inlineStr">
+        <is>
+          <t>SAHAMITR PRESSURE CONTAINER PUBLIC</t>
+        </is>
+      </c>
+      <c r="P829" t="inlineStr">
+        <is>
+          <t>SAHAMITR PRESSURE CONTAINER PUBLIC CO LTD</t>
+        </is>
+      </c>
+      <c r="Q829" t="inlineStr">
+        <is>
+          <t>2026-05-15 00:00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="830">
+      <c r="A830" t="inlineStr">
+        <is>
+          <t>2565904</t>
+        </is>
+      </c>
+      <c r="B830" t="inlineStr">
+        <is>
+          <t>EF4-0231900-0</t>
+        </is>
+      </c>
+      <c r="C830" t="inlineStr">
+        <is>
+          <t>Vessel, Container</t>
+        </is>
+      </c>
+      <c r="D830" t="inlineStr"/>
+      <c r="E830" t="inlineStr">
+        <is>
+          <t>9903.03.01</t>
+        </is>
+      </c>
+      <c r="F830" t="inlineStr">
+        <is>
+          <t>SECTION 122 - 10% DUTY</t>
+        </is>
+      </c>
+      <c r="G830" t="inlineStr">
+        <is>
+          <t>001</t>
+        </is>
+      </c>
+      <c r="H830" t="inlineStr">
+        <is>
+          <t>9903.03.01</t>
+        </is>
+      </c>
+      <c r="I830" t="inlineStr">
+        <is>
+          <t>5603.14.9090</t>
+        </is>
+      </c>
+      <c r="J830" t="inlineStr">
+        <is>
+          <t>VEER CORPORATIONS INC</t>
+        </is>
+      </c>
+      <c r="K830" t="inlineStr">
+        <is>
+          <t>VEECOR01</t>
+        </is>
+      </c>
+      <c r="L830" t="inlineStr">
+        <is>
+          <t>99-106989200</t>
+        </is>
+      </c>
+      <c r="M830" t="inlineStr">
+        <is>
+          <t>2026-07-08 00:00:00</t>
+        </is>
+      </c>
+      <c r="N830" t="inlineStr">
+        <is>
+          <t>2026-07-07 00:00:00</t>
+        </is>
+      </c>
+      <c r="O830" t="inlineStr">
+        <is>
+          <t>VEER PLASTIC PVT LTD</t>
+        </is>
+      </c>
+      <c r="P830" t="inlineStr">
+        <is>
+          <t>VEER PLASTIC PVT LTD</t>
+        </is>
+      </c>
+      <c r="Q830" t="inlineStr">
+        <is>
+          <t>2026-05-12 00:00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="831">
+      <c r="A831" t="inlineStr">
+        <is>
+          <t>2565991</t>
+        </is>
+      </c>
+      <c r="B831" t="inlineStr">
+        <is>
+          <t>EF4-0231968-7</t>
+        </is>
+      </c>
+      <c r="C831" t="inlineStr">
+        <is>
+          <t>Vessel, Container</t>
+        </is>
+      </c>
+      <c r="D831" t="inlineStr"/>
+      <c r="E831" t="inlineStr">
+        <is>
+          <t>9903.03.01</t>
+        </is>
+      </c>
+      <c r="F831" t="inlineStr">
+        <is>
+          <t>SECTION 122 - 10% DUTY</t>
+        </is>
+      </c>
+      <c r="G831" t="inlineStr">
+        <is>
+          <t>001</t>
+        </is>
+      </c>
+      <c r="H831" t="inlineStr">
+        <is>
+          <t>9903.03.01</t>
+        </is>
+      </c>
+      <c r="I831" t="inlineStr">
+        <is>
+          <t>5603.14.9090</t>
+        </is>
+      </c>
+      <c r="J831" t="inlineStr">
+        <is>
+          <t>VEER CORPORATIONS INC</t>
+        </is>
+      </c>
+      <c r="K831" t="inlineStr">
+        <is>
+          <t>VEECOR01</t>
+        </is>
+      </c>
+      <c r="L831" t="inlineStr">
+        <is>
+          <t>99-106989200</t>
+        </is>
+      </c>
+      <c r="M831" t="inlineStr">
+        <is>
+          <t>2026-07-07 00:00:00</t>
+        </is>
+      </c>
+      <c r="N831" t="inlineStr">
+        <is>
+          <t>2026-07-07 00:00:00</t>
+        </is>
+      </c>
+      <c r="O831" t="inlineStr">
+        <is>
+          <t>VEER PLASTIC PVT LTD</t>
+        </is>
+      </c>
+      <c r="P831" t="inlineStr">
+        <is>
+          <t>VEER PLASTIC PVT LTD</t>
+        </is>
+      </c>
+      <c r="Q831" t="inlineStr">
+        <is>
+          <t>2026-05-19 00:00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="832">
+      <c r="A832" t="inlineStr">
+        <is>
+          <t>2566335</t>
+        </is>
+      </c>
+      <c r="B832" t="inlineStr">
+        <is>
+          <t>EF4-0232734-2</t>
+        </is>
+      </c>
+      <c r="C832" t="inlineStr">
+        <is>
+          <t>Vessel, Container</t>
+        </is>
+      </c>
+      <c r="D832" t="inlineStr"/>
+      <c r="E832" t="inlineStr">
+        <is>
+          <t>9903.03.01</t>
+        </is>
+      </c>
+      <c r="F832" t="inlineStr">
+        <is>
+          <t>SECTION 122 - 10% DUTY</t>
+        </is>
+      </c>
+      <c r="G832" t="inlineStr">
+        <is>
+          <t>001</t>
+        </is>
+      </c>
+      <c r="H832" t="inlineStr">
+        <is>
+          <t>9903.03.01</t>
+        </is>
+      </c>
+      <c r="I832" t="inlineStr">
+        <is>
+          <t>3920.20.0055</t>
+        </is>
+      </c>
+      <c r="J832" t="inlineStr">
+        <is>
+          <t>TEUFELBERGER G.E.S.M.B.H</t>
+        </is>
+      </c>
+      <c r="K832" t="inlineStr">
+        <is>
+          <t>TEUSEI01</t>
+        </is>
+      </c>
+      <c r="L832" t="inlineStr">
+        <is>
+          <t>181704-13780</t>
+        </is>
+      </c>
+      <c r="M832" t="inlineStr">
+        <is>
+          <t>2026-07-07 00:00:00</t>
+        </is>
+      </c>
+      <c r="N832" t="inlineStr">
+        <is>
+          <t>2026-07-07 00:00:00</t>
+        </is>
+      </c>
+      <c r="O832" t="inlineStr">
+        <is>
+          <t>TEUFELBERGER GMBH</t>
+        </is>
+      </c>
+      <c r="P832" t="inlineStr">
+        <is>
+          <t>TEUFELBERGER GMBH</t>
+        </is>
+      </c>
+      <c r="Q832" t="inlineStr">
+        <is>
+          <t>2026-06-16 00:00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="833">
+      <c r="A833" t="inlineStr">
+        <is>
+          <t>4539551</t>
+        </is>
+      </c>
+      <c r="B833" t="inlineStr">
+        <is>
+          <t>EF4-0232798-7</t>
+        </is>
+      </c>
+      <c r="C833" t="inlineStr">
+        <is>
+          <t>Air, Non-container</t>
+        </is>
+      </c>
+      <c r="D833" t="inlineStr">
+        <is>
+          <t>02031887483</t>
+        </is>
+      </c>
+      <c r="E833" t="inlineStr">
+        <is>
+          <t>9903.03.06</t>
+        </is>
+      </c>
+      <c r="F833" t="inlineStr">
+        <is>
+          <t>S122 EXCL,IRN/STL/ALUM,DERIV</t>
+        </is>
+      </c>
+      <c r="G833" t="inlineStr">
+        <is>
+          <t>001</t>
+        </is>
+      </c>
+      <c r="H833" t="inlineStr">
+        <is>
+          <t>9903.03.06</t>
+        </is>
+      </c>
+      <c r="I833" t="inlineStr">
+        <is>
+          <t>9903.82.10,8431.39.0010</t>
+        </is>
+      </c>
+      <c r="J833" t="inlineStr">
+        <is>
+          <t>EISENMANN OF SOUTH CAROLINA INC</t>
+        </is>
+      </c>
+      <c r="K833" t="inlineStr">
+        <is>
+          <t>EISINC03</t>
+        </is>
+      </c>
+      <c r="L833" t="inlineStr">
+        <is>
+          <t>86-240963300</t>
+        </is>
+      </c>
+      <c r="M833" t="inlineStr">
+        <is>
+          <t>2026-07-03 00:00:00</t>
+        </is>
+      </c>
+      <c r="N833" t="inlineStr">
+        <is>
+          <t>2026-07-07 00:00:00</t>
+        </is>
+      </c>
+      <c r="O833" t="inlineStr">
+        <is>
+          <t>EISENMANN GMBH</t>
+        </is>
+      </c>
+      <c r="P833" t="inlineStr">
+        <is>
+          <t>EISENMANN GMBH</t>
+        </is>
+      </c>
+      <c r="Q833" t="inlineStr">
+        <is>
+          <t>2026-06-27 00:00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="834">
+      <c r="A834" t="inlineStr">
+        <is>
+          <t>4539551</t>
+        </is>
+      </c>
+      <c r="B834" t="inlineStr">
+        <is>
+          <t>EF4-0232798-7</t>
+        </is>
+      </c>
+      <c r="C834" t="inlineStr">
+        <is>
+          <t>Air, Non-container</t>
+        </is>
+      </c>
+      <c r="D834" t="inlineStr">
+        <is>
+          <t>02031887483</t>
+        </is>
+      </c>
+      <c r="E834" t="inlineStr">
+        <is>
+          <t>9903.03.06</t>
+        </is>
+      </c>
+      <c r="F834" t="inlineStr">
+        <is>
+          <t>S122 EXCL,IRN/STL/ALUM,DERIV</t>
+        </is>
+      </c>
+      <c r="G834" t="inlineStr">
+        <is>
+          <t>002</t>
+        </is>
+      </c>
+      <c r="H834" t="inlineStr">
+        <is>
+          <t>9903.03.06</t>
+        </is>
+      </c>
+      <c r="I834" t="inlineStr">
+        <is>
+          <t>9903.82.10,8431.39.0010</t>
+        </is>
+      </c>
+      <c r="J834" t="inlineStr">
+        <is>
+          <t>EISENMANN OF SOUTH CAROLINA INC</t>
+        </is>
+      </c>
+      <c r="K834" t="inlineStr">
+        <is>
+          <t>EISINC03</t>
+        </is>
+      </c>
+      <c r="L834" t="inlineStr">
+        <is>
+          <t>86-240963300</t>
+        </is>
+      </c>
+      <c r="M834" t="inlineStr">
+        <is>
+          <t>2026-07-03 00:00:00</t>
+        </is>
+      </c>
+      <c r="N834" t="inlineStr">
+        <is>
+          <t>2026-07-07 00:00:00</t>
+        </is>
+      </c>
+      <c r="O834" t="inlineStr">
+        <is>
+          <t>EISENMANN GMBH</t>
+        </is>
+      </c>
+      <c r="P834" t="inlineStr">
+        <is>
+          <t>EISENMANN GMBH</t>
+        </is>
+      </c>
+      <c r="Q834" t="inlineStr">
+        <is>
+          <t>2026-06-27 00:00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="835">
+      <c r="A835" t="inlineStr">
+        <is>
+          <t>4539551</t>
+        </is>
+      </c>
+      <c r="B835" t="inlineStr">
+        <is>
+          <t>EF4-0232798-7</t>
+        </is>
+      </c>
+      <c r="C835" t="inlineStr">
+        <is>
+          <t>Air, Non-container</t>
+        </is>
+      </c>
+      <c r="D835" t="inlineStr">
+        <is>
+          <t>02031887483</t>
+        </is>
+      </c>
+      <c r="E835" t="inlineStr">
+        <is>
+          <t>9903.03.06</t>
+        </is>
+      </c>
+      <c r="F835" t="inlineStr">
+        <is>
+          <t>S122 EXCL,IRN/STL/ALUM,DERIV</t>
+        </is>
+      </c>
+      <c r="G835" t="inlineStr">
+        <is>
+          <t>003</t>
+        </is>
+      </c>
+      <c r="H835" t="inlineStr">
+        <is>
+          <t>9903.03.06</t>
+        </is>
+      </c>
+      <c r="I835" t="inlineStr">
+        <is>
+          <t>9903.82.09,8483.10.5000</t>
+        </is>
+      </c>
+      <c r="J835" t="inlineStr">
+        <is>
+          <t>EISENMANN OF SOUTH CAROLINA INC</t>
+        </is>
+      </c>
+      <c r="K835" t="inlineStr">
+        <is>
+          <t>EISINC03</t>
+        </is>
+      </c>
+      <c r="L835" t="inlineStr">
+        <is>
+          <t>86-240963300</t>
+        </is>
+      </c>
+      <c r="M835" t="inlineStr">
+        <is>
+          <t>2026-07-03 00:00:00</t>
+        </is>
+      </c>
+      <c r="N835" t="inlineStr">
+        <is>
+          <t>2026-07-07 00:00:00</t>
+        </is>
+      </c>
+      <c r="O835" t="inlineStr">
+        <is>
+          <t>EISENMANN GMBH</t>
+        </is>
+      </c>
+      <c r="P835" t="inlineStr">
+        <is>
+          <t>EISENMANN GMBH</t>
+        </is>
+      </c>
+      <c r="Q835" t="inlineStr">
+        <is>
+          <t>2026-06-27 00:00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="836">
+      <c r="A836" t="inlineStr">
+        <is>
+          <t>4539551</t>
+        </is>
+      </c>
+      <c r="B836" t="inlineStr">
+        <is>
+          <t>EF4-0232798-7</t>
+        </is>
+      </c>
+      <c r="C836" t="inlineStr">
+        <is>
+          <t>Air, Non-container</t>
+        </is>
+      </c>
+      <c r="D836" t="inlineStr">
+        <is>
+          <t>02031887483</t>
+        </is>
+      </c>
+      <c r="E836" t="inlineStr">
+        <is>
+          <t>9903.03.06</t>
+        </is>
+      </c>
+      <c r="F836" t="inlineStr">
+        <is>
+          <t>S122 EXCL,IRN/STL/ALUM,DERIV</t>
+        </is>
+      </c>
+      <c r="G836" t="inlineStr">
+        <is>
+          <t>004</t>
+        </is>
+      </c>
+      <c r="H836" t="inlineStr">
+        <is>
+          <t>9903.03.06</t>
+        </is>
+      </c>
+      <c r="I836" t="inlineStr">
+        <is>
+          <t>9903.82.09,8483.10.5000</t>
+        </is>
+      </c>
+      <c r="J836" t="inlineStr">
+        <is>
+          <t>EISENMANN OF SOUTH CAROLINA INC</t>
+        </is>
+      </c>
+      <c r="K836" t="inlineStr">
+        <is>
+          <t>EISINC03</t>
+        </is>
+      </c>
+      <c r="L836" t="inlineStr">
+        <is>
+          <t>86-240963300</t>
+        </is>
+      </c>
+      <c r="M836" t="inlineStr">
+        <is>
+          <t>2026-07-03 00:00:00</t>
+        </is>
+      </c>
+      <c r="N836" t="inlineStr">
+        <is>
+          <t>2026-07-07 00:00:00</t>
+        </is>
+      </c>
+      <c r="O836" t="inlineStr">
+        <is>
+          <t>EISENMANN GMBH</t>
+        </is>
+      </c>
+      <c r="P836" t="inlineStr">
+        <is>
+          <t>EISENMANN GMBH</t>
+        </is>
+      </c>
+      <c r="Q836" t="inlineStr">
+        <is>
+          <t>2026-06-27 00:00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="837">
+      <c r="A837" t="inlineStr">
+        <is>
+          <t>4539551</t>
+        </is>
+      </c>
+      <c r="B837" t="inlineStr">
+        <is>
+          <t>EF4-0232798-7</t>
+        </is>
+      </c>
+      <c r="C837" t="inlineStr">
+        <is>
+          <t>Air, Non-container</t>
+        </is>
+      </c>
+      <c r="D837" t="inlineStr">
+        <is>
+          <t>02031887483</t>
+        </is>
+      </c>
+      <c r="E837" t="inlineStr">
+        <is>
+          <t>9903.03.06</t>
+        </is>
+      </c>
+      <c r="F837" t="inlineStr">
+        <is>
+          <t>S122 EXCL,IRN/STL/ALUM,DERIV</t>
+        </is>
+      </c>
+      <c r="G837" t="inlineStr">
+        <is>
+          <t>005</t>
+        </is>
+      </c>
+      <c r="H837" t="inlineStr">
+        <is>
+          <t>9903.03.06</t>
+        </is>
+      </c>
+      <c r="I837" t="inlineStr">
+        <is>
+          <t>9903.82.09,8483.10.5000</t>
+        </is>
+      </c>
+      <c r="J837" t="inlineStr">
+        <is>
+          <t>EISENMANN OF SOUTH CAROLINA INC</t>
+        </is>
+      </c>
+      <c r="K837" t="inlineStr">
+        <is>
+          <t>EISINC03</t>
+        </is>
+      </c>
+      <c r="L837" t="inlineStr">
+        <is>
+          <t>86-240963300</t>
+        </is>
+      </c>
+      <c r="M837" t="inlineStr">
+        <is>
+          <t>2026-07-03 00:00:00</t>
+        </is>
+      </c>
+      <c r="N837" t="inlineStr">
+        <is>
+          <t>2026-07-07 00:00:00</t>
+        </is>
+      </c>
+      <c r="O837" t="inlineStr">
+        <is>
+          <t>EISENMANN GMBH</t>
+        </is>
+      </c>
+      <c r="P837" t="inlineStr">
+        <is>
+          <t>EISENMANN GMBH</t>
+        </is>
+      </c>
+      <c r="Q837" t="inlineStr">
+        <is>
+          <t>2026-06-27 00:00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="838">
+      <c r="A838" t="inlineStr">
+        <is>
+          <t>4539551</t>
+        </is>
+      </c>
+      <c r="B838" t="inlineStr">
+        <is>
+          <t>EF4-0232798-7</t>
+        </is>
+      </c>
+      <c r="C838" t="inlineStr">
+        <is>
+          <t>Air, Non-container</t>
+        </is>
+      </c>
+      <c r="D838" t="inlineStr">
+        <is>
+          <t>02031887483</t>
+        </is>
+      </c>
+      <c r="E838" t="inlineStr">
+        <is>
+          <t>9903.03.06</t>
+        </is>
+      </c>
+      <c r="F838" t="inlineStr">
+        <is>
+          <t>S122 EXCL,IRN/STL/ALUM,DERIV</t>
+        </is>
+      </c>
+      <c r="G838" t="inlineStr">
+        <is>
+          <t>006</t>
+        </is>
+      </c>
+      <c r="H838" t="inlineStr">
+        <is>
+          <t>9903.03.06</t>
+        </is>
+      </c>
+      <c r="I838" t="inlineStr">
+        <is>
+          <t>9903.82.10,8431.39.0010</t>
+        </is>
+      </c>
+      <c r="J838" t="inlineStr">
+        <is>
+          <t>EISENMANN OF SOUTH CAROLINA INC</t>
+        </is>
+      </c>
+      <c r="K838" t="inlineStr">
+        <is>
+          <t>EISINC03</t>
+        </is>
+      </c>
+      <c r="L838" t="inlineStr">
+        <is>
+          <t>86-240963300</t>
+        </is>
+      </c>
+      <c r="M838" t="inlineStr">
+        <is>
+          <t>2026-07-03 00:00:00</t>
+        </is>
+      </c>
+      <c r="N838" t="inlineStr">
+        <is>
+          <t>2026-07-07 00:00:00</t>
+        </is>
+      </c>
+      <c r="O838" t="inlineStr">
+        <is>
+          <t>EISENMANN GMBH</t>
+        </is>
+      </c>
+      <c r="P838" t="inlineStr">
+        <is>
+          <t>EISENMANN GMBH</t>
+        </is>
+      </c>
+      <c r="Q838" t="inlineStr">
+        <is>
+          <t>2026-06-27 00:00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="839">
+      <c r="A839" t="inlineStr">
+        <is>
+          <t>4539551</t>
+        </is>
+      </c>
+      <c r="B839" t="inlineStr">
+        <is>
+          <t>EF4-0232798-7</t>
+        </is>
+      </c>
+      <c r="C839" t="inlineStr">
+        <is>
+          <t>Air, Non-container</t>
+        </is>
+      </c>
+      <c r="D839" t="inlineStr">
+        <is>
+          <t>02031887483</t>
+        </is>
+      </c>
+      <c r="E839" t="inlineStr">
+        <is>
+          <t>9903.03.06</t>
+        </is>
+      </c>
+      <c r="F839" t="inlineStr">
+        <is>
+          <t>S122 EXCL,IRN/STL/ALUM,DERIV</t>
+        </is>
+      </c>
+      <c r="G839" t="inlineStr">
+        <is>
+          <t>007</t>
+        </is>
+      </c>
+      <c r="H839" t="inlineStr">
+        <is>
+          <t>9903.03.06</t>
+        </is>
+      </c>
+      <c r="I839" t="inlineStr">
+        <is>
+          <t>9903.82.10,8431.39.0010</t>
+        </is>
+      </c>
+      <c r="J839" t="inlineStr">
+        <is>
+          <t>EISENMANN OF SOUTH CAROLINA INC</t>
+        </is>
+      </c>
+      <c r="K839" t="inlineStr">
+        <is>
+          <t>EISINC03</t>
+        </is>
+      </c>
+      <c r="L839" t="inlineStr">
+        <is>
+          <t>86-240963300</t>
+        </is>
+      </c>
+      <c r="M839" t="inlineStr">
+        <is>
+          <t>2026-07-03 00:00:00</t>
+        </is>
+      </c>
+      <c r="N839" t="inlineStr">
+        <is>
+          <t>2026-07-07 00:00:00</t>
+        </is>
+      </c>
+      <c r="O839" t="inlineStr">
+        <is>
+          <t>EISENMANN GMBH</t>
+        </is>
+      </c>
+      <c r="P839" t="inlineStr">
+        <is>
+          <t>EISENMANN GMBH</t>
+        </is>
+      </c>
+      <c r="Q839" t="inlineStr">
+        <is>
+          <t>2026-06-27 00:00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="840">
+      <c r="A840" t="inlineStr">
+        <is>
+          <t>4539551</t>
+        </is>
+      </c>
+      <c r="B840" t="inlineStr">
+        <is>
+          <t>EF4-0232798-7</t>
+        </is>
+      </c>
+      <c r="C840" t="inlineStr">
+        <is>
+          <t>Air, Non-container</t>
+        </is>
+      </c>
+      <c r="D840" t="inlineStr">
+        <is>
+          <t>02031887483</t>
+        </is>
+      </c>
+      <c r="E840" t="inlineStr">
+        <is>
+          <t>9903.03.01</t>
+        </is>
+      </c>
+      <c r="F840" t="inlineStr">
+        <is>
+          <t>SECTION 122 - 10% DUTY</t>
+        </is>
+      </c>
+      <c r="G840" t="inlineStr">
+        <is>
+          <t>008</t>
+        </is>
+      </c>
+      <c r="H840" t="inlineStr">
+        <is>
+          <t>9903.03.01</t>
+        </is>
+      </c>
+      <c r="I840" t="inlineStr">
+        <is>
+          <t>9903.82.01,8483.30.8040</t>
+        </is>
+      </c>
+      <c r="J840" t="inlineStr">
+        <is>
+          <t>EISENMANN OF SOUTH CAROLINA INC</t>
+        </is>
+      </c>
+      <c r="K840" t="inlineStr">
+        <is>
+          <t>EISINC03</t>
+        </is>
+      </c>
+      <c r="L840" t="inlineStr">
+        <is>
+          <t>86-240963300</t>
+        </is>
+      </c>
+      <c r="M840" t="inlineStr">
+        <is>
+          <t>2026-07-03 00:00:00</t>
+        </is>
+      </c>
+      <c r="N840" t="inlineStr">
+        <is>
+          <t>2026-07-07 00:00:00</t>
+        </is>
+      </c>
+      <c r="O840" t="inlineStr">
+        <is>
+          <t>EISENMANN GMBH</t>
+        </is>
+      </c>
+      <c r="P840" t="inlineStr">
+        <is>
+          <t>EISENMANN GMBH</t>
+        </is>
+      </c>
+      <c r="Q840" t="inlineStr">
+        <is>
+          <t>2026-06-27 00:00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="841">
+      <c r="A841" t="inlineStr">
+        <is>
+          <t>4539551</t>
+        </is>
+      </c>
+      <c r="B841" t="inlineStr">
+        <is>
+          <t>EF4-0232798-7</t>
+        </is>
+      </c>
+      <c r="C841" t="inlineStr">
+        <is>
+          <t>Air, Non-container</t>
+        </is>
+      </c>
+      <c r="D841" t="inlineStr">
+        <is>
+          <t>02031887483</t>
+        </is>
+      </c>
+      <c r="E841" t="inlineStr">
+        <is>
+          <t>9903.03.06</t>
+        </is>
+      </c>
+      <c r="F841" t="inlineStr">
+        <is>
+          <t>S122 EXCL,IRN/STL/ALUM,DERIV</t>
+        </is>
+      </c>
+      <c r="G841" t="inlineStr">
+        <is>
+          <t>009</t>
+        </is>
+      </c>
+      <c r="H841" t="inlineStr">
+        <is>
+          <t>9903.03.06</t>
+        </is>
+      </c>
+      <c r="I841" t="inlineStr">
+        <is>
+          <t>9903.82.10,8431.39.0010</t>
+        </is>
+      </c>
+      <c r="J841" t="inlineStr">
+        <is>
+          <t>EISENMANN OF SOUTH CAROLINA INC</t>
+        </is>
+      </c>
+      <c r="K841" t="inlineStr">
+        <is>
+          <t>EISINC03</t>
+        </is>
+      </c>
+      <c r="L841" t="inlineStr">
+        <is>
+          <t>86-240963300</t>
+        </is>
+      </c>
+      <c r="M841" t="inlineStr">
+        <is>
+          <t>2026-07-03 00:00:00</t>
+        </is>
+      </c>
+      <c r="N841" t="inlineStr">
+        <is>
+          <t>2026-07-07 00:00:00</t>
+        </is>
+      </c>
+      <c r="O841" t="inlineStr">
+        <is>
+          <t>EISENMANN GMBH</t>
+        </is>
+      </c>
+      <c r="P841" t="inlineStr">
+        <is>
+          <t>EISENMANN GMBH</t>
+        </is>
+      </c>
+      <c r="Q841" t="inlineStr">
+        <is>
+          <t>2026-06-27 00:00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="842">
+      <c r="A842" t="inlineStr">
+        <is>
+          <t>4539551</t>
+        </is>
+      </c>
+      <c r="B842" t="inlineStr">
+        <is>
+          <t>EF4-0232798-7</t>
+        </is>
+      </c>
+      <c r="C842" t="inlineStr">
+        <is>
+          <t>Air, Non-container</t>
+        </is>
+      </c>
+      <c r="D842" t="inlineStr">
+        <is>
+          <t>02031887483</t>
+        </is>
+      </c>
+      <c r="E842" t="inlineStr">
+        <is>
+          <t>9903.03.01</t>
+        </is>
+      </c>
+      <c r="F842" t="inlineStr">
+        <is>
+          <t>SECTION 122 - 10% DUTY</t>
+        </is>
+      </c>
+      <c r="G842" t="inlineStr">
+        <is>
+          <t>010</t>
+        </is>
+      </c>
+      <c r="H842" t="inlineStr">
+        <is>
+          <t>9903.03.01</t>
+        </is>
+      </c>
+      <c r="I842" t="inlineStr">
+        <is>
+          <t>8481.80.3075</t>
+        </is>
+      </c>
+      <c r="J842" t="inlineStr">
+        <is>
+          <t>EISENMANN OF SOUTH CAROLINA INC</t>
+        </is>
+      </c>
+      <c r="K842" t="inlineStr">
+        <is>
+          <t>EISINC03</t>
+        </is>
+      </c>
+      <c r="L842" t="inlineStr">
+        <is>
+          <t>86-240963300</t>
+        </is>
+      </c>
+      <c r="M842" t="inlineStr">
+        <is>
+          <t>2026-07-03 00:00:00</t>
+        </is>
+      </c>
+      <c r="N842" t="inlineStr">
+        <is>
+          <t>2026-07-07 00:00:00</t>
+        </is>
+      </c>
+      <c r="O842" t="inlineStr">
+        <is>
+          <t>EISENMANN GMBH</t>
+        </is>
+      </c>
+      <c r="P842" t="inlineStr">
+        <is>
+          <t>EISENMANN GMBH</t>
+        </is>
+      </c>
+      <c r="Q842" t="inlineStr">
+        <is>
+          <t>2026-06-27 00:00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="843">
+      <c r="A843" t="inlineStr">
+        <is>
+          <t>4539551</t>
+        </is>
+      </c>
+      <c r="B843" t="inlineStr">
+        <is>
+          <t>EF4-0232798-7</t>
+        </is>
+      </c>
+      <c r="C843" t="inlineStr">
+        <is>
+          <t>Air, Non-container</t>
+        </is>
+      </c>
+      <c r="D843" t="inlineStr">
+        <is>
+          <t>02031887483</t>
+        </is>
+      </c>
+      <c r="E843" t="inlineStr">
+        <is>
+          <t>9903.03.01</t>
+        </is>
+      </c>
+      <c r="F843" t="inlineStr">
+        <is>
+          <t>SECTION 122 - 10% DUTY</t>
+        </is>
+      </c>
+      <c r="G843" t="inlineStr">
+        <is>
+          <t>011</t>
+        </is>
+      </c>
+      <c r="H843" t="inlineStr">
+        <is>
+          <t>9903.03.01</t>
+        </is>
+      </c>
+      <c r="I843" t="inlineStr">
+        <is>
+          <t>8481.80.3075</t>
+        </is>
+      </c>
+      <c r="J843" t="inlineStr">
+        <is>
+          <t>EISENMANN OF SOUTH CAROLINA INC</t>
+        </is>
+      </c>
+      <c r="K843" t="inlineStr">
+        <is>
+          <t>EISINC03</t>
+        </is>
+      </c>
+      <c r="L843" t="inlineStr">
+        <is>
+          <t>86-240963300</t>
+        </is>
+      </c>
+      <c r="M843" t="inlineStr">
+        <is>
+          <t>2026-07-03 00:00:00</t>
+        </is>
+      </c>
+      <c r="N843" t="inlineStr">
+        <is>
+          <t>2026-07-07 00:00:00</t>
+        </is>
+      </c>
+      <c r="O843" t="inlineStr">
+        <is>
+          <t>EISENMANN GMBH</t>
+        </is>
+      </c>
+      <c r="P843" t="inlineStr">
+        <is>
+          <t>EISENMANN GMBH</t>
+        </is>
+      </c>
+      <c r="Q843" t="inlineStr">
+        <is>
+          <t>2026-06-27 00:00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="844">
+      <c r="A844" t="inlineStr">
+        <is>
+          <t>4539551</t>
+        </is>
+      </c>
+      <c r="B844" t="inlineStr">
+        <is>
+          <t>EF4-0232798-7</t>
+        </is>
+      </c>
+      <c r="C844" t="inlineStr">
+        <is>
+          <t>Air, Non-container</t>
+        </is>
+      </c>
+      <c r="D844" t="inlineStr">
+        <is>
+          <t>02031887483</t>
+        </is>
+      </c>
+      <c r="E844" t="inlineStr">
+        <is>
+          <t>9903.03.06</t>
+        </is>
+      </c>
+      <c r="F844" t="inlineStr">
+        <is>
+          <t>S122 EXCL,IRN/STL/ALUM,DERIV</t>
+        </is>
+      </c>
+      <c r="G844" t="inlineStr">
+        <is>
+          <t>012</t>
+        </is>
+      </c>
+      <c r="H844" t="inlineStr">
+        <is>
+          <t>9903.03.06</t>
+        </is>
+      </c>
+      <c r="I844" t="inlineStr">
+        <is>
+          <t>9903.82.10,8431.39.0010</t>
+        </is>
+      </c>
+      <c r="J844" t="inlineStr">
+        <is>
+          <t>EISENMANN OF SOUTH CAROLINA INC</t>
+        </is>
+      </c>
+      <c r="K844" t="inlineStr">
+        <is>
+          <t>EISINC03</t>
+        </is>
+      </c>
+      <c r="L844" t="inlineStr">
+        <is>
+          <t>86-240963300</t>
+        </is>
+      </c>
+      <c r="M844" t="inlineStr">
+        <is>
+          <t>2026-07-03 00:00:00</t>
+        </is>
+      </c>
+      <c r="N844" t="inlineStr">
+        <is>
+          <t>2026-07-07 00:00:00</t>
+        </is>
+      </c>
+      <c r="O844" t="inlineStr">
+        <is>
+          <t>EISENMANN GMBH</t>
+        </is>
+      </c>
+      <c r="P844" t="inlineStr">
+        <is>
+          <t>EISENMANN GMBH</t>
+        </is>
+      </c>
+      <c r="Q844" t="inlineStr">
+        <is>
+          <t>2026-06-27 00:00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="845">
+      <c r="A845" t="inlineStr">
+        <is>
+          <t>4539551</t>
+        </is>
+      </c>
+      <c r="B845" t="inlineStr">
+        <is>
+          <t>EF4-0232798-7</t>
+        </is>
+      </c>
+      <c r="C845" t="inlineStr">
+        <is>
+          <t>Air, Non-container</t>
+        </is>
+      </c>
+      <c r="D845" t="inlineStr">
+        <is>
+          <t>02031887483</t>
+        </is>
+      </c>
+      <c r="E845" t="inlineStr">
+        <is>
+          <t>9903.03.06</t>
+        </is>
+      </c>
+      <c r="F845" t="inlineStr">
+        <is>
+          <t>S122 EXCL,IRN/STL/ALUM,DERIV</t>
+        </is>
+      </c>
+      <c r="G845" t="inlineStr">
+        <is>
+          <t>013</t>
+        </is>
+      </c>
+      <c r="H845" t="inlineStr">
+        <is>
+          <t>9903.03.06</t>
+        </is>
+      </c>
+      <c r="I845" t="inlineStr">
+        <is>
+          <t>9903.82.10,8431.39.0010</t>
+        </is>
+      </c>
+      <c r="J845" t="inlineStr">
+        <is>
+          <t>EISENMANN OF SOUTH CAROLINA INC</t>
+        </is>
+      </c>
+      <c r="K845" t="inlineStr">
+        <is>
+          <t>EISINC03</t>
+        </is>
+      </c>
+      <c r="L845" t="inlineStr">
+        <is>
+          <t>86-240963300</t>
+        </is>
+      </c>
+      <c r="M845" t="inlineStr">
+        <is>
+          <t>2026-07-03 00:00:00</t>
+        </is>
+      </c>
+      <c r="N845" t="inlineStr">
+        <is>
+          <t>2026-07-07 00:00:00</t>
+        </is>
+      </c>
+      <c r="O845" t="inlineStr">
+        <is>
+          <t>EISENMANN GMBH</t>
+        </is>
+      </c>
+      <c r="P845" t="inlineStr">
+        <is>
+          <t>EISENMANN GMBH</t>
+        </is>
+      </c>
+      <c r="Q845" t="inlineStr">
+        <is>
+          <t>2026-06-27 00:00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="846">
+      <c r="A846" t="inlineStr">
+        <is>
+          <t>4539551</t>
+        </is>
+      </c>
+      <c r="B846" t="inlineStr">
+        <is>
+          <t>EF4-0232798-7</t>
+        </is>
+      </c>
+      <c r="C846" t="inlineStr">
+        <is>
+          <t>Air, Non-container</t>
+        </is>
+      </c>
+      <c r="D846" t="inlineStr">
+        <is>
+          <t>02031887483</t>
+        </is>
+      </c>
+      <c r="E846" t="inlineStr">
+        <is>
+          <t>9903.03.06</t>
+        </is>
+      </c>
+      <c r="F846" t="inlineStr">
+        <is>
+          <t>S122 EXCL,IRN/STL/ALUM,DERIV</t>
+        </is>
+      </c>
+      <c r="G846" t="inlineStr">
+        <is>
+          <t>014</t>
+        </is>
+      </c>
+      <c r="H846" t="inlineStr">
+        <is>
+          <t>9903.03.06</t>
+        </is>
+      </c>
+      <c r="I846" t="inlineStr">
+        <is>
+          <t>9903.82.10,8431.39.0010</t>
+        </is>
+      </c>
+      <c r="J846" t="inlineStr">
+        <is>
+          <t>EISENMANN OF SOUTH CAROLINA INC</t>
+        </is>
+      </c>
+      <c r="K846" t="inlineStr">
+        <is>
+          <t>EISINC03</t>
+        </is>
+      </c>
+      <c r="L846" t="inlineStr">
+        <is>
+          <t>86-240963300</t>
+        </is>
+      </c>
+      <c r="M846" t="inlineStr">
+        <is>
+          <t>2026-07-03 00:00:00</t>
+        </is>
+      </c>
+      <c r="N846" t="inlineStr">
+        <is>
+          <t>2026-07-07 00:00:00</t>
+        </is>
+      </c>
+      <c r="O846" t="inlineStr">
+        <is>
+          <t>EISENMANN GMBH</t>
+        </is>
+      </c>
+      <c r="P846" t="inlineStr">
+        <is>
+          <t>EISENMANN GMBH</t>
+        </is>
+      </c>
+      <c r="Q846" t="inlineStr">
+        <is>
+          <t>2026-06-27 00:00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="847">
+      <c r="A847" t="inlineStr">
+        <is>
+          <t>4539551</t>
+        </is>
+      </c>
+      <c r="B847" t="inlineStr">
+        <is>
+          <t>EF4-0232798-7</t>
+        </is>
+      </c>
+      <c r="C847" t="inlineStr">
+        <is>
+          <t>Air, Non-container</t>
+        </is>
+      </c>
+      <c r="D847" t="inlineStr">
+        <is>
+          <t>02031887483</t>
+        </is>
+      </c>
+      <c r="E847" t="inlineStr">
+        <is>
+          <t>9903.03.06</t>
+        </is>
+      </c>
+      <c r="F847" t="inlineStr">
+        <is>
+          <t>S122 EXCL,IRN/STL/ALUM,DERIV</t>
+        </is>
+      </c>
+      <c r="G847" t="inlineStr">
+        <is>
+          <t>015</t>
+        </is>
+      </c>
+      <c r="H847" t="inlineStr">
+        <is>
+          <t>9903.03.06</t>
+        </is>
+      </c>
+      <c r="I847" t="inlineStr">
+        <is>
+          <t>9903.82.10,8431.39.0010</t>
+        </is>
+      </c>
+      <c r="J847" t="inlineStr">
+        <is>
+          <t>EISENMANN OF SOUTH CAROLINA INC</t>
+        </is>
+      </c>
+      <c r="K847" t="inlineStr">
+        <is>
+          <t>EISINC03</t>
+        </is>
+      </c>
+      <c r="L847" t="inlineStr">
+        <is>
+          <t>86-240963300</t>
+        </is>
+      </c>
+      <c r="M847" t="inlineStr">
+        <is>
+          <t>2026-07-03 00:00:00</t>
+        </is>
+      </c>
+      <c r="N847" t="inlineStr">
+        <is>
+          <t>2026-07-07 00:00:00</t>
+        </is>
+      </c>
+      <c r="O847" t="inlineStr">
+        <is>
+          <t>EISENMANN GMBH</t>
+        </is>
+      </c>
+      <c r="P847" t="inlineStr">
+        <is>
+          <t>EISENMANN GMBH</t>
+        </is>
+      </c>
+      <c r="Q847" t="inlineStr">
+        <is>
+          <t>2026-06-27 00:00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="848">
+      <c r="A848" t="inlineStr">
+        <is>
+          <t>4539551</t>
+        </is>
+      </c>
+      <c r="B848" t="inlineStr">
+        <is>
+          <t>EF4-0232798-7</t>
+        </is>
+      </c>
+      <c r="C848" t="inlineStr">
+        <is>
+          <t>Air, Non-container</t>
+        </is>
+      </c>
+      <c r="D848" t="inlineStr">
+        <is>
+          <t>02031887483</t>
+        </is>
+      </c>
+      <c r="E848" t="inlineStr">
+        <is>
+          <t>9903.03.06</t>
+        </is>
+      </c>
+      <c r="F848" t="inlineStr">
+        <is>
+          <t>S122 EXCL,IRN/STL/ALUM,DERIV</t>
+        </is>
+      </c>
+      <c r="G848" t="inlineStr">
+        <is>
+          <t>016</t>
+        </is>
+      </c>
+      <c r="H848" t="inlineStr">
+        <is>
+          <t>9903.03.06</t>
+        </is>
+      </c>
+      <c r="I848" t="inlineStr">
+        <is>
+          <t>9903.82.10,8431.39.0010</t>
+        </is>
+      </c>
+      <c r="J848" t="inlineStr">
+        <is>
+          <t>EISENMANN OF SOUTH CAROLINA INC</t>
+        </is>
+      </c>
+      <c r="K848" t="inlineStr">
+        <is>
+          <t>EISINC03</t>
+        </is>
+      </c>
+      <c r="L848" t="inlineStr">
+        <is>
+          <t>86-240963300</t>
+        </is>
+      </c>
+      <c r="M848" t="inlineStr">
+        <is>
+          <t>2026-07-03 00:00:00</t>
+        </is>
+      </c>
+      <c r="N848" t="inlineStr">
+        <is>
+          <t>2026-07-07 00:00:00</t>
+        </is>
+      </c>
+      <c r="O848" t="inlineStr">
+        <is>
+          <t>EISENMANN GMBH</t>
+        </is>
+      </c>
+      <c r="P848" t="inlineStr">
+        <is>
+          <t>EISENMANN GMBH</t>
+        </is>
+      </c>
+      <c r="Q848" t="inlineStr">
+        <is>
+          <t>2026-06-27 00:00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="849">
+      <c r="A849" t="inlineStr">
+        <is>
+          <t>4539551</t>
+        </is>
+      </c>
+      <c r="B849" t="inlineStr">
+        <is>
+          <t>EF4-0232798-7</t>
+        </is>
+      </c>
+      <c r="C849" t="inlineStr">
+        <is>
+          <t>Air, Non-container</t>
+        </is>
+      </c>
+      <c r="D849" t="inlineStr">
+        <is>
+          <t>02031887483</t>
+        </is>
+      </c>
+      <c r="E849" t="inlineStr">
+        <is>
+          <t>9903.03.06</t>
+        </is>
+      </c>
+      <c r="F849" t="inlineStr">
+        <is>
+          <t>S122 EXCL,IRN/STL/ALUM,DERIV</t>
+        </is>
+      </c>
+      <c r="G849" t="inlineStr">
+        <is>
+          <t>017</t>
+        </is>
+      </c>
+      <c r="H849" t="inlineStr">
+        <is>
+          <t>9903.03.06</t>
+        </is>
+      </c>
+      <c r="I849" t="inlineStr">
+        <is>
+          <t>9903.82.10,8431.39.0010</t>
+        </is>
+      </c>
+      <c r="J849" t="inlineStr">
+        <is>
+          <t>EISENMANN OF SOUTH CAROLINA INC</t>
+        </is>
+      </c>
+      <c r="K849" t="inlineStr">
+        <is>
+          <t>EISINC03</t>
+        </is>
+      </c>
+      <c r="L849" t="inlineStr">
+        <is>
+          <t>86-240963300</t>
+        </is>
+      </c>
+      <c r="M849" t="inlineStr">
+        <is>
+          <t>2026-07-03 00:00:00</t>
+        </is>
+      </c>
+      <c r="N849" t="inlineStr">
+        <is>
+          <t>2026-07-07 00:00:00</t>
+        </is>
+      </c>
+      <c r="O849" t="inlineStr">
+        <is>
+          <t>EISENMANN GMBH</t>
+        </is>
+      </c>
+      <c r="P849" t="inlineStr">
+        <is>
+          <t>EISENMANN GMBH</t>
+        </is>
+      </c>
+      <c r="Q849" t="inlineStr">
+        <is>
+          <t>2026-06-27 00:00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="850">
+      <c r="A850" t="inlineStr">
+        <is>
+          <t>4539551</t>
+        </is>
+      </c>
+      <c r="B850" t="inlineStr">
+        <is>
+          <t>EF4-0232798-7</t>
+        </is>
+      </c>
+      <c r="C850" t="inlineStr">
+        <is>
+          <t>Air, Non-container</t>
+        </is>
+      </c>
+      <c r="D850" t="inlineStr">
+        <is>
+          <t>02031887483</t>
+        </is>
+      </c>
+      <c r="E850" t="inlineStr">
+        <is>
+          <t>9903.03.06</t>
+        </is>
+      </c>
+      <c r="F850" t="inlineStr">
+        <is>
+          <t>S122 EXCL,IRN/STL/ALUM,DERIV</t>
+        </is>
+      </c>
+      <c r="G850" t="inlineStr">
+        <is>
+          <t>018</t>
+        </is>
+      </c>
+      <c r="H850" t="inlineStr">
+        <is>
+          <t>9903.03.06</t>
+        </is>
+      </c>
+      <c r="I850" t="inlineStr">
+        <is>
+          <t>9903.82.10,8431.39.0010</t>
+        </is>
+      </c>
+      <c r="J850" t="inlineStr">
+        <is>
+          <t>EISENMANN OF SOUTH CAROLINA INC</t>
+        </is>
+      </c>
+      <c r="K850" t="inlineStr">
+        <is>
+          <t>EISINC03</t>
+        </is>
+      </c>
+      <c r="L850" t="inlineStr">
+      